--- a/jogos_2026-05-10.xlsx
+++ b/jogos_2026-05-10.xlsx
@@ -364,12 +364,12 @@
     <t>Australia New South Wales NPL</t>
   </si>
   <si>
+    <t>South Korea K League 1</t>
+  </si>
+  <si>
     <t>South Korea K League 2</t>
   </si>
   <si>
-    <t>South Korea K League 1</t>
-  </si>
-  <si>
     <t>China China League One</t>
   </si>
   <si>
@@ -388,114 +388,114 @@
     <t>Russia Russian Premier League</t>
   </si>
   <si>
+    <t>Spain Primera Division Women</t>
+  </si>
+  <si>
+    <t>Poland 1. Liga</t>
+  </si>
+  <si>
     <t>Vietnam V.League 1</t>
   </si>
   <si>
+    <t>Portugal Liga 3</t>
+  </si>
+  <si>
     <t>Ethiopia Ethiopia Premier League</t>
   </si>
   <si>
     <t>Kazakhstan Kazakhstan Premier League</t>
   </si>
   <si>
-    <t>Spain Primera Division Women</t>
-  </si>
-  <si>
-    <t>Poland 1. Liga</t>
-  </si>
-  <si>
-    <t>Portugal Liga 3</t>
-  </si>
-  <si>
     <t>Poland Ekstraklasa</t>
   </si>
   <si>
     <t>Italy Serie A</t>
   </si>
   <si>
+    <t>Sweden Damallsvenskan</t>
+  </si>
+  <si>
+    <t>Thailand Thai League T1</t>
+  </si>
+  <si>
     <t>Scotland Premiership</t>
   </si>
   <si>
-    <t>Thailand Thai League T1</t>
-  </si>
-  <si>
-    <t>Sweden Damallsvenskan</t>
-  </si>
-  <si>
     <t>Lithuania A Lyga</t>
   </si>
   <si>
     <t>Bulgaria First League</t>
   </si>
   <si>
+    <t>Singapore S.League</t>
+  </si>
+  <si>
+    <t>India Indian Super League</t>
+  </si>
+  <si>
+    <t>Germany 2. Bundesliga</t>
+  </si>
+  <si>
     <t>Belgium Pro League</t>
   </si>
   <si>
-    <t>Singapore S.League</t>
-  </si>
-  <si>
-    <t>India Indian Super League</t>
-  </si>
-  <si>
     <t>Estonia Meistriliiga</t>
   </si>
   <si>
     <t>Germany 3. Liga</t>
   </si>
   <si>
-    <t>Germany 2. Bundesliga</t>
-  </si>
-  <si>
     <t>Croatia Druga HNL</t>
   </si>
   <si>
     <t>Sweden Allsvenskan</t>
   </si>
   <si>
+    <t>Georgia Erovnuli Liga</t>
+  </si>
+  <si>
+    <t>Spain La Liga</t>
+  </si>
+  <si>
+    <t>Denmark Superliga</t>
+  </si>
+  <si>
+    <t>Spain Segunda División</t>
+  </si>
+  <si>
     <t>Switzerland Super League</t>
   </si>
   <si>
-    <t>Spain Segunda División</t>
-  </si>
-  <si>
-    <t>Georgia Erovnuli Liga</t>
-  </si>
-  <si>
-    <t>Spain La Liga</t>
-  </si>
-  <si>
-    <t>Denmark Superliga</t>
-  </si>
-  <si>
     <t>Malaysia Super League</t>
   </si>
   <si>
     <t>Norway Eliteserien</t>
   </si>
   <si>
+    <t>England Premier League</t>
+  </si>
+  <si>
+    <t>Slovenia PrvaLiga</t>
+  </si>
+  <si>
+    <t>Czech Republic First League</t>
+  </si>
+  <si>
     <t>Romania Liga I</t>
   </si>
   <si>
     <t>Azerbaijan Premyer Liqası</t>
   </si>
   <si>
-    <t>Czech Republic First League</t>
-  </si>
-  <si>
-    <t>England Premier League</t>
-  </si>
-  <si>
-    <t>Slovenia PrvaLiga</t>
-  </si>
-  <si>
     <t>Germany Bundesliga</t>
   </si>
   <si>
+    <t>Greece Super League</t>
+  </si>
+  <si>
     <t>Faroe Islands Faroe Islands Premier League</t>
   </si>
   <si>
-    <t>Greece Super League</t>
-  </si>
-  <si>
     <t>Croatia Prva HNL</t>
   </si>
   <si>
@@ -505,18 +505,18 @@
     <t>Netherlands Eredivisie</t>
   </si>
   <si>
+    <t>FYR Macedonia First Football League</t>
+  </si>
+  <si>
+    <t>Norway First Division</t>
+  </si>
+  <si>
+    <t>Cyprus First Division</t>
+  </si>
+  <si>
     <t>Austria Bundesliga</t>
   </si>
   <si>
-    <t>FYR Macedonia First Football League</t>
-  </si>
-  <si>
-    <t>Cyprus First Division</t>
-  </si>
-  <si>
-    <t>Norway First Division</t>
-  </si>
-  <si>
     <t>UAE Arabian Gulf League</t>
   </si>
   <si>
@@ -535,12 +535,12 @@
     <t>Serbia SuperLiga</t>
   </si>
   <si>
+    <t>USA NWSL</t>
+  </si>
+  <si>
     <t>Chile Primera B</t>
   </si>
   <si>
-    <t>USA NWSL</t>
-  </si>
-  <si>
     <t>Israel Israeli Premier League</t>
   </si>
   <si>
@@ -556,18 +556,18 @@
     <t>Argentina Prim B Nacional</t>
   </si>
   <si>
+    <t>Brazil Serie A</t>
+  </si>
+  <si>
     <t>France Ligue 1</t>
   </si>
   <si>
-    <t>Brazil Serie A</t>
+    <t>Brazil Serie B</t>
   </si>
   <si>
     <t>Bolivia LFPB</t>
   </si>
   <si>
-    <t>Brazil Serie B</t>
-  </si>
-  <si>
     <t>USA MLS</t>
   </si>
   <si>
@@ -580,225 +580,225 @@
     <t>2025</t>
   </si>
   <si>
+    <t>Rockdale City Suns</t>
+  </si>
+  <si>
+    <t>Ulsan</t>
+  </si>
+  <si>
+    <t>Seongnam</t>
+  </si>
+  <si>
     <t>Blacktown City</t>
   </si>
   <si>
-    <t>Rockdale City Suns</t>
-  </si>
-  <si>
-    <t>Seongnam</t>
-  </si>
-  <si>
-    <t>Ulsan</t>
-  </si>
-  <si>
     <t>APIA Leichhardt Tigers</t>
   </si>
   <si>
+    <t>Yanbian Longding</t>
+  </si>
+  <si>
+    <t>Shaanxi Union</t>
+  </si>
+  <si>
     <t>Dalian Huayi</t>
   </si>
   <si>
-    <t>Shaanxi Union</t>
-  </si>
-  <si>
-    <t>Yanbian Longding</t>
-  </si>
-  <si>
     <t>Ufa</t>
   </si>
   <si>
+    <t>Ansan Greeners</t>
+  </si>
+  <si>
     <t>Busan I'Park</t>
   </si>
   <si>
-    <t>Ansan Greeners</t>
-  </si>
-  <si>
     <t>Anyang</t>
   </si>
   <si>
+    <t>Slavia Praha U21</t>
+  </si>
+  <si>
     <t>Viktoria Žižkov</t>
   </si>
   <si>
-    <t>Slavia Praha U21</t>
+    <t>Persija</t>
   </si>
   <si>
     <t>Persita</t>
   </si>
   <si>
-    <t>Persija</t>
-  </si>
-  <si>
     <t>Qingdao Youth Island</t>
   </si>
   <si>
     <t>Orenburg</t>
   </si>
   <si>
+    <t>Sichuan Jiuniu</t>
+  </si>
+  <si>
+    <t>Levante W</t>
+  </si>
+  <si>
+    <t>Polonia Warszawa</t>
+  </si>
+  <si>
+    <t>Sokol Saratov</t>
+  </si>
+  <si>
     <t>Hoang Anh Gia Lai</t>
   </si>
   <si>
-    <t>Sichuan Jiuniu</t>
+    <t>Amarante</t>
+  </si>
+  <si>
+    <t>Gyeongnam</t>
   </si>
   <si>
     <t>Sheger Ketema</t>
   </si>
   <si>
-    <t>Gyeongnam</t>
-  </si>
-  <si>
     <t>Ulytau</t>
   </si>
   <si>
-    <t>Levante W</t>
-  </si>
-  <si>
-    <t>Polonia Warszawa</t>
-  </si>
-  <si>
-    <t>Sokol Saratov</t>
-  </si>
-  <si>
-    <t>Amarante</t>
-  </si>
-  <si>
     <t>Piast Gliwice</t>
   </si>
   <si>
     <t>Hellas Verona</t>
   </si>
   <si>
+    <t>Piteå Women</t>
+  </si>
+  <si>
+    <t>Bangkok Glass</t>
+  </si>
+  <si>
     <t>Celtic</t>
   </si>
   <si>
-    <t>Bangkok Glass</t>
-  </si>
-  <si>
     <t>Ayutthaya United</t>
   </si>
   <si>
+    <t>Hà Nội II</t>
+  </si>
+  <si>
+    <t>Altay</t>
+  </si>
+  <si>
+    <t>Rayong</t>
+  </si>
+  <si>
+    <t>Ho Chi Minh City</t>
+  </si>
+  <si>
+    <t>Buriram United</t>
+  </si>
+  <si>
     <t>Chiangrai United</t>
   </si>
   <si>
+    <t>Chonburi</t>
+  </si>
+  <si>
+    <t>Sukhothai</t>
+  </si>
+  <si>
     <t>Kanchanaburi</t>
   </si>
   <si>
-    <t>Altay</t>
-  </si>
-  <si>
-    <t>Piteå Women</t>
-  </si>
-  <si>
-    <t>Rayong</t>
+    <t>Shenyang Urban</t>
   </si>
   <si>
     <t>Shenzhen Juniors</t>
   </si>
   <si>
-    <t>Shenyang Urban</t>
-  </si>
-  <si>
-    <t>Chonburi</t>
-  </si>
-  <si>
-    <t>Sukhothai</t>
-  </si>
-  <si>
-    <t>Ho Chi Minh City</t>
-  </si>
-  <si>
-    <t>Buriram United</t>
-  </si>
-  <si>
-    <t>Hà Nội II</t>
-  </si>
-  <si>
     <t>Sūduva</t>
   </si>
   <si>
     <t>Spartak Varna</t>
   </si>
   <si>
+    <t>Home United</t>
+  </si>
+  <si>
+    <t>Kerala Blasters</t>
+  </si>
+  <si>
+    <t>Hougang United</t>
+  </si>
+  <si>
+    <t>Fortuna Düsseldorf</t>
+  </si>
+  <si>
+    <t>KAA Gent</t>
+  </si>
+  <si>
+    <t>Nantong Zhiyun</t>
+  </si>
+  <si>
+    <t>Nõmme Kalju</t>
+  </si>
+  <si>
+    <t>Havelse</t>
+  </si>
+  <si>
     <t>Dongguan United</t>
   </si>
   <si>
-    <t>KAA Gent</t>
-  </si>
-  <si>
-    <t>Home United</t>
-  </si>
-  <si>
-    <t>Kerala Blasters</t>
-  </si>
-  <si>
-    <t>Nõmme Kalju</t>
-  </si>
-  <si>
-    <t>Hougang United</t>
-  </si>
-  <si>
-    <t>Havelse</t>
-  </si>
-  <si>
-    <t>Fortuna Düsseldorf</t>
+    <t>Preußen Münster</t>
   </si>
   <si>
     <t>Hertha BSC</t>
   </si>
   <si>
-    <t>Preußen Münster</t>
-  </si>
-  <si>
-    <t>Nantong Zhiyun</t>
+    <t>Beijing Guoan</t>
   </si>
   <si>
     <t>Zhejiang FC</t>
   </si>
   <si>
-    <t>Beijing Guoan</t>
-  </si>
-  <si>
     <t>Hrvace</t>
   </si>
   <si>
     <t>PSIM Yogyakarta</t>
   </si>
   <si>
+    <t>AIK</t>
+  </si>
+  <si>
+    <t>Meshakhte</t>
+  </si>
+  <si>
+    <t>RCD Mallorca</t>
+  </si>
+  <si>
+    <t>Vejle</t>
+  </si>
+  <si>
+    <t>FC Andorra</t>
+  </si>
+  <si>
     <t>Zenit</t>
   </si>
   <si>
-    <t>AIK</t>
-  </si>
-  <si>
     <t>Lugano</t>
   </si>
   <si>
-    <t>FC Andorra</t>
-  </si>
-  <si>
-    <t>Meshakhte</t>
-  </si>
-  <si>
-    <t>RCD Mallorca</t>
+    <t>Aktobe</t>
+  </si>
+  <si>
+    <t>Kalmar</t>
+  </si>
+  <si>
+    <t>Bahardar</t>
   </si>
   <si>
     <t>Qingdao Jonoon</t>
   </si>
   <si>
-    <t>Bahardar</t>
-  </si>
-  <si>
-    <t>Aktobe</t>
-  </si>
-  <si>
-    <t>Vejle</t>
-  </si>
-  <si>
     <t>Nordsjælland</t>
   </si>
   <si>
-    <t>Kalmar</t>
-  </si>
-  <si>
     <t>Công An Nhân Dân</t>
   </si>
   <si>
@@ -808,103 +808,112 @@
     <t>Baník Ostrava U21</t>
   </si>
   <si>
+    <t>Tychy 71</t>
+  </si>
+  <si>
     <t>Rosenborg</t>
   </si>
   <si>
-    <t>Tychy 71</t>
-  </si>
-  <si>
     <t>Wisła Płock</t>
   </si>
   <si>
+    <t>Nottingham Forest</t>
+  </si>
+  <si>
+    <t>Kelantan United</t>
+  </si>
+  <si>
+    <t>NK Primorje</t>
+  </si>
+  <si>
+    <t>Cremonese</t>
+  </si>
+  <si>
+    <t>Sigma Olomouc</t>
+  </si>
+  <si>
+    <t>Pardubice</t>
+  </si>
+  <si>
+    <t>Burnley</t>
+  </si>
+  <si>
+    <t>Fiorentina</t>
+  </si>
+  <si>
+    <t>Arba Minch Kenema</t>
+  </si>
+  <si>
+    <t>Crystal Palace</t>
+  </si>
+  <si>
     <t>Botoşani</t>
   </si>
   <si>
     <t>Turan</t>
   </si>
   <si>
-    <t>Arba Minch Kenema</t>
-  </si>
-  <si>
-    <t>Pardubice</t>
-  </si>
-  <si>
-    <t>Kelantan United</t>
-  </si>
-  <si>
-    <t>Cremonese</t>
-  </si>
-  <si>
-    <t>Nottingham Forest</t>
-  </si>
-  <si>
-    <t>Burnley</t>
-  </si>
-  <si>
-    <t>Fiorentina</t>
-  </si>
-  <si>
     <t>Uppsala W</t>
   </si>
   <si>
-    <t>Sigma Olomouc</t>
-  </si>
-  <si>
-    <t>Crystal Palace</t>
-  </si>
-  <si>
     <t>Astana</t>
   </si>
   <si>
-    <t>NK Primorje</t>
-  </si>
-  <si>
     <t>Hamburger SV</t>
   </si>
   <si>
     <t>Botev Vratsa</t>
   </si>
   <si>
+    <t>Volos NFC</t>
+  </si>
+  <si>
+    <t>Aris</t>
+  </si>
+  <si>
+    <t>Silkeborg</t>
+  </si>
+  <si>
+    <t>NorthEast United</t>
+  </si>
+  <si>
+    <t>Royal Antwerp FC</t>
+  </si>
+  <si>
+    <t>B36</t>
+  </si>
+  <si>
+    <t>Osijek</t>
+  </si>
+  <si>
+    <t>Honvéd W</t>
+  </si>
+  <si>
     <t>EB - Streymur</t>
   </si>
   <si>
-    <t>NorthEast United</t>
+    <t>Banga</t>
   </si>
   <si>
     <t>Nõmme United</t>
   </si>
   <si>
-    <t>Volos NFC</t>
-  </si>
-  <si>
-    <t>Osijek</t>
-  </si>
-  <si>
-    <t>Royal Antwerp FC</t>
-  </si>
-  <si>
-    <t>Honvéd W</t>
-  </si>
-  <si>
-    <t>Aris</t>
-  </si>
-  <si>
-    <t>Silkeborg</t>
-  </si>
-  <si>
-    <t>B36</t>
-  </si>
-  <si>
-    <t>Banga</t>
+    <t>Leganés</t>
+  </si>
+  <si>
+    <t>Athletic Club Bilbao</t>
   </si>
   <si>
     <t>Akhmat Grozny</t>
   </si>
   <si>
-    <t>Athletic Club Bilbao</t>
-  </si>
-  <si>
-    <t>Leganés</t>
+    <t>Young Boys</t>
+  </si>
+  <si>
+    <t>Viktoria Köln</t>
+  </si>
+  <si>
+    <t>Sion</t>
   </si>
   <si>
     <t>Neftekhimik</t>
@@ -913,256 +922,253 @@
     <t>Häcken</t>
   </si>
   <si>
-    <t>Sion</t>
-  </si>
-  <si>
-    <t>Viktoria Köln</t>
-  </si>
-  <si>
-    <t>Young Boys</t>
-  </si>
-  <si>
     <t>Go Ahead Eagles</t>
   </si>
   <si>
+    <t>Ajax</t>
+  </si>
+  <si>
+    <t>Feyenoord</t>
+  </si>
+  <si>
+    <t>Twente</t>
+  </si>
+  <si>
+    <t>Fortuna Sittard</t>
+  </si>
+  <si>
     <t>Excelsior</t>
   </si>
   <si>
+    <t>NAC Breda</t>
+  </si>
+  <si>
     <t>Telstar</t>
   </si>
   <si>
-    <t>Feyenoord</t>
-  </si>
-  <si>
-    <t>Fortuna Sittard</t>
-  </si>
-  <si>
-    <t>Ajax</t>
-  </si>
-  <si>
     <t>Groningen</t>
   </si>
   <si>
-    <t>Twente</t>
-  </si>
-  <si>
-    <t>NAC Breda</t>
+    <t>Vardar</t>
+  </si>
+  <si>
+    <t>Real Madrid W</t>
+  </si>
+  <si>
+    <t>Aresimi</t>
+  </si>
+  <si>
+    <t>Pelister</t>
+  </si>
+  <si>
+    <t>Makedonija GjP</t>
+  </si>
+  <si>
+    <t>Zbrojovka Brno</t>
+  </si>
+  <si>
+    <t>Akademija Pandev</t>
+  </si>
+  <si>
+    <t>Croatia Zmijavci</t>
+  </si>
+  <si>
+    <t>Shkendija</t>
+  </si>
+  <si>
+    <t>Ajka</t>
+  </si>
+  <si>
+    <t>Kecskeméti TE</t>
+  </si>
+  <si>
+    <t>Åsane</t>
+  </si>
+  <si>
+    <t>Apollon</t>
+  </si>
+  <si>
+    <t>Budafoki MTE</t>
+  </si>
+  <si>
+    <t>Omonia Nicosia</t>
+  </si>
+  <si>
+    <t>Saburtalo</t>
+  </si>
+  <si>
+    <t>Karcag SE</t>
+  </si>
+  <si>
+    <t>Paphos</t>
+  </si>
+  <si>
+    <t>Moss</t>
+  </si>
+  <si>
+    <t>Mebrat Hayl</t>
+  </si>
+  <si>
+    <t>Sandnes Ulf</t>
+  </si>
+  <si>
+    <t>Sandefjord</t>
+  </si>
+  <si>
+    <t>Sogndal</t>
+  </si>
+  <si>
+    <t>Strømmen</t>
+  </si>
+  <si>
+    <t>Raufoss</t>
+  </si>
+  <si>
+    <t>Pogoń Siedlce</t>
+  </si>
+  <si>
+    <t>Rapid Wien</t>
+  </si>
+  <si>
+    <t>LASK Linz</t>
   </si>
   <si>
     <t>Hartberg</t>
   </si>
   <si>
-    <t>Zbrojovka Brno</t>
-  </si>
-  <si>
-    <t>Rapid Wien</t>
-  </si>
-  <si>
-    <t>LASK Linz</t>
-  </si>
-  <si>
-    <t>Aresimi</t>
+    <t>Szentlőrinc SE</t>
   </si>
   <si>
     <t>Tromsø</t>
   </si>
   <si>
-    <t>Pogoń Siedlce</t>
-  </si>
-  <si>
-    <t>Real Madrid W</t>
-  </si>
-  <si>
-    <t>Szentlőrinc SE</t>
-  </si>
-  <si>
-    <t>Pelister</t>
-  </si>
-  <si>
-    <t>Shkendija</t>
-  </si>
-  <si>
     <t>KFUM</t>
   </si>
   <si>
-    <t>Makedonija GjP</t>
-  </si>
-  <si>
-    <t>Akademija Pandev</t>
-  </si>
-  <si>
-    <t>Apollon</t>
-  </si>
-  <si>
-    <t>Omonia Nicosia</t>
-  </si>
-  <si>
-    <t>Sandefjord</t>
-  </si>
-  <si>
-    <t>Mebrat Hayl</t>
-  </si>
-  <si>
-    <t>Kecskeméti TE</t>
-  </si>
-  <si>
-    <t>Budafoki MTE</t>
-  </si>
-  <si>
-    <t>Ajka</t>
-  </si>
-  <si>
-    <t>Vardar</t>
-  </si>
-  <si>
-    <t>Karcag SE</t>
-  </si>
-  <si>
-    <t>Moss</t>
-  </si>
-  <si>
-    <t>Åsane</t>
-  </si>
-  <si>
-    <t>Raufoss</t>
-  </si>
-  <si>
-    <t>Saburtalo</t>
-  </si>
-  <si>
-    <t>Sogndal</t>
-  </si>
-  <si>
-    <t>Sandnes Ulf</t>
-  </si>
-  <si>
-    <t>Strømmen</t>
-  </si>
-  <si>
-    <t>Croatia Zmijavci</t>
-  </si>
-  <si>
-    <t>Paphos</t>
+    <t>Al Bataeh</t>
   </si>
   <si>
     <t>Bani Yas</t>
   </si>
   <si>
-    <t>Al Bataeh</t>
-  </si>
-  <si>
     <t>Dibba Al Fujairah</t>
   </si>
   <si>
     <t>Al Ain</t>
   </si>
   <si>
+    <t>Köln</t>
+  </si>
+  <si>
     <t>Sekhukhune United</t>
   </si>
   <si>
+    <t>West Ham United</t>
+  </si>
+  <si>
     <t>Nieciecza</t>
   </si>
   <si>
-    <t>West Ham United</t>
-  </si>
-  <si>
-    <t>Köln</t>
-  </si>
-  <si>
     <t>Neftçi</t>
   </si>
   <si>
+    <t>Mladost DG</t>
+  </si>
+  <si>
+    <t>Jedinstvo</t>
+  </si>
+  <si>
+    <t>Arsenal Tivat</t>
+  </si>
+  <si>
+    <t>Panevėžys</t>
+  </si>
+  <si>
     <t>Mornar</t>
   </si>
   <si>
+    <t>Ittihad Tanger</t>
+  </si>
+  <si>
+    <t>Parma</t>
+  </si>
+  <si>
+    <t>Brøndby</t>
+  </si>
+  <si>
+    <t>Dinamo Bucureşti</t>
+  </si>
+  <si>
+    <t>Vysočina Jihlava</t>
+  </si>
+  <si>
     <t>Dečić</t>
   </si>
   <si>
-    <t>Jedinstvo</t>
-  </si>
-  <si>
-    <t>Parma</t>
-  </si>
-  <si>
-    <t>Arsenal Tivat</t>
-  </si>
-  <si>
-    <t>Brøndby</t>
-  </si>
-  <si>
-    <t>Dinamo Bucureşti</t>
-  </si>
-  <si>
-    <t>Vysočina Jihlava</t>
-  </si>
-  <si>
-    <t>Panevėžys</t>
-  </si>
-  <si>
-    <t>Ittihad Tanger</t>
-  </si>
-  <si>
-    <t>Mladost DG</t>
-  </si>
-  <si>
     <t>Al Riyadh</t>
   </si>
   <si>
+    <t>Slaven Koprivnica</t>
+  </si>
+  <si>
     <t>Dobrudzha 1919</t>
   </si>
   <si>
-    <t>Slaven Koprivnica</t>
-  </si>
-  <si>
     <t>07 Vestur</t>
   </si>
   <si>
     <t>Skála</t>
   </si>
   <si>
+    <t>Radnički Niš</t>
+  </si>
+  <si>
+    <t>IMT Novi Beograd</t>
+  </si>
+  <si>
+    <t>Spartak Subotica</t>
+  </si>
+  <si>
+    <t>Mirandés</t>
+  </si>
+  <si>
+    <t>Bačka Topola</t>
+  </si>
+  <si>
+    <t>Córdoba</t>
+  </si>
+  <si>
+    <t>Olympiakos Piraeus</t>
+  </si>
+  <si>
     <t>Real Oviedo</t>
   </si>
   <si>
+    <t>Kansas City</t>
+  </si>
+  <si>
+    <t>Union Saint-Gilloise</t>
+  </si>
+  <si>
     <t>AEK Athens</t>
   </si>
   <si>
-    <t>Union Saint-Gilloise</t>
-  </si>
-  <si>
     <t>Lokomotiv Moskva</t>
   </si>
   <si>
+    <t>Antofagasta</t>
+  </si>
+  <si>
+    <t>Copiapó</t>
+  </si>
+  <si>
     <t>Jablonec</t>
   </si>
   <si>
-    <t>Córdoba</t>
-  </si>
-  <si>
-    <t>Bačka Topola</t>
-  </si>
-  <si>
-    <t>Mirandés</t>
-  </si>
-  <si>
-    <t>Olympiakos Piraeus</t>
-  </si>
-  <si>
-    <t>Radnički Niš</t>
-  </si>
-  <si>
-    <t>Spartak Subotica</t>
-  </si>
-  <si>
-    <t>Copiapó</t>
-  </si>
-  <si>
-    <t>Kansas City</t>
-  </si>
-  <si>
-    <t>Antofagasta</t>
-  </si>
-  <si>
-    <t>IMT Novi Beograd</t>
+    <t>Tenerife W</t>
+  </si>
+  <si>
+    <t>Hapoel Haifa</t>
   </si>
   <si>
     <t>Ironi Tiberias</t>
@@ -1171,24 +1177,18 @@
     <t>Hapoel Katamon</t>
   </si>
   <si>
+    <t>Dinamo Batumi</t>
+  </si>
+  <si>
+    <t>Csákvári TK</t>
+  </si>
+  <si>
+    <t>KA</t>
+  </si>
+  <si>
     <t>Békéscsaba</t>
   </si>
   <si>
-    <t>Hapoel Haifa</t>
-  </si>
-  <si>
-    <t>Tenerife W</t>
-  </si>
-  <si>
-    <t>Csákvári TK</t>
-  </si>
-  <si>
-    <t>Dinamo Batumi</t>
-  </si>
-  <si>
-    <t>KA</t>
-  </si>
-  <si>
     <t>KRC Genk</t>
   </si>
   <si>
@@ -1198,21 +1198,21 @@
     <t>Hoffenheim II</t>
   </si>
   <si>
+    <t>CODM Meknès</t>
+  </si>
+  <si>
+    <t>Al Ittihad</t>
+  </si>
+  <si>
+    <t>UTS Rabat</t>
+  </si>
+  <si>
     <t>SD Aucas</t>
   </si>
   <si>
-    <t>UTS Rabat</t>
-  </si>
-  <si>
-    <t>CODM Meknès</t>
-  </si>
-  <si>
     <t>New England II</t>
   </si>
   <si>
-    <t>Al Ittihad</t>
-  </si>
-  <si>
     <t>Varzim</t>
   </si>
   <si>
@@ -1222,75 +1222,75 @@
     <t>AC Milan</t>
   </si>
   <si>
+    <t>Remo</t>
+  </si>
+  <si>
+    <t>FC Barcelona</t>
+  </si>
+  <si>
     <t>Auxerre</t>
   </si>
   <si>
+    <t>Club Atlético Güemes</t>
+  </si>
+  <si>
+    <t>Monaco</t>
+  </si>
+  <si>
+    <t>Agropecuario</t>
+  </si>
+  <si>
     <t>Atlético Mineiro</t>
   </si>
   <si>
+    <t>Angers SCO</t>
+  </si>
+  <si>
+    <t>Metz</t>
+  </si>
+  <si>
+    <t>PSG</t>
+  </si>
+  <si>
     <t>Rennes</t>
   </si>
   <si>
-    <t>Remo</t>
+    <t>Toulouse</t>
+  </si>
+  <si>
+    <t>Náutico</t>
   </si>
   <si>
     <t>Independiente Petrolero</t>
   </si>
   <si>
-    <t>Monaco</t>
-  </si>
-  <si>
-    <t>Náutico</t>
-  </si>
-  <si>
-    <t>Agropecuario</t>
-  </si>
-  <si>
-    <t>Toulouse</t>
-  </si>
-  <si>
-    <t>Club Atlético Güemes</t>
-  </si>
-  <si>
-    <t>FC Barcelona</t>
-  </si>
-  <si>
     <t>Le Havre</t>
   </si>
   <si>
-    <t>Angers SCO</t>
-  </si>
-  <si>
-    <t>Metz</t>
-  </si>
-  <si>
-    <t>PSG</t>
+    <t>Chaco For Ever</t>
+  </si>
+  <si>
+    <t>Godoy Cruz</t>
   </si>
   <si>
     <t>San Martín San Juan</t>
   </si>
   <si>
-    <t>Godoy Cruz</t>
-  </si>
-  <si>
-    <t>Chaco For Ever</t>
+    <t>Bay</t>
+  </si>
+  <si>
+    <t>Central Norte</t>
+  </si>
+  <si>
+    <t>Portland Timbers II</t>
   </si>
   <si>
     <t>Los Angeles II</t>
   </si>
   <si>
-    <t>Bay</t>
-  </si>
-  <si>
     <t>Hassania Agadir</t>
   </si>
   <si>
-    <t>Central Norte</t>
-  </si>
-  <si>
-    <t>Portland Timbers II</t>
-  </si>
-  <si>
     <t>CS Emelec</t>
   </si>
   <si>
@@ -1306,15 +1306,15 @@
     <t>Avaí</t>
   </si>
   <si>
+    <t>Mirassol</t>
+  </si>
+  <si>
+    <t>Santos</t>
+  </si>
+  <si>
     <t>Corinthians</t>
   </si>
   <si>
-    <t>Santos</t>
-  </si>
-  <si>
-    <t>Mirassol</t>
-  </si>
-  <si>
     <t>FC Cincinnati II</t>
   </si>
   <si>
@@ -1324,15 +1324,15 @@
     <t>Novorizontino</t>
   </si>
   <si>
+    <t>Atlanta United II</t>
+  </si>
+  <si>
+    <t>Minnesota United</t>
+  </si>
+  <si>
     <t>Seattle Reign</t>
   </si>
   <si>
-    <t>Minnesota United</t>
-  </si>
-  <si>
-    <t>Atlanta United II</t>
-  </si>
-  <si>
     <t>Manta FC</t>
   </si>
   <si>
@@ -1351,225 +1351,225 @@
     <t>Los Angeles FC</t>
   </si>
   <si>
+    <t>Sydney II</t>
+  </si>
+  <si>
+    <t>Bucheon 1995</t>
+  </si>
+  <si>
+    <t>Jeonnam Dragons</t>
+  </si>
+  <si>
     <t>St. George Saints</t>
   </si>
   <si>
-    <t>Sydney II</t>
-  </si>
-  <si>
-    <t>Jeonnam Dragons</t>
-  </si>
-  <si>
-    <t>Bucheon 1995</t>
-  </si>
-  <si>
     <t>Sydney United</t>
   </si>
   <si>
+    <t>Guangxi Hengchen</t>
+  </si>
+  <si>
+    <t>Shanghai Jiading</t>
+  </si>
+  <si>
     <t>Guangzhou E-Power</t>
   </si>
   <si>
-    <t>Shanghai Jiading</t>
-  </si>
-  <si>
-    <t>Guangxi Hengchen</t>
-  </si>
-  <si>
     <t>Rotor Volgograd</t>
   </si>
   <si>
+    <t>Yongin City</t>
+  </si>
+  <si>
     <t>Cheonan City</t>
   </si>
   <si>
-    <t>Yongin City</t>
-  </si>
-  <si>
     <t>Jeonbuk Motors</t>
   </si>
   <si>
+    <t>Táborsko</t>
+  </si>
+  <si>
     <t>Sparta Praha II</t>
   </si>
   <si>
-    <t>Táborsko</t>
+    <t>Persib</t>
   </si>
   <si>
     <t>Persijap</t>
   </si>
   <si>
-    <t>Persib</t>
-  </si>
-  <si>
     <t>Wuhan Three Towns</t>
   </si>
   <si>
     <t>Krylya Sovetov</t>
   </si>
   <si>
+    <t>Shandong Luneng</t>
+  </si>
+  <si>
+    <t>Logroño W</t>
+  </si>
+  <si>
+    <t>Górnik Łęczna</t>
+  </si>
+  <si>
+    <t>Spartak Kostroma</t>
+  </si>
+  <si>
     <t>Pho Hien</t>
   </si>
   <si>
-    <t>Shandong Luneng</t>
+    <t>União Santarém</t>
+  </si>
+  <si>
+    <t>Gimhae City</t>
   </si>
   <si>
     <t>Sidama Bunna</t>
   </si>
   <si>
-    <t>Gimhae City</t>
-  </si>
-  <si>
     <t>Kairat</t>
   </si>
   <si>
-    <t>Logroño W</t>
-  </si>
-  <si>
-    <t>Górnik Łęczna</t>
-  </si>
-  <si>
-    <t>Spartak Kostroma</t>
-  </si>
-  <si>
-    <t>União Santarém</t>
-  </si>
-  <si>
     <t>GKS Katowice</t>
   </si>
   <si>
     <t>Como</t>
   </si>
   <si>
+    <t>Rosengard Women</t>
+  </si>
+  <si>
+    <t>Prachuap</t>
+  </si>
+  <si>
     <t>Rangers</t>
   </si>
   <si>
-    <t>Prachuap</t>
-  </si>
-  <si>
     <t>Port FC</t>
   </si>
   <si>
+    <t>Viettel</t>
+  </si>
+  <si>
+    <t>Ordabasy</t>
+  </si>
+  <si>
+    <t>Bangkok United</t>
+  </si>
+  <si>
+    <t>Song Lam Nghe An</t>
+  </si>
+  <si>
+    <t>Lamphun Warrior</t>
+  </si>
+  <si>
     <t>Uthai Thani</t>
   </si>
   <si>
+    <t>Nakhon Ratchasima</t>
+  </si>
+  <si>
+    <t>Muang Thong United</t>
+  </si>
+  <si>
     <t>Ratchaburi</t>
   </si>
   <si>
-    <t>Ordabasy</t>
-  </si>
-  <si>
-    <t>Rosengard Women</t>
-  </si>
-  <si>
-    <t>Bangkok United</t>
+    <t>Yunnan Yukun</t>
   </si>
   <si>
     <t>Hebei Kungfu</t>
   </si>
   <si>
-    <t>Yunnan Yukun</t>
-  </si>
-  <si>
-    <t>Nakhon Ratchasima</t>
-  </si>
-  <si>
-    <t>Muang Thong United</t>
-  </si>
-  <si>
-    <t>Song Lam Nghe An</t>
-  </si>
-  <si>
-    <t>Lamphun Warrior</t>
-  </si>
-  <si>
-    <t>Viettel</t>
-  </si>
-  <si>
     <t>Žalgiris</t>
   </si>
   <si>
     <t>Slavia Sofia</t>
   </si>
   <si>
+    <t>Albirex Niigata S</t>
+  </si>
+  <si>
+    <t>Mohammedan</t>
+  </si>
+  <si>
+    <t>Tampines Rovers</t>
+  </si>
+  <si>
+    <t>Elversberg</t>
+  </si>
+  <si>
+    <t>RSC Anderlecht</t>
+  </si>
+  <si>
+    <t>Wuxi Wugou</t>
+  </si>
+  <si>
+    <t>Tallinna FC Flora</t>
+  </si>
+  <si>
+    <t>Schweinfurt</t>
+  </si>
+  <si>
     <t>Suzhou Dongwu</t>
   </si>
   <si>
-    <t>RSC Anderlecht</t>
-  </si>
-  <si>
-    <t>Albirex Niigata S</t>
-  </si>
-  <si>
-    <t>Mohammedan</t>
-  </si>
-  <si>
-    <t>Tallinna FC Flora</t>
-  </si>
-  <si>
-    <t>Tampines Rovers</t>
-  </si>
-  <si>
-    <t>Schweinfurt</t>
-  </si>
-  <si>
-    <t>Elversberg</t>
+    <t>Darmstadt 98</t>
   </si>
   <si>
     <t>Greuther Fürth</t>
   </si>
   <si>
-    <t>Darmstadt 98</t>
-  </si>
-  <si>
-    <t>Wuxi Wugou</t>
+    <t>Shanghai SIPG</t>
   </si>
   <si>
     <t>Tianjin Teda</t>
   </si>
   <si>
-    <t>Shanghai SIPG</t>
-  </si>
-  <si>
     <t>Opatija</t>
   </si>
   <si>
     <t>Malut United</t>
   </si>
   <si>
+    <t>Djurgården</t>
+  </si>
+  <si>
+    <t>Dila</t>
+  </si>
+  <si>
+    <t>Villarreal</t>
+  </si>
+  <si>
+    <t>Fredericia</t>
+  </si>
+  <si>
+    <t>UD Las Palmas</t>
+  </si>
+  <si>
     <t>FK Sochi</t>
   </si>
   <si>
-    <t>Djurgården</t>
-  </si>
-  <si>
     <t>St. Gallen</t>
   </si>
   <si>
-    <t>UD Las Palmas</t>
-  </si>
-  <si>
-    <t>Dila</t>
-  </si>
-  <si>
-    <t>Villarreal</t>
+    <t>Kaisar</t>
+  </si>
+  <si>
+    <t>Halmstad</t>
+  </si>
+  <si>
+    <t>Welwalo Adigrat Uni</t>
   </si>
   <si>
     <t>Dalian Zhixing</t>
   </si>
   <si>
-    <t>Welwalo Adigrat Uni</t>
-  </si>
-  <si>
-    <t>Kaisar</t>
-  </si>
-  <si>
-    <t>Fredericia</t>
-  </si>
-  <si>
     <t>Midtjylland</t>
   </si>
   <si>
-    <t>Halmstad</t>
-  </si>
-  <si>
     <t>Nam Dinh</t>
   </si>
   <si>
@@ -1579,103 +1579,112 @@
     <t>Ústí nad Labem</t>
   </si>
   <si>
+    <t>Ruch Chorzów</t>
+  </si>
+  <si>
     <t>Lillestrøm</t>
   </si>
   <si>
-    <t>Ruch Chorzów</t>
-  </si>
-  <si>
     <t>Motor Lublin</t>
   </si>
   <si>
+    <t>Newcastle United</t>
+  </si>
+  <si>
+    <t>Johor Darul Ta'zim</t>
+  </si>
+  <si>
+    <t>Mura</t>
+  </si>
+  <si>
+    <t>Pisa</t>
+  </si>
+  <si>
+    <t>Bohemians 1905</t>
+  </si>
+  <si>
+    <t>Karviná</t>
+  </si>
+  <si>
+    <t>Aston Villa</t>
+  </si>
+  <si>
+    <t>Genoa</t>
+  </si>
+  <si>
+    <t>Welayta Dicha</t>
+  </si>
+  <si>
+    <t>Everton</t>
+  </si>
+  <si>
     <t>Petrolul 52</t>
   </si>
   <si>
     <t>Karvan FK</t>
   </si>
   <si>
-    <t>Welayta Dicha</t>
-  </si>
-  <si>
-    <t>Karviná</t>
-  </si>
-  <si>
-    <t>Johor Darul Ta'zim</t>
-  </si>
-  <si>
-    <t>Pisa</t>
-  </si>
-  <si>
-    <t>Newcastle United</t>
-  </si>
-  <si>
-    <t>Aston Villa</t>
-  </si>
-  <si>
-    <t>Genoa</t>
-  </si>
-  <si>
     <t>Vittsjö</t>
   </si>
   <si>
-    <t>Bohemians 1905</t>
-  </si>
-  <si>
-    <t>Everton</t>
-  </si>
-  <si>
     <t>Kyzyl-Zhar</t>
   </si>
   <si>
-    <t>Mura</t>
-  </si>
-  <si>
     <t>Freiburg</t>
   </si>
   <si>
     <t>Septemvri Sofia</t>
   </si>
   <si>
+    <t>Levadiakos</t>
+  </si>
+  <si>
+    <t>OFI</t>
+  </si>
+  <si>
+    <t>København</t>
+  </si>
+  <si>
+    <t>Chennaiyin</t>
+  </si>
+  <si>
+    <t>Sporting Charleroi</t>
+  </si>
+  <si>
+    <t>KÍ</t>
+  </si>
+  <si>
+    <t>Istra 1961</t>
+  </si>
+  <si>
+    <t>Vasas</t>
+  </si>
+  <si>
     <t>Víkingur</t>
   </si>
   <si>
-    <t>Chennaiyin</t>
+    <t>TransINVEST Vilnius</t>
   </si>
   <si>
     <t>Paide</t>
   </si>
   <si>
-    <t>Levadiakos</t>
-  </si>
-  <si>
-    <t>Istra 1961</t>
-  </si>
-  <si>
-    <t>Sporting Charleroi</t>
-  </si>
-  <si>
-    <t>Vasas</t>
-  </si>
-  <si>
-    <t>OFI</t>
-  </si>
-  <si>
-    <t>København</t>
-  </si>
-  <si>
-    <t>KÍ</t>
-  </si>
-  <si>
-    <t>TransINVEST Vilnius</t>
+    <t>Racing Santander</t>
+  </si>
+  <si>
+    <t>Valencia CF</t>
   </si>
   <si>
     <t>Makhachkala</t>
   </si>
   <si>
-    <t>Valencia CF</t>
-  </si>
-  <si>
-    <t>Racing Santander</t>
+    <t>Basel</t>
+  </si>
+  <si>
+    <t>Alemannia Aachen</t>
+  </si>
+  <si>
+    <t>Thun</t>
   </si>
   <si>
     <t>Volga Ulyanovsk</t>
@@ -1684,253 +1693,250 @@
     <t>Malmö FF</t>
   </si>
   <si>
-    <t>Thun</t>
-  </si>
-  <si>
-    <t>Alemannia Aachen</t>
-  </si>
-  <si>
-    <t>Basel</t>
-  </si>
-  <si>
     <t>PSV</t>
   </si>
   <si>
+    <t>Utrecht</t>
+  </si>
+  <si>
+    <t>AZ</t>
+  </si>
+  <si>
+    <t>Sparta Rotterdam</t>
+  </si>
+  <si>
+    <t>PEC Zwolle</t>
+  </si>
+  <si>
     <t>Volendam</t>
   </si>
   <si>
+    <t>Heerenveen</t>
+  </si>
+  <si>
     <t>Heracles</t>
   </si>
   <si>
-    <t>AZ</t>
-  </si>
-  <si>
-    <t>PEC Zwolle</t>
-  </si>
-  <si>
-    <t>Utrecht</t>
-  </si>
-  <si>
     <t>NEC</t>
   </si>
   <si>
-    <t>Sparta Rotterdam</t>
-  </si>
-  <si>
-    <t>Heerenveen</t>
+    <t>Sileks</t>
+  </si>
+  <si>
+    <t>Atletico Madrid W</t>
+  </si>
+  <si>
+    <t>FK Bashkimi Kumanovo</t>
+  </si>
+  <si>
+    <t>Shkupi</t>
+  </si>
+  <si>
+    <t>Tikveš</t>
+  </si>
+  <si>
+    <t>Vlašim</t>
+  </si>
+  <si>
+    <t>Rabotnički</t>
+  </si>
+  <si>
+    <t>Jarun</t>
+  </si>
+  <si>
+    <t>Struga</t>
+  </si>
+  <si>
+    <t>Szeged 2011</t>
+  </si>
+  <si>
+    <t>Mezőkövesd-Zsóry</t>
+  </si>
+  <si>
+    <t>Strømsgodset</t>
+  </si>
+  <si>
+    <t>APOEL</t>
+  </si>
+  <si>
+    <t>BVSC</t>
+  </si>
+  <si>
+    <t>AEK Larnaca</t>
+  </si>
+  <si>
+    <t>Torpedo Kutaisi</t>
+  </si>
+  <si>
+    <t>Tiszakécske</t>
+  </si>
+  <si>
+    <t>Bryne</t>
+  </si>
+  <si>
+    <t>Fasil Ketema</t>
+  </si>
+  <si>
+    <t>Stabæk</t>
+  </si>
+  <si>
+    <t>Kristiansund</t>
+  </si>
+  <si>
+    <t>Haugesund</t>
+  </si>
+  <si>
+    <t>Hødd</t>
+  </si>
+  <si>
+    <t>Lyn</t>
+  </si>
+  <si>
+    <t>Stal Rzeszów</t>
+  </si>
+  <si>
+    <t>Austria Wien</t>
+  </si>
+  <si>
+    <t>Salzburg</t>
   </si>
   <si>
     <t>Sturm Graz</t>
   </si>
   <si>
-    <t>Vlašim</t>
-  </si>
-  <si>
-    <t>Austria Wien</t>
-  </si>
-  <si>
-    <t>Salzburg</t>
-  </si>
-  <si>
-    <t>FK Bashkimi Kumanovo</t>
+    <t>Videoton</t>
   </si>
   <si>
     <t>Molde</t>
   </si>
   <si>
-    <t>Stal Rzeszów</t>
-  </si>
-  <si>
-    <t>Atletico Madrid W</t>
-  </si>
-  <si>
-    <t>Videoton</t>
-  </si>
-  <si>
-    <t>Shkupi</t>
-  </si>
-  <si>
-    <t>Struga</t>
-  </si>
-  <si>
     <t>Viking</t>
   </si>
   <si>
-    <t>Tikveš</t>
-  </si>
-  <si>
-    <t>Rabotnički</t>
-  </si>
-  <si>
-    <t>APOEL</t>
-  </si>
-  <si>
-    <t>AEK Larnaca</t>
-  </si>
-  <si>
-    <t>Kristiansund</t>
-  </si>
-  <si>
-    <t>Fasil Ketema</t>
-  </si>
-  <si>
-    <t>Mezőkövesd-Zsóry</t>
-  </si>
-  <si>
-    <t>BVSC</t>
-  </si>
-  <si>
-    <t>Szeged 2011</t>
-  </si>
-  <si>
-    <t>Sileks</t>
-  </si>
-  <si>
-    <t>Tiszakécske</t>
-  </si>
-  <si>
-    <t>Bryne</t>
-  </si>
-  <si>
-    <t>Strømsgodset</t>
-  </si>
-  <si>
-    <t>Lyn</t>
-  </si>
-  <si>
-    <t>Torpedo Kutaisi</t>
-  </si>
-  <si>
-    <t>Haugesund</t>
-  </si>
-  <si>
-    <t>Stabæk</t>
-  </si>
-  <si>
-    <t>Hødd</t>
-  </si>
-  <si>
-    <t>Jarun</t>
+    <t>Al Sharjah</t>
   </si>
   <si>
     <t>Shabab Al Ahli Dubai</t>
   </si>
   <si>
-    <t>Al Sharjah</t>
-  </si>
-  <si>
     <t>Ajman</t>
   </si>
   <si>
     <t>Al Dhafra</t>
   </si>
   <si>
+    <t>Heidenheim</t>
+  </si>
+  <si>
     <t>Kaizer Chiefs</t>
   </si>
   <si>
+    <t>Arsenal</t>
+  </si>
+  <si>
     <t>Legia Warszawa</t>
   </si>
   <si>
-    <t>Arsenal</t>
-  </si>
-  <si>
-    <t>Heidenheim</t>
-  </si>
-  <si>
     <t>İnter Bakı</t>
   </si>
   <si>
+    <t>Petrovac</t>
+  </si>
+  <si>
+    <t>Budućnost</t>
+  </si>
+  <si>
+    <t>Sutjeska</t>
+  </si>
+  <si>
+    <t>Kauno Žalgiris</t>
+  </si>
+  <si>
     <t>Bokelj</t>
   </si>
   <si>
+    <t>Difaâ El Jadida</t>
+  </si>
+  <si>
+    <t>Roma</t>
+  </si>
+  <si>
+    <t>AGF</t>
+  </si>
+  <si>
+    <t>Argeș</t>
+  </si>
+  <si>
+    <t>Hanácká</t>
+  </si>
+  <si>
     <t>FK Jezero Plav</t>
   </si>
   <si>
-    <t>Budućnost</t>
-  </si>
-  <si>
-    <t>Roma</t>
-  </si>
-  <si>
-    <t>Sutjeska</t>
-  </si>
-  <si>
-    <t>AGF</t>
-  </si>
-  <si>
-    <t>Argeș</t>
-  </si>
-  <si>
-    <t>Hanácká</t>
-  </si>
-  <si>
-    <t>Kauno Žalgiris</t>
-  </si>
-  <si>
-    <t>Difaâ El Jadida</t>
-  </si>
-  <si>
-    <t>Petrovac</t>
-  </si>
-  <si>
     <t>Al Fateh</t>
   </si>
   <si>
+    <t>Gorica</t>
+  </si>
+  <si>
     <t>Beroe</t>
   </si>
   <si>
-    <t>Gorica</t>
-  </si>
-  <si>
     <t>B68</t>
   </si>
   <si>
     <t>AB</t>
   </si>
   <si>
+    <t>LFK Mladost Lučani</t>
+  </si>
+  <si>
+    <t>Radnički Kragujevac</t>
+  </si>
+  <si>
+    <t>Napredak</t>
+  </si>
+  <si>
+    <t>SD Eibar</t>
+  </si>
+  <si>
+    <t>Javor Ivanjica</t>
+  </si>
+  <si>
+    <t>Granada CF</t>
+  </si>
+  <si>
+    <t>PAOK</t>
+  </si>
+  <si>
     <t>Getafe CF</t>
   </si>
   <si>
+    <t>Chicago Red Stars</t>
+  </si>
+  <si>
+    <t>KV Mechelen</t>
+  </si>
+  <si>
     <t>Panathinaikos</t>
   </si>
   <si>
-    <t>KV Mechelen</t>
-  </si>
-  <si>
     <t>Baltika</t>
   </si>
   <si>
+    <t>San Luis</t>
+  </si>
+  <si>
+    <t>Unión San Felipe</t>
+  </si>
+  <si>
     <t>Hradec Králové</t>
   </si>
   <si>
-    <t>Granada CF</t>
-  </si>
-  <si>
-    <t>Javor Ivanjica</t>
-  </si>
-  <si>
-    <t>SD Eibar</t>
-  </si>
-  <si>
-    <t>PAOK</t>
-  </si>
-  <si>
-    <t>LFK Mladost Lučani</t>
-  </si>
-  <si>
-    <t>Napredak</t>
-  </si>
-  <si>
-    <t>Unión San Felipe</t>
-  </si>
-  <si>
-    <t>Chicago Red Stars</t>
-  </si>
-  <si>
-    <t>San Luis</t>
-  </si>
-  <si>
-    <t>Radnički Kragujevac</t>
+    <t>Barcelona W</t>
+  </si>
+  <si>
+    <t>Ashdod</t>
   </si>
   <si>
     <t>Maccabi Netanya</t>
@@ -1939,24 +1945,18 @@
     <t>Bnei Sakhnin</t>
   </si>
   <si>
+    <t>Samgurali</t>
+  </si>
+  <si>
+    <t>Soroksár SC</t>
+  </si>
+  <si>
+    <t>ÍBV</t>
+  </si>
+  <si>
     <t>Kozármisleny</t>
   </si>
   <si>
-    <t>Ashdod</t>
-  </si>
-  <si>
-    <t>Barcelona W</t>
-  </si>
-  <si>
-    <t>Soroksár SC</t>
-  </si>
-  <si>
-    <t>Samgurali</t>
-  </si>
-  <si>
-    <t>ÍBV</t>
-  </si>
-  <si>
     <t>KVC Westerlo</t>
   </si>
   <si>
@@ -1966,21 +1966,21 @@
     <t>Saarbrucken</t>
   </si>
   <si>
+    <t>RSB Berkane</t>
+  </si>
+  <si>
+    <t>Dhamk</t>
+  </si>
+  <si>
+    <t>Maghreb Fès</t>
+  </si>
+  <si>
     <t>CD Universidad Católica</t>
   </si>
   <si>
-    <t>Maghreb Fès</t>
-  </si>
-  <si>
-    <t>RSB Berkane</t>
-  </si>
-  <si>
     <t>New York City II</t>
   </si>
   <si>
-    <t>Dhamk</t>
-  </si>
-  <si>
     <t>CF Os Belenenses</t>
   </si>
   <si>
@@ -1990,75 +1990,75 @@
     <t>Atalanta</t>
   </si>
   <si>
+    <t>Palmeiras</t>
+  </si>
+  <si>
+    <t>Real Madrid</t>
+  </si>
+  <si>
     <t>Nice</t>
   </si>
   <si>
+    <t>Quilmes</t>
+  </si>
+  <si>
+    <t>Lille</t>
+  </si>
+  <si>
+    <t>Atlanta</t>
+  </si>
+  <si>
     <t>Botafogo</t>
   </si>
   <si>
+    <t>Strasbourg</t>
+  </si>
+  <si>
+    <t>Lorient</t>
+  </si>
+  <si>
+    <t>Brest</t>
+  </si>
+  <si>
     <t>Paris</t>
   </si>
   <si>
-    <t>Palmeiras</t>
+    <t>Olympique Lyonnais</t>
+  </si>
+  <si>
+    <t>América Mineiro</t>
   </si>
   <si>
     <t>Club Always Ready</t>
   </si>
   <si>
-    <t>Lille</t>
-  </si>
-  <si>
-    <t>América Mineiro</t>
-  </si>
-  <si>
-    <t>Atlanta</t>
-  </si>
-  <si>
-    <t>Olympique Lyonnais</t>
-  </si>
-  <si>
-    <t>Quilmes</t>
-  </si>
-  <si>
-    <t>Real Madrid</t>
-  </si>
-  <si>
     <t>Olympique Marseille</t>
   </si>
   <si>
-    <t>Strasbourg</t>
-  </si>
-  <si>
-    <t>Lorient</t>
-  </si>
-  <si>
-    <t>Brest</t>
+    <t>Ciudad de Bolívar</t>
+  </si>
+  <si>
+    <t>Racing Córdoba</t>
   </si>
   <si>
     <t>Patronato</t>
   </si>
   <si>
-    <t>Racing Córdoba</t>
-  </si>
-  <si>
-    <t>Ciudad de Bolívar</t>
+    <t>Utah Royals</t>
+  </si>
+  <si>
+    <t>Deportivo Madryn</t>
+  </si>
+  <si>
+    <t>LA Galaxy II</t>
   </si>
   <si>
     <t>Real Monarchs</t>
   </si>
   <si>
-    <t>Utah Royals</t>
-  </si>
-  <si>
     <t>FAR Rabat</t>
   </si>
   <si>
-    <t>Deportivo Madryn</t>
-  </si>
-  <si>
-    <t>LA Galaxy II</t>
-  </si>
-  <si>
     <t>Libertad</t>
   </si>
   <si>
@@ -2074,15 +2074,15 @@
     <t>Fortaleza</t>
   </si>
   <si>
+    <t>Chapecoense</t>
+  </si>
+  <si>
+    <t>Bragantino</t>
+  </si>
+  <si>
     <t>São Paulo</t>
   </si>
   <si>
-    <t>Bragantino</t>
-  </si>
-  <si>
-    <t>Chapecoense</t>
-  </si>
-  <si>
     <t>Columbus Crew II</t>
   </si>
   <si>
@@ -2092,13 +2092,13 @@
     <t>Botafogo SP</t>
   </si>
   <si>
+    <t>Orlando City II</t>
+  </si>
+  <si>
+    <t>Austin</t>
+  </si>
+  <si>
     <t>Washington Spirit</t>
-  </si>
-  <si>
-    <t>Austin</t>
-  </si>
-  <si>
-    <t>Orlando City II</t>
   </si>
   <si>
     <t>Macará</t>
@@ -2864,7 +2864,7 @@
         <v>61</v>
       </c>
       <c r="C3" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="D3" t="s">
         <v>185</v>
@@ -3049,7 +3049,7 @@
         <v>61</v>
       </c>
       <c r="C4" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="D4" t="s">
         <v>185</v>
@@ -3234,7 +3234,7 @@
         <v>61</v>
       </c>
       <c r="C5" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="D5" t="s">
         <v>185</v>
@@ -4344,7 +4344,7 @@
         <v>64</v>
       </c>
       <c r="C11" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="D11" t="s">
         <v>185</v>
@@ -4529,7 +4529,7 @@
         <v>64</v>
       </c>
       <c r="C12" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="D12" t="s">
         <v>185</v>
@@ -4714,7 +4714,7 @@
         <v>64</v>
       </c>
       <c r="C13" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D13" t="s">
         <v>185</v>
@@ -6009,10 +6009,10 @@
         <v>68</v>
       </c>
       <c r="C20" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="D20" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E20" t="s">
         <v>206</v>
@@ -6194,10 +6194,10 @@
         <v>68</v>
       </c>
       <c r="C21" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="D21" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E21" t="s">
         <v>207</v>
@@ -6564,10 +6564,10 @@
         <v>68</v>
       </c>
       <c r="C23" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="D23" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E23" t="s">
         <v>209</v>
@@ -6752,7 +6752,7 @@
         <v>126</v>
       </c>
       <c r="D24" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E24" t="s">
         <v>210</v>
@@ -7119,10 +7119,10 @@
         <v>68</v>
       </c>
       <c r="C26" t="s">
-        <v>128</v>
+        <v>117</v>
       </c>
       <c r="D26" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E26" t="s">
         <v>212</v>
@@ -7304,7 +7304,7 @@
         <v>68</v>
       </c>
       <c r="C27" t="s">
-        <v>119</v>
+        <v>128</v>
       </c>
       <c r="D27" t="s">
         <v>186</v>
@@ -7492,7 +7492,7 @@
         <v>129</v>
       </c>
       <c r="D28" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E28" t="s">
         <v>214</v>
@@ -8047,7 +8047,7 @@
         <v>132</v>
       </c>
       <c r="D31" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E31" t="s">
         <v>217</v>
@@ -8083,13 +8083,13 @@
         <v>701</v>
       </c>
       <c r="P31">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Q31">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="R31">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="S31">
         <v>0</v>
@@ -8414,7 +8414,7 @@
         <v>71</v>
       </c>
       <c r="C33" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="D33" t="s">
         <v>186</v>
@@ -8453,13 +8453,13 @@
         <v>701</v>
       </c>
       <c r="P33">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Q33">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="R33">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="S33">
         <v>0</v>
@@ -8784,7 +8784,7 @@
         <v>71</v>
       </c>
       <c r="C35" t="s">
-        <v>133</v>
+        <v>126</v>
       </c>
       <c r="D35" t="s">
         <v>186</v>
@@ -8969,7 +8969,7 @@
         <v>71</v>
       </c>
       <c r="C36" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="D36" t="s">
         <v>185</v>
@@ -9154,10 +9154,10 @@
         <v>71</v>
       </c>
       <c r="C37" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="D37" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E37" t="s">
         <v>223</v>
@@ -9339,7 +9339,7 @@
         <v>71</v>
       </c>
       <c r="C38" t="s">
-        <v>133</v>
+        <v>126</v>
       </c>
       <c r="D38" t="s">
         <v>186</v>
@@ -9524,10 +9524,10 @@
         <v>71</v>
       </c>
       <c r="C39" t="s">
-        <v>118</v>
+        <v>133</v>
       </c>
       <c r="D39" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E39" t="s">
         <v>225</v>
@@ -9709,10 +9709,10 @@
         <v>71</v>
       </c>
       <c r="C40" t="s">
-        <v>122</v>
+        <v>133</v>
       </c>
       <c r="D40" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E40" t="s">
         <v>226</v>
@@ -10264,7 +10264,7 @@
         <v>71</v>
       </c>
       <c r="C43" t="s">
-        <v>124</v>
+        <v>133</v>
       </c>
       <c r="D43" t="s">
         <v>186</v>
@@ -10449,10 +10449,10 @@
         <v>71</v>
       </c>
       <c r="C44" t="s">
-        <v>133</v>
+        <v>122</v>
       </c>
       <c r="D44" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E44" t="s">
         <v>230</v>
@@ -10634,10 +10634,10 @@
         <v>71</v>
       </c>
       <c r="C45" t="s">
-        <v>124</v>
+        <v>118</v>
       </c>
       <c r="D45" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E45" t="s">
         <v>231</v>
@@ -11189,10 +11189,10 @@
         <v>73</v>
       </c>
       <c r="C48" t="s">
-        <v>118</v>
+        <v>137</v>
       </c>
       <c r="D48" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="E48" t="s">
         <v>234</v>
@@ -11374,7 +11374,7 @@
         <v>73</v>
       </c>
       <c r="C49" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="D49" t="s">
         <v>186</v>
@@ -11559,7 +11559,7 @@
         <v>73</v>
       </c>
       <c r="C50" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D50" t="s">
         <v>187</v>
@@ -11932,7 +11932,7 @@
         <v>140</v>
       </c>
       <c r="D52" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E52" t="s">
         <v>238</v>
@@ -12114,10 +12114,10 @@
         <v>73</v>
       </c>
       <c r="C53" t="s">
-        <v>138</v>
+        <v>118</v>
       </c>
       <c r="D53" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="E53" t="s">
         <v>239</v>
@@ -12302,7 +12302,7 @@
         <v>141</v>
       </c>
       <c r="D54" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E54" t="s">
         <v>240</v>
@@ -12669,10 +12669,10 @@
         <v>73</v>
       </c>
       <c r="C56" t="s">
-        <v>142</v>
+        <v>118</v>
       </c>
       <c r="D56" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E56" t="s">
         <v>242</v>
@@ -12854,7 +12854,7 @@
         <v>73</v>
       </c>
       <c r="C57" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="D57" t="s">
         <v>186</v>
@@ -13039,10 +13039,10 @@
         <v>73</v>
       </c>
       <c r="C58" t="s">
-        <v>118</v>
+        <v>139</v>
       </c>
       <c r="D58" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E58" t="s">
         <v>244</v>
@@ -13964,10 +13964,10 @@
         <v>76</v>
       </c>
       <c r="C63" t="s">
-        <v>123</v>
+        <v>144</v>
       </c>
       <c r="D63" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E63" t="s">
         <v>249</v>
@@ -14003,13 +14003,13 @@
         <v>701</v>
       </c>
       <c r="P63">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="Q63">
-        <v>7.41</v>
+        <v>0</v>
       </c>
       <c r="R63">
-        <v>17.5</v>
+        <v>0</v>
       </c>
       <c r="S63">
         <v>0</v>
@@ -14149,7 +14149,7 @@
         <v>76</v>
       </c>
       <c r="C64" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="D64" t="s">
         <v>185</v>
@@ -14334,7 +14334,7 @@
         <v>76</v>
       </c>
       <c r="C65" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D65" t="s">
         <v>186</v>
@@ -14519,7 +14519,7 @@
         <v>76</v>
       </c>
       <c r="C66" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="D66" t="s">
         <v>186</v>
@@ -14704,10 +14704,10 @@
         <v>76</v>
       </c>
       <c r="C67" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="D67" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E67" t="s">
         <v>253</v>
@@ -14889,7 +14889,7 @@
         <v>76</v>
       </c>
       <c r="C68" t="s">
-        <v>148</v>
+        <v>123</v>
       </c>
       <c r="D68" t="s">
         <v>186</v>
@@ -14928,13 +14928,13 @@
         <v>701</v>
       </c>
       <c r="P68">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="Q68">
-        <v>0</v>
+        <v>7.41</v>
       </c>
       <c r="R68">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="S68">
         <v>0</v>
@@ -15074,10 +15074,10 @@
         <v>76</v>
       </c>
       <c r="C69" t="s">
-        <v>122</v>
+        <v>149</v>
       </c>
       <c r="D69" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E69" t="s">
         <v>255</v>
@@ -15259,10 +15259,10 @@
         <v>76</v>
       </c>
       <c r="C70" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="D70" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E70" t="s">
         <v>256</v>
@@ -15444,7 +15444,7 @@
         <v>76</v>
       </c>
       <c r="C71" t="s">
-        <v>126</v>
+        <v>144</v>
       </c>
       <c r="D71" t="s">
         <v>185</v>
@@ -15629,7 +15629,7 @@
         <v>76</v>
       </c>
       <c r="C72" t="s">
-        <v>149</v>
+        <v>128</v>
       </c>
       <c r="D72" t="s">
         <v>186</v>
@@ -15814,10 +15814,10 @@
         <v>76</v>
       </c>
       <c r="C73" t="s">
-        <v>149</v>
+        <v>122</v>
       </c>
       <c r="D73" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E73" t="s">
         <v>259</v>
@@ -15853,13 +15853,13 @@
         <v>701</v>
       </c>
       <c r="P73">
-        <v>3.36</v>
+        <v>0</v>
       </c>
       <c r="Q73">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="R73">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="S73">
         <v>0</v>
@@ -15999,10 +15999,10 @@
         <v>76</v>
       </c>
       <c r="C74" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="D74" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E74" t="s">
         <v>260</v>
@@ -16038,13 +16038,13 @@
         <v>701</v>
       </c>
       <c r="P74">
-        <v>0</v>
+        <v>3.36</v>
       </c>
       <c r="Q74">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="R74">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="S74">
         <v>0</v>
@@ -16184,7 +16184,7 @@
         <v>77</v>
       </c>
       <c r="C75" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="D75" t="s">
         <v>186</v>
@@ -16739,10 +16739,10 @@
         <v>78</v>
       </c>
       <c r="C78" t="s">
-        <v>151</v>
+        <v>125</v>
       </c>
       <c r="D78" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E78" t="s">
         <v>264</v>
@@ -16924,10 +16924,10 @@
         <v>78</v>
       </c>
       <c r="C79" t="s">
-        <v>128</v>
+        <v>151</v>
       </c>
       <c r="D79" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E79" t="s">
         <v>265</v>
@@ -17333,13 +17333,13 @@
         <v>701</v>
       </c>
       <c r="P81">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="Q81">
-        <v>0</v>
+        <v>3.66</v>
       </c>
       <c r="R81">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="S81">
         <v>0</v>
@@ -17378,10 +17378,10 @@
         <v>0</v>
       </c>
       <c r="AE81">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AF81">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AG81">
         <v>0</v>
@@ -17479,7 +17479,7 @@
         <v>80</v>
       </c>
       <c r="C82" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="D82" t="s">
         <v>186</v>
@@ -17664,7 +17664,7 @@
         <v>80</v>
       </c>
       <c r="C83" t="s">
-        <v>125</v>
+        <v>153</v>
       </c>
       <c r="D83" t="s">
         <v>186</v>
@@ -17849,7 +17849,7 @@
         <v>80</v>
       </c>
       <c r="C84" t="s">
-        <v>154</v>
+        <v>131</v>
       </c>
       <c r="D84" t="s">
         <v>186</v>
@@ -17888,13 +17888,13 @@
         <v>701</v>
       </c>
       <c r="P84">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Q84">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="R84">
-        <v>0</v>
+        <v>4.07</v>
       </c>
       <c r="S84">
         <v>0</v>
@@ -17933,10 +17933,10 @@
         <v>0</v>
       </c>
       <c r="AE84">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AF84">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AG84">
         <v>0</v>
@@ -18034,7 +18034,7 @@
         <v>80</v>
       </c>
       <c r="C85" t="s">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="D85" t="s">
         <v>186</v>
@@ -18219,7 +18219,7 @@
         <v>80</v>
       </c>
       <c r="C86" t="s">
-        <v>131</v>
+        <v>154</v>
       </c>
       <c r="D86" t="s">
         <v>186</v>
@@ -18258,13 +18258,13 @@
         <v>701</v>
       </c>
       <c r="P86">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Q86">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="R86">
-        <v>4.07</v>
+        <v>0</v>
       </c>
       <c r="S86">
         <v>0</v>
@@ -18303,10 +18303,10 @@
         <v>0</v>
       </c>
       <c r="AE86">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AF86">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AG86">
         <v>0</v>
@@ -18404,7 +18404,7 @@
         <v>80</v>
       </c>
       <c r="C87" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="D87" t="s">
         <v>186</v>
@@ -18443,13 +18443,13 @@
         <v>701</v>
       </c>
       <c r="P87">
-        <v>2.46</v>
+        <v>5.38</v>
       </c>
       <c r="Q87">
-        <v>3.66</v>
+        <v>4.37</v>
       </c>
       <c r="R87">
-        <v>2.99</v>
+        <v>1.67</v>
       </c>
       <c r="S87">
         <v>0</v>
@@ -18488,10 +18488,10 @@
         <v>0</v>
       </c>
       <c r="AE87">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AF87">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AG87">
         <v>0</v>
@@ -18589,7 +18589,7 @@
         <v>80</v>
       </c>
       <c r="C88" t="s">
-        <v>155</v>
+        <v>131</v>
       </c>
       <c r="D88" t="s">
         <v>186</v>
@@ -18628,13 +18628,13 @@
         <v>701</v>
       </c>
       <c r="P88">
-        <v>5.38</v>
+        <v>2.09</v>
       </c>
       <c r="Q88">
-        <v>4.37</v>
+        <v>3.48</v>
       </c>
       <c r="R88">
-        <v>1.67</v>
+        <v>4.01</v>
       </c>
       <c r="S88">
         <v>0</v>
@@ -18673,10 +18673,10 @@
         <v>0</v>
       </c>
       <c r="AE88">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AF88">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AG88">
         <v>0</v>
@@ -18774,7 +18774,7 @@
         <v>80</v>
       </c>
       <c r="C89" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="D89" t="s">
         <v>186</v>
@@ -18813,13 +18813,13 @@
         <v>701</v>
       </c>
       <c r="P89">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="Q89">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="R89">
-        <v>4.01</v>
+        <v>0</v>
       </c>
       <c r="S89">
         <v>0</v>
@@ -18858,10 +18858,10 @@
         <v>0</v>
       </c>
       <c r="AE89">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AF89">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AG89">
         <v>0</v>
@@ -18959,10 +18959,10 @@
         <v>80</v>
       </c>
       <c r="C90" t="s">
-        <v>134</v>
+        <v>152</v>
       </c>
       <c r="D90" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E90" t="s">
         <v>276</v>
@@ -18998,13 +18998,13 @@
         <v>701</v>
       </c>
       <c r="P90">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="Q90">
-        <v>0</v>
+        <v>3.31</v>
       </c>
       <c r="R90">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="S90">
         <v>0</v>
@@ -19043,10 +19043,10 @@
         <v>0</v>
       </c>
       <c r="AE90">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AF90">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AG90">
         <v>0</v>
@@ -19144,7 +19144,7 @@
         <v>80</v>
       </c>
       <c r="C91" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="D91" t="s">
         <v>186</v>
@@ -19329,7 +19329,7 @@
         <v>80</v>
       </c>
       <c r="C92" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="D92" t="s">
         <v>186</v>
@@ -19368,13 +19368,13 @@
         <v>701</v>
       </c>
       <c r="P92">
-        <v>2.69</v>
+        <v>0</v>
       </c>
       <c r="Q92">
-        <v>3.31</v>
+        <v>0</v>
       </c>
       <c r="R92">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="S92">
         <v>0</v>
@@ -19413,10 +19413,10 @@
         <v>0</v>
       </c>
       <c r="AE92">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AF92">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AG92">
         <v>0</v>
@@ -19514,7 +19514,7 @@
         <v>80</v>
       </c>
       <c r="C93" t="s">
-        <v>126</v>
+        <v>132</v>
       </c>
       <c r="D93" t="s">
         <v>185</v>
@@ -19699,10 +19699,10 @@
         <v>80</v>
       </c>
       <c r="C94" t="s">
-        <v>156</v>
+        <v>129</v>
       </c>
       <c r="D94" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E94" t="s">
         <v>280</v>
@@ -20257,7 +20257,7 @@
         <v>158</v>
       </c>
       <c r="D97" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E97" t="s">
         <v>283</v>
@@ -20293,13 +20293,13 @@
         <v>701</v>
       </c>
       <c r="P97">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="Q97">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R97">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="S97">
         <v>0</v>
@@ -20439,7 +20439,7 @@
         <v>83</v>
       </c>
       <c r="C98" t="s">
-        <v>139</v>
+        <v>158</v>
       </c>
       <c r="D98" t="s">
         <v>186</v>
@@ -20624,10 +20624,10 @@
         <v>83</v>
       </c>
       <c r="C99" t="s">
-        <v>140</v>
+        <v>147</v>
       </c>
       <c r="D99" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E99" t="s">
         <v>285</v>
@@ -20663,13 +20663,13 @@
         <v>701</v>
       </c>
       <c r="P99">
-        <v>0</v>
+        <v>4.68</v>
       </c>
       <c r="Q99">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R99">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="S99">
         <v>0</v>
@@ -20809,7 +20809,7 @@
         <v>83</v>
       </c>
       <c r="C100" t="s">
-        <v>159</v>
+        <v>138</v>
       </c>
       <c r="D100" t="s">
         <v>186</v>
@@ -20848,13 +20848,13 @@
         <v>701</v>
       </c>
       <c r="P100">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="Q100">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="R100">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="S100">
         <v>0</v>
@@ -20994,7 +20994,7 @@
         <v>83</v>
       </c>
       <c r="C101" t="s">
-        <v>160</v>
+        <v>140</v>
       </c>
       <c r="D101" t="s">
         <v>186</v>
@@ -21179,10 +21179,10 @@
         <v>83</v>
       </c>
       <c r="C102" t="s">
-        <v>137</v>
+        <v>159</v>
       </c>
       <c r="D102" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E102" t="s">
         <v>288</v>
@@ -21364,7 +21364,7 @@
         <v>83</v>
       </c>
       <c r="C103" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="D103" t="s">
         <v>186</v>
@@ -21549,7 +21549,7 @@
         <v>83</v>
       </c>
       <c r="C104" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="D104" t="s">
         <v>186</v>
@@ -21734,10 +21734,10 @@
         <v>83</v>
       </c>
       <c r="C105" t="s">
-        <v>149</v>
+        <v>159</v>
       </c>
       <c r="D105" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E105" t="s">
         <v>291</v>
@@ -21773,13 +21773,13 @@
         <v>701</v>
       </c>
       <c r="P105">
-        <v>4.68</v>
+        <v>0</v>
       </c>
       <c r="Q105">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R105">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="S105">
         <v>0</v>
@@ -21919,7 +21919,7 @@
         <v>83</v>
       </c>
       <c r="C106" t="s">
-        <v>158</v>
+        <v>135</v>
       </c>
       <c r="D106" t="s">
         <v>185</v>
@@ -22104,7 +22104,7 @@
         <v>83</v>
       </c>
       <c r="C107" t="s">
-        <v>135</v>
+        <v>141</v>
       </c>
       <c r="D107" t="s">
         <v>185</v>
@@ -22289,7 +22289,7 @@
         <v>84</v>
       </c>
       <c r="C108" t="s">
-        <v>123</v>
+        <v>148</v>
       </c>
       <c r="D108" t="s">
         <v>186</v>
@@ -22328,13 +22328,13 @@
         <v>701</v>
       </c>
       <c r="P108">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="Q108">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="R108">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="S108">
         <v>0</v>
@@ -22474,7 +22474,7 @@
         <v>84</v>
       </c>
       <c r="C109" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="D109" t="s">
         <v>186</v>
@@ -22659,7 +22659,7 @@
         <v>84</v>
       </c>
       <c r="C110" t="s">
-        <v>146</v>
+        <v>123</v>
       </c>
       <c r="D110" t="s">
         <v>186</v>
@@ -22698,13 +22698,13 @@
         <v>701</v>
       </c>
       <c r="P110">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="Q110">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="R110">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="S110">
         <v>0</v>
@@ -22844,7 +22844,7 @@
         <v>85</v>
       </c>
       <c r="C111" t="s">
-        <v>119</v>
+        <v>149</v>
       </c>
       <c r="D111" t="s">
         <v>186</v>
@@ -23029,10 +23029,10 @@
         <v>85</v>
       </c>
       <c r="C112" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="D112" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E112" t="s">
         <v>298</v>
@@ -23214,7 +23214,7 @@
         <v>85</v>
       </c>
       <c r="C113" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="D113" t="s">
         <v>186</v>
@@ -23399,7 +23399,7 @@
         <v>85</v>
       </c>
       <c r="C114" t="s">
-        <v>141</v>
+        <v>119</v>
       </c>
       <c r="D114" t="s">
         <v>186</v>
@@ -23584,10 +23584,10 @@
         <v>85</v>
       </c>
       <c r="C115" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="D115" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E115" t="s">
         <v>301</v>
@@ -25619,7 +25619,7 @@
         <v>87</v>
       </c>
       <c r="C126" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="D126" t="s">
         <v>186</v>
@@ -26174,7 +26174,7 @@
         <v>87</v>
       </c>
       <c r="C129" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="D129" t="s">
         <v>186</v>
@@ -26359,10 +26359,10 @@
         <v>87</v>
       </c>
       <c r="C130" t="s">
-        <v>151</v>
+        <v>120</v>
       </c>
       <c r="D130" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E130" t="s">
         <v>316</v>
@@ -26544,7 +26544,7 @@
         <v>87</v>
       </c>
       <c r="C131" t="s">
-        <v>128</v>
+        <v>163</v>
       </c>
       <c r="D131" t="s">
         <v>186</v>
@@ -26729,7 +26729,7 @@
         <v>87</v>
       </c>
       <c r="C132" t="s">
-        <v>127</v>
+        <v>143</v>
       </c>
       <c r="D132" t="s">
         <v>186</v>
@@ -26914,7 +26914,7 @@
         <v>87</v>
       </c>
       <c r="C133" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="D133" t="s">
         <v>186</v>
@@ -27099,7 +27099,7 @@
         <v>87</v>
       </c>
       <c r="C134" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="D134" t="s">
         <v>186</v>
@@ -27284,7 +27284,7 @@
         <v>87</v>
       </c>
       <c r="C135" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="D135" t="s">
         <v>186</v>
@@ -27469,7 +27469,7 @@
         <v>87</v>
       </c>
       <c r="C136" t="s">
-        <v>151</v>
+        <v>164</v>
       </c>
       <c r="D136" t="s">
         <v>185</v>
@@ -27508,13 +27508,13 @@
         <v>701</v>
       </c>
       <c r="P136">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="Q136">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="R136">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="S136">
         <v>0</v>
@@ -27654,7 +27654,7 @@
         <v>87</v>
       </c>
       <c r="C137" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="D137" t="s">
         <v>186</v>
@@ -27839,7 +27839,7 @@
         <v>87</v>
       </c>
       <c r="C138" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="D138" t="s">
         <v>186</v>
@@ -28209,10 +28209,10 @@
         <v>87</v>
       </c>
       <c r="C140" t="s">
-        <v>165</v>
+        <v>145</v>
       </c>
       <c r="D140" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E140" t="s">
         <v>326</v>
@@ -28394,10 +28394,10 @@
         <v>87</v>
       </c>
       <c r="C141" t="s">
-        <v>151</v>
+        <v>161</v>
       </c>
       <c r="D141" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E141" t="s">
         <v>327</v>
@@ -28579,7 +28579,7 @@
         <v>87</v>
       </c>
       <c r="C142" t="s">
-        <v>125</v>
+        <v>165</v>
       </c>
       <c r="D142" t="s">
         <v>186</v>
@@ -28588,7 +28588,7 @@
         <v>328</v>
       </c>
       <c r="F142" t="s">
-        <v>585</v>
+        <v>284</v>
       </c>
       <c r="G142">
         <v>0</v>
@@ -28764,16 +28764,16 @@
         <v>87</v>
       </c>
       <c r="C143" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="D143" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E143" t="s">
         <v>329</v>
       </c>
       <c r="F143" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="G143">
         <v>0</v>
@@ -28803,13 +28803,13 @@
         <v>701</v>
       </c>
       <c r="P143">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Q143">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="R143">
-        <v>0</v>
+        <v>3.01</v>
       </c>
       <c r="S143">
         <v>0</v>
@@ -28949,7 +28949,7 @@
         <v>87</v>
       </c>
       <c r="C144" t="s">
-        <v>161</v>
+        <v>128</v>
       </c>
       <c r="D144" t="s">
         <v>186</v>
@@ -28958,7 +28958,7 @@
         <v>330</v>
       </c>
       <c r="F144" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="G144">
         <v>0</v>
@@ -29134,16 +29134,16 @@
         <v>87</v>
       </c>
       <c r="C145" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="D145" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E145" t="s">
         <v>331</v>
       </c>
       <c r="F145" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="G145">
         <v>0</v>
@@ -29173,13 +29173,13 @@
         <v>701</v>
       </c>
       <c r="P145">
-        <v>0</v>
+        <v>4.07</v>
       </c>
       <c r="Q145">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="R145">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="S145">
         <v>0</v>
@@ -29319,16 +29319,16 @@
         <v>87</v>
       </c>
       <c r="C146" t="s">
-        <v>164</v>
+        <v>151</v>
       </c>
       <c r="D146" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E146" t="s">
         <v>332</v>
       </c>
       <c r="F146" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="G146">
         <v>0</v>
@@ -29504,16 +29504,16 @@
         <v>87</v>
       </c>
       <c r="C147" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="D147" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E147" t="s">
         <v>333</v>
       </c>
       <c r="F147" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="G147">
         <v>0</v>
@@ -29543,13 +29543,13 @@
         <v>701</v>
       </c>
       <c r="P147">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="Q147">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="R147">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="S147">
         <v>0</v>
@@ -29689,7 +29689,7 @@
         <v>87</v>
       </c>
       <c r="C148" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="D148" t="s">
         <v>185</v>
@@ -29698,7 +29698,7 @@
         <v>334</v>
       </c>
       <c r="F148" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="G148">
         <v>0</v>
@@ -29728,13 +29728,13 @@
         <v>701</v>
       </c>
       <c r="P148">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="Q148">
-        <v>3.7</v>
+        <v>3.4</v>
       </c>
       <c r="R148">
-        <v>3.01</v>
+        <v>3.2</v>
       </c>
       <c r="S148">
         <v>0</v>
@@ -29874,7 +29874,7 @@
         <v>87</v>
       </c>
       <c r="C149" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="D149" t="s">
         <v>185</v>
@@ -29883,7 +29883,7 @@
         <v>335</v>
       </c>
       <c r="F149" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="G149">
         <v>0</v>
@@ -29913,13 +29913,13 @@
         <v>701</v>
       </c>
       <c r="P149">
-        <v>5.4</v>
+        <v>2.65</v>
       </c>
       <c r="Q149">
-        <v>4.6</v>
+        <v>3.6</v>
       </c>
       <c r="R149">
-        <v>1.51</v>
+        <v>2.4</v>
       </c>
       <c r="S149">
         <v>0</v>
@@ -30059,16 +30059,16 @@
         <v>87</v>
       </c>
       <c r="C150" t="s">
-        <v>166</v>
+        <v>125</v>
       </c>
       <c r="D150" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E150" t="s">
         <v>336</v>
       </c>
       <c r="F150" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="G150">
         <v>0</v>
@@ -30098,13 +30098,13 @@
         <v>701</v>
       </c>
       <c r="P150">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="Q150">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R150">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="S150">
         <v>0</v>
@@ -30244,16 +30244,16 @@
         <v>87</v>
       </c>
       <c r="C151" t="s">
-        <v>147</v>
+        <v>166</v>
       </c>
       <c r="D151" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E151" t="s">
         <v>337</v>
       </c>
       <c r="F151" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="G151">
         <v>0</v>
@@ -30432,13 +30432,13 @@
         <v>166</v>
       </c>
       <c r="D152" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E152" t="s">
         <v>338</v>
       </c>
       <c r="F152" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="G152">
         <v>0</v>
@@ -30468,13 +30468,13 @@
         <v>701</v>
       </c>
       <c r="P152">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="Q152">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="R152">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="S152">
         <v>0</v>
@@ -30617,13 +30617,13 @@
         <v>166</v>
       </c>
       <c r="D153" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E153" t="s">
         <v>339</v>
       </c>
       <c r="F153" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="G153">
         <v>0</v>
@@ -30653,13 +30653,13 @@
         <v>701</v>
       </c>
       <c r="P153">
-        <v>4.07</v>
+        <v>0</v>
       </c>
       <c r="Q153">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="R153">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="S153">
         <v>0</v>
@@ -30799,16 +30799,16 @@
         <v>87</v>
       </c>
       <c r="C154" t="s">
-        <v>166</v>
+        <v>161</v>
       </c>
       <c r="D154" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E154" t="s">
         <v>340</v>
       </c>
       <c r="F154" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="G154">
         <v>0</v>
@@ -30838,13 +30838,13 @@
         <v>701</v>
       </c>
       <c r="P154">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Q154">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="R154">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="S154">
         <v>0</v>
@@ -30984,16 +30984,16 @@
         <v>87</v>
       </c>
       <c r="C155" t="s">
-        <v>143</v>
+        <v>151</v>
       </c>
       <c r="D155" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E155" t="s">
         <v>341</v>
       </c>
       <c r="F155" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="G155">
         <v>0</v>
@@ -31169,16 +31169,16 @@
         <v>87</v>
       </c>
       <c r="C156" t="s">
-        <v>165</v>
+        <v>151</v>
       </c>
       <c r="D156" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E156" t="s">
         <v>342</v>
       </c>
       <c r="F156" t="s">
-        <v>290</v>
+        <v>598</v>
       </c>
       <c r="G156">
         <v>0</v>
@@ -32094,7 +32094,7 @@
         <v>89</v>
       </c>
       <c r="C161" t="s">
-        <v>168</v>
+        <v>157</v>
       </c>
       <c r="D161" t="s">
         <v>186</v>
@@ -32133,13 +32133,13 @@
         <v>701</v>
       </c>
       <c r="P161">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="Q161">
-        <v>0</v>
+        <v>4.32</v>
       </c>
       <c r="R161">
-        <v>0</v>
+        <v>4.52</v>
       </c>
       <c r="S161">
         <v>0</v>
@@ -32184,10 +32184,10 @@
         <v>0</v>
       </c>
       <c r="AG161">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AH161">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AI161">
         <v>0</v>
@@ -32279,7 +32279,7 @@
         <v>89</v>
       </c>
       <c r="C162" t="s">
-        <v>130</v>
+        <v>168</v>
       </c>
       <c r="D162" t="s">
         <v>186</v>
@@ -32464,7 +32464,7 @@
         <v>89</v>
       </c>
       <c r="C163" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="D163" t="s">
         <v>186</v>
@@ -32649,7 +32649,7 @@
         <v>89</v>
       </c>
       <c r="C164" t="s">
-        <v>157</v>
+        <v>130</v>
       </c>
       <c r="D164" t="s">
         <v>186</v>
@@ -32688,13 +32688,13 @@
         <v>701</v>
       </c>
       <c r="P164">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="Q164">
-        <v>4.32</v>
+        <v>0</v>
       </c>
       <c r="R164">
-        <v>4.52</v>
+        <v>0</v>
       </c>
       <c r="S164">
         <v>0</v>
@@ -32739,10 +32739,10 @@
         <v>0</v>
       </c>
       <c r="AG164">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AH164">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AI164">
         <v>0</v>
@@ -32834,7 +32834,7 @@
         <v>89</v>
       </c>
       <c r="C165" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="D165" t="s">
         <v>186</v>
@@ -33574,10 +33574,10 @@
         <v>90</v>
       </c>
       <c r="C169" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="D169" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E169" t="s">
         <v>355</v>
@@ -33613,13 +33613,13 @@
         <v>701</v>
       </c>
       <c r="P169">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="Q169">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="R169">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="S169">
         <v>0</v>
@@ -33944,7 +33944,7 @@
         <v>90</v>
       </c>
       <c r="C171" t="s">
-        <v>149</v>
+        <v>170</v>
       </c>
       <c r="D171" t="s">
         <v>186</v>
@@ -34129,7 +34129,7 @@
         <v>90</v>
       </c>
       <c r="C172" t="s">
-        <v>152</v>
+        <v>131</v>
       </c>
       <c r="D172" t="s">
         <v>186</v>
@@ -34168,13 +34168,13 @@
         <v>701</v>
       </c>
       <c r="P172">
-        <v>1.83</v>
+        <v>5</v>
       </c>
       <c r="Q172">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="R172">
-        <v>4.3</v>
+        <v>1.75</v>
       </c>
       <c r="S172">
         <v>0</v>
@@ -34314,7 +34314,7 @@
         <v>90</v>
       </c>
       <c r="C173" t="s">
-        <v>120</v>
+        <v>147</v>
       </c>
       <c r="D173" t="s">
         <v>186</v>
@@ -34499,10 +34499,10 @@
         <v>90</v>
       </c>
       <c r="C174" t="s">
-        <v>135</v>
+        <v>155</v>
       </c>
       <c r="D174" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E174" t="s">
         <v>360</v>
@@ -34538,13 +34538,13 @@
         <v>701</v>
       </c>
       <c r="P174">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="Q174">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R174">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="S174">
         <v>0</v>
@@ -34684,7 +34684,7 @@
         <v>90</v>
       </c>
       <c r="C175" t="s">
-        <v>170</v>
+        <v>120</v>
       </c>
       <c r="D175" t="s">
         <v>186</v>
@@ -35239,7 +35239,7 @@
         <v>92</v>
       </c>
       <c r="C178" t="s">
-        <v>136</v>
+        <v>160</v>
       </c>
       <c r="D178" t="s">
         <v>186</v>
@@ -35424,7 +35424,7 @@
         <v>92</v>
       </c>
       <c r="C179" t="s">
-        <v>160</v>
+        <v>136</v>
       </c>
       <c r="D179" t="s">
         <v>186</v>
@@ -35609,7 +35609,7 @@
         <v>92</v>
       </c>
       <c r="C180" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="D180" t="s">
         <v>185</v>
@@ -35794,7 +35794,7 @@
         <v>92</v>
       </c>
       <c r="C181" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="D181" t="s">
         <v>185</v>
@@ -35979,7 +35979,7 @@
         <v>93</v>
       </c>
       <c r="C182" t="s">
-        <v>148</v>
+        <v>172</v>
       </c>
       <c r="D182" t="s">
         <v>186</v>
@@ -36164,7 +36164,7 @@
         <v>93</v>
       </c>
       <c r="C183" t="s">
-        <v>159</v>
+        <v>172</v>
       </c>
       <c r="D183" t="s">
         <v>186</v>
@@ -36203,13 +36203,13 @@
         <v>701</v>
       </c>
       <c r="P183">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="Q183">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="R183">
-        <v>6.76</v>
+        <v>0</v>
       </c>
       <c r="S183">
         <v>0</v>
@@ -36349,7 +36349,7 @@
         <v>93</v>
       </c>
       <c r="C184" t="s">
-        <v>137</v>
+        <v>172</v>
       </c>
       <c r="D184" t="s">
         <v>186</v>
@@ -36534,7 +36534,7 @@
         <v>93</v>
       </c>
       <c r="C185" t="s">
-        <v>123</v>
+        <v>148</v>
       </c>
       <c r="D185" t="s">
         <v>186</v>
@@ -36573,13 +36573,13 @@
         <v>701</v>
       </c>
       <c r="P185">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Q185">
-        <v>3.66</v>
+        <v>0</v>
       </c>
       <c r="R185">
-        <v>3.36</v>
+        <v>0</v>
       </c>
       <c r="S185">
         <v>0</v>
@@ -36719,7 +36719,7 @@
         <v>93</v>
       </c>
       <c r="C186" t="s">
-        <v>154</v>
+        <v>172</v>
       </c>
       <c r="D186" t="s">
         <v>186</v>
@@ -36904,7 +36904,7 @@
         <v>93</v>
       </c>
       <c r="C187" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="D187" t="s">
         <v>186</v>
@@ -37089,7 +37089,7 @@
         <v>93</v>
       </c>
       <c r="C188" t="s">
-        <v>172</v>
+        <v>158</v>
       </c>
       <c r="D188" t="s">
         <v>186</v>
@@ -37128,13 +37128,13 @@
         <v>701</v>
       </c>
       <c r="P188">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="Q188">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R188">
-        <v>0</v>
+        <v>4.56</v>
       </c>
       <c r="S188">
         <v>0</v>
@@ -37459,10 +37459,10 @@
         <v>93</v>
       </c>
       <c r="C190" t="s">
-        <v>159</v>
+        <v>173</v>
       </c>
       <c r="D190" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E190" t="s">
         <v>376</v>
@@ -37498,13 +37498,13 @@
         <v>701</v>
       </c>
       <c r="P190">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="Q190">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="R190">
-        <v>4.56</v>
+        <v>0</v>
       </c>
       <c r="S190">
         <v>0</v>
@@ -37644,7 +37644,7 @@
         <v>93</v>
       </c>
       <c r="C191" t="s">
-        <v>172</v>
+        <v>140</v>
       </c>
       <c r="D191" t="s">
         <v>186</v>
@@ -37829,7 +37829,7 @@
         <v>93</v>
       </c>
       <c r="C192" t="s">
-        <v>172</v>
+        <v>158</v>
       </c>
       <c r="D192" t="s">
         <v>186</v>
@@ -37868,13 +37868,13 @@
         <v>701</v>
       </c>
       <c r="P192">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="Q192">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="R192">
-        <v>0</v>
+        <v>6.76</v>
       </c>
       <c r="S192">
         <v>0</v>
@@ -38014,10 +38014,10 @@
         <v>93</v>
       </c>
       <c r="C193" t="s">
-        <v>173</v>
+        <v>123</v>
       </c>
       <c r="D193" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E193" t="s">
         <v>379</v>
@@ -38053,13 +38053,13 @@
         <v>701</v>
       </c>
       <c r="P193">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Q193">
-        <v>0</v>
+        <v>3.66</v>
       </c>
       <c r="R193">
-        <v>0</v>
+        <v>3.36</v>
       </c>
       <c r="S193">
         <v>0</v>
@@ -38384,7 +38384,7 @@
         <v>93</v>
       </c>
       <c r="C195" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="D195" t="s">
         <v>185</v>
@@ -38569,7 +38569,7 @@
         <v>93</v>
       </c>
       <c r="C196" t="s">
-        <v>172</v>
+        <v>154</v>
       </c>
       <c r="D196" t="s">
         <v>186</v>
@@ -38754,7 +38754,7 @@
         <v>94</v>
       </c>
       <c r="C197" t="s">
-        <v>175</v>
+        <v>124</v>
       </c>
       <c r="D197" t="s">
         <v>186</v>
@@ -39124,7 +39124,7 @@
         <v>94</v>
       </c>
       <c r="C199" t="s">
-        <v>161</v>
+        <v>175</v>
       </c>
       <c r="D199" t="s">
         <v>186</v>
@@ -39494,10 +39494,10 @@
         <v>94</v>
       </c>
       <c r="C201" t="s">
-        <v>127</v>
+        <v>145</v>
       </c>
       <c r="D201" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E201" t="s">
         <v>387</v>
@@ -39864,7 +39864,7 @@
         <v>94</v>
       </c>
       <c r="C203" t="s">
-        <v>147</v>
+        <v>176</v>
       </c>
       <c r="D203" t="s">
         <v>185</v>
@@ -40049,10 +40049,10 @@
         <v>94</v>
       </c>
       <c r="C204" t="s">
-        <v>176</v>
+        <v>161</v>
       </c>
       <c r="D204" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E204" t="s">
         <v>390</v>
@@ -40234,7 +40234,7 @@
         <v>95</v>
       </c>
       <c r="C205" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="D205" t="s">
         <v>186</v>
@@ -40604,7 +40604,7 @@
         <v>96</v>
       </c>
       <c r="C207" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="D207" t="s">
         <v>186</v>
@@ -40789,10 +40789,10 @@
         <v>97</v>
       </c>
       <c r="C208" t="s">
-        <v>177</v>
+        <v>170</v>
       </c>
       <c r="D208" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E208" t="s">
         <v>394</v>
@@ -40974,7 +40974,7 @@
         <v>97</v>
       </c>
       <c r="C209" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="D209" t="s">
         <v>186</v>
@@ -41344,7 +41344,7 @@
         <v>97</v>
       </c>
       <c r="C211" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="D211" t="s">
         <v>185</v>
@@ -41529,10 +41529,10 @@
         <v>97</v>
       </c>
       <c r="C212" t="s">
-        <v>171</v>
+        <v>178</v>
       </c>
       <c r="D212" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E212" t="s">
         <v>398</v>
@@ -41714,7 +41714,7 @@
         <v>98</v>
       </c>
       <c r="C213" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="D213" t="s">
         <v>186</v>
@@ -42272,7 +42272,7 @@
         <v>180</v>
       </c>
       <c r="D216" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E216" t="s">
         <v>402</v>
@@ -42308,13 +42308,13 @@
         <v>701</v>
       </c>
       <c r="P216">
-        <v>2.48</v>
+        <v>5.3</v>
       </c>
       <c r="Q216">
-        <v>3.5</v>
+        <v>3.73</v>
       </c>
       <c r="R216">
-        <v>3.07</v>
+        <v>1.71</v>
       </c>
       <c r="S216">
         <v>0</v>
@@ -42353,10 +42353,10 @@
         <v>0</v>
       </c>
       <c r="AE216">
-        <v>1.8</v>
+        <v>1.95</v>
       </c>
       <c r="AF216">
-        <v>1.9</v>
+        <v>1.73</v>
       </c>
       <c r="AG216">
         <v>0</v>
@@ -42454,10 +42454,10 @@
         <v>100</v>
       </c>
       <c r="C217" t="s">
-        <v>181</v>
+        <v>146</v>
       </c>
       <c r="D217" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E217" t="s">
         <v>403</v>
@@ -42493,13 +42493,13 @@
         <v>701</v>
       </c>
       <c r="P217">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Q217">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="R217">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="S217">
         <v>0</v>
@@ -42538,10 +42538,10 @@
         <v>0</v>
       </c>
       <c r="AE217">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AF217">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AG217">
         <v>0</v>
@@ -42639,7 +42639,7 @@
         <v>100</v>
       </c>
       <c r="C218" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="D218" t="s">
         <v>186</v>
@@ -42678,13 +42678,13 @@
         <v>701</v>
       </c>
       <c r="P218">
-        <v>1.59</v>
+        <v>2.48</v>
       </c>
       <c r="Q218">
-        <v>4.73</v>
+        <v>3.5</v>
       </c>
       <c r="R218">
-        <v>5.79</v>
+        <v>3.07</v>
       </c>
       <c r="S218">
         <v>0</v>
@@ -42723,16 +42723,16 @@
         <v>0</v>
       </c>
       <c r="AE218">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AF218">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AG218">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AH218">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AI218">
         <v>0</v>
@@ -42824,7 +42824,7 @@
         <v>100</v>
       </c>
       <c r="C219" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="D219" t="s">
         <v>185</v>
@@ -42863,13 +42863,13 @@
         <v>701</v>
       </c>
       <c r="P219">
-        <v>5.3</v>
+        <v>0</v>
       </c>
       <c r="Q219">
-        <v>3.73</v>
+        <v>0</v>
       </c>
       <c r="R219">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="S219">
         <v>0</v>
@@ -42908,10 +42908,10 @@
         <v>0</v>
       </c>
       <c r="AE219">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AF219">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AG219">
         <v>0</v>
@@ -43009,10 +43009,10 @@
         <v>100</v>
       </c>
       <c r="C220" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="D220" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E220" t="s">
         <v>406</v>
@@ -43048,13 +43048,13 @@
         <v>701</v>
       </c>
       <c r="P220">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="Q220">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="R220">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="S220">
         <v>0</v>
@@ -43093,10 +43093,10 @@
         <v>0</v>
       </c>
       <c r="AE220">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AF220">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AG220">
         <v>0</v>
@@ -43194,10 +43194,10 @@
         <v>100</v>
       </c>
       <c r="C221" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="D221" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E221" t="s">
         <v>407</v>
@@ -43233,13 +43233,13 @@
         <v>701</v>
       </c>
       <c r="P221">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="Q221">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="R221">
-        <v>2.96</v>
+        <v>0</v>
       </c>
       <c r="S221">
         <v>0</v>
@@ -43278,10 +43278,10 @@
         <v>0</v>
       </c>
       <c r="AE221">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AF221">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AG221">
         <v>0</v>
@@ -43379,7 +43379,7 @@
         <v>100</v>
       </c>
       <c r="C222" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="D222" t="s">
         <v>185</v>
@@ -43418,13 +43418,13 @@
         <v>701</v>
       </c>
       <c r="P222">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Q222">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="R222">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="S222">
         <v>0</v>
@@ -43463,10 +43463,10 @@
         <v>0</v>
       </c>
       <c r="AE222">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AF222">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG222">
         <v>0</v>
@@ -43564,10 +43564,10 @@
         <v>100</v>
       </c>
       <c r="C223" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="D223" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E223" t="s">
         <v>409</v>
@@ -43603,13 +43603,13 @@
         <v>701</v>
       </c>
       <c r="P223">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="Q223">
-        <v>0</v>
+        <v>3.76</v>
       </c>
       <c r="R223">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="S223">
         <v>0</v>
@@ -43648,10 +43648,10 @@
         <v>0</v>
       </c>
       <c r="AE223">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AF223">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG223">
         <v>0</v>
@@ -43749,7 +43749,7 @@
         <v>100</v>
       </c>
       <c r="C224" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="D224" t="s">
         <v>186</v>
@@ -43788,13 +43788,13 @@
         <v>701</v>
       </c>
       <c r="P224">
-        <v>3.8</v>
+        <v>3.17</v>
       </c>
       <c r="Q224">
-        <v>3.78</v>
+        <v>3.68</v>
       </c>
       <c r="R224">
-        <v>2.05</v>
+        <v>2.34</v>
       </c>
       <c r="S224">
         <v>0</v>
@@ -43833,10 +43833,10 @@
         <v>0</v>
       </c>
       <c r="AE224">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="AF224">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="AG224">
         <v>0</v>
@@ -43934,10 +43934,10 @@
         <v>100</v>
       </c>
       <c r="C225" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="D225" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E225" t="s">
         <v>411</v>
@@ -43973,13 +43973,13 @@
         <v>701</v>
       </c>
       <c r="P225">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Q225">
-        <v>0</v>
+        <v>9.15</v>
       </c>
       <c r="R225">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="S225">
         <v>0</v>
@@ -44024,10 +44024,10 @@
         <v>0</v>
       </c>
       <c r="AG225">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AH225">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AI225">
         <v>0</v>
@@ -44119,7 +44119,7 @@
         <v>100</v>
       </c>
       <c r="C226" t="s">
-        <v>148</v>
+        <v>181</v>
       </c>
       <c r="D226" t="s">
         <v>186</v>
@@ -44158,13 +44158,13 @@
         <v>701</v>
       </c>
       <c r="P226">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="Q226">
-        <v>0</v>
+        <v>4.73</v>
       </c>
       <c r="R226">
-        <v>0</v>
+        <v>5.79</v>
       </c>
       <c r="S226">
         <v>0</v>
@@ -44209,10 +44209,10 @@
         <v>0</v>
       </c>
       <c r="AG226">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AH226">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AI226">
         <v>0</v>
@@ -44304,7 +44304,7 @@
         <v>100</v>
       </c>
       <c r="C227" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="D227" t="s">
         <v>186</v>
@@ -44343,13 +44343,13 @@
         <v>701</v>
       </c>
       <c r="P227">
-        <v>4.68</v>
+        <v>3.8</v>
       </c>
       <c r="Q227">
-        <v>4.32</v>
+        <v>3.78</v>
       </c>
       <c r="R227">
-        <v>1.76</v>
+        <v>2.05</v>
       </c>
       <c r="S227">
         <v>0</v>
@@ -44388,10 +44388,10 @@
         <v>0</v>
       </c>
       <c r="AE227">
-        <v>1.58</v>
+        <v>1.73</v>
       </c>
       <c r="AF227">
-        <v>2.25</v>
+        <v>1.98</v>
       </c>
       <c r="AG227">
         <v>0</v>
@@ -44489,10 +44489,10 @@
         <v>100</v>
       </c>
       <c r="C228" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="D228" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E228" t="s">
         <v>414</v>
@@ -44528,13 +44528,13 @@
         <v>701</v>
       </c>
       <c r="P228">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="Q228">
-        <v>3.76</v>
+        <v>0</v>
       </c>
       <c r="R228">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="S228">
         <v>0</v>
@@ -44573,10 +44573,10 @@
         <v>0</v>
       </c>
       <c r="AE228">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AF228">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AG228">
         <v>0</v>
@@ -44674,10 +44674,10 @@
         <v>100</v>
       </c>
       <c r="C229" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="D229" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E229" t="s">
         <v>415</v>
@@ -44713,13 +44713,13 @@
         <v>701</v>
       </c>
       <c r="P229">
-        <v>3.17</v>
+        <v>0</v>
       </c>
       <c r="Q229">
-        <v>3.68</v>
+        <v>0</v>
       </c>
       <c r="R229">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="S229">
         <v>0</v>
@@ -44758,10 +44758,10 @@
         <v>0</v>
       </c>
       <c r="AE229">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AF229">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AG229">
         <v>0</v>
@@ -44859,7 +44859,7 @@
         <v>100</v>
       </c>
       <c r="C230" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="D230" t="s">
         <v>186</v>
@@ -44898,13 +44898,13 @@
         <v>701</v>
       </c>
       <c r="P230">
-        <v>1.18</v>
+        <v>4.68</v>
       </c>
       <c r="Q230">
-        <v>9.15</v>
+        <v>4.32</v>
       </c>
       <c r="R230">
-        <v>17</v>
+        <v>1.76</v>
       </c>
       <c r="S230">
         <v>0</v>
@@ -44943,16 +44943,16 @@
         <v>0</v>
       </c>
       <c r="AE230">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AF230">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AG230">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AH230">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AI230">
         <v>0</v>
@@ -45599,7 +45599,7 @@
         <v>102</v>
       </c>
       <c r="C234" t="s">
-        <v>178</v>
+        <v>173</v>
       </c>
       <c r="D234" t="s">
         <v>185</v>
@@ -45784,7 +45784,7 @@
         <v>102</v>
       </c>
       <c r="C235" t="s">
-        <v>174</v>
+        <v>179</v>
       </c>
       <c r="D235" t="s">
         <v>185</v>
@@ -45969,10 +45969,10 @@
         <v>102</v>
       </c>
       <c r="C236" t="s">
-        <v>170</v>
+        <v>178</v>
       </c>
       <c r="D236" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E236" t="s">
         <v>422</v>
@@ -46154,7 +46154,7 @@
         <v>102</v>
       </c>
       <c r="C237" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="D237" t="s">
         <v>185</v>
@@ -46339,10 +46339,10 @@
         <v>102</v>
       </c>
       <c r="C238" t="s">
-        <v>178</v>
+        <v>170</v>
       </c>
       <c r="D238" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E238" t="s">
         <v>424</v>
@@ -47079,7 +47079,7 @@
         <v>105</v>
       </c>
       <c r="C242" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="D242" t="s">
         <v>185</v>
@@ -47264,7 +47264,7 @@
         <v>106</v>
       </c>
       <c r="C243" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="D243" t="s">
         <v>185</v>
@@ -47449,7 +47449,7 @@
         <v>106</v>
       </c>
       <c r="C244" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="D244" t="s">
         <v>185</v>
@@ -47488,13 +47488,13 @@
         <v>701</v>
       </c>
       <c r="P244">
-        <v>2.26</v>
+        <v>1.79</v>
       </c>
       <c r="Q244">
-        <v>3.22</v>
+        <v>3.62</v>
       </c>
       <c r="R244">
-        <v>3.46</v>
+        <v>4.84</v>
       </c>
       <c r="S244">
         <v>0</v>
@@ -47533,10 +47533,10 @@
         <v>0</v>
       </c>
       <c r="AE244">
-        <v>2.25</v>
+        <v>1.87</v>
       </c>
       <c r="AF244">
-        <v>1.57</v>
+        <v>1.8</v>
       </c>
       <c r="AG244">
         <v>0</v>
@@ -47634,7 +47634,7 @@
         <v>106</v>
       </c>
       <c r="C245" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="D245" t="s">
         <v>185</v>
@@ -47819,7 +47819,7 @@
         <v>106</v>
       </c>
       <c r="C246" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="D246" t="s">
         <v>185</v>
@@ -47858,13 +47858,13 @@
         <v>701</v>
       </c>
       <c r="P246">
-        <v>1.79</v>
+        <v>2.26</v>
       </c>
       <c r="Q246">
-        <v>3.62</v>
+        <v>3.22</v>
       </c>
       <c r="R246">
-        <v>4.84</v>
+        <v>3.46</v>
       </c>
       <c r="S246">
         <v>0</v>
@@ -47903,10 +47903,10 @@
         <v>0</v>
       </c>
       <c r="AE246">
-        <v>1.87</v>
+        <v>2.25</v>
       </c>
       <c r="AF246">
-        <v>1.8</v>
+        <v>1.57</v>
       </c>
       <c r="AG246">
         <v>0</v>
@@ -48189,7 +48189,7 @@
         <v>108</v>
       </c>
       <c r="C248" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="D248" t="s">
         <v>185</v>
@@ -48374,7 +48374,7 @@
         <v>108</v>
       </c>
       <c r="C249" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="D249" t="s">
         <v>185</v>
@@ -48559,7 +48559,7 @@
         <v>109</v>
       </c>
       <c r="C250" t="s">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="D250" t="s">
         <v>185</v>
@@ -48929,7 +48929,7 @@
         <v>109</v>
       </c>
       <c r="C252" t="s">
-        <v>178</v>
+        <v>173</v>
       </c>
       <c r="D252" t="s">
         <v>185</v>
@@ -49299,7 +49299,7 @@
         <v>111</v>
       </c>
       <c r="C254" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="D254" t="s">
         <v>185</v>
@@ -49484,7 +49484,7 @@
         <v>111</v>
       </c>
       <c r="C255" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="D255" t="s">
         <v>185</v>

--- a/jogos_2026-05-10.xlsx
+++ b/jogos_2026-05-10.xlsx
@@ -361,21 +361,21 @@
     <t>22:00</t>
   </si>
   <si>
+    <t>South Korea K League 2</t>
+  </si>
+  <si>
     <t>Australia New South Wales NPL</t>
   </si>
   <si>
     <t>South Korea K League 1</t>
   </si>
   <si>
-    <t>South Korea K League 2</t>
+    <t>China China League One</t>
   </si>
   <si>
     <t>Russia FNL</t>
   </si>
   <si>
-    <t>China China League One</t>
-  </si>
-  <si>
     <t>Czech Republic FNL</t>
   </si>
   <si>
@@ -391,120 +391,123 @@
     <t>Spain Primera Division Women</t>
   </si>
   <si>
+    <t>Ethiopia Ethiopia Premier League</t>
+  </si>
+  <si>
+    <t>Vietnam V.League 1</t>
+  </si>
+  <si>
     <t>Portugal Liga 3</t>
   </si>
   <si>
-    <t>Ethiopia Ethiopia Premier League</t>
+    <t>Kazakhstan Kazakhstan Premier League</t>
   </si>
   <si>
     <t>Poland 1. Liga</t>
   </si>
   <si>
-    <t>Kazakhstan Kazakhstan Premier League</t>
-  </si>
-  <si>
-    <t>Vietnam V.League 1</t>
-  </si>
-  <si>
     <t>Poland Ekstraklasa</t>
   </si>
   <si>
     <t>Italy Serie A</t>
   </si>
   <si>
+    <t>Sweden Damallsvenskan</t>
+  </si>
+  <si>
+    <t>Scotland Premiership</t>
+  </si>
+  <si>
     <t>Thailand Thai League T1</t>
   </si>
   <si>
-    <t>Scotland Premiership</t>
-  </si>
-  <si>
-    <t>Sweden Damallsvenskan</t>
+    <t>Bulgaria First League</t>
   </si>
   <si>
     <t>Lithuania A Lyga</t>
   </si>
   <si>
-    <t>Bulgaria First League</t>
+    <t>Germany 2. Bundesliga</t>
+  </si>
+  <si>
+    <t>Singapore S.League</t>
+  </si>
+  <si>
+    <t>Germany 3. Liga</t>
   </si>
   <si>
     <t>Belgium Pro League</t>
   </si>
   <si>
-    <t>Singapore S.League</t>
-  </si>
-  <si>
-    <t>Germany 2. Bundesliga</t>
+    <t>India Indian Super League</t>
   </si>
   <si>
     <t>Estonia Meistriliiga</t>
   </si>
   <si>
-    <t>India Indian Super League</t>
-  </si>
-  <si>
-    <t>Germany 3. Liga</t>
-  </si>
-  <si>
     <t>Croatia Druga HNL</t>
   </si>
   <si>
+    <t>Georgia Erovnuli Liga</t>
+  </si>
+  <si>
+    <t>Denmark Superliga</t>
+  </si>
+  <si>
+    <t>Switzerland Super League</t>
+  </si>
+  <si>
+    <t>Spain Segunda División</t>
+  </si>
+  <si>
     <t>Sweden Allsvenskan</t>
   </si>
   <si>
-    <t>Denmark Superliga</t>
-  </si>
-  <si>
     <t>Spain La Liga</t>
   </si>
   <si>
-    <t>Georgia Erovnuli Liga</t>
-  </si>
-  <si>
-    <t>Switzerland Super League</t>
-  </si>
-  <si>
-    <t>Spain Segunda División</t>
-  </si>
-  <si>
     <t>Malaysia Super League</t>
   </si>
   <si>
     <t>Norway Eliteserien</t>
   </si>
   <si>
+    <t>Romania Liga I</t>
+  </si>
+  <si>
+    <t>Slovenia PrvaLiga</t>
+  </si>
+  <si>
     <t>Czech Republic First League</t>
   </si>
   <si>
-    <t>Romania Liga I</t>
+    <t>England Premier League</t>
   </si>
   <si>
     <t>Azerbaijan Premyer Liqası</t>
   </si>
   <si>
-    <t>Slovenia PrvaLiga</t>
-  </si>
-  <si>
-    <t>England Premier League</t>
-  </si>
-  <si>
     <t>Germany Bundesliga</t>
   </si>
   <si>
+    <t>Greece Super League</t>
+  </si>
+  <si>
     <t>Faroe Islands Faroe Islands Premier League</t>
   </si>
   <si>
-    <t>Greece Super League</t>
+    <t>Croatia Prva HNL</t>
   </si>
   <si>
     <t>Hungary NB II</t>
   </si>
   <si>
-    <t>Croatia Prva HNL</t>
-  </si>
-  <si>
     <t>Netherlands Eredivisie</t>
   </si>
   <si>
+    <t>Austria Bundesliga</t>
+  </si>
+  <si>
     <t>FYR Macedonia First Football League</t>
   </si>
   <si>
@@ -514,9 +517,6 @@
     <t>Norway First Division</t>
   </si>
   <si>
-    <t>Austria Bundesliga</t>
-  </si>
-  <si>
     <t>UAE Arabian Gulf League</t>
   </si>
   <si>
@@ -556,12 +556,12 @@
     <t>France Ligue 1</t>
   </si>
   <si>
+    <t>Bolivia LFPB</t>
+  </si>
+  <si>
     <t>Brazil Serie A</t>
   </si>
   <si>
-    <t>Bolivia LFPB</t>
-  </si>
-  <si>
     <t>Brazil Serie B</t>
   </si>
   <si>
@@ -580,21 +580,24 @@
     <t>2025</t>
   </si>
   <si>
+    <t>Seongnam</t>
+  </si>
+  <si>
     <t>Rockdale City Suns</t>
   </si>
   <si>
     <t>Ulsan</t>
   </si>
   <si>
-    <t>Seongnam</t>
-  </si>
-  <si>
     <t>Blacktown City</t>
   </si>
   <si>
     <t>APIA Leichhardt Tigers</t>
   </si>
   <si>
+    <t>Shaanxi Union</t>
+  </si>
+  <si>
     <t>Ufa</t>
   </si>
   <si>
@@ -604,24 +607,21 @@
     <t>Dalian Huayi</t>
   </si>
   <si>
-    <t>Shaanxi Union</t>
+    <t>Ansan Greeners</t>
   </si>
   <si>
     <t>Busan I'Park</t>
   </si>
   <si>
-    <t>Ansan Greeners</t>
-  </si>
-  <si>
     <t>Anyang</t>
   </si>
   <si>
+    <t>Viktoria Žižkov</t>
+  </si>
+  <si>
     <t>Slavia Praha U21</t>
   </si>
   <si>
-    <t>Viktoria Žižkov</t>
-  </si>
-  <si>
     <t>Persija</t>
   </si>
   <si>
@@ -634,231 +634,231 @@
     <t>Qingdao Youth Island</t>
   </si>
   <si>
+    <t>Sichuan Jiuniu</t>
+  </si>
+  <si>
+    <t>Levante W</t>
+  </si>
+  <si>
+    <t>Sokol Saratov</t>
+  </si>
+  <si>
+    <t>Sheger Ketema</t>
+  </si>
+  <si>
     <t>Gyeongnam</t>
   </si>
   <si>
-    <t>Levante W</t>
+    <t>Hoang Anh Gia Lai</t>
   </si>
   <si>
     <t>Amarante</t>
   </si>
   <si>
-    <t>Sokol Saratov</t>
-  </si>
-  <si>
-    <t>Sheger Ketema</t>
+    <t>Ulytau</t>
   </si>
   <si>
     <t>Polonia Warszawa</t>
   </si>
   <si>
-    <t>Ulytau</t>
-  </si>
-  <si>
-    <t>Hoang Anh Gia Lai</t>
-  </si>
-  <si>
-    <t>Sichuan Jiuniu</t>
-  </si>
-  <si>
     <t>Piast Gliwice</t>
   </si>
   <si>
     <t>Hellas Verona</t>
   </si>
   <si>
+    <t>Shenzhen Juniors</t>
+  </si>
+  <si>
+    <t>Piteå Women</t>
+  </si>
+  <si>
+    <t>Celtic</t>
+  </si>
+  <si>
+    <t>Sukhothai</t>
+  </si>
+  <si>
+    <t>Chiangrai United</t>
+  </si>
+  <si>
+    <t>Bangkok Glass</t>
+  </si>
+  <si>
     <t>Kanchanaburi</t>
   </si>
   <si>
-    <t>Celtic</t>
+    <t>Hà Nội II</t>
+  </si>
+  <si>
+    <t>Shenyang Urban</t>
   </si>
   <si>
     <t>Buriram United</t>
   </si>
   <si>
+    <t>Chonburi</t>
+  </si>
+  <si>
     <t>Ayutthaya United</t>
   </si>
   <si>
-    <t>Bangkok Glass</t>
-  </si>
-  <si>
-    <t>Chonburi</t>
+    <t>Ho Chi Minh City</t>
+  </si>
+  <si>
+    <t>Altay</t>
   </si>
   <si>
     <t>Rayong</t>
   </si>
   <si>
-    <t>Shenyang Urban</t>
-  </si>
-  <si>
-    <t>Piteå Women</t>
-  </si>
-  <si>
-    <t>Shenzhen Juniors</t>
-  </si>
-  <si>
-    <t>Altay</t>
-  </si>
-  <si>
-    <t>Sukhothai</t>
-  </si>
-  <si>
-    <t>Chiangrai United</t>
-  </si>
-  <si>
-    <t>Hà Nội II</t>
-  </si>
-  <si>
-    <t>Ho Chi Minh City</t>
+    <t>Spartak Varna</t>
   </si>
   <si>
     <t>Sūduva</t>
   </si>
   <si>
-    <t>Spartak Varna</t>
+    <t>Preußen Münster</t>
+  </si>
+  <si>
+    <t>Hougang United</t>
+  </si>
+  <si>
+    <t>Hertha BSC</t>
   </si>
   <si>
     <t>Dongguan United</t>
   </si>
   <si>
+    <t>Fortuna Düsseldorf</t>
+  </si>
+  <si>
+    <t>Havelse</t>
+  </si>
+  <si>
     <t>KAA Gent</t>
   </si>
   <si>
-    <t>Hougang United</t>
+    <t>Kerala Blasters</t>
   </si>
   <si>
     <t>Nantong Zhiyun</t>
   </si>
   <si>
-    <t>Fortuna Düsseldorf</t>
+    <t>Home United</t>
   </si>
   <si>
     <t>Nõmme Kalju</t>
   </si>
   <si>
-    <t>Kerala Blasters</t>
-  </si>
-  <si>
-    <t>Home United</t>
-  </si>
-  <si>
-    <t>Preußen Münster</t>
-  </si>
-  <si>
-    <t>Hertha BSC</t>
-  </si>
-  <si>
-    <t>Havelse</t>
+    <t>Zhejiang FC</t>
   </si>
   <si>
     <t>Beijing Guoan</t>
   </si>
   <si>
-    <t>Zhejiang FC</t>
-  </si>
-  <si>
     <t>Hrvace</t>
   </si>
   <si>
+    <t>Aktobe</t>
+  </si>
+  <si>
+    <t>Qingdao Jonoon</t>
+  </si>
+  <si>
+    <t>Meshakhte</t>
+  </si>
+  <si>
+    <t>Nordsjælland</t>
+  </si>
+  <si>
+    <t>Lugano</t>
+  </si>
+  <si>
+    <t>FC Andorra</t>
+  </si>
+  <si>
+    <t>Vejle</t>
+  </si>
+  <si>
+    <t>AIK</t>
+  </si>
+  <si>
+    <t>RCD Mallorca</t>
+  </si>
+  <si>
+    <t>PSIM Yogyakarta</t>
+  </si>
+  <si>
+    <t>Zenit</t>
+  </si>
+  <si>
+    <t>Bahardar</t>
+  </si>
+  <si>
     <t>Kalmar</t>
   </si>
   <si>
-    <t>Aktobe</t>
-  </si>
-  <si>
-    <t>AIK</t>
-  </si>
-  <si>
-    <t>Nordsjælland</t>
-  </si>
-  <si>
-    <t>PSIM Yogyakarta</t>
-  </si>
-  <si>
-    <t>Zenit</t>
-  </si>
-  <si>
-    <t>RCD Mallorca</t>
-  </si>
-  <si>
-    <t>Meshakhte</t>
-  </si>
-  <si>
-    <t>Vejle</t>
-  </si>
-  <si>
-    <t>Bahardar</t>
-  </si>
-  <si>
-    <t>Qingdao Jonoon</t>
-  </si>
-  <si>
-    <t>Lugano</t>
-  </si>
-  <si>
-    <t>FC Andorra</t>
+    <t>Kuala Lumpur</t>
   </si>
   <si>
     <t>Công An Nhân Dân</t>
   </si>
   <si>
-    <t>Kuala Lumpur</t>
+    <t>Rosenborg</t>
   </si>
   <si>
     <t>Tychy 71</t>
   </si>
   <si>
-    <t>Rosenborg</t>
-  </si>
-  <si>
     <t>Baník Ostrava U21</t>
   </si>
   <si>
     <t>Wisła Płock</t>
   </si>
   <si>
+    <t>Botoşani</t>
+  </si>
+  <si>
+    <t>NK Primorje</t>
+  </si>
+  <si>
+    <t>Pardubice</t>
+  </si>
+  <si>
+    <t>Crystal Palace</t>
+  </si>
+  <si>
+    <t>Burnley</t>
+  </si>
+  <si>
+    <t>Kelantan United</t>
+  </si>
+  <si>
+    <t>Sigma Olomouc</t>
+  </si>
+  <si>
+    <t>Nottingham Forest</t>
+  </si>
+  <si>
+    <t>Fiorentina</t>
+  </si>
+  <si>
+    <t>Arba Minch Kenema</t>
+  </si>
+  <si>
+    <t>Uppsala W</t>
+  </si>
+  <si>
     <t>Astana</t>
   </si>
   <si>
-    <t>Fiorentina</t>
-  </si>
-  <si>
-    <t>Pardubice</t>
-  </si>
-  <si>
-    <t>Sigma Olomouc</t>
-  </si>
-  <si>
-    <t>Uppsala W</t>
+    <t>Turan</t>
   </si>
   <si>
     <t>Cremonese</t>
   </si>
   <si>
-    <t>Botoşani</t>
-  </si>
-  <si>
-    <t>Turan</t>
-  </si>
-  <si>
-    <t>NK Primorje</t>
-  </si>
-  <si>
-    <t>Kelantan United</t>
-  </si>
-  <si>
-    <t>Burnley</t>
-  </si>
-  <si>
-    <t>Nottingham Forest</t>
-  </si>
-  <si>
-    <t>Crystal Palace</t>
-  </si>
-  <si>
-    <t>Arba Minch Kenema</t>
-  </si>
-  <si>
     <t>Hamburger SV</t>
   </si>
   <si>
@@ -868,58 +868,67 @@
     <t>Royal Antwerp FC</t>
   </si>
   <si>
+    <t>Aris</t>
+  </si>
+  <si>
+    <t>Banga</t>
+  </si>
+  <si>
+    <t>Nõmme United</t>
+  </si>
+  <si>
+    <t>Volos NFC</t>
+  </si>
+  <si>
+    <t>EB - Streymur</t>
+  </si>
+  <si>
+    <t>Silkeborg</t>
+  </si>
+  <si>
+    <t>NorthEast United</t>
+  </si>
+  <si>
+    <t>Osijek</t>
+  </si>
+  <si>
     <t>B36</t>
   </si>
   <si>
-    <t>EB - Streymur</t>
-  </si>
-  <si>
-    <t>Nõmme United</t>
-  </si>
-  <si>
-    <t>Volos NFC</t>
-  </si>
-  <si>
-    <t>Silkeborg</t>
-  </si>
-  <si>
     <t>Honvéd W</t>
   </si>
   <si>
-    <t>Osijek</t>
-  </si>
-  <si>
-    <t>Aris</t>
-  </si>
-  <si>
-    <t>NorthEast United</t>
-  </si>
-  <si>
-    <t>Banga</t>
+    <t>Athletic Club Bilbao</t>
+  </si>
+  <si>
+    <t>Leganés</t>
   </si>
   <si>
     <t>Akhmat Grozny</t>
   </si>
   <si>
-    <t>Athletic Club Bilbao</t>
-  </si>
-  <si>
-    <t>Leganés</t>
+    <t>Young Boys</t>
+  </si>
+  <si>
+    <t>Sion</t>
+  </si>
+  <si>
+    <t>Neftekhimik</t>
   </si>
   <si>
     <t>Häcken</t>
   </si>
   <si>
-    <t>Sion</t>
-  </si>
-  <si>
-    <t>Neftekhimik</t>
-  </si>
-  <si>
     <t>Viktoria Köln</t>
   </si>
   <si>
-    <t>Young Boys</t>
+    <t>Go Ahead Eagles</t>
+  </si>
+  <si>
+    <t>Feyenoord</t>
+  </si>
+  <si>
+    <t>Ajax</t>
   </si>
   <si>
     <t>NAC Breda</t>
@@ -928,264 +937,255 @@
     <t>Twente</t>
   </si>
   <si>
-    <t>Go Ahead Eagles</t>
-  </si>
-  <si>
-    <t>Feyenoord</t>
+    <t>Fortuna Sittard</t>
   </si>
   <si>
     <t>Telstar</t>
   </si>
   <si>
+    <t>Excelsior</t>
+  </si>
+  <si>
     <t>Groningen</t>
   </si>
   <si>
-    <t>Fortuna Sittard</t>
-  </si>
-  <si>
-    <t>Ajax</t>
-  </si>
-  <si>
-    <t>Excelsior</t>
+    <t>LASK Linz</t>
+  </si>
+  <si>
+    <t>Rapid Wien</t>
+  </si>
+  <si>
+    <t>Hartberg</t>
+  </si>
+  <si>
+    <t>Pelister</t>
+  </si>
+  <si>
+    <t>Pogoń Siedlce</t>
+  </si>
+  <si>
+    <t>Makedonija GjP</t>
+  </si>
+  <si>
+    <t>Shkendija</t>
+  </si>
+  <si>
+    <t>Aresimi</t>
+  </si>
+  <si>
+    <t>Vardar</t>
+  </si>
+  <si>
+    <t>Zbrojovka Brno</t>
+  </si>
+  <si>
+    <t>Saburtalo</t>
+  </si>
+  <si>
+    <t>Karcag SE</t>
+  </si>
+  <si>
+    <t>Real Madrid W</t>
+  </si>
+  <si>
+    <t>Szentlőrinc SE</t>
+  </si>
+  <si>
+    <t>Croatia Zmijavci</t>
+  </si>
+  <si>
+    <t>Apollon</t>
+  </si>
+  <si>
+    <t>Omonia Nicosia</t>
+  </si>
+  <si>
+    <t>Paphos</t>
+  </si>
+  <si>
+    <t>KFUM</t>
+  </si>
+  <si>
+    <t>Tromsø</t>
+  </si>
+  <si>
+    <t>Sandefjord</t>
+  </si>
+  <si>
+    <t>Strømmen</t>
+  </si>
+  <si>
+    <t>Sandnes Ulf</t>
+  </si>
+  <si>
+    <t>Sogndal</t>
+  </si>
+  <si>
+    <t>Raufoss</t>
+  </si>
+  <si>
+    <t>Åsane</t>
+  </si>
+  <si>
+    <t>Moss</t>
+  </si>
+  <si>
+    <t>Kecskeméti TE</t>
+  </si>
+  <si>
+    <t>Ajka</t>
+  </si>
+  <si>
+    <t>Mebrat Hayl</t>
+  </si>
+  <si>
+    <t>Budafoki MTE</t>
   </si>
   <si>
     <t>Akademija Pandev</t>
   </si>
   <si>
-    <t>Makedonija GjP</t>
-  </si>
-  <si>
-    <t>Kecskeméti TE</t>
-  </si>
-  <si>
-    <t>Szentlőrinc SE</t>
-  </si>
-  <si>
-    <t>Pelister</t>
-  </si>
-  <si>
-    <t>Zbrojovka Brno</t>
-  </si>
-  <si>
-    <t>Shkendija</t>
-  </si>
-  <si>
-    <t>Vardar</t>
-  </si>
-  <si>
-    <t>Real Madrid W</t>
-  </si>
-  <si>
-    <t>Ajka</t>
-  </si>
-  <si>
-    <t>Aresimi</t>
-  </si>
-  <si>
-    <t>Pogoń Siedlce</t>
-  </si>
-  <si>
-    <t>Karcag SE</t>
-  </si>
-  <si>
-    <t>Budafoki MTE</t>
-  </si>
-  <si>
-    <t>Apollon</t>
-  </si>
-  <si>
-    <t>KFUM</t>
-  </si>
-  <si>
-    <t>Strømmen</t>
-  </si>
-  <si>
-    <t>Moss</t>
-  </si>
-  <si>
-    <t>Sandefjord</t>
-  </si>
-  <si>
-    <t>Croatia Zmijavci</t>
-  </si>
-  <si>
-    <t>Tromsø</t>
-  </si>
-  <si>
-    <t>Åsane</t>
-  </si>
-  <si>
-    <t>Sogndal</t>
-  </si>
-  <si>
-    <t>Mebrat Hayl</t>
-  </si>
-  <si>
-    <t>Raufoss</t>
-  </si>
-  <si>
-    <t>Sandnes Ulf</t>
-  </si>
-  <si>
-    <t>Rapid Wien</t>
-  </si>
-  <si>
-    <t>Paphos</t>
-  </si>
-  <si>
-    <t>LASK Linz</t>
-  </si>
-  <si>
-    <t>Hartberg</t>
-  </si>
-  <si>
-    <t>Omonia Nicosia</t>
-  </si>
-  <si>
-    <t>Saburtalo</t>
+    <t>Al Bataeh</t>
+  </si>
+  <si>
+    <t>Al Ain</t>
+  </si>
+  <si>
+    <t>Dibba Al Fujairah</t>
   </si>
   <si>
     <t>Bani Yas</t>
   </si>
   <si>
-    <t>Al Ain</t>
-  </si>
-  <si>
-    <t>Al Bataeh</t>
-  </si>
-  <si>
-    <t>Dibba Al Fujairah</t>
-  </si>
-  <si>
     <t>Nieciecza</t>
   </si>
   <si>
+    <t>Neftçi</t>
+  </si>
+  <si>
     <t>West Ham United</t>
   </si>
   <si>
     <t>Köln</t>
   </si>
   <si>
-    <t>Neftçi</t>
-  </si>
-  <si>
     <t>Sekhukhune United</t>
   </si>
   <si>
     <t>Vysočina Jihlava</t>
   </si>
   <si>
+    <t>Mladost DG</t>
+  </si>
+  <si>
+    <t>Arsenal Tivat</t>
+  </si>
+  <si>
+    <t>Jedinstvo</t>
+  </si>
+  <si>
+    <t>Dečić</t>
+  </si>
+  <si>
+    <t>Mornar</t>
+  </si>
+  <si>
+    <t>Parma</t>
+  </si>
+  <si>
+    <t>Dinamo Bucureşti</t>
+  </si>
+  <si>
+    <t>Ittihad Tanger</t>
+  </si>
+  <si>
+    <t>Brøndby</t>
+  </si>
+  <si>
     <t>Panevėžys</t>
   </si>
   <si>
-    <t>Dečić</t>
-  </si>
-  <si>
-    <t>Mladost DG</t>
-  </si>
-  <si>
-    <t>Brøndby</t>
-  </si>
-  <si>
-    <t>Ittihad Tanger</t>
-  </si>
-  <si>
-    <t>Arsenal Tivat</t>
-  </si>
-  <si>
-    <t>Jedinstvo</t>
-  </si>
-  <si>
-    <t>Parma</t>
-  </si>
-  <si>
-    <t>Mornar</t>
-  </si>
-  <si>
-    <t>Dinamo Bucureşti</t>
-  </si>
-  <si>
     <t>Al Riyadh</t>
   </si>
   <si>
+    <t>Skála</t>
+  </si>
+  <si>
     <t>Dobrudzha 1919</t>
   </si>
   <si>
-    <t>Skála</t>
+    <t>Slaven Koprivnica</t>
   </si>
   <si>
     <t>07 Vestur</t>
   </si>
   <si>
-    <t>Slaven Koprivnica</t>
+    <t>AEK Athens</t>
+  </si>
+  <si>
+    <t>Radnički Niš</t>
+  </si>
+  <si>
+    <t>Copiapó</t>
+  </si>
+  <si>
+    <t>Antofagasta</t>
+  </si>
+  <si>
+    <t>Spartak Subotica</t>
+  </si>
+  <si>
+    <t>IMT Novi Beograd</t>
+  </si>
+  <si>
+    <t>Union Saint-Gilloise</t>
+  </si>
+  <si>
+    <t>Córdoba</t>
+  </si>
+  <si>
+    <t>Olympiakos Piraeus</t>
+  </si>
+  <si>
+    <t>Jablonec</t>
+  </si>
+  <si>
+    <t>Mirandés</t>
+  </si>
+  <si>
+    <t>Kansas City</t>
   </si>
   <si>
     <t>Lokomotiv Moskva</t>
   </si>
   <si>
+    <t>Real Oviedo</t>
+  </si>
+  <si>
     <t>Bačka Topola</t>
   </si>
   <si>
-    <t>Córdoba</t>
-  </si>
-  <si>
-    <t>Spartak Subotica</t>
-  </si>
-  <si>
-    <t>Mirandés</t>
-  </si>
-  <si>
-    <t>Union Saint-Gilloise</t>
-  </si>
-  <si>
-    <t>Olympiakos Piraeus</t>
-  </si>
-  <si>
-    <t>Antofagasta</t>
-  </si>
-  <si>
-    <t>Copiapó</t>
-  </si>
-  <si>
-    <t>Kansas City</t>
-  </si>
-  <si>
-    <t>Radnički Niš</t>
-  </si>
-  <si>
-    <t>IMT Novi Beograd</t>
-  </si>
-  <si>
-    <t>Real Oviedo</t>
-  </si>
-  <si>
-    <t>Jablonec</t>
-  </si>
-  <si>
-    <t>AEK Athens</t>
+    <t>Dinamo Batumi</t>
+  </si>
+  <si>
+    <t>Hapoel Haifa</t>
+  </si>
+  <si>
+    <t>Ironi Tiberias</t>
+  </si>
+  <si>
+    <t>Tenerife W</t>
+  </si>
+  <si>
+    <t>Hapoel Katamon</t>
+  </si>
+  <si>
+    <t>KA</t>
   </si>
   <si>
     <t>Csákvári TK</t>
   </si>
   <si>
-    <t>Hapoel Haifa</t>
-  </si>
-  <si>
-    <t>Ironi Tiberias</t>
-  </si>
-  <si>
-    <t>Tenerife W</t>
-  </si>
-  <si>
-    <t>KA</t>
-  </si>
-  <si>
-    <t>Dinamo Batumi</t>
-  </si>
-  <si>
-    <t>Hapoel Katamon</t>
-  </si>
-  <si>
     <t>Békéscsaba</t>
   </si>
   <si>
@@ -1198,15 +1198,15 @@
     <t>Hoffenheim II</t>
   </si>
   <si>
+    <t>Al Ittihad</t>
+  </si>
+  <si>
+    <t>New England II</t>
+  </si>
+  <si>
     <t>UTS Rabat</t>
   </si>
   <si>
-    <t>Al Ittihad</t>
-  </si>
-  <si>
-    <t>New England II</t>
-  </si>
-  <si>
     <t>CODM Meknès</t>
   </si>
   <si>
@@ -1219,51 +1219,51 @@
     <t>AC Milan</t>
   </si>
   <si>
+    <t>Agropecuario</t>
+  </si>
+  <si>
     <t>Monaco</t>
   </si>
   <si>
+    <t>FC Barcelona</t>
+  </si>
+  <si>
+    <t>Independiente Petrolero</t>
+  </si>
+  <si>
+    <t>Club Atlético Güemes</t>
+  </si>
+  <si>
+    <t>Toulouse</t>
+  </si>
+  <si>
+    <t>Rennes</t>
+  </si>
+  <si>
+    <t>PSG</t>
+  </si>
+  <si>
+    <t>Remo</t>
+  </si>
+  <si>
+    <t>Auxerre</t>
+  </si>
+  <si>
+    <t>Angers SCO</t>
+  </si>
+  <si>
+    <t>Le Havre</t>
+  </si>
+  <si>
+    <t>Metz</t>
+  </si>
+  <si>
+    <t>Náutico</t>
+  </si>
+  <si>
     <t>Atlético Mineiro</t>
   </si>
   <si>
-    <t>Independiente Petrolero</t>
-  </si>
-  <si>
-    <t>Le Havre</t>
-  </si>
-  <si>
-    <t>FC Barcelona</t>
-  </si>
-  <si>
-    <t>Club Atlético Güemes</t>
-  </si>
-  <si>
-    <t>Metz</t>
-  </si>
-  <si>
-    <t>Auxerre</t>
-  </si>
-  <si>
-    <t>Agropecuario</t>
-  </si>
-  <si>
-    <t>Angers SCO</t>
-  </si>
-  <si>
-    <t>PSG</t>
-  </si>
-  <si>
-    <t>Rennes</t>
-  </si>
-  <si>
-    <t>Toulouse</t>
-  </si>
-  <si>
-    <t>Remo</t>
-  </si>
-  <si>
-    <t>Náutico</t>
-  </si>
-  <si>
     <t>San Martín San Juan</t>
   </si>
   <si>
@@ -1276,18 +1276,18 @@
     <t>Hassania Agadir</t>
   </si>
   <si>
+    <t>Los Angeles II</t>
+  </si>
+  <si>
+    <t>Central Norte</t>
+  </si>
+  <si>
+    <t>Bay</t>
+  </si>
+  <si>
     <t>Portland Timbers II</t>
   </si>
   <si>
-    <t>Los Angeles II</t>
-  </si>
-  <si>
-    <t>Bay</t>
-  </si>
-  <si>
-    <t>Central Norte</t>
-  </si>
-  <si>
     <t>CS Emelec</t>
   </si>
   <si>
@@ -1300,36 +1300,36 @@
     <t>The Strongest</t>
   </si>
   <si>
+    <t>Mirassol</t>
+  </si>
+  <si>
+    <t>Santos</t>
+  </si>
+  <si>
+    <t>Corinthians</t>
+  </si>
+  <si>
     <t>Avaí</t>
   </si>
   <si>
-    <t>Corinthians</t>
-  </si>
-  <si>
-    <t>Mirassol</t>
-  </si>
-  <si>
-    <t>Santos</t>
-  </si>
-  <si>
     <t>FC Cincinnati II</t>
   </si>
   <si>
+    <t>Novorizontino</t>
+  </si>
+  <si>
     <t>Grêmio</t>
   </si>
   <si>
-    <t>Novorizontino</t>
+    <t>Minnesota United</t>
+  </si>
+  <si>
+    <t>Seattle Reign</t>
   </si>
   <si>
     <t>Atlanta United II</t>
   </si>
   <si>
-    <t>Minnesota United</t>
-  </si>
-  <si>
-    <t>Seattle Reign</t>
-  </si>
-  <si>
     <t>Manta FC</t>
   </si>
   <si>
@@ -1348,21 +1348,24 @@
     <t>Los Angeles FC</t>
   </si>
   <si>
+    <t>Jeonnam Dragons</t>
+  </si>
+  <si>
     <t>Sydney II</t>
   </si>
   <si>
     <t>Bucheon 1995</t>
   </si>
   <si>
-    <t>Jeonnam Dragons</t>
-  </si>
-  <si>
     <t>St. George Saints</t>
   </si>
   <si>
     <t>Sydney United</t>
   </si>
   <si>
+    <t>Shanghai Jiading</t>
+  </si>
+  <si>
     <t>Rotor Volgograd</t>
   </si>
   <si>
@@ -1372,24 +1375,21 @@
     <t>Guangzhou E-Power</t>
   </si>
   <si>
-    <t>Shanghai Jiading</t>
+    <t>Yongin City</t>
   </si>
   <si>
     <t>Cheonan City</t>
   </si>
   <si>
-    <t>Yongin City</t>
-  </si>
-  <si>
     <t>Jeonbuk Motors</t>
   </si>
   <si>
+    <t>Sparta Praha II</t>
+  </si>
+  <si>
     <t>Táborsko</t>
   </si>
   <si>
-    <t>Sparta Praha II</t>
-  </si>
-  <si>
     <t>Persib</t>
   </si>
   <si>
@@ -1402,231 +1402,231 @@
     <t>Wuhan Three Towns</t>
   </si>
   <si>
+    <t>Shandong Luneng</t>
+  </si>
+  <si>
+    <t>Logroño W</t>
+  </si>
+  <si>
+    <t>Spartak Kostroma</t>
+  </si>
+  <si>
+    <t>Sidama Bunna</t>
+  </si>
+  <si>
     <t>Gimhae City</t>
   </si>
   <si>
-    <t>Logroño W</t>
+    <t>Pho Hien</t>
   </si>
   <si>
     <t>União Santarém</t>
   </si>
   <si>
-    <t>Spartak Kostroma</t>
-  </si>
-  <si>
-    <t>Sidama Bunna</t>
+    <t>Kairat</t>
   </si>
   <si>
     <t>Górnik Łęczna</t>
   </si>
   <si>
-    <t>Kairat</t>
-  </si>
-  <si>
-    <t>Pho Hien</t>
-  </si>
-  <si>
-    <t>Shandong Luneng</t>
-  </si>
-  <si>
     <t>GKS Katowice</t>
   </si>
   <si>
     <t>Como</t>
   </si>
   <si>
+    <t>Hebei Kungfu</t>
+  </si>
+  <si>
+    <t>Rosengard Women</t>
+  </si>
+  <si>
+    <t>Rangers</t>
+  </si>
+  <si>
+    <t>Muang Thong United</t>
+  </si>
+  <si>
+    <t>Uthai Thani</t>
+  </si>
+  <si>
+    <t>Prachuap</t>
+  </si>
+  <si>
     <t>Ratchaburi</t>
   </si>
   <si>
-    <t>Rangers</t>
+    <t>Viettel</t>
+  </si>
+  <si>
+    <t>Yunnan Yukun</t>
   </si>
   <si>
     <t>Lamphun Warrior</t>
   </si>
   <si>
+    <t>Nakhon Ratchasima</t>
+  </si>
+  <si>
     <t>Port FC</t>
   </si>
   <si>
-    <t>Prachuap</t>
-  </si>
-  <si>
-    <t>Nakhon Ratchasima</t>
+    <t>Song Lam Nghe An</t>
+  </si>
+  <si>
+    <t>Ordabasy</t>
   </si>
   <si>
     <t>Bangkok United</t>
   </si>
   <si>
-    <t>Yunnan Yukun</t>
-  </si>
-  <si>
-    <t>Rosengard Women</t>
-  </si>
-  <si>
-    <t>Hebei Kungfu</t>
-  </si>
-  <si>
-    <t>Ordabasy</t>
-  </si>
-  <si>
-    <t>Muang Thong United</t>
-  </si>
-  <si>
-    <t>Uthai Thani</t>
-  </si>
-  <si>
-    <t>Viettel</t>
-  </si>
-  <si>
-    <t>Song Lam Nghe An</t>
+    <t>Slavia Sofia</t>
   </si>
   <si>
     <t>Žalgiris</t>
   </si>
   <si>
-    <t>Slavia Sofia</t>
+    <t>Darmstadt 98</t>
+  </si>
+  <si>
+    <t>Tampines Rovers</t>
+  </si>
+  <si>
+    <t>Greuther Fürth</t>
   </si>
   <si>
     <t>Suzhou Dongwu</t>
   </si>
   <si>
+    <t>Elversberg</t>
+  </si>
+  <si>
+    <t>Schweinfurt</t>
+  </si>
+  <si>
     <t>RSC Anderlecht</t>
   </si>
   <si>
-    <t>Tampines Rovers</t>
+    <t>Mohammedan</t>
   </si>
   <si>
     <t>Wuxi Wugou</t>
   </si>
   <si>
-    <t>Elversberg</t>
+    <t>Albirex Niigata S</t>
   </si>
   <si>
     <t>Tallinna FC Flora</t>
   </si>
   <si>
-    <t>Mohammedan</t>
-  </si>
-  <si>
-    <t>Albirex Niigata S</t>
-  </si>
-  <si>
-    <t>Darmstadt 98</t>
-  </si>
-  <si>
-    <t>Greuther Fürth</t>
-  </si>
-  <si>
-    <t>Schweinfurt</t>
+    <t>Tianjin Teda</t>
   </si>
   <si>
     <t>Shanghai SIPG</t>
   </si>
   <si>
-    <t>Tianjin Teda</t>
-  </si>
-  <si>
     <t>Opatija</t>
   </si>
   <si>
+    <t>Kaisar</t>
+  </si>
+  <si>
+    <t>Dalian Zhixing</t>
+  </si>
+  <si>
+    <t>Dila</t>
+  </si>
+  <si>
+    <t>Midtjylland</t>
+  </si>
+  <si>
+    <t>St. Gallen</t>
+  </si>
+  <si>
+    <t>UD Las Palmas</t>
+  </si>
+  <si>
+    <t>Fredericia</t>
+  </si>
+  <si>
+    <t>Djurgården</t>
+  </si>
+  <si>
+    <t>Villarreal</t>
+  </si>
+  <si>
+    <t>Malut United</t>
+  </si>
+  <si>
+    <t>FK Sochi</t>
+  </si>
+  <si>
+    <t>Welwalo Adigrat Uni</t>
+  </si>
+  <si>
     <t>Halmstad</t>
   </si>
   <si>
-    <t>Kaisar</t>
-  </si>
-  <si>
-    <t>Djurgården</t>
-  </si>
-  <si>
-    <t>Midtjylland</t>
-  </si>
-  <si>
-    <t>Malut United</t>
-  </si>
-  <si>
-    <t>FK Sochi</t>
-  </si>
-  <si>
-    <t>Villarreal</t>
-  </si>
-  <si>
-    <t>Dila</t>
-  </si>
-  <si>
-    <t>Fredericia</t>
-  </si>
-  <si>
-    <t>Welwalo Adigrat Uni</t>
-  </si>
-  <si>
-    <t>Dalian Zhixing</t>
-  </si>
-  <si>
-    <t>St. Gallen</t>
-  </si>
-  <si>
-    <t>UD Las Palmas</t>
+    <t>Negeri Sembilan</t>
   </si>
   <si>
     <t>Nam Dinh</t>
   </si>
   <si>
-    <t>Negeri Sembilan</t>
+    <t>Lillestrøm</t>
   </si>
   <si>
     <t>Ruch Chorzów</t>
   </si>
   <si>
-    <t>Lillestrøm</t>
-  </si>
-  <si>
     <t>Ústí nad Labem</t>
   </si>
   <si>
     <t>Motor Lublin</t>
   </si>
   <si>
+    <t>Petrolul 52</t>
+  </si>
+  <si>
+    <t>Mura</t>
+  </si>
+  <si>
+    <t>Karviná</t>
+  </si>
+  <si>
+    <t>Everton</t>
+  </si>
+  <si>
+    <t>Aston Villa</t>
+  </si>
+  <si>
+    <t>Johor Darul Ta'zim</t>
+  </si>
+  <si>
+    <t>Bohemians 1905</t>
+  </si>
+  <si>
+    <t>Newcastle United</t>
+  </si>
+  <si>
+    <t>Genoa</t>
+  </si>
+  <si>
+    <t>Welayta Dicha</t>
+  </si>
+  <si>
+    <t>Vittsjö</t>
+  </si>
+  <si>
     <t>Kyzyl-Zhar</t>
   </si>
   <si>
-    <t>Genoa</t>
-  </si>
-  <si>
-    <t>Karviná</t>
-  </si>
-  <si>
-    <t>Bohemians 1905</t>
-  </si>
-  <si>
-    <t>Vittsjö</t>
+    <t>Karvan FK</t>
   </si>
   <si>
     <t>Pisa</t>
   </si>
   <si>
-    <t>Petrolul 52</t>
-  </si>
-  <si>
-    <t>Karvan FK</t>
-  </si>
-  <si>
-    <t>Mura</t>
-  </si>
-  <si>
-    <t>Johor Darul Ta'zim</t>
-  </si>
-  <si>
-    <t>Aston Villa</t>
-  </si>
-  <si>
-    <t>Newcastle United</t>
-  </si>
-  <si>
-    <t>Everton</t>
-  </si>
-  <si>
-    <t>Welayta Dicha</t>
-  </si>
-  <si>
     <t>Freiburg</t>
   </si>
   <si>
@@ -1636,58 +1636,67 @@
     <t>Sporting Charleroi</t>
   </si>
   <si>
+    <t>OFI</t>
+  </si>
+  <si>
+    <t>TransINVEST Vilnius</t>
+  </si>
+  <si>
+    <t>Paide</t>
+  </si>
+  <si>
+    <t>Levadiakos</t>
+  </si>
+  <si>
+    <t>Víkingur</t>
+  </si>
+  <si>
+    <t>København</t>
+  </si>
+  <si>
+    <t>Chennaiyin</t>
+  </si>
+  <si>
+    <t>Istra 1961</t>
+  </si>
+  <si>
     <t>KÍ</t>
   </si>
   <si>
-    <t>Víkingur</t>
-  </si>
-  <si>
-    <t>Paide</t>
-  </si>
-  <si>
-    <t>Levadiakos</t>
-  </si>
-  <si>
-    <t>København</t>
-  </si>
-  <si>
     <t>Vasas</t>
   </si>
   <si>
-    <t>Istra 1961</t>
-  </si>
-  <si>
-    <t>OFI</t>
-  </si>
-  <si>
-    <t>Chennaiyin</t>
-  </si>
-  <si>
-    <t>TransINVEST Vilnius</t>
+    <t>Valencia CF</t>
+  </si>
+  <si>
+    <t>Racing Santander</t>
   </si>
   <si>
     <t>Makhachkala</t>
   </si>
   <si>
-    <t>Valencia CF</t>
-  </si>
-  <si>
-    <t>Racing Santander</t>
+    <t>Basel</t>
+  </si>
+  <si>
+    <t>Thun</t>
+  </si>
+  <si>
+    <t>Volga Ulyanovsk</t>
   </si>
   <si>
     <t>Malmö FF</t>
   </si>
   <si>
-    <t>Thun</t>
-  </si>
-  <si>
-    <t>Volga Ulyanovsk</t>
-  </si>
-  <si>
     <t>Alemannia Aachen</t>
   </si>
   <si>
-    <t>Basel</t>
+    <t>PSV</t>
+  </si>
+  <si>
+    <t>AZ</t>
+  </si>
+  <si>
+    <t>Utrecht</t>
   </si>
   <si>
     <t>Heerenveen</t>
@@ -1696,261 +1705,252 @@
     <t>Sparta Rotterdam</t>
   </si>
   <si>
-    <t>PSV</t>
-  </si>
-  <si>
-    <t>AZ</t>
+    <t>PEC Zwolle</t>
   </si>
   <si>
     <t>Heracles</t>
   </si>
   <si>
+    <t>Volendam</t>
+  </si>
+  <si>
     <t>NEC</t>
   </si>
   <si>
-    <t>PEC Zwolle</t>
-  </si>
-  <si>
-    <t>Utrecht</t>
-  </si>
-  <si>
-    <t>Volendam</t>
+    <t>Salzburg</t>
+  </si>
+  <si>
+    <t>Austria Wien</t>
+  </si>
+  <si>
+    <t>Sturm Graz</t>
+  </si>
+  <si>
+    <t>Shkupi</t>
+  </si>
+  <si>
+    <t>Stal Rzeszów</t>
+  </si>
+  <si>
+    <t>Tikveš</t>
+  </si>
+  <si>
+    <t>Struga</t>
+  </si>
+  <si>
+    <t>FK Bashkimi Kumanovo</t>
+  </si>
+  <si>
+    <t>Sileks</t>
+  </si>
+  <si>
+    <t>Vlašim</t>
+  </si>
+  <si>
+    <t>Torpedo Kutaisi</t>
+  </si>
+  <si>
+    <t>Tiszakécske</t>
+  </si>
+  <si>
+    <t>Atletico Madrid W</t>
+  </si>
+  <si>
+    <t>Videoton</t>
+  </si>
+  <si>
+    <t>Jarun</t>
+  </si>
+  <si>
+    <t>APOEL</t>
+  </si>
+  <si>
+    <t>AEK Larnaca</t>
+  </si>
+  <si>
+    <t>Viking</t>
+  </si>
+  <si>
+    <t>Molde</t>
+  </si>
+  <si>
+    <t>Kristiansund</t>
+  </si>
+  <si>
+    <t>Hødd</t>
+  </si>
+  <si>
+    <t>Stabæk</t>
+  </si>
+  <si>
+    <t>Haugesund</t>
+  </si>
+  <si>
+    <t>Lyn</t>
+  </si>
+  <si>
+    <t>Strømsgodset</t>
+  </si>
+  <si>
+    <t>Bryne</t>
+  </si>
+  <si>
+    <t>Mezőkövesd-Zsóry</t>
+  </si>
+  <si>
+    <t>Szeged 2011</t>
+  </si>
+  <si>
+    <t>Fasil Ketema</t>
+  </si>
+  <si>
+    <t>BVSC</t>
   </si>
   <si>
     <t>Rabotnički</t>
   </si>
   <si>
-    <t>Tikveš</t>
-  </si>
-  <si>
-    <t>Mezőkövesd-Zsóry</t>
-  </si>
-  <si>
-    <t>Videoton</t>
-  </si>
-  <si>
-    <t>Shkupi</t>
-  </si>
-  <si>
-    <t>Vlašim</t>
-  </si>
-  <si>
-    <t>Struga</t>
-  </si>
-  <si>
-    <t>Sileks</t>
-  </si>
-  <si>
-    <t>Atletico Madrid W</t>
-  </si>
-  <si>
-    <t>Szeged 2011</t>
-  </si>
-  <si>
-    <t>FK Bashkimi Kumanovo</t>
-  </si>
-  <si>
-    <t>Stal Rzeszów</t>
-  </si>
-  <si>
-    <t>Tiszakécske</t>
-  </si>
-  <si>
-    <t>BVSC</t>
-  </si>
-  <si>
-    <t>APOEL</t>
-  </si>
-  <si>
-    <t>Viking</t>
-  </si>
-  <si>
-    <t>Hødd</t>
-  </si>
-  <si>
-    <t>Bryne</t>
-  </si>
-  <si>
-    <t>Kristiansund</t>
-  </si>
-  <si>
-    <t>Jarun</t>
-  </si>
-  <si>
-    <t>Molde</t>
-  </si>
-  <si>
-    <t>Strømsgodset</t>
-  </si>
-  <si>
-    <t>Haugesund</t>
-  </si>
-  <si>
-    <t>Fasil Ketema</t>
-  </si>
-  <si>
-    <t>Lyn</t>
-  </si>
-  <si>
-    <t>Stabæk</t>
-  </si>
-  <si>
-    <t>Austria Wien</t>
-  </si>
-  <si>
-    <t>Salzburg</t>
-  </si>
-  <si>
-    <t>Sturm Graz</t>
-  </si>
-  <si>
-    <t>AEK Larnaca</t>
-  </si>
-  <si>
-    <t>Torpedo Kutaisi</t>
+    <t>Al Sharjah</t>
+  </si>
+  <si>
+    <t>Al Dhafra</t>
+  </si>
+  <si>
+    <t>Ajman</t>
   </si>
   <si>
     <t>Shabab Al Ahli Dubai</t>
   </si>
   <si>
-    <t>Al Dhafra</t>
-  </si>
-  <si>
-    <t>Al Sharjah</t>
-  </si>
-  <si>
-    <t>Ajman</t>
-  </si>
-  <si>
     <t>Legia Warszawa</t>
   </si>
   <si>
+    <t>İnter Bakı</t>
+  </si>
+  <si>
     <t>Arsenal</t>
   </si>
   <si>
     <t>Heidenheim</t>
   </si>
   <si>
-    <t>İnter Bakı</t>
-  </si>
-  <si>
     <t>Kaizer Chiefs</t>
   </si>
   <si>
     <t>Hanácká</t>
   </si>
   <si>
+    <t>Petrovac</t>
+  </si>
+  <si>
+    <t>Sutjeska</t>
+  </si>
+  <si>
+    <t>Budućnost</t>
+  </si>
+  <si>
+    <t>FK Jezero Plav</t>
+  </si>
+  <si>
+    <t>Bokelj</t>
+  </si>
+  <si>
+    <t>Roma</t>
+  </si>
+  <si>
+    <t>Argeș</t>
+  </si>
+  <si>
+    <t>Difaâ El Jadida</t>
+  </si>
+  <si>
+    <t>AGF</t>
+  </si>
+  <si>
     <t>Kauno Žalgiris</t>
   </si>
   <si>
-    <t>FK Jezero Plav</t>
-  </si>
-  <si>
-    <t>Petrovac</t>
-  </si>
-  <si>
-    <t>AGF</t>
-  </si>
-  <si>
-    <t>Difaâ El Jadida</t>
-  </si>
-  <si>
-    <t>Sutjeska</t>
-  </si>
-  <si>
-    <t>Budućnost</t>
-  </si>
-  <si>
-    <t>Roma</t>
-  </si>
-  <si>
-    <t>Bokelj</t>
-  </si>
-  <si>
-    <t>Argeș</t>
-  </si>
-  <si>
     <t>Al Fateh</t>
   </si>
   <si>
+    <t>AB</t>
+  </si>
+  <si>
     <t>Beroe</t>
   </si>
   <si>
-    <t>AB</t>
+    <t>Gorica</t>
   </si>
   <si>
     <t>B68</t>
   </si>
   <si>
-    <t>Gorica</t>
+    <t>Panathinaikos</t>
+  </si>
+  <si>
+    <t>LFK Mladost Lučani</t>
+  </si>
+  <si>
+    <t>Unión San Felipe</t>
+  </si>
+  <si>
+    <t>San Luis</t>
+  </si>
+  <si>
+    <t>Napredak</t>
+  </si>
+  <si>
+    <t>Radnički Kragujevac</t>
+  </si>
+  <si>
+    <t>KV Mechelen</t>
+  </si>
+  <si>
+    <t>Granada CF</t>
+  </si>
+  <si>
+    <t>PAOK</t>
+  </si>
+  <si>
+    <t>Hradec Králové</t>
+  </si>
+  <si>
+    <t>SD Eibar</t>
+  </si>
+  <si>
+    <t>Chicago Red Stars</t>
   </si>
   <si>
     <t>Baltika</t>
   </si>
   <si>
+    <t>Getafe CF</t>
+  </si>
+  <si>
     <t>Javor Ivanjica</t>
   </si>
   <si>
-    <t>Granada CF</t>
-  </si>
-  <si>
-    <t>Napredak</t>
-  </si>
-  <si>
-    <t>SD Eibar</t>
-  </si>
-  <si>
-    <t>KV Mechelen</t>
-  </si>
-  <si>
-    <t>PAOK</t>
-  </si>
-  <si>
-    <t>San Luis</t>
-  </si>
-  <si>
-    <t>Unión San Felipe</t>
-  </si>
-  <si>
-    <t>Chicago Red Stars</t>
-  </si>
-  <si>
-    <t>LFK Mladost Lučani</t>
-  </si>
-  <si>
-    <t>Radnički Kragujevac</t>
-  </si>
-  <si>
-    <t>Getafe CF</t>
-  </si>
-  <si>
-    <t>Hradec Králové</t>
-  </si>
-  <si>
-    <t>Panathinaikos</t>
+    <t>Samgurali</t>
+  </si>
+  <si>
+    <t>Ashdod</t>
+  </si>
+  <si>
+    <t>Maccabi Netanya</t>
+  </si>
+  <si>
+    <t>Barcelona W</t>
+  </si>
+  <si>
+    <t>Bnei Sakhnin</t>
+  </si>
+  <si>
+    <t>ÍBV</t>
   </si>
   <si>
     <t>Soroksár SC</t>
   </si>
   <si>
-    <t>Ashdod</t>
-  </si>
-  <si>
-    <t>Maccabi Netanya</t>
-  </si>
-  <si>
-    <t>Barcelona W</t>
-  </si>
-  <si>
-    <t>ÍBV</t>
-  </si>
-  <si>
-    <t>Samgurali</t>
-  </si>
-  <si>
-    <t>Bnei Sakhnin</t>
-  </si>
-  <si>
     <t>Kozármisleny</t>
   </si>
   <si>
@@ -1963,15 +1963,15 @@
     <t>Saarbrucken</t>
   </si>
   <si>
+    <t>Dhamk</t>
+  </si>
+  <si>
+    <t>New York City II</t>
+  </si>
+  <si>
     <t>Maghreb Fès</t>
   </si>
   <si>
-    <t>Dhamk</t>
-  </si>
-  <si>
-    <t>New York City II</t>
-  </si>
-  <si>
     <t>RSB Berkane</t>
   </si>
   <si>
@@ -1984,51 +1984,51 @@
     <t>Atalanta</t>
   </si>
   <si>
+    <t>Atlanta</t>
+  </si>
+  <si>
     <t>Lille</t>
   </si>
   <si>
+    <t>Real Madrid</t>
+  </si>
+  <si>
+    <t>Club Always Ready</t>
+  </si>
+  <si>
+    <t>Quilmes</t>
+  </si>
+  <si>
+    <t>Olympique Lyonnais</t>
+  </si>
+  <si>
+    <t>Paris</t>
+  </si>
+  <si>
+    <t>Brest</t>
+  </si>
+  <si>
+    <t>Palmeiras</t>
+  </si>
+  <si>
+    <t>Nice</t>
+  </si>
+  <si>
+    <t>Strasbourg</t>
+  </si>
+  <si>
+    <t>Olympique Marseille</t>
+  </si>
+  <si>
+    <t>Lorient</t>
+  </si>
+  <si>
+    <t>América Mineiro</t>
+  </si>
+  <si>
     <t>Botafogo</t>
   </si>
   <si>
-    <t>Club Always Ready</t>
-  </si>
-  <si>
-    <t>Olympique Marseille</t>
-  </si>
-  <si>
-    <t>Real Madrid</t>
-  </si>
-  <si>
-    <t>Quilmes</t>
-  </si>
-  <si>
-    <t>Lorient</t>
-  </si>
-  <si>
-    <t>Nice</t>
-  </si>
-  <si>
-    <t>Atlanta</t>
-  </si>
-  <si>
-    <t>Strasbourg</t>
-  </si>
-  <si>
-    <t>Brest</t>
-  </si>
-  <si>
-    <t>Paris</t>
-  </si>
-  <si>
-    <t>Olympique Lyonnais</t>
-  </si>
-  <si>
-    <t>Palmeiras</t>
-  </si>
-  <si>
-    <t>América Mineiro</t>
-  </si>
-  <si>
     <t>Patronato</t>
   </si>
   <si>
@@ -2041,18 +2041,18 @@
     <t>FAR Rabat</t>
   </si>
   <si>
+    <t>Real Monarchs</t>
+  </si>
+  <si>
+    <t>Deportivo Madryn</t>
+  </si>
+  <si>
+    <t>Utah Royals</t>
+  </si>
+  <si>
     <t>LA Galaxy II</t>
   </si>
   <si>
-    <t>Real Monarchs</t>
-  </si>
-  <si>
-    <t>Utah Royals</t>
-  </si>
-  <si>
-    <t>Deportivo Madryn</t>
-  </si>
-  <si>
     <t>Libertad</t>
   </si>
   <si>
@@ -2065,34 +2065,34 @@
     <t>Real Potosí</t>
   </si>
   <si>
+    <t>Chapecoense</t>
+  </si>
+  <si>
+    <t>Bragantino</t>
+  </si>
+  <si>
+    <t>São Paulo</t>
+  </si>
+  <si>
     <t>Fortaleza</t>
   </si>
   <si>
-    <t>São Paulo</t>
-  </si>
-  <si>
-    <t>Chapecoense</t>
-  </si>
-  <si>
-    <t>Bragantino</t>
-  </si>
-  <si>
     <t>Columbus Crew II</t>
   </si>
   <si>
+    <t>Botafogo SP</t>
+  </si>
+  <si>
     <t>Flamengo</t>
   </si>
   <si>
-    <t>Botafogo SP</t>
+    <t>Austin</t>
+  </si>
+  <si>
+    <t>Washington Spirit</t>
   </si>
   <si>
     <t>Orlando City II</t>
-  </si>
-  <si>
-    <t>Austin</t>
-  </si>
-  <si>
-    <t>Washington Spirit</t>
   </si>
   <si>
     <t>Macará</t>
@@ -3228,7 +3228,7 @@
         <v>61</v>
       </c>
       <c r="C5" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="D5" t="s">
         <v>185</v>
@@ -3413,7 +3413,7 @@
         <v>62</v>
       </c>
       <c r="C6" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="D6" t="s">
         <v>185</v>
@@ -3601,7 +3601,7 @@
         <v>118</v>
       </c>
       <c r="D7" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E7" t="s">
         <v>193</v>
@@ -3786,7 +3786,7 @@
         <v>119</v>
       </c>
       <c r="D8" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E8" t="s">
         <v>194</v>
@@ -3968,7 +3968,7 @@
         <v>63</v>
       </c>
       <c r="C9" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D9" t="s">
         <v>185</v>
@@ -4153,7 +4153,7 @@
         <v>63</v>
       </c>
       <c r="C10" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D10" t="s">
         <v>185</v>
@@ -4338,7 +4338,7 @@
         <v>64</v>
       </c>
       <c r="C11" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="D11" t="s">
         <v>185</v>
@@ -4523,7 +4523,7 @@
         <v>64</v>
       </c>
       <c r="C12" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="D12" t="s">
         <v>185</v>
@@ -4708,7 +4708,7 @@
         <v>64</v>
       </c>
       <c r="C13" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="D13" t="s">
         <v>185</v>
@@ -6003,7 +6003,7 @@
         <v>68</v>
       </c>
       <c r="C20" t="s">
-        <v>117</v>
+        <v>123</v>
       </c>
       <c r="D20" t="s">
         <v>185</v>
@@ -6373,7 +6373,7 @@
         <v>68</v>
       </c>
       <c r="C22" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
       <c r="D22" t="s">
         <v>186</v>
@@ -6558,7 +6558,7 @@
         <v>68</v>
       </c>
       <c r="C23" t="s">
-        <v>118</v>
+        <v>125</v>
       </c>
       <c r="D23" t="s">
         <v>186</v>
@@ -6743,10 +6743,10 @@
         <v>68</v>
       </c>
       <c r="C24" t="s">
-        <v>126</v>
+        <v>115</v>
       </c>
       <c r="D24" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E24" t="s">
         <v>210</v>
@@ -6928,7 +6928,7 @@
         <v>68</v>
       </c>
       <c r="C25" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="D25" t="s">
         <v>186</v>
@@ -7113,10 +7113,10 @@
         <v>68</v>
       </c>
       <c r="C26" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="D26" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E26" t="s">
         <v>212</v>
@@ -7298,10 +7298,10 @@
         <v>68</v>
       </c>
       <c r="C27" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D27" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E27" t="s">
         <v>213</v>
@@ -7483,10 +7483,10 @@
         <v>68</v>
       </c>
       <c r="C28" t="s">
-        <v>123</v>
+        <v>129</v>
       </c>
       <c r="D28" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E28" t="s">
         <v>214</v>
@@ -8038,10 +8038,10 @@
         <v>71</v>
       </c>
       <c r="C31" t="s">
-        <v>132</v>
+        <v>118</v>
       </c>
       <c r="D31" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E31" t="s">
         <v>217</v>
@@ -8223,10 +8223,10 @@
         <v>71</v>
       </c>
       <c r="C32" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="D32" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E32" t="s">
         <v>218</v>
@@ -8262,13 +8262,13 @@
         <v>699</v>
       </c>
       <c r="P32">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Q32">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="R32">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="S32">
         <v>0</v>
@@ -8408,7 +8408,7 @@
         <v>71</v>
       </c>
       <c r="C33" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="D33" t="s">
         <v>186</v>
@@ -8447,13 +8447,13 @@
         <v>699</v>
       </c>
       <c r="P33">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Q33">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="R33">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="S33">
         <v>0</v>
@@ -8593,7 +8593,7 @@
         <v>71</v>
       </c>
       <c r="C34" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="D34" t="s">
         <v>186</v>
@@ -8778,7 +8778,7 @@
         <v>71</v>
       </c>
       <c r="C35" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="D35" t="s">
         <v>186</v>
@@ -8963,7 +8963,7 @@
         <v>71</v>
       </c>
       <c r="C36" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="D36" t="s">
         <v>186</v>
@@ -9148,7 +9148,7 @@
         <v>71</v>
       </c>
       <c r="C37" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="D37" t="s">
         <v>186</v>
@@ -9333,10 +9333,10 @@
         <v>71</v>
       </c>
       <c r="C38" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="D38" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E38" t="s">
         <v>224</v>
@@ -9518,7 +9518,7 @@
         <v>71</v>
       </c>
       <c r="C39" t="s">
-        <v>134</v>
+        <v>123</v>
       </c>
       <c r="D39" t="s">
         <v>185</v>
@@ -9703,10 +9703,10 @@
         <v>71</v>
       </c>
       <c r="C40" t="s">
-        <v>119</v>
+        <v>134</v>
       </c>
       <c r="D40" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E40" t="s">
         <v>226</v>
@@ -9888,10 +9888,10 @@
         <v>71</v>
       </c>
       <c r="C41" t="s">
-        <v>128</v>
+        <v>134</v>
       </c>
       <c r="D41" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E41" t="s">
         <v>227</v>
@@ -10073,7 +10073,7 @@
         <v>71</v>
       </c>
       <c r="C42" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="D42" t="s">
         <v>186</v>
@@ -10258,7 +10258,7 @@
         <v>71</v>
       </c>
       <c r="C43" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="D43" t="s">
         <v>186</v>
@@ -10443,10 +10443,10 @@
         <v>71</v>
       </c>
       <c r="C44" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D44" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E44" t="s">
         <v>230</v>
@@ -10628,7 +10628,7 @@
         <v>71</v>
       </c>
       <c r="C45" t="s">
-        <v>129</v>
+        <v>134</v>
       </c>
       <c r="D45" t="s">
         <v>186</v>
@@ -10816,7 +10816,7 @@
         <v>135</v>
       </c>
       <c r="D46" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E46" t="s">
         <v>232</v>
@@ -11001,7 +11001,7 @@
         <v>136</v>
       </c>
       <c r="D47" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E47" t="s">
         <v>233</v>
@@ -11183,10 +11183,10 @@
         <v>73</v>
       </c>
       <c r="C48" t="s">
-        <v>119</v>
+        <v>137</v>
       </c>
       <c r="D48" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E48" t="s">
         <v>234</v>
@@ -11368,10 +11368,10 @@
         <v>73</v>
       </c>
       <c r="C49" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="D49" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="E49" t="s">
         <v>235</v>
@@ -11553,10 +11553,10 @@
         <v>73</v>
       </c>
       <c r="C50" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D50" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="E50" t="s">
         <v>236</v>
@@ -11738,7 +11738,7 @@
         <v>73</v>
       </c>
       <c r="C51" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D51" t="s">
         <v>185</v>
@@ -11923,7 +11923,7 @@
         <v>73</v>
       </c>
       <c r="C52" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="D52" t="s">
         <v>186</v>
@@ -12108,10 +12108,10 @@
         <v>73</v>
       </c>
       <c r="C53" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="D53" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E53" t="s">
         <v>239</v>
@@ -12293,7 +12293,7 @@
         <v>73</v>
       </c>
       <c r="C54" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D54" t="s">
         <v>186</v>
@@ -12478,10 +12478,10 @@
         <v>73</v>
       </c>
       <c r="C55" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="D55" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="E55" t="s">
         <v>241</v>
@@ -12663,10 +12663,10 @@
         <v>73</v>
       </c>
       <c r="C56" t="s">
-        <v>139</v>
+        <v>118</v>
       </c>
       <c r="D56" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E56" t="s">
         <v>242</v>
@@ -12848,10 +12848,10 @@
         <v>73</v>
       </c>
       <c r="C57" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="D57" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="E57" t="s">
         <v>243</v>
@@ -13036,7 +13036,7 @@
         <v>142</v>
       </c>
       <c r="D58" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E58" t="s">
         <v>244</v>
@@ -13773,7 +13773,7 @@
         <v>76</v>
       </c>
       <c r="C62" t="s">
-        <v>144</v>
+        <v>128</v>
       </c>
       <c r="D62" t="s">
         <v>185</v>
@@ -13958,7 +13958,7 @@
         <v>76</v>
       </c>
       <c r="C63" t="s">
-        <v>128</v>
+        <v>123</v>
       </c>
       <c r="D63" t="s">
         <v>185</v>
@@ -14513,7 +14513,7 @@
         <v>76</v>
       </c>
       <c r="C66" t="s">
-        <v>121</v>
+        <v>146</v>
       </c>
       <c r="D66" t="s">
         <v>186</v>
@@ -14698,7 +14698,7 @@
         <v>76</v>
       </c>
       <c r="C67" t="s">
-        <v>122</v>
+        <v>147</v>
       </c>
       <c r="D67" t="s">
         <v>186</v>
@@ -14737,13 +14737,13 @@
         <v>699</v>
       </c>
       <c r="P67">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="Q67">
-        <v>7.41</v>
+        <v>0</v>
       </c>
       <c r="R67">
-        <v>17.5</v>
+        <v>0</v>
       </c>
       <c r="S67">
         <v>0</v>
@@ -14883,7 +14883,7 @@
         <v>76</v>
       </c>
       <c r="C68" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D68" t="s">
         <v>186</v>
@@ -15068,7 +15068,7 @@
         <v>76</v>
       </c>
       <c r="C69" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="D69" t="s">
         <v>185</v>
@@ -15253,7 +15253,7 @@
         <v>76</v>
       </c>
       <c r="C70" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="D70" t="s">
         <v>186</v>
@@ -15438,7 +15438,7 @@
         <v>76</v>
       </c>
       <c r="C71" t="s">
-        <v>126</v>
+        <v>121</v>
       </c>
       <c r="D71" t="s">
         <v>186</v>
@@ -15623,10 +15623,10 @@
         <v>76</v>
       </c>
       <c r="C72" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="D72" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E72" t="s">
         <v>258</v>
@@ -15662,13 +15662,13 @@
         <v>699</v>
       </c>
       <c r="P72">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="Q72">
-        <v>0</v>
+        <v>7.41</v>
       </c>
       <c r="R72">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="S72">
         <v>0</v>
@@ -15808,7 +15808,7 @@
         <v>76</v>
       </c>
       <c r="C73" t="s">
-        <v>148</v>
+        <v>125</v>
       </c>
       <c r="D73" t="s">
         <v>186</v>
@@ -15993,10 +15993,10 @@
         <v>76</v>
       </c>
       <c r="C74" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="D74" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E74" t="s">
         <v>260</v>
@@ -16178,7 +16178,7 @@
         <v>77</v>
       </c>
       <c r="C75" t="s">
-        <v>129</v>
+        <v>150</v>
       </c>
       <c r="D75" t="s">
         <v>186</v>
@@ -16363,7 +16363,7 @@
         <v>77</v>
       </c>
       <c r="C76" t="s">
-        <v>150</v>
+        <v>126</v>
       </c>
       <c r="D76" t="s">
         <v>186</v>
@@ -16548,10 +16548,10 @@
         <v>78</v>
       </c>
       <c r="C77" t="s">
-        <v>127</v>
+        <v>151</v>
       </c>
       <c r="D77" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E77" t="s">
         <v>263</v>
@@ -16733,10 +16733,10 @@
         <v>78</v>
       </c>
       <c r="C78" t="s">
-        <v>151</v>
+        <v>129</v>
       </c>
       <c r="D78" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E78" t="s">
         <v>264</v>
@@ -17288,10 +17288,10 @@
         <v>80</v>
       </c>
       <c r="C81" t="s">
-        <v>128</v>
+        <v>152</v>
       </c>
       <c r="D81" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E81" t="s">
         <v>267</v>
@@ -17473,7 +17473,7 @@
         <v>80</v>
       </c>
       <c r="C82" t="s">
-        <v>131</v>
+        <v>153</v>
       </c>
       <c r="D82" t="s">
         <v>186</v>
@@ -17512,13 +17512,13 @@
         <v>699</v>
       </c>
       <c r="P82">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="Q82">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="R82">
-        <v>4.01</v>
+        <v>0</v>
       </c>
       <c r="S82">
         <v>0</v>
@@ -17557,10 +17557,10 @@
         <v>0</v>
       </c>
       <c r="AE82">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AF82">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AG82">
         <v>0</v>
@@ -17658,7 +17658,7 @@
         <v>80</v>
       </c>
       <c r="C83" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="D83" t="s">
         <v>186</v>
@@ -17843,7 +17843,7 @@
         <v>80</v>
       </c>
       <c r="C84" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="D84" t="s">
         <v>186</v>
@@ -17882,13 +17882,13 @@
         <v>699</v>
       </c>
       <c r="P84">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="Q84">
-        <v>0</v>
+        <v>3.31</v>
       </c>
       <c r="R84">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="S84">
         <v>0</v>
@@ -17927,10 +17927,10 @@
         <v>0</v>
       </c>
       <c r="AE84">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AF84">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AG84">
         <v>0</v>
@@ -18028,10 +18028,10 @@
         <v>80</v>
       </c>
       <c r="C85" t="s">
-        <v>134</v>
+        <v>155</v>
       </c>
       <c r="D85" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E85" t="s">
         <v>271</v>
@@ -18067,13 +18067,13 @@
         <v>699</v>
       </c>
       <c r="P85">
-        <v>0</v>
+        <v>5.38</v>
       </c>
       <c r="Q85">
-        <v>0</v>
+        <v>4.37</v>
       </c>
       <c r="R85">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="S85">
         <v>0</v>
@@ -18213,7 +18213,7 @@
         <v>80</v>
       </c>
       <c r="C86" t="s">
-        <v>131</v>
+        <v>150</v>
       </c>
       <c r="D86" t="s">
         <v>186</v>
@@ -18252,13 +18252,13 @@
         <v>699</v>
       </c>
       <c r="P86">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Q86">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="R86">
-        <v>4.07</v>
+        <v>0</v>
       </c>
       <c r="S86">
         <v>0</v>
@@ -18297,10 +18297,10 @@
         <v>0</v>
       </c>
       <c r="AE86">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AF86">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AG86">
         <v>0</v>
@@ -18398,7 +18398,7 @@
         <v>80</v>
       </c>
       <c r="C87" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="D87" t="s">
         <v>186</v>
@@ -18583,7 +18583,7 @@
         <v>80</v>
       </c>
       <c r="C88" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="D88" t="s">
         <v>186</v>
@@ -18622,13 +18622,13 @@
         <v>699</v>
       </c>
       <c r="P88">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="Q88">
-        <v>0</v>
+        <v>3.66</v>
       </c>
       <c r="R88">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="S88">
         <v>0</v>
@@ -18667,10 +18667,10 @@
         <v>0</v>
       </c>
       <c r="AE88">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AF88">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AG88">
         <v>0</v>
@@ -18768,7 +18768,7 @@
         <v>80</v>
       </c>
       <c r="C89" t="s">
-        <v>155</v>
+        <v>131</v>
       </c>
       <c r="D89" t="s">
         <v>186</v>
@@ -18807,13 +18807,13 @@
         <v>699</v>
       </c>
       <c r="P89">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="Q89">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="R89">
-        <v>0</v>
+        <v>4.01</v>
       </c>
       <c r="S89">
         <v>0</v>
@@ -18852,10 +18852,10 @@
         <v>0</v>
       </c>
       <c r="AE89">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AF89">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AG89">
         <v>0</v>
@@ -18953,7 +18953,7 @@
         <v>80</v>
       </c>
       <c r="C90" t="s">
-        <v>150</v>
+        <v>125</v>
       </c>
       <c r="D90" t="s">
         <v>186</v>
@@ -19138,10 +19138,10 @@
         <v>80</v>
       </c>
       <c r="C91" t="s">
-        <v>156</v>
+        <v>132</v>
       </c>
       <c r="D91" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E91" t="s">
         <v>277</v>
@@ -19177,13 +19177,13 @@
         <v>699</v>
       </c>
       <c r="P91">
-        <v>5.38</v>
+        <v>0</v>
       </c>
       <c r="Q91">
-        <v>4.37</v>
+        <v>0</v>
       </c>
       <c r="R91">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="S91">
         <v>0</v>
@@ -19323,10 +19323,10 @@
         <v>80</v>
       </c>
       <c r="C92" t="s">
-        <v>156</v>
+        <v>128</v>
       </c>
       <c r="D92" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E92" t="s">
         <v>278</v>
@@ -19362,13 +19362,13 @@
         <v>699</v>
       </c>
       <c r="P92">
-        <v>2.46</v>
+        <v>0</v>
       </c>
       <c r="Q92">
-        <v>3.66</v>
+        <v>0</v>
       </c>
       <c r="R92">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="S92">
         <v>0</v>
@@ -19407,10 +19407,10 @@
         <v>0</v>
       </c>
       <c r="AE92">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AF92">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AG92">
         <v>0</v>
@@ -19547,13 +19547,13 @@
         <v>699</v>
       </c>
       <c r="P93">
-        <v>2.69</v>
+        <v>0</v>
       </c>
       <c r="Q93">
-        <v>3.31</v>
+        <v>0</v>
       </c>
       <c r="R93">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="S93">
         <v>0</v>
@@ -19592,10 +19592,10 @@
         <v>0</v>
       </c>
       <c r="AE93">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AF93">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AG93">
         <v>0</v>
@@ -19693,7 +19693,7 @@
         <v>80</v>
       </c>
       <c r="C94" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="D94" t="s">
         <v>186</v>
@@ -19732,13 +19732,13 @@
         <v>699</v>
       </c>
       <c r="P94">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Q94">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="R94">
-        <v>0</v>
+        <v>4.07</v>
       </c>
       <c r="S94">
         <v>0</v>
@@ -19777,10 +19777,10 @@
         <v>0</v>
       </c>
       <c r="AE94">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AF94">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AG94">
         <v>0</v>
@@ -20063,7 +20063,7 @@
         <v>82</v>
       </c>
       <c r="C96" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="D96" t="s">
         <v>186</v>
@@ -20248,7 +20248,7 @@
         <v>83</v>
       </c>
       <c r="C97" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="D97" t="s">
         <v>186</v>
@@ -20436,7 +20436,7 @@
         <v>158</v>
       </c>
       <c r="D98" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E98" t="s">
         <v>284</v>
@@ -20618,7 +20618,7 @@
         <v>83</v>
       </c>
       <c r="C99" t="s">
-        <v>158</v>
+        <v>136</v>
       </c>
       <c r="D99" t="s">
         <v>185</v>
@@ -20803,7 +20803,7 @@
         <v>83</v>
       </c>
       <c r="C100" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="D100" t="s">
         <v>185</v>
@@ -20988,7 +20988,7 @@
         <v>83</v>
       </c>
       <c r="C101" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="D101" t="s">
         <v>186</v>
@@ -21173,10 +21173,10 @@
         <v>83</v>
       </c>
       <c r="C102" t="s">
-        <v>145</v>
+        <v>159</v>
       </c>
       <c r="D102" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E102" t="s">
         <v>288</v>
@@ -21212,13 +21212,13 @@
         <v>699</v>
       </c>
       <c r="P102">
-        <v>4.68</v>
+        <v>0</v>
       </c>
       <c r="Q102">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R102">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="S102">
         <v>0</v>
@@ -21358,7 +21358,7 @@
         <v>83</v>
       </c>
       <c r="C103" t="s">
-        <v>160</v>
+        <v>145</v>
       </c>
       <c r="D103" t="s">
         <v>186</v>
@@ -21397,13 +21397,13 @@
         <v>699</v>
       </c>
       <c r="P103">
-        <v>0</v>
+        <v>4.68</v>
       </c>
       <c r="Q103">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R103">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="S103">
         <v>0</v>
@@ -21543,7 +21543,7 @@
         <v>83</v>
       </c>
       <c r="C104" t="s">
-        <v>161</v>
+        <v>141</v>
       </c>
       <c r="D104" t="s">
         <v>186</v>
@@ -21728,7 +21728,7 @@
         <v>83</v>
       </c>
       <c r="C105" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="D105" t="s">
         <v>186</v>
@@ -21913,10 +21913,10 @@
         <v>83</v>
       </c>
       <c r="C106" t="s">
-        <v>141</v>
+        <v>159</v>
       </c>
       <c r="D106" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E106" t="s">
         <v>292</v>
@@ -22098,10 +22098,10 @@
         <v>83</v>
       </c>
       <c r="C107" t="s">
-        <v>135</v>
+        <v>161</v>
       </c>
       <c r="D107" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E107" t="s">
         <v>293</v>
@@ -22283,7 +22283,7 @@
         <v>84</v>
       </c>
       <c r="C108" t="s">
-        <v>122</v>
+        <v>149</v>
       </c>
       <c r="D108" t="s">
         <v>186</v>
@@ -22322,13 +22322,13 @@
         <v>699</v>
       </c>
       <c r="P108">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="Q108">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="R108">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="S108">
         <v>0</v>
@@ -22468,7 +22468,7 @@
         <v>84</v>
       </c>
       <c r="C109" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="D109" t="s">
         <v>186</v>
@@ -22653,7 +22653,7 @@
         <v>84</v>
       </c>
       <c r="C110" t="s">
-        <v>149</v>
+        <v>122</v>
       </c>
       <c r="D110" t="s">
         <v>186</v>
@@ -22692,13 +22692,13 @@
         <v>699</v>
       </c>
       <c r="P110">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="Q110">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="R110">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="S110">
         <v>0</v>
@@ -22838,10 +22838,10 @@
         <v>85</v>
       </c>
       <c r="C111" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="D111" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E111" t="s">
         <v>297</v>
@@ -23023,7 +23023,7 @@
         <v>85</v>
       </c>
       <c r="C112" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="D112" t="s">
         <v>186</v>
@@ -23208,7 +23208,7 @@
         <v>85</v>
       </c>
       <c r="C113" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="D113" t="s">
         <v>186</v>
@@ -23393,10 +23393,10 @@
         <v>85</v>
       </c>
       <c r="C114" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
       <c r="D114" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E114" t="s">
         <v>300</v>
@@ -23578,7 +23578,7 @@
         <v>85</v>
       </c>
       <c r="C115" t="s">
-        <v>148</v>
+        <v>139</v>
       </c>
       <c r="D115" t="s">
         <v>186</v>
@@ -25798,7 +25798,7 @@
         <v>87</v>
       </c>
       <c r="C127" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="D127" t="s">
         <v>186</v>
@@ -25983,7 +25983,7 @@
         <v>87</v>
       </c>
       <c r="C128" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="D128" t="s">
         <v>186</v>
@@ -26168,7 +26168,7 @@
         <v>87</v>
       </c>
       <c r="C129" t="s">
-        <v>163</v>
+        <v>129</v>
       </c>
       <c r="D129" t="s">
         <v>186</v>
@@ -26353,7 +26353,7 @@
         <v>87</v>
       </c>
       <c r="C130" t="s">
-        <v>120</v>
+        <v>164</v>
       </c>
       <c r="D130" t="s">
         <v>186</v>
@@ -26538,7 +26538,7 @@
         <v>87</v>
       </c>
       <c r="C131" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="D131" t="s">
         <v>186</v>
@@ -26723,7 +26723,7 @@
         <v>87</v>
       </c>
       <c r="C132" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="D132" t="s">
         <v>186</v>
@@ -26908,7 +26908,7 @@
         <v>87</v>
       </c>
       <c r="C133" t="s">
-        <v>124</v>
+        <v>164</v>
       </c>
       <c r="D133" t="s">
         <v>186</v>
@@ -27093,7 +27093,7 @@
         <v>87</v>
       </c>
       <c r="C134" t="s">
-        <v>160</v>
+        <v>120</v>
       </c>
       <c r="D134" t="s">
         <v>186</v>
@@ -27278,10 +27278,10 @@
         <v>87</v>
       </c>
       <c r="C135" t="s">
-        <v>163</v>
+        <v>144</v>
       </c>
       <c r="D135" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E135" t="s">
         <v>321</v>
@@ -27463,7 +27463,7 @@
         <v>87</v>
       </c>
       <c r="C136" t="s">
-        <v>127</v>
+        <v>161</v>
       </c>
       <c r="D136" t="s">
         <v>186</v>
@@ -27648,7 +27648,7 @@
         <v>87</v>
       </c>
       <c r="C137" t="s">
-        <v>160</v>
+        <v>124</v>
       </c>
       <c r="D137" t="s">
         <v>186</v>
@@ -27833,7 +27833,7 @@
         <v>87</v>
       </c>
       <c r="C138" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="D138" t="s">
         <v>186</v>
@@ -28018,7 +28018,7 @@
         <v>87</v>
       </c>
       <c r="C139" t="s">
-        <v>164</v>
+        <v>143</v>
       </c>
       <c r="D139" t="s">
         <v>186</v>
@@ -28203,10 +28203,10 @@
         <v>87</v>
       </c>
       <c r="C140" t="s">
-        <v>151</v>
+        <v>165</v>
       </c>
       <c r="D140" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E140" t="s">
         <v>326</v>
@@ -28391,7 +28391,7 @@
         <v>165</v>
       </c>
       <c r="D141" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E141" t="s">
         <v>327</v>
@@ -28427,13 +28427,13 @@
         <v>699</v>
       </c>
       <c r="P141">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Q141">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="R141">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="S141">
         <v>0</v>
@@ -28576,13 +28576,13 @@
         <v>165</v>
       </c>
       <c r="D142" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E142" t="s">
         <v>328</v>
       </c>
       <c r="F142" t="s">
-        <v>584</v>
+        <v>284</v>
       </c>
       <c r="G142">
         <v>0</v>
@@ -28612,13 +28612,13 @@
         <v>699</v>
       </c>
       <c r="P142">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Q142">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="R142">
-        <v>3.01</v>
+        <v>0</v>
       </c>
       <c r="S142">
         <v>0</v>
@@ -28767,7 +28767,7 @@
         <v>329</v>
       </c>
       <c r="F143" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="G143">
         <v>0</v>
@@ -28943,16 +28943,16 @@
         <v>87</v>
       </c>
       <c r="C144" t="s">
-        <v>143</v>
+        <v>151</v>
       </c>
       <c r="D144" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E144" t="s">
         <v>330</v>
       </c>
       <c r="F144" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="G144">
         <v>0</v>
@@ -29137,7 +29137,7 @@
         <v>331</v>
       </c>
       <c r="F145" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="G145">
         <v>0</v>
@@ -29313,7 +29313,7 @@
         <v>87</v>
       </c>
       <c r="C146" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="D146" t="s">
         <v>185</v>
@@ -29322,7 +29322,7 @@
         <v>332</v>
       </c>
       <c r="F146" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="G146">
         <v>0</v>
@@ -29352,13 +29352,13 @@
         <v>699</v>
       </c>
       <c r="P146">
-        <v>5.4</v>
+        <v>2.2</v>
       </c>
       <c r="Q146">
-        <v>4.6</v>
+        <v>3.4</v>
       </c>
       <c r="R146">
-        <v>1.51</v>
+        <v>3.2</v>
       </c>
       <c r="S146">
         <v>0</v>
@@ -29498,7 +29498,7 @@
         <v>87</v>
       </c>
       <c r="C147" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="D147" t="s">
         <v>185</v>
@@ -29507,7 +29507,7 @@
         <v>333</v>
       </c>
       <c r="F147" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="G147">
         <v>0</v>
@@ -29537,13 +29537,13 @@
         <v>699</v>
       </c>
       <c r="P147">
-        <v>3.1</v>
+        <v>4.07</v>
       </c>
       <c r="Q147">
-        <v>3.7</v>
+        <v>3.9</v>
       </c>
       <c r="R147">
-        <v>2.12</v>
+        <v>1.78</v>
       </c>
       <c r="S147">
         <v>0</v>
@@ -29683,16 +29683,16 @@
         <v>87</v>
       </c>
       <c r="C148" t="s">
-        <v>126</v>
+        <v>166</v>
       </c>
       <c r="D148" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E148" t="s">
         <v>334</v>
       </c>
       <c r="F148" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="G148">
         <v>0</v>
@@ -29722,13 +29722,13 @@
         <v>699</v>
       </c>
       <c r="P148">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="Q148">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="R148">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="S148">
         <v>0</v>
@@ -29868,7 +29868,7 @@
         <v>87</v>
       </c>
       <c r="C149" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="D149" t="s">
         <v>185</v>
@@ -29877,7 +29877,7 @@
         <v>335</v>
       </c>
       <c r="F149" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="G149">
         <v>0</v>
@@ -30053,7 +30053,7 @@
         <v>87</v>
       </c>
       <c r="C150" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="D150" t="s">
         <v>185</v>
@@ -30062,7 +30062,7 @@
         <v>336</v>
       </c>
       <c r="F150" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="G150">
         <v>0</v>
@@ -30092,13 +30092,13 @@
         <v>699</v>
       </c>
       <c r="P150">
-        <v>4.07</v>
+        <v>5.4</v>
       </c>
       <c r="Q150">
-        <v>3.9</v>
+        <v>4.6</v>
       </c>
       <c r="R150">
-        <v>1.78</v>
+        <v>1.51</v>
       </c>
       <c r="S150">
         <v>0</v>
@@ -30241,13 +30241,13 @@
         <v>166</v>
       </c>
       <c r="D151" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E151" t="s">
         <v>337</v>
       </c>
       <c r="F151" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="G151">
         <v>0</v>
@@ -30277,13 +30277,13 @@
         <v>699</v>
       </c>
       <c r="P151">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Q151">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="R151">
-        <v>0</v>
+        <v>3.01</v>
       </c>
       <c r="S151">
         <v>0</v>
@@ -30423,7 +30423,7 @@
         <v>87</v>
       </c>
       <c r="C152" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="D152" t="s">
         <v>186</v>
@@ -30432,7 +30432,7 @@
         <v>338</v>
       </c>
       <c r="F152" t="s">
-        <v>291</v>
+        <v>593</v>
       </c>
       <c r="G152">
         <v>0</v>
@@ -30608,7 +30608,7 @@
         <v>87</v>
       </c>
       <c r="C153" t="s">
-        <v>166</v>
+        <v>161</v>
       </c>
       <c r="D153" t="s">
         <v>186</v>
@@ -30793,7 +30793,7 @@
         <v>87</v>
       </c>
       <c r="C154" t="s">
-        <v>166</v>
+        <v>125</v>
       </c>
       <c r="D154" t="s">
         <v>186</v>
@@ -30978,7 +30978,7 @@
         <v>87</v>
       </c>
       <c r="C155" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="D155" t="s">
         <v>186</v>
@@ -31163,10 +31163,10 @@
         <v>87</v>
       </c>
       <c r="C156" t="s">
-        <v>147</v>
+        <v>164</v>
       </c>
       <c r="D156" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E156" t="s">
         <v>342</v>
@@ -32312,13 +32312,13 @@
         <v>699</v>
       </c>
       <c r="P162">
-        <v>5.17</v>
+        <v>0</v>
       </c>
       <c r="Q162">
-        <v>4.37</v>
+        <v>0</v>
       </c>
       <c r="R162">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="S162">
         <v>0</v>
@@ -32357,10 +32357,10 @@
         <v>0</v>
       </c>
       <c r="AE162">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AF162">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AG162">
         <v>0</v>
@@ -32458,7 +32458,7 @@
         <v>89</v>
       </c>
       <c r="C163" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="D163" t="s">
         <v>186</v>
@@ -32497,13 +32497,13 @@
         <v>699</v>
       </c>
       <c r="P163">
-        <v>1.78</v>
+        <v>5.17</v>
       </c>
       <c r="Q163">
-        <v>4.32</v>
+        <v>4.37</v>
       </c>
       <c r="R163">
-        <v>4.52</v>
+        <v>1.69</v>
       </c>
       <c r="S163">
         <v>0</v>
@@ -32542,16 +32542,16 @@
         <v>0</v>
       </c>
       <c r="AE163">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AF163">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AG163">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AH163">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AI163">
         <v>0</v>
@@ -32643,7 +32643,7 @@
         <v>89</v>
       </c>
       <c r="C164" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="D164" t="s">
         <v>186</v>
@@ -32682,13 +32682,13 @@
         <v>699</v>
       </c>
       <c r="P164">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="Q164">
-        <v>0</v>
+        <v>4.32</v>
       </c>
       <c r="R164">
-        <v>0</v>
+        <v>4.52</v>
       </c>
       <c r="S164">
         <v>0</v>
@@ -32733,10 +32733,10 @@
         <v>0</v>
       </c>
       <c r="AG164">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AH164">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AI164">
         <v>0</v>
@@ -33198,10 +33198,10 @@
         <v>90</v>
       </c>
       <c r="C167" t="s">
-        <v>135</v>
+        <v>169</v>
       </c>
       <c r="D167" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E167" t="s">
         <v>353</v>
@@ -33753,7 +33753,7 @@
         <v>90</v>
       </c>
       <c r="C170" t="s">
-        <v>145</v>
+        <v>169</v>
       </c>
       <c r="D170" t="s">
         <v>186</v>
@@ -33938,7 +33938,7 @@
         <v>90</v>
       </c>
       <c r="C171" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="D171" t="s">
         <v>186</v>
@@ -34123,7 +34123,7 @@
         <v>90</v>
       </c>
       <c r="C172" t="s">
-        <v>169</v>
+        <v>131</v>
       </c>
       <c r="D172" t="s">
         <v>186</v>
@@ -34162,13 +34162,13 @@
         <v>699</v>
       </c>
       <c r="P172">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="Q172">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R172">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="S172">
         <v>0</v>
@@ -34308,7 +34308,7 @@
         <v>90</v>
       </c>
       <c r="C173" t="s">
-        <v>169</v>
+        <v>152</v>
       </c>
       <c r="D173" t="s">
         <v>186</v>
@@ -34347,13 +34347,13 @@
         <v>699</v>
       </c>
       <c r="P173">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="Q173">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R173">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="S173">
         <v>0</v>
@@ -34493,7 +34493,7 @@
         <v>90</v>
       </c>
       <c r="C174" t="s">
-        <v>131</v>
+        <v>170</v>
       </c>
       <c r="D174" t="s">
         <v>186</v>
@@ -34532,13 +34532,13 @@
         <v>699</v>
       </c>
       <c r="P174">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="Q174">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="R174">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="S174">
         <v>0</v>
@@ -34678,7 +34678,7 @@
         <v>90</v>
       </c>
       <c r="C175" t="s">
-        <v>169</v>
+        <v>145</v>
       </c>
       <c r="D175" t="s">
         <v>186</v>
@@ -34863,10 +34863,10 @@
         <v>90</v>
       </c>
       <c r="C176" t="s">
-        <v>153</v>
+        <v>136</v>
       </c>
       <c r="D176" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E176" t="s">
         <v>362</v>
@@ -34902,13 +34902,13 @@
         <v>699</v>
       </c>
       <c r="P176">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="Q176">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="R176">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="S176">
         <v>0</v>
@@ -35233,10 +35233,10 @@
         <v>92</v>
       </c>
       <c r="C178" t="s">
-        <v>136</v>
+        <v>159</v>
       </c>
       <c r="D178" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E178" t="s">
         <v>364</v>
@@ -35418,10 +35418,10 @@
         <v>92</v>
       </c>
       <c r="C179" t="s">
-        <v>158</v>
+        <v>135</v>
       </c>
       <c r="D179" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E179" t="s">
         <v>365</v>
@@ -35603,10 +35603,10 @@
         <v>92</v>
       </c>
       <c r="C180" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="D180" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E180" t="s">
         <v>366</v>
@@ -35788,10 +35788,10 @@
         <v>92</v>
       </c>
       <c r="C181" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="D181" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E181" t="s">
         <v>367</v>
@@ -35973,7 +35973,7 @@
         <v>93</v>
       </c>
       <c r="C182" t="s">
-        <v>122</v>
+        <v>158</v>
       </c>
       <c r="D182" t="s">
         <v>186</v>
@@ -36012,13 +36012,13 @@
         <v>699</v>
       </c>
       <c r="P182">
-        <v>2.25</v>
+        <v>1.45</v>
       </c>
       <c r="Q182">
-        <v>3.66</v>
+        <v>3.8</v>
       </c>
       <c r="R182">
-        <v>3.36</v>
+        <v>6.76</v>
       </c>
       <c r="S182">
         <v>0</v>
@@ -36343,10 +36343,10 @@
         <v>93</v>
       </c>
       <c r="C184" t="s">
-        <v>149</v>
+        <v>173</v>
       </c>
       <c r="D184" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E184" t="s">
         <v>370</v>
@@ -36528,10 +36528,10 @@
         <v>93</v>
       </c>
       <c r="C185" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="D185" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E185" t="s">
         <v>371</v>
@@ -36713,7 +36713,7 @@
         <v>93</v>
       </c>
       <c r="C186" t="s">
-        <v>149</v>
+        <v>172</v>
       </c>
       <c r="D186" t="s">
         <v>186</v>
@@ -36898,7 +36898,7 @@
         <v>93</v>
       </c>
       <c r="C187" t="s">
-        <v>137</v>
+        <v>172</v>
       </c>
       <c r="D187" t="s">
         <v>186</v>
@@ -37083,7 +37083,7 @@
         <v>93</v>
       </c>
       <c r="C188" t="s">
-        <v>159</v>
+        <v>140</v>
       </c>
       <c r="D188" t="s">
         <v>186</v>
@@ -37122,13 +37122,13 @@
         <v>699</v>
       </c>
       <c r="P188">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="Q188">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="R188">
-        <v>4.56</v>
+        <v>0</v>
       </c>
       <c r="S188">
         <v>0</v>
@@ -37268,10 +37268,10 @@
         <v>93</v>
       </c>
       <c r="C189" t="s">
-        <v>173</v>
+        <v>147</v>
       </c>
       <c r="D189" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E189" t="s">
         <v>375</v>
@@ -37453,10 +37453,10 @@
         <v>93</v>
       </c>
       <c r="C190" t="s">
-        <v>173</v>
+        <v>158</v>
       </c>
       <c r="D190" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E190" t="s">
         <v>376</v>
@@ -37492,13 +37492,13 @@
         <v>699</v>
       </c>
       <c r="P190">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="Q190">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R190">
-        <v>0</v>
+        <v>4.56</v>
       </c>
       <c r="S190">
         <v>0</v>
@@ -37638,10 +37638,10 @@
         <v>93</v>
       </c>
       <c r="C191" t="s">
-        <v>174</v>
+        <v>154</v>
       </c>
       <c r="D191" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E191" t="s">
         <v>377</v>
@@ -37823,7 +37823,7 @@
         <v>93</v>
       </c>
       <c r="C192" t="s">
-        <v>172</v>
+        <v>147</v>
       </c>
       <c r="D192" t="s">
         <v>186</v>
@@ -38008,10 +38008,10 @@
         <v>93</v>
       </c>
       <c r="C193" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="D193" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E193" t="s">
         <v>379</v>
@@ -38193,7 +38193,7 @@
         <v>93</v>
       </c>
       <c r="C194" t="s">
-        <v>146</v>
+        <v>122</v>
       </c>
       <c r="D194" t="s">
         <v>186</v>
@@ -38232,13 +38232,13 @@
         <v>699</v>
       </c>
       <c r="P194">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Q194">
-        <v>0</v>
+        <v>3.66</v>
       </c>
       <c r="R194">
-        <v>0</v>
+        <v>3.36</v>
       </c>
       <c r="S194">
         <v>0</v>
@@ -38378,7 +38378,7 @@
         <v>93</v>
       </c>
       <c r="C195" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="D195" t="s">
         <v>186</v>
@@ -38563,7 +38563,7 @@
         <v>93</v>
       </c>
       <c r="C196" t="s">
-        <v>159</v>
+        <v>172</v>
       </c>
       <c r="D196" t="s">
         <v>186</v>
@@ -38602,13 +38602,13 @@
         <v>699</v>
       </c>
       <c r="P196">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="Q196">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="R196">
-        <v>6.76</v>
+        <v>0</v>
       </c>
       <c r="S196">
         <v>0</v>
@@ -38748,10 +38748,10 @@
         <v>94</v>
       </c>
       <c r="C197" t="s">
-        <v>160</v>
+        <v>144</v>
       </c>
       <c r="D197" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E197" t="s">
         <v>383</v>
@@ -39488,10 +39488,10 @@
         <v>94</v>
       </c>
       <c r="C201" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="D201" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E201" t="s">
         <v>387</v>
@@ -39673,7 +39673,7 @@
         <v>94</v>
       </c>
       <c r="C202" t="s">
-        <v>147</v>
+        <v>176</v>
       </c>
       <c r="D202" t="s">
         <v>185</v>
@@ -39858,7 +39858,7 @@
         <v>94</v>
       </c>
       <c r="C203" t="s">
-        <v>175</v>
+        <v>161</v>
       </c>
       <c r="D203" t="s">
         <v>186</v>
@@ -40043,7 +40043,7 @@
         <v>94</v>
       </c>
       <c r="C204" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="D204" t="s">
         <v>186</v>
@@ -40228,7 +40228,7 @@
         <v>95</v>
       </c>
       <c r="C205" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="D205" t="s">
         <v>186</v>
@@ -40598,7 +40598,7 @@
         <v>96</v>
       </c>
       <c r="C207" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="D207" t="s">
         <v>186</v>
@@ -40783,7 +40783,7 @@
         <v>97</v>
       </c>
       <c r="C208" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="D208" t="s">
         <v>186</v>
@@ -40968,10 +40968,10 @@
         <v>97</v>
       </c>
       <c r="C209" t="s">
-        <v>171</v>
+        <v>177</v>
       </c>
       <c r="D209" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E209" t="s">
         <v>395</v>
@@ -41153,10 +41153,10 @@
         <v>97</v>
       </c>
       <c r="C210" t="s">
-        <v>177</v>
+        <v>170</v>
       </c>
       <c r="D210" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E210" t="s">
         <v>396</v>
@@ -41523,7 +41523,7 @@
         <v>98</v>
       </c>
       <c r="C212" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="D212" t="s">
         <v>186</v>
@@ -42078,10 +42078,10 @@
         <v>100</v>
       </c>
       <c r="C215" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="D215" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E215" t="s">
         <v>401</v>
@@ -42117,13 +42117,13 @@
         <v>699</v>
       </c>
       <c r="P215">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="Q215">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="R215">
-        <v>2.96</v>
+        <v>0</v>
       </c>
       <c r="S215">
         <v>0</v>
@@ -42162,10 +42162,10 @@
         <v>0</v>
       </c>
       <c r="AE215">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AF215">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AG215">
         <v>0</v>
@@ -42263,10 +42263,10 @@
         <v>100</v>
       </c>
       <c r="C216" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="D216" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E216" t="s">
         <v>402</v>
@@ -42302,13 +42302,13 @@
         <v>699</v>
       </c>
       <c r="P216">
-        <v>2.15</v>
+        <v>2.38</v>
       </c>
       <c r="Q216">
-        <v>3.44</v>
+        <v>3.9</v>
       </c>
       <c r="R216">
-        <v>3.5</v>
+        <v>2.96</v>
       </c>
       <c r="S216">
         <v>0</v>
@@ -42347,10 +42347,10 @@
         <v>0</v>
       </c>
       <c r="AE216">
-        <v>1.95</v>
+        <v>1.58</v>
       </c>
       <c r="AF216">
-        <v>1.75</v>
+        <v>2.25</v>
       </c>
       <c r="AG216">
         <v>0</v>
@@ -42448,10 +42448,10 @@
         <v>100</v>
       </c>
       <c r="C217" t="s">
-        <v>181</v>
+        <v>149</v>
       </c>
       <c r="D217" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E217" t="s">
         <v>403</v>
@@ -42633,10 +42633,10 @@
         <v>100</v>
       </c>
       <c r="C218" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="D218" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E218" t="s">
         <v>404</v>
@@ -42672,13 +42672,13 @@
         <v>699</v>
       </c>
       <c r="P218">
-        <v>4.68</v>
+        <v>0</v>
       </c>
       <c r="Q218">
-        <v>4.32</v>
+        <v>0</v>
       </c>
       <c r="R218">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="S218">
         <v>0</v>
@@ -42717,10 +42717,10 @@
         <v>0</v>
       </c>
       <c r="AE218">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AF218">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AG218">
         <v>0</v>
@@ -42818,10 +42818,10 @@
         <v>100</v>
       </c>
       <c r="C219" t="s">
-        <v>146</v>
+        <v>178</v>
       </c>
       <c r="D219" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E219" t="s">
         <v>405</v>
@@ -43003,10 +43003,10 @@
         <v>100</v>
       </c>
       <c r="C220" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="D220" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E220" t="s">
         <v>406</v>
@@ -43042,13 +43042,13 @@
         <v>699</v>
       </c>
       <c r="P220">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="Q220">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="R220">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="S220">
         <v>0</v>
@@ -43087,10 +43087,10 @@
         <v>0</v>
       </c>
       <c r="AE220">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AF220">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AG220">
         <v>0</v>
@@ -43227,13 +43227,13 @@
         <v>699</v>
       </c>
       <c r="P221">
-        <v>3.17</v>
+        <v>1.59</v>
       </c>
       <c r="Q221">
-        <v>3.68</v>
+        <v>4.73</v>
       </c>
       <c r="R221">
-        <v>2.34</v>
+        <v>5.79</v>
       </c>
       <c r="S221">
         <v>0</v>
@@ -43272,16 +43272,16 @@
         <v>0</v>
       </c>
       <c r="AE221">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AF221">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AG221">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AH221">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AI221">
         <v>0</v>
@@ -43412,13 +43412,13 @@
         <v>699</v>
       </c>
       <c r="P222">
-        <v>2.48</v>
+        <v>1.18</v>
       </c>
       <c r="Q222">
-        <v>3.5</v>
+        <v>9.15</v>
       </c>
       <c r="R222">
-        <v>3.07</v>
+        <v>17</v>
       </c>
       <c r="S222">
         <v>0</v>
@@ -43457,16 +43457,16 @@
         <v>0</v>
       </c>
       <c r="AE222">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AF222">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AG222">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AH222">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AI222">
         <v>0</v>
@@ -43558,7 +43558,7 @@
         <v>100</v>
       </c>
       <c r="C223" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="D223" t="s">
         <v>185</v>
@@ -43597,13 +43597,13 @@
         <v>699</v>
       </c>
       <c r="P223">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="Q223">
-        <v>0</v>
+        <v>3.73</v>
       </c>
       <c r="R223">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="S223">
         <v>0</v>
@@ -43642,10 +43642,10 @@
         <v>0</v>
       </c>
       <c r="AE223">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AF223">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AG223">
         <v>0</v>
@@ -43782,13 +43782,13 @@
         <v>699</v>
       </c>
       <c r="P224">
-        <v>4.05</v>
+        <v>2.48</v>
       </c>
       <c r="Q224">
-        <v>3.76</v>
+        <v>3.5</v>
       </c>
       <c r="R224">
-        <v>1.99</v>
+        <v>3.07</v>
       </c>
       <c r="S224">
         <v>0</v>
@@ -43827,10 +43827,10 @@
         <v>0</v>
       </c>
       <c r="AE224">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AF224">
-        <v>1.85</v>
+        <v>1.9</v>
       </c>
       <c r="AG224">
         <v>0</v>
@@ -43967,13 +43967,13 @@
         <v>699</v>
       </c>
       <c r="P225">
-        <v>1.18</v>
+        <v>4.05</v>
       </c>
       <c r="Q225">
-        <v>9.15</v>
+        <v>3.76</v>
       </c>
       <c r="R225">
-        <v>17</v>
+        <v>1.99</v>
       </c>
       <c r="S225">
         <v>0</v>
@@ -44012,16 +44012,16 @@
         <v>0</v>
       </c>
       <c r="AE225">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AF225">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG225">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AH225">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AI225">
         <v>0</v>
@@ -44152,13 +44152,13 @@
         <v>699</v>
       </c>
       <c r="P226">
-        <v>1.59</v>
+        <v>4.68</v>
       </c>
       <c r="Q226">
-        <v>4.73</v>
+        <v>4.32</v>
       </c>
       <c r="R226">
-        <v>5.79</v>
+        <v>1.76</v>
       </c>
       <c r="S226">
         <v>0</v>
@@ -44197,16 +44197,16 @@
         <v>0</v>
       </c>
       <c r="AE226">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AF226">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AG226">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AH226">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AI226">
         <v>0</v>
@@ -44337,13 +44337,13 @@
         <v>699</v>
       </c>
       <c r="P227">
-        <v>3.8</v>
+        <v>3.17</v>
       </c>
       <c r="Q227">
-        <v>3.78</v>
+        <v>3.68</v>
       </c>
       <c r="R227">
-        <v>2.05</v>
+        <v>2.34</v>
       </c>
       <c r="S227">
         <v>0</v>
@@ -44382,10 +44382,10 @@
         <v>0</v>
       </c>
       <c r="AE227">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="AF227">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="AG227">
         <v>0</v>
@@ -44483,7 +44483,7 @@
         <v>100</v>
       </c>
       <c r="C228" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="D228" t="s">
         <v>185</v>
@@ -44522,13 +44522,13 @@
         <v>699</v>
       </c>
       <c r="P228">
-        <v>5.3</v>
+        <v>0</v>
       </c>
       <c r="Q228">
-        <v>3.73</v>
+        <v>0</v>
       </c>
       <c r="R228">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="S228">
         <v>0</v>
@@ -44567,10 +44567,10 @@
         <v>0</v>
       </c>
       <c r="AE228">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AF228">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AG228">
         <v>0</v>
@@ -44668,7 +44668,7 @@
         <v>100</v>
       </c>
       <c r="C229" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="D229" t="s">
         <v>185</v>
@@ -44707,13 +44707,13 @@
         <v>699</v>
       </c>
       <c r="P229">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Q229">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="R229">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="S229">
         <v>0</v>
@@ -44752,10 +44752,10 @@
         <v>0</v>
       </c>
       <c r="AE229">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AF229">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG229">
         <v>0</v>
@@ -45778,7 +45778,7 @@
         <v>102</v>
       </c>
       <c r="C235" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="D235" t="s">
         <v>185</v>
@@ -46148,7 +46148,7 @@
         <v>102</v>
       </c>
       <c r="C237" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="D237" t="s">
         <v>185</v>
@@ -46888,7 +46888,7 @@
         <v>105</v>
       </c>
       <c r="C241" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="D241" t="s">
         <v>185</v>
@@ -47073,7 +47073,7 @@
         <v>106</v>
       </c>
       <c r="C242" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="D242" t="s">
         <v>185</v>
@@ -47112,13 +47112,13 @@
         <v>699</v>
       </c>
       <c r="P242">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="Q242">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="R242">
-        <v>0</v>
+        <v>4.84</v>
       </c>
       <c r="S242">
         <v>0</v>
@@ -47157,10 +47157,10 @@
         <v>0</v>
       </c>
       <c r="AE242">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AF242">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG242">
         <v>0</v>
@@ -47258,7 +47258,7 @@
         <v>106</v>
       </c>
       <c r="C243" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="D243" t="s">
         <v>185</v>
@@ -47297,13 +47297,13 @@
         <v>699</v>
       </c>
       <c r="P243">
-        <v>2.26</v>
+        <v>2.13</v>
       </c>
       <c r="Q243">
-        <v>3.22</v>
+        <v>3.34</v>
       </c>
       <c r="R243">
-        <v>3.46</v>
+        <v>3.67</v>
       </c>
       <c r="S243">
         <v>0</v>
@@ -47342,10 +47342,10 @@
         <v>0</v>
       </c>
       <c r="AE243">
-        <v>2.25</v>
+        <v>1.95</v>
       </c>
       <c r="AF243">
-        <v>1.57</v>
+        <v>1.73</v>
       </c>
       <c r="AG243">
         <v>0</v>
@@ -47443,7 +47443,7 @@
         <v>106</v>
       </c>
       <c r="C244" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="D244" t="s">
         <v>185</v>
@@ -47482,13 +47482,13 @@
         <v>699</v>
       </c>
       <c r="P244">
-        <v>1.79</v>
+        <v>2.26</v>
       </c>
       <c r="Q244">
-        <v>3.62</v>
+        <v>3.22</v>
       </c>
       <c r="R244">
-        <v>4.84</v>
+        <v>3.46</v>
       </c>
       <c r="S244">
         <v>0</v>
@@ -47527,10 +47527,10 @@
         <v>0</v>
       </c>
       <c r="AE244">
-        <v>1.87</v>
+        <v>2.25</v>
       </c>
       <c r="AF244">
-        <v>1.8</v>
+        <v>1.57</v>
       </c>
       <c r="AG244">
         <v>0</v>
@@ -47628,7 +47628,7 @@
         <v>106</v>
       </c>
       <c r="C245" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="D245" t="s">
         <v>185</v>
@@ -47667,13 +47667,13 @@
         <v>699</v>
       </c>
       <c r="P245">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="Q245">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="R245">
-        <v>3.67</v>
+        <v>0</v>
       </c>
       <c r="S245">
         <v>0</v>
@@ -47712,10 +47712,10 @@
         <v>0</v>
       </c>
       <c r="AE245">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AF245">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AG245">
         <v>0</v>
@@ -47998,7 +47998,7 @@
         <v>108</v>
       </c>
       <c r="C247" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="D247" t="s">
         <v>185</v>
@@ -48037,13 +48037,13 @@
         <v>699</v>
       </c>
       <c r="P247">
-        <v>3.79</v>
+        <v>0</v>
       </c>
       <c r="Q247">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="R247">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="S247">
         <v>0</v>
@@ -48082,10 +48082,10 @@
         <v>0</v>
       </c>
       <c r="AE247">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AF247">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AG247">
         <v>0</v>
@@ -48183,7 +48183,7 @@
         <v>108</v>
       </c>
       <c r="C248" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="D248" t="s">
         <v>185</v>
@@ -48222,13 +48222,13 @@
         <v>699</v>
       </c>
       <c r="P248">
-        <v>0</v>
+        <v>3.79</v>
       </c>
       <c r="Q248">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="R248">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="S248">
         <v>0</v>
@@ -48267,10 +48267,10 @@
         <v>0</v>
       </c>
       <c r="AE248">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AF248">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AG248">
         <v>0</v>
@@ -48368,7 +48368,7 @@
         <v>109</v>
       </c>
       <c r="C249" t="s">
-        <v>177</v>
+        <v>184</v>
       </c>
       <c r="D249" t="s">
         <v>185</v>
@@ -48553,7 +48553,7 @@
         <v>109</v>
       </c>
       <c r="C250" t="s">
-        <v>184</v>
+        <v>174</v>
       </c>
       <c r="D250" t="s">
         <v>185</v>
@@ -48738,7 +48738,7 @@
         <v>109</v>
       </c>
       <c r="C251" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="D251" t="s">
         <v>185</v>
@@ -49108,7 +49108,7 @@
         <v>111</v>
       </c>
       <c r="C253" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="D253" t="s">
         <v>185</v>
@@ -49293,7 +49293,7 @@
         <v>111</v>
       </c>
       <c r="C254" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="D254" t="s">
         <v>185</v>

--- a/jogos_2026-05-10.xlsx
+++ b/jogos_2026-05-10.xlsx
@@ -364,12 +364,12 @@
     <t>South Korea K League 2</t>
   </si>
   <si>
+    <t>South Korea K League 1</t>
+  </si>
+  <si>
     <t>Australia New South Wales NPL</t>
   </si>
   <si>
-    <t>South Korea K League 1</t>
-  </si>
-  <si>
     <t>China China League One</t>
   </si>
   <si>
@@ -391,21 +391,21 @@
     <t>Spain Primera Division Women</t>
   </si>
   <si>
+    <t>Poland 1. Liga</t>
+  </si>
+  <si>
+    <t>Portugal Liga 3</t>
+  </si>
+  <si>
+    <t>Kazakhstan Kazakhstan Premier League</t>
+  </si>
+  <si>
+    <t>Vietnam V.League 1</t>
+  </si>
+  <si>
     <t>Ethiopia Ethiopia Premier League</t>
   </si>
   <si>
-    <t>Vietnam V.League 1</t>
-  </si>
-  <si>
-    <t>Portugal Liga 3</t>
-  </si>
-  <si>
-    <t>Kazakhstan Kazakhstan Premier League</t>
-  </si>
-  <si>
-    <t>Poland 1. Liga</t>
-  </si>
-  <si>
     <t>Poland Ekstraklasa</t>
   </si>
   <si>
@@ -427,63 +427,63 @@
     <t>Lithuania A Lyga</t>
   </si>
   <si>
+    <t>Estonia Meistriliiga</t>
+  </si>
+  <si>
     <t>Germany 2. Bundesliga</t>
   </si>
   <si>
+    <t>India Indian Super League</t>
+  </si>
+  <si>
+    <t>Germany 3. Liga</t>
+  </si>
+  <si>
     <t>Singapore S.League</t>
   </si>
   <si>
-    <t>Germany 3. Liga</t>
-  </si>
-  <si>
     <t>Belgium Pro League</t>
   </si>
   <si>
-    <t>India Indian Super League</t>
-  </si>
-  <si>
-    <t>Estonia Meistriliiga</t>
-  </si>
-  <si>
     <t>Croatia Druga HNL</t>
   </si>
   <si>
+    <t>Sweden Allsvenskan</t>
+  </si>
+  <si>
+    <t>Denmark Superliga</t>
+  </si>
+  <si>
+    <t>Spain La Liga</t>
+  </si>
+  <si>
     <t>Georgia Erovnuli Liga</t>
   </si>
   <si>
-    <t>Denmark Superliga</t>
+    <t>Spain Segunda División</t>
   </si>
   <si>
     <t>Switzerland Super League</t>
   </si>
   <si>
-    <t>Spain Segunda División</t>
-  </si>
-  <si>
-    <t>Sweden Allsvenskan</t>
-  </si>
-  <si>
-    <t>Spain La Liga</t>
-  </si>
-  <si>
     <t>Malaysia Super League</t>
   </si>
   <si>
     <t>Norway Eliteserien</t>
   </si>
   <si>
+    <t>Slovenia PrvaLiga</t>
+  </si>
+  <si>
+    <t>Czech Republic First League</t>
+  </si>
+  <si>
+    <t>England Premier League</t>
+  </si>
+  <si>
     <t>Romania Liga I</t>
   </si>
   <si>
-    <t>Slovenia PrvaLiga</t>
-  </si>
-  <si>
-    <t>Czech Republic First League</t>
-  </si>
-  <si>
-    <t>England Premier League</t>
-  </si>
-  <si>
     <t>Azerbaijan Premyer Liqası</t>
   </si>
   <si>
@@ -493,30 +493,30 @@
     <t>Greece Super League</t>
   </si>
   <si>
+    <t>Hungary NB II</t>
+  </si>
+  <si>
+    <t>Croatia Prva HNL</t>
+  </si>
+  <si>
     <t>Faroe Islands Faroe Islands Premier League</t>
   </si>
   <si>
-    <t>Croatia Prva HNL</t>
-  </si>
-  <si>
-    <t>Hungary NB II</t>
-  </si>
-  <si>
     <t>Netherlands Eredivisie</t>
   </si>
   <si>
+    <t>Norway First Division</t>
+  </si>
+  <si>
+    <t>Cyprus First Division</t>
+  </si>
+  <si>
+    <t>FYR Macedonia First Football League</t>
+  </si>
+  <si>
     <t>Austria Bundesliga</t>
   </si>
   <si>
-    <t>FYR Macedonia First Football League</t>
-  </si>
-  <si>
-    <t>Cyprus First Division</t>
-  </si>
-  <si>
-    <t>Norway First Division</t>
-  </si>
-  <si>
     <t>UAE Arabian Gulf League</t>
   </si>
   <si>
@@ -532,12 +532,12 @@
     <t>Saudi Arabia Professional League</t>
   </si>
   <si>
+    <t>Chile Primera B</t>
+  </si>
+  <si>
     <t>Serbia SuperLiga</t>
   </si>
   <si>
-    <t>Chile Primera B</t>
-  </si>
-  <si>
     <t>USA NWSL</t>
   </si>
   <si>
@@ -556,21 +556,21 @@
     <t>France Ligue 1</t>
   </si>
   <si>
+    <t>Brazil Serie A</t>
+  </si>
+  <si>
     <t>Bolivia LFPB</t>
   </si>
   <si>
-    <t>Brazil Serie A</t>
-  </si>
-  <si>
     <t>Brazil Serie B</t>
   </si>
   <si>
+    <t>USA MLS</t>
+  </si>
+  <si>
     <t>Ecuador Primera Categoría Serie A</t>
   </si>
   <si>
-    <t>USA MLS</t>
-  </si>
-  <si>
     <t>2026</t>
   </si>
   <si>
@@ -583,100 +583,127 @@
     <t>Seongnam</t>
   </si>
   <si>
+    <t>Ulsan</t>
+  </si>
+  <si>
+    <t>Blacktown City</t>
+  </si>
+  <si>
     <t>Rockdale City Suns</t>
   </si>
   <si>
-    <t>Ulsan</t>
-  </si>
-  <si>
-    <t>Blacktown City</t>
-  </si>
-  <si>
     <t>APIA Leichhardt Tigers</t>
   </si>
   <si>
+    <t>Dalian Huayi</t>
+  </si>
+  <si>
+    <t>Yanbian Longding</t>
+  </si>
+  <si>
+    <t>Ufa</t>
+  </si>
+  <si>
     <t>Shaanxi Union</t>
   </si>
   <si>
-    <t>Ufa</t>
-  </si>
-  <si>
-    <t>Yanbian Longding</t>
-  </si>
-  <si>
-    <t>Dalian Huayi</t>
+    <t>Busan I'Park</t>
+  </si>
+  <si>
+    <t>Anyang</t>
   </si>
   <si>
     <t>Ansan Greeners</t>
   </si>
   <si>
-    <t>Busan I'Park</t>
-  </si>
-  <si>
-    <t>Anyang</t>
-  </si>
-  <si>
     <t>Viktoria Žižkov</t>
   </si>
   <si>
     <t>Slavia Praha U21</t>
   </si>
   <si>
+    <t>Persita</t>
+  </si>
+  <si>
     <t>Persija</t>
   </si>
   <si>
-    <t>Persita</t>
-  </si>
-  <si>
     <t>Orenburg</t>
   </si>
   <si>
     <t>Qingdao Youth Island</t>
   </si>
   <si>
+    <t>Levante W</t>
+  </si>
+  <si>
     <t>Sichuan Jiuniu</t>
   </si>
   <si>
-    <t>Levante W</t>
+    <t>Polonia Warszawa</t>
+  </si>
+  <si>
+    <t>Amarante</t>
+  </si>
+  <si>
+    <t>Ulytau</t>
+  </si>
+  <si>
+    <t>Gyeongnam</t>
   </si>
   <si>
     <t>Sokol Saratov</t>
   </si>
   <si>
+    <t>Hoang Anh Gia Lai</t>
+  </si>
+  <si>
     <t>Sheger Ketema</t>
   </si>
   <si>
-    <t>Gyeongnam</t>
-  </si>
-  <si>
-    <t>Hoang Anh Gia Lai</t>
-  </si>
-  <si>
-    <t>Amarante</t>
-  </si>
-  <si>
-    <t>Ulytau</t>
-  </si>
-  <si>
-    <t>Polonia Warszawa</t>
-  </si>
-  <si>
     <t>Piast Gliwice</t>
   </si>
   <si>
     <t>Hellas Verona</t>
   </si>
   <si>
+    <t>Piteå Women</t>
+  </si>
+  <si>
+    <t>Celtic</t>
+  </si>
+  <si>
+    <t>Sukhothai</t>
+  </si>
+  <si>
+    <t>Shenyang Urban</t>
+  </si>
+  <si>
+    <t>Kanchanaburi</t>
+  </si>
+  <si>
+    <t>Hà Nội II</t>
+  </si>
+  <si>
+    <t>Ayutthaya United</t>
+  </si>
+  <si>
+    <t>Chonburi</t>
+  </si>
+  <si>
     <t>Shenzhen Juniors</t>
   </si>
   <si>
-    <t>Piteå Women</t>
-  </si>
-  <si>
-    <t>Celtic</t>
-  </si>
-  <si>
-    <t>Sukhothai</t>
+    <t>Altay</t>
+  </si>
+  <si>
+    <t>Buriram United</t>
+  </si>
+  <si>
+    <t>Rayong</t>
+  </si>
+  <si>
+    <t>Ho Chi Minh City</t>
   </si>
   <si>
     <t>Chiangrai United</t>
@@ -685,72 +712,45 @@
     <t>Bangkok Glass</t>
   </si>
   <si>
-    <t>Kanchanaburi</t>
-  </si>
-  <si>
-    <t>Hà Nội II</t>
-  </si>
-  <si>
-    <t>Shenyang Urban</t>
-  </si>
-  <si>
-    <t>Buriram United</t>
-  </si>
-  <si>
-    <t>Chonburi</t>
-  </si>
-  <si>
-    <t>Ayutthaya United</t>
-  </si>
-  <si>
-    <t>Ho Chi Minh City</t>
-  </si>
-  <si>
-    <t>Altay</t>
-  </si>
-  <si>
-    <t>Rayong</t>
-  </si>
-  <si>
     <t>Spartak Varna</t>
   </si>
   <si>
     <t>Sūduva</t>
   </si>
   <si>
+    <t>Nõmme Kalju</t>
+  </si>
+  <si>
+    <t>Nantong Zhiyun</t>
+  </si>
+  <si>
+    <t>Fortuna Düsseldorf</t>
+  </si>
+  <si>
+    <t>Kerala Blasters</t>
+  </si>
+  <si>
+    <t>Havelse</t>
+  </si>
+  <si>
+    <t>Dongguan United</t>
+  </si>
+  <si>
+    <t>Hertha BSC</t>
+  </si>
+  <si>
+    <t>Home United</t>
+  </si>
+  <si>
+    <t>Hougang United</t>
+  </si>
+  <si>
+    <t>KAA Gent</t>
+  </si>
+  <si>
     <t>Preußen Münster</t>
   </si>
   <si>
-    <t>Hougang United</t>
-  </si>
-  <si>
-    <t>Hertha BSC</t>
-  </si>
-  <si>
-    <t>Dongguan United</t>
-  </si>
-  <si>
-    <t>Fortuna Düsseldorf</t>
-  </si>
-  <si>
-    <t>Havelse</t>
-  </si>
-  <si>
-    <t>KAA Gent</t>
-  </si>
-  <si>
-    <t>Kerala Blasters</t>
-  </si>
-  <si>
-    <t>Nantong Zhiyun</t>
-  </si>
-  <si>
-    <t>Home United</t>
-  </si>
-  <si>
-    <t>Nõmme Kalju</t>
-  </si>
-  <si>
     <t>Zhejiang FC</t>
   </si>
   <si>
@@ -760,45 +760,45 @@
     <t>Hrvace</t>
   </si>
   <si>
+    <t>AIK</t>
+  </si>
+  <si>
+    <t>Nordsjælland</t>
+  </si>
+  <si>
+    <t>RCD Mallorca</t>
+  </si>
+  <si>
+    <t>Qingdao Jonoon</t>
+  </si>
+  <si>
+    <t>Bahardar</t>
+  </si>
+  <si>
+    <t>Meshakhte</t>
+  </si>
+  <si>
+    <t>FC Andorra</t>
+  </si>
+  <si>
+    <t>Kalmar</t>
+  </si>
+  <si>
     <t>Aktobe</t>
   </si>
   <si>
-    <t>Qingdao Jonoon</t>
-  </si>
-  <si>
-    <t>Meshakhte</t>
-  </si>
-  <si>
-    <t>Nordsjælland</t>
+    <t>Zenit</t>
+  </si>
+  <si>
+    <t>PSIM Yogyakarta</t>
   </si>
   <si>
     <t>Lugano</t>
   </si>
   <si>
-    <t>FC Andorra</t>
-  </si>
-  <si>
     <t>Vejle</t>
   </si>
   <si>
-    <t>AIK</t>
-  </si>
-  <si>
-    <t>RCD Mallorca</t>
-  </si>
-  <si>
-    <t>PSIM Yogyakarta</t>
-  </si>
-  <si>
-    <t>Zenit</t>
-  </si>
-  <si>
-    <t>Bahardar</t>
-  </si>
-  <si>
-    <t>Kalmar</t>
-  </si>
-  <si>
     <t>Kuala Lumpur</t>
   </si>
   <si>
@@ -808,145 +808,214 @@
     <t>Rosenborg</t>
   </si>
   <si>
+    <t>Baník Ostrava U21</t>
+  </si>
+  <si>
     <t>Tychy 71</t>
   </si>
   <si>
-    <t>Baník Ostrava U21</t>
-  </si>
-  <si>
     <t>Wisła Płock</t>
   </si>
   <si>
+    <t>NK Primorje</t>
+  </si>
+  <si>
+    <t>Sigma Olomouc</t>
+  </si>
+  <si>
+    <t>Astana</t>
+  </si>
+  <si>
+    <t>Arba Minch Kenema</t>
+  </si>
+  <si>
+    <t>Uppsala W</t>
+  </si>
+  <si>
+    <t>Fiorentina</t>
+  </si>
+  <si>
+    <t>Nottingham Forest</t>
+  </si>
+  <si>
+    <t>Burnley</t>
+  </si>
+  <si>
+    <t>Crystal Palace</t>
+  </si>
+  <si>
+    <t>Cremonese</t>
+  </si>
+  <si>
     <t>Botoşani</t>
   </si>
   <si>
-    <t>NK Primorje</t>
+    <t>Turan</t>
   </si>
   <si>
     <t>Pardubice</t>
   </si>
   <si>
-    <t>Crystal Palace</t>
-  </si>
-  <si>
-    <t>Burnley</t>
-  </si>
-  <si>
     <t>Kelantan United</t>
   </si>
   <si>
-    <t>Sigma Olomouc</t>
-  </si>
-  <si>
-    <t>Nottingham Forest</t>
-  </si>
-  <si>
-    <t>Fiorentina</t>
-  </si>
-  <si>
-    <t>Arba Minch Kenema</t>
-  </si>
-  <si>
-    <t>Uppsala W</t>
-  </si>
-  <si>
-    <t>Astana</t>
-  </si>
-  <si>
-    <t>Turan</t>
-  </si>
-  <si>
-    <t>Cremonese</t>
-  </si>
-  <si>
     <t>Hamburger SV</t>
   </si>
   <si>
     <t>Botev Vratsa</t>
   </si>
   <si>
+    <t>Volos NFC</t>
+  </si>
+  <si>
+    <t>Banga</t>
+  </si>
+  <si>
+    <t>Honvéd W</t>
+  </si>
+  <si>
+    <t>NorthEast United</t>
+  </si>
+  <si>
+    <t>Nõmme United</t>
+  </si>
+  <si>
+    <t>Osijek</t>
+  </si>
+  <si>
+    <t>Silkeborg</t>
+  </si>
+  <si>
+    <t>B36</t>
+  </si>
+  <si>
+    <t>EB - Streymur</t>
+  </si>
+  <si>
     <t>Royal Antwerp FC</t>
   </si>
   <si>
     <t>Aris</t>
   </si>
   <si>
-    <t>Banga</t>
-  </si>
-  <si>
-    <t>Nõmme United</t>
-  </si>
-  <si>
-    <t>Volos NFC</t>
-  </si>
-  <si>
-    <t>EB - Streymur</t>
-  </si>
-  <si>
-    <t>Silkeborg</t>
-  </si>
-  <si>
-    <t>NorthEast United</t>
-  </si>
-  <si>
-    <t>Osijek</t>
-  </si>
-  <si>
-    <t>B36</t>
-  </si>
-  <si>
-    <t>Honvéd W</t>
+    <t>Leganés</t>
   </si>
   <si>
     <t>Athletic Club Bilbao</t>
   </si>
   <si>
-    <t>Leganés</t>
-  </si>
-  <si>
     <t>Akhmat Grozny</t>
   </si>
   <si>
+    <t>Häcken</t>
+  </si>
+  <si>
+    <t>Neftekhimik</t>
+  </si>
+  <si>
     <t>Young Boys</t>
   </si>
   <si>
     <t>Sion</t>
   </si>
   <si>
-    <t>Neftekhimik</t>
-  </si>
-  <si>
-    <t>Häcken</t>
-  </si>
-  <si>
     <t>Viktoria Köln</t>
   </si>
   <si>
+    <t>Telstar</t>
+  </si>
+  <si>
+    <t>Twente</t>
+  </si>
+  <si>
+    <t>Fortuna Sittard</t>
+  </si>
+  <si>
+    <t>Feyenoord</t>
+  </si>
+  <si>
+    <t>Groningen</t>
+  </si>
+  <si>
+    <t>Ajax</t>
+  </si>
+  <si>
     <t>Go Ahead Eagles</t>
   </si>
   <si>
-    <t>Feyenoord</t>
-  </si>
-  <si>
-    <t>Ajax</t>
+    <t>Excelsior</t>
   </si>
   <si>
     <t>NAC Breda</t>
   </si>
   <si>
-    <t>Twente</t>
-  </si>
-  <si>
-    <t>Fortuna Sittard</t>
-  </si>
-  <si>
-    <t>Telstar</t>
-  </si>
-  <si>
-    <t>Excelsior</t>
-  </si>
-  <si>
-    <t>Groningen</t>
+    <t>Zbrojovka Brno</t>
+  </si>
+  <si>
+    <t>Sandnes Ulf</t>
+  </si>
+  <si>
+    <t>Sogndal</t>
+  </si>
+  <si>
+    <t>Pogoń Siedlce</t>
+  </si>
+  <si>
+    <t>Raufoss</t>
+  </si>
+  <si>
+    <t>Åsane</t>
+  </si>
+  <si>
+    <t>Moss</t>
+  </si>
+  <si>
+    <t>Real Madrid W</t>
+  </si>
+  <si>
+    <t>Paphos</t>
+  </si>
+  <si>
+    <t>Croatia Zmijavci</t>
+  </si>
+  <si>
+    <t>Mebrat Hayl</t>
+  </si>
+  <si>
+    <t>Kecskeméti TE</t>
+  </si>
+  <si>
+    <t>Sandefjord</t>
+  </si>
+  <si>
+    <t>Tromsø</t>
+  </si>
+  <si>
+    <t>Karcag SE</t>
+  </si>
+  <si>
+    <t>Akademija Pandev</t>
+  </si>
+  <si>
+    <t>Szentlőrinc SE</t>
+  </si>
+  <si>
+    <t>Strømmen</t>
+  </si>
+  <si>
+    <t>Omonia Nicosia</t>
+  </si>
+  <si>
+    <t>Apollon</t>
+  </si>
+  <si>
+    <t>Vardar</t>
+  </si>
+  <si>
+    <t>Saburtalo</t>
+  </si>
+  <si>
+    <t>Hartberg</t>
   </si>
   <si>
     <t>LASK Linz</t>
@@ -955,94 +1024,28 @@
     <t>Rapid Wien</t>
   </si>
   <si>
-    <t>Hartberg</t>
+    <t>KFUM</t>
+  </si>
+  <si>
+    <t>Makedonija GjP</t>
+  </si>
+  <si>
+    <t>Budafoki MTE</t>
+  </si>
+  <si>
+    <t>Ajka</t>
   </si>
   <si>
     <t>Pelister</t>
   </si>
   <si>
-    <t>Pogoń Siedlce</t>
-  </si>
-  <si>
-    <t>Makedonija GjP</t>
-  </si>
-  <si>
     <t>Shkendija</t>
   </si>
   <si>
     <t>Aresimi</t>
   </si>
   <si>
-    <t>Vardar</t>
-  </si>
-  <si>
-    <t>Zbrojovka Brno</t>
-  </si>
-  <si>
-    <t>Saburtalo</t>
-  </si>
-  <si>
-    <t>Karcag SE</t>
-  </si>
-  <si>
-    <t>Real Madrid W</t>
-  </si>
-  <si>
-    <t>Szentlőrinc SE</t>
-  </si>
-  <si>
-    <t>Croatia Zmijavci</t>
-  </si>
-  <si>
-    <t>Apollon</t>
-  </si>
-  <si>
-    <t>Omonia Nicosia</t>
-  </si>
-  <si>
-    <t>Paphos</t>
-  </si>
-  <si>
-    <t>KFUM</t>
-  </si>
-  <si>
-    <t>Tromsø</t>
-  </si>
-  <si>
-    <t>Sandefjord</t>
-  </si>
-  <si>
-    <t>Strømmen</t>
-  </si>
-  <si>
-    <t>Sandnes Ulf</t>
-  </si>
-  <si>
-    <t>Sogndal</t>
-  </si>
-  <si>
-    <t>Raufoss</t>
-  </si>
-  <si>
-    <t>Åsane</t>
-  </si>
-  <si>
-    <t>Moss</t>
-  </si>
-  <si>
-    <t>Kecskeméti TE</t>
-  </si>
-  <si>
-    <t>Ajka</t>
-  </si>
-  <si>
-    <t>Mebrat Hayl</t>
-  </si>
-  <si>
-    <t>Budafoki MTE</t>
-  </si>
-  <si>
-    <t>Akademija Pandev</t>
+    <t>Dibba Al Fujairah</t>
   </si>
   <si>
     <t>Al Bataeh</t>
@@ -1051,82 +1054,106 @@
     <t>Al Ain</t>
   </si>
   <si>
-    <t>Dibba Al Fujairah</t>
-  </si>
-  <si>
     <t>Bani Yas</t>
   </si>
   <si>
+    <t>Neftçi</t>
+  </si>
+  <si>
+    <t>West Ham United</t>
+  </si>
+  <si>
     <t>Nieciecza</t>
   </si>
   <si>
-    <t>Neftçi</t>
-  </si>
-  <si>
-    <t>West Ham United</t>
+    <t>Sekhukhune United</t>
   </si>
   <si>
     <t>Köln</t>
   </si>
   <si>
-    <t>Sekhukhune United</t>
+    <t>Brøndby</t>
+  </si>
+  <si>
+    <t>Dečić</t>
   </si>
   <si>
     <t>Vysočina Jihlava</t>
   </si>
   <si>
+    <t>Mornar</t>
+  </si>
+  <si>
+    <t>Panevėžys</t>
+  </si>
+  <si>
+    <t>Arsenal Tivat</t>
+  </si>
+  <si>
     <t>Mladost DG</t>
   </si>
   <si>
-    <t>Arsenal Tivat</t>
+    <t>Ittihad Tanger</t>
+  </si>
+  <si>
+    <t>Parma</t>
+  </si>
+  <si>
+    <t>Dinamo Bucureşti</t>
   </si>
   <si>
     <t>Jedinstvo</t>
   </si>
   <si>
-    <t>Dečić</t>
-  </si>
-  <si>
-    <t>Mornar</t>
-  </si>
-  <si>
-    <t>Parma</t>
-  </si>
-  <si>
-    <t>Dinamo Bucureşti</t>
-  </si>
-  <si>
-    <t>Ittihad Tanger</t>
-  </si>
-  <si>
-    <t>Brøndby</t>
-  </si>
-  <si>
-    <t>Panevėžys</t>
-  </si>
-  <si>
     <t>Al Riyadh</t>
   </si>
   <si>
+    <t>Dobrudzha 1919</t>
+  </si>
+  <si>
+    <t>Slaven Koprivnica</t>
+  </si>
+  <si>
     <t>Skála</t>
   </si>
   <si>
-    <t>Dobrudzha 1919</t>
-  </si>
-  <si>
-    <t>Slaven Koprivnica</t>
-  </si>
-  <si>
     <t>07 Vestur</t>
   </si>
   <si>
+    <t>Copiapó</t>
+  </si>
+  <si>
+    <t>IMT Novi Beograd</t>
+  </si>
+  <si>
+    <t>Real Oviedo</t>
+  </si>
+  <si>
+    <t>Córdoba</t>
+  </si>
+  <si>
+    <t>Kansas City</t>
+  </si>
+  <si>
+    <t>Union Saint-Gilloise</t>
+  </si>
+  <si>
     <t>AEK Athens</t>
   </si>
   <si>
     <t>Radnički Niš</t>
   </si>
   <si>
-    <t>Copiapó</t>
+    <t>Mirandés</t>
+  </si>
+  <si>
+    <t>Jablonec</t>
+  </si>
+  <si>
+    <t>Bačka Topola</t>
+  </si>
+  <si>
+    <t>Olympiakos Piraeus</t>
   </si>
   <si>
     <t>Antofagasta</t>
@@ -1135,177 +1162,150 @@
     <t>Spartak Subotica</t>
   </si>
   <si>
-    <t>IMT Novi Beograd</t>
-  </si>
-  <si>
-    <t>Union Saint-Gilloise</t>
-  </si>
-  <si>
-    <t>Córdoba</t>
-  </si>
-  <si>
-    <t>Olympiakos Piraeus</t>
-  </si>
-  <si>
-    <t>Jablonec</t>
-  </si>
-  <si>
-    <t>Mirandés</t>
-  </si>
-  <si>
-    <t>Kansas City</t>
-  </si>
-  <si>
     <t>Lokomotiv Moskva</t>
   </si>
   <si>
-    <t>Real Oviedo</t>
-  </si>
-  <si>
-    <t>Bačka Topola</t>
+    <t>Hapoel Katamon</t>
+  </si>
+  <si>
+    <t>Tenerife W</t>
   </si>
   <si>
     <t>Dinamo Batumi</t>
   </si>
   <si>
+    <t>Ironi Tiberias</t>
+  </si>
+  <si>
+    <t>Csákvári TK</t>
+  </si>
+  <si>
+    <t>KA</t>
+  </si>
+  <si>
     <t>Hapoel Haifa</t>
   </si>
   <si>
-    <t>Ironi Tiberias</t>
-  </si>
-  <si>
-    <t>Tenerife W</t>
-  </si>
-  <si>
-    <t>Hapoel Katamon</t>
-  </si>
-  <si>
-    <t>KA</t>
-  </si>
-  <si>
-    <t>Csákvári TK</t>
-  </si>
-  <si>
     <t>Békéscsaba</t>
   </si>
   <si>
     <t>KRC Genk</t>
   </si>
   <si>
+    <t>Hoffenheim II</t>
+  </si>
+  <si>
     <t>Mainz 05</t>
   </si>
   <si>
-    <t>Hoffenheim II</t>
+    <t>New England II</t>
+  </si>
+  <si>
+    <t>UTS Rabat</t>
+  </si>
+  <si>
+    <t>CODM Meknès</t>
   </si>
   <si>
     <t>Al Ittihad</t>
   </si>
   <si>
-    <t>New England II</t>
-  </si>
-  <si>
-    <t>UTS Rabat</t>
-  </si>
-  <si>
-    <t>CODM Meknès</t>
+    <t>Chacarita Juniors</t>
   </si>
   <si>
     <t>Varzim</t>
   </si>
   <si>
-    <t>Chacarita Juniors</t>
-  </si>
-  <si>
     <t>AC Milan</t>
   </si>
   <si>
+    <t>Metz</t>
+  </si>
+  <si>
+    <t>Le Havre</t>
+  </si>
+  <si>
+    <t>Angers SCO</t>
+  </si>
+  <si>
+    <t>Monaco</t>
+  </si>
+  <si>
+    <t>FC Barcelona</t>
+  </si>
+  <si>
+    <t>Auxerre</t>
+  </si>
+  <si>
+    <t>Remo</t>
+  </si>
+  <si>
+    <t>PSG</t>
+  </si>
+  <si>
+    <t>Toulouse</t>
+  </si>
+  <si>
+    <t>Independiente Petrolero</t>
+  </si>
+  <si>
     <t>Agropecuario</t>
   </si>
   <si>
-    <t>Monaco</t>
-  </si>
-  <si>
-    <t>FC Barcelona</t>
-  </si>
-  <si>
-    <t>Independiente Petrolero</t>
+    <t>Náutico</t>
   </si>
   <si>
     <t>Club Atlético Güemes</t>
   </si>
   <si>
-    <t>Toulouse</t>
+    <t>Atlético Mineiro</t>
   </si>
   <si>
     <t>Rennes</t>
   </si>
   <si>
-    <t>PSG</t>
-  </si>
-  <si>
-    <t>Remo</t>
-  </si>
-  <si>
-    <t>Auxerre</t>
-  </si>
-  <si>
-    <t>Angers SCO</t>
-  </si>
-  <si>
-    <t>Le Havre</t>
-  </si>
-  <si>
-    <t>Metz</t>
-  </si>
-  <si>
-    <t>Náutico</t>
-  </si>
-  <si>
-    <t>Atlético Mineiro</t>
-  </si>
-  <si>
     <t>San Martín San Juan</t>
   </si>
   <si>
+    <t>Chaco For Ever</t>
+  </si>
+  <si>
     <t>Godoy Cruz</t>
   </si>
   <si>
-    <t>Chaco For Ever</t>
+    <t>Central Norte</t>
+  </si>
+  <si>
+    <t>Los Angeles II</t>
+  </si>
+  <si>
+    <t>Bay</t>
+  </si>
+  <si>
+    <t>Portland Timbers II</t>
   </si>
   <si>
     <t>Hassania Agadir</t>
   </si>
   <si>
-    <t>Los Angeles II</t>
-  </si>
-  <si>
-    <t>Central Norte</t>
-  </si>
-  <si>
-    <t>Bay</t>
-  </si>
-  <si>
-    <t>Portland Timbers II</t>
+    <t>New York City</t>
   </si>
   <si>
     <t>CS Emelec</t>
   </si>
   <si>
-    <t>New York City</t>
-  </si>
-  <si>
     <t>Colón</t>
   </si>
   <si>
     <t>The Strongest</t>
   </si>
   <si>
+    <t>Santos</t>
+  </si>
+  <si>
     <t>Mirassol</t>
   </si>
   <si>
-    <t>Santos</t>
-  </si>
-  <si>
     <t>Corinthians</t>
   </si>
   <si>
@@ -1315,10 +1315,13 @@
     <t>FC Cincinnati II</t>
   </si>
   <si>
+    <t>Grêmio</t>
+  </si>
+  <si>
     <t>Novorizontino</t>
   </si>
   <si>
-    <t>Grêmio</t>
+    <t>Atlanta United II</t>
   </si>
   <si>
     <t>Minnesota United</t>
@@ -1327,9 +1330,6 @@
     <t>Seattle Reign</t>
   </si>
   <si>
-    <t>Atlanta United II</t>
-  </si>
-  <si>
     <t>Manta FC</t>
   </si>
   <si>
@@ -1351,100 +1351,127 @@
     <t>Jeonnam Dragons</t>
   </si>
   <si>
+    <t>Bucheon 1995</t>
+  </si>
+  <si>
+    <t>St. George Saints</t>
+  </si>
+  <si>
     <t>Sydney II</t>
   </si>
   <si>
-    <t>Bucheon 1995</t>
-  </si>
-  <si>
-    <t>St. George Saints</t>
-  </si>
-  <si>
     <t>Sydney United</t>
   </si>
   <si>
+    <t>Guangzhou E-Power</t>
+  </si>
+  <si>
+    <t>Guangxi Hengchen</t>
+  </si>
+  <si>
+    <t>Rotor Volgograd</t>
+  </si>
+  <si>
     <t>Shanghai Jiading</t>
   </si>
   <si>
-    <t>Rotor Volgograd</t>
-  </si>
-  <si>
-    <t>Guangxi Hengchen</t>
-  </si>
-  <si>
-    <t>Guangzhou E-Power</t>
+    <t>Cheonan City</t>
+  </si>
+  <si>
+    <t>Jeonbuk Motors</t>
   </si>
   <si>
     <t>Yongin City</t>
   </si>
   <si>
-    <t>Cheonan City</t>
-  </si>
-  <si>
-    <t>Jeonbuk Motors</t>
-  </si>
-  <si>
     <t>Sparta Praha II</t>
   </si>
   <si>
     <t>Táborsko</t>
   </si>
   <si>
+    <t>Persijap</t>
+  </si>
+  <si>
     <t>Persib</t>
   </si>
   <si>
-    <t>Persijap</t>
-  </si>
-  <si>
     <t>Krylya Sovetov</t>
   </si>
   <si>
     <t>Wuhan Three Towns</t>
   </si>
   <si>
+    <t>Logroño W</t>
+  </si>
+  <si>
     <t>Shandong Luneng</t>
   </si>
   <si>
-    <t>Logroño W</t>
+    <t>Górnik Łęczna</t>
+  </si>
+  <si>
+    <t>União Santarém</t>
+  </si>
+  <si>
+    <t>Kairat</t>
+  </si>
+  <si>
+    <t>Gimhae City</t>
   </si>
   <si>
     <t>Spartak Kostroma</t>
   </si>
   <si>
+    <t>Pho Hien</t>
+  </si>
+  <si>
     <t>Sidama Bunna</t>
   </si>
   <si>
-    <t>Gimhae City</t>
-  </si>
-  <si>
-    <t>Pho Hien</t>
-  </si>
-  <si>
-    <t>União Santarém</t>
-  </si>
-  <si>
-    <t>Kairat</t>
-  </si>
-  <si>
-    <t>Górnik Łęczna</t>
-  </si>
-  <si>
     <t>GKS Katowice</t>
   </si>
   <si>
     <t>Como</t>
   </si>
   <si>
+    <t>Rosengard Women</t>
+  </si>
+  <si>
+    <t>Rangers</t>
+  </si>
+  <si>
+    <t>Muang Thong United</t>
+  </si>
+  <si>
+    <t>Yunnan Yukun</t>
+  </si>
+  <si>
+    <t>Ratchaburi</t>
+  </si>
+  <si>
+    <t>Viettel</t>
+  </si>
+  <si>
+    <t>Port FC</t>
+  </si>
+  <si>
+    <t>Nakhon Ratchasima</t>
+  </si>
+  <si>
     <t>Hebei Kungfu</t>
   </si>
   <si>
-    <t>Rosengard Women</t>
-  </si>
-  <si>
-    <t>Rangers</t>
-  </si>
-  <si>
-    <t>Muang Thong United</t>
+    <t>Ordabasy</t>
+  </si>
+  <si>
+    <t>Lamphun Warrior</t>
+  </si>
+  <si>
+    <t>Bangkok United</t>
+  </si>
+  <si>
+    <t>Song Lam Nghe An</t>
   </si>
   <si>
     <t>Uthai Thani</t>
@@ -1453,72 +1480,45 @@
     <t>Prachuap</t>
   </si>
   <si>
-    <t>Ratchaburi</t>
-  </si>
-  <si>
-    <t>Viettel</t>
-  </si>
-  <si>
-    <t>Yunnan Yukun</t>
-  </si>
-  <si>
-    <t>Lamphun Warrior</t>
-  </si>
-  <si>
-    <t>Nakhon Ratchasima</t>
-  </si>
-  <si>
-    <t>Port FC</t>
-  </si>
-  <si>
-    <t>Song Lam Nghe An</t>
-  </si>
-  <si>
-    <t>Ordabasy</t>
-  </si>
-  <si>
-    <t>Bangkok United</t>
-  </si>
-  <si>
     <t>Slavia Sofia</t>
   </si>
   <si>
     <t>Žalgiris</t>
   </si>
   <si>
+    <t>Tallinna FC Flora</t>
+  </si>
+  <si>
+    <t>Wuxi Wugou</t>
+  </si>
+  <si>
+    <t>Elversberg</t>
+  </si>
+  <si>
+    <t>Mohammedan</t>
+  </si>
+  <si>
+    <t>Schweinfurt</t>
+  </si>
+  <si>
+    <t>Suzhou Dongwu</t>
+  </si>
+  <si>
+    <t>Greuther Fürth</t>
+  </si>
+  <si>
+    <t>Albirex Niigata S</t>
+  </si>
+  <si>
+    <t>Tampines Rovers</t>
+  </si>
+  <si>
+    <t>RSC Anderlecht</t>
+  </si>
+  <si>
     <t>Darmstadt 98</t>
   </si>
   <si>
-    <t>Tampines Rovers</t>
-  </si>
-  <si>
-    <t>Greuther Fürth</t>
-  </si>
-  <si>
-    <t>Suzhou Dongwu</t>
-  </si>
-  <si>
-    <t>Elversberg</t>
-  </si>
-  <si>
-    <t>Schweinfurt</t>
-  </si>
-  <si>
-    <t>RSC Anderlecht</t>
-  </si>
-  <si>
-    <t>Mohammedan</t>
-  </si>
-  <si>
-    <t>Wuxi Wugou</t>
-  </si>
-  <si>
-    <t>Albirex Niigata S</t>
-  </si>
-  <si>
-    <t>Tallinna FC Flora</t>
-  </si>
-  <si>
     <t>Tianjin Teda</t>
   </si>
   <si>
@@ -1528,45 +1528,45 @@
     <t>Opatija</t>
   </si>
   <si>
+    <t>Djurgården</t>
+  </si>
+  <si>
+    <t>Midtjylland</t>
+  </si>
+  <si>
+    <t>Villarreal</t>
+  </si>
+  <si>
+    <t>Dalian Zhixing</t>
+  </si>
+  <si>
+    <t>Welwalo Adigrat Uni</t>
+  </si>
+  <si>
+    <t>Dila</t>
+  </si>
+  <si>
+    <t>UD Las Palmas</t>
+  </si>
+  <si>
+    <t>Halmstad</t>
+  </si>
+  <si>
     <t>Kaisar</t>
   </si>
   <si>
-    <t>Dalian Zhixing</t>
-  </si>
-  <si>
-    <t>Dila</t>
-  </si>
-  <si>
-    <t>Midtjylland</t>
+    <t>FK Sochi</t>
+  </si>
+  <si>
+    <t>Malut United</t>
   </si>
   <si>
     <t>St. Gallen</t>
   </si>
   <si>
-    <t>UD Las Palmas</t>
-  </si>
-  <si>
     <t>Fredericia</t>
   </si>
   <si>
-    <t>Djurgården</t>
-  </si>
-  <si>
-    <t>Villarreal</t>
-  </si>
-  <si>
-    <t>Malut United</t>
-  </si>
-  <si>
-    <t>FK Sochi</t>
-  </si>
-  <si>
-    <t>Welwalo Adigrat Uni</t>
-  </si>
-  <si>
-    <t>Halmstad</t>
-  </si>
-  <si>
     <t>Negeri Sembilan</t>
   </si>
   <si>
@@ -1576,145 +1576,211 @@
     <t>Lillestrøm</t>
   </si>
   <si>
+    <t>Ústí nad Labem</t>
+  </si>
+  <si>
     <t>Ruch Chorzów</t>
   </si>
   <si>
-    <t>Ústí nad Labem</t>
-  </si>
-  <si>
     <t>Motor Lublin</t>
   </si>
   <si>
+    <t>Mura</t>
+  </si>
+  <si>
+    <t>Bohemians 1905</t>
+  </si>
+  <si>
+    <t>Kyzyl-Zhar</t>
+  </si>
+  <si>
+    <t>Welayta Dicha</t>
+  </si>
+  <si>
+    <t>Vittsjö</t>
+  </si>
+  <si>
+    <t>Genoa</t>
+  </si>
+  <si>
+    <t>Newcastle United</t>
+  </si>
+  <si>
+    <t>Aston Villa</t>
+  </si>
+  <si>
+    <t>Everton</t>
+  </si>
+  <si>
+    <t>Pisa</t>
+  </si>
+  <si>
     <t>Petrolul 52</t>
   </si>
   <si>
-    <t>Mura</t>
+    <t>Karvan FK</t>
   </si>
   <si>
     <t>Karviná</t>
   </si>
   <si>
-    <t>Everton</t>
-  </si>
-  <si>
-    <t>Aston Villa</t>
-  </si>
-  <si>
     <t>Johor Darul Ta'zim</t>
   </si>
   <si>
-    <t>Bohemians 1905</t>
-  </si>
-  <si>
-    <t>Newcastle United</t>
-  </si>
-  <si>
-    <t>Genoa</t>
-  </si>
-  <si>
-    <t>Welayta Dicha</t>
-  </si>
-  <si>
-    <t>Vittsjö</t>
-  </si>
-  <si>
-    <t>Kyzyl-Zhar</t>
-  </si>
-  <si>
-    <t>Karvan FK</t>
-  </si>
-  <si>
-    <t>Pisa</t>
-  </si>
-  <si>
     <t>Freiburg</t>
   </si>
   <si>
     <t>Septemvri Sofia</t>
   </si>
   <si>
+    <t>Levadiakos</t>
+  </si>
+  <si>
+    <t>TransINVEST Vilnius</t>
+  </si>
+  <si>
+    <t>Vasas</t>
+  </si>
+  <si>
+    <t>Chennaiyin</t>
+  </si>
+  <si>
+    <t>Paide</t>
+  </si>
+  <si>
+    <t>Istra 1961</t>
+  </si>
+  <si>
+    <t>København</t>
+  </si>
+  <si>
+    <t>KÍ</t>
+  </si>
+  <si>
+    <t>Víkingur</t>
+  </si>
+  <si>
     <t>Sporting Charleroi</t>
   </si>
   <si>
     <t>OFI</t>
   </si>
   <si>
-    <t>TransINVEST Vilnius</t>
-  </si>
-  <si>
-    <t>Paide</t>
-  </si>
-  <si>
-    <t>Levadiakos</t>
-  </si>
-  <si>
-    <t>Víkingur</t>
-  </si>
-  <si>
-    <t>København</t>
-  </si>
-  <si>
-    <t>Chennaiyin</t>
-  </si>
-  <si>
-    <t>Istra 1961</t>
-  </si>
-  <si>
-    <t>KÍ</t>
-  </si>
-  <si>
-    <t>Vasas</t>
+    <t>Racing Santander</t>
   </si>
   <si>
     <t>Valencia CF</t>
   </si>
   <si>
-    <t>Racing Santander</t>
-  </si>
-  <si>
     <t>Makhachkala</t>
   </si>
   <si>
+    <t>Malmö FF</t>
+  </si>
+  <si>
+    <t>Volga Ulyanovsk</t>
+  </si>
+  <si>
     <t>Basel</t>
   </si>
   <si>
     <t>Thun</t>
   </si>
   <si>
-    <t>Volga Ulyanovsk</t>
-  </si>
-  <si>
-    <t>Malmö FF</t>
-  </si>
-  <si>
     <t>Alemannia Aachen</t>
   </si>
   <si>
+    <t>Heracles</t>
+  </si>
+  <si>
+    <t>Sparta Rotterdam</t>
+  </si>
+  <si>
+    <t>PEC Zwolle</t>
+  </si>
+  <si>
+    <t>AZ</t>
+  </si>
+  <si>
+    <t>NEC</t>
+  </si>
+  <si>
+    <t>Utrecht</t>
+  </si>
+  <si>
     <t>PSV</t>
   </si>
   <si>
-    <t>AZ</t>
-  </si>
-  <si>
-    <t>Utrecht</t>
+    <t>Volendam</t>
   </si>
   <si>
     <t>Heerenveen</t>
   </si>
   <si>
-    <t>Sparta Rotterdam</t>
-  </si>
-  <si>
-    <t>PEC Zwolle</t>
-  </si>
-  <si>
-    <t>Heracles</t>
-  </si>
-  <si>
-    <t>Volendam</t>
-  </si>
-  <si>
-    <t>NEC</t>
+    <t>Vlašim</t>
+  </si>
+  <si>
+    <t>Stabæk</t>
+  </si>
+  <si>
+    <t>Haugesund</t>
+  </si>
+  <si>
+    <t>Stal Rzeszów</t>
+  </si>
+  <si>
+    <t>Lyn</t>
+  </si>
+  <si>
+    <t>Strømsgodset</t>
+  </si>
+  <si>
+    <t>Bryne</t>
+  </si>
+  <si>
+    <t>Atletico Madrid W</t>
+  </si>
+  <si>
+    <t>Jarun</t>
+  </si>
+  <si>
+    <t>Fasil Ketema</t>
+  </si>
+  <si>
+    <t>Mezőkövesd-Zsóry</t>
+  </si>
+  <si>
+    <t>Kristiansund</t>
+  </si>
+  <si>
+    <t>Molde</t>
+  </si>
+  <si>
+    <t>Tiszakécske</t>
+  </si>
+  <si>
+    <t>Rabotnički</t>
+  </si>
+  <si>
+    <t>Videoton</t>
+  </si>
+  <si>
+    <t>Hødd</t>
+  </si>
+  <si>
+    <t>AEK Larnaca</t>
+  </si>
+  <si>
+    <t>APOEL</t>
+  </si>
+  <si>
+    <t>Sileks</t>
+  </si>
+  <si>
+    <t>Torpedo Kutaisi</t>
+  </si>
+  <si>
+    <t>Sturm Graz</t>
   </si>
   <si>
     <t>Salzburg</t>
@@ -1723,91 +1789,28 @@
     <t>Austria Wien</t>
   </si>
   <si>
-    <t>Sturm Graz</t>
+    <t>Viking</t>
+  </si>
+  <si>
+    <t>Tikveš</t>
+  </si>
+  <si>
+    <t>BVSC</t>
+  </si>
+  <si>
+    <t>Szeged 2011</t>
   </si>
   <si>
     <t>Shkupi</t>
   </si>
   <si>
-    <t>Stal Rzeszów</t>
-  </si>
-  <si>
-    <t>Tikveš</t>
-  </si>
-  <si>
     <t>Struga</t>
   </si>
   <si>
     <t>FK Bashkimi Kumanovo</t>
   </si>
   <si>
-    <t>Sileks</t>
-  </si>
-  <si>
-    <t>Vlašim</t>
-  </si>
-  <si>
-    <t>Torpedo Kutaisi</t>
-  </si>
-  <si>
-    <t>Tiszakécske</t>
-  </si>
-  <si>
-    <t>Atletico Madrid W</t>
-  </si>
-  <si>
-    <t>Videoton</t>
-  </si>
-  <si>
-    <t>Jarun</t>
-  </si>
-  <si>
-    <t>APOEL</t>
-  </si>
-  <si>
-    <t>AEK Larnaca</t>
-  </si>
-  <si>
-    <t>Viking</t>
-  </si>
-  <si>
-    <t>Molde</t>
-  </si>
-  <si>
-    <t>Kristiansund</t>
-  </si>
-  <si>
-    <t>Hødd</t>
-  </si>
-  <si>
-    <t>Stabæk</t>
-  </si>
-  <si>
-    <t>Haugesund</t>
-  </si>
-  <si>
-    <t>Lyn</t>
-  </si>
-  <si>
-    <t>Strømsgodset</t>
-  </si>
-  <si>
-    <t>Bryne</t>
-  </si>
-  <si>
-    <t>Mezőkövesd-Zsóry</t>
-  </si>
-  <si>
-    <t>Szeged 2011</t>
-  </si>
-  <si>
-    <t>Fasil Ketema</t>
-  </si>
-  <si>
-    <t>BVSC</t>
-  </si>
-  <si>
-    <t>Rabotnički</t>
+    <t>Ajman</t>
   </si>
   <si>
     <t>Al Sharjah</t>
@@ -1816,82 +1819,106 @@
     <t>Al Dhafra</t>
   </si>
   <si>
-    <t>Ajman</t>
-  </si>
-  <si>
     <t>Shabab Al Ahli Dubai</t>
   </si>
   <si>
+    <t>İnter Bakı</t>
+  </si>
+  <si>
+    <t>Arsenal</t>
+  </si>
+  <si>
     <t>Legia Warszawa</t>
   </si>
   <si>
-    <t>İnter Bakı</t>
-  </si>
-  <si>
-    <t>Arsenal</t>
+    <t>Kaizer Chiefs</t>
   </si>
   <si>
     <t>Heidenheim</t>
   </si>
   <si>
-    <t>Kaizer Chiefs</t>
+    <t>AGF</t>
+  </si>
+  <si>
+    <t>FK Jezero Plav</t>
   </si>
   <si>
     <t>Hanácká</t>
   </si>
   <si>
+    <t>Bokelj</t>
+  </si>
+  <si>
+    <t>Kauno Žalgiris</t>
+  </si>
+  <si>
+    <t>Sutjeska</t>
+  </si>
+  <si>
     <t>Petrovac</t>
   </si>
   <si>
-    <t>Sutjeska</t>
+    <t>Difaâ El Jadida</t>
+  </si>
+  <si>
+    <t>Roma</t>
+  </si>
+  <si>
+    <t>Argeș</t>
   </si>
   <si>
     <t>Budućnost</t>
   </si>
   <si>
-    <t>FK Jezero Plav</t>
-  </si>
-  <si>
-    <t>Bokelj</t>
-  </si>
-  <si>
-    <t>Roma</t>
-  </si>
-  <si>
-    <t>Argeș</t>
-  </si>
-  <si>
-    <t>Difaâ El Jadida</t>
-  </si>
-  <si>
-    <t>AGF</t>
-  </si>
-  <si>
-    <t>Kauno Žalgiris</t>
-  </si>
-  <si>
     <t>Al Fateh</t>
   </si>
   <si>
+    <t>Beroe</t>
+  </si>
+  <si>
+    <t>Gorica</t>
+  </si>
+  <si>
     <t>AB</t>
   </si>
   <si>
-    <t>Beroe</t>
-  </si>
-  <si>
-    <t>Gorica</t>
-  </si>
-  <si>
     <t>B68</t>
   </si>
   <si>
+    <t>Unión San Felipe</t>
+  </si>
+  <si>
+    <t>Radnički Kragujevac</t>
+  </si>
+  <si>
+    <t>Getafe CF</t>
+  </si>
+  <si>
+    <t>Granada CF</t>
+  </si>
+  <si>
+    <t>Chicago Red Stars</t>
+  </si>
+  <si>
+    <t>KV Mechelen</t>
+  </si>
+  <si>
     <t>Panathinaikos</t>
   </si>
   <si>
     <t>LFK Mladost Lučani</t>
   </si>
   <si>
-    <t>Unión San Felipe</t>
+    <t>SD Eibar</t>
+  </si>
+  <si>
+    <t>Hradec Králové</t>
+  </si>
+  <si>
+    <t>Javor Ivanjica</t>
+  </si>
+  <si>
+    <t>PAOK</t>
   </si>
   <si>
     <t>San Luis</t>
@@ -1900,177 +1927,150 @@
     <t>Napredak</t>
   </si>
   <si>
-    <t>Radnički Kragujevac</t>
-  </si>
-  <si>
-    <t>KV Mechelen</t>
-  </si>
-  <si>
-    <t>Granada CF</t>
-  </si>
-  <si>
-    <t>PAOK</t>
-  </si>
-  <si>
-    <t>Hradec Králové</t>
-  </si>
-  <si>
-    <t>SD Eibar</t>
-  </si>
-  <si>
-    <t>Chicago Red Stars</t>
-  </si>
-  <si>
     <t>Baltika</t>
   </si>
   <si>
-    <t>Getafe CF</t>
-  </si>
-  <si>
-    <t>Javor Ivanjica</t>
+    <t>Bnei Sakhnin</t>
+  </si>
+  <si>
+    <t>Barcelona W</t>
   </si>
   <si>
     <t>Samgurali</t>
   </si>
   <si>
+    <t>Maccabi Netanya</t>
+  </si>
+  <si>
+    <t>Soroksár SC</t>
+  </si>
+  <si>
+    <t>ÍBV</t>
+  </si>
+  <si>
     <t>Ashdod</t>
   </si>
   <si>
-    <t>Maccabi Netanya</t>
-  </si>
-  <si>
-    <t>Barcelona W</t>
-  </si>
-  <si>
-    <t>Bnei Sakhnin</t>
-  </si>
-  <si>
-    <t>ÍBV</t>
-  </si>
-  <si>
-    <t>Soroksár SC</t>
-  </si>
-  <si>
     <t>Kozármisleny</t>
   </si>
   <si>
     <t>KVC Westerlo</t>
   </si>
   <si>
+    <t>Saarbrucken</t>
+  </si>
+  <si>
     <t>Union Berlin</t>
   </si>
   <si>
-    <t>Saarbrucken</t>
+    <t>New York City II</t>
+  </si>
+  <si>
+    <t>Maghreb Fès</t>
+  </si>
+  <si>
+    <t>RSB Berkane</t>
   </si>
   <si>
     <t>Dhamk</t>
   </si>
   <si>
-    <t>New York City II</t>
-  </si>
-  <si>
-    <t>Maghreb Fès</t>
-  </si>
-  <si>
-    <t>RSB Berkane</t>
+    <t>Colegiales</t>
   </si>
   <si>
     <t>CF Os Belenenses</t>
   </si>
   <si>
-    <t>Colegiales</t>
-  </si>
-  <si>
     <t>Atalanta</t>
   </si>
   <si>
+    <t>Lorient</t>
+  </si>
+  <si>
+    <t>Olympique Marseille</t>
+  </si>
+  <si>
+    <t>Strasbourg</t>
+  </si>
+  <si>
+    <t>Lille</t>
+  </si>
+  <si>
+    <t>Real Madrid</t>
+  </si>
+  <si>
+    <t>Nice</t>
+  </si>
+  <si>
+    <t>Palmeiras</t>
+  </si>
+  <si>
+    <t>Brest</t>
+  </si>
+  <si>
+    <t>Olympique Lyonnais</t>
+  </si>
+  <si>
+    <t>Club Always Ready</t>
+  </si>
+  <si>
     <t>Atlanta</t>
   </si>
   <si>
-    <t>Lille</t>
-  </si>
-  <si>
-    <t>Real Madrid</t>
-  </si>
-  <si>
-    <t>Club Always Ready</t>
+    <t>América Mineiro</t>
   </si>
   <si>
     <t>Quilmes</t>
   </si>
   <si>
-    <t>Olympique Lyonnais</t>
+    <t>Botafogo</t>
   </si>
   <si>
     <t>Paris</t>
   </si>
   <si>
-    <t>Brest</t>
-  </si>
-  <si>
-    <t>Palmeiras</t>
-  </si>
-  <si>
-    <t>Nice</t>
-  </si>
-  <si>
-    <t>Strasbourg</t>
-  </si>
-  <si>
-    <t>Olympique Marseille</t>
-  </si>
-  <si>
-    <t>Lorient</t>
-  </si>
-  <si>
-    <t>América Mineiro</t>
-  </si>
-  <si>
-    <t>Botafogo</t>
-  </si>
-  <si>
     <t>Patronato</t>
   </si>
   <si>
+    <t>Ciudad de Bolívar</t>
+  </si>
+  <si>
     <t>Racing Córdoba</t>
   </si>
   <si>
-    <t>Ciudad de Bolívar</t>
+    <t>Deportivo Madryn</t>
+  </si>
+  <si>
+    <t>Real Monarchs</t>
+  </si>
+  <si>
+    <t>Utah Royals</t>
+  </si>
+  <si>
+    <t>LA Galaxy II</t>
   </si>
   <si>
     <t>FAR Rabat</t>
   </si>
   <si>
-    <t>Real Monarchs</t>
-  </si>
-  <si>
-    <t>Deportivo Madryn</t>
-  </si>
-  <si>
-    <t>Utah Royals</t>
-  </si>
-  <si>
-    <t>LA Galaxy II</t>
+    <t>Columbus Crew</t>
   </si>
   <si>
     <t>Libertad</t>
   </si>
   <si>
-    <t>Columbus Crew</t>
-  </si>
-  <si>
     <t>All Boys</t>
   </si>
   <si>
     <t>Real Potosí</t>
   </si>
   <si>
+    <t>Bragantino</t>
+  </si>
+  <si>
     <t>Chapecoense</t>
   </si>
   <si>
-    <t>Bragantino</t>
-  </si>
-  <si>
     <t>São Paulo</t>
   </si>
   <si>
@@ -2080,19 +2080,19 @@
     <t>Columbus Crew II</t>
   </si>
   <si>
+    <t>Flamengo</t>
+  </si>
+  <si>
     <t>Botafogo SP</t>
   </si>
   <si>
-    <t>Flamengo</t>
+    <t>Orlando City II</t>
   </si>
   <si>
     <t>Austin</t>
   </si>
   <si>
     <t>Washington Spirit</t>
-  </si>
-  <si>
-    <t>Orlando City II</t>
   </si>
   <si>
     <t>Macará</t>
@@ -3228,7 +3228,7 @@
         <v>61</v>
       </c>
       <c r="C5" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="D5" t="s">
         <v>185</v>
@@ -3413,7 +3413,7 @@
         <v>62</v>
       </c>
       <c r="C6" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="D6" t="s">
         <v>185</v>
@@ -3783,10 +3783,10 @@
         <v>63</v>
       </c>
       <c r="C8" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D8" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E8" t="s">
         <v>194</v>
@@ -3968,10 +3968,10 @@
         <v>63</v>
       </c>
       <c r="C9" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="D9" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E9" t="s">
         <v>195</v>
@@ -4523,7 +4523,7 @@
         <v>64</v>
       </c>
       <c r="C12" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="D12" t="s">
         <v>185</v>
@@ -4708,7 +4708,7 @@
         <v>64</v>
       </c>
       <c r="C13" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="D13" t="s">
         <v>185</v>
@@ -6003,10 +6003,10 @@
         <v>68</v>
       </c>
       <c r="C20" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="D20" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E20" t="s">
         <v>206</v>
@@ -6188,10 +6188,10 @@
         <v>68</v>
       </c>
       <c r="C21" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="D21" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E21" t="s">
         <v>207</v>
@@ -6373,7 +6373,7 @@
         <v>68</v>
       </c>
       <c r="C22" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="D22" t="s">
         <v>186</v>
@@ -6558,7 +6558,7 @@
         <v>68</v>
       </c>
       <c r="C23" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="D23" t="s">
         <v>186</v>
@@ -6743,7 +6743,7 @@
         <v>68</v>
       </c>
       <c r="C24" t="s">
-        <v>115</v>
+        <v>127</v>
       </c>
       <c r="D24" t="s">
         <v>185</v>
@@ -6928,10 +6928,10 @@
         <v>68</v>
       </c>
       <c r="C25" t="s">
-        <v>126</v>
+        <v>115</v>
       </c>
       <c r="D25" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E25" t="s">
         <v>211</v>
@@ -7113,7 +7113,7 @@
         <v>68</v>
       </c>
       <c r="C26" t="s">
-        <v>127</v>
+        <v>119</v>
       </c>
       <c r="D26" t="s">
         <v>186</v>
@@ -7301,7 +7301,7 @@
         <v>128</v>
       </c>
       <c r="D27" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E27" t="s">
         <v>213</v>
@@ -8038,7 +8038,7 @@
         <v>71</v>
       </c>
       <c r="C31" t="s">
-        <v>118</v>
+        <v>132</v>
       </c>
       <c r="D31" t="s">
         <v>185</v>
@@ -8223,10 +8223,10 @@
         <v>71</v>
       </c>
       <c r="C32" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="D32" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E32" t="s">
         <v>218</v>
@@ -8262,13 +8262,13 @@
         <v>699</v>
       </c>
       <c r="P32">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Q32">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="R32">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="S32">
         <v>0</v>
@@ -8408,7 +8408,7 @@
         <v>71</v>
       </c>
       <c r="C33" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="D33" t="s">
         <v>186</v>
@@ -8447,13 +8447,13 @@
         <v>699</v>
       </c>
       <c r="P33">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Q33">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="R33">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="S33">
         <v>0</v>
@@ -8593,10 +8593,10 @@
         <v>71</v>
       </c>
       <c r="C34" t="s">
-        <v>134</v>
+        <v>123</v>
       </c>
       <c r="D34" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E34" t="s">
         <v>220</v>
@@ -8963,7 +8963,7 @@
         <v>71</v>
       </c>
       <c r="C36" t="s">
-        <v>134</v>
+        <v>128</v>
       </c>
       <c r="D36" t="s">
         <v>186</v>
@@ -9333,7 +9333,7 @@
         <v>71</v>
       </c>
       <c r="C38" t="s">
-        <v>126</v>
+        <v>134</v>
       </c>
       <c r="D38" t="s">
         <v>186</v>
@@ -9518,7 +9518,7 @@
         <v>71</v>
       </c>
       <c r="C39" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="D39" t="s">
         <v>185</v>
@@ -9703,10 +9703,10 @@
         <v>71</v>
       </c>
       <c r="C40" t="s">
-        <v>134</v>
+        <v>127</v>
       </c>
       <c r="D40" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E40" t="s">
         <v>226</v>
@@ -10258,7 +10258,7 @@
         <v>71</v>
       </c>
       <c r="C43" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="D43" t="s">
         <v>186</v>
@@ -10443,10 +10443,10 @@
         <v>71</v>
       </c>
       <c r="C44" t="s">
-        <v>128</v>
+        <v>134</v>
       </c>
       <c r="D44" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E44" t="s">
         <v>230</v>
@@ -11186,7 +11186,7 @@
         <v>137</v>
       </c>
       <c r="D48" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E48" t="s">
         <v>234</v>
@@ -11368,10 +11368,10 @@
         <v>73</v>
       </c>
       <c r="C49" t="s">
-        <v>138</v>
+        <v>118</v>
       </c>
       <c r="D49" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="E49" t="s">
         <v>235</v>
@@ -11553,7 +11553,7 @@
         <v>73</v>
       </c>
       <c r="C50" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="D50" t="s">
         <v>186</v>
@@ -11738,10 +11738,10 @@
         <v>73</v>
       </c>
       <c r="C51" t="s">
-        <v>118</v>
+        <v>139</v>
       </c>
       <c r="D51" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E51" t="s">
         <v>237</v>
@@ -11923,7 +11923,7 @@
         <v>73</v>
       </c>
       <c r="C52" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="D52" t="s">
         <v>186</v>
@@ -12108,10 +12108,10 @@
         <v>73</v>
       </c>
       <c r="C53" t="s">
-        <v>139</v>
+        <v>118</v>
       </c>
       <c r="D53" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E53" t="s">
         <v>239</v>
@@ -12293,7 +12293,7 @@
         <v>73</v>
       </c>
       <c r="C54" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="D54" t="s">
         <v>186</v>
@@ -12481,7 +12481,7 @@
         <v>141</v>
       </c>
       <c r="D55" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="E55" t="s">
         <v>241</v>
@@ -12663,10 +12663,10 @@
         <v>73</v>
       </c>
       <c r="C56" t="s">
-        <v>118</v>
+        <v>141</v>
       </c>
       <c r="D56" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="E56" t="s">
         <v>242</v>
@@ -12848,10 +12848,10 @@
         <v>73</v>
       </c>
       <c r="C57" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="D57" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="E57" t="s">
         <v>243</v>
@@ -13033,10 +13033,10 @@
         <v>73</v>
       </c>
       <c r="C58" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="D58" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E58" t="s">
         <v>244</v>
@@ -13773,7 +13773,7 @@
         <v>76</v>
       </c>
       <c r="C62" t="s">
-        <v>128</v>
+        <v>144</v>
       </c>
       <c r="D62" t="s">
         <v>185</v>
@@ -13958,10 +13958,10 @@
         <v>76</v>
       </c>
       <c r="C63" t="s">
-        <v>123</v>
+        <v>145</v>
       </c>
       <c r="D63" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E63" t="s">
         <v>249</v>
@@ -13997,13 +13997,13 @@
         <v>699</v>
       </c>
       <c r="P63">
-        <v>0</v>
+        <v>3.36</v>
       </c>
       <c r="Q63">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="R63">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="S63">
         <v>0</v>
@@ -14143,10 +14143,10 @@
         <v>76</v>
       </c>
       <c r="C64" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="D64" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E64" t="s">
         <v>250</v>
@@ -14328,10 +14328,10 @@
         <v>76</v>
       </c>
       <c r="C65" t="s">
-        <v>145</v>
+        <v>123</v>
       </c>
       <c r="D65" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E65" t="s">
         <v>251</v>
@@ -14367,13 +14367,13 @@
         <v>699</v>
       </c>
       <c r="P65">
-        <v>3.36</v>
+        <v>0</v>
       </c>
       <c r="Q65">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="R65">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="S65">
         <v>0</v>
@@ -14513,7 +14513,7 @@
         <v>76</v>
       </c>
       <c r="C66" t="s">
-        <v>146</v>
+        <v>129</v>
       </c>
       <c r="D66" t="s">
         <v>186</v>
@@ -14701,7 +14701,7 @@
         <v>147</v>
       </c>
       <c r="D67" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E67" t="s">
         <v>253</v>
@@ -14883,7 +14883,7 @@
         <v>76</v>
       </c>
       <c r="C68" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="D68" t="s">
         <v>186</v>
@@ -15068,7 +15068,7 @@
         <v>76</v>
       </c>
       <c r="C69" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="D69" t="s">
         <v>185</v>
@@ -15253,10 +15253,10 @@
         <v>76</v>
       </c>
       <c r="C70" t="s">
-        <v>149</v>
+        <v>127</v>
       </c>
       <c r="D70" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E70" t="s">
         <v>256</v>
@@ -15438,7 +15438,7 @@
         <v>76</v>
       </c>
       <c r="C71" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="D71" t="s">
         <v>186</v>
@@ -15477,13 +15477,13 @@
         <v>699</v>
       </c>
       <c r="P71">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="Q71">
-        <v>0</v>
+        <v>7.41</v>
       </c>
       <c r="R71">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="S71">
         <v>0</v>
@@ -15623,7 +15623,7 @@
         <v>76</v>
       </c>
       <c r="C72" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="D72" t="s">
         <v>186</v>
@@ -15662,13 +15662,13 @@
         <v>699</v>
       </c>
       <c r="P72">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="Q72">
-        <v>7.41</v>
+        <v>0</v>
       </c>
       <c r="R72">
-        <v>17.5</v>
+        <v>0</v>
       </c>
       <c r="S72">
         <v>0</v>
@@ -15808,7 +15808,7 @@
         <v>76</v>
       </c>
       <c r="C73" t="s">
-        <v>125</v>
+        <v>149</v>
       </c>
       <c r="D73" t="s">
         <v>186</v>
@@ -15993,10 +15993,10 @@
         <v>76</v>
       </c>
       <c r="C74" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="D74" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E74" t="s">
         <v>260</v>
@@ -16363,7 +16363,7 @@
         <v>77</v>
       </c>
       <c r="C76" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="D76" t="s">
         <v>186</v>
@@ -16733,7 +16733,7 @@
         <v>78</v>
       </c>
       <c r="C78" t="s">
-        <v>129</v>
+        <v>120</v>
       </c>
       <c r="D78" t="s">
         <v>186</v>
@@ -16918,7 +16918,7 @@
         <v>78</v>
       </c>
       <c r="C79" t="s">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="D79" t="s">
         <v>186</v>
@@ -17658,10 +17658,10 @@
         <v>80</v>
       </c>
       <c r="C83" t="s">
-        <v>154</v>
+        <v>127</v>
       </c>
       <c r="D83" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E83" t="s">
         <v>269</v>
@@ -17843,7 +17843,7 @@
         <v>80</v>
       </c>
       <c r="C84" t="s">
-        <v>155</v>
+        <v>129</v>
       </c>
       <c r="D84" t="s">
         <v>186</v>
@@ -17882,13 +17882,13 @@
         <v>699</v>
       </c>
       <c r="P84">
-        <v>2.69</v>
+        <v>0</v>
       </c>
       <c r="Q84">
-        <v>3.31</v>
+        <v>0</v>
       </c>
       <c r="R84">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="S84">
         <v>0</v>
@@ -17927,10 +17927,10 @@
         <v>0</v>
       </c>
       <c r="AE84">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AF84">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AG84">
         <v>0</v>
@@ -18028,10 +18028,10 @@
         <v>80</v>
       </c>
       <c r="C85" t="s">
-        <v>155</v>
+        <v>132</v>
       </c>
       <c r="D85" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E85" t="s">
         <v>271</v>
@@ -18067,13 +18067,13 @@
         <v>699</v>
       </c>
       <c r="P85">
-        <v>5.38</v>
+        <v>0</v>
       </c>
       <c r="Q85">
-        <v>4.37</v>
+        <v>0</v>
       </c>
       <c r="R85">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="S85">
         <v>0</v>
@@ -18213,7 +18213,7 @@
         <v>80</v>
       </c>
       <c r="C86" t="s">
-        <v>150</v>
+        <v>131</v>
       </c>
       <c r="D86" t="s">
         <v>186</v>
@@ -18252,13 +18252,13 @@
         <v>699</v>
       </c>
       <c r="P86">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="Q86">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="R86">
-        <v>0</v>
+        <v>4.01</v>
       </c>
       <c r="S86">
         <v>0</v>
@@ -18297,10 +18297,10 @@
         <v>0</v>
       </c>
       <c r="AE86">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AF86">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AG86">
         <v>0</v>
@@ -18437,13 +18437,13 @@
         <v>699</v>
       </c>
       <c r="P87">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="Q87">
-        <v>0</v>
+        <v>3.66</v>
       </c>
       <c r="R87">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="S87">
         <v>0</v>
@@ -18482,10 +18482,10 @@
         <v>0</v>
       </c>
       <c r="AE87">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AF87">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AG87">
         <v>0</v>
@@ -18583,7 +18583,7 @@
         <v>80</v>
       </c>
       <c r="C88" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="D88" t="s">
         <v>186</v>
@@ -18622,13 +18622,13 @@
         <v>699</v>
       </c>
       <c r="P88">
-        <v>2.46</v>
+        <v>5.38</v>
       </c>
       <c r="Q88">
-        <v>3.66</v>
+        <v>4.37</v>
       </c>
       <c r="R88">
-        <v>2.99</v>
+        <v>1.67</v>
       </c>
       <c r="S88">
         <v>0</v>
@@ -18667,10 +18667,10 @@
         <v>0</v>
       </c>
       <c r="AE88">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AF88">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AG88">
         <v>0</v>
@@ -18768,7 +18768,7 @@
         <v>80</v>
       </c>
       <c r="C89" t="s">
-        <v>131</v>
+        <v>154</v>
       </c>
       <c r="D89" t="s">
         <v>186</v>
@@ -18807,13 +18807,13 @@
         <v>699</v>
       </c>
       <c r="P89">
-        <v>2.09</v>
+        <v>2.69</v>
       </c>
       <c r="Q89">
-        <v>3.48</v>
+        <v>3.31</v>
       </c>
       <c r="R89">
-        <v>4.01</v>
+        <v>2.92</v>
       </c>
       <c r="S89">
         <v>0</v>
@@ -18852,10 +18852,10 @@
         <v>0</v>
       </c>
       <c r="AE89">
-        <v>1.98</v>
+        <v>1.87</v>
       </c>
       <c r="AF89">
-        <v>1.73</v>
+        <v>1.89</v>
       </c>
       <c r="AG89">
         <v>0</v>
@@ -18953,7 +18953,7 @@
         <v>80</v>
       </c>
       <c r="C90" t="s">
-        <v>125</v>
+        <v>131</v>
       </c>
       <c r="D90" t="s">
         <v>186</v>
@@ -18992,13 +18992,13 @@
         <v>699</v>
       </c>
       <c r="P90">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Q90">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="R90">
-        <v>0</v>
+        <v>4.07</v>
       </c>
       <c r="S90">
         <v>0</v>
@@ -19037,10 +19037,10 @@
         <v>0</v>
       </c>
       <c r="AE90">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AF90">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AG90">
         <v>0</v>
@@ -19138,10 +19138,10 @@
         <v>80</v>
       </c>
       <c r="C91" t="s">
-        <v>132</v>
+        <v>155</v>
       </c>
       <c r="D91" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E91" t="s">
         <v>277</v>
@@ -19323,10 +19323,10 @@
         <v>80</v>
       </c>
       <c r="C92" t="s">
-        <v>128</v>
+        <v>156</v>
       </c>
       <c r="D92" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E92" t="s">
         <v>278</v>
@@ -19508,7 +19508,7 @@
         <v>80</v>
       </c>
       <c r="C93" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="D93" t="s">
         <v>186</v>
@@ -19693,7 +19693,7 @@
         <v>80</v>
       </c>
       <c r="C94" t="s">
-        <v>131</v>
+        <v>150</v>
       </c>
       <c r="D94" t="s">
         <v>186</v>
@@ -19732,13 +19732,13 @@
         <v>699</v>
       </c>
       <c r="P94">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Q94">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="R94">
-        <v>4.07</v>
+        <v>0</v>
       </c>
       <c r="S94">
         <v>0</v>
@@ -19777,10 +19777,10 @@
         <v>0</v>
       </c>
       <c r="AE94">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AF94">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AG94">
         <v>0</v>
@@ -20248,7 +20248,7 @@
         <v>83</v>
       </c>
       <c r="C97" t="s">
-        <v>140</v>
+        <v>158</v>
       </c>
       <c r="D97" t="s">
         <v>186</v>
@@ -20287,13 +20287,13 @@
         <v>699</v>
       </c>
       <c r="P97">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="Q97">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R97">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="S97">
         <v>0</v>
@@ -20433,10 +20433,10 @@
         <v>83</v>
       </c>
       <c r="C98" t="s">
-        <v>158</v>
+        <v>136</v>
       </c>
       <c r="D98" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E98" t="s">
         <v>284</v>
@@ -20618,10 +20618,10 @@
         <v>83</v>
       </c>
       <c r="C99" t="s">
-        <v>136</v>
+        <v>159</v>
       </c>
       <c r="D99" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E99" t="s">
         <v>285</v>
@@ -20803,10 +20803,10 @@
         <v>83</v>
       </c>
       <c r="C100" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="D100" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E100" t="s">
         <v>286</v>
@@ -20988,10 +20988,10 @@
         <v>83</v>
       </c>
       <c r="C101" t="s">
-        <v>158</v>
+        <v>137</v>
       </c>
       <c r="D101" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E101" t="s">
         <v>287</v>
@@ -21027,13 +21027,13 @@
         <v>699</v>
       </c>
       <c r="P101">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="Q101">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="R101">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="S101">
         <v>0</v>
@@ -21173,10 +21173,10 @@
         <v>83</v>
       </c>
       <c r="C102" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="D102" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E102" t="s">
         <v>288</v>
@@ -21543,10 +21543,10 @@
         <v>83</v>
       </c>
       <c r="C104" t="s">
-        <v>141</v>
+        <v>161</v>
       </c>
       <c r="D104" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E104" t="s">
         <v>290</v>
@@ -21728,10 +21728,10 @@
         <v>83</v>
       </c>
       <c r="C105" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="D105" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E105" t="s">
         <v>291</v>
@@ -21913,10 +21913,10 @@
         <v>83</v>
       </c>
       <c r="C106" t="s">
-        <v>159</v>
+        <v>142</v>
       </c>
       <c r="D106" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E106" t="s">
         <v>292</v>
@@ -22098,7 +22098,7 @@
         <v>83</v>
       </c>
       <c r="C107" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="D107" t="s">
         <v>186</v>
@@ -22283,7 +22283,7 @@
         <v>84</v>
       </c>
       <c r="C108" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="D108" t="s">
         <v>186</v>
@@ -22468,7 +22468,7 @@
         <v>84</v>
       </c>
       <c r="C109" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="D109" t="s">
         <v>186</v>
@@ -22838,10 +22838,10 @@
         <v>85</v>
       </c>
       <c r="C111" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="D111" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E111" t="s">
         <v>297</v>
@@ -23023,7 +23023,7 @@
         <v>85</v>
       </c>
       <c r="C112" t="s">
-        <v>146</v>
+        <v>119</v>
       </c>
       <c r="D112" t="s">
         <v>186</v>
@@ -23208,7 +23208,7 @@
         <v>85</v>
       </c>
       <c r="C113" t="s">
-        <v>119</v>
+        <v>149</v>
       </c>
       <c r="D113" t="s">
         <v>186</v>
@@ -23393,10 +23393,10 @@
         <v>85</v>
       </c>
       <c r="C114" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="D114" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E114" t="s">
         <v>300</v>
@@ -23578,7 +23578,7 @@
         <v>85</v>
       </c>
       <c r="C115" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="D115" t="s">
         <v>186</v>
@@ -25428,7 +25428,7 @@
         <v>87</v>
       </c>
       <c r="C125" t="s">
-        <v>163</v>
+        <v>120</v>
       </c>
       <c r="D125" t="s">
         <v>186</v>
@@ -25616,7 +25616,7 @@
         <v>163</v>
       </c>
       <c r="D126" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E126" t="s">
         <v>312</v>
@@ -25652,13 +25652,13 @@
         <v>699</v>
       </c>
       <c r="P126">
-        <v>0</v>
+        <v>4.07</v>
       </c>
       <c r="Q126">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="R126">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="S126">
         <v>0</v>
@@ -25801,7 +25801,7 @@
         <v>163</v>
       </c>
       <c r="D127" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E127" t="s">
         <v>313</v>
@@ -25837,13 +25837,13 @@
         <v>699</v>
       </c>
       <c r="P127">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="Q127">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="R127">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="S127">
         <v>0</v>
@@ -25983,7 +25983,7 @@
         <v>87</v>
       </c>
       <c r="C128" t="s">
-        <v>164</v>
+        <v>125</v>
       </c>
       <c r="D128" t="s">
         <v>186</v>
@@ -26168,10 +26168,10 @@
         <v>87</v>
       </c>
       <c r="C129" t="s">
-        <v>129</v>
+        <v>163</v>
       </c>
       <c r="D129" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E129" t="s">
         <v>315</v>
@@ -26207,13 +26207,13 @@
         <v>699</v>
       </c>
       <c r="P129">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="Q129">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R129">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="S129">
         <v>0</v>
@@ -26353,10 +26353,10 @@
         <v>87</v>
       </c>
       <c r="C130" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="D130" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E130" t="s">
         <v>316</v>
@@ -26392,13 +26392,13 @@
         <v>699</v>
       </c>
       <c r="P130">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="Q130">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="R130">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="S130">
         <v>0</v>
@@ -26538,10 +26538,10 @@
         <v>87</v>
       </c>
       <c r="C131" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="D131" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E131" t="s">
         <v>317</v>
@@ -26577,13 +26577,13 @@
         <v>699</v>
       </c>
       <c r="P131">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Q131">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="R131">
-        <v>0</v>
+        <v>3.01</v>
       </c>
       <c r="S131">
         <v>0</v>
@@ -26723,7 +26723,7 @@
         <v>87</v>
       </c>
       <c r="C132" t="s">
-        <v>164</v>
+        <v>124</v>
       </c>
       <c r="D132" t="s">
         <v>186</v>
@@ -26917,7 +26917,7 @@
         <v>319</v>
       </c>
       <c r="F133" t="s">
-        <v>575</v>
+        <v>293</v>
       </c>
       <c r="G133">
         <v>0</v>
@@ -27093,7 +27093,7 @@
         <v>87</v>
       </c>
       <c r="C134" t="s">
-        <v>120</v>
+        <v>143</v>
       </c>
       <c r="D134" t="s">
         <v>186</v>
@@ -27102,7 +27102,7 @@
         <v>320</v>
       </c>
       <c r="F134" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="G134">
         <v>0</v>
@@ -27278,16 +27278,16 @@
         <v>87</v>
       </c>
       <c r="C135" t="s">
-        <v>144</v>
+        <v>129</v>
       </c>
       <c r="D135" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E135" t="s">
         <v>321</v>
       </c>
       <c r="F135" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="G135">
         <v>0</v>
@@ -27463,7 +27463,7 @@
         <v>87</v>
       </c>
       <c r="C136" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="D136" t="s">
         <v>186</v>
@@ -27472,7 +27472,7 @@
         <v>322</v>
       </c>
       <c r="F136" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="G136">
         <v>0</v>
@@ -27648,16 +27648,16 @@
         <v>87</v>
       </c>
       <c r="C137" t="s">
-        <v>124</v>
+        <v>151</v>
       </c>
       <c r="D137" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E137" t="s">
         <v>323</v>
       </c>
       <c r="F137" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="G137">
         <v>0</v>
@@ -27833,16 +27833,16 @@
         <v>87</v>
       </c>
       <c r="C138" t="s">
-        <v>161</v>
+        <v>151</v>
       </c>
       <c r="D138" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E138" t="s">
         <v>324</v>
       </c>
       <c r="F138" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="G138">
         <v>0</v>
@@ -28018,7 +28018,7 @@
         <v>87</v>
       </c>
       <c r="C139" t="s">
-        <v>143</v>
+        <v>159</v>
       </c>
       <c r="D139" t="s">
         <v>186</v>
@@ -28027,7 +28027,7 @@
         <v>325</v>
       </c>
       <c r="F139" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="G139">
         <v>0</v>
@@ -28212,7 +28212,7 @@
         <v>326</v>
       </c>
       <c r="F140" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="G140">
         <v>0</v>
@@ -28388,7 +28388,7 @@
         <v>87</v>
       </c>
       <c r="C141" t="s">
-        <v>165</v>
+        <v>159</v>
       </c>
       <c r="D141" t="s">
         <v>186</v>
@@ -28397,7 +28397,7 @@
         <v>327</v>
       </c>
       <c r="F141" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="G141">
         <v>0</v>
@@ -28573,16 +28573,16 @@
         <v>87</v>
       </c>
       <c r="C142" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="D142" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E142" t="s">
         <v>328</v>
       </c>
       <c r="F142" t="s">
-        <v>284</v>
+        <v>583</v>
       </c>
       <c r="G142">
         <v>0</v>
@@ -28612,13 +28612,13 @@
         <v>699</v>
       </c>
       <c r="P142">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Q142">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R142">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="S142">
         <v>0</v>
@@ -28758,10 +28758,10 @@
         <v>87</v>
       </c>
       <c r="C143" t="s">
-        <v>151</v>
+        <v>164</v>
       </c>
       <c r="D143" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E143" t="s">
         <v>329</v>
@@ -28943,10 +28943,10 @@
         <v>87</v>
       </c>
       <c r="C144" t="s">
-        <v>151</v>
+        <v>164</v>
       </c>
       <c r="D144" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E144" t="s">
         <v>330</v>
@@ -29128,10 +29128,10 @@
         <v>87</v>
       </c>
       <c r="C145" t="s">
-        <v>151</v>
+        <v>165</v>
       </c>
       <c r="D145" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E145" t="s">
         <v>331</v>
@@ -29313,7 +29313,7 @@
         <v>87</v>
       </c>
       <c r="C146" t="s">
-        <v>166</v>
+        <v>147</v>
       </c>
       <c r="D146" t="s">
         <v>185</v>
@@ -29352,13 +29352,13 @@
         <v>699</v>
       </c>
       <c r="P146">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Q146">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="R146">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="S146">
         <v>0</v>
@@ -29501,7 +29501,7 @@
         <v>166</v>
       </c>
       <c r="D147" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E147" t="s">
         <v>333</v>
@@ -29537,13 +29537,13 @@
         <v>699</v>
       </c>
       <c r="P147">
-        <v>4.07</v>
+        <v>0</v>
       </c>
       <c r="Q147">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="R147">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="S147">
         <v>0</v>
@@ -29686,7 +29686,7 @@
         <v>166</v>
       </c>
       <c r="D148" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E148" t="s">
         <v>334</v>
@@ -29722,13 +29722,13 @@
         <v>699</v>
       </c>
       <c r="P148">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="Q148">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="R148">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="S148">
         <v>0</v>
@@ -29871,7 +29871,7 @@
         <v>166</v>
       </c>
       <c r="D149" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E149" t="s">
         <v>335</v>
@@ -29907,13 +29907,13 @@
         <v>699</v>
       </c>
       <c r="P149">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="Q149">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R149">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="S149">
         <v>0</v>
@@ -30053,7 +30053,7 @@
         <v>87</v>
       </c>
       <c r="C150" t="s">
-        <v>166</v>
+        <v>151</v>
       </c>
       <c r="D150" t="s">
         <v>185</v>
@@ -30092,13 +30092,13 @@
         <v>699</v>
       </c>
       <c r="P150">
-        <v>5.4</v>
+        <v>0</v>
       </c>
       <c r="Q150">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="R150">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="S150">
         <v>0</v>
@@ -30238,10 +30238,10 @@
         <v>87</v>
       </c>
       <c r="C151" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="D151" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E151" t="s">
         <v>337</v>
@@ -30277,13 +30277,13 @@
         <v>699</v>
       </c>
       <c r="P151">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Q151">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="R151">
-        <v>3.01</v>
+        <v>0</v>
       </c>
       <c r="S151">
         <v>0</v>
@@ -30423,7 +30423,7 @@
         <v>87</v>
       </c>
       <c r="C152" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="D152" t="s">
         <v>186</v>
@@ -30608,7 +30608,7 @@
         <v>87</v>
       </c>
       <c r="C153" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="D153" t="s">
         <v>186</v>
@@ -30793,7 +30793,7 @@
         <v>87</v>
       </c>
       <c r="C154" t="s">
-        <v>125</v>
+        <v>165</v>
       </c>
       <c r="D154" t="s">
         <v>186</v>
@@ -30978,7 +30978,7 @@
         <v>87</v>
       </c>
       <c r="C155" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="D155" t="s">
         <v>186</v>
@@ -31163,7 +31163,7 @@
         <v>87</v>
       </c>
       <c r="C156" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="D156" t="s">
         <v>186</v>
@@ -32088,7 +32088,7 @@
         <v>89</v>
       </c>
       <c r="C161" t="s">
-        <v>130</v>
+        <v>156</v>
       </c>
       <c r="D161" t="s">
         <v>186</v>
@@ -32273,7 +32273,7 @@
         <v>89</v>
       </c>
       <c r="C162" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="D162" t="s">
         <v>186</v>
@@ -32312,13 +32312,13 @@
         <v>699</v>
       </c>
       <c r="P162">
-        <v>0</v>
+        <v>5.17</v>
       </c>
       <c r="Q162">
-        <v>0</v>
+        <v>4.37</v>
       </c>
       <c r="R162">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="S162">
         <v>0</v>
@@ -32357,10 +32357,10 @@
         <v>0</v>
       </c>
       <c r="AE162">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AF162">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AG162">
         <v>0</v>
@@ -32458,7 +32458,7 @@
         <v>89</v>
       </c>
       <c r="C163" t="s">
-        <v>155</v>
+        <v>130</v>
       </c>
       <c r="D163" t="s">
         <v>186</v>
@@ -32497,13 +32497,13 @@
         <v>699</v>
       </c>
       <c r="P163">
-        <v>5.17</v>
+        <v>0</v>
       </c>
       <c r="Q163">
-        <v>4.37</v>
+        <v>0</v>
       </c>
       <c r="R163">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="S163">
         <v>0</v>
@@ -32542,10 +32542,10 @@
         <v>0</v>
       </c>
       <c r="AE163">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AF163">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AG163">
         <v>0</v>
@@ -32643,7 +32643,7 @@
         <v>89</v>
       </c>
       <c r="C164" t="s">
-        <v>157</v>
+        <v>168</v>
       </c>
       <c r="D164" t="s">
         <v>186</v>
@@ -32682,13 +32682,13 @@
         <v>699</v>
       </c>
       <c r="P164">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="Q164">
-        <v>4.32</v>
+        <v>0</v>
       </c>
       <c r="R164">
-        <v>4.52</v>
+        <v>0</v>
       </c>
       <c r="S164">
         <v>0</v>
@@ -32733,10 +32733,10 @@
         <v>0</v>
       </c>
       <c r="AG164">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AH164">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AI164">
         <v>0</v>
@@ -32828,7 +32828,7 @@
         <v>89</v>
       </c>
       <c r="C165" t="s">
-        <v>168</v>
+        <v>157</v>
       </c>
       <c r="D165" t="s">
         <v>186</v>
@@ -32867,13 +32867,13 @@
         <v>699</v>
       </c>
       <c r="P165">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="Q165">
-        <v>0</v>
+        <v>4.32</v>
       </c>
       <c r="R165">
-        <v>0</v>
+        <v>4.52</v>
       </c>
       <c r="S165">
         <v>0</v>
@@ -32918,10 +32918,10 @@
         <v>0</v>
       </c>
       <c r="AG165">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AH165">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AI165">
         <v>0</v>
@@ -33013,7 +33013,7 @@
         <v>90</v>
       </c>
       <c r="C166" t="s">
-        <v>120</v>
+        <v>145</v>
       </c>
       <c r="D166" t="s">
         <v>186</v>
@@ -33383,7 +33383,7 @@
         <v>90</v>
       </c>
       <c r="C168" t="s">
-        <v>169</v>
+        <v>120</v>
       </c>
       <c r="D168" t="s">
         <v>186</v>
@@ -33753,10 +33753,10 @@
         <v>90</v>
       </c>
       <c r="C170" t="s">
-        <v>169</v>
+        <v>136</v>
       </c>
       <c r="D170" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E170" t="s">
         <v>356</v>
@@ -34123,7 +34123,7 @@
         <v>90</v>
       </c>
       <c r="C172" t="s">
-        <v>131</v>
+        <v>169</v>
       </c>
       <c r="D172" t="s">
         <v>186</v>
@@ -34162,13 +34162,13 @@
         <v>699</v>
       </c>
       <c r="P172">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="Q172">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="R172">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="S172">
         <v>0</v>
@@ -34308,7 +34308,7 @@
         <v>90</v>
       </c>
       <c r="C173" t="s">
-        <v>152</v>
+        <v>170</v>
       </c>
       <c r="D173" t="s">
         <v>186</v>
@@ -34347,13 +34347,13 @@
         <v>699</v>
       </c>
       <c r="P173">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="Q173">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="R173">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="S173">
         <v>0</v>
@@ -34493,7 +34493,7 @@
         <v>90</v>
       </c>
       <c r="C174" t="s">
-        <v>170</v>
+        <v>131</v>
       </c>
       <c r="D174" t="s">
         <v>186</v>
@@ -34532,13 +34532,13 @@
         <v>699</v>
       </c>
       <c r="P174">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="Q174">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R174">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="S174">
         <v>0</v>
@@ -34678,7 +34678,7 @@
         <v>90</v>
       </c>
       <c r="C175" t="s">
-        <v>145</v>
+        <v>155</v>
       </c>
       <c r="D175" t="s">
         <v>186</v>
@@ -34717,13 +34717,13 @@
         <v>699</v>
       </c>
       <c r="P175">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="Q175">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R175">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="S175">
         <v>0</v>
@@ -34863,10 +34863,10 @@
         <v>90</v>
       </c>
       <c r="C176" t="s">
-        <v>136</v>
+        <v>169</v>
       </c>
       <c r="D176" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E176" t="s">
         <v>362</v>
@@ -35233,10 +35233,10 @@
         <v>92</v>
       </c>
       <c r="C178" t="s">
-        <v>159</v>
+        <v>135</v>
       </c>
       <c r="D178" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E178" t="s">
         <v>364</v>
@@ -35418,7 +35418,7 @@
         <v>92</v>
       </c>
       <c r="C179" t="s">
-        <v>135</v>
+        <v>160</v>
       </c>
       <c r="D179" t="s">
         <v>186</v>
@@ -35603,10 +35603,10 @@
         <v>92</v>
       </c>
       <c r="C180" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="D180" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E180" t="s">
         <v>366</v>
@@ -35788,7 +35788,7 @@
         <v>92</v>
       </c>
       <c r="C181" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="D181" t="s">
         <v>185</v>
@@ -35973,10 +35973,10 @@
         <v>93</v>
       </c>
       <c r="C182" t="s">
-        <v>158</v>
+        <v>172</v>
       </c>
       <c r="D182" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E182" t="s">
         <v>368</v>
@@ -36012,13 +36012,13 @@
         <v>699</v>
       </c>
       <c r="P182">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="Q182">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="R182">
-        <v>6.76</v>
+        <v>0</v>
       </c>
       <c r="S182">
         <v>0</v>
@@ -36158,7 +36158,7 @@
         <v>93</v>
       </c>
       <c r="C183" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="D183" t="s">
         <v>186</v>
@@ -36343,10 +36343,10 @@
         <v>93</v>
       </c>
       <c r="C184" t="s">
-        <v>173</v>
+        <v>146</v>
       </c>
       <c r="D184" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E184" t="s">
         <v>370</v>
@@ -36528,10 +36528,10 @@
         <v>93</v>
       </c>
       <c r="C185" t="s">
-        <v>173</v>
+        <v>148</v>
       </c>
       <c r="D185" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E185" t="s">
         <v>371</v>
@@ -36713,10 +36713,10 @@
         <v>93</v>
       </c>
       <c r="C186" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="D186" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E186" t="s">
         <v>372</v>
@@ -36898,7 +36898,7 @@
         <v>93</v>
       </c>
       <c r="C187" t="s">
-        <v>172</v>
+        <v>142</v>
       </c>
       <c r="D187" t="s">
         <v>186</v>
@@ -37083,7 +37083,7 @@
         <v>93</v>
       </c>
       <c r="C188" t="s">
-        <v>140</v>
+        <v>158</v>
       </c>
       <c r="D188" t="s">
         <v>186</v>
@@ -37122,13 +37122,13 @@
         <v>699</v>
       </c>
       <c r="P188">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="Q188">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="R188">
-        <v>0</v>
+        <v>6.76</v>
       </c>
       <c r="S188">
         <v>0</v>
@@ -37268,7 +37268,7 @@
         <v>93</v>
       </c>
       <c r="C189" t="s">
-        <v>147</v>
+        <v>173</v>
       </c>
       <c r="D189" t="s">
         <v>186</v>
@@ -37453,7 +37453,7 @@
         <v>93</v>
       </c>
       <c r="C190" t="s">
-        <v>158</v>
+        <v>148</v>
       </c>
       <c r="D190" t="s">
         <v>186</v>
@@ -37492,13 +37492,13 @@
         <v>699</v>
       </c>
       <c r="P190">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="Q190">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="R190">
-        <v>4.56</v>
+        <v>0</v>
       </c>
       <c r="S190">
         <v>0</v>
@@ -37638,7 +37638,7 @@
         <v>93</v>
       </c>
       <c r="C191" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="D191" t="s">
         <v>186</v>
@@ -37823,7 +37823,7 @@
         <v>93</v>
       </c>
       <c r="C192" t="s">
-        <v>147</v>
+        <v>173</v>
       </c>
       <c r="D192" t="s">
         <v>186</v>
@@ -38008,10 +38008,10 @@
         <v>93</v>
       </c>
       <c r="C193" t="s">
-        <v>174</v>
+        <v>158</v>
       </c>
       <c r="D193" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E193" t="s">
         <v>379</v>
@@ -38047,13 +38047,13 @@
         <v>699</v>
       </c>
       <c r="P193">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="Q193">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R193">
-        <v>0</v>
+        <v>4.56</v>
       </c>
       <c r="S193">
         <v>0</v>
@@ -38193,10 +38193,10 @@
         <v>93</v>
       </c>
       <c r="C194" t="s">
-        <v>122</v>
+        <v>172</v>
       </c>
       <c r="D194" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E194" t="s">
         <v>380</v>
@@ -38232,13 +38232,13 @@
         <v>699</v>
       </c>
       <c r="P194">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Q194">
-        <v>3.66</v>
+        <v>0</v>
       </c>
       <c r="R194">
-        <v>3.36</v>
+        <v>0</v>
       </c>
       <c r="S194">
         <v>0</v>
@@ -38378,7 +38378,7 @@
         <v>93</v>
       </c>
       <c r="C195" t="s">
-        <v>149</v>
+        <v>173</v>
       </c>
       <c r="D195" t="s">
         <v>186</v>
@@ -38563,7 +38563,7 @@
         <v>93</v>
       </c>
       <c r="C196" t="s">
-        <v>172</v>
+        <v>122</v>
       </c>
       <c r="D196" t="s">
         <v>186</v>
@@ -38602,13 +38602,13 @@
         <v>699</v>
       </c>
       <c r="P196">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Q196">
-        <v>0</v>
+        <v>3.66</v>
       </c>
       <c r="R196">
-        <v>0</v>
+        <v>3.36</v>
       </c>
       <c r="S196">
         <v>0</v>
@@ -38748,10 +38748,10 @@
         <v>94</v>
       </c>
       <c r="C197" t="s">
-        <v>144</v>
+        <v>175</v>
       </c>
       <c r="D197" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E197" t="s">
         <v>383</v>
@@ -38933,7 +38933,7 @@
         <v>94</v>
       </c>
       <c r="C198" t="s">
-        <v>175</v>
+        <v>124</v>
       </c>
       <c r="D198" t="s">
         <v>186</v>
@@ -39118,10 +39118,10 @@
         <v>94</v>
       </c>
       <c r="C199" t="s">
-        <v>175</v>
+        <v>147</v>
       </c>
       <c r="D199" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E199" t="s">
         <v>385</v>
@@ -39303,7 +39303,7 @@
         <v>94</v>
       </c>
       <c r="C200" t="s">
-        <v>124</v>
+        <v>175</v>
       </c>
       <c r="D200" t="s">
         <v>186</v>
@@ -39488,7 +39488,7 @@
         <v>94</v>
       </c>
       <c r="C201" t="s">
-        <v>175</v>
+        <v>159</v>
       </c>
       <c r="D201" t="s">
         <v>186</v>
@@ -39858,7 +39858,7 @@
         <v>94</v>
       </c>
       <c r="C203" t="s">
-        <v>161</v>
+        <v>175</v>
       </c>
       <c r="D203" t="s">
         <v>186</v>
@@ -40043,7 +40043,7 @@
         <v>94</v>
       </c>
       <c r="C204" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="D204" t="s">
         <v>186</v>
@@ -40228,7 +40228,7 @@
         <v>95</v>
       </c>
       <c r="C205" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="D205" t="s">
         <v>186</v>
@@ -40413,7 +40413,7 @@
         <v>96</v>
       </c>
       <c r="C206" t="s">
-        <v>157</v>
+        <v>140</v>
       </c>
       <c r="D206" t="s">
         <v>186</v>
@@ -40452,13 +40452,13 @@
         <v>699</v>
       </c>
       <c r="P206">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="Q206">
-        <v>3.94</v>
+        <v>0</v>
       </c>
       <c r="R206">
-        <v>4.41</v>
+        <v>0</v>
       </c>
       <c r="S206">
         <v>0</v>
@@ -40497,10 +40497,10 @@
         <v>0</v>
       </c>
       <c r="AE206">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AF206">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AG206">
         <v>0</v>
@@ -40598,7 +40598,7 @@
         <v>96</v>
       </c>
       <c r="C207" t="s">
-        <v>139</v>
+        <v>157</v>
       </c>
       <c r="D207" t="s">
         <v>186</v>
@@ -40637,13 +40637,13 @@
         <v>699</v>
       </c>
       <c r="P207">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="Q207">
-        <v>0</v>
+        <v>3.94</v>
       </c>
       <c r="R207">
-        <v>0</v>
+        <v>4.41</v>
       </c>
       <c r="S207">
         <v>0</v>
@@ -40682,10 +40682,10 @@
         <v>0</v>
       </c>
       <c r="AE207">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AF207">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AG207">
         <v>0</v>
@@ -40783,10 +40783,10 @@
         <v>97</v>
       </c>
       <c r="C208" t="s">
-        <v>171</v>
+        <v>177</v>
       </c>
       <c r="D208" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E208" t="s">
         <v>394</v>
@@ -40968,10 +40968,10 @@
         <v>97</v>
       </c>
       <c r="C209" t="s">
-        <v>177</v>
+        <v>170</v>
       </c>
       <c r="D209" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E209" t="s">
         <v>395</v>
@@ -41338,7 +41338,7 @@
         <v>97</v>
       </c>
       <c r="C211" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="D211" t="s">
         <v>186</v>
@@ -41523,10 +41523,10 @@
         <v>98</v>
       </c>
       <c r="C212" t="s">
-        <v>127</v>
+        <v>178</v>
       </c>
       <c r="D212" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E212" t="s">
         <v>398</v>
@@ -41708,10 +41708,10 @@
         <v>98</v>
       </c>
       <c r="C213" t="s">
-        <v>178</v>
+        <v>126</v>
       </c>
       <c r="D213" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E213" t="s">
         <v>399</v>
@@ -42078,10 +42078,10 @@
         <v>100</v>
       </c>
       <c r="C215" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="D215" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E215" t="s">
         <v>401</v>
@@ -42117,13 +42117,13 @@
         <v>699</v>
       </c>
       <c r="P215">
-        <v>0</v>
+        <v>3.17</v>
       </c>
       <c r="Q215">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="R215">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="S215">
         <v>0</v>
@@ -42162,10 +42162,10 @@
         <v>0</v>
       </c>
       <c r="AE215">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AF215">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG215">
         <v>0</v>
@@ -42302,13 +42302,13 @@
         <v>699</v>
       </c>
       <c r="P216">
-        <v>2.38</v>
+        <v>4.68</v>
       </c>
       <c r="Q216">
-        <v>3.9</v>
+        <v>4.32</v>
       </c>
       <c r="R216">
-        <v>2.96</v>
+        <v>1.76</v>
       </c>
       <c r="S216">
         <v>0</v>
@@ -42448,7 +42448,7 @@
         <v>100</v>
       </c>
       <c r="C217" t="s">
-        <v>149</v>
+        <v>179</v>
       </c>
       <c r="D217" t="s">
         <v>186</v>
@@ -42487,13 +42487,13 @@
         <v>699</v>
       </c>
       <c r="P217">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="Q217">
-        <v>0</v>
+        <v>3.76</v>
       </c>
       <c r="R217">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="S217">
         <v>0</v>
@@ -42532,10 +42532,10 @@
         <v>0</v>
       </c>
       <c r="AE217">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AF217">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG217">
         <v>0</v>
@@ -42633,10 +42633,10 @@
         <v>100</v>
       </c>
       <c r="C218" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="D218" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E218" t="s">
         <v>404</v>
@@ -42672,13 +42672,13 @@
         <v>699</v>
       </c>
       <c r="P218">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="Q218">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="R218">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="S218">
         <v>0</v>
@@ -42717,10 +42717,10 @@
         <v>0</v>
       </c>
       <c r="AE218">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AF218">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AG218">
         <v>0</v>
@@ -42818,10 +42818,10 @@
         <v>100</v>
       </c>
       <c r="C219" t="s">
-        <v>178</v>
+        <v>146</v>
       </c>
       <c r="D219" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E219" t="s">
         <v>405</v>
@@ -43042,13 +43042,13 @@
         <v>699</v>
       </c>
       <c r="P220">
-        <v>3.8</v>
+        <v>2.48</v>
       </c>
       <c r="Q220">
-        <v>3.78</v>
+        <v>3.5</v>
       </c>
       <c r="R220">
-        <v>2.05</v>
+        <v>3.07</v>
       </c>
       <c r="S220">
         <v>0</v>
@@ -43087,10 +43087,10 @@
         <v>0</v>
       </c>
       <c r="AE220">
-        <v>1.73</v>
+        <v>1.8</v>
       </c>
       <c r="AF220">
-        <v>1.98</v>
+        <v>1.9</v>
       </c>
       <c r="AG220">
         <v>0</v>
@@ -43188,10 +43188,10 @@
         <v>100</v>
       </c>
       <c r="C221" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="D221" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E221" t="s">
         <v>407</v>
@@ -43227,13 +43227,13 @@
         <v>699</v>
       </c>
       <c r="P221">
-        <v>1.59</v>
+        <v>5.3</v>
       </c>
       <c r="Q221">
-        <v>4.73</v>
+        <v>3.73</v>
       </c>
       <c r="R221">
-        <v>5.79</v>
+        <v>1.71</v>
       </c>
       <c r="S221">
         <v>0</v>
@@ -43272,16 +43272,16 @@
         <v>0</v>
       </c>
       <c r="AE221">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AF221">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AG221">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AH221">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AI221">
         <v>0</v>
@@ -43558,10 +43558,10 @@
         <v>100</v>
       </c>
       <c r="C223" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="D223" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E223" t="s">
         <v>409</v>
@@ -43597,13 +43597,13 @@
         <v>699</v>
       </c>
       <c r="P223">
-        <v>5.3</v>
+        <v>3.8</v>
       </c>
       <c r="Q223">
-        <v>3.73</v>
+        <v>3.78</v>
       </c>
       <c r="R223">
-        <v>1.71</v>
+        <v>2.05</v>
       </c>
       <c r="S223">
         <v>0</v>
@@ -43642,10 +43642,10 @@
         <v>0</v>
       </c>
       <c r="AE223">
-        <v>1.95</v>
+        <v>1.73</v>
       </c>
       <c r="AF223">
-        <v>1.73</v>
+        <v>1.98</v>
       </c>
       <c r="AG223">
         <v>0</v>
@@ -43743,10 +43743,10 @@
         <v>100</v>
       </c>
       <c r="C224" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="D224" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E224" t="s">
         <v>410</v>
@@ -43782,13 +43782,13 @@
         <v>699</v>
       </c>
       <c r="P224">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="Q224">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="R224">
-        <v>3.07</v>
+        <v>0</v>
       </c>
       <c r="S224">
         <v>0</v>
@@ -43827,10 +43827,10 @@
         <v>0</v>
       </c>
       <c r="AE224">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AF224">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AG224">
         <v>0</v>
@@ -43928,10 +43928,10 @@
         <v>100</v>
       </c>
       <c r="C225" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="D225" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E225" t="s">
         <v>411</v>
@@ -43967,13 +43967,13 @@
         <v>699</v>
       </c>
       <c r="P225">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="Q225">
-        <v>3.76</v>
+        <v>0</v>
       </c>
       <c r="R225">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="S225">
         <v>0</v>
@@ -44012,10 +44012,10 @@
         <v>0</v>
       </c>
       <c r="AE225">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AF225">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AG225">
         <v>0</v>
@@ -44113,10 +44113,10 @@
         <v>100</v>
       </c>
       <c r="C226" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="D226" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E226" t="s">
         <v>412</v>
@@ -44152,13 +44152,13 @@
         <v>699</v>
       </c>
       <c r="P226">
-        <v>4.68</v>
+        <v>0</v>
       </c>
       <c r="Q226">
-        <v>4.32</v>
+        <v>0</v>
       </c>
       <c r="R226">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="S226">
         <v>0</v>
@@ -44197,10 +44197,10 @@
         <v>0</v>
       </c>
       <c r="AE226">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AF226">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AG226">
         <v>0</v>
@@ -44298,10 +44298,10 @@
         <v>100</v>
       </c>
       <c r="C227" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="D227" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E227" t="s">
         <v>413</v>
@@ -44337,13 +44337,13 @@
         <v>699</v>
       </c>
       <c r="P227">
-        <v>3.17</v>
+        <v>0</v>
       </c>
       <c r="Q227">
-        <v>3.68</v>
+        <v>0</v>
       </c>
       <c r="R227">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="S227">
         <v>0</v>
@@ -44382,10 +44382,10 @@
         <v>0</v>
       </c>
       <c r="AE227">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AF227">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AG227">
         <v>0</v>
@@ -44483,7 +44483,7 @@
         <v>100</v>
       </c>
       <c r="C228" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="D228" t="s">
         <v>185</v>
@@ -44522,13 +44522,13 @@
         <v>699</v>
       </c>
       <c r="P228">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Q228">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="R228">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="S228">
         <v>0</v>
@@ -44567,10 +44567,10 @@
         <v>0</v>
       </c>
       <c r="AE228">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AF228">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG228">
         <v>0</v>
@@ -44668,10 +44668,10 @@
         <v>100</v>
       </c>
       <c r="C229" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="D229" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E229" t="s">
         <v>415</v>
@@ -44707,13 +44707,13 @@
         <v>699</v>
       </c>
       <c r="P229">
-        <v>2.15</v>
+        <v>1.59</v>
       </c>
       <c r="Q229">
-        <v>3.44</v>
+        <v>4.73</v>
       </c>
       <c r="R229">
-        <v>3.5</v>
+        <v>5.79</v>
       </c>
       <c r="S229">
         <v>0</v>
@@ -44752,16 +44752,16 @@
         <v>0</v>
       </c>
       <c r="AE229">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AF229">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AG229">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AH229">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AI229">
         <v>0</v>
@@ -45408,10 +45408,10 @@
         <v>102</v>
       </c>
       <c r="C233" t="s">
-        <v>170</v>
+        <v>178</v>
       </c>
       <c r="D233" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E233" t="s">
         <v>419</v>
@@ -45778,7 +45778,7 @@
         <v>102</v>
       </c>
       <c r="C235" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="D235" t="s">
         <v>185</v>
@@ -45963,7 +45963,7 @@
         <v>102</v>
       </c>
       <c r="C236" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="D236" t="s">
         <v>185</v>
@@ -46148,10 +46148,10 @@
         <v>102</v>
       </c>
       <c r="C237" t="s">
-        <v>177</v>
+        <v>170</v>
       </c>
       <c r="D237" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E237" t="s">
         <v>423</v>
@@ -46888,7 +46888,7 @@
         <v>105</v>
       </c>
       <c r="C241" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="D241" t="s">
         <v>185</v>
@@ -47073,7 +47073,7 @@
         <v>106</v>
       </c>
       <c r="C242" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="D242" t="s">
         <v>185</v>
@@ -47112,13 +47112,13 @@
         <v>699</v>
       </c>
       <c r="P242">
-        <v>1.79</v>
+        <v>2.13</v>
       </c>
       <c r="Q242">
-        <v>3.62</v>
+        <v>3.34</v>
       </c>
       <c r="R242">
-        <v>4.84</v>
+        <v>3.67</v>
       </c>
       <c r="S242">
         <v>0</v>
@@ -47157,10 +47157,10 @@
         <v>0</v>
       </c>
       <c r="AE242">
-        <v>1.87</v>
+        <v>1.95</v>
       </c>
       <c r="AF242">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="AG242">
         <v>0</v>
@@ -47258,7 +47258,7 @@
         <v>106</v>
       </c>
       <c r="C243" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="D243" t="s">
         <v>185</v>
@@ -47297,13 +47297,13 @@
         <v>699</v>
       </c>
       <c r="P243">
-        <v>2.13</v>
+        <v>1.79</v>
       </c>
       <c r="Q243">
-        <v>3.34</v>
+        <v>3.62</v>
       </c>
       <c r="R243">
-        <v>3.67</v>
+        <v>4.84</v>
       </c>
       <c r="S243">
         <v>0</v>
@@ -47342,10 +47342,10 @@
         <v>0</v>
       </c>
       <c r="AE243">
-        <v>1.95</v>
+        <v>1.87</v>
       </c>
       <c r="AF243">
-        <v>1.73</v>
+        <v>1.8</v>
       </c>
       <c r="AG243">
         <v>0</v>
@@ -47443,7 +47443,7 @@
         <v>106</v>
       </c>
       <c r="C244" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="D244" t="s">
         <v>185</v>
@@ -47998,7 +47998,7 @@
         <v>108</v>
       </c>
       <c r="C247" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="D247" t="s">
         <v>185</v>
@@ -48037,13 +48037,13 @@
         <v>699</v>
       </c>
       <c r="P247">
-        <v>0</v>
+        <v>3.79</v>
       </c>
       <c r="Q247">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="R247">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="S247">
         <v>0</v>
@@ -48082,10 +48082,10 @@
         <v>0</v>
       </c>
       <c r="AE247">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AF247">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AG247">
         <v>0</v>
@@ -48183,7 +48183,7 @@
         <v>108</v>
       </c>
       <c r="C248" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="D248" t="s">
         <v>185</v>
@@ -48222,13 +48222,13 @@
         <v>699</v>
       </c>
       <c r="P248">
-        <v>3.79</v>
+        <v>0</v>
       </c>
       <c r="Q248">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="R248">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="S248">
         <v>0</v>
@@ -48267,10 +48267,10 @@
         <v>0</v>
       </c>
       <c r="AE248">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AF248">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AG248">
         <v>0</v>
@@ -48368,7 +48368,7 @@
         <v>109</v>
       </c>
       <c r="C249" t="s">
-        <v>184</v>
+        <v>177</v>
       </c>
       <c r="D249" t="s">
         <v>185</v>
@@ -48553,7 +48553,7 @@
         <v>109</v>
       </c>
       <c r="C250" t="s">
-        <v>174</v>
+        <v>183</v>
       </c>
       <c r="D250" t="s">
         <v>185</v>
@@ -48738,7 +48738,7 @@
         <v>109</v>
       </c>
       <c r="C251" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="D251" t="s">
         <v>185</v>
@@ -48923,7 +48923,7 @@
         <v>110</v>
       </c>
       <c r="C252" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="D252" t="s">
         <v>185</v>
@@ -49108,7 +49108,7 @@
         <v>111</v>
       </c>
       <c r="C253" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="D253" t="s">
         <v>185</v>
@@ -49293,7 +49293,7 @@
         <v>111</v>
       </c>
       <c r="C254" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="D254" t="s">
         <v>185</v>
@@ -49848,7 +49848,7 @@
         <v>114</v>
       </c>
       <c r="C257" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="D257" t="s">
         <v>185</v>

--- a/jogos_2026-05-10.xlsx
+++ b/jogos_2026-05-10.xlsx
@@ -361,15 +361,15 @@
     <t>22:00</t>
   </si>
   <si>
+    <t>South Korea K League 1</t>
+  </si>
+  <si>
+    <t>Australia New South Wales NPL</t>
+  </si>
+  <si>
     <t>South Korea K League 2</t>
   </si>
   <si>
-    <t>South Korea K League 1</t>
-  </si>
-  <si>
-    <t>Australia New South Wales NPL</t>
-  </si>
-  <si>
     <t>China China League One</t>
   </si>
   <si>
@@ -382,24 +382,24 @@
     <t>Indonesia Liga 1</t>
   </si>
   <si>
+    <t>China Chinese Super League</t>
+  </si>
+  <si>
     <t>Russia Russian Premier League</t>
   </si>
   <si>
-    <t>China Chinese Super League</t>
-  </si>
-  <si>
     <t>Spain Primera Division Women</t>
   </si>
   <si>
+    <t>Kazakhstan Kazakhstan Premier League</t>
+  </si>
+  <si>
+    <t>Portugal Liga 3</t>
+  </si>
+  <si>
     <t>Poland 1. Liga</t>
   </si>
   <si>
-    <t>Portugal Liga 3</t>
-  </si>
-  <si>
-    <t>Kazakhstan Kazakhstan Premier League</t>
-  </si>
-  <si>
     <t>Vietnam V.League 1</t>
   </si>
   <si>
@@ -412,108 +412,108 @@
     <t>Italy Serie A</t>
   </si>
   <si>
+    <t>Thailand Thai League T1</t>
+  </si>
+  <si>
     <t>Sweden Damallsvenskan</t>
   </si>
   <si>
     <t>Scotland Premiership</t>
   </si>
   <si>
-    <t>Thailand Thai League T1</t>
+    <t>Lithuania A Lyga</t>
   </si>
   <si>
     <t>Bulgaria First League</t>
   </si>
   <si>
-    <t>Lithuania A Lyga</t>
+    <t>India Indian Super League</t>
+  </si>
+  <si>
+    <t>Germany 2. Bundesliga</t>
   </si>
   <si>
     <t>Estonia Meistriliiga</t>
   </si>
   <si>
-    <t>Germany 2. Bundesliga</t>
-  </si>
-  <si>
-    <t>India Indian Super League</t>
+    <t>Singapore S.League</t>
   </si>
   <si>
     <t>Germany 3. Liga</t>
   </si>
   <si>
-    <t>Singapore S.League</t>
-  </si>
-  <si>
     <t>Belgium Pro League</t>
   </si>
   <si>
     <t>Croatia Druga HNL</t>
   </si>
   <si>
+    <t>Switzerland Super League</t>
+  </si>
+  <si>
+    <t>Denmark Superliga</t>
+  </si>
+  <si>
+    <t>Spain La Liga</t>
+  </si>
+  <si>
     <t>Sweden Allsvenskan</t>
   </si>
   <si>
-    <t>Denmark Superliga</t>
-  </si>
-  <si>
-    <t>Spain La Liga</t>
+    <t>Spain Segunda División</t>
   </si>
   <si>
     <t>Georgia Erovnuli Liga</t>
   </si>
   <si>
-    <t>Spain Segunda División</t>
-  </si>
-  <si>
-    <t>Switzerland Super League</t>
-  </si>
-  <si>
     <t>Malaysia Super League</t>
   </si>
   <si>
     <t>Norway Eliteserien</t>
   </si>
   <si>
+    <t>England Premier League</t>
+  </si>
+  <si>
+    <t>Czech Republic First League</t>
+  </si>
+  <si>
+    <t>Azerbaijan Premyer Liqası</t>
+  </si>
+  <si>
     <t>Slovenia PrvaLiga</t>
   </si>
   <si>
-    <t>Czech Republic First League</t>
-  </si>
-  <si>
-    <t>England Premier League</t>
-  </si>
-  <si>
     <t>Romania Liga I</t>
   </si>
   <si>
-    <t>Azerbaijan Premyer Liqası</t>
-  </si>
-  <si>
     <t>Germany Bundesliga</t>
   </si>
   <si>
+    <t>Hungary NB II</t>
+  </si>
+  <si>
+    <t>Croatia Prva HNL</t>
+  </si>
+  <si>
     <t>Greece Super League</t>
   </si>
   <si>
-    <t>Hungary NB II</t>
-  </si>
-  <si>
-    <t>Croatia Prva HNL</t>
-  </si>
-  <si>
     <t>Faroe Islands Faroe Islands Premier League</t>
   </si>
   <si>
     <t>Netherlands Eredivisie</t>
   </si>
   <si>
+    <t>Cyprus First Division</t>
+  </si>
+  <si>
+    <t>FYR Macedonia First Football League</t>
+  </si>
+  <si>
     <t>Norway First Division</t>
   </si>
   <si>
-    <t>Cyprus First Division</t>
-  </si>
-  <si>
-    <t>FYR Macedonia First Football League</t>
-  </si>
-  <si>
     <t>Austria Bundesliga</t>
   </si>
   <si>
@@ -532,12 +532,12 @@
     <t>Saudi Arabia Professional League</t>
   </si>
   <si>
+    <t>Serbia SuperLiga</t>
+  </si>
+  <si>
     <t>Chile Primera B</t>
   </si>
   <si>
-    <t>Serbia SuperLiga</t>
-  </si>
-  <si>
     <t>USA NWSL</t>
   </si>
   <si>
@@ -556,15 +556,15 @@
     <t>France Ligue 1</t>
   </si>
   <si>
+    <t>Brazil Serie B</t>
+  </si>
+  <si>
     <t>Brazil Serie A</t>
   </si>
   <si>
     <t>Bolivia LFPB</t>
   </si>
   <si>
-    <t>Brazil Serie B</t>
-  </si>
-  <si>
     <t>USA MLS</t>
   </si>
   <si>
@@ -580,177 +580,177 @@
     <t>2025</t>
   </si>
   <si>
+    <t>Ulsan</t>
+  </si>
+  <si>
+    <t>Rockdale City Suns</t>
+  </si>
+  <si>
+    <t>Blacktown City</t>
+  </si>
+  <si>
     <t>Seongnam</t>
   </si>
   <si>
-    <t>Ulsan</t>
-  </si>
-  <si>
-    <t>Blacktown City</t>
-  </si>
-  <si>
-    <t>Rockdale City Suns</t>
-  </si>
-  <si>
     <t>APIA Leichhardt Tigers</t>
   </si>
   <si>
     <t>Dalian Huayi</t>
   </si>
   <si>
+    <t>Shaanxi Union</t>
+  </si>
+  <si>
     <t>Yanbian Longding</t>
   </si>
   <si>
     <t>Ufa</t>
   </si>
   <si>
-    <t>Shaanxi Union</t>
+    <t>Ansan Greeners</t>
+  </si>
+  <si>
+    <t>Anyang</t>
   </si>
   <si>
     <t>Busan I'Park</t>
   </si>
   <si>
-    <t>Anyang</t>
-  </si>
-  <si>
-    <t>Ansan Greeners</t>
+    <t>Slavia Praha U21</t>
   </si>
   <si>
     <t>Viktoria Žižkov</t>
   </si>
   <si>
-    <t>Slavia Praha U21</t>
+    <t>Persija</t>
   </si>
   <si>
     <t>Persita</t>
   </si>
   <si>
-    <t>Persija</t>
+    <t>Qingdao Youth Island</t>
   </si>
   <si>
     <t>Orenburg</t>
   </si>
   <si>
-    <t>Qingdao Youth Island</t>
+    <t>Gyeongnam</t>
   </si>
   <si>
     <t>Levante W</t>
   </si>
   <si>
+    <t>Sokol Saratov</t>
+  </si>
+  <si>
+    <t>Ulytau</t>
+  </si>
+  <si>
+    <t>Amarante</t>
+  </si>
+  <si>
+    <t>Polonia Warszawa</t>
+  </si>
+  <si>
+    <t>Hoang Anh Gia Lai</t>
+  </si>
+  <si>
+    <t>Sheger Ketema</t>
+  </si>
+  <si>
     <t>Sichuan Jiuniu</t>
   </si>
   <si>
-    <t>Polonia Warszawa</t>
-  </si>
-  <si>
-    <t>Amarante</t>
-  </si>
-  <si>
-    <t>Ulytau</t>
-  </si>
-  <si>
-    <t>Gyeongnam</t>
-  </si>
-  <si>
-    <t>Sokol Saratov</t>
-  </si>
-  <si>
-    <t>Hoang Anh Gia Lai</t>
-  </si>
-  <si>
-    <t>Sheger Ketema</t>
-  </si>
-  <si>
     <t>Piast Gliwice</t>
   </si>
   <si>
     <t>Hellas Verona</t>
   </si>
   <si>
+    <t>Chonburi</t>
+  </si>
+  <si>
     <t>Piteå Women</t>
   </si>
   <si>
+    <t>Ayutthaya United</t>
+  </si>
+  <si>
+    <t>Chiangrai United</t>
+  </si>
+  <si>
     <t>Celtic</t>
   </si>
   <si>
+    <t>Bangkok Glass</t>
+  </si>
+  <si>
+    <t>Shenzhen Juniors</t>
+  </si>
+  <si>
+    <t>Kanchanaburi</t>
+  </si>
+  <si>
     <t>Sukhothai</t>
   </si>
   <si>
+    <t>Ho Chi Minh City</t>
+  </si>
+  <si>
+    <t>Buriram United</t>
+  </si>
+  <si>
+    <t>Altay</t>
+  </si>
+  <si>
+    <t>Rayong</t>
+  </si>
+  <si>
     <t>Shenyang Urban</t>
   </si>
   <si>
-    <t>Kanchanaburi</t>
-  </si>
-  <si>
     <t>Hà Nội II</t>
   </si>
   <si>
-    <t>Ayutthaya United</t>
-  </si>
-  <si>
-    <t>Chonburi</t>
-  </si>
-  <si>
-    <t>Shenzhen Juniors</t>
-  </si>
-  <si>
-    <t>Altay</t>
-  </si>
-  <si>
-    <t>Buriram United</t>
-  </si>
-  <si>
-    <t>Rayong</t>
-  </si>
-  <si>
-    <t>Ho Chi Minh City</t>
-  </si>
-  <si>
-    <t>Chiangrai United</t>
-  </si>
-  <si>
-    <t>Bangkok Glass</t>
+    <t>Sūduva</t>
   </si>
   <si>
     <t>Spartak Varna</t>
   </si>
   <si>
-    <t>Sūduva</t>
+    <t>Kerala Blasters</t>
+  </si>
+  <si>
+    <t>Nantong Zhiyun</t>
+  </si>
+  <si>
+    <t>Hertha BSC</t>
   </si>
   <si>
     <t>Nõmme Kalju</t>
   </si>
   <si>
-    <t>Nantong Zhiyun</t>
+    <t>Preußen Münster</t>
+  </si>
+  <si>
+    <t>Hougang United</t>
   </si>
   <si>
     <t>Fortuna Düsseldorf</t>
   </si>
   <si>
-    <t>Kerala Blasters</t>
-  </si>
-  <si>
     <t>Havelse</t>
   </si>
   <si>
     <t>Dongguan United</t>
   </si>
   <si>
-    <t>Hertha BSC</t>
-  </si>
-  <si>
     <t>Home United</t>
   </si>
   <si>
-    <t>Hougang United</t>
-  </si>
-  <si>
     <t>KAA Gent</t>
   </si>
   <si>
-    <t>Preußen Münster</t>
-  </si>
-  <si>
     <t>Zhejiang FC</t>
   </si>
   <si>
@@ -760,102 +760,102 @@
     <t>Hrvace</t>
   </si>
   <si>
+    <t>Lugano</t>
+  </si>
+  <si>
+    <t>Vejle</t>
+  </si>
+  <si>
+    <t>Qingdao Jonoon</t>
+  </si>
+  <si>
+    <t>Bahardar</t>
+  </si>
+  <si>
+    <t>Nordsjælland</t>
+  </si>
+  <si>
+    <t>RCD Mallorca</t>
+  </si>
+  <si>
     <t>AIK</t>
   </si>
   <si>
-    <t>Nordsjælland</t>
-  </si>
-  <si>
-    <t>RCD Mallorca</t>
-  </si>
-  <si>
-    <t>Qingdao Jonoon</t>
-  </si>
-  <si>
-    <t>Bahardar</t>
+    <t>Aktobe</t>
+  </si>
+  <si>
+    <t>PSIM Yogyakarta</t>
+  </si>
+  <si>
+    <t>Zenit</t>
+  </si>
+  <si>
+    <t>FC Andorra</t>
+  </si>
+  <si>
+    <t>Kalmar</t>
   </si>
   <si>
     <t>Meshakhte</t>
   </si>
   <si>
-    <t>FC Andorra</t>
-  </si>
-  <si>
-    <t>Kalmar</t>
-  </si>
-  <si>
-    <t>Aktobe</t>
-  </si>
-  <si>
-    <t>Zenit</t>
-  </si>
-  <si>
-    <t>PSIM Yogyakarta</t>
-  </si>
-  <si>
-    <t>Lugano</t>
-  </si>
-  <si>
-    <t>Vejle</t>
-  </si>
-  <si>
     <t>Kuala Lumpur</t>
   </si>
   <si>
     <t>Công An Nhân Dân</t>
   </si>
   <si>
+    <t>Baník Ostrava U21</t>
+  </si>
+  <si>
+    <t>Tychy 71</t>
+  </si>
+  <si>
     <t>Rosenborg</t>
   </si>
   <si>
-    <t>Baník Ostrava U21</t>
-  </si>
-  <si>
-    <t>Tychy 71</t>
-  </si>
-  <si>
     <t>Wisła Płock</t>
   </si>
   <si>
+    <t>Nottingham Forest</t>
+  </si>
+  <si>
+    <t>Burnley</t>
+  </si>
+  <si>
+    <t>Astana</t>
+  </si>
+  <si>
+    <t>Fiorentina</t>
+  </si>
+  <si>
+    <t>Sigma Olomouc</t>
+  </si>
+  <si>
+    <t>Cremonese</t>
+  </si>
+  <si>
+    <t>Turan</t>
+  </si>
+  <si>
+    <t>Crystal Palace</t>
+  </si>
+  <si>
+    <t>Pardubice</t>
+  </si>
+  <si>
+    <t>Uppsala W</t>
+  </si>
+  <si>
     <t>NK Primorje</t>
   </si>
   <si>
-    <t>Sigma Olomouc</t>
-  </si>
-  <si>
-    <t>Astana</t>
+    <t>Botoşani</t>
   </si>
   <si>
     <t>Arba Minch Kenema</t>
   </si>
   <si>
-    <t>Uppsala W</t>
-  </si>
-  <si>
-    <t>Fiorentina</t>
-  </si>
-  <si>
-    <t>Nottingham Forest</t>
-  </si>
-  <si>
-    <t>Burnley</t>
-  </si>
-  <si>
-    <t>Crystal Palace</t>
-  </si>
-  <si>
-    <t>Cremonese</t>
-  </si>
-  <si>
-    <t>Botoşani</t>
-  </si>
-  <si>
-    <t>Turan</t>
-  </si>
-  <si>
-    <t>Pardubice</t>
-  </si>
-  <si>
     <t>Kelantan United</t>
   </si>
   <si>
@@ -865,37 +865,40 @@
     <t>Botev Vratsa</t>
   </si>
   <si>
+    <t>Honvéd W</t>
+  </si>
+  <si>
+    <t>Osijek</t>
+  </si>
+  <si>
+    <t>Silkeborg</t>
+  </si>
+  <si>
+    <t>NorthEast United</t>
+  </si>
+  <si>
     <t>Volos NFC</t>
   </si>
   <si>
+    <t>B36</t>
+  </si>
+  <si>
+    <t>Aris</t>
+  </si>
+  <si>
+    <t>EB - Streymur</t>
+  </si>
+  <si>
     <t>Banga</t>
   </si>
   <si>
-    <t>Honvéd W</t>
-  </si>
-  <si>
-    <t>NorthEast United</t>
+    <t>Royal Antwerp FC</t>
   </si>
   <si>
     <t>Nõmme United</t>
   </si>
   <si>
-    <t>Osijek</t>
-  </si>
-  <si>
-    <t>Silkeborg</t>
-  </si>
-  <si>
-    <t>B36</t>
-  </si>
-  <si>
-    <t>EB - Streymur</t>
-  </si>
-  <si>
-    <t>Royal Antwerp FC</t>
-  </si>
-  <si>
-    <t>Aris</t>
+    <t>Akhmat Grozny</t>
   </si>
   <si>
     <t>Leganés</t>
@@ -904,291 +907,288 @@
     <t>Athletic Club Bilbao</t>
   </si>
   <si>
-    <t>Akhmat Grozny</t>
+    <t>Sion</t>
   </si>
   <si>
     <t>Häcken</t>
   </si>
   <si>
+    <t>Viktoria Köln</t>
+  </si>
+  <si>
+    <t>Young Boys</t>
+  </si>
+  <si>
     <t>Neftekhimik</t>
   </si>
   <si>
-    <t>Young Boys</t>
-  </si>
-  <si>
-    <t>Sion</t>
-  </si>
-  <si>
-    <t>Viktoria Köln</t>
+    <t>Groningen</t>
+  </si>
+  <si>
+    <t>Go Ahead Eagles</t>
+  </si>
+  <si>
+    <t>Fortuna Sittard</t>
+  </si>
+  <si>
+    <t>Twente</t>
+  </si>
+  <si>
+    <t>Excelsior</t>
+  </si>
+  <si>
+    <t>NAC Breda</t>
+  </si>
+  <si>
+    <t>Ajax</t>
+  </si>
+  <si>
+    <t>Feyenoord</t>
   </si>
   <si>
     <t>Telstar</t>
   </si>
   <si>
-    <t>Twente</t>
-  </si>
-  <si>
-    <t>Fortuna Sittard</t>
-  </si>
-  <si>
-    <t>Feyenoord</t>
-  </si>
-  <si>
-    <t>Groningen</t>
-  </si>
-  <si>
-    <t>Ajax</t>
-  </si>
-  <si>
-    <t>Go Ahead Eagles</t>
-  </si>
-  <si>
-    <t>Excelsior</t>
-  </si>
-  <si>
-    <t>NAC Breda</t>
+    <t>Paphos</t>
   </si>
   <si>
     <t>Zbrojovka Brno</t>
   </si>
   <si>
+    <t>Szentlőrinc SE</t>
+  </si>
+  <si>
+    <t>Aresimi</t>
+  </si>
+  <si>
+    <t>Vardar</t>
+  </si>
+  <si>
+    <t>Akademija Pandev</t>
+  </si>
+  <si>
+    <t>Apollon</t>
+  </si>
+  <si>
+    <t>Shkendija</t>
+  </si>
+  <si>
+    <t>Pelister</t>
+  </si>
+  <si>
+    <t>Makedonija GjP</t>
+  </si>
+  <si>
+    <t>Croatia Zmijavci</t>
+  </si>
+  <si>
+    <t>Omonia Nicosia</t>
+  </si>
+  <si>
+    <t>Pogoń Siedlce</t>
+  </si>
+  <si>
+    <t>Budafoki MTE</t>
+  </si>
+  <si>
     <t>Sandnes Ulf</t>
   </si>
   <si>
+    <t>Karcag SE</t>
+  </si>
+  <si>
+    <t>Rapid Wien</t>
+  </si>
+  <si>
+    <t>Kecskeméti TE</t>
+  </si>
+  <si>
+    <t>Real Madrid W</t>
+  </si>
+  <si>
+    <t>Strømmen</t>
+  </si>
+  <si>
+    <t>Tromsø</t>
+  </si>
+  <si>
+    <t>Sandefjord</t>
+  </si>
+  <si>
+    <t>Saburtalo</t>
+  </si>
+  <si>
     <t>Sogndal</t>
   </si>
   <si>
-    <t>Pogoń Siedlce</t>
+    <t>Moss</t>
+  </si>
+  <si>
+    <t>KFUM</t>
+  </si>
+  <si>
+    <t>Åsane</t>
+  </si>
+  <si>
+    <t>Hartberg</t>
+  </si>
+  <si>
+    <t>LASK Linz</t>
+  </si>
+  <si>
+    <t>Mebrat Hayl</t>
+  </si>
+  <si>
+    <t>Ajka</t>
   </si>
   <si>
     <t>Raufoss</t>
   </si>
   <si>
-    <t>Åsane</t>
-  </si>
-  <si>
-    <t>Moss</t>
-  </si>
-  <si>
-    <t>Real Madrid W</t>
-  </si>
-  <si>
-    <t>Paphos</t>
-  </si>
-  <si>
-    <t>Croatia Zmijavci</t>
-  </si>
-  <si>
-    <t>Mebrat Hayl</t>
-  </si>
-  <si>
-    <t>Kecskeméti TE</t>
-  </si>
-  <si>
-    <t>Sandefjord</t>
-  </si>
-  <si>
-    <t>Tromsø</t>
-  </si>
-  <si>
-    <t>Karcag SE</t>
-  </si>
-  <si>
-    <t>Akademija Pandev</t>
-  </si>
-  <si>
-    <t>Szentlőrinc SE</t>
-  </si>
-  <si>
-    <t>Strømmen</t>
-  </si>
-  <si>
-    <t>Omonia Nicosia</t>
-  </si>
-  <si>
-    <t>Apollon</t>
-  </si>
-  <si>
-    <t>Vardar</t>
-  </si>
-  <si>
-    <t>Saburtalo</t>
-  </si>
-  <si>
-    <t>Hartberg</t>
-  </si>
-  <si>
-    <t>LASK Linz</t>
-  </si>
-  <si>
-    <t>Rapid Wien</t>
-  </si>
-  <si>
-    <t>KFUM</t>
-  </si>
-  <si>
-    <t>Makedonija GjP</t>
-  </si>
-  <si>
-    <t>Budafoki MTE</t>
-  </si>
-  <si>
-    <t>Ajka</t>
-  </si>
-  <si>
-    <t>Pelister</t>
-  </si>
-  <si>
-    <t>Shkendija</t>
-  </si>
-  <si>
-    <t>Aresimi</t>
+    <t>Al Ain</t>
+  </si>
+  <si>
+    <t>Al Bataeh</t>
+  </si>
+  <si>
+    <t>Bani Yas</t>
   </si>
   <si>
     <t>Dibba Al Fujairah</t>
   </si>
   <si>
-    <t>Al Bataeh</t>
-  </si>
-  <si>
-    <t>Al Ain</t>
-  </si>
-  <si>
-    <t>Bani Yas</t>
+    <t>West Ham United</t>
+  </si>
+  <si>
+    <t>Sekhukhune United</t>
   </si>
   <si>
     <t>Neftçi</t>
   </si>
   <si>
-    <t>West Ham United</t>
+    <t>Köln</t>
   </si>
   <si>
     <t>Nieciecza</t>
   </si>
   <si>
-    <t>Sekhukhune United</t>
-  </si>
-  <si>
-    <t>Köln</t>
+    <t>Panevėžys</t>
+  </si>
+  <si>
+    <t>Dečić</t>
+  </si>
+  <si>
+    <t>Arsenal Tivat</t>
   </si>
   <si>
     <t>Brøndby</t>
   </si>
   <si>
-    <t>Dečić</t>
+    <t>Jedinstvo</t>
   </si>
   <si>
     <t>Vysočina Jihlava</t>
   </si>
   <si>
+    <t>Mladost DG</t>
+  </si>
+  <si>
+    <t>Dinamo Bucureşti</t>
+  </si>
+  <si>
+    <t>Parma</t>
+  </si>
+  <si>
     <t>Mornar</t>
   </si>
   <si>
-    <t>Panevėžys</t>
-  </si>
-  <si>
-    <t>Arsenal Tivat</t>
-  </si>
-  <si>
-    <t>Mladost DG</t>
-  </si>
-  <si>
     <t>Ittihad Tanger</t>
   </si>
   <si>
-    <t>Parma</t>
-  </si>
-  <si>
-    <t>Dinamo Bucureşti</t>
-  </si>
-  <si>
-    <t>Jedinstvo</t>
-  </si>
-  <si>
     <t>Al Riyadh</t>
   </si>
   <si>
     <t>Dobrudzha 1919</t>
   </si>
   <si>
+    <t>07 Vestur</t>
+  </si>
+  <si>
     <t>Slaven Koprivnica</t>
   </si>
   <si>
     <t>Skála</t>
   </si>
   <si>
-    <t>07 Vestur</t>
+    <t>Córdoba</t>
+  </si>
+  <si>
+    <t>Lokomotiv Moskva</t>
+  </si>
+  <si>
+    <t>Spartak Subotica</t>
+  </si>
+  <si>
+    <t>IMT Novi Beograd</t>
+  </si>
+  <si>
+    <t>Jablonec</t>
+  </si>
+  <si>
+    <t>Antofagasta</t>
+  </si>
+  <si>
+    <t>Radnički Niš</t>
+  </si>
+  <si>
+    <t>Olympiakos Piraeus</t>
+  </si>
+  <si>
+    <t>Union Saint-Gilloise</t>
+  </si>
+  <si>
+    <t>Bačka Topola</t>
+  </si>
+  <si>
+    <t>Mirandés</t>
+  </si>
+  <si>
+    <t>Real Oviedo</t>
+  </si>
+  <si>
+    <t>AEK Athens</t>
   </si>
   <si>
     <t>Copiapó</t>
   </si>
   <si>
-    <t>IMT Novi Beograd</t>
-  </si>
-  <si>
-    <t>Real Oviedo</t>
-  </si>
-  <si>
-    <t>Córdoba</t>
-  </si>
-  <si>
     <t>Kansas City</t>
   </si>
   <si>
-    <t>Union Saint-Gilloise</t>
-  </si>
-  <si>
-    <t>AEK Athens</t>
-  </si>
-  <si>
-    <t>Radnički Niš</t>
-  </si>
-  <si>
-    <t>Mirandés</t>
-  </si>
-  <si>
-    <t>Jablonec</t>
-  </si>
-  <si>
-    <t>Bačka Topola</t>
-  </si>
-  <si>
-    <t>Olympiakos Piraeus</t>
-  </si>
-  <si>
-    <t>Antofagasta</t>
-  </si>
-  <si>
-    <t>Spartak Subotica</t>
-  </si>
-  <si>
-    <t>Lokomotiv Moskva</t>
+    <t>Ironi Tiberias</t>
+  </si>
+  <si>
+    <t>Hapoel Haifa</t>
+  </si>
+  <si>
+    <t>Tenerife W</t>
+  </si>
+  <si>
+    <t>Csákvári TK</t>
+  </si>
+  <si>
+    <t>Békéscsaba</t>
   </si>
   <si>
     <t>Hapoel Katamon</t>
   </si>
   <si>
-    <t>Tenerife W</t>
+    <t>KA</t>
   </si>
   <si>
     <t>Dinamo Batumi</t>
   </si>
   <si>
-    <t>Ironi Tiberias</t>
-  </si>
-  <si>
-    <t>Csákvári TK</t>
-  </si>
-  <si>
-    <t>KA</t>
-  </si>
-  <si>
-    <t>Hapoel Haifa</t>
-  </si>
-  <si>
-    <t>Békéscsaba</t>
-  </si>
-  <si>
     <t>KRC Genk</t>
   </si>
   <si>
@@ -1198,93 +1198,93 @@
     <t>Mainz 05</t>
   </si>
   <si>
+    <t>Al Ittihad</t>
+  </si>
+  <si>
+    <t>UTS Rabat</t>
+  </si>
+  <si>
+    <t>CODM Meknès</t>
+  </si>
+  <si>
     <t>New England II</t>
   </si>
   <si>
-    <t>UTS Rabat</t>
-  </si>
-  <si>
-    <t>CODM Meknès</t>
-  </si>
-  <si>
-    <t>Al Ittihad</t>
+    <t>Varzim</t>
   </si>
   <si>
     <t>Chacarita Juniors</t>
   </si>
   <si>
-    <t>Varzim</t>
-  </si>
-  <si>
     <t>AC Milan</t>
   </si>
   <si>
+    <t>Monaco</t>
+  </si>
+  <si>
+    <t>Le Havre</t>
+  </si>
+  <si>
+    <t>Náutico</t>
+  </si>
+  <si>
+    <t>Rennes</t>
+  </si>
+  <si>
+    <t>Toulouse</t>
+  </si>
+  <si>
     <t>Metz</t>
   </si>
   <si>
-    <t>Le Havre</t>
+    <t>Atlético Mineiro</t>
+  </si>
+  <si>
+    <t>Agropecuario</t>
+  </si>
+  <si>
+    <t>Remo</t>
+  </si>
+  <si>
+    <t>Club Atlético Güemes</t>
+  </si>
+  <si>
+    <t>PSG</t>
+  </si>
+  <si>
+    <t>Auxerre</t>
+  </si>
+  <si>
+    <t>FC Barcelona</t>
   </si>
   <si>
     <t>Angers SCO</t>
   </si>
   <si>
-    <t>Monaco</t>
-  </si>
-  <si>
-    <t>FC Barcelona</t>
-  </si>
-  <si>
-    <t>Auxerre</t>
-  </si>
-  <si>
-    <t>Remo</t>
-  </si>
-  <si>
-    <t>PSG</t>
-  </si>
-  <si>
-    <t>Toulouse</t>
-  </si>
-  <si>
     <t>Independiente Petrolero</t>
   </si>
   <si>
-    <t>Agropecuario</t>
-  </si>
-  <si>
-    <t>Náutico</t>
-  </si>
-  <si>
-    <t>Club Atlético Güemes</t>
-  </si>
-  <si>
-    <t>Atlético Mineiro</t>
-  </si>
-  <si>
-    <t>Rennes</t>
+    <t>Chaco For Ever</t>
   </si>
   <si>
     <t>San Martín San Juan</t>
   </si>
   <si>
-    <t>Chaco For Ever</t>
-  </si>
-  <si>
     <t>Godoy Cruz</t>
   </si>
   <si>
+    <t>Portland Timbers II</t>
+  </si>
+  <si>
     <t>Central Norte</t>
   </si>
   <si>
+    <t>Bay</t>
+  </si>
+  <si>
     <t>Los Angeles II</t>
   </si>
   <si>
-    <t>Bay</t>
-  </si>
-  <si>
-    <t>Portland Timbers II</t>
-  </si>
-  <si>
     <t>Hassania Agadir</t>
   </si>
   <si>
@@ -1300,36 +1300,36 @@
     <t>The Strongest</t>
   </si>
   <si>
+    <t>Mirassol</t>
+  </si>
+  <si>
+    <t>Corinthians</t>
+  </si>
+  <si>
     <t>Santos</t>
   </si>
   <si>
-    <t>Mirassol</t>
-  </si>
-  <si>
-    <t>Corinthians</t>
-  </si>
-  <si>
     <t>Avaí</t>
   </si>
   <si>
     <t>FC Cincinnati II</t>
   </si>
   <si>
+    <t>Novorizontino</t>
+  </si>
+  <si>
     <t>Grêmio</t>
   </si>
   <si>
-    <t>Novorizontino</t>
-  </si>
-  <si>
     <t>Atlanta United II</t>
   </si>
   <si>
+    <t>Seattle Reign</t>
+  </si>
+  <si>
     <t>Minnesota United</t>
   </si>
   <si>
-    <t>Seattle Reign</t>
-  </si>
-  <si>
     <t>Manta FC</t>
   </si>
   <si>
@@ -1348,177 +1348,177 @@
     <t>Los Angeles FC</t>
   </si>
   <si>
+    <t>Bucheon 1995</t>
+  </si>
+  <si>
+    <t>Sydney II</t>
+  </si>
+  <si>
+    <t>St. George Saints</t>
+  </si>
+  <si>
     <t>Jeonnam Dragons</t>
   </si>
   <si>
-    <t>Bucheon 1995</t>
-  </si>
-  <si>
-    <t>St. George Saints</t>
-  </si>
-  <si>
-    <t>Sydney II</t>
-  </si>
-  <si>
     <t>Sydney United</t>
   </si>
   <si>
     <t>Guangzhou E-Power</t>
   </si>
   <si>
+    <t>Shanghai Jiading</t>
+  </si>
+  <si>
     <t>Guangxi Hengchen</t>
   </si>
   <si>
     <t>Rotor Volgograd</t>
   </si>
   <si>
-    <t>Shanghai Jiading</t>
+    <t>Yongin City</t>
+  </si>
+  <si>
+    <t>Jeonbuk Motors</t>
   </si>
   <si>
     <t>Cheonan City</t>
   </si>
   <si>
-    <t>Jeonbuk Motors</t>
-  </si>
-  <si>
-    <t>Yongin City</t>
+    <t>Táborsko</t>
   </si>
   <si>
     <t>Sparta Praha II</t>
   </si>
   <si>
-    <t>Táborsko</t>
+    <t>Persib</t>
   </si>
   <si>
     <t>Persijap</t>
   </si>
   <si>
-    <t>Persib</t>
+    <t>Wuhan Three Towns</t>
   </si>
   <si>
     <t>Krylya Sovetov</t>
   </si>
   <si>
-    <t>Wuhan Three Towns</t>
+    <t>Gimhae City</t>
   </si>
   <si>
     <t>Logroño W</t>
   </si>
   <si>
+    <t>Spartak Kostroma</t>
+  </si>
+  <si>
+    <t>Kairat</t>
+  </si>
+  <si>
+    <t>União Santarém</t>
+  </si>
+  <si>
+    <t>Górnik Łęczna</t>
+  </si>
+  <si>
+    <t>Pho Hien</t>
+  </si>
+  <si>
+    <t>Sidama Bunna</t>
+  </si>
+  <si>
     <t>Shandong Luneng</t>
   </si>
   <si>
-    <t>Górnik Łęczna</t>
-  </si>
-  <si>
-    <t>União Santarém</t>
-  </si>
-  <si>
-    <t>Kairat</t>
-  </si>
-  <si>
-    <t>Gimhae City</t>
-  </si>
-  <si>
-    <t>Spartak Kostroma</t>
-  </si>
-  <si>
-    <t>Pho Hien</t>
-  </si>
-  <si>
-    <t>Sidama Bunna</t>
-  </si>
-  <si>
     <t>GKS Katowice</t>
   </si>
   <si>
     <t>Como</t>
   </si>
   <si>
+    <t>Nakhon Ratchasima</t>
+  </si>
+  <si>
     <t>Rosengard Women</t>
   </si>
   <si>
+    <t>Port FC</t>
+  </si>
+  <si>
+    <t>Uthai Thani</t>
+  </si>
+  <si>
     <t>Rangers</t>
   </si>
   <si>
+    <t>Prachuap</t>
+  </si>
+  <si>
+    <t>Hebei Kungfu</t>
+  </si>
+  <si>
+    <t>Ratchaburi</t>
+  </si>
+  <si>
     <t>Muang Thong United</t>
   </si>
   <si>
+    <t>Song Lam Nghe An</t>
+  </si>
+  <si>
+    <t>Lamphun Warrior</t>
+  </si>
+  <si>
+    <t>Ordabasy</t>
+  </si>
+  <si>
+    <t>Bangkok United</t>
+  </si>
+  <si>
     <t>Yunnan Yukun</t>
   </si>
   <si>
-    <t>Ratchaburi</t>
-  </si>
-  <si>
     <t>Viettel</t>
   </si>
   <si>
-    <t>Port FC</t>
-  </si>
-  <si>
-    <t>Nakhon Ratchasima</t>
-  </si>
-  <si>
-    <t>Hebei Kungfu</t>
-  </si>
-  <si>
-    <t>Ordabasy</t>
-  </si>
-  <si>
-    <t>Lamphun Warrior</t>
-  </si>
-  <si>
-    <t>Bangkok United</t>
-  </si>
-  <si>
-    <t>Song Lam Nghe An</t>
-  </si>
-  <si>
-    <t>Uthai Thani</t>
-  </si>
-  <si>
-    <t>Prachuap</t>
+    <t>Žalgiris</t>
   </si>
   <si>
     <t>Slavia Sofia</t>
   </si>
   <si>
-    <t>Žalgiris</t>
+    <t>Mohammedan</t>
+  </si>
+  <si>
+    <t>Wuxi Wugou</t>
+  </si>
+  <si>
+    <t>Greuther Fürth</t>
   </si>
   <si>
     <t>Tallinna FC Flora</t>
   </si>
   <si>
-    <t>Wuxi Wugou</t>
+    <t>Darmstadt 98</t>
+  </si>
+  <si>
+    <t>Tampines Rovers</t>
   </si>
   <si>
     <t>Elversberg</t>
   </si>
   <si>
-    <t>Mohammedan</t>
-  </si>
-  <si>
     <t>Schweinfurt</t>
   </si>
   <si>
     <t>Suzhou Dongwu</t>
   </si>
   <si>
-    <t>Greuther Fürth</t>
-  </si>
-  <si>
     <t>Albirex Niigata S</t>
   </si>
   <si>
-    <t>Tampines Rovers</t>
-  </si>
-  <si>
     <t>RSC Anderlecht</t>
   </si>
   <si>
-    <t>Darmstadt 98</t>
-  </si>
-  <si>
     <t>Tianjin Teda</t>
   </si>
   <si>
@@ -1528,102 +1528,102 @@
     <t>Opatija</t>
   </si>
   <si>
+    <t>St. Gallen</t>
+  </si>
+  <si>
+    <t>Fredericia</t>
+  </si>
+  <si>
+    <t>Dalian Zhixing</t>
+  </si>
+  <si>
+    <t>Welwalo Adigrat Uni</t>
+  </si>
+  <si>
+    <t>Midtjylland</t>
+  </si>
+  <si>
+    <t>Villarreal</t>
+  </si>
+  <si>
     <t>Djurgården</t>
   </si>
   <si>
-    <t>Midtjylland</t>
-  </si>
-  <si>
-    <t>Villarreal</t>
-  </si>
-  <si>
-    <t>Dalian Zhixing</t>
-  </si>
-  <si>
-    <t>Welwalo Adigrat Uni</t>
+    <t>Kaisar</t>
+  </si>
+  <si>
+    <t>Malut United</t>
+  </si>
+  <si>
+    <t>FK Sochi</t>
+  </si>
+  <si>
+    <t>UD Las Palmas</t>
+  </si>
+  <si>
+    <t>Halmstad</t>
   </si>
   <si>
     <t>Dila</t>
   </si>
   <si>
-    <t>UD Las Palmas</t>
-  </si>
-  <si>
-    <t>Halmstad</t>
-  </si>
-  <si>
-    <t>Kaisar</t>
-  </si>
-  <si>
-    <t>FK Sochi</t>
-  </si>
-  <si>
-    <t>Malut United</t>
-  </si>
-  <si>
-    <t>St. Gallen</t>
-  </si>
-  <si>
-    <t>Fredericia</t>
-  </si>
-  <si>
     <t>Negeri Sembilan</t>
   </si>
   <si>
     <t>Nam Dinh</t>
   </si>
   <si>
+    <t>Ústí nad Labem</t>
+  </si>
+  <si>
+    <t>Ruch Chorzów</t>
+  </si>
+  <si>
     <t>Lillestrøm</t>
   </si>
   <si>
-    <t>Ústí nad Labem</t>
-  </si>
-  <si>
-    <t>Ruch Chorzów</t>
-  </si>
-  <si>
     <t>Motor Lublin</t>
   </si>
   <si>
+    <t>Newcastle United</t>
+  </si>
+  <si>
+    <t>Aston Villa</t>
+  </si>
+  <si>
+    <t>Kyzyl-Zhar</t>
+  </si>
+  <si>
+    <t>Genoa</t>
+  </si>
+  <si>
+    <t>Bohemians 1905</t>
+  </si>
+  <si>
+    <t>Pisa</t>
+  </si>
+  <si>
+    <t>Karvan FK</t>
+  </si>
+  <si>
+    <t>Everton</t>
+  </si>
+  <si>
+    <t>Karviná</t>
+  </si>
+  <si>
+    <t>Vittsjö</t>
+  </si>
+  <si>
     <t>Mura</t>
   </si>
   <si>
-    <t>Bohemians 1905</t>
-  </si>
-  <si>
-    <t>Kyzyl-Zhar</t>
+    <t>Petrolul 52</t>
   </si>
   <si>
     <t>Welayta Dicha</t>
   </si>
   <si>
-    <t>Vittsjö</t>
-  </si>
-  <si>
-    <t>Genoa</t>
-  </si>
-  <si>
-    <t>Newcastle United</t>
-  </si>
-  <si>
-    <t>Aston Villa</t>
-  </si>
-  <si>
-    <t>Everton</t>
-  </si>
-  <si>
-    <t>Pisa</t>
-  </si>
-  <si>
-    <t>Petrolul 52</t>
-  </si>
-  <si>
-    <t>Karvan FK</t>
-  </si>
-  <si>
-    <t>Karviná</t>
-  </si>
-  <si>
     <t>Johor Darul Ta'zim</t>
   </si>
   <si>
@@ -1633,37 +1633,40 @@
     <t>Septemvri Sofia</t>
   </si>
   <si>
+    <t>Vasas</t>
+  </si>
+  <si>
+    <t>Istra 1961</t>
+  </si>
+  <si>
+    <t>København</t>
+  </si>
+  <si>
+    <t>Chennaiyin</t>
+  </si>
+  <si>
     <t>Levadiakos</t>
   </si>
   <si>
+    <t>KÍ</t>
+  </si>
+  <si>
+    <t>OFI</t>
+  </si>
+  <si>
+    <t>Víkingur</t>
+  </si>
+  <si>
     <t>TransINVEST Vilnius</t>
   </si>
   <si>
-    <t>Vasas</t>
-  </si>
-  <si>
-    <t>Chennaiyin</t>
+    <t>Sporting Charleroi</t>
   </si>
   <si>
     <t>Paide</t>
   </si>
   <si>
-    <t>Istra 1961</t>
-  </si>
-  <si>
-    <t>København</t>
-  </si>
-  <si>
-    <t>KÍ</t>
-  </si>
-  <si>
-    <t>Víkingur</t>
-  </si>
-  <si>
-    <t>Sporting Charleroi</t>
-  </si>
-  <si>
-    <t>OFI</t>
+    <t>Makhachkala</t>
   </si>
   <si>
     <t>Racing Santander</t>
@@ -1672,288 +1675,285 @@
     <t>Valencia CF</t>
   </si>
   <si>
-    <t>Makhachkala</t>
+    <t>Thun</t>
   </si>
   <si>
     <t>Malmö FF</t>
   </si>
   <si>
+    <t>Alemannia Aachen</t>
+  </si>
+  <si>
+    <t>Basel</t>
+  </si>
+  <si>
     <t>Volga Ulyanovsk</t>
   </si>
   <si>
-    <t>Basel</t>
-  </si>
-  <si>
-    <t>Thun</t>
-  </si>
-  <si>
-    <t>Alemannia Aachen</t>
+    <t>NEC</t>
+  </si>
+  <si>
+    <t>PSV</t>
+  </si>
+  <si>
+    <t>PEC Zwolle</t>
+  </si>
+  <si>
+    <t>Sparta Rotterdam</t>
+  </si>
+  <si>
+    <t>Volendam</t>
+  </si>
+  <si>
+    <t>Heerenveen</t>
+  </si>
+  <si>
+    <t>Utrecht</t>
+  </si>
+  <si>
+    <t>AZ</t>
   </si>
   <si>
     <t>Heracles</t>
   </si>
   <si>
-    <t>Sparta Rotterdam</t>
-  </si>
-  <si>
-    <t>PEC Zwolle</t>
-  </si>
-  <si>
-    <t>AZ</t>
-  </si>
-  <si>
-    <t>NEC</t>
-  </si>
-  <si>
-    <t>Utrecht</t>
-  </si>
-  <si>
-    <t>PSV</t>
-  </si>
-  <si>
-    <t>Volendam</t>
-  </si>
-  <si>
-    <t>Heerenveen</t>
-  </si>
-  <si>
     <t>Vlašim</t>
   </si>
   <si>
+    <t>Videoton</t>
+  </si>
+  <si>
+    <t>FK Bashkimi Kumanovo</t>
+  </si>
+  <si>
+    <t>Sileks</t>
+  </si>
+  <si>
+    <t>Rabotnički</t>
+  </si>
+  <si>
+    <t>APOEL</t>
+  </si>
+  <si>
+    <t>Struga</t>
+  </si>
+  <si>
+    <t>Shkupi</t>
+  </si>
+  <si>
+    <t>Tikveš</t>
+  </si>
+  <si>
+    <t>Jarun</t>
+  </si>
+  <si>
+    <t>AEK Larnaca</t>
+  </si>
+  <si>
+    <t>Stal Rzeszów</t>
+  </si>
+  <si>
+    <t>BVSC</t>
+  </si>
+  <si>
     <t>Stabæk</t>
   </si>
   <si>
+    <t>Tiszakécske</t>
+  </si>
+  <si>
+    <t>Austria Wien</t>
+  </si>
+  <si>
+    <t>Mezőkövesd-Zsóry</t>
+  </si>
+  <si>
+    <t>Atletico Madrid W</t>
+  </si>
+  <si>
+    <t>Hødd</t>
+  </si>
+  <si>
+    <t>Molde</t>
+  </si>
+  <si>
+    <t>Kristiansund</t>
+  </si>
+  <si>
+    <t>Torpedo Kutaisi</t>
+  </si>
+  <si>
     <t>Haugesund</t>
   </si>
   <si>
-    <t>Stal Rzeszów</t>
+    <t>Bryne</t>
+  </si>
+  <si>
+    <t>Viking</t>
+  </si>
+  <si>
+    <t>Strømsgodset</t>
+  </si>
+  <si>
+    <t>Sturm Graz</t>
+  </si>
+  <si>
+    <t>Salzburg</t>
+  </si>
+  <si>
+    <t>Fasil Ketema</t>
+  </si>
+  <si>
+    <t>Szeged 2011</t>
   </si>
   <si>
     <t>Lyn</t>
   </si>
   <si>
-    <t>Strømsgodset</t>
-  </si>
-  <si>
-    <t>Bryne</t>
-  </si>
-  <si>
-    <t>Atletico Madrid W</t>
-  </si>
-  <si>
-    <t>Jarun</t>
-  </si>
-  <si>
-    <t>Fasil Ketema</t>
-  </si>
-  <si>
-    <t>Mezőkövesd-Zsóry</t>
-  </si>
-  <si>
-    <t>Kristiansund</t>
-  </si>
-  <si>
-    <t>Molde</t>
-  </si>
-  <si>
-    <t>Tiszakécske</t>
-  </si>
-  <si>
-    <t>Rabotnički</t>
-  </si>
-  <si>
-    <t>Videoton</t>
-  </si>
-  <si>
-    <t>Hødd</t>
-  </si>
-  <si>
-    <t>AEK Larnaca</t>
-  </si>
-  <si>
-    <t>APOEL</t>
-  </si>
-  <si>
-    <t>Sileks</t>
-  </si>
-  <si>
-    <t>Torpedo Kutaisi</t>
-  </si>
-  <si>
-    <t>Sturm Graz</t>
-  </si>
-  <si>
-    <t>Salzburg</t>
-  </si>
-  <si>
-    <t>Austria Wien</t>
-  </si>
-  <si>
-    <t>Viking</t>
-  </si>
-  <si>
-    <t>Tikveš</t>
-  </si>
-  <si>
-    <t>BVSC</t>
-  </si>
-  <si>
-    <t>Szeged 2011</t>
-  </si>
-  <si>
-    <t>Shkupi</t>
-  </si>
-  <si>
-    <t>Struga</t>
-  </si>
-  <si>
-    <t>FK Bashkimi Kumanovo</t>
+    <t>Al Dhafra</t>
+  </si>
+  <si>
+    <t>Al Sharjah</t>
+  </si>
+  <si>
+    <t>Shabab Al Ahli Dubai</t>
   </si>
   <si>
     <t>Ajman</t>
   </si>
   <si>
-    <t>Al Sharjah</t>
-  </si>
-  <si>
-    <t>Al Dhafra</t>
-  </si>
-  <si>
-    <t>Shabab Al Ahli Dubai</t>
+    <t>Arsenal</t>
+  </si>
+  <si>
+    <t>Kaizer Chiefs</t>
   </si>
   <si>
     <t>İnter Bakı</t>
   </si>
   <si>
-    <t>Arsenal</t>
+    <t>Heidenheim</t>
   </si>
   <si>
     <t>Legia Warszawa</t>
   </si>
   <si>
-    <t>Kaizer Chiefs</t>
-  </si>
-  <si>
-    <t>Heidenheim</t>
+    <t>Kauno Žalgiris</t>
+  </si>
+  <si>
+    <t>FK Jezero Plav</t>
+  </si>
+  <si>
+    <t>Sutjeska</t>
   </si>
   <si>
     <t>AGF</t>
   </si>
   <si>
-    <t>FK Jezero Plav</t>
+    <t>Budućnost</t>
   </si>
   <si>
     <t>Hanácká</t>
   </si>
   <si>
+    <t>Petrovac</t>
+  </si>
+  <si>
+    <t>Argeș</t>
+  </si>
+  <si>
+    <t>Roma</t>
+  </si>
+  <si>
     <t>Bokelj</t>
   </si>
   <si>
-    <t>Kauno Žalgiris</t>
-  </si>
-  <si>
-    <t>Sutjeska</t>
-  </si>
-  <si>
-    <t>Petrovac</t>
-  </si>
-  <si>
     <t>Difaâ El Jadida</t>
   </si>
   <si>
-    <t>Roma</t>
-  </si>
-  <si>
-    <t>Argeș</t>
-  </si>
-  <si>
-    <t>Budućnost</t>
-  </si>
-  <si>
     <t>Al Fateh</t>
   </si>
   <si>
     <t>Beroe</t>
   </si>
   <si>
+    <t>B68</t>
+  </si>
+  <si>
     <t>Gorica</t>
   </si>
   <si>
     <t>AB</t>
   </si>
   <si>
-    <t>B68</t>
+    <t>Granada CF</t>
+  </si>
+  <si>
+    <t>Baltika</t>
+  </si>
+  <si>
+    <t>Napredak</t>
+  </si>
+  <si>
+    <t>Radnički Kragujevac</t>
+  </si>
+  <si>
+    <t>Hradec Králové</t>
+  </si>
+  <si>
+    <t>San Luis</t>
+  </si>
+  <si>
+    <t>LFK Mladost Lučani</t>
+  </si>
+  <si>
+    <t>PAOK</t>
+  </si>
+  <si>
+    <t>KV Mechelen</t>
+  </si>
+  <si>
+    <t>Javor Ivanjica</t>
+  </si>
+  <si>
+    <t>SD Eibar</t>
+  </si>
+  <si>
+    <t>Getafe CF</t>
+  </si>
+  <si>
+    <t>Panathinaikos</t>
   </si>
   <si>
     <t>Unión San Felipe</t>
   </si>
   <si>
-    <t>Radnički Kragujevac</t>
-  </si>
-  <si>
-    <t>Getafe CF</t>
-  </si>
-  <si>
-    <t>Granada CF</t>
-  </si>
-  <si>
     <t>Chicago Red Stars</t>
   </si>
   <si>
-    <t>KV Mechelen</t>
-  </si>
-  <si>
-    <t>Panathinaikos</t>
-  </si>
-  <si>
-    <t>LFK Mladost Lučani</t>
-  </si>
-  <si>
-    <t>SD Eibar</t>
-  </si>
-  <si>
-    <t>Hradec Králové</t>
-  </si>
-  <si>
-    <t>Javor Ivanjica</t>
-  </si>
-  <si>
-    <t>PAOK</t>
-  </si>
-  <si>
-    <t>San Luis</t>
-  </si>
-  <si>
-    <t>Napredak</t>
-  </si>
-  <si>
-    <t>Baltika</t>
+    <t>Maccabi Netanya</t>
+  </si>
+  <si>
+    <t>Ashdod</t>
+  </si>
+  <si>
+    <t>Barcelona W</t>
+  </si>
+  <si>
+    <t>Soroksár SC</t>
+  </si>
+  <si>
+    <t>Kozármisleny</t>
   </si>
   <si>
     <t>Bnei Sakhnin</t>
   </si>
   <si>
-    <t>Barcelona W</t>
+    <t>ÍBV</t>
   </si>
   <si>
     <t>Samgurali</t>
   </si>
   <si>
-    <t>Maccabi Netanya</t>
-  </si>
-  <si>
-    <t>Soroksár SC</t>
-  </si>
-  <si>
-    <t>ÍBV</t>
-  </si>
-  <si>
-    <t>Ashdod</t>
-  </si>
-  <si>
-    <t>Kozármisleny</t>
-  </si>
-  <si>
     <t>KVC Westerlo</t>
   </si>
   <si>
@@ -1963,93 +1963,93 @@
     <t>Union Berlin</t>
   </si>
   <si>
+    <t>Dhamk</t>
+  </si>
+  <si>
+    <t>Maghreb Fès</t>
+  </si>
+  <si>
+    <t>RSB Berkane</t>
+  </si>
+  <si>
     <t>New York City II</t>
   </si>
   <si>
-    <t>Maghreb Fès</t>
-  </si>
-  <si>
-    <t>RSB Berkane</t>
-  </si>
-  <si>
-    <t>Dhamk</t>
+    <t>CF Os Belenenses</t>
   </si>
   <si>
     <t>Colegiales</t>
   </si>
   <si>
-    <t>CF Os Belenenses</t>
-  </si>
-  <si>
     <t>Atalanta</t>
   </si>
   <si>
+    <t>Lille</t>
+  </si>
+  <si>
+    <t>Olympique Marseille</t>
+  </si>
+  <si>
+    <t>América Mineiro</t>
+  </si>
+  <si>
+    <t>Paris</t>
+  </si>
+  <si>
+    <t>Olympique Lyonnais</t>
+  </si>
+  <si>
     <t>Lorient</t>
   </si>
   <si>
-    <t>Olympique Marseille</t>
+    <t>Botafogo</t>
+  </si>
+  <si>
+    <t>Atlanta</t>
+  </si>
+  <si>
+    <t>Palmeiras</t>
+  </si>
+  <si>
+    <t>Quilmes</t>
+  </si>
+  <si>
+    <t>Brest</t>
+  </si>
+  <si>
+    <t>Nice</t>
+  </si>
+  <si>
+    <t>Real Madrid</t>
   </si>
   <si>
     <t>Strasbourg</t>
   </si>
   <si>
-    <t>Lille</t>
-  </si>
-  <si>
-    <t>Real Madrid</t>
-  </si>
-  <si>
-    <t>Nice</t>
-  </si>
-  <si>
-    <t>Palmeiras</t>
-  </si>
-  <si>
-    <t>Brest</t>
-  </si>
-  <si>
-    <t>Olympique Lyonnais</t>
-  </si>
-  <si>
     <t>Club Always Ready</t>
   </si>
   <si>
-    <t>Atlanta</t>
-  </si>
-  <si>
-    <t>América Mineiro</t>
-  </si>
-  <si>
-    <t>Quilmes</t>
-  </si>
-  <si>
-    <t>Botafogo</t>
-  </si>
-  <si>
-    <t>Paris</t>
+    <t>Ciudad de Bolívar</t>
   </si>
   <si>
     <t>Patronato</t>
   </si>
   <si>
-    <t>Ciudad de Bolívar</t>
-  </si>
-  <si>
     <t>Racing Córdoba</t>
   </si>
   <si>
+    <t>LA Galaxy II</t>
+  </si>
+  <si>
     <t>Deportivo Madryn</t>
   </si>
   <si>
+    <t>Utah Royals</t>
+  </si>
+  <si>
     <t>Real Monarchs</t>
   </si>
   <si>
-    <t>Utah Royals</t>
-  </si>
-  <si>
-    <t>LA Galaxy II</t>
-  </si>
-  <si>
     <t>FAR Rabat</t>
   </si>
   <si>
@@ -2065,34 +2065,34 @@
     <t>Real Potosí</t>
   </si>
   <si>
+    <t>Chapecoense</t>
+  </si>
+  <si>
+    <t>São Paulo</t>
+  </si>
+  <si>
     <t>Bragantino</t>
   </si>
   <si>
-    <t>Chapecoense</t>
-  </si>
-  <si>
-    <t>São Paulo</t>
-  </si>
-  <si>
     <t>Fortaleza</t>
   </si>
   <si>
     <t>Columbus Crew II</t>
   </si>
   <si>
+    <t>Botafogo SP</t>
+  </si>
+  <si>
     <t>Flamengo</t>
   </si>
   <si>
-    <t>Botafogo SP</t>
-  </si>
-  <si>
     <t>Orlando City II</t>
   </si>
   <si>
+    <t>Washington Spirit</t>
+  </si>
+  <si>
     <t>Austin</t>
-  </si>
-  <si>
-    <t>Washington Spirit</t>
   </si>
   <si>
     <t>Macará</t>
@@ -3043,7 +3043,7 @@
         <v>61</v>
       </c>
       <c r="C4" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D4" t="s">
         <v>185</v>
@@ -3267,13 +3267,13 @@
         <v>699</v>
       </c>
       <c r="P5">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="Q5">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R5">
-        <v>0</v>
+        <v>3.61</v>
       </c>
       <c r="S5">
         <v>0</v>
@@ -3413,7 +3413,7 @@
         <v>62</v>
       </c>
       <c r="C6" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D6" t="s">
         <v>185</v>
@@ -3968,10 +3968,10 @@
         <v>63</v>
       </c>
       <c r="C9" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D9" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E9" t="s">
         <v>195</v>
@@ -4153,10 +4153,10 @@
         <v>63</v>
       </c>
       <c r="C10" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="D10" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E10" t="s">
         <v>196</v>
@@ -4338,7 +4338,7 @@
         <v>64</v>
       </c>
       <c r="C11" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="D11" t="s">
         <v>185</v>
@@ -4377,13 +4377,13 @@
         <v>699</v>
       </c>
       <c r="P11">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="Q11">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="R11">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="S11">
         <v>0</v>
@@ -4523,7 +4523,7 @@
         <v>64</v>
       </c>
       <c r="C12" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D12" t="s">
         <v>185</v>
@@ -4708,7 +4708,7 @@
         <v>64</v>
       </c>
       <c r="C13" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="D13" t="s">
         <v>185</v>
@@ -4747,13 +4747,13 @@
         <v>699</v>
       </c>
       <c r="P13">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="Q13">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="R13">
-        <v>0</v>
+        <v>4.67</v>
       </c>
       <c r="S13">
         <v>0</v>
@@ -4792,10 +4792,10 @@
         <v>0</v>
       </c>
       <c r="AE13">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AF13">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AG13">
         <v>0</v>
@@ -5636,7 +5636,7 @@
         <v>122</v>
       </c>
       <c r="D18" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E18" t="s">
         <v>204</v>
@@ -5672,13 +5672,13 @@
         <v>699</v>
       </c>
       <c r="P18">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="Q18">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="R18">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="S18">
         <v>0</v>
@@ -5821,7 +5821,7 @@
         <v>123</v>
       </c>
       <c r="D19" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E19" t="s">
         <v>205</v>
@@ -5857,13 +5857,13 @@
         <v>699</v>
       </c>
       <c r="P19">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="Q19">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="R19">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="S19">
         <v>0</v>
@@ -6003,10 +6003,10 @@
         <v>68</v>
       </c>
       <c r="C20" t="s">
-        <v>124</v>
+        <v>117</v>
       </c>
       <c r="D20" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E20" t="s">
         <v>206</v>
@@ -6042,13 +6042,13 @@
         <v>699</v>
       </c>
       <c r="P20">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Q20">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="R20">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="S20">
         <v>0</v>
@@ -6188,10 +6188,10 @@
         <v>68</v>
       </c>
       <c r="C21" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="D21" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E21" t="s">
         <v>207</v>
@@ -6373,7 +6373,7 @@
         <v>68</v>
       </c>
       <c r="C22" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
       <c r="D22" t="s">
         <v>186</v>
@@ -6412,13 +6412,13 @@
         <v>699</v>
       </c>
       <c r="P22">
-        <v>0</v>
+        <v>4.98</v>
       </c>
       <c r="Q22">
-        <v>0</v>
+        <v>3.66</v>
       </c>
       <c r="R22">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="S22">
         <v>0</v>
@@ -6558,10 +6558,10 @@
         <v>68</v>
       </c>
       <c r="C23" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="D23" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E23" t="s">
         <v>209</v>
@@ -6743,10 +6743,10 @@
         <v>68</v>
       </c>
       <c r="C24" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="D24" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E24" t="s">
         <v>210</v>
@@ -6928,10 +6928,10 @@
         <v>68</v>
       </c>
       <c r="C25" t="s">
-        <v>115</v>
+        <v>127</v>
       </c>
       <c r="D25" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E25" t="s">
         <v>211</v>
@@ -7113,7 +7113,7 @@
         <v>68</v>
       </c>
       <c r="C26" t="s">
-        <v>119</v>
+        <v>128</v>
       </c>
       <c r="D26" t="s">
         <v>186</v>
@@ -7298,7 +7298,7 @@
         <v>68</v>
       </c>
       <c r="C27" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="D27" t="s">
         <v>186</v>
@@ -7483,10 +7483,10 @@
         <v>68</v>
       </c>
       <c r="C28" t="s">
-        <v>129</v>
+        <v>122</v>
       </c>
       <c r="D28" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E28" t="s">
         <v>214</v>
@@ -7707,13 +7707,13 @@
         <v>699</v>
       </c>
       <c r="P29">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="Q29">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="R29">
-        <v>0</v>
+        <v>3.21</v>
       </c>
       <c r="S29">
         <v>0</v>
@@ -8041,7 +8041,7 @@
         <v>132</v>
       </c>
       <c r="D31" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E31" t="s">
         <v>217</v>
@@ -8226,7 +8226,7 @@
         <v>133</v>
       </c>
       <c r="D32" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E32" t="s">
         <v>218</v>
@@ -8262,13 +8262,13 @@
         <v>699</v>
       </c>
       <c r="P32">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Q32">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="R32">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="S32">
         <v>0</v>
@@ -8408,7 +8408,7 @@
         <v>71</v>
       </c>
       <c r="C33" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="D33" t="s">
         <v>186</v>
@@ -8593,10 +8593,10 @@
         <v>71</v>
       </c>
       <c r="C34" t="s">
-        <v>123</v>
+        <v>132</v>
       </c>
       <c r="D34" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E34" t="s">
         <v>220</v>
@@ -8817,13 +8817,13 @@
         <v>699</v>
       </c>
       <c r="P35">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Q35">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="R35">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="S35">
         <v>0</v>
@@ -8963,7 +8963,7 @@
         <v>71</v>
       </c>
       <c r="C36" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="D36" t="s">
         <v>186</v>
@@ -9148,10 +9148,10 @@
         <v>71</v>
       </c>
       <c r="C37" t="s">
-        <v>134</v>
+        <v>118</v>
       </c>
       <c r="D37" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E37" t="s">
         <v>223</v>
@@ -9333,7 +9333,7 @@
         <v>71</v>
       </c>
       <c r="C38" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="D38" t="s">
         <v>186</v>
@@ -9518,10 +9518,10 @@
         <v>71</v>
       </c>
       <c r="C39" t="s">
-        <v>118</v>
+        <v>132</v>
       </c>
       <c r="D39" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E39" t="s">
         <v>225</v>
@@ -9703,10 +9703,10 @@
         <v>71</v>
       </c>
       <c r="C40" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="D40" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E40" t="s">
         <v>226</v>
@@ -9888,7 +9888,7 @@
         <v>71</v>
       </c>
       <c r="C41" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="D41" t="s">
         <v>186</v>
@@ -10073,10 +10073,10 @@
         <v>71</v>
       </c>
       <c r="C42" t="s">
-        <v>134</v>
+        <v>125</v>
       </c>
       <c r="D42" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E42" t="s">
         <v>228</v>
@@ -10258,7 +10258,7 @@
         <v>71</v>
       </c>
       <c r="C43" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="D43" t="s">
         <v>186</v>
@@ -10443,10 +10443,10 @@
         <v>71</v>
       </c>
       <c r="C44" t="s">
-        <v>134</v>
+        <v>122</v>
       </c>
       <c r="D44" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E44" t="s">
         <v>230</v>
@@ -10628,7 +10628,7 @@
         <v>71</v>
       </c>
       <c r="C45" t="s">
-        <v>134</v>
+        <v>128</v>
       </c>
       <c r="D45" t="s">
         <v>186</v>
@@ -10816,7 +10816,7 @@
         <v>135</v>
       </c>
       <c r="D46" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E46" t="s">
         <v>232</v>
@@ -11001,7 +11001,7 @@
         <v>136</v>
       </c>
       <c r="D47" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E47" t="s">
         <v>233</v>
@@ -11037,13 +11037,13 @@
         <v>699</v>
       </c>
       <c r="P47">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="Q47">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R47">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="S47">
         <v>0</v>
@@ -11186,7 +11186,7 @@
         <v>137</v>
       </c>
       <c r="D48" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E48" t="s">
         <v>234</v>
@@ -11222,13 +11222,13 @@
         <v>699</v>
       </c>
       <c r="P48">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="Q48">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="R48">
-        <v>0</v>
+        <v>7.37</v>
       </c>
       <c r="S48">
         <v>0</v>
@@ -11592,13 +11592,13 @@
         <v>699</v>
       </c>
       <c r="P50">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="Q50">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="R50">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="S50">
         <v>0</v>
@@ -11643,10 +11643,10 @@
         <v>0</v>
       </c>
       <c r="AG50">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AH50">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AI50">
         <v>0</v>
@@ -11741,7 +11741,7 @@
         <v>139</v>
       </c>
       <c r="D51" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E51" t="s">
         <v>237</v>
@@ -11923,7 +11923,7 @@
         <v>73</v>
       </c>
       <c r="C52" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="D52" t="s">
         <v>186</v>
@@ -11962,13 +11962,13 @@
         <v>699</v>
       </c>
       <c r="P52">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="Q52">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="R52">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="S52">
         <v>0</v>
@@ -12108,10 +12108,10 @@
         <v>73</v>
       </c>
       <c r="C53" t="s">
-        <v>118</v>
+        <v>140</v>
       </c>
       <c r="D53" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="E53" t="s">
         <v>239</v>
@@ -12332,13 +12332,13 @@
         <v>699</v>
       </c>
       <c r="P54">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="Q54">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="R54">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="S54">
         <v>0</v>
@@ -12481,7 +12481,7 @@
         <v>141</v>
       </c>
       <c r="D55" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="E55" t="s">
         <v>241</v>
@@ -12663,10 +12663,10 @@
         <v>73</v>
       </c>
       <c r="C56" t="s">
-        <v>141</v>
+        <v>118</v>
       </c>
       <c r="D56" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="E56" t="s">
         <v>242</v>
@@ -12848,10 +12848,10 @@
         <v>73</v>
       </c>
       <c r="C57" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="D57" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="E57" t="s">
         <v>243</v>
@@ -13033,7 +13033,7 @@
         <v>73</v>
       </c>
       <c r="C58" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="D58" t="s">
         <v>186</v>
@@ -13072,13 +13072,13 @@
         <v>699</v>
       </c>
       <c r="P58">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="Q58">
-        <v>0</v>
+        <v>3.71</v>
       </c>
       <c r="R58">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="S58">
         <v>0</v>
@@ -13218,7 +13218,7 @@
         <v>74</v>
       </c>
       <c r="C59" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="D59" t="s">
         <v>185</v>
@@ -13403,7 +13403,7 @@
         <v>74</v>
       </c>
       <c r="C60" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="D60" t="s">
         <v>185</v>
@@ -13776,7 +13776,7 @@
         <v>144</v>
       </c>
       <c r="D62" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E62" t="s">
         <v>248</v>
@@ -13812,13 +13812,13 @@
         <v>699</v>
       </c>
       <c r="P62">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="Q62">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="R62">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="S62">
         <v>0</v>
@@ -13997,13 +13997,13 @@
         <v>699</v>
       </c>
       <c r="P63">
-        <v>3.36</v>
+        <v>2.58</v>
       </c>
       <c r="Q63">
-        <v>3.65</v>
+        <v>3.62</v>
       </c>
       <c r="R63">
-        <v>1.99</v>
+        <v>2.45</v>
       </c>
       <c r="S63">
         <v>0</v>
@@ -14143,10 +14143,10 @@
         <v>76</v>
       </c>
       <c r="C64" t="s">
-        <v>146</v>
+        <v>122</v>
       </c>
       <c r="D64" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E64" t="s">
         <v>250</v>
@@ -14328,10 +14328,10 @@
         <v>76</v>
       </c>
       <c r="C65" t="s">
-        <v>123</v>
+        <v>129</v>
       </c>
       <c r="D65" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E65" t="s">
         <v>251</v>
@@ -14513,7 +14513,7 @@
         <v>76</v>
       </c>
       <c r="C66" t="s">
-        <v>129</v>
+        <v>145</v>
       </c>
       <c r="D66" t="s">
         <v>186</v>
@@ -14552,13 +14552,13 @@
         <v>699</v>
       </c>
       <c r="P66">
-        <v>0</v>
+        <v>3.36</v>
       </c>
       <c r="Q66">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="R66">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="S66">
         <v>0</v>
@@ -14698,10 +14698,10 @@
         <v>76</v>
       </c>
       <c r="C67" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="D67" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E67" t="s">
         <v>253</v>
@@ -14883,10 +14883,10 @@
         <v>76</v>
       </c>
       <c r="C68" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D68" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E68" t="s">
         <v>254</v>
@@ -14922,13 +14922,13 @@
         <v>699</v>
       </c>
       <c r="P68">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="Q68">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="R68">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="S68">
         <v>0</v>
@@ -15068,7 +15068,7 @@
         <v>76</v>
       </c>
       <c r="C69" t="s">
-        <v>144</v>
+        <v>125</v>
       </c>
       <c r="D69" t="s">
         <v>185</v>
@@ -15253,10 +15253,10 @@
         <v>76</v>
       </c>
       <c r="C70" t="s">
-        <v>127</v>
+        <v>121</v>
       </c>
       <c r="D70" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E70" t="s">
         <v>256</v>
@@ -15438,7 +15438,7 @@
         <v>76</v>
       </c>
       <c r="C71" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="D71" t="s">
         <v>186</v>
@@ -15623,7 +15623,7 @@
         <v>76</v>
       </c>
       <c r="C72" t="s">
-        <v>121</v>
+        <v>148</v>
       </c>
       <c r="D72" t="s">
         <v>186</v>
@@ -15662,13 +15662,13 @@
         <v>699</v>
       </c>
       <c r="P72">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="Q72">
-        <v>0</v>
+        <v>3.43</v>
       </c>
       <c r="R72">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="S72">
         <v>0</v>
@@ -15808,10 +15808,10 @@
         <v>76</v>
       </c>
       <c r="C73" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="D73" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E73" t="s">
         <v>259</v>
@@ -15847,13 +15847,13 @@
         <v>699</v>
       </c>
       <c r="P73">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="Q73">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R73">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="S73">
         <v>0</v>
@@ -15993,10 +15993,10 @@
         <v>76</v>
       </c>
       <c r="C74" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="D74" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E74" t="s">
         <v>260</v>
@@ -16548,10 +16548,10 @@
         <v>78</v>
       </c>
       <c r="C77" t="s">
-        <v>151</v>
+        <v>120</v>
       </c>
       <c r="D77" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E77" t="s">
         <v>263</v>
@@ -16733,7 +16733,7 @@
         <v>78</v>
       </c>
       <c r="C78" t="s">
-        <v>120</v>
+        <v>127</v>
       </c>
       <c r="D78" t="s">
         <v>186</v>
@@ -16772,13 +16772,13 @@
         <v>699</v>
       </c>
       <c r="P78">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Q78">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R78">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="S78">
         <v>0</v>
@@ -16918,10 +16918,10 @@
         <v>78</v>
       </c>
       <c r="C79" t="s">
-        <v>125</v>
+        <v>151</v>
       </c>
       <c r="D79" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E79" t="s">
         <v>265</v>
@@ -16957,13 +16957,13 @@
         <v>699</v>
       </c>
       <c r="P79">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="Q79">
-        <v>0</v>
+        <v>3.67</v>
       </c>
       <c r="R79">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="S79">
         <v>0</v>
@@ -17142,13 +17142,13 @@
         <v>699</v>
       </c>
       <c r="P80">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="Q80">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="R80">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="S80">
         <v>0</v>
@@ -17327,13 +17327,13 @@
         <v>699</v>
       </c>
       <c r="P81">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="Q81">
-        <v>0</v>
+        <v>3.66</v>
       </c>
       <c r="R81">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="S81">
         <v>0</v>
@@ -17372,10 +17372,10 @@
         <v>0</v>
       </c>
       <c r="AE81">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AF81">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AG81">
         <v>0</v>
@@ -17473,7 +17473,7 @@
         <v>80</v>
       </c>
       <c r="C82" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D82" t="s">
         <v>186</v>
@@ -17512,13 +17512,13 @@
         <v>699</v>
       </c>
       <c r="P82">
-        <v>0</v>
+        <v>5.38</v>
       </c>
       <c r="Q82">
-        <v>0</v>
+        <v>4.37</v>
       </c>
       <c r="R82">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="S82">
         <v>0</v>
@@ -17658,7 +17658,7 @@
         <v>80</v>
       </c>
       <c r="C83" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="D83" t="s">
         <v>185</v>
@@ -17843,7 +17843,7 @@
         <v>80</v>
       </c>
       <c r="C84" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="D84" t="s">
         <v>186</v>
@@ -17882,13 +17882,13 @@
         <v>699</v>
       </c>
       <c r="P84">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="Q84">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="R84">
-        <v>0</v>
+        <v>4.01</v>
       </c>
       <c r="S84">
         <v>0</v>
@@ -17927,10 +17927,10 @@
         <v>0</v>
       </c>
       <c r="AE84">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AF84">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AG84">
         <v>0</v>
@@ -18028,10 +18028,10 @@
         <v>80</v>
       </c>
       <c r="C85" t="s">
-        <v>132</v>
+        <v>153</v>
       </c>
       <c r="D85" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E85" t="s">
         <v>271</v>
@@ -18252,13 +18252,13 @@
         <v>699</v>
       </c>
       <c r="P86">
-        <v>2.09</v>
+        <v>2.1</v>
       </c>
       <c r="Q86">
-        <v>3.48</v>
+        <v>3.42</v>
       </c>
       <c r="R86">
-        <v>4.01</v>
+        <v>4.07</v>
       </c>
       <c r="S86">
         <v>0</v>
@@ -18297,10 +18297,10 @@
         <v>0</v>
       </c>
       <c r="AE86">
-        <v>1.98</v>
+        <v>2.15</v>
       </c>
       <c r="AF86">
-        <v>1.73</v>
+        <v>1.61</v>
       </c>
       <c r="AG86">
         <v>0</v>
@@ -18437,13 +18437,13 @@
         <v>699</v>
       </c>
       <c r="P87">
-        <v>2.46</v>
+        <v>0</v>
       </c>
       <c r="Q87">
-        <v>3.66</v>
+        <v>0</v>
       </c>
       <c r="R87">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="S87">
         <v>0</v>
@@ -18482,10 +18482,10 @@
         <v>0</v>
       </c>
       <c r="AE87">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AF87">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AG87">
         <v>0</v>
@@ -18583,7 +18583,7 @@
         <v>80</v>
       </c>
       <c r="C88" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="D88" t="s">
         <v>186</v>
@@ -18622,13 +18622,13 @@
         <v>699</v>
       </c>
       <c r="P88">
-        <v>5.38</v>
+        <v>2.69</v>
       </c>
       <c r="Q88">
-        <v>4.37</v>
+        <v>3.31</v>
       </c>
       <c r="R88">
-        <v>1.67</v>
+        <v>2.92</v>
       </c>
       <c r="S88">
         <v>0</v>
@@ -18667,10 +18667,10 @@
         <v>0</v>
       </c>
       <c r="AE88">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AF88">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AG88">
         <v>0</v>
@@ -18768,7 +18768,7 @@
         <v>80</v>
       </c>
       <c r="C89" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="D89" t="s">
         <v>186</v>
@@ -18807,13 +18807,13 @@
         <v>699</v>
       </c>
       <c r="P89">
-        <v>2.69</v>
+        <v>0</v>
       </c>
       <c r="Q89">
-        <v>3.31</v>
+        <v>0</v>
       </c>
       <c r="R89">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="S89">
         <v>0</v>
@@ -18852,10 +18852,10 @@
         <v>0</v>
       </c>
       <c r="AE89">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AF89">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AG89">
         <v>0</v>
@@ -18953,10 +18953,10 @@
         <v>80</v>
       </c>
       <c r="C90" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="D90" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E90" t="s">
         <v>276</v>
@@ -18992,13 +18992,13 @@
         <v>699</v>
       </c>
       <c r="P90">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Q90">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="R90">
-        <v>4.07</v>
+        <v>0</v>
       </c>
       <c r="S90">
         <v>0</v>
@@ -19037,10 +19037,10 @@
         <v>0</v>
       </c>
       <c r="AE90">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AF90">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AG90">
         <v>0</v>
@@ -19177,13 +19177,13 @@
         <v>699</v>
       </c>
       <c r="P91">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="Q91">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="R91">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S91">
         <v>0</v>
@@ -19362,13 +19362,13 @@
         <v>699</v>
       </c>
       <c r="P92">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="Q92">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="R92">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="S92">
         <v>0</v>
@@ -19508,7 +19508,7 @@
         <v>80</v>
       </c>
       <c r="C93" t="s">
-        <v>153</v>
+        <v>129</v>
       </c>
       <c r="D93" t="s">
         <v>186</v>
@@ -20063,7 +20063,7 @@
         <v>82</v>
       </c>
       <c r="C96" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="D96" t="s">
         <v>186</v>
@@ -20102,13 +20102,13 @@
         <v>699</v>
       </c>
       <c r="P96">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="Q96">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R96">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="S96">
         <v>0</v>
@@ -20287,13 +20287,13 @@
         <v>699</v>
       </c>
       <c r="P97">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="Q97">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="R97">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="S97">
         <v>0</v>
@@ -20433,10 +20433,10 @@
         <v>83</v>
       </c>
       <c r="C98" t="s">
-        <v>136</v>
+        <v>159</v>
       </c>
       <c r="D98" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E98" t="s">
         <v>284</v>
@@ -20618,7 +20618,7 @@
         <v>83</v>
       </c>
       <c r="C99" t="s">
-        <v>159</v>
+        <v>145</v>
       </c>
       <c r="D99" t="s">
         <v>186</v>
@@ -20657,13 +20657,13 @@
         <v>699</v>
       </c>
       <c r="P99">
-        <v>0</v>
+        <v>4.68</v>
       </c>
       <c r="Q99">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R99">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="S99">
         <v>0</v>
@@ -20803,7 +20803,7 @@
         <v>83</v>
       </c>
       <c r="C100" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="D100" t="s">
         <v>186</v>
@@ -20988,10 +20988,10 @@
         <v>83</v>
       </c>
       <c r="C101" t="s">
-        <v>137</v>
+        <v>160</v>
       </c>
       <c r="D101" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E101" t="s">
         <v>287</v>
@@ -21027,13 +21027,13 @@
         <v>699</v>
       </c>
       <c r="P101">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="Q101">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R101">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="S101">
         <v>0</v>
@@ -21173,10 +21173,10 @@
         <v>83</v>
       </c>
       <c r="C102" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="D102" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E102" t="s">
         <v>288</v>
@@ -21358,7 +21358,7 @@
         <v>83</v>
       </c>
       <c r="C103" t="s">
-        <v>145</v>
+        <v>160</v>
       </c>
       <c r="D103" t="s">
         <v>186</v>
@@ -21397,13 +21397,13 @@
         <v>699</v>
       </c>
       <c r="P103">
-        <v>4.68</v>
+        <v>0</v>
       </c>
       <c r="Q103">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R103">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="S103">
         <v>0</v>
@@ -21728,7 +21728,7 @@
         <v>83</v>
       </c>
       <c r="C105" t="s">
-        <v>161</v>
+        <v>135</v>
       </c>
       <c r="D105" t="s">
         <v>185</v>
@@ -21952,13 +21952,13 @@
         <v>699</v>
       </c>
       <c r="P106">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="Q106">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="R106">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="S106">
         <v>0</v>
@@ -21997,10 +21997,10 @@
         <v>0</v>
       </c>
       <c r="AE106">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AF106">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG106">
         <v>0</v>
@@ -22098,10 +22098,10 @@
         <v>83</v>
       </c>
       <c r="C107" t="s">
-        <v>158</v>
+        <v>139</v>
       </c>
       <c r="D107" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E107" t="s">
         <v>293</v>
@@ -22283,7 +22283,7 @@
         <v>84</v>
       </c>
       <c r="C108" t="s">
-        <v>148</v>
+        <v>123</v>
       </c>
       <c r="D108" t="s">
         <v>186</v>
@@ -22322,13 +22322,13 @@
         <v>699</v>
       </c>
       <c r="P108">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="Q108">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="R108">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="S108">
         <v>0</v>
@@ -22468,7 +22468,7 @@
         <v>84</v>
       </c>
       <c r="C109" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="D109" t="s">
         <v>186</v>
@@ -22507,13 +22507,13 @@
         <v>699</v>
       </c>
       <c r="P109">
-        <v>0</v>
+        <v>3.06</v>
       </c>
       <c r="Q109">
-        <v>0</v>
+        <v>3.61</v>
       </c>
       <c r="R109">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="S109">
         <v>0</v>
@@ -22653,7 +22653,7 @@
         <v>84</v>
       </c>
       <c r="C110" t="s">
-        <v>122</v>
+        <v>146</v>
       </c>
       <c r="D110" t="s">
         <v>186</v>
@@ -22692,13 +22692,13 @@
         <v>699</v>
       </c>
       <c r="P110">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="Q110">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="R110">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="S110">
         <v>0</v>
@@ -22841,7 +22841,7 @@
         <v>144</v>
       </c>
       <c r="D111" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E111" t="s">
         <v>297</v>
@@ -22877,13 +22877,13 @@
         <v>699</v>
       </c>
       <c r="P111">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Q111">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="R111">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="S111">
         <v>0</v>
@@ -23023,10 +23023,10 @@
         <v>85</v>
       </c>
       <c r="C112" t="s">
-        <v>119</v>
+        <v>147</v>
       </c>
       <c r="D112" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E112" t="s">
         <v>298</v>
@@ -23062,13 +23062,13 @@
         <v>699</v>
       </c>
       <c r="P112">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="Q112">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="R112">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="S112">
         <v>0</v>
@@ -23208,7 +23208,7 @@
         <v>85</v>
       </c>
       <c r="C113" t="s">
-        <v>149</v>
+        <v>141</v>
       </c>
       <c r="D113" t="s">
         <v>186</v>
@@ -23393,7 +23393,7 @@
         <v>85</v>
       </c>
       <c r="C114" t="s">
-        <v>149</v>
+        <v>144</v>
       </c>
       <c r="D114" t="s">
         <v>186</v>
@@ -23432,13 +23432,13 @@
         <v>699</v>
       </c>
       <c r="P114">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="Q114">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="R114">
-        <v>0</v>
+        <v>3.57</v>
       </c>
       <c r="S114">
         <v>0</v>
@@ -23483,10 +23483,10 @@
         <v>0</v>
       </c>
       <c r="AG114">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AH114">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AI114">
         <v>0</v>
@@ -23578,7 +23578,7 @@
         <v>85</v>
       </c>
       <c r="C115" t="s">
-        <v>140</v>
+        <v>119</v>
       </c>
       <c r="D115" t="s">
         <v>186</v>
@@ -23802,13 +23802,13 @@
         <v>699</v>
       </c>
       <c r="P116">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="Q116">
-        <v>0</v>
+        <v>3.89</v>
       </c>
       <c r="R116">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="S116">
         <v>0</v>
@@ -23853,10 +23853,10 @@
         <v>0</v>
       </c>
       <c r="AG116">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AH116">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AI116">
         <v>0</v>
@@ -23987,13 +23987,13 @@
         <v>699</v>
       </c>
       <c r="P117">
-        <v>0</v>
+        <v>4.48</v>
       </c>
       <c r="Q117">
-        <v>0</v>
+        <v>4.74</v>
       </c>
       <c r="R117">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="S117">
         <v>0</v>
@@ -24038,10 +24038,10 @@
         <v>0</v>
       </c>
       <c r="AG117">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AH117">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AI117">
         <v>0</v>
@@ -24172,13 +24172,13 @@
         <v>699</v>
       </c>
       <c r="P118">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="Q118">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="R118">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="S118">
         <v>0</v>
@@ -24223,10 +24223,10 @@
         <v>0</v>
       </c>
       <c r="AG118">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH118">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AI118">
         <v>0</v>
@@ -24357,13 +24357,13 @@
         <v>699</v>
       </c>
       <c r="P119">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="Q119">
-        <v>0</v>
+        <v>5.14</v>
       </c>
       <c r="R119">
-        <v>0</v>
+        <v>6.53</v>
       </c>
       <c r="S119">
         <v>0</v>
@@ -24408,10 +24408,10 @@
         <v>0</v>
       </c>
       <c r="AG119">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AH119">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AI119">
         <v>0</v>
@@ -24542,13 +24542,13 @@
         <v>699</v>
       </c>
       <c r="P120">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="Q120">
-        <v>0</v>
+        <v>4.17</v>
       </c>
       <c r="R120">
-        <v>0</v>
+        <v>4.22</v>
       </c>
       <c r="S120">
         <v>0</v>
@@ -24587,10 +24587,10 @@
         <v>0</v>
       </c>
       <c r="AE120">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AF120">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AG120">
         <v>0</v>
@@ -24727,13 +24727,13 @@
         <v>699</v>
       </c>
       <c r="P121">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="Q121">
-        <v>0</v>
+        <v>3.77</v>
       </c>
       <c r="R121">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="S121">
         <v>0</v>
@@ -24772,10 +24772,10 @@
         <v>0</v>
       </c>
       <c r="AE121">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AF121">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AG121">
         <v>0</v>
@@ -24912,13 +24912,13 @@
         <v>699</v>
       </c>
       <c r="P122">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="Q122">
-        <v>0</v>
+        <v>4.37</v>
       </c>
       <c r="R122">
-        <v>0</v>
+        <v>4.42</v>
       </c>
       <c r="S122">
         <v>0</v>
@@ -24963,10 +24963,10 @@
         <v>0</v>
       </c>
       <c r="AG122">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AH122">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AI122">
         <v>0</v>
@@ -25097,13 +25097,13 @@
         <v>699</v>
       </c>
       <c r="P123">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="Q123">
-        <v>0</v>
+        <v>4.17</v>
       </c>
       <c r="R123">
-        <v>0</v>
+        <v>4.17</v>
       </c>
       <c r="S123">
         <v>0</v>
@@ -25148,10 +25148,10 @@
         <v>0</v>
       </c>
       <c r="AG123">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AH123">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AI123">
         <v>0</v>
@@ -25282,13 +25282,13 @@
         <v>699</v>
       </c>
       <c r="P124">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="Q124">
-        <v>0</v>
+        <v>4.94</v>
       </c>
       <c r="R124">
-        <v>0</v>
+        <v>6.07</v>
       </c>
       <c r="S124">
         <v>0</v>
@@ -25333,10 +25333,10 @@
         <v>0</v>
       </c>
       <c r="AG124">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AH124">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AI124">
         <v>0</v>
@@ -25428,7 +25428,7 @@
         <v>87</v>
       </c>
       <c r="C125" t="s">
-        <v>120</v>
+        <v>163</v>
       </c>
       <c r="D125" t="s">
         <v>186</v>
@@ -25437,7 +25437,7 @@
         <v>311</v>
       </c>
       <c r="F125" t="s">
-        <v>567</v>
+        <v>289</v>
       </c>
       <c r="G125">
         <v>0</v>
@@ -25613,16 +25613,16 @@
         <v>87</v>
       </c>
       <c r="C126" t="s">
-        <v>163</v>
+        <v>120</v>
       </c>
       <c r="D126" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E126" t="s">
         <v>312</v>
       </c>
       <c r="F126" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="G126">
         <v>0</v>
@@ -25652,13 +25652,13 @@
         <v>699</v>
       </c>
       <c r="P126">
-        <v>4.07</v>
+        <v>0</v>
       </c>
       <c r="Q126">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="R126">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="S126">
         <v>0</v>
@@ -25798,16 +25798,16 @@
         <v>87</v>
       </c>
       <c r="C127" t="s">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="D127" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E127" t="s">
         <v>313</v>
       </c>
       <c r="F127" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="G127">
         <v>0</v>
@@ -25837,13 +25837,13 @@
         <v>699</v>
       </c>
       <c r="P127">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="Q127">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="R127">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="S127">
         <v>0</v>
@@ -25983,7 +25983,7 @@
         <v>87</v>
       </c>
       <c r="C128" t="s">
-        <v>125</v>
+        <v>164</v>
       </c>
       <c r="D128" t="s">
         <v>186</v>
@@ -25992,7 +25992,7 @@
         <v>314</v>
       </c>
       <c r="F128" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="G128">
         <v>0</v>
@@ -26168,16 +26168,16 @@
         <v>87</v>
       </c>
       <c r="C129" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="D129" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E129" t="s">
         <v>315</v>
       </c>
       <c r="F129" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="G129">
         <v>0</v>
@@ -26207,13 +26207,13 @@
         <v>699</v>
       </c>
       <c r="P129">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="Q129">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R129">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="S129">
         <v>0</v>
@@ -26353,16 +26353,16 @@
         <v>87</v>
       </c>
       <c r="C130" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="D130" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E130" t="s">
         <v>316</v>
       </c>
       <c r="F130" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="G130">
         <v>0</v>
@@ -26392,13 +26392,13 @@
         <v>699</v>
       </c>
       <c r="P130">
-        <v>5.4</v>
+        <v>0</v>
       </c>
       <c r="Q130">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="R130">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="S130">
         <v>0</v>
@@ -26541,13 +26541,13 @@
         <v>163</v>
       </c>
       <c r="D131" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E131" t="s">
         <v>317</v>
       </c>
       <c r="F131" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="G131">
         <v>0</v>
@@ -26577,13 +26577,13 @@
         <v>699</v>
       </c>
       <c r="P131">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Q131">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="R131">
-        <v>3.01</v>
+        <v>0</v>
       </c>
       <c r="S131">
         <v>0</v>
@@ -26723,7 +26723,7 @@
         <v>87</v>
       </c>
       <c r="C132" t="s">
-        <v>124</v>
+        <v>164</v>
       </c>
       <c r="D132" t="s">
         <v>186</v>
@@ -26732,7 +26732,7 @@
         <v>318</v>
       </c>
       <c r="F132" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="G132">
         <v>0</v>
@@ -26917,7 +26917,7 @@
         <v>319</v>
       </c>
       <c r="F133" t="s">
-        <v>293</v>
+        <v>574</v>
       </c>
       <c r="G133">
         <v>0</v>
@@ -27093,7 +27093,7 @@
         <v>87</v>
       </c>
       <c r="C134" t="s">
-        <v>143</v>
+        <v>164</v>
       </c>
       <c r="D134" t="s">
         <v>186</v>
@@ -27278,7 +27278,7 @@
         <v>87</v>
       </c>
       <c r="C135" t="s">
-        <v>129</v>
+        <v>143</v>
       </c>
       <c r="D135" t="s">
         <v>186</v>
@@ -27463,7 +27463,7 @@
         <v>87</v>
       </c>
       <c r="C136" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="D136" t="s">
         <v>186</v>
@@ -27648,10 +27648,10 @@
         <v>87</v>
       </c>
       <c r="C137" t="s">
-        <v>151</v>
+        <v>127</v>
       </c>
       <c r="D137" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E137" t="s">
         <v>323</v>
@@ -27833,10 +27833,10 @@
         <v>87</v>
       </c>
       <c r="C138" t="s">
-        <v>151</v>
+        <v>158</v>
       </c>
       <c r="D138" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E138" t="s">
         <v>324</v>
@@ -28018,10 +28018,10 @@
         <v>87</v>
       </c>
       <c r="C139" t="s">
-        <v>159</v>
+        <v>165</v>
       </c>
       <c r="D139" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E139" t="s">
         <v>325</v>
@@ -28057,13 +28057,13 @@
         <v>699</v>
       </c>
       <c r="P139">
-        <v>0</v>
+        <v>4.07</v>
       </c>
       <c r="Q139">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="R139">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="S139">
         <v>0</v>
@@ -28203,7 +28203,7 @@
         <v>87</v>
       </c>
       <c r="C140" t="s">
-        <v>165</v>
+        <v>158</v>
       </c>
       <c r="D140" t="s">
         <v>186</v>
@@ -28388,7 +28388,7 @@
         <v>87</v>
       </c>
       <c r="C141" t="s">
-        <v>159</v>
+        <v>166</v>
       </c>
       <c r="D141" t="s">
         <v>186</v>
@@ -28427,13 +28427,13 @@
         <v>699</v>
       </c>
       <c r="P141">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Q141">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="R141">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="S141">
         <v>0</v>
@@ -28573,10 +28573,10 @@
         <v>87</v>
       </c>
       <c r="C142" t="s">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="D142" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E142" t="s">
         <v>328</v>
@@ -28612,13 +28612,13 @@
         <v>699</v>
       </c>
       <c r="P142">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Q142">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="R142">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="S142">
         <v>0</v>
@@ -28758,7 +28758,7 @@
         <v>87</v>
       </c>
       <c r="C143" t="s">
-        <v>164</v>
+        <v>124</v>
       </c>
       <c r="D143" t="s">
         <v>186</v>
@@ -28943,10 +28943,10 @@
         <v>87</v>
       </c>
       <c r="C144" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="D144" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E144" t="s">
         <v>330</v>
@@ -28982,13 +28982,13 @@
         <v>699</v>
       </c>
       <c r="P144">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Q144">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R144">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="S144">
         <v>0</v>
@@ -29128,10 +29128,10 @@
         <v>87</v>
       </c>
       <c r="C145" t="s">
-        <v>165</v>
+        <v>151</v>
       </c>
       <c r="D145" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E145" t="s">
         <v>331</v>
@@ -29167,13 +29167,13 @@
         <v>699</v>
       </c>
       <c r="P145">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="Q145">
-        <v>0</v>
+        <v>3.82</v>
       </c>
       <c r="R145">
-        <v>0</v>
+        <v>4.13</v>
       </c>
       <c r="S145">
         <v>0</v>
@@ -29313,7 +29313,7 @@
         <v>87</v>
       </c>
       <c r="C146" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="D146" t="s">
         <v>185</v>
@@ -29352,13 +29352,13 @@
         <v>699</v>
       </c>
       <c r="P146">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="Q146">
-        <v>0</v>
+        <v>4.44</v>
       </c>
       <c r="R146">
-        <v>0</v>
+        <v>5.16</v>
       </c>
       <c r="S146">
         <v>0</v>
@@ -29498,10 +29498,10 @@
         <v>87</v>
       </c>
       <c r="C147" t="s">
-        <v>166</v>
+        <v>149</v>
       </c>
       <c r="D147" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E147" t="s">
         <v>333</v>
@@ -29683,10 +29683,10 @@
         <v>87</v>
       </c>
       <c r="C148" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="D148" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E148" t="s">
         <v>334</v>
@@ -29722,13 +29722,13 @@
         <v>699</v>
       </c>
       <c r="P148">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="Q148">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="R148">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="S148">
         <v>0</v>
@@ -29868,10 +29868,10 @@
         <v>87</v>
       </c>
       <c r="C149" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="D149" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E149" t="s">
         <v>335</v>
@@ -29907,13 +29907,13 @@
         <v>699</v>
       </c>
       <c r="P149">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Q149">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="R149">
-        <v>0</v>
+        <v>3.01</v>
       </c>
       <c r="S149">
         <v>0</v>
@@ -30092,13 +30092,13 @@
         <v>699</v>
       </c>
       <c r="P150">
-        <v>0</v>
+        <v>3.87</v>
       </c>
       <c r="Q150">
-        <v>0</v>
+        <v>3.87</v>
       </c>
       <c r="R150">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="S150">
         <v>0</v>
@@ -30241,7 +30241,7 @@
         <v>165</v>
       </c>
       <c r="D151" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E151" t="s">
         <v>337</v>
@@ -30277,13 +30277,13 @@
         <v>699</v>
       </c>
       <c r="P151">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="Q151">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="R151">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="S151">
         <v>0</v>
@@ -30423,7 +30423,7 @@
         <v>87</v>
       </c>
       <c r="C152" t="s">
-        <v>159</v>
+        <v>166</v>
       </c>
       <c r="D152" t="s">
         <v>186</v>
@@ -30462,13 +30462,13 @@
         <v>699</v>
       </c>
       <c r="P152">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="Q152">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R152">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="S152">
         <v>0</v>
@@ -30507,10 +30507,10 @@
         <v>0</v>
       </c>
       <c r="AE152">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AF152">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG152">
         <v>0</v>
@@ -30608,7 +30608,7 @@
         <v>87</v>
       </c>
       <c r="C153" t="s">
-        <v>159</v>
+        <v>166</v>
       </c>
       <c r="D153" t="s">
         <v>186</v>
@@ -30647,13 +30647,13 @@
         <v>699</v>
       </c>
       <c r="P153">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="Q153">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="R153">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="S153">
         <v>0</v>
@@ -30793,7 +30793,7 @@
         <v>87</v>
       </c>
       <c r="C154" t="s">
-        <v>165</v>
+        <v>129</v>
       </c>
       <c r="D154" t="s">
         <v>186</v>
@@ -30978,7 +30978,7 @@
         <v>87</v>
       </c>
       <c r="C155" t="s">
-        <v>165</v>
+        <v>158</v>
       </c>
       <c r="D155" t="s">
         <v>186</v>
@@ -31166,7 +31166,7 @@
         <v>165</v>
       </c>
       <c r="D156" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E156" t="s">
         <v>342</v>
@@ -31202,13 +31202,13 @@
         <v>699</v>
       </c>
       <c r="P156">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="Q156">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R156">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="S156">
         <v>0</v>
@@ -32088,7 +32088,7 @@
         <v>89</v>
       </c>
       <c r="C161" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="D161" t="s">
         <v>186</v>
@@ -32127,13 +32127,13 @@
         <v>699</v>
       </c>
       <c r="P161">
-        <v>0</v>
+        <v>5.17</v>
       </c>
       <c r="Q161">
-        <v>0</v>
+        <v>4.37</v>
       </c>
       <c r="R161">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="S161">
         <v>0</v>
@@ -32172,10 +32172,10 @@
         <v>0</v>
       </c>
       <c r="AE161">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AF161">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AG161">
         <v>0</v>
@@ -32273,7 +32273,7 @@
         <v>89</v>
       </c>
       <c r="C162" t="s">
-        <v>154</v>
+        <v>168</v>
       </c>
       <c r="D162" t="s">
         <v>186</v>
@@ -32312,13 +32312,13 @@
         <v>699</v>
       </c>
       <c r="P162">
-        <v>5.17</v>
+        <v>0</v>
       </c>
       <c r="Q162">
-        <v>4.37</v>
+        <v>0</v>
       </c>
       <c r="R162">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="S162">
         <v>0</v>
@@ -32357,10 +32357,10 @@
         <v>0</v>
       </c>
       <c r="AE162">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AF162">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AG162">
         <v>0</v>
@@ -32458,7 +32458,7 @@
         <v>89</v>
       </c>
       <c r="C163" t="s">
-        <v>130</v>
+        <v>154</v>
       </c>
       <c r="D163" t="s">
         <v>186</v>
@@ -32643,7 +32643,7 @@
         <v>89</v>
       </c>
       <c r="C164" t="s">
-        <v>168</v>
+        <v>157</v>
       </c>
       <c r="D164" t="s">
         <v>186</v>
@@ -32682,13 +32682,13 @@
         <v>699</v>
       </c>
       <c r="P164">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="Q164">
-        <v>0</v>
+        <v>4.32</v>
       </c>
       <c r="R164">
-        <v>0</v>
+        <v>4.52</v>
       </c>
       <c r="S164">
         <v>0</v>
@@ -32733,10 +32733,10 @@
         <v>0</v>
       </c>
       <c r="AG164">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AH164">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AI164">
         <v>0</v>
@@ -32828,7 +32828,7 @@
         <v>89</v>
       </c>
       <c r="C165" t="s">
-        <v>157</v>
+        <v>130</v>
       </c>
       <c r="D165" t="s">
         <v>186</v>
@@ -32867,13 +32867,13 @@
         <v>699</v>
       </c>
       <c r="P165">
-        <v>1.78</v>
+        <v>4.09</v>
       </c>
       <c r="Q165">
-        <v>4.32</v>
+        <v>3.78</v>
       </c>
       <c r="R165">
-        <v>4.52</v>
+        <v>1.77</v>
       </c>
       <c r="S165">
         <v>0</v>
@@ -32918,10 +32918,10 @@
         <v>0</v>
       </c>
       <c r="AG165">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AH165">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AI165">
         <v>0</v>
@@ -33013,10 +33013,10 @@
         <v>90</v>
       </c>
       <c r="C166" t="s">
-        <v>145</v>
+        <v>135</v>
       </c>
       <c r="D166" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E166" t="s">
         <v>352</v>
@@ -33383,7 +33383,7 @@
         <v>90</v>
       </c>
       <c r="C168" t="s">
-        <v>120</v>
+        <v>169</v>
       </c>
       <c r="D168" t="s">
         <v>186</v>
@@ -33568,7 +33568,7 @@
         <v>90</v>
       </c>
       <c r="C169" t="s">
-        <v>169</v>
+        <v>145</v>
       </c>
       <c r="D169" t="s">
         <v>186</v>
@@ -33753,10 +33753,10 @@
         <v>90</v>
       </c>
       <c r="C170" t="s">
-        <v>136</v>
+        <v>169</v>
       </c>
       <c r="D170" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E170" t="s">
         <v>356</v>
@@ -33938,7 +33938,7 @@
         <v>90</v>
       </c>
       <c r="C171" t="s">
-        <v>169</v>
+        <v>120</v>
       </c>
       <c r="D171" t="s">
         <v>186</v>
@@ -34308,7 +34308,7 @@
         <v>90</v>
       </c>
       <c r="C173" t="s">
-        <v>170</v>
+        <v>156</v>
       </c>
       <c r="D173" t="s">
         <v>186</v>
@@ -34347,13 +34347,13 @@
         <v>699</v>
       </c>
       <c r="P173">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="Q173">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R173">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="S173">
         <v>0</v>
@@ -34678,7 +34678,7 @@
         <v>90</v>
       </c>
       <c r="C175" t="s">
-        <v>155</v>
+        <v>169</v>
       </c>
       <c r="D175" t="s">
         <v>186</v>
@@ -34717,13 +34717,13 @@
         <v>699</v>
       </c>
       <c r="P175">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="Q175">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="R175">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="S175">
         <v>0</v>
@@ -34863,7 +34863,7 @@
         <v>90</v>
       </c>
       <c r="C176" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="D176" t="s">
         <v>186</v>
@@ -35233,7 +35233,7 @@
         <v>92</v>
       </c>
       <c r="C178" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="D178" t="s">
         <v>186</v>
@@ -35272,13 +35272,13 @@
         <v>699</v>
       </c>
       <c r="P178">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="Q178">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R178">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="S178">
         <v>0</v>
@@ -35418,10 +35418,10 @@
         <v>92</v>
       </c>
       <c r="C179" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="D179" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E179" t="s">
         <v>365</v>
@@ -35603,10 +35603,10 @@
         <v>92</v>
       </c>
       <c r="C180" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="D180" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E180" t="s">
         <v>366</v>
@@ -35973,10 +35973,10 @@
         <v>93</v>
       </c>
       <c r="C182" t="s">
-        <v>172</v>
+        <v>148</v>
       </c>
       <c r="D182" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E182" t="s">
         <v>368</v>
@@ -36012,13 +36012,13 @@
         <v>699</v>
       </c>
       <c r="P182">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="Q182">
-        <v>0</v>
+        <v>3.53</v>
       </c>
       <c r="R182">
-        <v>0</v>
+        <v>3.91</v>
       </c>
       <c r="S182">
         <v>0</v>
@@ -36057,10 +36057,10 @@
         <v>0</v>
       </c>
       <c r="AE182">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AF182">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AG182">
         <v>0</v>
@@ -36158,7 +36158,7 @@
         <v>93</v>
       </c>
       <c r="C183" t="s">
-        <v>173</v>
+        <v>123</v>
       </c>
       <c r="D183" t="s">
         <v>186</v>
@@ -36197,13 +36197,13 @@
         <v>699</v>
       </c>
       <c r="P183">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Q183">
-        <v>0</v>
+        <v>3.66</v>
       </c>
       <c r="R183">
-        <v>0</v>
+        <v>3.36</v>
       </c>
       <c r="S183">
         <v>0</v>
@@ -36343,7 +36343,7 @@
         <v>93</v>
       </c>
       <c r="C184" t="s">
-        <v>146</v>
+        <v>172</v>
       </c>
       <c r="D184" t="s">
         <v>186</v>
@@ -36528,7 +36528,7 @@
         <v>93</v>
       </c>
       <c r="C185" t="s">
-        <v>148</v>
+        <v>172</v>
       </c>
       <c r="D185" t="s">
         <v>186</v>
@@ -36713,10 +36713,10 @@
         <v>93</v>
       </c>
       <c r="C186" t="s">
-        <v>174</v>
+        <v>153</v>
       </c>
       <c r="D186" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E186" t="s">
         <v>372</v>
@@ -36898,10 +36898,10 @@
         <v>93</v>
       </c>
       <c r="C187" t="s">
-        <v>142</v>
+        <v>173</v>
       </c>
       <c r="D187" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E187" t="s">
         <v>373</v>
@@ -37083,7 +37083,7 @@
         <v>93</v>
       </c>
       <c r="C188" t="s">
-        <v>158</v>
+        <v>172</v>
       </c>
       <c r="D188" t="s">
         <v>186</v>
@@ -37122,13 +37122,13 @@
         <v>699</v>
       </c>
       <c r="P188">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="Q188">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="R188">
-        <v>6.76</v>
+        <v>0</v>
       </c>
       <c r="S188">
         <v>0</v>
@@ -37268,7 +37268,7 @@
         <v>93</v>
       </c>
       <c r="C189" t="s">
-        <v>173</v>
+        <v>160</v>
       </c>
       <c r="D189" t="s">
         <v>186</v>
@@ -37307,13 +37307,13 @@
         <v>699</v>
       </c>
       <c r="P189">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="Q189">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R189">
-        <v>0</v>
+        <v>4.56</v>
       </c>
       <c r="S189">
         <v>0</v>
@@ -37453,7 +37453,7 @@
         <v>93</v>
       </c>
       <c r="C190" t="s">
-        <v>148</v>
+        <v>142</v>
       </c>
       <c r="D190" t="s">
         <v>186</v>
@@ -37492,13 +37492,13 @@
         <v>699</v>
       </c>
       <c r="P190">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Q190">
-        <v>0</v>
+        <v>5.66</v>
       </c>
       <c r="R190">
-        <v>0</v>
+        <v>8.98</v>
       </c>
       <c r="S190">
         <v>0</v>
@@ -37638,7 +37638,7 @@
         <v>93</v>
       </c>
       <c r="C191" t="s">
-        <v>153</v>
+        <v>172</v>
       </c>
       <c r="D191" t="s">
         <v>186</v>
@@ -37823,7 +37823,7 @@
         <v>93</v>
       </c>
       <c r="C192" t="s">
-        <v>173</v>
+        <v>148</v>
       </c>
       <c r="D192" t="s">
         <v>186</v>
@@ -37862,13 +37862,13 @@
         <v>699</v>
       </c>
       <c r="P192">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="Q192">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="R192">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="S192">
         <v>0</v>
@@ -38008,7 +38008,7 @@
         <v>93</v>
       </c>
       <c r="C193" t="s">
-        <v>158</v>
+        <v>146</v>
       </c>
       <c r="D193" t="s">
         <v>186</v>
@@ -38047,13 +38047,13 @@
         <v>699</v>
       </c>
       <c r="P193">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="Q193">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="R193">
-        <v>4.56</v>
+        <v>0</v>
       </c>
       <c r="S193">
         <v>0</v>
@@ -38193,10 +38193,10 @@
         <v>93</v>
       </c>
       <c r="C194" t="s">
-        <v>172</v>
+        <v>160</v>
       </c>
       <c r="D194" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E194" t="s">
         <v>380</v>
@@ -38232,13 +38232,13 @@
         <v>699</v>
       </c>
       <c r="P194">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="Q194">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="R194">
-        <v>0</v>
+        <v>6.76</v>
       </c>
       <c r="S194">
         <v>0</v>
@@ -38381,7 +38381,7 @@
         <v>173</v>
       </c>
       <c r="D195" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E195" t="s">
         <v>381</v>
@@ -38563,10 +38563,10 @@
         <v>93</v>
       </c>
       <c r="C196" t="s">
-        <v>122</v>
+        <v>174</v>
       </c>
       <c r="D196" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E196" t="s">
         <v>382</v>
@@ -38602,13 +38602,13 @@
         <v>699</v>
       </c>
       <c r="P196">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Q196">
-        <v>3.66</v>
+        <v>0</v>
       </c>
       <c r="R196">
-        <v>3.36</v>
+        <v>0</v>
       </c>
       <c r="S196">
         <v>0</v>
@@ -38933,7 +38933,7 @@
         <v>94</v>
       </c>
       <c r="C198" t="s">
-        <v>124</v>
+        <v>175</v>
       </c>
       <c r="D198" t="s">
         <v>186</v>
@@ -39118,10 +39118,10 @@
         <v>94</v>
       </c>
       <c r="C199" t="s">
-        <v>147</v>
+        <v>124</v>
       </c>
       <c r="D199" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E199" t="s">
         <v>385</v>
@@ -39303,7 +39303,7 @@
         <v>94</v>
       </c>
       <c r="C200" t="s">
-        <v>175</v>
+        <v>158</v>
       </c>
       <c r="D200" t="s">
         <v>186</v>
@@ -39488,7 +39488,7 @@
         <v>94</v>
       </c>
       <c r="C201" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="D201" t="s">
         <v>186</v>
@@ -39673,10 +39673,10 @@
         <v>94</v>
       </c>
       <c r="C202" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="D202" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E202" t="s">
         <v>388</v>
@@ -39858,10 +39858,10 @@
         <v>94</v>
       </c>
       <c r="C203" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="D203" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E203" t="s">
         <v>389</v>
@@ -40043,10 +40043,10 @@
         <v>94</v>
       </c>
       <c r="C204" t="s">
-        <v>159</v>
+        <v>149</v>
       </c>
       <c r="D204" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E204" t="s">
         <v>390</v>
@@ -40413,7 +40413,7 @@
         <v>96</v>
       </c>
       <c r="C206" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="D206" t="s">
         <v>186</v>
@@ -40783,10 +40783,10 @@
         <v>97</v>
       </c>
       <c r="C208" t="s">
-        <v>177</v>
+        <v>171</v>
       </c>
       <c r="D208" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E208" t="s">
         <v>394</v>
@@ -41338,10 +41338,10 @@
         <v>97</v>
       </c>
       <c r="C211" t="s">
-        <v>171</v>
+        <v>177</v>
       </c>
       <c r="D211" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E211" t="s">
         <v>397</v>
@@ -41523,10 +41523,10 @@
         <v>98</v>
       </c>
       <c r="C212" t="s">
-        <v>178</v>
+        <v>126</v>
       </c>
       <c r="D212" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E212" t="s">
         <v>398</v>
@@ -41708,10 +41708,10 @@
         <v>98</v>
       </c>
       <c r="C213" t="s">
-        <v>126</v>
+        <v>178</v>
       </c>
       <c r="D213" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E213" t="s">
         <v>399</v>
@@ -42117,13 +42117,13 @@
         <v>699</v>
       </c>
       <c r="P215">
-        <v>3.17</v>
+        <v>2.38</v>
       </c>
       <c r="Q215">
-        <v>3.68</v>
+        <v>3.9</v>
       </c>
       <c r="R215">
-        <v>2.34</v>
+        <v>2.96</v>
       </c>
       <c r="S215">
         <v>0</v>
@@ -42162,10 +42162,10 @@
         <v>0</v>
       </c>
       <c r="AE215">
-        <v>1.72</v>
+        <v>1.58</v>
       </c>
       <c r="AF215">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="AG215">
         <v>0</v>
@@ -42448,10 +42448,10 @@
         <v>100</v>
       </c>
       <c r="C217" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="D217" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E217" t="s">
         <v>403</v>
@@ -42487,13 +42487,13 @@
         <v>699</v>
       </c>
       <c r="P217">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="Q217">
-        <v>3.76</v>
+        <v>0</v>
       </c>
       <c r="R217">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="S217">
         <v>0</v>
@@ -42532,10 +42532,10 @@
         <v>0</v>
       </c>
       <c r="AE217">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AF217">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AG217">
         <v>0</v>
@@ -42672,13 +42672,13 @@
         <v>699</v>
       </c>
       <c r="P218">
-        <v>2.38</v>
+        <v>1.59</v>
       </c>
       <c r="Q218">
-        <v>3.9</v>
+        <v>4.73</v>
       </c>
       <c r="R218">
-        <v>2.96</v>
+        <v>5.79</v>
       </c>
       <c r="S218">
         <v>0</v>
@@ -42717,16 +42717,16 @@
         <v>0</v>
       </c>
       <c r="AE218">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AF218">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AG218">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AH218">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AI218">
         <v>0</v>
@@ -42818,7 +42818,7 @@
         <v>100</v>
       </c>
       <c r="C219" t="s">
-        <v>146</v>
+        <v>179</v>
       </c>
       <c r="D219" t="s">
         <v>186</v>
@@ -42857,13 +42857,13 @@
         <v>699</v>
       </c>
       <c r="P219">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="Q219">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="R219">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="S219">
         <v>0</v>
@@ -42902,10 +42902,10 @@
         <v>0</v>
       </c>
       <c r="AE219">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AF219">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AG219">
         <v>0</v>
@@ -43042,13 +43042,13 @@
         <v>699</v>
       </c>
       <c r="P220">
-        <v>2.48</v>
+        <v>3.17</v>
       </c>
       <c r="Q220">
-        <v>3.5</v>
+        <v>3.68</v>
       </c>
       <c r="R220">
-        <v>3.07</v>
+        <v>2.34</v>
       </c>
       <c r="S220">
         <v>0</v>
@@ -43087,10 +43087,10 @@
         <v>0</v>
       </c>
       <c r="AE220">
-        <v>1.8</v>
+        <v>1.72</v>
       </c>
       <c r="AF220">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="AG220">
         <v>0</v>
@@ -43188,7 +43188,7 @@
         <v>100</v>
       </c>
       <c r="C221" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="D221" t="s">
         <v>185</v>
@@ -43227,13 +43227,13 @@
         <v>699</v>
       </c>
       <c r="P221">
-        <v>5.3</v>
+        <v>2.15</v>
       </c>
       <c r="Q221">
-        <v>3.73</v>
+        <v>3.44</v>
       </c>
       <c r="R221">
-        <v>1.71</v>
+        <v>3.5</v>
       </c>
       <c r="S221">
         <v>0</v>
@@ -43275,7 +43275,7 @@
         <v>1.95</v>
       </c>
       <c r="AF221">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="AG221">
         <v>0</v>
@@ -43373,10 +43373,10 @@
         <v>100</v>
       </c>
       <c r="C222" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="D222" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E222" t="s">
         <v>408</v>
@@ -43412,13 +43412,13 @@
         <v>699</v>
       </c>
       <c r="P222">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="Q222">
-        <v>9.15</v>
+        <v>0</v>
       </c>
       <c r="R222">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="S222">
         <v>0</v>
@@ -43463,10 +43463,10 @@
         <v>0</v>
       </c>
       <c r="AG222">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AH222">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AI222">
         <v>0</v>
@@ -43558,10 +43558,10 @@
         <v>100</v>
       </c>
       <c r="C223" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="D223" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E223" t="s">
         <v>409</v>
@@ -43597,13 +43597,13 @@
         <v>699</v>
       </c>
       <c r="P223">
-        <v>3.8</v>
+        <v>5.3</v>
       </c>
       <c r="Q223">
-        <v>3.78</v>
+        <v>3.73</v>
       </c>
       <c r="R223">
-        <v>2.05</v>
+        <v>1.71</v>
       </c>
       <c r="S223">
         <v>0</v>
@@ -43642,10 +43642,10 @@
         <v>0</v>
       </c>
       <c r="AE223">
+        <v>1.95</v>
+      </c>
+      <c r="AF223">
         <v>1.73</v>
-      </c>
-      <c r="AF223">
-        <v>1.98</v>
       </c>
       <c r="AG223">
         <v>0</v>
@@ -43743,7 +43743,7 @@
         <v>100</v>
       </c>
       <c r="C224" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="D224" t="s">
         <v>185</v>
@@ -43928,10 +43928,10 @@
         <v>100</v>
       </c>
       <c r="C225" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="D225" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E225" t="s">
         <v>411</v>
@@ -43967,13 +43967,13 @@
         <v>699</v>
       </c>
       <c r="P225">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Q225">
-        <v>0</v>
+        <v>9.15</v>
       </c>
       <c r="R225">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="S225">
         <v>0</v>
@@ -44018,10 +44018,10 @@
         <v>0</v>
       </c>
       <c r="AG225">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AH225">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AI225">
         <v>0</v>
@@ -44113,10 +44113,10 @@
         <v>100</v>
       </c>
       <c r="C226" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="D226" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E226" t="s">
         <v>412</v>
@@ -44152,13 +44152,13 @@
         <v>699</v>
       </c>
       <c r="P226">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="Q226">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R226">
-        <v>0</v>
+        <v>3.07</v>
       </c>
       <c r="S226">
         <v>0</v>
@@ -44197,10 +44197,10 @@
         <v>0</v>
       </c>
       <c r="AE226">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AF226">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AG226">
         <v>0</v>
@@ -44298,10 +44298,10 @@
         <v>100</v>
       </c>
       <c r="C227" t="s">
-        <v>178</v>
+        <v>146</v>
       </c>
       <c r="D227" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E227" t="s">
         <v>413</v>
@@ -44483,10 +44483,10 @@
         <v>100</v>
       </c>
       <c r="C228" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="D228" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E228" t="s">
         <v>414</v>
@@ -44522,13 +44522,13 @@
         <v>699</v>
       </c>
       <c r="P228">
-        <v>2.15</v>
+        <v>4.05</v>
       </c>
       <c r="Q228">
-        <v>3.44</v>
+        <v>3.76</v>
       </c>
       <c r="R228">
-        <v>3.5</v>
+        <v>1.99</v>
       </c>
       <c r="S228">
         <v>0</v>
@@ -44567,10 +44567,10 @@
         <v>0</v>
       </c>
       <c r="AE228">
-        <v>1.95</v>
+        <v>1.85</v>
       </c>
       <c r="AF228">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AG228">
         <v>0</v>
@@ -44668,10 +44668,10 @@
         <v>100</v>
       </c>
       <c r="C229" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="D229" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E229" t="s">
         <v>415</v>
@@ -44707,13 +44707,13 @@
         <v>699</v>
       </c>
       <c r="P229">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="Q229">
-        <v>4.73</v>
+        <v>0</v>
       </c>
       <c r="R229">
-        <v>5.79</v>
+        <v>0</v>
       </c>
       <c r="S229">
         <v>0</v>
@@ -44758,10 +44758,10 @@
         <v>0</v>
       </c>
       <c r="AG229">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AH229">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AI229">
         <v>0</v>
@@ -45408,7 +45408,7 @@
         <v>102</v>
       </c>
       <c r="C233" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="D233" t="s">
         <v>185</v>
@@ -45593,7 +45593,7 @@
         <v>102</v>
       </c>
       <c r="C234" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="D234" t="s">
         <v>185</v>
@@ -46888,7 +46888,7 @@
         <v>105</v>
       </c>
       <c r="C241" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="D241" t="s">
         <v>185</v>
@@ -47073,7 +47073,7 @@
         <v>106</v>
       </c>
       <c r="C242" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="D242" t="s">
         <v>185</v>
@@ -47112,13 +47112,13 @@
         <v>699</v>
       </c>
       <c r="P242">
-        <v>2.13</v>
+        <v>1.79</v>
       </c>
       <c r="Q242">
-        <v>3.34</v>
+        <v>3.62</v>
       </c>
       <c r="R242">
-        <v>3.67</v>
+        <v>4.84</v>
       </c>
       <c r="S242">
         <v>0</v>
@@ -47157,10 +47157,10 @@
         <v>0</v>
       </c>
       <c r="AE242">
-        <v>1.95</v>
+        <v>1.87</v>
       </c>
       <c r="AF242">
-        <v>1.73</v>
+        <v>1.8</v>
       </c>
       <c r="AG242">
         <v>0</v>
@@ -47258,7 +47258,7 @@
         <v>106</v>
       </c>
       <c r="C243" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="D243" t="s">
         <v>185</v>
@@ -47297,13 +47297,13 @@
         <v>699</v>
       </c>
       <c r="P243">
-        <v>1.79</v>
+        <v>2.26</v>
       </c>
       <c r="Q243">
-        <v>3.62</v>
+        <v>3.22</v>
       </c>
       <c r="R243">
-        <v>4.84</v>
+        <v>3.46</v>
       </c>
       <c r="S243">
         <v>0</v>
@@ -47342,10 +47342,10 @@
         <v>0</v>
       </c>
       <c r="AE243">
-        <v>1.87</v>
+        <v>2.25</v>
       </c>
       <c r="AF243">
-        <v>1.8</v>
+        <v>1.57</v>
       </c>
       <c r="AG243">
         <v>0</v>
@@ -47443,7 +47443,7 @@
         <v>106</v>
       </c>
       <c r="C244" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="D244" t="s">
         <v>185</v>
@@ -47482,13 +47482,13 @@
         <v>699</v>
       </c>
       <c r="P244">
-        <v>2.26</v>
+        <v>2.13</v>
       </c>
       <c r="Q244">
-        <v>3.22</v>
+        <v>3.34</v>
       </c>
       <c r="R244">
-        <v>3.46</v>
+        <v>3.67</v>
       </c>
       <c r="S244">
         <v>0</v>
@@ -47527,10 +47527,10 @@
         <v>0</v>
       </c>
       <c r="AE244">
-        <v>2.25</v>
+        <v>1.95</v>
       </c>
       <c r="AF244">
-        <v>1.57</v>
+        <v>1.73</v>
       </c>
       <c r="AG244">
         <v>0</v>
@@ -47628,7 +47628,7 @@
         <v>106</v>
       </c>
       <c r="C245" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="D245" t="s">
         <v>185</v>
@@ -48037,13 +48037,13 @@
         <v>699</v>
       </c>
       <c r="P247">
-        <v>3.79</v>
+        <v>0</v>
       </c>
       <c r="Q247">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="R247">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="S247">
         <v>0</v>
@@ -48082,10 +48082,10 @@
         <v>0</v>
       </c>
       <c r="AE247">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AF247">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AG247">
         <v>0</v>
@@ -48183,7 +48183,7 @@
         <v>108</v>
       </c>
       <c r="C248" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="D248" t="s">
         <v>185</v>
@@ -48222,13 +48222,13 @@
         <v>699</v>
       </c>
       <c r="P248">
-        <v>0</v>
+        <v>3.79</v>
       </c>
       <c r="Q248">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="R248">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="S248">
         <v>0</v>
@@ -48267,10 +48267,10 @@
         <v>0</v>
       </c>
       <c r="AE248">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AF248">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AG248">
         <v>0</v>
@@ -48553,7 +48553,7 @@
         <v>109</v>
       </c>
       <c r="C250" t="s">
-        <v>183</v>
+        <v>174</v>
       </c>
       <c r="D250" t="s">
         <v>185</v>
@@ -48738,7 +48738,7 @@
         <v>109</v>
       </c>
       <c r="C251" t="s">
-        <v>174</v>
+        <v>183</v>
       </c>
       <c r="D251" t="s">
         <v>185</v>
@@ -49108,7 +49108,7 @@
         <v>111</v>
       </c>
       <c r="C253" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="D253" t="s">
         <v>185</v>
@@ -49293,7 +49293,7 @@
         <v>111</v>
       </c>
       <c r="C254" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="D254" t="s">
         <v>185</v>

--- a/jogos_2026-05-10.xlsx
+++ b/jogos_2026-05-10.xlsx
@@ -361,15 +361,15 @@
     <t>22:00</t>
   </si>
   <si>
+    <t>Australia New South Wales NPL</t>
+  </si>
+  <si>
+    <t>South Korea K League 2</t>
+  </si>
+  <si>
     <t>South Korea K League 1</t>
   </si>
   <si>
-    <t>Australia New South Wales NPL</t>
-  </si>
-  <si>
-    <t>South Korea K League 2</t>
-  </si>
-  <si>
     <t>China China League One</t>
   </si>
   <si>
@@ -391,36 +391,36 @@
     <t>Spain Primera Division Women</t>
   </si>
   <si>
+    <t>Ethiopia Ethiopia Premier League</t>
+  </si>
+  <si>
+    <t>Vietnam V.League 1</t>
+  </si>
+  <si>
+    <t>Poland 1. Liga</t>
+  </si>
+  <si>
+    <t>Portugal Liga 3</t>
+  </si>
+  <si>
     <t>Kazakhstan Kazakhstan Premier League</t>
   </si>
   <si>
-    <t>Portugal Liga 3</t>
-  </si>
-  <si>
-    <t>Poland 1. Liga</t>
-  </si>
-  <si>
-    <t>Vietnam V.League 1</t>
-  </si>
-  <si>
-    <t>Ethiopia Ethiopia Premier League</t>
-  </si>
-  <si>
     <t>Poland Ekstraklasa</t>
   </si>
   <si>
     <t>Italy Serie A</t>
   </si>
   <si>
+    <t>Scotland Premiership</t>
+  </si>
+  <si>
     <t>Thailand Thai League T1</t>
   </si>
   <si>
     <t>Sweden Damallsvenskan</t>
   </si>
   <si>
-    <t>Scotland Premiership</t>
-  </si>
-  <si>
     <t>Lithuania A Lyga</t>
   </si>
   <si>
@@ -433,6 +433,9 @@
     <t>Germany 2. Bundesliga</t>
   </si>
   <si>
+    <t>Belgium Pro League</t>
+  </si>
+  <si>
     <t>Estonia Meistriliiga</t>
   </si>
   <si>
@@ -442,66 +445,63 @@
     <t>Germany 3. Liga</t>
   </si>
   <si>
-    <t>Belgium Pro League</t>
-  </si>
-  <si>
     <t>Croatia Druga HNL</t>
   </si>
   <si>
+    <t>Denmark Superliga</t>
+  </si>
+  <si>
+    <t>Sweden Allsvenskan</t>
+  </si>
+  <si>
+    <t>Georgia Erovnuli Liga</t>
+  </si>
+  <si>
     <t>Switzerland Super League</t>
   </si>
   <si>
-    <t>Denmark Superliga</t>
-  </si>
-  <si>
     <t>Spain La Liga</t>
   </si>
   <si>
-    <t>Sweden Allsvenskan</t>
-  </si>
-  <si>
     <t>Spain Segunda División</t>
   </si>
   <si>
-    <t>Georgia Erovnuli Liga</t>
-  </si>
-  <si>
     <t>Malaysia Super League</t>
   </si>
   <si>
     <t>Norway Eliteserien</t>
   </si>
   <si>
+    <t>Slovenia PrvaLiga</t>
+  </si>
+  <si>
     <t>England Premier League</t>
   </si>
   <si>
+    <t>Azerbaijan Premyer Liqası</t>
+  </si>
+  <si>
     <t>Czech Republic First League</t>
   </si>
   <si>
-    <t>Azerbaijan Premyer Liqası</t>
-  </si>
-  <si>
-    <t>Slovenia PrvaLiga</t>
-  </si>
-  <si>
     <t>Romania Liga I</t>
   </si>
   <si>
     <t>Germany Bundesliga</t>
   </si>
   <si>
+    <t>Croatia Prva HNL</t>
+  </si>
+  <si>
+    <t>Faroe Islands Faroe Islands Premier League</t>
+  </si>
+  <si>
     <t>Hungary NB II</t>
   </si>
   <si>
-    <t>Croatia Prva HNL</t>
-  </si>
-  <si>
     <t>Greece Super League</t>
   </si>
   <si>
-    <t>Faroe Islands Faroe Islands Premier League</t>
-  </si>
-  <si>
     <t>Netherlands Eredivisie</t>
   </si>
   <si>
@@ -511,12 +511,12 @@
     <t>FYR Macedonia First Football League</t>
   </si>
   <si>
+    <t>Austria Bundesliga</t>
+  </si>
+  <si>
     <t>Norway First Division</t>
   </si>
   <si>
-    <t>Austria Bundesliga</t>
-  </si>
-  <si>
     <t>UAE Arabian Gulf League</t>
   </si>
   <si>
@@ -535,12 +535,12 @@
     <t>Serbia SuperLiga</t>
   </si>
   <si>
+    <t>USA NWSL</t>
+  </si>
+  <si>
     <t>Chile Primera B</t>
   </si>
   <si>
-    <t>USA NWSL</t>
-  </si>
-  <si>
     <t>Israel Israeli Premier League</t>
   </si>
   <si>
@@ -553,18 +553,18 @@
     <t>Argentina Prim B Nacional</t>
   </si>
   <si>
+    <t>Brazil Serie A</t>
+  </si>
+  <si>
     <t>France Ligue 1</t>
   </si>
   <si>
+    <t>Bolivia LFPB</t>
+  </si>
+  <si>
     <t>Brazil Serie B</t>
   </si>
   <si>
-    <t>Brazil Serie A</t>
-  </si>
-  <si>
-    <t>Bolivia LFPB</t>
-  </si>
-  <si>
     <t>USA MLS</t>
   </si>
   <si>
@@ -580,33 +580,33 @@
     <t>2025</t>
   </si>
   <si>
+    <t>Blacktown City</t>
+  </si>
+  <si>
+    <t>Seongnam</t>
+  </si>
+  <si>
+    <t>Rockdale City Suns</t>
+  </si>
+  <si>
     <t>Ulsan</t>
   </si>
   <si>
-    <t>Rockdale City Suns</t>
-  </si>
-  <si>
-    <t>Blacktown City</t>
-  </si>
-  <si>
-    <t>Seongnam</t>
-  </si>
-  <si>
     <t>APIA Leichhardt Tigers</t>
   </si>
   <si>
+    <t>Shaanxi Union</t>
+  </si>
+  <si>
     <t>Dalian Huayi</t>
   </si>
   <si>
-    <t>Shaanxi Union</t>
+    <t>Ufa</t>
   </si>
   <si>
     <t>Yanbian Longding</t>
   </si>
   <si>
-    <t>Ufa</t>
-  </si>
-  <si>
     <t>Ansan Greeners</t>
   </si>
   <si>
@@ -634,84 +634,84 @@
     <t>Orenburg</t>
   </si>
   <si>
+    <t>Levante W</t>
+  </si>
+  <si>
+    <t>Sheger Ketema</t>
+  </si>
+  <si>
+    <t>Hoang Anh Gia Lai</t>
+  </si>
+  <si>
     <t>Gyeongnam</t>
   </si>
   <si>
-    <t>Levante W</t>
+    <t>Sichuan Jiuniu</t>
+  </si>
+  <si>
+    <t>Polonia Warszawa</t>
   </si>
   <si>
     <t>Sokol Saratov</t>
   </si>
   <si>
+    <t>Amarante</t>
+  </si>
+  <si>
     <t>Ulytau</t>
   </si>
   <si>
-    <t>Amarante</t>
-  </si>
-  <si>
-    <t>Polonia Warszawa</t>
-  </si>
-  <si>
-    <t>Hoang Anh Gia Lai</t>
-  </si>
-  <si>
-    <t>Sheger Ketema</t>
-  </si>
-  <si>
-    <t>Sichuan Jiuniu</t>
-  </si>
-  <si>
     <t>Piast Gliwice</t>
   </si>
   <si>
     <t>Hellas Verona</t>
   </si>
   <si>
+    <t>Celtic</t>
+  </si>
+  <si>
+    <t>Chiangrai United</t>
+  </si>
+  <si>
+    <t>Kanchanaburi</t>
+  </si>
+  <si>
+    <t>Shenzhen Juniors</t>
+  </si>
+  <si>
+    <t>Ho Chi Minh City</t>
+  </si>
+  <si>
+    <t>Piteå Women</t>
+  </si>
+  <si>
+    <t>Altay</t>
+  </si>
+  <si>
     <t>Chonburi</t>
   </si>
   <si>
-    <t>Piteå Women</t>
+    <t>Shenyang Urban</t>
+  </si>
+  <si>
+    <t>Bangkok Glass</t>
+  </si>
+  <si>
+    <t>Rayong</t>
+  </si>
+  <si>
+    <t>Buriram United</t>
+  </si>
+  <si>
+    <t>Hà Nội II</t>
   </si>
   <si>
     <t>Ayutthaya United</t>
   </si>
   <si>
-    <t>Chiangrai United</t>
-  </si>
-  <si>
-    <t>Celtic</t>
-  </si>
-  <si>
-    <t>Bangkok Glass</t>
-  </si>
-  <si>
-    <t>Shenzhen Juniors</t>
-  </si>
-  <si>
-    <t>Kanchanaburi</t>
-  </si>
-  <si>
     <t>Sukhothai</t>
   </si>
   <si>
-    <t>Ho Chi Minh City</t>
-  </si>
-  <si>
-    <t>Buriram United</t>
-  </si>
-  <si>
-    <t>Altay</t>
-  </si>
-  <si>
-    <t>Rayong</t>
-  </si>
-  <si>
-    <t>Shenyang Urban</t>
-  </si>
-  <si>
-    <t>Hà Nội II</t>
-  </si>
-  <si>
     <t>Sūduva</t>
   </si>
   <si>
@@ -721,36 +721,36 @@
     <t>Kerala Blasters</t>
   </si>
   <si>
+    <t>Fortuna Düsseldorf</t>
+  </si>
+  <si>
+    <t>KAA Gent</t>
+  </si>
+  <si>
+    <t>Nõmme Kalju</t>
+  </si>
+  <si>
     <t>Nantong Zhiyun</t>
   </si>
   <si>
+    <t>Hougang United</t>
+  </si>
+  <si>
+    <t>Home United</t>
+  </si>
+  <si>
+    <t>Dongguan United</t>
+  </si>
+  <si>
+    <t>Havelse</t>
+  </si>
+  <si>
+    <t>Preußen Münster</t>
+  </si>
+  <si>
     <t>Hertha BSC</t>
   </si>
   <si>
-    <t>Nõmme Kalju</t>
-  </si>
-  <si>
-    <t>Preußen Münster</t>
-  </si>
-  <si>
-    <t>Hougang United</t>
-  </si>
-  <si>
-    <t>Fortuna Düsseldorf</t>
-  </si>
-  <si>
-    <t>Havelse</t>
-  </si>
-  <si>
-    <t>Dongguan United</t>
-  </si>
-  <si>
-    <t>Home United</t>
-  </si>
-  <si>
-    <t>KAA Gent</t>
-  </si>
-  <si>
     <t>Zhejiang FC</t>
   </si>
   <si>
@@ -760,144 +760,144 @@
     <t>Hrvace</t>
   </si>
   <si>
+    <t>Vejle</t>
+  </si>
+  <si>
+    <t>AIK</t>
+  </si>
+  <si>
+    <t>Qingdao Jonoon</t>
+  </si>
+  <si>
+    <t>PSIM Yogyakarta</t>
+  </si>
+  <si>
+    <t>Meshakhte</t>
+  </si>
+  <si>
     <t>Lugano</t>
   </si>
   <si>
-    <t>Vejle</t>
-  </si>
-  <si>
-    <t>Qingdao Jonoon</t>
+    <t>RCD Mallorca</t>
+  </si>
+  <si>
+    <t>Kalmar</t>
+  </si>
+  <si>
+    <t>Aktobe</t>
   </si>
   <si>
     <t>Bahardar</t>
   </si>
   <si>
+    <t>Zenit</t>
+  </si>
+  <si>
     <t>Nordsjælland</t>
   </si>
   <si>
-    <t>RCD Mallorca</t>
-  </si>
-  <si>
-    <t>AIK</t>
-  </si>
-  <si>
-    <t>Aktobe</t>
-  </si>
-  <si>
-    <t>PSIM Yogyakarta</t>
-  </si>
-  <si>
-    <t>Zenit</t>
-  </si>
-  <si>
     <t>FC Andorra</t>
   </si>
   <si>
-    <t>Kalmar</t>
-  </si>
-  <si>
-    <t>Meshakhte</t>
+    <t>Công An Nhân Dân</t>
   </si>
   <si>
     <t>Kuala Lumpur</t>
   </si>
   <si>
-    <t>Công An Nhân Dân</t>
-  </si>
-  <si>
     <t>Baník Ostrava U21</t>
   </si>
   <si>
+    <t>Rosenborg</t>
+  </si>
+  <si>
     <t>Tychy 71</t>
   </si>
   <si>
-    <t>Rosenborg</t>
-  </si>
-  <si>
     <t>Wisła Płock</t>
   </si>
   <si>
+    <t>NK Primorje</t>
+  </si>
+  <si>
+    <t>Kelantan United</t>
+  </si>
+  <si>
+    <t>Astana</t>
+  </si>
+  <si>
+    <t>Burnley</t>
+  </si>
+  <si>
+    <t>Crystal Palace</t>
+  </si>
+  <si>
+    <t>Turan</t>
+  </si>
+  <si>
+    <t>Sigma Olomouc</t>
+  </si>
+  <si>
+    <t>Cremonese</t>
+  </si>
+  <si>
+    <t>Arba Minch Kenema</t>
+  </si>
+  <si>
     <t>Nottingham Forest</t>
   </si>
   <si>
-    <t>Burnley</t>
-  </si>
-  <si>
-    <t>Astana</t>
+    <t>Uppsala W</t>
   </si>
   <si>
     <t>Fiorentina</t>
   </si>
   <si>
-    <t>Sigma Olomouc</t>
-  </si>
-  <si>
-    <t>Cremonese</t>
-  </si>
-  <si>
-    <t>Turan</t>
-  </si>
-  <si>
-    <t>Crystal Palace</t>
+    <t>Botoşani</t>
   </si>
   <si>
     <t>Pardubice</t>
   </si>
   <si>
-    <t>Uppsala W</t>
-  </si>
-  <si>
-    <t>NK Primorje</t>
-  </si>
-  <si>
-    <t>Botoşani</t>
-  </si>
-  <si>
-    <t>Arba Minch Kenema</t>
-  </si>
-  <si>
-    <t>Kelantan United</t>
-  </si>
-  <si>
     <t>Hamburger SV</t>
   </si>
   <si>
     <t>Botev Vratsa</t>
   </si>
   <si>
+    <t>Osijek</t>
+  </si>
+  <si>
+    <t>Banga</t>
+  </si>
+  <si>
+    <t>Silkeborg</t>
+  </si>
+  <si>
+    <t>B36</t>
+  </si>
+  <si>
     <t>Honvéd W</t>
   </si>
   <si>
-    <t>Osijek</t>
-  </si>
-  <si>
-    <t>Silkeborg</t>
+    <t>Aris</t>
+  </si>
+  <si>
+    <t>EB - Streymur</t>
+  </si>
+  <si>
+    <t>Royal Antwerp FC</t>
+  </si>
+  <si>
+    <t>Nõmme United</t>
+  </si>
+  <si>
+    <t>Volos NFC</t>
   </si>
   <si>
     <t>NorthEast United</t>
   </si>
   <si>
-    <t>Volos NFC</t>
-  </si>
-  <si>
-    <t>B36</t>
-  </si>
-  <si>
-    <t>Aris</t>
-  </si>
-  <si>
-    <t>EB - Streymur</t>
-  </si>
-  <si>
-    <t>Banga</t>
-  </si>
-  <si>
-    <t>Royal Antwerp FC</t>
-  </si>
-  <si>
-    <t>Nõmme United</t>
-  </si>
-  <si>
     <t>Akhmat Grozny</t>
   </si>
   <si>
@@ -910,28 +910,37 @@
     <t>Sion</t>
   </si>
   <si>
+    <t>Young Boys</t>
+  </si>
+  <si>
     <t>Häcken</t>
   </si>
   <si>
     <t>Viktoria Köln</t>
   </si>
   <si>
-    <t>Young Boys</t>
-  </si>
-  <si>
     <t>Neftekhimik</t>
   </si>
   <si>
+    <t>Twente</t>
+  </si>
+  <si>
+    <t>Ajax</t>
+  </si>
+  <si>
     <t>Groningen</t>
   </si>
   <si>
+    <t>Fortuna Sittard</t>
+  </si>
+  <si>
     <t>Go Ahead Eagles</t>
   </si>
   <si>
-    <t>Fortuna Sittard</t>
-  </si>
-  <si>
-    <t>Twente</t>
+    <t>Feyenoord</t>
+  </si>
+  <si>
+    <t>Telstar</t>
   </si>
   <si>
     <t>Excelsior</t>
@@ -940,109 +949,106 @@
     <t>NAC Breda</t>
   </si>
   <si>
-    <t>Ajax</t>
-  </si>
-  <si>
-    <t>Feyenoord</t>
-  </si>
-  <si>
-    <t>Telstar</t>
+    <t>Apollon</t>
+  </si>
+  <si>
+    <t>Akademija Pandev</t>
+  </si>
+  <si>
+    <t>Rapid Wien</t>
+  </si>
+  <si>
+    <t>Omonia Nicosia</t>
+  </si>
+  <si>
+    <t>Pelister</t>
+  </si>
+  <si>
+    <t>Vardar</t>
+  </si>
+  <si>
+    <t>Mebrat Hayl</t>
   </si>
   <si>
     <t>Paphos</t>
   </si>
   <si>
+    <t>KFUM</t>
+  </si>
+  <si>
+    <t>Tromsø</t>
+  </si>
+  <si>
+    <t>Sandefjord</t>
+  </si>
+  <si>
+    <t>Aresimi</t>
+  </si>
+  <si>
+    <t>Shkendija</t>
+  </si>
+  <si>
     <t>Zbrojovka Brno</t>
   </si>
   <si>
+    <t>Strømmen</t>
+  </si>
+  <si>
+    <t>Makedonija GjP</t>
+  </si>
+  <si>
+    <t>Pogoń Siedlce</t>
+  </si>
+  <si>
+    <t>Saburtalo</t>
+  </si>
+  <si>
+    <t>Karcag SE</t>
+  </si>
+  <si>
+    <t>Sogndal</t>
+  </si>
+  <si>
+    <t>Moss</t>
+  </si>
+  <si>
+    <t>Sandnes Ulf</t>
+  </si>
+  <si>
+    <t>Raufoss</t>
+  </si>
+  <si>
+    <t>Åsane</t>
+  </si>
+  <si>
     <t>Szentlőrinc SE</t>
   </si>
   <si>
-    <t>Aresimi</t>
-  </si>
-  <si>
-    <t>Vardar</t>
-  </si>
-  <si>
-    <t>Akademija Pandev</t>
-  </si>
-  <si>
-    <t>Apollon</t>
-  </si>
-  <si>
-    <t>Shkendija</t>
-  </si>
-  <si>
-    <t>Pelister</t>
-  </si>
-  <si>
-    <t>Makedonija GjP</t>
+    <t>Real Madrid W</t>
+  </si>
+  <si>
+    <t>Ajka</t>
+  </si>
+  <si>
+    <t>Hartberg</t>
+  </si>
+  <si>
+    <t>LASK Linz</t>
+  </si>
+  <si>
+    <t>Kecskeméti TE</t>
   </si>
   <si>
     <t>Croatia Zmijavci</t>
   </si>
   <si>
-    <t>Omonia Nicosia</t>
-  </si>
-  <si>
-    <t>Pogoń Siedlce</t>
-  </si>
-  <si>
     <t>Budafoki MTE</t>
   </si>
   <si>
-    <t>Sandnes Ulf</t>
-  </si>
-  <si>
-    <t>Karcag SE</t>
-  </si>
-  <si>
-    <t>Rapid Wien</t>
-  </si>
-  <si>
-    <t>Kecskeméti TE</t>
-  </si>
-  <si>
-    <t>Real Madrid W</t>
-  </si>
-  <si>
-    <t>Strømmen</t>
-  </si>
-  <si>
-    <t>Tromsø</t>
-  </si>
-  <si>
-    <t>Sandefjord</t>
-  </si>
-  <si>
-    <t>Saburtalo</t>
-  </si>
-  <si>
-    <t>Sogndal</t>
-  </si>
-  <si>
-    <t>Moss</t>
-  </si>
-  <si>
-    <t>KFUM</t>
-  </si>
-  <si>
-    <t>Åsane</t>
-  </si>
-  <si>
-    <t>Hartberg</t>
-  </si>
-  <si>
-    <t>LASK Linz</t>
-  </si>
-  <si>
-    <t>Mebrat Hayl</t>
-  </si>
-  <si>
-    <t>Ajka</t>
-  </si>
-  <si>
-    <t>Raufoss</t>
+    <t>Dibba Al Fujairah</t>
+  </si>
+  <si>
+    <t>Bani Yas</t>
   </si>
   <si>
     <t>Al Ain</t>
@@ -1051,10 +1057,13 @@
     <t>Al Bataeh</t>
   </si>
   <si>
-    <t>Bani Yas</t>
-  </si>
-  <si>
-    <t>Dibba Al Fujairah</t>
+    <t>Köln</t>
+  </si>
+  <si>
+    <t>Nieciecza</t>
+  </si>
+  <si>
+    <t>Neftçi</t>
   </si>
   <si>
     <t>West Ham United</t>
@@ -1063,132 +1072,123 @@
     <t>Sekhukhune United</t>
   </si>
   <si>
-    <t>Neftçi</t>
-  </si>
-  <si>
-    <t>Köln</t>
-  </si>
-  <si>
-    <t>Nieciecza</t>
+    <t>Vysočina Jihlava</t>
+  </si>
+  <si>
+    <t>Mornar</t>
+  </si>
+  <si>
+    <t>Dinamo Bucureşti</t>
+  </si>
+  <si>
+    <t>Brøndby</t>
+  </si>
+  <si>
+    <t>Parma</t>
+  </si>
+  <si>
+    <t>Jedinstvo</t>
   </si>
   <si>
     <t>Panevėžys</t>
   </si>
   <si>
+    <t>Arsenal Tivat</t>
+  </si>
+  <si>
+    <t>Ittihad Tanger</t>
+  </si>
+  <si>
     <t>Dečić</t>
   </si>
   <si>
-    <t>Arsenal Tivat</t>
-  </si>
-  <si>
-    <t>Brøndby</t>
-  </si>
-  <si>
-    <t>Jedinstvo</t>
-  </si>
-  <si>
-    <t>Vysočina Jihlava</t>
-  </si>
-  <si>
     <t>Mladost DG</t>
   </si>
   <si>
-    <t>Dinamo Bucureşti</t>
-  </si>
-  <si>
-    <t>Parma</t>
-  </si>
-  <si>
-    <t>Mornar</t>
-  </si>
-  <si>
-    <t>Ittihad Tanger</t>
-  </si>
-  <si>
     <t>Al Riyadh</t>
   </si>
   <si>
     <t>Dobrudzha 1919</t>
   </si>
   <si>
+    <t>Skála</t>
+  </si>
+  <si>
+    <t>Slaven Koprivnica</t>
+  </si>
+  <si>
     <t>07 Vestur</t>
   </si>
   <si>
-    <t>Slaven Koprivnica</t>
-  </si>
-  <si>
-    <t>Skála</t>
+    <t>IMT Novi Beograd</t>
+  </si>
+  <si>
+    <t>Radnički Niš</t>
+  </si>
+  <si>
+    <t>Olympiakos Piraeus</t>
+  </si>
+  <si>
+    <t>AEK Athens</t>
+  </si>
+  <si>
+    <t>Union Saint-Gilloise</t>
+  </si>
+  <si>
+    <t>Bačka Topola</t>
+  </si>
+  <si>
+    <t>Spartak Subotica</t>
+  </si>
+  <si>
+    <t>Lokomotiv Moskva</t>
+  </si>
+  <si>
+    <t>Jablonec</t>
+  </si>
+  <si>
+    <t>Kansas City</t>
+  </si>
+  <si>
+    <t>Mirandés</t>
   </si>
   <si>
     <t>Córdoba</t>
   </si>
   <si>
-    <t>Lokomotiv Moskva</t>
-  </si>
-  <si>
-    <t>Spartak Subotica</t>
-  </si>
-  <si>
-    <t>IMT Novi Beograd</t>
-  </si>
-  <si>
-    <t>Jablonec</t>
-  </si>
-  <si>
     <t>Antofagasta</t>
   </si>
   <si>
-    <t>Radnički Niš</t>
-  </si>
-  <si>
-    <t>Olympiakos Piraeus</t>
-  </si>
-  <si>
-    <t>Union Saint-Gilloise</t>
-  </si>
-  <si>
-    <t>Bačka Topola</t>
-  </si>
-  <si>
-    <t>Mirandés</t>
-  </si>
-  <si>
     <t>Real Oviedo</t>
   </si>
   <si>
-    <t>AEK Athens</t>
-  </si>
-  <si>
     <t>Copiapó</t>
   </si>
   <si>
-    <t>Kansas City</t>
+    <t>Hapoel Haifa</t>
+  </si>
+  <si>
+    <t>Hapoel Katamon</t>
   </si>
   <si>
     <t>Ironi Tiberias</t>
   </si>
   <si>
-    <t>Hapoel Haifa</t>
+    <t>Dinamo Batumi</t>
   </si>
   <si>
     <t>Tenerife W</t>
   </si>
   <si>
+    <t>Békéscsaba</t>
+  </si>
+  <si>
+    <t>KA</t>
+  </si>
+  <si>
     <t>Csákvári TK</t>
   </si>
   <si>
-    <t>Békéscsaba</t>
-  </si>
-  <si>
-    <t>Hapoel Katamon</t>
-  </si>
-  <si>
-    <t>KA</t>
-  </si>
-  <si>
-    <t>Dinamo Batumi</t>
-  </si>
-  <si>
     <t>KRC Genk</t>
   </si>
   <si>
@@ -1198,93 +1198,93 @@
     <t>Mainz 05</t>
   </si>
   <si>
+    <t>New England II</t>
+  </si>
+  <si>
+    <t>UTS Rabat</t>
+  </si>
+  <si>
+    <t>CODM Meknès</t>
+  </si>
+  <si>
     <t>Al Ittihad</t>
   </si>
   <si>
-    <t>UTS Rabat</t>
-  </si>
-  <si>
-    <t>CODM Meknès</t>
-  </si>
-  <si>
-    <t>New England II</t>
+    <t>Chacarita Juniors</t>
   </si>
   <si>
     <t>Varzim</t>
   </si>
   <si>
-    <t>Chacarita Juniors</t>
-  </si>
-  <si>
     <t>AC Milan</t>
   </si>
   <si>
+    <t>Agropecuario</t>
+  </si>
+  <si>
+    <t>Atlético Mineiro</t>
+  </si>
+  <si>
+    <t>PSG</t>
+  </si>
+  <si>
+    <t>Club Atlético Güemes</t>
+  </si>
+  <si>
+    <t>Angers SCO</t>
+  </si>
+  <si>
     <t>Monaco</t>
   </si>
   <si>
+    <t>Independiente Petrolero</t>
+  </si>
+  <si>
+    <t>Toulouse</t>
+  </si>
+  <si>
+    <t>Náutico</t>
+  </si>
+  <si>
+    <t>Remo</t>
+  </si>
+  <si>
+    <t>Metz</t>
+  </si>
+  <si>
+    <t>Auxerre</t>
+  </si>
+  <si>
     <t>Le Havre</t>
   </si>
   <si>
-    <t>Náutico</t>
+    <t>FC Barcelona</t>
   </si>
   <si>
     <t>Rennes</t>
   </si>
   <si>
-    <t>Toulouse</t>
-  </si>
-  <si>
-    <t>Metz</t>
-  </si>
-  <si>
-    <t>Atlético Mineiro</t>
-  </si>
-  <si>
-    <t>Agropecuario</t>
-  </si>
-  <si>
-    <t>Remo</t>
-  </si>
-  <si>
-    <t>Club Atlético Güemes</t>
-  </si>
-  <si>
-    <t>PSG</t>
-  </si>
-  <si>
-    <t>Auxerre</t>
-  </si>
-  <si>
-    <t>FC Barcelona</t>
-  </si>
-  <si>
-    <t>Angers SCO</t>
-  </si>
-  <si>
-    <t>Independiente Petrolero</t>
+    <t>San Martín San Juan</t>
+  </si>
+  <si>
+    <t>Godoy Cruz</t>
   </si>
   <si>
     <t>Chaco For Ever</t>
   </si>
   <si>
-    <t>San Martín San Juan</t>
-  </si>
-  <si>
-    <t>Godoy Cruz</t>
+    <t>Los Angeles II</t>
+  </si>
+  <si>
+    <t>Central Norte</t>
   </si>
   <si>
     <t>Portland Timbers II</t>
   </si>
   <si>
-    <t>Central Norte</t>
-  </si>
-  <si>
     <t>Bay</t>
   </si>
   <si>
-    <t>Los Angeles II</t>
-  </si>
-  <si>
     <t>Hassania Agadir</t>
   </si>
   <si>
@@ -1300,25 +1300,28 @@
     <t>The Strongest</t>
   </si>
   <si>
+    <t>Corinthians</t>
+  </si>
+  <si>
+    <t>Santos</t>
+  </si>
+  <si>
     <t>Mirassol</t>
   </si>
   <si>
-    <t>Corinthians</t>
-  </si>
-  <si>
-    <t>Santos</t>
-  </si>
-  <si>
     <t>Avaí</t>
   </si>
   <si>
     <t>FC Cincinnati II</t>
   </si>
   <si>
+    <t>Grêmio</t>
+  </si>
+  <si>
     <t>Novorizontino</t>
   </si>
   <si>
-    <t>Grêmio</t>
+    <t>Minnesota United</t>
   </si>
   <si>
     <t>Atlanta United II</t>
@@ -1327,18 +1330,15 @@
     <t>Seattle Reign</t>
   </si>
   <si>
-    <t>Minnesota United</t>
-  </si>
-  <si>
     <t>Manta FC</t>
   </si>
   <si>
+    <t>Blooming</t>
+  </si>
+  <si>
     <t>Vasco da Gama</t>
   </si>
   <si>
-    <t>Blooming</t>
-  </si>
-  <si>
     <t>Colorado Rapids II</t>
   </si>
   <si>
@@ -1348,33 +1348,33 @@
     <t>Los Angeles FC</t>
   </si>
   <si>
+    <t>St. George Saints</t>
+  </si>
+  <si>
+    <t>Jeonnam Dragons</t>
+  </si>
+  <si>
+    <t>Sydney II</t>
+  </si>
+  <si>
     <t>Bucheon 1995</t>
   </si>
   <si>
-    <t>Sydney II</t>
-  </si>
-  <si>
-    <t>St. George Saints</t>
-  </si>
-  <si>
-    <t>Jeonnam Dragons</t>
-  </si>
-  <si>
     <t>Sydney United</t>
   </si>
   <si>
+    <t>Shanghai Jiading</t>
+  </si>
+  <si>
     <t>Guangzhou E-Power</t>
   </si>
   <si>
-    <t>Shanghai Jiading</t>
+    <t>Rotor Volgograd</t>
   </si>
   <si>
     <t>Guangxi Hengchen</t>
   </si>
   <si>
-    <t>Rotor Volgograd</t>
-  </si>
-  <si>
     <t>Yongin City</t>
   </si>
   <si>
@@ -1402,84 +1402,84 @@
     <t>Krylya Sovetov</t>
   </si>
   <si>
+    <t>Logroño W</t>
+  </si>
+  <si>
+    <t>Sidama Bunna</t>
+  </si>
+  <si>
+    <t>Pho Hien</t>
+  </si>
+  <si>
     <t>Gimhae City</t>
   </si>
   <si>
-    <t>Logroño W</t>
+    <t>Shandong Luneng</t>
+  </si>
+  <si>
+    <t>Górnik Łęczna</t>
   </si>
   <si>
     <t>Spartak Kostroma</t>
   </si>
   <si>
+    <t>União Santarém</t>
+  </si>
+  <si>
     <t>Kairat</t>
   </si>
   <si>
-    <t>União Santarém</t>
-  </si>
-  <si>
-    <t>Górnik Łęczna</t>
-  </si>
-  <si>
-    <t>Pho Hien</t>
-  </si>
-  <si>
-    <t>Sidama Bunna</t>
-  </si>
-  <si>
-    <t>Shandong Luneng</t>
-  </si>
-  <si>
     <t>GKS Katowice</t>
   </si>
   <si>
     <t>Como</t>
   </si>
   <si>
+    <t>Rangers</t>
+  </si>
+  <si>
+    <t>Uthai Thani</t>
+  </si>
+  <si>
+    <t>Ratchaburi</t>
+  </si>
+  <si>
+    <t>Hebei Kungfu</t>
+  </si>
+  <si>
+    <t>Song Lam Nghe An</t>
+  </si>
+  <si>
+    <t>Rosengard Women</t>
+  </si>
+  <si>
+    <t>Ordabasy</t>
+  </si>
+  <si>
     <t>Nakhon Ratchasima</t>
   </si>
   <si>
-    <t>Rosengard Women</t>
+    <t>Yunnan Yukun</t>
+  </si>
+  <si>
+    <t>Prachuap</t>
+  </si>
+  <si>
+    <t>Bangkok United</t>
+  </si>
+  <si>
+    <t>Lamphun Warrior</t>
+  </si>
+  <si>
+    <t>Viettel</t>
   </si>
   <si>
     <t>Port FC</t>
   </si>
   <si>
-    <t>Uthai Thani</t>
-  </si>
-  <si>
-    <t>Rangers</t>
-  </si>
-  <si>
-    <t>Prachuap</t>
-  </si>
-  <si>
-    <t>Hebei Kungfu</t>
-  </si>
-  <si>
-    <t>Ratchaburi</t>
-  </si>
-  <si>
     <t>Muang Thong United</t>
   </si>
   <si>
-    <t>Song Lam Nghe An</t>
-  </si>
-  <si>
-    <t>Lamphun Warrior</t>
-  </si>
-  <si>
-    <t>Ordabasy</t>
-  </si>
-  <si>
-    <t>Bangkok United</t>
-  </si>
-  <si>
-    <t>Yunnan Yukun</t>
-  </si>
-  <si>
-    <t>Viettel</t>
-  </si>
-  <si>
     <t>Žalgiris</t>
   </si>
   <si>
@@ -1489,36 +1489,36 @@
     <t>Mohammedan</t>
   </si>
   <si>
+    <t>Elversberg</t>
+  </si>
+  <si>
+    <t>RSC Anderlecht</t>
+  </si>
+  <si>
+    <t>Tallinna FC Flora</t>
+  </si>
+  <si>
     <t>Wuxi Wugou</t>
   </si>
   <si>
+    <t>Tampines Rovers</t>
+  </si>
+  <si>
+    <t>Albirex Niigata S</t>
+  </si>
+  <si>
+    <t>Suzhou Dongwu</t>
+  </si>
+  <si>
+    <t>Schweinfurt</t>
+  </si>
+  <si>
+    <t>Darmstadt 98</t>
+  </si>
+  <si>
     <t>Greuther Fürth</t>
   </si>
   <si>
-    <t>Tallinna FC Flora</t>
-  </si>
-  <si>
-    <t>Darmstadt 98</t>
-  </si>
-  <si>
-    <t>Tampines Rovers</t>
-  </si>
-  <si>
-    <t>Elversberg</t>
-  </si>
-  <si>
-    <t>Schweinfurt</t>
-  </si>
-  <si>
-    <t>Suzhou Dongwu</t>
-  </si>
-  <si>
-    <t>Albirex Niigata S</t>
-  </si>
-  <si>
-    <t>RSC Anderlecht</t>
-  </si>
-  <si>
     <t>Tianjin Teda</t>
   </si>
   <si>
@@ -1528,144 +1528,144 @@
     <t>Opatija</t>
   </si>
   <si>
+    <t>Fredericia</t>
+  </si>
+  <si>
+    <t>Djurgården</t>
+  </si>
+  <si>
+    <t>Dalian Zhixing</t>
+  </si>
+  <si>
+    <t>Malut United</t>
+  </si>
+  <si>
+    <t>Dila</t>
+  </si>
+  <si>
     <t>St. Gallen</t>
   </si>
   <si>
-    <t>Fredericia</t>
-  </si>
-  <si>
-    <t>Dalian Zhixing</t>
+    <t>Villarreal</t>
+  </si>
+  <si>
+    <t>Halmstad</t>
+  </si>
+  <si>
+    <t>Kaisar</t>
   </si>
   <si>
     <t>Welwalo Adigrat Uni</t>
   </si>
   <si>
+    <t>FK Sochi</t>
+  </si>
+  <si>
     <t>Midtjylland</t>
   </si>
   <si>
-    <t>Villarreal</t>
-  </si>
-  <si>
-    <t>Djurgården</t>
-  </si>
-  <si>
-    <t>Kaisar</t>
-  </si>
-  <si>
-    <t>Malut United</t>
-  </si>
-  <si>
-    <t>FK Sochi</t>
-  </si>
-  <si>
     <t>UD Las Palmas</t>
   </si>
   <si>
-    <t>Halmstad</t>
-  </si>
-  <si>
-    <t>Dila</t>
+    <t>Nam Dinh</t>
   </si>
   <si>
     <t>Negeri Sembilan</t>
   </si>
   <si>
-    <t>Nam Dinh</t>
-  </si>
-  <si>
     <t>Ústí nad Labem</t>
   </si>
   <si>
+    <t>Lillestrøm</t>
+  </si>
+  <si>
     <t>Ruch Chorzów</t>
   </si>
   <si>
-    <t>Lillestrøm</t>
-  </si>
-  <si>
     <t>Motor Lublin</t>
   </si>
   <si>
+    <t>Mura</t>
+  </si>
+  <si>
+    <t>Johor Darul Ta'zim</t>
+  </si>
+  <si>
+    <t>Kyzyl-Zhar</t>
+  </si>
+  <si>
+    <t>Aston Villa</t>
+  </si>
+  <si>
+    <t>Everton</t>
+  </si>
+  <si>
+    <t>Karvan FK</t>
+  </si>
+  <si>
+    <t>Bohemians 1905</t>
+  </si>
+  <si>
+    <t>Pisa</t>
+  </si>
+  <si>
+    <t>Welayta Dicha</t>
+  </si>
+  <si>
     <t>Newcastle United</t>
   </si>
   <si>
-    <t>Aston Villa</t>
-  </si>
-  <si>
-    <t>Kyzyl-Zhar</t>
+    <t>Vittsjö</t>
   </si>
   <si>
     <t>Genoa</t>
   </si>
   <si>
-    <t>Bohemians 1905</t>
-  </si>
-  <si>
-    <t>Pisa</t>
-  </si>
-  <si>
-    <t>Karvan FK</t>
-  </si>
-  <si>
-    <t>Everton</t>
+    <t>Petrolul 52</t>
   </si>
   <si>
     <t>Karviná</t>
   </si>
   <si>
-    <t>Vittsjö</t>
-  </si>
-  <si>
-    <t>Mura</t>
-  </si>
-  <si>
-    <t>Petrolul 52</t>
-  </si>
-  <si>
-    <t>Welayta Dicha</t>
-  </si>
-  <si>
-    <t>Johor Darul Ta'zim</t>
-  </si>
-  <si>
     <t>Freiburg</t>
   </si>
   <si>
     <t>Septemvri Sofia</t>
   </si>
   <si>
+    <t>Istra 1961</t>
+  </si>
+  <si>
+    <t>TransINVEST Vilnius</t>
+  </si>
+  <si>
+    <t>København</t>
+  </si>
+  <si>
+    <t>KÍ</t>
+  </si>
+  <si>
     <t>Vasas</t>
   </si>
   <si>
-    <t>Istra 1961</t>
-  </si>
-  <si>
-    <t>København</t>
+    <t>OFI</t>
+  </si>
+  <si>
+    <t>Víkingur</t>
+  </si>
+  <si>
+    <t>Sporting Charleroi</t>
+  </si>
+  <si>
+    <t>Paide</t>
+  </si>
+  <si>
+    <t>Levadiakos</t>
   </si>
   <si>
     <t>Chennaiyin</t>
   </si>
   <si>
-    <t>Levadiakos</t>
-  </si>
-  <si>
-    <t>KÍ</t>
-  </si>
-  <si>
-    <t>OFI</t>
-  </si>
-  <si>
-    <t>Víkingur</t>
-  </si>
-  <si>
-    <t>TransINVEST Vilnius</t>
-  </si>
-  <si>
-    <t>Sporting Charleroi</t>
-  </si>
-  <si>
-    <t>Paide</t>
-  </si>
-  <si>
     <t>Makhachkala</t>
   </si>
   <si>
@@ -1678,28 +1678,37 @@
     <t>Thun</t>
   </si>
   <si>
+    <t>Basel</t>
+  </si>
+  <si>
     <t>Malmö FF</t>
   </si>
   <si>
     <t>Alemannia Aachen</t>
   </si>
   <si>
-    <t>Basel</t>
-  </si>
-  <si>
     <t>Volga Ulyanovsk</t>
   </si>
   <si>
+    <t>Sparta Rotterdam</t>
+  </si>
+  <si>
+    <t>Utrecht</t>
+  </si>
+  <si>
     <t>NEC</t>
   </si>
   <si>
+    <t>PEC Zwolle</t>
+  </si>
+  <si>
     <t>PSV</t>
   </si>
   <si>
-    <t>PEC Zwolle</t>
-  </si>
-  <si>
-    <t>Sparta Rotterdam</t>
+    <t>AZ</t>
+  </si>
+  <si>
+    <t>Heracles</t>
   </si>
   <si>
     <t>Volendam</t>
@@ -1708,106 +1717,103 @@
     <t>Heerenveen</t>
   </si>
   <si>
-    <t>Utrecht</t>
-  </si>
-  <si>
-    <t>AZ</t>
-  </si>
-  <si>
-    <t>Heracles</t>
+    <t>APOEL</t>
+  </si>
+  <si>
+    <t>Rabotnički</t>
+  </si>
+  <si>
+    <t>Austria Wien</t>
+  </si>
+  <si>
+    <t>AEK Larnaca</t>
+  </si>
+  <si>
+    <t>Shkupi</t>
+  </si>
+  <si>
+    <t>Sileks</t>
+  </si>
+  <si>
+    <t>Fasil Ketema</t>
+  </si>
+  <si>
+    <t>Viking</t>
+  </si>
+  <si>
+    <t>Molde</t>
+  </si>
+  <si>
+    <t>Kristiansund</t>
+  </si>
+  <si>
+    <t>FK Bashkimi Kumanovo</t>
+  </si>
+  <si>
+    <t>Struga</t>
   </si>
   <si>
     <t>Vlašim</t>
   </si>
   <si>
+    <t>Hødd</t>
+  </si>
+  <si>
+    <t>Tikveš</t>
+  </si>
+  <si>
+    <t>Stal Rzeszów</t>
+  </si>
+  <si>
+    <t>Torpedo Kutaisi</t>
+  </si>
+  <si>
+    <t>Tiszakécske</t>
+  </si>
+  <si>
+    <t>Haugesund</t>
+  </si>
+  <si>
+    <t>Bryne</t>
+  </si>
+  <si>
+    <t>Stabæk</t>
+  </si>
+  <si>
+    <t>Lyn</t>
+  </si>
+  <si>
+    <t>Strømsgodset</t>
+  </si>
+  <si>
     <t>Videoton</t>
   </si>
   <si>
-    <t>FK Bashkimi Kumanovo</t>
-  </si>
-  <si>
-    <t>Sileks</t>
-  </si>
-  <si>
-    <t>Rabotnički</t>
-  </si>
-  <si>
-    <t>APOEL</t>
-  </si>
-  <si>
-    <t>Struga</t>
-  </si>
-  <si>
-    <t>Shkupi</t>
-  </si>
-  <si>
-    <t>Tikveš</t>
+    <t>Atletico Madrid W</t>
+  </si>
+  <si>
+    <t>Szeged 2011</t>
+  </si>
+  <si>
+    <t>Sturm Graz</t>
+  </si>
+  <si>
+    <t>Salzburg</t>
+  </si>
+  <si>
+    <t>Mezőkövesd-Zsóry</t>
   </si>
   <si>
     <t>Jarun</t>
   </si>
   <si>
-    <t>AEK Larnaca</t>
-  </si>
-  <si>
-    <t>Stal Rzeszów</t>
-  </si>
-  <si>
     <t>BVSC</t>
   </si>
   <si>
-    <t>Stabæk</t>
-  </si>
-  <si>
-    <t>Tiszakécske</t>
-  </si>
-  <si>
-    <t>Austria Wien</t>
-  </si>
-  <si>
-    <t>Mezőkövesd-Zsóry</t>
-  </si>
-  <si>
-    <t>Atletico Madrid W</t>
-  </si>
-  <si>
-    <t>Hødd</t>
-  </si>
-  <si>
-    <t>Molde</t>
-  </si>
-  <si>
-    <t>Kristiansund</t>
-  </si>
-  <si>
-    <t>Torpedo Kutaisi</t>
-  </si>
-  <si>
-    <t>Haugesund</t>
-  </si>
-  <si>
-    <t>Bryne</t>
-  </si>
-  <si>
-    <t>Viking</t>
-  </si>
-  <si>
-    <t>Strømsgodset</t>
-  </si>
-  <si>
-    <t>Sturm Graz</t>
-  </si>
-  <si>
-    <t>Salzburg</t>
-  </si>
-  <si>
-    <t>Fasil Ketema</t>
-  </si>
-  <si>
-    <t>Szeged 2011</t>
-  </si>
-  <si>
-    <t>Lyn</t>
+    <t>Ajman</t>
+  </si>
+  <si>
+    <t>Shabab Al Ahli Dubai</t>
   </si>
   <si>
     <t>Al Dhafra</t>
@@ -1816,10 +1822,13 @@
     <t>Al Sharjah</t>
   </si>
   <si>
-    <t>Shabab Al Ahli Dubai</t>
-  </si>
-  <si>
-    <t>Ajman</t>
+    <t>Heidenheim</t>
+  </si>
+  <si>
+    <t>Legia Warszawa</t>
+  </si>
+  <si>
+    <t>İnter Bakı</t>
   </si>
   <si>
     <t>Arsenal</t>
@@ -1828,132 +1837,123 @@
     <t>Kaizer Chiefs</t>
   </si>
   <si>
-    <t>İnter Bakı</t>
-  </si>
-  <si>
-    <t>Heidenheim</t>
-  </si>
-  <si>
-    <t>Legia Warszawa</t>
+    <t>Hanácká</t>
+  </si>
+  <si>
+    <t>Bokelj</t>
+  </si>
+  <si>
+    <t>Argeș</t>
+  </si>
+  <si>
+    <t>AGF</t>
+  </si>
+  <si>
+    <t>Roma</t>
+  </si>
+  <si>
+    <t>Budućnost</t>
   </si>
   <si>
     <t>Kauno Žalgiris</t>
   </si>
   <si>
+    <t>Sutjeska</t>
+  </si>
+  <si>
+    <t>Difaâ El Jadida</t>
+  </si>
+  <si>
     <t>FK Jezero Plav</t>
   </si>
   <si>
-    <t>Sutjeska</t>
-  </si>
-  <si>
-    <t>AGF</t>
-  </si>
-  <si>
-    <t>Budućnost</t>
-  </si>
-  <si>
-    <t>Hanácká</t>
-  </si>
-  <si>
     <t>Petrovac</t>
   </si>
   <si>
-    <t>Argeș</t>
-  </si>
-  <si>
-    <t>Roma</t>
-  </si>
-  <si>
-    <t>Bokelj</t>
-  </si>
-  <si>
-    <t>Difaâ El Jadida</t>
-  </si>
-  <si>
     <t>Al Fateh</t>
   </si>
   <si>
     <t>Beroe</t>
   </si>
   <si>
+    <t>AB</t>
+  </si>
+  <si>
+    <t>Gorica</t>
+  </si>
+  <si>
     <t>B68</t>
   </si>
   <si>
-    <t>Gorica</t>
-  </si>
-  <si>
-    <t>AB</t>
+    <t>Radnički Kragujevac</t>
+  </si>
+  <si>
+    <t>LFK Mladost Lučani</t>
+  </si>
+  <si>
+    <t>PAOK</t>
+  </si>
+  <si>
+    <t>Panathinaikos</t>
+  </si>
+  <si>
+    <t>KV Mechelen</t>
+  </si>
+  <si>
+    <t>Javor Ivanjica</t>
+  </si>
+  <si>
+    <t>Napredak</t>
+  </si>
+  <si>
+    <t>Baltika</t>
+  </si>
+  <si>
+    <t>Hradec Králové</t>
+  </si>
+  <si>
+    <t>Chicago Red Stars</t>
+  </si>
+  <si>
+    <t>SD Eibar</t>
   </si>
   <si>
     <t>Granada CF</t>
   </si>
   <si>
-    <t>Baltika</t>
-  </si>
-  <si>
-    <t>Napredak</t>
-  </si>
-  <si>
-    <t>Radnički Kragujevac</t>
-  </si>
-  <si>
-    <t>Hradec Králové</t>
-  </si>
-  <si>
     <t>San Luis</t>
   </si>
   <si>
-    <t>LFK Mladost Lučani</t>
-  </si>
-  <si>
-    <t>PAOK</t>
-  </si>
-  <si>
-    <t>KV Mechelen</t>
-  </si>
-  <si>
-    <t>Javor Ivanjica</t>
-  </si>
-  <si>
-    <t>SD Eibar</t>
-  </si>
-  <si>
     <t>Getafe CF</t>
   </si>
   <si>
-    <t>Panathinaikos</t>
-  </si>
-  <si>
     <t>Unión San Felipe</t>
   </si>
   <si>
-    <t>Chicago Red Stars</t>
+    <t>Ashdod</t>
+  </si>
+  <si>
+    <t>Bnei Sakhnin</t>
   </si>
   <si>
     <t>Maccabi Netanya</t>
   </si>
   <si>
-    <t>Ashdod</t>
+    <t>Samgurali</t>
   </si>
   <si>
     <t>Barcelona W</t>
   </si>
   <si>
+    <t>Kozármisleny</t>
+  </si>
+  <si>
+    <t>ÍBV</t>
+  </si>
+  <si>
     <t>Soroksár SC</t>
   </si>
   <si>
-    <t>Kozármisleny</t>
-  </si>
-  <si>
-    <t>Bnei Sakhnin</t>
-  </si>
-  <si>
-    <t>ÍBV</t>
-  </si>
-  <si>
-    <t>Samgurali</t>
-  </si>
-  <si>
     <t>KVC Westerlo</t>
   </si>
   <si>
@@ -1963,93 +1963,93 @@
     <t>Union Berlin</t>
   </si>
   <si>
+    <t>New York City II</t>
+  </si>
+  <si>
+    <t>Maghreb Fès</t>
+  </si>
+  <si>
+    <t>RSB Berkane</t>
+  </si>
+  <si>
     <t>Dhamk</t>
   </si>
   <si>
-    <t>Maghreb Fès</t>
-  </si>
-  <si>
-    <t>RSB Berkane</t>
-  </si>
-  <si>
-    <t>New York City II</t>
+    <t>Colegiales</t>
   </si>
   <si>
     <t>CF Os Belenenses</t>
   </si>
   <si>
-    <t>Colegiales</t>
-  </si>
-  <si>
     <t>Atalanta</t>
   </si>
   <si>
+    <t>Atlanta</t>
+  </si>
+  <si>
+    <t>Botafogo</t>
+  </si>
+  <si>
+    <t>Brest</t>
+  </si>
+  <si>
+    <t>Quilmes</t>
+  </si>
+  <si>
+    <t>Strasbourg</t>
+  </si>
+  <si>
     <t>Lille</t>
   </si>
   <si>
+    <t>Club Always Ready</t>
+  </si>
+  <si>
+    <t>Olympique Lyonnais</t>
+  </si>
+  <si>
+    <t>América Mineiro</t>
+  </si>
+  <si>
+    <t>Palmeiras</t>
+  </si>
+  <si>
+    <t>Lorient</t>
+  </si>
+  <si>
+    <t>Nice</t>
+  </si>
+  <si>
     <t>Olympique Marseille</t>
   </si>
   <si>
-    <t>América Mineiro</t>
+    <t>Real Madrid</t>
   </si>
   <si>
     <t>Paris</t>
   </si>
   <si>
-    <t>Olympique Lyonnais</t>
-  </si>
-  <si>
-    <t>Lorient</t>
-  </si>
-  <si>
-    <t>Botafogo</t>
-  </si>
-  <si>
-    <t>Atlanta</t>
-  </si>
-  <si>
-    <t>Palmeiras</t>
-  </si>
-  <si>
-    <t>Quilmes</t>
-  </si>
-  <si>
-    <t>Brest</t>
-  </si>
-  <si>
-    <t>Nice</t>
-  </si>
-  <si>
-    <t>Real Madrid</t>
-  </si>
-  <si>
-    <t>Strasbourg</t>
-  </si>
-  <si>
-    <t>Club Always Ready</t>
+    <t>Patronato</t>
+  </si>
+  <si>
+    <t>Racing Córdoba</t>
   </si>
   <si>
     <t>Ciudad de Bolívar</t>
   </si>
   <si>
-    <t>Patronato</t>
-  </si>
-  <si>
-    <t>Racing Córdoba</t>
+    <t>Real Monarchs</t>
+  </si>
+  <si>
+    <t>Deportivo Madryn</t>
   </si>
   <si>
     <t>LA Galaxy II</t>
   </si>
   <si>
-    <t>Deportivo Madryn</t>
-  </si>
-  <si>
     <t>Utah Royals</t>
   </si>
   <si>
-    <t>Real Monarchs</t>
-  </si>
-  <si>
     <t>FAR Rabat</t>
   </si>
   <si>
@@ -2065,25 +2065,28 @@
     <t>Real Potosí</t>
   </si>
   <si>
+    <t>São Paulo</t>
+  </si>
+  <si>
+    <t>Bragantino</t>
+  </si>
+  <si>
     <t>Chapecoense</t>
   </si>
   <si>
-    <t>São Paulo</t>
-  </si>
-  <si>
-    <t>Bragantino</t>
-  </si>
-  <si>
     <t>Fortaleza</t>
   </si>
   <si>
     <t>Columbus Crew II</t>
   </si>
   <si>
+    <t>Flamengo</t>
+  </si>
+  <si>
     <t>Botafogo SP</t>
   </si>
   <si>
-    <t>Flamengo</t>
+    <t>Austin</t>
   </si>
   <si>
     <t>Orlando City II</t>
@@ -2092,16 +2095,13 @@
     <t>Washington Spirit</t>
   </si>
   <si>
-    <t>Austin</t>
-  </si>
-  <si>
     <t>Macará</t>
   </si>
   <si>
+    <t>Bolívar</t>
+  </si>
+  <si>
     <t>Atlético PR</t>
-  </si>
-  <si>
-    <t>Bolívar</t>
   </si>
   <si>
     <t>Sporting KC II</t>
@@ -2897,13 +2897,13 @@
         <v>699</v>
       </c>
       <c r="P3">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="Q3">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R3">
-        <v>0</v>
+        <v>3.61</v>
       </c>
       <c r="S3">
         <v>0</v>
@@ -3043,7 +3043,7 @@
         <v>61</v>
       </c>
       <c r="C4" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D4" t="s">
         <v>185</v>
@@ -3267,13 +3267,13 @@
         <v>699</v>
       </c>
       <c r="P5">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="Q5">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="R5">
-        <v>3.61</v>
+        <v>0</v>
       </c>
       <c r="S5">
         <v>0</v>
@@ -3413,7 +3413,7 @@
         <v>62</v>
       </c>
       <c r="C6" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D6" t="s">
         <v>185</v>
@@ -3968,10 +3968,10 @@
         <v>63</v>
       </c>
       <c r="C9" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="D9" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E9" t="s">
         <v>195</v>
@@ -4153,10 +4153,10 @@
         <v>63</v>
       </c>
       <c r="C10" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D10" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E10" t="s">
         <v>196</v>
@@ -4338,7 +4338,7 @@
         <v>64</v>
       </c>
       <c r="C11" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D11" t="s">
         <v>185</v>
@@ -4523,7 +4523,7 @@
         <v>64</v>
       </c>
       <c r="C12" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="D12" t="s">
         <v>185</v>
@@ -4708,7 +4708,7 @@
         <v>64</v>
       </c>
       <c r="C13" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D13" t="s">
         <v>185</v>
@@ -6003,10 +6003,10 @@
         <v>68</v>
       </c>
       <c r="C20" t="s">
-        <v>117</v>
+        <v>124</v>
       </c>
       <c r="D20" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E20" t="s">
         <v>206</v>
@@ -6042,13 +6042,13 @@
         <v>699</v>
       </c>
       <c r="P20">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Q20">
-        <v>3.16</v>
+        <v>0</v>
       </c>
       <c r="R20">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="S20">
         <v>0</v>
@@ -6188,7 +6188,7 @@
         <v>68</v>
       </c>
       <c r="C21" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="D21" t="s">
         <v>186</v>
@@ -6373,7 +6373,7 @@
         <v>68</v>
       </c>
       <c r="C22" t="s">
-        <v>119</v>
+        <v>126</v>
       </c>
       <c r="D22" t="s">
         <v>186</v>
@@ -6412,13 +6412,13 @@
         <v>699</v>
       </c>
       <c r="P22">
-        <v>4.98</v>
+        <v>0</v>
       </c>
       <c r="Q22">
-        <v>3.66</v>
+        <v>0</v>
       </c>
       <c r="R22">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="S22">
         <v>0</v>
@@ -6558,7 +6558,7 @@
         <v>68</v>
       </c>
       <c r="C23" t="s">
-        <v>125</v>
+        <v>116</v>
       </c>
       <c r="D23" t="s">
         <v>185</v>
@@ -6597,13 +6597,13 @@
         <v>699</v>
       </c>
       <c r="P23">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Q23">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="R23">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="S23">
         <v>0</v>
@@ -6743,10 +6743,10 @@
         <v>68</v>
       </c>
       <c r="C24" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="D24" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E24" t="s">
         <v>210</v>
@@ -7113,7 +7113,7 @@
         <v>68</v>
       </c>
       <c r="C26" t="s">
-        <v>128</v>
+        <v>119</v>
       </c>
       <c r="D26" t="s">
         <v>186</v>
@@ -7152,13 +7152,13 @@
         <v>699</v>
       </c>
       <c r="P26">
-        <v>0</v>
+        <v>4.98</v>
       </c>
       <c r="Q26">
-        <v>0</v>
+        <v>3.66</v>
       </c>
       <c r="R26">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="S26">
         <v>0</v>
@@ -7298,7 +7298,7 @@
         <v>68</v>
       </c>
       <c r="C27" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D27" t="s">
         <v>186</v>
@@ -7483,7 +7483,7 @@
         <v>68</v>
       </c>
       <c r="C28" t="s">
-        <v>122</v>
+        <v>129</v>
       </c>
       <c r="D28" t="s">
         <v>185</v>
@@ -8077,13 +8077,13 @@
         <v>699</v>
       </c>
       <c r="P31">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Q31">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="R31">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="S31">
         <v>0</v>
@@ -8226,7 +8226,7 @@
         <v>133</v>
       </c>
       <c r="D32" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E32" t="s">
         <v>218</v>
@@ -8262,13 +8262,13 @@
         <v>699</v>
       </c>
       <c r="P32">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="Q32">
-        <v>0</v>
+        <v>3.36</v>
       </c>
       <c r="R32">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="S32">
         <v>0</v>
@@ -8307,10 +8307,10 @@
         <v>0</v>
       </c>
       <c r="AE32">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AF32">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AG32">
         <v>0</v>
@@ -8408,7 +8408,7 @@
         <v>71</v>
       </c>
       <c r="C33" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="D33" t="s">
         <v>186</v>
@@ -8447,13 +8447,13 @@
         <v>699</v>
       </c>
       <c r="P33">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="Q33">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="R33">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="S33">
         <v>0</v>
@@ -8593,10 +8593,10 @@
         <v>71</v>
       </c>
       <c r="C34" t="s">
-        <v>132</v>
+        <v>118</v>
       </c>
       <c r="D34" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E34" t="s">
         <v>220</v>
@@ -8778,7 +8778,7 @@
         <v>71</v>
       </c>
       <c r="C35" t="s">
-        <v>134</v>
+        <v>126</v>
       </c>
       <c r="D35" t="s">
         <v>186</v>
@@ -8817,13 +8817,13 @@
         <v>699</v>
       </c>
       <c r="P35">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Q35">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="R35">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="S35">
         <v>0</v>
@@ -8963,10 +8963,10 @@
         <v>71</v>
       </c>
       <c r="C36" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="D36" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E36" t="s">
         <v>222</v>
@@ -9148,7 +9148,7 @@
         <v>71</v>
       </c>
       <c r="C37" t="s">
-        <v>118</v>
+        <v>129</v>
       </c>
       <c r="D37" t="s">
         <v>185</v>
@@ -9333,7 +9333,7 @@
         <v>71</v>
       </c>
       <c r="C38" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="D38" t="s">
         <v>186</v>
@@ -9372,13 +9372,13 @@
         <v>699</v>
       </c>
       <c r="P38">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="Q38">
-        <v>0</v>
+        <v>4.18</v>
       </c>
       <c r="R38">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="S38">
         <v>0</v>
@@ -9518,10 +9518,10 @@
         <v>71</v>
       </c>
       <c r="C39" t="s">
-        <v>132</v>
+        <v>122</v>
       </c>
       <c r="D39" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E39" t="s">
         <v>225</v>
@@ -9703,7 +9703,7 @@
         <v>71</v>
       </c>
       <c r="C40" t="s">
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="D40" t="s">
         <v>186</v>
@@ -9742,13 +9742,13 @@
         <v>699</v>
       </c>
       <c r="P40">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="Q40">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="R40">
-        <v>0</v>
+        <v>4.35</v>
       </c>
       <c r="S40">
         <v>0</v>
@@ -9888,7 +9888,7 @@
         <v>71</v>
       </c>
       <c r="C41" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="D41" t="s">
         <v>186</v>
@@ -9927,13 +9927,13 @@
         <v>699</v>
       </c>
       <c r="P41">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="Q41">
-        <v>0</v>
+        <v>3.63</v>
       </c>
       <c r="R41">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="S41">
         <v>0</v>
@@ -10073,10 +10073,10 @@
         <v>71</v>
       </c>
       <c r="C42" t="s">
-        <v>125</v>
+        <v>133</v>
       </c>
       <c r="D42" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E42" t="s">
         <v>228</v>
@@ -10112,13 +10112,13 @@
         <v>699</v>
       </c>
       <c r="P42">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="Q42">
-        <v>0</v>
+        <v>6.73</v>
       </c>
       <c r="R42">
-        <v>0</v>
+        <v>10.6</v>
       </c>
       <c r="S42">
         <v>0</v>
@@ -10258,7 +10258,7 @@
         <v>71</v>
       </c>
       <c r="C43" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="D43" t="s">
         <v>186</v>
@@ -10443,10 +10443,10 @@
         <v>71</v>
       </c>
       <c r="C44" t="s">
-        <v>122</v>
+        <v>133</v>
       </c>
       <c r="D44" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E44" t="s">
         <v>230</v>
@@ -10482,13 +10482,13 @@
         <v>699</v>
       </c>
       <c r="P44">
-        <v>0</v>
+        <v>5.09</v>
       </c>
       <c r="Q44">
-        <v>0</v>
+        <v>4.18</v>
       </c>
       <c r="R44">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="S44">
         <v>0</v>
@@ -10628,7 +10628,7 @@
         <v>71</v>
       </c>
       <c r="C45" t="s">
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="D45" t="s">
         <v>186</v>
@@ -10667,13 +10667,13 @@
         <v>699</v>
       </c>
       <c r="P45">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="Q45">
-        <v>0</v>
+        <v>3.61</v>
       </c>
       <c r="R45">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="S45">
         <v>0</v>
@@ -11368,10 +11368,10 @@
         <v>73</v>
       </c>
       <c r="C49" t="s">
-        <v>118</v>
+        <v>138</v>
       </c>
       <c r="D49" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E49" t="s">
         <v>235</v>
@@ -11407,13 +11407,13 @@
         <v>699</v>
       </c>
       <c r="P49">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="Q49">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="R49">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="S49">
         <v>0</v>
@@ -11553,7 +11553,7 @@
         <v>73</v>
       </c>
       <c r="C50" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="D50" t="s">
         <v>186</v>
@@ -11592,13 +11592,13 @@
         <v>699</v>
       </c>
       <c r="P50">
-        <v>1.78</v>
+        <v>2.32</v>
       </c>
       <c r="Q50">
-        <v>4.15</v>
+        <v>3.71</v>
       </c>
       <c r="R50">
-        <v>3.8</v>
+        <v>2.89</v>
       </c>
       <c r="S50">
         <v>0</v>
@@ -11643,10 +11643,10 @@
         <v>0</v>
       </c>
       <c r="AG50">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AH50">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AI50">
         <v>0</v>
@@ -11738,7 +11738,7 @@
         <v>73</v>
       </c>
       <c r="C51" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="D51" t="s">
         <v>185</v>
@@ -11923,10 +11923,10 @@
         <v>73</v>
       </c>
       <c r="C52" t="s">
-        <v>138</v>
+        <v>118</v>
       </c>
       <c r="D52" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E52" t="s">
         <v>238</v>
@@ -11962,13 +11962,13 @@
         <v>699</v>
       </c>
       <c r="P52">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="Q52">
-        <v>3.74</v>
+        <v>0</v>
       </c>
       <c r="R52">
-        <v>2.76</v>
+        <v>0</v>
       </c>
       <c r="S52">
         <v>0</v>
@@ -12108,7 +12108,7 @@
         <v>73</v>
       </c>
       <c r="C53" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="D53" t="s">
         <v>187</v>
@@ -12293,10 +12293,10 @@
         <v>73</v>
       </c>
       <c r="C54" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="D54" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="E54" t="s">
         <v>240</v>
@@ -12332,13 +12332,13 @@
         <v>699</v>
       </c>
       <c r="P54">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="Q54">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="R54">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="S54">
         <v>0</v>
@@ -12478,10 +12478,10 @@
         <v>73</v>
       </c>
       <c r="C55" t="s">
-        <v>141</v>
+        <v>118</v>
       </c>
       <c r="D55" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E55" t="s">
         <v>241</v>
@@ -12663,10 +12663,10 @@
         <v>73</v>
       </c>
       <c r="C56" t="s">
-        <v>118</v>
+        <v>142</v>
       </c>
       <c r="D56" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E56" t="s">
         <v>242</v>
@@ -12848,10 +12848,10 @@
         <v>73</v>
       </c>
       <c r="C57" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="D57" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="E57" t="s">
         <v>243</v>
@@ -12887,13 +12887,13 @@
         <v>699</v>
       </c>
       <c r="P57">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="Q57">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="R57">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="S57">
         <v>0</v>
@@ -13033,7 +13033,7 @@
         <v>73</v>
       </c>
       <c r="C58" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="D58" t="s">
         <v>186</v>
@@ -13072,13 +13072,13 @@
         <v>699</v>
       </c>
       <c r="P58">
-        <v>2.32</v>
+        <v>1.78</v>
       </c>
       <c r="Q58">
-        <v>3.71</v>
+        <v>4.15</v>
       </c>
       <c r="R58">
-        <v>2.89</v>
+        <v>3.8</v>
       </c>
       <c r="S58">
         <v>0</v>
@@ -13123,10 +13123,10 @@
         <v>0</v>
       </c>
       <c r="AG58">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AH58">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AI58">
         <v>0</v>
@@ -13812,13 +13812,13 @@
         <v>699</v>
       </c>
       <c r="P62">
-        <v>2.36</v>
+        <v>2.58</v>
       </c>
       <c r="Q62">
-        <v>3.54</v>
+        <v>3.62</v>
       </c>
       <c r="R62">
-        <v>2.73</v>
+        <v>2.45</v>
       </c>
       <c r="S62">
         <v>0</v>
@@ -13961,7 +13961,7 @@
         <v>145</v>
       </c>
       <c r="D63" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E63" t="s">
         <v>249</v>
@@ -13997,13 +13997,13 @@
         <v>699</v>
       </c>
       <c r="P63">
-        <v>2.58</v>
+        <v>2.35</v>
       </c>
       <c r="Q63">
-        <v>3.62</v>
+        <v>3.35</v>
       </c>
       <c r="R63">
-        <v>2.45</v>
+        <v>2.87</v>
       </c>
       <c r="S63">
         <v>0</v>
@@ -14328,7 +14328,7 @@
         <v>76</v>
       </c>
       <c r="C65" t="s">
-        <v>129</v>
+        <v>121</v>
       </c>
       <c r="D65" t="s">
         <v>186</v>
@@ -14513,10 +14513,10 @@
         <v>76</v>
       </c>
       <c r="C66" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D66" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E66" t="s">
         <v>252</v>
@@ -14552,13 +14552,13 @@
         <v>699</v>
       </c>
       <c r="P66">
-        <v>3.36</v>
+        <v>0</v>
       </c>
       <c r="Q66">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="R66">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="S66">
         <v>0</v>
@@ -14698,7 +14698,7 @@
         <v>76</v>
       </c>
       <c r="C67" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="D67" t="s">
         <v>186</v>
@@ -14737,13 +14737,13 @@
         <v>699</v>
       </c>
       <c r="P67">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="Q67">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="R67">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="S67">
         <v>0</v>
@@ -14883,10 +14883,10 @@
         <v>76</v>
       </c>
       <c r="C68" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="D68" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E68" t="s">
         <v>254</v>
@@ -14922,13 +14922,13 @@
         <v>699</v>
       </c>
       <c r="P68">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="Q68">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="R68">
-        <v>2.87</v>
+        <v>0</v>
       </c>
       <c r="S68">
         <v>0</v>
@@ -15068,7 +15068,7 @@
         <v>76</v>
       </c>
       <c r="C69" t="s">
-        <v>125</v>
+        <v>145</v>
       </c>
       <c r="D69" t="s">
         <v>185</v>
@@ -15107,13 +15107,13 @@
         <v>699</v>
       </c>
       <c r="P69">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="Q69">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R69">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="S69">
         <v>0</v>
@@ -15253,10 +15253,10 @@
         <v>76</v>
       </c>
       <c r="C70" t="s">
-        <v>121</v>
+        <v>129</v>
       </c>
       <c r="D70" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E70" t="s">
         <v>256</v>
@@ -15438,7 +15438,7 @@
         <v>76</v>
       </c>
       <c r="C71" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="D71" t="s">
         <v>186</v>
@@ -15477,13 +15477,13 @@
         <v>699</v>
       </c>
       <c r="P71">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="Q71">
-        <v>7.41</v>
+        <v>0</v>
       </c>
       <c r="R71">
-        <v>17.5</v>
+        <v>0</v>
       </c>
       <c r="S71">
         <v>0</v>
@@ -15623,7 +15623,7 @@
         <v>76</v>
       </c>
       <c r="C72" t="s">
-        <v>148</v>
+        <v>123</v>
       </c>
       <c r="D72" t="s">
         <v>186</v>
@@ -15662,13 +15662,13 @@
         <v>699</v>
       </c>
       <c r="P72">
-        <v>2.46</v>
+        <v>1.21</v>
       </c>
       <c r="Q72">
-        <v>3.43</v>
+        <v>7.41</v>
       </c>
       <c r="R72">
-        <v>2.91</v>
+        <v>17.5</v>
       </c>
       <c r="S72">
         <v>0</v>
@@ -15808,10 +15808,10 @@
         <v>76</v>
       </c>
       <c r="C73" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="D73" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E73" t="s">
         <v>259</v>
@@ -15847,13 +15847,13 @@
         <v>699</v>
       </c>
       <c r="P73">
-        <v>1.92</v>
+        <v>3.36</v>
       </c>
       <c r="Q73">
-        <v>3.4</v>
+        <v>3.65</v>
       </c>
       <c r="R73">
-        <v>3.9</v>
+        <v>1.99</v>
       </c>
       <c r="S73">
         <v>0</v>
@@ -15996,7 +15996,7 @@
         <v>149</v>
       </c>
       <c r="D74" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E74" t="s">
         <v>260</v>
@@ -16032,13 +16032,13 @@
         <v>699</v>
       </c>
       <c r="P74">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="Q74">
-        <v>0</v>
+        <v>3.43</v>
       </c>
       <c r="R74">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="S74">
         <v>0</v>
@@ -16178,7 +16178,7 @@
         <v>77</v>
       </c>
       <c r="C75" t="s">
-        <v>150</v>
+        <v>126</v>
       </c>
       <c r="D75" t="s">
         <v>186</v>
@@ -16363,7 +16363,7 @@
         <v>77</v>
       </c>
       <c r="C76" t="s">
-        <v>128</v>
+        <v>150</v>
       </c>
       <c r="D76" t="s">
         <v>186</v>
@@ -16733,10 +16733,10 @@
         <v>78</v>
       </c>
       <c r="C78" t="s">
-        <v>127</v>
+        <v>151</v>
       </c>
       <c r="D78" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E78" t="s">
         <v>264</v>
@@ -16772,13 +16772,13 @@
         <v>699</v>
       </c>
       <c r="P78">
-        <v>4</v>
+        <v>2.79</v>
       </c>
       <c r="Q78">
-        <v>3.6</v>
+        <v>3.67</v>
       </c>
       <c r="R78">
-        <v>1.83</v>
+        <v>2.41</v>
       </c>
       <c r="S78">
         <v>0</v>
@@ -16918,10 +16918,10 @@
         <v>78</v>
       </c>
       <c r="C79" t="s">
-        <v>151</v>
+        <v>127</v>
       </c>
       <c r="D79" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E79" t="s">
         <v>265</v>
@@ -16957,13 +16957,13 @@
         <v>699</v>
       </c>
       <c r="P79">
-        <v>2.79</v>
+        <v>4</v>
       </c>
       <c r="Q79">
-        <v>3.67</v>
+        <v>3.6</v>
       </c>
       <c r="R79">
-        <v>2.41</v>
+        <v>1.83</v>
       </c>
       <c r="S79">
         <v>0</v>
@@ -17327,13 +17327,13 @@
         <v>699</v>
       </c>
       <c r="P81">
-        <v>2.46</v>
+        <v>2.59</v>
       </c>
       <c r="Q81">
-        <v>3.66</v>
+        <v>3.45</v>
       </c>
       <c r="R81">
-        <v>2.99</v>
+        <v>2.3</v>
       </c>
       <c r="S81">
         <v>0</v>
@@ -17372,10 +17372,10 @@
         <v>0</v>
       </c>
       <c r="AE81">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AF81">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AG81">
         <v>0</v>
@@ -17473,7 +17473,7 @@
         <v>80</v>
       </c>
       <c r="C82" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="D82" t="s">
         <v>186</v>
@@ -17512,13 +17512,13 @@
         <v>699</v>
       </c>
       <c r="P82">
-        <v>5.38</v>
+        <v>0</v>
       </c>
       <c r="Q82">
-        <v>4.37</v>
+        <v>0</v>
       </c>
       <c r="R82">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="S82">
         <v>0</v>
@@ -17658,7 +17658,7 @@
         <v>80</v>
       </c>
       <c r="C83" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="D83" t="s">
         <v>185</v>
@@ -17843,7 +17843,7 @@
         <v>80</v>
       </c>
       <c r="C84" t="s">
-        <v>131</v>
+        <v>153</v>
       </c>
       <c r="D84" t="s">
         <v>186</v>
@@ -17882,13 +17882,13 @@
         <v>699</v>
       </c>
       <c r="P84">
-        <v>2.09</v>
+        <v>5.38</v>
       </c>
       <c r="Q84">
-        <v>3.48</v>
+        <v>4.37</v>
       </c>
       <c r="R84">
-        <v>4.01</v>
+        <v>1.67</v>
       </c>
       <c r="S84">
         <v>0</v>
@@ -17927,10 +17927,10 @@
         <v>0</v>
       </c>
       <c r="AE84">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AF84">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AG84">
         <v>0</v>
@@ -18067,13 +18067,13 @@
         <v>699</v>
       </c>
       <c r="P85">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="Q85">
-        <v>0</v>
+        <v>3.31</v>
       </c>
       <c r="R85">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="S85">
         <v>0</v>
@@ -18112,10 +18112,10 @@
         <v>0</v>
       </c>
       <c r="AE85">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AF85">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AG85">
         <v>0</v>
@@ -18213,7 +18213,7 @@
         <v>80</v>
       </c>
       <c r="C86" t="s">
-        <v>131</v>
+        <v>154</v>
       </c>
       <c r="D86" t="s">
         <v>186</v>
@@ -18252,13 +18252,13 @@
         <v>699</v>
       </c>
       <c r="P86">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Q86">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="R86">
-        <v>4.07</v>
+        <v>0</v>
       </c>
       <c r="S86">
         <v>0</v>
@@ -18297,10 +18297,10 @@
         <v>0</v>
       </c>
       <c r="AE86">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AF86">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AG86">
         <v>0</v>
@@ -18398,7 +18398,7 @@
         <v>80</v>
       </c>
       <c r="C87" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="D87" t="s">
         <v>186</v>
@@ -18583,7 +18583,7 @@
         <v>80</v>
       </c>
       <c r="C88" t="s">
-        <v>152</v>
+        <v>131</v>
       </c>
       <c r="D88" t="s">
         <v>186</v>
@@ -18622,13 +18622,13 @@
         <v>699</v>
       </c>
       <c r="P88">
-        <v>2.69</v>
+        <v>2.1</v>
       </c>
       <c r="Q88">
-        <v>3.31</v>
+        <v>3.42</v>
       </c>
       <c r="R88">
-        <v>2.92</v>
+        <v>4.07</v>
       </c>
       <c r="S88">
         <v>0</v>
@@ -18667,10 +18667,10 @@
         <v>0</v>
       </c>
       <c r="AE88">
-        <v>1.87</v>
+        <v>2.15</v>
       </c>
       <c r="AF88">
-        <v>1.89</v>
+        <v>1.61</v>
       </c>
       <c r="AG88">
         <v>0</v>
@@ -18768,7 +18768,7 @@
         <v>80</v>
       </c>
       <c r="C89" t="s">
-        <v>153</v>
+        <v>125</v>
       </c>
       <c r="D89" t="s">
         <v>186</v>
@@ -18953,10 +18953,10 @@
         <v>80</v>
       </c>
       <c r="C90" t="s">
-        <v>133</v>
+        <v>153</v>
       </c>
       <c r="D90" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E90" t="s">
         <v>276</v>
@@ -18992,13 +18992,13 @@
         <v>699</v>
       </c>
       <c r="P90">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="Q90">
-        <v>0</v>
+        <v>3.66</v>
       </c>
       <c r="R90">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="S90">
         <v>0</v>
@@ -19037,10 +19037,10 @@
         <v>0</v>
       </c>
       <c r="AE90">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AF90">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AG90">
         <v>0</v>
@@ -19138,10 +19138,10 @@
         <v>80</v>
       </c>
       <c r="C91" t="s">
-        <v>155</v>
+        <v>134</v>
       </c>
       <c r="D91" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E91" t="s">
         <v>277</v>
@@ -19177,13 +19177,13 @@
         <v>699</v>
       </c>
       <c r="P91">
-        <v>2.59</v>
+        <v>0</v>
       </c>
       <c r="Q91">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="R91">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="S91">
         <v>0</v>
@@ -19323,7 +19323,7 @@
         <v>80</v>
       </c>
       <c r="C92" t="s">
-        <v>156</v>
+        <v>131</v>
       </c>
       <c r="D92" t="s">
         <v>186</v>
@@ -19362,13 +19362,13 @@
         <v>699</v>
       </c>
       <c r="P92">
-        <v>2.21</v>
+        <v>2.09</v>
       </c>
       <c r="Q92">
-        <v>3.22</v>
+        <v>3.48</v>
       </c>
       <c r="R92">
-        <v>3.22</v>
+        <v>4.01</v>
       </c>
       <c r="S92">
         <v>0</v>
@@ -19407,10 +19407,10 @@
         <v>0</v>
       </c>
       <c r="AE92">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AF92">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AG92">
         <v>0</v>
@@ -19508,7 +19508,7 @@
         <v>80</v>
       </c>
       <c r="C93" t="s">
-        <v>129</v>
+        <v>156</v>
       </c>
       <c r="D93" t="s">
         <v>186</v>
@@ -19547,13 +19547,13 @@
         <v>699</v>
       </c>
       <c r="P93">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="Q93">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="R93">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="S93">
         <v>0</v>
@@ -19693,7 +19693,7 @@
         <v>80</v>
       </c>
       <c r="C94" t="s">
-        <v>150</v>
+        <v>155</v>
       </c>
       <c r="D94" t="s">
         <v>186</v>
@@ -20433,10 +20433,10 @@
         <v>83</v>
       </c>
       <c r="C98" t="s">
-        <v>159</v>
+        <v>135</v>
       </c>
       <c r="D98" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E98" t="s">
         <v>284</v>
@@ -20618,7 +20618,7 @@
         <v>83</v>
       </c>
       <c r="C99" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="D99" t="s">
         <v>186</v>
@@ -20803,10 +20803,10 @@
         <v>83</v>
       </c>
       <c r="C100" t="s">
-        <v>137</v>
+        <v>159</v>
       </c>
       <c r="D100" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E100" t="s">
         <v>286</v>
@@ -21027,13 +21027,13 @@
         <v>699</v>
       </c>
       <c r="P101">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="Q101">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="R101">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="S101">
         <v>0</v>
@@ -21176,7 +21176,7 @@
         <v>161</v>
       </c>
       <c r="D102" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E102" t="s">
         <v>288</v>
@@ -21358,10 +21358,10 @@
         <v>83</v>
       </c>
       <c r="C103" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="D103" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E103" t="s">
         <v>289</v>
@@ -21543,10 +21543,10 @@
         <v>83</v>
       </c>
       <c r="C104" t="s">
-        <v>161</v>
+        <v>139</v>
       </c>
       <c r="D104" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E104" t="s">
         <v>290</v>
@@ -21582,13 +21582,13 @@
         <v>699</v>
       </c>
       <c r="P104">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="Q104">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="R104">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="S104">
         <v>0</v>
@@ -21627,10 +21627,10 @@
         <v>0</v>
       </c>
       <c r="AE104">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AF104">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG104">
         <v>0</v>
@@ -21728,7 +21728,7 @@
         <v>83</v>
       </c>
       <c r="C105" t="s">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="D105" t="s">
         <v>185</v>
@@ -21913,7 +21913,7 @@
         <v>83</v>
       </c>
       <c r="C106" t="s">
-        <v>142</v>
+        <v>161</v>
       </c>
       <c r="D106" t="s">
         <v>186</v>
@@ -21952,13 +21952,13 @@
         <v>699</v>
       </c>
       <c r="P106">
-        <v>2.38</v>
+        <v>3.04</v>
       </c>
       <c r="Q106">
-        <v>3.24</v>
+        <v>3.1</v>
       </c>
       <c r="R106">
-        <v>3.14</v>
+        <v>2.32</v>
       </c>
       <c r="S106">
         <v>0</v>
@@ -21997,10 +21997,10 @@
         <v>0</v>
       </c>
       <c r="AE106">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AF106">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AG106">
         <v>0</v>
@@ -22098,10 +22098,10 @@
         <v>83</v>
       </c>
       <c r="C107" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="D107" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E107" t="s">
         <v>293</v>
@@ -22468,7 +22468,7 @@
         <v>84</v>
       </c>
       <c r="C109" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="D109" t="s">
         <v>186</v>
@@ -22653,7 +22653,7 @@
         <v>84</v>
       </c>
       <c r="C110" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="D110" t="s">
         <v>186</v>
@@ -22838,7 +22838,7 @@
         <v>85</v>
       </c>
       <c r="C111" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="D111" t="s">
         <v>186</v>
@@ -23026,7 +23026,7 @@
         <v>147</v>
       </c>
       <c r="D112" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E112" t="s">
         <v>298</v>
@@ -23062,13 +23062,13 @@
         <v>699</v>
       </c>
       <c r="P112">
-        <v>2.27</v>
+        <v>1.85</v>
       </c>
       <c r="Q112">
-        <v>3.58</v>
+        <v>4.05</v>
       </c>
       <c r="R112">
-        <v>2.88</v>
+        <v>3.57</v>
       </c>
       <c r="S112">
         <v>0</v>
@@ -23113,10 +23113,10 @@
         <v>0</v>
       </c>
       <c r="AG112">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AH112">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AI112">
         <v>0</v>
@@ -23208,10 +23208,10 @@
         <v>85</v>
       </c>
       <c r="C113" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="D113" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E113" t="s">
         <v>299</v>
@@ -23247,13 +23247,13 @@
         <v>699</v>
       </c>
       <c r="P113">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="Q113">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="R113">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="S113">
         <v>0</v>
@@ -23393,7 +23393,7 @@
         <v>85</v>
       </c>
       <c r="C114" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="D114" t="s">
         <v>186</v>
@@ -23432,13 +23432,13 @@
         <v>699</v>
       </c>
       <c r="P114">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="Q114">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="R114">
-        <v>3.57</v>
+        <v>0</v>
       </c>
       <c r="S114">
         <v>0</v>
@@ -23483,10 +23483,10 @@
         <v>0</v>
       </c>
       <c r="AG114">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AH114">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AI114">
         <v>0</v>
@@ -23802,13 +23802,13 @@
         <v>699</v>
       </c>
       <c r="P116">
-        <v>2.78</v>
+        <v>1.44</v>
       </c>
       <c r="Q116">
-        <v>3.89</v>
+        <v>5.14</v>
       </c>
       <c r="R116">
-        <v>2.36</v>
+        <v>6.53</v>
       </c>
       <c r="S116">
         <v>0</v>
@@ -23853,10 +23853,10 @@
         <v>0</v>
       </c>
       <c r="AG116">
-        <v>2.05</v>
+        <v>1.93</v>
       </c>
       <c r="AH116">
-        <v>1.68</v>
+        <v>1.77</v>
       </c>
       <c r="AI116">
         <v>0</v>
@@ -23987,61 +23987,61 @@
         <v>699</v>
       </c>
       <c r="P117">
-        <v>4.48</v>
+        <v>1.71</v>
       </c>
       <c r="Q117">
-        <v>4.74</v>
+        <v>4.37</v>
       </c>
       <c r="R117">
+        <v>4.42</v>
+      </c>
+      <c r="S117">
+        <v>0</v>
+      </c>
+      <c r="T117">
+        <v>0</v>
+      </c>
+      <c r="U117">
+        <v>0</v>
+      </c>
+      <c r="V117">
+        <v>0</v>
+      </c>
+      <c r="W117">
+        <v>0</v>
+      </c>
+      <c r="X117">
+        <v>0</v>
+      </c>
+      <c r="Y117">
+        <v>0</v>
+      </c>
+      <c r="Z117">
+        <v>0</v>
+      </c>
+      <c r="AA117">
+        <v>0</v>
+      </c>
+      <c r="AB117">
+        <v>0</v>
+      </c>
+      <c r="AC117">
+        <v>0</v>
+      </c>
+      <c r="AD117">
+        <v>0</v>
+      </c>
+      <c r="AE117">
+        <v>0</v>
+      </c>
+      <c r="AF117">
+        <v>0</v>
+      </c>
+      <c r="AG117">
+        <v>2.1</v>
+      </c>
+      <c r="AH117">
         <v>1.65</v>
-      </c>
-      <c r="S117">
-        <v>0</v>
-      </c>
-      <c r="T117">
-        <v>0</v>
-      </c>
-      <c r="U117">
-        <v>0</v>
-      </c>
-      <c r="V117">
-        <v>0</v>
-      </c>
-      <c r="W117">
-        <v>0</v>
-      </c>
-      <c r="X117">
-        <v>0</v>
-      </c>
-      <c r="Y117">
-        <v>0</v>
-      </c>
-      <c r="Z117">
-        <v>0</v>
-      </c>
-      <c r="AA117">
-        <v>0</v>
-      </c>
-      <c r="AB117">
-        <v>0</v>
-      </c>
-      <c r="AC117">
-        <v>0</v>
-      </c>
-      <c r="AD117">
-        <v>0</v>
-      </c>
-      <c r="AE117">
-        <v>0</v>
-      </c>
-      <c r="AF117">
-        <v>0</v>
-      </c>
-      <c r="AG117">
-        <v>1.68</v>
-      </c>
-      <c r="AH117">
-        <v>2.05</v>
       </c>
       <c r="AI117">
         <v>0</v>
@@ -24172,13 +24172,13 @@
         <v>699</v>
       </c>
       <c r="P118">
-        <v>1.96</v>
+        <v>2.78</v>
       </c>
       <c r="Q118">
-        <v>4.05</v>
+        <v>3.89</v>
       </c>
       <c r="R118">
-        <v>3.5</v>
+        <v>2.36</v>
       </c>
       <c r="S118">
         <v>0</v>
@@ -24223,10 +24223,10 @@
         <v>0</v>
       </c>
       <c r="AG118">
-        <v>2.2</v>
+        <v>2.05</v>
       </c>
       <c r="AH118">
-        <v>1.58</v>
+        <v>1.68</v>
       </c>
       <c r="AI118">
         <v>0</v>
@@ -24357,13 +24357,13 @@
         <v>699</v>
       </c>
       <c r="P119">
-        <v>1.44</v>
+        <v>1.96</v>
       </c>
       <c r="Q119">
-        <v>5.14</v>
+        <v>4.05</v>
       </c>
       <c r="R119">
-        <v>6.53</v>
+        <v>3.5</v>
       </c>
       <c r="S119">
         <v>0</v>
@@ -24408,10 +24408,10 @@
         <v>0</v>
       </c>
       <c r="AG119">
-        <v>1.93</v>
+        <v>2.2</v>
       </c>
       <c r="AH119">
-        <v>1.77</v>
+        <v>1.58</v>
       </c>
       <c r="AI119">
         <v>0</v>
@@ -24542,13 +24542,13 @@
         <v>699</v>
       </c>
       <c r="P120">
-        <v>1.77</v>
+        <v>4.48</v>
       </c>
       <c r="Q120">
-        <v>4.17</v>
+        <v>4.74</v>
       </c>
       <c r="R120">
-        <v>4.22</v>
+        <v>1.65</v>
       </c>
       <c r="S120">
         <v>0</v>
@@ -24587,16 +24587,16 @@
         <v>0</v>
       </c>
       <c r="AE120">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AF120">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AG120">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AH120">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AI120">
         <v>0</v>
@@ -24727,13 +24727,13 @@
         <v>699</v>
       </c>
       <c r="P121">
-        <v>2.49</v>
+        <v>1.78</v>
       </c>
       <c r="Q121">
-        <v>3.77</v>
+        <v>4.17</v>
       </c>
       <c r="R121">
-        <v>2.67</v>
+        <v>4.17</v>
       </c>
       <c r="S121">
         <v>0</v>
@@ -24772,16 +24772,16 @@
         <v>0</v>
       </c>
       <c r="AE121">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AF121">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AG121">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AH121">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AI121">
         <v>0</v>
@@ -24912,13 +24912,13 @@
         <v>699</v>
       </c>
       <c r="P122">
-        <v>1.71</v>
+        <v>1.48</v>
       </c>
       <c r="Q122">
-        <v>4.37</v>
+        <v>4.94</v>
       </c>
       <c r="R122">
-        <v>4.42</v>
+        <v>6.07</v>
       </c>
       <c r="S122">
         <v>0</v>
@@ -24963,10 +24963,10 @@
         <v>0</v>
       </c>
       <c r="AG122">
-        <v>2.1</v>
+        <v>1.98</v>
       </c>
       <c r="AH122">
-        <v>1.65</v>
+        <v>1.72</v>
       </c>
       <c r="AI122">
         <v>0</v>
@@ -25097,13 +25097,13 @@
         <v>699</v>
       </c>
       <c r="P123">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="Q123">
         <v>4.17</v>
       </c>
       <c r="R123">
-        <v>4.17</v>
+        <v>4.22</v>
       </c>
       <c r="S123">
         <v>0</v>
@@ -25142,16 +25142,16 @@
         <v>0</v>
       </c>
       <c r="AE123">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AF123">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AG123">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AH123">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AI123">
         <v>0</v>
@@ -25282,13 +25282,13 @@
         <v>699</v>
       </c>
       <c r="P124">
-        <v>1.48</v>
+        <v>2.49</v>
       </c>
       <c r="Q124">
-        <v>4.94</v>
+        <v>3.77</v>
       </c>
       <c r="R124">
-        <v>6.07</v>
+        <v>2.67</v>
       </c>
       <c r="S124">
         <v>0</v>
@@ -25327,16 +25327,16 @@
         <v>0</v>
       </c>
       <c r="AE124">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AF124">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AG124">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AH124">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AI124">
         <v>0</v>
@@ -25437,7 +25437,7 @@
         <v>311</v>
       </c>
       <c r="F125" t="s">
-        <v>289</v>
+        <v>567</v>
       </c>
       <c r="G125">
         <v>0</v>
@@ -25613,7 +25613,7 @@
         <v>87</v>
       </c>
       <c r="C126" t="s">
-        <v>120</v>
+        <v>164</v>
       </c>
       <c r="D126" t="s">
         <v>186</v>
@@ -25622,7 +25622,7 @@
         <v>312</v>
       </c>
       <c r="F126" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="G126">
         <v>0</v>
@@ -25798,7 +25798,7 @@
         <v>87</v>
       </c>
       <c r="C127" t="s">
-        <v>158</v>
+        <v>165</v>
       </c>
       <c r="D127" t="s">
         <v>186</v>
@@ -25807,7 +25807,7 @@
         <v>313</v>
       </c>
       <c r="F127" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="G127">
         <v>0</v>
@@ -25837,13 +25837,13 @@
         <v>699</v>
       </c>
       <c r="P127">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Q127">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="R127">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="S127">
         <v>0</v>
@@ -25983,7 +25983,7 @@
         <v>87</v>
       </c>
       <c r="C128" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="D128" t="s">
         <v>186</v>
@@ -25992,7 +25992,7 @@
         <v>314</v>
       </c>
       <c r="F128" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="G128">
         <v>0</v>
@@ -26177,7 +26177,7 @@
         <v>315</v>
       </c>
       <c r="F129" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="G129">
         <v>0</v>
@@ -26362,7 +26362,7 @@
         <v>316</v>
       </c>
       <c r="F130" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="G130">
         <v>0</v>
@@ -26538,7 +26538,7 @@
         <v>87</v>
       </c>
       <c r="C131" t="s">
-        <v>163</v>
+        <v>125</v>
       </c>
       <c r="D131" t="s">
         <v>186</v>
@@ -26547,7 +26547,7 @@
         <v>317</v>
       </c>
       <c r="F131" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="G131">
         <v>0</v>
@@ -26723,7 +26723,7 @@
         <v>87</v>
       </c>
       <c r="C132" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="D132" t="s">
         <v>186</v>
@@ -26732,7 +26732,7 @@
         <v>318</v>
       </c>
       <c r="F132" t="s">
-        <v>573</v>
+        <v>288</v>
       </c>
       <c r="G132">
         <v>0</v>
@@ -26908,10 +26908,10 @@
         <v>87</v>
       </c>
       <c r="C133" t="s">
-        <v>164</v>
+        <v>151</v>
       </c>
       <c r="D133" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E133" t="s">
         <v>319</v>
@@ -26947,13 +26947,13 @@
         <v>699</v>
       </c>
       <c r="P133">
-        <v>0</v>
+        <v>3.87</v>
       </c>
       <c r="Q133">
-        <v>0</v>
+        <v>3.87</v>
       </c>
       <c r="R133">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="S133">
         <v>0</v>
@@ -27093,10 +27093,10 @@
         <v>87</v>
       </c>
       <c r="C134" t="s">
-        <v>164</v>
+        <v>151</v>
       </c>
       <c r="D134" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E134" t="s">
         <v>320</v>
@@ -27132,13 +27132,13 @@
         <v>699</v>
       </c>
       <c r="P134">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="Q134">
-        <v>0</v>
+        <v>3.82</v>
       </c>
       <c r="R134">
-        <v>0</v>
+        <v>4.13</v>
       </c>
       <c r="S134">
         <v>0</v>
@@ -27278,10 +27278,10 @@
         <v>87</v>
       </c>
       <c r="C135" t="s">
-        <v>143</v>
+        <v>151</v>
       </c>
       <c r="D135" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E135" t="s">
         <v>321</v>
@@ -27317,13 +27317,13 @@
         <v>699</v>
       </c>
       <c r="P135">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="Q135">
-        <v>0</v>
+        <v>4.44</v>
       </c>
       <c r="R135">
-        <v>0</v>
+        <v>5.16</v>
       </c>
       <c r="S135">
         <v>0</v>
@@ -27463,7 +27463,7 @@
         <v>87</v>
       </c>
       <c r="C136" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="D136" t="s">
         <v>186</v>
@@ -27648,7 +27648,7 @@
         <v>87</v>
       </c>
       <c r="C137" t="s">
-        <v>127</v>
+        <v>164</v>
       </c>
       <c r="D137" t="s">
         <v>186</v>
@@ -27833,7 +27833,7 @@
         <v>87</v>
       </c>
       <c r="C138" t="s">
-        <v>158</v>
+        <v>120</v>
       </c>
       <c r="D138" t="s">
         <v>186</v>
@@ -28018,7 +28018,7 @@
         <v>87</v>
       </c>
       <c r="C139" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="D139" t="s">
         <v>185</v>
@@ -28057,13 +28057,13 @@
         <v>699</v>
       </c>
       <c r="P139">
-        <v>4.07</v>
+        <v>2.2</v>
       </c>
       <c r="Q139">
-        <v>3.9</v>
+        <v>3.4</v>
       </c>
       <c r="R139">
-        <v>1.78</v>
+        <v>3.2</v>
       </c>
       <c r="S139">
         <v>0</v>
@@ -28203,7 +28203,7 @@
         <v>87</v>
       </c>
       <c r="C140" t="s">
-        <v>158</v>
+        <v>164</v>
       </c>
       <c r="D140" t="s">
         <v>186</v>
@@ -28388,7 +28388,7 @@
         <v>87</v>
       </c>
       <c r="C141" t="s">
-        <v>166</v>
+        <v>127</v>
       </c>
       <c r="D141" t="s">
         <v>186</v>
@@ -28427,13 +28427,13 @@
         <v>699</v>
       </c>
       <c r="P141">
-        <v>2.3</v>
+        <v>2.55</v>
       </c>
       <c r="Q141">
-        <v>3.35</v>
+        <v>3.6</v>
       </c>
       <c r="R141">
-        <v>2.96</v>
+        <v>2.43</v>
       </c>
       <c r="S141">
         <v>0</v>
@@ -28573,10 +28573,10 @@
         <v>87</v>
       </c>
       <c r="C142" t="s">
-        <v>158</v>
+        <v>146</v>
       </c>
       <c r="D142" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E142" t="s">
         <v>328</v>
@@ -28758,7 +28758,7 @@
         <v>87</v>
       </c>
       <c r="C143" t="s">
-        <v>124</v>
+        <v>160</v>
       </c>
       <c r="D143" t="s">
         <v>186</v>
@@ -28943,7 +28943,7 @@
         <v>87</v>
       </c>
       <c r="C144" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="D144" t="s">
         <v>185</v>
@@ -28982,13 +28982,13 @@
         <v>699</v>
       </c>
       <c r="P144">
-        <v>2.2</v>
+        <v>3.1</v>
       </c>
       <c r="Q144">
-        <v>3.4</v>
+        <v>3.7</v>
       </c>
       <c r="R144">
-        <v>3.2</v>
+        <v>2.12</v>
       </c>
       <c r="S144">
         <v>0</v>
@@ -29128,7 +29128,7 @@
         <v>87</v>
       </c>
       <c r="C145" t="s">
-        <v>151</v>
+        <v>166</v>
       </c>
       <c r="D145" t="s">
         <v>185</v>
@@ -29167,13 +29167,13 @@
         <v>699</v>
       </c>
       <c r="P145">
-        <v>1.84</v>
+        <v>2.15</v>
       </c>
       <c r="Q145">
-        <v>3.82</v>
+        <v>3.7</v>
       </c>
       <c r="R145">
-        <v>4.13</v>
+        <v>3.01</v>
       </c>
       <c r="S145">
         <v>0</v>
@@ -29313,7 +29313,7 @@
         <v>87</v>
       </c>
       <c r="C146" t="s">
-        <v>151</v>
+        <v>166</v>
       </c>
       <c r="D146" t="s">
         <v>185</v>
@@ -29352,13 +29352,13 @@
         <v>699</v>
       </c>
       <c r="P146">
-        <v>1.59</v>
+        <v>4.07</v>
       </c>
       <c r="Q146">
-        <v>4.44</v>
+        <v>3.9</v>
       </c>
       <c r="R146">
-        <v>5.16</v>
+        <v>1.78</v>
       </c>
       <c r="S146">
         <v>0</v>
@@ -29498,7 +29498,7 @@
         <v>87</v>
       </c>
       <c r="C147" t="s">
-        <v>149</v>
+        <v>166</v>
       </c>
       <c r="D147" t="s">
         <v>185</v>
@@ -29537,13 +29537,13 @@
         <v>699</v>
       </c>
       <c r="P147">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="Q147">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R147">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="S147">
         <v>0</v>
@@ -29683,7 +29683,7 @@
         <v>87</v>
       </c>
       <c r="C148" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="D148" t="s">
         <v>185</v>
@@ -29722,13 +29722,13 @@
         <v>699</v>
       </c>
       <c r="P148">
-        <v>3.1</v>
+        <v>5.4</v>
       </c>
       <c r="Q148">
-        <v>3.7</v>
+        <v>4.6</v>
       </c>
       <c r="R148">
-        <v>2.12</v>
+        <v>1.51</v>
       </c>
       <c r="S148">
         <v>0</v>
@@ -29868,10 +29868,10 @@
         <v>87</v>
       </c>
       <c r="C149" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="D149" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E149" t="s">
         <v>335</v>
@@ -29907,13 +29907,13 @@
         <v>699</v>
       </c>
       <c r="P149">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Q149">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="R149">
-        <v>3.01</v>
+        <v>0</v>
       </c>
       <c r="S149">
         <v>0</v>
@@ -30053,10 +30053,10 @@
         <v>87</v>
       </c>
       <c r="C150" t="s">
-        <v>151</v>
+        <v>124</v>
       </c>
       <c r="D150" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E150" t="s">
         <v>336</v>
@@ -30092,13 +30092,13 @@
         <v>699</v>
       </c>
       <c r="P150">
-        <v>3.87</v>
+        <v>0</v>
       </c>
       <c r="Q150">
-        <v>3.87</v>
+        <v>0</v>
       </c>
       <c r="R150">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="S150">
         <v>0</v>
@@ -30238,10 +30238,10 @@
         <v>87</v>
       </c>
       <c r="C151" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="D151" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E151" t="s">
         <v>337</v>
@@ -30277,13 +30277,13 @@
         <v>699</v>
       </c>
       <c r="P151">
-        <v>5.4</v>
+        <v>0</v>
       </c>
       <c r="Q151">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="R151">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="S151">
         <v>0</v>
@@ -30423,7 +30423,7 @@
         <v>87</v>
       </c>
       <c r="C152" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="D152" t="s">
         <v>186</v>
@@ -30608,7 +30608,7 @@
         <v>87</v>
       </c>
       <c r="C153" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="D153" t="s">
         <v>186</v>
@@ -30793,7 +30793,7 @@
         <v>87</v>
       </c>
       <c r="C154" t="s">
-        <v>129</v>
+        <v>160</v>
       </c>
       <c r="D154" t="s">
         <v>186</v>
@@ -30978,7 +30978,7 @@
         <v>87</v>
       </c>
       <c r="C155" t="s">
-        <v>158</v>
+        <v>143</v>
       </c>
       <c r="D155" t="s">
         <v>186</v>
@@ -31163,10 +31163,10 @@
         <v>87</v>
       </c>
       <c r="C156" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="D156" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E156" t="s">
         <v>342</v>
@@ -31202,13 +31202,13 @@
         <v>699</v>
       </c>
       <c r="P156">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="Q156">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R156">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="S156">
         <v>0</v>
@@ -32088,7 +32088,7 @@
         <v>89</v>
       </c>
       <c r="C161" t="s">
-        <v>152</v>
+        <v>157</v>
       </c>
       <c r="D161" t="s">
         <v>186</v>
@@ -32127,13 +32127,13 @@
         <v>699</v>
       </c>
       <c r="P161">
-        <v>5.17</v>
+        <v>1.78</v>
       </c>
       <c r="Q161">
-        <v>4.37</v>
+        <v>4.32</v>
       </c>
       <c r="R161">
-        <v>1.69</v>
+        <v>4.52</v>
       </c>
       <c r="S161">
         <v>0</v>
@@ -32172,16 +32172,16 @@
         <v>0</v>
       </c>
       <c r="AE161">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AF161">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AG161">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AH161">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AI161">
         <v>0</v>
@@ -32273,7 +32273,7 @@
         <v>89</v>
       </c>
       <c r="C162" t="s">
-        <v>168</v>
+        <v>130</v>
       </c>
       <c r="D162" t="s">
         <v>186</v>
@@ -32312,13 +32312,13 @@
         <v>699</v>
       </c>
       <c r="P162">
-        <v>0</v>
+        <v>4.09</v>
       </c>
       <c r="Q162">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="R162">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="S162">
         <v>0</v>
@@ -32643,7 +32643,7 @@
         <v>89</v>
       </c>
       <c r="C164" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="D164" t="s">
         <v>186</v>
@@ -32682,13 +32682,13 @@
         <v>699</v>
       </c>
       <c r="P164">
-        <v>1.78</v>
+        <v>5.17</v>
       </c>
       <c r="Q164">
-        <v>4.32</v>
+        <v>4.37</v>
       </c>
       <c r="R164">
-        <v>4.52</v>
+        <v>1.69</v>
       </c>
       <c r="S164">
         <v>0</v>
@@ -32727,16 +32727,16 @@
         <v>0</v>
       </c>
       <c r="AE164">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AF164">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AG164">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AH164">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AI164">
         <v>0</v>
@@ -32828,7 +32828,7 @@
         <v>89</v>
       </c>
       <c r="C165" t="s">
-        <v>130</v>
+        <v>168</v>
       </c>
       <c r="D165" t="s">
         <v>186</v>
@@ -32867,13 +32867,13 @@
         <v>699</v>
       </c>
       <c r="P165">
-        <v>4.09</v>
+        <v>0</v>
       </c>
       <c r="Q165">
-        <v>3.78</v>
+        <v>0</v>
       </c>
       <c r="R165">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="S165">
         <v>0</v>
@@ -33013,10 +33013,10 @@
         <v>90</v>
       </c>
       <c r="C166" t="s">
-        <v>135</v>
+        <v>120</v>
       </c>
       <c r="D166" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E166" t="s">
         <v>352</v>
@@ -33383,7 +33383,7 @@
         <v>90</v>
       </c>
       <c r="C168" t="s">
-        <v>169</v>
+        <v>156</v>
       </c>
       <c r="D168" t="s">
         <v>186</v>
@@ -33422,13 +33422,13 @@
         <v>699</v>
       </c>
       <c r="P168">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="Q168">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R168">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="S168">
         <v>0</v>
@@ -33568,7 +33568,7 @@
         <v>90</v>
       </c>
       <c r="C169" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="D169" t="s">
         <v>186</v>
@@ -33753,7 +33753,7 @@
         <v>90</v>
       </c>
       <c r="C170" t="s">
-        <v>169</v>
+        <v>131</v>
       </c>
       <c r="D170" t="s">
         <v>186</v>
@@ -33792,13 +33792,13 @@
         <v>699</v>
       </c>
       <c r="P170">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="Q170">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R170">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="S170">
         <v>0</v>
@@ -33938,7 +33938,7 @@
         <v>90</v>
       </c>
       <c r="C171" t="s">
-        <v>120</v>
+        <v>169</v>
       </c>
       <c r="D171" t="s">
         <v>186</v>
@@ -34123,10 +34123,10 @@
         <v>90</v>
       </c>
       <c r="C172" t="s">
-        <v>169</v>
+        <v>135</v>
       </c>
       <c r="D172" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E172" t="s">
         <v>358</v>
@@ -34308,7 +34308,7 @@
         <v>90</v>
       </c>
       <c r="C173" t="s">
-        <v>156</v>
+        <v>169</v>
       </c>
       <c r="D173" t="s">
         <v>186</v>
@@ -34347,13 +34347,13 @@
         <v>699</v>
       </c>
       <c r="P173">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="Q173">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="R173">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="S173">
         <v>0</v>
@@ -34493,7 +34493,7 @@
         <v>90</v>
       </c>
       <c r="C174" t="s">
-        <v>131</v>
+        <v>170</v>
       </c>
       <c r="D174" t="s">
         <v>186</v>
@@ -34532,13 +34532,13 @@
         <v>699</v>
       </c>
       <c r="P174">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="Q174">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="R174">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="S174">
         <v>0</v>
@@ -34863,7 +34863,7 @@
         <v>90</v>
       </c>
       <c r="C176" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="D176" t="s">
         <v>186</v>
@@ -35418,7 +35418,7 @@
         <v>92</v>
       </c>
       <c r="C179" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="D179" t="s">
         <v>185</v>
@@ -35603,7 +35603,7 @@
         <v>92</v>
       </c>
       <c r="C180" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="D180" t="s">
         <v>186</v>
@@ -35788,7 +35788,7 @@
         <v>92</v>
       </c>
       <c r="C181" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="D181" t="s">
         <v>185</v>
@@ -35973,7 +35973,7 @@
         <v>93</v>
       </c>
       <c r="C182" t="s">
-        <v>148</v>
+        <v>172</v>
       </c>
       <c r="D182" t="s">
         <v>186</v>
@@ -36012,13 +36012,13 @@
         <v>699</v>
       </c>
       <c r="P182">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="Q182">
-        <v>3.53</v>
+        <v>0</v>
       </c>
       <c r="R182">
-        <v>3.91</v>
+        <v>0</v>
       </c>
       <c r="S182">
         <v>0</v>
@@ -36057,10 +36057,10 @@
         <v>0</v>
       </c>
       <c r="AE182">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AF182">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AG182">
         <v>0</v>
@@ -36158,7 +36158,7 @@
         <v>93</v>
       </c>
       <c r="C183" t="s">
-        <v>123</v>
+        <v>172</v>
       </c>
       <c r="D183" t="s">
         <v>186</v>
@@ -36197,13 +36197,13 @@
         <v>699</v>
       </c>
       <c r="P183">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Q183">
-        <v>3.66</v>
+        <v>0</v>
       </c>
       <c r="R183">
-        <v>3.36</v>
+        <v>0</v>
       </c>
       <c r="S183">
         <v>0</v>
@@ -36343,7 +36343,7 @@
         <v>93</v>
       </c>
       <c r="C184" t="s">
-        <v>172</v>
+        <v>161</v>
       </c>
       <c r="D184" t="s">
         <v>186</v>
@@ -36382,13 +36382,13 @@
         <v>699</v>
       </c>
       <c r="P184">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="Q184">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R184">
-        <v>0</v>
+        <v>4.56</v>
       </c>
       <c r="S184">
         <v>0</v>
@@ -36528,7 +36528,7 @@
         <v>93</v>
       </c>
       <c r="C185" t="s">
-        <v>172</v>
+        <v>161</v>
       </c>
       <c r="D185" t="s">
         <v>186</v>
@@ -36567,13 +36567,13 @@
         <v>699</v>
       </c>
       <c r="P185">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="Q185">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="R185">
-        <v>0</v>
+        <v>6.76</v>
       </c>
       <c r="S185">
         <v>0</v>
@@ -36713,7 +36713,7 @@
         <v>93</v>
       </c>
       <c r="C186" t="s">
-        <v>153</v>
+        <v>139</v>
       </c>
       <c r="D186" t="s">
         <v>186</v>
@@ -36752,13 +36752,13 @@
         <v>699</v>
       </c>
       <c r="P186">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Q186">
-        <v>0</v>
+        <v>5.66</v>
       </c>
       <c r="R186">
-        <v>0</v>
+        <v>8.98</v>
       </c>
       <c r="S186">
         <v>0</v>
@@ -36898,10 +36898,10 @@
         <v>93</v>
       </c>
       <c r="C187" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="D187" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E187" t="s">
         <v>373</v>
@@ -37268,7 +37268,7 @@
         <v>93</v>
       </c>
       <c r="C189" t="s">
-        <v>160</v>
+        <v>123</v>
       </c>
       <c r="D189" t="s">
         <v>186</v>
@@ -37307,13 +37307,13 @@
         <v>699</v>
       </c>
       <c r="P189">
-        <v>1.82</v>
+        <v>2.25</v>
       </c>
       <c r="Q189">
-        <v>3.1</v>
+        <v>3.66</v>
       </c>
       <c r="R189">
-        <v>4.56</v>
+        <v>3.36</v>
       </c>
       <c r="S189">
         <v>0</v>
@@ -37453,7 +37453,7 @@
         <v>93</v>
       </c>
       <c r="C190" t="s">
-        <v>142</v>
+        <v>155</v>
       </c>
       <c r="D190" t="s">
         <v>186</v>
@@ -37492,13 +37492,13 @@
         <v>699</v>
       </c>
       <c r="P190">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="Q190">
-        <v>5.66</v>
+        <v>0</v>
       </c>
       <c r="R190">
-        <v>8.98</v>
+        <v>0</v>
       </c>
       <c r="S190">
         <v>0</v>
@@ -37638,10 +37638,10 @@
         <v>93</v>
       </c>
       <c r="C191" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="D191" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E191" t="s">
         <v>377</v>
@@ -37823,7 +37823,7 @@
         <v>93</v>
       </c>
       <c r="C192" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="D192" t="s">
         <v>186</v>
@@ -38008,7 +38008,7 @@
         <v>93</v>
       </c>
       <c r="C193" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="D193" t="s">
         <v>186</v>
@@ -38047,13 +38047,13 @@
         <v>699</v>
       </c>
       <c r="P193">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="Q193">
-        <v>0</v>
+        <v>3.53</v>
       </c>
       <c r="R193">
-        <v>0</v>
+        <v>3.91</v>
       </c>
       <c r="S193">
         <v>0</v>
@@ -38092,10 +38092,10 @@
         <v>0</v>
       </c>
       <c r="AE193">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AF193">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AG193">
         <v>0</v>
@@ -38193,10 +38193,10 @@
         <v>93</v>
       </c>
       <c r="C194" t="s">
-        <v>160</v>
+        <v>174</v>
       </c>
       <c r="D194" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E194" t="s">
         <v>380</v>
@@ -38232,13 +38232,13 @@
         <v>699</v>
       </c>
       <c r="P194">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="Q194">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="R194">
-        <v>6.76</v>
+        <v>0</v>
       </c>
       <c r="S194">
         <v>0</v>
@@ -38378,10 +38378,10 @@
         <v>93</v>
       </c>
       <c r="C195" t="s">
-        <v>173</v>
+        <v>148</v>
       </c>
       <c r="D195" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E195" t="s">
         <v>381</v>
@@ -39118,7 +39118,7 @@
         <v>94</v>
       </c>
       <c r="C199" t="s">
-        <v>124</v>
+        <v>175</v>
       </c>
       <c r="D199" t="s">
         <v>186</v>
@@ -39303,10 +39303,10 @@
         <v>94</v>
       </c>
       <c r="C200" t="s">
-        <v>158</v>
+        <v>146</v>
       </c>
       <c r="D200" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E200" t="s">
         <v>386</v>
@@ -39488,7 +39488,7 @@
         <v>94</v>
       </c>
       <c r="C201" t="s">
-        <v>158</v>
+        <v>124</v>
       </c>
       <c r="D201" t="s">
         <v>186</v>
@@ -39673,7 +39673,7 @@
         <v>94</v>
       </c>
       <c r="C202" t="s">
-        <v>175</v>
+        <v>160</v>
       </c>
       <c r="D202" t="s">
         <v>186</v>
@@ -40043,10 +40043,10 @@
         <v>94</v>
       </c>
       <c r="C204" t="s">
-        <v>149</v>
+        <v>160</v>
       </c>
       <c r="D204" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E204" t="s">
         <v>390</v>
@@ -40228,7 +40228,7 @@
         <v>95</v>
       </c>
       <c r="C205" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="D205" t="s">
         <v>186</v>
@@ -40267,13 +40267,13 @@
         <v>699</v>
       </c>
       <c r="P205">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="Q205">
-        <v>0</v>
+        <v>4.08</v>
       </c>
       <c r="R205">
-        <v>0</v>
+        <v>3.77</v>
       </c>
       <c r="S205">
         <v>0</v>
@@ -40318,10 +40318,10 @@
         <v>0</v>
       </c>
       <c r="AG205">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AH205">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AI205">
         <v>0</v>
@@ -40413,7 +40413,7 @@
         <v>96</v>
       </c>
       <c r="C206" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="D206" t="s">
         <v>186</v>
@@ -40783,10 +40783,10 @@
         <v>97</v>
       </c>
       <c r="C208" t="s">
-        <v>171</v>
+        <v>177</v>
       </c>
       <c r="D208" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E208" t="s">
         <v>394</v>
@@ -41338,10 +41338,10 @@
         <v>97</v>
       </c>
       <c r="C211" t="s">
-        <v>177</v>
+        <v>171</v>
       </c>
       <c r="D211" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E211" t="s">
         <v>397</v>
@@ -41523,10 +41523,10 @@
         <v>98</v>
       </c>
       <c r="C212" t="s">
-        <v>126</v>
+        <v>178</v>
       </c>
       <c r="D212" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E212" t="s">
         <v>398</v>
@@ -41708,10 +41708,10 @@
         <v>98</v>
       </c>
       <c r="C213" t="s">
-        <v>178</v>
+        <v>128</v>
       </c>
       <c r="D213" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E213" t="s">
         <v>399</v>
@@ -42078,10 +42078,10 @@
         <v>100</v>
       </c>
       <c r="C215" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="D215" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E215" t="s">
         <v>401</v>
@@ -42117,13 +42117,13 @@
         <v>699</v>
       </c>
       <c r="P215">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="Q215">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="R215">
-        <v>2.96</v>
+        <v>0</v>
       </c>
       <c r="S215">
         <v>0</v>
@@ -42162,10 +42162,10 @@
         <v>0</v>
       </c>
       <c r="AE215">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AF215">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AG215">
         <v>0</v>
@@ -42266,7 +42266,7 @@
         <v>179</v>
       </c>
       <c r="D216" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E216" t="s">
         <v>402</v>
@@ -42302,13 +42302,13 @@
         <v>699</v>
       </c>
       <c r="P216">
-        <v>4.68</v>
+        <v>2.15</v>
       </c>
       <c r="Q216">
-        <v>4.32</v>
+        <v>3.44</v>
       </c>
       <c r="R216">
-        <v>1.76</v>
+        <v>3.5</v>
       </c>
       <c r="S216">
         <v>0</v>
@@ -42347,10 +42347,10 @@
         <v>0</v>
       </c>
       <c r="AE216">
-        <v>1.58</v>
+        <v>1.95</v>
       </c>
       <c r="AF216">
-        <v>2.25</v>
+        <v>1.75</v>
       </c>
       <c r="AG216">
         <v>0</v>
@@ -42451,7 +42451,7 @@
         <v>180</v>
       </c>
       <c r="D217" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E217" t="s">
         <v>403</v>
@@ -42487,13 +42487,13 @@
         <v>699</v>
       </c>
       <c r="P217">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Q217">
-        <v>0</v>
+        <v>9.15</v>
       </c>
       <c r="R217">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="S217">
         <v>0</v>
@@ -42538,10 +42538,10 @@
         <v>0</v>
       </c>
       <c r="AG217">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AH217">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AI217">
         <v>0</v>
@@ -42633,10 +42633,10 @@
         <v>100</v>
       </c>
       <c r="C218" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="D218" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E218" t="s">
         <v>404</v>
@@ -42672,13 +42672,13 @@
         <v>699</v>
       </c>
       <c r="P218">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="Q218">
-        <v>4.73</v>
+        <v>0</v>
       </c>
       <c r="R218">
-        <v>5.79</v>
+        <v>0</v>
       </c>
       <c r="S218">
         <v>0</v>
@@ -42723,10 +42723,10 @@
         <v>0</v>
       </c>
       <c r="AG218">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AH218">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AI218">
         <v>0</v>
@@ -42818,7 +42818,7 @@
         <v>100</v>
       </c>
       <c r="C219" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="D219" t="s">
         <v>186</v>
@@ -42857,13 +42857,13 @@
         <v>699</v>
       </c>
       <c r="P219">
-        <v>3.8</v>
+        <v>4.05</v>
       </c>
       <c r="Q219">
-        <v>3.78</v>
+        <v>3.76</v>
       </c>
       <c r="R219">
-        <v>2.05</v>
+        <v>1.99</v>
       </c>
       <c r="S219">
         <v>0</v>
@@ -42902,10 +42902,10 @@
         <v>0</v>
       </c>
       <c r="AE219">
-        <v>1.73</v>
+        <v>1.85</v>
       </c>
       <c r="AF219">
-        <v>1.98</v>
+        <v>1.85</v>
       </c>
       <c r="AG219">
         <v>0</v>
@@ -43003,7 +43003,7 @@
         <v>100</v>
       </c>
       <c r="C220" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="D220" t="s">
         <v>186</v>
@@ -43042,13 +43042,13 @@
         <v>699</v>
       </c>
       <c r="P220">
-        <v>3.17</v>
+        <v>2.38</v>
       </c>
       <c r="Q220">
-        <v>3.68</v>
+        <v>3.9</v>
       </c>
       <c r="R220">
-        <v>2.34</v>
+        <v>2.96</v>
       </c>
       <c r="S220">
         <v>0</v>
@@ -43087,10 +43087,10 @@
         <v>0</v>
       </c>
       <c r="AE220">
-        <v>1.72</v>
+        <v>1.58</v>
       </c>
       <c r="AF220">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="AG220">
         <v>0</v>
@@ -43227,13 +43227,13 @@
         <v>699</v>
       </c>
       <c r="P221">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Q221">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="R221">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="S221">
         <v>0</v>
@@ -43272,10 +43272,10 @@
         <v>0</v>
       </c>
       <c r="AE221">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AF221">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AG221">
         <v>0</v>
@@ -43373,10 +43373,10 @@
         <v>100</v>
       </c>
       <c r="C222" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="D222" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E222" t="s">
         <v>408</v>
@@ -43412,13 +43412,13 @@
         <v>699</v>
       </c>
       <c r="P222">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="Q222">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="R222">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="S222">
         <v>0</v>
@@ -43457,10 +43457,10 @@
         <v>0</v>
       </c>
       <c r="AE222">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AF222">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AG222">
         <v>0</v>
@@ -43558,7 +43558,7 @@
         <v>100</v>
       </c>
       <c r="C223" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="D223" t="s">
         <v>185</v>
@@ -43597,13 +43597,13 @@
         <v>699</v>
       </c>
       <c r="P223">
-        <v>5.3</v>
+        <v>0</v>
       </c>
       <c r="Q223">
-        <v>3.73</v>
+        <v>0</v>
       </c>
       <c r="R223">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="S223">
         <v>0</v>
@@ -43642,10 +43642,10 @@
         <v>0</v>
       </c>
       <c r="AE223">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AF223">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AG223">
         <v>0</v>
@@ -43743,7 +43743,7 @@
         <v>100</v>
       </c>
       <c r="C224" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="D224" t="s">
         <v>185</v>
@@ -43782,13 +43782,13 @@
         <v>699</v>
       </c>
       <c r="P224">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="Q224">
-        <v>0</v>
+        <v>3.73</v>
       </c>
       <c r="R224">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="S224">
         <v>0</v>
@@ -43827,10 +43827,10 @@
         <v>0</v>
       </c>
       <c r="AE224">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AF224">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AG224">
         <v>0</v>
@@ -43928,7 +43928,7 @@
         <v>100</v>
       </c>
       <c r="C225" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="D225" t="s">
         <v>186</v>
@@ -43967,13 +43967,13 @@
         <v>699</v>
       </c>
       <c r="P225">
-        <v>1.18</v>
+        <v>3.17</v>
       </c>
       <c r="Q225">
-        <v>9.15</v>
+        <v>3.68</v>
       </c>
       <c r="R225">
-        <v>17</v>
+        <v>2.34</v>
       </c>
       <c r="S225">
         <v>0</v>
@@ -44012,16 +44012,16 @@
         <v>0</v>
       </c>
       <c r="AE225">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AF225">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG225">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AH225">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AI225">
         <v>0</v>
@@ -44113,7 +44113,7 @@
         <v>100</v>
       </c>
       <c r="C226" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="D226" t="s">
         <v>186</v>
@@ -44298,7 +44298,7 @@
         <v>100</v>
       </c>
       <c r="C227" t="s">
-        <v>146</v>
+        <v>180</v>
       </c>
       <c r="D227" t="s">
         <v>186</v>
@@ -44337,13 +44337,13 @@
         <v>699</v>
       </c>
       <c r="P227">
-        <v>0</v>
+        <v>4.68</v>
       </c>
       <c r="Q227">
-        <v>0</v>
+        <v>4.32</v>
       </c>
       <c r="R227">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="S227">
         <v>0</v>
@@ -44382,10 +44382,10 @@
         <v>0</v>
       </c>
       <c r="AE227">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AF227">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AG227">
         <v>0</v>
@@ -44483,7 +44483,7 @@
         <v>100</v>
       </c>
       <c r="C228" t="s">
-        <v>179</v>
+        <v>148</v>
       </c>
       <c r="D228" t="s">
         <v>186</v>
@@ -44522,13 +44522,13 @@
         <v>699</v>
       </c>
       <c r="P228">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="Q228">
-        <v>3.76</v>
+        <v>0</v>
       </c>
       <c r="R228">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="S228">
         <v>0</v>
@@ -44567,10 +44567,10 @@
         <v>0</v>
       </c>
       <c r="AE228">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AF228">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AG228">
         <v>0</v>
@@ -44668,10 +44668,10 @@
         <v>100</v>
       </c>
       <c r="C229" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="D229" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E229" t="s">
         <v>415</v>
@@ -44707,13 +44707,13 @@
         <v>699</v>
       </c>
       <c r="P229">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="Q229">
-        <v>0</v>
+        <v>4.73</v>
       </c>
       <c r="R229">
-        <v>0</v>
+        <v>5.79</v>
       </c>
       <c r="S229">
         <v>0</v>
@@ -44758,10 +44758,10 @@
         <v>0</v>
       </c>
       <c r="AG229">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AH229">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AI229">
         <v>0</v>
@@ -45778,7 +45778,7 @@
         <v>102</v>
       </c>
       <c r="C235" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="D235" t="s">
         <v>185</v>
@@ -45963,7 +45963,7 @@
         <v>102</v>
       </c>
       <c r="C236" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="D236" t="s">
         <v>185</v>
@@ -46557,13 +46557,13 @@
         <v>699</v>
       </c>
       <c r="P239">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="Q239">
-        <v>0</v>
+        <v>3.61</v>
       </c>
       <c r="R239">
-        <v>0</v>
+        <v>5.14</v>
       </c>
       <c r="S239">
         <v>0</v>
@@ -46888,7 +46888,7 @@
         <v>105</v>
       </c>
       <c r="C241" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="D241" t="s">
         <v>185</v>
@@ -47073,7 +47073,7 @@
         <v>106</v>
       </c>
       <c r="C242" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="D242" t="s">
         <v>185</v>
@@ -47112,13 +47112,13 @@
         <v>699</v>
       </c>
       <c r="P242">
-        <v>1.79</v>
+        <v>2.26</v>
       </c>
       <c r="Q242">
-        <v>3.62</v>
+        <v>3.22</v>
       </c>
       <c r="R242">
-        <v>4.84</v>
+        <v>3.46</v>
       </c>
       <c r="S242">
         <v>0</v>
@@ -47157,10 +47157,10 @@
         <v>0</v>
       </c>
       <c r="AE242">
-        <v>1.87</v>
+        <v>2.25</v>
       </c>
       <c r="AF242">
-        <v>1.8</v>
+        <v>1.57</v>
       </c>
       <c r="AG242">
         <v>0</v>
@@ -47258,7 +47258,7 @@
         <v>106</v>
       </c>
       <c r="C243" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="D243" t="s">
         <v>185</v>
@@ -47297,13 +47297,13 @@
         <v>699</v>
       </c>
       <c r="P243">
-        <v>2.26</v>
+        <v>2.13</v>
       </c>
       <c r="Q243">
-        <v>3.22</v>
+        <v>3.34</v>
       </c>
       <c r="R243">
-        <v>3.46</v>
+        <v>3.67</v>
       </c>
       <c r="S243">
         <v>0</v>
@@ -47342,10 +47342,10 @@
         <v>0</v>
       </c>
       <c r="AE243">
-        <v>2.25</v>
+        <v>1.95</v>
       </c>
       <c r="AF243">
-        <v>1.57</v>
+        <v>1.73</v>
       </c>
       <c r="AG243">
         <v>0</v>
@@ -47443,7 +47443,7 @@
         <v>106</v>
       </c>
       <c r="C244" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="D244" t="s">
         <v>185</v>
@@ -47482,13 +47482,13 @@
         <v>699</v>
       </c>
       <c r="P244">
-        <v>2.13</v>
+        <v>1.79</v>
       </c>
       <c r="Q244">
-        <v>3.34</v>
+        <v>3.62</v>
       </c>
       <c r="R244">
-        <v>3.67</v>
+        <v>4.84</v>
       </c>
       <c r="S244">
         <v>0</v>
@@ -47527,10 +47527,10 @@
         <v>0</v>
       </c>
       <c r="AE244">
-        <v>1.95</v>
+        <v>1.87</v>
       </c>
       <c r="AF244">
-        <v>1.73</v>
+        <v>1.8</v>
       </c>
       <c r="AG244">
         <v>0</v>
@@ -47628,7 +47628,7 @@
         <v>106</v>
       </c>
       <c r="C245" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="D245" t="s">
         <v>185</v>
@@ -47998,7 +47998,7 @@
         <v>108</v>
       </c>
       <c r="C247" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="D247" t="s">
         <v>185</v>
@@ -48037,13 +48037,13 @@
         <v>699</v>
       </c>
       <c r="P247">
-        <v>0</v>
+        <v>3.79</v>
       </c>
       <c r="Q247">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="R247">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="S247">
         <v>0</v>
@@ -48082,10 +48082,10 @@
         <v>0</v>
       </c>
       <c r="AE247">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AF247">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AG247">
         <v>0</v>
@@ -48183,7 +48183,7 @@
         <v>108</v>
       </c>
       <c r="C248" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="D248" t="s">
         <v>185</v>
@@ -48222,13 +48222,13 @@
         <v>699</v>
       </c>
       <c r="P248">
-        <v>3.79</v>
+        <v>0</v>
       </c>
       <c r="Q248">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="R248">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="S248">
         <v>0</v>
@@ -48267,10 +48267,10 @@
         <v>0</v>
       </c>
       <c r="AE248">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AF248">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AG248">
         <v>0</v>
@@ -48368,7 +48368,7 @@
         <v>109</v>
       </c>
       <c r="C249" t="s">
-        <v>177</v>
+        <v>183</v>
       </c>
       <c r="D249" t="s">
         <v>185</v>
@@ -48553,7 +48553,7 @@
         <v>109</v>
       </c>
       <c r="C250" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="D250" t="s">
         <v>185</v>
@@ -48738,7 +48738,7 @@
         <v>109</v>
       </c>
       <c r="C251" t="s">
-        <v>183</v>
+        <v>173</v>
       </c>
       <c r="D251" t="s">
         <v>185</v>
@@ -48962,13 +48962,13 @@
         <v>699</v>
       </c>
       <c r="P252">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="Q252">
-        <v>0</v>
+        <v>3.03</v>
       </c>
       <c r="R252">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="S252">
         <v>0</v>
@@ -49147,13 +49147,13 @@
         <v>699</v>
       </c>
       <c r="P253">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="Q253">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="R253">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="S253">
         <v>0</v>
@@ -49293,7 +49293,7 @@
         <v>111</v>
       </c>
       <c r="C254" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="D254" t="s">
         <v>185</v>
@@ -49332,13 +49332,13 @@
         <v>699</v>
       </c>
       <c r="P254">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="Q254">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R254">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="S254">
         <v>0</v>

--- a/jogos_2026-05-10.xlsx
+++ b/jogos_2026-05-10.xlsx
@@ -388,21 +388,21 @@
     <t>Russia Russian Premier League</t>
   </si>
   <si>
+    <t>Ethiopia Ethiopia Premier League</t>
+  </si>
+  <si>
     <t>Spain Primera Division Women</t>
   </si>
   <si>
-    <t>Ethiopia Ethiopia Premier League</t>
-  </si>
-  <si>
     <t>Vietnam V.League 1</t>
   </si>
   <si>
+    <t>Portugal Liga 3</t>
+  </si>
+  <si>
     <t>Poland 1. Liga</t>
   </si>
   <si>
-    <t>Portugal Liga 3</t>
-  </si>
-  <si>
     <t>Kazakhstan Kazakhstan Premier League</t>
   </si>
   <si>
@@ -412,12 +412,12 @@
     <t>Italy Serie A</t>
   </si>
   <si>
+    <t>Thailand Thai League T1</t>
+  </si>
+  <si>
     <t>Scotland Premiership</t>
   </si>
   <si>
-    <t>Thailand Thai League T1</t>
-  </si>
-  <si>
     <t>Sweden Damallsvenskan</t>
   </si>
   <si>
@@ -427,42 +427,42 @@
     <t>Bulgaria First League</t>
   </si>
   <si>
+    <t>Germany 3. Liga</t>
+  </si>
+  <si>
+    <t>Singapore S.League</t>
+  </si>
+  <si>
+    <t>Germany 2. Bundesliga</t>
+  </si>
+  <si>
     <t>India Indian Super League</t>
   </si>
   <si>
-    <t>Germany 2. Bundesliga</t>
+    <t>Estonia Meistriliiga</t>
   </si>
   <si>
     <t>Belgium Pro League</t>
   </si>
   <si>
-    <t>Estonia Meistriliiga</t>
-  </si>
-  <si>
-    <t>Singapore S.League</t>
-  </si>
-  <si>
-    <t>Germany 3. Liga</t>
-  </si>
-  <si>
     <t>Croatia Druga HNL</t>
   </si>
   <si>
+    <t>Switzerland Super League</t>
+  </si>
+  <si>
+    <t>Georgia Erovnuli Liga</t>
+  </si>
+  <si>
     <t>Denmark Superliga</t>
   </si>
   <si>
+    <t>Spain La Liga</t>
+  </si>
+  <si>
     <t>Sweden Allsvenskan</t>
   </si>
   <si>
-    <t>Georgia Erovnuli Liga</t>
-  </si>
-  <si>
-    <t>Switzerland Super League</t>
-  </si>
-  <si>
-    <t>Spain La Liga</t>
-  </si>
-  <si>
     <t>Spain Segunda División</t>
   </si>
   <si>
@@ -472,51 +472,51 @@
     <t>Norway Eliteserien</t>
   </si>
   <si>
+    <t>Czech Republic First League</t>
+  </si>
+  <si>
+    <t>Romania Liga I</t>
+  </si>
+  <si>
+    <t>England Premier League</t>
+  </si>
+  <si>
     <t>Slovenia PrvaLiga</t>
   </si>
   <si>
-    <t>England Premier League</t>
-  </si>
-  <si>
     <t>Azerbaijan Premyer Liqası</t>
   </si>
   <si>
-    <t>Czech Republic First League</t>
-  </si>
-  <si>
-    <t>Romania Liga I</t>
-  </si>
-  <si>
     <t>Germany Bundesliga</t>
   </si>
   <si>
+    <t>Hungary NB II</t>
+  </si>
+  <si>
+    <t>Greece Super League</t>
+  </si>
+  <si>
+    <t>Faroe Islands Faroe Islands Premier League</t>
+  </si>
+  <si>
     <t>Croatia Prva HNL</t>
   </si>
   <si>
-    <t>Faroe Islands Faroe Islands Premier League</t>
-  </si>
-  <si>
-    <t>Hungary NB II</t>
-  </si>
-  <si>
-    <t>Greece Super League</t>
-  </si>
-  <si>
     <t>Netherlands Eredivisie</t>
   </si>
   <si>
+    <t>FYR Macedonia First Football League</t>
+  </si>
+  <si>
+    <t>Austria Bundesliga</t>
+  </si>
+  <si>
+    <t>Norway First Division</t>
+  </si>
+  <si>
     <t>Cyprus First Division</t>
   </si>
   <si>
-    <t>FYR Macedonia First Football League</t>
-  </si>
-  <si>
-    <t>Austria Bundesliga</t>
-  </si>
-  <si>
-    <t>Norway First Division</t>
-  </si>
-  <si>
     <t>UAE Arabian Gulf League</t>
   </si>
   <si>
@@ -553,24 +553,24 @@
     <t>Argentina Prim B Nacional</t>
   </si>
   <si>
+    <t>France Ligue 1</t>
+  </si>
+  <si>
+    <t>Brazil Serie B</t>
+  </si>
+  <si>
     <t>Brazil Serie A</t>
   </si>
   <si>
-    <t>France Ligue 1</t>
-  </si>
-  <si>
     <t>Bolivia LFPB</t>
   </si>
   <si>
-    <t>Brazil Serie B</t>
+    <t>Ecuador Primera Categoría Serie A</t>
   </si>
   <si>
     <t>USA MLS</t>
   </si>
   <si>
-    <t>Ecuador Primera Categoría Serie A</t>
-  </si>
-  <si>
     <t>2026</t>
   </si>
   <si>
@@ -580,15 +580,15 @@
     <t>2025</t>
   </si>
   <si>
+    <t>Rockdale City Suns</t>
+  </si>
+  <si>
+    <t>Seongnam</t>
+  </si>
+  <si>
     <t>Blacktown City</t>
   </si>
   <si>
-    <t>Seongnam</t>
-  </si>
-  <si>
-    <t>Rockdale City Suns</t>
-  </si>
-  <si>
     <t>Ulsan</t>
   </si>
   <si>
@@ -598,13 +598,16 @@
     <t>Shaanxi Union</t>
   </si>
   <si>
+    <t>Ufa</t>
+  </si>
+  <si>
+    <t>Yanbian Longding</t>
+  </si>
+  <si>
     <t>Dalian Huayi</t>
   </si>
   <si>
-    <t>Ufa</t>
-  </si>
-  <si>
-    <t>Yanbian Longding</t>
+    <t>Busan I'Park</t>
   </si>
   <si>
     <t>Ansan Greeners</t>
@@ -613,9 +616,6 @@
     <t>Anyang</t>
   </si>
   <si>
-    <t>Busan I'Park</t>
-  </si>
-  <si>
     <t>Slavia Praha U21</t>
   </si>
   <si>
@@ -634,282 +634,285 @@
     <t>Orenburg</t>
   </si>
   <si>
+    <t>Sheger Ketema</t>
+  </si>
+  <si>
     <t>Levante W</t>
   </si>
   <si>
-    <t>Sheger Ketema</t>
+    <t>Sichuan Jiuniu</t>
+  </si>
+  <si>
+    <t>Sokol Saratov</t>
   </si>
   <si>
     <t>Hoang Anh Gia Lai</t>
   </si>
   <si>
+    <t>Amarante</t>
+  </si>
+  <si>
+    <t>Polonia Warszawa</t>
+  </si>
+  <si>
+    <t>Ulytau</t>
+  </si>
+  <si>
     <t>Gyeongnam</t>
   </si>
   <si>
-    <t>Sichuan Jiuniu</t>
-  </si>
-  <si>
-    <t>Polonia Warszawa</t>
-  </si>
-  <si>
-    <t>Sokol Saratov</t>
-  </si>
-  <si>
-    <t>Amarante</t>
-  </si>
-  <si>
-    <t>Ulytau</t>
-  </si>
-  <si>
     <t>Piast Gliwice</t>
   </si>
   <si>
     <t>Hellas Verona</t>
   </si>
   <si>
+    <t>Sukhothai</t>
+  </si>
+  <si>
+    <t>Chonburi</t>
+  </si>
+  <si>
+    <t>Altay</t>
+  </si>
+  <si>
     <t>Celtic</t>
   </si>
   <si>
+    <t>Hà Nội II</t>
+  </si>
+  <si>
+    <t>Shenzhen Juniors</t>
+  </si>
+  <si>
+    <t>Shenyang Urban</t>
+  </si>
+  <si>
+    <t>Piteå Women</t>
+  </si>
+  <si>
+    <t>Ho Chi Minh City</t>
+  </si>
+  <si>
+    <t>Rayong</t>
+  </si>
+  <si>
+    <t>Buriram United</t>
+  </si>
+  <si>
+    <t>Kanchanaburi</t>
+  </si>
+  <si>
+    <t>Ayutthaya United</t>
+  </si>
+  <si>
     <t>Chiangrai United</t>
   </si>
   <si>
-    <t>Kanchanaburi</t>
-  </si>
-  <si>
-    <t>Shenzhen Juniors</t>
-  </si>
-  <si>
-    <t>Ho Chi Minh City</t>
-  </si>
-  <si>
-    <t>Piteå Women</t>
-  </si>
-  <si>
-    <t>Altay</t>
-  </si>
-  <si>
-    <t>Chonburi</t>
-  </si>
-  <si>
-    <t>Shenyang Urban</t>
-  </si>
-  <si>
     <t>Bangkok Glass</t>
   </si>
   <si>
-    <t>Rayong</t>
-  </si>
-  <si>
-    <t>Buriram United</t>
-  </si>
-  <si>
-    <t>Hà Nội II</t>
-  </si>
-  <si>
-    <t>Ayutthaya United</t>
-  </si>
-  <si>
-    <t>Sukhothai</t>
-  </si>
-  <si>
     <t>Sūduva</t>
   </si>
   <si>
     <t>Spartak Varna</t>
   </si>
   <si>
+    <t>Havelse</t>
+  </si>
+  <si>
+    <t>Hougang United</t>
+  </si>
+  <si>
+    <t>Home United</t>
+  </si>
+  <si>
+    <t>Hertha BSC</t>
+  </si>
+  <si>
     <t>Kerala Blasters</t>
   </si>
   <si>
+    <t>Nõmme Kalju</t>
+  </si>
+  <si>
     <t>Fortuna Düsseldorf</t>
   </si>
   <si>
     <t>KAA Gent</t>
   </si>
   <si>
-    <t>Nõmme Kalju</t>
+    <t>Preußen Münster</t>
+  </si>
+  <si>
+    <t>Dongguan United</t>
   </si>
   <si>
     <t>Nantong Zhiyun</t>
   </si>
   <si>
-    <t>Hougang United</t>
-  </si>
-  <si>
-    <t>Home United</t>
-  </si>
-  <si>
-    <t>Dongguan United</t>
-  </si>
-  <si>
-    <t>Havelse</t>
-  </si>
-  <si>
-    <t>Preußen Münster</t>
-  </si>
-  <si>
-    <t>Hertha BSC</t>
+    <t>Beijing Guoan</t>
   </si>
   <si>
     <t>Zhejiang FC</t>
   </si>
   <si>
-    <t>Beijing Guoan</t>
-  </si>
-  <si>
     <t>Hrvace</t>
   </si>
   <si>
+    <t>Lugano</t>
+  </si>
+  <si>
+    <t>Meshakhte</t>
+  </si>
+  <si>
+    <t>Nordsjælland</t>
+  </si>
+  <si>
+    <t>PSIM Yogyakarta</t>
+  </si>
+  <si>
+    <t>RCD Mallorca</t>
+  </si>
+  <si>
+    <t>Kalmar</t>
+  </si>
+  <si>
     <t>Vejle</t>
   </si>
   <si>
+    <t>Aktobe</t>
+  </si>
+  <si>
+    <t>Bahardar</t>
+  </si>
+  <si>
     <t>AIK</t>
   </si>
   <si>
+    <t>FC Andorra</t>
+  </si>
+  <si>
     <t>Qingdao Jonoon</t>
   </si>
   <si>
-    <t>PSIM Yogyakarta</t>
-  </si>
-  <si>
-    <t>Meshakhte</t>
-  </si>
-  <si>
-    <t>Lugano</t>
-  </si>
-  <si>
-    <t>RCD Mallorca</t>
-  </si>
-  <si>
-    <t>Kalmar</t>
-  </si>
-  <si>
-    <t>Aktobe</t>
-  </si>
-  <si>
-    <t>Bahardar</t>
-  </si>
-  <si>
     <t>Zenit</t>
   </si>
   <si>
-    <t>Nordsjælland</t>
-  </si>
-  <si>
-    <t>FC Andorra</t>
-  </si>
-  <si>
     <t>Công An Nhân Dân</t>
   </si>
   <si>
     <t>Kuala Lumpur</t>
   </si>
   <si>
+    <t>Tychy 71</t>
+  </si>
+  <si>
     <t>Baník Ostrava U21</t>
   </si>
   <si>
     <t>Rosenborg</t>
   </si>
   <si>
-    <t>Tychy 71</t>
-  </si>
-  <si>
     <t>Wisła Płock</t>
   </si>
   <si>
+    <t>Sigma Olomouc</t>
+  </si>
+  <si>
+    <t>Astana</t>
+  </si>
+  <si>
+    <t>Fiorentina</t>
+  </si>
+  <si>
+    <t>Pardubice</t>
+  </si>
+  <si>
+    <t>Botoşani</t>
+  </si>
+  <si>
+    <t>Uppsala W</t>
+  </si>
+  <si>
+    <t>Crystal Palace</t>
+  </si>
+  <si>
+    <t>Cremonese</t>
+  </si>
+  <si>
+    <t>Burnley</t>
+  </si>
+  <si>
     <t>NK Primorje</t>
   </si>
   <si>
+    <t>Turan</t>
+  </si>
+  <si>
+    <t>Arba Minch Kenema</t>
+  </si>
+  <si>
     <t>Kelantan United</t>
   </si>
   <si>
-    <t>Astana</t>
-  </si>
-  <si>
-    <t>Burnley</t>
-  </si>
-  <si>
-    <t>Crystal Palace</t>
-  </si>
-  <si>
-    <t>Turan</t>
-  </si>
-  <si>
-    <t>Sigma Olomouc</t>
-  </si>
-  <si>
-    <t>Cremonese</t>
-  </si>
-  <si>
-    <t>Arba Minch Kenema</t>
-  </si>
-  <si>
     <t>Nottingham Forest</t>
   </si>
   <si>
-    <t>Uppsala W</t>
-  </si>
-  <si>
-    <t>Fiorentina</t>
-  </si>
-  <si>
-    <t>Botoşani</t>
-  </si>
-  <si>
-    <t>Pardubice</t>
-  </si>
-  <si>
     <t>Hamburger SV</t>
   </si>
   <si>
     <t>Botev Vratsa</t>
   </si>
   <si>
+    <t>Royal Antwerp FC</t>
+  </si>
+  <si>
+    <t>Honvéd W</t>
+  </si>
+  <si>
+    <t>Volos NFC</t>
+  </si>
+  <si>
+    <t>Nõmme United</t>
+  </si>
+  <si>
+    <t>Silkeborg</t>
+  </si>
+  <si>
+    <t>Banga</t>
+  </si>
+  <si>
+    <t>NorthEast United</t>
+  </si>
+  <si>
+    <t>Aris</t>
+  </si>
+  <si>
+    <t>EB - Streymur</t>
+  </si>
+  <si>
     <t>Osijek</t>
   </si>
   <si>
-    <t>Banga</t>
-  </si>
-  <si>
-    <t>Silkeborg</t>
-  </si>
-  <si>
     <t>B36</t>
   </si>
   <si>
-    <t>Honvéd W</t>
-  </si>
-  <si>
-    <t>Aris</t>
-  </si>
-  <si>
-    <t>EB - Streymur</t>
-  </si>
-  <si>
-    <t>Royal Antwerp FC</t>
-  </si>
-  <si>
-    <t>Nõmme United</t>
-  </si>
-  <si>
-    <t>Volos NFC</t>
-  </si>
-  <si>
-    <t>NorthEast United</t>
+    <t>Athletic Club Bilbao</t>
+  </si>
+  <si>
+    <t>Leganés</t>
   </si>
   <si>
     <t>Akhmat Grozny</t>
   </si>
   <si>
-    <t>Leganés</t>
-  </si>
-  <si>
-    <t>Athletic Club Bilbao</t>
-  </si>
-  <si>
     <t>Sion</t>
   </si>
   <si>
+    <t>Neftekhimik</t>
+  </si>
+  <si>
     <t>Young Boys</t>
   </si>
   <si>
@@ -919,192 +922,189 @@
     <t>Viktoria Köln</t>
   </si>
   <si>
-    <t>Neftekhimik</t>
+    <t>Ajax</t>
   </si>
   <si>
     <t>Twente</t>
   </si>
   <si>
-    <t>Ajax</t>
+    <t>Fortuna Sittard</t>
   </si>
   <si>
     <t>Groningen</t>
   </si>
   <si>
-    <t>Fortuna Sittard</t>
+    <t>Excelsior</t>
+  </si>
+  <si>
+    <t>Feyenoord</t>
+  </si>
+  <si>
+    <t>NAC Breda</t>
   </si>
   <si>
     <t>Go Ahead Eagles</t>
   </si>
   <si>
-    <t>Feyenoord</t>
-  </si>
-  <si>
     <t>Telstar</t>
   </si>
   <si>
-    <t>Excelsior</t>
-  </si>
-  <si>
-    <t>NAC Breda</t>
+    <t>Sandefjord</t>
+  </si>
+  <si>
+    <t>Kecskeméti TE</t>
+  </si>
+  <si>
+    <t>Szentlőrinc SE</t>
+  </si>
+  <si>
+    <t>Real Madrid W</t>
+  </si>
+  <si>
+    <t>Vardar</t>
+  </si>
+  <si>
+    <t>Zbrojovka Brno</t>
+  </si>
+  <si>
+    <t>Tromsø</t>
+  </si>
+  <si>
+    <t>Mebrat Hayl</t>
+  </si>
+  <si>
+    <t>Croatia Zmijavci</t>
+  </si>
+  <si>
+    <t>Hartberg</t>
+  </si>
+  <si>
+    <t>Karcag SE</t>
+  </si>
+  <si>
+    <t>Moss</t>
+  </si>
+  <si>
+    <t>Sandnes Ulf</t>
+  </si>
+  <si>
+    <t>Raufoss</t>
+  </si>
+  <si>
+    <t>LASK Linz</t>
+  </si>
+  <si>
+    <t>Åsane</t>
+  </si>
+  <si>
+    <t>Aresimi</t>
+  </si>
+  <si>
+    <t>Shkendija</t>
+  </si>
+  <si>
+    <t>Budafoki MTE</t>
+  </si>
+  <si>
+    <t>Pelister</t>
+  </si>
+  <si>
+    <t>KFUM</t>
+  </si>
+  <si>
+    <t>Makedonija GjP</t>
+  </si>
+  <si>
+    <t>Paphos</t>
+  </si>
+  <si>
+    <t>Sogndal</t>
+  </si>
+  <si>
+    <t>Rapid Wien</t>
+  </si>
+  <si>
+    <t>Ajka</t>
+  </si>
+  <si>
+    <t>Saburtalo</t>
   </si>
   <si>
     <t>Apollon</t>
   </si>
   <si>
+    <t>Omonia Nicosia</t>
+  </si>
+  <si>
     <t>Akademija Pandev</t>
   </si>
   <si>
-    <t>Rapid Wien</t>
-  </si>
-  <si>
-    <t>Omonia Nicosia</t>
-  </si>
-  <si>
-    <t>Pelister</t>
-  </si>
-  <si>
-    <t>Vardar</t>
-  </si>
-  <si>
-    <t>Mebrat Hayl</t>
-  </si>
-  <si>
-    <t>Paphos</t>
-  </si>
-  <si>
-    <t>KFUM</t>
-  </si>
-  <si>
-    <t>Tromsø</t>
-  </si>
-  <si>
-    <t>Sandefjord</t>
-  </si>
-  <si>
-    <t>Aresimi</t>
-  </si>
-  <si>
-    <t>Shkendija</t>
-  </si>
-  <si>
-    <t>Zbrojovka Brno</t>
+    <t>Pogoń Siedlce</t>
   </si>
   <si>
     <t>Strømmen</t>
   </si>
   <si>
-    <t>Makedonija GjP</t>
-  </si>
-  <si>
-    <t>Pogoń Siedlce</t>
-  </si>
-  <si>
-    <t>Saburtalo</t>
-  </si>
-  <si>
-    <t>Karcag SE</t>
-  </si>
-  <si>
-    <t>Sogndal</t>
-  </si>
-  <si>
-    <t>Moss</t>
-  </si>
-  <si>
-    <t>Sandnes Ulf</t>
-  </si>
-  <si>
-    <t>Raufoss</t>
-  </si>
-  <si>
-    <t>Åsane</t>
-  </si>
-  <si>
-    <t>Szentlőrinc SE</t>
-  </si>
-  <si>
-    <t>Real Madrid W</t>
-  </si>
-  <si>
-    <t>Ajka</t>
-  </si>
-  <si>
-    <t>Hartberg</t>
-  </si>
-  <si>
-    <t>LASK Linz</t>
-  </si>
-  <si>
-    <t>Kecskeméti TE</t>
-  </si>
-  <si>
-    <t>Croatia Zmijavci</t>
-  </si>
-  <si>
-    <t>Budafoki MTE</t>
+    <t>Bani Yas</t>
   </si>
   <si>
     <t>Dibba Al Fujairah</t>
   </si>
   <si>
-    <t>Bani Yas</t>
-  </si>
-  <si>
     <t>Al Ain</t>
   </si>
   <si>
     <t>Al Bataeh</t>
   </si>
   <si>
+    <t>West Ham United</t>
+  </si>
+  <si>
+    <t>Nieciecza</t>
+  </si>
+  <si>
+    <t>Neftçi</t>
+  </si>
+  <si>
     <t>Köln</t>
   </si>
   <si>
-    <t>Nieciecza</t>
-  </si>
-  <si>
-    <t>Neftçi</t>
-  </si>
-  <si>
-    <t>West Ham United</t>
-  </si>
-  <si>
     <t>Sekhukhune United</t>
   </si>
   <si>
+    <t>Jedinstvo</t>
+  </si>
+  <si>
+    <t>Arsenal Tivat</t>
+  </si>
+  <si>
     <t>Vysočina Jihlava</t>
   </si>
   <si>
+    <t>Mladost DG</t>
+  </si>
+  <si>
+    <t>Ittihad Tanger</t>
+  </si>
+  <si>
+    <t>Dečić</t>
+  </si>
+  <si>
+    <t>Parma</t>
+  </si>
+  <si>
+    <t>Brøndby</t>
+  </si>
+  <si>
+    <t>Dinamo Bucureşti</t>
+  </si>
+  <si>
+    <t>Panevėžys</t>
+  </si>
+  <si>
     <t>Mornar</t>
   </si>
   <si>
-    <t>Dinamo Bucureşti</t>
-  </si>
-  <si>
-    <t>Brøndby</t>
-  </si>
-  <si>
-    <t>Parma</t>
-  </si>
-  <si>
-    <t>Jedinstvo</t>
-  </si>
-  <si>
-    <t>Panevėžys</t>
-  </si>
-  <si>
-    <t>Arsenal Tivat</t>
-  </si>
-  <si>
-    <t>Ittihad Tanger</t>
-  </si>
-  <si>
-    <t>Dečić</t>
-  </si>
-  <si>
-    <t>Mladost DG</t>
-  </si>
-  <si>
     <t>Al Riyadh</t>
   </si>
   <si>
@@ -1120,109 +1120,139 @@
     <t>07 Vestur</t>
   </si>
   <si>
+    <t>Lokomotiv Moskva</t>
+  </si>
+  <si>
+    <t>Spartak Subotica</t>
+  </si>
+  <si>
+    <t>Bačka Topola</t>
+  </si>
+  <si>
+    <t>Jablonec</t>
+  </si>
+  <si>
+    <t>Córdoba</t>
+  </si>
+  <si>
+    <t>Kansas City</t>
+  </si>
+  <si>
+    <t>Real Oviedo</t>
+  </si>
+  <si>
+    <t>Radnički Niš</t>
+  </si>
+  <si>
+    <t>Mirandés</t>
+  </si>
+  <si>
+    <t>Union Saint-Gilloise</t>
+  </si>
+  <si>
+    <t>AEK Athens</t>
+  </si>
+  <si>
+    <t>Antofagasta</t>
+  </si>
+  <si>
     <t>IMT Novi Beograd</t>
   </si>
   <si>
-    <t>Radnički Niš</t>
+    <t>Copiapó</t>
   </si>
   <si>
     <t>Olympiakos Piraeus</t>
   </si>
   <si>
-    <t>AEK Athens</t>
-  </si>
-  <si>
-    <t>Union Saint-Gilloise</t>
-  </si>
-  <si>
-    <t>Bačka Topola</t>
-  </si>
-  <si>
-    <t>Spartak Subotica</t>
-  </si>
-  <si>
-    <t>Lokomotiv Moskva</t>
-  </si>
-  <si>
-    <t>Jablonec</t>
-  </si>
-  <si>
-    <t>Kansas City</t>
-  </si>
-  <si>
-    <t>Mirandés</t>
-  </si>
-  <si>
-    <t>Córdoba</t>
-  </si>
-  <si>
-    <t>Antofagasta</t>
-  </si>
-  <si>
-    <t>Real Oviedo</t>
-  </si>
-  <si>
-    <t>Copiapó</t>
+    <t>Csákvári TK</t>
+  </si>
+  <si>
+    <t>Tenerife W</t>
+  </si>
+  <si>
+    <t>Békéscsaba</t>
   </si>
   <si>
     <t>Hapoel Haifa</t>
   </si>
   <si>
+    <t>Ironi Tiberias</t>
+  </si>
+  <si>
+    <t>Dinamo Batumi</t>
+  </si>
+  <si>
     <t>Hapoel Katamon</t>
   </si>
   <si>
-    <t>Ironi Tiberias</t>
-  </si>
-  <si>
-    <t>Dinamo Batumi</t>
-  </si>
-  <si>
-    <t>Tenerife W</t>
-  </si>
-  <si>
-    <t>Békéscsaba</t>
-  </si>
-  <si>
     <t>KA</t>
   </si>
   <si>
-    <t>Csákvári TK</t>
-  </si>
-  <si>
     <t>KRC Genk</t>
   </si>
   <si>
+    <t>Mainz 05</t>
+  </si>
+  <si>
     <t>Hoffenheim II</t>
   </si>
   <si>
-    <t>Mainz 05</t>
-  </si>
-  <si>
     <t>New England II</t>
   </si>
   <si>
+    <t>CODM Meknès</t>
+  </si>
+  <si>
+    <t>Al Ittihad</t>
+  </si>
+  <si>
     <t>UTS Rabat</t>
   </si>
   <si>
-    <t>CODM Meknès</t>
-  </si>
-  <si>
-    <t>Al Ittihad</t>
+    <t>Varzim</t>
   </si>
   <si>
     <t>Chacarita Juniors</t>
   </si>
   <si>
-    <t>Varzim</t>
-  </si>
-  <si>
     <t>AC Milan</t>
   </si>
   <si>
+    <t>Rennes</t>
+  </si>
+  <si>
+    <t>FC Barcelona</t>
+  </si>
+  <si>
+    <t>Metz</t>
+  </si>
+  <si>
+    <t>Náutico</t>
+  </si>
+  <si>
+    <t>Atlético Mineiro</t>
+  </si>
+  <si>
+    <t>Monaco</t>
+  </si>
+  <si>
+    <t>Toulouse</t>
+  </si>
+  <si>
+    <t>Remo</t>
+  </si>
+  <si>
     <t>Agropecuario</t>
   </si>
   <si>
-    <t>Atlético Mineiro</t>
+    <t>Independiente Petrolero</t>
+  </si>
+  <si>
+    <t>Le Havre</t>
+  </si>
+  <si>
+    <t>Angers SCO</t>
   </si>
   <si>
     <t>PSG</t>
@@ -1231,69 +1261,39 @@
     <t>Club Atlético Güemes</t>
   </si>
   <si>
-    <t>Angers SCO</t>
-  </si>
-  <si>
-    <t>Monaco</t>
-  </si>
-  <si>
-    <t>Independiente Petrolero</t>
-  </si>
-  <si>
-    <t>Toulouse</t>
-  </si>
-  <si>
-    <t>Náutico</t>
-  </si>
-  <si>
-    <t>Remo</t>
-  </si>
-  <si>
-    <t>Metz</t>
-  </si>
-  <si>
     <t>Auxerre</t>
   </si>
   <si>
-    <t>Le Havre</t>
-  </si>
-  <si>
-    <t>FC Barcelona</t>
-  </si>
-  <si>
-    <t>Rennes</t>
+    <t>Godoy Cruz</t>
   </si>
   <si>
     <t>San Martín San Juan</t>
   </si>
   <si>
-    <t>Godoy Cruz</t>
-  </si>
-  <si>
     <t>Chaco For Ever</t>
   </si>
   <si>
     <t>Los Angeles II</t>
   </si>
   <si>
+    <t>Bay</t>
+  </si>
+  <si>
     <t>Central Norte</t>
   </si>
   <si>
     <t>Portland Timbers II</t>
   </si>
   <si>
-    <t>Bay</t>
-  </si>
-  <si>
     <t>Hassania Agadir</t>
   </si>
   <si>
+    <t>CS Emelec</t>
+  </si>
+  <si>
     <t>New York City</t>
   </si>
   <si>
-    <t>CS Emelec</t>
-  </si>
-  <si>
     <t>Colón</t>
   </si>
   <si>
@@ -1303,15 +1303,15 @@
     <t>Corinthians</t>
   </si>
   <si>
+    <t>Avaí</t>
+  </si>
+  <si>
+    <t>Mirassol</t>
+  </si>
+  <si>
     <t>Santos</t>
   </si>
   <si>
-    <t>Mirassol</t>
-  </si>
-  <si>
-    <t>Avaí</t>
-  </si>
-  <si>
     <t>FC Cincinnati II</t>
   </si>
   <si>
@@ -1324,21 +1324,21 @@
     <t>Minnesota United</t>
   </si>
   <si>
+    <t>Seattle Reign</t>
+  </si>
+  <si>
     <t>Atlanta United II</t>
   </si>
   <si>
-    <t>Seattle Reign</t>
-  </si>
-  <si>
     <t>Manta FC</t>
   </si>
   <si>
+    <t>Vasco da Gama</t>
+  </si>
+  <si>
     <t>Blooming</t>
   </si>
   <si>
-    <t>Vasco da Gama</t>
-  </si>
-  <si>
     <t>Colorado Rapids II</t>
   </si>
   <si>
@@ -1348,15 +1348,15 @@
     <t>Los Angeles FC</t>
   </si>
   <si>
+    <t>Sydney II</t>
+  </si>
+  <si>
+    <t>Jeonnam Dragons</t>
+  </si>
+  <si>
     <t>St. George Saints</t>
   </si>
   <si>
-    <t>Jeonnam Dragons</t>
-  </si>
-  <si>
-    <t>Sydney II</t>
-  </si>
-  <si>
     <t>Bucheon 1995</t>
   </si>
   <si>
@@ -1366,13 +1366,16 @@
     <t>Shanghai Jiading</t>
   </si>
   <si>
+    <t>Rotor Volgograd</t>
+  </si>
+  <si>
+    <t>Guangxi Hengchen</t>
+  </si>
+  <si>
     <t>Guangzhou E-Power</t>
   </si>
   <si>
-    <t>Rotor Volgograd</t>
-  </si>
-  <si>
-    <t>Guangxi Hengchen</t>
+    <t>Cheonan City</t>
   </si>
   <si>
     <t>Yongin City</t>
@@ -1381,9 +1384,6 @@
     <t>Jeonbuk Motors</t>
   </si>
   <si>
-    <t>Cheonan City</t>
-  </si>
-  <si>
     <t>Táborsko</t>
   </si>
   <si>
@@ -1402,282 +1402,285 @@
     <t>Krylya Sovetov</t>
   </si>
   <si>
+    <t>Sidama Bunna</t>
+  </si>
+  <si>
     <t>Logroño W</t>
   </si>
   <si>
-    <t>Sidama Bunna</t>
+    <t>Shandong Luneng</t>
+  </si>
+  <si>
+    <t>Spartak Kostroma</t>
   </si>
   <si>
     <t>Pho Hien</t>
   </si>
   <si>
+    <t>União Santarém</t>
+  </si>
+  <si>
+    <t>Górnik Łęczna</t>
+  </si>
+  <si>
+    <t>Kairat</t>
+  </si>
+  <si>
     <t>Gimhae City</t>
   </si>
   <si>
-    <t>Shandong Luneng</t>
-  </si>
-  <si>
-    <t>Górnik Łęczna</t>
-  </si>
-  <si>
-    <t>Spartak Kostroma</t>
-  </si>
-  <si>
-    <t>União Santarém</t>
-  </si>
-  <si>
-    <t>Kairat</t>
-  </si>
-  <si>
     <t>GKS Katowice</t>
   </si>
   <si>
     <t>Como</t>
   </si>
   <si>
+    <t>Muang Thong United</t>
+  </si>
+  <si>
+    <t>Nakhon Ratchasima</t>
+  </si>
+  <si>
+    <t>Ordabasy</t>
+  </si>
+  <si>
     <t>Rangers</t>
   </si>
   <si>
+    <t>Viettel</t>
+  </si>
+  <si>
+    <t>Hebei Kungfu</t>
+  </si>
+  <si>
+    <t>Yunnan Yukun</t>
+  </si>
+  <si>
+    <t>Rosengard Women</t>
+  </si>
+  <si>
+    <t>Song Lam Nghe An</t>
+  </si>
+  <si>
+    <t>Bangkok United</t>
+  </si>
+  <si>
+    <t>Lamphun Warrior</t>
+  </si>
+  <si>
+    <t>Ratchaburi</t>
+  </si>
+  <si>
+    <t>Port FC</t>
+  </si>
+  <si>
     <t>Uthai Thani</t>
   </si>
   <si>
-    <t>Ratchaburi</t>
-  </si>
-  <si>
-    <t>Hebei Kungfu</t>
-  </si>
-  <si>
-    <t>Song Lam Nghe An</t>
-  </si>
-  <si>
-    <t>Rosengard Women</t>
-  </si>
-  <si>
-    <t>Ordabasy</t>
-  </si>
-  <si>
-    <t>Nakhon Ratchasima</t>
-  </si>
-  <si>
-    <t>Yunnan Yukun</t>
-  </si>
-  <si>
     <t>Prachuap</t>
   </si>
   <si>
-    <t>Bangkok United</t>
-  </si>
-  <si>
-    <t>Lamphun Warrior</t>
-  </si>
-  <si>
-    <t>Viettel</t>
-  </si>
-  <si>
-    <t>Port FC</t>
-  </si>
-  <si>
-    <t>Muang Thong United</t>
-  </si>
-  <si>
     <t>Žalgiris</t>
   </si>
   <si>
     <t>Slavia Sofia</t>
   </si>
   <si>
+    <t>Schweinfurt</t>
+  </si>
+  <si>
+    <t>Tampines Rovers</t>
+  </si>
+  <si>
+    <t>Albirex Niigata S</t>
+  </si>
+  <si>
+    <t>Greuther Fürth</t>
+  </si>
+  <si>
     <t>Mohammedan</t>
   </si>
   <si>
+    <t>Tallinna FC Flora</t>
+  </si>
+  <si>
     <t>Elversberg</t>
   </si>
   <si>
     <t>RSC Anderlecht</t>
   </si>
   <si>
-    <t>Tallinna FC Flora</t>
+    <t>Darmstadt 98</t>
+  </si>
+  <si>
+    <t>Suzhou Dongwu</t>
   </si>
   <si>
     <t>Wuxi Wugou</t>
   </si>
   <si>
-    <t>Tampines Rovers</t>
-  </si>
-  <si>
-    <t>Albirex Niigata S</t>
-  </si>
-  <si>
-    <t>Suzhou Dongwu</t>
-  </si>
-  <si>
-    <t>Schweinfurt</t>
-  </si>
-  <si>
-    <t>Darmstadt 98</t>
-  </si>
-  <si>
-    <t>Greuther Fürth</t>
+    <t>Shanghai SIPG</t>
   </si>
   <si>
     <t>Tianjin Teda</t>
   </si>
   <si>
-    <t>Shanghai SIPG</t>
-  </si>
-  <si>
     <t>Opatija</t>
   </si>
   <si>
+    <t>St. Gallen</t>
+  </si>
+  <si>
+    <t>Dila</t>
+  </si>
+  <si>
+    <t>Midtjylland</t>
+  </si>
+  <si>
+    <t>Malut United</t>
+  </si>
+  <si>
+    <t>Villarreal</t>
+  </si>
+  <si>
+    <t>Halmstad</t>
+  </si>
+  <si>
     <t>Fredericia</t>
   </si>
   <si>
+    <t>Kaisar</t>
+  </si>
+  <si>
+    <t>Welwalo Adigrat Uni</t>
+  </si>
+  <si>
     <t>Djurgården</t>
   </si>
   <si>
+    <t>UD Las Palmas</t>
+  </si>
+  <si>
     <t>Dalian Zhixing</t>
   </si>
   <si>
-    <t>Malut United</t>
-  </si>
-  <si>
-    <t>Dila</t>
-  </si>
-  <si>
-    <t>St. Gallen</t>
-  </si>
-  <si>
-    <t>Villarreal</t>
-  </si>
-  <si>
-    <t>Halmstad</t>
-  </si>
-  <si>
-    <t>Kaisar</t>
-  </si>
-  <si>
-    <t>Welwalo Adigrat Uni</t>
-  </si>
-  <si>
     <t>FK Sochi</t>
   </si>
   <si>
-    <t>Midtjylland</t>
-  </si>
-  <si>
-    <t>UD Las Palmas</t>
-  </si>
-  <si>
     <t>Nam Dinh</t>
   </si>
   <si>
     <t>Negeri Sembilan</t>
   </si>
   <si>
+    <t>Ruch Chorzów</t>
+  </si>
+  <si>
     <t>Ústí nad Labem</t>
   </si>
   <si>
     <t>Lillestrøm</t>
   </si>
   <si>
-    <t>Ruch Chorzów</t>
-  </si>
-  <si>
     <t>Motor Lublin</t>
   </si>
   <si>
+    <t>Bohemians 1905</t>
+  </si>
+  <si>
+    <t>Kyzyl-Zhar</t>
+  </si>
+  <si>
+    <t>Genoa</t>
+  </si>
+  <si>
+    <t>Karviná</t>
+  </si>
+  <si>
+    <t>Petrolul 52</t>
+  </si>
+  <si>
+    <t>Vittsjö</t>
+  </si>
+  <si>
+    <t>Everton</t>
+  </si>
+  <si>
+    <t>Pisa</t>
+  </si>
+  <si>
+    <t>Aston Villa</t>
+  </si>
+  <si>
     <t>Mura</t>
   </si>
   <si>
+    <t>Karvan FK</t>
+  </si>
+  <si>
+    <t>Welayta Dicha</t>
+  </si>
+  <si>
     <t>Johor Darul Ta'zim</t>
   </si>
   <si>
-    <t>Kyzyl-Zhar</t>
-  </si>
-  <si>
-    <t>Aston Villa</t>
-  </si>
-  <si>
-    <t>Everton</t>
-  </si>
-  <si>
-    <t>Karvan FK</t>
-  </si>
-  <si>
-    <t>Bohemians 1905</t>
-  </si>
-  <si>
-    <t>Pisa</t>
-  </si>
-  <si>
-    <t>Welayta Dicha</t>
-  </si>
-  <si>
     <t>Newcastle United</t>
   </si>
   <si>
-    <t>Vittsjö</t>
-  </si>
-  <si>
-    <t>Genoa</t>
-  </si>
-  <si>
-    <t>Petrolul 52</t>
-  </si>
-  <si>
-    <t>Karviná</t>
-  </si>
-  <si>
     <t>Freiburg</t>
   </si>
   <si>
     <t>Septemvri Sofia</t>
   </si>
   <si>
+    <t>Sporting Charleroi</t>
+  </si>
+  <si>
+    <t>Vasas</t>
+  </si>
+  <si>
+    <t>Levadiakos</t>
+  </si>
+  <si>
+    <t>Paide</t>
+  </si>
+  <si>
+    <t>København</t>
+  </si>
+  <si>
+    <t>TransINVEST Vilnius</t>
+  </si>
+  <si>
+    <t>Chennaiyin</t>
+  </si>
+  <si>
+    <t>OFI</t>
+  </si>
+  <si>
+    <t>Víkingur</t>
+  </si>
+  <si>
     <t>Istra 1961</t>
   </si>
   <si>
-    <t>TransINVEST Vilnius</t>
-  </si>
-  <si>
-    <t>København</t>
-  </si>
-  <si>
     <t>KÍ</t>
   </si>
   <si>
-    <t>Vasas</t>
-  </si>
-  <si>
-    <t>OFI</t>
-  </si>
-  <si>
-    <t>Víkingur</t>
-  </si>
-  <si>
-    <t>Sporting Charleroi</t>
-  </si>
-  <si>
-    <t>Paide</t>
-  </si>
-  <si>
-    <t>Levadiakos</t>
-  </si>
-  <si>
-    <t>Chennaiyin</t>
+    <t>Valencia CF</t>
+  </si>
+  <si>
+    <t>Racing Santander</t>
   </si>
   <si>
     <t>Makhachkala</t>
   </si>
   <si>
-    <t>Racing Santander</t>
-  </si>
-  <si>
-    <t>Valencia CF</t>
-  </si>
-  <si>
     <t>Thun</t>
   </si>
   <si>
+    <t>Volga Ulyanovsk</t>
+  </si>
+  <si>
     <t>Basel</t>
   </si>
   <si>
@@ -1687,189 +1690,186 @@
     <t>Alemannia Aachen</t>
   </si>
   <si>
-    <t>Volga Ulyanovsk</t>
+    <t>Utrecht</t>
   </si>
   <si>
     <t>Sparta Rotterdam</t>
   </si>
   <si>
-    <t>Utrecht</t>
+    <t>PEC Zwolle</t>
   </si>
   <si>
     <t>NEC</t>
   </si>
   <si>
-    <t>PEC Zwolle</t>
+    <t>Volendam</t>
+  </si>
+  <si>
+    <t>AZ</t>
+  </si>
+  <si>
+    <t>Heerenveen</t>
   </si>
   <si>
     <t>PSV</t>
   </si>
   <si>
-    <t>AZ</t>
-  </si>
-  <si>
     <t>Heracles</t>
   </si>
   <si>
-    <t>Volendam</t>
-  </si>
-  <si>
-    <t>Heerenveen</t>
+    <t>Kristiansund</t>
+  </si>
+  <si>
+    <t>Mezőkövesd-Zsóry</t>
+  </si>
+  <si>
+    <t>Videoton</t>
+  </si>
+  <si>
+    <t>Atletico Madrid W</t>
+  </si>
+  <si>
+    <t>Sileks</t>
+  </si>
+  <si>
+    <t>Vlašim</t>
+  </si>
+  <si>
+    <t>Molde</t>
+  </si>
+  <si>
+    <t>Fasil Ketema</t>
+  </si>
+  <si>
+    <t>Jarun</t>
+  </si>
+  <si>
+    <t>Sturm Graz</t>
+  </si>
+  <si>
+    <t>Tiszakécske</t>
+  </si>
+  <si>
+    <t>Bryne</t>
+  </si>
+  <si>
+    <t>Stabæk</t>
+  </si>
+  <si>
+    <t>Lyn</t>
+  </si>
+  <si>
+    <t>Salzburg</t>
+  </si>
+  <si>
+    <t>Strømsgodset</t>
+  </si>
+  <si>
+    <t>FK Bashkimi Kumanovo</t>
+  </si>
+  <si>
+    <t>Struga</t>
+  </si>
+  <si>
+    <t>BVSC</t>
+  </si>
+  <si>
+    <t>Shkupi</t>
+  </si>
+  <si>
+    <t>Viking</t>
+  </si>
+  <si>
+    <t>Tikveš</t>
+  </si>
+  <si>
+    <t>Haugesund</t>
+  </si>
+  <si>
+    <t>Austria Wien</t>
+  </si>
+  <si>
+    <t>Szeged 2011</t>
+  </si>
+  <si>
+    <t>Torpedo Kutaisi</t>
   </si>
   <si>
     <t>APOEL</t>
   </si>
   <si>
+    <t>AEK Larnaca</t>
+  </si>
+  <si>
     <t>Rabotnički</t>
   </si>
   <si>
-    <t>Austria Wien</t>
-  </si>
-  <si>
-    <t>AEK Larnaca</t>
-  </si>
-  <si>
-    <t>Shkupi</t>
-  </si>
-  <si>
-    <t>Sileks</t>
-  </si>
-  <si>
-    <t>Fasil Ketema</t>
-  </si>
-  <si>
-    <t>Viking</t>
-  </si>
-  <si>
-    <t>Molde</t>
-  </si>
-  <si>
-    <t>Kristiansund</t>
-  </si>
-  <si>
-    <t>FK Bashkimi Kumanovo</t>
-  </si>
-  <si>
-    <t>Struga</t>
-  </si>
-  <si>
-    <t>Vlašim</t>
+    <t>Stal Rzeszów</t>
   </si>
   <si>
     <t>Hødd</t>
   </si>
   <si>
-    <t>Tikveš</t>
-  </si>
-  <si>
-    <t>Stal Rzeszów</t>
-  </si>
-  <si>
-    <t>Torpedo Kutaisi</t>
-  </si>
-  <si>
-    <t>Tiszakécske</t>
-  </si>
-  <si>
-    <t>Haugesund</t>
-  </si>
-  <si>
-    <t>Bryne</t>
-  </si>
-  <si>
-    <t>Stabæk</t>
-  </si>
-  <si>
-    <t>Lyn</t>
-  </si>
-  <si>
-    <t>Strømsgodset</t>
-  </si>
-  <si>
-    <t>Videoton</t>
-  </si>
-  <si>
-    <t>Atletico Madrid W</t>
-  </si>
-  <si>
-    <t>Szeged 2011</t>
-  </si>
-  <si>
-    <t>Sturm Graz</t>
-  </si>
-  <si>
-    <t>Salzburg</t>
-  </si>
-  <si>
-    <t>Mezőkövesd-Zsóry</t>
-  </si>
-  <si>
-    <t>Jarun</t>
-  </si>
-  <si>
-    <t>BVSC</t>
+    <t>Shabab Al Ahli Dubai</t>
   </si>
   <si>
     <t>Ajman</t>
   </si>
   <si>
-    <t>Shabab Al Ahli Dubai</t>
-  </si>
-  <si>
     <t>Al Dhafra</t>
   </si>
   <si>
     <t>Al Sharjah</t>
   </si>
   <si>
+    <t>Arsenal</t>
+  </si>
+  <si>
+    <t>Legia Warszawa</t>
+  </si>
+  <si>
+    <t>İnter Bakı</t>
+  </si>
+  <si>
     <t>Heidenheim</t>
   </si>
   <si>
-    <t>Legia Warszawa</t>
-  </si>
-  <si>
-    <t>İnter Bakı</t>
-  </si>
-  <si>
-    <t>Arsenal</t>
-  </si>
-  <si>
     <t>Kaizer Chiefs</t>
   </si>
   <si>
+    <t>Budućnost</t>
+  </si>
+  <si>
+    <t>Sutjeska</t>
+  </si>
+  <si>
     <t>Hanácká</t>
   </si>
   <si>
+    <t>Petrovac</t>
+  </si>
+  <si>
+    <t>Difaâ El Jadida</t>
+  </si>
+  <si>
+    <t>FK Jezero Plav</t>
+  </si>
+  <si>
+    <t>Roma</t>
+  </si>
+  <si>
+    <t>AGF</t>
+  </si>
+  <si>
+    <t>Argeș</t>
+  </si>
+  <si>
+    <t>Kauno Žalgiris</t>
+  </si>
+  <si>
     <t>Bokelj</t>
   </si>
   <si>
-    <t>Argeș</t>
-  </si>
-  <si>
-    <t>AGF</t>
-  </si>
-  <si>
-    <t>Roma</t>
-  </si>
-  <si>
-    <t>Budućnost</t>
-  </si>
-  <si>
-    <t>Kauno Žalgiris</t>
-  </si>
-  <si>
-    <t>Sutjeska</t>
-  </si>
-  <si>
-    <t>Difaâ El Jadida</t>
-  </si>
-  <si>
-    <t>FK Jezero Plav</t>
-  </si>
-  <si>
-    <t>Petrovac</t>
-  </si>
-  <si>
     <t>Al Fateh</t>
   </si>
   <si>
@@ -1885,109 +1885,139 @@
     <t>B68</t>
   </si>
   <si>
+    <t>Baltika</t>
+  </si>
+  <si>
+    <t>Napredak</t>
+  </si>
+  <si>
+    <t>Javor Ivanjica</t>
+  </si>
+  <si>
+    <t>Hradec Králové</t>
+  </si>
+  <si>
+    <t>Granada CF</t>
+  </si>
+  <si>
+    <t>Chicago Red Stars</t>
+  </si>
+  <si>
+    <t>Getafe CF</t>
+  </si>
+  <si>
+    <t>LFK Mladost Lučani</t>
+  </si>
+  <si>
+    <t>SD Eibar</t>
+  </si>
+  <si>
+    <t>KV Mechelen</t>
+  </si>
+  <si>
+    <t>Panathinaikos</t>
+  </si>
+  <si>
+    <t>San Luis</t>
+  </si>
+  <si>
     <t>Radnički Kragujevac</t>
   </si>
   <si>
-    <t>LFK Mladost Lučani</t>
+    <t>Unión San Felipe</t>
   </si>
   <si>
     <t>PAOK</t>
   </si>
   <si>
-    <t>Panathinaikos</t>
-  </si>
-  <si>
-    <t>KV Mechelen</t>
-  </si>
-  <si>
-    <t>Javor Ivanjica</t>
-  </si>
-  <si>
-    <t>Napredak</t>
-  </si>
-  <si>
-    <t>Baltika</t>
-  </si>
-  <si>
-    <t>Hradec Králové</t>
-  </si>
-  <si>
-    <t>Chicago Red Stars</t>
-  </si>
-  <si>
-    <t>SD Eibar</t>
-  </si>
-  <si>
-    <t>Granada CF</t>
-  </si>
-  <si>
-    <t>San Luis</t>
-  </si>
-  <si>
-    <t>Getafe CF</t>
-  </si>
-  <si>
-    <t>Unión San Felipe</t>
+    <t>Soroksár SC</t>
+  </si>
+  <si>
+    <t>Barcelona W</t>
+  </si>
+  <si>
+    <t>Kozármisleny</t>
   </si>
   <si>
     <t>Ashdod</t>
   </si>
   <si>
+    <t>Maccabi Netanya</t>
+  </si>
+  <si>
+    <t>Samgurali</t>
+  </si>
+  <si>
     <t>Bnei Sakhnin</t>
   </si>
   <si>
-    <t>Maccabi Netanya</t>
-  </si>
-  <si>
-    <t>Samgurali</t>
-  </si>
-  <si>
-    <t>Barcelona W</t>
-  </si>
-  <si>
-    <t>Kozármisleny</t>
-  </si>
-  <si>
     <t>ÍBV</t>
   </si>
   <si>
-    <t>Soroksár SC</t>
-  </si>
-  <si>
     <t>KVC Westerlo</t>
   </si>
   <si>
+    <t>Union Berlin</t>
+  </si>
+  <si>
     <t>Saarbrucken</t>
   </si>
   <si>
-    <t>Union Berlin</t>
-  </si>
-  <si>
     <t>New York City II</t>
   </si>
   <si>
+    <t>RSB Berkane</t>
+  </si>
+  <si>
+    <t>Dhamk</t>
+  </si>
+  <si>
     <t>Maghreb Fès</t>
   </si>
   <si>
-    <t>RSB Berkane</t>
-  </si>
-  <si>
-    <t>Dhamk</t>
+    <t>CF Os Belenenses</t>
   </si>
   <si>
     <t>Colegiales</t>
   </si>
   <si>
-    <t>CF Os Belenenses</t>
-  </si>
-  <si>
     <t>Atalanta</t>
   </si>
   <si>
+    <t>Paris</t>
+  </si>
+  <si>
+    <t>Real Madrid</t>
+  </si>
+  <si>
+    <t>Lorient</t>
+  </si>
+  <si>
+    <t>América Mineiro</t>
+  </si>
+  <si>
+    <t>Botafogo</t>
+  </si>
+  <si>
+    <t>Lille</t>
+  </si>
+  <si>
+    <t>Olympique Lyonnais</t>
+  </si>
+  <si>
+    <t>Palmeiras</t>
+  </si>
+  <si>
     <t>Atlanta</t>
   </si>
   <si>
-    <t>Botafogo</t>
+    <t>Club Always Ready</t>
+  </si>
+  <si>
+    <t>Olympique Marseille</t>
+  </si>
+  <si>
+    <t>Strasbourg</t>
   </si>
   <si>
     <t>Brest</t>
@@ -1996,69 +2026,39 @@
     <t>Quilmes</t>
   </si>
   <si>
-    <t>Strasbourg</t>
-  </si>
-  <si>
-    <t>Lille</t>
-  </si>
-  <si>
-    <t>Club Always Ready</t>
-  </si>
-  <si>
-    <t>Olympique Lyonnais</t>
-  </si>
-  <si>
-    <t>América Mineiro</t>
-  </si>
-  <si>
-    <t>Palmeiras</t>
-  </si>
-  <si>
-    <t>Lorient</t>
-  </si>
-  <si>
     <t>Nice</t>
   </si>
   <si>
-    <t>Olympique Marseille</t>
-  </si>
-  <si>
-    <t>Real Madrid</t>
-  </si>
-  <si>
-    <t>Paris</t>
+    <t>Racing Córdoba</t>
   </si>
   <si>
     <t>Patronato</t>
   </si>
   <si>
-    <t>Racing Córdoba</t>
-  </si>
-  <si>
     <t>Ciudad de Bolívar</t>
   </si>
   <si>
     <t>Real Monarchs</t>
   </si>
   <si>
+    <t>Utah Royals</t>
+  </si>
+  <si>
     <t>Deportivo Madryn</t>
   </si>
   <si>
     <t>LA Galaxy II</t>
   </si>
   <si>
-    <t>Utah Royals</t>
-  </si>
-  <si>
     <t>FAR Rabat</t>
   </si>
   <si>
+    <t>Libertad</t>
+  </si>
+  <si>
     <t>Columbus Crew</t>
   </si>
   <si>
-    <t>Libertad</t>
-  </si>
-  <si>
     <t>All Boys</t>
   </si>
   <si>
@@ -2068,15 +2068,15 @@
     <t>São Paulo</t>
   </si>
   <si>
+    <t>Fortaleza</t>
+  </si>
+  <si>
+    <t>Chapecoense</t>
+  </si>
+  <si>
     <t>Bragantino</t>
   </si>
   <si>
-    <t>Chapecoense</t>
-  </si>
-  <si>
-    <t>Fortaleza</t>
-  </si>
-  <si>
     <t>Columbus Crew II</t>
   </si>
   <si>
@@ -2089,19 +2089,19 @@
     <t>Austin</t>
   </si>
   <si>
+    <t>Washington Spirit</t>
+  </si>
+  <si>
     <t>Orlando City II</t>
   </si>
   <si>
-    <t>Washington Spirit</t>
-  </si>
-  <si>
     <t>Macará</t>
   </si>
   <si>
+    <t>Atlético PR</t>
+  </si>
+  <si>
     <t>Bolívar</t>
-  </si>
-  <si>
-    <t>Atlético PR</t>
   </si>
   <si>
     <t>Sporting KC II</t>
@@ -3783,10 +3783,10 @@
         <v>63</v>
       </c>
       <c r="C8" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="D8" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E8" t="s">
         <v>194</v>
@@ -3968,10 +3968,10 @@
         <v>63</v>
       </c>
       <c r="C9" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D9" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E9" t="s">
         <v>195</v>
@@ -4377,13 +4377,13 @@
         <v>699</v>
       </c>
       <c r="P11">
-        <v>3.65</v>
+        <v>1.63</v>
       </c>
       <c r="Q11">
-        <v>3.32</v>
+        <v>3.7</v>
       </c>
       <c r="R11">
-        <v>1.91</v>
+        <v>4.67</v>
       </c>
       <c r="S11">
         <v>0</v>
@@ -4422,10 +4422,10 @@
         <v>0</v>
       </c>
       <c r="AE11">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AF11">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AG11">
         <v>0</v>
@@ -4523,7 +4523,7 @@
         <v>64</v>
       </c>
       <c r="C12" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D12" t="s">
         <v>185</v>
@@ -4562,13 +4562,13 @@
         <v>699</v>
       </c>
       <c r="P12">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="Q12">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="R12">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="S12">
         <v>0</v>
@@ -4708,7 +4708,7 @@
         <v>64</v>
       </c>
       <c r="C13" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="D13" t="s">
         <v>185</v>
@@ -4747,13 +4747,13 @@
         <v>699</v>
       </c>
       <c r="P13">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="Q13">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="R13">
-        <v>4.67</v>
+        <v>0</v>
       </c>
       <c r="S13">
         <v>0</v>
@@ -4792,10 +4792,10 @@
         <v>0</v>
       </c>
       <c r="AE13">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AF13">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AG13">
         <v>0</v>
@@ -6373,10 +6373,10 @@
         <v>68</v>
       </c>
       <c r="C22" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="D22" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E22" t="s">
         <v>208</v>
@@ -6558,10 +6558,10 @@
         <v>68</v>
       </c>
       <c r="C23" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="D23" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E23" t="s">
         <v>209</v>
@@ -6597,13 +6597,13 @@
         <v>699</v>
       </c>
       <c r="P23">
-        <v>2.15</v>
+        <v>4.98</v>
       </c>
       <c r="Q23">
-        <v>3.16</v>
+        <v>3.66</v>
       </c>
       <c r="R23">
-        <v>3.14</v>
+        <v>1.75</v>
       </c>
       <c r="S23">
         <v>0</v>
@@ -6743,10 +6743,10 @@
         <v>68</v>
       </c>
       <c r="C24" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="D24" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E24" t="s">
         <v>210</v>
@@ -7113,7 +7113,7 @@
         <v>68</v>
       </c>
       <c r="C26" t="s">
-        <v>119</v>
+        <v>128</v>
       </c>
       <c r="D26" t="s">
         <v>186</v>
@@ -7152,13 +7152,13 @@
         <v>699</v>
       </c>
       <c r="P26">
-        <v>4.98</v>
+        <v>0</v>
       </c>
       <c r="Q26">
-        <v>3.66</v>
+        <v>0</v>
       </c>
       <c r="R26">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="S26">
         <v>0</v>
@@ -7298,10 +7298,10 @@
         <v>68</v>
       </c>
       <c r="C27" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="D27" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E27" t="s">
         <v>213</v>
@@ -7483,7 +7483,7 @@
         <v>68</v>
       </c>
       <c r="C28" t="s">
-        <v>129</v>
+        <v>116</v>
       </c>
       <c r="D28" t="s">
         <v>185</v>
@@ -7522,13 +7522,13 @@
         <v>699</v>
       </c>
       <c r="P28">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Q28">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="R28">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="S28">
         <v>0</v>
@@ -8077,13 +8077,13 @@
         <v>699</v>
       </c>
       <c r="P31">
-        <v>2.2</v>
+        <v>2.44</v>
       </c>
       <c r="Q31">
-        <v>3.7</v>
+        <v>3.61</v>
       </c>
       <c r="R31">
-        <v>3</v>
+        <v>2.77</v>
       </c>
       <c r="S31">
         <v>0</v>
@@ -8223,7 +8223,7 @@
         <v>71</v>
       </c>
       <c r="C32" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="D32" t="s">
         <v>186</v>
@@ -8262,13 +8262,13 @@
         <v>699</v>
       </c>
       <c r="P32">
-        <v>2.7</v>
+        <v>1.61</v>
       </c>
       <c r="Q32">
-        <v>3.36</v>
+        <v>4.18</v>
       </c>
       <c r="R32">
-        <v>2.64</v>
+        <v>5.3</v>
       </c>
       <c r="S32">
         <v>0</v>
@@ -8307,10 +8307,10 @@
         <v>0</v>
       </c>
       <c r="AE32">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AF32">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AG32">
         <v>0</v>
@@ -8408,10 +8408,10 @@
         <v>71</v>
       </c>
       <c r="C33" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="D33" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E33" t="s">
         <v>219</v>
@@ -8447,13 +8447,13 @@
         <v>699</v>
       </c>
       <c r="P33">
-        <v>3.32</v>
+        <v>0</v>
       </c>
       <c r="Q33">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="R33">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="S33">
         <v>0</v>
@@ -8593,10 +8593,10 @@
         <v>71</v>
       </c>
       <c r="C34" t="s">
-        <v>118</v>
+        <v>133</v>
       </c>
       <c r="D34" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E34" t="s">
         <v>220</v>
@@ -8632,13 +8632,13 @@
         <v>699</v>
       </c>
       <c r="P34">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Q34">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="R34">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="S34">
         <v>0</v>
@@ -8963,7 +8963,7 @@
         <v>71</v>
       </c>
       <c r="C36" t="s">
-        <v>134</v>
+        <v>118</v>
       </c>
       <c r="D36" t="s">
         <v>185</v>
@@ -9148,7 +9148,7 @@
         <v>71</v>
       </c>
       <c r="C37" t="s">
-        <v>129</v>
+        <v>122</v>
       </c>
       <c r="D37" t="s">
         <v>185</v>
@@ -9333,10 +9333,10 @@
         <v>71</v>
       </c>
       <c r="C38" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="D38" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E38" t="s">
         <v>224</v>
@@ -9372,13 +9372,13 @@
         <v>699</v>
       </c>
       <c r="P38">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="Q38">
-        <v>4.18</v>
+        <v>0</v>
       </c>
       <c r="R38">
-        <v>5.3</v>
+        <v>0</v>
       </c>
       <c r="S38">
         <v>0</v>
@@ -9518,10 +9518,10 @@
         <v>71</v>
       </c>
       <c r="C39" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="D39" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E39" t="s">
         <v>225</v>
@@ -9703,7 +9703,7 @@
         <v>71</v>
       </c>
       <c r="C40" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="D40" t="s">
         <v>186</v>
@@ -9742,13 +9742,13 @@
         <v>699</v>
       </c>
       <c r="P40">
-        <v>1.78</v>
+        <v>3.4</v>
       </c>
       <c r="Q40">
-        <v>3.9</v>
+        <v>3.63</v>
       </c>
       <c r="R40">
-        <v>4.35</v>
+        <v>2.09</v>
       </c>
       <c r="S40">
         <v>0</v>
@@ -9888,7 +9888,7 @@
         <v>71</v>
       </c>
       <c r="C41" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="D41" t="s">
         <v>186</v>
@@ -9927,13 +9927,13 @@
         <v>699</v>
       </c>
       <c r="P41">
-        <v>3.4</v>
+        <v>1.24</v>
       </c>
       <c r="Q41">
-        <v>3.63</v>
+        <v>6.73</v>
       </c>
       <c r="R41">
-        <v>2.09</v>
+        <v>10.6</v>
       </c>
       <c r="S41">
         <v>0</v>
@@ -10073,7 +10073,7 @@
         <v>71</v>
       </c>
       <c r="C42" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="D42" t="s">
         <v>186</v>
@@ -10112,13 +10112,13 @@
         <v>699</v>
       </c>
       <c r="P42">
-        <v>1.24</v>
+        <v>3.32</v>
       </c>
       <c r="Q42">
-        <v>6.73</v>
+        <v>3.95</v>
       </c>
       <c r="R42">
-        <v>10.6</v>
+        <v>2.03</v>
       </c>
       <c r="S42">
         <v>0</v>
@@ -10258,7 +10258,7 @@
         <v>71</v>
       </c>
       <c r="C43" t="s">
-        <v>126</v>
+        <v>132</v>
       </c>
       <c r="D43" t="s">
         <v>186</v>
@@ -10297,13 +10297,13 @@
         <v>699</v>
       </c>
       <c r="P43">
-        <v>0</v>
+        <v>5.09</v>
       </c>
       <c r="Q43">
-        <v>0</v>
+        <v>4.18</v>
       </c>
       <c r="R43">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="S43">
         <v>0</v>
@@ -10443,7 +10443,7 @@
         <v>71</v>
       </c>
       <c r="C44" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="D44" t="s">
         <v>186</v>
@@ -10482,13 +10482,13 @@
         <v>699</v>
       </c>
       <c r="P44">
-        <v>5.09</v>
+        <v>2.7</v>
       </c>
       <c r="Q44">
-        <v>4.18</v>
+        <v>3.36</v>
       </c>
       <c r="R44">
-        <v>1.64</v>
+        <v>2.64</v>
       </c>
       <c r="S44">
         <v>0</v>
@@ -10527,10 +10527,10 @@
         <v>0</v>
       </c>
       <c r="AE44">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AF44">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AG44">
         <v>0</v>
@@ -10628,7 +10628,7 @@
         <v>71</v>
       </c>
       <c r="C45" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="D45" t="s">
         <v>186</v>
@@ -10667,13 +10667,13 @@
         <v>699</v>
       </c>
       <c r="P45">
-        <v>2.44</v>
+        <v>1.78</v>
       </c>
       <c r="Q45">
-        <v>3.61</v>
+        <v>3.9</v>
       </c>
       <c r="R45">
-        <v>2.77</v>
+        <v>4.35</v>
       </c>
       <c r="S45">
         <v>0</v>
@@ -11222,13 +11222,13 @@
         <v>699</v>
       </c>
       <c r="P48">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="Q48">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="R48">
-        <v>7.37</v>
+        <v>0</v>
       </c>
       <c r="S48">
         <v>0</v>
@@ -11371,7 +11371,7 @@
         <v>138</v>
       </c>
       <c r="D49" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="E49" t="s">
         <v>235</v>
@@ -11407,13 +11407,13 @@
         <v>699</v>
       </c>
       <c r="P49">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="Q49">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="R49">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="S49">
         <v>0</v>
@@ -11553,10 +11553,10 @@
         <v>73</v>
       </c>
       <c r="C50" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="D50" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="E50" t="s">
         <v>236</v>
@@ -11592,13 +11592,13 @@
         <v>699</v>
       </c>
       <c r="P50">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="Q50">
-        <v>3.71</v>
+        <v>0</v>
       </c>
       <c r="R50">
-        <v>2.89</v>
+        <v>0</v>
       </c>
       <c r="S50">
         <v>0</v>
@@ -11738,10 +11738,10 @@
         <v>73</v>
       </c>
       <c r="C51" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="D51" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E51" t="s">
         <v>237</v>
@@ -11777,13 +11777,13 @@
         <v>699</v>
       </c>
       <c r="P51">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="Q51">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="R51">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="S51">
         <v>0</v>
@@ -11828,10 +11828,10 @@
         <v>0</v>
       </c>
       <c r="AG51">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AH51">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AI51">
         <v>0</v>
@@ -11923,10 +11923,10 @@
         <v>73</v>
       </c>
       <c r="C52" t="s">
-        <v>118</v>
+        <v>140</v>
       </c>
       <c r="D52" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E52" t="s">
         <v>238</v>
@@ -11962,13 +11962,13 @@
         <v>699</v>
       </c>
       <c r="P52">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="Q52">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="R52">
-        <v>0</v>
+        <v>7.37</v>
       </c>
       <c r="S52">
         <v>0</v>
@@ -12111,7 +12111,7 @@
         <v>141</v>
       </c>
       <c r="D53" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="E53" t="s">
         <v>239</v>
@@ -12293,10 +12293,10 @@
         <v>73</v>
       </c>
       <c r="C54" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="D54" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="E54" t="s">
         <v>240</v>
@@ -12332,13 +12332,13 @@
         <v>699</v>
       </c>
       <c r="P54">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="Q54">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="R54">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="S54">
         <v>0</v>
@@ -12478,10 +12478,10 @@
         <v>73</v>
       </c>
       <c r="C55" t="s">
-        <v>118</v>
+        <v>142</v>
       </c>
       <c r="D55" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E55" t="s">
         <v>241</v>
@@ -12517,13 +12517,13 @@
         <v>699</v>
       </c>
       <c r="P55">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="Q55">
-        <v>0</v>
+        <v>3.71</v>
       </c>
       <c r="R55">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="S55">
         <v>0</v>
@@ -12663,7 +12663,7 @@
         <v>73</v>
       </c>
       <c r="C56" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="D56" t="s">
         <v>186</v>
@@ -12702,13 +12702,13 @@
         <v>699</v>
       </c>
       <c r="P56">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="Q56">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="R56">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="S56">
         <v>0</v>
@@ -12848,10 +12848,10 @@
         <v>73</v>
       </c>
       <c r="C57" t="s">
-        <v>138</v>
+        <v>118</v>
       </c>
       <c r="D57" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E57" t="s">
         <v>243</v>
@@ -12887,13 +12887,13 @@
         <v>699</v>
       </c>
       <c r="P57">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="Q57">
-        <v>3.74</v>
+        <v>0</v>
       </c>
       <c r="R57">
-        <v>2.76</v>
+        <v>0</v>
       </c>
       <c r="S57">
         <v>0</v>
@@ -13033,10 +13033,10 @@
         <v>73</v>
       </c>
       <c r="C58" t="s">
-        <v>138</v>
+        <v>118</v>
       </c>
       <c r="D58" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E58" t="s">
         <v>244</v>
@@ -13072,13 +13072,13 @@
         <v>699</v>
       </c>
       <c r="P58">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="Q58">
-        <v>4.15</v>
+        <v>0</v>
       </c>
       <c r="R58">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="S58">
         <v>0</v>
@@ -13123,10 +13123,10 @@
         <v>0</v>
       </c>
       <c r="AG58">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AH58">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AI58">
         <v>0</v>
@@ -13812,13 +13812,13 @@
         <v>699</v>
       </c>
       <c r="P62">
-        <v>2.58</v>
+        <v>2.36</v>
       </c>
       <c r="Q62">
-        <v>3.62</v>
+        <v>3.54</v>
       </c>
       <c r="R62">
-        <v>2.45</v>
+        <v>2.73</v>
       </c>
       <c r="S62">
         <v>0</v>
@@ -13997,13 +13997,13 @@
         <v>699</v>
       </c>
       <c r="P63">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="Q63">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="R63">
-        <v>2.87</v>
+        <v>0</v>
       </c>
       <c r="S63">
         <v>0</v>
@@ -14143,10 +14143,10 @@
         <v>76</v>
       </c>
       <c r="C64" t="s">
-        <v>122</v>
+        <v>146</v>
       </c>
       <c r="D64" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E64" t="s">
         <v>250</v>
@@ -14182,13 +14182,13 @@
         <v>699</v>
       </c>
       <c r="P64">
-        <v>0</v>
+        <v>3.36</v>
       </c>
       <c r="Q64">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="R64">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="S64">
         <v>0</v>
@@ -14513,10 +14513,10 @@
         <v>76</v>
       </c>
       <c r="C66" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="D66" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E66" t="s">
         <v>252</v>
@@ -14698,10 +14698,10 @@
         <v>76</v>
       </c>
       <c r="C67" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="D67" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E67" t="s">
         <v>253</v>
@@ -14737,13 +14737,13 @@
         <v>699</v>
       </c>
       <c r="P67">
-        <v>2.36</v>
+        <v>1.92</v>
       </c>
       <c r="Q67">
-        <v>3.54</v>
+        <v>3.4</v>
       </c>
       <c r="R67">
-        <v>2.73</v>
+        <v>3.9</v>
       </c>
       <c r="S67">
         <v>0</v>
@@ -14883,7 +14883,7 @@
         <v>76</v>
       </c>
       <c r="C68" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="D68" t="s">
         <v>186</v>
@@ -14922,13 +14922,13 @@
         <v>699</v>
       </c>
       <c r="P68">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="Q68">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="R68">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="S68">
         <v>0</v>
@@ -15068,7 +15068,7 @@
         <v>76</v>
       </c>
       <c r="C69" t="s">
-        <v>145</v>
+        <v>129</v>
       </c>
       <c r="D69" t="s">
         <v>185</v>
@@ -15107,13 +15107,13 @@
         <v>699</v>
       </c>
       <c r="P69">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="Q69">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="R69">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="S69">
         <v>0</v>
@@ -15253,10 +15253,10 @@
         <v>76</v>
       </c>
       <c r="C70" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
       <c r="D70" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E70" t="s">
         <v>256</v>
@@ -15438,10 +15438,10 @@
         <v>76</v>
       </c>
       <c r="C71" t="s">
-        <v>125</v>
+        <v>148</v>
       </c>
       <c r="D71" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E71" t="s">
         <v>257</v>
@@ -15477,13 +15477,13 @@
         <v>699</v>
       </c>
       <c r="P71">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="Q71">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="R71">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="S71">
         <v>0</v>
@@ -15623,7 +15623,7 @@
         <v>76</v>
       </c>
       <c r="C72" t="s">
-        <v>123</v>
+        <v>149</v>
       </c>
       <c r="D72" t="s">
         <v>186</v>
@@ -15662,13 +15662,13 @@
         <v>699</v>
       </c>
       <c r="P72">
-        <v>1.21</v>
+        <v>2.46</v>
       </c>
       <c r="Q72">
-        <v>7.41</v>
+        <v>3.43</v>
       </c>
       <c r="R72">
-        <v>17.5</v>
+        <v>2.91</v>
       </c>
       <c r="S72">
         <v>0</v>
@@ -15808,10 +15808,10 @@
         <v>76</v>
       </c>
       <c r="C73" t="s">
-        <v>144</v>
+        <v>122</v>
       </c>
       <c r="D73" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E73" t="s">
         <v>259</v>
@@ -15847,13 +15847,13 @@
         <v>699</v>
       </c>
       <c r="P73">
-        <v>3.36</v>
+        <v>0</v>
       </c>
       <c r="Q73">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="R73">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="S73">
         <v>0</v>
@@ -15993,7 +15993,7 @@
         <v>76</v>
       </c>
       <c r="C74" t="s">
-        <v>149</v>
+        <v>123</v>
       </c>
       <c r="D74" t="s">
         <v>186</v>
@@ -16032,13 +16032,13 @@
         <v>699</v>
       </c>
       <c r="P74">
-        <v>2.46</v>
+        <v>1.21</v>
       </c>
       <c r="Q74">
-        <v>3.43</v>
+        <v>7.41</v>
       </c>
       <c r="R74">
-        <v>2.91</v>
+        <v>17.5</v>
       </c>
       <c r="S74">
         <v>0</v>
@@ -16548,7 +16548,7 @@
         <v>78</v>
       </c>
       <c r="C77" t="s">
-        <v>120</v>
+        <v>128</v>
       </c>
       <c r="D77" t="s">
         <v>186</v>
@@ -16587,13 +16587,13 @@
         <v>699</v>
       </c>
       <c r="P77">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Q77">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R77">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="S77">
         <v>0</v>
@@ -16733,10 +16733,10 @@
         <v>78</v>
       </c>
       <c r="C78" t="s">
-        <v>151</v>
+        <v>120</v>
       </c>
       <c r="D78" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E78" t="s">
         <v>264</v>
@@ -16772,13 +16772,13 @@
         <v>699</v>
       </c>
       <c r="P78">
-        <v>2.79</v>
+        <v>0</v>
       </c>
       <c r="Q78">
-        <v>3.67</v>
+        <v>0</v>
       </c>
       <c r="R78">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="S78">
         <v>0</v>
@@ -16918,10 +16918,10 @@
         <v>78</v>
       </c>
       <c r="C79" t="s">
-        <v>127</v>
+        <v>151</v>
       </c>
       <c r="D79" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E79" t="s">
         <v>265</v>
@@ -16957,13 +16957,13 @@
         <v>699</v>
       </c>
       <c r="P79">
-        <v>4</v>
+        <v>2.79</v>
       </c>
       <c r="Q79">
-        <v>3.6</v>
+        <v>3.67</v>
       </c>
       <c r="R79">
-        <v>1.83</v>
+        <v>2.41</v>
       </c>
       <c r="S79">
         <v>0</v>
@@ -17327,13 +17327,13 @@
         <v>699</v>
       </c>
       <c r="P81">
-        <v>2.59</v>
+        <v>0</v>
       </c>
       <c r="Q81">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="R81">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="S81">
         <v>0</v>
@@ -17473,10 +17473,10 @@
         <v>80</v>
       </c>
       <c r="C82" t="s">
-        <v>150</v>
+        <v>129</v>
       </c>
       <c r="D82" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E82" t="s">
         <v>268</v>
@@ -17658,10 +17658,10 @@
         <v>80</v>
       </c>
       <c r="C83" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="D83" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E83" t="s">
         <v>269</v>
@@ -17697,13 +17697,13 @@
         <v>699</v>
       </c>
       <c r="P83">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="Q83">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="R83">
-        <v>0</v>
+        <v>4.01</v>
       </c>
       <c r="S83">
         <v>0</v>
@@ -17742,10 +17742,10 @@
         <v>0</v>
       </c>
       <c r="AE83">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AF83">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AG83">
         <v>0</v>
@@ -17843,7 +17843,7 @@
         <v>80</v>
       </c>
       <c r="C84" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D84" t="s">
         <v>186</v>
@@ -17882,13 +17882,13 @@
         <v>699</v>
       </c>
       <c r="P84">
-        <v>5.38</v>
+        <v>0</v>
       </c>
       <c r="Q84">
-        <v>4.37</v>
+        <v>0</v>
       </c>
       <c r="R84">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="S84">
         <v>0</v>
@@ -18067,13 +18067,13 @@
         <v>699</v>
       </c>
       <c r="P85">
-        <v>2.69</v>
+        <v>2.21</v>
       </c>
       <c r="Q85">
-        <v>3.31</v>
+        <v>3.22</v>
       </c>
       <c r="R85">
-        <v>2.92</v>
+        <v>3.22</v>
       </c>
       <c r="S85">
         <v>0</v>
@@ -18112,10 +18112,10 @@
         <v>0</v>
       </c>
       <c r="AE85">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AF85">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AG85">
         <v>0</v>
@@ -18213,10 +18213,10 @@
         <v>80</v>
       </c>
       <c r="C86" t="s">
-        <v>154</v>
+        <v>134</v>
       </c>
       <c r="D86" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E86" t="s">
         <v>272</v>
@@ -18398,7 +18398,7 @@
         <v>80</v>
       </c>
       <c r="C87" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="D87" t="s">
         <v>186</v>
@@ -18437,13 +18437,13 @@
         <v>699</v>
       </c>
       <c r="P87">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="Q87">
-        <v>0</v>
+        <v>3.31</v>
       </c>
       <c r="R87">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="S87">
         <v>0</v>
@@ -18482,10 +18482,10 @@
         <v>0</v>
       </c>
       <c r="AE87">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AF87">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AG87">
         <v>0</v>
@@ -18768,7 +18768,7 @@
         <v>80</v>
       </c>
       <c r="C89" t="s">
-        <v>125</v>
+        <v>154</v>
       </c>
       <c r="D89" t="s">
         <v>186</v>
@@ -18807,13 +18807,13 @@
         <v>699</v>
       </c>
       <c r="P89">
-        <v>0</v>
+        <v>5.38</v>
       </c>
       <c r="Q89">
-        <v>0</v>
+        <v>4.37</v>
       </c>
       <c r="R89">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="S89">
         <v>0</v>
@@ -18953,7 +18953,7 @@
         <v>80</v>
       </c>
       <c r="C90" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="D90" t="s">
         <v>186</v>
@@ -18992,13 +18992,13 @@
         <v>699</v>
       </c>
       <c r="P90">
-        <v>2.46</v>
+        <v>2.59</v>
       </c>
       <c r="Q90">
-        <v>3.66</v>
+        <v>3.45</v>
       </c>
       <c r="R90">
-        <v>2.99</v>
+        <v>2.3</v>
       </c>
       <c r="S90">
         <v>0</v>
@@ -19037,10 +19037,10 @@
         <v>0</v>
       </c>
       <c r="AE90">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AF90">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AG90">
         <v>0</v>
@@ -19138,10 +19138,10 @@
         <v>80</v>
       </c>
       <c r="C91" t="s">
-        <v>134</v>
+        <v>156</v>
       </c>
       <c r="D91" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E91" t="s">
         <v>277</v>
@@ -19323,7 +19323,7 @@
         <v>80</v>
       </c>
       <c r="C92" t="s">
-        <v>131</v>
+        <v>124</v>
       </c>
       <c r="D92" t="s">
         <v>186</v>
@@ -19362,13 +19362,13 @@
         <v>699</v>
       </c>
       <c r="P92">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="Q92">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="R92">
-        <v>4.01</v>
+        <v>0</v>
       </c>
       <c r="S92">
         <v>0</v>
@@ -19407,10 +19407,10 @@
         <v>0</v>
       </c>
       <c r="AE92">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AF92">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AG92">
         <v>0</v>
@@ -19508,7 +19508,7 @@
         <v>80</v>
       </c>
       <c r="C93" t="s">
-        <v>156</v>
+        <v>150</v>
       </c>
       <c r="D93" t="s">
         <v>186</v>
@@ -19547,13 +19547,13 @@
         <v>699</v>
       </c>
       <c r="P93">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="Q93">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="R93">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="S93">
         <v>0</v>
@@ -19693,7 +19693,7 @@
         <v>80</v>
       </c>
       <c r="C94" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="D94" t="s">
         <v>186</v>
@@ -19732,13 +19732,13 @@
         <v>699</v>
       </c>
       <c r="P94">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="Q94">
-        <v>0</v>
+        <v>3.66</v>
       </c>
       <c r="R94">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="S94">
         <v>0</v>
@@ -19777,10 +19777,10 @@
         <v>0</v>
       </c>
       <c r="AE94">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AF94">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AG94">
         <v>0</v>
@@ -20248,7 +20248,7 @@
         <v>83</v>
       </c>
       <c r="C97" t="s">
-        <v>158</v>
+        <v>142</v>
       </c>
       <c r="D97" t="s">
         <v>186</v>
@@ -20287,13 +20287,13 @@
         <v>699</v>
       </c>
       <c r="P97">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="Q97">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="R97">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="S97">
         <v>0</v>
@@ -20332,10 +20332,10 @@
         <v>0</v>
       </c>
       <c r="AE97">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AF97">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG97">
         <v>0</v>
@@ -20433,10 +20433,10 @@
         <v>83</v>
       </c>
       <c r="C98" t="s">
-        <v>135</v>
+        <v>158</v>
       </c>
       <c r="D98" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E98" t="s">
         <v>284</v>
@@ -20618,7 +20618,7 @@
         <v>83</v>
       </c>
       <c r="C99" t="s">
-        <v>144</v>
+        <v>159</v>
       </c>
       <c r="D99" t="s">
         <v>186</v>
@@ -20657,13 +20657,13 @@
         <v>699</v>
       </c>
       <c r="P99">
-        <v>4.68</v>
+        <v>3.04</v>
       </c>
       <c r="Q99">
-        <v>4</v>
+        <v>3.1</v>
       </c>
       <c r="R99">
-        <v>1.63</v>
+        <v>2.32</v>
       </c>
       <c r="S99">
         <v>0</v>
@@ -20803,7 +20803,7 @@
         <v>83</v>
       </c>
       <c r="C100" t="s">
-        <v>159</v>
+        <v>141</v>
       </c>
       <c r="D100" t="s">
         <v>185</v>
@@ -20988,7 +20988,7 @@
         <v>83</v>
       </c>
       <c r="C101" t="s">
-        <v>160</v>
+        <v>146</v>
       </c>
       <c r="D101" t="s">
         <v>186</v>
@@ -21027,13 +21027,13 @@
         <v>699</v>
       </c>
       <c r="P101">
-        <v>0</v>
+        <v>4.68</v>
       </c>
       <c r="Q101">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R101">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="S101">
         <v>0</v>
@@ -21173,10 +21173,10 @@
         <v>83</v>
       </c>
       <c r="C102" t="s">
-        <v>161</v>
+        <v>135</v>
       </c>
       <c r="D102" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E102" t="s">
         <v>288</v>
@@ -21358,10 +21358,10 @@
         <v>83</v>
       </c>
       <c r="C103" t="s">
-        <v>159</v>
+        <v>140</v>
       </c>
       <c r="D103" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E103" t="s">
         <v>289</v>
@@ -21543,7 +21543,7 @@
         <v>83</v>
       </c>
       <c r="C104" t="s">
-        <v>139</v>
+        <v>159</v>
       </c>
       <c r="D104" t="s">
         <v>186</v>
@@ -21582,13 +21582,13 @@
         <v>699</v>
       </c>
       <c r="P104">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="Q104">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="R104">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="S104">
         <v>0</v>
@@ -21627,10 +21627,10 @@
         <v>0</v>
       </c>
       <c r="AE104">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AF104">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AG104">
         <v>0</v>
@@ -21728,7 +21728,7 @@
         <v>83</v>
       </c>
       <c r="C105" t="s">
-        <v>140</v>
+        <v>160</v>
       </c>
       <c r="D105" t="s">
         <v>185</v>
@@ -21952,13 +21952,13 @@
         <v>699</v>
       </c>
       <c r="P106">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="Q106">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="R106">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="S106">
         <v>0</v>
@@ -22098,10 +22098,10 @@
         <v>83</v>
       </c>
       <c r="C107" t="s">
-        <v>137</v>
+        <v>160</v>
       </c>
       <c r="D107" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E107" t="s">
         <v>293</v>
@@ -22283,7 +22283,7 @@
         <v>84</v>
       </c>
       <c r="C108" t="s">
-        <v>123</v>
+        <v>147</v>
       </c>
       <c r="D108" t="s">
         <v>186</v>
@@ -22322,13 +22322,13 @@
         <v>699</v>
       </c>
       <c r="P108">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="Q108">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="R108">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="S108">
         <v>0</v>
@@ -22653,7 +22653,7 @@
         <v>84</v>
       </c>
       <c r="C110" t="s">
-        <v>148</v>
+        <v>123</v>
       </c>
       <c r="D110" t="s">
         <v>186</v>
@@ -22692,13 +22692,13 @@
         <v>699</v>
       </c>
       <c r="P110">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="Q110">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="R110">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="S110">
         <v>0</v>
@@ -22838,7 +22838,7 @@
         <v>85</v>
       </c>
       <c r="C111" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="D111" t="s">
         <v>186</v>
@@ -23023,7 +23023,7 @@
         <v>85</v>
       </c>
       <c r="C112" t="s">
-        <v>147</v>
+        <v>119</v>
       </c>
       <c r="D112" t="s">
         <v>186</v>
@@ -23062,13 +23062,13 @@
         <v>699</v>
       </c>
       <c r="P112">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="Q112">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="R112">
-        <v>3.57</v>
+        <v>0</v>
       </c>
       <c r="S112">
         <v>0</v>
@@ -23113,10 +23113,10 @@
         <v>0</v>
       </c>
       <c r="AG112">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AH112">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AI112">
         <v>0</v>
@@ -23208,10 +23208,10 @@
         <v>85</v>
       </c>
       <c r="C113" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="D113" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E113" t="s">
         <v>299</v>
@@ -23247,13 +23247,13 @@
         <v>699</v>
       </c>
       <c r="P113">
-        <v>2.27</v>
+        <v>1.85</v>
       </c>
       <c r="Q113">
-        <v>3.58</v>
+        <v>4.05</v>
       </c>
       <c r="R113">
-        <v>2.88</v>
+        <v>3.57</v>
       </c>
       <c r="S113">
         <v>0</v>
@@ -23298,10 +23298,10 @@
         <v>0</v>
       </c>
       <c r="AG113">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AH113">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AI113">
         <v>0</v>
@@ -23393,10 +23393,10 @@
         <v>85</v>
       </c>
       <c r="C114" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
       <c r="D114" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E114" t="s">
         <v>300</v>
@@ -23432,13 +23432,13 @@
         <v>699</v>
       </c>
       <c r="P114">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="Q114">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="R114">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="S114">
         <v>0</v>
@@ -23578,7 +23578,7 @@
         <v>85</v>
       </c>
       <c r="C115" t="s">
-        <v>119</v>
+        <v>137</v>
       </c>
       <c r="D115" t="s">
         <v>186</v>
@@ -23802,13 +23802,13 @@
         <v>699</v>
       </c>
       <c r="P116">
-        <v>1.44</v>
+        <v>1.71</v>
       </c>
       <c r="Q116">
-        <v>5.14</v>
+        <v>4.37</v>
       </c>
       <c r="R116">
-        <v>6.53</v>
+        <v>4.42</v>
       </c>
       <c r="S116">
         <v>0</v>
@@ -23853,10 +23853,10 @@
         <v>0</v>
       </c>
       <c r="AG116">
-        <v>1.93</v>
+        <v>2.1</v>
       </c>
       <c r="AH116">
-        <v>1.77</v>
+        <v>1.65</v>
       </c>
       <c r="AI116">
         <v>0</v>
@@ -23987,13 +23987,13 @@
         <v>699</v>
       </c>
       <c r="P117">
-        <v>1.71</v>
+        <v>1.44</v>
       </c>
       <c r="Q117">
-        <v>4.37</v>
+        <v>5.14</v>
       </c>
       <c r="R117">
-        <v>4.42</v>
+        <v>6.53</v>
       </c>
       <c r="S117">
         <v>0</v>
@@ -24038,10 +24038,10 @@
         <v>0</v>
       </c>
       <c r="AG117">
-        <v>2.1</v>
+        <v>1.93</v>
       </c>
       <c r="AH117">
-        <v>1.65</v>
+        <v>1.77</v>
       </c>
       <c r="AI117">
         <v>0</v>
@@ -24172,13 +24172,13 @@
         <v>699</v>
       </c>
       <c r="P118">
-        <v>2.78</v>
+        <v>1.96</v>
       </c>
       <c r="Q118">
-        <v>3.89</v>
+        <v>4.05</v>
       </c>
       <c r="R118">
-        <v>2.36</v>
+        <v>3.5</v>
       </c>
       <c r="S118">
         <v>0</v>
@@ -24223,10 +24223,10 @@
         <v>0</v>
       </c>
       <c r="AG118">
-        <v>2.05</v>
+        <v>2.2</v>
       </c>
       <c r="AH118">
-        <v>1.68</v>
+        <v>1.58</v>
       </c>
       <c r="AI118">
         <v>0</v>
@@ -24357,13 +24357,13 @@
         <v>699</v>
       </c>
       <c r="P119">
-        <v>1.96</v>
+        <v>2.78</v>
       </c>
       <c r="Q119">
-        <v>4.05</v>
+        <v>3.89</v>
       </c>
       <c r="R119">
-        <v>3.5</v>
+        <v>2.36</v>
       </c>
       <c r="S119">
         <v>0</v>
@@ -24408,10 +24408,10 @@
         <v>0</v>
       </c>
       <c r="AG119">
-        <v>2.2</v>
+        <v>2.05</v>
       </c>
       <c r="AH119">
-        <v>1.58</v>
+        <v>1.68</v>
       </c>
       <c r="AI119">
         <v>0</v>
@@ -24542,13 +24542,13 @@
         <v>699</v>
       </c>
       <c r="P120">
-        <v>4.48</v>
+        <v>1.77</v>
       </c>
       <c r="Q120">
-        <v>4.74</v>
+        <v>4.17</v>
       </c>
       <c r="R120">
-        <v>1.65</v>
+        <v>4.22</v>
       </c>
       <c r="S120">
         <v>0</v>
@@ -24587,16 +24587,16 @@
         <v>0</v>
       </c>
       <c r="AE120">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AF120">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AG120">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AH120">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AI120">
         <v>0</v>
@@ -24912,13 +24912,13 @@
         <v>699</v>
       </c>
       <c r="P122">
-        <v>1.48</v>
+        <v>2.49</v>
       </c>
       <c r="Q122">
-        <v>4.94</v>
+        <v>3.77</v>
       </c>
       <c r="R122">
-        <v>6.07</v>
+        <v>2.67</v>
       </c>
       <c r="S122">
         <v>0</v>
@@ -24957,16 +24957,16 @@
         <v>0</v>
       </c>
       <c r="AE122">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AF122">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AG122">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AH122">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AI122">
         <v>0</v>
@@ -25097,13 +25097,13 @@
         <v>699</v>
       </c>
       <c r="P123">
-        <v>1.77</v>
+        <v>4.48</v>
       </c>
       <c r="Q123">
-        <v>4.17</v>
+        <v>4.74</v>
       </c>
       <c r="R123">
-        <v>4.22</v>
+        <v>1.65</v>
       </c>
       <c r="S123">
         <v>0</v>
@@ -25142,16 +25142,16 @@
         <v>0</v>
       </c>
       <c r="AE123">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AF123">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AG123">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AH123">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AI123">
         <v>0</v>
@@ -25282,13 +25282,13 @@
         <v>699</v>
       </c>
       <c r="P124">
-        <v>2.49</v>
+        <v>1.48</v>
       </c>
       <c r="Q124">
-        <v>3.77</v>
+        <v>4.94</v>
       </c>
       <c r="R124">
-        <v>2.67</v>
+        <v>6.07</v>
       </c>
       <c r="S124">
         <v>0</v>
@@ -25327,16 +25327,16 @@
         <v>0</v>
       </c>
       <c r="AE124">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AF124">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AG124">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AH124">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AI124">
         <v>0</v>
@@ -25428,10 +25428,10 @@
         <v>87</v>
       </c>
       <c r="C125" t="s">
-        <v>163</v>
+        <v>151</v>
       </c>
       <c r="D125" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E125" t="s">
         <v>311</v>
@@ -25467,13 +25467,13 @@
         <v>699</v>
       </c>
       <c r="P125">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="Q125">
-        <v>0</v>
+        <v>4.44</v>
       </c>
       <c r="R125">
-        <v>0</v>
+        <v>5.16</v>
       </c>
       <c r="S125">
         <v>0</v>
@@ -25613,7 +25613,7 @@
         <v>87</v>
       </c>
       <c r="C126" t="s">
-        <v>164</v>
+        <v>158</v>
       </c>
       <c r="D126" t="s">
         <v>186</v>
@@ -25798,7 +25798,7 @@
         <v>87</v>
       </c>
       <c r="C127" t="s">
-        <v>165</v>
+        <v>158</v>
       </c>
       <c r="D127" t="s">
         <v>186</v>
@@ -25837,13 +25837,13 @@
         <v>699</v>
       </c>
       <c r="P127">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Q127">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="R127">
-        <v>2.96</v>
+        <v>0</v>
       </c>
       <c r="S127">
         <v>0</v>
@@ -25983,7 +25983,7 @@
         <v>87</v>
       </c>
       <c r="C128" t="s">
-        <v>163</v>
+        <v>125</v>
       </c>
       <c r="D128" t="s">
         <v>186</v>
@@ -26168,7 +26168,7 @@
         <v>87</v>
       </c>
       <c r="C129" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="D129" t="s">
         <v>186</v>
@@ -26353,7 +26353,7 @@
         <v>87</v>
       </c>
       <c r="C130" t="s">
-        <v>164</v>
+        <v>120</v>
       </c>
       <c r="D130" t="s">
         <v>186</v>
@@ -26538,10 +26538,10 @@
         <v>87</v>
       </c>
       <c r="C131" t="s">
-        <v>125</v>
+        <v>151</v>
       </c>
       <c r="D131" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E131" t="s">
         <v>317</v>
@@ -26577,13 +26577,13 @@
         <v>699</v>
       </c>
       <c r="P131">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="Q131">
-        <v>0</v>
+        <v>3.82</v>
       </c>
       <c r="R131">
-        <v>0</v>
+        <v>4.13</v>
       </c>
       <c r="S131">
         <v>0</v>
@@ -26723,7 +26723,7 @@
         <v>87</v>
       </c>
       <c r="C132" t="s">
-        <v>163</v>
+        <v>124</v>
       </c>
       <c r="D132" t="s">
         <v>186</v>
@@ -26732,7 +26732,7 @@
         <v>318</v>
       </c>
       <c r="F132" t="s">
-        <v>288</v>
+        <v>574</v>
       </c>
       <c r="G132">
         <v>0</v>
@@ -26908,16 +26908,16 @@
         <v>87</v>
       </c>
       <c r="C133" t="s">
-        <v>151</v>
+        <v>143</v>
       </c>
       <c r="D133" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E133" t="s">
         <v>319</v>
       </c>
       <c r="F133" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="G133">
         <v>0</v>
@@ -26947,13 +26947,13 @@
         <v>699</v>
       </c>
       <c r="P133">
-        <v>3.87</v>
+        <v>0</v>
       </c>
       <c r="Q133">
-        <v>3.87</v>
+        <v>0</v>
       </c>
       <c r="R133">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="S133">
         <v>0</v>
@@ -27093,16 +27093,16 @@
         <v>87</v>
       </c>
       <c r="C134" t="s">
-        <v>151</v>
+        <v>164</v>
       </c>
       <c r="D134" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E134" t="s">
         <v>320</v>
       </c>
       <c r="F134" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="G134">
         <v>0</v>
@@ -27132,13 +27132,13 @@
         <v>699</v>
       </c>
       <c r="P134">
-        <v>1.84</v>
+        <v>3.75</v>
       </c>
       <c r="Q134">
-        <v>3.82</v>
+        <v>3.6</v>
       </c>
       <c r="R134">
-        <v>4.13</v>
+        <v>1.91</v>
       </c>
       <c r="S134">
         <v>0</v>
@@ -27177,10 +27177,10 @@
         <v>0</v>
       </c>
       <c r="AE134">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AF134">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG134">
         <v>0</v>
@@ -27278,16 +27278,16 @@
         <v>87</v>
       </c>
       <c r="C135" t="s">
-        <v>151</v>
+        <v>158</v>
       </c>
       <c r="D135" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E135" t="s">
         <v>321</v>
       </c>
       <c r="F135" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="G135">
         <v>0</v>
@@ -27317,13 +27317,13 @@
         <v>699</v>
       </c>
       <c r="P135">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="Q135">
-        <v>4.44</v>
+        <v>0</v>
       </c>
       <c r="R135">
-        <v>5.16</v>
+        <v>0</v>
       </c>
       <c r="S135">
         <v>0</v>
@@ -27463,16 +27463,16 @@
         <v>87</v>
       </c>
       <c r="C136" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="D136" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E136" t="s">
         <v>322</v>
       </c>
       <c r="F136" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="G136">
         <v>0</v>
@@ -27502,13 +27502,13 @@
         <v>699</v>
       </c>
       <c r="P136">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Q136">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="R136">
-        <v>0</v>
+        <v>3.01</v>
       </c>
       <c r="S136">
         <v>0</v>
@@ -27648,16 +27648,16 @@
         <v>87</v>
       </c>
       <c r="C137" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="D137" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E137" t="s">
         <v>323</v>
       </c>
       <c r="F137" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="G137">
         <v>0</v>
@@ -27687,13 +27687,13 @@
         <v>699</v>
       </c>
       <c r="P137">
-        <v>0</v>
+        <v>4.07</v>
       </c>
       <c r="Q137">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="R137">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="S137">
         <v>0</v>
@@ -27833,16 +27833,16 @@
         <v>87</v>
       </c>
       <c r="C138" t="s">
-        <v>120</v>
+        <v>165</v>
       </c>
       <c r="D138" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E138" t="s">
         <v>324</v>
       </c>
       <c r="F138" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="G138">
         <v>0</v>
@@ -27872,13 +27872,13 @@
         <v>699</v>
       </c>
       <c r="P138">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="Q138">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R138">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="S138">
         <v>0</v>
@@ -28018,16 +28018,16 @@
         <v>87</v>
       </c>
       <c r="C139" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="D139" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E139" t="s">
         <v>325</v>
       </c>
       <c r="F139" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="G139">
         <v>0</v>
@@ -28057,13 +28057,13 @@
         <v>699</v>
       </c>
       <c r="P139">
-        <v>2.2</v>
+        <v>2.51</v>
       </c>
       <c r="Q139">
-        <v>3.4</v>
+        <v>3.78</v>
       </c>
       <c r="R139">
-        <v>3.2</v>
+        <v>2.44</v>
       </c>
       <c r="S139">
         <v>0</v>
@@ -28203,16 +28203,16 @@
         <v>87</v>
       </c>
       <c r="C140" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="D140" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E140" t="s">
         <v>326</v>
       </c>
       <c r="F140" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="G140">
         <v>0</v>
@@ -28242,13 +28242,13 @@
         <v>699</v>
       </c>
       <c r="P140">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="Q140">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="R140">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="S140">
         <v>0</v>
@@ -28388,7 +28388,7 @@
         <v>87</v>
       </c>
       <c r="C141" t="s">
-        <v>127</v>
+        <v>163</v>
       </c>
       <c r="D141" t="s">
         <v>186</v>
@@ -28397,7 +28397,7 @@
         <v>327</v>
       </c>
       <c r="F141" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="G141">
         <v>0</v>
@@ -28427,13 +28427,13 @@
         <v>699</v>
       </c>
       <c r="P141">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="Q141">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R141">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="S141">
         <v>0</v>
@@ -28573,16 +28573,16 @@
         <v>87</v>
       </c>
       <c r="C142" t="s">
-        <v>146</v>
+        <v>163</v>
       </c>
       <c r="D142" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E142" t="s">
         <v>328</v>
       </c>
       <c r="F142" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="G142">
         <v>0</v>
@@ -28758,7 +28758,7 @@
         <v>87</v>
       </c>
       <c r="C143" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="D143" t="s">
         <v>186</v>
@@ -28767,7 +28767,7 @@
         <v>329</v>
       </c>
       <c r="F143" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="G143">
         <v>0</v>
@@ -28943,16 +28943,16 @@
         <v>87</v>
       </c>
       <c r="C144" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="D144" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E144" t="s">
         <v>330</v>
       </c>
       <c r="F144" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="G144">
         <v>0</v>
@@ -28982,13 +28982,13 @@
         <v>699</v>
       </c>
       <c r="P144">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="Q144">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="R144">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="S144">
         <v>0</v>
@@ -29128,7 +29128,7 @@
         <v>87</v>
       </c>
       <c r="C145" t="s">
-        <v>166</v>
+        <v>151</v>
       </c>
       <c r="D145" t="s">
         <v>185</v>
@@ -29137,7 +29137,7 @@
         <v>331</v>
       </c>
       <c r="F145" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="G145">
         <v>0</v>
@@ -29167,13 +29167,13 @@
         <v>699</v>
       </c>
       <c r="P145">
-        <v>2.15</v>
+        <v>3.87</v>
       </c>
       <c r="Q145">
-        <v>3.7</v>
+        <v>3.87</v>
       </c>
       <c r="R145">
-        <v>3.01</v>
+        <v>1.89</v>
       </c>
       <c r="S145">
         <v>0</v>
@@ -29313,16 +29313,16 @@
         <v>87</v>
       </c>
       <c r="C146" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="D146" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E146" t="s">
         <v>332</v>
       </c>
       <c r="F146" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="G146">
         <v>0</v>
@@ -29352,13 +29352,13 @@
         <v>699</v>
       </c>
       <c r="P146">
-        <v>4.07</v>
+        <v>0</v>
       </c>
       <c r="Q146">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="R146">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="S146">
         <v>0</v>
@@ -29501,13 +29501,13 @@
         <v>166</v>
       </c>
       <c r="D147" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E147" t="s">
         <v>333</v>
       </c>
       <c r="F147" t="s">
-        <v>588</v>
+        <v>290</v>
       </c>
       <c r="G147">
         <v>0</v>
@@ -29537,13 +29537,13 @@
         <v>699</v>
       </c>
       <c r="P147">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="Q147">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R147">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="S147">
         <v>0</v>
@@ -29683,7 +29683,7 @@
         <v>87</v>
       </c>
       <c r="C148" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="D148" t="s">
         <v>185</v>
@@ -29722,13 +29722,13 @@
         <v>699</v>
       </c>
       <c r="P148">
-        <v>5.4</v>
+        <v>3.1</v>
       </c>
       <c r="Q148">
-        <v>4.6</v>
+        <v>3.7</v>
       </c>
       <c r="R148">
-        <v>1.51</v>
+        <v>2.12</v>
       </c>
       <c r="S148">
         <v>0</v>
@@ -29868,7 +29868,7 @@
         <v>87</v>
       </c>
       <c r="C149" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="D149" t="s">
         <v>186</v>
@@ -29907,13 +29907,13 @@
         <v>699</v>
       </c>
       <c r="P149">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Q149">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="R149">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="S149">
         <v>0</v>
@@ -30053,7 +30053,7 @@
         <v>87</v>
       </c>
       <c r="C150" t="s">
-        <v>124</v>
+        <v>158</v>
       </c>
       <c r="D150" t="s">
         <v>186</v>
@@ -30238,10 +30238,10 @@
         <v>87</v>
       </c>
       <c r="C151" t="s">
-        <v>160</v>
+        <v>145</v>
       </c>
       <c r="D151" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E151" t="s">
         <v>337</v>
@@ -30423,7 +30423,7 @@
         <v>87</v>
       </c>
       <c r="C152" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="D152" t="s">
         <v>186</v>
@@ -30462,13 +30462,13 @@
         <v>699</v>
       </c>
       <c r="P152">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="Q152">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R152">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="S152">
         <v>0</v>
@@ -30507,10 +30507,10 @@
         <v>0</v>
       </c>
       <c r="AE152">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AF152">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AG152">
         <v>0</v>
@@ -30608,7 +30608,7 @@
         <v>87</v>
       </c>
       <c r="C153" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="D153" t="s">
         <v>186</v>
@@ -30647,13 +30647,13 @@
         <v>699</v>
       </c>
       <c r="P153">
-        <v>2.51</v>
+        <v>0</v>
       </c>
       <c r="Q153">
-        <v>3.78</v>
+        <v>0</v>
       </c>
       <c r="R153">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="S153">
         <v>0</v>
@@ -30793,7 +30793,7 @@
         <v>87</v>
       </c>
       <c r="C154" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="D154" t="s">
         <v>186</v>
@@ -30978,7 +30978,7 @@
         <v>87</v>
       </c>
       <c r="C155" t="s">
-        <v>143</v>
+        <v>128</v>
       </c>
       <c r="D155" t="s">
         <v>186</v>
@@ -31017,13 +31017,13 @@
         <v>699</v>
       </c>
       <c r="P155">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="Q155">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R155">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="S155">
         <v>0</v>
@@ -31163,10 +31163,10 @@
         <v>87</v>
       </c>
       <c r="C156" t="s">
-        <v>160</v>
+        <v>165</v>
       </c>
       <c r="D156" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E156" t="s">
         <v>342</v>
@@ -31202,13 +31202,13 @@
         <v>699</v>
       </c>
       <c r="P156">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Q156">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R156">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="S156">
         <v>0</v>
@@ -32088,7 +32088,7 @@
         <v>89</v>
       </c>
       <c r="C161" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="D161" t="s">
         <v>186</v>
@@ -32127,13 +32127,13 @@
         <v>699</v>
       </c>
       <c r="P161">
-        <v>1.78</v>
+        <v>5.17</v>
       </c>
       <c r="Q161">
-        <v>4.32</v>
+        <v>4.37</v>
       </c>
       <c r="R161">
-        <v>4.52</v>
+        <v>1.69</v>
       </c>
       <c r="S161">
         <v>0</v>
@@ -32172,16 +32172,16 @@
         <v>0</v>
       </c>
       <c r="AE161">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AF161">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AG161">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AH161">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AI161">
         <v>0</v>
@@ -32458,7 +32458,7 @@
         <v>89</v>
       </c>
       <c r="C163" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="D163" t="s">
         <v>186</v>
@@ -32643,7 +32643,7 @@
         <v>89</v>
       </c>
       <c r="C164" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="D164" t="s">
         <v>186</v>
@@ -32682,13 +32682,13 @@
         <v>699</v>
       </c>
       <c r="P164">
-        <v>5.17</v>
+        <v>1.78</v>
       </c>
       <c r="Q164">
-        <v>4.37</v>
+        <v>4.32</v>
       </c>
       <c r="R164">
-        <v>1.69</v>
+        <v>4.52</v>
       </c>
       <c r="S164">
         <v>0</v>
@@ -32727,16 +32727,16 @@
         <v>0</v>
       </c>
       <c r="AE164">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AF164">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AG164">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AH164">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AI164">
         <v>0</v>
@@ -33013,7 +33013,7 @@
         <v>90</v>
       </c>
       <c r="C166" t="s">
-        <v>120</v>
+        <v>169</v>
       </c>
       <c r="D166" t="s">
         <v>186</v>
@@ -33383,7 +33383,7 @@
         <v>90</v>
       </c>
       <c r="C168" t="s">
-        <v>156</v>
+        <v>120</v>
       </c>
       <c r="D168" t="s">
         <v>186</v>
@@ -33422,13 +33422,13 @@
         <v>699</v>
       </c>
       <c r="P168">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="Q168">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="R168">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="S168">
         <v>0</v>
@@ -33568,7 +33568,7 @@
         <v>90</v>
       </c>
       <c r="C169" t="s">
-        <v>144</v>
+        <v>169</v>
       </c>
       <c r="D169" t="s">
         <v>186</v>
@@ -33753,7 +33753,7 @@
         <v>90</v>
       </c>
       <c r="C170" t="s">
-        <v>131</v>
+        <v>170</v>
       </c>
       <c r="D170" t="s">
         <v>186</v>
@@ -33792,13 +33792,13 @@
         <v>699</v>
       </c>
       <c r="P170">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="Q170">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="R170">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="S170">
         <v>0</v>
@@ -34123,10 +34123,10 @@
         <v>90</v>
       </c>
       <c r="C172" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="D172" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E172" t="s">
         <v>358</v>
@@ -34162,13 +34162,13 @@
         <v>699</v>
       </c>
       <c r="P172">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="Q172">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R172">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="S172">
         <v>0</v>
@@ -34308,7 +34308,7 @@
         <v>90</v>
       </c>
       <c r="C173" t="s">
-        <v>169</v>
+        <v>146</v>
       </c>
       <c r="D173" t="s">
         <v>186</v>
@@ -34493,7 +34493,7 @@
         <v>90</v>
       </c>
       <c r="C174" t="s">
-        <v>170</v>
+        <v>153</v>
       </c>
       <c r="D174" t="s">
         <v>186</v>
@@ -34532,13 +34532,13 @@
         <v>699</v>
       </c>
       <c r="P174">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="Q174">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R174">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="S174">
         <v>0</v>
@@ -34678,10 +34678,10 @@
         <v>90</v>
       </c>
       <c r="C175" t="s">
-        <v>169</v>
+        <v>135</v>
       </c>
       <c r="D175" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E175" t="s">
         <v>361</v>
@@ -35418,7 +35418,7 @@
         <v>92</v>
       </c>
       <c r="C179" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="D179" t="s">
         <v>185</v>
@@ -35603,7 +35603,7 @@
         <v>92</v>
       </c>
       <c r="C180" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="D180" t="s">
         <v>186</v>
@@ -35788,7 +35788,7 @@
         <v>92</v>
       </c>
       <c r="C181" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="D181" t="s">
         <v>185</v>
@@ -35973,7 +35973,7 @@
         <v>93</v>
       </c>
       <c r="C182" t="s">
-        <v>172</v>
+        <v>123</v>
       </c>
       <c r="D182" t="s">
         <v>186</v>
@@ -36012,13 +36012,13 @@
         <v>699</v>
       </c>
       <c r="P182">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Q182">
-        <v>0</v>
+        <v>3.66</v>
       </c>
       <c r="R182">
-        <v>0</v>
+        <v>3.36</v>
       </c>
       <c r="S182">
         <v>0</v>
@@ -36343,7 +36343,7 @@
         <v>93</v>
       </c>
       <c r="C184" t="s">
-        <v>161</v>
+        <v>172</v>
       </c>
       <c r="D184" t="s">
         <v>186</v>
@@ -36382,13 +36382,13 @@
         <v>699</v>
       </c>
       <c r="P184">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="Q184">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="R184">
-        <v>4.56</v>
+        <v>0</v>
       </c>
       <c r="S184">
         <v>0</v>
@@ -36528,7 +36528,7 @@
         <v>93</v>
       </c>
       <c r="C185" t="s">
-        <v>161</v>
+        <v>152</v>
       </c>
       <c r="D185" t="s">
         <v>186</v>
@@ -36567,13 +36567,13 @@
         <v>699</v>
       </c>
       <c r="P185">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="Q185">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="R185">
-        <v>6.76</v>
+        <v>0</v>
       </c>
       <c r="S185">
         <v>0</v>
@@ -36713,7 +36713,7 @@
         <v>93</v>
       </c>
       <c r="C186" t="s">
-        <v>139</v>
+        <v>149</v>
       </c>
       <c r="D186" t="s">
         <v>186</v>
@@ -36752,13 +36752,13 @@
         <v>699</v>
       </c>
       <c r="P186">
-        <v>1.28</v>
+        <v>1.91</v>
       </c>
       <c r="Q186">
-        <v>5.66</v>
+        <v>3.53</v>
       </c>
       <c r="R186">
-        <v>8.98</v>
+        <v>3.91</v>
       </c>
       <c r="S186">
         <v>0</v>
@@ -36797,10 +36797,10 @@
         <v>0</v>
       </c>
       <c r="AE186">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AF186">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AG186">
         <v>0</v>
@@ -36898,10 +36898,10 @@
         <v>93</v>
       </c>
       <c r="C187" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="D187" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E187" t="s">
         <v>373</v>
@@ -36937,13 +36937,13 @@
         <v>699</v>
       </c>
       <c r="P187">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Q187">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="R187">
-        <v>0</v>
+        <v>7.95</v>
       </c>
       <c r="S187">
         <v>0</v>
@@ -37083,7 +37083,7 @@
         <v>93</v>
       </c>
       <c r="C188" t="s">
-        <v>172</v>
+        <v>147</v>
       </c>
       <c r="D188" t="s">
         <v>186</v>
@@ -37268,7 +37268,7 @@
         <v>93</v>
       </c>
       <c r="C189" t="s">
-        <v>123</v>
+        <v>172</v>
       </c>
       <c r="D189" t="s">
         <v>186</v>
@@ -37307,13 +37307,13 @@
         <v>699</v>
       </c>
       <c r="P189">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Q189">
-        <v>3.66</v>
+        <v>0</v>
       </c>
       <c r="R189">
-        <v>3.36</v>
+        <v>0</v>
       </c>
       <c r="S189">
         <v>0</v>
@@ -37453,7 +37453,7 @@
         <v>93</v>
       </c>
       <c r="C190" t="s">
-        <v>155</v>
+        <v>149</v>
       </c>
       <c r="D190" t="s">
         <v>186</v>
@@ -37492,13 +37492,13 @@
         <v>699</v>
       </c>
       <c r="P190">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="Q190">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="R190">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="S190">
         <v>0</v>
@@ -37638,10 +37638,10 @@
         <v>93</v>
       </c>
       <c r="C191" t="s">
-        <v>173</v>
+        <v>142</v>
       </c>
       <c r="D191" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E191" t="s">
         <v>377</v>
@@ -37677,13 +37677,13 @@
         <v>699</v>
       </c>
       <c r="P191">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Q191">
-        <v>0</v>
+        <v>5.66</v>
       </c>
       <c r="R191">
-        <v>0</v>
+        <v>8.98</v>
       </c>
       <c r="S191">
         <v>0</v>
@@ -37823,7 +37823,7 @@
         <v>93</v>
       </c>
       <c r="C192" t="s">
-        <v>149</v>
+        <v>159</v>
       </c>
       <c r="D192" t="s">
         <v>186</v>
@@ -37862,13 +37862,13 @@
         <v>699</v>
       </c>
       <c r="P192">
-        <v>3.12</v>
+        <v>1.45</v>
       </c>
       <c r="Q192">
-        <v>3.22</v>
+        <v>3.8</v>
       </c>
       <c r="R192">
-        <v>2.43</v>
+        <v>6.76</v>
       </c>
       <c r="S192">
         <v>0</v>
@@ -38008,10 +38008,10 @@
         <v>93</v>
       </c>
       <c r="C193" t="s">
-        <v>149</v>
+        <v>174</v>
       </c>
       <c r="D193" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E193" t="s">
         <v>379</v>
@@ -38047,13 +38047,13 @@
         <v>699</v>
       </c>
       <c r="P193">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="Q193">
-        <v>3.53</v>
+        <v>0</v>
       </c>
       <c r="R193">
-        <v>3.91</v>
+        <v>0</v>
       </c>
       <c r="S193">
         <v>0</v>
@@ -38092,10 +38092,10 @@
         <v>0</v>
       </c>
       <c r="AE193">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AF193">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AG193">
         <v>0</v>
@@ -38193,10 +38193,10 @@
         <v>93</v>
       </c>
       <c r="C194" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="D194" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E194" t="s">
         <v>380</v>
@@ -38378,10 +38378,10 @@
         <v>93</v>
       </c>
       <c r="C195" t="s">
-        <v>148</v>
+        <v>174</v>
       </c>
       <c r="D195" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E195" t="s">
         <v>381</v>
@@ -38563,10 +38563,10 @@
         <v>93</v>
       </c>
       <c r="C196" t="s">
-        <v>174</v>
+        <v>159</v>
       </c>
       <c r="D196" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E196" t="s">
         <v>382</v>
@@ -38602,13 +38602,13 @@
         <v>699</v>
       </c>
       <c r="P196">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="Q196">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R196">
-        <v>0</v>
+        <v>4.56</v>
       </c>
       <c r="S196">
         <v>0</v>
@@ -38748,7 +38748,7 @@
         <v>94</v>
       </c>
       <c r="C197" t="s">
-        <v>175</v>
+        <v>158</v>
       </c>
       <c r="D197" t="s">
         <v>186</v>
@@ -38933,7 +38933,7 @@
         <v>94</v>
       </c>
       <c r="C198" t="s">
-        <v>175</v>
+        <v>125</v>
       </c>
       <c r="D198" t="s">
         <v>186</v>
@@ -39118,7 +39118,7 @@
         <v>94</v>
       </c>
       <c r="C199" t="s">
-        <v>175</v>
+        <v>158</v>
       </c>
       <c r="D199" t="s">
         <v>186</v>
@@ -39303,10 +39303,10 @@
         <v>94</v>
       </c>
       <c r="C200" t="s">
-        <v>146</v>
+        <v>175</v>
       </c>
       <c r="D200" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E200" t="s">
         <v>386</v>
@@ -39488,7 +39488,7 @@
         <v>94</v>
       </c>
       <c r="C201" t="s">
-        <v>124</v>
+        <v>175</v>
       </c>
       <c r="D201" t="s">
         <v>186</v>
@@ -39673,10 +39673,10 @@
         <v>94</v>
       </c>
       <c r="C202" t="s">
-        <v>160</v>
+        <v>145</v>
       </c>
       <c r="D202" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E202" t="s">
         <v>388</v>
@@ -39858,10 +39858,10 @@
         <v>94</v>
       </c>
       <c r="C203" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="D203" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E203" t="s">
         <v>389</v>
@@ -40043,10 +40043,10 @@
         <v>94</v>
       </c>
       <c r="C204" t="s">
-        <v>160</v>
+        <v>176</v>
       </c>
       <c r="D204" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E204" t="s">
         <v>390</v>
@@ -40082,13 +40082,13 @@
         <v>699</v>
       </c>
       <c r="P204">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="Q204">
-        <v>0</v>
+        <v>4.45</v>
       </c>
       <c r="R204">
-        <v>0</v>
+        <v>5.12</v>
       </c>
       <c r="S204">
         <v>0</v>
@@ -40228,7 +40228,7 @@
         <v>95</v>
       </c>
       <c r="C205" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="D205" t="s">
         <v>186</v>
@@ -40413,7 +40413,7 @@
         <v>96</v>
       </c>
       <c r="C206" t="s">
-        <v>142</v>
+        <v>157</v>
       </c>
       <c r="D206" t="s">
         <v>186</v>
@@ -40452,13 +40452,13 @@
         <v>699</v>
       </c>
       <c r="P206">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="Q206">
-        <v>0</v>
+        <v>3.94</v>
       </c>
       <c r="R206">
-        <v>0</v>
+        <v>4.41</v>
       </c>
       <c r="S206">
         <v>0</v>
@@ -40497,10 +40497,10 @@
         <v>0</v>
       </c>
       <c r="AE206">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AF206">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AG206">
         <v>0</v>
@@ -40598,7 +40598,7 @@
         <v>96</v>
       </c>
       <c r="C207" t="s">
-        <v>157</v>
+        <v>137</v>
       </c>
       <c r="D207" t="s">
         <v>186</v>
@@ -40637,13 +40637,13 @@
         <v>699</v>
       </c>
       <c r="P207">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="Q207">
-        <v>3.94</v>
+        <v>0</v>
       </c>
       <c r="R207">
-        <v>4.41</v>
+        <v>0</v>
       </c>
       <c r="S207">
         <v>0</v>
@@ -40682,10 +40682,10 @@
         <v>0</v>
       </c>
       <c r="AE207">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AF207">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AG207">
         <v>0</v>
@@ -41153,7 +41153,7 @@
         <v>97</v>
       </c>
       <c r="C210" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="D210" t="s">
         <v>186</v>
@@ -41338,7 +41338,7 @@
         <v>97</v>
       </c>
       <c r="C211" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="D211" t="s">
         <v>186</v>
@@ -41523,10 +41523,10 @@
         <v>98</v>
       </c>
       <c r="C212" t="s">
-        <v>178</v>
+        <v>127</v>
       </c>
       <c r="D212" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E212" t="s">
         <v>398</v>
@@ -41708,10 +41708,10 @@
         <v>98</v>
       </c>
       <c r="C213" t="s">
-        <v>128</v>
+        <v>178</v>
       </c>
       <c r="D213" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E213" t="s">
         <v>399</v>
@@ -42078,10 +42078,10 @@
         <v>100</v>
       </c>
       <c r="C215" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="D215" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E215" t="s">
         <v>401</v>
@@ -42117,13 +42117,13 @@
         <v>699</v>
       </c>
       <c r="P215">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="Q215">
-        <v>0</v>
+        <v>4.73</v>
       </c>
       <c r="R215">
-        <v>0</v>
+        <v>5.79</v>
       </c>
       <c r="S215">
         <v>0</v>
@@ -42168,10 +42168,10 @@
         <v>0</v>
       </c>
       <c r="AG215">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AH215">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AI215">
         <v>0</v>
@@ -42263,10 +42263,10 @@
         <v>100</v>
       </c>
       <c r="C216" t="s">
-        <v>179</v>
+        <v>147</v>
       </c>
       <c r="D216" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E216" t="s">
         <v>402</v>
@@ -42302,13 +42302,13 @@
         <v>699</v>
       </c>
       <c r="P216">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Q216">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="R216">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="S216">
         <v>0</v>
@@ -42347,10 +42347,10 @@
         <v>0</v>
       </c>
       <c r="AE216">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AF216">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AG216">
         <v>0</v>
@@ -42448,7 +42448,7 @@
         <v>100</v>
       </c>
       <c r="C217" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="D217" t="s">
         <v>186</v>
@@ -42487,13 +42487,13 @@
         <v>699</v>
       </c>
       <c r="P217">
-        <v>1.18</v>
+        <v>3.17</v>
       </c>
       <c r="Q217">
-        <v>9.15</v>
+        <v>3.68</v>
       </c>
       <c r="R217">
-        <v>17</v>
+        <v>2.34</v>
       </c>
       <c r="S217">
         <v>0</v>
@@ -42532,16 +42532,16 @@
         <v>0</v>
       </c>
       <c r="AE217">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AF217">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG217">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AH217">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AI217">
         <v>0</v>
@@ -42633,7 +42633,7 @@
         <v>100</v>
       </c>
       <c r="C218" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="D218" t="s">
         <v>185</v>
@@ -42818,10 +42818,10 @@
         <v>100</v>
       </c>
       <c r="C219" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="D219" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E219" t="s">
         <v>405</v>
@@ -42857,13 +42857,13 @@
         <v>699</v>
       </c>
       <c r="P219">
-        <v>4.05</v>
+        <v>2.15</v>
       </c>
       <c r="Q219">
-        <v>3.76</v>
+        <v>3.44</v>
       </c>
       <c r="R219">
-        <v>1.99</v>
+        <v>3.5</v>
       </c>
       <c r="S219">
         <v>0</v>
@@ -42902,10 +42902,10 @@
         <v>0</v>
       </c>
       <c r="AE219">
-        <v>1.85</v>
+        <v>1.95</v>
       </c>
       <c r="AF219">
-        <v>1.85</v>
+        <v>1.75</v>
       </c>
       <c r="AG219">
         <v>0</v>
@@ -43003,7 +43003,7 @@
         <v>100</v>
       </c>
       <c r="C220" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="D220" t="s">
         <v>186</v>
@@ -43188,10 +43188,10 @@
         <v>100</v>
       </c>
       <c r="C221" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="D221" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E221" t="s">
         <v>407</v>
@@ -43227,13 +43227,13 @@
         <v>699</v>
       </c>
       <c r="P221">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="Q221">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="R221">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="S221">
         <v>0</v>
@@ -43272,10 +43272,10 @@
         <v>0</v>
       </c>
       <c r="AE221">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AF221">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AG221">
         <v>0</v>
@@ -43373,10 +43373,10 @@
         <v>100</v>
       </c>
       <c r="C222" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="D222" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E222" t="s">
         <v>408</v>
@@ -43412,13 +43412,13 @@
         <v>699</v>
       </c>
       <c r="P222">
-        <v>3.8</v>
+        <v>5.3</v>
       </c>
       <c r="Q222">
-        <v>3.78</v>
+        <v>3.73</v>
       </c>
       <c r="R222">
-        <v>2.05</v>
+        <v>1.71</v>
       </c>
       <c r="S222">
         <v>0</v>
@@ -43457,10 +43457,10 @@
         <v>0</v>
       </c>
       <c r="AE222">
+        <v>1.95</v>
+      </c>
+      <c r="AF222">
         <v>1.73</v>
-      </c>
-      <c r="AF222">
-        <v>1.98</v>
       </c>
       <c r="AG222">
         <v>0</v>
@@ -43558,7 +43558,7 @@
         <v>100</v>
       </c>
       <c r="C223" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="D223" t="s">
         <v>185</v>
@@ -43743,7 +43743,7 @@
         <v>100</v>
       </c>
       <c r="C224" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="D224" t="s">
         <v>185</v>
@@ -43782,13 +43782,13 @@
         <v>699</v>
       </c>
       <c r="P224">
-        <v>5.3</v>
+        <v>0</v>
       </c>
       <c r="Q224">
-        <v>3.73</v>
+        <v>0</v>
       </c>
       <c r="R224">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="S224">
         <v>0</v>
@@ -43827,10 +43827,10 @@
         <v>0</v>
       </c>
       <c r="AE224">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AF224">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AG224">
         <v>0</v>
@@ -43928,7 +43928,7 @@
         <v>100</v>
       </c>
       <c r="C225" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="D225" t="s">
         <v>186</v>
@@ -43967,13 +43967,13 @@
         <v>699</v>
       </c>
       <c r="P225">
-        <v>3.17</v>
+        <v>4.68</v>
       </c>
       <c r="Q225">
-        <v>3.68</v>
+        <v>4.32</v>
       </c>
       <c r="R225">
-        <v>2.34</v>
+        <v>1.76</v>
       </c>
       <c r="S225">
         <v>0</v>
@@ -44012,10 +44012,10 @@
         <v>0</v>
       </c>
       <c r="AE225">
-        <v>1.72</v>
+        <v>1.58</v>
       </c>
       <c r="AF225">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="AG225">
         <v>0</v>
@@ -44113,7 +44113,7 @@
         <v>100</v>
       </c>
       <c r="C226" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="D226" t="s">
         <v>186</v>
@@ -44152,13 +44152,13 @@
         <v>699</v>
       </c>
       <c r="P226">
-        <v>2.48</v>
+        <v>4.05</v>
       </c>
       <c r="Q226">
-        <v>3.5</v>
+        <v>3.76</v>
       </c>
       <c r="R226">
-        <v>3.07</v>
+        <v>1.99</v>
       </c>
       <c r="S226">
         <v>0</v>
@@ -44197,10 +44197,10 @@
         <v>0</v>
       </c>
       <c r="AE226">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="AF226">
-        <v>1.9</v>
+        <v>1.85</v>
       </c>
       <c r="AG226">
         <v>0</v>
@@ -44298,7 +44298,7 @@
         <v>100</v>
       </c>
       <c r="C227" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="D227" t="s">
         <v>186</v>
@@ -44337,13 +44337,13 @@
         <v>699</v>
       </c>
       <c r="P227">
-        <v>4.68</v>
+        <v>1.18</v>
       </c>
       <c r="Q227">
-        <v>4.32</v>
+        <v>9.15</v>
       </c>
       <c r="R227">
-        <v>1.76</v>
+        <v>17</v>
       </c>
       <c r="S227">
         <v>0</v>
@@ -44382,16 +44382,16 @@
         <v>0</v>
       </c>
       <c r="AE227">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AF227">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AG227">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AH227">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AI227">
         <v>0</v>
@@ -44483,10 +44483,10 @@
         <v>100</v>
       </c>
       <c r="C228" t="s">
-        <v>148</v>
+        <v>178</v>
       </c>
       <c r="D228" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E228" t="s">
         <v>414</v>
@@ -44668,7 +44668,7 @@
         <v>100</v>
       </c>
       <c r="C229" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="D229" t="s">
         <v>186</v>
@@ -44707,13 +44707,13 @@
         <v>699</v>
       </c>
       <c r="P229">
-        <v>1.59</v>
+        <v>2.48</v>
       </c>
       <c r="Q229">
-        <v>4.73</v>
+        <v>3.5</v>
       </c>
       <c r="R229">
-        <v>5.79</v>
+        <v>3.07</v>
       </c>
       <c r="S229">
         <v>0</v>
@@ -44752,16 +44752,16 @@
         <v>0</v>
       </c>
       <c r="AE229">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AF229">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AG229">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AH229">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AI229">
         <v>0</v>
@@ -45593,7 +45593,7 @@
         <v>102</v>
       </c>
       <c r="C234" t="s">
-        <v>178</v>
+        <v>173</v>
       </c>
       <c r="D234" t="s">
         <v>185</v>
@@ -45778,7 +45778,7 @@
         <v>102</v>
       </c>
       <c r="C235" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="D235" t="s">
         <v>185</v>
@@ -45963,7 +45963,7 @@
         <v>102</v>
       </c>
       <c r="C236" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="D236" t="s">
         <v>185</v>
@@ -46372,13 +46372,13 @@
         <v>699</v>
       </c>
       <c r="P238">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="Q238">
-        <v>0</v>
+        <v>3.61</v>
       </c>
       <c r="R238">
-        <v>0</v>
+        <v>5.14</v>
       </c>
       <c r="S238">
         <v>0</v>
@@ -46557,13 +46557,13 @@
         <v>699</v>
       </c>
       <c r="P239">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="Q239">
-        <v>3.61</v>
+        <v>0</v>
       </c>
       <c r="R239">
-        <v>5.14</v>
+        <v>0</v>
       </c>
       <c r="S239">
         <v>0</v>
@@ -46888,7 +46888,7 @@
         <v>105</v>
       </c>
       <c r="C241" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="D241" t="s">
         <v>185</v>
@@ -47073,7 +47073,7 @@
         <v>106</v>
       </c>
       <c r="C242" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="D242" t="s">
         <v>185</v>
@@ -47258,7 +47258,7 @@
         <v>106</v>
       </c>
       <c r="C243" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="D243" t="s">
         <v>185</v>
@@ -47297,13 +47297,13 @@
         <v>699</v>
       </c>
       <c r="P243">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="Q243">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="R243">
-        <v>3.67</v>
+        <v>0</v>
       </c>
       <c r="S243">
         <v>0</v>
@@ -47342,10 +47342,10 @@
         <v>0</v>
       </c>
       <c r="AE243">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AF243">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AG243">
         <v>0</v>
@@ -47443,7 +47443,7 @@
         <v>106</v>
       </c>
       <c r="C244" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="D244" t="s">
         <v>185</v>
@@ -47628,7 +47628,7 @@
         <v>106</v>
       </c>
       <c r="C245" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="D245" t="s">
         <v>185</v>
@@ -47667,13 +47667,13 @@
         <v>699</v>
       </c>
       <c r="P245">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="Q245">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="R245">
-        <v>0</v>
+        <v>3.67</v>
       </c>
       <c r="S245">
         <v>0</v>
@@ -47712,10 +47712,10 @@
         <v>0</v>
       </c>
       <c r="AE245">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AF245">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AG245">
         <v>0</v>
@@ -47998,7 +47998,7 @@
         <v>108</v>
       </c>
       <c r="C247" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="D247" t="s">
         <v>185</v>
@@ -48183,7 +48183,7 @@
         <v>108</v>
       </c>
       <c r="C248" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="D248" t="s">
         <v>185</v>
@@ -48368,7 +48368,7 @@
         <v>109</v>
       </c>
       <c r="C249" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="D249" t="s">
         <v>185</v>
@@ -48553,7 +48553,7 @@
         <v>109</v>
       </c>
       <c r="C250" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="D250" t="s">
         <v>185</v>
@@ -48738,7 +48738,7 @@
         <v>109</v>
       </c>
       <c r="C251" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="D251" t="s">
         <v>185</v>
@@ -48923,7 +48923,7 @@
         <v>110</v>
       </c>
       <c r="C252" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="D252" t="s">
         <v>185</v>
@@ -49147,13 +49147,13 @@
         <v>699</v>
       </c>
       <c r="P253">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="Q253">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R253">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="S253">
         <v>0</v>
@@ -49293,7 +49293,7 @@
         <v>111</v>
       </c>
       <c r="C254" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="D254" t="s">
         <v>185</v>
@@ -49332,13 +49332,13 @@
         <v>699</v>
       </c>
       <c r="P254">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="Q254">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="R254">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="S254">
         <v>0</v>
@@ -49848,7 +49848,7 @@
         <v>114</v>
       </c>
       <c r="C257" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="D257" t="s">
         <v>185</v>

--- a/jogos_2026-05-10.xlsx
+++ b/jogos_2026-05-10.xlsx
@@ -361,21 +361,21 @@
     <t>22:00</t>
   </si>
   <si>
+    <t>South Korea K League 2</t>
+  </si>
+  <si>
     <t>Australia New South Wales NPL</t>
   </si>
   <si>
-    <t>South Korea K League 2</t>
-  </si>
-  <si>
     <t>South Korea K League 1</t>
   </si>
   <si>
+    <t>Russia FNL</t>
+  </si>
+  <si>
     <t>China China League One</t>
   </si>
   <si>
-    <t>Russia FNL</t>
-  </si>
-  <si>
     <t>Czech Republic FNL</t>
   </si>
   <si>
@@ -388,24 +388,24 @@
     <t>Russia Russian Premier League</t>
   </si>
   <si>
+    <t>Kazakhstan Kazakhstan Premier League</t>
+  </si>
+  <si>
+    <t>Vietnam V.League 1</t>
+  </si>
+  <si>
     <t>Ethiopia Ethiopia Premier League</t>
   </si>
   <si>
+    <t>Portugal Liga 3</t>
+  </si>
+  <si>
     <t>Spain Primera Division Women</t>
   </si>
   <si>
-    <t>Vietnam V.League 1</t>
-  </si>
-  <si>
-    <t>Portugal Liga 3</t>
-  </si>
-  <si>
     <t>Poland 1. Liga</t>
   </si>
   <si>
-    <t>Kazakhstan Kazakhstan Premier League</t>
-  </si>
-  <si>
     <t>Poland Ekstraklasa</t>
   </si>
   <si>
@@ -415,87 +415,87 @@
     <t>Thailand Thai League T1</t>
   </si>
   <si>
+    <t>Sweden Damallsvenskan</t>
+  </si>
+  <si>
     <t>Scotland Premiership</t>
   </si>
   <si>
-    <t>Sweden Damallsvenskan</t>
+    <t>Bulgaria First League</t>
   </si>
   <si>
     <t>Lithuania A Lyga</t>
   </si>
   <si>
-    <t>Bulgaria First League</t>
+    <t>Germany 2. Bundesliga</t>
+  </si>
+  <si>
+    <t>Singapore S.League</t>
+  </si>
+  <si>
+    <t>Belgium Pro League</t>
   </si>
   <si>
     <t>Germany 3. Liga</t>
   </si>
   <si>
-    <t>Singapore S.League</t>
-  </si>
-  <si>
-    <t>Germany 2. Bundesliga</t>
+    <t>Estonia Meistriliiga</t>
   </si>
   <si>
     <t>India Indian Super League</t>
   </si>
   <si>
-    <t>Estonia Meistriliiga</t>
-  </si>
-  <si>
-    <t>Belgium Pro League</t>
-  </si>
-  <si>
     <t>Croatia Druga HNL</t>
   </si>
   <si>
+    <t>Sweden Allsvenskan</t>
+  </si>
+  <si>
+    <t>Denmark Superliga</t>
+  </si>
+  <si>
+    <t>Spain La Liga</t>
+  </si>
+  <si>
+    <t>Spain Segunda División</t>
+  </si>
+  <si>
+    <t>Georgia Erovnuli Liga</t>
+  </si>
+  <si>
     <t>Switzerland Super League</t>
   </si>
   <si>
-    <t>Georgia Erovnuli Liga</t>
-  </si>
-  <si>
-    <t>Denmark Superliga</t>
-  </si>
-  <si>
-    <t>Spain La Liga</t>
-  </si>
-  <si>
-    <t>Sweden Allsvenskan</t>
-  </si>
-  <si>
-    <t>Spain Segunda División</t>
-  </si>
-  <si>
     <t>Malaysia Super League</t>
   </si>
   <si>
     <t>Norway Eliteserien</t>
   </si>
   <si>
+    <t>Slovenia PrvaLiga</t>
+  </si>
+  <si>
+    <t>England Premier League</t>
+  </si>
+  <si>
     <t>Czech Republic First League</t>
   </si>
   <si>
+    <t>Azerbaijan Premyer Liqası</t>
+  </si>
+  <si>
     <t>Romania Liga I</t>
   </si>
   <si>
-    <t>England Premier League</t>
-  </si>
-  <si>
-    <t>Slovenia PrvaLiga</t>
-  </si>
-  <si>
-    <t>Azerbaijan Premyer Liqası</t>
-  </si>
-  <si>
     <t>Germany Bundesliga</t>
   </si>
   <si>
+    <t>Greece Super League</t>
+  </si>
+  <si>
     <t>Hungary NB II</t>
   </si>
   <si>
-    <t>Greece Super League</t>
-  </si>
-  <si>
     <t>Faroe Islands Faroe Islands Premier League</t>
   </si>
   <si>
@@ -508,12 +508,12 @@
     <t>FYR Macedonia First Football League</t>
   </si>
   <si>
+    <t>Norway First Division</t>
+  </si>
+  <si>
     <t>Austria Bundesliga</t>
   </si>
   <si>
-    <t>Norway First Division</t>
-  </si>
-  <si>
     <t>Cyprus First Division</t>
   </si>
   <si>
@@ -523,24 +523,24 @@
     <t>South Africa Premier Soccer League</t>
   </si>
   <si>
+    <t>Morocco Botola Pro</t>
+  </si>
+  <si>
     <t>Montenegro Montenegrin First League</t>
   </si>
   <si>
-    <t>Morocco Botola Pro</t>
-  </si>
-  <si>
     <t>Saudi Arabia Professional League</t>
   </si>
   <si>
     <t>Serbia SuperLiga</t>
   </si>
   <si>
+    <t>Chile Primera B</t>
+  </si>
+  <si>
     <t>USA NWSL</t>
   </si>
   <si>
-    <t>Chile Primera B</t>
-  </si>
-  <si>
     <t>Israel Israeli Premier League</t>
   </si>
   <si>
@@ -559,18 +559,18 @@
     <t>Brazil Serie B</t>
   </si>
   <si>
+    <t>Bolivia LFPB</t>
+  </si>
+  <si>
     <t>Brazil Serie A</t>
   </si>
   <si>
-    <t>Bolivia LFPB</t>
+    <t>USA MLS</t>
   </si>
   <si>
     <t>Ecuador Primera Categoría Serie A</t>
   </si>
   <si>
-    <t>USA MLS</t>
-  </si>
-  <si>
     <t>2026</t>
   </si>
   <si>
@@ -580,12 +580,12 @@
     <t>2025</t>
   </si>
   <si>
+    <t>Seongnam</t>
+  </si>
+  <si>
     <t>Rockdale City Suns</t>
   </si>
   <si>
-    <t>Seongnam</t>
-  </si>
-  <si>
     <t>Blacktown City</t>
   </si>
   <si>
@@ -595,33 +595,33 @@
     <t>APIA Leichhardt Tigers</t>
   </si>
   <si>
+    <t>Ufa</t>
+  </si>
+  <si>
     <t>Shaanxi Union</t>
   </si>
   <si>
-    <t>Ufa</t>
+    <t>Dalian Huayi</t>
   </si>
   <si>
     <t>Yanbian Longding</t>
   </si>
   <si>
-    <t>Dalian Huayi</t>
+    <t>Ansan Greeners</t>
   </si>
   <si>
     <t>Busan I'Park</t>
   </si>
   <si>
-    <t>Ansan Greeners</t>
-  </si>
-  <si>
     <t>Anyang</t>
   </si>
   <si>
+    <t>Viktoria Žižkov</t>
+  </si>
+  <si>
     <t>Slavia Praha U21</t>
   </si>
   <si>
-    <t>Viktoria Žižkov</t>
-  </si>
-  <si>
     <t>Persija</t>
   </si>
   <si>
@@ -634,123 +634,123 @@
     <t>Orenburg</t>
   </si>
   <si>
+    <t>Ulytau</t>
+  </si>
+  <si>
+    <t>Gyeongnam</t>
+  </si>
+  <si>
+    <t>Hoang Anh Gia Lai</t>
+  </si>
+  <si>
     <t>Sheger Ketema</t>
   </si>
   <si>
+    <t>Sichuan Jiuniu</t>
+  </si>
+  <si>
+    <t>Amarante</t>
+  </si>
+  <si>
+    <t>Sokol Saratov</t>
+  </si>
+  <si>
     <t>Levante W</t>
   </si>
   <si>
-    <t>Sichuan Jiuniu</t>
-  </si>
-  <si>
-    <t>Sokol Saratov</t>
-  </si>
-  <si>
-    <t>Hoang Anh Gia Lai</t>
-  </si>
-  <si>
-    <t>Amarante</t>
-  </si>
-  <si>
     <t>Polonia Warszawa</t>
   </si>
   <si>
-    <t>Ulytau</t>
-  </si>
-  <si>
-    <t>Gyeongnam</t>
-  </si>
-  <si>
     <t>Piast Gliwice</t>
   </si>
   <si>
     <t>Hellas Verona</t>
   </si>
   <si>
+    <t>Chonburi</t>
+  </si>
+  <si>
+    <t>Ayutthaya United</t>
+  </si>
+  <si>
+    <t>Shenzhen Juniors</t>
+  </si>
+  <si>
+    <t>Bangkok Glass</t>
+  </si>
+  <si>
+    <t>Buriram United</t>
+  </si>
+  <si>
+    <t>Hà Nội II</t>
+  </si>
+  <si>
+    <t>Rayong</t>
+  </si>
+  <si>
+    <t>Piteå Women</t>
+  </si>
+  <si>
+    <t>Chiangrai United</t>
+  </si>
+  <si>
+    <t>Shenyang Urban</t>
+  </si>
+  <si>
+    <t>Kanchanaburi</t>
+  </si>
+  <si>
+    <t>Celtic</t>
+  </si>
+  <si>
+    <t>Ho Chi Minh City</t>
+  </si>
+  <si>
+    <t>Altay</t>
+  </si>
+  <si>
     <t>Sukhothai</t>
   </si>
   <si>
-    <t>Chonburi</t>
-  </si>
-  <si>
-    <t>Altay</t>
-  </si>
-  <si>
-    <t>Celtic</t>
-  </si>
-  <si>
-    <t>Hà Nội II</t>
-  </si>
-  <si>
-    <t>Shenzhen Juniors</t>
-  </si>
-  <si>
-    <t>Shenyang Urban</t>
-  </si>
-  <si>
-    <t>Piteå Women</t>
-  </si>
-  <si>
-    <t>Ho Chi Minh City</t>
-  </si>
-  <si>
-    <t>Rayong</t>
-  </si>
-  <si>
-    <t>Buriram United</t>
-  </si>
-  <si>
-    <t>Kanchanaburi</t>
-  </si>
-  <si>
-    <t>Ayutthaya United</t>
-  </si>
-  <si>
-    <t>Chiangrai United</t>
-  </si>
-  <si>
-    <t>Bangkok Glass</t>
+    <t>Spartak Varna</t>
   </si>
   <si>
     <t>Sūduva</t>
   </si>
   <si>
-    <t>Spartak Varna</t>
+    <t>Fortuna Düsseldorf</t>
+  </si>
+  <si>
+    <t>Nantong Zhiyun</t>
+  </si>
+  <si>
+    <t>Preußen Münster</t>
+  </si>
+  <si>
+    <t>Home United</t>
+  </si>
+  <si>
+    <t>Dongguan United</t>
+  </si>
+  <si>
+    <t>KAA Gent</t>
   </si>
   <si>
     <t>Havelse</t>
   </si>
   <si>
+    <t>Nõmme Kalju</t>
+  </si>
+  <si>
+    <t>Hertha BSC</t>
+  </si>
+  <si>
+    <t>Kerala Blasters</t>
+  </si>
+  <si>
     <t>Hougang United</t>
   </si>
   <si>
-    <t>Home United</t>
-  </si>
-  <si>
-    <t>Hertha BSC</t>
-  </si>
-  <si>
-    <t>Kerala Blasters</t>
-  </si>
-  <si>
-    <t>Nõmme Kalju</t>
-  </si>
-  <si>
-    <t>Fortuna Düsseldorf</t>
-  </si>
-  <si>
-    <t>KAA Gent</t>
-  </si>
-  <si>
-    <t>Preußen Münster</t>
-  </si>
-  <si>
-    <t>Dongguan United</t>
-  </si>
-  <si>
-    <t>Nantong Zhiyun</t>
-  </si>
-  <si>
     <t>Beijing Guoan</t>
   </si>
   <si>
@@ -760,166 +760,181 @@
     <t>Hrvace</t>
   </si>
   <si>
+    <t>AIK</t>
+  </si>
+  <si>
+    <t>Vejle</t>
+  </si>
+  <si>
+    <t>Kalmar</t>
+  </si>
+  <si>
+    <t>RCD Mallorca</t>
+  </si>
+  <si>
+    <t>Qingdao Jonoon</t>
+  </si>
+  <si>
+    <t>Aktobe</t>
+  </si>
+  <si>
+    <t>FC Andorra</t>
+  </si>
+  <si>
+    <t>Meshakhte</t>
+  </si>
+  <si>
     <t>Lugano</t>
   </si>
   <si>
-    <t>Meshakhte</t>
+    <t>PSIM Yogyakarta</t>
   </si>
   <si>
     <t>Nordsjælland</t>
   </si>
   <si>
-    <t>PSIM Yogyakarta</t>
-  </si>
-  <si>
-    <t>RCD Mallorca</t>
-  </si>
-  <si>
-    <t>Kalmar</t>
-  </si>
-  <si>
-    <t>Vejle</t>
-  </si>
-  <si>
-    <t>Aktobe</t>
+    <t>Zenit</t>
   </si>
   <si>
     <t>Bahardar</t>
   </si>
   <si>
-    <t>AIK</t>
-  </si>
-  <si>
-    <t>FC Andorra</t>
-  </si>
-  <si>
-    <t>Qingdao Jonoon</t>
-  </si>
-  <si>
-    <t>Zenit</t>
-  </si>
-  <si>
     <t>Công An Nhân Dân</t>
   </si>
   <si>
     <t>Kuala Lumpur</t>
   </si>
   <si>
+    <t>Rosenborg</t>
+  </si>
+  <si>
+    <t>Baník Ostrava U21</t>
+  </si>
+  <si>
     <t>Tychy 71</t>
   </si>
   <si>
-    <t>Baník Ostrava U21</t>
-  </si>
-  <si>
-    <t>Rosenborg</t>
-  </si>
-  <si>
     <t>Wisła Płock</t>
   </si>
   <si>
+    <t>NK Primorje</t>
+  </si>
+  <si>
+    <t>Nottingham Forest</t>
+  </si>
+  <si>
+    <t>Pardubice</t>
+  </si>
+  <si>
+    <t>Astana</t>
+  </si>
+  <si>
+    <t>Uppsala W</t>
+  </si>
+  <si>
+    <t>Cremonese</t>
+  </si>
+  <si>
+    <t>Burnley</t>
+  </si>
+  <si>
+    <t>Crystal Palace</t>
+  </si>
+  <si>
+    <t>Fiorentina</t>
+  </si>
+  <si>
+    <t>Arba Minch Kenema</t>
+  </si>
+  <si>
+    <t>Kelantan United</t>
+  </si>
+  <si>
     <t>Sigma Olomouc</t>
   </si>
   <si>
-    <t>Astana</t>
-  </si>
-  <si>
-    <t>Fiorentina</t>
-  </si>
-  <si>
-    <t>Pardubice</t>
+    <t>Turan</t>
   </si>
   <si>
     <t>Botoşani</t>
   </si>
   <si>
-    <t>Uppsala W</t>
-  </si>
-  <si>
-    <t>Crystal Palace</t>
-  </si>
-  <si>
-    <t>Cremonese</t>
-  </si>
-  <si>
-    <t>Burnley</t>
-  </si>
-  <si>
-    <t>NK Primorje</t>
-  </si>
-  <si>
-    <t>Turan</t>
-  </si>
-  <si>
-    <t>Arba Minch Kenema</t>
-  </si>
-  <si>
-    <t>Kelantan United</t>
-  </si>
-  <si>
-    <t>Nottingham Forest</t>
-  </si>
-  <si>
     <t>Hamburger SV</t>
   </si>
   <si>
     <t>Botev Vratsa</t>
   </si>
   <si>
+    <t>Nõmme United</t>
+  </si>
+  <si>
+    <t>Volos NFC</t>
+  </si>
+  <si>
     <t>Royal Antwerp FC</t>
   </si>
   <si>
     <t>Honvéd W</t>
   </si>
   <si>
-    <t>Volos NFC</t>
-  </si>
-  <si>
-    <t>Nõmme United</t>
+    <t>EB - Streymur</t>
+  </si>
+  <si>
+    <t>Aris</t>
+  </si>
+  <si>
+    <t>Banga</t>
+  </si>
+  <si>
+    <t>Osijek</t>
+  </si>
+  <si>
+    <t>B36</t>
   </si>
   <si>
     <t>Silkeborg</t>
   </si>
   <si>
-    <t>Banga</t>
-  </si>
-  <si>
     <t>NorthEast United</t>
   </si>
   <si>
-    <t>Aris</t>
-  </si>
-  <si>
-    <t>EB - Streymur</t>
-  </si>
-  <si>
-    <t>Osijek</t>
-  </si>
-  <si>
-    <t>B36</t>
+    <t>Akhmat Grozny</t>
+  </si>
+  <si>
+    <t>Leganés</t>
   </si>
   <si>
     <t>Athletic Club Bilbao</t>
   </si>
   <si>
-    <t>Leganés</t>
-  </si>
-  <si>
-    <t>Akhmat Grozny</t>
+    <t>Häcken</t>
   </si>
   <si>
     <t>Sion</t>
   </si>
   <si>
+    <t>Viktoria Köln</t>
+  </si>
+  <si>
     <t>Neftekhimik</t>
   </si>
   <si>
     <t>Young Boys</t>
   </si>
   <si>
-    <t>Häcken</t>
-  </si>
-  <si>
-    <t>Viktoria Köln</t>
+    <t>Excelsior</t>
+  </si>
+  <si>
+    <t>Feyenoord</t>
+  </si>
+  <si>
+    <t>Groningen</t>
+  </si>
+  <si>
+    <t>Telstar</t>
+  </si>
+  <si>
+    <t>Fortuna Sittard</t>
   </si>
   <si>
     <t>Ajax</t>
@@ -928,121 +943,112 @@
     <t>Twente</t>
   </si>
   <si>
-    <t>Fortuna Sittard</t>
-  </si>
-  <si>
-    <t>Groningen</t>
-  </si>
-  <si>
-    <t>Excelsior</t>
-  </si>
-  <si>
-    <t>Feyenoord</t>
+    <t>Go Ahead Eagles</t>
   </si>
   <si>
     <t>NAC Breda</t>
   </si>
   <si>
-    <t>Go Ahead Eagles</t>
-  </si>
-  <si>
-    <t>Telstar</t>
+    <t>Shkendija</t>
+  </si>
+  <si>
+    <t>Sandnes Ulf</t>
+  </si>
+  <si>
+    <t>Moss</t>
+  </si>
+  <si>
+    <t>Budafoki MTE</t>
+  </si>
+  <si>
+    <t>Sogndal</t>
+  </si>
+  <si>
+    <t>Real Madrid W</t>
+  </si>
+  <si>
+    <t>Ajka</t>
+  </si>
+  <si>
+    <t>Zbrojovka Brno</t>
+  </si>
+  <si>
+    <t>Vardar</t>
+  </si>
+  <si>
+    <t>Croatia Zmijavci</t>
+  </si>
+  <si>
+    <t>Strømmen</t>
+  </si>
+  <si>
+    <t>Tromsø</t>
   </si>
   <si>
     <t>Sandefjord</t>
   </si>
   <si>
+    <t>Mebrat Hayl</t>
+  </si>
+  <si>
+    <t>LASK Linz</t>
+  </si>
+  <si>
+    <t>Hartberg</t>
+  </si>
+  <si>
+    <t>Karcag SE</t>
+  </si>
+  <si>
+    <t>Raufoss</t>
+  </si>
+  <si>
+    <t>KFUM</t>
+  </si>
+  <si>
+    <t>Szentlőrinc SE</t>
+  </si>
+  <si>
+    <t>Pogoń Siedlce</t>
+  </si>
+  <si>
+    <t>Åsane</t>
+  </si>
+  <si>
+    <t>Makedonija GjP</t>
+  </si>
+  <si>
+    <t>Paphos</t>
+  </si>
+  <si>
+    <t>Aresimi</t>
+  </si>
+  <si>
+    <t>Pelister</t>
+  </si>
+  <si>
+    <t>Rapid Wien</t>
+  </si>
+  <si>
+    <t>Saburtalo</t>
+  </si>
+  <si>
     <t>Kecskeméti TE</t>
   </si>
   <si>
-    <t>Szentlőrinc SE</t>
-  </si>
-  <si>
-    <t>Real Madrid W</t>
-  </si>
-  <si>
-    <t>Vardar</t>
-  </si>
-  <si>
-    <t>Zbrojovka Brno</t>
-  </si>
-  <si>
-    <t>Tromsø</t>
-  </si>
-  <si>
-    <t>Mebrat Hayl</t>
-  </si>
-  <si>
-    <t>Croatia Zmijavci</t>
-  </si>
-  <si>
-    <t>Hartberg</t>
-  </si>
-  <si>
-    <t>Karcag SE</t>
-  </si>
-  <si>
-    <t>Moss</t>
-  </si>
-  <si>
-    <t>Sandnes Ulf</t>
-  </si>
-  <si>
-    <t>Raufoss</t>
-  </si>
-  <si>
-    <t>LASK Linz</t>
-  </si>
-  <si>
-    <t>Åsane</t>
-  </si>
-  <si>
-    <t>Aresimi</t>
-  </si>
-  <si>
-    <t>Shkendija</t>
-  </si>
-  <si>
-    <t>Budafoki MTE</t>
-  </si>
-  <si>
-    <t>Pelister</t>
-  </si>
-  <si>
-    <t>KFUM</t>
-  </si>
-  <si>
-    <t>Makedonija GjP</t>
-  </si>
-  <si>
-    <t>Paphos</t>
-  </si>
-  <si>
-    <t>Sogndal</t>
-  </si>
-  <si>
-    <t>Rapid Wien</t>
-  </si>
-  <si>
-    <t>Ajka</t>
-  </si>
-  <si>
-    <t>Saburtalo</t>
+    <t>Akademija Pandev</t>
+  </si>
+  <si>
+    <t>Omonia Nicosia</t>
   </si>
   <si>
     <t>Apollon</t>
   </si>
   <si>
-    <t>Omonia Nicosia</t>
-  </si>
-  <si>
-    <t>Akademija Pandev</t>
-  </si>
-  <si>
-    <t>Pogoń Siedlce</t>
-  </si>
-  <si>
-    <t>Strømmen</t>
+    <t>Al Ain</t>
+  </si>
+  <si>
+    <t>Al Bataeh</t>
   </si>
   <si>
     <t>Bani Yas</t>
@@ -1051,60 +1057,54 @@
     <t>Dibba Al Fujairah</t>
   </si>
   <si>
-    <t>Al Ain</t>
-  </si>
-  <si>
-    <t>Al Bataeh</t>
+    <t>Sekhukhune United</t>
+  </si>
+  <si>
+    <t>Nieciecza</t>
   </si>
   <si>
     <t>West Ham United</t>
   </si>
   <si>
-    <t>Nieciecza</t>
+    <t>Köln</t>
   </si>
   <si>
     <t>Neftçi</t>
   </si>
   <si>
-    <t>Köln</t>
-  </si>
-  <si>
-    <t>Sekhukhune United</t>
+    <t>Brøndby</t>
+  </si>
+  <si>
+    <t>Dinamo Bucureşti</t>
+  </si>
+  <si>
+    <t>Panevėžys</t>
+  </si>
+  <si>
+    <t>Ittihad Tanger</t>
+  </si>
+  <si>
+    <t>Vysočina Jihlava</t>
   </si>
   <si>
     <t>Jedinstvo</t>
   </si>
   <si>
+    <t>Mladost DG</t>
+  </si>
+  <si>
+    <t>Dečić</t>
+  </si>
+  <si>
+    <t>Parma</t>
+  </si>
+  <si>
+    <t>Mornar</t>
+  </si>
+  <si>
     <t>Arsenal Tivat</t>
   </si>
   <si>
-    <t>Vysočina Jihlava</t>
-  </si>
-  <si>
-    <t>Mladost DG</t>
-  </si>
-  <si>
-    <t>Ittihad Tanger</t>
-  </si>
-  <si>
-    <t>Dečić</t>
-  </si>
-  <si>
-    <t>Parma</t>
-  </si>
-  <si>
-    <t>Brøndby</t>
-  </si>
-  <si>
-    <t>Dinamo Bucureşti</t>
-  </si>
-  <si>
-    <t>Panevėžys</t>
-  </si>
-  <si>
-    <t>Mornar</t>
-  </si>
-  <si>
     <t>Al Riyadh</t>
   </si>
   <si>
@@ -1120,75 +1120,75 @@
     <t>07 Vestur</t>
   </si>
   <si>
+    <t>Bačka Topola</t>
+  </si>
+  <si>
+    <t>Radnički Niš</t>
+  </si>
+  <si>
+    <t>Copiapó</t>
+  </si>
+  <si>
+    <t>Córdoba</t>
+  </si>
+  <si>
+    <t>Mirandés</t>
+  </si>
+  <si>
+    <t>Jablonec</t>
+  </si>
+  <si>
+    <t>IMT Novi Beograd</t>
+  </si>
+  <si>
+    <t>Spartak Subotica</t>
+  </si>
+  <si>
     <t>Lokomotiv Moskva</t>
   </si>
   <si>
-    <t>Spartak Subotica</t>
-  </si>
-  <si>
-    <t>Bačka Topola</t>
-  </si>
-  <si>
-    <t>Jablonec</t>
-  </si>
-  <si>
-    <t>Córdoba</t>
+    <t>Real Oviedo</t>
+  </si>
+  <si>
+    <t>Antofagasta</t>
+  </si>
+  <si>
+    <t>Union Saint-Gilloise</t>
   </si>
   <si>
     <t>Kansas City</t>
   </si>
   <si>
-    <t>Real Oviedo</t>
-  </si>
-  <si>
-    <t>Radnički Niš</t>
-  </si>
-  <si>
-    <t>Mirandés</t>
-  </si>
-  <si>
-    <t>Union Saint-Gilloise</t>
+    <t>Olympiakos Piraeus</t>
   </si>
   <si>
     <t>AEK Athens</t>
   </si>
   <si>
-    <t>Antofagasta</t>
-  </si>
-  <si>
-    <t>IMT Novi Beograd</t>
-  </si>
-  <si>
-    <t>Copiapó</t>
-  </si>
-  <si>
-    <t>Olympiakos Piraeus</t>
+    <t>Tenerife W</t>
+  </si>
+  <si>
+    <t>Dinamo Batumi</t>
+  </si>
+  <si>
+    <t>Hapoel Haifa</t>
+  </si>
+  <si>
+    <t>Békéscsaba</t>
+  </si>
+  <si>
+    <t>Ironi Tiberias</t>
+  </si>
+  <si>
+    <t>KA</t>
   </si>
   <si>
     <t>Csákvári TK</t>
   </si>
   <si>
-    <t>Tenerife W</t>
-  </si>
-  <si>
-    <t>Békéscsaba</t>
-  </si>
-  <si>
-    <t>Hapoel Haifa</t>
-  </si>
-  <si>
-    <t>Ironi Tiberias</t>
-  </si>
-  <si>
-    <t>Dinamo Batumi</t>
-  </si>
-  <si>
     <t>Hapoel Katamon</t>
   </si>
   <si>
-    <t>KA</t>
-  </si>
-  <si>
     <t>KRC Genk</t>
   </si>
   <si>
@@ -1198,18 +1198,18 @@
     <t>Hoffenheim II</t>
   </si>
   <si>
+    <t>CODM Meknès</t>
+  </si>
+  <si>
+    <t>UTS Rabat</t>
+  </si>
+  <si>
+    <t>Al Ittihad</t>
+  </si>
+  <si>
     <t>New England II</t>
   </si>
   <si>
-    <t>CODM Meknès</t>
-  </si>
-  <si>
-    <t>Al Ittihad</t>
-  </si>
-  <si>
-    <t>UTS Rabat</t>
-  </si>
-  <si>
     <t>Varzim</t>
   </si>
   <si>
@@ -1219,99 +1219,99 @@
     <t>AC Milan</t>
   </si>
   <si>
+    <t>Agropecuario</t>
+  </si>
+  <si>
+    <t>Le Havre</t>
+  </si>
+  <si>
+    <t>Náutico</t>
+  </si>
+  <si>
+    <t>Independiente Petrolero</t>
+  </si>
+  <si>
+    <t>PSG</t>
+  </si>
+  <si>
+    <t>Toulouse</t>
+  </si>
+  <si>
+    <t>Club Atlético Güemes</t>
+  </si>
+  <si>
+    <t>Metz</t>
+  </si>
+  <si>
+    <t>Remo</t>
+  </si>
+  <si>
     <t>Rennes</t>
   </si>
   <si>
+    <t>Auxerre</t>
+  </si>
+  <si>
+    <t>Atlético Mineiro</t>
+  </si>
+  <si>
+    <t>Angers SCO</t>
+  </si>
+  <si>
     <t>FC Barcelona</t>
   </si>
   <si>
-    <t>Metz</t>
-  </si>
-  <si>
-    <t>Náutico</t>
-  </si>
-  <si>
-    <t>Atlético Mineiro</t>
-  </si>
-  <si>
     <t>Monaco</t>
   </si>
   <si>
-    <t>Toulouse</t>
-  </si>
-  <si>
-    <t>Remo</t>
-  </si>
-  <si>
-    <t>Agropecuario</t>
-  </si>
-  <si>
-    <t>Independiente Petrolero</t>
-  </si>
-  <si>
-    <t>Le Havre</t>
-  </si>
-  <si>
-    <t>Angers SCO</t>
-  </si>
-  <si>
-    <t>PSG</t>
-  </si>
-  <si>
-    <t>Club Atlético Güemes</t>
-  </si>
-  <si>
-    <t>Auxerre</t>
-  </si>
-  <si>
     <t>Godoy Cruz</t>
   </si>
   <si>
+    <t>Chaco For Ever</t>
+  </si>
+  <si>
     <t>San Martín San Juan</t>
   </si>
   <si>
-    <t>Chaco For Ever</t>
+    <t>Hassania Agadir</t>
   </si>
   <si>
     <t>Los Angeles II</t>
   </si>
   <si>
+    <t>Portland Timbers II</t>
+  </si>
+  <si>
     <t>Bay</t>
   </si>
   <si>
     <t>Central Norte</t>
   </si>
   <si>
-    <t>Portland Timbers II</t>
-  </si>
-  <si>
-    <t>Hassania Agadir</t>
+    <t>New York City</t>
   </si>
   <si>
     <t>CS Emelec</t>
   </si>
   <si>
-    <t>New York City</t>
-  </si>
-  <si>
     <t>Colón</t>
   </si>
   <si>
     <t>The Strongest</t>
   </si>
   <si>
+    <t>Mirassol</t>
+  </si>
+  <si>
+    <t>Santos</t>
+  </si>
+  <si>
     <t>Corinthians</t>
   </si>
   <si>
     <t>Avaí</t>
   </si>
   <si>
-    <t>Mirassol</t>
-  </si>
-  <si>
-    <t>Santos</t>
-  </si>
-  <si>
     <t>FC Cincinnati II</t>
   </si>
   <si>
@@ -1324,12 +1324,12 @@
     <t>Minnesota United</t>
   </si>
   <si>
+    <t>Atlanta United II</t>
+  </si>
+  <si>
     <t>Seattle Reign</t>
   </si>
   <si>
-    <t>Atlanta United II</t>
-  </si>
-  <si>
     <t>Manta FC</t>
   </si>
   <si>
@@ -1348,12 +1348,12 @@
     <t>Los Angeles FC</t>
   </si>
   <si>
+    <t>Jeonnam Dragons</t>
+  </si>
+  <si>
     <t>Sydney II</t>
   </si>
   <si>
-    <t>Jeonnam Dragons</t>
-  </si>
-  <si>
     <t>St. George Saints</t>
   </si>
   <si>
@@ -1363,33 +1363,33 @@
     <t>Sydney United</t>
   </si>
   <si>
+    <t>Rotor Volgograd</t>
+  </si>
+  <si>
     <t>Shanghai Jiading</t>
   </si>
   <si>
-    <t>Rotor Volgograd</t>
+    <t>Guangzhou E-Power</t>
   </si>
   <si>
     <t>Guangxi Hengchen</t>
   </si>
   <si>
-    <t>Guangzhou E-Power</t>
+    <t>Yongin City</t>
   </si>
   <si>
     <t>Cheonan City</t>
   </si>
   <si>
-    <t>Yongin City</t>
-  </si>
-  <si>
     <t>Jeonbuk Motors</t>
   </si>
   <si>
+    <t>Sparta Praha II</t>
+  </si>
+  <si>
     <t>Táborsko</t>
   </si>
   <si>
-    <t>Sparta Praha II</t>
-  </si>
-  <si>
     <t>Persib</t>
   </si>
   <si>
@@ -1402,123 +1402,123 @@
     <t>Krylya Sovetov</t>
   </si>
   <si>
+    <t>Kairat</t>
+  </si>
+  <si>
+    <t>Gimhae City</t>
+  </si>
+  <si>
+    <t>Pho Hien</t>
+  </si>
+  <si>
     <t>Sidama Bunna</t>
   </si>
   <si>
+    <t>Shandong Luneng</t>
+  </si>
+  <si>
+    <t>União Santarém</t>
+  </si>
+  <si>
+    <t>Spartak Kostroma</t>
+  </si>
+  <si>
     <t>Logroño W</t>
   </si>
   <si>
-    <t>Shandong Luneng</t>
-  </si>
-  <si>
-    <t>Spartak Kostroma</t>
-  </si>
-  <si>
-    <t>Pho Hien</t>
-  </si>
-  <si>
-    <t>União Santarém</t>
-  </si>
-  <si>
     <t>Górnik Łęczna</t>
   </si>
   <si>
-    <t>Kairat</t>
-  </si>
-  <si>
-    <t>Gimhae City</t>
-  </si>
-  <si>
     <t>GKS Katowice</t>
   </si>
   <si>
     <t>Como</t>
   </si>
   <si>
+    <t>Nakhon Ratchasima</t>
+  </si>
+  <si>
+    <t>Port FC</t>
+  </si>
+  <si>
+    <t>Hebei Kungfu</t>
+  </si>
+  <si>
+    <t>Prachuap</t>
+  </si>
+  <si>
+    <t>Lamphun Warrior</t>
+  </si>
+  <si>
+    <t>Viettel</t>
+  </si>
+  <si>
+    <t>Bangkok United</t>
+  </si>
+  <si>
+    <t>Rosengard Women</t>
+  </si>
+  <si>
+    <t>Uthai Thani</t>
+  </si>
+  <si>
+    <t>Yunnan Yukun</t>
+  </si>
+  <si>
+    <t>Ratchaburi</t>
+  </si>
+  <si>
+    <t>Rangers</t>
+  </si>
+  <si>
+    <t>Song Lam Nghe An</t>
+  </si>
+  <si>
+    <t>Ordabasy</t>
+  </si>
+  <si>
     <t>Muang Thong United</t>
   </si>
   <si>
-    <t>Nakhon Ratchasima</t>
-  </si>
-  <si>
-    <t>Ordabasy</t>
-  </si>
-  <si>
-    <t>Rangers</t>
-  </si>
-  <si>
-    <t>Viettel</t>
-  </si>
-  <si>
-    <t>Hebei Kungfu</t>
-  </si>
-  <si>
-    <t>Yunnan Yukun</t>
-  </si>
-  <si>
-    <t>Rosengard Women</t>
-  </si>
-  <si>
-    <t>Song Lam Nghe An</t>
-  </si>
-  <si>
-    <t>Bangkok United</t>
-  </si>
-  <si>
-    <t>Lamphun Warrior</t>
-  </si>
-  <si>
-    <t>Ratchaburi</t>
-  </si>
-  <si>
-    <t>Port FC</t>
-  </si>
-  <si>
-    <t>Uthai Thani</t>
-  </si>
-  <si>
-    <t>Prachuap</t>
+    <t>Slavia Sofia</t>
   </si>
   <si>
     <t>Žalgiris</t>
   </si>
   <si>
-    <t>Slavia Sofia</t>
+    <t>Elversberg</t>
+  </si>
+  <si>
+    <t>Wuxi Wugou</t>
+  </si>
+  <si>
+    <t>Darmstadt 98</t>
+  </si>
+  <si>
+    <t>Albirex Niigata S</t>
+  </si>
+  <si>
+    <t>Suzhou Dongwu</t>
+  </si>
+  <si>
+    <t>RSC Anderlecht</t>
   </si>
   <si>
     <t>Schweinfurt</t>
   </si>
   <si>
+    <t>Tallinna FC Flora</t>
+  </si>
+  <si>
+    <t>Greuther Fürth</t>
+  </si>
+  <si>
+    <t>Mohammedan</t>
+  </si>
+  <si>
     <t>Tampines Rovers</t>
   </si>
   <si>
-    <t>Albirex Niigata S</t>
-  </si>
-  <si>
-    <t>Greuther Fürth</t>
-  </si>
-  <si>
-    <t>Mohammedan</t>
-  </si>
-  <si>
-    <t>Tallinna FC Flora</t>
-  </si>
-  <si>
-    <t>Elversberg</t>
-  </si>
-  <si>
-    <t>RSC Anderlecht</t>
-  </si>
-  <si>
-    <t>Darmstadt 98</t>
-  </si>
-  <si>
-    <t>Suzhou Dongwu</t>
-  </si>
-  <si>
-    <t>Wuxi Wugou</t>
-  </si>
-  <si>
     <t>Shanghai SIPG</t>
   </si>
   <si>
@@ -1528,166 +1528,181 @@
     <t>Opatija</t>
   </si>
   <si>
+    <t>Djurgården</t>
+  </si>
+  <si>
+    <t>Fredericia</t>
+  </si>
+  <si>
+    <t>Halmstad</t>
+  </si>
+  <si>
+    <t>Villarreal</t>
+  </si>
+  <si>
+    <t>Dalian Zhixing</t>
+  </si>
+  <si>
+    <t>Kaisar</t>
+  </si>
+  <si>
+    <t>UD Las Palmas</t>
+  </si>
+  <si>
+    <t>Dila</t>
+  </si>
+  <si>
     <t>St. Gallen</t>
   </si>
   <si>
-    <t>Dila</t>
+    <t>Malut United</t>
   </si>
   <si>
     <t>Midtjylland</t>
   </si>
   <si>
-    <t>Malut United</t>
-  </si>
-  <si>
-    <t>Villarreal</t>
-  </si>
-  <si>
-    <t>Halmstad</t>
-  </si>
-  <si>
-    <t>Fredericia</t>
-  </si>
-  <si>
-    <t>Kaisar</t>
+    <t>FK Sochi</t>
   </si>
   <si>
     <t>Welwalo Adigrat Uni</t>
   </si>
   <si>
-    <t>Djurgården</t>
-  </si>
-  <si>
-    <t>UD Las Palmas</t>
-  </si>
-  <si>
-    <t>Dalian Zhixing</t>
-  </si>
-  <si>
-    <t>FK Sochi</t>
-  </si>
-  <si>
     <t>Nam Dinh</t>
   </si>
   <si>
     <t>Negeri Sembilan</t>
   </si>
   <si>
+    <t>Lillestrøm</t>
+  </si>
+  <si>
+    <t>Ústí nad Labem</t>
+  </si>
+  <si>
     <t>Ruch Chorzów</t>
   </si>
   <si>
-    <t>Ústí nad Labem</t>
-  </si>
-  <si>
-    <t>Lillestrøm</t>
-  </si>
-  <si>
     <t>Motor Lublin</t>
   </si>
   <si>
+    <t>Mura</t>
+  </si>
+  <si>
+    <t>Newcastle United</t>
+  </si>
+  <si>
+    <t>Karviná</t>
+  </si>
+  <si>
+    <t>Kyzyl-Zhar</t>
+  </si>
+  <si>
+    <t>Vittsjö</t>
+  </si>
+  <si>
+    <t>Pisa</t>
+  </si>
+  <si>
+    <t>Aston Villa</t>
+  </si>
+  <si>
+    <t>Everton</t>
+  </si>
+  <si>
+    <t>Genoa</t>
+  </si>
+  <si>
+    <t>Welayta Dicha</t>
+  </si>
+  <si>
+    <t>Johor Darul Ta'zim</t>
+  </si>
+  <si>
     <t>Bohemians 1905</t>
   </si>
   <si>
-    <t>Kyzyl-Zhar</t>
-  </si>
-  <si>
-    <t>Genoa</t>
-  </si>
-  <si>
-    <t>Karviná</t>
+    <t>Karvan FK</t>
   </si>
   <si>
     <t>Petrolul 52</t>
   </si>
   <si>
-    <t>Vittsjö</t>
-  </si>
-  <si>
-    <t>Everton</t>
-  </si>
-  <si>
-    <t>Pisa</t>
-  </si>
-  <si>
-    <t>Aston Villa</t>
-  </si>
-  <si>
-    <t>Mura</t>
-  </si>
-  <si>
-    <t>Karvan FK</t>
-  </si>
-  <si>
-    <t>Welayta Dicha</t>
-  </si>
-  <si>
-    <t>Johor Darul Ta'zim</t>
-  </si>
-  <si>
-    <t>Newcastle United</t>
-  </si>
-  <si>
     <t>Freiburg</t>
   </si>
   <si>
     <t>Septemvri Sofia</t>
   </si>
   <si>
+    <t>Paide</t>
+  </si>
+  <si>
+    <t>Levadiakos</t>
+  </si>
+  <si>
     <t>Sporting Charleroi</t>
   </si>
   <si>
     <t>Vasas</t>
   </si>
   <si>
-    <t>Levadiakos</t>
-  </si>
-  <si>
-    <t>Paide</t>
+    <t>Víkingur</t>
+  </si>
+  <si>
+    <t>OFI</t>
+  </si>
+  <si>
+    <t>TransINVEST Vilnius</t>
+  </si>
+  <si>
+    <t>Istra 1961</t>
+  </si>
+  <si>
+    <t>KÍ</t>
   </si>
   <si>
     <t>København</t>
   </si>
   <si>
-    <t>TransINVEST Vilnius</t>
-  </si>
-  <si>
     <t>Chennaiyin</t>
   </si>
   <si>
-    <t>OFI</t>
-  </si>
-  <si>
-    <t>Víkingur</t>
-  </si>
-  <si>
-    <t>Istra 1961</t>
-  </si>
-  <si>
-    <t>KÍ</t>
+    <t>Makhachkala</t>
+  </si>
+  <si>
+    <t>Racing Santander</t>
   </si>
   <si>
     <t>Valencia CF</t>
   </si>
   <si>
-    <t>Racing Santander</t>
-  </si>
-  <si>
-    <t>Makhachkala</t>
+    <t>Malmö FF</t>
   </si>
   <si>
     <t>Thun</t>
   </si>
   <si>
+    <t>Alemannia Aachen</t>
+  </si>
+  <si>
     <t>Volga Ulyanovsk</t>
   </si>
   <si>
     <t>Basel</t>
   </si>
   <si>
-    <t>Malmö FF</t>
-  </si>
-  <si>
-    <t>Alemannia Aachen</t>
+    <t>Volendam</t>
+  </si>
+  <si>
+    <t>AZ</t>
+  </si>
+  <si>
+    <t>NEC</t>
+  </si>
+  <si>
+    <t>Heracles</t>
+  </si>
+  <si>
+    <t>PEC Zwolle</t>
   </si>
   <si>
     <t>Utrecht</t>
@@ -1696,118 +1711,109 @@
     <t>Sparta Rotterdam</t>
   </si>
   <si>
-    <t>PEC Zwolle</t>
-  </si>
-  <si>
-    <t>NEC</t>
-  </si>
-  <si>
-    <t>Volendam</t>
-  </si>
-  <si>
-    <t>AZ</t>
+    <t>PSV</t>
   </si>
   <si>
     <t>Heerenveen</t>
   </si>
   <si>
-    <t>PSV</t>
-  </si>
-  <si>
-    <t>Heracles</t>
+    <t>Struga</t>
+  </si>
+  <si>
+    <t>Stabæk</t>
+  </si>
+  <si>
+    <t>Bryne</t>
+  </si>
+  <si>
+    <t>BVSC</t>
+  </si>
+  <si>
+    <t>Haugesund</t>
+  </si>
+  <si>
+    <t>Atletico Madrid W</t>
+  </si>
+  <si>
+    <t>Szeged 2011</t>
+  </si>
+  <si>
+    <t>Vlašim</t>
+  </si>
+  <si>
+    <t>Sileks</t>
+  </si>
+  <si>
+    <t>Jarun</t>
+  </si>
+  <si>
+    <t>Hødd</t>
+  </si>
+  <si>
+    <t>Molde</t>
   </si>
   <si>
     <t>Kristiansund</t>
   </si>
   <si>
+    <t>Fasil Ketema</t>
+  </si>
+  <si>
+    <t>Salzburg</t>
+  </si>
+  <si>
+    <t>Sturm Graz</t>
+  </si>
+  <si>
+    <t>Tiszakécske</t>
+  </si>
+  <si>
+    <t>Lyn</t>
+  </si>
+  <si>
+    <t>Viking</t>
+  </si>
+  <si>
+    <t>Videoton</t>
+  </si>
+  <si>
+    <t>Stal Rzeszów</t>
+  </si>
+  <si>
+    <t>Strømsgodset</t>
+  </si>
+  <si>
+    <t>Tikveš</t>
+  </si>
+  <si>
+    <t>FK Bashkimi Kumanovo</t>
+  </si>
+  <si>
+    <t>Shkupi</t>
+  </si>
+  <si>
+    <t>Austria Wien</t>
+  </si>
+  <si>
+    <t>Torpedo Kutaisi</t>
+  </si>
+  <si>
     <t>Mezőkövesd-Zsóry</t>
   </si>
   <si>
-    <t>Videoton</t>
-  </si>
-  <si>
-    <t>Atletico Madrid W</t>
-  </si>
-  <si>
-    <t>Sileks</t>
-  </si>
-  <si>
-    <t>Vlašim</t>
-  </si>
-  <si>
-    <t>Molde</t>
-  </si>
-  <si>
-    <t>Fasil Ketema</t>
-  </si>
-  <si>
-    <t>Jarun</t>
-  </si>
-  <si>
-    <t>Sturm Graz</t>
-  </si>
-  <si>
-    <t>Tiszakécske</t>
-  </si>
-  <si>
-    <t>Bryne</t>
-  </si>
-  <si>
-    <t>Stabæk</t>
-  </si>
-  <si>
-    <t>Lyn</t>
-  </si>
-  <si>
-    <t>Salzburg</t>
-  </si>
-  <si>
-    <t>Strømsgodset</t>
-  </si>
-  <si>
-    <t>FK Bashkimi Kumanovo</t>
-  </si>
-  <si>
-    <t>Struga</t>
-  </si>
-  <si>
-    <t>BVSC</t>
-  </si>
-  <si>
-    <t>Shkupi</t>
-  </si>
-  <si>
-    <t>Viking</t>
-  </si>
-  <si>
-    <t>Tikveš</t>
-  </si>
-  <si>
-    <t>Haugesund</t>
-  </si>
-  <si>
-    <t>Austria Wien</t>
-  </si>
-  <si>
-    <t>Szeged 2011</t>
-  </si>
-  <si>
-    <t>Torpedo Kutaisi</t>
+    <t>Rabotnički</t>
+  </si>
+  <si>
+    <t>AEK Larnaca</t>
   </si>
   <si>
     <t>APOEL</t>
   </si>
   <si>
-    <t>AEK Larnaca</t>
-  </si>
-  <si>
-    <t>Rabotnički</t>
-  </si>
-  <si>
-    <t>Stal Rzeszów</t>
-  </si>
-  <si>
-    <t>Hødd</t>
+    <t>Al Dhafra</t>
+  </si>
+  <si>
+    <t>Al Sharjah</t>
   </si>
   <si>
     <t>Shabab Al Ahli Dubai</t>
@@ -1816,60 +1822,54 @@
     <t>Ajman</t>
   </si>
   <si>
-    <t>Al Dhafra</t>
-  </si>
-  <si>
-    <t>Al Sharjah</t>
+    <t>Kaizer Chiefs</t>
+  </si>
+  <si>
+    <t>Legia Warszawa</t>
   </si>
   <si>
     <t>Arsenal</t>
   </si>
   <si>
-    <t>Legia Warszawa</t>
+    <t>Heidenheim</t>
   </si>
   <si>
     <t>İnter Bakı</t>
   </si>
   <si>
-    <t>Heidenheim</t>
-  </si>
-  <si>
-    <t>Kaizer Chiefs</t>
+    <t>AGF</t>
+  </si>
+  <si>
+    <t>Argeș</t>
+  </si>
+  <si>
+    <t>Kauno Žalgiris</t>
+  </si>
+  <si>
+    <t>Difaâ El Jadida</t>
+  </si>
+  <si>
+    <t>Hanácká</t>
   </si>
   <si>
     <t>Budućnost</t>
   </si>
   <si>
+    <t>Petrovac</t>
+  </si>
+  <si>
+    <t>FK Jezero Plav</t>
+  </si>
+  <si>
+    <t>Roma</t>
+  </si>
+  <si>
+    <t>Bokelj</t>
+  </si>
+  <si>
     <t>Sutjeska</t>
   </si>
   <si>
-    <t>Hanácká</t>
-  </si>
-  <si>
-    <t>Petrovac</t>
-  </si>
-  <si>
-    <t>Difaâ El Jadida</t>
-  </si>
-  <si>
-    <t>FK Jezero Plav</t>
-  </si>
-  <si>
-    <t>Roma</t>
-  </si>
-  <si>
-    <t>AGF</t>
-  </si>
-  <si>
-    <t>Argeș</t>
-  </si>
-  <si>
-    <t>Kauno Žalgiris</t>
-  </si>
-  <si>
-    <t>Bokelj</t>
-  </si>
-  <si>
     <t>Al Fateh</t>
   </si>
   <si>
@@ -1885,75 +1885,75 @@
     <t>B68</t>
   </si>
   <si>
+    <t>Javor Ivanjica</t>
+  </si>
+  <si>
+    <t>LFK Mladost Lučani</t>
+  </si>
+  <si>
+    <t>Unión San Felipe</t>
+  </si>
+  <si>
+    <t>Granada CF</t>
+  </si>
+  <si>
+    <t>SD Eibar</t>
+  </si>
+  <si>
+    <t>Hradec Králové</t>
+  </si>
+  <si>
+    <t>Radnički Kragujevac</t>
+  </si>
+  <si>
+    <t>Napredak</t>
+  </si>
+  <si>
     <t>Baltika</t>
   </si>
   <si>
-    <t>Napredak</t>
-  </si>
-  <si>
-    <t>Javor Ivanjica</t>
-  </si>
-  <si>
-    <t>Hradec Králové</t>
-  </si>
-  <si>
-    <t>Granada CF</t>
+    <t>Getafe CF</t>
+  </si>
+  <si>
+    <t>San Luis</t>
+  </si>
+  <si>
+    <t>KV Mechelen</t>
   </si>
   <si>
     <t>Chicago Red Stars</t>
   </si>
   <si>
-    <t>Getafe CF</t>
-  </si>
-  <si>
-    <t>LFK Mladost Lučani</t>
-  </si>
-  <si>
-    <t>SD Eibar</t>
-  </si>
-  <si>
-    <t>KV Mechelen</t>
+    <t>PAOK</t>
   </si>
   <si>
     <t>Panathinaikos</t>
   </si>
   <si>
-    <t>San Luis</t>
-  </si>
-  <si>
-    <t>Radnički Kragujevac</t>
-  </si>
-  <si>
-    <t>Unión San Felipe</t>
-  </si>
-  <si>
-    <t>PAOK</t>
+    <t>Barcelona W</t>
+  </si>
+  <si>
+    <t>Samgurali</t>
+  </si>
+  <si>
+    <t>Ashdod</t>
+  </si>
+  <si>
+    <t>Kozármisleny</t>
+  </si>
+  <si>
+    <t>Maccabi Netanya</t>
+  </si>
+  <si>
+    <t>ÍBV</t>
   </si>
   <si>
     <t>Soroksár SC</t>
   </si>
   <si>
-    <t>Barcelona W</t>
-  </si>
-  <si>
-    <t>Kozármisleny</t>
-  </si>
-  <si>
-    <t>Ashdod</t>
-  </si>
-  <si>
-    <t>Maccabi Netanya</t>
-  </si>
-  <si>
-    <t>Samgurali</t>
-  </si>
-  <si>
     <t>Bnei Sakhnin</t>
   </si>
   <si>
-    <t>ÍBV</t>
-  </si>
-  <si>
     <t>KVC Westerlo</t>
   </si>
   <si>
@@ -1963,18 +1963,18 @@
     <t>Saarbrucken</t>
   </si>
   <si>
+    <t>RSB Berkane</t>
+  </si>
+  <si>
+    <t>Maghreb Fès</t>
+  </si>
+  <si>
+    <t>Dhamk</t>
+  </si>
+  <si>
     <t>New York City II</t>
   </si>
   <si>
-    <t>RSB Berkane</t>
-  </si>
-  <si>
-    <t>Dhamk</t>
-  </si>
-  <si>
-    <t>Maghreb Fès</t>
-  </si>
-  <si>
     <t>CF Os Belenenses</t>
   </si>
   <si>
@@ -1984,99 +1984,99 @@
     <t>Atalanta</t>
   </si>
   <si>
+    <t>Atlanta</t>
+  </si>
+  <si>
+    <t>Olympique Marseille</t>
+  </si>
+  <si>
+    <t>América Mineiro</t>
+  </si>
+  <si>
+    <t>Club Always Ready</t>
+  </si>
+  <si>
+    <t>Brest</t>
+  </si>
+  <si>
+    <t>Olympique Lyonnais</t>
+  </si>
+  <si>
+    <t>Quilmes</t>
+  </si>
+  <si>
+    <t>Lorient</t>
+  </si>
+  <si>
+    <t>Palmeiras</t>
+  </si>
+  <si>
     <t>Paris</t>
   </si>
   <si>
+    <t>Nice</t>
+  </si>
+  <si>
+    <t>Botafogo</t>
+  </si>
+  <si>
+    <t>Strasbourg</t>
+  </si>
+  <si>
     <t>Real Madrid</t>
   </si>
   <si>
-    <t>Lorient</t>
-  </si>
-  <si>
-    <t>América Mineiro</t>
-  </si>
-  <si>
-    <t>Botafogo</t>
-  </si>
-  <si>
     <t>Lille</t>
   </si>
   <si>
-    <t>Olympique Lyonnais</t>
-  </si>
-  <si>
-    <t>Palmeiras</t>
-  </si>
-  <si>
-    <t>Atlanta</t>
-  </si>
-  <si>
-    <t>Club Always Ready</t>
-  </si>
-  <si>
-    <t>Olympique Marseille</t>
-  </si>
-  <si>
-    <t>Strasbourg</t>
-  </si>
-  <si>
-    <t>Brest</t>
-  </si>
-  <si>
-    <t>Quilmes</t>
-  </si>
-  <si>
-    <t>Nice</t>
-  </si>
-  <si>
     <t>Racing Córdoba</t>
   </si>
   <si>
+    <t>Ciudad de Bolívar</t>
+  </si>
+  <si>
     <t>Patronato</t>
   </si>
   <si>
-    <t>Ciudad de Bolívar</t>
+    <t>FAR Rabat</t>
   </si>
   <si>
     <t>Real Monarchs</t>
   </si>
   <si>
+    <t>LA Galaxy II</t>
+  </si>
+  <si>
     <t>Utah Royals</t>
   </si>
   <si>
     <t>Deportivo Madryn</t>
   </si>
   <si>
-    <t>LA Galaxy II</t>
-  </si>
-  <si>
-    <t>FAR Rabat</t>
+    <t>Columbus Crew</t>
   </si>
   <si>
     <t>Libertad</t>
   </si>
   <si>
-    <t>Columbus Crew</t>
-  </si>
-  <si>
     <t>All Boys</t>
   </si>
   <si>
     <t>Real Potosí</t>
   </si>
   <si>
+    <t>Chapecoense</t>
+  </si>
+  <si>
+    <t>Bragantino</t>
+  </si>
+  <si>
     <t>São Paulo</t>
   </si>
   <si>
     <t>Fortaleza</t>
   </si>
   <si>
-    <t>Chapecoense</t>
-  </si>
-  <si>
-    <t>Bragantino</t>
-  </si>
-  <si>
     <t>Columbus Crew II</t>
   </si>
   <si>
@@ -2089,10 +2089,10 @@
     <t>Austin</t>
   </si>
   <si>
+    <t>Orlando City II</t>
+  </si>
+  <si>
     <t>Washington Spirit</t>
-  </si>
-  <si>
-    <t>Orlando City II</t>
   </si>
   <si>
     <t>Macará</t>
@@ -2712,13 +2712,13 @@
         <v>699</v>
       </c>
       <c r="P2">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="Q2">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>3.61</v>
       </c>
       <c r="S2">
         <v>0</v>
@@ -2897,13 +2897,13 @@
         <v>699</v>
       </c>
       <c r="P3">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="Q3">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="R3">
-        <v>3.61</v>
+        <v>0</v>
       </c>
       <c r="S3">
         <v>0</v>
@@ -3043,7 +3043,7 @@
         <v>61</v>
       </c>
       <c r="C4" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="D4" t="s">
         <v>185</v>
@@ -3413,7 +3413,7 @@
         <v>62</v>
       </c>
       <c r="C6" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="D6" t="s">
         <v>185</v>
@@ -3601,7 +3601,7 @@
         <v>118</v>
       </c>
       <c r="D7" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E7" t="s">
         <v>193</v>
@@ -3786,7 +3786,7 @@
         <v>119</v>
       </c>
       <c r="D8" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E8" t="s">
         <v>194</v>
@@ -3968,7 +3968,7 @@
         <v>63</v>
       </c>
       <c r="C9" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="D9" t="s">
         <v>185</v>
@@ -4153,7 +4153,7 @@
         <v>63</v>
       </c>
       <c r="C10" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="D10" t="s">
         <v>185</v>
@@ -4338,7 +4338,7 @@
         <v>64</v>
       </c>
       <c r="C11" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D11" t="s">
         <v>185</v>
@@ -4377,13 +4377,13 @@
         <v>699</v>
       </c>
       <c r="P11">
-        <v>1.63</v>
+        <v>3.65</v>
       </c>
       <c r="Q11">
-        <v>3.7</v>
+        <v>3.32</v>
       </c>
       <c r="R11">
-        <v>4.67</v>
+        <v>1.91</v>
       </c>
       <c r="S11">
         <v>0</v>
@@ -4422,10 +4422,10 @@
         <v>0</v>
       </c>
       <c r="AE11">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AF11">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AG11">
         <v>0</v>
@@ -4523,7 +4523,7 @@
         <v>64</v>
       </c>
       <c r="C12" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D12" t="s">
         <v>185</v>
@@ -4562,13 +4562,13 @@
         <v>699</v>
       </c>
       <c r="P12">
-        <v>3.65</v>
+        <v>1.63</v>
       </c>
       <c r="Q12">
-        <v>3.32</v>
+        <v>3.7</v>
       </c>
       <c r="R12">
-        <v>1.91</v>
+        <v>4.67</v>
       </c>
       <c r="S12">
         <v>0</v>
@@ -4607,10 +4607,10 @@
         <v>0</v>
       </c>
       <c r="AE12">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AF12">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AG12">
         <v>0</v>
@@ -6006,7 +6006,7 @@
         <v>124</v>
       </c>
       <c r="D20" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E20" t="s">
         <v>206</v>
@@ -6188,10 +6188,10 @@
         <v>68</v>
       </c>
       <c r="C21" t="s">
-        <v>125</v>
+        <v>115</v>
       </c>
       <c r="D21" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E21" t="s">
         <v>207</v>
@@ -6227,13 +6227,13 @@
         <v>699</v>
       </c>
       <c r="P21">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Q21">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="R21">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="S21">
         <v>0</v>
@@ -6373,10 +6373,10 @@
         <v>68</v>
       </c>
       <c r="C22" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="D22" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E22" t="s">
         <v>208</v>
@@ -6558,7 +6558,7 @@
         <v>68</v>
       </c>
       <c r="C23" t="s">
-        <v>119</v>
+        <v>126</v>
       </c>
       <c r="D23" t="s">
         <v>186</v>
@@ -6597,13 +6597,13 @@
         <v>699</v>
       </c>
       <c r="P23">
-        <v>4.98</v>
+        <v>0</v>
       </c>
       <c r="Q23">
-        <v>3.66</v>
+        <v>0</v>
       </c>
       <c r="R23">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="S23">
         <v>0</v>
@@ -6743,10 +6743,10 @@
         <v>68</v>
       </c>
       <c r="C24" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="D24" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E24" t="s">
         <v>210</v>
@@ -7113,7 +7113,7 @@
         <v>68</v>
       </c>
       <c r="C26" t="s">
-        <v>128</v>
+        <v>118</v>
       </c>
       <c r="D26" t="s">
         <v>186</v>
@@ -7152,13 +7152,13 @@
         <v>699</v>
       </c>
       <c r="P26">
-        <v>0</v>
+        <v>4.98</v>
       </c>
       <c r="Q26">
-        <v>0</v>
+        <v>3.66</v>
       </c>
       <c r="R26">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="S26">
         <v>0</v>
@@ -7298,10 +7298,10 @@
         <v>68</v>
       </c>
       <c r="C27" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D27" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E27" t="s">
         <v>213</v>
@@ -7483,10 +7483,10 @@
         <v>68</v>
       </c>
       <c r="C28" t="s">
-        <v>116</v>
+        <v>129</v>
       </c>
       <c r="D28" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E28" t="s">
         <v>214</v>
@@ -7522,13 +7522,13 @@
         <v>699</v>
       </c>
       <c r="P28">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Q28">
-        <v>3.16</v>
+        <v>0</v>
       </c>
       <c r="R28">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="S28">
         <v>0</v>
@@ -8077,13 +8077,13 @@
         <v>699</v>
       </c>
       <c r="P31">
-        <v>2.44</v>
+        <v>1.61</v>
       </c>
       <c r="Q31">
-        <v>3.61</v>
+        <v>4.18</v>
       </c>
       <c r="R31">
-        <v>2.77</v>
+        <v>5.3</v>
       </c>
       <c r="S31">
         <v>0</v>
@@ -8262,13 +8262,13 @@
         <v>699</v>
       </c>
       <c r="P32">
-        <v>1.61</v>
+        <v>5.09</v>
       </c>
       <c r="Q32">
         <v>4.18</v>
       </c>
       <c r="R32">
-        <v>5.3</v>
+        <v>1.64</v>
       </c>
       <c r="S32">
         <v>0</v>
@@ -8408,7 +8408,7 @@
         <v>71</v>
       </c>
       <c r="C33" t="s">
-        <v>129</v>
+        <v>119</v>
       </c>
       <c r="D33" t="s">
         <v>185</v>
@@ -8593,7 +8593,7 @@
         <v>71</v>
       </c>
       <c r="C34" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="D34" t="s">
         <v>186</v>
@@ -8632,13 +8632,13 @@
         <v>699</v>
       </c>
       <c r="P34">
-        <v>2.2</v>
+        <v>1.78</v>
       </c>
       <c r="Q34">
-        <v>3.7</v>
+        <v>3.9</v>
       </c>
       <c r="R34">
-        <v>3</v>
+        <v>4.35</v>
       </c>
       <c r="S34">
         <v>0</v>
@@ -8778,7 +8778,7 @@
         <v>71</v>
       </c>
       <c r="C35" t="s">
-        <v>126</v>
+        <v>132</v>
       </c>
       <c r="D35" t="s">
         <v>186</v>
@@ -8817,13 +8817,13 @@
         <v>699</v>
       </c>
       <c r="P35">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="Q35">
-        <v>0</v>
+        <v>6.73</v>
       </c>
       <c r="R35">
-        <v>0</v>
+        <v>10.6</v>
       </c>
       <c r="S35">
         <v>0</v>
@@ -8963,10 +8963,10 @@
         <v>71</v>
       </c>
       <c r="C36" t="s">
-        <v>118</v>
+        <v>125</v>
       </c>
       <c r="D36" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E36" t="s">
         <v>222</v>
@@ -9148,10 +9148,10 @@
         <v>71</v>
       </c>
       <c r="C37" t="s">
-        <v>122</v>
+        <v>132</v>
       </c>
       <c r="D37" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E37" t="s">
         <v>223</v>
@@ -9187,13 +9187,13 @@
         <v>699</v>
       </c>
       <c r="P37">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="Q37">
-        <v>0</v>
+        <v>3.63</v>
       </c>
       <c r="R37">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="S37">
         <v>0</v>
@@ -9333,7 +9333,7 @@
         <v>71</v>
       </c>
       <c r="C38" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="D38" t="s">
         <v>185</v>
@@ -9518,7 +9518,7 @@
         <v>71</v>
       </c>
       <c r="C39" t="s">
-        <v>126</v>
+        <v>132</v>
       </c>
       <c r="D39" t="s">
         <v>186</v>
@@ -9557,13 +9557,13 @@
         <v>699</v>
       </c>
       <c r="P39">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="Q39">
-        <v>0</v>
+        <v>3.36</v>
       </c>
       <c r="R39">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="S39">
         <v>0</v>
@@ -9602,10 +9602,10 @@
         <v>0</v>
       </c>
       <c r="AE39">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AF39">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AG39">
         <v>0</v>
@@ -9703,10 +9703,10 @@
         <v>71</v>
       </c>
       <c r="C40" t="s">
-        <v>132</v>
+        <v>122</v>
       </c>
       <c r="D40" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E40" t="s">
         <v>226</v>
@@ -9742,13 +9742,13 @@
         <v>699</v>
       </c>
       <c r="P40">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="Q40">
-        <v>3.63</v>
+        <v>0</v>
       </c>
       <c r="R40">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="S40">
         <v>0</v>
@@ -9927,13 +9927,13 @@
         <v>699</v>
       </c>
       <c r="P41">
-        <v>1.24</v>
+        <v>3.32</v>
       </c>
       <c r="Q41">
-        <v>6.73</v>
+        <v>3.95</v>
       </c>
       <c r="R41">
-        <v>10.6</v>
+        <v>2.03</v>
       </c>
       <c r="S41">
         <v>0</v>
@@ -10073,7 +10073,7 @@
         <v>71</v>
       </c>
       <c r="C42" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="D42" t="s">
         <v>186</v>
@@ -10112,13 +10112,13 @@
         <v>699</v>
       </c>
       <c r="P42">
-        <v>3.32</v>
+        <v>2.2</v>
       </c>
       <c r="Q42">
-        <v>3.95</v>
+        <v>3.7</v>
       </c>
       <c r="R42">
-        <v>2.03</v>
+        <v>3</v>
       </c>
       <c r="S42">
         <v>0</v>
@@ -10258,7 +10258,7 @@
         <v>71</v>
       </c>
       <c r="C43" t="s">
-        <v>132</v>
+        <v>125</v>
       </c>
       <c r="D43" t="s">
         <v>186</v>
@@ -10297,13 +10297,13 @@
         <v>699</v>
       </c>
       <c r="P43">
-        <v>5.09</v>
+        <v>0</v>
       </c>
       <c r="Q43">
-        <v>4.18</v>
+        <v>0</v>
       </c>
       <c r="R43">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="S43">
         <v>0</v>
@@ -10443,10 +10443,10 @@
         <v>71</v>
       </c>
       <c r="C44" t="s">
-        <v>132</v>
+        <v>124</v>
       </c>
       <c r="D44" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E44" t="s">
         <v>230</v>
@@ -10482,13 +10482,13 @@
         <v>699</v>
       </c>
       <c r="P44">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="Q44">
-        <v>3.36</v>
+        <v>0</v>
       </c>
       <c r="R44">
-        <v>2.64</v>
+        <v>0</v>
       </c>
       <c r="S44">
         <v>0</v>
@@ -10527,10 +10527,10 @@
         <v>0</v>
       </c>
       <c r="AE44">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AF44">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AG44">
         <v>0</v>
@@ -10667,13 +10667,13 @@
         <v>699</v>
       </c>
       <c r="P45">
-        <v>1.78</v>
+        <v>2.44</v>
       </c>
       <c r="Q45">
-        <v>3.9</v>
+        <v>3.61</v>
       </c>
       <c r="R45">
-        <v>4.35</v>
+        <v>2.77</v>
       </c>
       <c r="S45">
         <v>0</v>
@@ -10816,7 +10816,7 @@
         <v>135</v>
       </c>
       <c r="D46" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E46" t="s">
         <v>232</v>
@@ -10852,13 +10852,13 @@
         <v>699</v>
       </c>
       <c r="P46">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="Q46">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R46">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="S46">
         <v>0</v>
@@ -11001,7 +11001,7 @@
         <v>136</v>
       </c>
       <c r="D47" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E47" t="s">
         <v>233</v>
@@ -11037,13 +11037,13 @@
         <v>699</v>
       </c>
       <c r="P47">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="Q47">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="R47">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="S47">
         <v>0</v>
@@ -11222,13 +11222,13 @@
         <v>699</v>
       </c>
       <c r="P48">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="Q48">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="R48">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="S48">
         <v>0</v>
@@ -11368,10 +11368,10 @@
         <v>73</v>
       </c>
       <c r="C49" t="s">
-        <v>138</v>
+        <v>119</v>
       </c>
       <c r="D49" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="E49" t="s">
         <v>235</v>
@@ -11553,10 +11553,10 @@
         <v>73</v>
       </c>
       <c r="C50" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D50" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="E50" t="s">
         <v>236</v>
@@ -11592,13 +11592,13 @@
         <v>699</v>
       </c>
       <c r="P50">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="Q50">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="R50">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="S50">
         <v>0</v>
@@ -11738,10 +11738,10 @@
         <v>73</v>
       </c>
       <c r="C51" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="D51" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="E51" t="s">
         <v>237</v>
@@ -11777,13 +11777,13 @@
         <v>699</v>
       </c>
       <c r="P51">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="Q51">
-        <v>4.15</v>
+        <v>0</v>
       </c>
       <c r="R51">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="S51">
         <v>0</v>
@@ -11828,10 +11828,10 @@
         <v>0</v>
       </c>
       <c r="AG51">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AH51">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AI51">
         <v>0</v>
@@ -11923,10 +11923,10 @@
         <v>73</v>
       </c>
       <c r="C52" t="s">
-        <v>140</v>
+        <v>119</v>
       </c>
       <c r="D52" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E52" t="s">
         <v>238</v>
@@ -11962,13 +11962,13 @@
         <v>699</v>
       </c>
       <c r="P52">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="Q52">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="R52">
-        <v>7.37</v>
+        <v>0</v>
       </c>
       <c r="S52">
         <v>0</v>
@@ -12108,10 +12108,10 @@
         <v>73</v>
       </c>
       <c r="C53" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="D53" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E53" t="s">
         <v>239</v>
@@ -12147,13 +12147,13 @@
         <v>699</v>
       </c>
       <c r="P53">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="Q53">
-        <v>0</v>
+        <v>3.71</v>
       </c>
       <c r="R53">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="S53">
         <v>0</v>
@@ -12293,7 +12293,7 @@
         <v>73</v>
       </c>
       <c r="C54" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="D54" t="s">
         <v>186</v>
@@ -12332,13 +12332,13 @@
         <v>699</v>
       </c>
       <c r="P54">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="Q54">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="R54">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="S54">
         <v>0</v>
@@ -12478,10 +12478,10 @@
         <v>73</v>
       </c>
       <c r="C55" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="D55" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E55" t="s">
         <v>241</v>
@@ -12517,13 +12517,13 @@
         <v>699</v>
       </c>
       <c r="P55">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="Q55">
-        <v>3.71</v>
+        <v>0</v>
       </c>
       <c r="R55">
-        <v>2.89</v>
+        <v>0</v>
       </c>
       <c r="S55">
         <v>0</v>
@@ -12663,7 +12663,7 @@
         <v>73</v>
       </c>
       <c r="C56" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="D56" t="s">
         <v>186</v>
@@ -12702,13 +12702,13 @@
         <v>699</v>
       </c>
       <c r="P56">
-        <v>2.29</v>
+        <v>1.78</v>
       </c>
       <c r="Q56">
-        <v>3.74</v>
+        <v>4.15</v>
       </c>
       <c r="R56">
-        <v>2.76</v>
+        <v>3.8</v>
       </c>
       <c r="S56">
         <v>0</v>
@@ -12753,10 +12753,10 @@
         <v>0</v>
       </c>
       <c r="AG56">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AH56">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AI56">
         <v>0</v>
@@ -12848,10 +12848,10 @@
         <v>73</v>
       </c>
       <c r="C57" t="s">
-        <v>118</v>
+        <v>142</v>
       </c>
       <c r="D57" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E57" t="s">
         <v>243</v>
@@ -12887,13 +12887,13 @@
         <v>699</v>
       </c>
       <c r="P57">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="Q57">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="R57">
-        <v>0</v>
+        <v>7.37</v>
       </c>
       <c r="S57">
         <v>0</v>
@@ -13033,10 +13033,10 @@
         <v>73</v>
       </c>
       <c r="C58" t="s">
-        <v>118</v>
+        <v>138</v>
       </c>
       <c r="D58" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="E58" t="s">
         <v>244</v>
@@ -13776,7 +13776,7 @@
         <v>144</v>
       </c>
       <c r="D62" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E62" t="s">
         <v>248</v>
@@ -13812,13 +13812,13 @@
         <v>699</v>
       </c>
       <c r="P62">
-        <v>2.36</v>
+        <v>2.35</v>
       </c>
       <c r="Q62">
-        <v>3.54</v>
+        <v>3.35</v>
       </c>
       <c r="R62">
-        <v>2.73</v>
+        <v>2.87</v>
       </c>
       <c r="S62">
         <v>0</v>
@@ -13961,7 +13961,7 @@
         <v>145</v>
       </c>
       <c r="D63" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E63" t="s">
         <v>249</v>
@@ -13997,13 +13997,13 @@
         <v>699</v>
       </c>
       <c r="P63">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="Q63">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="R63">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="S63">
         <v>0</v>
@@ -14143,10 +14143,10 @@
         <v>76</v>
       </c>
       <c r="C64" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="D64" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E64" t="s">
         <v>250</v>
@@ -14182,13 +14182,13 @@
         <v>699</v>
       </c>
       <c r="P64">
-        <v>3.36</v>
+        <v>1.92</v>
       </c>
       <c r="Q64">
-        <v>3.65</v>
+        <v>3.4</v>
       </c>
       <c r="R64">
-        <v>1.99</v>
+        <v>3.9</v>
       </c>
       <c r="S64">
         <v>0</v>
@@ -14328,7 +14328,7 @@
         <v>76</v>
       </c>
       <c r="C65" t="s">
-        <v>121</v>
+        <v>146</v>
       </c>
       <c r="D65" t="s">
         <v>186</v>
@@ -14513,10 +14513,10 @@
         <v>76</v>
       </c>
       <c r="C66" t="s">
-        <v>147</v>
+        <v>122</v>
       </c>
       <c r="D66" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E66" t="s">
         <v>252</v>
@@ -14698,7 +14698,7 @@
         <v>76</v>
       </c>
       <c r="C67" t="s">
-        <v>148</v>
+        <v>124</v>
       </c>
       <c r="D67" t="s">
         <v>185</v>
@@ -14737,13 +14737,13 @@
         <v>699</v>
       </c>
       <c r="P67">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="Q67">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="R67">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="S67">
         <v>0</v>
@@ -14883,7 +14883,7 @@
         <v>76</v>
       </c>
       <c r="C68" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="D68" t="s">
         <v>186</v>
@@ -14922,13 +14922,13 @@
         <v>699</v>
       </c>
       <c r="P68">
-        <v>2.58</v>
+        <v>2.46</v>
       </c>
       <c r="Q68">
-        <v>3.62</v>
+        <v>3.43</v>
       </c>
       <c r="R68">
-        <v>2.45</v>
+        <v>2.91</v>
       </c>
       <c r="S68">
         <v>0</v>
@@ -15068,7 +15068,7 @@
         <v>76</v>
       </c>
       <c r="C69" t="s">
-        <v>129</v>
+        <v>148</v>
       </c>
       <c r="D69" t="s">
         <v>185</v>
@@ -15253,7 +15253,7 @@
         <v>76</v>
       </c>
       <c r="C70" t="s">
-        <v>124</v>
+        <v>149</v>
       </c>
       <c r="D70" t="s">
         <v>186</v>
@@ -15292,13 +15292,13 @@
         <v>699</v>
       </c>
       <c r="P70">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="Q70">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="R70">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="S70">
         <v>0</v>
@@ -15438,10 +15438,10 @@
         <v>76</v>
       </c>
       <c r="C71" t="s">
-        <v>148</v>
+        <v>121</v>
       </c>
       <c r="D71" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E71" t="s">
         <v>257</v>
@@ -15477,13 +15477,13 @@
         <v>699</v>
       </c>
       <c r="P71">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="Q71">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="R71">
-        <v>2.87</v>
+        <v>0</v>
       </c>
       <c r="S71">
         <v>0</v>
@@ -15623,7 +15623,7 @@
         <v>76</v>
       </c>
       <c r="C72" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="D72" t="s">
         <v>186</v>
@@ -15662,13 +15662,13 @@
         <v>699</v>
       </c>
       <c r="P72">
-        <v>2.46</v>
+        <v>3.36</v>
       </c>
       <c r="Q72">
-        <v>3.43</v>
+        <v>3.65</v>
       </c>
       <c r="R72">
-        <v>2.91</v>
+        <v>1.99</v>
       </c>
       <c r="S72">
         <v>0</v>
@@ -15808,10 +15808,10 @@
         <v>76</v>
       </c>
       <c r="C73" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="D73" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E73" t="s">
         <v>259</v>
@@ -15847,13 +15847,13 @@
         <v>699</v>
       </c>
       <c r="P73">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="Q73">
-        <v>0</v>
+        <v>7.41</v>
       </c>
       <c r="R73">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="S73">
         <v>0</v>
@@ -15993,7 +15993,7 @@
         <v>76</v>
       </c>
       <c r="C74" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="D74" t="s">
         <v>186</v>
@@ -16032,13 +16032,13 @@
         <v>699</v>
       </c>
       <c r="P74">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="Q74">
-        <v>7.41</v>
+        <v>0</v>
       </c>
       <c r="R74">
-        <v>17.5</v>
+        <v>0</v>
       </c>
       <c r="S74">
         <v>0</v>
@@ -16178,7 +16178,7 @@
         <v>77</v>
       </c>
       <c r="C75" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="D75" t="s">
         <v>186</v>
@@ -16548,10 +16548,10 @@
         <v>78</v>
       </c>
       <c r="C77" t="s">
-        <v>128</v>
+        <v>151</v>
       </c>
       <c r="D77" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E77" t="s">
         <v>263</v>
@@ -16587,13 +16587,13 @@
         <v>699</v>
       </c>
       <c r="P77">
-        <v>4</v>
+        <v>2.79</v>
       </c>
       <c r="Q77">
-        <v>3.6</v>
+        <v>3.67</v>
       </c>
       <c r="R77">
-        <v>1.83</v>
+        <v>2.41</v>
       </c>
       <c r="S77">
         <v>0</v>
@@ -16918,10 +16918,10 @@
         <v>78</v>
       </c>
       <c r="C79" t="s">
-        <v>151</v>
+        <v>129</v>
       </c>
       <c r="D79" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E79" t="s">
         <v>265</v>
@@ -16957,13 +16957,13 @@
         <v>699</v>
       </c>
       <c r="P79">
-        <v>2.79</v>
+        <v>4</v>
       </c>
       <c r="Q79">
-        <v>3.67</v>
+        <v>3.6</v>
       </c>
       <c r="R79">
-        <v>2.41</v>
+        <v>1.83</v>
       </c>
       <c r="S79">
         <v>0</v>
@@ -17327,13 +17327,13 @@
         <v>699</v>
       </c>
       <c r="P81">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="Q81">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="R81">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S81">
         <v>0</v>
@@ -17473,10 +17473,10 @@
         <v>80</v>
       </c>
       <c r="C82" t="s">
-        <v>129</v>
+        <v>153</v>
       </c>
       <c r="D82" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E82" t="s">
         <v>268</v>
@@ -17512,13 +17512,13 @@
         <v>699</v>
       </c>
       <c r="P82">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="Q82">
-        <v>0</v>
+        <v>3.66</v>
       </c>
       <c r="R82">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="S82">
         <v>0</v>
@@ -17557,10 +17557,10 @@
         <v>0</v>
       </c>
       <c r="AE82">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AF82">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AG82">
         <v>0</v>
@@ -17658,7 +17658,7 @@
         <v>80</v>
       </c>
       <c r="C83" t="s">
-        <v>131</v>
+        <v>154</v>
       </c>
       <c r="D83" t="s">
         <v>186</v>
@@ -17697,13 +17697,13 @@
         <v>699</v>
       </c>
       <c r="P83">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="Q83">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="R83">
-        <v>4.01</v>
+        <v>0</v>
       </c>
       <c r="S83">
         <v>0</v>
@@ -17742,10 +17742,10 @@
         <v>0</v>
       </c>
       <c r="AE83">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AF83">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AG83">
         <v>0</v>
@@ -17843,10 +17843,10 @@
         <v>80</v>
       </c>
       <c r="C84" t="s">
-        <v>152</v>
+        <v>124</v>
       </c>
       <c r="D84" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E84" t="s">
         <v>270</v>
@@ -18028,10 +18028,10 @@
         <v>80</v>
       </c>
       <c r="C85" t="s">
-        <v>153</v>
+        <v>133</v>
       </c>
       <c r="D85" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E85" t="s">
         <v>271</v>
@@ -18067,13 +18067,13 @@
         <v>699</v>
       </c>
       <c r="P85">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="Q85">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="R85">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="S85">
         <v>0</v>
@@ -18213,10 +18213,10 @@
         <v>80</v>
       </c>
       <c r="C86" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="D86" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E86" t="s">
         <v>272</v>
@@ -18252,13 +18252,13 @@
         <v>699</v>
       </c>
       <c r="P86">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Q86">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="R86">
-        <v>0</v>
+        <v>4.07</v>
       </c>
       <c r="S86">
         <v>0</v>
@@ -18297,10 +18297,10 @@
         <v>0</v>
       </c>
       <c r="AE86">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AF86">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AG86">
         <v>0</v>
@@ -18398,7 +18398,7 @@
         <v>80</v>
       </c>
       <c r="C87" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="D87" t="s">
         <v>186</v>
@@ -18437,13 +18437,13 @@
         <v>699</v>
       </c>
       <c r="P87">
-        <v>2.69</v>
+        <v>5.38</v>
       </c>
       <c r="Q87">
-        <v>3.31</v>
+        <v>4.37</v>
       </c>
       <c r="R87">
-        <v>2.92</v>
+        <v>1.67</v>
       </c>
       <c r="S87">
         <v>0</v>
@@ -18482,10 +18482,10 @@
         <v>0</v>
       </c>
       <c r="AE87">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AF87">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AG87">
         <v>0</v>
@@ -18583,7 +18583,7 @@
         <v>80</v>
       </c>
       <c r="C88" t="s">
-        <v>131</v>
+        <v>153</v>
       </c>
       <c r="D88" t="s">
         <v>186</v>
@@ -18622,13 +18622,13 @@
         <v>699</v>
       </c>
       <c r="P88">
-        <v>2.1</v>
+        <v>2.69</v>
       </c>
       <c r="Q88">
-        <v>3.42</v>
+        <v>3.31</v>
       </c>
       <c r="R88">
-        <v>4.07</v>
+        <v>2.92</v>
       </c>
       <c r="S88">
         <v>0</v>
@@ -18667,10 +18667,10 @@
         <v>0</v>
       </c>
       <c r="AE88">
-        <v>2.15</v>
+        <v>1.87</v>
       </c>
       <c r="AF88">
-        <v>1.61</v>
+        <v>1.89</v>
       </c>
       <c r="AG88">
         <v>0</v>
@@ -18768,7 +18768,7 @@
         <v>80</v>
       </c>
       <c r="C89" t="s">
-        <v>154</v>
+        <v>131</v>
       </c>
       <c r="D89" t="s">
         <v>186</v>
@@ -18807,13 +18807,13 @@
         <v>699</v>
       </c>
       <c r="P89">
-        <v>5.38</v>
+        <v>2.09</v>
       </c>
       <c r="Q89">
-        <v>4.37</v>
+        <v>3.48</v>
       </c>
       <c r="R89">
-        <v>1.67</v>
+        <v>4.01</v>
       </c>
       <c r="S89">
         <v>0</v>
@@ -18852,10 +18852,10 @@
         <v>0</v>
       </c>
       <c r="AE89">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AF89">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AG89">
         <v>0</v>
@@ -18953,7 +18953,7 @@
         <v>80</v>
       </c>
       <c r="C90" t="s">
-        <v>155</v>
+        <v>126</v>
       </c>
       <c r="D90" t="s">
         <v>186</v>
@@ -18992,13 +18992,13 @@
         <v>699</v>
       </c>
       <c r="P90">
-        <v>2.59</v>
+        <v>0</v>
       </c>
       <c r="Q90">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="R90">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="S90">
         <v>0</v>
@@ -19138,7 +19138,7 @@
         <v>80</v>
       </c>
       <c r="C91" t="s">
-        <v>156</v>
+        <v>150</v>
       </c>
       <c r="D91" t="s">
         <v>186</v>
@@ -19323,7 +19323,7 @@
         <v>80</v>
       </c>
       <c r="C92" t="s">
-        <v>124</v>
+        <v>154</v>
       </c>
       <c r="D92" t="s">
         <v>186</v>
@@ -19508,7 +19508,7 @@
         <v>80</v>
       </c>
       <c r="C93" t="s">
-        <v>150</v>
+        <v>155</v>
       </c>
       <c r="D93" t="s">
         <v>186</v>
@@ -19693,7 +19693,7 @@
         <v>80</v>
       </c>
       <c r="C94" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="D94" t="s">
         <v>186</v>
@@ -19732,13 +19732,13 @@
         <v>699</v>
       </c>
       <c r="P94">
-        <v>2.46</v>
+        <v>2.21</v>
       </c>
       <c r="Q94">
-        <v>3.66</v>
+        <v>3.22</v>
       </c>
       <c r="R94">
-        <v>2.99</v>
+        <v>3.22</v>
       </c>
       <c r="S94">
         <v>0</v>
@@ -19777,10 +19777,10 @@
         <v>0</v>
       </c>
       <c r="AE94">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AF94">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AG94">
         <v>0</v>
@@ -20063,7 +20063,7 @@
         <v>82</v>
       </c>
       <c r="C96" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="D96" t="s">
         <v>186</v>
@@ -20248,10 +20248,10 @@
         <v>83</v>
       </c>
       <c r="C97" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="D97" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E97" t="s">
         <v>283</v>
@@ -20287,13 +20287,13 @@
         <v>699</v>
       </c>
       <c r="P97">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="Q97">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="R97">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="S97">
         <v>0</v>
@@ -20332,10 +20332,10 @@
         <v>0</v>
       </c>
       <c r="AE97">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AF97">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AG97">
         <v>0</v>
@@ -20472,13 +20472,13 @@
         <v>699</v>
       </c>
       <c r="P98">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="Q98">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R98">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="S98">
         <v>0</v>
@@ -20618,7 +20618,7 @@
         <v>83</v>
       </c>
       <c r="C99" t="s">
-        <v>159</v>
+        <v>139</v>
       </c>
       <c r="D99" t="s">
         <v>186</v>
@@ -20657,13 +20657,13 @@
         <v>699</v>
       </c>
       <c r="P99">
-        <v>3.04</v>
+        <v>2.38</v>
       </c>
       <c r="Q99">
-        <v>3.1</v>
+        <v>3.24</v>
       </c>
       <c r="R99">
-        <v>2.32</v>
+        <v>3.14</v>
       </c>
       <c r="S99">
         <v>0</v>
@@ -20702,10 +20702,10 @@
         <v>0</v>
       </c>
       <c r="AE99">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AF99">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG99">
         <v>0</v>
@@ -20803,10 +20803,10 @@
         <v>83</v>
       </c>
       <c r="C100" t="s">
-        <v>141</v>
+        <v>159</v>
       </c>
       <c r="D100" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E100" t="s">
         <v>286</v>
@@ -20988,10 +20988,10 @@
         <v>83</v>
       </c>
       <c r="C101" t="s">
-        <v>146</v>
+        <v>160</v>
       </c>
       <c r="D101" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E101" t="s">
         <v>287</v>
@@ -21027,13 +21027,13 @@
         <v>699</v>
       </c>
       <c r="P101">
-        <v>4.68</v>
+        <v>0</v>
       </c>
       <c r="Q101">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R101">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="S101">
         <v>0</v>
@@ -21173,10 +21173,10 @@
         <v>83</v>
       </c>
       <c r="C102" t="s">
-        <v>135</v>
+        <v>158</v>
       </c>
       <c r="D102" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E102" t="s">
         <v>288</v>
@@ -21358,10 +21358,10 @@
         <v>83</v>
       </c>
       <c r="C103" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="D103" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E103" t="s">
         <v>289</v>
@@ -21543,7 +21543,7 @@
         <v>83</v>
       </c>
       <c r="C104" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="D104" t="s">
         <v>186</v>
@@ -21913,7 +21913,7 @@
         <v>83</v>
       </c>
       <c r="C106" t="s">
-        <v>161</v>
+        <v>145</v>
       </c>
       <c r="D106" t="s">
         <v>186</v>
@@ -21952,13 +21952,13 @@
         <v>699</v>
       </c>
       <c r="P106">
-        <v>0</v>
+        <v>4.68</v>
       </c>
       <c r="Q106">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R106">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="S106">
         <v>0</v>
@@ -22098,10 +22098,10 @@
         <v>83</v>
       </c>
       <c r="C107" t="s">
-        <v>160</v>
+        <v>142</v>
       </c>
       <c r="D107" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E107" t="s">
         <v>293</v>
@@ -22283,7 +22283,7 @@
         <v>84</v>
       </c>
       <c r="C108" t="s">
-        <v>147</v>
+        <v>123</v>
       </c>
       <c r="D108" t="s">
         <v>186</v>
@@ -22322,13 +22322,13 @@
         <v>699</v>
       </c>
       <c r="P108">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="Q108">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="R108">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="S108">
         <v>0</v>
@@ -22468,7 +22468,7 @@
         <v>84</v>
       </c>
       <c r="C109" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="D109" t="s">
         <v>186</v>
@@ -22653,7 +22653,7 @@
         <v>84</v>
       </c>
       <c r="C110" t="s">
-        <v>123</v>
+        <v>146</v>
       </c>
       <c r="D110" t="s">
         <v>186</v>
@@ -22692,13 +22692,13 @@
         <v>699</v>
       </c>
       <c r="P110">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="Q110">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="R110">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="S110">
         <v>0</v>
@@ -22841,7 +22841,7 @@
         <v>144</v>
       </c>
       <c r="D111" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E111" t="s">
         <v>297</v>
@@ -22877,13 +22877,13 @@
         <v>699</v>
       </c>
       <c r="P111">
-        <v>2.05</v>
+        <v>2.27</v>
       </c>
       <c r="Q111">
-        <v>3.64</v>
+        <v>3.58</v>
       </c>
       <c r="R111">
-        <v>3.28</v>
+        <v>2.88</v>
       </c>
       <c r="S111">
         <v>0</v>
@@ -23023,7 +23023,7 @@
         <v>85</v>
       </c>
       <c r="C112" t="s">
-        <v>119</v>
+        <v>149</v>
       </c>
       <c r="D112" t="s">
         <v>186</v>
@@ -23062,13 +23062,13 @@
         <v>699</v>
       </c>
       <c r="P112">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Q112">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="R112">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="S112">
         <v>0</v>
@@ -23208,7 +23208,7 @@
         <v>85</v>
       </c>
       <c r="C113" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="D113" t="s">
         <v>186</v>
@@ -23247,13 +23247,13 @@
         <v>699</v>
       </c>
       <c r="P113">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="Q113">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="R113">
-        <v>3.57</v>
+        <v>0</v>
       </c>
       <c r="S113">
         <v>0</v>
@@ -23298,10 +23298,10 @@
         <v>0</v>
       </c>
       <c r="AG113">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AH113">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AI113">
         <v>0</v>
@@ -23393,10 +23393,10 @@
         <v>85</v>
       </c>
       <c r="C114" t="s">
-        <v>148</v>
+        <v>118</v>
       </c>
       <c r="D114" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E114" t="s">
         <v>300</v>
@@ -23432,13 +23432,13 @@
         <v>699</v>
       </c>
       <c r="P114">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="Q114">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="R114">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="S114">
         <v>0</v>
@@ -23578,7 +23578,7 @@
         <v>85</v>
       </c>
       <c r="C115" t="s">
-        <v>137</v>
+        <v>149</v>
       </c>
       <c r="D115" t="s">
         <v>186</v>
@@ -23617,13 +23617,13 @@
         <v>699</v>
       </c>
       <c r="P115">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="Q115">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="R115">
-        <v>0</v>
+        <v>3.57</v>
       </c>
       <c r="S115">
         <v>0</v>
@@ -23668,10 +23668,10 @@
         <v>0</v>
       </c>
       <c r="AG115">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AH115">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AI115">
         <v>0</v>
@@ -23802,13 +23802,13 @@
         <v>699</v>
       </c>
       <c r="P116">
-        <v>1.71</v>
+        <v>1.77</v>
       </c>
       <c r="Q116">
-        <v>4.37</v>
+        <v>4.17</v>
       </c>
       <c r="R116">
-        <v>4.42</v>
+        <v>4.22</v>
       </c>
       <c r="S116">
         <v>0</v>
@@ -23847,16 +23847,16 @@
         <v>0</v>
       </c>
       <c r="AE116">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AF116">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AG116">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AH116">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AI116">
         <v>0</v>
@@ -23987,13 +23987,13 @@
         <v>699</v>
       </c>
       <c r="P117">
-        <v>1.44</v>
+        <v>1.78</v>
       </c>
       <c r="Q117">
-        <v>5.14</v>
+        <v>4.17</v>
       </c>
       <c r="R117">
-        <v>6.53</v>
+        <v>4.17</v>
       </c>
       <c r="S117">
         <v>0</v>
@@ -24038,7 +24038,7 @@
         <v>0</v>
       </c>
       <c r="AG117">
-        <v>1.93</v>
+        <v>1.9</v>
       </c>
       <c r="AH117">
         <v>1.77</v>
@@ -24172,13 +24172,13 @@
         <v>699</v>
       </c>
       <c r="P118">
-        <v>1.96</v>
+        <v>2.78</v>
       </c>
       <c r="Q118">
-        <v>4.05</v>
+        <v>3.89</v>
       </c>
       <c r="R118">
-        <v>3.5</v>
+        <v>2.36</v>
       </c>
       <c r="S118">
         <v>0</v>
@@ -24223,10 +24223,10 @@
         <v>0</v>
       </c>
       <c r="AG118">
-        <v>2.2</v>
+        <v>2.05</v>
       </c>
       <c r="AH118">
-        <v>1.58</v>
+        <v>1.68</v>
       </c>
       <c r="AI118">
         <v>0</v>
@@ -24357,13 +24357,13 @@
         <v>699</v>
       </c>
       <c r="P119">
-        <v>2.78</v>
+        <v>1.48</v>
       </c>
       <c r="Q119">
-        <v>3.89</v>
+        <v>4.94</v>
       </c>
       <c r="R119">
-        <v>2.36</v>
+        <v>6.07</v>
       </c>
       <c r="S119">
         <v>0</v>
@@ -24408,10 +24408,10 @@
         <v>0</v>
       </c>
       <c r="AG119">
-        <v>2.05</v>
+        <v>1.98</v>
       </c>
       <c r="AH119">
-        <v>1.68</v>
+        <v>1.72</v>
       </c>
       <c r="AI119">
         <v>0</v>
@@ -24542,13 +24542,13 @@
         <v>699</v>
       </c>
       <c r="P120">
-        <v>1.77</v>
+        <v>1.96</v>
       </c>
       <c r="Q120">
-        <v>4.17</v>
+        <v>4.05</v>
       </c>
       <c r="R120">
-        <v>4.22</v>
+        <v>3.5</v>
       </c>
       <c r="S120">
         <v>0</v>
@@ -24587,16 +24587,16 @@
         <v>0</v>
       </c>
       <c r="AE120">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AF120">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AG120">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH120">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AI120">
         <v>0</v>
@@ -24727,13 +24727,13 @@
         <v>699</v>
       </c>
       <c r="P121">
-        <v>1.78</v>
+        <v>1.71</v>
       </c>
       <c r="Q121">
-        <v>4.17</v>
+        <v>4.37</v>
       </c>
       <c r="R121">
-        <v>4.17</v>
+        <v>4.42</v>
       </c>
       <c r="S121">
         <v>0</v>
@@ -24778,10 +24778,10 @@
         <v>0</v>
       </c>
       <c r="AG121">
-        <v>1.9</v>
+        <v>2.1</v>
       </c>
       <c r="AH121">
-        <v>1.77</v>
+        <v>1.65</v>
       </c>
       <c r="AI121">
         <v>0</v>
@@ -24912,13 +24912,13 @@
         <v>699</v>
       </c>
       <c r="P122">
-        <v>2.49</v>
+        <v>1.44</v>
       </c>
       <c r="Q122">
-        <v>3.77</v>
+        <v>5.14</v>
       </c>
       <c r="R122">
-        <v>2.67</v>
+        <v>6.53</v>
       </c>
       <c r="S122">
         <v>0</v>
@@ -24957,16 +24957,16 @@
         <v>0</v>
       </c>
       <c r="AE122">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AF122">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AG122">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AH122">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AI122">
         <v>0</v>
@@ -25282,13 +25282,13 @@
         <v>699</v>
       </c>
       <c r="P124">
-        <v>1.48</v>
+        <v>2.49</v>
       </c>
       <c r="Q124">
-        <v>4.94</v>
+        <v>3.77</v>
       </c>
       <c r="R124">
-        <v>6.07</v>
+        <v>2.67</v>
       </c>
       <c r="S124">
         <v>0</v>
@@ -25327,16 +25327,16 @@
         <v>0</v>
       </c>
       <c r="AE124">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AF124">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AG124">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AH124">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AI124">
         <v>0</v>
@@ -25428,10 +25428,10 @@
         <v>87</v>
       </c>
       <c r="C125" t="s">
-        <v>151</v>
+        <v>163</v>
       </c>
       <c r="D125" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E125" t="s">
         <v>311</v>
@@ -25467,13 +25467,13 @@
         <v>699</v>
       </c>
       <c r="P125">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="Q125">
-        <v>4.44</v>
+        <v>0</v>
       </c>
       <c r="R125">
-        <v>5.16</v>
+        <v>0</v>
       </c>
       <c r="S125">
         <v>0</v>
@@ -25613,10 +25613,10 @@
         <v>87</v>
       </c>
       <c r="C126" t="s">
-        <v>158</v>
+        <v>164</v>
       </c>
       <c r="D126" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E126" t="s">
         <v>312</v>
@@ -25652,13 +25652,13 @@
         <v>699</v>
       </c>
       <c r="P126">
-        <v>0</v>
+        <v>4.07</v>
       </c>
       <c r="Q126">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="R126">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="S126">
         <v>0</v>
@@ -25798,10 +25798,10 @@
         <v>87</v>
       </c>
       <c r="C127" t="s">
-        <v>158</v>
+        <v>164</v>
       </c>
       <c r="D127" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E127" t="s">
         <v>313</v>
@@ -25837,13 +25837,13 @@
         <v>699</v>
       </c>
       <c r="P127">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Q127">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="R127">
-        <v>0</v>
+        <v>3.01</v>
       </c>
       <c r="S127">
         <v>0</v>
@@ -25983,7 +25983,7 @@
         <v>87</v>
       </c>
       <c r="C128" t="s">
-        <v>125</v>
+        <v>159</v>
       </c>
       <c r="D128" t="s">
         <v>186</v>
@@ -26168,10 +26168,10 @@
         <v>87</v>
       </c>
       <c r="C129" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="D129" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E129" t="s">
         <v>315</v>
@@ -26207,13 +26207,13 @@
         <v>699</v>
       </c>
       <c r="P129">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="Q129">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="R129">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="S129">
         <v>0</v>
@@ -26353,7 +26353,7 @@
         <v>87</v>
       </c>
       <c r="C130" t="s">
-        <v>120</v>
+        <v>128</v>
       </c>
       <c r="D130" t="s">
         <v>186</v>
@@ -26538,10 +26538,10 @@
         <v>87</v>
       </c>
       <c r="C131" t="s">
-        <v>151</v>
+        <v>159</v>
       </c>
       <c r="D131" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E131" t="s">
         <v>317</v>
@@ -26577,13 +26577,13 @@
         <v>699</v>
       </c>
       <c r="P131">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="Q131">
-        <v>3.82</v>
+        <v>0</v>
       </c>
       <c r="R131">
-        <v>4.13</v>
+        <v>0</v>
       </c>
       <c r="S131">
         <v>0</v>
@@ -26723,7 +26723,7 @@
         <v>87</v>
       </c>
       <c r="C132" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="D132" t="s">
         <v>186</v>
@@ -26908,7 +26908,7 @@
         <v>87</v>
       </c>
       <c r="C133" t="s">
-        <v>143</v>
+        <v>163</v>
       </c>
       <c r="D133" t="s">
         <v>186</v>
@@ -27093,7 +27093,7 @@
         <v>87</v>
       </c>
       <c r="C134" t="s">
-        <v>164</v>
+        <v>143</v>
       </c>
       <c r="D134" t="s">
         <v>186</v>
@@ -27132,13 +27132,13 @@
         <v>699</v>
       </c>
       <c r="P134">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="Q134">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R134">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="S134">
         <v>0</v>
@@ -27177,10 +27177,10 @@
         <v>0</v>
       </c>
       <c r="AE134">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AF134">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AG134">
         <v>0</v>
@@ -27278,10 +27278,10 @@
         <v>87</v>
       </c>
       <c r="C135" t="s">
-        <v>158</v>
+        <v>164</v>
       </c>
       <c r="D135" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E135" t="s">
         <v>321</v>
@@ -27317,13 +27317,13 @@
         <v>699</v>
       </c>
       <c r="P135">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Q135">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R135">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="S135">
         <v>0</v>
@@ -27463,7 +27463,7 @@
         <v>87</v>
       </c>
       <c r="C136" t="s">
-        <v>165</v>
+        <v>151</v>
       </c>
       <c r="D136" t="s">
         <v>185</v>
@@ -27502,13 +27502,13 @@
         <v>699</v>
       </c>
       <c r="P136">
-        <v>2.15</v>
+        <v>1.84</v>
       </c>
       <c r="Q136">
-        <v>3.7</v>
+        <v>3.82</v>
       </c>
       <c r="R136">
-        <v>3.01</v>
+        <v>4.13</v>
       </c>
       <c r="S136">
         <v>0</v>
@@ -27648,7 +27648,7 @@
         <v>87</v>
       </c>
       <c r="C137" t="s">
-        <v>165</v>
+        <v>151</v>
       </c>
       <c r="D137" t="s">
         <v>185</v>
@@ -27687,13 +27687,13 @@
         <v>699</v>
       </c>
       <c r="P137">
-        <v>4.07</v>
+        <v>1.59</v>
       </c>
       <c r="Q137">
-        <v>3.9</v>
+        <v>4.44</v>
       </c>
       <c r="R137">
-        <v>1.78</v>
+        <v>5.16</v>
       </c>
       <c r="S137">
         <v>0</v>
@@ -27833,10 +27833,10 @@
         <v>87</v>
       </c>
       <c r="C138" t="s">
-        <v>165</v>
+        <v>126</v>
       </c>
       <c r="D138" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E138" t="s">
         <v>324</v>
@@ -27872,13 +27872,13 @@
         <v>699</v>
       </c>
       <c r="P138">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="Q138">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R138">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="S138">
         <v>0</v>
@@ -28018,7 +28018,7 @@
         <v>87</v>
       </c>
       <c r="C139" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="D139" t="s">
         <v>186</v>
@@ -28206,7 +28206,7 @@
         <v>165</v>
       </c>
       <c r="D140" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E140" t="s">
         <v>326</v>
@@ -28242,13 +28242,13 @@
         <v>699</v>
       </c>
       <c r="P140">
-        <v>5.4</v>
+        <v>3.75</v>
       </c>
       <c r="Q140">
-        <v>4.6</v>
+        <v>3.6</v>
       </c>
       <c r="R140">
-        <v>1.51</v>
+        <v>1.91</v>
       </c>
       <c r="S140">
         <v>0</v>
@@ -28287,10 +28287,10 @@
         <v>0</v>
       </c>
       <c r="AE140">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AF140">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG140">
         <v>0</v>
@@ -28388,7 +28388,7 @@
         <v>87</v>
       </c>
       <c r="C141" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="D141" t="s">
         <v>186</v>
@@ -28573,10 +28573,10 @@
         <v>87</v>
       </c>
       <c r="C142" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="D142" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E142" t="s">
         <v>328</v>
@@ -28612,13 +28612,13 @@
         <v>699</v>
       </c>
       <c r="P142">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="Q142">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R142">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="S142">
         <v>0</v>
@@ -28758,10 +28758,10 @@
         <v>87</v>
       </c>
       <c r="C143" t="s">
-        <v>158</v>
+        <v>151</v>
       </c>
       <c r="D143" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E143" t="s">
         <v>329</v>
@@ -28797,13 +28797,13 @@
         <v>699</v>
       </c>
       <c r="P143">
-        <v>0</v>
+        <v>3.87</v>
       </c>
       <c r="Q143">
-        <v>0</v>
+        <v>3.87</v>
       </c>
       <c r="R143">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="S143">
         <v>0</v>
@@ -28943,7 +28943,7 @@
         <v>87</v>
       </c>
       <c r="C144" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="D144" t="s">
         <v>186</v>
@@ -29128,10 +29128,10 @@
         <v>87</v>
       </c>
       <c r="C145" t="s">
-        <v>151</v>
+        <v>129</v>
       </c>
       <c r="D145" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E145" t="s">
         <v>331</v>
@@ -29167,13 +29167,13 @@
         <v>699</v>
       </c>
       <c r="P145">
-        <v>3.87</v>
+        <v>2.55</v>
       </c>
       <c r="Q145">
-        <v>3.87</v>
+        <v>3.6</v>
       </c>
       <c r="R145">
-        <v>1.89</v>
+        <v>2.43</v>
       </c>
       <c r="S145">
         <v>0</v>
@@ -29313,10 +29313,10 @@
         <v>87</v>
       </c>
       <c r="C146" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="D146" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E146" t="s">
         <v>332</v>
@@ -29352,13 +29352,13 @@
         <v>699</v>
       </c>
       <c r="P146">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="Q146">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="R146">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="S146">
         <v>0</v>
@@ -29498,7 +29498,7 @@
         <v>87</v>
       </c>
       <c r="C147" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="D147" t="s">
         <v>186</v>
@@ -29507,7 +29507,7 @@
         <v>333</v>
       </c>
       <c r="F147" t="s">
-        <v>290</v>
+        <v>589</v>
       </c>
       <c r="G147">
         <v>0</v>
@@ -29683,16 +29683,16 @@
         <v>87</v>
       </c>
       <c r="C148" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="D148" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E148" t="s">
         <v>334</v>
       </c>
       <c r="F148" t="s">
-        <v>589</v>
+        <v>288</v>
       </c>
       <c r="G148">
         <v>0</v>
@@ -29722,13 +29722,13 @@
         <v>699</v>
       </c>
       <c r="P148">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="Q148">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="R148">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="S148">
         <v>0</v>
@@ -29868,7 +29868,7 @@
         <v>87</v>
       </c>
       <c r="C149" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="D149" t="s">
         <v>186</v>
@@ -29907,13 +29907,13 @@
         <v>699</v>
       </c>
       <c r="P149">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Q149">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="R149">
-        <v>2.96</v>
+        <v>0</v>
       </c>
       <c r="S149">
         <v>0</v>
@@ -30053,7 +30053,7 @@
         <v>87</v>
       </c>
       <c r="C150" t="s">
-        <v>158</v>
+        <v>163</v>
       </c>
       <c r="D150" t="s">
         <v>186</v>
@@ -30238,10 +30238,10 @@
         <v>87</v>
       </c>
       <c r="C151" t="s">
-        <v>145</v>
+        <v>165</v>
       </c>
       <c r="D151" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E151" t="s">
         <v>337</v>
@@ -30277,13 +30277,13 @@
         <v>699</v>
       </c>
       <c r="P151">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Q151">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="R151">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="S151">
         <v>0</v>
@@ -30423,10 +30423,10 @@
         <v>87</v>
       </c>
       <c r="C152" t="s">
-        <v>166</v>
+        <v>148</v>
       </c>
       <c r="D152" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E152" t="s">
         <v>338</v>
@@ -30608,7 +30608,7 @@
         <v>87</v>
       </c>
       <c r="C153" t="s">
-        <v>166</v>
+        <v>159</v>
       </c>
       <c r="D153" t="s">
         <v>186</v>
@@ -30978,7 +30978,7 @@
         <v>87</v>
       </c>
       <c r="C155" t="s">
-        <v>128</v>
+        <v>166</v>
       </c>
       <c r="D155" t="s">
         <v>186</v>
@@ -31017,13 +31017,13 @@
         <v>699</v>
       </c>
       <c r="P155">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="Q155">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R155">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="S155">
         <v>0</v>
@@ -31163,10 +31163,10 @@
         <v>87</v>
       </c>
       <c r="C156" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="D156" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E156" t="s">
         <v>342</v>
@@ -31202,13 +31202,13 @@
         <v>699</v>
       </c>
       <c r="P156">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Q156">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="R156">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="S156">
         <v>0</v>
@@ -32088,7 +32088,7 @@
         <v>89</v>
       </c>
       <c r="C161" t="s">
-        <v>154</v>
+        <v>168</v>
       </c>
       <c r="D161" t="s">
         <v>186</v>
@@ -32127,13 +32127,13 @@
         <v>699</v>
       </c>
       <c r="P161">
-        <v>5.17</v>
+        <v>0</v>
       </c>
       <c r="Q161">
-        <v>4.37</v>
+        <v>0</v>
       </c>
       <c r="R161">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="S161">
         <v>0</v>
@@ -32172,10 +32172,10 @@
         <v>0</v>
       </c>
       <c r="AE161">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AF161">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AG161">
         <v>0</v>
@@ -32458,7 +32458,7 @@
         <v>89</v>
       </c>
       <c r="C163" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="D163" t="s">
         <v>186</v>
@@ -32497,13 +32497,13 @@
         <v>699</v>
       </c>
       <c r="P163">
-        <v>0</v>
+        <v>5.17</v>
       </c>
       <c r="Q163">
-        <v>0</v>
+        <v>4.37</v>
       </c>
       <c r="R163">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="S163">
         <v>0</v>
@@ -32542,10 +32542,10 @@
         <v>0</v>
       </c>
       <c r="AE163">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AF163">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AG163">
         <v>0</v>
@@ -32828,7 +32828,7 @@
         <v>89</v>
       </c>
       <c r="C165" t="s">
-        <v>168</v>
+        <v>155</v>
       </c>
       <c r="D165" t="s">
         <v>186</v>
@@ -33013,7 +33013,7 @@
         <v>90</v>
       </c>
       <c r="C166" t="s">
-        <v>169</v>
+        <v>145</v>
       </c>
       <c r="D166" t="s">
         <v>186</v>
@@ -33198,7 +33198,7 @@
         <v>90</v>
       </c>
       <c r="C167" t="s">
-        <v>169</v>
+        <v>156</v>
       </c>
       <c r="D167" t="s">
         <v>186</v>
@@ -33237,13 +33237,13 @@
         <v>699</v>
       </c>
       <c r="P167">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="Q167">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R167">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="S167">
         <v>0</v>
@@ -33383,10 +33383,10 @@
         <v>90</v>
       </c>
       <c r="C168" t="s">
-        <v>120</v>
+        <v>136</v>
       </c>
       <c r="D168" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E168" t="s">
         <v>354</v>
@@ -33753,7 +33753,7 @@
         <v>90</v>
       </c>
       <c r="C170" t="s">
-        <v>170</v>
+        <v>120</v>
       </c>
       <c r="D170" t="s">
         <v>186</v>
@@ -33938,7 +33938,7 @@
         <v>90</v>
       </c>
       <c r="C171" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="D171" t="s">
         <v>186</v>
@@ -34123,7 +34123,7 @@
         <v>90</v>
       </c>
       <c r="C172" t="s">
-        <v>131</v>
+        <v>170</v>
       </c>
       <c r="D172" t="s">
         <v>186</v>
@@ -34162,13 +34162,13 @@
         <v>699</v>
       </c>
       <c r="P172">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="Q172">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="R172">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="S172">
         <v>0</v>
@@ -34308,7 +34308,7 @@
         <v>90</v>
       </c>
       <c r="C173" t="s">
-        <v>146</v>
+        <v>170</v>
       </c>
       <c r="D173" t="s">
         <v>186</v>
@@ -34493,7 +34493,7 @@
         <v>90</v>
       </c>
       <c r="C174" t="s">
-        <v>153</v>
+        <v>131</v>
       </c>
       <c r="D174" t="s">
         <v>186</v>
@@ -34532,13 +34532,13 @@
         <v>699</v>
       </c>
       <c r="P174">
-        <v>1.83</v>
+        <v>5</v>
       </c>
       <c r="Q174">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="R174">
-        <v>4.3</v>
+        <v>1.75</v>
       </c>
       <c r="S174">
         <v>0</v>
@@ -34678,10 +34678,10 @@
         <v>90</v>
       </c>
       <c r="C175" t="s">
-        <v>135</v>
+        <v>170</v>
       </c>
       <c r="D175" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E175" t="s">
         <v>361</v>
@@ -34863,7 +34863,7 @@
         <v>90</v>
       </c>
       <c r="C176" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="D176" t="s">
         <v>186</v>
@@ -35233,7 +35233,7 @@
         <v>92</v>
       </c>
       <c r="C178" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="D178" t="s">
         <v>186</v>
@@ -35973,7 +35973,7 @@
         <v>93</v>
       </c>
       <c r="C182" t="s">
-        <v>123</v>
+        <v>172</v>
       </c>
       <c r="D182" t="s">
         <v>186</v>
@@ -36012,13 +36012,13 @@
         <v>699</v>
       </c>
       <c r="P182">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Q182">
-        <v>3.66</v>
+        <v>0</v>
       </c>
       <c r="R182">
-        <v>3.36</v>
+        <v>0</v>
       </c>
       <c r="S182">
         <v>0</v>
@@ -36343,10 +36343,10 @@
         <v>93</v>
       </c>
       <c r="C184" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="D184" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E184" t="s">
         <v>370</v>
@@ -36528,7 +36528,7 @@
         <v>93</v>
       </c>
       <c r="C185" t="s">
-        <v>152</v>
+        <v>147</v>
       </c>
       <c r="D185" t="s">
         <v>186</v>
@@ -36567,13 +36567,13 @@
         <v>699</v>
       </c>
       <c r="P185">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="Q185">
-        <v>0</v>
+        <v>3.53</v>
       </c>
       <c r="R185">
-        <v>0</v>
+        <v>3.91</v>
       </c>
       <c r="S185">
         <v>0</v>
@@ -36612,10 +36612,10 @@
         <v>0</v>
       </c>
       <c r="AE185">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AF185">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AG185">
         <v>0</v>
@@ -36713,7 +36713,7 @@
         <v>93</v>
       </c>
       <c r="C186" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="D186" t="s">
         <v>186</v>
@@ -36752,13 +36752,13 @@
         <v>699</v>
       </c>
       <c r="P186">
-        <v>1.91</v>
+        <v>3.12</v>
       </c>
       <c r="Q186">
-        <v>3.53</v>
+        <v>3.22</v>
       </c>
       <c r="R186">
-        <v>3.91</v>
+        <v>2.43</v>
       </c>
       <c r="S186">
         <v>0</v>
@@ -36797,10 +36797,10 @@
         <v>0</v>
       </c>
       <c r="AE186">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AF186">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AG186">
         <v>0</v>
@@ -36898,10 +36898,10 @@
         <v>93</v>
       </c>
       <c r="C187" t="s">
-        <v>173</v>
+        <v>154</v>
       </c>
       <c r="D187" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E187" t="s">
         <v>373</v>
@@ -36937,13 +36937,13 @@
         <v>699</v>
       </c>
       <c r="P187">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="Q187">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="R187">
-        <v>7.95</v>
+        <v>0</v>
       </c>
       <c r="S187">
         <v>0</v>
@@ -37083,7 +37083,7 @@
         <v>93</v>
       </c>
       <c r="C188" t="s">
-        <v>147</v>
+        <v>172</v>
       </c>
       <c r="D188" t="s">
         <v>186</v>
@@ -37453,7 +37453,7 @@
         <v>93</v>
       </c>
       <c r="C190" t="s">
-        <v>149</v>
+        <v>123</v>
       </c>
       <c r="D190" t="s">
         <v>186</v>
@@ -37492,13 +37492,13 @@
         <v>699</v>
       </c>
       <c r="P190">
-        <v>3.12</v>
+        <v>2.25</v>
       </c>
       <c r="Q190">
-        <v>3.22</v>
+        <v>3.66</v>
       </c>
       <c r="R190">
-        <v>2.43</v>
+        <v>3.36</v>
       </c>
       <c r="S190">
         <v>0</v>
@@ -37638,7 +37638,7 @@
         <v>93</v>
       </c>
       <c r="C191" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="D191" t="s">
         <v>186</v>
@@ -37677,13 +37677,13 @@
         <v>699</v>
       </c>
       <c r="P191">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="Q191">
-        <v>5.66</v>
+        <v>0</v>
       </c>
       <c r="R191">
-        <v>8.98</v>
+        <v>0</v>
       </c>
       <c r="S191">
         <v>0</v>
@@ -37823,10 +37823,10 @@
         <v>93</v>
       </c>
       <c r="C192" t="s">
-        <v>159</v>
+        <v>173</v>
       </c>
       <c r="D192" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E192" t="s">
         <v>378</v>
@@ -37862,13 +37862,13 @@
         <v>699</v>
       </c>
       <c r="P192">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="Q192">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="R192">
-        <v>6.76</v>
+        <v>0</v>
       </c>
       <c r="S192">
         <v>0</v>
@@ -38008,10 +38008,10 @@
         <v>93</v>
       </c>
       <c r="C193" t="s">
-        <v>174</v>
+        <v>139</v>
       </c>
       <c r="D193" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E193" t="s">
         <v>379</v>
@@ -38047,13 +38047,13 @@
         <v>699</v>
       </c>
       <c r="P193">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Q193">
-        <v>0</v>
+        <v>5.66</v>
       </c>
       <c r="R193">
-        <v>0</v>
+        <v>8.98</v>
       </c>
       <c r="S193">
         <v>0</v>
@@ -38193,10 +38193,10 @@
         <v>93</v>
       </c>
       <c r="C194" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="D194" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E194" t="s">
         <v>380</v>
@@ -38232,13 +38232,13 @@
         <v>699</v>
       </c>
       <c r="P194">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Q194">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="R194">
-        <v>0</v>
+        <v>7.95</v>
       </c>
       <c r="S194">
         <v>0</v>
@@ -38378,10 +38378,10 @@
         <v>93</v>
       </c>
       <c r="C195" t="s">
-        <v>174</v>
+        <v>158</v>
       </c>
       <c r="D195" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E195" t="s">
         <v>381</v>
@@ -38417,13 +38417,13 @@
         <v>699</v>
       </c>
       <c r="P195">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="Q195">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R195">
-        <v>0</v>
+        <v>4.56</v>
       </c>
       <c r="S195">
         <v>0</v>
@@ -38563,7 +38563,7 @@
         <v>93</v>
       </c>
       <c r="C196" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="D196" t="s">
         <v>186</v>
@@ -38602,13 +38602,13 @@
         <v>699</v>
       </c>
       <c r="P196">
-        <v>1.82</v>
+        <v>1.45</v>
       </c>
       <c r="Q196">
-        <v>3.1</v>
+        <v>3.8</v>
       </c>
       <c r="R196">
-        <v>4.56</v>
+        <v>6.76</v>
       </c>
       <c r="S196">
         <v>0</v>
@@ -38748,7 +38748,7 @@
         <v>94</v>
       </c>
       <c r="C197" t="s">
-        <v>158</v>
+        <v>128</v>
       </c>
       <c r="D197" t="s">
         <v>186</v>
@@ -38933,10 +38933,10 @@
         <v>94</v>
       </c>
       <c r="C198" t="s">
-        <v>125</v>
+        <v>148</v>
       </c>
       <c r="D198" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E198" t="s">
         <v>384</v>
@@ -39118,7 +39118,7 @@
         <v>94</v>
       </c>
       <c r="C199" t="s">
-        <v>158</v>
+        <v>175</v>
       </c>
       <c r="D199" t="s">
         <v>186</v>
@@ -39303,7 +39303,7 @@
         <v>94</v>
       </c>
       <c r="C200" t="s">
-        <v>175</v>
+        <v>159</v>
       </c>
       <c r="D200" t="s">
         <v>186</v>
@@ -39673,7 +39673,7 @@
         <v>94</v>
       </c>
       <c r="C202" t="s">
-        <v>145</v>
+        <v>176</v>
       </c>
       <c r="D202" t="s">
         <v>185</v>
@@ -39712,13 +39712,13 @@
         <v>699</v>
       </c>
       <c r="P202">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="Q202">
-        <v>0</v>
+        <v>4.45</v>
       </c>
       <c r="R202">
-        <v>0</v>
+        <v>5.12</v>
       </c>
       <c r="S202">
         <v>0</v>
@@ -39858,7 +39858,7 @@
         <v>94</v>
       </c>
       <c r="C203" t="s">
-        <v>175</v>
+        <v>159</v>
       </c>
       <c r="D203" t="s">
         <v>186</v>
@@ -40043,10 +40043,10 @@
         <v>94</v>
       </c>
       <c r="C204" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="D204" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E204" t="s">
         <v>390</v>
@@ -40082,13 +40082,13 @@
         <v>699</v>
       </c>
       <c r="P204">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="Q204">
-        <v>4.45</v>
+        <v>0</v>
       </c>
       <c r="R204">
-        <v>5.12</v>
+        <v>0</v>
       </c>
       <c r="S204">
         <v>0</v>
@@ -40228,7 +40228,7 @@
         <v>95</v>
       </c>
       <c r="C205" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="D205" t="s">
         <v>186</v>
@@ -40598,7 +40598,7 @@
         <v>96</v>
       </c>
       <c r="C207" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="D207" t="s">
         <v>186</v>
@@ -40783,10 +40783,10 @@
         <v>97</v>
       </c>
       <c r="C208" t="s">
-        <v>177</v>
+        <v>169</v>
       </c>
       <c r="D208" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E208" t="s">
         <v>394</v>
@@ -40968,7 +40968,7 @@
         <v>97</v>
       </c>
       <c r="C209" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="D209" t="s">
         <v>186</v>
@@ -41338,10 +41338,10 @@
         <v>97</v>
       </c>
       <c r="C211" t="s">
-        <v>170</v>
+        <v>177</v>
       </c>
       <c r="D211" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E211" t="s">
         <v>397</v>
@@ -42078,10 +42078,10 @@
         <v>100</v>
       </c>
       <c r="C215" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="D215" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E215" t="s">
         <v>401</v>
@@ -42117,13 +42117,13 @@
         <v>699</v>
       </c>
       <c r="P215">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="Q215">
-        <v>4.73</v>
+        <v>0</v>
       </c>
       <c r="R215">
-        <v>5.79</v>
+        <v>0</v>
       </c>
       <c r="S215">
         <v>0</v>
@@ -42168,10 +42168,10 @@
         <v>0</v>
       </c>
       <c r="AG215">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AH215">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AI215">
         <v>0</v>
@@ -42263,7 +42263,7 @@
         <v>100</v>
       </c>
       <c r="C216" t="s">
-        <v>147</v>
+        <v>179</v>
       </c>
       <c r="D216" t="s">
         <v>186</v>
@@ -42302,13 +42302,13 @@
         <v>699</v>
       </c>
       <c r="P216">
-        <v>0</v>
+        <v>4.68</v>
       </c>
       <c r="Q216">
-        <v>0</v>
+        <v>4.32</v>
       </c>
       <c r="R216">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="S216">
         <v>0</v>
@@ -42347,10 +42347,10 @@
         <v>0</v>
       </c>
       <c r="AE216">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AF216">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AG216">
         <v>0</v>
@@ -42448,10 +42448,10 @@
         <v>100</v>
       </c>
       <c r="C217" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="D217" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E217" t="s">
         <v>403</v>
@@ -42487,13 +42487,13 @@
         <v>699</v>
       </c>
       <c r="P217">
-        <v>3.17</v>
+        <v>0</v>
       </c>
       <c r="Q217">
-        <v>3.68</v>
+        <v>0</v>
       </c>
       <c r="R217">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="S217">
         <v>0</v>
@@ -42532,10 +42532,10 @@
         <v>0</v>
       </c>
       <c r="AE217">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AF217">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AG217">
         <v>0</v>
@@ -42633,7 +42633,7 @@
         <v>100</v>
       </c>
       <c r="C218" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="D218" t="s">
         <v>185</v>
@@ -42818,10 +42818,10 @@
         <v>100</v>
       </c>
       <c r="C219" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="D219" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E219" t="s">
         <v>405</v>
@@ -42857,13 +42857,13 @@
         <v>699</v>
       </c>
       <c r="P219">
-        <v>2.15</v>
+        <v>1.18</v>
       </c>
       <c r="Q219">
-        <v>3.44</v>
+        <v>9.15</v>
       </c>
       <c r="R219">
-        <v>3.5</v>
+        <v>17</v>
       </c>
       <c r="S219">
         <v>0</v>
@@ -42902,16 +42902,16 @@
         <v>0</v>
       </c>
       <c r="AE219">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AF219">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AG219">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AH219">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AI219">
         <v>0</v>
@@ -43042,13 +43042,13 @@
         <v>699</v>
       </c>
       <c r="P220">
-        <v>2.38</v>
+        <v>3.8</v>
       </c>
       <c r="Q220">
-        <v>3.9</v>
+        <v>3.78</v>
       </c>
       <c r="R220">
-        <v>2.96</v>
+        <v>2.05</v>
       </c>
       <c r="S220">
         <v>0</v>
@@ -43087,10 +43087,10 @@
         <v>0</v>
       </c>
       <c r="AE220">
-        <v>1.58</v>
+        <v>1.73</v>
       </c>
       <c r="AF220">
-        <v>2.25</v>
+        <v>1.98</v>
       </c>
       <c r="AG220">
         <v>0</v>
@@ -43188,10 +43188,10 @@
         <v>100</v>
       </c>
       <c r="C221" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="D221" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E221" t="s">
         <v>407</v>
@@ -43227,13 +43227,13 @@
         <v>699</v>
       </c>
       <c r="P221">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="Q221">
-        <v>3.78</v>
+        <v>0</v>
       </c>
       <c r="R221">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="S221">
         <v>0</v>
@@ -43272,10 +43272,10 @@
         <v>0</v>
       </c>
       <c r="AE221">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AF221">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AG221">
         <v>0</v>
@@ -43373,10 +43373,10 @@
         <v>100</v>
       </c>
       <c r="C222" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="D222" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E222" t="s">
         <v>408</v>
@@ -43412,13 +43412,13 @@
         <v>699</v>
       </c>
       <c r="P222">
-        <v>5.3</v>
+        <v>3.17</v>
       </c>
       <c r="Q222">
-        <v>3.73</v>
+        <v>3.68</v>
       </c>
       <c r="R222">
-        <v>1.71</v>
+        <v>2.34</v>
       </c>
       <c r="S222">
         <v>0</v>
@@ -43457,10 +43457,10 @@
         <v>0</v>
       </c>
       <c r="AE222">
-        <v>1.95</v>
+        <v>1.72</v>
       </c>
       <c r="AF222">
-        <v>1.73</v>
+        <v>2</v>
       </c>
       <c r="AG222">
         <v>0</v>
@@ -43558,7 +43558,7 @@
         <v>100</v>
       </c>
       <c r="C223" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="D223" t="s">
         <v>185</v>
@@ -43597,13 +43597,13 @@
         <v>699</v>
       </c>
       <c r="P223">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="Q223">
-        <v>0</v>
+        <v>3.73</v>
       </c>
       <c r="R223">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="S223">
         <v>0</v>
@@ -43642,10 +43642,10 @@
         <v>0</v>
       </c>
       <c r="AE223">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AF223">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AG223">
         <v>0</v>
@@ -43743,10 +43743,10 @@
         <v>100</v>
       </c>
       <c r="C224" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="D224" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E224" t="s">
         <v>410</v>
@@ -43782,13 +43782,13 @@
         <v>699</v>
       </c>
       <c r="P224">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="Q224">
-        <v>0</v>
+        <v>4.73</v>
       </c>
       <c r="R224">
-        <v>0</v>
+        <v>5.79</v>
       </c>
       <c r="S224">
         <v>0</v>
@@ -43833,10 +43833,10 @@
         <v>0</v>
       </c>
       <c r="AG224">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AH224">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AI224">
         <v>0</v>
@@ -43967,13 +43967,13 @@
         <v>699</v>
       </c>
       <c r="P225">
-        <v>4.68</v>
+        <v>2.48</v>
       </c>
       <c r="Q225">
-        <v>4.32</v>
+        <v>3.5</v>
       </c>
       <c r="R225">
-        <v>1.76</v>
+        <v>3.07</v>
       </c>
       <c r="S225">
         <v>0</v>
@@ -44012,10 +44012,10 @@
         <v>0</v>
       </c>
       <c r="AE225">
-        <v>1.58</v>
+        <v>1.8</v>
       </c>
       <c r="AF225">
-        <v>2.25</v>
+        <v>1.9</v>
       </c>
       <c r="AG225">
         <v>0</v>
@@ -44113,10 +44113,10 @@
         <v>100</v>
       </c>
       <c r="C226" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="D226" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E226" t="s">
         <v>412</v>
@@ -44152,13 +44152,13 @@
         <v>699</v>
       </c>
       <c r="P226">
-        <v>4.05</v>
+        <v>2.15</v>
       </c>
       <c r="Q226">
-        <v>3.76</v>
+        <v>3.44</v>
       </c>
       <c r="R226">
-        <v>1.99</v>
+        <v>3.5</v>
       </c>
       <c r="S226">
         <v>0</v>
@@ -44197,10 +44197,10 @@
         <v>0</v>
       </c>
       <c r="AE226">
-        <v>1.85</v>
+        <v>1.95</v>
       </c>
       <c r="AF226">
-        <v>1.85</v>
+        <v>1.75</v>
       </c>
       <c r="AG226">
         <v>0</v>
@@ -44337,13 +44337,13 @@
         <v>699</v>
       </c>
       <c r="P227">
-        <v>1.18</v>
+        <v>4.05</v>
       </c>
       <c r="Q227">
-        <v>9.15</v>
+        <v>3.76</v>
       </c>
       <c r="R227">
-        <v>17</v>
+        <v>1.99</v>
       </c>
       <c r="S227">
         <v>0</v>
@@ -44382,16 +44382,16 @@
         <v>0</v>
       </c>
       <c r="AE227">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AF227">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG227">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AH227">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AI227">
         <v>0</v>
@@ -44483,10 +44483,10 @@
         <v>100</v>
       </c>
       <c r="C228" t="s">
-        <v>178</v>
+        <v>146</v>
       </c>
       <c r="D228" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E228" t="s">
         <v>414</v>
@@ -44707,13 +44707,13 @@
         <v>699</v>
       </c>
       <c r="P229">
-        <v>2.48</v>
+        <v>2.38</v>
       </c>
       <c r="Q229">
-        <v>3.5</v>
+        <v>3.9</v>
       </c>
       <c r="R229">
-        <v>3.07</v>
+        <v>2.96</v>
       </c>
       <c r="S229">
         <v>0</v>
@@ -44752,10 +44752,10 @@
         <v>0</v>
       </c>
       <c r="AE229">
-        <v>1.8</v>
+        <v>1.58</v>
       </c>
       <c r="AF229">
-        <v>1.9</v>
+        <v>2.25</v>
       </c>
       <c r="AG229">
         <v>0</v>
@@ -45408,10 +45408,10 @@
         <v>102</v>
       </c>
       <c r="C233" t="s">
-        <v>177</v>
+        <v>169</v>
       </c>
       <c r="D233" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E233" t="s">
         <v>419</v>
@@ -45593,7 +45593,7 @@
         <v>102</v>
       </c>
       <c r="C234" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="D234" t="s">
         <v>185</v>
@@ -45778,7 +45778,7 @@
         <v>102</v>
       </c>
       <c r="C235" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="D235" t="s">
         <v>185</v>
@@ -45963,7 +45963,7 @@
         <v>102</v>
       </c>
       <c r="C236" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="D236" t="s">
         <v>185</v>
@@ -46148,10 +46148,10 @@
         <v>102</v>
       </c>
       <c r="C237" t="s">
-        <v>170</v>
+        <v>178</v>
       </c>
       <c r="D237" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E237" t="s">
         <v>423</v>
@@ -46372,13 +46372,13 @@
         <v>699</v>
       </c>
       <c r="P238">
-        <v>1.67</v>
+        <v>2.23</v>
       </c>
       <c r="Q238">
-        <v>3.61</v>
+        <v>3.71</v>
       </c>
       <c r="R238">
-        <v>5.14</v>
+        <v>3.21</v>
       </c>
       <c r="S238">
         <v>0</v>
@@ -46417,10 +46417,10 @@
         <v>0</v>
       </c>
       <c r="AE238">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AF238">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AG238">
         <v>0</v>
@@ -46557,13 +46557,13 @@
         <v>699</v>
       </c>
       <c r="P239">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="Q239">
-        <v>0</v>
+        <v>3.61</v>
       </c>
       <c r="R239">
-        <v>0</v>
+        <v>5.14</v>
       </c>
       <c r="S239">
         <v>0</v>
@@ -46888,7 +46888,7 @@
         <v>105</v>
       </c>
       <c r="C241" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="D241" t="s">
         <v>185</v>
@@ -47073,7 +47073,7 @@
         <v>106</v>
       </c>
       <c r="C242" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="D242" t="s">
         <v>185</v>
@@ -47112,13 +47112,13 @@
         <v>699</v>
       </c>
       <c r="P242">
-        <v>2.26</v>
+        <v>1.79</v>
       </c>
       <c r="Q242">
-        <v>3.22</v>
+        <v>3.62</v>
       </c>
       <c r="R242">
-        <v>3.46</v>
+        <v>4.84</v>
       </c>
       <c r="S242">
         <v>0</v>
@@ -47157,10 +47157,10 @@
         <v>0</v>
       </c>
       <c r="AE242">
-        <v>2.25</v>
+        <v>1.87</v>
       </c>
       <c r="AF242">
-        <v>1.57</v>
+        <v>1.8</v>
       </c>
       <c r="AG242">
         <v>0</v>
@@ -47258,7 +47258,7 @@
         <v>106</v>
       </c>
       <c r="C243" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="D243" t="s">
         <v>185</v>
@@ -47297,13 +47297,13 @@
         <v>699</v>
       </c>
       <c r="P243">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="Q243">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="R243">
-        <v>0</v>
+        <v>3.67</v>
       </c>
       <c r="S243">
         <v>0</v>
@@ -47342,10 +47342,10 @@
         <v>0</v>
       </c>
       <c r="AE243">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AF243">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AG243">
         <v>0</v>
@@ -47443,7 +47443,7 @@
         <v>106</v>
       </c>
       <c r="C244" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="D244" t="s">
         <v>185</v>
@@ -47482,13 +47482,13 @@
         <v>699</v>
       </c>
       <c r="P244">
-        <v>1.79</v>
+        <v>2.26</v>
       </c>
       <c r="Q244">
-        <v>3.62</v>
+        <v>3.22</v>
       </c>
       <c r="R244">
-        <v>4.84</v>
+        <v>3.46</v>
       </c>
       <c r="S244">
         <v>0</v>
@@ -47527,10 +47527,10 @@
         <v>0</v>
       </c>
       <c r="AE244">
-        <v>1.87</v>
+        <v>2.25</v>
       </c>
       <c r="AF244">
-        <v>1.8</v>
+        <v>1.57</v>
       </c>
       <c r="AG244">
         <v>0</v>
@@ -47628,7 +47628,7 @@
         <v>106</v>
       </c>
       <c r="C245" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="D245" t="s">
         <v>185</v>
@@ -47667,13 +47667,13 @@
         <v>699</v>
       </c>
       <c r="P245">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="Q245">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="R245">
-        <v>3.67</v>
+        <v>0</v>
       </c>
       <c r="S245">
         <v>0</v>
@@ -47712,10 +47712,10 @@
         <v>0</v>
       </c>
       <c r="AE245">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AF245">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AG245">
         <v>0</v>
@@ -47998,7 +47998,7 @@
         <v>108</v>
       </c>
       <c r="C247" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="D247" t="s">
         <v>185</v>
@@ -48368,7 +48368,7 @@
         <v>109</v>
       </c>
       <c r="C249" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="D249" t="s">
         <v>185</v>
@@ -48407,13 +48407,13 @@
         <v>699</v>
       </c>
       <c r="P249">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="Q249">
-        <v>0</v>
+        <v>3.97</v>
       </c>
       <c r="R249">
-        <v>0</v>
+        <v>5.09</v>
       </c>
       <c r="S249">
         <v>0</v>
@@ -48452,10 +48452,10 @@
         <v>0</v>
       </c>
       <c r="AE249">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AF249">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG249">
         <v>0</v>
@@ -48553,7 +48553,7 @@
         <v>109</v>
       </c>
       <c r="C250" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="D250" t="s">
         <v>185</v>
@@ -48738,7 +48738,7 @@
         <v>109</v>
       </c>
       <c r="C251" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="D251" t="s">
         <v>185</v>
@@ -48923,7 +48923,7 @@
         <v>110</v>
       </c>
       <c r="C252" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="D252" t="s">
         <v>185</v>
@@ -49108,7 +49108,7 @@
         <v>111</v>
       </c>
       <c r="C253" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="D253" t="s">
         <v>185</v>
@@ -49293,7 +49293,7 @@
         <v>111</v>
       </c>
       <c r="C254" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="D254" t="s">
         <v>185</v>
@@ -49848,7 +49848,7 @@
         <v>114</v>
       </c>
       <c r="C257" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="D257" t="s">
         <v>185</v>
@@ -49887,13 +49887,13 @@
         <v>699</v>
       </c>
       <c r="P257">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="Q257">
-        <v>0</v>
+        <v>4.32</v>
       </c>
       <c r="R257">
-        <v>0</v>
+        <v>5.04</v>
       </c>
       <c r="S257">
         <v>0</v>
@@ -49938,10 +49938,10 @@
         <v>0</v>
       </c>
       <c r="AG257">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AH257">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AI257">
         <v>0</v>

--- a/jogos_2026-05-10.xlsx
+++ b/jogos_2026-05-10.xlsx
@@ -364,12 +364,12 @@
     <t>South Korea K League 2</t>
   </si>
   <si>
+    <t>South Korea K League 1</t>
+  </si>
+  <si>
     <t>Australia New South Wales NPL</t>
   </si>
   <si>
-    <t>South Korea K League 1</t>
-  </si>
-  <si>
     <t>Russia FNL</t>
   </si>
   <si>
@@ -382,10 +382,13 @@
     <t>Indonesia Liga 1</t>
   </si>
   <si>
+    <t>Russia Russian Premier League</t>
+  </si>
+  <si>
     <t>China Chinese Super League</t>
   </si>
   <si>
-    <t>Russia Russian Premier League</t>
+    <t>Portugal Liga 3</t>
   </si>
   <si>
     <t>Kazakhstan Kazakhstan Premier League</t>
@@ -397,9 +400,6 @@
     <t>Ethiopia Ethiopia Premier League</t>
   </si>
   <si>
-    <t>Portugal Liga 3</t>
-  </si>
-  <si>
     <t>Spain Primera Division Women</t>
   </si>
   <si>
@@ -415,12 +415,12 @@
     <t>Thailand Thai League T1</t>
   </si>
   <si>
+    <t>Scotland Premiership</t>
+  </si>
+  <si>
     <t>Sweden Damallsvenskan</t>
   </si>
   <si>
-    <t>Scotland Premiership</t>
-  </si>
-  <si>
     <t>Bulgaria First League</t>
   </si>
   <si>
@@ -430,36 +430,36 @@
     <t>Germany 2. Bundesliga</t>
   </si>
   <si>
+    <t>India Indian Super League</t>
+  </si>
+  <si>
+    <t>Estonia Meistriliiga</t>
+  </si>
+  <si>
+    <t>Germany 3. Liga</t>
+  </si>
+  <si>
     <t>Singapore S.League</t>
   </si>
   <si>
     <t>Belgium Pro League</t>
   </si>
   <si>
-    <t>Germany 3. Liga</t>
-  </si>
-  <si>
-    <t>Estonia Meistriliiga</t>
-  </si>
-  <si>
-    <t>India Indian Super League</t>
-  </si>
-  <si>
     <t>Croatia Druga HNL</t>
   </si>
   <si>
+    <t>Denmark Superliga</t>
+  </si>
+  <si>
     <t>Sweden Allsvenskan</t>
   </si>
   <si>
-    <t>Denmark Superliga</t>
+    <t>Spain Segunda División</t>
   </si>
   <si>
     <t>Spain La Liga</t>
   </si>
   <si>
-    <t>Spain Segunda División</t>
-  </si>
-  <si>
     <t>Georgia Erovnuli Liga</t>
   </si>
   <si>
@@ -472,63 +472,63 @@
     <t>Norway Eliteserien</t>
   </si>
   <si>
+    <t>England Premier League</t>
+  </si>
+  <si>
+    <t>Czech Republic First League</t>
+  </si>
+  <si>
+    <t>Azerbaijan Premyer Liqası</t>
+  </si>
+  <si>
+    <t>Romania Liga I</t>
+  </si>
+  <si>
     <t>Slovenia PrvaLiga</t>
   </si>
   <si>
-    <t>England Premier League</t>
-  </si>
-  <si>
-    <t>Czech Republic First League</t>
-  </si>
-  <si>
-    <t>Azerbaijan Premyer Liqası</t>
-  </si>
-  <si>
-    <t>Romania Liga I</t>
-  </si>
-  <si>
     <t>Germany Bundesliga</t>
   </si>
   <si>
+    <t>Croatia Prva HNL</t>
+  </si>
+  <si>
+    <t>Faroe Islands Faroe Islands Premier League</t>
+  </si>
+  <si>
+    <t>Hungary NB II</t>
+  </si>
+  <si>
     <t>Greece Super League</t>
   </si>
   <si>
-    <t>Hungary NB II</t>
-  </si>
-  <si>
-    <t>Faroe Islands Faroe Islands Premier League</t>
-  </si>
-  <si>
-    <t>Croatia Prva HNL</t>
-  </si>
-  <si>
     <t>Netherlands Eredivisie</t>
   </si>
   <si>
+    <t>Norway First Division</t>
+  </si>
+  <si>
+    <t>Austria Bundesliga</t>
+  </si>
+  <si>
+    <t>Cyprus First Division</t>
+  </si>
+  <si>
     <t>FYR Macedonia First Football League</t>
   </si>
   <si>
-    <t>Norway First Division</t>
-  </si>
-  <si>
-    <t>Austria Bundesliga</t>
-  </si>
-  <si>
-    <t>Cyprus First Division</t>
-  </si>
-  <si>
     <t>UAE Arabian Gulf League</t>
   </si>
   <si>
     <t>South Africa Premier Soccer League</t>
   </si>
   <si>
+    <t>Montenegro Montenegrin First League</t>
+  </si>
+  <si>
     <t>Morocco Botola Pro</t>
   </si>
   <si>
-    <t>Montenegro Montenegrin First League</t>
-  </si>
-  <si>
     <t>Saudi Arabia Professional League</t>
   </si>
   <si>
@@ -541,36 +541,36 @@
     <t>USA NWSL</t>
   </si>
   <si>
+    <t>Iceland Úrvalsdeild</t>
+  </si>
+  <si>
     <t>Israel Israeli Premier League</t>
   </si>
   <si>
-    <t>Iceland Úrvalsdeild</t>
-  </si>
-  <si>
     <t>USA MLS Next Pro</t>
   </si>
   <si>
     <t>Argentina Prim B Nacional</t>
   </si>
   <si>
+    <t>Brazil Serie A</t>
+  </si>
+  <si>
     <t>France Ligue 1</t>
   </si>
   <si>
+    <t>Bolivia LFPB</t>
+  </si>
+  <si>
     <t>Brazil Serie B</t>
   </si>
   <si>
-    <t>Bolivia LFPB</t>
-  </si>
-  <si>
-    <t>Brazil Serie A</t>
+    <t>Ecuador Primera Categoría Serie A</t>
   </si>
   <si>
     <t>USA MLS</t>
   </si>
   <si>
-    <t>Ecuador Primera Categoría Serie A</t>
-  </si>
-  <si>
     <t>2026</t>
   </si>
   <si>
@@ -583,174 +583,174 @@
     <t>Seongnam</t>
   </si>
   <si>
+    <t>Ulsan</t>
+  </si>
+  <si>
     <t>Rockdale City Suns</t>
   </si>
   <si>
     <t>Blacktown City</t>
   </si>
   <si>
-    <t>Ulsan</t>
-  </si>
-  <si>
     <t>APIA Leichhardt Tigers</t>
   </si>
   <si>
     <t>Ufa</t>
   </si>
   <si>
+    <t>Yanbian Longding</t>
+  </si>
+  <si>
+    <t>Dalian Huayi</t>
+  </si>
+  <si>
     <t>Shaanxi Union</t>
   </si>
   <si>
-    <t>Dalian Huayi</t>
-  </si>
-  <si>
-    <t>Yanbian Longding</t>
+    <t>Anyang</t>
+  </si>
+  <si>
+    <t>Busan I'Park</t>
   </si>
   <si>
     <t>Ansan Greeners</t>
   </si>
   <si>
-    <t>Busan I'Park</t>
-  </si>
-  <si>
-    <t>Anyang</t>
-  </si>
-  <si>
     <t>Viktoria Žižkov</t>
   </si>
   <si>
     <t>Slavia Praha U21</t>
   </si>
   <si>
+    <t>Persita</t>
+  </si>
+  <si>
     <t>Persija</t>
   </si>
   <si>
-    <t>Persita</t>
+    <t>Orenburg</t>
   </si>
   <si>
     <t>Qingdao Youth Island</t>
   </si>
   <si>
-    <t>Orenburg</t>
+    <t>Amarante</t>
+  </si>
+  <si>
+    <t>Sichuan Jiuniu</t>
+  </si>
+  <si>
+    <t>Gyeongnam</t>
   </si>
   <si>
     <t>Ulytau</t>
   </si>
   <si>
-    <t>Gyeongnam</t>
-  </si>
-  <si>
     <t>Hoang Anh Gia Lai</t>
   </si>
   <si>
     <t>Sheger Ketema</t>
   </si>
   <si>
-    <t>Sichuan Jiuniu</t>
-  </si>
-  <si>
-    <t>Amarante</t>
+    <t>Levante W</t>
+  </si>
+  <si>
+    <t>Polonia Warszawa</t>
   </si>
   <si>
     <t>Sokol Saratov</t>
   </si>
   <si>
-    <t>Levante W</t>
-  </si>
-  <si>
-    <t>Polonia Warszawa</t>
-  </si>
-  <si>
     <t>Piast Gliwice</t>
   </si>
   <si>
     <t>Hellas Verona</t>
   </si>
   <si>
+    <t>Bangkok Glass</t>
+  </si>
+  <si>
+    <t>Sukhothai</t>
+  </si>
+  <si>
+    <t>Celtic</t>
+  </si>
+  <si>
+    <t>Hà Nội II</t>
+  </si>
+  <si>
+    <t>Piteå Women</t>
+  </si>
+  <si>
+    <t>Ho Chi Minh City</t>
+  </si>
+  <si>
     <t>Chonburi</t>
   </si>
   <si>
+    <t>Kanchanaburi</t>
+  </si>
+  <si>
+    <t>Shenyang Urban</t>
+  </si>
+  <si>
+    <t>Rayong</t>
+  </si>
+  <si>
+    <t>Buriram United</t>
+  </si>
+  <si>
+    <t>Chiangrai United</t>
+  </si>
+  <si>
+    <t>Altay</t>
+  </si>
+  <si>
+    <t>Shenzhen Juniors</t>
+  </si>
+  <si>
     <t>Ayutthaya United</t>
   </si>
   <si>
-    <t>Shenzhen Juniors</t>
-  </si>
-  <si>
-    <t>Bangkok Glass</t>
-  </si>
-  <si>
-    <t>Buriram United</t>
-  </si>
-  <si>
-    <t>Hà Nội II</t>
-  </si>
-  <si>
-    <t>Rayong</t>
-  </si>
-  <si>
-    <t>Piteå Women</t>
-  </si>
-  <si>
-    <t>Chiangrai United</t>
-  </si>
-  <si>
-    <t>Shenyang Urban</t>
-  </si>
-  <si>
-    <t>Kanchanaburi</t>
-  </si>
-  <si>
-    <t>Celtic</t>
-  </si>
-  <si>
-    <t>Ho Chi Minh City</t>
-  </si>
-  <si>
-    <t>Altay</t>
-  </si>
-  <si>
-    <t>Sukhothai</t>
-  </si>
-  <si>
     <t>Spartak Varna</t>
   </si>
   <si>
     <t>Sūduva</t>
   </si>
   <si>
+    <t>Preußen Münster</t>
+  </si>
+  <si>
+    <t>Kerala Blasters</t>
+  </si>
+  <si>
+    <t>Nõmme Kalju</t>
+  </si>
+  <si>
+    <t>Hertha BSC</t>
+  </si>
+  <si>
+    <t>Havelse</t>
+  </si>
+  <si>
     <t>Fortuna Düsseldorf</t>
   </si>
   <si>
+    <t>Home United</t>
+  </si>
+  <si>
+    <t>Hougang United</t>
+  </si>
+  <si>
+    <t>Dongguan United</t>
+  </si>
+  <si>
     <t>Nantong Zhiyun</t>
   </si>
   <si>
-    <t>Preußen Münster</t>
-  </si>
-  <si>
-    <t>Home United</t>
-  </si>
-  <si>
-    <t>Dongguan United</t>
-  </si>
-  <si>
     <t>KAA Gent</t>
   </si>
   <si>
-    <t>Havelse</t>
-  </si>
-  <si>
-    <t>Nõmme Kalju</t>
-  </si>
-  <si>
-    <t>Hertha BSC</t>
-  </si>
-  <si>
-    <t>Kerala Blasters</t>
-  </si>
-  <si>
-    <t>Hougang United</t>
-  </si>
-  <si>
     <t>Beijing Guoan</t>
   </si>
   <si>
@@ -760,409 +760,412 @@
     <t>Hrvace</t>
   </si>
   <si>
+    <t>Aktobe</t>
+  </si>
+  <si>
+    <t>Vejle</t>
+  </si>
+  <si>
+    <t>Bahardar</t>
+  </si>
+  <si>
+    <t>Kalmar</t>
+  </si>
+  <si>
+    <t>Qingdao Jonoon</t>
+  </si>
+  <si>
     <t>AIK</t>
   </si>
   <si>
-    <t>Vejle</t>
-  </si>
-  <si>
-    <t>Kalmar</t>
+    <t>FC Andorra</t>
   </si>
   <si>
     <t>RCD Mallorca</t>
   </si>
   <si>
-    <t>Qingdao Jonoon</t>
-  </si>
-  <si>
-    <t>Aktobe</t>
-  </si>
-  <si>
-    <t>FC Andorra</t>
-  </si>
-  <si>
     <t>Meshakhte</t>
   </si>
   <si>
+    <t>Nordsjælland</t>
+  </si>
+  <si>
+    <t>Zenit</t>
+  </si>
+  <si>
     <t>Lugano</t>
   </si>
   <si>
     <t>PSIM Yogyakarta</t>
   </si>
   <si>
-    <t>Nordsjælland</t>
-  </si>
-  <si>
-    <t>Zenit</t>
-  </si>
-  <si>
-    <t>Bahardar</t>
+    <t>Kuala Lumpur</t>
   </si>
   <si>
     <t>Công An Nhân Dân</t>
   </si>
   <si>
-    <t>Kuala Lumpur</t>
+    <t>Baník Ostrava U21</t>
   </si>
   <si>
     <t>Rosenborg</t>
   </si>
   <si>
-    <t>Baník Ostrava U21</t>
-  </si>
-  <si>
     <t>Tychy 71</t>
   </si>
   <si>
     <t>Wisła Płock</t>
   </si>
   <si>
+    <t>Nottingham Forest</t>
+  </si>
+  <si>
+    <t>Crystal Palace</t>
+  </si>
+  <si>
+    <t>Astana</t>
+  </si>
+  <si>
+    <t>Kelantan United</t>
+  </si>
+  <si>
+    <t>Pardubice</t>
+  </si>
+  <si>
+    <t>Burnley</t>
+  </si>
+  <si>
+    <t>Turan</t>
+  </si>
+  <si>
+    <t>Botoşani</t>
+  </si>
+  <si>
+    <t>Arba Minch Kenema</t>
+  </si>
+  <si>
+    <t>Cremonese</t>
+  </si>
+  <si>
+    <t>Sigma Olomouc</t>
+  </si>
+  <si>
+    <t>Uppsala W</t>
+  </si>
+  <si>
+    <t>Fiorentina</t>
+  </si>
+  <si>
     <t>NK Primorje</t>
   </si>
   <si>
-    <t>Nottingham Forest</t>
-  </si>
-  <si>
-    <t>Pardubice</t>
-  </si>
-  <si>
-    <t>Astana</t>
-  </si>
-  <si>
-    <t>Uppsala W</t>
-  </si>
-  <si>
-    <t>Cremonese</t>
-  </si>
-  <si>
-    <t>Burnley</t>
-  </si>
-  <si>
-    <t>Crystal Palace</t>
-  </si>
-  <si>
-    <t>Fiorentina</t>
-  </si>
-  <si>
-    <t>Arba Minch Kenema</t>
-  </si>
-  <si>
-    <t>Kelantan United</t>
-  </si>
-  <si>
-    <t>Sigma Olomouc</t>
-  </si>
-  <si>
-    <t>Turan</t>
-  </si>
-  <si>
-    <t>Botoşani</t>
-  </si>
-  <si>
     <t>Hamburger SV</t>
   </si>
   <si>
     <t>Botev Vratsa</t>
   </si>
   <si>
+    <t>Osijek</t>
+  </si>
+  <si>
+    <t>EB - Streymur</t>
+  </si>
+  <si>
+    <t>B36</t>
+  </si>
+  <si>
+    <t>Silkeborg</t>
+  </si>
+  <si>
+    <t>Royal Antwerp FC</t>
+  </si>
+  <si>
+    <t>NorthEast United</t>
+  </si>
+  <si>
+    <t>Honvéd W</t>
+  </si>
+  <si>
+    <t>Volos NFC</t>
+  </si>
+  <si>
+    <t>Banga</t>
+  </si>
+  <si>
     <t>Nõmme United</t>
   </si>
   <si>
-    <t>Volos NFC</t>
-  </si>
-  <si>
-    <t>Royal Antwerp FC</t>
-  </si>
-  <si>
-    <t>Honvéd W</t>
-  </si>
-  <si>
-    <t>EB - Streymur</t>
-  </si>
-  <si>
     <t>Aris</t>
   </si>
   <si>
-    <t>Banga</t>
-  </si>
-  <si>
-    <t>Osijek</t>
-  </si>
-  <si>
-    <t>B36</t>
-  </si>
-  <si>
-    <t>Silkeborg</t>
-  </si>
-  <si>
-    <t>NorthEast United</t>
+    <t>Leganés</t>
   </si>
   <si>
     <t>Akhmat Grozny</t>
   </si>
   <si>
-    <t>Leganés</t>
-  </si>
-  <si>
     <t>Athletic Club Bilbao</t>
   </si>
   <si>
+    <t>Sion</t>
+  </si>
+  <si>
+    <t>Viktoria Köln</t>
+  </si>
+  <si>
+    <t>Neftekhimik</t>
+  </si>
+  <si>
     <t>Häcken</t>
   </si>
   <si>
-    <t>Sion</t>
-  </si>
-  <si>
-    <t>Viktoria Köln</t>
-  </si>
-  <si>
-    <t>Neftekhimik</t>
-  </si>
-  <si>
     <t>Young Boys</t>
   </si>
   <si>
+    <t>Go Ahead Eagles</t>
+  </si>
+  <si>
     <t>Excelsior</t>
   </si>
   <si>
+    <t>Ajax</t>
+  </si>
+  <si>
+    <t>Groningen</t>
+  </si>
+  <si>
     <t>Feyenoord</t>
   </si>
   <si>
-    <t>Groningen</t>
+    <t>Fortuna Sittard</t>
+  </si>
+  <si>
+    <t>Twente</t>
+  </si>
+  <si>
+    <t>NAC Breda</t>
   </si>
   <si>
     <t>Telstar</t>
   </si>
   <si>
-    <t>Fortuna Sittard</t>
-  </si>
-  <si>
-    <t>Ajax</t>
-  </si>
-  <si>
-    <t>Twente</t>
-  </si>
-  <si>
-    <t>Go Ahead Eagles</t>
-  </si>
-  <si>
-    <t>NAC Breda</t>
+    <t>KFUM</t>
+  </si>
+  <si>
+    <t>Sogndal</t>
+  </si>
+  <si>
+    <t>Moss</t>
+  </si>
+  <si>
+    <t>Zbrojovka Brno</t>
+  </si>
+  <si>
+    <t>Sandefjord</t>
+  </si>
+  <si>
+    <t>Real Madrid W</t>
+  </si>
+  <si>
+    <t>Budafoki MTE</t>
+  </si>
+  <si>
+    <t>Hartberg</t>
+  </si>
+  <si>
+    <t>LASK Linz</t>
+  </si>
+  <si>
+    <t>Paphos</t>
+  </si>
+  <si>
+    <t>Saburtalo</t>
+  </si>
+  <si>
+    <t>Karcag SE</t>
+  </si>
+  <si>
+    <t>Szentlőrinc SE</t>
+  </si>
+  <si>
+    <t>Strømmen</t>
+  </si>
+  <si>
+    <t>Åsane</t>
+  </si>
+  <si>
+    <t>Ajka</t>
+  </si>
+  <si>
+    <t>Akademija Pandev</t>
+  </si>
+  <si>
+    <t>Mebrat Hayl</t>
+  </si>
+  <si>
+    <t>Kecskeméti TE</t>
+  </si>
+  <si>
+    <t>Omonia Nicosia</t>
   </si>
   <si>
     <t>Shkendija</t>
   </si>
   <si>
+    <t>Vardar</t>
+  </si>
+  <si>
+    <t>Pogoń Siedlce</t>
+  </si>
+  <si>
+    <t>Rapid Wien</t>
+  </si>
+  <si>
+    <t>Raufoss</t>
+  </si>
+  <si>
+    <t>Aresimi</t>
+  </si>
+  <si>
+    <t>Pelister</t>
+  </si>
+  <si>
+    <t>Tromsø</t>
+  </si>
+  <si>
+    <t>Apollon</t>
+  </si>
+  <si>
+    <t>Croatia Zmijavci</t>
+  </si>
+  <si>
     <t>Sandnes Ulf</t>
   </si>
   <si>
-    <t>Moss</t>
-  </si>
-  <si>
-    <t>Budafoki MTE</t>
-  </si>
-  <si>
-    <t>Sogndal</t>
-  </si>
-  <si>
-    <t>Real Madrid W</t>
-  </si>
-  <si>
-    <t>Ajka</t>
-  </si>
-  <si>
-    <t>Zbrojovka Brno</t>
-  </si>
-  <si>
-    <t>Vardar</t>
-  </si>
-  <si>
-    <t>Croatia Zmijavci</t>
-  </si>
-  <si>
-    <t>Strømmen</t>
-  </si>
-  <si>
-    <t>Tromsø</t>
-  </si>
-  <si>
-    <t>Sandefjord</t>
-  </si>
-  <si>
-    <t>Mebrat Hayl</t>
-  </si>
-  <si>
-    <t>LASK Linz</t>
-  </si>
-  <si>
-    <t>Hartberg</t>
-  </si>
-  <si>
-    <t>Karcag SE</t>
-  </si>
-  <si>
-    <t>Raufoss</t>
-  </si>
-  <si>
-    <t>KFUM</t>
-  </si>
-  <si>
-    <t>Szentlőrinc SE</t>
-  </si>
-  <si>
-    <t>Pogoń Siedlce</t>
-  </si>
-  <si>
-    <t>Åsane</t>
-  </si>
-  <si>
     <t>Makedonija GjP</t>
   </si>
   <si>
-    <t>Paphos</t>
-  </si>
-  <si>
-    <t>Aresimi</t>
-  </si>
-  <si>
-    <t>Pelister</t>
-  </si>
-  <si>
-    <t>Rapid Wien</t>
-  </si>
-  <si>
-    <t>Saburtalo</t>
-  </si>
-  <si>
-    <t>Kecskeméti TE</t>
-  </si>
-  <si>
-    <t>Akademija Pandev</t>
-  </si>
-  <si>
-    <t>Omonia Nicosia</t>
-  </si>
-  <si>
-    <t>Apollon</t>
+    <t>Dibba Al Fujairah</t>
+  </si>
+  <si>
+    <t>Bani Yas</t>
+  </si>
+  <si>
+    <t>Al Bataeh</t>
   </si>
   <si>
     <t>Al Ain</t>
   </si>
   <si>
-    <t>Al Bataeh</t>
-  </si>
-  <si>
-    <t>Bani Yas</t>
-  </si>
-  <si>
-    <t>Dibba Al Fujairah</t>
+    <t>Köln</t>
+  </si>
+  <si>
+    <t>Nieciecza</t>
+  </si>
+  <si>
+    <t>West Ham United</t>
   </si>
   <si>
     <t>Sekhukhune United</t>
   </si>
   <si>
-    <t>Nieciecza</t>
-  </si>
-  <si>
-    <t>West Ham United</t>
-  </si>
-  <si>
-    <t>Köln</t>
-  </si>
-  <si>
     <t>Neftçi</t>
   </si>
   <si>
+    <t>Jedinstvo</t>
+  </si>
+  <si>
     <t>Brøndby</t>
   </si>
   <si>
+    <t>Mornar</t>
+  </si>
+  <si>
+    <t>Ittihad Tanger</t>
+  </si>
+  <si>
+    <t>Arsenal Tivat</t>
+  </si>
+  <si>
+    <t>Vysočina Jihlava</t>
+  </si>
+  <si>
+    <t>Dečić</t>
+  </si>
+  <si>
+    <t>Parma</t>
+  </si>
+  <si>
+    <t>Mladost DG</t>
+  </si>
+  <si>
     <t>Dinamo Bucureşti</t>
   </si>
   <si>
     <t>Panevėžys</t>
   </si>
   <si>
-    <t>Ittihad Tanger</t>
-  </si>
-  <si>
-    <t>Vysočina Jihlava</t>
-  </si>
-  <si>
-    <t>Jedinstvo</t>
-  </si>
-  <si>
-    <t>Mladost DG</t>
-  </si>
-  <si>
-    <t>Dečić</t>
-  </si>
-  <si>
-    <t>Parma</t>
-  </si>
-  <si>
-    <t>Mornar</t>
-  </si>
-  <si>
-    <t>Arsenal Tivat</t>
-  </si>
-  <si>
     <t>Al Riyadh</t>
   </si>
   <si>
+    <t>Skála</t>
+  </si>
+  <si>
     <t>Dobrudzha 1919</t>
   </si>
   <si>
-    <t>Skála</t>
+    <t>07 Vestur</t>
   </si>
   <si>
     <t>Slaven Koprivnica</t>
   </si>
   <si>
-    <t>07 Vestur</t>
+    <t>Union Saint-Gilloise</t>
+  </si>
+  <si>
+    <t>Radnički Niš</t>
+  </si>
+  <si>
+    <t>Real Oviedo</t>
+  </si>
+  <si>
+    <t>Jablonec</t>
   </si>
   <si>
     <t>Bačka Topola</t>
   </si>
   <si>
-    <t>Radnički Niš</t>
+    <t>Spartak Subotica</t>
+  </si>
+  <si>
+    <t>AEK Athens</t>
+  </si>
+  <si>
+    <t>Antofagasta</t>
+  </si>
+  <si>
+    <t>Olympiakos Piraeus</t>
+  </si>
+  <si>
+    <t>IMT Novi Beograd</t>
+  </si>
+  <si>
+    <t>Kansas City</t>
+  </si>
+  <si>
+    <t>Lokomotiv Moskva</t>
+  </si>
+  <si>
+    <t>Córdoba</t>
+  </si>
+  <si>
+    <t>Mirandés</t>
   </si>
   <si>
     <t>Copiapó</t>
   </si>
   <si>
-    <t>Córdoba</t>
-  </si>
-  <si>
-    <t>Mirandés</t>
-  </si>
-  <si>
-    <t>Jablonec</t>
-  </si>
-  <si>
-    <t>IMT Novi Beograd</t>
-  </si>
-  <si>
-    <t>Spartak Subotica</t>
-  </si>
-  <si>
-    <t>Lokomotiv Moskva</t>
-  </si>
-  <si>
-    <t>Real Oviedo</t>
-  </si>
-  <si>
-    <t>Antofagasta</t>
-  </si>
-  <si>
-    <t>Union Saint-Gilloise</t>
-  </si>
-  <si>
-    <t>Kansas City</t>
-  </si>
-  <si>
-    <t>Olympiakos Piraeus</t>
-  </si>
-  <si>
-    <t>AEK Athens</t>
+    <t>KA</t>
   </si>
   <si>
     <t>Tenerife W</t>
@@ -1171,24 +1174,21 @@
     <t>Dinamo Batumi</t>
   </si>
   <si>
+    <t>Ironi Tiberias</t>
+  </si>
+  <si>
+    <t>Hapoel Katamon</t>
+  </si>
+  <si>
     <t>Hapoel Haifa</t>
   </si>
   <si>
     <t>Békéscsaba</t>
   </si>
   <si>
-    <t>Ironi Tiberias</t>
-  </si>
-  <si>
-    <t>KA</t>
-  </si>
-  <si>
     <t>Csákvári TK</t>
   </si>
   <si>
-    <t>Hapoel Katamon</t>
-  </si>
-  <si>
     <t>KRC Genk</t>
   </si>
   <si>
@@ -1198,70 +1198,73 @@
     <t>Hoffenheim II</t>
   </si>
   <si>
+    <t>Al Ittihad</t>
+  </si>
+  <si>
+    <t>UTS Rabat</t>
+  </si>
+  <si>
+    <t>New England II</t>
+  </si>
+  <si>
     <t>CODM Meknès</t>
   </si>
   <si>
-    <t>UTS Rabat</t>
-  </si>
-  <si>
-    <t>Al Ittihad</t>
-  </si>
-  <si>
-    <t>New England II</t>
+    <t>Chacarita Juniors</t>
   </si>
   <si>
     <t>Varzim</t>
   </si>
   <si>
-    <t>Chacarita Juniors</t>
-  </si>
-  <si>
     <t>AC Milan</t>
   </si>
   <si>
+    <t>Club Atlético Güemes</t>
+  </si>
+  <si>
+    <t>Remo</t>
+  </si>
+  <si>
+    <t>Rennes</t>
+  </si>
+  <si>
+    <t>Auxerre</t>
+  </si>
+  <si>
+    <t>FC Barcelona</t>
+  </si>
+  <si>
+    <t>Atlético Mineiro</t>
+  </si>
+  <si>
+    <t>Toulouse</t>
+  </si>
+  <si>
+    <t>Angers SCO</t>
+  </si>
+  <si>
+    <t>Independiente Petrolero</t>
+  </si>
+  <si>
+    <t>Le Havre</t>
+  </si>
+  <si>
     <t>Agropecuario</t>
   </si>
   <si>
-    <t>Le Havre</t>
+    <t>Metz</t>
+  </si>
+  <si>
+    <t>Monaco</t>
   </si>
   <si>
     <t>Náutico</t>
   </si>
   <si>
-    <t>Independiente Petrolero</t>
-  </si>
-  <si>
     <t>PSG</t>
   </si>
   <si>
-    <t>Toulouse</t>
-  </si>
-  <si>
-    <t>Club Atlético Güemes</t>
-  </si>
-  <si>
-    <t>Metz</t>
-  </si>
-  <si>
-    <t>Remo</t>
-  </si>
-  <si>
-    <t>Rennes</t>
-  </si>
-  <si>
-    <t>Auxerre</t>
-  </si>
-  <si>
-    <t>Atlético Mineiro</t>
-  </si>
-  <si>
-    <t>Angers SCO</t>
-  </si>
-  <si>
-    <t>FC Barcelona</t>
-  </si>
-  <si>
-    <t>Monaco</t>
+    <t>San Martín San Juan</t>
   </si>
   <si>
     <t>Godoy Cruz</t>
@@ -1270,7 +1273,10 @@
     <t>Chaco For Ever</t>
   </si>
   <si>
-    <t>San Martín San Juan</t>
+    <t>Portland Timbers II</t>
+  </si>
+  <si>
+    <t>Central Norte</t>
   </si>
   <si>
     <t>Hassania Agadir</t>
@@ -1279,21 +1285,15 @@
     <t>Los Angeles II</t>
   </si>
   <si>
-    <t>Portland Timbers II</t>
-  </si>
-  <si>
     <t>Bay</t>
   </si>
   <si>
-    <t>Central Norte</t>
+    <t>CS Emelec</t>
   </si>
   <si>
     <t>New York City</t>
   </si>
   <si>
-    <t>CS Emelec</t>
-  </si>
-  <si>
     <t>Colón</t>
   </si>
   <si>
@@ -1303,24 +1303,24 @@
     <t>Mirassol</t>
   </si>
   <si>
+    <t>Avaí</t>
+  </si>
+  <si>
     <t>Santos</t>
   </si>
   <si>
     <t>Corinthians</t>
   </si>
   <si>
-    <t>Avaí</t>
-  </si>
-  <si>
     <t>FC Cincinnati II</t>
   </si>
   <si>
+    <t>Novorizontino</t>
+  </si>
+  <si>
     <t>Grêmio</t>
   </si>
   <si>
-    <t>Novorizontino</t>
-  </si>
-  <si>
     <t>Minnesota United</t>
   </si>
   <si>
@@ -1351,174 +1351,174 @@
     <t>Jeonnam Dragons</t>
   </si>
   <si>
+    <t>Bucheon 1995</t>
+  </si>
+  <si>
     <t>Sydney II</t>
   </si>
   <si>
     <t>St. George Saints</t>
   </si>
   <si>
-    <t>Bucheon 1995</t>
-  </si>
-  <si>
     <t>Sydney United</t>
   </si>
   <si>
     <t>Rotor Volgograd</t>
   </si>
   <si>
+    <t>Guangxi Hengchen</t>
+  </si>
+  <si>
+    <t>Guangzhou E-Power</t>
+  </si>
+  <si>
     <t>Shanghai Jiading</t>
   </si>
   <si>
-    <t>Guangzhou E-Power</t>
-  </si>
-  <si>
-    <t>Guangxi Hengchen</t>
+    <t>Jeonbuk Motors</t>
+  </si>
+  <si>
+    <t>Cheonan City</t>
   </si>
   <si>
     <t>Yongin City</t>
   </si>
   <si>
-    <t>Cheonan City</t>
-  </si>
-  <si>
-    <t>Jeonbuk Motors</t>
-  </si>
-  <si>
     <t>Sparta Praha II</t>
   </si>
   <si>
     <t>Táborsko</t>
   </si>
   <si>
+    <t>Persijap</t>
+  </si>
+  <si>
     <t>Persib</t>
   </si>
   <si>
-    <t>Persijap</t>
+    <t>Krylya Sovetov</t>
   </si>
   <si>
     <t>Wuhan Three Towns</t>
   </si>
   <si>
-    <t>Krylya Sovetov</t>
+    <t>União Santarém</t>
+  </si>
+  <si>
+    <t>Shandong Luneng</t>
+  </si>
+  <si>
+    <t>Gimhae City</t>
   </si>
   <si>
     <t>Kairat</t>
   </si>
   <si>
-    <t>Gimhae City</t>
-  </si>
-  <si>
     <t>Pho Hien</t>
   </si>
   <si>
     <t>Sidama Bunna</t>
   </si>
   <si>
-    <t>Shandong Luneng</t>
-  </si>
-  <si>
-    <t>União Santarém</t>
+    <t>Logroño W</t>
+  </si>
+  <si>
+    <t>Górnik Łęczna</t>
   </si>
   <si>
     <t>Spartak Kostroma</t>
   </si>
   <si>
-    <t>Logroño W</t>
-  </si>
-  <si>
-    <t>Górnik Łęczna</t>
-  </si>
-  <si>
     <t>GKS Katowice</t>
   </si>
   <si>
     <t>Como</t>
   </si>
   <si>
+    <t>Prachuap</t>
+  </si>
+  <si>
+    <t>Muang Thong United</t>
+  </si>
+  <si>
+    <t>Rangers</t>
+  </si>
+  <si>
+    <t>Viettel</t>
+  </si>
+  <si>
+    <t>Rosengard Women</t>
+  </si>
+  <si>
+    <t>Song Lam Nghe An</t>
+  </si>
+  <si>
     <t>Nakhon Ratchasima</t>
   </si>
   <si>
+    <t>Ratchaburi</t>
+  </si>
+  <si>
+    <t>Yunnan Yukun</t>
+  </si>
+  <si>
+    <t>Bangkok United</t>
+  </si>
+  <si>
+    <t>Lamphun Warrior</t>
+  </si>
+  <si>
+    <t>Uthai Thani</t>
+  </si>
+  <si>
+    <t>Ordabasy</t>
+  </si>
+  <si>
+    <t>Hebei Kungfu</t>
+  </si>
+  <si>
     <t>Port FC</t>
   </si>
   <si>
-    <t>Hebei Kungfu</t>
-  </si>
-  <si>
-    <t>Prachuap</t>
-  </si>
-  <si>
-    <t>Lamphun Warrior</t>
-  </si>
-  <si>
-    <t>Viettel</t>
-  </si>
-  <si>
-    <t>Bangkok United</t>
-  </si>
-  <si>
-    <t>Rosengard Women</t>
-  </si>
-  <si>
-    <t>Uthai Thani</t>
-  </si>
-  <si>
-    <t>Yunnan Yukun</t>
-  </si>
-  <si>
-    <t>Ratchaburi</t>
-  </si>
-  <si>
-    <t>Rangers</t>
-  </si>
-  <si>
-    <t>Song Lam Nghe An</t>
-  </si>
-  <si>
-    <t>Ordabasy</t>
-  </si>
-  <si>
-    <t>Muang Thong United</t>
-  </si>
-  <si>
     <t>Slavia Sofia</t>
   </si>
   <si>
     <t>Žalgiris</t>
   </si>
   <si>
+    <t>Darmstadt 98</t>
+  </si>
+  <si>
+    <t>Mohammedan</t>
+  </si>
+  <si>
+    <t>Tallinna FC Flora</t>
+  </si>
+  <si>
+    <t>Greuther Fürth</t>
+  </si>
+  <si>
+    <t>Schweinfurt</t>
+  </si>
+  <si>
     <t>Elversberg</t>
   </si>
   <si>
+    <t>Albirex Niigata S</t>
+  </si>
+  <si>
+    <t>Tampines Rovers</t>
+  </si>
+  <si>
+    <t>Suzhou Dongwu</t>
+  </si>
+  <si>
     <t>Wuxi Wugou</t>
   </si>
   <si>
-    <t>Darmstadt 98</t>
-  </si>
-  <si>
-    <t>Albirex Niigata S</t>
-  </si>
-  <si>
-    <t>Suzhou Dongwu</t>
-  </si>
-  <si>
     <t>RSC Anderlecht</t>
   </si>
   <si>
-    <t>Schweinfurt</t>
-  </si>
-  <si>
-    <t>Tallinna FC Flora</t>
-  </si>
-  <si>
-    <t>Greuther Fürth</t>
-  </si>
-  <si>
-    <t>Mohammedan</t>
-  </si>
-  <si>
-    <t>Tampines Rovers</t>
-  </si>
-  <si>
     <t>Shanghai SIPG</t>
   </si>
   <si>
@@ -1528,406 +1528,409 @@
     <t>Opatija</t>
   </si>
   <si>
+    <t>Kaisar</t>
+  </si>
+  <si>
+    <t>Fredericia</t>
+  </si>
+  <si>
+    <t>Welwalo Adigrat Uni</t>
+  </si>
+  <si>
+    <t>Halmstad</t>
+  </si>
+  <si>
+    <t>Dalian Zhixing</t>
+  </si>
+  <si>
     <t>Djurgården</t>
   </si>
   <si>
-    <t>Fredericia</t>
-  </si>
-  <si>
-    <t>Halmstad</t>
+    <t>UD Las Palmas</t>
   </si>
   <si>
     <t>Villarreal</t>
   </si>
   <si>
-    <t>Dalian Zhixing</t>
-  </si>
-  <si>
-    <t>Kaisar</t>
-  </si>
-  <si>
-    <t>UD Las Palmas</t>
-  </si>
-  <si>
     <t>Dila</t>
   </si>
   <si>
+    <t>Midtjylland</t>
+  </si>
+  <si>
+    <t>FK Sochi</t>
+  </si>
+  <si>
     <t>St. Gallen</t>
   </si>
   <si>
     <t>Malut United</t>
   </si>
   <si>
-    <t>Midtjylland</t>
-  </si>
-  <si>
-    <t>FK Sochi</t>
-  </si>
-  <si>
-    <t>Welwalo Adigrat Uni</t>
+    <t>Negeri Sembilan</t>
   </si>
   <si>
     <t>Nam Dinh</t>
   </si>
   <si>
-    <t>Negeri Sembilan</t>
+    <t>Ústí nad Labem</t>
   </si>
   <si>
     <t>Lillestrøm</t>
   </si>
   <si>
-    <t>Ústí nad Labem</t>
-  </si>
-  <si>
     <t>Ruch Chorzów</t>
   </si>
   <si>
     <t>Motor Lublin</t>
   </si>
   <si>
+    <t>Newcastle United</t>
+  </si>
+  <si>
+    <t>Everton</t>
+  </si>
+  <si>
+    <t>Kyzyl-Zhar</t>
+  </si>
+  <si>
+    <t>Johor Darul Ta'zim</t>
+  </si>
+  <si>
+    <t>Karviná</t>
+  </si>
+  <si>
+    <t>Aston Villa</t>
+  </si>
+  <si>
+    <t>Karvan FK</t>
+  </si>
+  <si>
+    <t>Petrolul 52</t>
+  </si>
+  <si>
+    <t>Welayta Dicha</t>
+  </si>
+  <si>
+    <t>Pisa</t>
+  </si>
+  <si>
+    <t>Bohemians 1905</t>
+  </si>
+  <si>
+    <t>Vittsjö</t>
+  </si>
+  <si>
+    <t>Genoa</t>
+  </si>
+  <si>
     <t>Mura</t>
   </si>
   <si>
-    <t>Newcastle United</t>
-  </si>
-  <si>
-    <t>Karviná</t>
-  </si>
-  <si>
-    <t>Kyzyl-Zhar</t>
-  </si>
-  <si>
-    <t>Vittsjö</t>
-  </si>
-  <si>
-    <t>Pisa</t>
-  </si>
-  <si>
-    <t>Aston Villa</t>
-  </si>
-  <si>
-    <t>Everton</t>
-  </si>
-  <si>
-    <t>Genoa</t>
-  </si>
-  <si>
-    <t>Welayta Dicha</t>
-  </si>
-  <si>
-    <t>Johor Darul Ta'zim</t>
-  </si>
-  <si>
-    <t>Bohemians 1905</t>
-  </si>
-  <si>
-    <t>Karvan FK</t>
-  </si>
-  <si>
-    <t>Petrolul 52</t>
-  </si>
-  <si>
     <t>Freiburg</t>
   </si>
   <si>
     <t>Septemvri Sofia</t>
   </si>
   <si>
+    <t>Istra 1961</t>
+  </si>
+  <si>
+    <t>Víkingur</t>
+  </si>
+  <si>
+    <t>KÍ</t>
+  </si>
+  <si>
+    <t>København</t>
+  </si>
+  <si>
+    <t>Sporting Charleroi</t>
+  </si>
+  <si>
+    <t>Chennaiyin</t>
+  </si>
+  <si>
+    <t>Vasas</t>
+  </si>
+  <si>
+    <t>Levadiakos</t>
+  </si>
+  <si>
+    <t>TransINVEST Vilnius</t>
+  </si>
+  <si>
     <t>Paide</t>
   </si>
   <si>
-    <t>Levadiakos</t>
-  </si>
-  <si>
-    <t>Sporting Charleroi</t>
-  </si>
-  <si>
-    <t>Vasas</t>
-  </si>
-  <si>
-    <t>Víkingur</t>
-  </si>
-  <si>
     <t>OFI</t>
   </si>
   <si>
-    <t>TransINVEST Vilnius</t>
-  </si>
-  <si>
-    <t>Istra 1961</t>
-  </si>
-  <si>
-    <t>KÍ</t>
-  </si>
-  <si>
-    <t>København</t>
-  </si>
-  <si>
-    <t>Chennaiyin</t>
+    <t>Racing Santander</t>
   </si>
   <si>
     <t>Makhachkala</t>
   </si>
   <si>
-    <t>Racing Santander</t>
-  </si>
-  <si>
     <t>Valencia CF</t>
   </si>
   <si>
+    <t>Thun</t>
+  </si>
+  <si>
+    <t>Alemannia Aachen</t>
+  </si>
+  <si>
+    <t>Volga Ulyanovsk</t>
+  </si>
+  <si>
     <t>Malmö FF</t>
   </si>
   <si>
-    <t>Thun</t>
-  </si>
-  <si>
-    <t>Alemannia Aachen</t>
-  </si>
-  <si>
-    <t>Volga Ulyanovsk</t>
-  </si>
-  <si>
     <t>Basel</t>
   </si>
   <si>
+    <t>PSV</t>
+  </si>
+  <si>
     <t>Volendam</t>
   </si>
   <si>
+    <t>Utrecht</t>
+  </si>
+  <si>
+    <t>NEC</t>
+  </si>
+  <si>
     <t>AZ</t>
   </si>
   <si>
-    <t>NEC</t>
+    <t>PEC Zwolle</t>
+  </si>
+  <si>
+    <t>Sparta Rotterdam</t>
+  </si>
+  <si>
+    <t>Heerenveen</t>
   </si>
   <si>
     <t>Heracles</t>
   </si>
   <si>
-    <t>PEC Zwolle</t>
-  </si>
-  <si>
-    <t>Utrecht</t>
-  </si>
-  <si>
-    <t>Sparta Rotterdam</t>
-  </si>
-  <si>
-    <t>PSV</t>
-  </si>
-  <si>
-    <t>Heerenveen</t>
+    <t>Viking</t>
+  </si>
+  <si>
+    <t>Haugesund</t>
+  </si>
+  <si>
+    <t>Bryne</t>
+  </si>
+  <si>
+    <t>Vlašim</t>
+  </si>
+  <si>
+    <t>Kristiansund</t>
+  </si>
+  <si>
+    <t>Atletico Madrid W</t>
+  </si>
+  <si>
+    <t>BVSC</t>
+  </si>
+  <si>
+    <t>Sturm Graz</t>
+  </si>
+  <si>
+    <t>Salzburg</t>
+  </si>
+  <si>
+    <t>Torpedo Kutaisi</t>
+  </si>
+  <si>
+    <t>Tiszakécske</t>
+  </si>
+  <si>
+    <t>Videoton</t>
+  </si>
+  <si>
+    <t>Hødd</t>
+  </si>
+  <si>
+    <t>Strømsgodset</t>
+  </si>
+  <si>
+    <t>Szeged 2011</t>
+  </si>
+  <si>
+    <t>Rabotnički</t>
+  </si>
+  <si>
+    <t>Fasil Ketema</t>
+  </si>
+  <si>
+    <t>Mezőkövesd-Zsóry</t>
+  </si>
+  <si>
+    <t>AEK Larnaca</t>
   </si>
   <si>
     <t>Struga</t>
   </si>
   <si>
+    <t>Sileks</t>
+  </si>
+  <si>
+    <t>Stal Rzeszów</t>
+  </si>
+  <si>
+    <t>Austria Wien</t>
+  </si>
+  <si>
+    <t>Lyn</t>
+  </si>
+  <si>
+    <t>FK Bashkimi Kumanovo</t>
+  </si>
+  <si>
+    <t>Shkupi</t>
+  </si>
+  <si>
+    <t>Molde</t>
+  </si>
+  <si>
+    <t>APOEL</t>
+  </si>
+  <si>
+    <t>Jarun</t>
+  </si>
+  <si>
     <t>Stabæk</t>
   </si>
   <si>
-    <t>Bryne</t>
-  </si>
-  <si>
-    <t>BVSC</t>
-  </si>
-  <si>
-    <t>Haugesund</t>
-  </si>
-  <si>
-    <t>Atletico Madrid W</t>
-  </si>
-  <si>
-    <t>Szeged 2011</t>
-  </si>
-  <si>
-    <t>Vlašim</t>
-  </si>
-  <si>
-    <t>Sileks</t>
-  </si>
-  <si>
-    <t>Jarun</t>
-  </si>
-  <si>
-    <t>Hødd</t>
-  </si>
-  <si>
-    <t>Molde</t>
-  </si>
-  <si>
-    <t>Kristiansund</t>
-  </si>
-  <si>
-    <t>Fasil Ketema</t>
-  </si>
-  <si>
-    <t>Salzburg</t>
-  </si>
-  <si>
-    <t>Sturm Graz</t>
-  </si>
-  <si>
-    <t>Tiszakécske</t>
-  </si>
-  <si>
-    <t>Lyn</t>
-  </si>
-  <si>
-    <t>Viking</t>
-  </si>
-  <si>
-    <t>Videoton</t>
-  </si>
-  <si>
-    <t>Stal Rzeszów</t>
-  </si>
-  <si>
-    <t>Strømsgodset</t>
-  </si>
-  <si>
     <t>Tikveš</t>
   </si>
   <si>
-    <t>FK Bashkimi Kumanovo</t>
-  </si>
-  <si>
-    <t>Shkupi</t>
-  </si>
-  <si>
-    <t>Austria Wien</t>
-  </si>
-  <si>
-    <t>Torpedo Kutaisi</t>
-  </si>
-  <si>
-    <t>Mezőkövesd-Zsóry</t>
-  </si>
-  <si>
-    <t>Rabotnički</t>
-  </si>
-  <si>
-    <t>AEK Larnaca</t>
-  </si>
-  <si>
-    <t>APOEL</t>
+    <t>Ajman</t>
+  </si>
+  <si>
+    <t>Shabab Al Ahli Dubai</t>
+  </si>
+  <si>
+    <t>Al Sharjah</t>
   </si>
   <si>
     <t>Al Dhafra</t>
   </si>
   <si>
-    <t>Al Sharjah</t>
-  </si>
-  <si>
-    <t>Shabab Al Ahli Dubai</t>
-  </si>
-  <si>
-    <t>Ajman</t>
+    <t>Heidenheim</t>
+  </si>
+  <si>
+    <t>Legia Warszawa</t>
+  </si>
+  <si>
+    <t>Arsenal</t>
   </si>
   <si>
     <t>Kaizer Chiefs</t>
   </si>
   <si>
-    <t>Legia Warszawa</t>
-  </si>
-  <si>
-    <t>Arsenal</t>
-  </si>
-  <si>
-    <t>Heidenheim</t>
-  </si>
-  <si>
     <t>İnter Bakı</t>
   </si>
   <si>
+    <t>Budućnost</t>
+  </si>
+  <si>
     <t>AGF</t>
   </si>
   <si>
+    <t>Bokelj</t>
+  </si>
+  <si>
+    <t>Difaâ El Jadida</t>
+  </si>
+  <si>
+    <t>Sutjeska</t>
+  </si>
+  <si>
+    <t>Hanácká</t>
+  </si>
+  <si>
+    <t>FK Jezero Plav</t>
+  </si>
+  <si>
+    <t>Roma</t>
+  </si>
+  <si>
+    <t>Petrovac</t>
+  </si>
+  <si>
     <t>Argeș</t>
   </si>
   <si>
     <t>Kauno Žalgiris</t>
   </si>
   <si>
-    <t>Difaâ El Jadida</t>
-  </si>
-  <si>
-    <t>Hanácká</t>
-  </si>
-  <si>
-    <t>Budućnost</t>
-  </si>
-  <si>
-    <t>Petrovac</t>
-  </si>
-  <si>
-    <t>FK Jezero Plav</t>
-  </si>
-  <si>
-    <t>Roma</t>
-  </si>
-  <si>
-    <t>Bokelj</t>
-  </si>
-  <si>
-    <t>Sutjeska</t>
-  </si>
-  <si>
     <t>Al Fateh</t>
   </si>
   <si>
+    <t>AB</t>
+  </si>
+  <si>
     <t>Beroe</t>
   </si>
   <si>
-    <t>AB</t>
+    <t>B68</t>
   </si>
   <si>
     <t>Gorica</t>
   </si>
   <si>
-    <t>B68</t>
+    <t>KV Mechelen</t>
+  </si>
+  <si>
+    <t>LFK Mladost Lučani</t>
+  </si>
+  <si>
+    <t>Getafe CF</t>
+  </si>
+  <si>
+    <t>Hradec Králové</t>
   </si>
   <si>
     <t>Javor Ivanjica</t>
   </si>
   <si>
-    <t>LFK Mladost Lučani</t>
+    <t>Napredak</t>
+  </si>
+  <si>
+    <t>Panathinaikos</t>
+  </si>
+  <si>
+    <t>San Luis</t>
+  </si>
+  <si>
+    <t>PAOK</t>
+  </si>
+  <si>
+    <t>Radnički Kragujevac</t>
+  </si>
+  <si>
+    <t>Chicago Red Stars</t>
+  </si>
+  <si>
+    <t>Baltika</t>
+  </si>
+  <si>
+    <t>Granada CF</t>
+  </si>
+  <si>
+    <t>SD Eibar</t>
   </si>
   <si>
     <t>Unión San Felipe</t>
   </si>
   <si>
-    <t>Granada CF</t>
-  </si>
-  <si>
-    <t>SD Eibar</t>
-  </si>
-  <si>
-    <t>Hradec Králové</t>
-  </si>
-  <si>
-    <t>Radnički Kragujevac</t>
-  </si>
-  <si>
-    <t>Napredak</t>
-  </si>
-  <si>
-    <t>Baltika</t>
-  </si>
-  <si>
-    <t>Getafe CF</t>
-  </si>
-  <si>
-    <t>San Luis</t>
-  </si>
-  <si>
-    <t>KV Mechelen</t>
-  </si>
-  <si>
-    <t>Chicago Red Stars</t>
-  </si>
-  <si>
-    <t>PAOK</t>
-  </si>
-  <si>
-    <t>Panathinaikos</t>
+    <t>ÍBV</t>
   </si>
   <si>
     <t>Barcelona W</t>
@@ -1936,24 +1939,21 @@
     <t>Samgurali</t>
   </si>
   <si>
+    <t>Maccabi Netanya</t>
+  </si>
+  <si>
+    <t>Bnei Sakhnin</t>
+  </si>
+  <si>
     <t>Ashdod</t>
   </si>
   <si>
     <t>Kozármisleny</t>
   </si>
   <si>
-    <t>Maccabi Netanya</t>
-  </si>
-  <si>
-    <t>ÍBV</t>
-  </si>
-  <si>
     <t>Soroksár SC</t>
   </si>
   <si>
-    <t>Bnei Sakhnin</t>
-  </si>
-  <si>
     <t>KVC Westerlo</t>
   </si>
   <si>
@@ -1963,70 +1963,73 @@
     <t>Saarbrucken</t>
   </si>
   <si>
+    <t>Dhamk</t>
+  </si>
+  <si>
+    <t>Maghreb Fès</t>
+  </si>
+  <si>
+    <t>New York City II</t>
+  </si>
+  <si>
     <t>RSB Berkane</t>
   </si>
   <si>
-    <t>Maghreb Fès</t>
-  </si>
-  <si>
-    <t>Dhamk</t>
-  </si>
-  <si>
-    <t>New York City II</t>
+    <t>Colegiales</t>
   </si>
   <si>
     <t>CF Os Belenenses</t>
   </si>
   <si>
-    <t>Colegiales</t>
-  </si>
-  <si>
     <t>Atalanta</t>
   </si>
   <si>
+    <t>Quilmes</t>
+  </si>
+  <si>
+    <t>Palmeiras</t>
+  </si>
+  <si>
+    <t>Paris</t>
+  </si>
+  <si>
+    <t>Nice</t>
+  </si>
+  <si>
+    <t>Real Madrid</t>
+  </si>
+  <si>
+    <t>Botafogo</t>
+  </si>
+  <si>
+    <t>Olympique Lyonnais</t>
+  </si>
+  <si>
+    <t>Strasbourg</t>
+  </si>
+  <si>
+    <t>Club Always Ready</t>
+  </si>
+  <si>
+    <t>Olympique Marseille</t>
+  </si>
+  <si>
     <t>Atlanta</t>
   </si>
   <si>
-    <t>Olympique Marseille</t>
+    <t>Lorient</t>
+  </si>
+  <si>
+    <t>Lille</t>
   </si>
   <si>
     <t>América Mineiro</t>
   </si>
   <si>
-    <t>Club Always Ready</t>
-  </si>
-  <si>
     <t>Brest</t>
   </si>
   <si>
-    <t>Olympique Lyonnais</t>
-  </si>
-  <si>
-    <t>Quilmes</t>
-  </si>
-  <si>
-    <t>Lorient</t>
-  </si>
-  <si>
-    <t>Palmeiras</t>
-  </si>
-  <si>
-    <t>Paris</t>
-  </si>
-  <si>
-    <t>Nice</t>
-  </si>
-  <si>
-    <t>Botafogo</t>
-  </si>
-  <si>
-    <t>Strasbourg</t>
-  </si>
-  <si>
-    <t>Real Madrid</t>
-  </si>
-  <si>
-    <t>Lille</t>
+    <t>Patronato</t>
   </si>
   <si>
     <t>Racing Córdoba</t>
@@ -2035,7 +2038,10 @@
     <t>Ciudad de Bolívar</t>
   </si>
   <si>
-    <t>Patronato</t>
+    <t>LA Galaxy II</t>
+  </si>
+  <si>
+    <t>Deportivo Madryn</t>
   </si>
   <si>
     <t>FAR Rabat</t>
@@ -2044,21 +2050,15 @@
     <t>Real Monarchs</t>
   </si>
   <si>
-    <t>LA Galaxy II</t>
-  </si>
-  <si>
     <t>Utah Royals</t>
   </si>
   <si>
-    <t>Deportivo Madryn</t>
+    <t>Libertad</t>
   </si>
   <si>
     <t>Columbus Crew</t>
   </si>
   <si>
-    <t>Libertad</t>
-  </si>
-  <si>
     <t>All Boys</t>
   </si>
   <si>
@@ -2068,22 +2068,22 @@
     <t>Chapecoense</t>
   </si>
   <si>
+    <t>Fortaleza</t>
+  </si>
+  <si>
     <t>Bragantino</t>
   </si>
   <si>
     <t>São Paulo</t>
   </si>
   <si>
-    <t>Fortaleza</t>
-  </si>
-  <si>
     <t>Columbus Crew II</t>
   </si>
   <si>
+    <t>Botafogo SP</t>
+  </si>
+  <si>
     <t>Flamengo</t>
-  </si>
-  <si>
-    <t>Botafogo SP</t>
   </si>
   <si>
     <t>Austin</t>
@@ -3043,7 +3043,7 @@
         <v>61</v>
       </c>
       <c r="C4" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="D4" t="s">
         <v>185</v>
@@ -3413,7 +3413,7 @@
         <v>62</v>
       </c>
       <c r="C6" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="D6" t="s">
         <v>185</v>
@@ -4338,7 +4338,7 @@
         <v>64</v>
       </c>
       <c r="C11" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="D11" t="s">
         <v>185</v>
@@ -4377,13 +4377,13 @@
         <v>699</v>
       </c>
       <c r="P11">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="Q11">
-        <v>3.32</v>
+        <v>0</v>
       </c>
       <c r="R11">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="S11">
         <v>0</v>
@@ -4708,7 +4708,7 @@
         <v>64</v>
       </c>
       <c r="C13" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="D13" t="s">
         <v>185</v>
@@ -4747,13 +4747,13 @@
         <v>699</v>
       </c>
       <c r="P13">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="Q13">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="R13">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="S13">
         <v>0</v>
@@ -5636,7 +5636,7 @@
         <v>122</v>
       </c>
       <c r="D18" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E18" t="s">
         <v>204</v>
@@ -5672,13 +5672,13 @@
         <v>699</v>
       </c>
       <c r="P18">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="Q18">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="R18">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="S18">
         <v>0</v>
@@ -5821,7 +5821,7 @@
         <v>123</v>
       </c>
       <c r="D19" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E19" t="s">
         <v>205</v>
@@ -5857,13 +5857,13 @@
         <v>699</v>
       </c>
       <c r="P19">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="Q19">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="R19">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="S19">
         <v>0</v>
@@ -6006,7 +6006,7 @@
         <v>124</v>
       </c>
       <c r="D20" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E20" t="s">
         <v>206</v>
@@ -6188,7 +6188,7 @@
         <v>68</v>
       </c>
       <c r="C21" t="s">
-        <v>115</v>
+        <v>123</v>
       </c>
       <c r="D21" t="s">
         <v>185</v>
@@ -6227,13 +6227,13 @@
         <v>699</v>
       </c>
       <c r="P21">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Q21">
-        <v>3.16</v>
+        <v>0</v>
       </c>
       <c r="R21">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="S21">
         <v>0</v>
@@ -6373,10 +6373,10 @@
         <v>68</v>
       </c>
       <c r="C22" t="s">
-        <v>125</v>
+        <v>115</v>
       </c>
       <c r="D22" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E22" t="s">
         <v>208</v>
@@ -6412,13 +6412,13 @@
         <v>699</v>
       </c>
       <c r="P22">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Q22">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="R22">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="S22">
         <v>0</v>
@@ -6558,10 +6558,10 @@
         <v>68</v>
       </c>
       <c r="C23" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="D23" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E23" t="s">
         <v>209</v>
@@ -6743,10 +6743,10 @@
         <v>68</v>
       </c>
       <c r="C24" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="D24" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E24" t="s">
         <v>210</v>
@@ -7113,7 +7113,7 @@
         <v>68</v>
       </c>
       <c r="C26" t="s">
-        <v>118</v>
+        <v>128</v>
       </c>
       <c r="D26" t="s">
         <v>186</v>
@@ -7152,13 +7152,13 @@
         <v>699</v>
       </c>
       <c r="P26">
-        <v>4.98</v>
+        <v>0</v>
       </c>
       <c r="Q26">
-        <v>3.66</v>
+        <v>0</v>
       </c>
       <c r="R26">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="S26">
         <v>0</v>
@@ -7298,7 +7298,7 @@
         <v>68</v>
       </c>
       <c r="C27" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="D27" t="s">
         <v>186</v>
@@ -7483,7 +7483,7 @@
         <v>68</v>
       </c>
       <c r="C28" t="s">
-        <v>129</v>
+        <v>118</v>
       </c>
       <c r="D28" t="s">
         <v>186</v>
@@ -7522,13 +7522,13 @@
         <v>699</v>
       </c>
       <c r="P28">
-        <v>0</v>
+        <v>4.98</v>
       </c>
       <c r="Q28">
-        <v>0</v>
+        <v>3.66</v>
       </c>
       <c r="R28">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="S28">
         <v>0</v>
@@ -8077,13 +8077,13 @@
         <v>699</v>
       </c>
       <c r="P31">
-        <v>1.61</v>
+        <v>1.78</v>
       </c>
       <c r="Q31">
-        <v>4.18</v>
+        <v>3.9</v>
       </c>
       <c r="R31">
-        <v>5.3</v>
+        <v>4.35</v>
       </c>
       <c r="S31">
         <v>0</v>
@@ -8262,13 +8262,13 @@
         <v>699</v>
       </c>
       <c r="P32">
-        <v>5.09</v>
+        <v>2.44</v>
       </c>
       <c r="Q32">
-        <v>4.18</v>
+        <v>3.61</v>
       </c>
       <c r="R32">
-        <v>1.64</v>
+        <v>2.77</v>
       </c>
       <c r="S32">
         <v>0</v>
@@ -8408,10 +8408,10 @@
         <v>71</v>
       </c>
       <c r="C33" t="s">
-        <v>119</v>
+        <v>133</v>
       </c>
       <c r="D33" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E33" t="s">
         <v>219</v>
@@ -8447,13 +8447,13 @@
         <v>699</v>
       </c>
       <c r="P33">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Q33">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="R33">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="S33">
         <v>0</v>
@@ -8593,7 +8593,7 @@
         <v>71</v>
       </c>
       <c r="C34" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="D34" t="s">
         <v>186</v>
@@ -8632,13 +8632,13 @@
         <v>699</v>
       </c>
       <c r="P34">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="Q34">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="R34">
-        <v>4.35</v>
+        <v>0</v>
       </c>
       <c r="S34">
         <v>0</v>
@@ -8778,10 +8778,10 @@
         <v>71</v>
       </c>
       <c r="C35" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="D35" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E35" t="s">
         <v>221</v>
@@ -8817,13 +8817,13 @@
         <v>699</v>
       </c>
       <c r="P35">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="Q35">
-        <v>6.73</v>
+        <v>0</v>
       </c>
       <c r="R35">
-        <v>10.6</v>
+        <v>0</v>
       </c>
       <c r="S35">
         <v>0</v>
@@ -8963,7 +8963,7 @@
         <v>71</v>
       </c>
       <c r="C36" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="D36" t="s">
         <v>186</v>
@@ -9187,13 +9187,13 @@
         <v>699</v>
       </c>
       <c r="P37">
-        <v>3.4</v>
+        <v>1.61</v>
       </c>
       <c r="Q37">
-        <v>3.63</v>
+        <v>4.18</v>
       </c>
       <c r="R37">
-        <v>2.09</v>
+        <v>5.3</v>
       </c>
       <c r="S37">
         <v>0</v>
@@ -9333,10 +9333,10 @@
         <v>71</v>
       </c>
       <c r="C38" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="D38" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E38" t="s">
         <v>224</v>
@@ -9372,13 +9372,13 @@
         <v>699</v>
       </c>
       <c r="P38">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="Q38">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="R38">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="S38">
         <v>0</v>
@@ -9518,10 +9518,10 @@
         <v>71</v>
       </c>
       <c r="C39" t="s">
-        <v>132</v>
+        <v>123</v>
       </c>
       <c r="D39" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E39" t="s">
         <v>225</v>
@@ -9557,13 +9557,13 @@
         <v>699</v>
       </c>
       <c r="P39">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="Q39">
-        <v>3.36</v>
+        <v>0</v>
       </c>
       <c r="R39">
-        <v>2.64</v>
+        <v>0</v>
       </c>
       <c r="S39">
         <v>0</v>
@@ -9602,10 +9602,10 @@
         <v>0</v>
       </c>
       <c r="AE39">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AF39">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AG39">
         <v>0</v>
@@ -9703,10 +9703,10 @@
         <v>71</v>
       </c>
       <c r="C40" t="s">
-        <v>122</v>
+        <v>132</v>
       </c>
       <c r="D40" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E40" t="s">
         <v>226</v>
@@ -9742,13 +9742,13 @@
         <v>699</v>
       </c>
       <c r="P40">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="Q40">
-        <v>0</v>
+        <v>3.63</v>
       </c>
       <c r="R40">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="S40">
         <v>0</v>
@@ -9927,13 +9927,13 @@
         <v>699</v>
       </c>
       <c r="P41">
-        <v>3.32</v>
+        <v>1.24</v>
       </c>
       <c r="Q41">
-        <v>3.95</v>
+        <v>6.73</v>
       </c>
       <c r="R41">
-        <v>2.03</v>
+        <v>10.6</v>
       </c>
       <c r="S41">
         <v>0</v>
@@ -10073,7 +10073,7 @@
         <v>71</v>
       </c>
       <c r="C42" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="D42" t="s">
         <v>186</v>
@@ -10112,13 +10112,13 @@
         <v>699</v>
       </c>
       <c r="P42">
-        <v>2.2</v>
+        <v>2.7</v>
       </c>
       <c r="Q42">
-        <v>3.7</v>
+        <v>3.36</v>
       </c>
       <c r="R42">
-        <v>3</v>
+        <v>2.64</v>
       </c>
       <c r="S42">
         <v>0</v>
@@ -10157,10 +10157,10 @@
         <v>0</v>
       </c>
       <c r="AE42">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AF42">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AG42">
         <v>0</v>
@@ -10261,7 +10261,7 @@
         <v>125</v>
       </c>
       <c r="D43" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E43" t="s">
         <v>229</v>
@@ -10443,7 +10443,7 @@
         <v>71</v>
       </c>
       <c r="C44" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
       <c r="D44" t="s">
         <v>185</v>
@@ -10667,13 +10667,13 @@
         <v>699</v>
       </c>
       <c r="P45">
-        <v>2.44</v>
+        <v>5.09</v>
       </c>
       <c r="Q45">
-        <v>3.61</v>
+        <v>4.18</v>
       </c>
       <c r="R45">
-        <v>2.77</v>
+        <v>1.64</v>
       </c>
       <c r="S45">
         <v>0</v>
@@ -11222,13 +11222,13 @@
         <v>699</v>
       </c>
       <c r="P48">
-        <v>2.88</v>
+        <v>2.29</v>
       </c>
       <c r="Q48">
-        <v>3.8</v>
+        <v>3.74</v>
       </c>
       <c r="R48">
-        <v>2.19</v>
+        <v>2.76</v>
       </c>
       <c r="S48">
         <v>0</v>
@@ -11368,10 +11368,10 @@
         <v>73</v>
       </c>
       <c r="C49" t="s">
-        <v>119</v>
+        <v>138</v>
       </c>
       <c r="D49" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E49" t="s">
         <v>235</v>
@@ -11407,13 +11407,13 @@
         <v>699</v>
       </c>
       <c r="P49">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="Q49">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="R49">
-        <v>0</v>
+        <v>7.37</v>
       </c>
       <c r="S49">
         <v>0</v>
@@ -11553,10 +11553,10 @@
         <v>73</v>
       </c>
       <c r="C50" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="D50" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E50" t="s">
         <v>236</v>
@@ -11592,13 +11592,13 @@
         <v>699</v>
       </c>
       <c r="P50">
-        <v>2.29</v>
+        <v>2.27</v>
       </c>
       <c r="Q50">
-        <v>3.74</v>
+        <v>3.7</v>
       </c>
       <c r="R50">
-        <v>2.76</v>
+        <v>2.6</v>
       </c>
       <c r="S50">
         <v>0</v>
@@ -11738,10 +11738,10 @@
         <v>73</v>
       </c>
       <c r="C51" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D51" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="E51" t="s">
         <v>237</v>
@@ -11777,13 +11777,13 @@
         <v>699</v>
       </c>
       <c r="P51">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="Q51">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="R51">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="S51">
         <v>0</v>
@@ -11828,10 +11828,10 @@
         <v>0</v>
       </c>
       <c r="AG51">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AH51">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AI51">
         <v>0</v>
@@ -11923,10 +11923,10 @@
         <v>73</v>
       </c>
       <c r="C52" t="s">
-        <v>119</v>
+        <v>140</v>
       </c>
       <c r="D52" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E52" t="s">
         <v>238</v>
@@ -12108,7 +12108,7 @@
         <v>73</v>
       </c>
       <c r="C53" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="D53" t="s">
         <v>186</v>
@@ -12147,13 +12147,13 @@
         <v>699</v>
       </c>
       <c r="P53">
-        <v>2.32</v>
+        <v>2.88</v>
       </c>
       <c r="Q53">
-        <v>3.71</v>
+        <v>3.8</v>
       </c>
       <c r="R53">
-        <v>2.89</v>
+        <v>2.19</v>
       </c>
       <c r="S53">
         <v>0</v>
@@ -12293,10 +12293,10 @@
         <v>73</v>
       </c>
       <c r="C54" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="D54" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="E54" t="s">
         <v>240</v>
@@ -12481,7 +12481,7 @@
         <v>141</v>
       </c>
       <c r="D55" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="E55" t="s">
         <v>241</v>
@@ -12663,10 +12663,10 @@
         <v>73</v>
       </c>
       <c r="C56" t="s">
-        <v>137</v>
+        <v>119</v>
       </c>
       <c r="D56" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E56" t="s">
         <v>242</v>
@@ -12702,13 +12702,13 @@
         <v>699</v>
       </c>
       <c r="P56">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="Q56">
-        <v>4.15</v>
+        <v>0</v>
       </c>
       <c r="R56">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="S56">
         <v>0</v>
@@ -12753,10 +12753,10 @@
         <v>0</v>
       </c>
       <c r="AG56">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AH56">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AI56">
         <v>0</v>
@@ -12848,10 +12848,10 @@
         <v>73</v>
       </c>
       <c r="C57" t="s">
-        <v>142</v>
+        <v>119</v>
       </c>
       <c r="D57" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E57" t="s">
         <v>243</v>
@@ -12887,13 +12887,13 @@
         <v>699</v>
       </c>
       <c r="P57">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="Q57">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="R57">
-        <v>7.37</v>
+        <v>0</v>
       </c>
       <c r="S57">
         <v>0</v>
@@ -13033,10 +13033,10 @@
         <v>73</v>
       </c>
       <c r="C58" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="D58" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="E58" t="s">
         <v>244</v>
@@ -13072,13 +13072,13 @@
         <v>699</v>
       </c>
       <c r="P58">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="Q58">
-        <v>0</v>
+        <v>3.71</v>
       </c>
       <c r="R58">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="S58">
         <v>0</v>
@@ -13218,7 +13218,7 @@
         <v>74</v>
       </c>
       <c r="C59" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="D59" t="s">
         <v>185</v>
@@ -13403,7 +13403,7 @@
         <v>74</v>
       </c>
       <c r="C60" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="D60" t="s">
         <v>185</v>
@@ -13773,7 +13773,7 @@
         <v>76</v>
       </c>
       <c r="C62" t="s">
-        <v>144</v>
+        <v>125</v>
       </c>
       <c r="D62" t="s">
         <v>185</v>
@@ -13812,13 +13812,13 @@
         <v>699</v>
       </c>
       <c r="P62">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="Q62">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="R62">
-        <v>2.87</v>
+        <v>0</v>
       </c>
       <c r="S62">
         <v>0</v>
@@ -13958,7 +13958,7 @@
         <v>76</v>
       </c>
       <c r="C63" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="D63" t="s">
         <v>186</v>
@@ -14143,10 +14143,10 @@
         <v>76</v>
       </c>
       <c r="C64" t="s">
-        <v>144</v>
+        <v>127</v>
       </c>
       <c r="D64" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E64" t="s">
         <v>250</v>
@@ -14182,13 +14182,13 @@
         <v>699</v>
       </c>
       <c r="P64">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="Q64">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="R64">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="S64">
         <v>0</v>
@@ -14328,10 +14328,10 @@
         <v>76</v>
       </c>
       <c r="C65" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D65" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E65" t="s">
         <v>251</v>
@@ -14367,13 +14367,13 @@
         <v>699</v>
       </c>
       <c r="P65">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="Q65">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R65">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="S65">
         <v>0</v>
@@ -14513,7 +14513,7 @@
         <v>76</v>
       </c>
       <c r="C66" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="D66" t="s">
         <v>185</v>
@@ -14698,7 +14698,7 @@
         <v>76</v>
       </c>
       <c r="C67" t="s">
-        <v>124</v>
+        <v>145</v>
       </c>
       <c r="D67" t="s">
         <v>185</v>
@@ -14737,13 +14737,13 @@
         <v>699</v>
       </c>
       <c r="P67">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="Q67">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="R67">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="S67">
         <v>0</v>
@@ -14883,7 +14883,7 @@
         <v>76</v>
       </c>
       <c r="C68" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="D68" t="s">
         <v>186</v>
@@ -15068,10 +15068,10 @@
         <v>76</v>
       </c>
       <c r="C69" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D69" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E69" t="s">
         <v>255</v>
@@ -15253,10 +15253,10 @@
         <v>76</v>
       </c>
       <c r="C70" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="D70" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E70" t="s">
         <v>256</v>
@@ -15292,13 +15292,13 @@
         <v>699</v>
       </c>
       <c r="P70">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="Q70">
-        <v>3.54</v>
+        <v>0</v>
       </c>
       <c r="R70">
-        <v>2.73</v>
+        <v>0</v>
       </c>
       <c r="S70">
         <v>0</v>
@@ -15438,7 +15438,7 @@
         <v>76</v>
       </c>
       <c r="C71" t="s">
-        <v>121</v>
+        <v>144</v>
       </c>
       <c r="D71" t="s">
         <v>186</v>
@@ -15477,13 +15477,13 @@
         <v>699</v>
       </c>
       <c r="P71">
-        <v>0</v>
+        <v>3.36</v>
       </c>
       <c r="Q71">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="R71">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="S71">
         <v>0</v>
@@ -15623,7 +15623,7 @@
         <v>76</v>
       </c>
       <c r="C72" t="s">
-        <v>145</v>
+        <v>122</v>
       </c>
       <c r="D72" t="s">
         <v>186</v>
@@ -15662,13 +15662,13 @@
         <v>699</v>
       </c>
       <c r="P72">
-        <v>3.36</v>
+        <v>1.21</v>
       </c>
       <c r="Q72">
-        <v>3.65</v>
+        <v>7.41</v>
       </c>
       <c r="R72">
-        <v>1.99</v>
+        <v>17.5</v>
       </c>
       <c r="S72">
         <v>0</v>
@@ -15808,7 +15808,7 @@
         <v>76</v>
       </c>
       <c r="C73" t="s">
-        <v>123</v>
+        <v>149</v>
       </c>
       <c r="D73" t="s">
         <v>186</v>
@@ -15847,13 +15847,13 @@
         <v>699</v>
       </c>
       <c r="P73">
-        <v>1.21</v>
+        <v>2.36</v>
       </c>
       <c r="Q73">
-        <v>7.41</v>
+        <v>3.54</v>
       </c>
       <c r="R73">
-        <v>17.5</v>
+        <v>2.73</v>
       </c>
       <c r="S73">
         <v>0</v>
@@ -15993,7 +15993,7 @@
         <v>76</v>
       </c>
       <c r="C74" t="s">
-        <v>126</v>
+        <v>121</v>
       </c>
       <c r="D74" t="s">
         <v>186</v>
@@ -16178,7 +16178,7 @@
         <v>77</v>
       </c>
       <c r="C75" t="s">
-        <v>125</v>
+        <v>150</v>
       </c>
       <c r="D75" t="s">
         <v>186</v>
@@ -16363,7 +16363,7 @@
         <v>77</v>
       </c>
       <c r="C76" t="s">
-        <v>150</v>
+        <v>126</v>
       </c>
       <c r="D76" t="s">
         <v>186</v>
@@ -16548,10 +16548,10 @@
         <v>78</v>
       </c>
       <c r="C77" t="s">
-        <v>151</v>
+        <v>120</v>
       </c>
       <c r="D77" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E77" t="s">
         <v>263</v>
@@ -16587,13 +16587,13 @@
         <v>699</v>
       </c>
       <c r="P77">
-        <v>2.79</v>
+        <v>0</v>
       </c>
       <c r="Q77">
-        <v>3.67</v>
+        <v>0</v>
       </c>
       <c r="R77">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="S77">
         <v>0</v>
@@ -16733,10 +16733,10 @@
         <v>78</v>
       </c>
       <c r="C78" t="s">
-        <v>120</v>
+        <v>151</v>
       </c>
       <c r="D78" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E78" t="s">
         <v>264</v>
@@ -16772,13 +16772,13 @@
         <v>699</v>
       </c>
       <c r="P78">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="Q78">
-        <v>0</v>
+        <v>3.67</v>
       </c>
       <c r="R78">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="S78">
         <v>0</v>
@@ -17327,13 +17327,13 @@
         <v>699</v>
       </c>
       <c r="P81">
-        <v>2.59</v>
+        <v>2.46</v>
       </c>
       <c r="Q81">
-        <v>3.45</v>
+        <v>3.66</v>
       </c>
       <c r="R81">
-        <v>2.3</v>
+        <v>2.99</v>
       </c>
       <c r="S81">
         <v>0</v>
@@ -17372,10 +17372,10 @@
         <v>0</v>
       </c>
       <c r="AE81">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AF81">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AG81">
         <v>0</v>
@@ -17473,7 +17473,7 @@
         <v>80</v>
       </c>
       <c r="C82" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D82" t="s">
         <v>186</v>
@@ -17512,13 +17512,13 @@
         <v>699</v>
       </c>
       <c r="P82">
-        <v>2.46</v>
+        <v>2.69</v>
       </c>
       <c r="Q82">
-        <v>3.66</v>
+        <v>3.31</v>
       </c>
       <c r="R82">
-        <v>2.99</v>
+        <v>2.92</v>
       </c>
       <c r="S82">
         <v>0</v>
@@ -17557,10 +17557,10 @@
         <v>0</v>
       </c>
       <c r="AE82">
-        <v>1.68</v>
+        <v>1.87</v>
       </c>
       <c r="AF82">
-        <v>2.05</v>
+        <v>1.89</v>
       </c>
       <c r="AG82">
         <v>0</v>
@@ -17658,10 +17658,10 @@
         <v>80</v>
       </c>
       <c r="C83" t="s">
-        <v>154</v>
+        <v>125</v>
       </c>
       <c r="D83" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E83" t="s">
         <v>269</v>
@@ -17843,10 +17843,10 @@
         <v>80</v>
       </c>
       <c r="C84" t="s">
-        <v>124</v>
+        <v>150</v>
       </c>
       <c r="D84" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E84" t="s">
         <v>270</v>
@@ -18028,10 +18028,10 @@
         <v>80</v>
       </c>
       <c r="C85" t="s">
-        <v>133</v>
+        <v>153</v>
       </c>
       <c r="D85" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E85" t="s">
         <v>271</v>
@@ -18213,7 +18213,7 @@
         <v>80</v>
       </c>
       <c r="C86" t="s">
-        <v>131</v>
+        <v>152</v>
       </c>
       <c r="D86" t="s">
         <v>186</v>
@@ -18252,13 +18252,13 @@
         <v>699</v>
       </c>
       <c r="P86">
-        <v>2.1</v>
+        <v>5.38</v>
       </c>
       <c r="Q86">
-        <v>3.42</v>
+        <v>4.37</v>
       </c>
       <c r="R86">
-        <v>4.07</v>
+        <v>1.67</v>
       </c>
       <c r="S86">
         <v>0</v>
@@ -18297,10 +18297,10 @@
         <v>0</v>
       </c>
       <c r="AE86">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AF86">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AG86">
         <v>0</v>
@@ -18398,7 +18398,7 @@
         <v>80</v>
       </c>
       <c r="C87" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="D87" t="s">
         <v>186</v>
@@ -18437,13 +18437,13 @@
         <v>699</v>
       </c>
       <c r="P87">
-        <v>5.38</v>
+        <v>0</v>
       </c>
       <c r="Q87">
-        <v>4.37</v>
+        <v>0</v>
       </c>
       <c r="R87">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="S87">
         <v>0</v>
@@ -18583,7 +18583,7 @@
         <v>80</v>
       </c>
       <c r="C88" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="D88" t="s">
         <v>186</v>
@@ -18622,13 +18622,13 @@
         <v>699</v>
       </c>
       <c r="P88">
-        <v>2.69</v>
+        <v>2.21</v>
       </c>
       <c r="Q88">
-        <v>3.31</v>
+        <v>3.22</v>
       </c>
       <c r="R88">
-        <v>2.92</v>
+        <v>3.22</v>
       </c>
       <c r="S88">
         <v>0</v>
@@ -18667,10 +18667,10 @@
         <v>0</v>
       </c>
       <c r="AE88">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AF88">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AG88">
         <v>0</v>
@@ -18768,7 +18768,7 @@
         <v>80</v>
       </c>
       <c r="C89" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="D89" t="s">
         <v>186</v>
@@ -18807,13 +18807,13 @@
         <v>699</v>
       </c>
       <c r="P89">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="Q89">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="R89">
-        <v>4.01</v>
+        <v>0</v>
       </c>
       <c r="S89">
         <v>0</v>
@@ -18852,10 +18852,10 @@
         <v>0</v>
       </c>
       <c r="AE89">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AF89">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AG89">
         <v>0</v>
@@ -18953,7 +18953,7 @@
         <v>80</v>
       </c>
       <c r="C90" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="D90" t="s">
         <v>186</v>
@@ -18992,13 +18992,13 @@
         <v>699</v>
       </c>
       <c r="P90">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Q90">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="R90">
-        <v>0</v>
+        <v>4.07</v>
       </c>
       <c r="S90">
         <v>0</v>
@@ -19037,10 +19037,10 @@
         <v>0</v>
       </c>
       <c r="AE90">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AF90">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AG90">
         <v>0</v>
@@ -19138,7 +19138,7 @@
         <v>80</v>
       </c>
       <c r="C91" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="D91" t="s">
         <v>186</v>
@@ -19323,10 +19323,10 @@
         <v>80</v>
       </c>
       <c r="C92" t="s">
-        <v>154</v>
+        <v>134</v>
       </c>
       <c r="D92" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E92" t="s">
         <v>278</v>
@@ -19508,7 +19508,7 @@
         <v>80</v>
       </c>
       <c r="C93" t="s">
-        <v>155</v>
+        <v>131</v>
       </c>
       <c r="D93" t="s">
         <v>186</v>
@@ -19547,13 +19547,13 @@
         <v>699</v>
       </c>
       <c r="P93">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="Q93">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="R93">
-        <v>0</v>
+        <v>4.01</v>
       </c>
       <c r="S93">
         <v>0</v>
@@ -19592,10 +19592,10 @@
         <v>0</v>
       </c>
       <c r="AE93">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AF93">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AG93">
         <v>0</v>
@@ -19732,13 +19732,13 @@
         <v>699</v>
       </c>
       <c r="P94">
-        <v>2.21</v>
+        <v>2.59</v>
       </c>
       <c r="Q94">
-        <v>3.22</v>
+        <v>3.45</v>
       </c>
       <c r="R94">
-        <v>3.22</v>
+        <v>2.3</v>
       </c>
       <c r="S94">
         <v>0</v>
@@ -20248,10 +20248,10 @@
         <v>83</v>
       </c>
       <c r="C97" t="s">
-        <v>141</v>
+        <v>158</v>
       </c>
       <c r="D97" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E97" t="s">
         <v>283</v>
@@ -20433,10 +20433,10 @@
         <v>83</v>
       </c>
       <c r="C98" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="D98" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E98" t="s">
         <v>284</v>
@@ -20472,13 +20472,13 @@
         <v>699</v>
       </c>
       <c r="P98">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="Q98">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="R98">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="S98">
         <v>0</v>
@@ -20618,10 +20618,10 @@
         <v>83</v>
       </c>
       <c r="C99" t="s">
-        <v>139</v>
+        <v>159</v>
       </c>
       <c r="D99" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E99" t="s">
         <v>285</v>
@@ -20657,13 +20657,13 @@
         <v>699</v>
       </c>
       <c r="P99">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="Q99">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="R99">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="S99">
         <v>0</v>
@@ -20702,10 +20702,10 @@
         <v>0</v>
       </c>
       <c r="AE99">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AF99">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AG99">
         <v>0</v>
@@ -20803,7 +20803,7 @@
         <v>83</v>
       </c>
       <c r="C100" t="s">
-        <v>159</v>
+        <v>144</v>
       </c>
       <c r="D100" t="s">
         <v>186</v>
@@ -20842,13 +20842,13 @@
         <v>699</v>
       </c>
       <c r="P100">
-        <v>0</v>
+        <v>4.68</v>
       </c>
       <c r="Q100">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R100">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="S100">
         <v>0</v>
@@ -20988,10 +20988,10 @@
         <v>83</v>
       </c>
       <c r="C101" t="s">
-        <v>160</v>
+        <v>142</v>
       </c>
       <c r="D101" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E101" t="s">
         <v>287</v>
@@ -21027,13 +21027,13 @@
         <v>699</v>
       </c>
       <c r="P101">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="Q101">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="R101">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="S101">
         <v>0</v>
@@ -21072,10 +21072,10 @@
         <v>0</v>
       </c>
       <c r="AE101">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AF101">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG101">
         <v>0</v>
@@ -21173,7 +21173,7 @@
         <v>83</v>
       </c>
       <c r="C102" t="s">
-        <v>158</v>
+        <v>138</v>
       </c>
       <c r="D102" t="s">
         <v>186</v>
@@ -21358,10 +21358,10 @@
         <v>83</v>
       </c>
       <c r="C103" t="s">
-        <v>136</v>
+        <v>160</v>
       </c>
       <c r="D103" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E103" t="s">
         <v>289</v>
@@ -21582,13 +21582,13 @@
         <v>699</v>
       </c>
       <c r="P104">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="Q104">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R104">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="S104">
         <v>0</v>
@@ -21728,7 +21728,7 @@
         <v>83</v>
       </c>
       <c r="C105" t="s">
-        <v>160</v>
+        <v>136</v>
       </c>
       <c r="D105" t="s">
         <v>185</v>
@@ -21913,10 +21913,10 @@
         <v>83</v>
       </c>
       <c r="C106" t="s">
-        <v>145</v>
+        <v>139</v>
       </c>
       <c r="D106" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E106" t="s">
         <v>292</v>
@@ -21952,13 +21952,13 @@
         <v>699</v>
       </c>
       <c r="P106">
-        <v>4.68</v>
+        <v>0</v>
       </c>
       <c r="Q106">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R106">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="S106">
         <v>0</v>
@@ -22098,7 +22098,7 @@
         <v>83</v>
       </c>
       <c r="C107" t="s">
-        <v>142</v>
+        <v>161</v>
       </c>
       <c r="D107" t="s">
         <v>186</v>
@@ -22283,7 +22283,7 @@
         <v>84</v>
       </c>
       <c r="C108" t="s">
-        <v>123</v>
+        <v>146</v>
       </c>
       <c r="D108" t="s">
         <v>186</v>
@@ -22322,13 +22322,13 @@
         <v>699</v>
       </c>
       <c r="P108">
-        <v>2.16</v>
+        <v>3.06</v>
       </c>
       <c r="Q108">
-        <v>3.42</v>
+        <v>3.61</v>
       </c>
       <c r="R108">
-        <v>3.85</v>
+        <v>2.29</v>
       </c>
       <c r="S108">
         <v>0</v>
@@ -22468,7 +22468,7 @@
         <v>84</v>
       </c>
       <c r="C109" t="s">
-        <v>147</v>
+        <v>122</v>
       </c>
       <c r="D109" t="s">
         <v>186</v>
@@ -22507,13 +22507,13 @@
         <v>699</v>
       </c>
       <c r="P109">
-        <v>3.06</v>
+        <v>2.16</v>
       </c>
       <c r="Q109">
-        <v>3.61</v>
+        <v>3.42</v>
       </c>
       <c r="R109">
-        <v>2.29</v>
+        <v>3.85</v>
       </c>
       <c r="S109">
         <v>0</v>
@@ -22653,7 +22653,7 @@
         <v>84</v>
       </c>
       <c r="C110" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="D110" t="s">
         <v>186</v>
@@ -22838,10 +22838,10 @@
         <v>85</v>
       </c>
       <c r="C111" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="D111" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E111" t="s">
         <v>297</v>
@@ -22877,13 +22877,13 @@
         <v>699</v>
       </c>
       <c r="P111">
-        <v>2.27</v>
+        <v>2.05</v>
       </c>
       <c r="Q111">
-        <v>3.58</v>
+        <v>3.64</v>
       </c>
       <c r="R111">
-        <v>2.88</v>
+        <v>3.28</v>
       </c>
       <c r="S111">
         <v>0</v>
@@ -23023,7 +23023,7 @@
         <v>85</v>
       </c>
       <c r="C112" t="s">
-        <v>149</v>
+        <v>140</v>
       </c>
       <c r="D112" t="s">
         <v>186</v>
@@ -23062,13 +23062,13 @@
         <v>699</v>
       </c>
       <c r="P112">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Q112">
-        <v>3.64</v>
+        <v>0</v>
       </c>
       <c r="R112">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="S112">
         <v>0</v>
@@ -23208,7 +23208,7 @@
         <v>85</v>
       </c>
       <c r="C113" t="s">
-        <v>140</v>
+        <v>118</v>
       </c>
       <c r="D113" t="s">
         <v>186</v>
@@ -23393,10 +23393,10 @@
         <v>85</v>
       </c>
       <c r="C114" t="s">
-        <v>118</v>
+        <v>145</v>
       </c>
       <c r="D114" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E114" t="s">
         <v>300</v>
@@ -23432,13 +23432,13 @@
         <v>699</v>
       </c>
       <c r="P114">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="Q114">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="R114">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="S114">
         <v>0</v>
@@ -23802,13 +23802,13 @@
         <v>699</v>
       </c>
       <c r="P116">
-        <v>1.77</v>
+        <v>4.48</v>
       </c>
       <c r="Q116">
-        <v>4.17</v>
+        <v>4.74</v>
       </c>
       <c r="R116">
-        <v>4.22</v>
+        <v>1.65</v>
       </c>
       <c r="S116">
         <v>0</v>
@@ -23847,16 +23847,16 @@
         <v>0</v>
       </c>
       <c r="AE116">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AF116">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AG116">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AH116">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AI116">
         <v>0</v>
@@ -23987,13 +23987,13 @@
         <v>699</v>
       </c>
       <c r="P117">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="Q117">
         <v>4.17</v>
       </c>
       <c r="R117">
-        <v>4.17</v>
+        <v>4.22</v>
       </c>
       <c r="S117">
         <v>0</v>
@@ -24032,16 +24032,16 @@
         <v>0</v>
       </c>
       <c r="AE117">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AF117">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AG117">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AH117">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AI117">
         <v>0</v>
@@ -24172,13 +24172,13 @@
         <v>699</v>
       </c>
       <c r="P118">
-        <v>2.78</v>
+        <v>1.71</v>
       </c>
       <c r="Q118">
-        <v>3.89</v>
+        <v>4.37</v>
       </c>
       <c r="R118">
-        <v>2.36</v>
+        <v>4.42</v>
       </c>
       <c r="S118">
         <v>0</v>
@@ -24223,10 +24223,10 @@
         <v>0</v>
       </c>
       <c r="AG118">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="AH118">
-        <v>1.68</v>
+        <v>1.65</v>
       </c>
       <c r="AI118">
         <v>0</v>
@@ -24357,13 +24357,13 @@
         <v>699</v>
       </c>
       <c r="P119">
-        <v>1.48</v>
+        <v>2.78</v>
       </c>
       <c r="Q119">
-        <v>4.94</v>
+        <v>3.89</v>
       </c>
       <c r="R119">
-        <v>6.07</v>
+        <v>2.36</v>
       </c>
       <c r="S119">
         <v>0</v>
@@ -24408,10 +24408,10 @@
         <v>0</v>
       </c>
       <c r="AG119">
-        <v>1.98</v>
+        <v>2.05</v>
       </c>
       <c r="AH119">
-        <v>1.72</v>
+        <v>1.68</v>
       </c>
       <c r="AI119">
         <v>0</v>
@@ -24542,13 +24542,13 @@
         <v>699</v>
       </c>
       <c r="P120">
-        <v>1.96</v>
+        <v>1.78</v>
       </c>
       <c r="Q120">
-        <v>4.05</v>
+        <v>4.17</v>
       </c>
       <c r="R120">
-        <v>3.5</v>
+        <v>4.17</v>
       </c>
       <c r="S120">
         <v>0</v>
@@ -24593,10 +24593,10 @@
         <v>0</v>
       </c>
       <c r="AG120">
-        <v>2.2</v>
+        <v>1.9</v>
       </c>
       <c r="AH120">
-        <v>1.58</v>
+        <v>1.77</v>
       </c>
       <c r="AI120">
         <v>0</v>
@@ -24727,13 +24727,13 @@
         <v>699</v>
       </c>
       <c r="P121">
-        <v>1.71</v>
+        <v>1.96</v>
       </c>
       <c r="Q121">
-        <v>4.37</v>
+        <v>4.05</v>
       </c>
       <c r="R121">
-        <v>4.42</v>
+        <v>3.5</v>
       </c>
       <c r="S121">
         <v>0</v>
@@ -24778,10 +24778,10 @@
         <v>0</v>
       </c>
       <c r="AG121">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="AH121">
-        <v>1.65</v>
+        <v>1.58</v>
       </c>
       <c r="AI121">
         <v>0</v>
@@ -25097,13 +25097,13 @@
         <v>699</v>
       </c>
       <c r="P123">
-        <v>4.48</v>
+        <v>2.49</v>
       </c>
       <c r="Q123">
-        <v>4.74</v>
+        <v>3.77</v>
       </c>
       <c r="R123">
-        <v>1.65</v>
+        <v>2.67</v>
       </c>
       <c r="S123">
         <v>0</v>
@@ -25142,16 +25142,16 @@
         <v>0</v>
       </c>
       <c r="AE123">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AF123">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AG123">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AH123">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AI123">
         <v>0</v>
@@ -25282,13 +25282,13 @@
         <v>699</v>
       </c>
       <c r="P124">
-        <v>2.49</v>
+        <v>1.48</v>
       </c>
       <c r="Q124">
-        <v>3.77</v>
+        <v>4.94</v>
       </c>
       <c r="R124">
-        <v>2.67</v>
+        <v>6.07</v>
       </c>
       <c r="S124">
         <v>0</v>
@@ -25327,16 +25327,16 @@
         <v>0</v>
       </c>
       <c r="AE124">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AF124">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AG124">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AH124">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AI124">
         <v>0</v>
@@ -25428,10 +25428,10 @@
         <v>87</v>
       </c>
       <c r="C125" t="s">
-        <v>163</v>
+        <v>151</v>
       </c>
       <c r="D125" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E125" t="s">
         <v>311</v>
@@ -25467,13 +25467,13 @@
         <v>699</v>
       </c>
       <c r="P125">
-        <v>0</v>
+        <v>3.87</v>
       </c>
       <c r="Q125">
-        <v>0</v>
+        <v>3.87</v>
       </c>
       <c r="R125">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="S125">
         <v>0</v>
@@ -25613,7 +25613,7 @@
         <v>87</v>
       </c>
       <c r="C126" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="D126" t="s">
         <v>185</v>
@@ -25652,13 +25652,13 @@
         <v>699</v>
       </c>
       <c r="P126">
-        <v>4.07</v>
+        <v>3.1</v>
       </c>
       <c r="Q126">
-        <v>3.9</v>
+        <v>3.7</v>
       </c>
       <c r="R126">
-        <v>1.78</v>
+        <v>2.12</v>
       </c>
       <c r="S126">
         <v>0</v>
@@ -25798,7 +25798,7 @@
         <v>87</v>
       </c>
       <c r="C127" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="D127" t="s">
         <v>185</v>
@@ -25983,7 +25983,7 @@
         <v>87</v>
       </c>
       <c r="C128" t="s">
-        <v>159</v>
+        <v>120</v>
       </c>
       <c r="D128" t="s">
         <v>186</v>
@@ -26168,7 +26168,7 @@
         <v>87</v>
       </c>
       <c r="C129" t="s">
-        <v>164</v>
+        <v>151</v>
       </c>
       <c r="D129" t="s">
         <v>185</v>
@@ -26207,13 +26207,13 @@
         <v>699</v>
       </c>
       <c r="P129">
-        <v>3.1</v>
+        <v>1.59</v>
       </c>
       <c r="Q129">
-        <v>3.7</v>
+        <v>4.44</v>
       </c>
       <c r="R129">
-        <v>2.12</v>
+        <v>5.16</v>
       </c>
       <c r="S129">
         <v>0</v>
@@ -26538,7 +26538,7 @@
         <v>87</v>
       </c>
       <c r="C131" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="D131" t="s">
         <v>186</v>
@@ -26723,7 +26723,7 @@
         <v>87</v>
       </c>
       <c r="C132" t="s">
-        <v>120</v>
+        <v>164</v>
       </c>
       <c r="D132" t="s">
         <v>186</v>
@@ -26762,13 +26762,13 @@
         <v>699</v>
       </c>
       <c r="P132">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="Q132">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R132">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="S132">
         <v>0</v>
@@ -26807,10 +26807,10 @@
         <v>0</v>
       </c>
       <c r="AE132">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AF132">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG132">
         <v>0</v>
@@ -26908,7 +26908,7 @@
         <v>87</v>
       </c>
       <c r="C133" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="D133" t="s">
         <v>186</v>
@@ -26947,13 +26947,13 @@
         <v>699</v>
       </c>
       <c r="P133">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="Q133">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="R133">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="S133">
         <v>0</v>
@@ -27093,7 +27093,7 @@
         <v>87</v>
       </c>
       <c r="C134" t="s">
-        <v>143</v>
+        <v>165</v>
       </c>
       <c r="D134" t="s">
         <v>186</v>
@@ -27102,7 +27102,7 @@
         <v>320</v>
       </c>
       <c r="F134" t="s">
-        <v>576</v>
+        <v>293</v>
       </c>
       <c r="G134">
         <v>0</v>
@@ -27278,7 +27278,7 @@
         <v>87</v>
       </c>
       <c r="C135" t="s">
-        <v>164</v>
+        <v>148</v>
       </c>
       <c r="D135" t="s">
         <v>185</v>
@@ -27287,7 +27287,7 @@
         <v>321</v>
       </c>
       <c r="F135" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="G135">
         <v>0</v>
@@ -27317,13 +27317,13 @@
         <v>699</v>
       </c>
       <c r="P135">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Q135">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="R135">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="S135">
         <v>0</v>
@@ -27463,16 +27463,16 @@
         <v>87</v>
       </c>
       <c r="C136" t="s">
-        <v>151</v>
+        <v>160</v>
       </c>
       <c r="D136" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E136" t="s">
         <v>322</v>
       </c>
       <c r="F136" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="G136">
         <v>0</v>
@@ -27502,13 +27502,13 @@
         <v>699</v>
       </c>
       <c r="P136">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="Q136">
-        <v>3.82</v>
+        <v>0</v>
       </c>
       <c r="R136">
-        <v>4.13</v>
+        <v>0</v>
       </c>
       <c r="S136">
         <v>0</v>
@@ -27648,16 +27648,16 @@
         <v>87</v>
       </c>
       <c r="C137" t="s">
-        <v>151</v>
+        <v>160</v>
       </c>
       <c r="D137" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E137" t="s">
         <v>323</v>
       </c>
       <c r="F137" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="G137">
         <v>0</v>
@@ -27687,13 +27687,13 @@
         <v>699</v>
       </c>
       <c r="P137">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="Q137">
-        <v>4.44</v>
+        <v>0</v>
       </c>
       <c r="R137">
-        <v>5.16</v>
+        <v>0</v>
       </c>
       <c r="S137">
         <v>0</v>
@@ -27833,16 +27833,16 @@
         <v>87</v>
       </c>
       <c r="C138" t="s">
-        <v>126</v>
+        <v>163</v>
       </c>
       <c r="D138" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E138" t="s">
         <v>324</v>
       </c>
       <c r="F138" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="G138">
         <v>0</v>
@@ -27872,13 +27872,13 @@
         <v>699</v>
       </c>
       <c r="P138">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Q138">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R138">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="S138">
         <v>0</v>
@@ -28018,16 +28018,16 @@
         <v>87</v>
       </c>
       <c r="C139" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="D139" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E139" t="s">
         <v>325</v>
       </c>
       <c r="F139" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="G139">
         <v>0</v>
@@ -28057,13 +28057,13 @@
         <v>699</v>
       </c>
       <c r="P139">
-        <v>2.51</v>
+        <v>5.4</v>
       </c>
       <c r="Q139">
-        <v>3.78</v>
+        <v>4.6</v>
       </c>
       <c r="R139">
-        <v>2.44</v>
+        <v>1.51</v>
       </c>
       <c r="S139">
         <v>0</v>
@@ -28203,7 +28203,7 @@
         <v>87</v>
       </c>
       <c r="C140" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="D140" t="s">
         <v>186</v>
@@ -28212,7 +28212,7 @@
         <v>326</v>
       </c>
       <c r="F140" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="G140">
         <v>0</v>
@@ -28242,13 +28242,13 @@
         <v>699</v>
       </c>
       <c r="P140">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="Q140">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R140">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="S140">
         <v>0</v>
@@ -28287,10 +28287,10 @@
         <v>0</v>
       </c>
       <c r="AE140">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AF140">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AG140">
         <v>0</v>
@@ -28388,7 +28388,7 @@
         <v>87</v>
       </c>
       <c r="C141" t="s">
-        <v>159</v>
+        <v>166</v>
       </c>
       <c r="D141" t="s">
         <v>186</v>
@@ -28397,7 +28397,7 @@
         <v>327</v>
       </c>
       <c r="F141" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="G141">
         <v>0</v>
@@ -28573,16 +28573,16 @@
         <v>87</v>
       </c>
       <c r="C142" t="s">
-        <v>164</v>
+        <v>127</v>
       </c>
       <c r="D142" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E142" t="s">
         <v>328</v>
       </c>
       <c r="F142" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="G142">
         <v>0</v>
@@ -28612,13 +28612,13 @@
         <v>699</v>
       </c>
       <c r="P142">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="Q142">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R142">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="S142">
         <v>0</v>
@@ -28758,16 +28758,16 @@
         <v>87</v>
       </c>
       <c r="C143" t="s">
-        <v>151</v>
+        <v>160</v>
       </c>
       <c r="D143" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E143" t="s">
         <v>329</v>
       </c>
       <c r="F143" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="G143">
         <v>0</v>
@@ -28797,13 +28797,13 @@
         <v>699</v>
       </c>
       <c r="P143">
-        <v>3.87</v>
+        <v>0</v>
       </c>
       <c r="Q143">
-        <v>3.87</v>
+        <v>0</v>
       </c>
       <c r="R143">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="S143">
         <v>0</v>
@@ -28943,7 +28943,7 @@
         <v>87</v>
       </c>
       <c r="C144" t="s">
-        <v>159</v>
+        <v>165</v>
       </c>
       <c r="D144" t="s">
         <v>186</v>
@@ -28952,7 +28952,7 @@
         <v>330</v>
       </c>
       <c r="F144" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="G144">
         <v>0</v>
@@ -29128,7 +29128,7 @@
         <v>87</v>
       </c>
       <c r="C145" t="s">
-        <v>129</v>
+        <v>166</v>
       </c>
       <c r="D145" t="s">
         <v>186</v>
@@ -29137,7 +29137,7 @@
         <v>331</v>
       </c>
       <c r="F145" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="G145">
         <v>0</v>
@@ -29167,13 +29167,13 @@
         <v>699</v>
       </c>
       <c r="P145">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="Q145">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R145">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="S145">
         <v>0</v>
@@ -29313,16 +29313,16 @@
         <v>87</v>
       </c>
       <c r="C146" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="D146" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E146" t="s">
         <v>332</v>
       </c>
       <c r="F146" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="G146">
         <v>0</v>
@@ -29352,13 +29352,13 @@
         <v>699</v>
       </c>
       <c r="P146">
-        <v>5.4</v>
+        <v>0</v>
       </c>
       <c r="Q146">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="R146">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="S146">
         <v>0</v>
@@ -29498,7 +29498,7 @@
         <v>87</v>
       </c>
       <c r="C147" t="s">
-        <v>163</v>
+        <v>129</v>
       </c>
       <c r="D147" t="s">
         <v>186</v>
@@ -29507,7 +29507,7 @@
         <v>333</v>
       </c>
       <c r="F147" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="G147">
         <v>0</v>
@@ -29537,13 +29537,13 @@
         <v>699</v>
       </c>
       <c r="P147">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="Q147">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R147">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="S147">
         <v>0</v>
@@ -29683,7 +29683,7 @@
         <v>87</v>
       </c>
       <c r="C148" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="D148" t="s">
         <v>186</v>
@@ -29692,7 +29692,7 @@
         <v>334</v>
       </c>
       <c r="F148" t="s">
-        <v>288</v>
+        <v>589</v>
       </c>
       <c r="G148">
         <v>0</v>
@@ -29722,13 +29722,13 @@
         <v>699</v>
       </c>
       <c r="P148">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Q148">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="R148">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="S148">
         <v>0</v>
@@ -29871,7 +29871,7 @@
         <v>163</v>
       </c>
       <c r="D149" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E149" t="s">
         <v>335</v>
@@ -29907,13 +29907,13 @@
         <v>699</v>
       </c>
       <c r="P149">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="Q149">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R149">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="S149">
         <v>0</v>
@@ -30053,7 +30053,7 @@
         <v>87</v>
       </c>
       <c r="C150" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="D150" t="s">
         <v>186</v>
@@ -30238,7 +30238,7 @@
         <v>87</v>
       </c>
       <c r="C151" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="D151" t="s">
         <v>186</v>
@@ -30277,13 +30277,13 @@
         <v>699</v>
       </c>
       <c r="P151">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Q151">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="R151">
-        <v>2.96</v>
+        <v>0</v>
       </c>
       <c r="S151">
         <v>0</v>
@@ -30423,7 +30423,7 @@
         <v>87</v>
       </c>
       <c r="C152" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="D152" t="s">
         <v>185</v>
@@ -30462,13 +30462,13 @@
         <v>699</v>
       </c>
       <c r="P152">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="Q152">
-        <v>0</v>
+        <v>3.82</v>
       </c>
       <c r="R152">
-        <v>0</v>
+        <v>4.13</v>
       </c>
       <c r="S152">
         <v>0</v>
@@ -30608,7 +30608,7 @@
         <v>87</v>
       </c>
       <c r="C153" t="s">
-        <v>159</v>
+        <v>165</v>
       </c>
       <c r="D153" t="s">
         <v>186</v>
@@ -30793,7 +30793,7 @@
         <v>87</v>
       </c>
       <c r="C154" t="s">
-        <v>163</v>
+        <v>143</v>
       </c>
       <c r="D154" t="s">
         <v>186</v>
@@ -30978,10 +30978,10 @@
         <v>87</v>
       </c>
       <c r="C155" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="D155" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E155" t="s">
         <v>341</v>
@@ -31017,13 +31017,13 @@
         <v>699</v>
       </c>
       <c r="P155">
-        <v>0</v>
+        <v>4.07</v>
       </c>
       <c r="Q155">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="R155">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="S155">
         <v>0</v>
@@ -32088,7 +32088,7 @@
         <v>89</v>
       </c>
       <c r="C161" t="s">
-        <v>168</v>
+        <v>157</v>
       </c>
       <c r="D161" t="s">
         <v>186</v>
@@ -32127,13 +32127,13 @@
         <v>699</v>
       </c>
       <c r="P161">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="Q161">
-        <v>0</v>
+        <v>4.32</v>
       </c>
       <c r="R161">
-        <v>0</v>
+        <v>4.52</v>
       </c>
       <c r="S161">
         <v>0</v>
@@ -32178,10 +32178,10 @@
         <v>0</v>
       </c>
       <c r="AG161">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AH161">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AI161">
         <v>0</v>
@@ -32458,7 +32458,7 @@
         <v>89</v>
       </c>
       <c r="C163" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D163" t="s">
         <v>186</v>
@@ -32643,7 +32643,7 @@
         <v>89</v>
       </c>
       <c r="C164" t="s">
-        <v>157</v>
+        <v>168</v>
       </c>
       <c r="D164" t="s">
         <v>186</v>
@@ -32682,13 +32682,13 @@
         <v>699</v>
       </c>
       <c r="P164">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="Q164">
-        <v>4.32</v>
+        <v>0</v>
       </c>
       <c r="R164">
-        <v>4.52</v>
+        <v>0</v>
       </c>
       <c r="S164">
         <v>0</v>
@@ -32733,10 +32733,10 @@
         <v>0</v>
       </c>
       <c r="AG164">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AH164">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AI164">
         <v>0</v>
@@ -32828,7 +32828,7 @@
         <v>89</v>
       </c>
       <c r="C165" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="D165" t="s">
         <v>186</v>
@@ -33013,7 +33013,7 @@
         <v>90</v>
       </c>
       <c r="C166" t="s">
-        <v>145</v>
+        <v>169</v>
       </c>
       <c r="D166" t="s">
         <v>186</v>
@@ -33198,7 +33198,7 @@
         <v>90</v>
       </c>
       <c r="C167" t="s">
-        <v>156</v>
+        <v>144</v>
       </c>
       <c r="D167" t="s">
         <v>186</v>
@@ -33237,13 +33237,13 @@
         <v>699</v>
       </c>
       <c r="P167">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="Q167">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="R167">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="S167">
         <v>0</v>
@@ -33383,10 +33383,10 @@
         <v>90</v>
       </c>
       <c r="C168" t="s">
-        <v>136</v>
+        <v>169</v>
       </c>
       <c r="D168" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E168" t="s">
         <v>354</v>
@@ -33568,7 +33568,7 @@
         <v>90</v>
       </c>
       <c r="C169" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="D169" t="s">
         <v>186</v>
@@ -33753,7 +33753,7 @@
         <v>90</v>
       </c>
       <c r="C170" t="s">
-        <v>120</v>
+        <v>169</v>
       </c>
       <c r="D170" t="s">
         <v>186</v>
@@ -33938,7 +33938,7 @@
         <v>90</v>
       </c>
       <c r="C171" t="s">
-        <v>170</v>
+        <v>120</v>
       </c>
       <c r="D171" t="s">
         <v>186</v>
@@ -34123,7 +34123,7 @@
         <v>90</v>
       </c>
       <c r="C172" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="D172" t="s">
         <v>186</v>
@@ -34308,7 +34308,7 @@
         <v>90</v>
       </c>
       <c r="C173" t="s">
-        <v>170</v>
+        <v>131</v>
       </c>
       <c r="D173" t="s">
         <v>186</v>
@@ -34347,13 +34347,13 @@
         <v>699</v>
       </c>
       <c r="P173">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="Q173">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R173">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="S173">
         <v>0</v>
@@ -34493,7 +34493,7 @@
         <v>90</v>
       </c>
       <c r="C174" t="s">
-        <v>131</v>
+        <v>169</v>
       </c>
       <c r="D174" t="s">
         <v>186</v>
@@ -34532,13 +34532,13 @@
         <v>699</v>
       </c>
       <c r="P174">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="Q174">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="R174">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="S174">
         <v>0</v>
@@ -34678,7 +34678,7 @@
         <v>90</v>
       </c>
       <c r="C175" t="s">
-        <v>170</v>
+        <v>155</v>
       </c>
       <c r="D175" t="s">
         <v>186</v>
@@ -34717,13 +34717,13 @@
         <v>699</v>
       </c>
       <c r="P175">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="Q175">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R175">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="S175">
         <v>0</v>
@@ -34863,10 +34863,10 @@
         <v>90</v>
       </c>
       <c r="C176" t="s">
-        <v>170</v>
+        <v>136</v>
       </c>
       <c r="D176" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E176" t="s">
         <v>362</v>
@@ -35233,10 +35233,10 @@
         <v>92</v>
       </c>
       <c r="C178" t="s">
-        <v>135</v>
+        <v>159</v>
       </c>
       <c r="D178" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E178" t="s">
         <v>364</v>
@@ -35272,13 +35272,13 @@
         <v>699</v>
       </c>
       <c r="P178">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="Q178">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="R178">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="S178">
         <v>0</v>
@@ -35418,10 +35418,10 @@
         <v>92</v>
       </c>
       <c r="C179" t="s">
-        <v>160</v>
+        <v>135</v>
       </c>
       <c r="D179" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E179" t="s">
         <v>365</v>
@@ -35457,13 +35457,13 @@
         <v>699</v>
       </c>
       <c r="P179">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="Q179">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R179">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="S179">
         <v>0</v>
@@ -35603,10 +35603,10 @@
         <v>92</v>
       </c>
       <c r="C180" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="D180" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E180" t="s">
         <v>366</v>
@@ -35788,10 +35788,10 @@
         <v>92</v>
       </c>
       <c r="C181" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="D181" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E181" t="s">
         <v>367</v>
@@ -35973,7 +35973,7 @@
         <v>93</v>
       </c>
       <c r="C182" t="s">
-        <v>172</v>
+        <v>142</v>
       </c>
       <c r="D182" t="s">
         <v>186</v>
@@ -36012,13 +36012,13 @@
         <v>699</v>
       </c>
       <c r="P182">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Q182">
-        <v>0</v>
+        <v>5.66</v>
       </c>
       <c r="R182">
-        <v>0</v>
+        <v>8.98</v>
       </c>
       <c r="S182">
         <v>0</v>
@@ -36343,10 +36343,10 @@
         <v>93</v>
       </c>
       <c r="C184" t="s">
-        <v>173</v>
+        <v>147</v>
       </c>
       <c r="D184" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E184" t="s">
         <v>370</v>
@@ -36528,7 +36528,7 @@
         <v>93</v>
       </c>
       <c r="C185" t="s">
-        <v>147</v>
+        <v>153</v>
       </c>
       <c r="D185" t="s">
         <v>186</v>
@@ -36567,13 +36567,13 @@
         <v>699</v>
       </c>
       <c r="P185">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="Q185">
-        <v>3.53</v>
+        <v>0</v>
       </c>
       <c r="R185">
-        <v>3.91</v>
+        <v>0</v>
       </c>
       <c r="S185">
         <v>0</v>
@@ -36612,10 +36612,10 @@
         <v>0</v>
       </c>
       <c r="AE185">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AF185">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AG185">
         <v>0</v>
@@ -36713,7 +36713,7 @@
         <v>93</v>
       </c>
       <c r="C186" t="s">
-        <v>147</v>
+        <v>172</v>
       </c>
       <c r="D186" t="s">
         <v>186</v>
@@ -36752,13 +36752,13 @@
         <v>699</v>
       </c>
       <c r="P186">
-        <v>3.12</v>
+        <v>0</v>
       </c>
       <c r="Q186">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="R186">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="S186">
         <v>0</v>
@@ -36898,7 +36898,7 @@
         <v>93</v>
       </c>
       <c r="C187" t="s">
-        <v>154</v>
+        <v>172</v>
       </c>
       <c r="D187" t="s">
         <v>186</v>
@@ -37083,7 +37083,7 @@
         <v>93</v>
       </c>
       <c r="C188" t="s">
-        <v>172</v>
+        <v>161</v>
       </c>
       <c r="D188" t="s">
         <v>186</v>
@@ -37122,13 +37122,13 @@
         <v>699</v>
       </c>
       <c r="P188">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="Q188">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="R188">
-        <v>0</v>
+        <v>6.76</v>
       </c>
       <c r="S188">
         <v>0</v>
@@ -37268,10 +37268,10 @@
         <v>93</v>
       </c>
       <c r="C189" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="D189" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E189" t="s">
         <v>375</v>
@@ -37453,7 +37453,7 @@
         <v>93</v>
       </c>
       <c r="C190" t="s">
-        <v>123</v>
+        <v>161</v>
       </c>
       <c r="D190" t="s">
         <v>186</v>
@@ -37492,13 +37492,13 @@
         <v>699</v>
       </c>
       <c r="P190">
-        <v>2.25</v>
+        <v>1.82</v>
       </c>
       <c r="Q190">
-        <v>3.66</v>
+        <v>3.1</v>
       </c>
       <c r="R190">
-        <v>3.36</v>
+        <v>4.56</v>
       </c>
       <c r="S190">
         <v>0</v>
@@ -37638,7 +37638,7 @@
         <v>93</v>
       </c>
       <c r="C191" t="s">
-        <v>146</v>
+        <v>172</v>
       </c>
       <c r="D191" t="s">
         <v>186</v>
@@ -37823,7 +37823,7 @@
         <v>93</v>
       </c>
       <c r="C192" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="D192" t="s">
         <v>185</v>
@@ -37862,13 +37862,13 @@
         <v>699</v>
       </c>
       <c r="P192">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Q192">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="R192">
-        <v>0</v>
+        <v>7.95</v>
       </c>
       <c r="S192">
         <v>0</v>
@@ -38008,7 +38008,7 @@
         <v>93</v>
       </c>
       <c r="C193" t="s">
-        <v>139</v>
+        <v>122</v>
       </c>
       <c r="D193" t="s">
         <v>186</v>
@@ -38047,13 +38047,13 @@
         <v>699</v>
       </c>
       <c r="P193">
-        <v>1.28</v>
+        <v>2.25</v>
       </c>
       <c r="Q193">
-        <v>5.66</v>
+        <v>3.66</v>
       </c>
       <c r="R193">
-        <v>8.98</v>
+        <v>3.36</v>
       </c>
       <c r="S193">
         <v>0</v>
@@ -38193,10 +38193,10 @@
         <v>93</v>
       </c>
       <c r="C194" t="s">
-        <v>174</v>
+        <v>146</v>
       </c>
       <c r="D194" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E194" t="s">
         <v>380</v>
@@ -38232,13 +38232,13 @@
         <v>699</v>
       </c>
       <c r="P194">
-        <v>1.3</v>
+        <v>1.91</v>
       </c>
       <c r="Q194">
-        <v>5.1</v>
+        <v>3.53</v>
       </c>
       <c r="R194">
-        <v>7.95</v>
+        <v>3.91</v>
       </c>
       <c r="S194">
         <v>0</v>
@@ -38277,10 +38277,10 @@
         <v>0</v>
       </c>
       <c r="AE194">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AF194">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AG194">
         <v>0</v>
@@ -38378,7 +38378,7 @@
         <v>93</v>
       </c>
       <c r="C195" t="s">
-        <v>158</v>
+        <v>146</v>
       </c>
       <c r="D195" t="s">
         <v>186</v>
@@ -38417,13 +38417,13 @@
         <v>699</v>
       </c>
       <c r="P195">
-        <v>1.82</v>
+        <v>3.12</v>
       </c>
       <c r="Q195">
-        <v>3.1</v>
+        <v>3.22</v>
       </c>
       <c r="R195">
-        <v>4.56</v>
+        <v>2.43</v>
       </c>
       <c r="S195">
         <v>0</v>
@@ -38563,10 +38563,10 @@
         <v>93</v>
       </c>
       <c r="C196" t="s">
-        <v>158</v>
+        <v>173</v>
       </c>
       <c r="D196" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E196" t="s">
         <v>382</v>
@@ -38602,13 +38602,13 @@
         <v>699</v>
       </c>
       <c r="P196">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="Q196">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="R196">
-        <v>6.76</v>
+        <v>0</v>
       </c>
       <c r="S196">
         <v>0</v>
@@ -38748,10 +38748,10 @@
         <v>94</v>
       </c>
       <c r="C197" t="s">
-        <v>128</v>
+        <v>175</v>
       </c>
       <c r="D197" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E197" t="s">
         <v>383</v>
@@ -38787,13 +38787,13 @@
         <v>699</v>
       </c>
       <c r="P197">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="Q197">
-        <v>0</v>
+        <v>4.45</v>
       </c>
       <c r="R197">
-        <v>0</v>
+        <v>5.12</v>
       </c>
       <c r="S197">
         <v>0</v>
@@ -38933,10 +38933,10 @@
         <v>94</v>
       </c>
       <c r="C198" t="s">
-        <v>148</v>
+        <v>128</v>
       </c>
       <c r="D198" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E198" t="s">
         <v>384</v>
@@ -39118,10 +39118,10 @@
         <v>94</v>
       </c>
       <c r="C199" t="s">
-        <v>175</v>
+        <v>148</v>
       </c>
       <c r="D199" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E199" t="s">
         <v>385</v>
@@ -39303,7 +39303,7 @@
         <v>94</v>
       </c>
       <c r="C200" t="s">
-        <v>159</v>
+        <v>176</v>
       </c>
       <c r="D200" t="s">
         <v>186</v>
@@ -39488,7 +39488,7 @@
         <v>94</v>
       </c>
       <c r="C201" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="D201" t="s">
         <v>186</v>
@@ -39676,7 +39676,7 @@
         <v>176</v>
       </c>
       <c r="D202" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E202" t="s">
         <v>388</v>
@@ -39712,13 +39712,13 @@
         <v>699</v>
       </c>
       <c r="P202">
-        <v>1.53</v>
+        <v>2.25</v>
       </c>
       <c r="Q202">
-        <v>4.45</v>
+        <v>3.38</v>
       </c>
       <c r="R202">
-        <v>5.12</v>
+        <v>3</v>
       </c>
       <c r="S202">
         <v>0</v>
@@ -39858,7 +39858,7 @@
         <v>94</v>
       </c>
       <c r="C203" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="D203" t="s">
         <v>186</v>
@@ -40043,7 +40043,7 @@
         <v>94</v>
       </c>
       <c r="C204" t="s">
-        <v>175</v>
+        <v>160</v>
       </c>
       <c r="D204" t="s">
         <v>186</v>
@@ -40228,7 +40228,7 @@
         <v>95</v>
       </c>
       <c r="C205" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="D205" t="s">
         <v>186</v>
@@ -40783,7 +40783,7 @@
         <v>97</v>
       </c>
       <c r="C208" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="D208" t="s">
         <v>186</v>
@@ -40968,7 +40968,7 @@
         <v>97</v>
       </c>
       <c r="C209" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="D209" t="s">
         <v>186</v>
@@ -41153,10 +41153,10 @@
         <v>97</v>
       </c>
       <c r="C210" t="s">
-        <v>171</v>
+        <v>177</v>
       </c>
       <c r="D210" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E210" t="s">
         <v>396</v>
@@ -41338,10 +41338,10 @@
         <v>97</v>
       </c>
       <c r="C211" t="s">
-        <v>177</v>
+        <v>170</v>
       </c>
       <c r="D211" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E211" t="s">
         <v>397</v>
@@ -41523,10 +41523,10 @@
         <v>98</v>
       </c>
       <c r="C212" t="s">
-        <v>127</v>
+        <v>178</v>
       </c>
       <c r="D212" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E212" t="s">
         <v>398</v>
@@ -41708,10 +41708,10 @@
         <v>98</v>
       </c>
       <c r="C213" t="s">
-        <v>178</v>
+        <v>124</v>
       </c>
       <c r="D213" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E213" t="s">
         <v>399</v>
@@ -42266,7 +42266,7 @@
         <v>179</v>
       </c>
       <c r="D216" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E216" t="s">
         <v>402</v>
@@ -42302,13 +42302,13 @@
         <v>699</v>
       </c>
       <c r="P216">
-        <v>4.68</v>
+        <v>5.3</v>
       </c>
       <c r="Q216">
-        <v>4.32</v>
+        <v>3.73</v>
       </c>
       <c r="R216">
-        <v>1.76</v>
+        <v>1.71</v>
       </c>
       <c r="S216">
         <v>0</v>
@@ -42347,10 +42347,10 @@
         <v>0</v>
       </c>
       <c r="AE216">
-        <v>1.58</v>
+        <v>1.95</v>
       </c>
       <c r="AF216">
-        <v>2.25</v>
+        <v>1.73</v>
       </c>
       <c r="AG216">
         <v>0</v>
@@ -42451,7 +42451,7 @@
         <v>180</v>
       </c>
       <c r="D217" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E217" t="s">
         <v>403</v>
@@ -42487,13 +42487,13 @@
         <v>699</v>
       </c>
       <c r="P217">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="Q217">
-        <v>0</v>
+        <v>4.73</v>
       </c>
       <c r="R217">
-        <v>0</v>
+        <v>5.79</v>
       </c>
       <c r="S217">
         <v>0</v>
@@ -42538,10 +42538,10 @@
         <v>0</v>
       </c>
       <c r="AG217">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AH217">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AI217">
         <v>0</v>
@@ -42633,10 +42633,10 @@
         <v>100</v>
       </c>
       <c r="C218" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="D218" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E218" t="s">
         <v>404</v>
@@ -42672,13 +42672,13 @@
         <v>699</v>
       </c>
       <c r="P218">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="Q218">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R218">
-        <v>0</v>
+        <v>3.07</v>
       </c>
       <c r="S218">
         <v>0</v>
@@ -42717,10 +42717,10 @@
         <v>0</v>
       </c>
       <c r="AE218">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AF218">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AG218">
         <v>0</v>
@@ -42818,7 +42818,7 @@
         <v>100</v>
       </c>
       <c r="C219" t="s">
-        <v>179</v>
+        <v>147</v>
       </c>
       <c r="D219" t="s">
         <v>186</v>
@@ -42857,13 +42857,13 @@
         <v>699</v>
       </c>
       <c r="P219">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="Q219">
-        <v>9.15</v>
+        <v>0</v>
       </c>
       <c r="R219">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="S219">
         <v>0</v>
@@ -42908,10 +42908,10 @@
         <v>0</v>
       </c>
       <c r="AG219">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AH219">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AI219">
         <v>0</v>
@@ -43006,7 +43006,7 @@
         <v>179</v>
       </c>
       <c r="D220" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E220" t="s">
         <v>406</v>
@@ -43042,13 +43042,13 @@
         <v>699</v>
       </c>
       <c r="P220">
-        <v>3.8</v>
+        <v>2.15</v>
       </c>
       <c r="Q220">
-        <v>3.78</v>
+        <v>3.44</v>
       </c>
       <c r="R220">
-        <v>2.05</v>
+        <v>3.5</v>
       </c>
       <c r="S220">
         <v>0</v>
@@ -43087,10 +43087,10 @@
         <v>0</v>
       </c>
       <c r="AE220">
-        <v>1.73</v>
+        <v>1.95</v>
       </c>
       <c r="AF220">
-        <v>1.98</v>
+        <v>1.75</v>
       </c>
       <c r="AG220">
         <v>0</v>
@@ -43188,10 +43188,10 @@
         <v>100</v>
       </c>
       <c r="C221" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="D221" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E221" t="s">
         <v>407</v>
@@ -43227,13 +43227,13 @@
         <v>699</v>
       </c>
       <c r="P221">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="Q221">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="R221">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="S221">
         <v>0</v>
@@ -43272,10 +43272,10 @@
         <v>0</v>
       </c>
       <c r="AE221">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AF221">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AG221">
         <v>0</v>
@@ -43373,7 +43373,7 @@
         <v>100</v>
       </c>
       <c r="C222" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="D222" t="s">
         <v>186</v>
@@ -43412,13 +43412,13 @@
         <v>699</v>
       </c>
       <c r="P222">
-        <v>3.17</v>
+        <v>4.05</v>
       </c>
       <c r="Q222">
-        <v>3.68</v>
+        <v>3.76</v>
       </c>
       <c r="R222">
-        <v>2.34</v>
+        <v>1.99</v>
       </c>
       <c r="S222">
         <v>0</v>
@@ -43457,10 +43457,10 @@
         <v>0</v>
       </c>
       <c r="AE222">
-        <v>1.72</v>
+        <v>1.85</v>
       </c>
       <c r="AF222">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="AG222">
         <v>0</v>
@@ -43558,7 +43558,7 @@
         <v>100</v>
       </c>
       <c r="C223" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="D223" t="s">
         <v>185</v>
@@ -43597,13 +43597,13 @@
         <v>699</v>
       </c>
       <c r="P223">
-        <v>5.3</v>
+        <v>0</v>
       </c>
       <c r="Q223">
-        <v>3.73</v>
+        <v>0</v>
       </c>
       <c r="R223">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="S223">
         <v>0</v>
@@ -43642,10 +43642,10 @@
         <v>0</v>
       </c>
       <c r="AE223">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AF223">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AG223">
         <v>0</v>
@@ -43743,7 +43743,7 @@
         <v>100</v>
       </c>
       <c r="C224" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="D224" t="s">
         <v>186</v>
@@ -43782,13 +43782,13 @@
         <v>699</v>
       </c>
       <c r="P224">
-        <v>1.59</v>
+        <v>4.68</v>
       </c>
       <c r="Q224">
-        <v>4.73</v>
+        <v>4.32</v>
       </c>
       <c r="R224">
-        <v>5.79</v>
+        <v>1.76</v>
       </c>
       <c r="S224">
         <v>0</v>
@@ -43827,16 +43827,16 @@
         <v>0</v>
       </c>
       <c r="AE224">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AF224">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AG224">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AH224">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AI224">
         <v>0</v>
@@ -43928,10 +43928,10 @@
         <v>100</v>
       </c>
       <c r="C225" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="D225" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E225" t="s">
         <v>411</v>
@@ -43967,13 +43967,13 @@
         <v>699</v>
       </c>
       <c r="P225">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="Q225">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="R225">
-        <v>3.07</v>
+        <v>0</v>
       </c>
       <c r="S225">
         <v>0</v>
@@ -44012,10 +44012,10 @@
         <v>0</v>
       </c>
       <c r="AE225">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AF225">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AG225">
         <v>0</v>
@@ -44113,10 +44113,10 @@
         <v>100</v>
       </c>
       <c r="C226" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="D226" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E226" t="s">
         <v>412</v>
@@ -44152,13 +44152,13 @@
         <v>699</v>
       </c>
       <c r="P226">
-        <v>2.15</v>
+        <v>3.17</v>
       </c>
       <c r="Q226">
-        <v>3.44</v>
+        <v>3.68</v>
       </c>
       <c r="R226">
-        <v>3.5</v>
+        <v>2.34</v>
       </c>
       <c r="S226">
         <v>0</v>
@@ -44197,10 +44197,10 @@
         <v>0</v>
       </c>
       <c r="AE226">
-        <v>1.95</v>
+        <v>1.72</v>
       </c>
       <c r="AF226">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="AG226">
         <v>0</v>
@@ -44298,7 +44298,7 @@
         <v>100</v>
       </c>
       <c r="C227" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="D227" t="s">
         <v>186</v>
@@ -44337,13 +44337,13 @@
         <v>699</v>
       </c>
       <c r="P227">
-        <v>4.05</v>
+        <v>2.38</v>
       </c>
       <c r="Q227">
-        <v>3.76</v>
+        <v>3.9</v>
       </c>
       <c r="R227">
-        <v>1.99</v>
+        <v>2.96</v>
       </c>
       <c r="S227">
         <v>0</v>
@@ -44382,10 +44382,10 @@
         <v>0</v>
       </c>
       <c r="AE227">
-        <v>1.85</v>
+        <v>1.58</v>
       </c>
       <c r="AF227">
-        <v>1.85</v>
+        <v>2.25</v>
       </c>
       <c r="AG227">
         <v>0</v>
@@ -44483,10 +44483,10 @@
         <v>100</v>
       </c>
       <c r="C228" t="s">
-        <v>146</v>
+        <v>182</v>
       </c>
       <c r="D228" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E228" t="s">
         <v>414</v>
@@ -44522,13 +44522,13 @@
         <v>699</v>
       </c>
       <c r="P228">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="Q228">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R228">
-        <v>0</v>
+        <v>4.39</v>
       </c>
       <c r="S228">
         <v>0</v>
@@ -44668,7 +44668,7 @@
         <v>100</v>
       </c>
       <c r="C229" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="D229" t="s">
         <v>186</v>
@@ -44707,13 +44707,13 @@
         <v>699</v>
       </c>
       <c r="P229">
-        <v>2.38</v>
+        <v>1.18</v>
       </c>
       <c r="Q229">
-        <v>3.9</v>
+        <v>9.15</v>
       </c>
       <c r="R229">
-        <v>2.96</v>
+        <v>17</v>
       </c>
       <c r="S229">
         <v>0</v>
@@ -44752,16 +44752,16 @@
         <v>0</v>
       </c>
       <c r="AE229">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AF229">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AG229">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AH229">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AI229">
         <v>0</v>
@@ -45408,10 +45408,10 @@
         <v>102</v>
       </c>
       <c r="C233" t="s">
-        <v>169</v>
+        <v>177</v>
       </c>
       <c r="D233" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E233" t="s">
         <v>419</v>
@@ -45593,7 +45593,7 @@
         <v>102</v>
       </c>
       <c r="C234" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="D234" t="s">
         <v>185</v>
@@ -45778,10 +45778,10 @@
         <v>102</v>
       </c>
       <c r="C235" t="s">
-        <v>177</v>
+        <v>170</v>
       </c>
       <c r="D235" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E235" t="s">
         <v>421</v>
@@ -45963,7 +45963,7 @@
         <v>102</v>
       </c>
       <c r="C236" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="D236" t="s">
         <v>185</v>
@@ -46148,7 +46148,7 @@
         <v>102</v>
       </c>
       <c r="C237" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="D237" t="s">
         <v>185</v>
@@ -46372,13 +46372,13 @@
         <v>699</v>
       </c>
       <c r="P238">
-        <v>2.23</v>
+        <v>1.67</v>
       </c>
       <c r="Q238">
-        <v>3.71</v>
+        <v>3.61</v>
       </c>
       <c r="R238">
-        <v>3.21</v>
+        <v>5.14</v>
       </c>
       <c r="S238">
         <v>0</v>
@@ -46417,10 +46417,10 @@
         <v>0</v>
       </c>
       <c r="AE238">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AF238">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AG238">
         <v>0</v>
@@ -46557,13 +46557,13 @@
         <v>699</v>
       </c>
       <c r="P239">
-        <v>1.67</v>
+        <v>2.23</v>
       </c>
       <c r="Q239">
-        <v>3.61</v>
+        <v>3.71</v>
       </c>
       <c r="R239">
-        <v>5.14</v>
+        <v>3.21</v>
       </c>
       <c r="S239">
         <v>0</v>
@@ -46602,10 +46602,10 @@
         <v>0</v>
       </c>
       <c r="AE239">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AF239">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AG239">
         <v>0</v>
@@ -47073,7 +47073,7 @@
         <v>106</v>
       </c>
       <c r="C242" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="D242" t="s">
         <v>185</v>
@@ -47297,13 +47297,13 @@
         <v>699</v>
       </c>
       <c r="P243">
-        <v>2.13</v>
+        <v>2.81</v>
       </c>
       <c r="Q243">
-        <v>3.34</v>
+        <v>3.08</v>
       </c>
       <c r="R243">
-        <v>3.67</v>
+        <v>2.51</v>
       </c>
       <c r="S243">
         <v>0</v>
@@ -47342,10 +47342,10 @@
         <v>0</v>
       </c>
       <c r="AE243">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AF243">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AG243">
         <v>0</v>
@@ -47443,7 +47443,7 @@
         <v>106</v>
       </c>
       <c r="C244" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="D244" t="s">
         <v>185</v>
@@ -47482,13 +47482,13 @@
         <v>699</v>
       </c>
       <c r="P244">
-        <v>2.26</v>
+        <v>2.13</v>
       </c>
       <c r="Q244">
-        <v>3.22</v>
+        <v>3.34</v>
       </c>
       <c r="R244">
-        <v>3.46</v>
+        <v>3.67</v>
       </c>
       <c r="S244">
         <v>0</v>
@@ -47527,10 +47527,10 @@
         <v>0</v>
       </c>
       <c r="AE244">
-        <v>2.25</v>
+        <v>1.95</v>
       </c>
       <c r="AF244">
-        <v>1.57</v>
+        <v>1.73</v>
       </c>
       <c r="AG244">
         <v>0</v>
@@ -47628,7 +47628,7 @@
         <v>106</v>
       </c>
       <c r="C245" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="D245" t="s">
         <v>185</v>
@@ -47667,13 +47667,13 @@
         <v>699</v>
       </c>
       <c r="P245">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="Q245">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="R245">
-        <v>0</v>
+        <v>3.46</v>
       </c>
       <c r="S245">
         <v>0</v>
@@ -47712,10 +47712,10 @@
         <v>0</v>
       </c>
       <c r="AE245">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AF245">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AG245">
         <v>0</v>
@@ -48037,13 +48037,13 @@
         <v>699</v>
       </c>
       <c r="P247">
-        <v>3.79</v>
+        <v>0</v>
       </c>
       <c r="Q247">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="R247">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="S247">
         <v>0</v>
@@ -48082,10 +48082,10 @@
         <v>0</v>
       </c>
       <c r="AE247">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AF247">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AG247">
         <v>0</v>
@@ -48183,7 +48183,7 @@
         <v>108</v>
       </c>
       <c r="C248" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="D248" t="s">
         <v>185</v>
@@ -48222,13 +48222,13 @@
         <v>699</v>
       </c>
       <c r="P248">
-        <v>0</v>
+        <v>3.79</v>
       </c>
       <c r="Q248">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="R248">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="S248">
         <v>0</v>
@@ -48267,10 +48267,10 @@
         <v>0</v>
       </c>
       <c r="AE248">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AF248">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AG248">
         <v>0</v>
@@ -48368,7 +48368,7 @@
         <v>109</v>
       </c>
       <c r="C249" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="D249" t="s">
         <v>185</v>
@@ -48777,13 +48777,13 @@
         <v>699</v>
       </c>
       <c r="P251">
-        <v>0</v>
+        <v>4.44</v>
       </c>
       <c r="Q251">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R251">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="S251">
         <v>0</v>
@@ -48822,10 +48822,10 @@
         <v>0</v>
       </c>
       <c r="AE251">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AF251">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AG251">
         <v>0</v>
@@ -48923,7 +48923,7 @@
         <v>110</v>
       </c>
       <c r="C252" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="D252" t="s">
         <v>185</v>
@@ -49108,7 +49108,7 @@
         <v>111</v>
       </c>
       <c r="C253" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="D253" t="s">
         <v>185</v>
@@ -49848,7 +49848,7 @@
         <v>114</v>
       </c>
       <c r="C257" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="D257" t="s">
         <v>185</v>

--- a/jogos_2026-05-10.xlsx
+++ b/jogos_2026-05-10.xlsx
@@ -364,48 +364,48 @@
     <t>South Korea K League 2</t>
   </si>
   <si>
+    <t>Australia New South Wales NPL</t>
+  </si>
+  <si>
     <t>South Korea K League 1</t>
   </si>
   <si>
-    <t>Australia New South Wales NPL</t>
+    <t>China China League One</t>
   </si>
   <si>
     <t>Russia FNL</t>
   </si>
   <si>
-    <t>China China League One</t>
-  </si>
-  <si>
     <t>Czech Republic FNL</t>
   </si>
   <si>
     <t>Indonesia Liga 1</t>
   </si>
   <si>
+    <t>China Chinese Super League</t>
+  </si>
+  <si>
     <t>Russia Russian Premier League</t>
   </si>
   <si>
-    <t>China Chinese Super League</t>
+    <t>Kazakhstan Kazakhstan Premier League</t>
+  </si>
+  <si>
+    <t>Spain Primera Division Women</t>
+  </si>
+  <si>
+    <t>Ethiopia Ethiopia Premier League</t>
   </si>
   <si>
     <t>Portugal Liga 3</t>
   </si>
   <si>
-    <t>Kazakhstan Kazakhstan Premier League</t>
+    <t>Poland 1. Liga</t>
   </si>
   <si>
     <t>Vietnam V.League 1</t>
   </si>
   <si>
-    <t>Ethiopia Ethiopia Premier League</t>
-  </si>
-  <si>
-    <t>Spain Primera Division Women</t>
-  </si>
-  <si>
-    <t>Poland 1. Liga</t>
-  </si>
-  <si>
     <t>Poland Ekstraklasa</t>
   </si>
   <si>
@@ -415,30 +415,30 @@
     <t>Thailand Thai League T1</t>
   </si>
   <si>
+    <t>Sweden Damallsvenskan</t>
+  </si>
+  <si>
     <t>Scotland Premiership</t>
   </si>
   <si>
-    <t>Sweden Damallsvenskan</t>
-  </si>
-  <si>
     <t>Bulgaria First League</t>
   </si>
   <si>
     <t>Lithuania A Lyga</t>
   </si>
   <si>
+    <t>Germany 3. Liga</t>
+  </si>
+  <si>
+    <t>India Indian Super League</t>
+  </si>
+  <si>
+    <t>Estonia Meistriliiga</t>
+  </si>
+  <si>
     <t>Germany 2. Bundesliga</t>
   </si>
   <si>
-    <t>India Indian Super League</t>
-  </si>
-  <si>
-    <t>Estonia Meistriliiga</t>
-  </si>
-  <si>
-    <t>Germany 3. Liga</t>
-  </si>
-  <si>
     <t>Singapore S.League</t>
   </si>
   <si>
@@ -454,18 +454,18 @@
     <t>Sweden Allsvenskan</t>
   </si>
   <si>
+    <t>Switzerland Super League</t>
+  </si>
+  <si>
+    <t>Georgia Erovnuli Liga</t>
+  </si>
+  <si>
+    <t>Spain La Liga</t>
+  </si>
+  <si>
     <t>Spain Segunda División</t>
   </si>
   <si>
-    <t>Spain La Liga</t>
-  </si>
-  <si>
-    <t>Georgia Erovnuli Liga</t>
-  </si>
-  <si>
-    <t>Switzerland Super League</t>
-  </si>
-  <si>
     <t>Malaysia Super League</t>
   </si>
   <si>
@@ -481,39 +481,39 @@
     <t>Azerbaijan Premyer Liqası</t>
   </si>
   <si>
+    <t>Slovenia PrvaLiga</t>
+  </si>
+  <si>
     <t>Romania Liga I</t>
   </si>
   <si>
-    <t>Slovenia PrvaLiga</t>
-  </si>
-  <si>
     <t>Germany Bundesliga</t>
   </si>
   <si>
+    <t>Greece Super League</t>
+  </si>
+  <si>
+    <t>Faroe Islands Faroe Islands Premier League</t>
+  </si>
+  <si>
     <t>Croatia Prva HNL</t>
   </si>
   <si>
-    <t>Faroe Islands Faroe Islands Premier League</t>
-  </si>
-  <si>
     <t>Hungary NB II</t>
   </si>
   <si>
-    <t>Greece Super League</t>
-  </si>
-  <si>
     <t>Netherlands Eredivisie</t>
   </si>
   <si>
+    <t>Cyprus First Division</t>
+  </si>
+  <si>
     <t>Norway First Division</t>
   </si>
   <si>
     <t>Austria Bundesliga</t>
   </si>
   <si>
-    <t>Cyprus First Division</t>
-  </si>
-  <si>
     <t>FYR Macedonia First Football League</t>
   </si>
   <si>
@@ -532,45 +532,45 @@
     <t>Saudi Arabia Professional League</t>
   </si>
   <si>
+    <t>Chile Primera B</t>
+  </si>
+  <si>
     <t>Serbia SuperLiga</t>
   </si>
   <si>
-    <t>Chile Primera B</t>
-  </si>
-  <si>
     <t>USA NWSL</t>
   </si>
   <si>
+    <t>Israel Israeli Premier League</t>
+  </si>
+  <si>
     <t>Iceland Úrvalsdeild</t>
   </si>
   <si>
-    <t>Israel Israeli Premier League</t>
-  </si>
-  <si>
     <t>USA MLS Next Pro</t>
   </si>
   <si>
     <t>Argentina Prim B Nacional</t>
   </si>
   <si>
+    <t>France Ligue 1</t>
+  </si>
+  <si>
     <t>Brazil Serie A</t>
   </si>
   <si>
-    <t>France Ligue 1</t>
-  </si>
-  <si>
     <t>Bolivia LFPB</t>
   </si>
   <si>
     <t>Brazil Serie B</t>
   </si>
   <si>
+    <t>USA MLS</t>
+  </si>
+  <si>
     <t>Ecuador Primera Categoría Serie A</t>
   </si>
   <si>
-    <t>USA MLS</t>
-  </si>
-  <si>
     <t>2026</t>
   </si>
   <si>
@@ -583,28 +583,31 @@
     <t>Seongnam</t>
   </si>
   <si>
+    <t>Rockdale City Suns</t>
+  </si>
+  <si>
     <t>Ulsan</t>
   </si>
   <si>
-    <t>Rockdale City Suns</t>
-  </si>
-  <si>
     <t>Blacktown City</t>
   </si>
   <si>
     <t>APIA Leichhardt Tigers</t>
   </si>
   <si>
+    <t>Yanbian Longding</t>
+  </si>
+  <si>
     <t>Ufa</t>
   </si>
   <si>
-    <t>Yanbian Longding</t>
+    <t>Shaanxi Union</t>
   </si>
   <si>
     <t>Dalian Huayi</t>
   </si>
   <si>
-    <t>Shaanxi Union</t>
+    <t>Ansan Greeners</t>
   </si>
   <si>
     <t>Anyang</t>
@@ -613,198 +616,195 @@
     <t>Busan I'Park</t>
   </si>
   <si>
-    <t>Ansan Greeners</t>
+    <t>Slavia Praha U21</t>
   </si>
   <si>
     <t>Viktoria Žižkov</t>
   </si>
   <si>
-    <t>Slavia Praha U21</t>
-  </si>
-  <si>
     <t>Persita</t>
   </si>
   <si>
     <t>Persija</t>
   </si>
   <si>
+    <t>Qingdao Youth Island</t>
+  </si>
+  <si>
     <t>Orenburg</t>
   </si>
   <si>
-    <t>Qingdao Youth Island</t>
+    <t>Ulytau</t>
+  </si>
+  <si>
+    <t>Levante W</t>
+  </si>
+  <si>
+    <t>Sheger Ketema</t>
   </si>
   <si>
     <t>Amarante</t>
   </si>
   <si>
+    <t>Polonia Warszawa</t>
+  </si>
+  <si>
+    <t>Sokol Saratov</t>
+  </si>
+  <si>
     <t>Sichuan Jiuniu</t>
   </si>
   <si>
     <t>Gyeongnam</t>
   </si>
   <si>
-    <t>Ulytau</t>
-  </si>
-  <si>
     <t>Hoang Anh Gia Lai</t>
   </si>
   <si>
-    <t>Sheger Ketema</t>
-  </si>
-  <si>
-    <t>Levante W</t>
-  </si>
-  <si>
-    <t>Polonia Warszawa</t>
-  </si>
-  <si>
-    <t>Sokol Saratov</t>
-  </si>
-  <si>
     <t>Piast Gliwice</t>
   </si>
   <si>
     <t>Hellas Verona</t>
   </si>
   <si>
+    <t>Kanchanaburi</t>
+  </si>
+  <si>
     <t>Bangkok Glass</t>
   </si>
   <si>
+    <t>Ho Chi Minh City</t>
+  </si>
+  <si>
+    <t>Shenzhen Juniors</t>
+  </si>
+  <si>
+    <t>Hà Nội II</t>
+  </si>
+  <si>
+    <t>Chonburi</t>
+  </si>
+  <si>
+    <t>Altay</t>
+  </si>
+  <si>
+    <t>Chiangrai United</t>
+  </si>
+  <si>
+    <t>Buriram United</t>
+  </si>
+  <si>
+    <t>Ayutthaya United</t>
+  </si>
+  <si>
+    <t>Piteå Women</t>
+  </si>
+  <si>
+    <t>Celtic</t>
+  </si>
+  <si>
+    <t>Shenyang Urban</t>
+  </si>
+  <si>
+    <t>Rayong</t>
+  </si>
+  <si>
     <t>Sukhothai</t>
   </si>
   <si>
-    <t>Celtic</t>
-  </si>
-  <si>
-    <t>Hà Nội II</t>
-  </si>
-  <si>
-    <t>Piteå Women</t>
-  </si>
-  <si>
-    <t>Ho Chi Minh City</t>
-  </si>
-  <si>
-    <t>Chonburi</t>
-  </si>
-  <si>
-    <t>Kanchanaburi</t>
-  </si>
-  <si>
-    <t>Shenyang Urban</t>
-  </si>
-  <si>
-    <t>Rayong</t>
-  </si>
-  <si>
-    <t>Buriram United</t>
-  </si>
-  <si>
-    <t>Chiangrai United</t>
-  </si>
-  <si>
-    <t>Altay</t>
-  </si>
-  <si>
-    <t>Shenzhen Juniors</t>
-  </si>
-  <si>
-    <t>Ayutthaya United</t>
-  </si>
-  <si>
     <t>Spartak Varna</t>
   </si>
   <si>
     <t>Sūduva</t>
   </si>
   <si>
+    <t>Havelse</t>
+  </si>
+  <si>
+    <t>Kerala Blasters</t>
+  </si>
+  <si>
+    <t>Nõmme Kalju</t>
+  </si>
+  <si>
+    <t>Fortuna Düsseldorf</t>
+  </si>
+  <si>
     <t>Preußen Münster</t>
   </si>
   <si>
-    <t>Kerala Blasters</t>
-  </si>
-  <si>
-    <t>Nõmme Kalju</t>
-  </si>
-  <si>
     <t>Hertha BSC</t>
   </si>
   <si>
-    <t>Havelse</t>
-  </si>
-  <si>
-    <t>Fortuna Düsseldorf</t>
+    <t>Dongguan United</t>
   </si>
   <si>
     <t>Home United</t>
   </si>
   <si>
+    <t>KAA Gent</t>
+  </si>
+  <si>
+    <t>Nantong Zhiyun</t>
+  </si>
+  <si>
     <t>Hougang United</t>
   </si>
   <si>
-    <t>Dongguan United</t>
-  </si>
-  <si>
-    <t>Nantong Zhiyun</t>
-  </si>
-  <si>
-    <t>KAA Gent</t>
+    <t>Zhejiang FC</t>
   </si>
   <si>
     <t>Beijing Guoan</t>
   </si>
   <si>
-    <t>Zhejiang FC</t>
-  </si>
-  <si>
     <t>Hrvace</t>
   </si>
   <si>
+    <t>Vejle</t>
+  </si>
+  <si>
+    <t>Bahardar</t>
+  </si>
+  <si>
+    <t>Zenit</t>
+  </si>
+  <si>
+    <t>Kalmar</t>
+  </si>
+  <si>
     <t>Aktobe</t>
   </si>
   <si>
-    <t>Vejle</t>
-  </si>
-  <si>
-    <t>Bahardar</t>
-  </si>
-  <si>
-    <t>Kalmar</t>
+    <t>Lugano</t>
   </si>
   <si>
     <t>Qingdao Jonoon</t>
   </si>
   <si>
+    <t>Nordsjælland</t>
+  </si>
+  <si>
+    <t>Meshakhte</t>
+  </si>
+  <si>
+    <t>RCD Mallorca</t>
+  </si>
+  <si>
+    <t>PSIM Yogyakarta</t>
+  </si>
+  <si>
+    <t>FC Andorra</t>
+  </si>
+  <si>
     <t>AIK</t>
   </si>
   <si>
-    <t>FC Andorra</t>
-  </si>
-  <si>
-    <t>RCD Mallorca</t>
-  </si>
-  <si>
-    <t>Meshakhte</t>
-  </si>
-  <si>
-    <t>Nordsjælland</t>
-  </si>
-  <si>
-    <t>Zenit</t>
-  </si>
-  <si>
-    <t>Lugano</t>
-  </si>
-  <si>
-    <t>PSIM Yogyakarta</t>
+    <t>Công An Nhân Dân</t>
   </si>
   <si>
     <t>Kuala Lumpur</t>
   </si>
   <si>
-    <t>Công An Nhân Dân</t>
-  </si>
-  <si>
     <t>Baník Ostrava U21</t>
   </si>
   <si>
@@ -817,166 +817,220 @@
     <t>Wisła Płock</t>
   </si>
   <si>
+    <t>Uppsala W</t>
+  </si>
+  <si>
+    <t>Crystal Palace</t>
+  </si>
+  <si>
+    <t>Cremonese</t>
+  </si>
+  <si>
+    <t>Sigma Olomouc</t>
+  </si>
+  <si>
+    <t>Pardubice</t>
+  </si>
+  <si>
+    <t>Astana</t>
+  </si>
+  <si>
+    <t>Turan</t>
+  </si>
+  <si>
+    <t>Kelantan United</t>
+  </si>
+  <si>
+    <t>NK Primorje</t>
+  </si>
+  <si>
+    <t>Botoşani</t>
+  </si>
+  <si>
+    <t>Fiorentina</t>
+  </si>
+  <si>
+    <t>Burnley</t>
+  </si>
+  <si>
+    <t>Arba Minch Kenema</t>
+  </si>
+  <si>
     <t>Nottingham Forest</t>
   </si>
   <si>
-    <t>Crystal Palace</t>
-  </si>
-  <si>
-    <t>Astana</t>
-  </si>
-  <si>
-    <t>Kelantan United</t>
-  </si>
-  <si>
-    <t>Pardubice</t>
-  </si>
-  <si>
-    <t>Burnley</t>
-  </si>
-  <si>
-    <t>Turan</t>
-  </si>
-  <si>
-    <t>Botoşani</t>
-  </si>
-  <si>
-    <t>Arba Minch Kenema</t>
-  </si>
-  <si>
-    <t>Cremonese</t>
-  </si>
-  <si>
-    <t>Sigma Olomouc</t>
-  </si>
-  <si>
-    <t>Uppsala W</t>
-  </si>
-  <si>
-    <t>Fiorentina</t>
-  </si>
-  <si>
-    <t>NK Primorje</t>
-  </si>
-  <si>
     <t>Hamburger SV</t>
   </si>
   <si>
     <t>Botev Vratsa</t>
   </si>
   <si>
+    <t>Aris</t>
+  </si>
+  <si>
+    <t>B36</t>
+  </si>
+  <si>
+    <t>Royal Antwerp FC</t>
+  </si>
+  <si>
     <t>Osijek</t>
   </si>
   <si>
+    <t>Nõmme United</t>
+  </si>
+  <si>
     <t>EB - Streymur</t>
   </si>
   <si>
-    <t>B36</t>
+    <t>Banga</t>
+  </si>
+  <si>
+    <t>NorthEast United</t>
   </si>
   <si>
     <t>Silkeborg</t>
   </si>
   <si>
-    <t>Royal Antwerp FC</t>
-  </si>
-  <si>
-    <t>NorthEast United</t>
-  </si>
-  <si>
     <t>Honvéd W</t>
   </si>
   <si>
     <t>Volos NFC</t>
   </si>
   <si>
-    <t>Banga</t>
-  </si>
-  <si>
-    <t>Nõmme United</t>
-  </si>
-  <si>
-    <t>Aris</t>
-  </si>
-  <si>
     <t>Leganés</t>
   </si>
   <si>
+    <t>Athletic Club Bilbao</t>
+  </si>
+  <si>
     <t>Akhmat Grozny</t>
   </si>
   <si>
-    <t>Athletic Club Bilbao</t>
+    <t>Häcken</t>
   </si>
   <si>
     <t>Sion</t>
   </si>
   <si>
+    <t>Young Boys</t>
+  </si>
+  <si>
+    <t>Neftekhimik</t>
+  </si>
+  <si>
     <t>Viktoria Köln</t>
   </si>
   <si>
-    <t>Neftekhimik</t>
-  </si>
-  <si>
-    <t>Häcken</t>
-  </si>
-  <si>
-    <t>Young Boys</t>
-  </si>
-  <si>
     <t>Go Ahead Eagles</t>
   </si>
   <si>
+    <t>Telstar</t>
+  </si>
+  <si>
+    <t>Groningen</t>
+  </si>
+  <si>
+    <t>Ajax</t>
+  </si>
+  <si>
+    <t>Twente</t>
+  </si>
+  <si>
+    <t>NAC Breda</t>
+  </si>
+  <si>
+    <t>Fortuna Sittard</t>
+  </si>
+  <si>
+    <t>Feyenoord</t>
+  </si>
+  <si>
     <t>Excelsior</t>
   </si>
   <si>
-    <t>Ajax</t>
-  </si>
-  <si>
-    <t>Groningen</t>
-  </si>
-  <si>
-    <t>Feyenoord</t>
-  </si>
-  <si>
-    <t>Fortuna Sittard</t>
-  </si>
-  <si>
-    <t>Twente</t>
-  </si>
-  <si>
-    <t>NAC Breda</t>
-  </si>
-  <si>
-    <t>Telstar</t>
+    <t>Omonia Nicosia</t>
+  </si>
+  <si>
+    <t>Åsane</t>
+  </si>
+  <si>
+    <t>Rapid Wien</t>
+  </si>
+  <si>
+    <t>Moss</t>
+  </si>
+  <si>
+    <t>Pogoń Siedlce</t>
+  </si>
+  <si>
+    <t>Sandefjord</t>
   </si>
   <si>
     <t>KFUM</t>
   </si>
   <si>
+    <t>Hartberg</t>
+  </si>
+  <si>
+    <t>LASK Linz</t>
+  </si>
+  <si>
+    <t>Makedonija GjP</t>
+  </si>
+  <si>
+    <t>Pelister</t>
+  </si>
+  <si>
+    <t>Aresimi</t>
+  </si>
+  <si>
+    <t>Strømmen</t>
+  </si>
+  <si>
+    <t>Zbrojovka Brno</t>
+  </si>
+  <si>
+    <t>Paphos</t>
+  </si>
+  <si>
+    <t>Real Madrid W</t>
+  </si>
+  <si>
     <t>Sogndal</t>
   </si>
   <si>
-    <t>Moss</t>
-  </si>
-  <si>
-    <t>Zbrojovka Brno</t>
-  </si>
-  <si>
-    <t>Sandefjord</t>
-  </si>
-  <si>
-    <t>Real Madrid W</t>
+    <t>Tromsø</t>
+  </si>
+  <si>
+    <t>Shkendija</t>
+  </si>
+  <si>
+    <t>Vardar</t>
+  </si>
+  <si>
+    <t>Sandnes Ulf</t>
+  </si>
+  <si>
+    <t>Croatia Zmijavci</t>
+  </si>
+  <si>
+    <t>Kecskeméti TE</t>
+  </si>
+  <si>
+    <t>Raufoss</t>
+  </si>
+  <si>
+    <t>Mebrat Hayl</t>
+  </si>
+  <si>
+    <t>Akademija Pandev</t>
   </si>
   <si>
     <t>Budafoki MTE</t>
   </si>
   <si>
-    <t>Hartberg</t>
-  </si>
-  <si>
-    <t>LASK Linz</t>
-  </si>
-  <si>
-    <t>Paphos</t>
+    <t>Ajka</t>
   </si>
   <si>
     <t>Saburtalo</t>
@@ -988,214 +1042,163 @@
     <t>Szentlőrinc SE</t>
   </si>
   <si>
-    <t>Strømmen</t>
-  </si>
-  <si>
-    <t>Åsane</t>
-  </si>
-  <si>
-    <t>Ajka</t>
-  </si>
-  <si>
-    <t>Akademija Pandev</t>
-  </si>
-  <si>
-    <t>Mebrat Hayl</t>
-  </si>
-  <si>
-    <t>Kecskeméti TE</t>
-  </si>
-  <si>
-    <t>Omonia Nicosia</t>
-  </si>
-  <si>
-    <t>Shkendija</t>
-  </si>
-  <si>
-    <t>Vardar</t>
-  </si>
-  <si>
-    <t>Pogoń Siedlce</t>
-  </si>
-  <si>
-    <t>Rapid Wien</t>
-  </si>
-  <si>
-    <t>Raufoss</t>
-  </si>
-  <si>
-    <t>Aresimi</t>
-  </si>
-  <si>
-    <t>Pelister</t>
-  </si>
-  <si>
-    <t>Tromsø</t>
-  </si>
-  <si>
     <t>Apollon</t>
   </si>
   <si>
-    <t>Croatia Zmijavci</t>
-  </si>
-  <si>
-    <t>Sandnes Ulf</t>
-  </si>
-  <si>
-    <t>Makedonija GjP</t>
+    <t>Al Ain</t>
+  </si>
+  <si>
+    <t>Bani Yas</t>
+  </si>
+  <si>
+    <t>Al Bataeh</t>
   </si>
   <si>
     <t>Dibba Al Fujairah</t>
   </si>
   <si>
-    <t>Bani Yas</t>
-  </si>
-  <si>
-    <t>Al Bataeh</t>
-  </si>
-  <si>
-    <t>Al Ain</t>
+    <t>Neftçi</t>
   </si>
   <si>
     <t>Köln</t>
   </si>
   <si>
+    <t>West Ham United</t>
+  </si>
+  <si>
     <t>Nieciecza</t>
   </si>
   <si>
-    <t>West Ham United</t>
-  </si>
-  <si>
     <t>Sekhukhune United</t>
   </si>
   <si>
-    <t>Neftçi</t>
+    <t>Brøndby</t>
+  </si>
+  <si>
+    <t>Arsenal Tivat</t>
   </si>
   <si>
     <t>Jedinstvo</t>
   </si>
   <si>
-    <t>Brøndby</t>
+    <t>Panevėžys</t>
+  </si>
+  <si>
+    <t>Dečić</t>
   </si>
   <si>
     <t>Mornar</t>
   </si>
   <si>
+    <t>Parma</t>
+  </si>
+  <si>
     <t>Ittihad Tanger</t>
   </si>
   <si>
-    <t>Arsenal Tivat</t>
-  </si>
-  <si>
     <t>Vysočina Jihlava</t>
   </si>
   <si>
-    <t>Dečić</t>
-  </si>
-  <si>
-    <t>Parma</t>
-  </si>
-  <si>
     <t>Mladost DG</t>
   </si>
   <si>
     <t>Dinamo Bucureşti</t>
   </si>
   <si>
-    <t>Panevėžys</t>
-  </si>
-  <si>
     <t>Al Riyadh</t>
   </si>
   <si>
+    <t>07 Vestur</t>
+  </si>
+  <si>
     <t>Skála</t>
   </si>
   <si>
+    <t>Slaven Koprivnica</t>
+  </si>
+  <si>
     <t>Dobrudzha 1919</t>
   </si>
   <si>
-    <t>07 Vestur</t>
-  </si>
-  <si>
-    <t>Slaven Koprivnica</t>
+    <t>AEK Athens</t>
+  </si>
+  <si>
+    <t>Antofagasta</t>
+  </si>
+  <si>
+    <t>Real Oviedo</t>
+  </si>
+  <si>
+    <t>Spartak Subotica</t>
+  </si>
+  <si>
+    <t>IMT Novi Beograd</t>
+  </si>
+  <si>
+    <t>Lokomotiv Moskva</t>
+  </si>
+  <si>
+    <t>Kansas City</t>
+  </si>
+  <si>
+    <t>Olympiakos Piraeus</t>
+  </si>
+  <si>
+    <t>Radnički Niš</t>
+  </si>
+  <si>
+    <t>Córdoba</t>
+  </si>
+  <si>
+    <t>Bačka Topola</t>
+  </si>
+  <si>
+    <t>Mirandés</t>
+  </si>
+  <si>
+    <t>Copiapó</t>
   </si>
   <si>
     <t>Union Saint-Gilloise</t>
   </si>
   <si>
-    <t>Radnički Niš</t>
-  </si>
-  <si>
-    <t>Real Oviedo</t>
-  </si>
-  <si>
     <t>Jablonec</t>
   </si>
   <si>
-    <t>Bačka Topola</t>
-  </si>
-  <si>
-    <t>Spartak Subotica</t>
-  </si>
-  <si>
-    <t>AEK Athens</t>
-  </si>
-  <si>
-    <t>Antofagasta</t>
-  </si>
-  <si>
-    <t>Olympiakos Piraeus</t>
-  </si>
-  <si>
-    <t>IMT Novi Beograd</t>
-  </si>
-  <si>
-    <t>Kansas City</t>
-  </si>
-  <si>
-    <t>Lokomotiv Moskva</t>
-  </si>
-  <si>
-    <t>Córdoba</t>
-  </si>
-  <si>
-    <t>Mirandés</t>
-  </si>
-  <si>
-    <t>Copiapó</t>
+    <t>Hapoel Haifa</t>
+  </si>
+  <si>
+    <t>Ironi Tiberias</t>
+  </si>
+  <si>
+    <t>Hapoel Katamon</t>
+  </si>
+  <si>
+    <t>Tenerife W</t>
+  </si>
+  <si>
+    <t>Békéscsaba</t>
+  </si>
+  <si>
+    <t>Dinamo Batumi</t>
+  </si>
+  <si>
+    <t>Csákvári TK</t>
   </si>
   <si>
     <t>KA</t>
   </si>
   <si>
-    <t>Tenerife W</t>
-  </si>
-  <si>
-    <t>Dinamo Batumi</t>
-  </si>
-  <si>
-    <t>Ironi Tiberias</t>
-  </si>
-  <si>
-    <t>Hapoel Katamon</t>
-  </si>
-  <si>
-    <t>Hapoel Haifa</t>
-  </si>
-  <si>
-    <t>Békéscsaba</t>
-  </si>
-  <si>
-    <t>Csákvári TK</t>
-  </si>
-  <si>
     <t>KRC Genk</t>
   </si>
   <si>
+    <t>Hoffenheim II</t>
+  </si>
+  <si>
     <t>Mainz 05</t>
   </si>
   <si>
-    <t>Hoffenheim II</t>
+    <t>New England II</t>
   </si>
   <si>
     <t>Al Ittihad</t>
@@ -1204,64 +1207,64 @@
     <t>UTS Rabat</t>
   </si>
   <si>
-    <t>New England II</t>
-  </si>
-  <si>
     <t>CODM Meknès</t>
   </si>
   <si>
+    <t>Varzim</t>
+  </si>
+  <si>
     <t>Chacarita Juniors</t>
   </si>
   <si>
-    <t>Varzim</t>
-  </si>
-  <si>
     <t>AC Milan</t>
   </si>
   <si>
+    <t>Angers SCO</t>
+  </si>
+  <si>
     <t>Club Atlético Güemes</t>
   </si>
   <si>
+    <t>Atlético Mineiro</t>
+  </si>
+  <si>
+    <t>Le Havre</t>
+  </si>
+  <si>
+    <t>Metz</t>
+  </si>
+  <si>
+    <t>Monaco</t>
+  </si>
+  <si>
+    <t>Agropecuario</t>
+  </si>
+  <si>
     <t>Remo</t>
   </si>
   <si>
+    <t>Independiente Petrolero</t>
+  </si>
+  <si>
+    <t>Náutico</t>
+  </si>
+  <si>
+    <t>Toulouse</t>
+  </si>
+  <si>
+    <t>FC Barcelona</t>
+  </si>
+  <si>
+    <t>PSG</t>
+  </si>
+  <si>
+    <t>Auxerre</t>
+  </si>
+  <si>
     <t>Rennes</t>
   </si>
   <si>
-    <t>Auxerre</t>
-  </si>
-  <si>
-    <t>FC Barcelona</t>
-  </si>
-  <si>
-    <t>Atlético Mineiro</t>
-  </si>
-  <si>
-    <t>Toulouse</t>
-  </si>
-  <si>
-    <t>Angers SCO</t>
-  </si>
-  <si>
-    <t>Independiente Petrolero</t>
-  </si>
-  <si>
-    <t>Le Havre</t>
-  </si>
-  <si>
-    <t>Agropecuario</t>
-  </si>
-  <si>
-    <t>Metz</t>
-  </si>
-  <si>
-    <t>Monaco</t>
-  </si>
-  <si>
-    <t>Náutico</t>
-  </si>
-  <si>
-    <t>PSG</t>
+    <t>Chaco For Ever</t>
   </si>
   <si>
     <t>San Martín San Juan</t>
@@ -1270,55 +1273,55 @@
     <t>Godoy Cruz</t>
   </si>
   <si>
-    <t>Chaco For Ever</t>
+    <t>Hassania Agadir</t>
+  </si>
+  <si>
+    <t>Bay</t>
+  </si>
+  <si>
+    <t>Los Angeles II</t>
+  </si>
+  <si>
+    <t>Central Norte</t>
   </si>
   <si>
     <t>Portland Timbers II</t>
   </si>
   <si>
-    <t>Central Norte</t>
-  </si>
-  <si>
-    <t>Hassania Agadir</t>
-  </si>
-  <si>
-    <t>Los Angeles II</t>
-  </si>
-  <si>
-    <t>Bay</t>
+    <t>New York City</t>
   </si>
   <si>
     <t>CS Emelec</t>
   </si>
   <si>
-    <t>New York City</t>
-  </si>
-  <si>
     <t>Colón</t>
   </si>
   <si>
     <t>The Strongest</t>
   </si>
   <si>
+    <t>Avaí</t>
+  </si>
+  <si>
+    <t>Santos</t>
+  </si>
+  <si>
+    <t>Corinthians</t>
+  </si>
+  <si>
     <t>Mirassol</t>
   </si>
   <si>
-    <t>Avaí</t>
-  </si>
-  <si>
-    <t>Santos</t>
-  </si>
-  <si>
-    <t>Corinthians</t>
-  </si>
-  <si>
     <t>FC Cincinnati II</t>
   </si>
   <si>
+    <t>Grêmio</t>
+  </si>
+  <si>
     <t>Novorizontino</t>
   </si>
   <si>
-    <t>Grêmio</t>
+    <t>Seattle Reign</t>
   </si>
   <si>
     <t>Minnesota United</t>
@@ -1327,9 +1330,6 @@
     <t>Atlanta United II</t>
   </si>
   <si>
-    <t>Seattle Reign</t>
-  </si>
-  <si>
     <t>Manta FC</t>
   </si>
   <si>
@@ -1351,28 +1351,31 @@
     <t>Jeonnam Dragons</t>
   </si>
   <si>
+    <t>Sydney II</t>
+  </si>
+  <si>
     <t>Bucheon 1995</t>
   </si>
   <si>
-    <t>Sydney II</t>
-  </si>
-  <si>
     <t>St. George Saints</t>
   </si>
   <si>
     <t>Sydney United</t>
   </si>
   <si>
+    <t>Guangxi Hengchen</t>
+  </si>
+  <si>
     <t>Rotor Volgograd</t>
   </si>
   <si>
-    <t>Guangxi Hengchen</t>
+    <t>Shanghai Jiading</t>
   </si>
   <si>
     <t>Guangzhou E-Power</t>
   </si>
   <si>
-    <t>Shanghai Jiading</t>
+    <t>Yongin City</t>
   </si>
   <si>
     <t>Jeonbuk Motors</t>
@@ -1381,198 +1384,195 @@
     <t>Cheonan City</t>
   </si>
   <si>
-    <t>Yongin City</t>
+    <t>Táborsko</t>
   </si>
   <si>
     <t>Sparta Praha II</t>
   </si>
   <si>
-    <t>Táborsko</t>
-  </si>
-  <si>
     <t>Persijap</t>
   </si>
   <si>
     <t>Persib</t>
   </si>
   <si>
+    <t>Wuhan Three Towns</t>
+  </si>
+  <si>
     <t>Krylya Sovetov</t>
   </si>
   <si>
-    <t>Wuhan Three Towns</t>
+    <t>Kairat</t>
+  </si>
+  <si>
+    <t>Logroño W</t>
+  </si>
+  <si>
+    <t>Sidama Bunna</t>
   </si>
   <si>
     <t>União Santarém</t>
   </si>
   <si>
+    <t>Górnik Łęczna</t>
+  </si>
+  <si>
+    <t>Spartak Kostroma</t>
+  </si>
+  <si>
     <t>Shandong Luneng</t>
   </si>
   <si>
     <t>Gimhae City</t>
   </si>
   <si>
-    <t>Kairat</t>
-  </si>
-  <si>
     <t>Pho Hien</t>
   </si>
   <si>
-    <t>Sidama Bunna</t>
-  </si>
-  <si>
-    <t>Logroño W</t>
-  </si>
-  <si>
-    <t>Górnik Łęczna</t>
-  </si>
-  <si>
-    <t>Spartak Kostroma</t>
-  </si>
-  <si>
     <t>GKS Katowice</t>
   </si>
   <si>
     <t>Como</t>
   </si>
   <si>
+    <t>Ratchaburi</t>
+  </si>
+  <si>
     <t>Prachuap</t>
   </si>
   <si>
+    <t>Song Lam Nghe An</t>
+  </si>
+  <si>
+    <t>Hebei Kungfu</t>
+  </si>
+  <si>
+    <t>Viettel</t>
+  </si>
+  <si>
+    <t>Nakhon Ratchasima</t>
+  </si>
+  <si>
+    <t>Ordabasy</t>
+  </si>
+  <si>
+    <t>Uthai Thani</t>
+  </si>
+  <si>
+    <t>Lamphun Warrior</t>
+  </si>
+  <si>
+    <t>Port FC</t>
+  </si>
+  <si>
+    <t>Rosengard Women</t>
+  </si>
+  <si>
+    <t>Rangers</t>
+  </si>
+  <si>
+    <t>Yunnan Yukun</t>
+  </si>
+  <si>
+    <t>Bangkok United</t>
+  </si>
+  <si>
     <t>Muang Thong United</t>
   </si>
   <si>
-    <t>Rangers</t>
-  </si>
-  <si>
-    <t>Viettel</t>
-  </si>
-  <si>
-    <t>Rosengard Women</t>
-  </si>
-  <si>
-    <t>Song Lam Nghe An</t>
-  </si>
-  <si>
-    <t>Nakhon Ratchasima</t>
-  </si>
-  <si>
-    <t>Ratchaburi</t>
-  </si>
-  <si>
-    <t>Yunnan Yukun</t>
-  </si>
-  <si>
-    <t>Bangkok United</t>
-  </si>
-  <si>
-    <t>Lamphun Warrior</t>
-  </si>
-  <si>
-    <t>Uthai Thani</t>
-  </si>
-  <si>
-    <t>Ordabasy</t>
-  </si>
-  <si>
-    <t>Hebei Kungfu</t>
-  </si>
-  <si>
-    <t>Port FC</t>
-  </si>
-  <si>
     <t>Slavia Sofia</t>
   </si>
   <si>
     <t>Žalgiris</t>
   </si>
   <si>
+    <t>Schweinfurt</t>
+  </si>
+  <si>
+    <t>Mohammedan</t>
+  </si>
+  <si>
+    <t>Tallinna FC Flora</t>
+  </si>
+  <si>
+    <t>Elversberg</t>
+  </si>
+  <si>
     <t>Darmstadt 98</t>
   </si>
   <si>
-    <t>Mohammedan</t>
-  </si>
-  <si>
-    <t>Tallinna FC Flora</t>
-  </si>
-  <si>
     <t>Greuther Fürth</t>
   </si>
   <si>
-    <t>Schweinfurt</t>
-  </si>
-  <si>
-    <t>Elversberg</t>
+    <t>Suzhou Dongwu</t>
   </si>
   <si>
     <t>Albirex Niigata S</t>
   </si>
   <si>
+    <t>RSC Anderlecht</t>
+  </si>
+  <si>
+    <t>Wuxi Wugou</t>
+  </si>
+  <si>
     <t>Tampines Rovers</t>
   </si>
   <si>
-    <t>Suzhou Dongwu</t>
-  </si>
-  <si>
-    <t>Wuxi Wugou</t>
-  </si>
-  <si>
-    <t>RSC Anderlecht</t>
+    <t>Tianjin Teda</t>
   </si>
   <si>
     <t>Shanghai SIPG</t>
   </si>
   <si>
-    <t>Tianjin Teda</t>
-  </si>
-  <si>
     <t>Opatija</t>
   </si>
   <si>
+    <t>Fredericia</t>
+  </si>
+  <si>
+    <t>Welwalo Adigrat Uni</t>
+  </si>
+  <si>
+    <t>FK Sochi</t>
+  </si>
+  <si>
+    <t>Halmstad</t>
+  </si>
+  <si>
     <t>Kaisar</t>
   </si>
   <si>
-    <t>Fredericia</t>
-  </si>
-  <si>
-    <t>Welwalo Adigrat Uni</t>
-  </si>
-  <si>
-    <t>Halmstad</t>
+    <t>St. Gallen</t>
   </si>
   <si>
     <t>Dalian Zhixing</t>
   </si>
   <si>
+    <t>Midtjylland</t>
+  </si>
+  <si>
+    <t>Dila</t>
+  </si>
+  <si>
+    <t>Villarreal</t>
+  </si>
+  <si>
+    <t>Malut United</t>
+  </si>
+  <si>
+    <t>UD Las Palmas</t>
+  </si>
+  <si>
     <t>Djurgården</t>
   </si>
   <si>
-    <t>UD Las Palmas</t>
-  </si>
-  <si>
-    <t>Villarreal</t>
-  </si>
-  <si>
-    <t>Dila</t>
-  </si>
-  <si>
-    <t>Midtjylland</t>
-  </si>
-  <si>
-    <t>FK Sochi</t>
-  </si>
-  <si>
-    <t>St. Gallen</t>
-  </si>
-  <si>
-    <t>Malut United</t>
+    <t>Nam Dinh</t>
   </si>
   <si>
     <t>Negeri Sembilan</t>
   </si>
   <si>
-    <t>Nam Dinh</t>
-  </si>
-  <si>
     <t>Ústí nad Labem</t>
   </si>
   <si>
@@ -1585,163 +1585,217 @@
     <t>Motor Lublin</t>
   </si>
   <si>
+    <t>Vittsjö</t>
+  </si>
+  <si>
+    <t>Everton</t>
+  </si>
+  <si>
+    <t>Pisa</t>
+  </si>
+  <si>
+    <t>Bohemians 1905</t>
+  </si>
+  <si>
+    <t>Karviná</t>
+  </si>
+  <si>
+    <t>Kyzyl-Zhar</t>
+  </si>
+  <si>
+    <t>Karvan FK</t>
+  </si>
+  <si>
+    <t>Johor Darul Ta'zim</t>
+  </si>
+  <si>
+    <t>Mura</t>
+  </si>
+  <si>
+    <t>Petrolul 52</t>
+  </si>
+  <si>
+    <t>Genoa</t>
+  </si>
+  <si>
+    <t>Aston Villa</t>
+  </si>
+  <si>
+    <t>Welayta Dicha</t>
+  </si>
+  <si>
     <t>Newcastle United</t>
   </si>
   <si>
-    <t>Everton</t>
-  </si>
-  <si>
-    <t>Kyzyl-Zhar</t>
-  </si>
-  <si>
-    <t>Johor Darul Ta'zim</t>
-  </si>
-  <si>
-    <t>Karviná</t>
-  </si>
-  <si>
-    <t>Aston Villa</t>
-  </si>
-  <si>
-    <t>Karvan FK</t>
-  </si>
-  <si>
-    <t>Petrolul 52</t>
-  </si>
-  <si>
-    <t>Welayta Dicha</t>
-  </si>
-  <si>
-    <t>Pisa</t>
-  </si>
-  <si>
-    <t>Bohemians 1905</t>
-  </si>
-  <si>
-    <t>Vittsjö</t>
-  </si>
-  <si>
-    <t>Genoa</t>
-  </si>
-  <si>
-    <t>Mura</t>
-  </si>
-  <si>
     <t>Freiburg</t>
   </si>
   <si>
     <t>Septemvri Sofia</t>
   </si>
   <si>
+    <t>OFI</t>
+  </si>
+  <si>
+    <t>KÍ</t>
+  </si>
+  <si>
+    <t>Sporting Charleroi</t>
+  </si>
+  <si>
     <t>Istra 1961</t>
   </si>
   <si>
+    <t>Paide</t>
+  </si>
+  <si>
     <t>Víkingur</t>
   </si>
   <si>
-    <t>KÍ</t>
+    <t>TransINVEST Vilnius</t>
+  </si>
+  <si>
+    <t>Chennaiyin</t>
   </si>
   <si>
     <t>København</t>
   </si>
   <si>
-    <t>Sporting Charleroi</t>
-  </si>
-  <si>
-    <t>Chennaiyin</t>
-  </si>
-  <si>
     <t>Vasas</t>
   </si>
   <si>
     <t>Levadiakos</t>
   </si>
   <si>
-    <t>TransINVEST Vilnius</t>
-  </si>
-  <si>
-    <t>Paide</t>
-  </si>
-  <si>
-    <t>OFI</t>
-  </si>
-  <si>
     <t>Racing Santander</t>
   </si>
   <si>
+    <t>Valencia CF</t>
+  </si>
+  <si>
     <t>Makhachkala</t>
   </si>
   <si>
-    <t>Valencia CF</t>
+    <t>Malmö FF</t>
   </si>
   <si>
     <t>Thun</t>
   </si>
   <si>
+    <t>Basel</t>
+  </si>
+  <si>
+    <t>Volga Ulyanovsk</t>
+  </si>
+  <si>
     <t>Alemannia Aachen</t>
   </si>
   <si>
-    <t>Volga Ulyanovsk</t>
-  </si>
-  <si>
-    <t>Malmö FF</t>
-  </si>
-  <si>
-    <t>Basel</t>
-  </si>
-  <si>
     <t>PSV</t>
   </si>
   <si>
+    <t>Heracles</t>
+  </si>
+  <si>
+    <t>NEC</t>
+  </si>
+  <si>
+    <t>Utrecht</t>
+  </si>
+  <si>
+    <t>Sparta Rotterdam</t>
+  </si>
+  <si>
+    <t>Heerenveen</t>
+  </si>
+  <si>
+    <t>PEC Zwolle</t>
+  </si>
+  <si>
+    <t>AZ</t>
+  </si>
+  <si>
     <t>Volendam</t>
   </si>
   <si>
-    <t>Utrecht</t>
-  </si>
-  <si>
-    <t>NEC</t>
-  </si>
-  <si>
-    <t>AZ</t>
-  </si>
-  <si>
-    <t>PEC Zwolle</t>
-  </si>
-  <si>
-    <t>Sparta Rotterdam</t>
-  </si>
-  <si>
-    <t>Heerenveen</t>
-  </si>
-  <si>
-    <t>Heracles</t>
+    <t>AEK Larnaca</t>
+  </si>
+  <si>
+    <t>Strømsgodset</t>
+  </si>
+  <si>
+    <t>Austria Wien</t>
+  </si>
+  <si>
+    <t>Bryne</t>
+  </si>
+  <si>
+    <t>Stal Rzeszów</t>
+  </si>
+  <si>
+    <t>Kristiansund</t>
   </si>
   <si>
     <t>Viking</t>
   </si>
   <si>
+    <t>Sturm Graz</t>
+  </si>
+  <si>
+    <t>Salzburg</t>
+  </si>
+  <si>
+    <t>Tikveš</t>
+  </si>
+  <si>
+    <t>Shkupi</t>
+  </si>
+  <si>
+    <t>FK Bashkimi Kumanovo</t>
+  </si>
+  <si>
+    <t>Hødd</t>
+  </si>
+  <si>
+    <t>Vlašim</t>
+  </si>
+  <si>
+    <t>Atletico Madrid W</t>
+  </si>
+  <si>
     <t>Haugesund</t>
   </si>
   <si>
-    <t>Bryne</t>
-  </si>
-  <si>
-    <t>Vlašim</t>
-  </si>
-  <si>
-    <t>Kristiansund</t>
-  </si>
-  <si>
-    <t>Atletico Madrid W</t>
+    <t>Molde</t>
+  </si>
+  <si>
+    <t>Struga</t>
+  </si>
+  <si>
+    <t>Sileks</t>
+  </si>
+  <si>
+    <t>Stabæk</t>
+  </si>
+  <si>
+    <t>Jarun</t>
+  </si>
+  <si>
+    <t>Mezőkövesd-Zsóry</t>
+  </si>
+  <si>
+    <t>Lyn</t>
+  </si>
+  <si>
+    <t>Fasil Ketema</t>
+  </si>
+  <si>
+    <t>Rabotnički</t>
   </si>
   <si>
     <t>BVSC</t>
   </si>
   <si>
-    <t>Sturm Graz</t>
-  </si>
-  <si>
-    <t>Salzburg</t>
+    <t>Szeged 2011</t>
   </si>
   <si>
     <t>Torpedo Kutaisi</t>
@@ -1753,214 +1807,163 @@
     <t>Videoton</t>
   </si>
   <si>
-    <t>Hødd</t>
-  </si>
-  <si>
-    <t>Strømsgodset</t>
-  </si>
-  <si>
-    <t>Szeged 2011</t>
-  </si>
-  <si>
-    <t>Rabotnički</t>
-  </si>
-  <si>
-    <t>Fasil Ketema</t>
-  </si>
-  <si>
-    <t>Mezőkövesd-Zsóry</t>
-  </si>
-  <si>
-    <t>AEK Larnaca</t>
-  </si>
-  <si>
-    <t>Struga</t>
-  </si>
-  <si>
-    <t>Sileks</t>
-  </si>
-  <si>
-    <t>Stal Rzeszów</t>
-  </si>
-  <si>
-    <t>Austria Wien</t>
-  </si>
-  <si>
-    <t>Lyn</t>
-  </si>
-  <si>
-    <t>FK Bashkimi Kumanovo</t>
-  </si>
-  <si>
-    <t>Shkupi</t>
-  </si>
-  <si>
-    <t>Molde</t>
-  </si>
-  <si>
     <t>APOEL</t>
   </si>
   <si>
-    <t>Jarun</t>
-  </si>
-  <si>
-    <t>Stabæk</t>
-  </si>
-  <si>
-    <t>Tikveš</t>
+    <t>Al Dhafra</t>
+  </si>
+  <si>
+    <t>Shabab Al Ahli Dubai</t>
+  </si>
+  <si>
+    <t>Al Sharjah</t>
   </si>
   <si>
     <t>Ajman</t>
   </si>
   <si>
-    <t>Shabab Al Ahli Dubai</t>
-  </si>
-  <si>
-    <t>Al Sharjah</t>
-  </si>
-  <si>
-    <t>Al Dhafra</t>
+    <t>İnter Bakı</t>
   </si>
   <si>
     <t>Heidenheim</t>
   </si>
   <si>
+    <t>Arsenal</t>
+  </si>
+  <si>
     <t>Legia Warszawa</t>
   </si>
   <si>
-    <t>Arsenal</t>
-  </si>
-  <si>
     <t>Kaizer Chiefs</t>
   </si>
   <si>
-    <t>İnter Bakı</t>
+    <t>AGF</t>
+  </si>
+  <si>
+    <t>Sutjeska</t>
   </si>
   <si>
     <t>Budućnost</t>
   </si>
   <si>
-    <t>AGF</t>
+    <t>Kauno Žalgiris</t>
+  </si>
+  <si>
+    <t>FK Jezero Plav</t>
   </si>
   <si>
     <t>Bokelj</t>
   </si>
   <si>
+    <t>Roma</t>
+  </si>
+  <si>
     <t>Difaâ El Jadida</t>
   </si>
   <si>
-    <t>Sutjeska</t>
-  </si>
-  <si>
     <t>Hanácká</t>
   </si>
   <si>
-    <t>FK Jezero Plav</t>
-  </si>
-  <si>
-    <t>Roma</t>
-  </si>
-  <si>
     <t>Petrovac</t>
   </si>
   <si>
     <t>Argeș</t>
   </si>
   <si>
-    <t>Kauno Žalgiris</t>
-  </si>
-  <si>
     <t>Al Fateh</t>
   </si>
   <si>
+    <t>B68</t>
+  </si>
+  <si>
     <t>AB</t>
   </si>
   <si>
+    <t>Gorica</t>
+  </si>
+  <si>
     <t>Beroe</t>
   </si>
   <si>
-    <t>B68</t>
-  </si>
-  <si>
-    <t>Gorica</t>
+    <t>Panathinaikos</t>
+  </si>
+  <si>
+    <t>San Luis</t>
+  </si>
+  <si>
+    <t>Getafe CF</t>
+  </si>
+  <si>
+    <t>Napredak</t>
+  </si>
+  <si>
+    <t>Radnički Kragujevac</t>
+  </si>
+  <si>
+    <t>Baltika</t>
+  </si>
+  <si>
+    <t>Chicago Red Stars</t>
+  </si>
+  <si>
+    <t>PAOK</t>
+  </si>
+  <si>
+    <t>LFK Mladost Lučani</t>
+  </si>
+  <si>
+    <t>Granada CF</t>
+  </si>
+  <si>
+    <t>Javor Ivanjica</t>
+  </si>
+  <si>
+    <t>SD Eibar</t>
+  </si>
+  <si>
+    <t>Unión San Felipe</t>
   </si>
   <si>
     <t>KV Mechelen</t>
   </si>
   <si>
-    <t>LFK Mladost Lučani</t>
-  </si>
-  <si>
-    <t>Getafe CF</t>
-  </si>
-  <si>
     <t>Hradec Králové</t>
   </si>
   <si>
-    <t>Javor Ivanjica</t>
-  </si>
-  <si>
-    <t>Napredak</t>
-  </si>
-  <si>
-    <t>Panathinaikos</t>
-  </si>
-  <si>
-    <t>San Luis</t>
-  </si>
-  <si>
-    <t>PAOK</t>
-  </si>
-  <si>
-    <t>Radnički Kragujevac</t>
-  </si>
-  <si>
-    <t>Chicago Red Stars</t>
-  </si>
-  <si>
-    <t>Baltika</t>
-  </si>
-  <si>
-    <t>Granada CF</t>
-  </si>
-  <si>
-    <t>SD Eibar</t>
-  </si>
-  <si>
-    <t>Unión San Felipe</t>
+    <t>Ashdod</t>
+  </si>
+  <si>
+    <t>Maccabi Netanya</t>
+  </si>
+  <si>
+    <t>Bnei Sakhnin</t>
+  </si>
+  <si>
+    <t>Barcelona W</t>
+  </si>
+  <si>
+    <t>Kozármisleny</t>
+  </si>
+  <si>
+    <t>Samgurali</t>
+  </si>
+  <si>
+    <t>Soroksár SC</t>
   </si>
   <si>
     <t>ÍBV</t>
   </si>
   <si>
-    <t>Barcelona W</t>
-  </si>
-  <si>
-    <t>Samgurali</t>
-  </si>
-  <si>
-    <t>Maccabi Netanya</t>
-  </si>
-  <si>
-    <t>Bnei Sakhnin</t>
-  </si>
-  <si>
-    <t>Ashdod</t>
-  </si>
-  <si>
-    <t>Kozármisleny</t>
-  </si>
-  <si>
-    <t>Soroksár SC</t>
-  </si>
-  <si>
     <t>KVC Westerlo</t>
   </si>
   <si>
+    <t>Saarbrucken</t>
+  </si>
+  <si>
     <t>Union Berlin</t>
   </si>
   <si>
-    <t>Saarbrucken</t>
+    <t>New York City II</t>
   </si>
   <si>
     <t>Dhamk</t>
@@ -1969,64 +1972,64 @@
     <t>Maghreb Fès</t>
   </si>
   <si>
-    <t>New York City II</t>
-  </si>
-  <si>
     <t>RSB Berkane</t>
   </si>
   <si>
+    <t>CF Os Belenenses</t>
+  </si>
+  <si>
     <t>Colegiales</t>
   </si>
   <si>
-    <t>CF Os Belenenses</t>
-  </si>
-  <si>
     <t>Atalanta</t>
   </si>
   <si>
+    <t>Strasbourg</t>
+  </si>
+  <si>
     <t>Quilmes</t>
   </si>
   <si>
+    <t>Botafogo</t>
+  </si>
+  <si>
+    <t>Olympique Marseille</t>
+  </si>
+  <si>
+    <t>Lorient</t>
+  </si>
+  <si>
+    <t>Lille</t>
+  </si>
+  <si>
+    <t>Atlanta</t>
+  </si>
+  <si>
     <t>Palmeiras</t>
   </si>
   <si>
+    <t>Club Always Ready</t>
+  </si>
+  <si>
+    <t>América Mineiro</t>
+  </si>
+  <si>
+    <t>Olympique Lyonnais</t>
+  </si>
+  <si>
+    <t>Real Madrid</t>
+  </si>
+  <si>
+    <t>Brest</t>
+  </si>
+  <si>
+    <t>Nice</t>
+  </si>
+  <si>
     <t>Paris</t>
   </si>
   <si>
-    <t>Nice</t>
-  </si>
-  <si>
-    <t>Real Madrid</t>
-  </si>
-  <si>
-    <t>Botafogo</t>
-  </si>
-  <si>
-    <t>Olympique Lyonnais</t>
-  </si>
-  <si>
-    <t>Strasbourg</t>
-  </si>
-  <si>
-    <t>Club Always Ready</t>
-  </si>
-  <si>
-    <t>Olympique Marseille</t>
-  </si>
-  <si>
-    <t>Atlanta</t>
-  </si>
-  <si>
-    <t>Lorient</t>
-  </si>
-  <si>
-    <t>Lille</t>
-  </si>
-  <si>
-    <t>América Mineiro</t>
-  </si>
-  <si>
-    <t>Brest</t>
+    <t>Ciudad de Bolívar</t>
   </si>
   <si>
     <t>Patronato</t>
@@ -2035,64 +2038,61 @@
     <t>Racing Córdoba</t>
   </si>
   <si>
-    <t>Ciudad de Bolívar</t>
+    <t>FAR Rabat</t>
+  </si>
+  <si>
+    <t>Utah Royals</t>
+  </si>
+  <si>
+    <t>Real Monarchs</t>
+  </si>
+  <si>
+    <t>Deportivo Madryn</t>
   </si>
   <si>
     <t>LA Galaxy II</t>
   </si>
   <si>
-    <t>Deportivo Madryn</t>
-  </si>
-  <si>
-    <t>FAR Rabat</t>
-  </si>
-  <si>
-    <t>Real Monarchs</t>
-  </si>
-  <si>
-    <t>Utah Royals</t>
+    <t>Columbus Crew</t>
   </si>
   <si>
     <t>Libertad</t>
   </si>
   <si>
-    <t>Columbus Crew</t>
-  </si>
-  <si>
     <t>All Boys</t>
   </si>
   <si>
     <t>Real Potosí</t>
   </si>
   <si>
+    <t>Fortaleza</t>
+  </si>
+  <si>
+    <t>Bragantino</t>
+  </si>
+  <si>
+    <t>São Paulo</t>
+  </si>
+  <si>
     <t>Chapecoense</t>
   </si>
   <si>
-    <t>Fortaleza</t>
-  </si>
-  <si>
-    <t>Bragantino</t>
-  </si>
-  <si>
-    <t>São Paulo</t>
-  </si>
-  <si>
     <t>Columbus Crew II</t>
   </si>
   <si>
+    <t>Flamengo</t>
+  </si>
+  <si>
     <t>Botafogo SP</t>
   </si>
   <si>
-    <t>Flamengo</t>
+    <t>Washington Spirit</t>
   </si>
   <si>
     <t>Austin</t>
   </si>
   <si>
     <t>Orlando City II</t>
-  </si>
-  <si>
-    <t>Washington Spirit</t>
   </si>
   <si>
     <t>Macará</t>
@@ -3228,7 +3228,7 @@
         <v>61</v>
       </c>
       <c r="C5" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D5" t="s">
         <v>185</v>
@@ -3413,7 +3413,7 @@
         <v>62</v>
       </c>
       <c r="C6" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D6" t="s">
         <v>185</v>
@@ -3601,7 +3601,7 @@
         <v>118</v>
       </c>
       <c r="D7" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E7" t="s">
         <v>193</v>
@@ -3786,7 +3786,7 @@
         <v>119</v>
       </c>
       <c r="D8" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E8" t="s">
         <v>194</v>
@@ -3968,7 +3968,7 @@
         <v>63</v>
       </c>
       <c r="C9" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D9" t="s">
         <v>185</v>
@@ -4153,7 +4153,7 @@
         <v>63</v>
       </c>
       <c r="C10" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D10" t="s">
         <v>185</v>
@@ -4338,7 +4338,7 @@
         <v>64</v>
       </c>
       <c r="C11" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D11" t="s">
         <v>185</v>
@@ -4377,13 +4377,13 @@
         <v>699</v>
       </c>
       <c r="P11">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="Q11">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="R11">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="S11">
         <v>0</v>
@@ -4523,7 +4523,7 @@
         <v>64</v>
       </c>
       <c r="C12" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="D12" t="s">
         <v>185</v>
@@ -4562,13 +4562,13 @@
         <v>699</v>
       </c>
       <c r="P12">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="Q12">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="R12">
-        <v>4.67</v>
+        <v>0</v>
       </c>
       <c r="S12">
         <v>0</v>
@@ -4607,10 +4607,10 @@
         <v>0</v>
       </c>
       <c r="AE12">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AF12">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AG12">
         <v>0</v>
@@ -4747,13 +4747,13 @@
         <v>699</v>
       </c>
       <c r="P13">
-        <v>3.65</v>
+        <v>1.63</v>
       </c>
       <c r="Q13">
-        <v>3.32</v>
+        <v>3.7</v>
       </c>
       <c r="R13">
-        <v>1.91</v>
+        <v>4.67</v>
       </c>
       <c r="S13">
         <v>0</v>
@@ -4792,10 +4792,10 @@
         <v>0</v>
       </c>
       <c r="AE13">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AF13">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AG13">
         <v>0</v>
@@ -5636,7 +5636,7 @@
         <v>122</v>
       </c>
       <c r="D18" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E18" t="s">
         <v>204</v>
@@ -5672,13 +5672,13 @@
         <v>699</v>
       </c>
       <c r="P18">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="Q18">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="R18">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="S18">
         <v>0</v>
@@ -5821,7 +5821,7 @@
         <v>123</v>
       </c>
       <c r="D19" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E19" t="s">
         <v>205</v>
@@ -5857,13 +5857,13 @@
         <v>699</v>
       </c>
       <c r="P19">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="Q19">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="R19">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="S19">
         <v>0</v>
@@ -6006,7 +6006,7 @@
         <v>124</v>
       </c>
       <c r="D20" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E20" t="s">
         <v>206</v>
@@ -6188,10 +6188,10 @@
         <v>68</v>
       </c>
       <c r="C21" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="D21" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E21" t="s">
         <v>207</v>
@@ -6373,10 +6373,10 @@
         <v>68</v>
       </c>
       <c r="C22" t="s">
-        <v>115</v>
+        <v>126</v>
       </c>
       <c r="D22" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E22" t="s">
         <v>208</v>
@@ -6412,13 +6412,13 @@
         <v>699</v>
       </c>
       <c r="P22">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Q22">
-        <v>3.16</v>
+        <v>0</v>
       </c>
       <c r="R22">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="S22">
         <v>0</v>
@@ -6558,10 +6558,10 @@
         <v>68</v>
       </c>
       <c r="C23" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="D23" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E23" t="s">
         <v>209</v>
@@ -6743,7 +6743,7 @@
         <v>68</v>
       </c>
       <c r="C24" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="D24" t="s">
         <v>186</v>
@@ -6928,7 +6928,7 @@
         <v>68</v>
       </c>
       <c r="C25" t="s">
-        <v>127</v>
+        <v>119</v>
       </c>
       <c r="D25" t="s">
         <v>186</v>
@@ -6967,13 +6967,13 @@
         <v>699</v>
       </c>
       <c r="P25">
-        <v>0</v>
+        <v>4.98</v>
       </c>
       <c r="Q25">
-        <v>0</v>
+        <v>3.66</v>
       </c>
       <c r="R25">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="S25">
         <v>0</v>
@@ -7113,10 +7113,10 @@
         <v>68</v>
       </c>
       <c r="C26" t="s">
-        <v>128</v>
+        <v>122</v>
       </c>
       <c r="D26" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E26" t="s">
         <v>212</v>
@@ -7298,10 +7298,10 @@
         <v>68</v>
       </c>
       <c r="C27" t="s">
-        <v>129</v>
+        <v>115</v>
       </c>
       <c r="D27" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E27" t="s">
         <v>213</v>
@@ -7337,13 +7337,13 @@
         <v>699</v>
       </c>
       <c r="P27">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Q27">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="R27">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="S27">
         <v>0</v>
@@ -7483,7 +7483,7 @@
         <v>68</v>
       </c>
       <c r="C28" t="s">
-        <v>118</v>
+        <v>129</v>
       </c>
       <c r="D28" t="s">
         <v>186</v>
@@ -7522,13 +7522,13 @@
         <v>699</v>
       </c>
       <c r="P28">
-        <v>4.98</v>
+        <v>0</v>
       </c>
       <c r="Q28">
-        <v>3.66</v>
+        <v>0</v>
       </c>
       <c r="R28">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="S28">
         <v>0</v>
@@ -8077,13 +8077,13 @@
         <v>699</v>
       </c>
       <c r="P31">
-        <v>1.78</v>
+        <v>3.32</v>
       </c>
       <c r="Q31">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="R31">
-        <v>4.35</v>
+        <v>2.03</v>
       </c>
       <c r="S31">
         <v>0</v>
@@ -8262,13 +8262,13 @@
         <v>699</v>
       </c>
       <c r="P32">
-        <v>2.44</v>
+        <v>1.78</v>
       </c>
       <c r="Q32">
-        <v>3.61</v>
+        <v>3.9</v>
       </c>
       <c r="R32">
-        <v>2.77</v>
+        <v>4.35</v>
       </c>
       <c r="S32">
         <v>0</v>
@@ -8408,7 +8408,7 @@
         <v>71</v>
       </c>
       <c r="C33" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="D33" t="s">
         <v>186</v>
@@ -8447,13 +8447,13 @@
         <v>699</v>
       </c>
       <c r="P33">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Q33">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="R33">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="S33">
         <v>0</v>
@@ -8593,10 +8593,10 @@
         <v>71</v>
       </c>
       <c r="C34" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="D34" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E34" t="s">
         <v>220</v>
@@ -8778,10 +8778,10 @@
         <v>71</v>
       </c>
       <c r="C35" t="s">
-        <v>134</v>
+        <v>129</v>
       </c>
       <c r="D35" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E35" t="s">
         <v>221</v>
@@ -8963,7 +8963,7 @@
         <v>71</v>
       </c>
       <c r="C36" t="s">
-        <v>126</v>
+        <v>132</v>
       </c>
       <c r="D36" t="s">
         <v>186</v>
@@ -9002,13 +9002,13 @@
         <v>699</v>
       </c>
       <c r="P36">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="Q36">
-        <v>0</v>
+        <v>4.18</v>
       </c>
       <c r="R36">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="S36">
         <v>0</v>
@@ -9148,10 +9148,10 @@
         <v>71</v>
       </c>
       <c r="C37" t="s">
-        <v>132</v>
+        <v>124</v>
       </c>
       <c r="D37" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E37" t="s">
         <v>223</v>
@@ -9187,13 +9187,13 @@
         <v>699</v>
       </c>
       <c r="P37">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="Q37">
-        <v>4.18</v>
+        <v>0</v>
       </c>
       <c r="R37">
-        <v>5.3</v>
+        <v>0</v>
       </c>
       <c r="S37">
         <v>0</v>
@@ -9372,13 +9372,13 @@
         <v>699</v>
       </c>
       <c r="P38">
-        <v>3.32</v>
+        <v>2.7</v>
       </c>
       <c r="Q38">
-        <v>3.95</v>
+        <v>3.36</v>
       </c>
       <c r="R38">
-        <v>2.03</v>
+        <v>2.64</v>
       </c>
       <c r="S38">
         <v>0</v>
@@ -9417,10 +9417,10 @@
         <v>0</v>
       </c>
       <c r="AE38">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AF38">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AG38">
         <v>0</v>
@@ -9518,10 +9518,10 @@
         <v>71</v>
       </c>
       <c r="C39" t="s">
-        <v>123</v>
+        <v>132</v>
       </c>
       <c r="D39" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E39" t="s">
         <v>225</v>
@@ -9557,13 +9557,13 @@
         <v>699</v>
       </c>
       <c r="P39">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="Q39">
-        <v>0</v>
+        <v>6.73</v>
       </c>
       <c r="R39">
-        <v>0</v>
+        <v>10.6</v>
       </c>
       <c r="S39">
         <v>0</v>
@@ -9742,13 +9742,13 @@
         <v>699</v>
       </c>
       <c r="P40">
-        <v>3.4</v>
+        <v>5.09</v>
       </c>
       <c r="Q40">
-        <v>3.63</v>
+        <v>4.18</v>
       </c>
       <c r="R40">
-        <v>2.09</v>
+        <v>1.64</v>
       </c>
       <c r="S40">
         <v>0</v>
@@ -9888,10 +9888,10 @@
         <v>71</v>
       </c>
       <c r="C41" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="D41" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E41" t="s">
         <v>227</v>
@@ -9927,13 +9927,13 @@
         <v>699</v>
       </c>
       <c r="P41">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="Q41">
-        <v>6.73</v>
+        <v>0</v>
       </c>
       <c r="R41">
-        <v>10.6</v>
+        <v>0</v>
       </c>
       <c r="S41">
         <v>0</v>
@@ -10073,7 +10073,7 @@
         <v>71</v>
       </c>
       <c r="C42" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="D42" t="s">
         <v>186</v>
@@ -10112,13 +10112,13 @@
         <v>699</v>
       </c>
       <c r="P42">
-        <v>2.7</v>
+        <v>2.2</v>
       </c>
       <c r="Q42">
-        <v>3.36</v>
+        <v>3.7</v>
       </c>
       <c r="R42">
-        <v>2.64</v>
+        <v>3</v>
       </c>
       <c r="S42">
         <v>0</v>
@@ -10157,10 +10157,10 @@
         <v>0</v>
       </c>
       <c r="AE42">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AF42">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AG42">
         <v>0</v>
@@ -10258,7 +10258,7 @@
         <v>71</v>
       </c>
       <c r="C43" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="D43" t="s">
         <v>185</v>
@@ -10443,10 +10443,10 @@
         <v>71</v>
       </c>
       <c r="C44" t="s">
-        <v>119</v>
+        <v>132</v>
       </c>
       <c r="D44" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E44" t="s">
         <v>230</v>
@@ -10482,13 +10482,13 @@
         <v>699</v>
       </c>
       <c r="P44">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="Q44">
-        <v>0</v>
+        <v>3.63</v>
       </c>
       <c r="R44">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="S44">
         <v>0</v>
@@ -10667,13 +10667,13 @@
         <v>699</v>
       </c>
       <c r="P45">
-        <v>5.09</v>
+        <v>2.44</v>
       </c>
       <c r="Q45">
-        <v>4.18</v>
+        <v>3.61</v>
       </c>
       <c r="R45">
-        <v>1.64</v>
+        <v>2.77</v>
       </c>
       <c r="S45">
         <v>0</v>
@@ -11222,13 +11222,13 @@
         <v>699</v>
       </c>
       <c r="P48">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="Q48">
-        <v>3.74</v>
+        <v>0</v>
       </c>
       <c r="R48">
-        <v>2.76</v>
+        <v>0</v>
       </c>
       <c r="S48">
         <v>0</v>
@@ -11738,7 +11738,7 @@
         <v>73</v>
       </c>
       <c r="C51" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="D51" t="s">
         <v>186</v>
@@ -11777,13 +11777,13 @@
         <v>699</v>
       </c>
       <c r="P51">
-        <v>1.78</v>
+        <v>2.88</v>
       </c>
       <c r="Q51">
-        <v>4.15</v>
+        <v>3.8</v>
       </c>
       <c r="R51">
-        <v>3.8</v>
+        <v>2.19</v>
       </c>
       <c r="S51">
         <v>0</v>
@@ -11828,10 +11828,10 @@
         <v>0</v>
       </c>
       <c r="AG51">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AH51">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AI51">
         <v>0</v>
@@ -11962,13 +11962,13 @@
         <v>699</v>
       </c>
       <c r="P52">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="Q52">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="R52">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="S52">
         <v>0</v>
@@ -12108,7 +12108,7 @@
         <v>73</v>
       </c>
       <c r="C53" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="D53" t="s">
         <v>186</v>
@@ -12147,14 +12147,14 @@
         <v>699</v>
       </c>
       <c r="P53">
-        <v>2.88</v>
+        <v>1.78</v>
       </c>
       <c r="Q53">
+        <v>4.15</v>
+      </c>
+      <c r="R53">
         <v>3.8</v>
       </c>
-      <c r="R53">
-        <v>2.19</v>
-      </c>
       <c r="S53">
         <v>0</v>
       </c>
@@ -12198,10 +12198,10 @@
         <v>0</v>
       </c>
       <c r="AG53">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AH53">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AI53">
         <v>0</v>
@@ -12293,10 +12293,10 @@
         <v>73</v>
       </c>
       <c r="C54" t="s">
-        <v>141</v>
+        <v>118</v>
       </c>
       <c r="D54" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="E54" t="s">
         <v>240</v>
@@ -12663,10 +12663,10 @@
         <v>73</v>
       </c>
       <c r="C56" t="s">
-        <v>119</v>
+        <v>142</v>
       </c>
       <c r="D56" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E56" t="s">
         <v>242</v>
@@ -12702,13 +12702,13 @@
         <v>699</v>
       </c>
       <c r="P56">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="Q56">
-        <v>0</v>
+        <v>3.71</v>
       </c>
       <c r="R56">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="S56">
         <v>0</v>
@@ -12848,7 +12848,7 @@
         <v>73</v>
       </c>
       <c r="C57" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D57" t="s">
         <v>185</v>
@@ -13033,10 +13033,10 @@
         <v>73</v>
       </c>
       <c r="C58" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="D58" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="E58" t="s">
         <v>244</v>
@@ -13072,13 +13072,13 @@
         <v>699</v>
       </c>
       <c r="P58">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="Q58">
-        <v>3.71</v>
+        <v>0</v>
       </c>
       <c r="R58">
-        <v>2.89</v>
+        <v>0</v>
       </c>
       <c r="S58">
         <v>0</v>
@@ -13218,7 +13218,7 @@
         <v>74</v>
       </c>
       <c r="C59" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="D59" t="s">
         <v>185</v>
@@ -13403,7 +13403,7 @@
         <v>74</v>
       </c>
       <c r="C60" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="D60" t="s">
         <v>185</v>
@@ -13773,10 +13773,10 @@
         <v>76</v>
       </c>
       <c r="C62" t="s">
-        <v>125</v>
+        <v>144</v>
       </c>
       <c r="D62" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E62" t="s">
         <v>248</v>
@@ -13812,13 +13812,13 @@
         <v>699</v>
       </c>
       <c r="P62">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="Q62">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="R62">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="S62">
         <v>0</v>
@@ -13958,7 +13958,7 @@
         <v>76</v>
       </c>
       <c r="C63" t="s">
-        <v>144</v>
+        <v>126</v>
       </c>
       <c r="D63" t="s">
         <v>186</v>
@@ -13997,13 +13997,13 @@
         <v>699</v>
       </c>
       <c r="P63">
-        <v>2.58</v>
+        <v>0</v>
       </c>
       <c r="Q63">
-        <v>3.62</v>
+        <v>0</v>
       </c>
       <c r="R63">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="S63">
         <v>0</v>
@@ -14143,7 +14143,7 @@
         <v>76</v>
       </c>
       <c r="C64" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="D64" t="s">
         <v>186</v>
@@ -14182,13 +14182,13 @@
         <v>699</v>
       </c>
       <c r="P64">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="Q64">
-        <v>0</v>
+        <v>7.41</v>
       </c>
       <c r="R64">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="S64">
         <v>0</v>
@@ -14513,7 +14513,7 @@
         <v>76</v>
       </c>
       <c r="C66" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="D66" t="s">
         <v>185</v>
@@ -14698,10 +14698,10 @@
         <v>76</v>
       </c>
       <c r="C67" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D67" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E67" t="s">
         <v>253</v>
@@ -14737,13 +14737,13 @@
         <v>699</v>
       </c>
       <c r="P67">
-        <v>2.35</v>
+        <v>2.36</v>
       </c>
       <c r="Q67">
-        <v>3.35</v>
+        <v>3.54</v>
       </c>
       <c r="R67">
-        <v>2.87</v>
+        <v>2.73</v>
       </c>
       <c r="S67">
         <v>0</v>
@@ -14883,10 +14883,10 @@
         <v>76</v>
       </c>
       <c r="C68" t="s">
-        <v>146</v>
+        <v>122</v>
       </c>
       <c r="D68" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E68" t="s">
         <v>254</v>
@@ -14922,13 +14922,13 @@
         <v>699</v>
       </c>
       <c r="P68">
-        <v>2.46</v>
+        <v>0</v>
       </c>
       <c r="Q68">
-        <v>3.43</v>
+        <v>0</v>
       </c>
       <c r="R68">
-        <v>2.91</v>
+        <v>0</v>
       </c>
       <c r="S68">
         <v>0</v>
@@ -15068,7 +15068,7 @@
         <v>76</v>
       </c>
       <c r="C69" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="D69" t="s">
         <v>186</v>
@@ -15107,13 +15107,13 @@
         <v>699</v>
       </c>
       <c r="P69">
-        <v>0</v>
+        <v>3.36</v>
       </c>
       <c r="Q69">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="R69">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="S69">
         <v>0</v>
@@ -15253,7 +15253,7 @@
         <v>76</v>
       </c>
       <c r="C70" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D70" t="s">
         <v>185</v>
@@ -15438,7 +15438,7 @@
         <v>76</v>
       </c>
       <c r="C71" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="D71" t="s">
         <v>186</v>
@@ -15477,13 +15477,13 @@
         <v>699</v>
       </c>
       <c r="P71">
-        <v>3.36</v>
+        <v>0</v>
       </c>
       <c r="Q71">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="R71">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="S71">
         <v>0</v>
@@ -15623,7 +15623,7 @@
         <v>76</v>
       </c>
       <c r="C72" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="D72" t="s">
         <v>186</v>
@@ -15662,13 +15662,13 @@
         <v>699</v>
       </c>
       <c r="P72">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="Q72">
-        <v>7.41</v>
+        <v>0</v>
       </c>
       <c r="R72">
-        <v>17.5</v>
+        <v>0</v>
       </c>
       <c r="S72">
         <v>0</v>
@@ -15847,13 +15847,13 @@
         <v>699</v>
       </c>
       <c r="P73">
-        <v>2.36</v>
+        <v>2.46</v>
       </c>
       <c r="Q73">
-        <v>3.54</v>
+        <v>3.43</v>
       </c>
       <c r="R73">
-        <v>2.73</v>
+        <v>2.91</v>
       </c>
       <c r="S73">
         <v>0</v>
@@ -15993,10 +15993,10 @@
         <v>76</v>
       </c>
       <c r="C74" t="s">
-        <v>121</v>
+        <v>145</v>
       </c>
       <c r="D74" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E74" t="s">
         <v>260</v>
@@ -16032,13 +16032,13 @@
         <v>699</v>
       </c>
       <c r="P74">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="Q74">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="R74">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="S74">
         <v>0</v>
@@ -16178,7 +16178,7 @@
         <v>77</v>
       </c>
       <c r="C75" t="s">
-        <v>150</v>
+        <v>129</v>
       </c>
       <c r="D75" t="s">
         <v>186</v>
@@ -16363,7 +16363,7 @@
         <v>77</v>
       </c>
       <c r="C76" t="s">
-        <v>126</v>
+        <v>150</v>
       </c>
       <c r="D76" t="s">
         <v>186</v>
@@ -16918,7 +16918,7 @@
         <v>78</v>
       </c>
       <c r="C79" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D79" t="s">
         <v>186</v>
@@ -17288,10 +17288,10 @@
         <v>80</v>
       </c>
       <c r="C81" t="s">
-        <v>152</v>
+        <v>133</v>
       </c>
       <c r="D81" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E81" t="s">
         <v>267</v>
@@ -17327,13 +17327,13 @@
         <v>699</v>
       </c>
       <c r="P81">
-        <v>2.46</v>
+        <v>0</v>
       </c>
       <c r="Q81">
-        <v>3.66</v>
+        <v>0</v>
       </c>
       <c r="R81">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="S81">
         <v>0</v>
@@ -17372,10 +17372,10 @@
         <v>0</v>
       </c>
       <c r="AE81">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AF81">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AG81">
         <v>0</v>
@@ -17658,10 +17658,10 @@
         <v>80</v>
       </c>
       <c r="C83" t="s">
-        <v>125</v>
+        <v>131</v>
       </c>
       <c r="D83" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E83" t="s">
         <v>269</v>
@@ -17697,13 +17697,13 @@
         <v>699</v>
       </c>
       <c r="P83">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Q83">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="R83">
-        <v>0</v>
+        <v>4.07</v>
       </c>
       <c r="S83">
         <v>0</v>
@@ -17742,10 +17742,10 @@
         <v>0</v>
       </c>
       <c r="AE83">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AF83">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AG83">
         <v>0</v>
@@ -17843,7 +17843,7 @@
         <v>80</v>
       </c>
       <c r="C84" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="D84" t="s">
         <v>186</v>
@@ -18213,10 +18213,10 @@
         <v>80</v>
       </c>
       <c r="C86" t="s">
-        <v>152</v>
+        <v>124</v>
       </c>
       <c r="D86" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E86" t="s">
         <v>272</v>
@@ -18252,13 +18252,13 @@
         <v>699</v>
       </c>
       <c r="P86">
-        <v>5.38</v>
+        <v>0</v>
       </c>
       <c r="Q86">
-        <v>4.37</v>
+        <v>0</v>
       </c>
       <c r="R86">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="S86">
         <v>0</v>
@@ -18583,7 +18583,7 @@
         <v>80</v>
       </c>
       <c r="C88" t="s">
-        <v>155</v>
+        <v>150</v>
       </c>
       <c r="D88" t="s">
         <v>186</v>
@@ -18622,13 +18622,13 @@
         <v>699</v>
       </c>
       <c r="P88">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="Q88">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="R88">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="S88">
         <v>0</v>
@@ -18768,7 +18768,7 @@
         <v>80</v>
       </c>
       <c r="C89" t="s">
-        <v>127</v>
+        <v>155</v>
       </c>
       <c r="D89" t="s">
         <v>186</v>
@@ -18807,13 +18807,13 @@
         <v>699</v>
       </c>
       <c r="P89">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="Q89">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="R89">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S89">
         <v>0</v>
@@ -18953,7 +18953,7 @@
         <v>80</v>
       </c>
       <c r="C90" t="s">
-        <v>131</v>
+        <v>156</v>
       </c>
       <c r="D90" t="s">
         <v>186</v>
@@ -18992,13 +18992,13 @@
         <v>699</v>
       </c>
       <c r="P90">
-        <v>2.1</v>
+        <v>2.21</v>
       </c>
       <c r="Q90">
-        <v>3.42</v>
+        <v>3.22</v>
       </c>
       <c r="R90">
-        <v>4.07</v>
+        <v>3.22</v>
       </c>
       <c r="S90">
         <v>0</v>
@@ -19037,10 +19037,10 @@
         <v>0</v>
       </c>
       <c r="AE90">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AF90">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AG90">
         <v>0</v>
@@ -19138,7 +19138,7 @@
         <v>80</v>
       </c>
       <c r="C91" t="s">
-        <v>153</v>
+        <v>131</v>
       </c>
       <c r="D91" t="s">
         <v>186</v>
@@ -19177,13 +19177,13 @@
         <v>699</v>
       </c>
       <c r="P91">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="Q91">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="R91">
-        <v>0</v>
+        <v>4.01</v>
       </c>
       <c r="S91">
         <v>0</v>
@@ -19222,10 +19222,10 @@
         <v>0</v>
       </c>
       <c r="AE91">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AF91">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AG91">
         <v>0</v>
@@ -19323,10 +19323,10 @@
         <v>80</v>
       </c>
       <c r="C92" t="s">
-        <v>134</v>
+        <v>152</v>
       </c>
       <c r="D92" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E92" t="s">
         <v>278</v>
@@ -19362,13 +19362,13 @@
         <v>699</v>
       </c>
       <c r="P92">
-        <v>0</v>
+        <v>5.38</v>
       </c>
       <c r="Q92">
-        <v>0</v>
+        <v>4.37</v>
       </c>
       <c r="R92">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="S92">
         <v>0</v>
@@ -19508,7 +19508,7 @@
         <v>80</v>
       </c>
       <c r="C93" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="D93" t="s">
         <v>186</v>
@@ -19547,13 +19547,13 @@
         <v>699</v>
       </c>
       <c r="P93">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="Q93">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="R93">
-        <v>4.01</v>
+        <v>0</v>
       </c>
       <c r="S93">
         <v>0</v>
@@ -19592,10 +19592,10 @@
         <v>0</v>
       </c>
       <c r="AE93">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AF93">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AG93">
         <v>0</v>
@@ -19693,7 +19693,7 @@
         <v>80</v>
       </c>
       <c r="C94" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="D94" t="s">
         <v>186</v>
@@ -19732,13 +19732,13 @@
         <v>699</v>
       </c>
       <c r="P94">
-        <v>2.59</v>
+        <v>2.46</v>
       </c>
       <c r="Q94">
-        <v>3.45</v>
+        <v>3.66</v>
       </c>
       <c r="R94">
-        <v>2.3</v>
+        <v>2.99</v>
       </c>
       <c r="S94">
         <v>0</v>
@@ -19777,10 +19777,10 @@
         <v>0</v>
       </c>
       <c r="AE94">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AF94">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AG94">
         <v>0</v>
@@ -20618,10 +20618,10 @@
         <v>83</v>
       </c>
       <c r="C99" t="s">
-        <v>159</v>
+        <v>142</v>
       </c>
       <c r="D99" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E99" t="s">
         <v>285</v>
@@ -20657,13 +20657,13 @@
         <v>699</v>
       </c>
       <c r="P99">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="Q99">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="R99">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="S99">
         <v>0</v>
@@ -20702,10 +20702,10 @@
         <v>0</v>
       </c>
       <c r="AE99">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AF99">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG99">
         <v>0</v>
@@ -20803,7 +20803,7 @@
         <v>83</v>
       </c>
       <c r="C100" t="s">
-        <v>144</v>
+        <v>160</v>
       </c>
       <c r="D100" t="s">
         <v>186</v>
@@ -20842,13 +20842,13 @@
         <v>699</v>
       </c>
       <c r="P100">
-        <v>4.68</v>
+        <v>0</v>
       </c>
       <c r="Q100">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R100">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="S100">
         <v>0</v>
@@ -20988,10 +20988,10 @@
         <v>83</v>
       </c>
       <c r="C101" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="D101" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E101" t="s">
         <v>287</v>
@@ -21027,13 +21027,13 @@
         <v>699</v>
       </c>
       <c r="P101">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="Q101">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="R101">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="S101">
         <v>0</v>
@@ -21072,10 +21072,10 @@
         <v>0</v>
       </c>
       <c r="AE101">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AF101">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AG101">
         <v>0</v>
@@ -21173,10 +21173,10 @@
         <v>83</v>
       </c>
       <c r="C102" t="s">
-        <v>138</v>
+        <v>159</v>
       </c>
       <c r="D102" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E102" t="s">
         <v>288</v>
@@ -21358,10 +21358,10 @@
         <v>83</v>
       </c>
       <c r="C103" t="s">
-        <v>160</v>
+        <v>136</v>
       </c>
       <c r="D103" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E103" t="s">
         <v>289</v>
@@ -21543,7 +21543,7 @@
         <v>83</v>
       </c>
       <c r="C104" t="s">
-        <v>161</v>
+        <v>138</v>
       </c>
       <c r="D104" t="s">
         <v>186</v>
@@ -21582,13 +21582,13 @@
         <v>699</v>
       </c>
       <c r="P104">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="Q104">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="R104">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="S104">
         <v>0</v>
@@ -21728,10 +21728,10 @@
         <v>83</v>
       </c>
       <c r="C105" t="s">
-        <v>136</v>
+        <v>144</v>
       </c>
       <c r="D105" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E105" t="s">
         <v>291</v>
@@ -21767,13 +21767,13 @@
         <v>699</v>
       </c>
       <c r="P105">
-        <v>0</v>
+        <v>4.68</v>
       </c>
       <c r="Q105">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R105">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="S105">
         <v>0</v>
@@ -21913,10 +21913,10 @@
         <v>83</v>
       </c>
       <c r="C106" t="s">
-        <v>139</v>
+        <v>161</v>
       </c>
       <c r="D106" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E106" t="s">
         <v>292</v>
@@ -22098,7 +22098,7 @@
         <v>83</v>
       </c>
       <c r="C107" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="D107" t="s">
         <v>186</v>
@@ -22137,13 +22137,13 @@
         <v>699</v>
       </c>
       <c r="P107">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="Q107">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R107">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="S107">
         <v>0</v>
@@ -22283,7 +22283,7 @@
         <v>84</v>
       </c>
       <c r="C108" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="D108" t="s">
         <v>186</v>
@@ -22468,7 +22468,7 @@
         <v>84</v>
       </c>
       <c r="C109" t="s">
-        <v>122</v>
+        <v>148</v>
       </c>
       <c r="D109" t="s">
         <v>186</v>
@@ -22507,13 +22507,13 @@
         <v>699</v>
       </c>
       <c r="P109">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="Q109">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="R109">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="S109">
         <v>0</v>
@@ -22653,7 +22653,7 @@
         <v>84</v>
       </c>
       <c r="C110" t="s">
-        <v>147</v>
+        <v>123</v>
       </c>
       <c r="D110" t="s">
         <v>186</v>
@@ -22692,13 +22692,13 @@
         <v>699</v>
       </c>
       <c r="P110">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="Q110">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="R110">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="S110">
         <v>0</v>
@@ -22838,10 +22838,10 @@
         <v>85</v>
       </c>
       <c r="C111" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="D111" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E111" t="s">
         <v>297</v>
@@ -22877,13 +22877,13 @@
         <v>699</v>
       </c>
       <c r="P111">
-        <v>2.05</v>
+        <v>2.27</v>
       </c>
       <c r="Q111">
-        <v>3.64</v>
+        <v>3.58</v>
       </c>
       <c r="R111">
-        <v>3.28</v>
+        <v>2.88</v>
       </c>
       <c r="S111">
         <v>0</v>
@@ -23023,7 +23023,7 @@
         <v>85</v>
       </c>
       <c r="C112" t="s">
-        <v>140</v>
+        <v>146</v>
       </c>
       <c r="D112" t="s">
         <v>186</v>
@@ -23062,13 +23062,13 @@
         <v>699</v>
       </c>
       <c r="P112">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Q112">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="R112">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="S112">
         <v>0</v>
@@ -23208,7 +23208,7 @@
         <v>85</v>
       </c>
       <c r="C113" t="s">
-        <v>118</v>
+        <v>146</v>
       </c>
       <c r="D113" t="s">
         <v>186</v>
@@ -23247,13 +23247,13 @@
         <v>699</v>
       </c>
       <c r="P113">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="Q113">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="R113">
-        <v>0</v>
+        <v>3.57</v>
       </c>
       <c r="S113">
         <v>0</v>
@@ -23298,10 +23298,10 @@
         <v>0</v>
       </c>
       <c r="AG113">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AH113">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AI113">
         <v>0</v>
@@ -23393,10 +23393,10 @@
         <v>85</v>
       </c>
       <c r="C114" t="s">
-        <v>145</v>
+        <v>119</v>
       </c>
       <c r="D114" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E114" t="s">
         <v>300</v>
@@ -23432,13 +23432,13 @@
         <v>699</v>
       </c>
       <c r="P114">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="Q114">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="R114">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="S114">
         <v>0</v>
@@ -23578,7 +23578,7 @@
         <v>85</v>
       </c>
       <c r="C115" t="s">
-        <v>149</v>
+        <v>137</v>
       </c>
       <c r="D115" t="s">
         <v>186</v>
@@ -23617,13 +23617,13 @@
         <v>699</v>
       </c>
       <c r="P115">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="Q115">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="R115">
-        <v>3.57</v>
+        <v>0</v>
       </c>
       <c r="S115">
         <v>0</v>
@@ -23668,10 +23668,10 @@
         <v>0</v>
       </c>
       <c r="AG115">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AH115">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AI115">
         <v>0</v>
@@ -23987,13 +23987,13 @@
         <v>699</v>
       </c>
       <c r="P117">
-        <v>1.77</v>
+        <v>1.48</v>
       </c>
       <c r="Q117">
-        <v>4.17</v>
+        <v>4.94</v>
       </c>
       <c r="R117">
-        <v>4.22</v>
+        <v>6.07</v>
       </c>
       <c r="S117">
         <v>0</v>
@@ -24032,16 +24032,16 @@
         <v>0</v>
       </c>
       <c r="AE117">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AF117">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AG117">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AH117">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AI117">
         <v>0</v>
@@ -24172,13 +24172,13 @@
         <v>699</v>
       </c>
       <c r="P118">
-        <v>1.71</v>
+        <v>2.78</v>
       </c>
       <c r="Q118">
-        <v>4.37</v>
+        <v>3.89</v>
       </c>
       <c r="R118">
-        <v>4.42</v>
+        <v>2.36</v>
       </c>
       <c r="S118">
         <v>0</v>
@@ -24223,10 +24223,10 @@
         <v>0</v>
       </c>
       <c r="AG118">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="AH118">
-        <v>1.65</v>
+        <v>1.68</v>
       </c>
       <c r="AI118">
         <v>0</v>
@@ -24357,13 +24357,13 @@
         <v>699</v>
       </c>
       <c r="P119">
-        <v>2.78</v>
+        <v>1.71</v>
       </c>
       <c r="Q119">
-        <v>3.89</v>
+        <v>4.37</v>
       </c>
       <c r="R119">
-        <v>2.36</v>
+        <v>4.42</v>
       </c>
       <c r="S119">
         <v>0</v>
@@ -24408,10 +24408,10 @@
         <v>0</v>
       </c>
       <c r="AG119">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="AH119">
-        <v>1.68</v>
+        <v>1.65</v>
       </c>
       <c r="AI119">
         <v>0</v>
@@ -24542,13 +24542,13 @@
         <v>699</v>
       </c>
       <c r="P120">
-        <v>1.78</v>
+        <v>1.44</v>
       </c>
       <c r="Q120">
-        <v>4.17</v>
+        <v>5.14</v>
       </c>
       <c r="R120">
-        <v>4.17</v>
+        <v>6.53</v>
       </c>
       <c r="S120">
         <v>0</v>
@@ -24593,7 +24593,7 @@
         <v>0</v>
       </c>
       <c r="AG120">
-        <v>1.9</v>
+        <v>1.93</v>
       </c>
       <c r="AH120">
         <v>1.77</v>
@@ -24727,13 +24727,13 @@
         <v>699</v>
       </c>
       <c r="P121">
-        <v>1.96</v>
+        <v>2.49</v>
       </c>
       <c r="Q121">
-        <v>4.05</v>
+        <v>3.77</v>
       </c>
       <c r="R121">
-        <v>3.5</v>
+        <v>2.67</v>
       </c>
       <c r="S121">
         <v>0</v>
@@ -24772,16 +24772,16 @@
         <v>0</v>
       </c>
       <c r="AE121">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AF121">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AG121">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AH121">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AI121">
         <v>0</v>
@@ -24912,13 +24912,13 @@
         <v>699</v>
       </c>
       <c r="P122">
-        <v>1.44</v>
+        <v>1.96</v>
       </c>
       <c r="Q122">
-        <v>5.14</v>
+        <v>4.05</v>
       </c>
       <c r="R122">
-        <v>6.53</v>
+        <v>3.5</v>
       </c>
       <c r="S122">
         <v>0</v>
@@ -24963,10 +24963,10 @@
         <v>0</v>
       </c>
       <c r="AG122">
-        <v>1.93</v>
+        <v>2.2</v>
       </c>
       <c r="AH122">
-        <v>1.77</v>
+        <v>1.58</v>
       </c>
       <c r="AI122">
         <v>0</v>
@@ -25097,13 +25097,13 @@
         <v>699</v>
       </c>
       <c r="P123">
-        <v>2.49</v>
+        <v>1.78</v>
       </c>
       <c r="Q123">
-        <v>3.77</v>
+        <v>4.17</v>
       </c>
       <c r="R123">
-        <v>2.67</v>
+        <v>4.17</v>
       </c>
       <c r="S123">
         <v>0</v>
@@ -25142,16 +25142,16 @@
         <v>0</v>
       </c>
       <c r="AE123">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AF123">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AG123">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AH123">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AI123">
         <v>0</v>
@@ -25282,13 +25282,13 @@
         <v>699</v>
       </c>
       <c r="P124">
-        <v>1.48</v>
+        <v>1.77</v>
       </c>
       <c r="Q124">
-        <v>4.94</v>
+        <v>4.17</v>
       </c>
       <c r="R124">
-        <v>6.07</v>
+        <v>4.22</v>
       </c>
       <c r="S124">
         <v>0</v>
@@ -25327,16 +25327,16 @@
         <v>0</v>
       </c>
       <c r="AE124">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AF124">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AG124">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AH124">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AI124">
         <v>0</v>
@@ -25428,10 +25428,10 @@
         <v>87</v>
       </c>
       <c r="C125" t="s">
-        <v>151</v>
+        <v>163</v>
       </c>
       <c r="D125" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E125" t="s">
         <v>311</v>
@@ -25467,13 +25467,13 @@
         <v>699</v>
       </c>
       <c r="P125">
-        <v>3.87</v>
+        <v>0</v>
       </c>
       <c r="Q125">
-        <v>3.87</v>
+        <v>0</v>
       </c>
       <c r="R125">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="S125">
         <v>0</v>
@@ -25613,7 +25613,7 @@
         <v>87</v>
       </c>
       <c r="C126" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="D126" t="s">
         <v>185</v>
@@ -25652,13 +25652,13 @@
         <v>699</v>
       </c>
       <c r="P126">
-        <v>3.1</v>
+        <v>5.4</v>
       </c>
       <c r="Q126">
-        <v>3.7</v>
+        <v>4.6</v>
       </c>
       <c r="R126">
-        <v>2.12</v>
+        <v>1.51</v>
       </c>
       <c r="S126">
         <v>0</v>
@@ -25798,10 +25798,10 @@
         <v>87</v>
       </c>
       <c r="C127" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="D127" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E127" t="s">
         <v>313</v>
@@ -25837,13 +25837,13 @@
         <v>699</v>
       </c>
       <c r="P127">
-        <v>2.15</v>
+        <v>2.3</v>
       </c>
       <c r="Q127">
-        <v>3.7</v>
+        <v>3.35</v>
       </c>
       <c r="R127">
-        <v>3.01</v>
+        <v>2.96</v>
       </c>
       <c r="S127">
         <v>0</v>
@@ -25983,10 +25983,10 @@
         <v>87</v>
       </c>
       <c r="C128" t="s">
-        <v>120</v>
+        <v>164</v>
       </c>
       <c r="D128" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E128" t="s">
         <v>314</v>
@@ -26022,13 +26022,13 @@
         <v>699</v>
       </c>
       <c r="P128">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Q128">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="R128">
-        <v>0</v>
+        <v>3.01</v>
       </c>
       <c r="S128">
         <v>0</v>
@@ -26168,10 +26168,10 @@
         <v>87</v>
       </c>
       <c r="C129" t="s">
-        <v>151</v>
+        <v>128</v>
       </c>
       <c r="D129" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E129" t="s">
         <v>315</v>
@@ -26207,13 +26207,13 @@
         <v>699</v>
       </c>
       <c r="P129">
-        <v>1.59</v>
+        <v>2.55</v>
       </c>
       <c r="Q129">
-        <v>4.44</v>
+        <v>3.6</v>
       </c>
       <c r="R129">
-        <v>5.16</v>
+        <v>2.43</v>
       </c>
       <c r="S129">
         <v>0</v>
@@ -26353,10 +26353,10 @@
         <v>87</v>
       </c>
       <c r="C130" t="s">
-        <v>128</v>
+        <v>151</v>
       </c>
       <c r="D130" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E130" t="s">
         <v>316</v>
@@ -26392,13 +26392,13 @@
         <v>699</v>
       </c>
       <c r="P130">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="Q130">
-        <v>0</v>
+        <v>4.44</v>
       </c>
       <c r="R130">
-        <v>0</v>
+        <v>5.16</v>
       </c>
       <c r="S130">
         <v>0</v>
@@ -26538,10 +26538,10 @@
         <v>87</v>
       </c>
       <c r="C131" t="s">
-        <v>160</v>
+        <v>151</v>
       </c>
       <c r="D131" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E131" t="s">
         <v>317</v>
@@ -26577,13 +26577,13 @@
         <v>699</v>
       </c>
       <c r="P131">
-        <v>0</v>
+        <v>3.87</v>
       </c>
       <c r="Q131">
-        <v>0</v>
+        <v>3.87</v>
       </c>
       <c r="R131">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="S131">
         <v>0</v>
@@ -26723,7 +26723,7 @@
         <v>87</v>
       </c>
       <c r="C132" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="D132" t="s">
         <v>186</v>
@@ -26908,7 +26908,7 @@
         <v>87</v>
       </c>
       <c r="C133" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="D133" t="s">
         <v>186</v>
@@ -27093,7 +27093,7 @@
         <v>87</v>
       </c>
       <c r="C134" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="D134" t="s">
         <v>186</v>
@@ -27102,7 +27102,7 @@
         <v>320</v>
       </c>
       <c r="F134" t="s">
-        <v>293</v>
+        <v>576</v>
       </c>
       <c r="G134">
         <v>0</v>
@@ -27278,16 +27278,16 @@
         <v>87</v>
       </c>
       <c r="C135" t="s">
-        <v>148</v>
+        <v>166</v>
       </c>
       <c r="D135" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E135" t="s">
         <v>321</v>
       </c>
       <c r="F135" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="G135">
         <v>0</v>
@@ -27463,7 +27463,7 @@
         <v>87</v>
       </c>
       <c r="C136" t="s">
-        <v>160</v>
+        <v>166</v>
       </c>
       <c r="D136" t="s">
         <v>186</v>
@@ -27472,7 +27472,7 @@
         <v>322</v>
       </c>
       <c r="F136" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="G136">
         <v>0</v>
@@ -27648,16 +27648,16 @@
         <v>87</v>
       </c>
       <c r="C137" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="D137" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E137" t="s">
         <v>323</v>
       </c>
       <c r="F137" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="G137">
         <v>0</v>
@@ -27687,13 +27687,13 @@
         <v>699</v>
       </c>
       <c r="P137">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Q137">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R137">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="S137">
         <v>0</v>
@@ -27833,16 +27833,16 @@
         <v>87</v>
       </c>
       <c r="C138" t="s">
-        <v>163</v>
+        <v>120</v>
       </c>
       <c r="D138" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E138" t="s">
         <v>324</v>
       </c>
       <c r="F138" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="G138">
         <v>0</v>
@@ -27872,13 +27872,13 @@
         <v>699</v>
       </c>
       <c r="P138">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Q138">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="R138">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="S138">
         <v>0</v>
@@ -28021,13 +28021,13 @@
         <v>163</v>
       </c>
       <c r="D139" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E139" t="s">
         <v>325</v>
       </c>
       <c r="F139" t="s">
-        <v>580</v>
+        <v>283</v>
       </c>
       <c r="G139">
         <v>0</v>
@@ -28057,13 +28057,13 @@
         <v>699</v>
       </c>
       <c r="P139">
-        <v>5.4</v>
+        <v>0</v>
       </c>
       <c r="Q139">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="R139">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="S139">
         <v>0</v>
@@ -28203,7 +28203,7 @@
         <v>87</v>
       </c>
       <c r="C140" t="s">
-        <v>160</v>
+        <v>125</v>
       </c>
       <c r="D140" t="s">
         <v>186</v>
@@ -28388,10 +28388,10 @@
         <v>87</v>
       </c>
       <c r="C141" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="D141" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E141" t="s">
         <v>327</v>
@@ -28427,13 +28427,13 @@
         <v>699</v>
       </c>
       <c r="P141">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="Q141">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="R141">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="S141">
         <v>0</v>
@@ -28573,10 +28573,10 @@
         <v>87</v>
       </c>
       <c r="C142" t="s">
-        <v>127</v>
+        <v>151</v>
       </c>
       <c r="D142" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E142" t="s">
         <v>328</v>
@@ -28612,13 +28612,13 @@
         <v>699</v>
       </c>
       <c r="P142">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="Q142">
-        <v>0</v>
+        <v>3.82</v>
       </c>
       <c r="R142">
-        <v>0</v>
+        <v>4.13</v>
       </c>
       <c r="S142">
         <v>0</v>
@@ -28758,7 +28758,7 @@
         <v>87</v>
       </c>
       <c r="C143" t="s">
-        <v>160</v>
+        <v>166</v>
       </c>
       <c r="D143" t="s">
         <v>186</v>
@@ -28943,7 +28943,7 @@
         <v>87</v>
       </c>
       <c r="C144" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="D144" t="s">
         <v>186</v>
@@ -29128,10 +29128,10 @@
         <v>87</v>
       </c>
       <c r="C145" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="D145" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E145" t="s">
         <v>331</v>
@@ -29167,13 +29167,13 @@
         <v>699</v>
       </c>
       <c r="P145">
-        <v>0</v>
+        <v>4.07</v>
       </c>
       <c r="Q145">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="R145">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="S145">
         <v>0</v>
@@ -29313,7 +29313,7 @@
         <v>87</v>
       </c>
       <c r="C146" t="s">
-        <v>166</v>
+        <v>143</v>
       </c>
       <c r="D146" t="s">
         <v>186</v>
@@ -29498,7 +29498,7 @@
         <v>87</v>
       </c>
       <c r="C147" t="s">
-        <v>129</v>
+        <v>161</v>
       </c>
       <c r="D147" t="s">
         <v>186</v>
@@ -29537,13 +29537,13 @@
         <v>699</v>
       </c>
       <c r="P147">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="Q147">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R147">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="S147">
         <v>0</v>
@@ -29686,7 +29686,7 @@
         <v>164</v>
       </c>
       <c r="D148" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E148" t="s">
         <v>334</v>
@@ -29722,13 +29722,13 @@
         <v>699</v>
       </c>
       <c r="P148">
-        <v>2.3</v>
+        <v>2.65</v>
       </c>
       <c r="Q148">
-        <v>3.35</v>
+        <v>3.6</v>
       </c>
       <c r="R148">
-        <v>2.96</v>
+        <v>2.4</v>
       </c>
       <c r="S148">
         <v>0</v>
@@ -29868,10 +29868,10 @@
         <v>87</v>
       </c>
       <c r="C149" t="s">
-        <v>163</v>
+        <v>126</v>
       </c>
       <c r="D149" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E149" t="s">
         <v>335</v>
@@ -29907,13 +29907,13 @@
         <v>699</v>
       </c>
       <c r="P149">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="Q149">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R149">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="S149">
         <v>0</v>
@@ -30238,7 +30238,7 @@
         <v>87</v>
       </c>
       <c r="C151" t="s">
-        <v>166</v>
+        <v>161</v>
       </c>
       <c r="D151" t="s">
         <v>186</v>
@@ -30423,10 +30423,10 @@
         <v>87</v>
       </c>
       <c r="C152" t="s">
-        <v>151</v>
+        <v>161</v>
       </c>
       <c r="D152" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E152" t="s">
         <v>338</v>
@@ -30462,13 +30462,13 @@
         <v>699</v>
       </c>
       <c r="P152">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="Q152">
-        <v>3.82</v>
+        <v>0</v>
       </c>
       <c r="R152">
-        <v>4.13</v>
+        <v>0</v>
       </c>
       <c r="S152">
         <v>0</v>
@@ -30608,10 +30608,10 @@
         <v>87</v>
       </c>
       <c r="C153" t="s">
-        <v>165</v>
+        <v>147</v>
       </c>
       <c r="D153" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E153" t="s">
         <v>339</v>
@@ -30793,7 +30793,7 @@
         <v>87</v>
       </c>
       <c r="C154" t="s">
-        <v>143</v>
+        <v>161</v>
       </c>
       <c r="D154" t="s">
         <v>186</v>
@@ -30978,10 +30978,10 @@
         <v>87</v>
       </c>
       <c r="C155" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="D155" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E155" t="s">
         <v>341</v>
@@ -31017,13 +31017,13 @@
         <v>699</v>
       </c>
       <c r="P155">
-        <v>4.07</v>
+        <v>0</v>
       </c>
       <c r="Q155">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="R155">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="S155">
         <v>0</v>
@@ -31163,7 +31163,7 @@
         <v>87</v>
       </c>
       <c r="C156" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="D156" t="s">
         <v>186</v>
@@ -32088,7 +32088,7 @@
         <v>89</v>
       </c>
       <c r="C161" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="D161" t="s">
         <v>186</v>
@@ -32127,13 +32127,13 @@
         <v>699</v>
       </c>
       <c r="P161">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="Q161">
-        <v>4.32</v>
+        <v>0</v>
       </c>
       <c r="R161">
-        <v>4.52</v>
+        <v>0</v>
       </c>
       <c r="S161">
         <v>0</v>
@@ -32178,10 +32178,10 @@
         <v>0</v>
       </c>
       <c r="AG161">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AH161">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AI161">
         <v>0</v>
@@ -32273,7 +32273,7 @@
         <v>89</v>
       </c>
       <c r="C162" t="s">
-        <v>130</v>
+        <v>157</v>
       </c>
       <c r="D162" t="s">
         <v>186</v>
@@ -32312,13 +32312,13 @@
         <v>699</v>
       </c>
       <c r="P162">
-        <v>4.09</v>
+        <v>1.78</v>
       </c>
       <c r="Q162">
-        <v>3.78</v>
+        <v>4.32</v>
       </c>
       <c r="R162">
-        <v>1.77</v>
+        <v>4.52</v>
       </c>
       <c r="S162">
         <v>0</v>
@@ -32363,10 +32363,10 @@
         <v>0</v>
       </c>
       <c r="AG162">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AH162">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AI162">
         <v>0</v>
@@ -32643,7 +32643,7 @@
         <v>89</v>
       </c>
       <c r="C164" t="s">
-        <v>168</v>
+        <v>130</v>
       </c>
       <c r="D164" t="s">
         <v>186</v>
@@ -32682,13 +32682,13 @@
         <v>699</v>
       </c>
       <c r="P164">
-        <v>0</v>
+        <v>4.09</v>
       </c>
       <c r="Q164">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="R164">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="S164">
         <v>0</v>
@@ -32828,7 +32828,7 @@
         <v>89</v>
       </c>
       <c r="C165" t="s">
-        <v>154</v>
+        <v>168</v>
       </c>
       <c r="D165" t="s">
         <v>186</v>
@@ -33013,7 +33013,7 @@
         <v>90</v>
       </c>
       <c r="C166" t="s">
-        <v>169</v>
+        <v>144</v>
       </c>
       <c r="D166" t="s">
         <v>186</v>
@@ -33198,7 +33198,7 @@
         <v>90</v>
       </c>
       <c r="C167" t="s">
-        <v>144</v>
+        <v>169</v>
       </c>
       <c r="D167" t="s">
         <v>186</v>
@@ -33568,10 +33568,10 @@
         <v>90</v>
       </c>
       <c r="C169" t="s">
-        <v>170</v>
+        <v>136</v>
       </c>
       <c r="D169" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E169" t="s">
         <v>355</v>
@@ -33938,7 +33938,7 @@
         <v>90</v>
       </c>
       <c r="C171" t="s">
-        <v>120</v>
+        <v>169</v>
       </c>
       <c r="D171" t="s">
         <v>186</v>
@@ -34123,7 +34123,7 @@
         <v>90</v>
       </c>
       <c r="C172" t="s">
-        <v>169</v>
+        <v>131</v>
       </c>
       <c r="D172" t="s">
         <v>186</v>
@@ -34162,13 +34162,13 @@
         <v>699</v>
       </c>
       <c r="P172">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="Q172">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R172">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="S172">
         <v>0</v>
@@ -34308,7 +34308,7 @@
         <v>90</v>
       </c>
       <c r="C173" t="s">
-        <v>131</v>
+        <v>170</v>
       </c>
       <c r="D173" t="s">
         <v>186</v>
@@ -34347,13 +34347,13 @@
         <v>699</v>
       </c>
       <c r="P173">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="Q173">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="R173">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="S173">
         <v>0</v>
@@ -34493,7 +34493,7 @@
         <v>90</v>
       </c>
       <c r="C174" t="s">
-        <v>169</v>
+        <v>120</v>
       </c>
       <c r="D174" t="s">
         <v>186</v>
@@ -34678,7 +34678,7 @@
         <v>90</v>
       </c>
       <c r="C175" t="s">
-        <v>155</v>
+        <v>169</v>
       </c>
       <c r="D175" t="s">
         <v>186</v>
@@ -34717,13 +34717,13 @@
         <v>699</v>
       </c>
       <c r="P175">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="Q175">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="R175">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="S175">
         <v>0</v>
@@ -34863,10 +34863,10 @@
         <v>90</v>
       </c>
       <c r="C176" t="s">
-        <v>136</v>
+        <v>156</v>
       </c>
       <c r="D176" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E176" t="s">
         <v>362</v>
@@ -34902,13 +34902,13 @@
         <v>699</v>
       </c>
       <c r="P176">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="Q176">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R176">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="S176">
         <v>0</v>
@@ -35418,10 +35418,10 @@
         <v>92</v>
       </c>
       <c r="C179" t="s">
-        <v>135</v>
+        <v>159</v>
       </c>
       <c r="D179" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E179" t="s">
         <v>365</v>
@@ -35457,13 +35457,13 @@
         <v>699</v>
       </c>
       <c r="P179">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="Q179">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="R179">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="S179">
         <v>0</v>
@@ -35603,10 +35603,10 @@
         <v>92</v>
       </c>
       <c r="C180" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="D180" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E180" t="s">
         <v>366</v>
@@ -35788,7 +35788,7 @@
         <v>92</v>
       </c>
       <c r="C181" t="s">
-        <v>158</v>
+        <v>135</v>
       </c>
       <c r="D181" t="s">
         <v>186</v>
@@ -35827,13 +35827,13 @@
         <v>699</v>
       </c>
       <c r="P181">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="Q181">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R181">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="S181">
         <v>0</v>
@@ -35973,7 +35973,7 @@
         <v>93</v>
       </c>
       <c r="C182" t="s">
-        <v>142</v>
+        <v>158</v>
       </c>
       <c r="D182" t="s">
         <v>186</v>
@@ -36012,13 +36012,13 @@
         <v>699</v>
       </c>
       <c r="P182">
-        <v>1.28</v>
+        <v>1.45</v>
       </c>
       <c r="Q182">
-        <v>5.66</v>
+        <v>3.8</v>
       </c>
       <c r="R182">
-        <v>8.98</v>
+        <v>6.76</v>
       </c>
       <c r="S182">
         <v>0</v>
@@ -36161,7 +36161,7 @@
         <v>172</v>
       </c>
       <c r="D183" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E183" t="s">
         <v>369</v>
@@ -36343,7 +36343,7 @@
         <v>93</v>
       </c>
       <c r="C184" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="D184" t="s">
         <v>186</v>
@@ -36528,7 +36528,7 @@
         <v>93</v>
       </c>
       <c r="C185" t="s">
-        <v>153</v>
+        <v>173</v>
       </c>
       <c r="D185" t="s">
         <v>186</v>
@@ -36713,7 +36713,7 @@
         <v>93</v>
       </c>
       <c r="C186" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="D186" t="s">
         <v>186</v>
@@ -36898,7 +36898,7 @@
         <v>93</v>
       </c>
       <c r="C187" t="s">
-        <v>172</v>
+        <v>123</v>
       </c>
       <c r="D187" t="s">
         <v>186</v>
@@ -36937,13 +36937,13 @@
         <v>699</v>
       </c>
       <c r="P187">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Q187">
-        <v>0</v>
+        <v>3.66</v>
       </c>
       <c r="R187">
-        <v>0</v>
+        <v>3.36</v>
       </c>
       <c r="S187">
         <v>0</v>
@@ -37083,10 +37083,10 @@
         <v>93</v>
       </c>
       <c r="C188" t="s">
-        <v>161</v>
+        <v>174</v>
       </c>
       <c r="D188" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E188" t="s">
         <v>374</v>
@@ -37122,13 +37122,13 @@
         <v>699</v>
       </c>
       <c r="P188">
-        <v>1.45</v>
+        <v>1.3</v>
       </c>
       <c r="Q188">
-        <v>3.8</v>
+        <v>5.1</v>
       </c>
       <c r="R188">
-        <v>6.76</v>
+        <v>7.95</v>
       </c>
       <c r="S188">
         <v>0</v>
@@ -37268,10 +37268,10 @@
         <v>93</v>
       </c>
       <c r="C189" t="s">
-        <v>173</v>
+        <v>158</v>
       </c>
       <c r="D189" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E189" t="s">
         <v>375</v>
@@ -37307,13 +37307,13 @@
         <v>699</v>
       </c>
       <c r="P189">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="Q189">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R189">
-        <v>0</v>
+        <v>4.56</v>
       </c>
       <c r="S189">
         <v>0</v>
@@ -37453,7 +37453,7 @@
         <v>93</v>
       </c>
       <c r="C190" t="s">
-        <v>161</v>
+        <v>173</v>
       </c>
       <c r="D190" t="s">
         <v>186</v>
@@ -37492,13 +37492,13 @@
         <v>699</v>
       </c>
       <c r="P190">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="Q190">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="R190">
-        <v>4.56</v>
+        <v>0</v>
       </c>
       <c r="S190">
         <v>0</v>
@@ -37638,7 +37638,7 @@
         <v>93</v>
       </c>
       <c r="C191" t="s">
-        <v>172</v>
+        <v>149</v>
       </c>
       <c r="D191" t="s">
         <v>186</v>
@@ -37677,13 +37677,13 @@
         <v>699</v>
       </c>
       <c r="P191">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="Q191">
-        <v>0</v>
+        <v>3.53</v>
       </c>
       <c r="R191">
-        <v>0</v>
+        <v>3.91</v>
       </c>
       <c r="S191">
         <v>0</v>
@@ -37722,10 +37722,10 @@
         <v>0</v>
       </c>
       <c r="AE191">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AF191">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AG191">
         <v>0</v>
@@ -37823,10 +37823,10 @@
         <v>93</v>
       </c>
       <c r="C192" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="D192" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E192" t="s">
         <v>378</v>
@@ -37862,13 +37862,13 @@
         <v>699</v>
       </c>
       <c r="P192">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="Q192">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="R192">
-        <v>7.95</v>
+        <v>0</v>
       </c>
       <c r="S192">
         <v>0</v>
@@ -38008,7 +38008,7 @@
         <v>93</v>
       </c>
       <c r="C193" t="s">
-        <v>122</v>
+        <v>149</v>
       </c>
       <c r="D193" t="s">
         <v>186</v>
@@ -38047,13 +38047,13 @@
         <v>699</v>
       </c>
       <c r="P193">
-        <v>2.25</v>
+        <v>3.12</v>
       </c>
       <c r="Q193">
-        <v>3.66</v>
+        <v>3.22</v>
       </c>
       <c r="R193">
-        <v>3.36</v>
+        <v>2.43</v>
       </c>
       <c r="S193">
         <v>0</v>
@@ -38193,10 +38193,10 @@
         <v>93</v>
       </c>
       <c r="C194" t="s">
-        <v>146</v>
+        <v>172</v>
       </c>
       <c r="D194" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E194" t="s">
         <v>380</v>
@@ -38232,13 +38232,13 @@
         <v>699</v>
       </c>
       <c r="P194">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="Q194">
-        <v>3.53</v>
+        <v>0</v>
       </c>
       <c r="R194">
-        <v>3.91</v>
+        <v>0</v>
       </c>
       <c r="S194">
         <v>0</v>
@@ -38277,10 +38277,10 @@
         <v>0</v>
       </c>
       <c r="AE194">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AF194">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AG194">
         <v>0</v>
@@ -38378,7 +38378,7 @@
         <v>93</v>
       </c>
       <c r="C195" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="D195" t="s">
         <v>186</v>
@@ -38417,13 +38417,13 @@
         <v>699</v>
       </c>
       <c r="P195">
-        <v>3.12</v>
+        <v>1.28</v>
       </c>
       <c r="Q195">
-        <v>3.22</v>
+        <v>5.66</v>
       </c>
       <c r="R195">
-        <v>2.43</v>
+        <v>8.98</v>
       </c>
       <c r="S195">
         <v>0</v>
@@ -38563,10 +38563,10 @@
         <v>93</v>
       </c>
       <c r="C196" t="s">
-        <v>173</v>
+        <v>153</v>
       </c>
       <c r="D196" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E196" t="s">
         <v>382</v>
@@ -38751,7 +38751,7 @@
         <v>175</v>
       </c>
       <c r="D197" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E197" t="s">
         <v>383</v>
@@ -38787,13 +38787,13 @@
         <v>699</v>
       </c>
       <c r="P197">
-        <v>1.53</v>
+        <v>2.25</v>
       </c>
       <c r="Q197">
-        <v>4.45</v>
+        <v>3.38</v>
       </c>
       <c r="R197">
-        <v>5.12</v>
+        <v>3</v>
       </c>
       <c r="S197">
         <v>0</v>
@@ -38933,7 +38933,7 @@
         <v>94</v>
       </c>
       <c r="C198" t="s">
-        <v>128</v>
+        <v>175</v>
       </c>
       <c r="D198" t="s">
         <v>186</v>
@@ -39118,10 +39118,10 @@
         <v>94</v>
       </c>
       <c r="C199" t="s">
-        <v>148</v>
+        <v>175</v>
       </c>
       <c r="D199" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E199" t="s">
         <v>385</v>
@@ -39303,7 +39303,7 @@
         <v>94</v>
       </c>
       <c r="C200" t="s">
-        <v>176</v>
+        <v>125</v>
       </c>
       <c r="D200" t="s">
         <v>186</v>
@@ -39488,7 +39488,7 @@
         <v>94</v>
       </c>
       <c r="C201" t="s">
-        <v>176</v>
+        <v>161</v>
       </c>
       <c r="D201" t="s">
         <v>186</v>
@@ -39673,10 +39673,10 @@
         <v>94</v>
       </c>
       <c r="C202" t="s">
-        <v>176</v>
+        <v>147</v>
       </c>
       <c r="D202" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E202" t="s">
         <v>388</v>
@@ -39712,13 +39712,13 @@
         <v>699</v>
       </c>
       <c r="P202">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Q202">
-        <v>3.38</v>
+        <v>0</v>
       </c>
       <c r="R202">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="S202">
         <v>0</v>
@@ -39858,7 +39858,7 @@
         <v>94</v>
       </c>
       <c r="C203" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="D203" t="s">
         <v>186</v>
@@ -40043,10 +40043,10 @@
         <v>94</v>
       </c>
       <c r="C204" t="s">
-        <v>160</v>
+        <v>176</v>
       </c>
       <c r="D204" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E204" t="s">
         <v>390</v>
@@ -40082,13 +40082,13 @@
         <v>699</v>
       </c>
       <c r="P204">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="Q204">
-        <v>0</v>
+        <v>4.45</v>
       </c>
       <c r="R204">
-        <v>0</v>
+        <v>5.12</v>
       </c>
       <c r="S204">
         <v>0</v>
@@ -40413,7 +40413,7 @@
         <v>96</v>
       </c>
       <c r="C206" t="s">
-        <v>157</v>
+        <v>137</v>
       </c>
       <c r="D206" t="s">
         <v>186</v>
@@ -40452,13 +40452,13 @@
         <v>699</v>
       </c>
       <c r="P206">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="Q206">
-        <v>3.94</v>
+        <v>0</v>
       </c>
       <c r="R206">
-        <v>4.41</v>
+        <v>0</v>
       </c>
       <c r="S206">
         <v>0</v>
@@ -40497,10 +40497,10 @@
         <v>0</v>
       </c>
       <c r="AE206">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AF206">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AG206">
         <v>0</v>
@@ -40598,7 +40598,7 @@
         <v>96</v>
       </c>
       <c r="C207" t="s">
-        <v>140</v>
+        <v>157</v>
       </c>
       <c r="D207" t="s">
         <v>186</v>
@@ -40637,13 +40637,13 @@
         <v>699</v>
       </c>
       <c r="P207">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="Q207">
-        <v>0</v>
+        <v>3.94</v>
       </c>
       <c r="R207">
-        <v>0</v>
+        <v>4.41</v>
       </c>
       <c r="S207">
         <v>0</v>
@@ -40682,10 +40682,10 @@
         <v>0</v>
       </c>
       <c r="AE207">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AF207">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AG207">
         <v>0</v>
@@ -40783,10 +40783,10 @@
         <v>97</v>
       </c>
       <c r="C208" t="s">
-        <v>171</v>
+        <v>177</v>
       </c>
       <c r="D208" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E208" t="s">
         <v>394</v>
@@ -40968,7 +40968,7 @@
         <v>97</v>
       </c>
       <c r="C209" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="D209" t="s">
         <v>186</v>
@@ -41153,10 +41153,10 @@
         <v>97</v>
       </c>
       <c r="C210" t="s">
-        <v>177</v>
+        <v>170</v>
       </c>
       <c r="D210" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E210" t="s">
         <v>396</v>
@@ -41523,10 +41523,10 @@
         <v>98</v>
       </c>
       <c r="C212" t="s">
-        <v>178</v>
+        <v>127</v>
       </c>
       <c r="D212" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E212" t="s">
         <v>398</v>
@@ -41708,10 +41708,10 @@
         <v>98</v>
       </c>
       <c r="C213" t="s">
-        <v>124</v>
+        <v>178</v>
       </c>
       <c r="D213" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E213" t="s">
         <v>399</v>
@@ -42078,10 +42078,10 @@
         <v>100</v>
       </c>
       <c r="C215" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="D215" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E215" t="s">
         <v>401</v>
@@ -42117,13 +42117,13 @@
         <v>699</v>
       </c>
       <c r="P215">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="Q215">
-        <v>0</v>
+        <v>3.76</v>
       </c>
       <c r="R215">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="S215">
         <v>0</v>
@@ -42162,10 +42162,10 @@
         <v>0</v>
       </c>
       <c r="AE215">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AF215">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG215">
         <v>0</v>
@@ -42263,7 +42263,7 @@
         <v>100</v>
       </c>
       <c r="C216" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="D216" t="s">
         <v>185</v>
@@ -42302,13 +42302,13 @@
         <v>699</v>
       </c>
       <c r="P216">
-        <v>5.3</v>
+        <v>0</v>
       </c>
       <c r="Q216">
-        <v>3.73</v>
+        <v>0</v>
       </c>
       <c r="R216">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="S216">
         <v>0</v>
@@ -42347,10 +42347,10 @@
         <v>0</v>
       </c>
       <c r="AE216">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AF216">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AG216">
         <v>0</v>
@@ -42451,7 +42451,7 @@
         <v>180</v>
       </c>
       <c r="D217" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E217" t="s">
         <v>403</v>
@@ -42487,13 +42487,13 @@
         <v>699</v>
       </c>
       <c r="P217">
-        <v>1.59</v>
+        <v>2.15</v>
       </c>
       <c r="Q217">
-        <v>4.73</v>
+        <v>3.44</v>
       </c>
       <c r="R217">
-        <v>5.79</v>
+        <v>3.5</v>
       </c>
       <c r="S217">
         <v>0</v>
@@ -42532,16 +42532,16 @@
         <v>0</v>
       </c>
       <c r="AE217">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AF217">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG217">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AH217">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AI217">
         <v>0</v>
@@ -42633,7 +42633,7 @@
         <v>100</v>
       </c>
       <c r="C218" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="D218" t="s">
         <v>186</v>
@@ -42672,13 +42672,13 @@
         <v>699</v>
       </c>
       <c r="P218">
-        <v>2.48</v>
+        <v>4.68</v>
       </c>
       <c r="Q218">
-        <v>3.5</v>
+        <v>4.32</v>
       </c>
       <c r="R218">
-        <v>3.07</v>
+        <v>1.76</v>
       </c>
       <c r="S218">
         <v>0</v>
@@ -42717,10 +42717,10 @@
         <v>0</v>
       </c>
       <c r="AE218">
-        <v>1.8</v>
+        <v>1.58</v>
       </c>
       <c r="AF218">
-        <v>1.9</v>
+        <v>2.25</v>
       </c>
       <c r="AG218">
         <v>0</v>
@@ -42818,7 +42818,7 @@
         <v>100</v>
       </c>
       <c r="C219" t="s">
-        <v>147</v>
+        <v>179</v>
       </c>
       <c r="D219" t="s">
         <v>186</v>
@@ -42857,13 +42857,13 @@
         <v>699</v>
       </c>
       <c r="P219">
-        <v>0</v>
+        <v>3.17</v>
       </c>
       <c r="Q219">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="R219">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="S219">
         <v>0</v>
@@ -42902,10 +42902,10 @@
         <v>0</v>
       </c>
       <c r="AE219">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AF219">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG219">
         <v>0</v>
@@ -43006,7 +43006,7 @@
         <v>179</v>
       </c>
       <c r="D220" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E220" t="s">
         <v>406</v>
@@ -43042,13 +43042,13 @@
         <v>699</v>
       </c>
       <c r="P220">
-        <v>2.15</v>
+        <v>2.38</v>
       </c>
       <c r="Q220">
-        <v>3.44</v>
+        <v>3.9</v>
       </c>
       <c r="R220">
-        <v>3.5</v>
+        <v>2.96</v>
       </c>
       <c r="S220">
         <v>0</v>
@@ -43087,10 +43087,10 @@
         <v>0</v>
       </c>
       <c r="AE220">
-        <v>1.95</v>
+        <v>1.58</v>
       </c>
       <c r="AF220">
-        <v>1.75</v>
+        <v>2.25</v>
       </c>
       <c r="AG220">
         <v>0</v>
@@ -43188,10 +43188,10 @@
         <v>100</v>
       </c>
       <c r="C221" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="D221" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E221" t="s">
         <v>407</v>
@@ -43227,13 +43227,13 @@
         <v>699</v>
       </c>
       <c r="P221">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="Q221">
-        <v>3.78</v>
+        <v>0</v>
       </c>
       <c r="R221">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="S221">
         <v>0</v>
@@ -43272,10 +43272,10 @@
         <v>0</v>
       </c>
       <c r="AE221">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AF221">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AG221">
         <v>0</v>
@@ -43376,7 +43376,7 @@
         <v>180</v>
       </c>
       <c r="D222" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E222" t="s">
         <v>408</v>
@@ -43412,13 +43412,13 @@
         <v>699</v>
       </c>
       <c r="P222">
-        <v>4.05</v>
+        <v>5.3</v>
       </c>
       <c r="Q222">
-        <v>3.76</v>
+        <v>3.73</v>
       </c>
       <c r="R222">
-        <v>1.99</v>
+        <v>1.71</v>
       </c>
       <c r="S222">
         <v>0</v>
@@ -43457,10 +43457,10 @@
         <v>0</v>
       </c>
       <c r="AE222">
-        <v>1.85</v>
+        <v>1.95</v>
       </c>
       <c r="AF222">
-        <v>1.85</v>
+        <v>1.73</v>
       </c>
       <c r="AG222">
         <v>0</v>
@@ -43743,10 +43743,10 @@
         <v>100</v>
       </c>
       <c r="C224" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="D224" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E224" t="s">
         <v>410</v>
@@ -43782,13 +43782,13 @@
         <v>699</v>
       </c>
       <c r="P224">
-        <v>4.68</v>
+        <v>1.79</v>
       </c>
       <c r="Q224">
-        <v>4.32</v>
+        <v>3.5</v>
       </c>
       <c r="R224">
-        <v>1.76</v>
+        <v>4.39</v>
       </c>
       <c r="S224">
         <v>0</v>
@@ -43827,10 +43827,10 @@
         <v>0</v>
       </c>
       <c r="AE224">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AF224">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AG224">
         <v>0</v>
@@ -43928,10 +43928,10 @@
         <v>100</v>
       </c>
       <c r="C225" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="D225" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E225" t="s">
         <v>411</v>
@@ -43967,13 +43967,13 @@
         <v>699</v>
       </c>
       <c r="P225">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="Q225">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="R225">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="S225">
         <v>0</v>
@@ -44012,10 +44012,10 @@
         <v>0</v>
       </c>
       <c r="AE225">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AF225">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AG225">
         <v>0</v>
@@ -44113,7 +44113,7 @@
         <v>100</v>
       </c>
       <c r="C226" t="s">
-        <v>180</v>
+        <v>148</v>
       </c>
       <c r="D226" t="s">
         <v>186</v>
@@ -44152,13 +44152,13 @@
         <v>699</v>
       </c>
       <c r="P226">
-        <v>3.17</v>
+        <v>0</v>
       </c>
       <c r="Q226">
-        <v>3.68</v>
+        <v>0</v>
       </c>
       <c r="R226">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="S226">
         <v>0</v>
@@ -44197,10 +44197,10 @@
         <v>0</v>
       </c>
       <c r="AE226">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AF226">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AG226">
         <v>0</v>
@@ -44298,7 +44298,7 @@
         <v>100</v>
       </c>
       <c r="C227" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="D227" t="s">
         <v>186</v>
@@ -44337,13 +44337,13 @@
         <v>699</v>
       </c>
       <c r="P227">
-        <v>2.38</v>
+        <v>1.18</v>
       </c>
       <c r="Q227">
-        <v>3.9</v>
+        <v>9.15</v>
       </c>
       <c r="R227">
-        <v>2.96</v>
+        <v>17</v>
       </c>
       <c r="S227">
         <v>0</v>
@@ -44382,16 +44382,16 @@
         <v>0</v>
       </c>
       <c r="AE227">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AF227">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AG227">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AH227">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AI227">
         <v>0</v>
@@ -44483,10 +44483,10 @@
         <v>100</v>
       </c>
       <c r="C228" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="D228" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E228" t="s">
         <v>414</v>
@@ -44522,13 +44522,13 @@
         <v>699</v>
       </c>
       <c r="P228">
-        <v>1.79</v>
+        <v>2.48</v>
       </c>
       <c r="Q228">
         <v>3.5</v>
       </c>
       <c r="R228">
-        <v>4.39</v>
+        <v>3.07</v>
       </c>
       <c r="S228">
         <v>0</v>
@@ -44567,10 +44567,10 @@
         <v>0</v>
       </c>
       <c r="AE228">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AF228">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AG228">
         <v>0</v>
@@ -44668,7 +44668,7 @@
         <v>100</v>
       </c>
       <c r="C229" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="D229" t="s">
         <v>186</v>
@@ -44707,13 +44707,13 @@
         <v>699</v>
       </c>
       <c r="P229">
-        <v>1.18</v>
+        <v>1.59</v>
       </c>
       <c r="Q229">
-        <v>9.15</v>
+        <v>4.73</v>
       </c>
       <c r="R229">
-        <v>17</v>
+        <v>5.79</v>
       </c>
       <c r="S229">
         <v>0</v>
@@ -44758,10 +44758,10 @@
         <v>0</v>
       </c>
       <c r="AG229">
-        <v>1.73</v>
+        <v>2.3</v>
       </c>
       <c r="AH229">
-        <v>1.98</v>
+        <v>1.55</v>
       </c>
       <c r="AI229">
         <v>0</v>
@@ -45408,10 +45408,10 @@
         <v>102</v>
       </c>
       <c r="C233" t="s">
-        <v>177</v>
+        <v>170</v>
       </c>
       <c r="D233" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E233" t="s">
         <v>419</v>
@@ -45593,7 +45593,7 @@
         <v>102</v>
       </c>
       <c r="C234" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="D234" t="s">
         <v>185</v>
@@ -45778,10 +45778,10 @@
         <v>102</v>
       </c>
       <c r="C235" t="s">
-        <v>170</v>
+        <v>177</v>
       </c>
       <c r="D235" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E235" t="s">
         <v>421</v>
@@ -45963,7 +45963,7 @@
         <v>102</v>
       </c>
       <c r="C236" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="D236" t="s">
         <v>185</v>
@@ -46148,7 +46148,7 @@
         <v>102</v>
       </c>
       <c r="C237" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="D237" t="s">
         <v>185</v>
@@ -46372,13 +46372,13 @@
         <v>699</v>
       </c>
       <c r="P238">
-        <v>1.67</v>
+        <v>2.23</v>
       </c>
       <c r="Q238">
-        <v>3.61</v>
+        <v>3.71</v>
       </c>
       <c r="R238">
-        <v>5.14</v>
+        <v>3.21</v>
       </c>
       <c r="S238">
         <v>0</v>
@@ -46417,10 +46417,10 @@
         <v>0</v>
       </c>
       <c r="AE238">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AF238">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AG238">
         <v>0</v>
@@ -46557,13 +46557,13 @@
         <v>699</v>
       </c>
       <c r="P239">
-        <v>2.23</v>
+        <v>1.67</v>
       </c>
       <c r="Q239">
-        <v>3.71</v>
+        <v>3.61</v>
       </c>
       <c r="R239">
-        <v>3.21</v>
+        <v>5.14</v>
       </c>
       <c r="S239">
         <v>0</v>
@@ -46602,10 +46602,10 @@
         <v>0</v>
       </c>
       <c r="AE239">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AF239">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AG239">
         <v>0</v>
@@ -47073,7 +47073,7 @@
         <v>106</v>
       </c>
       <c r="C242" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="D242" t="s">
         <v>185</v>
@@ -47112,13 +47112,13 @@
         <v>699</v>
       </c>
       <c r="P242">
-        <v>1.79</v>
+        <v>2.81</v>
       </c>
       <c r="Q242">
-        <v>3.62</v>
+        <v>3.08</v>
       </c>
       <c r="R242">
-        <v>4.84</v>
+        <v>2.51</v>
       </c>
       <c r="S242">
         <v>0</v>
@@ -47157,10 +47157,10 @@
         <v>0</v>
       </c>
       <c r="AE242">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AF242">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AG242">
         <v>0</v>
@@ -47258,7 +47258,7 @@
         <v>106</v>
       </c>
       <c r="C243" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="D243" t="s">
         <v>185</v>
@@ -47297,13 +47297,13 @@
         <v>699</v>
       </c>
       <c r="P243">
-        <v>2.81</v>
+        <v>2.13</v>
       </c>
       <c r="Q243">
-        <v>3.08</v>
+        <v>3.34</v>
       </c>
       <c r="R243">
-        <v>2.51</v>
+        <v>3.67</v>
       </c>
       <c r="S243">
         <v>0</v>
@@ -47342,10 +47342,10 @@
         <v>0</v>
       </c>
       <c r="AE243">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AF243">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AG243">
         <v>0</v>
@@ -47443,7 +47443,7 @@
         <v>106</v>
       </c>
       <c r="C244" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="D244" t="s">
         <v>185</v>
@@ -47482,13 +47482,13 @@
         <v>699</v>
       </c>
       <c r="P244">
-        <v>2.13</v>
+        <v>2.26</v>
       </c>
       <c r="Q244">
-        <v>3.34</v>
+        <v>3.22</v>
       </c>
       <c r="R244">
-        <v>3.67</v>
+        <v>3.46</v>
       </c>
       <c r="S244">
         <v>0</v>
@@ -47527,10 +47527,10 @@
         <v>0</v>
       </c>
       <c r="AE244">
-        <v>1.95</v>
+        <v>2.25</v>
       </c>
       <c r="AF244">
-        <v>1.73</v>
+        <v>1.57</v>
       </c>
       <c r="AG244">
         <v>0</v>
@@ -47628,7 +47628,7 @@
         <v>106</v>
       </c>
       <c r="C245" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="D245" t="s">
         <v>185</v>
@@ -47667,13 +47667,13 @@
         <v>699</v>
       </c>
       <c r="P245">
-        <v>2.26</v>
+        <v>1.79</v>
       </c>
       <c r="Q245">
-        <v>3.22</v>
+        <v>3.62</v>
       </c>
       <c r="R245">
-        <v>3.46</v>
+        <v>4.84</v>
       </c>
       <c r="S245">
         <v>0</v>
@@ -47712,10 +47712,10 @@
         <v>0</v>
       </c>
       <c r="AE245">
-        <v>2.25</v>
+        <v>1.87</v>
       </c>
       <c r="AF245">
-        <v>1.57</v>
+        <v>1.8</v>
       </c>
       <c r="AG245">
         <v>0</v>
@@ -47998,7 +47998,7 @@
         <v>108</v>
       </c>
       <c r="C247" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="D247" t="s">
         <v>185</v>
@@ -48037,13 +48037,13 @@
         <v>699</v>
       </c>
       <c r="P247">
-        <v>0</v>
+        <v>3.79</v>
       </c>
       <c r="Q247">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="R247">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="S247">
         <v>0</v>
@@ -48082,10 +48082,10 @@
         <v>0</v>
       </c>
       <c r="AE247">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AF247">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AG247">
         <v>0</v>
@@ -48183,7 +48183,7 @@
         <v>108</v>
       </c>
       <c r="C248" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="D248" t="s">
         <v>185</v>
@@ -48222,13 +48222,13 @@
         <v>699</v>
       </c>
       <c r="P248">
-        <v>3.79</v>
+        <v>0</v>
       </c>
       <c r="Q248">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="R248">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="S248">
         <v>0</v>
@@ -48267,10 +48267,10 @@
         <v>0</v>
       </c>
       <c r="AE248">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AF248">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AG248">
         <v>0</v>
@@ -48368,7 +48368,7 @@
         <v>109</v>
       </c>
       <c r="C249" t="s">
-        <v>184</v>
+        <v>174</v>
       </c>
       <c r="D249" t="s">
         <v>185</v>
@@ -48407,13 +48407,13 @@
         <v>699</v>
       </c>
       <c r="P249">
-        <v>1.72</v>
+        <v>4.44</v>
       </c>
       <c r="Q249">
-        <v>3.97</v>
+        <v>3.5</v>
       </c>
       <c r="R249">
-        <v>5.09</v>
+        <v>1.73</v>
       </c>
       <c r="S249">
         <v>0</v>
@@ -48452,10 +48452,10 @@
         <v>0</v>
       </c>
       <c r="AE249">
-        <v>1.7</v>
+        <v>1.99</v>
       </c>
       <c r="AF249">
-        <v>2</v>
+        <v>1.76</v>
       </c>
       <c r="AG249">
         <v>0</v>
@@ -48553,7 +48553,7 @@
         <v>109</v>
       </c>
       <c r="C250" t="s">
-        <v>177</v>
+        <v>183</v>
       </c>
       <c r="D250" t="s">
         <v>185</v>
@@ -48592,13 +48592,13 @@
         <v>699</v>
       </c>
       <c r="P250">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="Q250">
-        <v>0</v>
+        <v>3.97</v>
       </c>
       <c r="R250">
-        <v>0</v>
+        <v>5.09</v>
       </c>
       <c r="S250">
         <v>0</v>
@@ -48637,10 +48637,10 @@
         <v>0</v>
       </c>
       <c r="AE250">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AF250">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG250">
         <v>0</v>
@@ -48738,7 +48738,7 @@
         <v>109</v>
       </c>
       <c r="C251" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="D251" t="s">
         <v>185</v>
@@ -48777,13 +48777,13 @@
         <v>699</v>
       </c>
       <c r="P251">
-        <v>4.44</v>
+        <v>0</v>
       </c>
       <c r="Q251">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="R251">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="S251">
         <v>0</v>
@@ -48822,10 +48822,10 @@
         <v>0</v>
       </c>
       <c r="AE251">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="AF251">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AG251">
         <v>0</v>
@@ -48923,7 +48923,7 @@
         <v>110</v>
       </c>
       <c r="C252" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="D252" t="s">
         <v>185</v>
@@ -49108,7 +49108,7 @@
         <v>111</v>
       </c>
       <c r="C253" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="D253" t="s">
         <v>185</v>
@@ -49848,7 +49848,7 @@
         <v>114</v>
       </c>
       <c r="C257" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="D257" t="s">
         <v>185</v>

--- a/jogos_2026-05-10.xlsx
+++ b/jogos_2026-05-10.xlsx
@@ -370,12 +370,12 @@
     <t>South Korea K League 1</t>
   </si>
   <si>
+    <t>Russia FNL</t>
+  </si>
+  <si>
     <t>China China League One</t>
   </si>
   <si>
-    <t>Russia FNL</t>
-  </si>
-  <si>
     <t>Czech Republic FNL</t>
   </si>
   <si>
@@ -388,24 +388,24 @@
     <t>Russia Russian Premier League</t>
   </si>
   <si>
+    <t>Vietnam V.League 1</t>
+  </si>
+  <si>
+    <t>Spain Primera Division Women</t>
+  </si>
+  <si>
+    <t>Ethiopia Ethiopia Premier League</t>
+  </si>
+  <si>
+    <t>Poland 1. Liga</t>
+  </si>
+  <si>
+    <t>Portugal Liga 3</t>
+  </si>
+  <si>
     <t>Kazakhstan Kazakhstan Premier League</t>
   </si>
   <si>
-    <t>Spain Primera Division Women</t>
-  </si>
-  <si>
-    <t>Ethiopia Ethiopia Premier League</t>
-  </si>
-  <si>
-    <t>Portugal Liga 3</t>
-  </si>
-  <si>
-    <t>Poland 1. Liga</t>
-  </si>
-  <si>
-    <t>Vietnam V.League 1</t>
-  </si>
-  <si>
     <t>Poland Ekstraklasa</t>
   </si>
   <si>
@@ -427,42 +427,42 @@
     <t>Lithuania A Lyga</t>
   </si>
   <si>
+    <t>Germany 2. Bundesliga</t>
+  </si>
+  <si>
     <t>Germany 3. Liga</t>
   </si>
   <si>
     <t>India Indian Super League</t>
   </si>
   <si>
+    <t>Belgium Pro League</t>
+  </si>
+  <si>
     <t>Estonia Meistriliiga</t>
   </si>
   <si>
-    <t>Germany 2. Bundesliga</t>
-  </si>
-  <si>
     <t>Singapore S.League</t>
   </si>
   <si>
-    <t>Belgium Pro League</t>
-  </si>
-  <si>
     <t>Croatia Druga HNL</t>
   </si>
   <si>
+    <t>Sweden Allsvenskan</t>
+  </si>
+  <si>
     <t>Denmark Superliga</t>
   </si>
   <si>
-    <t>Sweden Allsvenskan</t>
+    <t>Georgia Erovnuli Liga</t>
+  </si>
+  <si>
+    <t>Spain La Liga</t>
   </si>
   <si>
     <t>Switzerland Super League</t>
   </si>
   <si>
-    <t>Georgia Erovnuli Liga</t>
-  </si>
-  <si>
-    <t>Spain La Liga</t>
-  </si>
-  <si>
     <t>Spain Segunda División</t>
   </si>
   <si>
@@ -475,6 +475,9 @@
     <t>England Premier League</t>
   </si>
   <si>
+    <t>Romania Liga I</t>
+  </si>
+  <si>
     <t>Czech Republic First League</t>
   </si>
   <si>
@@ -484,12 +487,12 @@
     <t>Slovenia PrvaLiga</t>
   </si>
   <si>
-    <t>Romania Liga I</t>
-  </si>
-  <si>
     <t>Germany Bundesliga</t>
   </si>
   <si>
+    <t>Hungary NB II</t>
+  </si>
+  <si>
     <t>Greece Super League</t>
   </si>
   <si>
@@ -499,9 +502,6 @@
     <t>Croatia Prva HNL</t>
   </si>
   <si>
-    <t>Hungary NB II</t>
-  </si>
-  <si>
     <t>Netherlands Eredivisie</t>
   </si>
   <si>
@@ -511,12 +511,12 @@
     <t>Norway First Division</t>
   </si>
   <si>
+    <t>FYR Macedonia First Football League</t>
+  </si>
+  <si>
     <t>Austria Bundesliga</t>
   </si>
   <si>
-    <t>FYR Macedonia First Football League</t>
-  </si>
-  <si>
     <t>UAE Arabian Gulf League</t>
   </si>
   <si>
@@ -532,15 +532,15 @@
     <t>Saudi Arabia Professional League</t>
   </si>
   <si>
+    <t>Serbia SuperLiga</t>
+  </si>
+  <si>
+    <t>USA NWSL</t>
+  </si>
+  <si>
     <t>Chile Primera B</t>
   </si>
   <si>
-    <t>Serbia SuperLiga</t>
-  </si>
-  <si>
-    <t>USA NWSL</t>
-  </si>
-  <si>
     <t>Israel Israeli Premier League</t>
   </si>
   <si>
@@ -553,18 +553,18 @@
     <t>Argentina Prim B Nacional</t>
   </si>
   <si>
+    <t>Brazil Serie A</t>
+  </si>
+  <si>
+    <t>Brazil Serie B</t>
+  </si>
+  <si>
     <t>France Ligue 1</t>
   </si>
   <si>
-    <t>Brazil Serie A</t>
-  </si>
-  <si>
     <t>Bolivia LFPB</t>
   </si>
   <si>
-    <t>Brazil Serie B</t>
-  </si>
-  <si>
     <t>USA MLS</t>
   </si>
   <si>
@@ -583,39 +583,39 @@
     <t>Seongnam</t>
   </si>
   <si>
+    <t>Blacktown City</t>
+  </si>
+  <si>
+    <t>Ulsan</t>
+  </si>
+  <si>
     <t>Rockdale City Suns</t>
   </si>
   <si>
-    <t>Ulsan</t>
-  </si>
-  <si>
-    <t>Blacktown City</t>
-  </si>
-  <si>
     <t>APIA Leichhardt Tigers</t>
   </si>
   <si>
+    <t>Ufa</t>
+  </si>
+  <si>
     <t>Yanbian Longding</t>
   </si>
   <si>
-    <t>Ufa</t>
+    <t>Dalian Huayi</t>
   </si>
   <si>
     <t>Shaanxi Union</t>
   </si>
   <si>
-    <t>Dalian Huayi</t>
+    <t>Anyang</t>
+  </si>
+  <si>
+    <t>Busan I'Park</t>
   </si>
   <si>
     <t>Ansan Greeners</t>
   </si>
   <si>
-    <t>Anyang</t>
-  </si>
-  <si>
-    <t>Busan I'Park</t>
-  </si>
-  <si>
     <t>Slavia Praha U21</t>
   </si>
   <si>
@@ -634,442 +634,463 @@
     <t>Orenburg</t>
   </si>
   <si>
+    <t>Sichuan Jiuniu</t>
+  </si>
+  <si>
+    <t>Gyeongnam</t>
+  </si>
+  <si>
+    <t>Hoang Anh Gia Lai</t>
+  </si>
+  <si>
+    <t>Levante W</t>
+  </si>
+  <si>
+    <t>Sheger Ketema</t>
+  </si>
+  <si>
+    <t>Polonia Warszawa</t>
+  </si>
+  <si>
+    <t>Amarante</t>
+  </si>
+  <si>
     <t>Ulytau</t>
   </si>
   <si>
-    <t>Levante W</t>
-  </si>
-  <si>
-    <t>Sheger Ketema</t>
-  </si>
-  <si>
-    <t>Amarante</t>
-  </si>
-  <si>
-    <t>Polonia Warszawa</t>
-  </si>
-  <si>
     <t>Sokol Saratov</t>
   </si>
   <si>
-    <t>Sichuan Jiuniu</t>
-  </si>
-  <si>
-    <t>Gyeongnam</t>
-  </si>
-  <si>
-    <t>Hoang Anh Gia Lai</t>
-  </si>
-  <si>
     <t>Piast Gliwice</t>
   </si>
   <si>
     <t>Hellas Verona</t>
   </si>
   <si>
+    <t>Rayong</t>
+  </si>
+  <si>
+    <t>Chonburi</t>
+  </si>
+  <si>
+    <t>Shenyang Urban</t>
+  </si>
+  <si>
+    <t>Shenzhen Juniors</t>
+  </si>
+  <si>
+    <t>Ho Chi Minh City</t>
+  </si>
+  <si>
+    <t>Hà Nội II</t>
+  </si>
+  <si>
+    <t>Piteå Women</t>
+  </si>
+  <si>
+    <t>Celtic</t>
+  </si>
+  <si>
+    <t>Chiangrai United</t>
+  </si>
+  <si>
+    <t>Bangkok Glass</t>
+  </si>
+  <si>
+    <t>Ayutthaya United</t>
+  </si>
+  <si>
+    <t>Buriram United</t>
+  </si>
+  <si>
     <t>Kanchanaburi</t>
   </si>
   <si>
-    <t>Bangkok Glass</t>
-  </si>
-  <si>
-    <t>Ho Chi Minh City</t>
-  </si>
-  <si>
-    <t>Shenzhen Juniors</t>
-  </si>
-  <si>
-    <t>Hà Nội II</t>
-  </si>
-  <si>
-    <t>Chonburi</t>
+    <t>Sukhothai</t>
   </si>
   <si>
     <t>Altay</t>
   </si>
   <si>
-    <t>Chiangrai United</t>
-  </si>
-  <si>
-    <t>Buriram United</t>
-  </si>
-  <si>
-    <t>Ayutthaya United</t>
-  </si>
-  <si>
-    <t>Piteå Women</t>
-  </si>
-  <si>
-    <t>Celtic</t>
-  </si>
-  <si>
-    <t>Shenyang Urban</t>
-  </si>
-  <si>
-    <t>Rayong</t>
-  </si>
-  <si>
-    <t>Sukhothai</t>
-  </si>
-  <si>
     <t>Spartak Varna</t>
   </si>
   <si>
     <t>Sūduva</t>
   </si>
   <si>
+    <t>Preußen Münster</t>
+  </si>
+  <si>
+    <t>Dongguan United</t>
+  </si>
+  <si>
+    <t>Fortuna Düsseldorf</t>
+  </si>
+  <si>
     <t>Havelse</t>
   </si>
   <si>
+    <t>Hertha BSC</t>
+  </si>
+  <si>
     <t>Kerala Blasters</t>
   </si>
   <si>
+    <t>KAA Gent</t>
+  </si>
+  <si>
     <t>Nõmme Kalju</t>
   </si>
   <si>
-    <t>Fortuna Düsseldorf</t>
-  </si>
-  <si>
-    <t>Preußen Münster</t>
-  </si>
-  <si>
-    <t>Hertha BSC</t>
-  </si>
-  <si>
-    <t>Dongguan United</t>
+    <t>Hougang United</t>
+  </si>
+  <si>
+    <t>Nantong Zhiyun</t>
   </si>
   <si>
     <t>Home United</t>
   </si>
   <si>
-    <t>KAA Gent</t>
-  </si>
-  <si>
-    <t>Nantong Zhiyun</t>
-  </si>
-  <si>
-    <t>Hougang United</t>
+    <t>Beijing Guoan</t>
   </si>
   <si>
     <t>Zhejiang FC</t>
   </si>
   <si>
-    <t>Beijing Guoan</t>
-  </si>
-  <si>
     <t>Hrvace</t>
   </si>
   <si>
+    <t>Kalmar</t>
+  </si>
+  <si>
+    <t>Nordsjælland</t>
+  </si>
+  <si>
+    <t>Meshakhte</t>
+  </si>
+  <si>
+    <t>RCD Mallorca</t>
+  </si>
+  <si>
+    <t>Bahardar</t>
+  </si>
+  <si>
+    <t>Aktobe</t>
+  </si>
+  <si>
+    <t>Qingdao Jonoon</t>
+  </si>
+  <si>
+    <t>Lugano</t>
+  </si>
+  <si>
+    <t>FC Andorra</t>
+  </si>
+  <si>
+    <t>AIK</t>
+  </si>
+  <si>
     <t>Vejle</t>
   </si>
   <si>
-    <t>Bahardar</t>
-  </si>
-  <si>
     <t>Zenit</t>
   </si>
   <si>
-    <t>Kalmar</t>
-  </si>
-  <si>
-    <t>Aktobe</t>
-  </si>
-  <si>
-    <t>Lugano</t>
-  </si>
-  <si>
-    <t>Qingdao Jonoon</t>
-  </si>
-  <si>
-    <t>Nordsjælland</t>
-  </si>
-  <si>
-    <t>Meshakhte</t>
-  </si>
-  <si>
-    <t>RCD Mallorca</t>
-  </si>
-  <si>
     <t>PSIM Yogyakarta</t>
   </si>
   <si>
-    <t>FC Andorra</t>
-  </si>
-  <si>
-    <t>AIK</t>
+    <t>Kuala Lumpur</t>
   </si>
   <si>
     <t>Công An Nhân Dân</t>
   </si>
   <si>
-    <t>Kuala Lumpur</t>
+    <t>Rosenborg</t>
   </si>
   <si>
     <t>Baník Ostrava U21</t>
   </si>
   <si>
-    <t>Rosenborg</t>
-  </si>
-  <si>
     <t>Tychy 71</t>
   </si>
   <si>
     <t>Wisła Płock</t>
   </si>
   <si>
+    <t>Arba Minch Kenema</t>
+  </si>
+  <si>
+    <t>Crystal Palace</t>
+  </si>
+  <si>
+    <t>Botoşani</t>
+  </si>
+  <si>
+    <t>Burnley</t>
+  </si>
+  <si>
     <t>Uppsala W</t>
   </si>
   <si>
-    <t>Crystal Palace</t>
+    <t>Astana</t>
+  </si>
+  <si>
+    <t>Pardubice</t>
+  </si>
+  <si>
+    <t>Nottingham Forest</t>
+  </si>
+  <si>
+    <t>Sigma Olomouc</t>
+  </si>
+  <si>
+    <t>Turan</t>
   </si>
   <si>
     <t>Cremonese</t>
   </si>
   <si>
-    <t>Sigma Olomouc</t>
-  </si>
-  <si>
-    <t>Pardubice</t>
-  </si>
-  <si>
-    <t>Astana</t>
-  </si>
-  <si>
-    <t>Turan</t>
+    <t>NK Primorje</t>
   </si>
   <si>
     <t>Kelantan United</t>
   </si>
   <si>
-    <t>NK Primorje</t>
-  </si>
-  <si>
-    <t>Botoşani</t>
-  </si>
-  <si>
     <t>Fiorentina</t>
   </si>
   <si>
-    <t>Burnley</t>
-  </si>
-  <si>
-    <t>Arba Minch Kenema</t>
-  </si>
-  <si>
-    <t>Nottingham Forest</t>
-  </si>
-  <si>
     <t>Hamburger SV</t>
   </si>
   <si>
     <t>Botev Vratsa</t>
   </si>
   <si>
+    <t>Honvéd W</t>
+  </si>
+  <si>
     <t>Aris</t>
   </si>
   <si>
+    <t>Nõmme United</t>
+  </si>
+  <si>
+    <t>Royal Antwerp FC</t>
+  </si>
+  <si>
+    <t>EB - Streymur</t>
+  </si>
+  <si>
+    <t>Volos NFC</t>
+  </si>
+  <si>
+    <t>Osijek</t>
+  </si>
+  <si>
     <t>B36</t>
   </si>
   <si>
-    <t>Royal Antwerp FC</t>
-  </si>
-  <si>
-    <t>Osijek</t>
-  </si>
-  <si>
-    <t>Nõmme United</t>
-  </si>
-  <si>
-    <t>EB - Streymur</t>
+    <t>Silkeborg</t>
+  </si>
+  <si>
+    <t>NorthEast United</t>
   </si>
   <si>
     <t>Banga</t>
   </si>
   <si>
-    <t>NorthEast United</t>
-  </si>
-  <si>
-    <t>Silkeborg</t>
-  </si>
-  <si>
-    <t>Honvéd W</t>
-  </si>
-  <si>
-    <t>Volos NFC</t>
-  </si>
-  <si>
     <t>Leganés</t>
   </si>
   <si>
+    <t>Akhmat Grozny</t>
+  </si>
+  <si>
     <t>Athletic Club Bilbao</t>
   </si>
   <si>
-    <t>Akhmat Grozny</t>
-  </si>
-  <si>
     <t>Häcken</t>
   </si>
   <si>
     <t>Sion</t>
   </si>
   <si>
+    <t>Viktoria Köln</t>
+  </si>
+  <si>
     <t>Young Boys</t>
   </si>
   <si>
     <t>Neftekhimik</t>
   </si>
   <si>
-    <t>Viktoria Köln</t>
+    <t>Groningen</t>
   </si>
   <si>
     <t>Go Ahead Eagles</t>
   </si>
   <si>
+    <t>NAC Breda</t>
+  </si>
+  <si>
+    <t>Twente</t>
+  </si>
+  <si>
+    <t>Excelsior</t>
+  </si>
+  <si>
+    <t>Fortuna Sittard</t>
+  </si>
+  <si>
     <t>Telstar</t>
   </si>
   <si>
-    <t>Groningen</t>
-  </si>
-  <si>
     <t>Ajax</t>
   </si>
   <si>
-    <t>Twente</t>
-  </si>
-  <si>
-    <t>NAC Breda</t>
-  </si>
-  <si>
-    <t>Fortuna Sittard</t>
-  </si>
-  <si>
     <t>Feyenoord</t>
   </si>
   <si>
-    <t>Excelsior</t>
+    <t>Sandefjord</t>
+  </si>
+  <si>
+    <t>KFUM</t>
+  </si>
+  <si>
+    <t>Kecskeméti TE</t>
   </si>
   <si>
     <t>Omonia Nicosia</t>
   </si>
   <si>
+    <t>Strømmen</t>
+  </si>
+  <si>
+    <t>Pogoń Siedlce</t>
+  </si>
+  <si>
+    <t>Akademija Pandev</t>
+  </si>
+  <si>
+    <t>Makedonija GjP</t>
+  </si>
+  <si>
+    <t>Real Madrid W</t>
+  </si>
+  <si>
+    <t>Mebrat Hayl</t>
+  </si>
+  <si>
+    <t>Rapid Wien</t>
+  </si>
+  <si>
+    <t>Hartberg</t>
+  </si>
+  <si>
+    <t>LASK Linz</t>
+  </si>
+  <si>
+    <t>Sandnes Ulf</t>
+  </si>
+  <si>
     <t>Åsane</t>
   </si>
   <si>
-    <t>Rapid Wien</t>
+    <t>Szentlőrinc SE</t>
   </si>
   <si>
     <t>Moss</t>
   </si>
   <si>
-    <t>Pogoń Siedlce</t>
-  </si>
-  <si>
-    <t>Sandefjord</t>
-  </si>
-  <si>
-    <t>KFUM</t>
-  </si>
-  <si>
-    <t>Hartberg</t>
-  </si>
-  <si>
-    <t>LASK Linz</t>
-  </si>
-  <si>
-    <t>Makedonija GjP</t>
+    <t>Karcag SE</t>
+  </si>
+  <si>
+    <t>Vardar</t>
+  </si>
+  <si>
+    <t>Tromsø</t>
+  </si>
+  <si>
+    <t>Sogndal</t>
+  </si>
+  <si>
+    <t>Raufoss</t>
   </si>
   <si>
     <t>Pelister</t>
   </si>
   <si>
+    <t>Apollon</t>
+  </si>
+  <si>
     <t>Aresimi</t>
   </si>
   <si>
-    <t>Strømmen</t>
+    <t>Shkendija</t>
+  </si>
+  <si>
+    <t>Budafoki MTE</t>
   </si>
   <si>
     <t>Zbrojovka Brno</t>
   </si>
   <si>
+    <t>Saburtalo</t>
+  </si>
+  <si>
+    <t>Ajka</t>
+  </si>
+  <si>
+    <t>Croatia Zmijavci</t>
+  </si>
+  <si>
     <t>Paphos</t>
   </si>
   <si>
-    <t>Real Madrid W</t>
-  </si>
-  <si>
-    <t>Sogndal</t>
-  </si>
-  <si>
-    <t>Tromsø</t>
-  </si>
-  <si>
-    <t>Shkendija</t>
-  </si>
-  <si>
-    <t>Vardar</t>
-  </si>
-  <si>
-    <t>Sandnes Ulf</t>
-  </si>
-  <si>
-    <t>Croatia Zmijavci</t>
-  </si>
-  <si>
-    <t>Kecskeméti TE</t>
-  </si>
-  <si>
-    <t>Raufoss</t>
-  </si>
-  <si>
-    <t>Mebrat Hayl</t>
-  </si>
-  <si>
-    <t>Akademija Pandev</t>
-  </si>
-  <si>
-    <t>Budafoki MTE</t>
-  </si>
-  <si>
-    <t>Ajka</t>
-  </si>
-  <si>
-    <t>Saburtalo</t>
-  </si>
-  <si>
-    <t>Karcag SE</t>
-  </si>
-  <si>
-    <t>Szentlőrinc SE</t>
-  </si>
-  <si>
-    <t>Apollon</t>
+    <t>Bani Yas</t>
+  </si>
+  <si>
+    <t>Dibba Al Fujairah</t>
   </si>
   <si>
     <t>Al Ain</t>
   </si>
   <si>
-    <t>Bani Yas</t>
-  </si>
-  <si>
     <t>Al Bataeh</t>
   </si>
   <si>
-    <t>Dibba Al Fujairah</t>
+    <t>West Ham United</t>
+  </si>
+  <si>
+    <t>Köln</t>
+  </si>
+  <si>
+    <t>Nieciecza</t>
+  </si>
+  <si>
+    <t>Sekhukhune United</t>
   </si>
   <si>
     <t>Neftçi</t>
   </si>
   <si>
-    <t>Köln</t>
-  </si>
-  <si>
-    <t>West Ham United</t>
-  </si>
-  <si>
-    <t>Nieciecza</t>
-  </si>
-  <si>
-    <t>Sekhukhune United</t>
+    <t>Dečić</t>
+  </si>
+  <si>
+    <t>Parma</t>
+  </si>
+  <si>
+    <t>Mornar</t>
+  </si>
+  <si>
+    <t>Jedinstvo</t>
+  </si>
+  <si>
+    <t>Panevėžys</t>
+  </si>
+  <si>
+    <t>Vysočina Jihlava</t>
+  </si>
+  <si>
+    <t>Ittihad Tanger</t>
   </si>
   <si>
     <t>Brøndby</t>
@@ -1078,117 +1099,96 @@
     <t>Arsenal Tivat</t>
   </si>
   <si>
-    <t>Jedinstvo</t>
-  </si>
-  <si>
-    <t>Panevėžys</t>
-  </si>
-  <si>
-    <t>Dečić</t>
-  </si>
-  <si>
-    <t>Mornar</t>
-  </si>
-  <si>
-    <t>Parma</t>
-  </si>
-  <si>
-    <t>Ittihad Tanger</t>
-  </si>
-  <si>
-    <t>Vysočina Jihlava</t>
+    <t>Dinamo Bucureşti</t>
   </si>
   <si>
     <t>Mladost DG</t>
   </si>
   <si>
-    <t>Dinamo Bucureşti</t>
-  </si>
-  <si>
     <t>Al Riyadh</t>
   </si>
   <si>
+    <t>Slaven Koprivnica</t>
+  </si>
+  <si>
+    <t>Skála</t>
+  </si>
+  <si>
+    <t>Dobrudzha 1919</t>
+  </si>
+  <si>
     <t>07 Vestur</t>
   </si>
   <si>
-    <t>Skála</t>
-  </si>
-  <si>
-    <t>Slaven Koprivnica</t>
-  </si>
-  <si>
-    <t>Dobrudzha 1919</t>
+    <t>Real Oviedo</t>
+  </si>
+  <si>
+    <t>Jablonec</t>
+  </si>
+  <si>
+    <t>Union Saint-Gilloise</t>
+  </si>
+  <si>
+    <t>Mirandés</t>
+  </si>
+  <si>
+    <t>Olympiakos Piraeus</t>
+  </si>
+  <si>
+    <t>Spartak Subotica</t>
+  </si>
+  <si>
+    <t>Kansas City</t>
   </si>
   <si>
     <t>AEK Athens</t>
   </si>
   <si>
+    <t>Radnički Niš</t>
+  </si>
+  <si>
+    <t>Copiapó</t>
+  </si>
+  <si>
     <t>Antofagasta</t>
   </si>
   <si>
-    <t>Real Oviedo</t>
-  </si>
-  <si>
-    <t>Spartak Subotica</t>
+    <t>Bačka Topola</t>
+  </si>
+  <si>
+    <t>Lokomotiv Moskva</t>
+  </si>
+  <si>
+    <t>Córdoba</t>
   </si>
   <si>
     <t>IMT Novi Beograd</t>
   </si>
   <si>
-    <t>Lokomotiv Moskva</t>
-  </si>
-  <si>
-    <t>Kansas City</t>
-  </si>
-  <si>
-    <t>Olympiakos Piraeus</t>
-  </si>
-  <si>
-    <t>Radnički Niš</t>
-  </si>
-  <si>
-    <t>Córdoba</t>
-  </si>
-  <si>
-    <t>Bačka Topola</t>
-  </si>
-  <si>
-    <t>Mirandés</t>
-  </si>
-  <si>
-    <t>Copiapó</t>
-  </si>
-  <si>
-    <t>Union Saint-Gilloise</t>
-  </si>
-  <si>
-    <t>Jablonec</t>
+    <t>Dinamo Batumi</t>
   </si>
   <si>
     <t>Hapoel Haifa</t>
   </si>
   <si>
+    <t>Hapoel Katamon</t>
+  </si>
+  <si>
+    <t>Tenerife W</t>
+  </si>
+  <si>
     <t>Ironi Tiberias</t>
   </si>
   <si>
-    <t>Hapoel Katamon</t>
-  </si>
-  <si>
-    <t>Tenerife W</t>
+    <t>KA</t>
   </si>
   <si>
     <t>Békéscsaba</t>
   </si>
   <si>
-    <t>Dinamo Batumi</t>
-  </si>
-  <si>
     <t>Csákvári TK</t>
   </si>
   <si>
-    <t>KA</t>
-  </si>
-  <si>
     <t>KRC Genk</t>
   </si>
   <si>
@@ -1204,12 +1204,12 @@
     <t>Al Ittihad</t>
   </si>
   <si>
+    <t>CODM Meknès</t>
+  </si>
+  <si>
     <t>UTS Rabat</t>
   </si>
   <si>
-    <t>CODM Meknès</t>
-  </si>
-  <si>
     <t>Varzim</t>
   </si>
   <si>
@@ -1219,58 +1219,64 @@
     <t>AC Milan</t>
   </si>
   <si>
+    <t>Atlético Mineiro</t>
+  </si>
+  <si>
+    <t>Náutico</t>
+  </si>
+  <si>
+    <t>Metz</t>
+  </si>
+  <si>
+    <t>Auxerre</t>
+  </si>
+  <si>
+    <t>Monaco</t>
+  </si>
+  <si>
+    <t>Club Atlético Güemes</t>
+  </si>
+  <si>
+    <t>Remo</t>
+  </si>
+  <si>
+    <t>PSG</t>
+  </si>
+  <si>
+    <t>Rennes</t>
+  </si>
+  <si>
     <t>Angers SCO</t>
   </si>
   <si>
-    <t>Club Atlético Güemes</t>
-  </si>
-  <si>
-    <t>Atlético Mineiro</t>
-  </si>
-  <si>
     <t>Le Havre</t>
   </si>
   <si>
-    <t>Metz</t>
-  </si>
-  <si>
-    <t>Monaco</t>
+    <t>Toulouse</t>
+  </si>
+  <si>
+    <t>FC Barcelona</t>
+  </si>
+  <si>
+    <t>Independiente Petrolero</t>
   </si>
   <si>
     <t>Agropecuario</t>
   </si>
   <si>
-    <t>Remo</t>
-  </si>
-  <si>
-    <t>Independiente Petrolero</t>
-  </si>
-  <si>
-    <t>Náutico</t>
-  </si>
-  <si>
-    <t>Toulouse</t>
-  </si>
-  <si>
-    <t>FC Barcelona</t>
-  </si>
-  <si>
-    <t>PSG</t>
-  </si>
-  <si>
-    <t>Auxerre</t>
-  </si>
-  <si>
-    <t>Rennes</t>
+    <t>San Martín San Juan</t>
+  </si>
+  <si>
+    <t>Godoy Cruz</t>
   </si>
   <si>
     <t>Chaco For Ever</t>
   </si>
   <si>
-    <t>San Martín San Juan</t>
-  </si>
-  <si>
-    <t>Godoy Cruz</t>
+    <t>Central Norte</t>
+  </si>
+  <si>
+    <t>Portland Timbers II</t>
   </si>
   <si>
     <t>Hassania Agadir</t>
@@ -1282,12 +1288,6 @@
     <t>Los Angeles II</t>
   </si>
   <si>
-    <t>Central Norte</t>
-  </si>
-  <si>
-    <t>Portland Timbers II</t>
-  </si>
-  <si>
     <t>New York City</t>
   </si>
   <si>
@@ -1300,18 +1300,18 @@
     <t>The Strongest</t>
   </si>
   <si>
+    <t>Mirassol</t>
+  </si>
+  <si>
+    <t>Santos</t>
+  </si>
+  <si>
     <t>Avaí</t>
   </si>
   <si>
-    <t>Santos</t>
-  </si>
-  <si>
     <t>Corinthians</t>
   </si>
   <si>
-    <t>Mirassol</t>
-  </si>
-  <si>
     <t>FC Cincinnati II</t>
   </si>
   <si>
@@ -1321,12 +1321,12 @@
     <t>Novorizontino</t>
   </si>
   <si>
+    <t>Minnesota United</t>
+  </si>
+  <si>
     <t>Seattle Reign</t>
   </si>
   <si>
-    <t>Minnesota United</t>
-  </si>
-  <si>
     <t>Atlanta United II</t>
   </si>
   <si>
@@ -1351,39 +1351,39 @@
     <t>Jeonnam Dragons</t>
   </si>
   <si>
+    <t>St. George Saints</t>
+  </si>
+  <si>
+    <t>Bucheon 1995</t>
+  </si>
+  <si>
     <t>Sydney II</t>
   </si>
   <si>
-    <t>Bucheon 1995</t>
-  </si>
-  <si>
-    <t>St. George Saints</t>
-  </si>
-  <si>
     <t>Sydney United</t>
   </si>
   <si>
+    <t>Rotor Volgograd</t>
+  </si>
+  <si>
     <t>Guangxi Hengchen</t>
   </si>
   <si>
-    <t>Rotor Volgograd</t>
+    <t>Guangzhou E-Power</t>
   </si>
   <si>
     <t>Shanghai Jiading</t>
   </si>
   <si>
-    <t>Guangzhou E-Power</t>
+    <t>Jeonbuk Motors</t>
+  </si>
+  <si>
+    <t>Cheonan City</t>
   </si>
   <si>
     <t>Yongin City</t>
   </si>
   <si>
-    <t>Jeonbuk Motors</t>
-  </si>
-  <si>
-    <t>Cheonan City</t>
-  </si>
-  <si>
     <t>Táborsko</t>
   </si>
   <si>
@@ -1402,439 +1402,460 @@
     <t>Krylya Sovetov</t>
   </si>
   <si>
+    <t>Shandong Luneng</t>
+  </si>
+  <si>
+    <t>Gimhae City</t>
+  </si>
+  <si>
+    <t>Pho Hien</t>
+  </si>
+  <si>
+    <t>Logroño W</t>
+  </si>
+  <si>
+    <t>Sidama Bunna</t>
+  </si>
+  <si>
+    <t>Górnik Łęczna</t>
+  </si>
+  <si>
+    <t>União Santarém</t>
+  </si>
+  <si>
     <t>Kairat</t>
   </si>
   <si>
-    <t>Logroño W</t>
-  </si>
-  <si>
-    <t>Sidama Bunna</t>
-  </si>
-  <si>
-    <t>União Santarém</t>
-  </si>
-  <si>
-    <t>Górnik Łęczna</t>
-  </si>
-  <si>
     <t>Spartak Kostroma</t>
   </si>
   <si>
-    <t>Shandong Luneng</t>
-  </si>
-  <si>
-    <t>Gimhae City</t>
-  </si>
-  <si>
-    <t>Pho Hien</t>
-  </si>
-  <si>
     <t>GKS Katowice</t>
   </si>
   <si>
     <t>Como</t>
   </si>
   <si>
+    <t>Bangkok United</t>
+  </si>
+  <si>
+    <t>Nakhon Ratchasima</t>
+  </si>
+  <si>
+    <t>Yunnan Yukun</t>
+  </si>
+  <si>
+    <t>Hebei Kungfu</t>
+  </si>
+  <si>
+    <t>Song Lam Nghe An</t>
+  </si>
+  <si>
+    <t>Viettel</t>
+  </si>
+  <si>
+    <t>Rosengard Women</t>
+  </si>
+  <si>
+    <t>Rangers</t>
+  </si>
+  <si>
+    <t>Uthai Thani</t>
+  </si>
+  <si>
+    <t>Prachuap</t>
+  </si>
+  <si>
+    <t>Port FC</t>
+  </si>
+  <si>
+    <t>Lamphun Warrior</t>
+  </si>
+  <si>
     <t>Ratchaburi</t>
   </si>
   <si>
-    <t>Prachuap</t>
-  </si>
-  <si>
-    <t>Song Lam Nghe An</t>
-  </si>
-  <si>
-    <t>Hebei Kungfu</t>
-  </si>
-  <si>
-    <t>Viettel</t>
-  </si>
-  <si>
-    <t>Nakhon Ratchasima</t>
+    <t>Muang Thong United</t>
   </si>
   <si>
     <t>Ordabasy</t>
   </si>
   <si>
-    <t>Uthai Thani</t>
-  </si>
-  <si>
-    <t>Lamphun Warrior</t>
-  </si>
-  <si>
-    <t>Port FC</t>
-  </si>
-  <si>
-    <t>Rosengard Women</t>
-  </si>
-  <si>
-    <t>Rangers</t>
-  </si>
-  <si>
-    <t>Yunnan Yukun</t>
-  </si>
-  <si>
-    <t>Bangkok United</t>
-  </si>
-  <si>
-    <t>Muang Thong United</t>
-  </si>
-  <si>
     <t>Slavia Sofia</t>
   </si>
   <si>
     <t>Žalgiris</t>
   </si>
   <si>
+    <t>Darmstadt 98</t>
+  </si>
+  <si>
+    <t>Suzhou Dongwu</t>
+  </si>
+  <si>
+    <t>Elversberg</t>
+  </si>
+  <si>
     <t>Schweinfurt</t>
   </si>
   <si>
+    <t>Greuther Fürth</t>
+  </si>
+  <si>
     <t>Mohammedan</t>
   </si>
   <si>
+    <t>RSC Anderlecht</t>
+  </si>
+  <si>
     <t>Tallinna FC Flora</t>
   </si>
   <si>
-    <t>Elversberg</t>
-  </si>
-  <si>
-    <t>Darmstadt 98</t>
-  </si>
-  <si>
-    <t>Greuther Fürth</t>
-  </si>
-  <si>
-    <t>Suzhou Dongwu</t>
+    <t>Tampines Rovers</t>
+  </si>
+  <si>
+    <t>Wuxi Wugou</t>
   </si>
   <si>
     <t>Albirex Niigata S</t>
   </si>
   <si>
-    <t>RSC Anderlecht</t>
-  </si>
-  <si>
-    <t>Wuxi Wugou</t>
-  </si>
-  <si>
-    <t>Tampines Rovers</t>
+    <t>Shanghai SIPG</t>
   </si>
   <si>
     <t>Tianjin Teda</t>
   </si>
   <si>
-    <t>Shanghai SIPG</t>
-  </si>
-  <si>
     <t>Opatija</t>
   </si>
   <si>
+    <t>Halmstad</t>
+  </si>
+  <si>
+    <t>Midtjylland</t>
+  </si>
+  <si>
+    <t>Dila</t>
+  </si>
+  <si>
+    <t>Villarreal</t>
+  </si>
+  <si>
+    <t>Welwalo Adigrat Uni</t>
+  </si>
+  <si>
+    <t>Kaisar</t>
+  </si>
+  <si>
+    <t>Dalian Zhixing</t>
+  </si>
+  <si>
+    <t>St. Gallen</t>
+  </si>
+  <si>
+    <t>UD Las Palmas</t>
+  </si>
+  <si>
+    <t>Djurgården</t>
+  </si>
+  <si>
     <t>Fredericia</t>
   </si>
   <si>
-    <t>Welwalo Adigrat Uni</t>
-  </si>
-  <si>
     <t>FK Sochi</t>
   </si>
   <si>
-    <t>Halmstad</t>
-  </si>
-  <si>
-    <t>Kaisar</t>
-  </si>
-  <si>
-    <t>St. Gallen</t>
-  </si>
-  <si>
-    <t>Dalian Zhixing</t>
-  </si>
-  <si>
-    <t>Midtjylland</t>
-  </si>
-  <si>
-    <t>Dila</t>
-  </si>
-  <si>
-    <t>Villarreal</t>
-  </si>
-  <si>
     <t>Malut United</t>
   </si>
   <si>
-    <t>UD Las Palmas</t>
-  </si>
-  <si>
-    <t>Djurgården</t>
+    <t>Negeri Sembilan</t>
   </si>
   <si>
     <t>Nam Dinh</t>
   </si>
   <si>
-    <t>Negeri Sembilan</t>
+    <t>Lillestrøm</t>
   </si>
   <si>
     <t>Ústí nad Labem</t>
   </si>
   <si>
-    <t>Lillestrøm</t>
-  </si>
-  <si>
     <t>Ruch Chorzów</t>
   </si>
   <si>
     <t>Motor Lublin</t>
   </si>
   <si>
+    <t>Welayta Dicha</t>
+  </si>
+  <si>
+    <t>Everton</t>
+  </si>
+  <si>
+    <t>Petrolul 52</t>
+  </si>
+  <si>
+    <t>Aston Villa</t>
+  </si>
+  <si>
     <t>Vittsjö</t>
   </si>
   <si>
-    <t>Everton</t>
+    <t>Kyzyl-Zhar</t>
+  </si>
+  <si>
+    <t>Karviná</t>
+  </si>
+  <si>
+    <t>Newcastle United</t>
+  </si>
+  <si>
+    <t>Bohemians 1905</t>
+  </si>
+  <si>
+    <t>Karvan FK</t>
   </si>
   <si>
     <t>Pisa</t>
   </si>
   <si>
-    <t>Bohemians 1905</t>
-  </si>
-  <si>
-    <t>Karviná</t>
-  </si>
-  <si>
-    <t>Kyzyl-Zhar</t>
-  </si>
-  <si>
-    <t>Karvan FK</t>
+    <t>Mura</t>
   </si>
   <si>
     <t>Johor Darul Ta'zim</t>
   </si>
   <si>
-    <t>Mura</t>
-  </si>
-  <si>
-    <t>Petrolul 52</t>
-  </si>
-  <si>
     <t>Genoa</t>
   </si>
   <si>
-    <t>Aston Villa</t>
-  </si>
-  <si>
-    <t>Welayta Dicha</t>
-  </si>
-  <si>
-    <t>Newcastle United</t>
-  </si>
-  <si>
     <t>Freiburg</t>
   </si>
   <si>
     <t>Septemvri Sofia</t>
   </si>
   <si>
+    <t>Vasas</t>
+  </si>
+  <si>
     <t>OFI</t>
   </si>
   <si>
+    <t>Paide</t>
+  </si>
+  <si>
+    <t>Sporting Charleroi</t>
+  </si>
+  <si>
+    <t>Víkingur</t>
+  </si>
+  <si>
+    <t>Levadiakos</t>
+  </si>
+  <si>
+    <t>Istra 1961</t>
+  </si>
+  <si>
     <t>KÍ</t>
   </si>
   <si>
-    <t>Sporting Charleroi</t>
-  </si>
-  <si>
-    <t>Istra 1961</t>
-  </si>
-  <si>
-    <t>Paide</t>
-  </si>
-  <si>
-    <t>Víkingur</t>
+    <t>København</t>
+  </si>
+  <si>
+    <t>Chennaiyin</t>
   </si>
   <si>
     <t>TransINVEST Vilnius</t>
   </si>
   <si>
-    <t>Chennaiyin</t>
-  </si>
-  <si>
-    <t>København</t>
-  </si>
-  <si>
-    <t>Vasas</t>
-  </si>
-  <si>
-    <t>Levadiakos</t>
-  </si>
-  <si>
     <t>Racing Santander</t>
   </si>
   <si>
+    <t>Makhachkala</t>
+  </si>
+  <si>
     <t>Valencia CF</t>
   </si>
   <si>
-    <t>Makhachkala</t>
-  </si>
-  <si>
     <t>Malmö FF</t>
   </si>
   <si>
     <t>Thun</t>
   </si>
   <si>
+    <t>Alemannia Aachen</t>
+  </si>
+  <si>
     <t>Basel</t>
   </si>
   <si>
     <t>Volga Ulyanovsk</t>
   </si>
   <si>
-    <t>Alemannia Aachen</t>
+    <t>NEC</t>
   </si>
   <si>
     <t>PSV</t>
   </si>
   <si>
+    <t>Heerenveen</t>
+  </si>
+  <si>
+    <t>Sparta Rotterdam</t>
+  </si>
+  <si>
+    <t>Volendam</t>
+  </si>
+  <si>
+    <t>PEC Zwolle</t>
+  </si>
+  <si>
     <t>Heracles</t>
   </si>
   <si>
-    <t>NEC</t>
-  </si>
-  <si>
     <t>Utrecht</t>
   </si>
   <si>
-    <t>Sparta Rotterdam</t>
-  </si>
-  <si>
-    <t>Heerenveen</t>
-  </si>
-  <si>
-    <t>PEC Zwolle</t>
-  </si>
-  <si>
     <t>AZ</t>
   </si>
   <si>
-    <t>Volendam</t>
+    <t>Kristiansund</t>
+  </si>
+  <si>
+    <t>Viking</t>
+  </si>
+  <si>
+    <t>Mezőkövesd-Zsóry</t>
   </si>
   <si>
     <t>AEK Larnaca</t>
   </si>
   <si>
+    <t>Hødd</t>
+  </si>
+  <si>
+    <t>Stal Rzeszów</t>
+  </si>
+  <si>
+    <t>Rabotnički</t>
+  </si>
+  <si>
+    <t>Tikveš</t>
+  </si>
+  <si>
+    <t>Atletico Madrid W</t>
+  </si>
+  <si>
+    <t>Fasil Ketema</t>
+  </si>
+  <si>
+    <t>Austria Wien</t>
+  </si>
+  <si>
+    <t>Sturm Graz</t>
+  </si>
+  <si>
+    <t>Salzburg</t>
+  </si>
+  <si>
+    <t>Stabæk</t>
+  </si>
+  <si>
     <t>Strømsgodset</t>
   </si>
   <si>
-    <t>Austria Wien</t>
+    <t>Videoton</t>
   </si>
   <si>
     <t>Bryne</t>
   </si>
   <si>
-    <t>Stal Rzeszów</t>
-  </si>
-  <si>
-    <t>Kristiansund</t>
-  </si>
-  <si>
-    <t>Viking</t>
-  </si>
-  <si>
-    <t>Sturm Graz</t>
-  </si>
-  <si>
-    <t>Salzburg</t>
-  </si>
-  <si>
-    <t>Tikveš</t>
+    <t>Tiszakécske</t>
+  </si>
+  <si>
+    <t>Sileks</t>
+  </si>
+  <si>
+    <t>Molde</t>
+  </si>
+  <si>
+    <t>Haugesund</t>
+  </si>
+  <si>
+    <t>Lyn</t>
   </si>
   <si>
     <t>Shkupi</t>
   </si>
   <si>
+    <t>APOEL</t>
+  </si>
+  <si>
     <t>FK Bashkimi Kumanovo</t>
   </si>
   <si>
-    <t>Hødd</t>
+    <t>Struga</t>
+  </si>
+  <si>
+    <t>BVSC</t>
   </si>
   <si>
     <t>Vlašim</t>
   </si>
   <si>
-    <t>Atletico Madrid W</t>
-  </si>
-  <si>
-    <t>Haugesund</t>
-  </si>
-  <si>
-    <t>Molde</t>
-  </si>
-  <si>
-    <t>Struga</t>
-  </si>
-  <si>
-    <t>Sileks</t>
-  </si>
-  <si>
-    <t>Stabæk</t>
+    <t>Torpedo Kutaisi</t>
+  </si>
+  <si>
+    <t>Szeged 2011</t>
   </si>
   <si>
     <t>Jarun</t>
   </si>
   <si>
-    <t>Mezőkövesd-Zsóry</t>
-  </si>
-  <si>
-    <t>Lyn</t>
-  </si>
-  <si>
-    <t>Fasil Ketema</t>
-  </si>
-  <si>
-    <t>Rabotnički</t>
-  </si>
-  <si>
-    <t>BVSC</t>
-  </si>
-  <si>
-    <t>Szeged 2011</t>
-  </si>
-  <si>
-    <t>Torpedo Kutaisi</t>
-  </si>
-  <si>
-    <t>Tiszakécske</t>
-  </si>
-  <si>
-    <t>Videoton</t>
-  </si>
-  <si>
-    <t>APOEL</t>
+    <t>Shabab Al Ahli Dubai</t>
+  </si>
+  <si>
+    <t>Ajman</t>
   </si>
   <si>
     <t>Al Dhafra</t>
   </si>
   <si>
-    <t>Shabab Al Ahli Dubai</t>
-  </si>
-  <si>
     <t>Al Sharjah</t>
   </si>
   <si>
-    <t>Ajman</t>
+    <t>Arsenal</t>
+  </si>
+  <si>
+    <t>Heidenheim</t>
+  </si>
+  <si>
+    <t>Legia Warszawa</t>
+  </si>
+  <si>
+    <t>Kaizer Chiefs</t>
   </si>
   <si>
     <t>İnter Bakı</t>
   </si>
   <si>
-    <t>Heidenheim</t>
-  </si>
-  <si>
-    <t>Arsenal</t>
-  </si>
-  <si>
-    <t>Legia Warszawa</t>
-  </si>
-  <si>
-    <t>Kaizer Chiefs</t>
+    <t>FK Jezero Plav</t>
+  </si>
+  <si>
+    <t>Roma</t>
+  </si>
+  <si>
+    <t>Bokelj</t>
+  </si>
+  <si>
+    <t>Budućnost</t>
+  </si>
+  <si>
+    <t>Kauno Žalgiris</t>
+  </si>
+  <si>
+    <t>Hanácká</t>
+  </si>
+  <si>
+    <t>Difaâ El Jadida</t>
   </si>
   <si>
     <t>AGF</t>
@@ -1843,117 +1864,96 @@
     <t>Sutjeska</t>
   </si>
   <si>
-    <t>Budućnost</t>
-  </si>
-  <si>
-    <t>Kauno Žalgiris</t>
-  </si>
-  <si>
-    <t>FK Jezero Plav</t>
-  </si>
-  <si>
-    <t>Bokelj</t>
-  </si>
-  <si>
-    <t>Roma</t>
-  </si>
-  <si>
-    <t>Difaâ El Jadida</t>
-  </si>
-  <si>
-    <t>Hanácká</t>
+    <t>Argeș</t>
   </si>
   <si>
     <t>Petrovac</t>
   </si>
   <si>
-    <t>Argeș</t>
-  </si>
-  <si>
     <t>Al Fateh</t>
   </si>
   <si>
+    <t>Gorica</t>
+  </si>
+  <si>
+    <t>AB</t>
+  </si>
+  <si>
+    <t>Beroe</t>
+  </si>
+  <si>
     <t>B68</t>
   </si>
   <si>
-    <t>AB</t>
-  </si>
-  <si>
-    <t>Gorica</t>
-  </si>
-  <si>
-    <t>Beroe</t>
+    <t>Getafe CF</t>
+  </si>
+  <si>
+    <t>Hradec Králové</t>
+  </si>
+  <si>
+    <t>KV Mechelen</t>
+  </si>
+  <si>
+    <t>SD Eibar</t>
+  </si>
+  <si>
+    <t>PAOK</t>
+  </si>
+  <si>
+    <t>Napredak</t>
+  </si>
+  <si>
+    <t>Chicago Red Stars</t>
   </si>
   <si>
     <t>Panathinaikos</t>
   </si>
   <si>
+    <t>LFK Mladost Lučani</t>
+  </si>
+  <si>
+    <t>Unión San Felipe</t>
+  </si>
+  <si>
     <t>San Luis</t>
   </si>
   <si>
-    <t>Getafe CF</t>
-  </si>
-  <si>
-    <t>Napredak</t>
+    <t>Javor Ivanjica</t>
+  </si>
+  <si>
+    <t>Baltika</t>
+  </si>
+  <si>
+    <t>Granada CF</t>
   </si>
   <si>
     <t>Radnički Kragujevac</t>
   </si>
   <si>
-    <t>Baltika</t>
-  </si>
-  <si>
-    <t>Chicago Red Stars</t>
-  </si>
-  <si>
-    <t>PAOK</t>
-  </si>
-  <si>
-    <t>LFK Mladost Lučani</t>
-  </si>
-  <si>
-    <t>Granada CF</t>
-  </si>
-  <si>
-    <t>Javor Ivanjica</t>
-  </si>
-  <si>
-    <t>SD Eibar</t>
-  </si>
-  <si>
-    <t>Unión San Felipe</t>
-  </si>
-  <si>
-    <t>KV Mechelen</t>
-  </si>
-  <si>
-    <t>Hradec Králové</t>
+    <t>Samgurali</t>
   </si>
   <si>
     <t>Ashdod</t>
   </si>
   <si>
+    <t>Bnei Sakhnin</t>
+  </si>
+  <si>
+    <t>Barcelona W</t>
+  </si>
+  <si>
     <t>Maccabi Netanya</t>
   </si>
   <si>
-    <t>Bnei Sakhnin</t>
-  </si>
-  <si>
-    <t>Barcelona W</t>
+    <t>ÍBV</t>
   </si>
   <si>
     <t>Kozármisleny</t>
   </si>
   <si>
-    <t>Samgurali</t>
-  </si>
-  <si>
     <t>Soroksár SC</t>
   </si>
   <si>
-    <t>ÍBV</t>
-  </si>
-  <si>
     <t>KVC Westerlo</t>
   </si>
   <si>
@@ -1969,12 +1969,12 @@
     <t>Dhamk</t>
   </si>
   <si>
+    <t>RSB Berkane</t>
+  </si>
+  <si>
     <t>Maghreb Fès</t>
   </si>
   <si>
-    <t>RSB Berkane</t>
-  </si>
-  <si>
     <t>CF Os Belenenses</t>
   </si>
   <si>
@@ -1984,58 +1984,64 @@
     <t>Atalanta</t>
   </si>
   <si>
+    <t>Botafogo</t>
+  </si>
+  <si>
+    <t>América Mineiro</t>
+  </si>
+  <si>
+    <t>Lorient</t>
+  </si>
+  <si>
+    <t>Nice</t>
+  </si>
+  <si>
+    <t>Lille</t>
+  </si>
+  <si>
+    <t>Quilmes</t>
+  </si>
+  <si>
+    <t>Palmeiras</t>
+  </si>
+  <si>
+    <t>Brest</t>
+  </si>
+  <si>
+    <t>Paris</t>
+  </si>
+  <si>
     <t>Strasbourg</t>
   </si>
   <si>
-    <t>Quilmes</t>
-  </si>
-  <si>
-    <t>Botafogo</t>
-  </si>
-  <si>
     <t>Olympique Marseille</t>
   </si>
   <si>
-    <t>Lorient</t>
-  </si>
-  <si>
-    <t>Lille</t>
+    <t>Olympique Lyonnais</t>
+  </si>
+  <si>
+    <t>Real Madrid</t>
+  </si>
+  <si>
+    <t>Club Always Ready</t>
   </si>
   <si>
     <t>Atlanta</t>
   </si>
   <si>
-    <t>Palmeiras</t>
-  </si>
-  <si>
-    <t>Club Always Ready</t>
-  </si>
-  <si>
-    <t>América Mineiro</t>
-  </si>
-  <si>
-    <t>Olympique Lyonnais</t>
-  </si>
-  <si>
-    <t>Real Madrid</t>
-  </si>
-  <si>
-    <t>Brest</t>
-  </si>
-  <si>
-    <t>Nice</t>
-  </si>
-  <si>
-    <t>Paris</t>
+    <t>Patronato</t>
+  </si>
+  <si>
+    <t>Racing Córdoba</t>
   </si>
   <si>
     <t>Ciudad de Bolívar</t>
   </si>
   <si>
-    <t>Patronato</t>
-  </si>
-  <si>
-    <t>Racing Córdoba</t>
+    <t>Deportivo Madryn</t>
+  </si>
+  <si>
+    <t>LA Galaxy II</t>
   </si>
   <si>
     <t>FAR Rabat</t>
@@ -2047,12 +2053,6 @@
     <t>Real Monarchs</t>
   </si>
   <si>
-    <t>Deportivo Madryn</t>
-  </si>
-  <si>
-    <t>LA Galaxy II</t>
-  </si>
-  <si>
     <t>Columbus Crew</t>
   </si>
   <si>
@@ -2065,18 +2065,18 @@
     <t>Real Potosí</t>
   </si>
   <si>
+    <t>Chapecoense</t>
+  </si>
+  <si>
+    <t>Bragantino</t>
+  </si>
+  <si>
     <t>Fortaleza</t>
   </si>
   <si>
-    <t>Bragantino</t>
-  </si>
-  <si>
     <t>São Paulo</t>
   </si>
   <si>
-    <t>Chapecoense</t>
-  </si>
-  <si>
     <t>Columbus Crew II</t>
   </si>
   <si>
@@ -2086,10 +2086,10 @@
     <t>Botafogo SP</t>
   </si>
   <si>
+    <t>Austin</t>
+  </si>
+  <si>
     <t>Washington Spirit</t>
-  </si>
-  <si>
-    <t>Austin</t>
   </si>
   <si>
     <t>Orlando City II</t>
@@ -3601,7 +3601,7 @@
         <v>118</v>
       </c>
       <c r="D7" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E7" t="s">
         <v>193</v>
@@ -3786,7 +3786,7 @@
         <v>119</v>
       </c>
       <c r="D8" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E8" t="s">
         <v>194</v>
@@ -3968,7 +3968,7 @@
         <v>63</v>
       </c>
       <c r="C9" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="D9" t="s">
         <v>185</v>
@@ -4153,7 +4153,7 @@
         <v>63</v>
       </c>
       <c r="C10" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="D10" t="s">
         <v>185</v>
@@ -4338,7 +4338,7 @@
         <v>64</v>
       </c>
       <c r="C11" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="D11" t="s">
         <v>185</v>
@@ -4377,13 +4377,13 @@
         <v>699</v>
       </c>
       <c r="P11">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="Q11">
-        <v>3.32</v>
+        <v>0</v>
       </c>
       <c r="R11">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="S11">
         <v>0</v>
@@ -4523,7 +4523,7 @@
         <v>64</v>
       </c>
       <c r="C12" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="D12" t="s">
         <v>185</v>
@@ -4562,13 +4562,13 @@
         <v>699</v>
       </c>
       <c r="P12">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="Q12">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="R12">
-        <v>0</v>
+        <v>4.67</v>
       </c>
       <c r="S12">
         <v>0</v>
@@ -4607,10 +4607,10 @@
         <v>0</v>
       </c>
       <c r="AE12">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AF12">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AG12">
         <v>0</v>
@@ -4747,13 +4747,13 @@
         <v>699</v>
       </c>
       <c r="P13">
-        <v>1.63</v>
+        <v>3.65</v>
       </c>
       <c r="Q13">
-        <v>3.7</v>
+        <v>3.32</v>
       </c>
       <c r="R13">
-        <v>4.67</v>
+        <v>1.91</v>
       </c>
       <c r="S13">
         <v>0</v>
@@ -4792,10 +4792,10 @@
         <v>0</v>
       </c>
       <c r="AE13">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AF13">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AG13">
         <v>0</v>
@@ -6003,7 +6003,7 @@
         <v>68</v>
       </c>
       <c r="C20" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="D20" t="s">
         <v>185</v>
@@ -6188,10 +6188,10 @@
         <v>68</v>
       </c>
       <c r="C21" t="s">
-        <v>125</v>
+        <v>115</v>
       </c>
       <c r="D21" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E21" t="s">
         <v>207</v>
@@ -6227,13 +6227,13 @@
         <v>699</v>
       </c>
       <c r="P21">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Q21">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="R21">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="S21">
         <v>0</v>
@@ -6373,7 +6373,7 @@
         <v>68</v>
       </c>
       <c r="C22" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="D22" t="s">
         <v>186</v>
@@ -6558,7 +6558,7 @@
         <v>68</v>
       </c>
       <c r="C23" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="D23" t="s">
         <v>186</v>
@@ -6743,7 +6743,7 @@
         <v>68</v>
       </c>
       <c r="C24" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="D24" t="s">
         <v>186</v>
@@ -6928,7 +6928,7 @@
         <v>68</v>
       </c>
       <c r="C25" t="s">
-        <v>119</v>
+        <v>127</v>
       </c>
       <c r="D25" t="s">
         <v>186</v>
@@ -6967,13 +6967,13 @@
         <v>699</v>
       </c>
       <c r="P25">
-        <v>4.98</v>
+        <v>0</v>
       </c>
       <c r="Q25">
-        <v>3.66</v>
+        <v>0</v>
       </c>
       <c r="R25">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="S25">
         <v>0</v>
@@ -7113,10 +7113,10 @@
         <v>68</v>
       </c>
       <c r="C26" t="s">
-        <v>122</v>
+        <v>128</v>
       </c>
       <c r="D26" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E26" t="s">
         <v>212</v>
@@ -7298,7 +7298,7 @@
         <v>68</v>
       </c>
       <c r="C27" t="s">
-        <v>115</v>
+        <v>129</v>
       </c>
       <c r="D27" t="s">
         <v>185</v>
@@ -7337,13 +7337,13 @@
         <v>699</v>
       </c>
       <c r="P27">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Q27">
-        <v>3.16</v>
+        <v>0</v>
       </c>
       <c r="R27">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="S27">
         <v>0</v>
@@ -7483,7 +7483,7 @@
         <v>68</v>
       </c>
       <c r="C28" t="s">
-        <v>129</v>
+        <v>118</v>
       </c>
       <c r="D28" t="s">
         <v>186</v>
@@ -7522,13 +7522,13 @@
         <v>699</v>
       </c>
       <c r="P28">
-        <v>0</v>
+        <v>4.98</v>
       </c>
       <c r="Q28">
-        <v>0</v>
+        <v>3.66</v>
       </c>
       <c r="R28">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="S28">
         <v>0</v>
@@ -8077,13 +8077,13 @@
         <v>699</v>
       </c>
       <c r="P31">
-        <v>3.32</v>
+        <v>3.4</v>
       </c>
       <c r="Q31">
-        <v>3.95</v>
+        <v>3.63</v>
       </c>
       <c r="R31">
-        <v>2.03</v>
+        <v>2.09</v>
       </c>
       <c r="S31">
         <v>0</v>
@@ -8262,13 +8262,13 @@
         <v>699</v>
       </c>
       <c r="P32">
-        <v>1.78</v>
+        <v>1.61</v>
       </c>
       <c r="Q32">
-        <v>3.9</v>
+        <v>4.18</v>
       </c>
       <c r="R32">
-        <v>4.35</v>
+        <v>5.3</v>
       </c>
       <c r="S32">
         <v>0</v>
@@ -8408,10 +8408,10 @@
         <v>71</v>
       </c>
       <c r="C33" t="s">
-        <v>129</v>
+        <v>122</v>
       </c>
       <c r="D33" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E33" t="s">
         <v>219</v>
@@ -8593,7 +8593,7 @@
         <v>71</v>
       </c>
       <c r="C34" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="D34" t="s">
         <v>185</v>
@@ -8778,7 +8778,7 @@
         <v>71</v>
       </c>
       <c r="C35" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
       <c r="D35" t="s">
         <v>186</v>
@@ -8963,7 +8963,7 @@
         <v>71</v>
       </c>
       <c r="C36" t="s">
-        <v>132</v>
+        <v>124</v>
       </c>
       <c r="D36" t="s">
         <v>186</v>
@@ -9002,13 +9002,13 @@
         <v>699</v>
       </c>
       <c r="P36">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="Q36">
-        <v>4.18</v>
+        <v>0</v>
       </c>
       <c r="R36">
-        <v>5.3</v>
+        <v>0</v>
       </c>
       <c r="S36">
         <v>0</v>
@@ -9148,7 +9148,7 @@
         <v>71</v>
       </c>
       <c r="C37" t="s">
-        <v>124</v>
+        <v>133</v>
       </c>
       <c r="D37" t="s">
         <v>185</v>
@@ -9333,7 +9333,7 @@
         <v>71</v>
       </c>
       <c r="C38" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="D38" t="s">
         <v>186</v>
@@ -9372,13 +9372,13 @@
         <v>699</v>
       </c>
       <c r="P38">
-        <v>2.7</v>
+        <v>2.2</v>
       </c>
       <c r="Q38">
-        <v>3.36</v>
+        <v>3.7</v>
       </c>
       <c r="R38">
-        <v>2.64</v>
+        <v>3</v>
       </c>
       <c r="S38">
         <v>0</v>
@@ -9417,10 +9417,10 @@
         <v>0</v>
       </c>
       <c r="AE38">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AF38">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AG38">
         <v>0</v>
@@ -9557,13 +9557,13 @@
         <v>699</v>
       </c>
       <c r="P39">
-        <v>1.24</v>
+        <v>2.7</v>
       </c>
       <c r="Q39">
-        <v>6.73</v>
+        <v>3.36</v>
       </c>
       <c r="R39">
-        <v>10.6</v>
+        <v>2.64</v>
       </c>
       <c r="S39">
         <v>0</v>
@@ -9602,10 +9602,10 @@
         <v>0</v>
       </c>
       <c r="AE39">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AF39">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AG39">
         <v>0</v>
@@ -9742,13 +9742,13 @@
         <v>699</v>
       </c>
       <c r="P40">
-        <v>5.09</v>
+        <v>1.78</v>
       </c>
       <c r="Q40">
-        <v>4.18</v>
+        <v>3.9</v>
       </c>
       <c r="R40">
-        <v>1.64</v>
+        <v>4.35</v>
       </c>
       <c r="S40">
         <v>0</v>
@@ -9888,10 +9888,10 @@
         <v>71</v>
       </c>
       <c r="C41" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="D41" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E41" t="s">
         <v>227</v>
@@ -9927,13 +9927,13 @@
         <v>699</v>
       </c>
       <c r="P41">
-        <v>0</v>
+        <v>5.09</v>
       </c>
       <c r="Q41">
-        <v>0</v>
+        <v>4.18</v>
       </c>
       <c r="R41">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="S41">
         <v>0</v>
@@ -10073,7 +10073,7 @@
         <v>71</v>
       </c>
       <c r="C42" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="D42" t="s">
         <v>186</v>
@@ -10112,13 +10112,13 @@
         <v>699</v>
       </c>
       <c r="P42">
-        <v>2.2</v>
+        <v>1.24</v>
       </c>
       <c r="Q42">
-        <v>3.7</v>
+        <v>6.73</v>
       </c>
       <c r="R42">
-        <v>3</v>
+        <v>10.6</v>
       </c>
       <c r="S42">
         <v>0</v>
@@ -10258,10 +10258,10 @@
         <v>71</v>
       </c>
       <c r="C43" t="s">
-        <v>122</v>
+        <v>132</v>
       </c>
       <c r="D43" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E43" t="s">
         <v>229</v>
@@ -10297,13 +10297,13 @@
         <v>699</v>
       </c>
       <c r="P43">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="Q43">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="R43">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="S43">
         <v>0</v>
@@ -10482,13 +10482,13 @@
         <v>699</v>
       </c>
       <c r="P44">
-        <v>3.4</v>
+        <v>2.44</v>
       </c>
       <c r="Q44">
-        <v>3.63</v>
+        <v>3.61</v>
       </c>
       <c r="R44">
-        <v>2.09</v>
+        <v>2.77</v>
       </c>
       <c r="S44">
         <v>0</v>
@@ -10628,10 +10628,10 @@
         <v>71</v>
       </c>
       <c r="C45" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="D45" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E45" t="s">
         <v>231</v>
@@ -10667,13 +10667,13 @@
         <v>699</v>
       </c>
       <c r="P45">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="Q45">
-        <v>3.61</v>
+        <v>0</v>
       </c>
       <c r="R45">
-        <v>2.77</v>
+        <v>0</v>
       </c>
       <c r="S45">
         <v>0</v>
@@ -11222,13 +11222,13 @@
         <v>699</v>
       </c>
       <c r="P48">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="Q48">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="R48">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="S48">
         <v>0</v>
@@ -11368,10 +11368,10 @@
         <v>73</v>
       </c>
       <c r="C49" t="s">
-        <v>138</v>
+        <v>119</v>
       </c>
       <c r="D49" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E49" t="s">
         <v>235</v>
@@ -11407,13 +11407,13 @@
         <v>699</v>
       </c>
       <c r="P49">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="Q49">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="R49">
-        <v>7.37</v>
+        <v>0</v>
       </c>
       <c r="S49">
         <v>0</v>
@@ -11553,10 +11553,10 @@
         <v>73</v>
       </c>
       <c r="C50" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="D50" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E50" t="s">
         <v>236</v>
@@ -11592,13 +11592,13 @@
         <v>699</v>
       </c>
       <c r="P50">
-        <v>2.27</v>
+        <v>2.88</v>
       </c>
       <c r="Q50">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="R50">
-        <v>2.6</v>
+        <v>2.19</v>
       </c>
       <c r="S50">
         <v>0</v>
@@ -11738,7 +11738,7 @@
         <v>73</v>
       </c>
       <c r="C51" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="D51" t="s">
         <v>186</v>
@@ -11777,13 +11777,13 @@
         <v>699</v>
       </c>
       <c r="P51">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="Q51">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="R51">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="S51">
         <v>0</v>
@@ -11923,7 +11923,7 @@
         <v>73</v>
       </c>
       <c r="C52" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="D52" t="s">
         <v>186</v>
@@ -11962,13 +11962,13 @@
         <v>699</v>
       </c>
       <c r="P52">
-        <v>2.29</v>
+        <v>1.78</v>
       </c>
       <c r="Q52">
-        <v>3.74</v>
+        <v>4.15</v>
       </c>
       <c r="R52">
-        <v>2.76</v>
+        <v>3.8</v>
       </c>
       <c r="S52">
         <v>0</v>
@@ -12013,10 +12013,10 @@
         <v>0</v>
       </c>
       <c r="AG52">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AH52">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AI52">
         <v>0</v>
@@ -12108,7 +12108,7 @@
         <v>73</v>
       </c>
       <c r="C53" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="D53" t="s">
         <v>186</v>
@@ -12147,13 +12147,13 @@
         <v>699</v>
       </c>
       <c r="P53">
-        <v>1.78</v>
+        <v>1.34</v>
       </c>
       <c r="Q53">
-        <v>4.15</v>
+        <v>4.6</v>
       </c>
       <c r="R53">
-        <v>3.8</v>
+        <v>7.37</v>
       </c>
       <c r="S53">
         <v>0</v>
@@ -12198,10 +12198,10 @@
         <v>0</v>
       </c>
       <c r="AG53">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AH53">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AI53">
         <v>0</v>
@@ -12293,10 +12293,10 @@
         <v>73</v>
       </c>
       <c r="C54" t="s">
-        <v>118</v>
+        <v>140</v>
       </c>
       <c r="D54" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E54" t="s">
         <v>240</v>
@@ -12332,13 +12332,13 @@
         <v>699</v>
       </c>
       <c r="P54">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="Q54">
-        <v>0</v>
+        <v>3.71</v>
       </c>
       <c r="R54">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="S54">
         <v>0</v>
@@ -12481,7 +12481,7 @@
         <v>141</v>
       </c>
       <c r="D55" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="E55" t="s">
         <v>241</v>
@@ -12517,13 +12517,13 @@
         <v>699</v>
       </c>
       <c r="P55">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="Q55">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="R55">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="S55">
         <v>0</v>
@@ -12666,7 +12666,7 @@
         <v>142</v>
       </c>
       <c r="D56" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="E56" t="s">
         <v>242</v>
@@ -12702,13 +12702,13 @@
         <v>699</v>
       </c>
       <c r="P56">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="Q56">
-        <v>3.71</v>
+        <v>0</v>
       </c>
       <c r="R56">
-        <v>2.89</v>
+        <v>0</v>
       </c>
       <c r="S56">
         <v>0</v>
@@ -12848,7 +12848,7 @@
         <v>73</v>
       </c>
       <c r="C57" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="D57" t="s">
         <v>185</v>
@@ -13033,7 +13033,7 @@
         <v>73</v>
       </c>
       <c r="C58" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="D58" t="s">
         <v>187</v>
@@ -13776,7 +13776,7 @@
         <v>144</v>
       </c>
       <c r="D62" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E62" t="s">
         <v>248</v>
@@ -13812,13 +13812,13 @@
         <v>699</v>
       </c>
       <c r="P62">
-        <v>2.58</v>
+        <v>1.92</v>
       </c>
       <c r="Q62">
-        <v>3.62</v>
+        <v>3.4</v>
       </c>
       <c r="R62">
-        <v>2.45</v>
+        <v>3.9</v>
       </c>
       <c r="S62">
         <v>0</v>
@@ -13958,7 +13958,7 @@
         <v>76</v>
       </c>
       <c r="C63" t="s">
-        <v>126</v>
+        <v>145</v>
       </c>
       <c r="D63" t="s">
         <v>186</v>
@@ -13997,13 +13997,13 @@
         <v>699</v>
       </c>
       <c r="P63">
-        <v>0</v>
+        <v>3.36</v>
       </c>
       <c r="Q63">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="R63">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="S63">
         <v>0</v>
@@ -14143,10 +14143,10 @@
         <v>76</v>
       </c>
       <c r="C64" t="s">
-        <v>123</v>
+        <v>146</v>
       </c>
       <c r="D64" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E64" t="s">
         <v>250</v>
@@ -14182,13 +14182,13 @@
         <v>699</v>
       </c>
       <c r="P64">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="Q64">
-        <v>7.41</v>
+        <v>0</v>
       </c>
       <c r="R64">
-        <v>17.5</v>
+        <v>0</v>
       </c>
       <c r="S64">
         <v>0</v>
@@ -14328,10 +14328,10 @@
         <v>76</v>
       </c>
       <c r="C65" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="D65" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E65" t="s">
         <v>251</v>
@@ -14367,13 +14367,13 @@
         <v>699</v>
       </c>
       <c r="P65">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="Q65">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="R65">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="S65">
         <v>0</v>
@@ -14513,10 +14513,10 @@
         <v>76</v>
       </c>
       <c r="C66" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="D66" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E66" t="s">
         <v>252</v>
@@ -14698,10 +14698,10 @@
         <v>76</v>
       </c>
       <c r="C67" t="s">
-        <v>146</v>
+        <v>129</v>
       </c>
       <c r="D67" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E67" t="s">
         <v>253</v>
@@ -14737,13 +14737,13 @@
         <v>699</v>
       </c>
       <c r="P67">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="Q67">
-        <v>3.54</v>
+        <v>0</v>
       </c>
       <c r="R67">
-        <v>2.73</v>
+        <v>0</v>
       </c>
       <c r="S67">
         <v>0</v>
@@ -15068,7 +15068,7 @@
         <v>76</v>
       </c>
       <c r="C69" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="D69" t="s">
         <v>186</v>
@@ -15107,13 +15107,13 @@
         <v>699</v>
       </c>
       <c r="P69">
-        <v>3.36</v>
+        <v>2.36</v>
       </c>
       <c r="Q69">
-        <v>3.65</v>
+        <v>3.54</v>
       </c>
       <c r="R69">
-        <v>1.99</v>
+        <v>2.73</v>
       </c>
       <c r="S69">
         <v>0</v>
@@ -15253,10 +15253,10 @@
         <v>76</v>
       </c>
       <c r="C70" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="D70" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E70" t="s">
         <v>256</v>
@@ -15292,13 +15292,13 @@
         <v>699</v>
       </c>
       <c r="P70">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="Q70">
-        <v>0</v>
+        <v>3.43</v>
       </c>
       <c r="R70">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="S70">
         <v>0</v>
@@ -15438,10 +15438,10 @@
         <v>76</v>
       </c>
       <c r="C71" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="D71" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E71" t="s">
         <v>257</v>
@@ -15477,13 +15477,13 @@
         <v>699</v>
       </c>
       <c r="P71">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="Q71">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="R71">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="S71">
         <v>0</v>
@@ -15623,7 +15623,7 @@
         <v>76</v>
       </c>
       <c r="C72" t="s">
-        <v>121</v>
+        <v>145</v>
       </c>
       <c r="D72" t="s">
         <v>186</v>
@@ -15662,13 +15662,13 @@
         <v>699</v>
       </c>
       <c r="P72">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="Q72">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="R72">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="S72">
         <v>0</v>
@@ -15808,7 +15808,7 @@
         <v>76</v>
       </c>
       <c r="C73" t="s">
-        <v>149</v>
+        <v>123</v>
       </c>
       <c r="D73" t="s">
         <v>186</v>
@@ -15847,13 +15847,13 @@
         <v>699</v>
       </c>
       <c r="P73">
-        <v>2.46</v>
+        <v>1.21</v>
       </c>
       <c r="Q73">
-        <v>3.43</v>
+        <v>7.41</v>
       </c>
       <c r="R73">
-        <v>2.91</v>
+        <v>17.5</v>
       </c>
       <c r="S73">
         <v>0</v>
@@ -15993,10 +15993,10 @@
         <v>76</v>
       </c>
       <c r="C74" t="s">
-        <v>145</v>
+        <v>121</v>
       </c>
       <c r="D74" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E74" t="s">
         <v>260</v>
@@ -16032,13 +16032,13 @@
         <v>699</v>
       </c>
       <c r="P74">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="Q74">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="R74">
-        <v>2.87</v>
+        <v>0</v>
       </c>
       <c r="S74">
         <v>0</v>
@@ -16178,7 +16178,7 @@
         <v>77</v>
       </c>
       <c r="C75" t="s">
-        <v>129</v>
+        <v>150</v>
       </c>
       <c r="D75" t="s">
         <v>186</v>
@@ -16363,7 +16363,7 @@
         <v>77</v>
       </c>
       <c r="C76" t="s">
-        <v>150</v>
+        <v>124</v>
       </c>
       <c r="D76" t="s">
         <v>186</v>
@@ -16548,10 +16548,10 @@
         <v>78</v>
       </c>
       <c r="C77" t="s">
-        <v>120</v>
+        <v>151</v>
       </c>
       <c r="D77" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E77" t="s">
         <v>263</v>
@@ -16587,13 +16587,13 @@
         <v>699</v>
       </c>
       <c r="P77">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="Q77">
-        <v>0</v>
+        <v>3.67</v>
       </c>
       <c r="R77">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="S77">
         <v>0</v>
@@ -16733,10 +16733,10 @@
         <v>78</v>
       </c>
       <c r="C78" t="s">
-        <v>151</v>
+        <v>120</v>
       </c>
       <c r="D78" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E78" t="s">
         <v>264</v>
@@ -16772,13 +16772,13 @@
         <v>699</v>
       </c>
       <c r="P78">
-        <v>2.79</v>
+        <v>0</v>
       </c>
       <c r="Q78">
-        <v>3.67</v>
+        <v>0</v>
       </c>
       <c r="R78">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="S78">
         <v>0</v>
@@ -16918,7 +16918,7 @@
         <v>78</v>
       </c>
       <c r="C79" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="D79" t="s">
         <v>186</v>
@@ -17288,10 +17288,10 @@
         <v>80</v>
       </c>
       <c r="C81" t="s">
-        <v>133</v>
+        <v>126</v>
       </c>
       <c r="D81" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E81" t="s">
         <v>267</v>
@@ -17658,7 +17658,7 @@
         <v>80</v>
       </c>
       <c r="C83" t="s">
-        <v>131</v>
+        <v>153</v>
       </c>
       <c r="D83" t="s">
         <v>186</v>
@@ -17697,13 +17697,13 @@
         <v>699</v>
       </c>
       <c r="P83">
-        <v>2.1</v>
+        <v>2.21</v>
       </c>
       <c r="Q83">
-        <v>3.42</v>
+        <v>3.22</v>
       </c>
       <c r="R83">
-        <v>4.07</v>
+        <v>3.22</v>
       </c>
       <c r="S83">
         <v>0</v>
@@ -17742,10 +17742,10 @@
         <v>0</v>
       </c>
       <c r="AE83">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AF83">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AG83">
         <v>0</v>
@@ -17843,7 +17843,7 @@
         <v>80</v>
       </c>
       <c r="C84" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D84" t="s">
         <v>186</v>
@@ -17882,13 +17882,13 @@
         <v>699</v>
       </c>
       <c r="P84">
-        <v>0</v>
+        <v>5.38</v>
       </c>
       <c r="Q84">
-        <v>0</v>
+        <v>4.37</v>
       </c>
       <c r="R84">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="S84">
         <v>0</v>
@@ -18028,10 +18028,10 @@
         <v>80</v>
       </c>
       <c r="C85" t="s">
-        <v>153</v>
+        <v>133</v>
       </c>
       <c r="D85" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E85" t="s">
         <v>271</v>
@@ -18213,7 +18213,7 @@
         <v>80</v>
       </c>
       <c r="C86" t="s">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="D86" t="s">
         <v>185</v>
@@ -18583,7 +18583,7 @@
         <v>80</v>
       </c>
       <c r="C88" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="D88" t="s">
         <v>186</v>
@@ -18622,13 +18622,13 @@
         <v>699</v>
       </c>
       <c r="P88">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="Q88">
-        <v>0</v>
+        <v>3.66</v>
       </c>
       <c r="R88">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="S88">
         <v>0</v>
@@ -18667,10 +18667,10 @@
         <v>0</v>
       </c>
       <c r="AE88">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AF88">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AG88">
         <v>0</v>
@@ -18768,7 +18768,7 @@
         <v>80</v>
       </c>
       <c r="C89" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="D89" t="s">
         <v>186</v>
@@ -18807,13 +18807,13 @@
         <v>699</v>
       </c>
       <c r="P89">
-        <v>2.59</v>
+        <v>0</v>
       </c>
       <c r="Q89">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="R89">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="S89">
         <v>0</v>
@@ -18953,7 +18953,7 @@
         <v>80</v>
       </c>
       <c r="C90" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="D90" t="s">
         <v>186</v>
@@ -18992,13 +18992,13 @@
         <v>699</v>
       </c>
       <c r="P90">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="Q90">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="R90">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="S90">
         <v>0</v>
@@ -19177,13 +19177,13 @@
         <v>699</v>
       </c>
       <c r="P91">
-        <v>2.09</v>
+        <v>2.1</v>
       </c>
       <c r="Q91">
-        <v>3.48</v>
+        <v>3.42</v>
       </c>
       <c r="R91">
-        <v>4.01</v>
+        <v>4.07</v>
       </c>
       <c r="S91">
         <v>0</v>
@@ -19222,10 +19222,10 @@
         <v>0</v>
       </c>
       <c r="AE91">
-        <v>1.98</v>
+        <v>2.15</v>
       </c>
       <c r="AF91">
-        <v>1.73</v>
+        <v>1.61</v>
       </c>
       <c r="AG91">
         <v>0</v>
@@ -19323,7 +19323,7 @@
         <v>80</v>
       </c>
       <c r="C92" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="D92" t="s">
         <v>186</v>
@@ -19362,13 +19362,13 @@
         <v>699</v>
       </c>
       <c r="P92">
-        <v>5.38</v>
+        <v>2.59</v>
       </c>
       <c r="Q92">
-        <v>4.37</v>
+        <v>3.45</v>
       </c>
       <c r="R92">
-        <v>1.67</v>
+        <v>2.3</v>
       </c>
       <c r="S92">
         <v>0</v>
@@ -19508,7 +19508,7 @@
         <v>80</v>
       </c>
       <c r="C93" t="s">
-        <v>126</v>
+        <v>150</v>
       </c>
       <c r="D93" t="s">
         <v>186</v>
@@ -19693,7 +19693,7 @@
         <v>80</v>
       </c>
       <c r="C94" t="s">
-        <v>152</v>
+        <v>131</v>
       </c>
       <c r="D94" t="s">
         <v>186</v>
@@ -19732,13 +19732,13 @@
         <v>699</v>
       </c>
       <c r="P94">
-        <v>2.46</v>
+        <v>2.09</v>
       </c>
       <c r="Q94">
-        <v>3.66</v>
+        <v>3.48</v>
       </c>
       <c r="R94">
-        <v>2.99</v>
+        <v>4.01</v>
       </c>
       <c r="S94">
         <v>0</v>
@@ -19777,10 +19777,10 @@
         <v>0</v>
       </c>
       <c r="AE94">
-        <v>1.68</v>
+        <v>1.98</v>
       </c>
       <c r="AF94">
-        <v>2.05</v>
+        <v>1.73</v>
       </c>
       <c r="AG94">
         <v>0</v>
@@ -20436,7 +20436,7 @@
         <v>159</v>
       </c>
       <c r="D98" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E98" t="s">
         <v>284</v>
@@ -20618,10 +20618,10 @@
         <v>83</v>
       </c>
       <c r="C99" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="D99" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E99" t="s">
         <v>285</v>
@@ -20657,13 +20657,13 @@
         <v>699</v>
       </c>
       <c r="P99">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="Q99">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="R99">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="S99">
         <v>0</v>
@@ -20702,10 +20702,10 @@
         <v>0</v>
       </c>
       <c r="AE99">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AF99">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AG99">
         <v>0</v>
@@ -20803,7 +20803,7 @@
         <v>83</v>
       </c>
       <c r="C100" t="s">
-        <v>160</v>
+        <v>140</v>
       </c>
       <c r="D100" t="s">
         <v>186</v>
@@ -20842,13 +20842,13 @@
         <v>699</v>
       </c>
       <c r="P100">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="Q100">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="R100">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="S100">
         <v>0</v>
@@ -20887,10 +20887,10 @@
         <v>0</v>
       </c>
       <c r="AE100">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AF100">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG100">
         <v>0</v>
@@ -20988,7 +20988,7 @@
         <v>83</v>
       </c>
       <c r="C101" t="s">
-        <v>139</v>
+        <v>160</v>
       </c>
       <c r="D101" t="s">
         <v>185</v>
@@ -21176,7 +21176,7 @@
         <v>159</v>
       </c>
       <c r="D102" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E102" t="s">
         <v>288</v>
@@ -21212,13 +21212,13 @@
         <v>699</v>
       </c>
       <c r="P102">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="Q102">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R102">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="S102">
         <v>0</v>
@@ -21358,10 +21358,10 @@
         <v>83</v>
       </c>
       <c r="C103" t="s">
-        <v>136</v>
+        <v>161</v>
       </c>
       <c r="D103" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E103" t="s">
         <v>289</v>
@@ -21543,10 +21543,10 @@
         <v>83</v>
       </c>
       <c r="C104" t="s">
-        <v>138</v>
+        <v>160</v>
       </c>
       <c r="D104" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E104" t="s">
         <v>290</v>
@@ -21728,7 +21728,7 @@
         <v>83</v>
       </c>
       <c r="C105" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="D105" t="s">
         <v>186</v>
@@ -21913,7 +21913,7 @@
         <v>83</v>
       </c>
       <c r="C106" t="s">
-        <v>161</v>
+        <v>139</v>
       </c>
       <c r="D106" t="s">
         <v>186</v>
@@ -22098,10 +22098,10 @@
         <v>83</v>
       </c>
       <c r="C107" t="s">
-        <v>158</v>
+        <v>136</v>
       </c>
       <c r="D107" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E107" t="s">
         <v>293</v>
@@ -22137,13 +22137,13 @@
         <v>699</v>
       </c>
       <c r="P107">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="Q107">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="R107">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="S107">
         <v>0</v>
@@ -22468,7 +22468,7 @@
         <v>84</v>
       </c>
       <c r="C109" t="s">
-        <v>148</v>
+        <v>123</v>
       </c>
       <c r="D109" t="s">
         <v>186</v>
@@ -22507,13 +22507,13 @@
         <v>699</v>
       </c>
       <c r="P109">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="Q109">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="R109">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="S109">
         <v>0</v>
@@ -22653,7 +22653,7 @@
         <v>84</v>
       </c>
       <c r="C110" t="s">
-        <v>123</v>
+        <v>147</v>
       </c>
       <c r="D110" t="s">
         <v>186</v>
@@ -22692,13 +22692,13 @@
         <v>699</v>
       </c>
       <c r="P110">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="Q110">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="R110">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="S110">
         <v>0</v>
@@ -22838,7 +22838,7 @@
         <v>85</v>
       </c>
       <c r="C111" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="D111" t="s">
         <v>185</v>
@@ -23023,7 +23023,7 @@
         <v>85</v>
       </c>
       <c r="C112" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="D112" t="s">
         <v>186</v>
@@ -23208,7 +23208,7 @@
         <v>85</v>
       </c>
       <c r="C113" t="s">
-        <v>146</v>
+        <v>138</v>
       </c>
       <c r="D113" t="s">
         <v>186</v>
@@ -23247,13 +23247,13 @@
         <v>699</v>
       </c>
       <c r="P113">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="Q113">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="R113">
-        <v>3.57</v>
+        <v>0</v>
       </c>
       <c r="S113">
         <v>0</v>
@@ -23298,10 +23298,10 @@
         <v>0</v>
       </c>
       <c r="AG113">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AH113">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AI113">
         <v>0</v>
@@ -23393,7 +23393,7 @@
         <v>85</v>
       </c>
       <c r="C114" t="s">
-        <v>119</v>
+        <v>148</v>
       </c>
       <c r="D114" t="s">
         <v>186</v>
@@ -23432,13 +23432,13 @@
         <v>699</v>
       </c>
       <c r="P114">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="Q114">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="R114">
-        <v>0</v>
+        <v>3.57</v>
       </c>
       <c r="S114">
         <v>0</v>
@@ -23483,10 +23483,10 @@
         <v>0</v>
       </c>
       <c r="AG114">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AH114">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AI114">
         <v>0</v>
@@ -23578,7 +23578,7 @@
         <v>85</v>
       </c>
       <c r="C115" t="s">
-        <v>137</v>
+        <v>118</v>
       </c>
       <c r="D115" t="s">
         <v>186</v>
@@ -23802,13 +23802,13 @@
         <v>699</v>
       </c>
       <c r="P116">
-        <v>4.48</v>
+        <v>2.78</v>
       </c>
       <c r="Q116">
-        <v>4.74</v>
+        <v>3.89</v>
       </c>
       <c r="R116">
-        <v>1.65</v>
+        <v>2.36</v>
       </c>
       <c r="S116">
         <v>0</v>
@@ -23853,10 +23853,10 @@
         <v>0</v>
       </c>
       <c r="AG116">
+        <v>2.05</v>
+      </c>
+      <c r="AH116">
         <v>1.68</v>
-      </c>
-      <c r="AH116">
-        <v>2.05</v>
       </c>
       <c r="AI116">
         <v>0</v>
@@ -23987,13 +23987,13 @@
         <v>699</v>
       </c>
       <c r="P117">
-        <v>1.48</v>
+        <v>4.48</v>
       </c>
       <c r="Q117">
-        <v>4.94</v>
+        <v>4.74</v>
       </c>
       <c r="R117">
-        <v>6.07</v>
+        <v>1.65</v>
       </c>
       <c r="S117">
         <v>0</v>
@@ -24038,10 +24038,10 @@
         <v>0</v>
       </c>
       <c r="AG117">
-        <v>1.98</v>
+        <v>1.68</v>
       </c>
       <c r="AH117">
-        <v>1.72</v>
+        <v>2.05</v>
       </c>
       <c r="AI117">
         <v>0</v>
@@ -24172,13 +24172,13 @@
         <v>699</v>
       </c>
       <c r="P118">
-        <v>2.78</v>
+        <v>2.49</v>
       </c>
       <c r="Q118">
-        <v>3.89</v>
+        <v>3.77</v>
       </c>
       <c r="R118">
-        <v>2.36</v>
+        <v>2.67</v>
       </c>
       <c r="S118">
         <v>0</v>
@@ -24217,16 +24217,16 @@
         <v>0</v>
       </c>
       <c r="AE118">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AF118">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AG118">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AH118">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AI118">
         <v>0</v>
@@ -24357,13 +24357,13 @@
         <v>699</v>
       </c>
       <c r="P119">
-        <v>1.71</v>
+        <v>1.44</v>
       </c>
       <c r="Q119">
-        <v>4.37</v>
+        <v>5.14</v>
       </c>
       <c r="R119">
-        <v>4.42</v>
+        <v>6.53</v>
       </c>
       <c r="S119">
         <v>0</v>
@@ -24408,10 +24408,10 @@
         <v>0</v>
       </c>
       <c r="AG119">
-        <v>2.1</v>
+        <v>1.93</v>
       </c>
       <c r="AH119">
-        <v>1.65</v>
+        <v>1.77</v>
       </c>
       <c r="AI119">
         <v>0</v>
@@ -24542,13 +24542,13 @@
         <v>699</v>
       </c>
       <c r="P120">
-        <v>1.44</v>
+        <v>1.77</v>
       </c>
       <c r="Q120">
-        <v>5.14</v>
+        <v>4.17</v>
       </c>
       <c r="R120">
-        <v>6.53</v>
+        <v>4.22</v>
       </c>
       <c r="S120">
         <v>0</v>
@@ -24587,16 +24587,16 @@
         <v>0</v>
       </c>
       <c r="AE120">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AF120">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AG120">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AH120">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AI120">
         <v>0</v>
@@ -24727,13 +24727,13 @@
         <v>699</v>
       </c>
       <c r="P121">
-        <v>2.49</v>
+        <v>1.96</v>
       </c>
       <c r="Q121">
-        <v>3.77</v>
+        <v>4.05</v>
       </c>
       <c r="R121">
-        <v>2.67</v>
+        <v>3.5</v>
       </c>
       <c r="S121">
         <v>0</v>
@@ -24772,16 +24772,16 @@
         <v>0</v>
       </c>
       <c r="AE121">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AF121">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AG121">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH121">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AI121">
         <v>0</v>
@@ -24912,13 +24912,13 @@
         <v>699</v>
       </c>
       <c r="P122">
-        <v>1.96</v>
+        <v>1.48</v>
       </c>
       <c r="Q122">
-        <v>4.05</v>
+        <v>4.94</v>
       </c>
       <c r="R122">
-        <v>3.5</v>
+        <v>6.07</v>
       </c>
       <c r="S122">
         <v>0</v>
@@ -24963,10 +24963,10 @@
         <v>0</v>
       </c>
       <c r="AG122">
-        <v>2.2</v>
+        <v>1.98</v>
       </c>
       <c r="AH122">
-        <v>1.58</v>
+        <v>1.72</v>
       </c>
       <c r="AI122">
         <v>0</v>
@@ -25097,13 +25097,13 @@
         <v>699</v>
       </c>
       <c r="P123">
-        <v>1.78</v>
+        <v>1.71</v>
       </c>
       <c r="Q123">
-        <v>4.17</v>
+        <v>4.37</v>
       </c>
       <c r="R123">
-        <v>4.17</v>
+        <v>4.42</v>
       </c>
       <c r="S123">
         <v>0</v>
@@ -25148,10 +25148,10 @@
         <v>0</v>
       </c>
       <c r="AG123">
-        <v>1.9</v>
+        <v>2.1</v>
       </c>
       <c r="AH123">
-        <v>1.77</v>
+        <v>1.65</v>
       </c>
       <c r="AI123">
         <v>0</v>
@@ -25282,13 +25282,13 @@
         <v>699</v>
       </c>
       <c r="P124">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="Q124">
         <v>4.17</v>
       </c>
       <c r="R124">
-        <v>4.22</v>
+        <v>4.17</v>
       </c>
       <c r="S124">
         <v>0</v>
@@ -25327,16 +25327,16 @@
         <v>0</v>
       </c>
       <c r="AE124">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AF124">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AG124">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AH124">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AI124">
         <v>0</v>
@@ -25428,10 +25428,10 @@
         <v>87</v>
       </c>
       <c r="C125" t="s">
-        <v>163</v>
+        <v>151</v>
       </c>
       <c r="D125" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E125" t="s">
         <v>311</v>
@@ -25467,13 +25467,13 @@
         <v>699</v>
       </c>
       <c r="P125">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="Q125">
-        <v>0</v>
+        <v>4.44</v>
       </c>
       <c r="R125">
-        <v>0</v>
+        <v>5.16</v>
       </c>
       <c r="S125">
         <v>0</v>
@@ -25613,7 +25613,7 @@
         <v>87</v>
       </c>
       <c r="C126" t="s">
-        <v>164</v>
+        <v>151</v>
       </c>
       <c r="D126" t="s">
         <v>185</v>
@@ -25652,13 +25652,13 @@
         <v>699</v>
       </c>
       <c r="P126">
-        <v>5.4</v>
+        <v>3.87</v>
       </c>
       <c r="Q126">
-        <v>4.6</v>
+        <v>3.87</v>
       </c>
       <c r="R126">
-        <v>1.51</v>
+        <v>1.89</v>
       </c>
       <c r="S126">
         <v>0</v>
@@ -25798,7 +25798,7 @@
         <v>87</v>
       </c>
       <c r="C127" t="s">
-        <v>165</v>
+        <v>158</v>
       </c>
       <c r="D127" t="s">
         <v>186</v>
@@ -25837,13 +25837,13 @@
         <v>699</v>
       </c>
       <c r="P127">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Q127">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="R127">
-        <v>2.96</v>
+        <v>0</v>
       </c>
       <c r="S127">
         <v>0</v>
@@ -25983,10 +25983,10 @@
         <v>87</v>
       </c>
       <c r="C128" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="D128" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E128" t="s">
         <v>314</v>
@@ -26022,13 +26022,13 @@
         <v>699</v>
       </c>
       <c r="P128">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Q128">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="R128">
-        <v>3.01</v>
+        <v>0</v>
       </c>
       <c r="S128">
         <v>0</v>
@@ -26168,10 +26168,10 @@
         <v>87</v>
       </c>
       <c r="C129" t="s">
-        <v>128</v>
+        <v>164</v>
       </c>
       <c r="D129" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E129" t="s">
         <v>315</v>
@@ -26207,13 +26207,13 @@
         <v>699</v>
       </c>
       <c r="P129">
-        <v>2.55</v>
+        <v>2.2</v>
       </c>
       <c r="Q129">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="R129">
-        <v>2.43</v>
+        <v>3.2</v>
       </c>
       <c r="S129">
         <v>0</v>
@@ -26353,10 +26353,10 @@
         <v>87</v>
       </c>
       <c r="C130" t="s">
-        <v>151</v>
+        <v>127</v>
       </c>
       <c r="D130" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E130" t="s">
         <v>316</v>
@@ -26392,13 +26392,13 @@
         <v>699</v>
       </c>
       <c r="P130">
-        <v>1.59</v>
+        <v>2.55</v>
       </c>
       <c r="Q130">
-        <v>4.44</v>
+        <v>3.6</v>
       </c>
       <c r="R130">
-        <v>5.16</v>
+        <v>2.43</v>
       </c>
       <c r="S130">
         <v>0</v>
@@ -26538,10 +26538,10 @@
         <v>87</v>
       </c>
       <c r="C131" t="s">
-        <v>151</v>
+        <v>165</v>
       </c>
       <c r="D131" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E131" t="s">
         <v>317</v>
@@ -26577,13 +26577,13 @@
         <v>699</v>
       </c>
       <c r="P131">
-        <v>3.87</v>
+        <v>0</v>
       </c>
       <c r="Q131">
-        <v>3.87</v>
+        <v>0</v>
       </c>
       <c r="R131">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="S131">
         <v>0</v>
@@ -26762,13 +26762,13 @@
         <v>699</v>
       </c>
       <c r="P132">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="Q132">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R132">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="S132">
         <v>0</v>
@@ -26807,10 +26807,10 @@
         <v>0</v>
       </c>
       <c r="AE132">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AF132">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AG132">
         <v>0</v>
@@ -26908,7 +26908,7 @@
         <v>87</v>
       </c>
       <c r="C133" t="s">
-        <v>165</v>
+        <v>125</v>
       </c>
       <c r="D133" t="s">
         <v>186</v>
@@ -26947,13 +26947,13 @@
         <v>699</v>
       </c>
       <c r="P133">
-        <v>2.51</v>
+        <v>0</v>
       </c>
       <c r="Q133">
-        <v>3.78</v>
+        <v>0</v>
       </c>
       <c r="R133">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="S133">
         <v>0</v>
@@ -27093,7 +27093,7 @@
         <v>87</v>
       </c>
       <c r="C134" t="s">
-        <v>166</v>
+        <v>126</v>
       </c>
       <c r="D134" t="s">
         <v>186</v>
@@ -27317,13 +27317,13 @@
         <v>699</v>
       </c>
       <c r="P135">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Q135">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="R135">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="S135">
         <v>0</v>
@@ -27502,13 +27502,13 @@
         <v>699</v>
       </c>
       <c r="P136">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="Q136">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R136">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="S136">
         <v>0</v>
@@ -27547,10 +27547,10 @@
         <v>0</v>
       </c>
       <c r="AE136">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AF136">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG136">
         <v>0</v>
@@ -27648,10 +27648,10 @@
         <v>87</v>
       </c>
       <c r="C137" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="D137" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E137" t="s">
         <v>323</v>
@@ -27687,13 +27687,13 @@
         <v>699</v>
       </c>
       <c r="P137">
-        <v>2.2</v>
+        <v>2.51</v>
       </c>
       <c r="Q137">
-        <v>3.4</v>
+        <v>3.78</v>
       </c>
       <c r="R137">
-        <v>3.2</v>
+        <v>2.44</v>
       </c>
       <c r="S137">
         <v>0</v>
@@ -27833,10 +27833,10 @@
         <v>87</v>
       </c>
       <c r="C138" t="s">
-        <v>120</v>
+        <v>164</v>
       </c>
       <c r="D138" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E138" t="s">
         <v>324</v>
@@ -27872,13 +27872,13 @@
         <v>699</v>
       </c>
       <c r="P138">
-        <v>0</v>
+        <v>4.07</v>
       </c>
       <c r="Q138">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="R138">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="S138">
         <v>0</v>
@@ -28018,16 +28018,16 @@
         <v>87</v>
       </c>
       <c r="C139" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="D139" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E139" t="s">
         <v>325</v>
       </c>
       <c r="F139" t="s">
-        <v>283</v>
+        <v>581</v>
       </c>
       <c r="G139">
         <v>0</v>
@@ -28057,13 +28057,13 @@
         <v>699</v>
       </c>
       <c r="P139">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="Q139">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="R139">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="S139">
         <v>0</v>
@@ -28203,7 +28203,7 @@
         <v>87</v>
       </c>
       <c r="C140" t="s">
-        <v>125</v>
+        <v>158</v>
       </c>
       <c r="D140" t="s">
         <v>186</v>
@@ -28212,7 +28212,7 @@
         <v>326</v>
       </c>
       <c r="F140" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="G140">
         <v>0</v>
@@ -28397,7 +28397,7 @@
         <v>327</v>
       </c>
       <c r="F141" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="G141">
         <v>0</v>
@@ -28427,13 +28427,13 @@
         <v>699</v>
       </c>
       <c r="P141">
-        <v>3.1</v>
+        <v>2.15</v>
       </c>
       <c r="Q141">
         <v>3.7</v>
       </c>
       <c r="R141">
-        <v>2.12</v>
+        <v>3.01</v>
       </c>
       <c r="S141">
         <v>0</v>
@@ -28573,16 +28573,16 @@
         <v>87</v>
       </c>
       <c r="C142" t="s">
-        <v>151</v>
+        <v>158</v>
       </c>
       <c r="D142" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E142" t="s">
         <v>328</v>
       </c>
       <c r="F142" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="G142">
         <v>0</v>
@@ -28612,13 +28612,13 @@
         <v>699</v>
       </c>
       <c r="P142">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="Q142">
-        <v>3.82</v>
+        <v>0</v>
       </c>
       <c r="R142">
-        <v>4.13</v>
+        <v>0</v>
       </c>
       <c r="S142">
         <v>0</v>
@@ -28758,7 +28758,7 @@
         <v>87</v>
       </c>
       <c r="C143" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="D143" t="s">
         <v>186</v>
@@ -28767,7 +28767,7 @@
         <v>329</v>
       </c>
       <c r="F143" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="G143">
         <v>0</v>
@@ -28943,16 +28943,16 @@
         <v>87</v>
       </c>
       <c r="C144" t="s">
-        <v>166</v>
+        <v>151</v>
       </c>
       <c r="D144" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E144" t="s">
         <v>330</v>
       </c>
       <c r="F144" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="G144">
         <v>0</v>
@@ -28982,13 +28982,13 @@
         <v>699</v>
       </c>
       <c r="P144">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="Q144">
-        <v>0</v>
+        <v>3.82</v>
       </c>
       <c r="R144">
-        <v>0</v>
+        <v>4.13</v>
       </c>
       <c r="S144">
         <v>0</v>
@@ -29137,7 +29137,7 @@
         <v>331</v>
       </c>
       <c r="F145" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="G145">
         <v>0</v>
@@ -29167,13 +29167,13 @@
         <v>699</v>
       </c>
       <c r="P145">
-        <v>4.07</v>
+        <v>3.1</v>
       </c>
       <c r="Q145">
-        <v>3.9</v>
+        <v>3.7</v>
       </c>
       <c r="R145">
-        <v>1.78</v>
+        <v>2.12</v>
       </c>
       <c r="S145">
         <v>0</v>
@@ -29313,16 +29313,16 @@
         <v>87</v>
       </c>
       <c r="C146" t="s">
-        <v>143</v>
+        <v>164</v>
       </c>
       <c r="D146" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E146" t="s">
         <v>332</v>
       </c>
       <c r="F146" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="G146">
         <v>0</v>
@@ -29352,13 +29352,13 @@
         <v>699</v>
       </c>
       <c r="P146">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="Q146">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R146">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="S146">
         <v>0</v>
@@ -29498,7 +29498,7 @@
         <v>87</v>
       </c>
       <c r="C147" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="D147" t="s">
         <v>186</v>
@@ -29507,7 +29507,7 @@
         <v>333</v>
       </c>
       <c r="F147" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="G147">
         <v>0</v>
@@ -29683,16 +29683,16 @@
         <v>87</v>
       </c>
       <c r="C148" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="D148" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E148" t="s">
         <v>334</v>
       </c>
       <c r="F148" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="G148">
         <v>0</v>
@@ -29722,13 +29722,13 @@
         <v>699</v>
       </c>
       <c r="P148">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="Q148">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R148">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="S148">
         <v>0</v>
@@ -29868,7 +29868,7 @@
         <v>87</v>
       </c>
       <c r="C149" t="s">
-        <v>126</v>
+        <v>165</v>
       </c>
       <c r="D149" t="s">
         <v>186</v>
@@ -29877,7 +29877,7 @@
         <v>335</v>
       </c>
       <c r="F149" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="G149">
         <v>0</v>
@@ -30053,7 +30053,7 @@
         <v>87</v>
       </c>
       <c r="C150" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="D150" t="s">
         <v>186</v>
@@ -30062,7 +30062,7 @@
         <v>336</v>
       </c>
       <c r="F150" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="G150">
         <v>0</v>
@@ -30238,7 +30238,7 @@
         <v>87</v>
       </c>
       <c r="C151" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="D151" t="s">
         <v>186</v>
@@ -30247,7 +30247,7 @@
         <v>337</v>
       </c>
       <c r="F151" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="G151">
         <v>0</v>
@@ -30423,7 +30423,7 @@
         <v>87</v>
       </c>
       <c r="C152" t="s">
-        <v>161</v>
+        <v>120</v>
       </c>
       <c r="D152" t="s">
         <v>186</v>
@@ -30432,7 +30432,7 @@
         <v>338</v>
       </c>
       <c r="F152" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="G152">
         <v>0</v>
@@ -30608,7 +30608,7 @@
         <v>87</v>
       </c>
       <c r="C153" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="D153" t="s">
         <v>185</v>
@@ -30617,7 +30617,7 @@
         <v>339</v>
       </c>
       <c r="F153" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="G153">
         <v>0</v>
@@ -30793,7 +30793,7 @@
         <v>87</v>
       </c>
       <c r="C154" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="D154" t="s">
         <v>186</v>
@@ -30802,7 +30802,7 @@
         <v>340</v>
       </c>
       <c r="F154" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="G154">
         <v>0</v>
@@ -30978,7 +30978,7 @@
         <v>87</v>
       </c>
       <c r="C155" t="s">
-        <v>161</v>
+        <v>143</v>
       </c>
       <c r="D155" t="s">
         <v>186</v>
@@ -30987,7 +30987,7 @@
         <v>341</v>
       </c>
       <c r="F155" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="G155">
         <v>0</v>
@@ -31172,7 +31172,7 @@
         <v>342</v>
       </c>
       <c r="F156" t="s">
-        <v>597</v>
+        <v>284</v>
       </c>
       <c r="G156">
         <v>0</v>
@@ -32088,7 +32088,7 @@
         <v>89</v>
       </c>
       <c r="C161" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="D161" t="s">
         <v>186</v>
@@ -32127,13 +32127,13 @@
         <v>699</v>
       </c>
       <c r="P161">
-        <v>0</v>
+        <v>5.17</v>
       </c>
       <c r="Q161">
-        <v>0</v>
+        <v>4.37</v>
       </c>
       <c r="R161">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="S161">
         <v>0</v>
@@ -32172,10 +32172,10 @@
         <v>0</v>
       </c>
       <c r="AE161">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AF161">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AG161">
         <v>0</v>
@@ -32458,7 +32458,7 @@
         <v>89</v>
       </c>
       <c r="C163" t="s">
-        <v>152</v>
+        <v>130</v>
       </c>
       <c r="D163" t="s">
         <v>186</v>
@@ -32497,13 +32497,13 @@
         <v>699</v>
       </c>
       <c r="P163">
-        <v>5.17</v>
+        <v>4.09</v>
       </c>
       <c r="Q163">
-        <v>4.37</v>
+        <v>3.78</v>
       </c>
       <c r="R163">
-        <v>1.69</v>
+        <v>1.77</v>
       </c>
       <c r="S163">
         <v>0</v>
@@ -32542,10 +32542,10 @@
         <v>0</v>
       </c>
       <c r="AE163">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AF163">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AG163">
         <v>0</v>
@@ -32643,7 +32643,7 @@
         <v>89</v>
       </c>
       <c r="C164" t="s">
-        <v>130</v>
+        <v>168</v>
       </c>
       <c r="D164" t="s">
         <v>186</v>
@@ -32682,13 +32682,13 @@
         <v>699</v>
       </c>
       <c r="P164">
-        <v>4.09</v>
+        <v>0</v>
       </c>
       <c r="Q164">
-        <v>3.78</v>
+        <v>0</v>
       </c>
       <c r="R164">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="S164">
         <v>0</v>
@@ -32828,7 +32828,7 @@
         <v>89</v>
       </c>
       <c r="C165" t="s">
-        <v>168</v>
+        <v>155</v>
       </c>
       <c r="D165" t="s">
         <v>186</v>
@@ -33013,7 +33013,7 @@
         <v>90</v>
       </c>
       <c r="C166" t="s">
-        <v>144</v>
+        <v>169</v>
       </c>
       <c r="D166" t="s">
         <v>186</v>
@@ -33198,7 +33198,7 @@
         <v>90</v>
       </c>
       <c r="C167" t="s">
-        <v>169</v>
+        <v>131</v>
       </c>
       <c r="D167" t="s">
         <v>186</v>
@@ -33237,13 +33237,13 @@
         <v>699</v>
       </c>
       <c r="P167">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="Q167">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R167">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="S167">
         <v>0</v>
@@ -33568,10 +33568,10 @@
         <v>90</v>
       </c>
       <c r="C169" t="s">
-        <v>136</v>
+        <v>169</v>
       </c>
       <c r="D169" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E169" t="s">
         <v>355</v>
@@ -33753,10 +33753,10 @@
         <v>90</v>
       </c>
       <c r="C170" t="s">
-        <v>169</v>
+        <v>136</v>
       </c>
       <c r="D170" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E170" t="s">
         <v>356</v>
@@ -33938,7 +33938,7 @@
         <v>90</v>
       </c>
       <c r="C171" t="s">
-        <v>169</v>
+        <v>120</v>
       </c>
       <c r="D171" t="s">
         <v>186</v>
@@ -34123,7 +34123,7 @@
         <v>90</v>
       </c>
       <c r="C172" t="s">
-        <v>131</v>
+        <v>170</v>
       </c>
       <c r="D172" t="s">
         <v>186</v>
@@ -34162,13 +34162,13 @@
         <v>699</v>
       </c>
       <c r="P172">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="Q172">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="R172">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="S172">
         <v>0</v>
@@ -34308,7 +34308,7 @@
         <v>90</v>
       </c>
       <c r="C173" t="s">
-        <v>170</v>
+        <v>145</v>
       </c>
       <c r="D173" t="s">
         <v>186</v>
@@ -34493,7 +34493,7 @@
         <v>90</v>
       </c>
       <c r="C174" t="s">
-        <v>120</v>
+        <v>169</v>
       </c>
       <c r="D174" t="s">
         <v>186</v>
@@ -34678,7 +34678,7 @@
         <v>90</v>
       </c>
       <c r="C175" t="s">
-        <v>169</v>
+        <v>153</v>
       </c>
       <c r="D175" t="s">
         <v>186</v>
@@ -34717,13 +34717,13 @@
         <v>699</v>
       </c>
       <c r="P175">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="Q175">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R175">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="S175">
         <v>0</v>
@@ -34863,7 +34863,7 @@
         <v>90</v>
       </c>
       <c r="C176" t="s">
-        <v>156</v>
+        <v>169</v>
       </c>
       <c r="D176" t="s">
         <v>186</v>
@@ -34902,13 +34902,13 @@
         <v>699</v>
       </c>
       <c r="P176">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="Q176">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="R176">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="S176">
         <v>0</v>
@@ -35233,10 +35233,10 @@
         <v>92</v>
       </c>
       <c r="C178" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="D178" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E178" t="s">
         <v>364</v>
@@ -35418,7 +35418,7 @@
         <v>92</v>
       </c>
       <c r="C179" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="D179" t="s">
         <v>185</v>
@@ -35603,7 +35603,7 @@
         <v>92</v>
       </c>
       <c r="C180" t="s">
-        <v>160</v>
+        <v>135</v>
       </c>
       <c r="D180" t="s">
         <v>186</v>
@@ -35642,13 +35642,13 @@
         <v>699</v>
       </c>
       <c r="P180">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="Q180">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R180">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="S180">
         <v>0</v>
@@ -35788,10 +35788,10 @@
         <v>92</v>
       </c>
       <c r="C181" t="s">
-        <v>135</v>
+        <v>160</v>
       </c>
       <c r="D181" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E181" t="s">
         <v>367</v>
@@ -35827,13 +35827,13 @@
         <v>699</v>
       </c>
       <c r="P181">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="Q181">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="R181">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="S181">
         <v>0</v>
@@ -35973,7 +35973,7 @@
         <v>93</v>
       </c>
       <c r="C182" t="s">
-        <v>158</v>
+        <v>147</v>
       </c>
       <c r="D182" t="s">
         <v>186</v>
@@ -36012,13 +36012,13 @@
         <v>699</v>
       </c>
       <c r="P182">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="Q182">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="R182">
-        <v>6.76</v>
+        <v>0</v>
       </c>
       <c r="S182">
         <v>0</v>
@@ -36158,10 +36158,10 @@
         <v>93</v>
       </c>
       <c r="C183" t="s">
-        <v>172</v>
+        <v>154</v>
       </c>
       <c r="D183" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E183" t="s">
         <v>369</v>
@@ -36343,7 +36343,7 @@
         <v>93</v>
       </c>
       <c r="C184" t="s">
-        <v>148</v>
+        <v>140</v>
       </c>
       <c r="D184" t="s">
         <v>186</v>
@@ -36382,13 +36382,13 @@
         <v>699</v>
       </c>
       <c r="P184">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Q184">
-        <v>0</v>
+        <v>5.66</v>
       </c>
       <c r="R184">
-        <v>0</v>
+        <v>8.98</v>
       </c>
       <c r="S184">
         <v>0</v>
@@ -36528,7 +36528,7 @@
         <v>93</v>
       </c>
       <c r="C185" t="s">
-        <v>173</v>
+        <v>149</v>
       </c>
       <c r="D185" t="s">
         <v>186</v>
@@ -36567,13 +36567,13 @@
         <v>699</v>
       </c>
       <c r="P185">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="Q185">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="R185">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="S185">
         <v>0</v>
@@ -36713,7 +36713,7 @@
         <v>93</v>
       </c>
       <c r="C186" t="s">
-        <v>173</v>
+        <v>159</v>
       </c>
       <c r="D186" t="s">
         <v>186</v>
@@ -36752,13 +36752,13 @@
         <v>699</v>
       </c>
       <c r="P186">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="Q186">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R186">
-        <v>0</v>
+        <v>4.56</v>
       </c>
       <c r="S186">
         <v>0</v>
@@ -36898,7 +36898,7 @@
         <v>93</v>
       </c>
       <c r="C187" t="s">
-        <v>123</v>
+        <v>172</v>
       </c>
       <c r="D187" t="s">
         <v>186</v>
@@ -36937,13 +36937,13 @@
         <v>699</v>
       </c>
       <c r="P187">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Q187">
-        <v>3.66</v>
+        <v>0</v>
       </c>
       <c r="R187">
-        <v>3.36</v>
+        <v>0</v>
       </c>
       <c r="S187">
         <v>0</v>
@@ -37083,7 +37083,7 @@
         <v>93</v>
       </c>
       <c r="C188" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="D188" t="s">
         <v>185</v>
@@ -37268,7 +37268,7 @@
         <v>93</v>
       </c>
       <c r="C189" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="D189" t="s">
         <v>186</v>
@@ -37307,13 +37307,13 @@
         <v>699</v>
       </c>
       <c r="P189">
-        <v>1.82</v>
+        <v>1.45</v>
       </c>
       <c r="Q189">
-        <v>3.1</v>
+        <v>3.8</v>
       </c>
       <c r="R189">
-        <v>4.56</v>
+        <v>6.76</v>
       </c>
       <c r="S189">
         <v>0</v>
@@ -37453,7 +37453,7 @@
         <v>93</v>
       </c>
       <c r="C190" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="D190" t="s">
         <v>186</v>
@@ -37638,10 +37638,10 @@
         <v>93</v>
       </c>
       <c r="C191" t="s">
-        <v>149</v>
+        <v>174</v>
       </c>
       <c r="D191" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E191" t="s">
         <v>377</v>
@@ -37677,13 +37677,13 @@
         <v>699</v>
       </c>
       <c r="P191">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="Q191">
-        <v>3.53</v>
+        <v>0</v>
       </c>
       <c r="R191">
-        <v>3.91</v>
+        <v>0</v>
       </c>
       <c r="S191">
         <v>0</v>
@@ -37722,10 +37722,10 @@
         <v>0</v>
       </c>
       <c r="AE191">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AF191">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AG191">
         <v>0</v>
@@ -37823,10 +37823,10 @@
         <v>93</v>
       </c>
       <c r="C192" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="D192" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E192" t="s">
         <v>378</v>
@@ -38008,7 +38008,7 @@
         <v>93</v>
       </c>
       <c r="C193" t="s">
-        <v>149</v>
+        <v>172</v>
       </c>
       <c r="D193" t="s">
         <v>186</v>
@@ -38047,13 +38047,13 @@
         <v>699</v>
       </c>
       <c r="P193">
-        <v>3.12</v>
+        <v>0</v>
       </c>
       <c r="Q193">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="R193">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="S193">
         <v>0</v>
@@ -38193,10 +38193,10 @@
         <v>93</v>
       </c>
       <c r="C194" t="s">
-        <v>172</v>
+        <v>123</v>
       </c>
       <c r="D194" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E194" t="s">
         <v>380</v>
@@ -38232,13 +38232,13 @@
         <v>699</v>
       </c>
       <c r="P194">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Q194">
-        <v>0</v>
+        <v>3.66</v>
       </c>
       <c r="R194">
-        <v>0</v>
+        <v>3.36</v>
       </c>
       <c r="S194">
         <v>0</v>
@@ -38378,7 +38378,7 @@
         <v>93</v>
       </c>
       <c r="C195" t="s">
-        <v>142</v>
+        <v>149</v>
       </c>
       <c r="D195" t="s">
         <v>186</v>
@@ -38417,13 +38417,13 @@
         <v>699</v>
       </c>
       <c r="P195">
-        <v>1.28</v>
+        <v>1.91</v>
       </c>
       <c r="Q195">
-        <v>5.66</v>
+        <v>3.53</v>
       </c>
       <c r="R195">
-        <v>8.98</v>
+        <v>3.91</v>
       </c>
       <c r="S195">
         <v>0</v>
@@ -38462,10 +38462,10 @@
         <v>0</v>
       </c>
       <c r="AE195">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AF195">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AG195">
         <v>0</v>
@@ -38563,7 +38563,7 @@
         <v>93</v>
       </c>
       <c r="C196" t="s">
-        <v>153</v>
+        <v>172</v>
       </c>
       <c r="D196" t="s">
         <v>186</v>
@@ -38748,10 +38748,10 @@
         <v>94</v>
       </c>
       <c r="C197" t="s">
-        <v>175</v>
+        <v>146</v>
       </c>
       <c r="D197" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E197" t="s">
         <v>383</v>
@@ -38787,13 +38787,13 @@
         <v>699</v>
       </c>
       <c r="P197">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Q197">
-        <v>3.38</v>
+        <v>0</v>
       </c>
       <c r="R197">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="S197">
         <v>0</v>
@@ -38972,13 +38972,13 @@
         <v>699</v>
       </c>
       <c r="P198">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Q198">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="R198">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="S198">
         <v>0</v>
@@ -39488,7 +39488,7 @@
         <v>94</v>
       </c>
       <c r="C201" t="s">
-        <v>161</v>
+        <v>175</v>
       </c>
       <c r="D201" t="s">
         <v>186</v>
@@ -39673,7 +39673,7 @@
         <v>94</v>
       </c>
       <c r="C202" t="s">
-        <v>147</v>
+        <v>176</v>
       </c>
       <c r="D202" t="s">
         <v>185</v>
@@ -39712,13 +39712,13 @@
         <v>699</v>
       </c>
       <c r="P202">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="Q202">
-        <v>0</v>
+        <v>4.45</v>
       </c>
       <c r="R202">
-        <v>0</v>
+        <v>5.12</v>
       </c>
       <c r="S202">
         <v>0</v>
@@ -39858,7 +39858,7 @@
         <v>94</v>
       </c>
       <c r="C203" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="D203" t="s">
         <v>186</v>
@@ -40043,10 +40043,10 @@
         <v>94</v>
       </c>
       <c r="C204" t="s">
-        <v>176</v>
+        <v>158</v>
       </c>
       <c r="D204" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E204" t="s">
         <v>390</v>
@@ -40082,13 +40082,13 @@
         <v>699</v>
       </c>
       <c r="P204">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="Q204">
-        <v>4.45</v>
+        <v>0</v>
       </c>
       <c r="R204">
-        <v>5.12</v>
+        <v>0</v>
       </c>
       <c r="S204">
         <v>0</v>
@@ -40228,7 +40228,7 @@
         <v>95</v>
       </c>
       <c r="C205" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="D205" t="s">
         <v>186</v>
@@ -40413,7 +40413,7 @@
         <v>96</v>
       </c>
       <c r="C206" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="D206" t="s">
         <v>186</v>
@@ -41523,7 +41523,7 @@
         <v>98</v>
       </c>
       <c r="C212" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="D212" t="s">
         <v>186</v>
@@ -42081,7 +42081,7 @@
         <v>179</v>
       </c>
       <c r="D215" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E215" t="s">
         <v>401</v>
@@ -42117,13 +42117,13 @@
         <v>699</v>
       </c>
       <c r="P215">
-        <v>4.05</v>
+        <v>2.15</v>
       </c>
       <c r="Q215">
-        <v>3.76</v>
+        <v>3.44</v>
       </c>
       <c r="R215">
-        <v>1.99</v>
+        <v>3.5</v>
       </c>
       <c r="S215">
         <v>0</v>
@@ -42162,10 +42162,10 @@
         <v>0</v>
       </c>
       <c r="AE215">
-        <v>1.85</v>
+        <v>1.95</v>
       </c>
       <c r="AF215">
-        <v>1.85</v>
+        <v>1.75</v>
       </c>
       <c r="AG215">
         <v>0</v>
@@ -42263,7 +42263,7 @@
         <v>100</v>
       </c>
       <c r="C216" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="D216" t="s">
         <v>185</v>
@@ -42302,13 +42302,13 @@
         <v>699</v>
       </c>
       <c r="P216">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="Q216">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R216">
-        <v>0</v>
+        <v>4.39</v>
       </c>
       <c r="S216">
         <v>0</v>
@@ -42448,10 +42448,10 @@
         <v>100</v>
       </c>
       <c r="C217" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="D217" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E217" t="s">
         <v>403</v>
@@ -42487,13 +42487,13 @@
         <v>699</v>
       </c>
       <c r="P217">
-        <v>2.15</v>
+        <v>3.17</v>
       </c>
       <c r="Q217">
-        <v>3.44</v>
+        <v>3.68</v>
       </c>
       <c r="R217">
-        <v>3.5</v>
+        <v>2.34</v>
       </c>
       <c r="S217">
         <v>0</v>
@@ -42532,10 +42532,10 @@
         <v>0</v>
       </c>
       <c r="AE217">
-        <v>1.95</v>
+        <v>1.72</v>
       </c>
       <c r="AF217">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="AG217">
         <v>0</v>
@@ -42633,7 +42633,7 @@
         <v>100</v>
       </c>
       <c r="C218" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="D218" t="s">
         <v>186</v>
@@ -42672,13 +42672,13 @@
         <v>699</v>
       </c>
       <c r="P218">
-        <v>4.68</v>
+        <v>2.48</v>
       </c>
       <c r="Q218">
-        <v>4.32</v>
+        <v>3.5</v>
       </c>
       <c r="R218">
-        <v>1.76</v>
+        <v>3.07</v>
       </c>
       <c r="S218">
         <v>0</v>
@@ -42717,10 +42717,10 @@
         <v>0</v>
       </c>
       <c r="AE218">
-        <v>1.58</v>
+        <v>1.8</v>
       </c>
       <c r="AF218">
-        <v>2.25</v>
+        <v>1.9</v>
       </c>
       <c r="AG218">
         <v>0</v>
@@ -42818,7 +42818,7 @@
         <v>100</v>
       </c>
       <c r="C219" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="D219" t="s">
         <v>186</v>
@@ -42857,13 +42857,13 @@
         <v>699</v>
       </c>
       <c r="P219">
-        <v>3.17</v>
+        <v>2.38</v>
       </c>
       <c r="Q219">
-        <v>3.68</v>
+        <v>3.9</v>
       </c>
       <c r="R219">
-        <v>2.34</v>
+        <v>2.96</v>
       </c>
       <c r="S219">
         <v>0</v>
@@ -42902,10 +42902,10 @@
         <v>0</v>
       </c>
       <c r="AE219">
-        <v>1.72</v>
+        <v>1.58</v>
       </c>
       <c r="AF219">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="AG219">
         <v>0</v>
@@ -43003,10 +43003,10 @@
         <v>100</v>
       </c>
       <c r="C220" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="D220" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E220" t="s">
         <v>406</v>
@@ -43042,13 +43042,13 @@
         <v>699</v>
       </c>
       <c r="P220">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="Q220">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="R220">
-        <v>2.96</v>
+        <v>0</v>
       </c>
       <c r="S220">
         <v>0</v>
@@ -43087,10 +43087,10 @@
         <v>0</v>
       </c>
       <c r="AE220">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AF220">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AG220">
         <v>0</v>
@@ -43188,7 +43188,7 @@
         <v>100</v>
       </c>
       <c r="C221" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="D221" t="s">
         <v>185</v>
@@ -43227,13 +43227,13 @@
         <v>699</v>
       </c>
       <c r="P221">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="Q221">
-        <v>0</v>
+        <v>3.73</v>
       </c>
       <c r="R221">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="S221">
         <v>0</v>
@@ -43272,10 +43272,10 @@
         <v>0</v>
       </c>
       <c r="AE221">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AF221">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AG221">
         <v>0</v>
@@ -43373,10 +43373,10 @@
         <v>100</v>
       </c>
       <c r="C222" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="D222" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E222" t="s">
         <v>408</v>
@@ -43412,13 +43412,13 @@
         <v>699</v>
       </c>
       <c r="P222">
-        <v>5.3</v>
+        <v>1.18</v>
       </c>
       <c r="Q222">
-        <v>3.73</v>
+        <v>9.15</v>
       </c>
       <c r="R222">
-        <v>1.71</v>
+        <v>17</v>
       </c>
       <c r="S222">
         <v>0</v>
@@ -43457,16 +43457,16 @@
         <v>0</v>
       </c>
       <c r="AE222">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AF222">
+        <v>0</v>
+      </c>
+      <c r="AG222">
         <v>1.73</v>
       </c>
-      <c r="AG222">
-        <v>0</v>
-      </c>
       <c r="AH222">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AI222">
         <v>0</v>
@@ -43561,7 +43561,7 @@
         <v>181</v>
       </c>
       <c r="D223" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E223" t="s">
         <v>409</v>
@@ -43597,13 +43597,13 @@
         <v>699</v>
       </c>
       <c r="P223">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="Q223">
-        <v>0</v>
+        <v>4.73</v>
       </c>
       <c r="R223">
-        <v>0</v>
+        <v>5.79</v>
       </c>
       <c r="S223">
         <v>0</v>
@@ -43648,10 +43648,10 @@
         <v>0</v>
       </c>
       <c r="AG223">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AH223">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AI223">
         <v>0</v>
@@ -43743,10 +43743,10 @@
         <v>100</v>
       </c>
       <c r="C224" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="D224" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E224" t="s">
         <v>410</v>
@@ -43782,13 +43782,13 @@
         <v>699</v>
       </c>
       <c r="P224">
-        <v>1.79</v>
+        <v>4.05</v>
       </c>
       <c r="Q224">
-        <v>3.5</v>
+        <v>3.76</v>
       </c>
       <c r="R224">
-        <v>4.39</v>
+        <v>1.99</v>
       </c>
       <c r="S224">
         <v>0</v>
@@ -43827,10 +43827,10 @@
         <v>0</v>
       </c>
       <c r="AE224">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AF224">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG224">
         <v>0</v>
@@ -43928,7 +43928,7 @@
         <v>100</v>
       </c>
       <c r="C225" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="D225" t="s">
         <v>186</v>
@@ -43967,13 +43967,13 @@
         <v>699</v>
       </c>
       <c r="P225">
-        <v>3.8</v>
+        <v>4.68</v>
       </c>
       <c r="Q225">
-        <v>3.78</v>
+        <v>4.32</v>
       </c>
       <c r="R225">
-        <v>2.05</v>
+        <v>1.76</v>
       </c>
       <c r="S225">
         <v>0</v>
@@ -44012,10 +44012,10 @@
         <v>0</v>
       </c>
       <c r="AE225">
-        <v>1.73</v>
+        <v>1.58</v>
       </c>
       <c r="AF225">
-        <v>1.98</v>
+        <v>2.25</v>
       </c>
       <c r="AG225">
         <v>0</v>
@@ -44113,7 +44113,7 @@
         <v>100</v>
       </c>
       <c r="C226" t="s">
-        <v>148</v>
+        <v>181</v>
       </c>
       <c r="D226" t="s">
         <v>186</v>
@@ -44152,13 +44152,13 @@
         <v>699</v>
       </c>
       <c r="P226">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="Q226">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="R226">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="S226">
         <v>0</v>
@@ -44197,10 +44197,10 @@
         <v>0</v>
       </c>
       <c r="AE226">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AF226">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AG226">
         <v>0</v>
@@ -44298,7 +44298,7 @@
         <v>100</v>
       </c>
       <c r="C227" t="s">
-        <v>179</v>
+        <v>147</v>
       </c>
       <c r="D227" t="s">
         <v>186</v>
@@ -44337,13 +44337,13 @@
         <v>699</v>
       </c>
       <c r="P227">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="Q227">
-        <v>9.15</v>
+        <v>0</v>
       </c>
       <c r="R227">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="S227">
         <v>0</v>
@@ -44388,10 +44388,10 @@
         <v>0</v>
       </c>
       <c r="AG227">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AH227">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AI227">
         <v>0</v>
@@ -44483,10 +44483,10 @@
         <v>100</v>
       </c>
       <c r="C228" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="D228" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E228" t="s">
         <v>414</v>
@@ -44522,13 +44522,13 @@
         <v>699</v>
       </c>
       <c r="P228">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="Q228">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="R228">
-        <v>3.07</v>
+        <v>0</v>
       </c>
       <c r="S228">
         <v>0</v>
@@ -44567,10 +44567,10 @@
         <v>0</v>
       </c>
       <c r="AE228">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AF228">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AG228">
         <v>0</v>
@@ -44668,10 +44668,10 @@
         <v>100</v>
       </c>
       <c r="C229" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="D229" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E229" t="s">
         <v>415</v>
@@ -44707,13 +44707,13 @@
         <v>699</v>
       </c>
       <c r="P229">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="Q229">
-        <v>4.73</v>
+        <v>0</v>
       </c>
       <c r="R229">
-        <v>5.79</v>
+        <v>0</v>
       </c>
       <c r="S229">
         <v>0</v>
@@ -44758,10 +44758,10 @@
         <v>0</v>
       </c>
       <c r="AG229">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AH229">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AI229">
         <v>0</v>
@@ -45408,10 +45408,10 @@
         <v>102</v>
       </c>
       <c r="C233" t="s">
-        <v>170</v>
+        <v>178</v>
       </c>
       <c r="D233" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E233" t="s">
         <v>419</v>
@@ -45593,7 +45593,7 @@
         <v>102</v>
       </c>
       <c r="C234" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="D234" t="s">
         <v>185</v>
@@ -45778,10 +45778,10 @@
         <v>102</v>
       </c>
       <c r="C235" t="s">
-        <v>177</v>
+        <v>170</v>
       </c>
       <c r="D235" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E235" t="s">
         <v>421</v>
@@ -45963,7 +45963,7 @@
         <v>102</v>
       </c>
       <c r="C236" t="s">
-        <v>178</v>
+        <v>173</v>
       </c>
       <c r="D236" t="s">
         <v>185</v>
@@ -46888,7 +46888,7 @@
         <v>105</v>
       </c>
       <c r="C241" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="D241" t="s">
         <v>185</v>
@@ -47073,7 +47073,7 @@
         <v>106</v>
       </c>
       <c r="C242" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="D242" t="s">
         <v>185</v>
@@ -47112,13 +47112,13 @@
         <v>699</v>
       </c>
       <c r="P242">
-        <v>2.81</v>
+        <v>1.79</v>
       </c>
       <c r="Q242">
-        <v>3.08</v>
+        <v>3.62</v>
       </c>
       <c r="R242">
-        <v>2.51</v>
+        <v>4.84</v>
       </c>
       <c r="S242">
         <v>0</v>
@@ -47157,10 +47157,10 @@
         <v>0</v>
       </c>
       <c r="AE242">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AF242">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG242">
         <v>0</v>
@@ -47258,7 +47258,7 @@
         <v>106</v>
       </c>
       <c r="C243" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="D243" t="s">
         <v>185</v>
@@ -47482,13 +47482,13 @@
         <v>699</v>
       </c>
       <c r="P244">
-        <v>2.26</v>
+        <v>2.81</v>
       </c>
       <c r="Q244">
-        <v>3.22</v>
+        <v>3.08</v>
       </c>
       <c r="R244">
-        <v>3.46</v>
+        <v>2.51</v>
       </c>
       <c r="S244">
         <v>0</v>
@@ -47527,10 +47527,10 @@
         <v>0</v>
       </c>
       <c r="AE244">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AF244">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AG244">
         <v>0</v>
@@ -47628,7 +47628,7 @@
         <v>106</v>
       </c>
       <c r="C245" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="D245" t="s">
         <v>185</v>
@@ -47667,13 +47667,13 @@
         <v>699</v>
       </c>
       <c r="P245">
-        <v>1.79</v>
+        <v>2.26</v>
       </c>
       <c r="Q245">
-        <v>3.62</v>
+        <v>3.22</v>
       </c>
       <c r="R245">
-        <v>4.84</v>
+        <v>3.46</v>
       </c>
       <c r="S245">
         <v>0</v>
@@ -47712,10 +47712,10 @@
         <v>0</v>
       </c>
       <c r="AE245">
-        <v>1.87</v>
+        <v>2.25</v>
       </c>
       <c r="AF245">
-        <v>1.8</v>
+        <v>1.57</v>
       </c>
       <c r="AG245">
         <v>0</v>
@@ -47998,7 +47998,7 @@
         <v>108</v>
       </c>
       <c r="C247" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="D247" t="s">
         <v>185</v>
@@ -48183,7 +48183,7 @@
         <v>108</v>
       </c>
       <c r="C248" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="D248" t="s">
         <v>185</v>
@@ -48368,7 +48368,7 @@
         <v>109</v>
       </c>
       <c r="C249" t="s">
-        <v>174</v>
+        <v>183</v>
       </c>
       <c r="D249" t="s">
         <v>185</v>
@@ -48407,13 +48407,13 @@
         <v>699</v>
       </c>
       <c r="P249">
-        <v>4.44</v>
+        <v>1.72</v>
       </c>
       <c r="Q249">
-        <v>3.5</v>
+        <v>3.97</v>
       </c>
       <c r="R249">
-        <v>1.73</v>
+        <v>5.09</v>
       </c>
       <c r="S249">
         <v>0</v>
@@ -48452,10 +48452,10 @@
         <v>0</v>
       </c>
       <c r="AE249">
-        <v>1.99</v>
+        <v>1.7</v>
       </c>
       <c r="AF249">
-        <v>1.76</v>
+        <v>2</v>
       </c>
       <c r="AG249">
         <v>0</v>
@@ -48553,7 +48553,7 @@
         <v>109</v>
       </c>
       <c r="C250" t="s">
-        <v>183</v>
+        <v>173</v>
       </c>
       <c r="D250" t="s">
         <v>185</v>
@@ -48592,13 +48592,13 @@
         <v>699</v>
       </c>
       <c r="P250">
-        <v>1.72</v>
+        <v>4.44</v>
       </c>
       <c r="Q250">
-        <v>3.97</v>
+        <v>3.5</v>
       </c>
       <c r="R250">
-        <v>5.09</v>
+        <v>1.73</v>
       </c>
       <c r="S250">
         <v>0</v>
@@ -48637,10 +48637,10 @@
         <v>0</v>
       </c>
       <c r="AE250">
-        <v>1.7</v>
+        <v>1.99</v>
       </c>
       <c r="AF250">
-        <v>2</v>
+        <v>1.76</v>
       </c>
       <c r="AG250">
         <v>0</v>
@@ -49108,7 +49108,7 @@
         <v>111</v>
       </c>
       <c r="C253" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="D253" t="s">
         <v>185</v>
@@ -49293,7 +49293,7 @@
         <v>111</v>
       </c>
       <c r="C254" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="D254" t="s">
         <v>185</v>

--- a/jogos_2026-05-10.xlsx
+++ b/jogos_2026-05-10.xlsx
@@ -753,7 +753,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>Australia New South Wales NPL</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -763,12 +763,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Seongnam</t>
+          <t>Blacktown City</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Jeonnam Dragons</t>
+          <t>St. George Saints</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -801,13 +801,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>3.61</v>
+        <v>0</v>
       </c>
       <c r="S2" t="n">
         <v>0</v>
@@ -950,7 +950,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Australia New South Wales NPL</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Blacktown City</t>
+          <t>Ulsan</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>St. George Saints</t>
+          <t>Bucheon 1995</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Australia New South Wales NPL</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Rockdale City Suns</t>
+          <t>Seongnam</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Sydney II</t>
+          <t>Jeonnam Dragons</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1195,13 +1195,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>3.61</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
@@ -1344,7 +1344,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>Australia New South Wales NPL</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Ulsan</t>
+          <t>Rockdale City Suns</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Bucheon 1995</t>
+          <t>Sydney II</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Dalian Huayi</t>
+          <t>Shaanxi Union</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Guangzhou E-Power</t>
+          <t>Shanghai Jiading</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Shaanxi Union</t>
+          <t>Dalian Huayi</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Shanghai Jiading</t>
+          <t>Guangzhou E-Power</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Persita</t>
+          <t>Persija</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Persijap</t>
+          <t>Persib</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Persija</t>
+          <t>Persita</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Persib</t>
+          <t>Persijap</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -4299,22 +4299,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Polonia Warszawa</t>
+          <t>Ulytau</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Górnik Łęczna</t>
+          <t>Kairat</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4693,7 +4693,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Hoang Anh Gia Lai</t>
+          <t>Amarante</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Pho Hien</t>
+          <t>União Santarém</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Gyeongnam</t>
+          <t>Sichuan Jiuniu</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Gimhae City</t>
+          <t>Shandong Luneng</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4938,13 +4938,13 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>3.16</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="S23" t="n">
         <v>0</v>
@@ -5087,7 +5087,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Sokol Saratov</t>
+          <t>Hoang Anh Gia Lai</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Spartak Kostroma</t>
+          <t>Pho Hien</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5135,13 +5135,13 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>4.98</v>
+        <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>3.66</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="S24" t="n">
         <v>0</v>
@@ -5284,22 +5284,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Levante W</t>
+          <t>Gyeongnam</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Logroño W</t>
+          <t>Gimhae City</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5332,13 +5332,13 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="R25" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="S25" t="n">
         <v>0</v>
@@ -5481,22 +5481,22 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Sichuan Jiuniu</t>
+          <t>Levante W</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Shandong Luneng</t>
+          <t>Logroño W</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5678,22 +5678,22 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Ulytau</t>
+          <t>Sokol Saratov</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Kairat</t>
+          <t>Spartak Kostroma</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5726,13 +5726,13 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>0</v>
+        <v>4.98</v>
       </c>
       <c r="Q27" t="n">
-        <v>0</v>
+        <v>3.66</v>
       </c>
       <c r="R27" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="S27" t="n">
         <v>0</v>
@@ -5875,7 +5875,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Amarante</t>
+          <t>Polonia Warszawa</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>União Santarém</t>
+          <t>Górnik Łęczna</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -6466,22 +6466,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Rayong</t>
+          <t>Shenyang Urban</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Bangkok United</t>
+          <t>Yunnan Yukun</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6514,13 +6514,13 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>3.63</v>
+        <v>0</v>
       </c>
       <c r="R31" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="S31" t="n">
         <v>0</v>
@@ -6663,7 +6663,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Bangkok Glass</t>
+          <t>Ho Chi Minh City</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Prachuap</t>
+          <t>Song Lam Nghe An</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6711,13 +6711,13 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="R32" t="n">
-        <v>4.35</v>
+        <v>0</v>
       </c>
       <c r="S32" t="n">
         <v>0</v>
@@ -7057,7 +7057,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Ho Chi Minh City</t>
+          <t>Kanchanaburi</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Song Lam Nghe An</t>
+          <t>Ratchaburi</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7105,13 +7105,13 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="Q34" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="R34" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="S34" t="n">
         <v>0</v>
@@ -7254,7 +7254,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Hà Nội II</t>
+          <t>Bangkok Glass</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Viettel</t>
+          <t>Prachuap</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7302,13 +7302,13 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="Q35" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="R35" t="n">
-        <v>0</v>
+        <v>4.35</v>
       </c>
       <c r="S35" t="n">
         <v>0</v>
@@ -7451,22 +7451,22 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Altay</t>
+          <t>Rayong</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Ordabasy</t>
+          <t>Bangkok United</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7499,13 +7499,13 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="Q36" t="n">
-        <v>0</v>
+        <v>3.63</v>
       </c>
       <c r="R36" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="S36" t="n">
         <v>0</v>
@@ -7648,22 +7648,22 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Piteå Women</t>
+          <t>Buriram United</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Rosengard Women</t>
+          <t>Lamphun Warrior</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7696,13 +7696,13 @@
         </is>
       </c>
       <c r="P37" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="Q37" t="n">
-        <v>0</v>
+        <v>6.73</v>
       </c>
       <c r="R37" t="n">
-        <v>0</v>
+        <v>10.6</v>
       </c>
       <c r="S37" t="n">
         <v>0</v>
@@ -7845,7 +7845,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Buriram United</t>
+          <t>Hà Nội II</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Lamphun Warrior</t>
+          <t>Viettel</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -7893,13 +7893,13 @@
         </is>
       </c>
       <c r="P38" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>6.73</v>
+        <v>0</v>
       </c>
       <c r="R38" t="n">
-        <v>10.6</v>
+        <v>0</v>
       </c>
       <c r="S38" t="n">
         <v>0</v>
@@ -8042,7 +8042,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Shenzhen Juniors</t>
+          <t>Piteå Women</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Hebei Kungfu</t>
+          <t>Rosengard Women</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Kanchanaburi</t>
+          <t>Ayutthaya United</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Ratchaburi</t>
+          <t>Port FC</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8287,13 +8287,13 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>3.32</v>
+        <v>5.09</v>
       </c>
       <c r="Q40" t="n">
-        <v>3.95</v>
+        <v>4.18</v>
       </c>
       <c r="R40" t="n">
-        <v>2.03</v>
+        <v>1.64</v>
       </c>
       <c r="S40" t="n">
         <v>0</v>
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Ayutthaya United</t>
+          <t>Sukhothai</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Port FC</t>
+          <t>Muang Thong United</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8484,13 +8484,13 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>5.09</v>
+        <v>2.44</v>
       </c>
       <c r="Q41" t="n">
-        <v>4.18</v>
+        <v>3.61</v>
       </c>
       <c r="R41" t="n">
-        <v>1.64</v>
+        <v>2.77</v>
       </c>
       <c r="S41" t="n">
         <v>0</v>
@@ -8830,22 +8830,22 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Sukhothai</t>
+          <t>Shenzhen Juniors</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Muang Thong United</t>
+          <t>Hebei Kungfu</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -8878,13 +8878,13 @@
         </is>
       </c>
       <c r="P43" t="n">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>3.61</v>
+        <v>0</v>
       </c>
       <c r="R43" t="n">
-        <v>2.77</v>
+        <v>0</v>
       </c>
       <c r="S43" t="n">
         <v>0</v>
@@ -9027,7 +9027,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Shenyang Urban</t>
+          <t>Altay</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Yunnan Yukun</t>
+          <t>Ordabasy</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9815,22 +9815,22 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Dongguan United</t>
+          <t>Kerala Blasters</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Suzhou Dongwu</t>
+          <t>Mohammedan</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -9863,13 +9863,13 @@
         </is>
       </c>
       <c r="P48" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="Q48" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="R48" t="n">
-        <v>0</v>
+        <v>7.37</v>
       </c>
       <c r="S48" t="n">
         <v>0</v>
@@ -10012,22 +10012,22 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Singapore S.League</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Nõmme Kalju</t>
+          <t>Home United</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Tallinna FC Flora</t>
+          <t>Albirex Niigata S</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10060,13 +10060,13 @@
         </is>
       </c>
       <c r="P49" t="n">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="Q49" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="R49" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="S49" t="n">
         <v>0</v>
@@ -10209,22 +10209,22 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Singapore S.League</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Preußen Münster</t>
+          <t>Hougang United</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Darmstadt 98</t>
+          <t>Tampines Rovers</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10257,13 +10257,13 @@
         </is>
       </c>
       <c r="P50" t="n">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="Q50" t="n">
-        <v>3.74</v>
+        <v>0</v>
       </c>
       <c r="R50" t="n">
-        <v>2.76</v>
+        <v>0</v>
       </c>
       <c r="S50" t="n">
         <v>0</v>
@@ -10406,7 +10406,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Nantong Zhiyun</t>
+          <t>Nõmme Kalju</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Wuxi Wugou</t>
+          <t>Tallinna FC Flora</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10454,13 +10454,13 @@
         </is>
       </c>
       <c r="P51" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="Q51" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="R51" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="S51" t="n">
         <v>0</v>
@@ -10603,22 +10603,22 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Singapore S.League</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Hougang United</t>
+          <t>Preußen Münster</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Tampines Rovers</t>
+          <t>Darmstadt 98</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10651,13 +10651,13 @@
         </is>
       </c>
       <c r="P52" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="Q52" t="n">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="R52" t="n">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="S52" t="n">
         <v>0</v>
@@ -10800,7 +10800,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -10810,12 +10810,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Fortuna Düsseldorf</t>
+          <t>Havelse</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Elversberg</t>
+          <t>Schweinfurt</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -10848,13 +10848,13 @@
         </is>
       </c>
       <c r="P53" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="Q53" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="R53" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="S53" t="n">
         <v>0</v>
@@ -10997,22 +10997,22 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>KAA Gent</t>
+          <t>Dongguan United</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>RSC Anderlecht</t>
+          <t>Suzhou Dongwu</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11045,13 +11045,13 @@
         </is>
       </c>
       <c r="P54" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="Q54" t="n">
-        <v>3.71</v>
+        <v>0</v>
       </c>
       <c r="R54" t="n">
-        <v>2.89</v>
+        <v>0</v>
       </c>
       <c r="S54" t="n">
         <v>0</v>
@@ -11194,7 +11194,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -11204,12 +11204,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Kerala Blasters</t>
+          <t>Hertha BSC</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Mohammedan</t>
+          <t>Greuther Fürth</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11242,13 +11242,13 @@
         </is>
       </c>
       <c r="P55" t="n">
-        <v>1.34</v>
+        <v>1.78</v>
       </c>
       <c r="Q55" t="n">
-        <v>4.6</v>
+        <v>4.15</v>
       </c>
       <c r="R55" t="n">
-        <v>7.37</v>
+        <v>3.8</v>
       </c>
       <c r="S55" t="n">
         <v>0</v>
@@ -11293,10 +11293,10 @@
         <v>0</v>
       </c>
       <c r="AG55" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AH55" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AI55" t="n">
         <v>0</v>
@@ -11391,7 +11391,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -11401,12 +11401,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Havelse</t>
+          <t>Fortuna Düsseldorf</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Schweinfurt</t>
+          <t>Elversberg</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11439,13 +11439,13 @@
         </is>
       </c>
       <c r="P56" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="Q56" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="R56" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="S56" t="n">
         <v>0</v>
@@ -11588,22 +11588,22 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Hertha BSC</t>
+          <t>Nantong Zhiyun</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Greuther Fürth</t>
+          <t>Wuxi Wugou</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11636,13 +11636,13 @@
         </is>
       </c>
       <c r="P57" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="Q57" t="n">
-        <v>4.15</v>
+        <v>0</v>
       </c>
       <c r="R57" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="S57" t="n">
         <v>0</v>
@@ -11687,10 +11687,10 @@
         <v>0</v>
       </c>
       <c r="AG57" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AH57" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AI57" t="n">
         <v>0</v>
@@ -11785,22 +11785,22 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Singapore S.League</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Home United</t>
+          <t>KAA Gent</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Albirex Niigata S</t>
+          <t>RSC Anderlecht</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -11833,13 +11833,13 @@
         </is>
       </c>
       <c r="P58" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="Q58" t="n">
-        <v>0</v>
+        <v>3.71</v>
       </c>
       <c r="R58" t="n">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="S58" t="n">
         <v>0</v>
@@ -11992,12 +11992,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Zhejiang FC</t>
+          <t>Beijing Guoan</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Tianjin Teda</t>
+          <t>Shanghai SIPG</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -12189,12 +12189,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Beijing Guoan</t>
+          <t>Zhejiang FC</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Shanghai SIPG</t>
+          <t>Tianjin Teda</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -12583,12 +12583,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Nordsjælland</t>
+          <t>Vejle</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Midtjylland</t>
+          <t>Fredericia</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12621,13 +12621,13 @@
         </is>
       </c>
       <c r="P62" t="n">
-        <v>3.36</v>
+        <v>2.58</v>
       </c>
       <c r="Q62" t="n">
-        <v>3.65</v>
+        <v>3.62</v>
       </c>
       <c r="R62" t="n">
-        <v>1.99</v>
+        <v>2.45</v>
       </c>
       <c r="S62" t="n">
         <v>0</v>
@@ -12770,22 +12770,22 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Qingdao Jonoon</t>
+          <t>FC Andorra</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Dalian Zhixing</t>
+          <t>UD Las Palmas</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -12818,13 +12818,13 @@
         </is>
       </c>
       <c r="P63" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="Q63" t="n">
-        <v>0</v>
+        <v>3.43</v>
       </c>
       <c r="R63" t="n">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="S63" t="n">
         <v>0</v>
@@ -12967,7 +12967,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -12977,12 +12977,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Aktobe</t>
+          <t>Kalmar</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Kaisar</t>
+          <t>Halmstad</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -13015,13 +13015,13 @@
         </is>
       </c>
       <c r="P64" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="Q64" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R64" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="S64" t="n">
         <v>0</v>
@@ -13164,7 +13164,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -13174,12 +13174,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Vejle</t>
+          <t>Bahardar</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Fredericia</t>
+          <t>Welwalo Adigrat Uni</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -13212,13 +13212,13 @@
         </is>
       </c>
       <c r="P65" t="n">
-        <v>2.58</v>
+        <v>0</v>
       </c>
       <c r="Q65" t="n">
-        <v>3.62</v>
+        <v>0</v>
       </c>
       <c r="R65" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="S65" t="n">
         <v>0</v>
@@ -13361,7 +13361,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -13371,12 +13371,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Bahardar</t>
+          <t>RCD Mallorca</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Welwalo Adigrat Uni</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -13558,22 +13558,22 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AIK</t>
+          <t>Zenit</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Djurgården</t>
+          <t>FK Sochi</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -13606,13 +13606,13 @@
         </is>
       </c>
       <c r="P67" t="n">
-        <v>2.35</v>
+        <v>1.21</v>
       </c>
       <c r="Q67" t="n">
-        <v>3.35</v>
+        <v>7.41</v>
       </c>
       <c r="R67" t="n">
-        <v>2.87</v>
+        <v>17.5</v>
       </c>
       <c r="S67" t="n">
         <v>0</v>
@@ -13755,22 +13755,22 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>RCD Mallorca</t>
+          <t>Aktobe</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>Kaisar</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -13952,22 +13952,22 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Meshakhte</t>
+          <t>Nordsjælland</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Dila</t>
+          <t>Midtjylland</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -14000,13 +14000,13 @@
         </is>
       </c>
       <c r="P69" t="n">
-        <v>0</v>
+        <v>3.36</v>
       </c>
       <c r="Q69" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="R69" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="S69" t="n">
         <v>0</v>
@@ -14149,22 +14149,22 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Zenit</t>
+          <t>AIK</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>FK Sochi</t>
+          <t>Djurgården</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -14197,13 +14197,13 @@
         </is>
       </c>
       <c r="P70" t="n">
-        <v>1.21</v>
+        <v>2.35</v>
       </c>
       <c r="Q70" t="n">
-        <v>7.41</v>
+        <v>3.35</v>
       </c>
       <c r="R70" t="n">
-        <v>17.5</v>
+        <v>2.87</v>
       </c>
       <c r="S70" t="n">
         <v>0</v>
@@ -14346,22 +14346,22 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Lugano</t>
+          <t>Meshakhte</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>St. Gallen</t>
+          <t>Dila</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -14394,13 +14394,13 @@
         </is>
       </c>
       <c r="P71" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="Q71" t="n">
-        <v>3.54</v>
+        <v>0</v>
       </c>
       <c r="R71" t="n">
-        <v>2.73</v>
+        <v>0</v>
       </c>
       <c r="S71" t="n">
         <v>0</v>
@@ -14543,22 +14543,22 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Kalmar</t>
+          <t>Lugano</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Halmstad</t>
+          <t>St. Gallen</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -14591,13 +14591,13 @@
         </is>
       </c>
       <c r="P72" t="n">
-        <v>1.92</v>
+        <v>2.36</v>
       </c>
       <c r="Q72" t="n">
-        <v>3.4</v>
+        <v>3.54</v>
       </c>
       <c r="R72" t="n">
-        <v>3.9</v>
+        <v>2.73</v>
       </c>
       <c r="S72" t="n">
         <v>0</v>
@@ -14740,22 +14740,22 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>FC Andorra</t>
+          <t>Qingdao Jonoon</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>UD Las Palmas</t>
+          <t>Dalian Zhixing</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -14788,13 +14788,13 @@
         </is>
       </c>
       <c r="P73" t="n">
-        <v>2.46</v>
+        <v>0</v>
       </c>
       <c r="Q73" t="n">
-        <v>3.43</v>
+        <v>0</v>
       </c>
       <c r="R73" t="n">
-        <v>2.91</v>
+        <v>0</v>
       </c>
       <c r="S73" t="n">
         <v>0</v>
@@ -15134,7 +15134,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -15144,12 +15144,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Kuala Lumpur</t>
+          <t>Công An Nhân Dân</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Negeri Sembilan</t>
+          <t>Nam Dinh</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -15331,7 +15331,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -15341,12 +15341,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Công An Nhân Dân</t>
+          <t>Kuala Lumpur</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Nam Dinh</t>
+          <t>Negeri Sembilan</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -15528,22 +15528,22 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Rosenborg</t>
+          <t>Tychy 71</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Lillestrøm</t>
+          <t>Ruch Chorzów</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -15576,13 +15576,13 @@
         </is>
       </c>
       <c r="P77" t="n">
-        <v>2.79</v>
+        <v>4</v>
       </c>
       <c r="Q77" t="n">
-        <v>3.67</v>
+        <v>3.6</v>
       </c>
       <c r="R77" t="n">
-        <v>2.41</v>
+        <v>1.83</v>
       </c>
       <c r="S77" t="n">
         <v>0</v>
@@ -15725,7 +15725,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -15735,12 +15735,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Tychy 71</t>
+          <t>Baník Ostrava U21</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Ruch Chorzów</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -15773,13 +15773,13 @@
         </is>
       </c>
       <c r="P78" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="Q78" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R78" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="S78" t="n">
         <v>0</v>
@@ -15922,22 +15922,22 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Baník Ostrava U21</t>
+          <t>Rosenborg</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Ústí nad Labem</t>
+          <t>Lillestrøm</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -15970,13 +15970,13 @@
         </is>
       </c>
       <c r="P79" t="n">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="Q79" t="n">
-        <v>0</v>
+        <v>3.67</v>
       </c>
       <c r="R79" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="S79" t="n">
         <v>0</v>
@@ -16316,7 +16316,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -16326,12 +16326,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Sigma Olomouc</t>
+          <t>Nottingham Forest</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Bohemians 1905</t>
+          <t>Newcastle United</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -16364,13 +16364,13 @@
         </is>
       </c>
       <c r="P81" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="Q81" t="n">
-        <v>0</v>
+        <v>3.66</v>
       </c>
       <c r="R81" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="S81" t="n">
         <v>0</v>
@@ -16409,10 +16409,10 @@
         <v>0</v>
       </c>
       <c r="AE81" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AF81" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AG81" t="n">
         <v>0</v>
@@ -16907,7 +16907,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -16917,12 +16917,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Turan</t>
+          <t>Botoşani</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Karvan FK</t>
+          <t>Petrolul 52</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -16955,13 +16955,13 @@
         </is>
       </c>
       <c r="P84" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="Q84" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="R84" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="S84" t="n">
         <v>0</v>
@@ -17104,7 +17104,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -17114,12 +17114,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Arba Minch Kenema</t>
+          <t>Turan</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Welayta Dicha</t>
+          <t>Karvan FK</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -17301,22 +17301,22 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Uppsala W</t>
+          <t>Burnley</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Vittsjö</t>
+          <t>Aston Villa</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -17349,13 +17349,13 @@
         </is>
       </c>
       <c r="P86" t="n">
-        <v>0</v>
+        <v>5.38</v>
       </c>
       <c r="Q86" t="n">
-        <v>0</v>
+        <v>4.37</v>
       </c>
       <c r="R86" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="S86" t="n">
         <v>0</v>
@@ -17498,7 +17498,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -17508,12 +17508,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Kelantan United</t>
+          <t>Crystal Palace</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Johor Darul Ta'zim</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -17546,13 +17546,13 @@
         </is>
       </c>
       <c r="P87" t="n">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="Q87" t="n">
-        <v>0</v>
+        <v>3.31</v>
       </c>
       <c r="R87" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="S87" t="n">
         <v>0</v>
@@ -17591,10 +17591,10 @@
         <v>0</v>
       </c>
       <c r="AE87" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AF87" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AG87" t="n">
         <v>0</v>
@@ -17695,7 +17695,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -17705,12 +17705,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Pardubice</t>
+          <t>NK Primorje</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Karviná</t>
+          <t>Mura</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -17743,13 +17743,13 @@
         </is>
       </c>
       <c r="P88" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="Q88" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="R88" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S88" t="n">
         <v>0</v>
@@ -17892,7 +17892,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -17902,12 +17902,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Burnley</t>
+          <t>Pardubice</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Aston Villa</t>
+          <t>Karviná</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -17940,13 +17940,13 @@
         </is>
       </c>
       <c r="P89" t="n">
-        <v>5.38</v>
+        <v>0</v>
       </c>
       <c r="Q89" t="n">
-        <v>4.37</v>
+        <v>0</v>
       </c>
       <c r="R89" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="S89" t="n">
         <v>0</v>
@@ -18089,7 +18089,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -18099,12 +18099,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Nottingham Forest</t>
+          <t>Arba Minch Kenema</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Newcastle United</t>
+          <t>Welayta Dicha</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -18137,13 +18137,13 @@
         </is>
       </c>
       <c r="P90" t="n">
-        <v>2.46</v>
+        <v>0</v>
       </c>
       <c r="Q90" t="n">
-        <v>3.66</v>
+        <v>0</v>
       </c>
       <c r="R90" t="n">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="S90" t="n">
         <v>0</v>
@@ -18182,10 +18182,10 @@
         <v>0</v>
       </c>
       <c r="AE90" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AF90" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AG90" t="n">
         <v>0</v>
@@ -18286,22 +18286,22 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>NK Primorje</t>
+          <t>Uppsala W</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Mura</t>
+          <t>Vittsjö</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -18334,13 +18334,13 @@
         </is>
       </c>
       <c r="P91" t="n">
-        <v>2.59</v>
+        <v>0</v>
       </c>
       <c r="Q91" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="R91" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="S91" t="n">
         <v>0</v>
@@ -18483,7 +18483,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -18493,12 +18493,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Crystal Palace</t>
+          <t>Sigma Olomouc</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Bohemians 1905</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -18531,13 +18531,13 @@
         </is>
       </c>
       <c r="P92" t="n">
-        <v>2.69</v>
+        <v>0</v>
       </c>
       <c r="Q92" t="n">
-        <v>3.31</v>
+        <v>0</v>
       </c>
       <c r="R92" t="n">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="S92" t="n">
         <v>0</v>
@@ -18576,10 +18576,10 @@
         <v>0</v>
       </c>
       <c r="AE92" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AF92" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AG92" t="n">
         <v>0</v>
@@ -18680,22 +18680,22 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Botoşani</t>
+          <t>Astana</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Petrolul 52</t>
+          <t>Kyzyl-Zhar</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -18728,13 +18728,13 @@
         </is>
       </c>
       <c r="P93" t="n">
-        <v>2.21</v>
+        <v>1.8</v>
       </c>
       <c r="Q93" t="n">
-        <v>3.22</v>
+        <v>3.76</v>
       </c>
       <c r="R93" t="n">
-        <v>3.22</v>
+        <v>4.15</v>
       </c>
       <c r="S93" t="n">
         <v>0</v>
@@ -18877,22 +18877,22 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Astana</t>
+          <t>Kelantan United</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Kyzyl-Zhar</t>
+          <t>Johor Darul Ta'zim</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -18925,13 +18925,13 @@
         </is>
       </c>
       <c r="P94" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Q94" t="n">
-        <v>3.76</v>
+        <v>0</v>
       </c>
       <c r="R94" t="n">
-        <v>4.15</v>
+        <v>0</v>
       </c>
       <c r="S94" t="n">
         <v>0</v>
@@ -19468,7 +19468,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -19478,12 +19478,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Honvéd W</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Vasas</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -19516,13 +19516,13 @@
         </is>
       </c>
       <c r="P97" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="Q97" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R97" t="n">
-        <v>0</v>
+        <v>3.21</v>
       </c>
       <c r="S97" t="n">
         <v>0</v>
@@ -19561,10 +19561,10 @@
         <v>0</v>
       </c>
       <c r="AE97" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AF97" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AG97" t="n">
         <v>0</v>
@@ -19665,7 +19665,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -19675,12 +19675,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>NorthEast United</t>
+          <t>Osijek</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Chennaiyin</t>
+          <t>Istra 1961</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -19862,7 +19862,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -19872,12 +19872,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Osijek</t>
+          <t>Aris</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Istra 1961</t>
+          <t>OFI</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -20059,22 +20059,22 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Aris</t>
+          <t>Banga</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>OFI</t>
+          <t>TransINVEST Vilnius</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -20256,7 +20256,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -20266,12 +20266,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Volos NFC</t>
+          <t>NorthEast United</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Levadiakos</t>
+          <t>Chennaiyin</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -20304,13 +20304,13 @@
         </is>
       </c>
       <c r="P101" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="Q101" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="R101" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="S101" t="n">
         <v>0</v>
@@ -20453,22 +20453,22 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Nõmme United</t>
+          <t>Silkeborg</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Paide</t>
+          <t>København</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -20501,13 +20501,13 @@
         </is>
       </c>
       <c r="P102" t="n">
-        <v>3.58</v>
+        <v>4.68</v>
       </c>
       <c r="Q102" t="n">
-        <v>3.88</v>
+        <v>4</v>
       </c>
       <c r="R102" t="n">
-        <v>1.78</v>
+        <v>1.63</v>
       </c>
       <c r="S102" t="n">
         <v>0</v>
@@ -20650,22 +20650,22 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>B36</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>KÍ</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -20698,13 +20698,13 @@
         </is>
       </c>
       <c r="P103" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="Q103" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="R103" t="n">
-        <v>3.21</v>
+        <v>0</v>
       </c>
       <c r="S103" t="n">
         <v>0</v>
@@ -20743,10 +20743,10 @@
         <v>0</v>
       </c>
       <c r="AE103" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AF103" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AG103" t="n">
         <v>0</v>
@@ -21044,7 +21044,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -21054,12 +21054,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Silkeborg</t>
+          <t>Royal Antwerp FC</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>Sporting Charleroi</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -21092,13 +21092,13 @@
         </is>
       </c>
       <c r="P105" t="n">
-        <v>4.68</v>
+        <v>2.38</v>
       </c>
       <c r="Q105" t="n">
-        <v>4</v>
+        <v>3.24</v>
       </c>
       <c r="R105" t="n">
-        <v>1.63</v>
+        <v>3.14</v>
       </c>
       <c r="S105" t="n">
         <v>0</v>
@@ -21137,10 +21137,10 @@
         <v>0</v>
       </c>
       <c r="AE105" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AF105" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG105" t="n">
         <v>0</v>
@@ -21241,22 +21241,22 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Banga</t>
+          <t>Honvéd W</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>TransINVEST Vilnius</t>
+          <t>Vasas</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -21438,22 +21438,22 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Royal Antwerp FC</t>
+          <t>Nõmme United</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Sporting Charleroi</t>
+          <t>Paide</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -21486,13 +21486,13 @@
         </is>
       </c>
       <c r="P107" t="n">
-        <v>2.38</v>
+        <v>3.58</v>
       </c>
       <c r="Q107" t="n">
-        <v>3.24</v>
+        <v>3.88</v>
       </c>
       <c r="R107" t="n">
-        <v>3.14</v>
+        <v>1.78</v>
       </c>
       <c r="S107" t="n">
         <v>0</v>
@@ -21531,10 +21531,10 @@
         <v>0</v>
       </c>
       <c r="AE107" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AF107" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AG107" t="n">
         <v>0</v>
@@ -21635,22 +21635,22 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>B36</t>
+          <t>Volos NFC</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>KÍ</t>
+          <t>Levadiakos</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -21683,13 +21683,13 @@
         </is>
       </c>
       <c r="P108" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="Q108" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R108" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="S108" t="n">
         <v>0</v>
@@ -21832,7 +21832,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -21842,12 +21842,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Akhmat Grozny</t>
+          <t>Leganés</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Makhachkala</t>
+          <t>Racing Santander</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -21880,13 +21880,13 @@
         </is>
       </c>
       <c r="P109" t="n">
-        <v>2.16</v>
+        <v>3.06</v>
       </c>
       <c r="Q109" t="n">
-        <v>3.42</v>
+        <v>3.61</v>
       </c>
       <c r="R109" t="n">
-        <v>3.85</v>
+        <v>2.29</v>
       </c>
       <c r="S109" t="n">
         <v>0</v>
@@ -22029,7 +22029,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -22039,12 +22039,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Leganés</t>
+          <t>Athletic Club Bilbao</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Racing Santander</t>
+          <t>Valencia CF</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -22077,13 +22077,13 @@
         </is>
       </c>
       <c r="P110" t="n">
-        <v>3.06</v>
+        <v>0</v>
       </c>
       <c r="Q110" t="n">
-        <v>3.61</v>
+        <v>0</v>
       </c>
       <c r="R110" t="n">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="S110" t="n">
         <v>0</v>
@@ -22226,7 +22226,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -22236,12 +22236,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Athletic Club Bilbao</t>
+          <t>Akhmat Grozny</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Valencia CF</t>
+          <t>Makhachkala</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -22274,13 +22274,13 @@
         </is>
       </c>
       <c r="P111" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="Q111" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="R111" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="S111" t="n">
         <v>0</v>
@@ -22423,22 +22423,22 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Neftekhimik</t>
+          <t>Häcken</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Volga Ulyanovsk</t>
+          <t>Malmö FF</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -22471,13 +22471,13 @@
         </is>
       </c>
       <c r="P112" t="n">
-        <v>2.09</v>
+        <v>2.27</v>
       </c>
       <c r="Q112" t="n">
-        <v>3.17</v>
+        <v>3.58</v>
       </c>
       <c r="R112" t="n">
-        <v>3.6</v>
+        <v>2.88</v>
       </c>
       <c r="S112" t="n">
         <v>0</v>
@@ -22620,22 +22620,22 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Häcken</t>
+          <t>Sion</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Malmö FF</t>
+          <t>Thun</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -22668,13 +22668,13 @@
         </is>
       </c>
       <c r="P113" t="n">
-        <v>2.27</v>
+        <v>2.05</v>
       </c>
       <c r="Q113" t="n">
-        <v>3.58</v>
+        <v>3.64</v>
       </c>
       <c r="R113" t="n">
-        <v>2.88</v>
+        <v>3.28</v>
       </c>
       <c r="S113" t="n">
         <v>0</v>
@@ -22817,7 +22817,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -22827,12 +22827,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Sion</t>
+          <t>Neftekhimik</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Thun</t>
+          <t>Volga Ulyanovsk</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -22865,13 +22865,13 @@
         </is>
       </c>
       <c r="P114" t="n">
-        <v>2.05</v>
+        <v>2.09</v>
       </c>
       <c r="Q114" t="n">
-        <v>3.64</v>
+        <v>3.17</v>
       </c>
       <c r="R114" t="n">
-        <v>3.28</v>
+        <v>3.6</v>
       </c>
       <c r="S114" t="n">
         <v>0</v>
@@ -23615,12 +23615,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Fortuna Sittard</t>
+          <t>Telstar</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>PEC Zwolle</t>
+          <t>Heracles</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -23653,13 +23653,13 @@
         </is>
       </c>
       <c r="P118" t="n">
-        <v>1.96</v>
+        <v>1.48</v>
       </c>
       <c r="Q118" t="n">
-        <v>4.05</v>
+        <v>4.94</v>
       </c>
       <c r="R118" t="n">
-        <v>3.5</v>
+        <v>6.07</v>
       </c>
       <c r="S118" t="n">
         <v>0</v>
@@ -23704,10 +23704,10 @@
         <v>0</v>
       </c>
       <c r="AG118" t="n">
-        <v>2.2</v>
+        <v>1.98</v>
       </c>
       <c r="AH118" t="n">
-        <v>1.58</v>
+        <v>1.72</v>
       </c>
       <c r="AI118" t="n">
         <v>0</v>
@@ -23812,12 +23812,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Feyenoord</t>
+          <t>Go Ahead Eagles</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>AZ</t>
+          <t>PSV</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -23850,13 +23850,13 @@
         </is>
       </c>
       <c r="P119" t="n">
-        <v>1.78</v>
+        <v>4.48</v>
       </c>
       <c r="Q119" t="n">
-        <v>4.17</v>
+        <v>4.74</v>
       </c>
       <c r="R119" t="n">
-        <v>4.17</v>
+        <v>1.65</v>
       </c>
       <c r="S119" t="n">
         <v>0</v>
@@ -23901,10 +23901,10 @@
         <v>0</v>
       </c>
       <c r="AG119" t="n">
-        <v>1.9</v>
+        <v>1.68</v>
       </c>
       <c r="AH119" t="n">
-        <v>1.77</v>
+        <v>2.05</v>
       </c>
       <c r="AI119" t="n">
         <v>0</v>
@@ -24009,12 +24009,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>NAC Breda</t>
+          <t>Groningen</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Heerenveen</t>
+          <t>NEC</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -24047,13 +24047,13 @@
         </is>
       </c>
       <c r="P120" t="n">
-        <v>2.49</v>
+        <v>2.78</v>
       </c>
       <c r="Q120" t="n">
-        <v>3.77</v>
+        <v>3.89</v>
       </c>
       <c r="R120" t="n">
-        <v>2.67</v>
+        <v>2.36</v>
       </c>
       <c r="S120" t="n">
         <v>0</v>
@@ -24092,16 +24092,16 @@
         <v>0</v>
       </c>
       <c r="AE120" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AF120" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AG120" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AH120" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AI120" t="n">
         <v>0</v>
@@ -24206,12 +24206,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Go Ahead Eagles</t>
+          <t>Ajax</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>PSV</t>
+          <t>Utrecht</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -24244,61 +24244,61 @@
         </is>
       </c>
       <c r="P121" t="n">
-        <v>4.48</v>
+        <v>1.71</v>
       </c>
       <c r="Q121" t="n">
-        <v>4.74</v>
+        <v>4.37</v>
       </c>
       <c r="R121" t="n">
+        <v>4.42</v>
+      </c>
+      <c r="S121" t="n">
+        <v>0</v>
+      </c>
+      <c r="T121" t="n">
+        <v>0</v>
+      </c>
+      <c r="U121" t="n">
+        <v>0</v>
+      </c>
+      <c r="V121" t="n">
+        <v>0</v>
+      </c>
+      <c r="W121" t="n">
+        <v>0</v>
+      </c>
+      <c r="X121" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y121" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z121" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA121" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB121" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC121" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD121" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE121" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF121" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG121" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AH121" t="n">
         <v>1.65</v>
-      </c>
-      <c r="S121" t="n">
-        <v>0</v>
-      </c>
-      <c r="T121" t="n">
-        <v>0</v>
-      </c>
-      <c r="U121" t="n">
-        <v>0</v>
-      </c>
-      <c r="V121" t="n">
-        <v>0</v>
-      </c>
-      <c r="W121" t="n">
-        <v>0</v>
-      </c>
-      <c r="X121" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y121" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z121" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA121" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB121" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC121" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD121" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE121" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF121" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG121" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AH121" t="n">
-        <v>2.05</v>
       </c>
       <c r="AI121" t="n">
         <v>0</v>
@@ -24403,12 +24403,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Telstar</t>
+          <t>Fortuna Sittard</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Heracles</t>
+          <t>PEC Zwolle</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -24441,13 +24441,13 @@
         </is>
       </c>
       <c r="P122" t="n">
-        <v>1.48</v>
+        <v>1.96</v>
       </c>
       <c r="Q122" t="n">
-        <v>4.94</v>
+        <v>4.05</v>
       </c>
       <c r="R122" t="n">
-        <v>6.07</v>
+        <v>3.5</v>
       </c>
       <c r="S122" t="n">
         <v>0</v>
@@ -24492,10 +24492,10 @@
         <v>0</v>
       </c>
       <c r="AG122" t="n">
-        <v>1.98</v>
+        <v>2.2</v>
       </c>
       <c r="AH122" t="n">
-        <v>1.72</v>
+        <v>1.58</v>
       </c>
       <c r="AI122" t="n">
         <v>0</v>
@@ -24600,12 +24600,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Groningen</t>
+          <t>Excelsior</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>NEC</t>
+          <t>Volendam</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -24638,13 +24638,13 @@
         </is>
       </c>
       <c r="P123" t="n">
-        <v>2.78</v>
+        <v>1.77</v>
       </c>
       <c r="Q123" t="n">
-        <v>3.89</v>
+        <v>4.17</v>
       </c>
       <c r="R123" t="n">
-        <v>2.36</v>
+        <v>4.22</v>
       </c>
       <c r="S123" t="n">
         <v>0</v>
@@ -24683,16 +24683,16 @@
         <v>0</v>
       </c>
       <c r="AE123" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AF123" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AG123" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AH123" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AI123" t="n">
         <v>0</v>
@@ -24797,12 +24797,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Excelsior</t>
+          <t>NAC Breda</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Volendam</t>
+          <t>Heerenveen</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -24835,13 +24835,13 @@
         </is>
       </c>
       <c r="P124" t="n">
-        <v>1.77</v>
+        <v>2.49</v>
       </c>
       <c r="Q124" t="n">
-        <v>4.17</v>
+        <v>3.77</v>
       </c>
       <c r="R124" t="n">
-        <v>4.22</v>
+        <v>2.67</v>
       </c>
       <c r="S124" t="n">
         <v>0</v>
@@ -24880,7 +24880,7 @@
         <v>0</v>
       </c>
       <c r="AE124" t="n">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="AF124" t="n">
         <v>2.3</v>
@@ -24994,12 +24994,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Ajax</t>
+          <t>Feyenoord</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Utrecht</t>
+          <t>AZ</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -25032,13 +25032,13 @@
         </is>
       </c>
       <c r="P125" t="n">
-        <v>1.71</v>
+        <v>1.78</v>
       </c>
       <c r="Q125" t="n">
-        <v>4.37</v>
+        <v>4.17</v>
       </c>
       <c r="R125" t="n">
-        <v>4.42</v>
+        <v>4.17</v>
       </c>
       <c r="S125" t="n">
         <v>0</v>
@@ -25083,10 +25083,10 @@
         <v>0</v>
       </c>
       <c r="AG125" t="n">
-        <v>2.1</v>
+        <v>1.9</v>
       </c>
       <c r="AH125" t="n">
-        <v>1.65</v>
+        <v>1.77</v>
       </c>
       <c r="AI125" t="n">
         <v>0</v>
@@ -25181,22 +25181,22 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Paphos</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Aris</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -25229,13 +25229,13 @@
         </is>
       </c>
       <c r="P126" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="Q126" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R126" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="S126" t="n">
         <v>0</v>
@@ -25378,7 +25378,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -25388,12 +25388,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Karcag SE</t>
+          <t>Mebrat Hayl</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Tiszakécske</t>
+          <t>Fasil Ketema</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -25575,7 +25575,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -25585,12 +25585,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Real Madrid W</t>
+          <t>Pogoń Siedlce</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Atletico Madrid W</t>
+          <t>Stal Rzeszów</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -25623,13 +25623,13 @@
         </is>
       </c>
       <c r="P128" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="Q128" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R128" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="S128" t="n">
         <v>0</v>
@@ -25772,7 +25772,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -25782,12 +25782,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Akademija Pandev</t>
+          <t>Ajka</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Rabotnički</t>
+          <t>Szeged 2011</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -25969,7 +25969,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -25979,12 +25979,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Shkendija</t>
+          <t>Rapid Wien</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Struga</t>
+          <t>Austria Wien</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -26017,13 +26017,13 @@
         </is>
       </c>
       <c r="P130" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Q130" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="R130" t="n">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="S130" t="n">
         <v>0</v>
@@ -26166,22 +26166,22 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Ajka</t>
+          <t>Tromsø</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Szeged 2011</t>
+          <t>Molde</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -26214,13 +26214,13 @@
         </is>
       </c>
       <c r="P131" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="Q131" t="n">
-        <v>0</v>
+        <v>3.82</v>
       </c>
       <c r="R131" t="n">
-        <v>0</v>
+        <v>4.13</v>
       </c>
       <c r="S131" t="n">
         <v>0</v>
@@ -26363,22 +26363,22 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Åsane</t>
+          <t>Hartberg</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Strømsgodset</t>
+          <t>Sturm Graz</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -26411,13 +26411,13 @@
         </is>
       </c>
       <c r="P132" t="n">
-        <v>5.4</v>
+        <v>3.75</v>
       </c>
       <c r="Q132" t="n">
-        <v>4.6</v>
+        <v>3.6</v>
       </c>
       <c r="R132" t="n">
-        <v>1.51</v>
+        <v>1.91</v>
       </c>
       <c r="S132" t="n">
         <v>0</v>
@@ -26456,10 +26456,10 @@
         <v>0</v>
       </c>
       <c r="AE132" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AF132" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG132" t="n">
         <v>0</v>
@@ -26560,7 +26560,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -26570,12 +26570,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Mebrat Hayl</t>
+          <t>LASK Linz</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Fasil Ketema</t>
+          <t>Salzburg</t>
         </is>
       </c>
       <c r="G133" t="n">
@@ -26608,13 +26608,13 @@
         </is>
       </c>
       <c r="P133" t="n">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="Q133" t="n">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="R133" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="S133" t="n">
         <v>0</v>
@@ -26757,22 +26757,22 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Zbrojovka Brno</t>
+          <t>Sandefjord</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Vlašim</t>
+          <t>Kristiansund</t>
         </is>
       </c>
       <c r="G134" t="n">
@@ -26805,13 +26805,13 @@
         </is>
       </c>
       <c r="P134" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="Q134" t="n">
-        <v>0</v>
+        <v>4.44</v>
       </c>
       <c r="R134" t="n">
-        <v>0</v>
+        <v>5.16</v>
       </c>
       <c r="S134" t="n">
         <v>0</v>
@@ -26954,22 +26954,22 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Aresimi</t>
+          <t>KFUM</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>FK Bashkimi Kumanovo</t>
+          <t>Viking</t>
         </is>
       </c>
       <c r="G135" t="n">
@@ -27002,13 +27002,13 @@
         </is>
       </c>
       <c r="P135" t="n">
-        <v>0</v>
+        <v>3.87</v>
       </c>
       <c r="Q135" t="n">
-        <v>0</v>
+        <v>3.87</v>
       </c>
       <c r="R135" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="S135" t="n">
         <v>0</v>
@@ -27151,7 +27151,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -27161,12 +27161,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Pelister</t>
+          <t>Budafoki MTE</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Shkupi</t>
+          <t>BVSC</t>
         </is>
       </c>
       <c r="G136" t="n">
@@ -27348,22 +27348,22 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Strømmen</t>
+          <t>Karcag SE</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Hødd</t>
+          <t>Tiszakécske</t>
         </is>
       </c>
       <c r="G137" t="n">
@@ -27396,13 +27396,13 @@
         </is>
       </c>
       <c r="P137" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Q137" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="R137" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="S137" t="n">
         <v>0</v>
@@ -27545,7 +27545,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -27555,12 +27555,12 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Vardar</t>
+          <t>Kecskeméti TE</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Sileks</t>
+          <t>Mezőkövesd-Zsóry</t>
         </is>
       </c>
       <c r="G138" t="n">
@@ -27742,7 +27742,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -27752,12 +27752,12 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Budafoki MTE</t>
+          <t>Omonia Nicosia</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>BVSC</t>
+          <t>AEK Larnaca</t>
         </is>
       </c>
       <c r="G139" t="n">
@@ -28136,22 +28136,22 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Moss</t>
+          <t>Aresimi</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Bryne</t>
+          <t>FK Bashkimi Kumanovo</t>
         </is>
       </c>
       <c r="G141" t="n">
@@ -28184,13 +28184,13 @@
         </is>
       </c>
       <c r="P141" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Q141" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="R141" t="n">
-        <v>3.01</v>
+        <v>0</v>
       </c>
       <c r="S141" t="n">
         <v>0</v>
@@ -28333,22 +28333,22 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Pogoń Siedlce</t>
+          <t>Sogndal</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Stal Rzeszów</t>
+          <t>Haugesund</t>
         </is>
       </c>
       <c r="G142" t="n">
@@ -28381,13 +28381,13 @@
         </is>
       </c>
       <c r="P142" t="n">
-        <v>2.55</v>
+        <v>3.1</v>
       </c>
       <c r="Q142" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="R142" t="n">
-        <v>2.43</v>
+        <v>2.12</v>
       </c>
       <c r="S142" t="n">
         <v>0</v>
@@ -28530,7 +28530,7 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -28540,12 +28540,12 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Tromsø</t>
+          <t>Åsane</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Molde</t>
+          <t>Strømsgodset</t>
         </is>
       </c>
       <c r="G143" t="n">
@@ -28578,13 +28578,13 @@
         </is>
       </c>
       <c r="P143" t="n">
-        <v>1.84</v>
+        <v>5.4</v>
       </c>
       <c r="Q143" t="n">
-        <v>3.82</v>
+        <v>4.6</v>
       </c>
       <c r="R143" t="n">
-        <v>4.13</v>
+        <v>1.51</v>
       </c>
       <c r="S143" t="n">
         <v>0</v>
@@ -28727,22 +28727,22 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Sandefjord</t>
+          <t>Zbrojovka Brno</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Kristiansund</t>
+          <t>Vlašim</t>
         </is>
       </c>
       <c r="G144" t="n">
@@ -28775,13 +28775,13 @@
         </is>
       </c>
       <c r="P144" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="Q144" t="n">
-        <v>4.44</v>
+        <v>0</v>
       </c>
       <c r="R144" t="n">
-        <v>5.16</v>
+        <v>0</v>
       </c>
       <c r="S144" t="n">
         <v>0</v>
@@ -28924,7 +28924,7 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -28934,12 +28934,12 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>KFUM</t>
+          <t>Sandnes Ulf</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Viking</t>
+          <t>Stabæk</t>
         </is>
       </c>
       <c r="G145" t="n">
@@ -28972,13 +28972,13 @@
         </is>
       </c>
       <c r="P145" t="n">
-        <v>3.87</v>
+        <v>4.07</v>
       </c>
       <c r="Q145" t="n">
-        <v>3.87</v>
+        <v>3.9</v>
       </c>
       <c r="R145" t="n">
-        <v>1.89</v>
+        <v>1.78</v>
       </c>
       <c r="S145" t="n">
         <v>0</v>
@@ -29121,22 +29121,22 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Paphos</t>
+          <t>Saburtalo</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Aris</t>
+          <t>Torpedo Kutaisi</t>
         </is>
       </c>
       <c r="G146" t="n">
@@ -29318,7 +29318,7 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
@@ -29328,12 +29328,12 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Omonia Nicosia</t>
+          <t>Vardar</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>AEK Larnaca</t>
+          <t>Sileks</t>
         </is>
       </c>
       <c r="G147" t="n">
@@ -29515,7 +29515,7 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
@@ -29525,12 +29525,12 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Apollon</t>
+          <t>Shkendija</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>APOEL</t>
+          <t>Struga</t>
         </is>
       </c>
       <c r="G148" t="n">
@@ -29712,7 +29712,7 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
@@ -29722,12 +29722,12 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Croatia Zmijavci</t>
+          <t>Makedonija GjP</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Jarun</t>
+          <t>Tikveš</t>
         </is>
       </c>
       <c r="G149" t="n">
@@ -29919,12 +29919,12 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Makedonija GjP</t>
+          <t>Pelister</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Tikveš</t>
+          <t>Shkupi</t>
         </is>
       </c>
       <c r="G150" t="n">
@@ -30106,7 +30106,7 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
@@ -30116,12 +30116,12 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Saburtalo</t>
+          <t>Moss</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Torpedo Kutaisi</t>
+          <t>Bryne</t>
         </is>
       </c>
       <c r="G151" t="n">
@@ -30154,13 +30154,13 @@
         </is>
       </c>
       <c r="P151" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Q151" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="R151" t="n">
-        <v>0</v>
+        <v>3.01</v>
       </c>
       <c r="S151" t="n">
         <v>0</v>
@@ -30303,7 +30303,7 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
@@ -30313,12 +30313,12 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>LASK Linz</t>
+          <t>Akademija Pandev</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Salzburg</t>
+          <t>Rabotnički</t>
         </is>
       </c>
       <c r="G152" t="n">
@@ -30351,13 +30351,13 @@
         </is>
       </c>
       <c r="P152" t="n">
-        <v>2.51</v>
+        <v>0</v>
       </c>
       <c r="Q152" t="n">
-        <v>3.78</v>
+        <v>0</v>
       </c>
       <c r="R152" t="n">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="S152" t="n">
         <v>0</v>
@@ -30500,7 +30500,7 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
@@ -30510,12 +30510,12 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Kecskeméti TE</t>
+          <t>Real Madrid W</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Mezőkövesd-Zsóry</t>
+          <t>Atletico Madrid W</t>
         </is>
       </c>
       <c r="G153" t="n">
@@ -30697,7 +30697,7 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
@@ -30707,12 +30707,12 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Hartberg</t>
+          <t>Apollon</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Sturm Graz</t>
+          <t>APOEL</t>
         </is>
       </c>
       <c r="G154" t="n">
@@ -30745,13 +30745,13 @@
         </is>
       </c>
       <c r="P154" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="Q154" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R154" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="S154" t="n">
         <v>0</v>
@@ -30790,10 +30790,10 @@
         <v>0</v>
       </c>
       <c r="AE154" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AF154" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AG154" t="n">
         <v>0</v>
@@ -30894,22 +30894,22 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Sogndal</t>
+          <t>Croatia Zmijavci</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Haugesund</t>
+          <t>Jarun</t>
         </is>
       </c>
       <c r="G155" t="n">
@@ -30942,13 +30942,13 @@
         </is>
       </c>
       <c r="P155" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="Q155" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="R155" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="S155" t="n">
         <v>0</v>
@@ -31091,22 +31091,22 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Rapid Wien</t>
+          <t>Strømmen</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Austria Wien</t>
+          <t>Hødd</t>
         </is>
       </c>
       <c r="G156" t="n">
@@ -31139,13 +31139,13 @@
         </is>
       </c>
       <c r="P156" t="n">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="Q156" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="R156" t="n">
-        <v>2.96</v>
+        <v>3.2</v>
       </c>
       <c r="S156" t="n">
         <v>0</v>
@@ -31298,12 +31298,12 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Sandnes Ulf</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Stabæk</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="G157" t="n">
@@ -31336,13 +31336,13 @@
         </is>
       </c>
       <c r="P157" t="n">
-        <v>4.07</v>
+        <v>2.65</v>
       </c>
       <c r="Q157" t="n">
-        <v>3.9</v>
+        <v>3.6</v>
       </c>
       <c r="R157" t="n">
-        <v>1.78</v>
+        <v>2.4</v>
       </c>
       <c r="S157" t="n">
         <v>0</v>
@@ -31889,12 +31889,12 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>Al Ain</t>
+          <t>Al Bataeh</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Al Dhafra</t>
+          <t>Al Sharjah</t>
         </is>
       </c>
       <c r="G160" t="n">
@@ -32086,12 +32086,12 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Al Bataeh</t>
+          <t>Al Ain</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Al Sharjah</t>
+          <t>Al Dhafra</t>
         </is>
       </c>
       <c r="G161" t="n">
@@ -32273,7 +32273,7 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
@@ -32283,12 +32283,12 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>Neftçi</t>
+          <t>Köln</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>İnter Bakı</t>
+          <t>Heidenheim</t>
         </is>
       </c>
       <c r="G162" t="n">
@@ -32321,13 +32321,13 @@
         </is>
       </c>
       <c r="P162" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="Q162" t="n">
-        <v>0</v>
+        <v>4.32</v>
       </c>
       <c r="R162" t="n">
-        <v>0</v>
+        <v>4.52</v>
       </c>
       <c r="S162" t="n">
         <v>0</v>
@@ -32372,10 +32372,10 @@
         <v>0</v>
       </c>
       <c r="AG162" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AH162" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AI162" t="n">
         <v>0</v>
@@ -32470,7 +32470,7 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
@@ -32480,12 +32480,12 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>Köln</t>
+          <t>Nieciecza</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Heidenheim</t>
+          <t>Legia Warszawa</t>
         </is>
       </c>
       <c r="G163" t="n">
@@ -32518,13 +32518,13 @@
         </is>
       </c>
       <c r="P163" t="n">
-        <v>1.78</v>
+        <v>4.09</v>
       </c>
       <c r="Q163" t="n">
-        <v>4.32</v>
+        <v>3.78</v>
       </c>
       <c r="R163" t="n">
-        <v>4.52</v>
+        <v>1.77</v>
       </c>
       <c r="S163" t="n">
         <v>0</v>
@@ -32569,10 +32569,10 @@
         <v>0</v>
       </c>
       <c r="AG163" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AH163" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AI163" t="n">
         <v>0</v>
@@ -32667,7 +32667,7 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
@@ -32677,12 +32677,12 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>West Ham United</t>
+          <t>Sekhukhune United</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Kaizer Chiefs</t>
         </is>
       </c>
       <c r="G164" t="n">
@@ -32715,13 +32715,13 @@
         </is>
       </c>
       <c r="P164" t="n">
-        <v>5.17</v>
+        <v>0</v>
       </c>
       <c r="Q164" t="n">
-        <v>4.37</v>
+        <v>0</v>
       </c>
       <c r="R164" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="S164" t="n">
         <v>0</v>
@@ -32760,10 +32760,10 @@
         <v>0</v>
       </c>
       <c r="AE164" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AF164" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AG164" t="n">
         <v>0</v>
@@ -32864,7 +32864,7 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
@@ -32874,12 +32874,12 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>Nieciecza</t>
+          <t>Neftçi</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Legia Warszawa</t>
+          <t>İnter Bakı</t>
         </is>
       </c>
       <c r="G165" t="n">
@@ -32912,13 +32912,13 @@
         </is>
       </c>
       <c r="P165" t="n">
-        <v>4.09</v>
+        <v>0</v>
       </c>
       <c r="Q165" t="n">
-        <v>3.78</v>
+        <v>0</v>
       </c>
       <c r="R165" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="S165" t="n">
         <v>0</v>
@@ -33061,7 +33061,7 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
@@ -33071,12 +33071,12 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>Sekhukhune United</t>
+          <t>West Ham United</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Kaizer Chiefs</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="G166" t="n">
@@ -33109,13 +33109,13 @@
         </is>
       </c>
       <c r="P166" t="n">
-        <v>0</v>
+        <v>5.17</v>
       </c>
       <c r="Q166" t="n">
-        <v>0</v>
+        <v>4.37</v>
       </c>
       <c r="R166" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="S166" t="n">
         <v>0</v>
@@ -33154,10 +33154,10 @@
         <v>0</v>
       </c>
       <c r="AE166" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AF166" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AG166" t="n">
         <v>0</v>
@@ -33258,7 +33258,7 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
@@ -33268,12 +33268,12 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>Ittihad Tanger</t>
+          <t>Arsenal Tivat</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Difaâ El Jadida</t>
+          <t>Sutjeska</t>
         </is>
       </c>
       <c r="G167" t="n">
@@ -33455,22 +33455,22 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>Arsenal Tivat</t>
+          <t>Panevėžys</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Sutjeska</t>
+          <t>Kauno Žalgiris</t>
         </is>
       </c>
       <c r="G168" t="n">
@@ -33662,12 +33662,12 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>Jedinstvo</t>
+          <t>Dečić</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Budućnost</t>
+          <t>FK Jezero Plav</t>
         </is>
       </c>
       <c r="G169" t="n">
@@ -33849,7 +33849,7 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
@@ -33859,12 +33859,12 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>Brøndby</t>
+          <t>Dinamo Bucureşti</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>AGF</t>
+          <t>Argeș</t>
         </is>
       </c>
       <c r="G170" t="n">
@@ -33897,13 +33897,13 @@
         </is>
       </c>
       <c r="P170" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="Q170" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R170" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="S170" t="n">
         <v>0</v>
@@ -34046,22 +34046,22 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>Panevėžys</t>
+          <t>Mornar</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Kauno Žalgiris</t>
+          <t>Bokelj</t>
         </is>
       </c>
       <c r="G171" t="n">
@@ -34253,12 +34253,12 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>Dečić</t>
+          <t>Jedinstvo</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>FK Jezero Plav</t>
+          <t>Budućnost</t>
         </is>
       </c>
       <c r="G172" t="n">
@@ -34440,7 +34440,7 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
@@ -34450,12 +34450,12 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>Vysočina Jihlava</t>
+          <t>Mladost DG</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Hanácká</t>
+          <t>Petrovac</t>
         </is>
       </c>
       <c r="G173" t="n">
@@ -34637,7 +34637,7 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
@@ -34647,12 +34647,12 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>Mornar</t>
+          <t>Vysočina Jihlava</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Bokelj</t>
+          <t>Hanácká</t>
         </is>
       </c>
       <c r="G174" t="n">
@@ -34834,7 +34834,7 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
@@ -34844,12 +34844,12 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>Parma</t>
+          <t>Ittihad Tanger</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Roma</t>
+          <t>Difaâ El Jadida</t>
         </is>
       </c>
       <c r="G175" t="n">
@@ -34882,13 +34882,13 @@
         </is>
       </c>
       <c r="P175" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="Q175" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="R175" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="S175" t="n">
         <v>0</v>
@@ -35031,7 +35031,7 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
@@ -35041,12 +35041,12 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>Dinamo Bucureşti</t>
+          <t>Brøndby</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Argeș</t>
+          <t>AGF</t>
         </is>
       </c>
       <c r="G176" t="n">
@@ -35079,13 +35079,13 @@
         </is>
       </c>
       <c r="P176" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="Q176" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="R176" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="S176" t="n">
         <v>0</v>
@@ -35228,7 +35228,7 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
@@ -35238,12 +35238,12 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>Mladost DG</t>
+          <t>Parma</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Petrovac</t>
+          <t>Roma</t>
         </is>
       </c>
       <c r="G177" t="n">
@@ -35276,13 +35276,13 @@
         </is>
       </c>
       <c r="P177" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="Q177" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R177" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="S177" t="n">
         <v>0</v>
@@ -35622,7 +35622,7 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
@@ -35632,12 +35632,12 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>Slaven Koprivnica</t>
+          <t>Dobrudzha 1919</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Gorica</t>
+          <t>Beroe</t>
         </is>
       </c>
       <c r="G179" t="n">
@@ -35670,13 +35670,13 @@
         </is>
       </c>
       <c r="P179" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="Q179" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R179" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="S179" t="n">
         <v>0</v>
@@ -35829,12 +35829,12 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>Skála</t>
+          <t>07 Vestur</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>AB</t>
+          <t>B68</t>
         </is>
       </c>
       <c r="G180" t="n">
@@ -36026,12 +36026,12 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>07 Vestur</t>
+          <t>Skála</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>B68</t>
+          <t>AB</t>
         </is>
       </c>
       <c r="G181" t="n">
@@ -36213,7 +36213,7 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
@@ -36223,12 +36223,12 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>Dobrudzha 1919</t>
+          <t>Slaven Koprivnica</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Beroe</t>
+          <t>Gorica</t>
         </is>
       </c>
       <c r="G182" t="n">
@@ -36261,13 +36261,13 @@
         </is>
       </c>
       <c r="P182" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="Q182" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="R182" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="S182" t="n">
         <v>0</v>
@@ -36410,7 +36410,7 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
@@ -36420,12 +36420,12 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>Bačka Topola</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Javor Ivanjica</t>
+          <t>Granada CF</t>
         </is>
       </c>
       <c r="G183" t="n">
@@ -36458,13 +36458,13 @@
         </is>
       </c>
       <c r="P183" t="n">
-        <v>1.51</v>
+        <v>1.91</v>
       </c>
       <c r="Q183" t="n">
-        <v>3.8</v>
+        <v>3.53</v>
       </c>
       <c r="R183" t="n">
-        <v>5.75</v>
+        <v>3.91</v>
       </c>
       <c r="S183" t="n">
         <v>0</v>
@@ -36503,10 +36503,10 @@
         <v>0</v>
       </c>
       <c r="AE183" t="n">
-        <v>1.85</v>
+        <v>1.88</v>
       </c>
       <c r="AF183" t="n">
-        <v>1.95</v>
+        <v>1.92</v>
       </c>
       <c r="AG183" t="n">
         <v>0</v>
@@ -36804,7 +36804,7 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
@@ -36814,12 +36814,12 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>AEK Athens</t>
+          <t>Jablonec</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Panathinaikos</t>
+          <t>Hradec Králové</t>
         </is>
       </c>
       <c r="G185" t="n">
@@ -36852,13 +36852,13 @@
         </is>
       </c>
       <c r="P185" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="Q185" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="R185" t="n">
-        <v>6.76</v>
+        <v>0</v>
       </c>
       <c r="S185" t="n">
         <v>0</v>
@@ -37198,7 +37198,7 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
@@ -37208,12 +37208,12 @@
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>Real Oviedo</t>
+          <t>Radnički Niš</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Getafe CF</t>
+          <t>LFK Mladost Lučani</t>
         </is>
       </c>
       <c r="G187" t="n">
@@ -37246,13 +37246,13 @@
         </is>
       </c>
       <c r="P187" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="Q187" t="n">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="R187" t="n">
-        <v>0</v>
+        <v>4.32</v>
       </c>
       <c r="S187" t="n">
         <v>0</v>
@@ -37291,10 +37291,10 @@
         <v>0</v>
       </c>
       <c r="AE187" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AF187" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG187" t="n">
         <v>0</v>
@@ -37395,7 +37395,7 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
@@ -37405,12 +37405,12 @@
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>Olympiakos Piraeus</t>
+          <t>Mirandés</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>PAOK</t>
+          <t>SD Eibar</t>
         </is>
       </c>
       <c r="G188" t="n">
@@ -37443,13 +37443,13 @@
         </is>
       </c>
       <c r="P188" t="n">
-        <v>1.82</v>
+        <v>3.12</v>
       </c>
       <c r="Q188" t="n">
-        <v>3.1</v>
+        <v>3.22</v>
       </c>
       <c r="R188" t="n">
-        <v>4.56</v>
+        <v>2.43</v>
       </c>
       <c r="S188" t="n">
         <v>0</v>
@@ -37592,7 +37592,7 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
@@ -37602,12 +37602,12 @@
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>Radnički Niš</t>
+          <t>Olympiakos Piraeus</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>LFK Mladost Lučani</t>
+          <t>PAOK</t>
         </is>
       </c>
       <c r="G189" t="n">
@@ -37640,13 +37640,13 @@
         </is>
       </c>
       <c r="P189" t="n">
-        <v>1.71</v>
+        <v>1.82</v>
       </c>
       <c r="Q189" t="n">
-        <v>3.54</v>
+        <v>3.1</v>
       </c>
       <c r="R189" t="n">
-        <v>4.32</v>
+        <v>4.56</v>
       </c>
       <c r="S189" t="n">
         <v>0</v>
@@ -37685,10 +37685,10 @@
         <v>0</v>
       </c>
       <c r="AE189" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AF189" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AG189" t="n">
         <v>0</v>
@@ -37789,7 +37789,7 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
@@ -37799,12 +37799,12 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>Union Saint-Gilloise</t>
+          <t>Lokomotiv Moskva</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>KV Mechelen</t>
+          <t>Baltika</t>
         </is>
       </c>
       <c r="G190" t="n">
@@ -37837,13 +37837,13 @@
         </is>
       </c>
       <c r="P190" t="n">
-        <v>1.28</v>
+        <v>2.25</v>
       </c>
       <c r="Q190" t="n">
-        <v>5.66</v>
+        <v>3.66</v>
       </c>
       <c r="R190" t="n">
-        <v>8.98</v>
+        <v>3.36</v>
       </c>
       <c r="S190" t="n">
         <v>0</v>
@@ -37986,7 +37986,7 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
@@ -37996,12 +37996,12 @@
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>Córdoba</t>
+          <t>Real Oviedo</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Granada CF</t>
+          <t>Getafe CF</t>
         </is>
       </c>
       <c r="G191" t="n">
@@ -38034,13 +38034,13 @@
         </is>
       </c>
       <c r="P191" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="Q191" t="n">
-        <v>3.53</v>
+        <v>0</v>
       </c>
       <c r="R191" t="n">
-        <v>3.91</v>
+        <v>0</v>
       </c>
       <c r="S191" t="n">
         <v>0</v>
@@ -38079,10 +38079,10 @@
         <v>0</v>
       </c>
       <c r="AE191" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AF191" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AG191" t="n">
         <v>0</v>
@@ -38183,22 +38183,22 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>Mirandés</t>
+          <t>Kansas City</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>SD Eibar</t>
+          <t>Chicago Red Stars</t>
         </is>
       </c>
       <c r="G192" t="n">
@@ -38231,13 +38231,13 @@
         </is>
       </c>
       <c r="P192" t="n">
-        <v>3.12</v>
+        <v>1.3</v>
       </c>
       <c r="Q192" t="n">
-        <v>3.22</v>
+        <v>5.1</v>
       </c>
       <c r="R192" t="n">
-        <v>2.43</v>
+        <v>7.95</v>
       </c>
       <c r="S192" t="n">
         <v>0</v>
@@ -38380,22 +38380,22 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>Jablonec</t>
+          <t>Copiapó</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Hradec Králové</t>
+          <t>Unión San Felipe</t>
         </is>
       </c>
       <c r="G193" t="n">
@@ -38577,22 +38577,22 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>Copiapó</t>
+          <t>Union Saint-Gilloise</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Unión San Felipe</t>
+          <t>KV Mechelen</t>
         </is>
       </c>
       <c r="G194" t="n">
@@ -38625,13 +38625,13 @@
         </is>
       </c>
       <c r="P194" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Q194" t="n">
-        <v>0</v>
+        <v>5.66</v>
       </c>
       <c r="R194" t="n">
-        <v>0</v>
+        <v>8.98</v>
       </c>
       <c r="S194" t="n">
         <v>0</v>
@@ -38774,7 +38774,7 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
@@ -38784,12 +38784,12 @@
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>Kansas City</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Chicago Red Stars</t>
+          <t>San Luis</t>
         </is>
       </c>
       <c r="G195" t="n">
@@ -38822,13 +38822,13 @@
         </is>
       </c>
       <c r="P195" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="Q195" t="n">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="R195" t="n">
-        <v>7.95</v>
+        <v>0</v>
       </c>
       <c r="S195" t="n">
         <v>0</v>
@@ -38971,22 +38971,22 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Bačka Topola</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>San Luis</t>
+          <t>Javor Ivanjica</t>
         </is>
       </c>
       <c r="G196" t="n">
@@ -39019,13 +39019,13 @@
         </is>
       </c>
       <c r="P196" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="Q196" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="R196" t="n">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="S196" t="n">
         <v>0</v>
@@ -39064,10 +39064,10 @@
         <v>0</v>
       </c>
       <c r="AE196" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AF196" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG196" t="n">
         <v>0</v>
@@ -39168,7 +39168,7 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
@@ -39178,12 +39178,12 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>Lokomotiv Moskva</t>
+          <t>AEK Athens</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Baltika</t>
+          <t>Panathinaikos</t>
         </is>
       </c>
       <c r="G197" t="n">
@@ -39216,13 +39216,13 @@
         </is>
       </c>
       <c r="P197" t="n">
-        <v>2.25</v>
+        <v>1.45</v>
       </c>
       <c r="Q197" t="n">
-        <v>3.66</v>
+        <v>3.8</v>
       </c>
       <c r="R197" t="n">
-        <v>3.36</v>
+        <v>6.76</v>
       </c>
       <c r="S197" t="n">
         <v>0</v>
@@ -39365,22 +39365,22 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>Ironi Tiberias</t>
+          <t>KA</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Maccabi Netanya</t>
+          <t>ÍBV</t>
         </is>
       </c>
       <c r="G198" t="n">
@@ -39413,13 +39413,13 @@
         </is>
       </c>
       <c r="P198" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="Q198" t="n">
-        <v>0</v>
+        <v>4.45</v>
       </c>
       <c r="R198" t="n">
-        <v>0</v>
+        <v>5.12</v>
       </c>
       <c r="S198" t="n">
         <v>0</v>
@@ -39562,22 +39562,22 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>Csákvári TK</t>
+          <t>Dinamo Batumi</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>Soroksár SC</t>
+          <t>Samgurali</t>
         </is>
       </c>
       <c r="G199" t="n">
@@ -39759,7 +39759,7 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
@@ -39769,12 +39769,12 @@
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Hapoel Haifa</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Ashdod</t>
         </is>
       </c>
       <c r="G200" t="n">
@@ -39807,13 +39807,13 @@
         </is>
       </c>
       <c r="P200" t="n">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="Q200" t="n">
-        <v>3.4</v>
+        <v>3.38</v>
       </c>
       <c r="R200" t="n">
-        <v>3.13</v>
+        <v>3</v>
       </c>
       <c r="S200" t="n">
         <v>0</v>
@@ -39852,10 +39852,10 @@
         <v>0</v>
       </c>
       <c r="AE200" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AF200" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AG200" t="n">
         <v>0</v>
@@ -39956,7 +39956,7 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
@@ -39966,12 +39966,12 @@
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>Békéscsaba</t>
+          <t>Hapoel Katamon</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Kozármisleny</t>
+          <t>Bnei Sakhnin</t>
         </is>
       </c>
       <c r="G201" t="n">
@@ -40360,12 +40360,12 @@
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>Hapoel Haifa</t>
+          <t>Ironi Tiberias</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>Ashdod</t>
+          <t>Maccabi Netanya</t>
         </is>
       </c>
       <c r="G203" t="n">
@@ -40398,13 +40398,13 @@
         </is>
       </c>
       <c r="P203" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Q203" t="n">
-        <v>3.38</v>
+        <v>0</v>
       </c>
       <c r="R203" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="S203" t="n">
         <v>0</v>
@@ -40547,7 +40547,7 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
@@ -40557,12 +40557,12 @@
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>Hapoel Katamon</t>
+          <t>Békéscsaba</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>Bnei Sakhnin</t>
+          <t>Kozármisleny</t>
         </is>
       </c>
       <c r="G204" t="n">
@@ -40744,22 +40744,22 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>Dinamo Batumi</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>Samgurali</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="G205" t="n">
@@ -40792,13 +40792,13 @@
         </is>
       </c>
       <c r="P205" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Q205" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R205" t="n">
-        <v>0</v>
+        <v>3.13</v>
       </c>
       <c r="S205" t="n">
         <v>0</v>
@@ -40837,10 +40837,10 @@
         <v>0</v>
       </c>
       <c r="AE205" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AF205" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AG205" t="n">
         <v>0</v>
@@ -40941,22 +40941,22 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>KA</t>
+          <t>Csákvári TK</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>ÍBV</t>
+          <t>Soroksár SC</t>
         </is>
       </c>
       <c r="G206" t="n">
@@ -40989,13 +40989,13 @@
         </is>
       </c>
       <c r="P206" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="Q206" t="n">
-        <v>4.45</v>
+        <v>0</v>
       </c>
       <c r="R206" t="n">
-        <v>5.12</v>
+        <v>0</v>
       </c>
       <c r="S206" t="n">
         <v>0</v>
@@ -41729,22 +41729,22 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>UTS Rabat</t>
+          <t>New England II</t>
         </is>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>Maghreb Fès</t>
+          <t>New York City II</t>
         </is>
       </c>
       <c r="G210" t="n">
@@ -42320,22 +42320,22 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>New England II</t>
+          <t>UTS Rabat</t>
         </is>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>New York City II</t>
+          <t>Maghreb Fès</t>
         </is>
       </c>
       <c r="G213" t="n">
@@ -42517,22 +42517,22 @@
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>Chacarita Juniors</t>
+          <t>Varzim</t>
         </is>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>CF Os Belenenses</t>
         </is>
       </c>
       <c r="G214" t="n">
@@ -42714,22 +42714,22 @@
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>Varzim</t>
+          <t>Chacarita Juniors</t>
         </is>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>CF Os Belenenses</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="G215" t="n">
@@ -43305,22 +43305,22 @@
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>Independiente Petrolero</t>
+          <t>Angers SCO</t>
         </is>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>Club Always Ready</t>
+          <t>Strasbourg</t>
         </is>
       </c>
       <c r="G218" t="n">
@@ -43353,13 +43353,13 @@
         </is>
       </c>
       <c r="P218" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="Q218" t="n">
-        <v>0</v>
+        <v>3.76</v>
       </c>
       <c r="R218" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="S218" t="n">
         <v>0</v>
@@ -43398,10 +43398,10 @@
         <v>0</v>
       </c>
       <c r="AE218" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AF218" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG218" t="n">
         <v>0</v>
@@ -43502,7 +43502,7 @@
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
@@ -43512,12 +43512,12 @@
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>Remo</t>
+          <t>Club Atlético Güemes</t>
         </is>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>Quilmes</t>
         </is>
       </c>
       <c r="G219" t="n">
@@ -43550,13 +43550,13 @@
         </is>
       </c>
       <c r="P219" t="n">
-        <v>5.3</v>
+        <v>0</v>
       </c>
       <c r="Q219" t="n">
-        <v>3.73</v>
+        <v>0</v>
       </c>
       <c r="R219" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="S219" t="n">
         <v>0</v>
@@ -43595,10 +43595,10 @@
         <v>0</v>
       </c>
       <c r="AE219" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AF219" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AG219" t="n">
         <v>0</v>
@@ -43709,12 +43709,12 @@
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>Auxerre</t>
+          <t>Toulouse</t>
         </is>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>Nice</t>
+          <t>Olympique Lyonnais</t>
         </is>
       </c>
       <c r="G220" t="n">
@@ -43747,13 +43747,13 @@
         </is>
       </c>
       <c r="P220" t="n">
-        <v>2.48</v>
+        <v>3.8</v>
       </c>
       <c r="Q220" t="n">
-        <v>3.5</v>
+        <v>3.78</v>
       </c>
       <c r="R220" t="n">
-        <v>3.07</v>
+        <v>2.05</v>
       </c>
       <c r="S220" t="n">
         <v>0</v>
@@ -43792,10 +43792,10 @@
         <v>0</v>
       </c>
       <c r="AE220" t="n">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="AF220" t="n">
-        <v>1.9</v>
+        <v>1.98</v>
       </c>
       <c r="AG220" t="n">
         <v>0</v>
@@ -43896,22 +43896,22 @@
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>FC Barcelona</t>
+          <t>Independiente Petrolero</t>
         </is>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Club Always Ready</t>
         </is>
       </c>
       <c r="G221" t="n">
@@ -44093,22 +44093,22 @@
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>Club Atlético Güemes</t>
+          <t>Monaco</t>
         </is>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>Quilmes</t>
+          <t>Lille</t>
         </is>
       </c>
       <c r="G222" t="n">
@@ -44141,13 +44141,13 @@
         </is>
       </c>
       <c r="P222" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="Q222" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="R222" t="n">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="S222" t="n">
         <v>0</v>
@@ -44186,10 +44186,10 @@
         <v>0</v>
       </c>
       <c r="AE222" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AF222" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AG222" t="n">
         <v>0</v>
@@ -44487,22 +44487,22 @@
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>Monaco</t>
+          <t>Remo</t>
         </is>
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>Lille</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="G224" t="n">
@@ -44535,13 +44535,13 @@
         </is>
       </c>
       <c r="P224" t="n">
-        <v>2.38</v>
+        <v>5.3</v>
       </c>
       <c r="Q224" t="n">
-        <v>3.9</v>
+        <v>3.73</v>
       </c>
       <c r="R224" t="n">
-        <v>2.96</v>
+        <v>1.71</v>
       </c>
       <c r="S224" t="n">
         <v>0</v>
@@ -44580,10 +44580,10 @@
         <v>0</v>
       </c>
       <c r="AE224" t="n">
-        <v>1.58</v>
+        <v>1.95</v>
       </c>
       <c r="AF224" t="n">
-        <v>2.25</v>
+        <v>1.73</v>
       </c>
       <c r="AG224" t="n">
         <v>0</v>
@@ -44694,12 +44694,12 @@
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>Le Havre</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>Olympique Marseille</t>
+          <t>Brest</t>
         </is>
       </c>
       <c r="G225" t="n">
@@ -44732,13 +44732,13 @@
         </is>
       </c>
       <c r="P225" t="n">
-        <v>4.68</v>
+        <v>1.18</v>
       </c>
       <c r="Q225" t="n">
-        <v>4.32</v>
+        <v>9.15</v>
       </c>
       <c r="R225" t="n">
-        <v>1.76</v>
+        <v>17</v>
       </c>
       <c r="S225" t="n">
         <v>0</v>
@@ -44777,16 +44777,16 @@
         <v>0</v>
       </c>
       <c r="AE225" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AF225" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AG225" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AH225" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AI225" t="n">
         <v>0</v>
@@ -44891,12 +44891,12 @@
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>Angers SCO</t>
+          <t>Le Havre</t>
         </is>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>Strasbourg</t>
+          <t>Olympique Marseille</t>
         </is>
       </c>
       <c r="G226" t="n">
@@ -44929,13 +44929,13 @@
         </is>
       </c>
       <c r="P226" t="n">
-        <v>4.05</v>
+        <v>4.68</v>
       </c>
       <c r="Q226" t="n">
-        <v>3.76</v>
+        <v>4.32</v>
       </c>
       <c r="R226" t="n">
-        <v>1.99</v>
+        <v>1.76</v>
       </c>
       <c r="S226" t="n">
         <v>0</v>
@@ -44974,10 +44974,10 @@
         <v>0</v>
       </c>
       <c r="AE226" t="n">
-        <v>1.85</v>
+        <v>1.58</v>
       </c>
       <c r="AF226" t="n">
-        <v>1.85</v>
+        <v>2.25</v>
       </c>
       <c r="AG226" t="n">
         <v>0</v>
@@ -45088,12 +45088,12 @@
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Auxerre</t>
         </is>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>Brest</t>
+          <t>Nice</t>
         </is>
       </c>
       <c r="G227" t="n">
@@ -45126,13 +45126,13 @@
         </is>
       </c>
       <c r="P227" t="n">
-        <v>1.18</v>
+        <v>2.48</v>
       </c>
       <c r="Q227" t="n">
-        <v>9.15</v>
+        <v>3.5</v>
       </c>
       <c r="R227" t="n">
-        <v>17</v>
+        <v>3.07</v>
       </c>
       <c r="S227" t="n">
         <v>0</v>
@@ -45171,16 +45171,16 @@
         <v>0</v>
       </c>
       <c r="AE227" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AF227" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AG227" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AH227" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AI227" t="n">
         <v>0</v>
@@ -45275,7 +45275,7 @@
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D228" t="inlineStr">
@@ -45285,12 +45285,12 @@
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>Náutico</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>América Mineiro</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="G228" t="n">
@@ -45323,13 +45323,13 @@
         </is>
       </c>
       <c r="P228" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="Q228" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="R228" t="n">
-        <v>4.39</v>
+        <v>0</v>
       </c>
       <c r="S228" t="n">
         <v>0</v>
@@ -45472,22 +45472,22 @@
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>Rennes</t>
+          <t>Náutico</t>
         </is>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>Paris</t>
+          <t>América Mineiro</t>
         </is>
       </c>
       <c r="G229" t="n">
@@ -45520,13 +45520,13 @@
         </is>
       </c>
       <c r="P229" t="n">
-        <v>1.59</v>
+        <v>1.79</v>
       </c>
       <c r="Q229" t="n">
-        <v>4.73</v>
+        <v>3.5</v>
       </c>
       <c r="R229" t="n">
-        <v>5.79</v>
+        <v>4.39</v>
       </c>
       <c r="S229" t="n">
         <v>0</v>
@@ -45571,10 +45571,10 @@
         <v>0</v>
       </c>
       <c r="AG229" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AH229" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AI229" t="n">
         <v>0</v>
@@ -45669,7 +45669,7 @@
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D230" t="inlineStr">
@@ -45679,12 +45679,12 @@
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>Toulouse</t>
+          <t>FC Barcelona</t>
         </is>
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>Olympique Lyonnais</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="G230" t="n">
@@ -45717,13 +45717,13 @@
         </is>
       </c>
       <c r="P230" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="Q230" t="n">
-        <v>3.78</v>
+        <v>0</v>
       </c>
       <c r="R230" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="S230" t="n">
         <v>0</v>
@@ -45762,10 +45762,10 @@
         <v>0</v>
       </c>
       <c r="AE230" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AF230" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AG230" t="n">
         <v>0</v>
@@ -45866,22 +45866,22 @@
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>Rennes</t>
         </is>
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>Paris</t>
         </is>
       </c>
       <c r="G231" t="n">
@@ -45914,13 +45914,13 @@
         </is>
       </c>
       <c r="P231" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="Q231" t="n">
-        <v>0</v>
+        <v>4.73</v>
       </c>
       <c r="R231" t="n">
-        <v>0</v>
+        <v>5.79</v>
       </c>
       <c r="S231" t="n">
         <v>0</v>
@@ -45965,10 +45965,10 @@
         <v>0</v>
       </c>
       <c r="AG231" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AH231" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AI231" t="n">
         <v>0</v>
@@ -46270,12 +46270,12 @@
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>Chaco For Ever</t>
+          <t>San Martín San Juan</t>
         </is>
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>Ciudad de Bolívar</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="G233" t="n">
@@ -46467,12 +46467,12 @@
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>San Martín San Juan</t>
+          <t>Chaco For Ever</t>
         </is>
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>Patronato</t>
+          <t>Ciudad de Bolívar</t>
         </is>
       </c>
       <c r="G234" t="n">
@@ -46851,7 +46851,7 @@
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D236" t="inlineStr">
@@ -46861,12 +46861,12 @@
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>Central Norte</t>
+          <t>Bay</t>
         </is>
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>Deportivo Madryn</t>
+          <t>Utah Royals</t>
         </is>
       </c>
       <c r="G236" t="n">
@@ -47048,7 +47048,7 @@
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D237" t="inlineStr">
@@ -47058,12 +47058,12 @@
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>Bay</t>
+          <t>Portland Timbers II</t>
         </is>
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>Utah Royals</t>
+          <t>LA Galaxy II</t>
         </is>
       </c>
       <c r="G237" t="n">
@@ -47255,12 +47255,12 @@
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>Portland Timbers II</t>
+          <t>Los Angeles II</t>
         </is>
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>LA Galaxy II</t>
+          <t>Real Monarchs</t>
         </is>
       </c>
       <c r="G238" t="n">
@@ -47442,7 +47442,7 @@
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D239" t="inlineStr">
@@ -47452,12 +47452,12 @@
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t>Los Angeles II</t>
+          <t>Central Norte</t>
         </is>
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>Real Monarchs</t>
+          <t>Deportivo Madryn</t>
         </is>
       </c>
       <c r="G239" t="n">
@@ -48437,12 +48437,12 @@
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>Mirassol</t>
         </is>
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>Bragantino</t>
+          <t>Chapecoense</t>
         </is>
       </c>
       <c r="G244" t="n">
@@ -48475,13 +48475,13 @@
         </is>
       </c>
       <c r="P244" t="n">
-        <v>2.13</v>
+        <v>1.79</v>
       </c>
       <c r="Q244" t="n">
-        <v>3.34</v>
+        <v>3.62</v>
       </c>
       <c r="R244" t="n">
-        <v>3.67</v>
+        <v>4.84</v>
       </c>
       <c r="S244" t="n">
         <v>0</v>
@@ -48520,10 +48520,10 @@
         <v>0</v>
       </c>
       <c r="AE244" t="n">
-        <v>1.95</v>
+        <v>1.87</v>
       </c>
       <c r="AF244" t="n">
-        <v>1.73</v>
+        <v>1.8</v>
       </c>
       <c r="AG244" t="n">
         <v>0</v>
@@ -48624,7 +48624,7 @@
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D245" t="inlineStr">
@@ -48634,12 +48634,12 @@
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>Corinthians</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>São Paulo</t>
+          <t>Fortaleza</t>
         </is>
       </c>
       <c r="G245" t="n">
@@ -48672,13 +48672,13 @@
         </is>
       </c>
       <c r="P245" t="n">
-        <v>2.26</v>
+        <v>2.81</v>
       </c>
       <c r="Q245" t="n">
-        <v>3.22</v>
+        <v>3.08</v>
       </c>
       <c r="R245" t="n">
-        <v>3.46</v>
+        <v>2.51</v>
       </c>
       <c r="S245" t="n">
         <v>0</v>
@@ -48717,10 +48717,10 @@
         <v>0</v>
       </c>
       <c r="AE245" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AF245" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AG245" t="n">
         <v>0</v>
@@ -48831,12 +48831,12 @@
       </c>
       <c r="E246" t="inlineStr">
         <is>
-          <t>Mirassol</t>
+          <t>Corinthians</t>
         </is>
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>Chapecoense</t>
+          <t>São Paulo</t>
         </is>
       </c>
       <c r="G246" t="n">
@@ -48869,13 +48869,13 @@
         </is>
       </c>
       <c r="P246" t="n">
-        <v>1.79</v>
+        <v>2.26</v>
       </c>
       <c r="Q246" t="n">
-        <v>3.62</v>
+        <v>3.22</v>
       </c>
       <c r="R246" t="n">
-        <v>4.84</v>
+        <v>3.46</v>
       </c>
       <c r="S246" t="n">
         <v>0</v>
@@ -48914,10 +48914,10 @@
         <v>0</v>
       </c>
       <c r="AE246" t="n">
-        <v>1.87</v>
+        <v>2.25</v>
       </c>
       <c r="AF246" t="n">
-        <v>1.8</v>
+        <v>1.57</v>
       </c>
       <c r="AG246" t="n">
         <v>0</v>
@@ -49018,7 +49018,7 @@
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D247" t="inlineStr">
@@ -49028,12 +49028,12 @@
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>Santos</t>
         </is>
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>Bragantino</t>
         </is>
       </c>
       <c r="G247" t="n">
@@ -49066,13 +49066,13 @@
         </is>
       </c>
       <c r="P247" t="n">
-        <v>2.81</v>
+        <v>2.13</v>
       </c>
       <c r="Q247" t="n">
-        <v>3.08</v>
+        <v>3.34</v>
       </c>
       <c r="R247" t="n">
-        <v>2.51</v>
+        <v>3.67</v>
       </c>
       <c r="S247" t="n">
         <v>0</v>
@@ -49111,10 +49111,10 @@
         <v>0</v>
       </c>
       <c r="AE247" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AF247" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AG247" t="n">
         <v>0</v>
@@ -49412,7 +49412,7 @@
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D249" t="inlineStr">
@@ -49422,12 +49422,12 @@
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>Grêmio</t>
+          <t>Novorizontino</t>
         </is>
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="G249" t="n">
@@ -49460,13 +49460,13 @@
         </is>
       </c>
       <c r="P249" t="n">
-        <v>3.79</v>
+        <v>0</v>
       </c>
       <c r="Q249" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="R249" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="S249" t="n">
         <v>0</v>
@@ -49505,10 +49505,10 @@
         <v>0</v>
       </c>
       <c r="AE249" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AF249" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AG249" t="n">
         <v>0</v>
@@ -49609,7 +49609,7 @@
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D250" t="inlineStr">
@@ -49619,12 +49619,12 @@
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>Grêmio</t>
         </is>
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="G250" t="n">
@@ -49657,13 +49657,13 @@
         </is>
       </c>
       <c r="P250" t="n">
-        <v>0</v>
+        <v>3.79</v>
       </c>
       <c r="Q250" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="R250" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="S250" t="n">
         <v>0</v>
@@ -49702,10 +49702,10 @@
         <v>0</v>
       </c>
       <c r="AE250" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AF250" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AG250" t="n">
         <v>0</v>
@@ -49806,7 +49806,7 @@
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
@@ -49816,12 +49816,12 @@
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>Minnesota United</t>
+          <t>Atlanta United II</t>
         </is>
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>Austin</t>
+          <t>Orlando City II</t>
         </is>
       </c>
       <c r="G251" t="n">
@@ -49854,13 +49854,13 @@
         </is>
       </c>
       <c r="P251" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="Q251" t="n">
-        <v>3.97</v>
+        <v>0</v>
       </c>
       <c r="R251" t="n">
-        <v>5.09</v>
+        <v>0</v>
       </c>
       <c r="S251" t="n">
         <v>0</v>
@@ -49899,10 +49899,10 @@
         <v>0</v>
       </c>
       <c r="AE251" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AF251" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AG251" t="n">
         <v>0</v>
@@ -50200,7 +50200,7 @@
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
@@ -50210,12 +50210,12 @@
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>Atlanta United II</t>
+          <t>Minnesota United</t>
         </is>
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>Orlando City II</t>
+          <t>Austin</t>
         </is>
       </c>
       <c r="G253" t="n">
@@ -50248,13 +50248,13 @@
         </is>
       </c>
       <c r="P253" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="Q253" t="n">
-        <v>0</v>
+        <v>3.97</v>
       </c>
       <c r="R253" t="n">
-        <v>0</v>
+        <v>5.09</v>
       </c>
       <c r="S253" t="n">
         <v>0</v>
@@ -50293,10 +50293,10 @@
         <v>0</v>
       </c>
       <c r="AE253" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AF253" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG253" t="n">
         <v>0</v>

--- a/jogos_2026-05-10.xlsx
+++ b/jogos_2026-05-10.xlsx
@@ -753,7 +753,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Australia New South Wales NPL</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -763,12 +763,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Blacktown City</t>
+          <t>Seongnam</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>St. George Saints</t>
+          <t>Jeonnam Dragons</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -801,13 +801,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>3.61</v>
       </c>
       <c r="S2" t="n">
         <v>0</v>
@@ -950,7 +950,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>Australia New South Wales NPL</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Ulsan</t>
+          <t>Rockdale City Suns</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Bucheon 1995</t>
+          <t>Sydney II</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>Australia New South Wales NPL</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Seongnam</t>
+          <t>Blacktown City</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Jeonnam Dragons</t>
+          <t>St. George Saints</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1195,13 +1195,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>3.61</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
@@ -1344,7 +1344,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Australia New South Wales NPL</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Rockdale City Suns</t>
+          <t>Ulsan</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Sydney II</t>
+          <t>Bucheon 1995</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Shaanxi Union</t>
+          <t>Dalian Huayi</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Shanghai Jiading</t>
+          <t>Guangzhou E-Power</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Dalian Huayi</t>
+          <t>Shaanxi Union</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Guangzhou E-Power</t>
+          <t>Shanghai Jiading</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2723,7 +2723,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Ansan Greeners</t>
+          <t>Anyang</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Yongin City</t>
+          <t>Jeonbuk Motors</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2771,13 +2771,13 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>3.32</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
         <v>0</v>
@@ -2920,7 +2920,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Anyang</t>
+          <t>Ansan Greeners</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Jeonbuk Motors</t>
+          <t>Yongin City</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2968,13 +2968,13 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="S13" t="n">
         <v>0</v>
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Persija</t>
+          <t>Persita</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Persib</t>
+          <t>Persijap</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Persita</t>
+          <t>Persija</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Persijap</t>
+          <t>Persib</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -4299,22 +4299,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Ulytau</t>
+          <t>Polonia Warszawa</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Kairat</t>
+          <t>Górnik Łęczna</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4496,7 +4496,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Sheger Ketema</t>
+          <t>Levante W</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Sidama Bunna</t>
+          <t>Logroño W</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4693,22 +4693,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Amarante</t>
+          <t>Sichuan Jiuniu</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>União Santarém</t>
+          <t>Shandong Luneng</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4890,22 +4890,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Sichuan Jiuniu</t>
+          <t>Hoang Anh Gia Lai</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Shandong Luneng</t>
+          <t>Pho Hien</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -5087,22 +5087,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Hoang Anh Gia Lai</t>
+          <t>Gyeongnam</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Pho Hien</t>
+          <t>Gimhae City</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5135,13 +5135,13 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="S24" t="n">
         <v>0</v>
@@ -5284,7 +5284,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Gyeongnam</t>
+          <t>Ulytau</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Gimhae City</t>
+          <t>Kairat</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5332,13 +5332,13 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>3.16</v>
+        <v>0</v>
       </c>
       <c r="R25" t="n">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="S25" t="n">
         <v>0</v>
@@ -5481,7 +5481,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Levante W</t>
+          <t>Sheger Ketema</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Logroño W</t>
+          <t>Sidama Bunna</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5678,7 +5678,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Sokol Saratov</t>
+          <t>Amarante</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Spartak Kostroma</t>
+          <t>União Santarém</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5726,13 +5726,13 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>4.98</v>
+        <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>3.66</v>
+        <v>0</v>
       </c>
       <c r="R27" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="S27" t="n">
         <v>0</v>
@@ -5875,7 +5875,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Polonia Warszawa</t>
+          <t>Sokol Saratov</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Górnik Łęczna</t>
+          <t>Spartak Kostroma</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -5923,13 +5923,13 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>0</v>
+        <v>4.98</v>
       </c>
       <c r="Q28" t="n">
-        <v>0</v>
+        <v>3.66</v>
       </c>
       <c r="R28" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="S28" t="n">
         <v>0</v>
@@ -6466,22 +6466,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Shenyang Urban</t>
+          <t>Ho Chi Minh City</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Yunnan Yukun</t>
+          <t>Song Lam Nghe An</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Ho Chi Minh City</t>
+          <t>Hà Nội II</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Song Lam Nghe An</t>
+          <t>Viettel</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6860,22 +6860,22 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Celtic</t>
+          <t>Shenzhen Juniors</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Hebei Kungfu</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -6908,13 +6908,13 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="R33" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="S33" t="n">
         <v>0</v>
@@ -7057,22 +7057,22 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Kanchanaburi</t>
+          <t>Altay</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Ratchaburi</t>
+          <t>Ordabasy</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7105,13 +7105,13 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>3.32</v>
+        <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="R34" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="S34" t="n">
         <v>0</v>
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Bangkok Glass</t>
+          <t>Sukhothai</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Prachuap</t>
+          <t>Muang Thong United</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7302,13 +7302,13 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>1.78</v>
+        <v>2.44</v>
       </c>
       <c r="Q35" t="n">
-        <v>3.9</v>
+        <v>3.61</v>
       </c>
       <c r="R35" t="n">
-        <v>4.35</v>
+        <v>2.77</v>
       </c>
       <c r="S35" t="n">
         <v>0</v>
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Rayong</t>
+          <t>Chiangrai United</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Bangkok United</t>
+          <t>Uthai Thani</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7499,13 +7499,13 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>3.4</v>
+        <v>2.7</v>
       </c>
       <c r="Q36" t="n">
-        <v>3.63</v>
+        <v>3.36</v>
       </c>
       <c r="R36" t="n">
-        <v>2.09</v>
+        <v>2.64</v>
       </c>
       <c r="S36" t="n">
         <v>0</v>
@@ -7544,10 +7544,10 @@
         <v>0</v>
       </c>
       <c r="AE36" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AF36" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AG36" t="n">
         <v>0</v>
@@ -7648,22 +7648,22 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Buriram United</t>
+          <t>Shenyang Urban</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Lamphun Warrior</t>
+          <t>Yunnan Yukun</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7696,13 +7696,13 @@
         </is>
       </c>
       <c r="P37" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>6.73</v>
+        <v>0</v>
       </c>
       <c r="R37" t="n">
-        <v>10.6</v>
+        <v>0</v>
       </c>
       <c r="S37" t="n">
         <v>0</v>
@@ -7845,7 +7845,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Hà Nội II</t>
+          <t>Celtic</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Viettel</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -7893,13 +7893,13 @@
         </is>
       </c>
       <c r="P38" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Q38" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="R38" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="S38" t="n">
         <v>0</v>
@@ -8042,22 +8042,22 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Piteå Women</t>
+          <t>Kanchanaburi</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Rosengard Women</t>
+          <t>Ratchaburi</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8090,13 +8090,13 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="Q39" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="R39" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="S39" t="n">
         <v>0</v>
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Ayutthaya United</t>
+          <t>Buriram United</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Port FC</t>
+          <t>Lamphun Warrior</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8287,13 +8287,13 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>5.09</v>
+        <v>1.24</v>
       </c>
       <c r="Q40" t="n">
-        <v>4.18</v>
+        <v>6.73</v>
       </c>
       <c r="R40" t="n">
-        <v>1.64</v>
+        <v>10.6</v>
       </c>
       <c r="S40" t="n">
         <v>0</v>
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Sukhothai</t>
+          <t>Ayutthaya United</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Muang Thong United</t>
+          <t>Port FC</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8484,13 +8484,13 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>2.44</v>
+        <v>5.09</v>
       </c>
       <c r="Q41" t="n">
-        <v>3.61</v>
+        <v>4.18</v>
       </c>
       <c r="R41" t="n">
-        <v>2.77</v>
+        <v>1.64</v>
       </c>
       <c r="S41" t="n">
         <v>0</v>
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Chonburi</t>
+          <t>Rayong</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Nakhon Ratchasima</t>
+          <t>Bangkok United</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8681,13 +8681,13 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>1.61</v>
+        <v>3.4</v>
       </c>
       <c r="Q42" t="n">
-        <v>4.18</v>
+        <v>3.63</v>
       </c>
       <c r="R42" t="n">
-        <v>5.3</v>
+        <v>2.09</v>
       </c>
       <c r="S42" t="n">
         <v>0</v>
@@ -8830,22 +8830,22 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Shenzhen Juniors</t>
+          <t>Bangkok Glass</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Hebei Kungfu</t>
+          <t>Prachuap</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -8878,13 +8878,13 @@
         </is>
       </c>
       <c r="P43" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="Q43" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="R43" t="n">
-        <v>0</v>
+        <v>4.35</v>
       </c>
       <c r="S43" t="n">
         <v>0</v>
@@ -9027,22 +9027,22 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Altay</t>
+          <t>Chonburi</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Ordabasy</t>
+          <t>Nakhon Ratchasima</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9075,13 +9075,13 @@
         </is>
       </c>
       <c r="P44" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="Q44" t="n">
-        <v>0</v>
+        <v>4.18</v>
       </c>
       <c r="R44" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="S44" t="n">
         <v>0</v>
@@ -9224,22 +9224,22 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Chiangrai United</t>
+          <t>Piteå Women</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Uthai Thani</t>
+          <t>Rosengard Women</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9272,13 +9272,13 @@
         </is>
       </c>
       <c r="P45" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>3.36</v>
+        <v>0</v>
       </c>
       <c r="R45" t="n">
-        <v>2.64</v>
+        <v>0</v>
       </c>
       <c r="S45" t="n">
         <v>0</v>
@@ -9317,10 +9317,10 @@
         <v>0</v>
       </c>
       <c r="AE45" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AF45" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AG45" t="n">
         <v>0</v>
@@ -9421,22 +9421,22 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Spartak Varna</t>
+          <t>Sūduva</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Slavia Sofia</t>
+          <t>Žalgiris</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9469,13 +9469,13 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="Q46" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="R46" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="S46" t="n">
         <v>0</v>
@@ -9618,22 +9618,22 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Sūduva</t>
+          <t>Spartak Varna</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Žalgiris</t>
+          <t>Slavia Sofia</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9666,13 +9666,13 @@
         </is>
       </c>
       <c r="P47" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="Q47" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R47" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="S47" t="n">
         <v>0</v>
@@ -9815,22 +9815,22 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Singapore S.League</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Kerala Blasters</t>
+          <t>Home United</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Mohammedan</t>
+          <t>Albirex Niigata S</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -9863,13 +9863,13 @@
         </is>
       </c>
       <c r="P48" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="Q48" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="R48" t="n">
-        <v>7.37</v>
+        <v>0</v>
       </c>
       <c r="S48" t="n">
         <v>0</v>
@@ -10012,22 +10012,22 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Singapore S.League</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Home United</t>
+          <t>Preußen Münster</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Albirex Niigata S</t>
+          <t>Darmstadt 98</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10060,13 +10060,13 @@
         </is>
       </c>
       <c r="P49" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="Q49" t="n">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="R49" t="n">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="S49" t="n">
         <v>0</v>
@@ -10209,22 +10209,22 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Singapore S.League</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Hougang United</t>
+          <t>Dongguan United</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Tampines Rovers</t>
+          <t>Suzhou Dongwu</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10406,7 +10406,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Nõmme Kalju</t>
+          <t>Nantong Zhiyun</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Tallinna FC Flora</t>
+          <t>Wuxi Wugou</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10454,13 +10454,13 @@
         </is>
       </c>
       <c r="P51" t="n">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="Q51" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="R51" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="S51" t="n">
         <v>0</v>
@@ -10603,22 +10603,22 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Singapore S.League</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Preußen Münster</t>
+          <t>Hougang United</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Darmstadt 98</t>
+          <t>Tampines Rovers</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10651,13 +10651,13 @@
         </is>
       </c>
       <c r="P52" t="n">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="Q52" t="n">
-        <v>3.74</v>
+        <v>0</v>
       </c>
       <c r="R52" t="n">
-        <v>2.76</v>
+        <v>0</v>
       </c>
       <c r="S52" t="n">
         <v>0</v>
@@ -10800,7 +10800,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -10810,12 +10810,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Havelse</t>
+          <t>Kerala Blasters</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Schweinfurt</t>
+          <t>Mohammedan</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -10848,13 +10848,13 @@
         </is>
       </c>
       <c r="P53" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="Q53" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="R53" t="n">
-        <v>0</v>
+        <v>7.37</v>
       </c>
       <c r="S53" t="n">
         <v>0</v>
@@ -10997,22 +10997,22 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Dongguan United</t>
+          <t>Havelse</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Suzhou Dongwu</t>
+          <t>Schweinfurt</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11204,12 +11204,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Hertha BSC</t>
+          <t>Fortuna Düsseldorf</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Greuther Fürth</t>
+          <t>Elversberg</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11242,13 +11242,13 @@
         </is>
       </c>
       <c r="P55" t="n">
-        <v>1.78</v>
+        <v>2.88</v>
       </c>
       <c r="Q55" t="n">
-        <v>4.15</v>
+        <v>3.8</v>
       </c>
       <c r="R55" t="n">
-        <v>3.8</v>
+        <v>2.19</v>
       </c>
       <c r="S55" t="n">
         <v>0</v>
@@ -11293,10 +11293,10 @@
         <v>0</v>
       </c>
       <c r="AG55" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AH55" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AI55" t="n">
         <v>0</v>
@@ -11391,22 +11391,22 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Fortuna Düsseldorf</t>
+          <t>Nõmme Kalju</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Elversberg</t>
+          <t>Tallinna FC Flora</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11439,13 +11439,13 @@
         </is>
       </c>
       <c r="P56" t="n">
-        <v>2.88</v>
+        <v>2.27</v>
       </c>
       <c r="Q56" t="n">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="R56" t="n">
-        <v>2.19</v>
+        <v>2.6</v>
       </c>
       <c r="S56" t="n">
         <v>0</v>
@@ -11588,22 +11588,22 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Nantong Zhiyun</t>
+          <t>Hertha BSC</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Wuxi Wugou</t>
+          <t>Greuther Fürth</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11636,13 +11636,13 @@
         </is>
       </c>
       <c r="P57" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="Q57" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="R57" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="S57" t="n">
         <v>0</v>
@@ -11687,10 +11687,10 @@
         <v>0</v>
       </c>
       <c r="AG57" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AH57" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AI57" t="n">
         <v>0</v>
@@ -11992,12 +11992,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Beijing Guoan</t>
+          <t>Zhejiang FC</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Shanghai SIPG</t>
+          <t>Tianjin Teda</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -12189,12 +12189,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Zhejiang FC</t>
+          <t>Beijing Guoan</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Tianjin Teda</t>
+          <t>Shanghai SIPG</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -12573,22 +12573,22 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Vejle</t>
+          <t>Meshakhte</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Fredericia</t>
+          <t>Dila</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12621,13 +12621,13 @@
         </is>
       </c>
       <c r="P62" t="n">
-        <v>2.58</v>
+        <v>0</v>
       </c>
       <c r="Q62" t="n">
-        <v>3.62</v>
+        <v>0</v>
       </c>
       <c r="R62" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="S62" t="n">
         <v>0</v>
@@ -12770,7 +12770,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -12780,12 +12780,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>FC Andorra</t>
+          <t>Nordsjælland</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>UD Las Palmas</t>
+          <t>Midtjylland</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -12818,13 +12818,13 @@
         </is>
       </c>
       <c r="P63" t="n">
-        <v>2.46</v>
+        <v>3.36</v>
       </c>
       <c r="Q63" t="n">
-        <v>3.43</v>
+        <v>3.65</v>
       </c>
       <c r="R63" t="n">
-        <v>2.91</v>
+        <v>1.99</v>
       </c>
       <c r="S63" t="n">
         <v>0</v>
@@ -12967,22 +12967,22 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Kalmar</t>
+          <t>Zenit</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Halmstad</t>
+          <t>FK Sochi</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -13015,13 +13015,13 @@
         </is>
       </c>
       <c r="P64" t="n">
-        <v>1.92</v>
+        <v>1.21</v>
       </c>
       <c r="Q64" t="n">
-        <v>3.4</v>
+        <v>7.41</v>
       </c>
       <c r="R64" t="n">
-        <v>3.9</v>
+        <v>17.5</v>
       </c>
       <c r="S64" t="n">
         <v>0</v>
@@ -13164,22 +13164,22 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Bahardar</t>
+          <t>AIK</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Welwalo Adigrat Uni</t>
+          <t>Djurgården</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -13212,13 +13212,13 @@
         </is>
       </c>
       <c r="P65" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="Q65" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="R65" t="n">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="S65" t="n">
         <v>0</v>
@@ -13361,7 +13361,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -13371,12 +13371,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>RCD Mallorca</t>
+          <t>Vejle</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>Fredericia</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -13409,13 +13409,13 @@
         </is>
       </c>
       <c r="P66" t="n">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="Q66" t="n">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="R66" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="S66" t="n">
         <v>0</v>
@@ -13558,22 +13558,22 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Zenit</t>
+          <t>Kalmar</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>FK Sochi</t>
+          <t>Halmstad</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -13606,13 +13606,13 @@
         </is>
       </c>
       <c r="P67" t="n">
-        <v>1.21</v>
+        <v>1.92</v>
       </c>
       <c r="Q67" t="n">
-        <v>7.41</v>
+        <v>3.4</v>
       </c>
       <c r="R67" t="n">
-        <v>17.5</v>
+        <v>3.9</v>
       </c>
       <c r="S67" t="n">
         <v>0</v>
@@ -13755,22 +13755,22 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Aktobe</t>
+          <t>FC Andorra</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Kaisar</t>
+          <t>UD Las Palmas</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -13803,13 +13803,13 @@
         </is>
       </c>
       <c r="P68" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="Q68" t="n">
-        <v>0</v>
+        <v>3.43</v>
       </c>
       <c r="R68" t="n">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="S68" t="n">
         <v>0</v>
@@ -13952,7 +13952,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -13962,12 +13962,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Nordsjælland</t>
+          <t>RCD Mallorca</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Midtjylland</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -14000,13 +14000,13 @@
         </is>
       </c>
       <c r="P69" t="n">
-        <v>3.36</v>
+        <v>0</v>
       </c>
       <c r="Q69" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="R69" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="S69" t="n">
         <v>0</v>
@@ -14149,22 +14149,22 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AIK</t>
+          <t>Bahardar</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Djurgården</t>
+          <t>Welwalo Adigrat Uni</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -14197,13 +14197,13 @@
         </is>
       </c>
       <c r="P70" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="Q70" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="R70" t="n">
-        <v>2.87</v>
+        <v>0</v>
       </c>
       <c r="S70" t="n">
         <v>0</v>
@@ -14346,7 +14346,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -14356,12 +14356,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Meshakhte</t>
+          <t>Aktobe</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Dila</t>
+          <t>Kaisar</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -14543,7 +14543,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -14553,12 +14553,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Lugano</t>
+          <t>PSIM Yogyakarta</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>St. Gallen</t>
+          <t>Malut United</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -14591,13 +14591,13 @@
         </is>
       </c>
       <c r="P72" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="Q72" t="n">
-        <v>3.54</v>
+        <v>0</v>
       </c>
       <c r="R72" t="n">
-        <v>2.73</v>
+        <v>0</v>
       </c>
       <c r="S72" t="n">
         <v>0</v>
@@ -14740,22 +14740,22 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Qingdao Jonoon</t>
+          <t>Lugano</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Dalian Zhixing</t>
+          <t>St. Gallen</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -14788,13 +14788,13 @@
         </is>
       </c>
       <c r="P73" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="Q73" t="n">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="R73" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="S73" t="n">
         <v>0</v>
@@ -14937,22 +14937,22 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>PSIM Yogyakarta</t>
+          <t>Qingdao Jonoon</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Malut United</t>
+          <t>Dalian Zhixing</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -15134,7 +15134,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -15144,12 +15144,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Công An Nhân Dân</t>
+          <t>Kuala Lumpur</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Nam Dinh</t>
+          <t>Negeri Sembilan</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -15331,7 +15331,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -15341,12 +15341,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Kuala Lumpur</t>
+          <t>Công An Nhân Dân</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Negeri Sembilan</t>
+          <t>Nam Dinh</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -15528,22 +15528,22 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Tychy 71</t>
+          <t>Rosenborg</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Ruch Chorzów</t>
+          <t>Lillestrøm</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -15576,13 +15576,13 @@
         </is>
       </c>
       <c r="P77" t="n">
-        <v>4</v>
+        <v>2.79</v>
       </c>
       <c r="Q77" t="n">
-        <v>3.6</v>
+        <v>3.67</v>
       </c>
       <c r="R77" t="n">
-        <v>1.83</v>
+        <v>2.41</v>
       </c>
       <c r="S77" t="n">
         <v>0</v>
@@ -15922,22 +15922,22 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Rosenborg</t>
+          <t>Tychy 71</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Lillestrøm</t>
+          <t>Ruch Chorzów</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -15970,13 +15970,13 @@
         </is>
       </c>
       <c r="P79" t="n">
-        <v>2.79</v>
+        <v>4</v>
       </c>
       <c r="Q79" t="n">
-        <v>3.67</v>
+        <v>3.6</v>
       </c>
       <c r="R79" t="n">
-        <v>2.41</v>
+        <v>1.83</v>
       </c>
       <c r="S79" t="n">
         <v>0</v>
@@ -16316,7 +16316,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -16326,12 +16326,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Nottingham Forest</t>
+          <t>Arba Minch Kenema</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Newcastle United</t>
+          <t>Welayta Dicha</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -16364,13 +16364,13 @@
         </is>
       </c>
       <c r="P81" t="n">
-        <v>2.46</v>
+        <v>0</v>
       </c>
       <c r="Q81" t="n">
-        <v>3.66</v>
+        <v>0</v>
       </c>
       <c r="R81" t="n">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="S81" t="n">
         <v>0</v>
@@ -16409,10 +16409,10 @@
         <v>0</v>
       </c>
       <c r="AE81" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AF81" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AG81" t="n">
         <v>0</v>
@@ -16513,7 +16513,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -16523,12 +16523,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Cremonese</t>
+          <t>Burnley</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Pisa</t>
+          <t>Aston Villa</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -16561,13 +16561,13 @@
         </is>
       </c>
       <c r="P82" t="n">
-        <v>2.1</v>
+        <v>5.38</v>
       </c>
       <c r="Q82" t="n">
-        <v>3.42</v>
+        <v>4.37</v>
       </c>
       <c r="R82" t="n">
-        <v>4.07</v>
+        <v>1.67</v>
       </c>
       <c r="S82" t="n">
         <v>0</v>
@@ -16606,10 +16606,10 @@
         <v>0</v>
       </c>
       <c r="AE82" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AF82" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AG82" t="n">
         <v>0</v>
@@ -16710,7 +16710,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -16720,12 +16720,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Fiorentina</t>
+          <t>Botoşani</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Genoa</t>
+          <t>Petrolul 52</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -16758,13 +16758,13 @@
         </is>
       </c>
       <c r="P83" t="n">
-        <v>2.09</v>
+        <v>2.21</v>
       </c>
       <c r="Q83" t="n">
-        <v>3.48</v>
+        <v>3.22</v>
       </c>
       <c r="R83" t="n">
-        <v>4.01</v>
+        <v>3.22</v>
       </c>
       <c r="S83" t="n">
         <v>0</v>
@@ -16803,10 +16803,10 @@
         <v>0</v>
       </c>
       <c r="AE83" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AF83" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AG83" t="n">
         <v>0</v>
@@ -16907,7 +16907,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -16917,12 +16917,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Botoşani</t>
+          <t>NK Primorje</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Petrolul 52</t>
+          <t>Mura</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -16955,13 +16955,13 @@
         </is>
       </c>
       <c r="P84" t="n">
-        <v>2.21</v>
+        <v>2.59</v>
       </c>
       <c r="Q84" t="n">
-        <v>3.22</v>
+        <v>3.45</v>
       </c>
       <c r="R84" t="n">
-        <v>3.22</v>
+        <v>2.3</v>
       </c>
       <c r="S84" t="n">
         <v>0</v>
@@ -17104,7 +17104,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -17114,12 +17114,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Turan</t>
+          <t>Pardubice</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Karvan FK</t>
+          <t>Karviná</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -17301,22 +17301,22 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Burnley</t>
+          <t>Uppsala W</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Aston Villa</t>
+          <t>Vittsjö</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -17349,13 +17349,13 @@
         </is>
       </c>
       <c r="P86" t="n">
-        <v>5.38</v>
+        <v>0</v>
       </c>
       <c r="Q86" t="n">
-        <v>4.37</v>
+        <v>0</v>
       </c>
       <c r="R86" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="S86" t="n">
         <v>0</v>
@@ -17498,22 +17498,22 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Crystal Palace</t>
+          <t>Astana</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Kyzyl-Zhar</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -17546,13 +17546,13 @@
         </is>
       </c>
       <c r="P87" t="n">
-        <v>2.69</v>
+        <v>1.8</v>
       </c>
       <c r="Q87" t="n">
-        <v>3.31</v>
+        <v>3.76</v>
       </c>
       <c r="R87" t="n">
-        <v>2.92</v>
+        <v>4.15</v>
       </c>
       <c r="S87" t="n">
         <v>0</v>
@@ -17591,10 +17591,10 @@
         <v>0</v>
       </c>
       <c r="AE87" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AF87" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AG87" t="n">
         <v>0</v>
@@ -17695,7 +17695,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -17705,12 +17705,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>NK Primorje</t>
+          <t>Nottingham Forest</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Mura</t>
+          <t>Newcastle United</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -17743,13 +17743,13 @@
         </is>
       </c>
       <c r="P88" t="n">
-        <v>2.59</v>
+        <v>2.46</v>
       </c>
       <c r="Q88" t="n">
-        <v>3.45</v>
+        <v>3.66</v>
       </c>
       <c r="R88" t="n">
-        <v>2.3</v>
+        <v>2.99</v>
       </c>
       <c r="S88" t="n">
         <v>0</v>
@@ -17788,10 +17788,10 @@
         <v>0</v>
       </c>
       <c r="AE88" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AF88" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AG88" t="n">
         <v>0</v>
@@ -17892,7 +17892,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -17902,12 +17902,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Pardubice</t>
+          <t>Crystal Palace</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Karviná</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -17940,13 +17940,13 @@
         </is>
       </c>
       <c r="P89" t="n">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="Q89" t="n">
-        <v>0</v>
+        <v>3.31</v>
       </c>
       <c r="R89" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="S89" t="n">
         <v>0</v>
@@ -17985,10 +17985,10 @@
         <v>0</v>
       </c>
       <c r="AE89" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AF89" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AG89" t="n">
         <v>0</v>
@@ -18089,7 +18089,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -18099,12 +18099,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Arba Minch Kenema</t>
+          <t>Sigma Olomouc</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Welayta Dicha</t>
+          <t>Bohemians 1905</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -18286,22 +18286,22 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Uppsala W</t>
+          <t>Fiorentina</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Vittsjö</t>
+          <t>Genoa</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -18334,13 +18334,13 @@
         </is>
       </c>
       <c r="P91" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="Q91" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="R91" t="n">
-        <v>0</v>
+        <v>4.01</v>
       </c>
       <c r="S91" t="n">
         <v>0</v>
@@ -18379,10 +18379,10 @@
         <v>0</v>
       </c>
       <c r="AE91" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AF91" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AG91" t="n">
         <v>0</v>
@@ -18483,7 +18483,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -18493,12 +18493,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Sigma Olomouc</t>
+          <t>Turan</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Bohemians 1905</t>
+          <t>Karvan FK</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -18680,22 +18680,22 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Astana</t>
+          <t>Cremonese</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Kyzyl-Zhar</t>
+          <t>Pisa</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -18728,13 +18728,13 @@
         </is>
       </c>
       <c r="P93" t="n">
-        <v>1.8</v>
+        <v>2.1</v>
       </c>
       <c r="Q93" t="n">
-        <v>3.76</v>
+        <v>3.42</v>
       </c>
       <c r="R93" t="n">
-        <v>4.15</v>
+        <v>4.07</v>
       </c>
       <c r="S93" t="n">
         <v>0</v>
@@ -18773,10 +18773,10 @@
         <v>0</v>
       </c>
       <c r="AE93" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AF93" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AG93" t="n">
         <v>0</v>
@@ -19468,7 +19468,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -19478,12 +19478,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Osijek</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Istra 1961</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -19516,13 +19516,13 @@
         </is>
       </c>
       <c r="P97" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="Q97" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="R97" t="n">
-        <v>3.21</v>
+        <v>0</v>
       </c>
       <c r="S97" t="n">
         <v>0</v>
@@ -19561,10 +19561,10 @@
         <v>0</v>
       </c>
       <c r="AE97" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AF97" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AG97" t="n">
         <v>0</v>
@@ -19665,7 +19665,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -19675,12 +19675,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Osijek</t>
+          <t>Aris</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Istra 1961</t>
+          <t>OFI</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -19872,12 +19872,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Aris</t>
+          <t>Volos NFC</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>OFI</t>
+          <t>Levadiakos</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -19910,13 +19910,13 @@
         </is>
       </c>
       <c r="P99" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="Q99" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R99" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="S99" t="n">
         <v>0</v>
@@ -20059,22 +20059,22 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Banga</t>
+          <t>NorthEast United</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>TransINVEST Vilnius</t>
+          <t>Chennaiyin</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -20256,7 +20256,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -20266,12 +20266,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>NorthEast United</t>
+          <t>Silkeborg</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Chennaiyin</t>
+          <t>København</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -20304,13 +20304,13 @@
         </is>
       </c>
       <c r="P101" t="n">
-        <v>0</v>
+        <v>4.68</v>
       </c>
       <c r="Q101" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R101" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="S101" t="n">
         <v>0</v>
@@ -20453,22 +20453,22 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Silkeborg</t>
+          <t>Banga</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>TransINVEST Vilnius</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -20501,13 +20501,13 @@
         </is>
       </c>
       <c r="P102" t="n">
-        <v>4.68</v>
+        <v>0</v>
       </c>
       <c r="Q102" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R102" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="S102" t="n">
         <v>0</v>
@@ -20660,12 +20660,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>B36</t>
+          <t>EB - Streymur</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>KÍ</t>
+          <t>Víkingur</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -20847,22 +20847,22 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>EB - Streymur</t>
+          <t>Royal Antwerp FC</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Víkingur</t>
+          <t>Sporting Charleroi</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -20895,13 +20895,13 @@
         </is>
       </c>
       <c r="P104" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="Q104" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="R104" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="S104" t="n">
         <v>0</v>
@@ -20940,10 +20940,10 @@
         <v>0</v>
       </c>
       <c r="AE104" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AF104" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG104" t="n">
         <v>0</v>
@@ -21044,7 +21044,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -21054,12 +21054,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Royal Antwerp FC</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Sporting Charleroi</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -21092,13 +21092,13 @@
         </is>
       </c>
       <c r="P105" t="n">
-        <v>2.38</v>
+        <v>2.17</v>
       </c>
       <c r="Q105" t="n">
-        <v>3.24</v>
+        <v>3.4</v>
       </c>
       <c r="R105" t="n">
-        <v>3.14</v>
+        <v>3.21</v>
       </c>
       <c r="S105" t="n">
         <v>0</v>
@@ -21137,10 +21137,10 @@
         <v>0</v>
       </c>
       <c r="AE105" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AF105" t="n">
         <v>1.88</v>
-      </c>
-      <c r="AF105" t="n">
-        <v>1.8</v>
       </c>
       <c r="AG105" t="n">
         <v>0</v>
@@ -21241,22 +21241,22 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Honvéd W</t>
+          <t>B36</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Vasas</t>
+          <t>KÍ</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -21635,7 +21635,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -21645,12 +21645,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Volos NFC</t>
+          <t>Honvéd W</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Levadiakos</t>
+          <t>Vasas</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -21683,13 +21683,13 @@
         </is>
       </c>
       <c r="P108" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="Q108" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="R108" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="S108" t="n">
         <v>0</v>
@@ -22029,7 +22029,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -22039,12 +22039,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Athletic Club Bilbao</t>
+          <t>Akhmat Grozny</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Valencia CF</t>
+          <t>Makhachkala</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -22077,13 +22077,13 @@
         </is>
       </c>
       <c r="P110" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="Q110" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="R110" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="S110" t="n">
         <v>0</v>
@@ -22226,7 +22226,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -22236,12 +22236,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Akhmat Grozny</t>
+          <t>Athletic Club Bilbao</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Makhachkala</t>
+          <t>Valencia CF</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -22274,13 +22274,13 @@
         </is>
       </c>
       <c r="P111" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="Q111" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="R111" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="S111" t="n">
         <v>0</v>
@@ -22423,22 +22423,22 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Häcken</t>
+          <t>Young Boys</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Malmö FF</t>
+          <t>Basel</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -22471,13 +22471,13 @@
         </is>
       </c>
       <c r="P112" t="n">
-        <v>2.27</v>
+        <v>1.85</v>
       </c>
       <c r="Q112" t="n">
-        <v>3.58</v>
+        <v>4.05</v>
       </c>
       <c r="R112" t="n">
-        <v>2.88</v>
+        <v>3.57</v>
       </c>
       <c r="S112" t="n">
         <v>0</v>
@@ -22522,10 +22522,10 @@
         <v>0</v>
       </c>
       <c r="AG112" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AH112" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AI112" t="n">
         <v>0</v>
@@ -22620,22 +22620,22 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Sion</t>
+          <t>Häcken</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Thun</t>
+          <t>Malmö FF</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -22668,13 +22668,13 @@
         </is>
       </c>
       <c r="P113" t="n">
-        <v>2.05</v>
+        <v>2.27</v>
       </c>
       <c r="Q113" t="n">
-        <v>3.64</v>
+        <v>3.58</v>
       </c>
       <c r="R113" t="n">
-        <v>3.28</v>
+        <v>2.88</v>
       </c>
       <c r="S113" t="n">
         <v>0</v>
@@ -23014,7 +23014,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -23024,12 +23024,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Young Boys</t>
+          <t>Viktoria Köln</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Basel</t>
+          <t>Alemannia Aachen</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -23062,13 +23062,13 @@
         </is>
       </c>
       <c r="P115" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="Q115" t="n">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="R115" t="n">
-        <v>3.57</v>
+        <v>0</v>
       </c>
       <c r="S115" t="n">
         <v>0</v>
@@ -23113,10 +23113,10 @@
         <v>0</v>
       </c>
       <c r="AG115" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AH115" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AI115" t="n">
         <v>0</v>
@@ -23211,7 +23211,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -23221,12 +23221,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Viktoria Köln</t>
+          <t>Sion</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Alemannia Aachen</t>
+          <t>Thun</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -23259,13 +23259,13 @@
         </is>
       </c>
       <c r="P116" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Q116" t="n">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="R116" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="S116" t="n">
         <v>0</v>
@@ -23615,12 +23615,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Telstar</t>
+          <t>Fortuna Sittard</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Heracles</t>
+          <t>PEC Zwolle</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -23653,13 +23653,13 @@
         </is>
       </c>
       <c r="P118" t="n">
-        <v>1.48</v>
+        <v>1.96</v>
       </c>
       <c r="Q118" t="n">
-        <v>4.94</v>
+        <v>4.05</v>
       </c>
       <c r="R118" t="n">
-        <v>6.07</v>
+        <v>3.5</v>
       </c>
       <c r="S118" t="n">
         <v>0</v>
@@ -23704,10 +23704,10 @@
         <v>0</v>
       </c>
       <c r="AG118" t="n">
-        <v>1.98</v>
+        <v>2.2</v>
       </c>
       <c r="AH118" t="n">
-        <v>1.72</v>
+        <v>1.58</v>
       </c>
       <c r="AI118" t="n">
         <v>0</v>
@@ -23812,12 +23812,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Go Ahead Eagles</t>
+          <t>Feyenoord</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>PSV</t>
+          <t>AZ</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -23850,13 +23850,13 @@
         </is>
       </c>
       <c r="P119" t="n">
-        <v>4.48</v>
+        <v>1.78</v>
       </c>
       <c r="Q119" t="n">
-        <v>4.74</v>
+        <v>4.17</v>
       </c>
       <c r="R119" t="n">
-        <v>1.65</v>
+        <v>4.17</v>
       </c>
       <c r="S119" t="n">
         <v>0</v>
@@ -23901,10 +23901,10 @@
         <v>0</v>
       </c>
       <c r="AG119" t="n">
-        <v>1.68</v>
+        <v>1.9</v>
       </c>
       <c r="AH119" t="n">
-        <v>2.05</v>
+        <v>1.77</v>
       </c>
       <c r="AI119" t="n">
         <v>0</v>
@@ -24009,12 +24009,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Groningen</t>
+          <t>Telstar</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>NEC</t>
+          <t>Heracles</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -24047,13 +24047,13 @@
         </is>
       </c>
       <c r="P120" t="n">
-        <v>2.78</v>
+        <v>1.48</v>
       </c>
       <c r="Q120" t="n">
-        <v>3.89</v>
+        <v>4.94</v>
       </c>
       <c r="R120" t="n">
-        <v>2.36</v>
+        <v>6.07</v>
       </c>
       <c r="S120" t="n">
         <v>0</v>
@@ -24098,10 +24098,10 @@
         <v>0</v>
       </c>
       <c r="AG120" t="n">
-        <v>2.05</v>
+        <v>1.98</v>
       </c>
       <c r="AH120" t="n">
-        <v>1.68</v>
+        <v>1.72</v>
       </c>
       <c r="AI120" t="n">
         <v>0</v>
@@ -24206,12 +24206,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Ajax</t>
+          <t>Excelsior</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Utrecht</t>
+          <t>Volendam</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -24244,13 +24244,13 @@
         </is>
       </c>
       <c r="P121" t="n">
-        <v>1.71</v>
+        <v>1.77</v>
       </c>
       <c r="Q121" t="n">
-        <v>4.37</v>
+        <v>4.17</v>
       </c>
       <c r="R121" t="n">
-        <v>4.42</v>
+        <v>4.22</v>
       </c>
       <c r="S121" t="n">
         <v>0</v>
@@ -24289,16 +24289,16 @@
         <v>0</v>
       </c>
       <c r="AE121" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AF121" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AG121" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AH121" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AI121" t="n">
         <v>0</v>
@@ -24403,12 +24403,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Fortuna Sittard</t>
+          <t>NAC Breda</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>PEC Zwolle</t>
+          <t>Heerenveen</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -24441,13 +24441,13 @@
         </is>
       </c>
       <c r="P122" t="n">
-        <v>1.96</v>
+        <v>2.49</v>
       </c>
       <c r="Q122" t="n">
-        <v>4.05</v>
+        <v>3.77</v>
       </c>
       <c r="R122" t="n">
-        <v>3.5</v>
+        <v>2.67</v>
       </c>
       <c r="S122" t="n">
         <v>0</v>
@@ -24486,16 +24486,16 @@
         <v>0</v>
       </c>
       <c r="AE122" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AF122" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AG122" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AH122" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AI122" t="n">
         <v>0</v>
@@ -24600,12 +24600,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Excelsior</t>
+          <t>Groningen</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Volendam</t>
+          <t>NEC</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -24638,13 +24638,13 @@
         </is>
       </c>
       <c r="P123" t="n">
-        <v>1.77</v>
+        <v>2.78</v>
       </c>
       <c r="Q123" t="n">
-        <v>4.17</v>
+        <v>3.89</v>
       </c>
       <c r="R123" t="n">
-        <v>4.22</v>
+        <v>2.36</v>
       </c>
       <c r="S123" t="n">
         <v>0</v>
@@ -24683,16 +24683,16 @@
         <v>0</v>
       </c>
       <c r="AE123" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AF123" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AG123" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AH123" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AI123" t="n">
         <v>0</v>
@@ -24797,12 +24797,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>NAC Breda</t>
+          <t>Go Ahead Eagles</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Heerenveen</t>
+          <t>PSV</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -24835,13 +24835,13 @@
         </is>
       </c>
       <c r="P124" t="n">
-        <v>2.49</v>
+        <v>4.48</v>
       </c>
       <c r="Q124" t="n">
-        <v>3.77</v>
+        <v>4.74</v>
       </c>
       <c r="R124" t="n">
-        <v>2.67</v>
+        <v>1.65</v>
       </c>
       <c r="S124" t="n">
         <v>0</v>
@@ -24880,16 +24880,16 @@
         <v>0</v>
       </c>
       <c r="AE124" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AF124" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AG124" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AH124" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AI124" t="n">
         <v>0</v>
@@ -24994,12 +24994,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Feyenoord</t>
+          <t>Ajax</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>AZ</t>
+          <t>Utrecht</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -25032,13 +25032,13 @@
         </is>
       </c>
       <c r="P125" t="n">
-        <v>1.78</v>
+        <v>1.71</v>
       </c>
       <c r="Q125" t="n">
-        <v>4.17</v>
+        <v>4.37</v>
       </c>
       <c r="R125" t="n">
-        <v>4.17</v>
+        <v>4.42</v>
       </c>
       <c r="S125" t="n">
         <v>0</v>
@@ -25083,10 +25083,10 @@
         <v>0</v>
       </c>
       <c r="AG125" t="n">
-        <v>1.9</v>
+        <v>2.1</v>
       </c>
       <c r="AH125" t="n">
-        <v>1.77</v>
+        <v>1.65</v>
       </c>
       <c r="AI125" t="n">
         <v>0</v>
@@ -25181,7 +25181,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -25191,12 +25191,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Paphos</t>
+          <t>Makedonija GjP</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Aris</t>
+          <t>Tikveš</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -25378,22 +25378,22 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Mebrat Hayl</t>
+          <t>Strømmen</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Fasil Ketema</t>
+          <t>Hødd</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -25426,13 +25426,13 @@
         </is>
       </c>
       <c r="P127" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Q127" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R127" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="S127" t="n">
         <v>0</v>
@@ -25575,22 +25575,22 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Pogoń Siedlce</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Stal Rzeszów</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -25623,13 +25623,13 @@
         </is>
       </c>
       <c r="P128" t="n">
-        <v>2.55</v>
+        <v>2.65</v>
       </c>
       <c r="Q128" t="n">
         <v>3.6</v>
       </c>
       <c r="R128" t="n">
-        <v>2.43</v>
+        <v>2.4</v>
       </c>
       <c r="S128" t="n">
         <v>0</v>
@@ -25772,22 +25772,22 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Ajka</t>
+          <t>Sandnes Ulf</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Szeged 2011</t>
+          <t>Stabæk</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -25820,13 +25820,13 @@
         </is>
       </c>
       <c r="P129" t="n">
-        <v>0</v>
+        <v>4.07</v>
       </c>
       <c r="Q129" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="R129" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="S129" t="n">
         <v>0</v>
@@ -25969,22 +25969,22 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Rapid Wien</t>
+          <t>Moss</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Austria Wien</t>
+          <t>Bryne</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -26017,13 +26017,13 @@
         </is>
       </c>
       <c r="P130" t="n">
-        <v>2.3</v>
+        <v>2.15</v>
       </c>
       <c r="Q130" t="n">
-        <v>3.35</v>
+        <v>3.7</v>
       </c>
       <c r="R130" t="n">
-        <v>2.96</v>
+        <v>3.01</v>
       </c>
       <c r="S130" t="n">
         <v>0</v>
@@ -26166,7 +26166,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -26176,12 +26176,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Tromsø</t>
+          <t>Åsane</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Molde</t>
+          <t>Strømsgodset</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -26214,13 +26214,13 @@
         </is>
       </c>
       <c r="P131" t="n">
-        <v>1.84</v>
+        <v>5.4</v>
       </c>
       <c r="Q131" t="n">
-        <v>3.82</v>
+        <v>4.6</v>
       </c>
       <c r="R131" t="n">
-        <v>4.13</v>
+        <v>1.51</v>
       </c>
       <c r="S131" t="n">
         <v>0</v>
@@ -26363,22 +26363,22 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Hartberg</t>
+          <t>Sogndal</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Sturm Graz</t>
+          <t>Haugesund</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -26411,13 +26411,13 @@
         </is>
       </c>
       <c r="P132" t="n">
-        <v>3.75</v>
+        <v>3.1</v>
       </c>
       <c r="Q132" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="R132" t="n">
-        <v>1.91</v>
+        <v>2.12</v>
       </c>
       <c r="S132" t="n">
         <v>0</v>
@@ -26456,10 +26456,10 @@
         <v>0</v>
       </c>
       <c r="AE132" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AF132" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AG132" t="n">
         <v>0</v>
@@ -26560,7 +26560,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -26570,12 +26570,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>LASK Linz</t>
+          <t>Pelister</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Salzburg</t>
+          <t>Shkupi</t>
         </is>
       </c>
       <c r="G133" t="n">
@@ -26608,13 +26608,13 @@
         </is>
       </c>
       <c r="P133" t="n">
-        <v>2.51</v>
+        <v>0</v>
       </c>
       <c r="Q133" t="n">
-        <v>3.78</v>
+        <v>0</v>
       </c>
       <c r="R133" t="n">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="S133" t="n">
         <v>0</v>
@@ -26767,12 +26767,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Sandefjord</t>
+          <t>Tromsø</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Kristiansund</t>
+          <t>Molde</t>
         </is>
       </c>
       <c r="G134" t="n">
@@ -26805,13 +26805,13 @@
         </is>
       </c>
       <c r="P134" t="n">
-        <v>1.59</v>
+        <v>1.84</v>
       </c>
       <c r="Q134" t="n">
-        <v>4.44</v>
+        <v>3.82</v>
       </c>
       <c r="R134" t="n">
-        <v>5.16</v>
+        <v>4.13</v>
       </c>
       <c r="S134" t="n">
         <v>0</v>
@@ -26954,22 +26954,22 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>KFUM</t>
+          <t>Real Madrid W</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Viking</t>
+          <t>Atletico Madrid W</t>
         </is>
       </c>
       <c r="G135" t="n">
@@ -27002,13 +27002,13 @@
         </is>
       </c>
       <c r="P135" t="n">
-        <v>3.87</v>
+        <v>0</v>
       </c>
       <c r="Q135" t="n">
-        <v>3.87</v>
+        <v>0</v>
       </c>
       <c r="R135" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="S135" t="n">
         <v>0</v>
@@ -27151,7 +27151,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -27161,12 +27161,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Budafoki MTE</t>
+          <t>LASK Linz</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>BVSC</t>
+          <t>Salzburg</t>
         </is>
       </c>
       <c r="G136" t="n">
@@ -27199,13 +27199,13 @@
         </is>
       </c>
       <c r="P136" t="n">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="Q136" t="n">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="R136" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="S136" t="n">
         <v>0</v>
@@ -27348,7 +27348,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -27358,12 +27358,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Karcag SE</t>
+          <t>Hartberg</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Tiszakécske</t>
+          <t>Sturm Graz</t>
         </is>
       </c>
       <c r="G137" t="n">
@@ -27396,13 +27396,13 @@
         </is>
       </c>
       <c r="P137" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="Q137" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R137" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="S137" t="n">
         <v>0</v>
@@ -27441,10 +27441,10 @@
         <v>0</v>
       </c>
       <c r="AE137" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AF137" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG137" t="n">
         <v>0</v>
@@ -27545,7 +27545,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -27555,12 +27555,12 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Kecskeméti TE</t>
+          <t>Zbrojovka Brno</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Mezőkövesd-Zsóry</t>
+          <t>Vlašim</t>
         </is>
       </c>
       <c r="G138" t="n">
@@ -27742,7 +27742,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -27752,12 +27752,12 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Omonia Nicosia</t>
+          <t>Akademija Pandev</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>AEK Larnaca</t>
+          <t>Rabotnički</t>
         </is>
       </c>
       <c r="G139" t="n">
@@ -27939,7 +27939,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -27949,12 +27949,12 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Szentlőrinc SE</t>
+          <t>Pogoń Siedlce</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Videoton</t>
+          <t>Stal Rzeszów</t>
         </is>
       </c>
       <c r="G140" t="n">
@@ -27987,13 +27987,13 @@
         </is>
       </c>
       <c r="P140" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="Q140" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R140" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="S140" t="n">
         <v>0</v>
@@ -28136,7 +28136,7 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -28146,12 +28146,12 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Aresimi</t>
+          <t>Apollon</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>FK Bashkimi Kumanovo</t>
+          <t>APOEL</t>
         </is>
       </c>
       <c r="G141" t="n">
@@ -28333,22 +28333,22 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Sogndal</t>
+          <t>Croatia Zmijavci</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Haugesund</t>
+          <t>Jarun</t>
         </is>
       </c>
       <c r="G142" t="n">
@@ -28381,13 +28381,13 @@
         </is>
       </c>
       <c r="P142" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="Q142" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="R142" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="S142" t="n">
         <v>0</v>
@@ -28530,22 +28530,22 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Åsane</t>
+          <t>Paphos</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Strømsgodset</t>
+          <t>Aris</t>
         </is>
       </c>
       <c r="G143" t="n">
@@ -28578,13 +28578,13 @@
         </is>
       </c>
       <c r="P143" t="n">
-        <v>5.4</v>
+        <v>0</v>
       </c>
       <c r="Q143" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="R143" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="S143" t="n">
         <v>0</v>
@@ -28727,7 +28727,7 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -28737,12 +28737,12 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Zbrojovka Brno</t>
+          <t>Aresimi</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Vlašim</t>
+          <t>FK Bashkimi Kumanovo</t>
         </is>
       </c>
       <c r="G144" t="n">
@@ -28924,7 +28924,7 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -28934,12 +28934,12 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Sandnes Ulf</t>
+          <t>KFUM</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Stabæk</t>
+          <t>Viking</t>
         </is>
       </c>
       <c r="G145" t="n">
@@ -28972,13 +28972,13 @@
         </is>
       </c>
       <c r="P145" t="n">
-        <v>4.07</v>
+        <v>3.87</v>
       </c>
       <c r="Q145" t="n">
-        <v>3.9</v>
+        <v>3.87</v>
       </c>
       <c r="R145" t="n">
-        <v>1.78</v>
+        <v>1.89</v>
       </c>
       <c r="S145" t="n">
         <v>0</v>
@@ -29121,7 +29121,7 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -29131,12 +29131,12 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Saburtalo</t>
+          <t>Sandefjord</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Torpedo Kutaisi</t>
+          <t>Kristiansund</t>
         </is>
       </c>
       <c r="G146" t="n">
@@ -29169,13 +29169,13 @@
         </is>
       </c>
       <c r="P146" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="Q146" t="n">
-        <v>0</v>
+        <v>4.44</v>
       </c>
       <c r="R146" t="n">
-        <v>0</v>
+        <v>5.16</v>
       </c>
       <c r="S146" t="n">
         <v>0</v>
@@ -29318,7 +29318,7 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
@@ -29328,12 +29328,12 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Vardar</t>
+          <t>Rapid Wien</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Sileks</t>
+          <t>Austria Wien</t>
         </is>
       </c>
       <c r="G147" t="n">
@@ -29366,13 +29366,13 @@
         </is>
       </c>
       <c r="P147" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Q147" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="R147" t="n">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="S147" t="n">
         <v>0</v>
@@ -29515,7 +29515,7 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
@@ -29525,12 +29525,12 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Shkendija</t>
+          <t>Omonia Nicosia</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Struga</t>
+          <t>AEK Larnaca</t>
         </is>
       </c>
       <c r="G148" t="n">
@@ -29712,7 +29712,7 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
@@ -29722,12 +29722,12 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Makedonija GjP</t>
+          <t>Szentlőrinc SE</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Tikveš</t>
+          <t>Videoton</t>
         </is>
       </c>
       <c r="G149" t="n">
@@ -29909,7 +29909,7 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
@@ -29919,12 +29919,12 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Pelister</t>
+          <t>Karcag SE</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Shkupi</t>
+          <t>Tiszakécske</t>
         </is>
       </c>
       <c r="G150" t="n">
@@ -30106,22 +30106,22 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Moss</t>
+          <t>Vardar</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Bryne</t>
+          <t>Sileks</t>
         </is>
       </c>
       <c r="G151" t="n">
@@ -30154,13 +30154,13 @@
         </is>
       </c>
       <c r="P151" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Q151" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="R151" t="n">
-        <v>3.01</v>
+        <v>0</v>
       </c>
       <c r="S151" t="n">
         <v>0</v>
@@ -30303,7 +30303,7 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
@@ -30313,12 +30313,12 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Akademija Pandev</t>
+          <t>Mebrat Hayl</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Rabotnički</t>
+          <t>Fasil Ketema</t>
         </is>
       </c>
       <c r="G152" t="n">
@@ -30500,7 +30500,7 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
@@ -30510,12 +30510,12 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Real Madrid W</t>
+          <t>Ajka</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Atletico Madrid W</t>
+          <t>Szeged 2011</t>
         </is>
       </c>
       <c r="G153" t="n">
@@ -30697,7 +30697,7 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
@@ -30707,12 +30707,12 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Apollon</t>
+          <t>Budafoki MTE</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>APOEL</t>
+          <t>BVSC</t>
         </is>
       </c>
       <c r="G154" t="n">
@@ -30894,7 +30894,7 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
@@ -30904,12 +30904,12 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Croatia Zmijavci</t>
+          <t>Kecskeméti TE</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Jarun</t>
+          <t>Mezőkövesd-Zsóry</t>
         </is>
       </c>
       <c r="G155" t="n">
@@ -31091,7 +31091,7 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
@@ -31101,12 +31101,12 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Strømmen</t>
+          <t>Saburtalo</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Hødd</t>
+          <t>Torpedo Kutaisi</t>
         </is>
       </c>
       <c r="G156" t="n">
@@ -31139,13 +31139,13 @@
         </is>
       </c>
       <c r="P156" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Q156" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="R156" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="S156" t="n">
         <v>0</v>
@@ -31288,22 +31288,22 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Shkendija</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Struga</t>
         </is>
       </c>
       <c r="G157" t="n">
@@ -31336,13 +31336,13 @@
         </is>
       </c>
       <c r="P157" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="Q157" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R157" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="S157" t="n">
         <v>0</v>
@@ -32273,7 +32273,7 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
@@ -32283,12 +32283,12 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>Köln</t>
+          <t>Neftçi</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Heidenheim</t>
+          <t>İnter Bakı</t>
         </is>
       </c>
       <c r="G162" t="n">
@@ -32321,13 +32321,13 @@
         </is>
       </c>
       <c r="P162" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="Q162" t="n">
-        <v>4.32</v>
+        <v>0</v>
       </c>
       <c r="R162" t="n">
-        <v>4.52</v>
+        <v>0</v>
       </c>
       <c r="S162" t="n">
         <v>0</v>
@@ -32372,10 +32372,10 @@
         <v>0</v>
       </c>
       <c r="AG162" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AH162" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AI162" t="n">
         <v>0</v>
@@ -32470,7 +32470,7 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
@@ -32480,12 +32480,12 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>Nieciecza</t>
+          <t>Köln</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Legia Warszawa</t>
+          <t>Heidenheim</t>
         </is>
       </c>
       <c r="G163" t="n">
@@ -32518,13 +32518,13 @@
         </is>
       </c>
       <c r="P163" t="n">
-        <v>4.09</v>
+        <v>1.78</v>
       </c>
       <c r="Q163" t="n">
-        <v>3.78</v>
+        <v>4.32</v>
       </c>
       <c r="R163" t="n">
-        <v>1.77</v>
+        <v>4.52</v>
       </c>
       <c r="S163" t="n">
         <v>0</v>
@@ -32569,10 +32569,10 @@
         <v>0</v>
       </c>
       <c r="AG163" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AH163" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AI163" t="n">
         <v>0</v>
@@ -32667,7 +32667,7 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
@@ -32677,12 +32677,12 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>Sekhukhune United</t>
+          <t>West Ham United</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Kaizer Chiefs</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="G164" t="n">
@@ -32715,13 +32715,13 @@
         </is>
       </c>
       <c r="P164" t="n">
-        <v>0</v>
+        <v>5.17</v>
       </c>
       <c r="Q164" t="n">
-        <v>0</v>
+        <v>4.37</v>
       </c>
       <c r="R164" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="S164" t="n">
         <v>0</v>
@@ -32760,10 +32760,10 @@
         <v>0</v>
       </c>
       <c r="AE164" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AF164" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AG164" t="n">
         <v>0</v>
@@ -32864,7 +32864,7 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
@@ -32874,12 +32874,12 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>Neftçi</t>
+          <t>Sekhukhune United</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>İnter Bakı</t>
+          <t>Kaizer Chiefs</t>
         </is>
       </c>
       <c r="G165" t="n">
@@ -33061,7 +33061,7 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
@@ -33071,12 +33071,12 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>West Ham United</t>
+          <t>Nieciecza</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Legia Warszawa</t>
         </is>
       </c>
       <c r="G166" t="n">
@@ -33109,13 +33109,13 @@
         </is>
       </c>
       <c r="P166" t="n">
-        <v>5.17</v>
+        <v>4.09</v>
       </c>
       <c r="Q166" t="n">
-        <v>4.37</v>
+        <v>3.78</v>
       </c>
       <c r="R166" t="n">
-        <v>1.69</v>
+        <v>1.77</v>
       </c>
       <c r="S166" t="n">
         <v>0</v>
@@ -33154,10 +33154,10 @@
         <v>0</v>
       </c>
       <c r="AE166" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AF166" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AG166" t="n">
         <v>0</v>
@@ -33258,22 +33258,22 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>Arsenal Tivat</t>
+          <t>Panevėžys</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Sutjeska</t>
+          <t>Kauno Žalgiris</t>
         </is>
       </c>
       <c r="G167" t="n">
@@ -33455,22 +33455,22 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>Panevėžys</t>
+          <t>Brøndby</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Kauno Žalgiris</t>
+          <t>AGF</t>
         </is>
       </c>
       <c r="G168" t="n">
@@ -33662,12 +33662,12 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>Dečić</t>
+          <t>Arsenal Tivat</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>FK Jezero Plav</t>
+          <t>Sutjeska</t>
         </is>
       </c>
       <c r="G169" t="n">
@@ -33849,7 +33849,7 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
@@ -33859,12 +33859,12 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>Dinamo Bucureşti</t>
+          <t>Parma</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Argeș</t>
+          <t>Roma</t>
         </is>
       </c>
       <c r="G170" t="n">
@@ -33897,13 +33897,13 @@
         </is>
       </c>
       <c r="P170" t="n">
-        <v>1.83</v>
+        <v>5</v>
       </c>
       <c r="Q170" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="R170" t="n">
-        <v>4.3</v>
+        <v>1.75</v>
       </c>
       <c r="S170" t="n">
         <v>0</v>
@@ -34056,12 +34056,12 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>Mornar</t>
+          <t>Dečić</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Bokelj</t>
+          <t>FK Jezero Plav</t>
         </is>
       </c>
       <c r="G171" t="n">
@@ -34243,7 +34243,7 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
@@ -34253,12 +34253,12 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>Jedinstvo</t>
+          <t>Dinamo Bucureşti</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Budućnost</t>
+          <t>Argeș</t>
         </is>
       </c>
       <c r="G172" t="n">
@@ -34291,13 +34291,13 @@
         </is>
       </c>
       <c r="P172" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="Q172" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R172" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="S172" t="n">
         <v>0</v>
@@ -34440,7 +34440,7 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
@@ -34450,12 +34450,12 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>Mladost DG</t>
+          <t>Ittihad Tanger</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Petrovac</t>
+          <t>Difaâ El Jadida</t>
         </is>
       </c>
       <c r="G173" t="n">
@@ -34834,7 +34834,7 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
@@ -34844,12 +34844,12 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>Ittihad Tanger</t>
+          <t>Jedinstvo</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Difaâ El Jadida</t>
+          <t>Budućnost</t>
         </is>
       </c>
       <c r="G175" t="n">
@@ -35031,7 +35031,7 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
@@ -35041,12 +35041,12 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>Brøndby</t>
+          <t>Mladost DG</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>AGF</t>
+          <t>Petrovac</t>
         </is>
       </c>
       <c r="G176" t="n">
@@ -35228,7 +35228,7 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
@@ -35238,12 +35238,12 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>Parma</t>
+          <t>Mornar</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Roma</t>
+          <t>Bokelj</t>
         </is>
       </c>
       <c r="G177" t="n">
@@ -35276,13 +35276,13 @@
         </is>
       </c>
       <c r="P177" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="Q177" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="R177" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="S177" t="n">
         <v>0</v>
@@ -35622,22 +35622,22 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>Dobrudzha 1919</t>
+          <t>Skála</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Beroe</t>
+          <t>AB</t>
         </is>
       </c>
       <c r="G179" t="n">
@@ -35670,13 +35670,13 @@
         </is>
       </c>
       <c r="P179" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="Q179" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="R179" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="S179" t="n">
         <v>0</v>
@@ -35819,22 +35819,22 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>07 Vestur</t>
+          <t>Slaven Koprivnica</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>B68</t>
+          <t>Gorica</t>
         </is>
       </c>
       <c r="G180" t="n">
@@ -36026,12 +36026,12 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>Skála</t>
+          <t>07 Vestur</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>AB</t>
+          <t>B68</t>
         </is>
       </c>
       <c r="G181" t="n">
@@ -36213,7 +36213,7 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
@@ -36223,12 +36223,12 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>Slaven Koprivnica</t>
+          <t>Dobrudzha 1919</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Gorica</t>
+          <t>Beroe</t>
         </is>
       </c>
       <c r="G182" t="n">
@@ -36261,13 +36261,13 @@
         </is>
       </c>
       <c r="P182" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="Q182" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R182" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="S182" t="n">
         <v>0</v>
@@ -36410,7 +36410,7 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
@@ -36420,12 +36420,12 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>Córdoba</t>
+          <t>Union Saint-Gilloise</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Granada CF</t>
+          <t>KV Mechelen</t>
         </is>
       </c>
       <c r="G183" t="n">
@@ -36458,13 +36458,13 @@
         </is>
       </c>
       <c r="P183" t="n">
-        <v>1.91</v>
+        <v>1.28</v>
       </c>
       <c r="Q183" t="n">
-        <v>3.53</v>
+        <v>5.66</v>
       </c>
       <c r="R183" t="n">
-        <v>3.91</v>
+        <v>8.98</v>
       </c>
       <c r="S183" t="n">
         <v>0</v>
@@ -36503,10 +36503,10 @@
         <v>0</v>
       </c>
       <c r="AE183" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AF183" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AG183" t="n">
         <v>0</v>
@@ -36607,7 +36607,7 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
@@ -36617,12 +36617,12 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>IMT Novi Beograd</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>Granada CF</t>
         </is>
       </c>
       <c r="G184" t="n">
@@ -36655,13 +36655,13 @@
         </is>
       </c>
       <c r="P184" t="n">
-        <v>2.15</v>
+        <v>1.91</v>
       </c>
       <c r="Q184" t="n">
-        <v>3.3</v>
+        <v>3.53</v>
       </c>
       <c r="R184" t="n">
-        <v>3.25</v>
+        <v>3.91</v>
       </c>
       <c r="S184" t="n">
         <v>0</v>
@@ -36700,10 +36700,10 @@
         <v>0</v>
       </c>
       <c r="AE184" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AF184" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AG184" t="n">
         <v>0</v>
@@ -36804,7 +36804,7 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
@@ -36814,12 +36814,12 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>Jablonec</t>
+          <t>AEK Athens</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Hradec Králové</t>
+          <t>Panathinaikos</t>
         </is>
       </c>
       <c r="G185" t="n">
@@ -36852,13 +36852,13 @@
         </is>
       </c>
       <c r="P185" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="Q185" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="R185" t="n">
-        <v>0</v>
+        <v>6.76</v>
       </c>
       <c r="S185" t="n">
         <v>0</v>
@@ -37011,12 +37011,12 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>Spartak Subotica</t>
+          <t>Bačka Topola</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Napredak</t>
+          <t>Javor Ivanjica</t>
         </is>
       </c>
       <c r="G186" t="n">
@@ -37049,13 +37049,13 @@
         </is>
       </c>
       <c r="P186" t="n">
-        <v>1.55</v>
+        <v>1.51</v>
       </c>
       <c r="Q186" t="n">
-        <v>3.95</v>
+        <v>3.8</v>
       </c>
       <c r="R186" t="n">
-        <v>4.96</v>
+        <v>5.75</v>
       </c>
       <c r="S186" t="n">
         <v>0</v>
@@ -37094,10 +37094,10 @@
         <v>0</v>
       </c>
       <c r="AE186" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AF186" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG186" t="n">
         <v>0</v>
@@ -37198,22 +37198,22 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>Radnički Niš</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>LFK Mladost Lučani</t>
+          <t>San Luis</t>
         </is>
       </c>
       <c r="G187" t="n">
@@ -37246,13 +37246,13 @@
         </is>
       </c>
       <c r="P187" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="Q187" t="n">
-        <v>3.54</v>
+        <v>0</v>
       </c>
       <c r="R187" t="n">
-        <v>4.32</v>
+        <v>0</v>
       </c>
       <c r="S187" t="n">
         <v>0</v>
@@ -37291,10 +37291,10 @@
         <v>0</v>
       </c>
       <c r="AE187" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AF187" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AG187" t="n">
         <v>0</v>
@@ -37395,22 +37395,22 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>Mirandés</t>
+          <t>Copiapó</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>SD Eibar</t>
+          <t>Unión San Felipe</t>
         </is>
       </c>
       <c r="G188" t="n">
@@ -37443,13 +37443,13 @@
         </is>
       </c>
       <c r="P188" t="n">
-        <v>3.12</v>
+        <v>0</v>
       </c>
       <c r="Q188" t="n">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="R188" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="S188" t="n">
         <v>0</v>
@@ -37789,7 +37789,7 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
@@ -37799,12 +37799,12 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>Lokomotiv Moskva</t>
+          <t>Mirandés</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Baltika</t>
+          <t>SD Eibar</t>
         </is>
       </c>
       <c r="G190" t="n">
@@ -37837,13 +37837,13 @@
         </is>
       </c>
       <c r="P190" t="n">
-        <v>2.25</v>
+        <v>3.12</v>
       </c>
       <c r="Q190" t="n">
-        <v>3.66</v>
+        <v>3.22</v>
       </c>
       <c r="R190" t="n">
-        <v>3.36</v>
+        <v>2.43</v>
       </c>
       <c r="S190" t="n">
         <v>0</v>
@@ -38183,22 +38183,22 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>Kansas City</t>
+          <t>IMT Novi Beograd</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Chicago Red Stars</t>
+          <t>Radnički Kragujevac</t>
         </is>
       </c>
       <c r="G192" t="n">
@@ -38231,13 +38231,13 @@
         </is>
       </c>
       <c r="P192" t="n">
-        <v>1.3</v>
+        <v>2.15</v>
       </c>
       <c r="Q192" t="n">
-        <v>5.1</v>
+        <v>3.3</v>
       </c>
       <c r="R192" t="n">
-        <v>7.95</v>
+        <v>3.25</v>
       </c>
       <c r="S192" t="n">
         <v>0</v>
@@ -38380,22 +38380,22 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>Copiapó</t>
+          <t>Jablonec</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Unión San Felipe</t>
+          <t>Hradec Králové</t>
         </is>
       </c>
       <c r="G193" t="n">
@@ -38577,7 +38577,7 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
@@ -38587,12 +38587,12 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>Union Saint-Gilloise</t>
+          <t>Lokomotiv Moskva</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>KV Mechelen</t>
+          <t>Baltika</t>
         </is>
       </c>
       <c r="G194" t="n">
@@ -38625,13 +38625,13 @@
         </is>
       </c>
       <c r="P194" t="n">
-        <v>1.28</v>
+        <v>2.25</v>
       </c>
       <c r="Q194" t="n">
-        <v>5.66</v>
+        <v>3.66</v>
       </c>
       <c r="R194" t="n">
-        <v>8.98</v>
+        <v>3.36</v>
       </c>
       <c r="S194" t="n">
         <v>0</v>
@@ -38774,22 +38774,22 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Radnički Niš</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>San Luis</t>
+          <t>LFK Mladost Lučani</t>
         </is>
       </c>
       <c r="G195" t="n">
@@ -38822,13 +38822,13 @@
         </is>
       </c>
       <c r="P195" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="Q195" t="n">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="R195" t="n">
-        <v>0</v>
+        <v>4.32</v>
       </c>
       <c r="S195" t="n">
         <v>0</v>
@@ -38867,10 +38867,10 @@
         <v>0</v>
       </c>
       <c r="AE195" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AF195" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG195" t="n">
         <v>0</v>
@@ -38981,12 +38981,12 @@
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>Bačka Topola</t>
+          <t>Spartak Subotica</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Javor Ivanjica</t>
+          <t>Napredak</t>
         </is>
       </c>
       <c r="G196" t="n">
@@ -39019,13 +39019,13 @@
         </is>
       </c>
       <c r="P196" t="n">
-        <v>1.51</v>
+        <v>1.55</v>
       </c>
       <c r="Q196" t="n">
-        <v>3.8</v>
+        <v>3.95</v>
       </c>
       <c r="R196" t="n">
-        <v>5.75</v>
+        <v>4.96</v>
       </c>
       <c r="S196" t="n">
         <v>0</v>
@@ -39064,10 +39064,10 @@
         <v>0</v>
       </c>
       <c r="AE196" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AF196" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AG196" t="n">
         <v>0</v>
@@ -39168,22 +39168,22 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>AEK Athens</t>
+          <t>Kansas City</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Panathinaikos</t>
+          <t>Chicago Red Stars</t>
         </is>
       </c>
       <c r="G197" t="n">
@@ -39216,13 +39216,13 @@
         </is>
       </c>
       <c r="P197" t="n">
-        <v>1.45</v>
+        <v>1.3</v>
       </c>
       <c r="Q197" t="n">
-        <v>3.8</v>
+        <v>5.1</v>
       </c>
       <c r="R197" t="n">
-        <v>6.76</v>
+        <v>7.95</v>
       </c>
       <c r="S197" t="n">
         <v>0</v>
@@ -39365,22 +39365,22 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>KA</t>
+          <t>Hapoel Haifa</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>ÍBV</t>
+          <t>Ashdod</t>
         </is>
       </c>
       <c r="G198" t="n">
@@ -39413,13 +39413,13 @@
         </is>
       </c>
       <c r="P198" t="n">
-        <v>1.53</v>
+        <v>2.25</v>
       </c>
       <c r="Q198" t="n">
-        <v>4.45</v>
+        <v>3.38</v>
       </c>
       <c r="R198" t="n">
-        <v>5.12</v>
+        <v>3</v>
       </c>
       <c r="S198" t="n">
         <v>0</v>
@@ -39562,7 +39562,7 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
@@ -39572,12 +39572,12 @@
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>Dinamo Batumi</t>
+          <t>KA</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>Samgurali</t>
+          <t>ÍBV</t>
         </is>
       </c>
       <c r="G199" t="n">
@@ -39610,13 +39610,13 @@
         </is>
       </c>
       <c r="P199" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="Q199" t="n">
-        <v>0</v>
+        <v>4.45</v>
       </c>
       <c r="R199" t="n">
-        <v>0</v>
+        <v>5.12</v>
       </c>
       <c r="S199" t="n">
         <v>0</v>
@@ -39759,7 +39759,7 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
@@ -39769,12 +39769,12 @@
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>Hapoel Haifa</t>
+          <t>Tenerife W</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Ashdod</t>
+          <t>Barcelona W</t>
         </is>
       </c>
       <c r="G200" t="n">
@@ -39807,13 +39807,13 @@
         </is>
       </c>
       <c r="P200" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Q200" t="n">
-        <v>3.38</v>
+        <v>0</v>
       </c>
       <c r="R200" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="S200" t="n">
         <v>0</v>
@@ -40153,7 +40153,7 @@
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
@@ -40163,12 +40163,12 @@
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>Tenerife W</t>
+          <t>Ironi Tiberias</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>Barcelona W</t>
+          <t>Maccabi Netanya</t>
         </is>
       </c>
       <c r="G202" t="n">
@@ -40350,7 +40350,7 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
@@ -40360,12 +40360,12 @@
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>Ironi Tiberias</t>
+          <t>Csákvári TK</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>Maccabi Netanya</t>
+          <t>Soroksár SC</t>
         </is>
       </c>
       <c r="G203" t="n">
@@ -40744,22 +40744,22 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Dinamo Batumi</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Samgurali</t>
         </is>
       </c>
       <c r="G205" t="n">
@@ -40792,13 +40792,13 @@
         </is>
       </c>
       <c r="P205" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Q205" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="R205" t="n">
-        <v>3.13</v>
+        <v>0</v>
       </c>
       <c r="S205" t="n">
         <v>0</v>
@@ -40837,10 +40837,10 @@
         <v>0</v>
       </c>
       <c r="AE205" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AF205" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AG205" t="n">
         <v>0</v>
@@ -40941,7 +40941,7 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
@@ -40951,12 +40951,12 @@
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>Csákvári TK</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>Soroksár SC</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="G206" t="n">
@@ -40989,13 +40989,13 @@
         </is>
       </c>
       <c r="P206" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Q206" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R206" t="n">
-        <v>0</v>
+        <v>3.13</v>
       </c>
       <c r="S206" t="n">
         <v>0</v>
@@ -41034,10 +41034,10 @@
         <v>0</v>
       </c>
       <c r="AE206" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AF206" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AG206" t="n">
         <v>0</v>
@@ -41335,7 +41335,7 @@
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
@@ -41345,12 +41345,12 @@
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>Hoffenheim II</t>
+          <t>Mainz 05</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>Saarbrucken</t>
+          <t>Union Berlin</t>
         </is>
       </c>
       <c r="G208" t="n">
@@ -41383,13 +41383,13 @@
         </is>
       </c>
       <c r="P208" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="Q208" t="n">
-        <v>0</v>
+        <v>3.94</v>
       </c>
       <c r="R208" t="n">
-        <v>0</v>
+        <v>4.41</v>
       </c>
       <c r="S208" t="n">
         <v>0</v>
@@ -41428,10 +41428,10 @@
         <v>0</v>
       </c>
       <c r="AE208" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AF208" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AG208" t="n">
         <v>0</v>
@@ -41532,7 +41532,7 @@
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
@@ -41542,12 +41542,12 @@
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>Mainz 05</t>
+          <t>Hoffenheim II</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>Union Berlin</t>
+          <t>Saarbrucken</t>
         </is>
       </c>
       <c r="G209" t="n">
@@ -41580,13 +41580,13 @@
         </is>
       </c>
       <c r="P209" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="Q209" t="n">
-        <v>3.94</v>
+        <v>0</v>
       </c>
       <c r="R209" t="n">
-        <v>4.41</v>
+        <v>0</v>
       </c>
       <c r="S209" t="n">
         <v>0</v>
@@ -41625,10 +41625,10 @@
         <v>0</v>
       </c>
       <c r="AE209" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AF209" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AG209" t="n">
         <v>0</v>
@@ -41729,22 +41729,22 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>New England II</t>
+          <t>UTS Rabat</t>
         </is>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>New York City II</t>
+          <t>Maghreb Fès</t>
         </is>
       </c>
       <c r="G210" t="n">
@@ -42123,22 +42123,22 @@
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>New England II</t>
         </is>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>Dhamk</t>
+          <t>New York City II</t>
         </is>
       </c>
       <c r="G212" t="n">
@@ -42320,7 +42320,7 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
@@ -42330,12 +42330,12 @@
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>UTS Rabat</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>Maghreb Fès</t>
+          <t>Dhamk</t>
         </is>
       </c>
       <c r="G213" t="n">
@@ -42762,13 +42762,13 @@
         </is>
       </c>
       <c r="P215" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="Q215" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="R215" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="S215" t="n">
         <v>0</v>
@@ -42801,10 +42801,10 @@
         <v>0</v>
       </c>
       <c r="AC215" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AD215" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AE215" t="n">
         <v>0</v>
@@ -43108,22 +43108,22 @@
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>Atlético Mineiro</t>
+          <t>FC Barcelona</t>
         </is>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>Botafogo</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="G217" t="n">
@@ -43156,13 +43156,13 @@
         </is>
       </c>
       <c r="P217" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Q217" t="n">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="R217" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="S217" t="n">
         <v>0</v>
@@ -43201,10 +43201,10 @@
         <v>0</v>
       </c>
       <c r="AE217" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AF217" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AG217" t="n">
         <v>0</v>
@@ -43305,22 +43305,22 @@
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>Angers SCO</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>Strasbourg</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="G218" t="n">
@@ -43353,13 +43353,13 @@
         </is>
       </c>
       <c r="P218" t="n">
-        <v>4.05</v>
+        <v>2.35</v>
       </c>
       <c r="Q218" t="n">
-        <v>3.76</v>
+        <v>2.9</v>
       </c>
       <c r="R218" t="n">
-        <v>1.99</v>
+        <v>3.04</v>
       </c>
       <c r="S218" t="n">
         <v>0</v>
@@ -43392,16 +43392,16 @@
         <v>0</v>
       </c>
       <c r="AC218" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AD218" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AE218" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AF218" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AG218" t="n">
         <v>0</v>
@@ -43502,22 +43502,22 @@
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>Club Atlético Güemes</t>
+          <t>Toulouse</t>
         </is>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>Quilmes</t>
+          <t>Olympique Lyonnais</t>
         </is>
       </c>
       <c r="G219" t="n">
@@ -43550,13 +43550,13 @@
         </is>
       </c>
       <c r="P219" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="Q219" t="n">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="R219" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="S219" t="n">
         <v>0</v>
@@ -43595,10 +43595,10 @@
         <v>0</v>
       </c>
       <c r="AE219" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AF219" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AG219" t="n">
         <v>0</v>
@@ -43709,12 +43709,12 @@
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>Toulouse</t>
+          <t>Rennes</t>
         </is>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>Olympique Lyonnais</t>
+          <t>Paris</t>
         </is>
       </c>
       <c r="G220" t="n">
@@ -43747,13 +43747,13 @@
         </is>
       </c>
       <c r="P220" t="n">
-        <v>3.8</v>
+        <v>1.59</v>
       </c>
       <c r="Q220" t="n">
-        <v>3.78</v>
+        <v>4.73</v>
       </c>
       <c r="R220" t="n">
-        <v>2.05</v>
+        <v>5.79</v>
       </c>
       <c r="S220" t="n">
         <v>0</v>
@@ -43792,16 +43792,16 @@
         <v>0</v>
       </c>
       <c r="AE220" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AF220" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AG220" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AH220" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AI220" t="n">
         <v>0</v>
@@ -43896,22 +43896,22 @@
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>Independiente Petrolero</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>Club Always Ready</t>
+          <t>Brest</t>
         </is>
       </c>
       <c r="G221" t="n">
@@ -43944,13 +43944,13 @@
         </is>
       </c>
       <c r="P221" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Q221" t="n">
-        <v>0</v>
+        <v>9.15</v>
       </c>
       <c r="R221" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="S221" t="n">
         <v>0</v>
@@ -43995,10 +43995,10 @@
         <v>0</v>
       </c>
       <c r="AG221" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AH221" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AI221" t="n">
         <v>0</v>
@@ -44487,7 +44487,7 @@
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
@@ -44497,12 +44497,12 @@
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>Remo</t>
+          <t>Club Atlético Güemes</t>
         </is>
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>Quilmes</t>
         </is>
       </c>
       <c r="G224" t="n">
@@ -44535,13 +44535,13 @@
         </is>
       </c>
       <c r="P224" t="n">
-        <v>5.3</v>
+        <v>2.61</v>
       </c>
       <c r="Q224" t="n">
-        <v>3.73</v>
+        <v>2.74</v>
       </c>
       <c r="R224" t="n">
-        <v>1.71</v>
+        <v>2.76</v>
       </c>
       <c r="S224" t="n">
         <v>0</v>
@@ -44574,16 +44574,16 @@
         <v>0</v>
       </c>
       <c r="AC224" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AD224" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AE224" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AF224" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AG224" t="n">
         <v>0</v>
@@ -44684,22 +44684,22 @@
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Independiente Petrolero</t>
         </is>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>Brest</t>
+          <t>Club Always Ready</t>
         </is>
       </c>
       <c r="G225" t="n">
@@ -44732,13 +44732,13 @@
         </is>
       </c>
       <c r="P225" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="Q225" t="n">
-        <v>9.15</v>
+        <v>0</v>
       </c>
       <c r="R225" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="S225" t="n">
         <v>0</v>
@@ -44783,10 +44783,10 @@
         <v>0</v>
       </c>
       <c r="AG225" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AH225" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AI225" t="n">
         <v>0</v>
@@ -44891,12 +44891,12 @@
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>Le Havre</t>
+          <t>Angers SCO</t>
         </is>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>Olympique Marseille</t>
+          <t>Strasbourg</t>
         </is>
       </c>
       <c r="G226" t="n">
@@ -44929,13 +44929,13 @@
         </is>
       </c>
       <c r="P226" t="n">
-        <v>4.68</v>
+        <v>4.05</v>
       </c>
       <c r="Q226" t="n">
-        <v>4.32</v>
+        <v>3.76</v>
       </c>
       <c r="R226" t="n">
-        <v>1.76</v>
+        <v>1.99</v>
       </c>
       <c r="S226" t="n">
         <v>0</v>
@@ -44974,10 +44974,10 @@
         <v>0</v>
       </c>
       <c r="AE226" t="n">
-        <v>1.58</v>
+        <v>1.85</v>
       </c>
       <c r="AF226" t="n">
-        <v>2.25</v>
+        <v>1.85</v>
       </c>
       <c r="AG226" t="n">
         <v>0</v>
@@ -45088,12 +45088,12 @@
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>Auxerre</t>
+          <t>Le Havre</t>
         </is>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>Nice</t>
+          <t>Olympique Marseille</t>
         </is>
       </c>
       <c r="G227" t="n">
@@ -45126,13 +45126,13 @@
         </is>
       </c>
       <c r="P227" t="n">
-        <v>2.48</v>
+        <v>4.68</v>
       </c>
       <c r="Q227" t="n">
-        <v>3.5</v>
+        <v>4.32</v>
       </c>
       <c r="R227" t="n">
-        <v>3.07</v>
+        <v>1.76</v>
       </c>
       <c r="S227" t="n">
         <v>0</v>
@@ -45171,10 +45171,10 @@
         <v>0</v>
       </c>
       <c r="AE227" t="n">
-        <v>1.8</v>
+        <v>1.58</v>
       </c>
       <c r="AF227" t="n">
-        <v>1.9</v>
+        <v>2.25</v>
       </c>
       <c r="AG227" t="n">
         <v>0</v>
@@ -45275,7 +45275,7 @@
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D228" t="inlineStr">
@@ -45285,12 +45285,12 @@
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>Botafogo</t>
         </is>
       </c>
       <c r="G228" t="n">
@@ -45323,13 +45323,13 @@
         </is>
       </c>
       <c r="P228" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Q228" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="R228" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="S228" t="n">
         <v>0</v>
@@ -45368,10 +45368,10 @@
         <v>0</v>
       </c>
       <c r="AE228" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AF228" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG228" t="n">
         <v>0</v>
@@ -45472,7 +45472,7 @@
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D229" t="inlineStr">
@@ -45482,12 +45482,12 @@
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>Náutico</t>
+          <t>Remo</t>
         </is>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>América Mineiro</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="G229" t="n">
@@ -45520,13 +45520,13 @@
         </is>
       </c>
       <c r="P229" t="n">
-        <v>1.79</v>
+        <v>5.3</v>
       </c>
       <c r="Q229" t="n">
-        <v>3.5</v>
+        <v>3.73</v>
       </c>
       <c r="R229" t="n">
-        <v>4.39</v>
+        <v>1.71</v>
       </c>
       <c r="S229" t="n">
         <v>0</v>
@@ -45565,10 +45565,10 @@
         <v>0</v>
       </c>
       <c r="AE229" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AF229" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AG229" t="n">
         <v>0</v>
@@ -45669,22 +45669,22 @@
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>FC Barcelona</t>
+          <t>Náutico</t>
         </is>
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>América Mineiro</t>
         </is>
       </c>
       <c r="G230" t="n">
@@ -45717,13 +45717,13 @@
         </is>
       </c>
       <c r="P230" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="Q230" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R230" t="n">
-        <v>0</v>
+        <v>4.39</v>
       </c>
       <c r="S230" t="n">
         <v>0</v>
@@ -45876,12 +45876,12 @@
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>Rennes</t>
+          <t>Auxerre</t>
         </is>
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>Paris</t>
+          <t>Nice</t>
         </is>
       </c>
       <c r="G231" t="n">
@@ -45914,13 +45914,13 @@
         </is>
       </c>
       <c r="P231" t="n">
-        <v>1.59</v>
+        <v>2.48</v>
       </c>
       <c r="Q231" t="n">
-        <v>4.73</v>
+        <v>3.5</v>
       </c>
       <c r="R231" t="n">
-        <v>5.79</v>
+        <v>3.07</v>
       </c>
       <c r="S231" t="n">
         <v>0</v>
@@ -45959,16 +45959,16 @@
         <v>0</v>
       </c>
       <c r="AE231" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AF231" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AG231" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AH231" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AI231" t="n">
         <v>0</v>
@@ -46073,12 +46073,12 @@
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>Godoy Cruz</t>
+          <t>Chaco For Ever</t>
         </is>
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>Racing Córdoba</t>
+          <t>Ciudad de Bolívar</t>
         </is>
       </c>
       <c r="G232" t="n">
@@ -46111,13 +46111,13 @@
         </is>
       </c>
       <c r="P232" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="Q232" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="R232" t="n">
-        <v>0</v>
+        <v>3.77</v>
       </c>
       <c r="S232" t="n">
         <v>0</v>
@@ -46150,10 +46150,10 @@
         <v>0</v>
       </c>
       <c r="AC232" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AD232" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AE232" t="n">
         <v>0</v>
@@ -46308,13 +46308,13 @@
         </is>
       </c>
       <c r="P233" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="Q233" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="R233" t="n">
-        <v>0</v>
+        <v>4.66</v>
       </c>
       <c r="S233" t="n">
         <v>0</v>
@@ -46347,10 +46347,10 @@
         <v>0</v>
       </c>
       <c r="AC233" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AD233" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AE233" t="n">
         <v>0</v>
@@ -46467,12 +46467,12 @@
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>Chaco For Ever</t>
+          <t>Godoy Cruz</t>
         </is>
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>Ciudad de Bolívar</t>
+          <t>Racing Córdoba</t>
         </is>
       </c>
       <c r="G234" t="n">
@@ -46505,13 +46505,13 @@
         </is>
       </c>
       <c r="P234" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="Q234" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="R234" t="n">
-        <v>0</v>
+        <v>6.94</v>
       </c>
       <c r="S234" t="n">
         <v>0</v>
@@ -46544,10 +46544,10 @@
         <v>0</v>
       </c>
       <c r="AC234" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AD234" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AE234" t="n">
         <v>0</v>
@@ -46654,22 +46654,22 @@
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>Hassania Agadir</t>
+          <t>Central Norte</t>
         </is>
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>FAR Rabat</t>
+          <t>Deportivo Madryn</t>
         </is>
       </c>
       <c r="G235" t="n">
@@ -46702,13 +46702,13 @@
         </is>
       </c>
       <c r="P235" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="Q235" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="R235" t="n">
-        <v>0</v>
+        <v>3.17</v>
       </c>
       <c r="S235" t="n">
         <v>0</v>
@@ -46741,10 +46741,10 @@
         <v>0</v>
       </c>
       <c r="AC235" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AD235" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AE235" t="n">
         <v>0</v>
@@ -46851,22 +46851,22 @@
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>Bay</t>
+          <t>Hassania Agadir</t>
         </is>
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>Utah Royals</t>
+          <t>FAR Rabat</t>
         </is>
       </c>
       <c r="G236" t="n">
@@ -47048,7 +47048,7 @@
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D237" t="inlineStr">
@@ -47058,12 +47058,12 @@
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>Portland Timbers II</t>
+          <t>Bay</t>
         </is>
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>LA Galaxy II</t>
+          <t>Utah Royals</t>
         </is>
       </c>
       <c r="G237" t="n">
@@ -47442,7 +47442,7 @@
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D239" t="inlineStr">
@@ -47452,12 +47452,12 @@
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t>Central Norte</t>
+          <t>Portland Timbers II</t>
         </is>
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>Deportivo Madryn</t>
+          <t>LA Galaxy II</t>
         </is>
       </c>
       <c r="G239" t="n">
@@ -47639,7 +47639,7 @@
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
@@ -47649,12 +47649,12 @@
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>New York City</t>
+          <t>CS Emelec</t>
         </is>
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>Columbus Crew</t>
+          <t>Libertad</t>
         </is>
       </c>
       <c r="G240" t="n">
@@ -47687,13 +47687,13 @@
         </is>
       </c>
       <c r="P240" t="n">
-        <v>2.23</v>
+        <v>1.67</v>
       </c>
       <c r="Q240" t="n">
-        <v>3.71</v>
+        <v>3.61</v>
       </c>
       <c r="R240" t="n">
-        <v>3.21</v>
+        <v>5.14</v>
       </c>
       <c r="S240" t="n">
         <v>0</v>
@@ -47732,10 +47732,10 @@
         <v>0</v>
       </c>
       <c r="AE240" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AF240" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AG240" t="n">
         <v>0</v>
@@ -47836,7 +47836,7 @@
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D241" t="inlineStr">
@@ -47846,12 +47846,12 @@
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>CS Emelec</t>
+          <t>New York City</t>
         </is>
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>Libertad</t>
+          <t>Columbus Crew</t>
         </is>
       </c>
       <c r="G241" t="n">
@@ -47884,13 +47884,13 @@
         </is>
       </c>
       <c r="P241" t="n">
-        <v>1.67</v>
+        <v>2.23</v>
       </c>
       <c r="Q241" t="n">
-        <v>3.61</v>
+        <v>3.71</v>
       </c>
       <c r="R241" t="n">
-        <v>5.14</v>
+        <v>3.21</v>
       </c>
       <c r="S241" t="n">
         <v>0</v>
@@ -47929,10 +47929,10 @@
         <v>0</v>
       </c>
       <c r="AE241" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AF241" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AG241" t="n">
         <v>0</v>
@@ -48081,13 +48081,13 @@
         </is>
       </c>
       <c r="P242" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="Q242" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="R242" t="n">
-        <v>0</v>
+        <v>5.05</v>
       </c>
       <c r="S242" t="n">
         <v>0</v>
@@ -48120,10 +48120,10 @@
         <v>0</v>
       </c>
       <c r="AC242" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AD242" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AE242" t="n">
         <v>0</v>
@@ -48427,7 +48427,7 @@
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D244" t="inlineStr">
@@ -48437,12 +48437,12 @@
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t>Mirassol</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>Chapecoense</t>
+          <t>Fortaleza</t>
         </is>
       </c>
       <c r="G244" t="n">
@@ -48475,13 +48475,13 @@
         </is>
       </c>
       <c r="P244" t="n">
-        <v>1.79</v>
+        <v>2.81</v>
       </c>
       <c r="Q244" t="n">
-        <v>3.62</v>
+        <v>3.08</v>
       </c>
       <c r="R244" t="n">
-        <v>4.84</v>
+        <v>2.51</v>
       </c>
       <c r="S244" t="n">
         <v>0</v>
@@ -48520,10 +48520,10 @@
         <v>0</v>
       </c>
       <c r="AE244" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AF244" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AG244" t="n">
         <v>0</v>
@@ -48624,7 +48624,7 @@
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D245" t="inlineStr">
@@ -48634,12 +48634,12 @@
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>Santos</t>
         </is>
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>Bragantino</t>
         </is>
       </c>
       <c r="G245" t="n">
@@ -48672,13 +48672,13 @@
         </is>
       </c>
       <c r="P245" t="n">
-        <v>2.81</v>
+        <v>2.13</v>
       </c>
       <c r="Q245" t="n">
-        <v>3.08</v>
+        <v>3.34</v>
       </c>
       <c r="R245" t="n">
-        <v>2.51</v>
+        <v>3.67</v>
       </c>
       <c r="S245" t="n">
         <v>0</v>
@@ -48717,10 +48717,10 @@
         <v>0</v>
       </c>
       <c r="AE245" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AF245" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AG245" t="n">
         <v>0</v>
@@ -48831,12 +48831,12 @@
       </c>
       <c r="E246" t="inlineStr">
         <is>
-          <t>Corinthians</t>
+          <t>Mirassol</t>
         </is>
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>São Paulo</t>
+          <t>Chapecoense</t>
         </is>
       </c>
       <c r="G246" t="n">
@@ -48869,13 +48869,13 @@
         </is>
       </c>
       <c r="P246" t="n">
-        <v>2.26</v>
+        <v>1.79</v>
       </c>
       <c r="Q246" t="n">
-        <v>3.22</v>
+        <v>3.62</v>
       </c>
       <c r="R246" t="n">
-        <v>3.46</v>
+        <v>4.84</v>
       </c>
       <c r="S246" t="n">
         <v>0</v>
@@ -48914,10 +48914,10 @@
         <v>0</v>
       </c>
       <c r="AE246" t="n">
-        <v>2.25</v>
+        <v>1.87</v>
       </c>
       <c r="AF246" t="n">
-        <v>1.57</v>
+        <v>1.8</v>
       </c>
       <c r="AG246" t="n">
         <v>0</v>
@@ -49028,12 +49028,12 @@
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>Corinthians</t>
         </is>
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>Bragantino</t>
+          <t>São Paulo</t>
         </is>
       </c>
       <c r="G247" t="n">
@@ -49066,13 +49066,13 @@
         </is>
       </c>
       <c r="P247" t="n">
-        <v>2.13</v>
+        <v>2.26</v>
       </c>
       <c r="Q247" t="n">
-        <v>3.34</v>
+        <v>3.22</v>
       </c>
       <c r="R247" t="n">
-        <v>3.67</v>
+        <v>3.46</v>
       </c>
       <c r="S247" t="n">
         <v>0</v>
@@ -49111,10 +49111,10 @@
         <v>0</v>
       </c>
       <c r="AE247" t="n">
-        <v>1.95</v>
+        <v>2.25</v>
       </c>
       <c r="AF247" t="n">
-        <v>1.73</v>
+        <v>1.57</v>
       </c>
       <c r="AG247" t="n">
         <v>0</v>
@@ -49412,7 +49412,7 @@
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D249" t="inlineStr">
@@ -49422,12 +49422,12 @@
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>Grêmio</t>
         </is>
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="G249" t="n">
@@ -49460,13 +49460,13 @@
         </is>
       </c>
       <c r="P249" t="n">
-        <v>0</v>
+        <v>3.79</v>
       </c>
       <c r="Q249" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="R249" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="S249" t="n">
         <v>0</v>
@@ -49505,10 +49505,10 @@
         <v>0</v>
       </c>
       <c r="AE249" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AF249" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AG249" t="n">
         <v>0</v>
@@ -49609,7 +49609,7 @@
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D250" t="inlineStr">
@@ -49619,12 +49619,12 @@
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>Grêmio</t>
+          <t>Novorizontino</t>
         </is>
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="G250" t="n">
@@ -49657,13 +49657,13 @@
         </is>
       </c>
       <c r="P250" t="n">
-        <v>3.79</v>
+        <v>0</v>
       </c>
       <c r="Q250" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="R250" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="S250" t="n">
         <v>0</v>
@@ -49702,10 +49702,10 @@
         <v>0</v>
       </c>
       <c r="AE250" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AF250" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AG250" t="n">
         <v>0</v>
@@ -49806,7 +49806,7 @@
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
@@ -49816,12 +49816,12 @@
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>Atlanta United II</t>
+          <t>Seattle Reign</t>
         </is>
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>Orlando City II</t>
+          <t>Washington Spirit</t>
         </is>
       </c>
       <c r="G251" t="n">
@@ -49854,13 +49854,13 @@
         </is>
       </c>
       <c r="P251" t="n">
-        <v>0</v>
+        <v>4.44</v>
       </c>
       <c r="Q251" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R251" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="S251" t="n">
         <v>0</v>
@@ -49899,10 +49899,10 @@
         <v>0</v>
       </c>
       <c r="AE251" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AF251" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AG251" t="n">
         <v>0</v>
@@ -50003,7 +50003,7 @@
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D252" t="inlineStr">
@@ -50013,12 +50013,12 @@
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>Seattle Reign</t>
+          <t>Minnesota United</t>
         </is>
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>Washington Spirit</t>
+          <t>Austin</t>
         </is>
       </c>
       <c r="G252" t="n">
@@ -50051,13 +50051,13 @@
         </is>
       </c>
       <c r="P252" t="n">
-        <v>4.44</v>
+        <v>1.72</v>
       </c>
       <c r="Q252" t="n">
-        <v>3.5</v>
+        <v>3.97</v>
       </c>
       <c r="R252" t="n">
-        <v>1.73</v>
+        <v>5.09</v>
       </c>
       <c r="S252" t="n">
         <v>0</v>
@@ -50096,10 +50096,10 @@
         <v>0</v>
       </c>
       <c r="AE252" t="n">
-        <v>1.99</v>
+        <v>1.7</v>
       </c>
       <c r="AF252" t="n">
-        <v>1.76</v>
+        <v>2</v>
       </c>
       <c r="AG252" t="n">
         <v>0</v>
@@ -50200,7 +50200,7 @@
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
@@ -50210,12 +50210,12 @@
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>Minnesota United</t>
+          <t>Atlanta United II</t>
         </is>
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>Austin</t>
+          <t>Orlando City II</t>
         </is>
       </c>
       <c r="G253" t="n">
@@ -50248,13 +50248,13 @@
         </is>
       </c>
       <c r="P253" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="Q253" t="n">
-        <v>3.97</v>
+        <v>0</v>
       </c>
       <c r="R253" t="n">
-        <v>5.09</v>
+        <v>0</v>
       </c>
       <c r="S253" t="n">
         <v>0</v>
@@ -50293,10 +50293,10 @@
         <v>0</v>
       </c>
       <c r="AE253" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AF253" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AG253" t="n">
         <v>0</v>
@@ -50594,7 +50594,7 @@
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D255" t="inlineStr">
@@ -50604,12 +50604,12 @@
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>Blooming</t>
+          <t>Vasco da Gama</t>
         </is>
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>Bolívar</t>
+          <t>Atlético PR</t>
         </is>
       </c>
       <c r="G255" t="n">
@@ -50642,13 +50642,13 @@
         </is>
       </c>
       <c r="P255" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="Q255" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R255" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="S255" t="n">
         <v>0</v>
@@ -50791,7 +50791,7 @@
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D256" t="inlineStr">
@@ -50801,12 +50801,12 @@
       </c>
       <c r="E256" t="inlineStr">
         <is>
-          <t>Vasco da Gama</t>
+          <t>Blooming</t>
         </is>
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>Atlético PR</t>
+          <t>Bolívar</t>
         </is>
       </c>
       <c r="G256" t="n">
@@ -50839,13 +50839,13 @@
         </is>
       </c>
       <c r="P256" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="Q256" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="R256" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="S256" t="n">
         <v>0</v>

--- a/jogos_2026-05-10.xlsx
+++ b/jogos_2026-05-10.xlsx
@@ -753,7 +753,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>Australia New South Wales NPL</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -763,12 +763,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Seongnam</t>
+          <t>Rockdale City Suns</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Jeonnam Dragons</t>
+          <t>Sydney II</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -801,13 +801,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>3.61</v>
+        <v>0</v>
       </c>
       <c r="S2" t="n">
         <v>0</v>
@@ -950,7 +950,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Australia New South Wales NPL</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Rockdale City Suns</t>
+          <t>Seongnam</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Sydney II</t>
+          <t>Jeonnam Dragons</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -998,13 +998,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>3.61</v>
       </c>
       <c r="S3" t="n">
         <v>0</v>
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Dalian Huayi</t>
+          <t>Yanbian Longding</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Guangzhou E-Power</t>
+          <t>Guangxi Hengchen</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -2132,22 +2132,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Ufa</t>
+          <t>Dalian Huayi</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rotor Volgograd</t>
+          <t>Guangzhou E-Power</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2329,22 +2329,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Yanbian Longding</t>
+          <t>Ufa</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Guangxi Hengchen</t>
+          <t>Rotor Volgograd</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Slavia Praha U21</t>
+          <t>Viktoria Žižkov</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Táborsko</t>
+          <t>Sparta Praha II</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Viktoria Žižkov</t>
+          <t>Slavia Praha U21</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Sparta Praha II</t>
+          <t>Táborsko</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Persita</t>
+          <t>Persija</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Persijap</t>
+          <t>Persib</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Persija</t>
+          <t>Persita</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Persib</t>
+          <t>Persijap</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -4496,7 +4496,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Levante W</t>
+          <t>Sokol Saratov</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Logroño W</t>
+          <t>Spartak Kostroma</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,13 +4544,13 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>4.98</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>3.66</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="S21" t="n">
         <v>0</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Hoang Anh Gia Lai</t>
+          <t>Levante W</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Pho Hien</t>
+          <t>Logroño W</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -5087,22 +5087,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Gyeongnam</t>
+          <t>Sheger Ketema</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Gimhae City</t>
+          <t>Sidama Bunna</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5135,13 +5135,13 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>3.16</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="S24" t="n">
         <v>0</v>
@@ -5481,7 +5481,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Sheger Ketema</t>
+          <t>Hoang Anh Gia Lai</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Sidama Bunna</t>
+          <t>Pho Hien</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5678,22 +5678,22 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Amarante</t>
+          <t>Gyeongnam</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>União Santarém</t>
+          <t>Gimhae City</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5726,13 +5726,13 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Q27" t="n">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="R27" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="S27" t="n">
         <v>0</v>
@@ -5875,7 +5875,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Sokol Saratov</t>
+          <t>Amarante</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Spartak Kostroma</t>
+          <t>União Santarém</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -5923,13 +5923,13 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>4.98</v>
+        <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>3.66</v>
+        <v>0</v>
       </c>
       <c r="R28" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="S28" t="n">
         <v>0</v>
@@ -6466,7 +6466,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Ho Chi Minh City</t>
+          <t>Ayutthaya United</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Song Lam Nghe An</t>
+          <t>Port FC</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6514,13 +6514,13 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>0</v>
+        <v>5.09</v>
       </c>
       <c r="Q31" t="n">
-        <v>0</v>
+        <v>4.18</v>
       </c>
       <c r="R31" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="S31" t="n">
         <v>0</v>
@@ -6663,7 +6663,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Hà Nội II</t>
+          <t>Rayong</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Viettel</t>
+          <t>Bangkok United</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6711,13 +6711,13 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="Q32" t="n">
-        <v>0</v>
+        <v>3.63</v>
       </c>
       <c r="R32" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="S32" t="n">
         <v>0</v>
@@ -6860,7 +6860,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Shenzhen Juniors</t>
+          <t>Piteå Women</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Hebei Kungfu</t>
+          <t>Rosengard Women</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -7057,22 +7057,22 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Altay</t>
+          <t>Celtic</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Ordabasy</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7105,13 +7105,13 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Q34" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="R34" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="S34" t="n">
         <v>0</v>
@@ -7254,22 +7254,22 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Sukhothai</t>
+          <t>Shenzhen Juniors</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Muang Thong United</t>
+          <t>Hebei Kungfu</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7302,13 +7302,13 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>3.61</v>
+        <v>0</v>
       </c>
       <c r="R35" t="n">
-        <v>2.77</v>
+        <v>0</v>
       </c>
       <c r="S35" t="n">
         <v>0</v>
@@ -7648,22 +7648,22 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Shenyang Urban</t>
+          <t>Kanchanaburi</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Yunnan Yukun</t>
+          <t>Ratchaburi</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7696,13 +7696,13 @@
         </is>
       </c>
       <c r="P37" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="Q37" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="R37" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="S37" t="n">
         <v>0</v>
@@ -7845,22 +7845,22 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Celtic</t>
+          <t>Altay</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Ordabasy</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -7893,13 +7893,13 @@
         </is>
       </c>
       <c r="P38" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="R38" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="S38" t="n">
         <v>0</v>
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Kanchanaburi</t>
+          <t>Chonburi</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Ratchaburi</t>
+          <t>Nakhon Ratchasima</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8090,13 +8090,13 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>3.32</v>
+        <v>1.61</v>
       </c>
       <c r="Q39" t="n">
-        <v>3.95</v>
+        <v>4.18</v>
       </c>
       <c r="R39" t="n">
-        <v>2.03</v>
+        <v>5.3</v>
       </c>
       <c r="S39" t="n">
         <v>0</v>
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Buriram United</t>
+          <t>Bangkok Glass</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Lamphun Warrior</t>
+          <t>Prachuap</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8287,13 +8287,13 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>1.24</v>
+        <v>1.78</v>
       </c>
       <c r="Q40" t="n">
-        <v>6.73</v>
+        <v>3.9</v>
       </c>
       <c r="R40" t="n">
-        <v>10.6</v>
+        <v>4.35</v>
       </c>
       <c r="S40" t="n">
         <v>0</v>
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Ayutthaya United</t>
+          <t>Buriram United</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Port FC</t>
+          <t>Lamphun Warrior</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8484,13 +8484,13 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>5.09</v>
+        <v>1.24</v>
       </c>
       <c r="Q41" t="n">
-        <v>4.18</v>
+        <v>6.73</v>
       </c>
       <c r="R41" t="n">
-        <v>1.64</v>
+        <v>10.6</v>
       </c>
       <c r="S41" t="n">
         <v>0</v>
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Rayong</t>
+          <t>Sukhothai</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Bangkok United</t>
+          <t>Muang Thong United</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8681,13 +8681,13 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>3.4</v>
+        <v>2.44</v>
       </c>
       <c r="Q42" t="n">
-        <v>3.63</v>
+        <v>3.61</v>
       </c>
       <c r="R42" t="n">
-        <v>2.09</v>
+        <v>2.77</v>
       </c>
       <c r="S42" t="n">
         <v>0</v>
@@ -8830,7 +8830,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Bangkok Glass</t>
+          <t>Hà Nội II</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Prachuap</t>
+          <t>Viettel</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -8878,13 +8878,13 @@
         </is>
       </c>
       <c r="P43" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="R43" t="n">
-        <v>4.35</v>
+        <v>0</v>
       </c>
       <c r="S43" t="n">
         <v>0</v>
@@ -9027,22 +9027,22 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Chonburi</t>
+          <t>Shenyang Urban</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Nakhon Ratchasima</t>
+          <t>Yunnan Yukun</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9075,13 +9075,13 @@
         </is>
       </c>
       <c r="P44" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>4.18</v>
+        <v>0</v>
       </c>
       <c r="R44" t="n">
-        <v>5.3</v>
+        <v>0</v>
       </c>
       <c r="S44" t="n">
         <v>0</v>
@@ -9224,22 +9224,22 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Piteå Women</t>
+          <t>Ho Chi Minh City</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Rosengard Women</t>
+          <t>Song Lam Nghe An</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -10012,22 +10012,22 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Preußen Münster</t>
+          <t>Nõmme Kalju</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Darmstadt 98</t>
+          <t>Tallinna FC Flora</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10060,13 +10060,13 @@
         </is>
       </c>
       <c r="P49" t="n">
-        <v>2.29</v>
+        <v>2.27</v>
       </c>
       <c r="Q49" t="n">
-        <v>3.74</v>
+        <v>3.7</v>
       </c>
       <c r="R49" t="n">
-        <v>2.76</v>
+        <v>2.6</v>
       </c>
       <c r="S49" t="n">
         <v>0</v>
@@ -10209,22 +10209,22 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Dongguan United</t>
+          <t>Havelse</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Suzhou Dongwu</t>
+          <t>Schweinfurt</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10406,22 +10406,22 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Nantong Zhiyun</t>
+          <t>Kerala Blasters</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Wuxi Wugou</t>
+          <t>Mohammedan</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10454,13 +10454,13 @@
         </is>
       </c>
       <c r="P51" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="Q51" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="R51" t="n">
-        <v>0</v>
+        <v>7.37</v>
       </c>
       <c r="S51" t="n">
         <v>0</v>
@@ -10800,7 +10800,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -10810,12 +10810,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Kerala Blasters</t>
+          <t>Hertha BSC</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Mohammedan</t>
+          <t>Greuther Fürth</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -10848,13 +10848,13 @@
         </is>
       </c>
       <c r="P53" t="n">
-        <v>1.34</v>
+        <v>1.78</v>
       </c>
       <c r="Q53" t="n">
-        <v>4.6</v>
+        <v>4.15</v>
       </c>
       <c r="R53" t="n">
-        <v>7.37</v>
+        <v>3.8</v>
       </c>
       <c r="S53" t="n">
         <v>0</v>
@@ -10899,10 +10899,10 @@
         <v>0</v>
       </c>
       <c r="AG53" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AH53" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AI53" t="n">
         <v>0</v>
@@ -10997,22 +10997,22 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Havelse</t>
+          <t>Nantong Zhiyun</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Schweinfurt</t>
+          <t>Wuxi Wugou</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11194,22 +11194,22 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Fortuna Düsseldorf</t>
+          <t>Dongguan United</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Elversberg</t>
+          <t>Suzhou Dongwu</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11242,13 +11242,13 @@
         </is>
       </c>
       <c r="P55" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="Q55" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="R55" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="S55" t="n">
         <v>0</v>
@@ -11391,22 +11391,22 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Nõmme Kalju</t>
+          <t>Fortuna Düsseldorf</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Tallinna FC Flora</t>
+          <t>Elversberg</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11439,13 +11439,13 @@
         </is>
       </c>
       <c r="P56" t="n">
-        <v>2.27</v>
+        <v>2.88</v>
       </c>
       <c r="Q56" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="R56" t="n">
-        <v>2.6</v>
+        <v>2.19</v>
       </c>
       <c r="S56" t="n">
         <v>0</v>
@@ -11598,12 +11598,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Hertha BSC</t>
+          <t>Preußen Münster</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Greuther Fürth</t>
+          <t>Darmstadt 98</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11636,13 +11636,13 @@
         </is>
       </c>
       <c r="P57" t="n">
-        <v>1.78</v>
+        <v>2.29</v>
       </c>
       <c r="Q57" t="n">
-        <v>4.15</v>
+        <v>3.74</v>
       </c>
       <c r="R57" t="n">
-        <v>3.8</v>
+        <v>2.76</v>
       </c>
       <c r="S57" t="n">
         <v>0</v>
@@ -11687,10 +11687,10 @@
         <v>0</v>
       </c>
       <c r="AG57" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AH57" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AI57" t="n">
         <v>0</v>
@@ -11992,12 +11992,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Zhejiang FC</t>
+          <t>Beijing Guoan</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Tianjin Teda</t>
+          <t>Shanghai SIPG</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -12189,12 +12189,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Beijing Guoan</t>
+          <t>Zhejiang FC</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Shanghai SIPG</t>
+          <t>Tianjin Teda</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -12573,22 +12573,22 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Meshakhte</t>
+          <t>Bahardar</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Dila</t>
+          <t>Welwalo Adigrat Uni</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12770,7 +12770,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -12780,12 +12780,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Nordsjælland</t>
+          <t>RCD Mallorca</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Midtjylland</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -12818,13 +12818,13 @@
         </is>
       </c>
       <c r="P63" t="n">
-        <v>3.36</v>
+        <v>0</v>
       </c>
       <c r="Q63" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="R63" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="S63" t="n">
         <v>0</v>
@@ -12967,22 +12967,22 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Zenit</t>
+          <t>AIK</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>FK Sochi</t>
+          <t>Djurgården</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -13015,13 +13015,13 @@
         </is>
       </c>
       <c r="P64" t="n">
-        <v>1.21</v>
+        <v>2.35</v>
       </c>
       <c r="Q64" t="n">
-        <v>7.41</v>
+        <v>3.35</v>
       </c>
       <c r="R64" t="n">
-        <v>17.5</v>
+        <v>2.87</v>
       </c>
       <c r="S64" t="n">
         <v>0</v>
@@ -13164,22 +13164,22 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AIK</t>
+          <t>Lugano</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Djurgården</t>
+          <t>St. Gallen</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -13212,13 +13212,13 @@
         </is>
       </c>
       <c r="P65" t="n">
-        <v>2.35</v>
+        <v>2.36</v>
       </c>
       <c r="Q65" t="n">
-        <v>3.35</v>
+        <v>3.54</v>
       </c>
       <c r="R65" t="n">
-        <v>2.87</v>
+        <v>2.73</v>
       </c>
       <c r="S65" t="n">
         <v>0</v>
@@ -13361,7 +13361,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -13371,12 +13371,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Vejle</t>
+          <t>FC Andorra</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Fredericia</t>
+          <t>UD Las Palmas</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -13409,13 +13409,13 @@
         </is>
       </c>
       <c r="P66" t="n">
-        <v>2.58</v>
+        <v>2.46</v>
       </c>
       <c r="Q66" t="n">
-        <v>3.62</v>
+        <v>3.43</v>
       </c>
       <c r="R66" t="n">
-        <v>2.45</v>
+        <v>2.91</v>
       </c>
       <c r="S66" t="n">
         <v>0</v>
@@ -13558,7 +13558,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -13568,12 +13568,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Kalmar</t>
+          <t>Aktobe</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Halmstad</t>
+          <t>Kaisar</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -13606,13 +13606,13 @@
         </is>
       </c>
       <c r="P67" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="Q67" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="R67" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="S67" t="n">
         <v>0</v>
@@ -13755,7 +13755,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -13765,12 +13765,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>FC Andorra</t>
+          <t>Vejle</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>UD Las Palmas</t>
+          <t>Fredericia</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -13803,13 +13803,13 @@
         </is>
       </c>
       <c r="P68" t="n">
-        <v>2.46</v>
+        <v>2.58</v>
       </c>
       <c r="Q68" t="n">
-        <v>3.43</v>
+        <v>3.62</v>
       </c>
       <c r="R68" t="n">
-        <v>2.91</v>
+        <v>2.45</v>
       </c>
       <c r="S68" t="n">
         <v>0</v>
@@ -13952,7 +13952,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -13962,12 +13962,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>RCD Mallorca</t>
+          <t>Nordsjælland</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>Midtjylland</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -14000,13 +14000,13 @@
         </is>
       </c>
       <c r="P69" t="n">
-        <v>0</v>
+        <v>3.36</v>
       </c>
       <c r="Q69" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="R69" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="S69" t="n">
         <v>0</v>
@@ -14149,22 +14149,22 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Bahardar</t>
+          <t>Qingdao Jonoon</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Welwalo Adigrat Uni</t>
+          <t>Dalian Zhixing</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -14346,7 +14346,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -14356,12 +14356,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Aktobe</t>
+          <t>Meshakhte</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Kaisar</t>
+          <t>Dila</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -14543,22 +14543,22 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>PSIM Yogyakarta</t>
+          <t>Kalmar</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Malut United</t>
+          <t>Halmstad</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -14591,13 +14591,13 @@
         </is>
       </c>
       <c r="P72" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="Q72" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R72" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="S72" t="n">
         <v>0</v>
@@ -14740,7 +14740,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -14750,12 +14750,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Lugano</t>
+          <t>Zenit</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>St. Gallen</t>
+          <t>FK Sochi</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -14788,13 +14788,13 @@
         </is>
       </c>
       <c r="P73" t="n">
-        <v>2.36</v>
+        <v>1.21</v>
       </c>
       <c r="Q73" t="n">
-        <v>3.54</v>
+        <v>7.41</v>
       </c>
       <c r="R73" t="n">
-        <v>2.73</v>
+        <v>17.5</v>
       </c>
       <c r="S73" t="n">
         <v>0</v>
@@ -14937,22 +14937,22 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Qingdao Jonoon</t>
+          <t>PSIM Yogyakarta</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Dalian Zhixing</t>
+          <t>Malut United</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -15725,7 +15725,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -15735,12 +15735,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Baník Ostrava U21</t>
+          <t>Tychy 71</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Ústí nad Labem</t>
+          <t>Ruch Chorzów</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -15773,13 +15773,13 @@
         </is>
       </c>
       <c r="P78" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Q78" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R78" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="S78" t="n">
         <v>0</v>
@@ -15922,7 +15922,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -15932,12 +15932,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Tychy 71</t>
+          <t>Baník Ostrava U21</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Ruch Chorzów</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -15970,13 +15970,13 @@
         </is>
       </c>
       <c r="P79" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="Q79" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R79" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="S79" t="n">
         <v>0</v>
@@ -16316,22 +16316,22 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Arba Minch Kenema</t>
+          <t>Uppsala W</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Welayta Dicha</t>
+          <t>Vittsjö</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -16513,7 +16513,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -16523,12 +16523,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Burnley</t>
+          <t>Arba Minch Kenema</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Aston Villa</t>
+          <t>Welayta Dicha</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -16561,13 +16561,13 @@
         </is>
       </c>
       <c r="P82" t="n">
-        <v>5.38</v>
+        <v>0</v>
       </c>
       <c r="Q82" t="n">
-        <v>4.37</v>
+        <v>0</v>
       </c>
       <c r="R82" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="S82" t="n">
         <v>0</v>
@@ -16710,7 +16710,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -16720,12 +16720,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Botoşani</t>
+          <t>Burnley</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Petrolul 52</t>
+          <t>Aston Villa</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -16758,13 +16758,13 @@
         </is>
       </c>
       <c r="P83" t="n">
-        <v>2.21</v>
+        <v>5.38</v>
       </c>
       <c r="Q83" t="n">
-        <v>3.22</v>
+        <v>4.37</v>
       </c>
       <c r="R83" t="n">
-        <v>3.22</v>
+        <v>1.67</v>
       </c>
       <c r="S83" t="n">
         <v>0</v>
@@ -16907,7 +16907,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -16917,12 +16917,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>NK Primorje</t>
+          <t>Nottingham Forest</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Mura</t>
+          <t>Newcastle United</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -16955,13 +16955,13 @@
         </is>
       </c>
       <c r="P84" t="n">
-        <v>2.59</v>
+        <v>2.46</v>
       </c>
       <c r="Q84" t="n">
-        <v>3.45</v>
+        <v>3.66</v>
       </c>
       <c r="R84" t="n">
-        <v>2.3</v>
+        <v>2.99</v>
       </c>
       <c r="S84" t="n">
         <v>0</v>
@@ -17000,10 +17000,10 @@
         <v>0</v>
       </c>
       <c r="AE84" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AF84" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AG84" t="n">
         <v>0</v>
@@ -17104,7 +17104,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -17114,12 +17114,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Pardubice</t>
+          <t>Botoşani</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Karviná</t>
+          <t>Petrolul 52</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -17152,13 +17152,13 @@
         </is>
       </c>
       <c r="P85" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="Q85" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="R85" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="S85" t="n">
         <v>0</v>
@@ -17301,22 +17301,22 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Uppsala W</t>
+          <t>Crystal Palace</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Vittsjö</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -17349,13 +17349,13 @@
         </is>
       </c>
       <c r="P86" t="n">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="Q86" t="n">
-        <v>0</v>
+        <v>3.31</v>
       </c>
       <c r="R86" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="S86" t="n">
         <v>0</v>
@@ -17394,10 +17394,10 @@
         <v>0</v>
       </c>
       <c r="AE86" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AF86" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AG86" t="n">
         <v>0</v>
@@ -17498,22 +17498,22 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Astana</t>
+          <t>Sigma Olomouc</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Kyzyl-Zhar</t>
+          <t>Bohemians 1905</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -17546,13 +17546,13 @@
         </is>
       </c>
       <c r="P87" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Q87" t="n">
-        <v>3.76</v>
+        <v>0</v>
       </c>
       <c r="R87" t="n">
-        <v>4.15</v>
+        <v>0</v>
       </c>
       <c r="S87" t="n">
         <v>0</v>
@@ -17695,7 +17695,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -17705,12 +17705,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Nottingham Forest</t>
+          <t>Cremonese</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Newcastle United</t>
+          <t>Pisa</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -17743,13 +17743,13 @@
         </is>
       </c>
       <c r="P88" t="n">
-        <v>2.46</v>
+        <v>2.1</v>
       </c>
       <c r="Q88" t="n">
-        <v>3.66</v>
+        <v>3.42</v>
       </c>
       <c r="R88" t="n">
-        <v>2.99</v>
+        <v>4.07</v>
       </c>
       <c r="S88" t="n">
         <v>0</v>
@@ -17788,10 +17788,10 @@
         <v>0</v>
       </c>
       <c r="AE88" t="n">
-        <v>1.68</v>
+        <v>2.15</v>
       </c>
       <c r="AF88" t="n">
-        <v>2.05</v>
+        <v>1.61</v>
       </c>
       <c r="AG88" t="n">
         <v>0</v>
@@ -17892,7 +17892,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -17902,12 +17902,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Crystal Palace</t>
+          <t>Turan</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Karvan FK</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -17940,13 +17940,13 @@
         </is>
       </c>
       <c r="P89" t="n">
-        <v>2.69</v>
+        <v>0</v>
       </c>
       <c r="Q89" t="n">
-        <v>3.31</v>
+        <v>0</v>
       </c>
       <c r="R89" t="n">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="S89" t="n">
         <v>0</v>
@@ -17985,10 +17985,10 @@
         <v>0</v>
       </c>
       <c r="AE89" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AF89" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AG89" t="n">
         <v>0</v>
@@ -18089,7 +18089,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -18099,12 +18099,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Sigma Olomouc</t>
+          <t>NK Primorje</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Bohemians 1905</t>
+          <t>Mura</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -18137,13 +18137,13 @@
         </is>
       </c>
       <c r="P90" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="Q90" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="R90" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S90" t="n">
         <v>0</v>
@@ -18286,22 +18286,22 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Fiorentina</t>
+          <t>Astana</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Genoa</t>
+          <t>Kyzyl-Zhar</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -18334,13 +18334,13 @@
         </is>
       </c>
       <c r="P91" t="n">
-        <v>2.09</v>
+        <v>1.8</v>
       </c>
       <c r="Q91" t="n">
-        <v>3.48</v>
+        <v>3.76</v>
       </c>
       <c r="R91" t="n">
-        <v>4.01</v>
+        <v>4.15</v>
       </c>
       <c r="S91" t="n">
         <v>0</v>
@@ -18379,10 +18379,10 @@
         <v>0</v>
       </c>
       <c r="AE91" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AF91" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AG91" t="n">
         <v>0</v>
@@ -18483,7 +18483,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -18493,12 +18493,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Turan</t>
+          <t>Pardubice</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Karvan FK</t>
+          <t>Karviná</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -18690,12 +18690,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Cremonese</t>
+          <t>Fiorentina</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Pisa</t>
+          <t>Genoa</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -18728,13 +18728,13 @@
         </is>
       </c>
       <c r="P93" t="n">
-        <v>2.1</v>
+        <v>2.09</v>
       </c>
       <c r="Q93" t="n">
-        <v>3.42</v>
+        <v>3.48</v>
       </c>
       <c r="R93" t="n">
-        <v>4.07</v>
+        <v>4.01</v>
       </c>
       <c r="S93" t="n">
         <v>0</v>
@@ -18773,10 +18773,10 @@
         <v>0</v>
       </c>
       <c r="AE93" t="n">
-        <v>2.15</v>
+        <v>1.98</v>
       </c>
       <c r="AF93" t="n">
-        <v>1.61</v>
+        <v>1.73</v>
       </c>
       <c r="AG93" t="n">
         <v>0</v>
@@ -19468,7 +19468,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -19478,12 +19478,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Osijek</t>
+          <t>Volos NFC</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Istra 1961</t>
+          <t>Levadiakos</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -19516,13 +19516,13 @@
         </is>
       </c>
       <c r="P97" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="Q97" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R97" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="S97" t="n">
         <v>0</v>
@@ -19665,7 +19665,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -19675,12 +19675,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Aris</t>
+          <t>NorthEast United</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>OFI</t>
+          <t>Chennaiyin</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -19862,22 +19862,22 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Volos NFC</t>
+          <t>EB - Streymur</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Levadiakos</t>
+          <t>Víkingur</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -19910,13 +19910,13 @@
         </is>
       </c>
       <c r="P99" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="Q99" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="R99" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="S99" t="n">
         <v>0</v>
@@ -20059,22 +20059,22 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>NorthEast United</t>
+          <t>Nõmme United</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Chennaiyin</t>
+          <t>Paide</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -20107,13 +20107,13 @@
         </is>
       </c>
       <c r="P100" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="Q100" t="n">
-        <v>0</v>
+        <v>3.88</v>
       </c>
       <c r="R100" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="S100" t="n">
         <v>0</v>
@@ -20256,7 +20256,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -20266,12 +20266,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Silkeborg</t>
+          <t>Royal Antwerp FC</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>Sporting Charleroi</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -20304,13 +20304,13 @@
         </is>
       </c>
       <c r="P101" t="n">
-        <v>4.68</v>
+        <v>2.38</v>
       </c>
       <c r="Q101" t="n">
-        <v>4</v>
+        <v>3.24</v>
       </c>
       <c r="R101" t="n">
-        <v>1.63</v>
+        <v>3.14</v>
       </c>
       <c r="S101" t="n">
         <v>0</v>
@@ -20349,10 +20349,10 @@
         <v>0</v>
       </c>
       <c r="AE101" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AF101" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG101" t="n">
         <v>0</v>
@@ -20453,22 +20453,22 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Banga</t>
+          <t>Aris</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>TransINVEST Vilnius</t>
+          <t>OFI</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -20650,22 +20650,22 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>EB - Streymur</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Víkingur</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -20698,13 +20698,13 @@
         </is>
       </c>
       <c r="P103" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="Q103" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R103" t="n">
-        <v>0</v>
+        <v>3.21</v>
       </c>
       <c r="S103" t="n">
         <v>0</v>
@@ -20743,10 +20743,10 @@
         <v>0</v>
       </c>
       <c r="AE103" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AF103" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AG103" t="n">
         <v>0</v>
@@ -20847,22 +20847,22 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Royal Antwerp FC</t>
+          <t>Banga</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Sporting Charleroi</t>
+          <t>TransINVEST Vilnius</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -20895,13 +20895,13 @@
         </is>
       </c>
       <c r="P104" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="Q104" t="n">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="R104" t="n">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="S104" t="n">
         <v>0</v>
@@ -20940,10 +20940,10 @@
         <v>0</v>
       </c>
       <c r="AE104" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AF104" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AG104" t="n">
         <v>0</v>
@@ -21044,7 +21044,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -21054,12 +21054,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Silkeborg</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>København</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -21092,13 +21092,13 @@
         </is>
       </c>
       <c r="P105" t="n">
-        <v>2.17</v>
+        <v>4.68</v>
       </c>
       <c r="Q105" t="n">
-        <v>3.4</v>
+        <v>4</v>
       </c>
       <c r="R105" t="n">
-        <v>3.21</v>
+        <v>1.63</v>
       </c>
       <c r="S105" t="n">
         <v>0</v>
@@ -21137,10 +21137,10 @@
         <v>0</v>
       </c>
       <c r="AE105" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AF105" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AG105" t="n">
         <v>0</v>
@@ -21241,22 +21241,22 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>B36</t>
+          <t>Osijek</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>KÍ</t>
+          <t>Istra 1961</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -21438,22 +21438,22 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Nõmme United</t>
+          <t>Honvéd W</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Paide</t>
+          <t>Vasas</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -21486,13 +21486,13 @@
         </is>
       </c>
       <c r="P107" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="Q107" t="n">
-        <v>3.88</v>
+        <v>0</v>
       </c>
       <c r="R107" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="S107" t="n">
         <v>0</v>
@@ -21635,22 +21635,22 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Honvéd W</t>
+          <t>B36</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Vasas</t>
+          <t>KÍ</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -21832,7 +21832,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -21842,12 +21842,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Leganés</t>
+          <t>Akhmat Grozny</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Racing Santander</t>
+          <t>Makhachkala</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -21880,13 +21880,13 @@
         </is>
       </c>
       <c r="P109" t="n">
-        <v>3.06</v>
+        <v>2.16</v>
       </c>
       <c r="Q109" t="n">
-        <v>3.61</v>
+        <v>3.42</v>
       </c>
       <c r="R109" t="n">
-        <v>2.29</v>
+        <v>3.85</v>
       </c>
       <c r="S109" t="n">
         <v>0</v>
@@ -22029,7 +22029,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -22039,12 +22039,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Akhmat Grozny</t>
+          <t>Leganés</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Makhachkala</t>
+          <t>Racing Santander</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -22077,13 +22077,13 @@
         </is>
       </c>
       <c r="P110" t="n">
-        <v>2.16</v>
+        <v>3.06</v>
       </c>
       <c r="Q110" t="n">
-        <v>3.42</v>
+        <v>3.61</v>
       </c>
       <c r="R110" t="n">
-        <v>3.85</v>
+        <v>2.29</v>
       </c>
       <c r="S110" t="n">
         <v>0</v>
@@ -22620,22 +22620,22 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Häcken</t>
+          <t>Sion</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Malmö FF</t>
+          <t>Thun</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -22668,13 +22668,13 @@
         </is>
       </c>
       <c r="P113" t="n">
-        <v>2.27</v>
+        <v>2.05</v>
       </c>
       <c r="Q113" t="n">
-        <v>3.58</v>
+        <v>3.64</v>
       </c>
       <c r="R113" t="n">
-        <v>2.88</v>
+        <v>3.28</v>
       </c>
       <c r="S113" t="n">
         <v>0</v>
@@ -23211,22 +23211,22 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Sion</t>
+          <t>Häcken</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Thun</t>
+          <t>Malmö FF</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -23259,13 +23259,13 @@
         </is>
       </c>
       <c r="P116" t="n">
-        <v>2.05</v>
+        <v>2.27</v>
       </c>
       <c r="Q116" t="n">
-        <v>3.64</v>
+        <v>3.58</v>
       </c>
       <c r="R116" t="n">
-        <v>3.28</v>
+        <v>2.88</v>
       </c>
       <c r="S116" t="n">
         <v>0</v>
@@ -23418,12 +23418,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Twente</t>
+          <t>Feyenoord</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Sparta Rotterdam</t>
+          <t>AZ</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -23456,13 +23456,13 @@
         </is>
       </c>
       <c r="P117" t="n">
-        <v>1.44</v>
+        <v>1.78</v>
       </c>
       <c r="Q117" t="n">
-        <v>5.14</v>
+        <v>4.17</v>
       </c>
       <c r="R117" t="n">
-        <v>6.53</v>
+        <v>4.17</v>
       </c>
       <c r="S117" t="n">
         <v>0</v>
@@ -23507,7 +23507,7 @@
         <v>0</v>
       </c>
       <c r="AG117" t="n">
-        <v>1.93</v>
+        <v>1.9</v>
       </c>
       <c r="AH117" t="n">
         <v>1.77</v>
@@ -23615,12 +23615,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Fortuna Sittard</t>
+          <t>NAC Breda</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>PEC Zwolle</t>
+          <t>Heerenveen</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -23653,13 +23653,13 @@
         </is>
       </c>
       <c r="P118" t="n">
-        <v>1.96</v>
+        <v>2.49</v>
       </c>
       <c r="Q118" t="n">
-        <v>4.05</v>
+        <v>3.77</v>
       </c>
       <c r="R118" t="n">
-        <v>3.5</v>
+        <v>2.67</v>
       </c>
       <c r="S118" t="n">
         <v>0</v>
@@ -23698,16 +23698,16 @@
         <v>0</v>
       </c>
       <c r="AE118" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AF118" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AG118" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AH118" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AI118" t="n">
         <v>0</v>
@@ -23812,12 +23812,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Feyenoord</t>
+          <t>Twente</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>AZ</t>
+          <t>Sparta Rotterdam</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -23850,13 +23850,13 @@
         </is>
       </c>
       <c r="P119" t="n">
-        <v>1.78</v>
+        <v>1.44</v>
       </c>
       <c r="Q119" t="n">
-        <v>4.17</v>
+        <v>5.14</v>
       </c>
       <c r="R119" t="n">
-        <v>4.17</v>
+        <v>6.53</v>
       </c>
       <c r="S119" t="n">
         <v>0</v>
@@ -23901,7 +23901,7 @@
         <v>0</v>
       </c>
       <c r="AG119" t="n">
-        <v>1.9</v>
+        <v>1.93</v>
       </c>
       <c r="AH119" t="n">
         <v>1.77</v>
@@ -24009,12 +24009,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Telstar</t>
+          <t>Fortuna Sittard</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Heracles</t>
+          <t>PEC Zwolle</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -24047,13 +24047,13 @@
         </is>
       </c>
       <c r="P120" t="n">
-        <v>1.48</v>
+        <v>1.96</v>
       </c>
       <c r="Q120" t="n">
-        <v>4.94</v>
+        <v>4.05</v>
       </c>
       <c r="R120" t="n">
-        <v>6.07</v>
+        <v>3.5</v>
       </c>
       <c r="S120" t="n">
         <v>0</v>
@@ -24098,10 +24098,10 @@
         <v>0</v>
       </c>
       <c r="AG120" t="n">
-        <v>1.98</v>
+        <v>2.2</v>
       </c>
       <c r="AH120" t="n">
-        <v>1.72</v>
+        <v>1.58</v>
       </c>
       <c r="AI120" t="n">
         <v>0</v>
@@ -24206,12 +24206,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Excelsior</t>
+          <t>Telstar</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Volendam</t>
+          <t>Heracles</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -24244,13 +24244,13 @@
         </is>
       </c>
       <c r="P121" t="n">
-        <v>1.77</v>
+        <v>1.48</v>
       </c>
       <c r="Q121" t="n">
-        <v>4.17</v>
+        <v>4.94</v>
       </c>
       <c r="R121" t="n">
-        <v>4.22</v>
+        <v>6.07</v>
       </c>
       <c r="S121" t="n">
         <v>0</v>
@@ -24289,16 +24289,16 @@
         <v>0</v>
       </c>
       <c r="AE121" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AF121" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AG121" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AH121" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AI121" t="n">
         <v>0</v>
@@ -24403,12 +24403,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>NAC Breda</t>
+          <t>Excelsior</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Heerenveen</t>
+          <t>Volendam</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -24441,13 +24441,13 @@
         </is>
       </c>
       <c r="P122" t="n">
-        <v>2.49</v>
+        <v>1.77</v>
       </c>
       <c r="Q122" t="n">
-        <v>3.77</v>
+        <v>4.17</v>
       </c>
       <c r="R122" t="n">
-        <v>2.67</v>
+        <v>4.22</v>
       </c>
       <c r="S122" t="n">
         <v>0</v>
@@ -24486,7 +24486,7 @@
         <v>0</v>
       </c>
       <c r="AE122" t="n">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="AF122" t="n">
         <v>2.3</v>
@@ -24600,12 +24600,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Groningen</t>
+          <t>Ajax</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>NEC</t>
+          <t>Utrecht</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -24638,13 +24638,13 @@
         </is>
       </c>
       <c r="P123" t="n">
-        <v>2.78</v>
+        <v>1.71</v>
       </c>
       <c r="Q123" t="n">
-        <v>3.89</v>
+        <v>4.37</v>
       </c>
       <c r="R123" t="n">
-        <v>2.36</v>
+        <v>4.42</v>
       </c>
       <c r="S123" t="n">
         <v>0</v>
@@ -24689,10 +24689,10 @@
         <v>0</v>
       </c>
       <c r="AG123" t="n">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="AH123" t="n">
-        <v>1.68</v>
+        <v>1.65</v>
       </c>
       <c r="AI123" t="n">
         <v>0</v>
@@ -24797,12 +24797,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Go Ahead Eagles</t>
+          <t>Groningen</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>PSV</t>
+          <t>NEC</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -24835,13 +24835,13 @@
         </is>
       </c>
       <c r="P124" t="n">
-        <v>4.48</v>
+        <v>2.78</v>
       </c>
       <c r="Q124" t="n">
-        <v>4.74</v>
+        <v>3.89</v>
       </c>
       <c r="R124" t="n">
-        <v>1.65</v>
+        <v>2.36</v>
       </c>
       <c r="S124" t="n">
         <v>0</v>
@@ -24886,10 +24886,10 @@
         <v>0</v>
       </c>
       <c r="AG124" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AH124" t="n">
         <v>1.68</v>
-      </c>
-      <c r="AH124" t="n">
-        <v>2.05</v>
       </c>
       <c r="AI124" t="n">
         <v>0</v>
@@ -24994,12 +24994,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Ajax</t>
+          <t>Go Ahead Eagles</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Utrecht</t>
+          <t>PSV</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -25032,13 +25032,13 @@
         </is>
       </c>
       <c r="P125" t="n">
-        <v>1.71</v>
+        <v>4.48</v>
       </c>
       <c r="Q125" t="n">
-        <v>4.37</v>
+        <v>4.74</v>
       </c>
       <c r="R125" t="n">
-        <v>4.42</v>
+        <v>1.65</v>
       </c>
       <c r="S125" t="n">
         <v>0</v>
@@ -25083,10 +25083,10 @@
         <v>0</v>
       </c>
       <c r="AG125" t="n">
-        <v>2.1</v>
+        <v>1.68</v>
       </c>
       <c r="AH125" t="n">
-        <v>1.65</v>
+        <v>2.05</v>
       </c>
       <c r="AI125" t="n">
         <v>0</v>
@@ -25191,12 +25191,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Makedonija GjP</t>
+          <t>Shkendija</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Tikveš</t>
+          <t>Struga</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -25378,7 +25378,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -25388,12 +25388,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Strømmen</t>
+          <t>KFUM</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Hødd</t>
+          <t>Viking</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -25426,13 +25426,13 @@
         </is>
       </c>
       <c r="P127" t="n">
-        <v>2.2</v>
+        <v>3.87</v>
       </c>
       <c r="Q127" t="n">
-        <v>3.4</v>
+        <v>3.87</v>
       </c>
       <c r="R127" t="n">
-        <v>3.2</v>
+        <v>1.89</v>
       </c>
       <c r="S127" t="n">
         <v>0</v>
@@ -25575,22 +25575,22 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Croatia Zmijavci</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Jarun</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -25623,13 +25623,13 @@
         </is>
       </c>
       <c r="P128" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="Q128" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R128" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="S128" t="n">
         <v>0</v>
@@ -25772,22 +25772,22 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Sandnes Ulf</t>
+          <t>Real Madrid W</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Stabæk</t>
+          <t>Atletico Madrid W</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -25820,13 +25820,13 @@
         </is>
       </c>
       <c r="P129" t="n">
-        <v>4.07</v>
+        <v>0</v>
       </c>
       <c r="Q129" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="R129" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="S129" t="n">
         <v>0</v>
@@ -25969,22 +25969,22 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Moss</t>
+          <t>Zbrojovka Brno</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Bryne</t>
+          <t>Vlašim</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -26017,13 +26017,13 @@
         </is>
       </c>
       <c r="P130" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Q130" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="R130" t="n">
-        <v>3.01</v>
+        <v>0</v>
       </c>
       <c r="S130" t="n">
         <v>0</v>
@@ -26166,22 +26166,22 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Åsane</t>
+          <t>Rapid Wien</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Strømsgodset</t>
+          <t>Austria Wien</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -26214,13 +26214,13 @@
         </is>
       </c>
       <c r="P131" t="n">
-        <v>5.4</v>
+        <v>2.3</v>
       </c>
       <c r="Q131" t="n">
-        <v>4.6</v>
+        <v>3.35</v>
       </c>
       <c r="R131" t="n">
-        <v>1.51</v>
+        <v>2.96</v>
       </c>
       <c r="S131" t="n">
         <v>0</v>
@@ -26363,7 +26363,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -26373,12 +26373,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Sogndal</t>
+          <t>Sandefjord</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Haugesund</t>
+          <t>Kristiansund</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -26411,13 +26411,13 @@
         </is>
       </c>
       <c r="P132" t="n">
-        <v>3.1</v>
+        <v>1.59</v>
       </c>
       <c r="Q132" t="n">
-        <v>3.7</v>
+        <v>4.44</v>
       </c>
       <c r="R132" t="n">
-        <v>2.12</v>
+        <v>5.16</v>
       </c>
       <c r="S132" t="n">
         <v>0</v>
@@ -26560,22 +26560,22 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Pelister</t>
+          <t>Saburtalo</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Shkupi</t>
+          <t>Torpedo Kutaisi</t>
         </is>
       </c>
       <c r="G133" t="n">
@@ -26757,22 +26757,22 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Tromsø</t>
+          <t>Pelister</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Molde</t>
+          <t>Shkupi</t>
         </is>
       </c>
       <c r="G134" t="n">
@@ -26805,13 +26805,13 @@
         </is>
       </c>
       <c r="P134" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="Q134" t="n">
-        <v>3.82</v>
+        <v>0</v>
       </c>
       <c r="R134" t="n">
-        <v>4.13</v>
+        <v>0</v>
       </c>
       <c r="S134" t="n">
         <v>0</v>
@@ -26954,7 +26954,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -26964,12 +26964,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Real Madrid W</t>
+          <t>Budafoki MTE</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Atletico Madrid W</t>
+          <t>BVSC</t>
         </is>
       </c>
       <c r="G135" t="n">
@@ -27151,7 +27151,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -27161,12 +27161,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>LASK Linz</t>
+          <t>Paphos</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Salzburg</t>
+          <t>Aris</t>
         </is>
       </c>
       <c r="G136" t="n">
@@ -27199,13 +27199,13 @@
         </is>
       </c>
       <c r="P136" t="n">
-        <v>2.51</v>
+        <v>0</v>
       </c>
       <c r="Q136" t="n">
-        <v>3.78</v>
+        <v>0</v>
       </c>
       <c r="R136" t="n">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="S136" t="n">
         <v>0</v>
@@ -27348,22 +27348,22 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Hartberg</t>
+          <t>Tromsø</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Sturm Graz</t>
+          <t>Molde</t>
         </is>
       </c>
       <c r="G137" t="n">
@@ -27396,13 +27396,13 @@
         </is>
       </c>
       <c r="P137" t="n">
-        <v>3.75</v>
+        <v>1.84</v>
       </c>
       <c r="Q137" t="n">
-        <v>3.6</v>
+        <v>3.82</v>
       </c>
       <c r="R137" t="n">
-        <v>1.91</v>
+        <v>4.13</v>
       </c>
       <c r="S137" t="n">
         <v>0</v>
@@ -27441,10 +27441,10 @@
         <v>0</v>
       </c>
       <c r="AE137" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AF137" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AG137" t="n">
         <v>0</v>
@@ -27545,22 +27545,22 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Zbrojovka Brno</t>
+          <t>Åsane</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Vlašim</t>
+          <t>Strømsgodset</t>
         </is>
       </c>
       <c r="G138" t="n">
@@ -27593,13 +27593,13 @@
         </is>
       </c>
       <c r="P138" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="Q138" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="R138" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="S138" t="n">
         <v>0</v>
@@ -27939,7 +27939,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -27949,12 +27949,12 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Pogoń Siedlce</t>
+          <t>Aresimi</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Stal Rzeszów</t>
+          <t>FK Bashkimi Kumanovo</t>
         </is>
       </c>
       <c r="G140" t="n">
@@ -27987,13 +27987,13 @@
         </is>
       </c>
       <c r="P140" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="Q140" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R140" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="S140" t="n">
         <v>0</v>
@@ -28136,7 +28136,7 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -28146,12 +28146,12 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Apollon</t>
+          <t>Vardar</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>APOEL</t>
+          <t>Sileks</t>
         </is>
       </c>
       <c r="G141" t="n">
@@ -28333,22 +28333,22 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Croatia Zmijavci</t>
+          <t>Sandnes Ulf</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Jarun</t>
+          <t>Stabæk</t>
         </is>
       </c>
       <c r="G142" t="n">
@@ -28381,13 +28381,13 @@
         </is>
       </c>
       <c r="P142" t="n">
-        <v>0</v>
+        <v>4.07</v>
       </c>
       <c r="Q142" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="R142" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="S142" t="n">
         <v>0</v>
@@ -28530,7 +28530,7 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -28540,12 +28540,12 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Paphos</t>
+          <t>Makedonija GjP</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Aris</t>
+          <t>Tikveš</t>
         </is>
       </c>
       <c r="G143" t="n">
@@ -28727,7 +28727,7 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -28737,12 +28737,12 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Aresimi</t>
+          <t>Omonia Nicosia</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>FK Bashkimi Kumanovo</t>
+          <t>AEK Larnaca</t>
         </is>
       </c>
       <c r="G144" t="n">
@@ -28924,7 +28924,7 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -28934,12 +28934,12 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>KFUM</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Viking</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="G145" t="n">
@@ -28972,13 +28972,13 @@
         </is>
       </c>
       <c r="P145" t="n">
-        <v>3.87</v>
+        <v>2.65</v>
       </c>
       <c r="Q145" t="n">
-        <v>3.87</v>
+        <v>3.6</v>
       </c>
       <c r="R145" t="n">
-        <v>1.89</v>
+        <v>2.4</v>
       </c>
       <c r="S145" t="n">
         <v>0</v>
@@ -29121,22 +29121,22 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Sandefjord</t>
+          <t>Hartberg</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Kristiansund</t>
+          <t>Sturm Graz</t>
         </is>
       </c>
       <c r="G146" t="n">
@@ -29169,13 +29169,13 @@
         </is>
       </c>
       <c r="P146" t="n">
-        <v>1.59</v>
+        <v>3.75</v>
       </c>
       <c r="Q146" t="n">
-        <v>4.44</v>
+        <v>3.6</v>
       </c>
       <c r="R146" t="n">
-        <v>5.16</v>
+        <v>1.91</v>
       </c>
       <c r="S146" t="n">
         <v>0</v>
@@ -29214,10 +29214,10 @@
         <v>0</v>
       </c>
       <c r="AE146" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AF146" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG146" t="n">
         <v>0</v>
@@ -29318,7 +29318,7 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
@@ -29328,12 +29328,12 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Rapid Wien</t>
+          <t>Szentlőrinc SE</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Austria Wien</t>
+          <t>Videoton</t>
         </is>
       </c>
       <c r="G147" t="n">
@@ -29366,13 +29366,13 @@
         </is>
       </c>
       <c r="P147" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Q147" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="R147" t="n">
-        <v>2.96</v>
+        <v>0</v>
       </c>
       <c r="S147" t="n">
         <v>0</v>
@@ -29515,22 +29515,22 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Omonia Nicosia</t>
+          <t>Moss</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>AEK Larnaca</t>
+          <t>Bryne</t>
         </is>
       </c>
       <c r="G148" t="n">
@@ -29563,13 +29563,13 @@
         </is>
       </c>
       <c r="P148" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Q148" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="R148" t="n">
-        <v>0</v>
+        <v>3.01</v>
       </c>
       <c r="S148" t="n">
         <v>0</v>
@@ -29712,7 +29712,7 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
@@ -29722,12 +29722,12 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Szentlőrinc SE</t>
+          <t>Pogoń Siedlce</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Videoton</t>
+          <t>Stal Rzeszów</t>
         </is>
       </c>
       <c r="G149" t="n">
@@ -29760,13 +29760,13 @@
         </is>
       </c>
       <c r="P149" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="Q149" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R149" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="S149" t="n">
         <v>0</v>
@@ -29919,12 +29919,12 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Karcag SE</t>
+          <t>Ajka</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Tiszakécske</t>
+          <t>Szeged 2011</t>
         </is>
       </c>
       <c r="G150" t="n">
@@ -30106,22 +30106,22 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Vardar</t>
+          <t>Sogndal</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Sileks</t>
+          <t>Haugesund</t>
         </is>
       </c>
       <c r="G151" t="n">
@@ -30154,13 +30154,13 @@
         </is>
       </c>
       <c r="P151" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="Q151" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="R151" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="S151" t="n">
         <v>0</v>
@@ -30303,7 +30303,7 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
@@ -30313,12 +30313,12 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Mebrat Hayl</t>
+          <t>Apollon</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Fasil Ketema</t>
+          <t>APOEL</t>
         </is>
       </c>
       <c r="G152" t="n">
@@ -30500,7 +30500,7 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
@@ -30510,12 +30510,12 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Ajka</t>
+          <t>LASK Linz</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Szeged 2011</t>
+          <t>Salzburg</t>
         </is>
       </c>
       <c r="G153" t="n">
@@ -30548,13 +30548,13 @@
         </is>
       </c>
       <c r="P153" t="n">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="Q153" t="n">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="R153" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="S153" t="n">
         <v>0</v>
@@ -30697,7 +30697,7 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
@@ -30707,12 +30707,12 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Budafoki MTE</t>
+          <t>Mebrat Hayl</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>BVSC</t>
+          <t>Fasil Ketema</t>
         </is>
       </c>
       <c r="G154" t="n">
@@ -30904,12 +30904,12 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Kecskeméti TE</t>
+          <t>Karcag SE</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Mezőkövesd-Zsóry</t>
+          <t>Tiszakécske</t>
         </is>
       </c>
       <c r="G155" t="n">
@@ -31091,22 +31091,22 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Saburtalo</t>
+          <t>Kecskeméti TE</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Torpedo Kutaisi</t>
+          <t>Mezőkövesd-Zsóry</t>
         </is>
       </c>
       <c r="G156" t="n">
@@ -31288,22 +31288,22 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Shkendija</t>
+          <t>Strømmen</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Struga</t>
+          <t>Hødd</t>
         </is>
       </c>
       <c r="G157" t="n">
@@ -31336,13 +31336,13 @@
         </is>
       </c>
       <c r="P157" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Q157" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R157" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="S157" t="n">
         <v>0</v>
@@ -31889,12 +31889,12 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>Al Bataeh</t>
+          <t>Al Ain</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Al Sharjah</t>
+          <t>Al Dhafra</t>
         </is>
       </c>
       <c r="G160" t="n">
@@ -32086,12 +32086,12 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Al Ain</t>
+          <t>Al Bataeh</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Al Dhafra</t>
+          <t>Al Sharjah</t>
         </is>
       </c>
       <c r="G161" t="n">
@@ -32470,7 +32470,7 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
@@ -32480,12 +32480,12 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>Köln</t>
+          <t>Nieciecza</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Heidenheim</t>
+          <t>Legia Warszawa</t>
         </is>
       </c>
       <c r="G163" t="n">
@@ -32518,13 +32518,13 @@
         </is>
       </c>
       <c r="P163" t="n">
-        <v>1.78</v>
+        <v>4.09</v>
       </c>
       <c r="Q163" t="n">
-        <v>4.32</v>
+        <v>3.78</v>
       </c>
       <c r="R163" t="n">
-        <v>4.52</v>
+        <v>1.77</v>
       </c>
       <c r="S163" t="n">
         <v>0</v>
@@ -32569,10 +32569,10 @@
         <v>0</v>
       </c>
       <c r="AG163" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AH163" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AI163" t="n">
         <v>0</v>
@@ -32667,7 +32667,7 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
@@ -32677,12 +32677,12 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>West Ham United</t>
+          <t>Sekhukhune United</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Kaizer Chiefs</t>
         </is>
       </c>
       <c r="G164" t="n">
@@ -32715,13 +32715,13 @@
         </is>
       </c>
       <c r="P164" t="n">
-        <v>5.17</v>
+        <v>0</v>
       </c>
       <c r="Q164" t="n">
-        <v>4.37</v>
+        <v>0</v>
       </c>
       <c r="R164" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="S164" t="n">
         <v>0</v>
@@ -32760,10 +32760,10 @@
         <v>0</v>
       </c>
       <c r="AE164" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AF164" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AG164" t="n">
         <v>0</v>
@@ -32864,7 +32864,7 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
@@ -32874,12 +32874,12 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>Sekhukhune United</t>
+          <t>West Ham United</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Kaizer Chiefs</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="G165" t="n">
@@ -32912,13 +32912,13 @@
         </is>
       </c>
       <c r="P165" t="n">
-        <v>0</v>
+        <v>5.17</v>
       </c>
       <c r="Q165" t="n">
-        <v>0</v>
+        <v>4.37</v>
       </c>
       <c r="R165" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="S165" t="n">
         <v>0</v>
@@ -32957,10 +32957,10 @@
         <v>0</v>
       </c>
       <c r="AE165" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AF165" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AG165" t="n">
         <v>0</v>
@@ -33061,7 +33061,7 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
@@ -33071,12 +33071,12 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>Nieciecza</t>
+          <t>Köln</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Legia Warszawa</t>
+          <t>Heidenheim</t>
         </is>
       </c>
       <c r="G166" t="n">
@@ -33109,13 +33109,13 @@
         </is>
       </c>
       <c r="P166" t="n">
-        <v>4.09</v>
+        <v>1.78</v>
       </c>
       <c r="Q166" t="n">
-        <v>3.78</v>
+        <v>4.32</v>
       </c>
       <c r="R166" t="n">
-        <v>1.77</v>
+        <v>4.52</v>
       </c>
       <c r="S166" t="n">
         <v>0</v>
@@ -33160,10 +33160,10 @@
         <v>0</v>
       </c>
       <c r="AG166" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AH166" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AI166" t="n">
         <v>0</v>
@@ -33258,22 +33258,22 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>Panevėžys</t>
+          <t>Dečić</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Kauno Žalgiris</t>
+          <t>FK Jezero Plav</t>
         </is>
       </c>
       <c r="G167" t="n">
@@ -33455,7 +33455,7 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
@@ -33465,12 +33465,12 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>Brøndby</t>
+          <t>Mladost DG</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>AGF</t>
+          <t>Petrovac</t>
         </is>
       </c>
       <c r="G168" t="n">
@@ -33652,7 +33652,7 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
@@ -33662,12 +33662,12 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>Arsenal Tivat</t>
+          <t>Vysočina Jihlava</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Sutjeska</t>
+          <t>Hanácká</t>
         </is>
       </c>
       <c r="G169" t="n">
@@ -33849,7 +33849,7 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
@@ -33859,12 +33859,12 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>Parma</t>
+          <t>Dinamo Bucureşti</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Roma</t>
+          <t>Argeș</t>
         </is>
       </c>
       <c r="G170" t="n">
@@ -33897,13 +33897,13 @@
         </is>
       </c>
       <c r="P170" t="n">
-        <v>5</v>
+        <v>1.83</v>
       </c>
       <c r="Q170" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="R170" t="n">
-        <v>1.75</v>
+        <v>4.3</v>
       </c>
       <c r="S170" t="n">
         <v>0</v>
@@ -34046,7 +34046,7 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
@@ -34056,12 +34056,12 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>Dečić</t>
+          <t>Parma</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>FK Jezero Plav</t>
+          <t>Roma</t>
         </is>
       </c>
       <c r="G171" t="n">
@@ -34094,13 +34094,13 @@
         </is>
       </c>
       <c r="P171" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="Q171" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R171" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="S171" t="n">
         <v>0</v>
@@ -34243,22 +34243,22 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>Dinamo Bucureşti</t>
+          <t>Panevėžys</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Argeș</t>
+          <t>Kauno Žalgiris</t>
         </is>
       </c>
       <c r="G172" t="n">
@@ -34291,13 +34291,13 @@
         </is>
       </c>
       <c r="P172" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="Q172" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="R172" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="S172" t="n">
         <v>0</v>
@@ -34637,7 +34637,7 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
@@ -34647,12 +34647,12 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>Vysočina Jihlava</t>
+          <t>Mornar</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Hanácká</t>
+          <t>Bokelj</t>
         </is>
       </c>
       <c r="G174" t="n">
@@ -35031,7 +35031,7 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
@@ -35041,12 +35041,12 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>Mladost DG</t>
+          <t>Brøndby</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Petrovac</t>
+          <t>AGF</t>
         </is>
       </c>
       <c r="G176" t="n">
@@ -35238,12 +35238,12 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>Mornar</t>
+          <t>Arsenal Tivat</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Bokelj</t>
+          <t>Sutjeska</t>
         </is>
       </c>
       <c r="G177" t="n">
@@ -35622,22 +35622,22 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>Skála</t>
+          <t>Slaven Koprivnica</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>AB</t>
+          <t>Gorica</t>
         </is>
       </c>
       <c r="G179" t="n">
@@ -35819,22 +35819,22 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>Slaven Koprivnica</t>
+          <t>Skála</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Gorica</t>
+          <t>AB</t>
         </is>
       </c>
       <c r="G180" t="n">
@@ -36410,7 +36410,7 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
@@ -36420,12 +36420,12 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>Union Saint-Gilloise</t>
+          <t>Jablonec</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>KV Mechelen</t>
+          <t>Hradec Králové</t>
         </is>
       </c>
       <c r="G183" t="n">
@@ -36458,13 +36458,13 @@
         </is>
       </c>
       <c r="P183" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="Q183" t="n">
-        <v>5.66</v>
+        <v>0</v>
       </c>
       <c r="R183" t="n">
-        <v>8.98</v>
+        <v>0</v>
       </c>
       <c r="S183" t="n">
         <v>0</v>
@@ -36607,7 +36607,7 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
@@ -36617,12 +36617,12 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>Córdoba</t>
+          <t>Lokomotiv Moskva</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Granada CF</t>
+          <t>Baltika</t>
         </is>
       </c>
       <c r="G184" t="n">
@@ -36655,13 +36655,13 @@
         </is>
       </c>
       <c r="P184" t="n">
-        <v>1.91</v>
+        <v>2.25</v>
       </c>
       <c r="Q184" t="n">
-        <v>3.53</v>
+        <v>3.66</v>
       </c>
       <c r="R184" t="n">
-        <v>3.91</v>
+        <v>3.36</v>
       </c>
       <c r="S184" t="n">
         <v>0</v>
@@ -36700,10 +36700,10 @@
         <v>0</v>
       </c>
       <c r="AE184" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AF184" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AG184" t="n">
         <v>0</v>
@@ -36814,12 +36814,12 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>AEK Athens</t>
+          <t>Olympiakos Piraeus</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Panathinaikos</t>
+          <t>PAOK</t>
         </is>
       </c>
       <c r="G185" t="n">
@@ -36852,13 +36852,13 @@
         </is>
       </c>
       <c r="P185" t="n">
-        <v>1.45</v>
+        <v>1.82</v>
       </c>
       <c r="Q185" t="n">
-        <v>3.8</v>
+        <v>3.1</v>
       </c>
       <c r="R185" t="n">
-        <v>6.76</v>
+        <v>4.56</v>
       </c>
       <c r="S185" t="n">
         <v>0</v>
@@ -37001,22 +37001,22 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>Bačka Topola</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Javor Ivanjica</t>
+          <t>San Luis</t>
         </is>
       </c>
       <c r="G186" t="n">
@@ -37049,13 +37049,13 @@
         </is>
       </c>
       <c r="P186" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="Q186" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="R186" t="n">
-        <v>5.75</v>
+        <v>0</v>
       </c>
       <c r="S186" t="n">
         <v>0</v>
@@ -37094,10 +37094,10 @@
         <v>0</v>
       </c>
       <c r="AE186" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AF186" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AG186" t="n">
         <v>0</v>
@@ -37198,22 +37198,22 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Union Saint-Gilloise</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>San Luis</t>
+          <t>KV Mechelen</t>
         </is>
       </c>
       <c r="G187" t="n">
@@ -37246,13 +37246,13 @@
         </is>
       </c>
       <c r="P187" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Q187" t="n">
-        <v>0</v>
+        <v>5.66</v>
       </c>
       <c r="R187" t="n">
-        <v>0</v>
+        <v>8.98</v>
       </c>
       <c r="S187" t="n">
         <v>0</v>
@@ -37395,22 +37395,22 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>Copiapó</t>
+          <t>Bačka Topola</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Unión San Felipe</t>
+          <t>Javor Ivanjica</t>
         </is>
       </c>
       <c r="G188" t="n">
@@ -37443,13 +37443,13 @@
         </is>
       </c>
       <c r="P188" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="Q188" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="R188" t="n">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="S188" t="n">
         <v>0</v>
@@ -37488,10 +37488,10 @@
         <v>0</v>
       </c>
       <c r="AE188" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AF188" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG188" t="n">
         <v>0</v>
@@ -37592,7 +37592,7 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
@@ -37602,12 +37602,12 @@
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>Olympiakos Piraeus</t>
+          <t>Real Oviedo</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>PAOK</t>
+          <t>Getafe CF</t>
         </is>
       </c>
       <c r="G189" t="n">
@@ -37640,13 +37640,13 @@
         </is>
       </c>
       <c r="P189" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="Q189" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="R189" t="n">
-        <v>4.56</v>
+        <v>0</v>
       </c>
       <c r="S189" t="n">
         <v>0</v>
@@ -37986,7 +37986,7 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
@@ -37996,12 +37996,12 @@
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>Real Oviedo</t>
+          <t>IMT Novi Beograd</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Getafe CF</t>
+          <t>Radnički Kragujevac</t>
         </is>
       </c>
       <c r="G191" t="n">
@@ -38034,13 +38034,13 @@
         </is>
       </c>
       <c r="P191" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Q191" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R191" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="S191" t="n">
         <v>0</v>
@@ -38183,7 +38183,7 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
@@ -38193,12 +38193,12 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>IMT Novi Beograd</t>
+          <t>AEK Athens</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>Panathinaikos</t>
         </is>
       </c>
       <c r="G192" t="n">
@@ -38231,13 +38231,13 @@
         </is>
       </c>
       <c r="P192" t="n">
-        <v>2.15</v>
+        <v>1.45</v>
       </c>
       <c r="Q192" t="n">
-        <v>3.3</v>
+        <v>3.8</v>
       </c>
       <c r="R192" t="n">
-        <v>3.25</v>
+        <v>6.76</v>
       </c>
       <c r="S192" t="n">
         <v>0</v>
@@ -38380,22 +38380,22 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>Jablonec</t>
+          <t>Kansas City</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Hradec Králové</t>
+          <t>Chicago Red Stars</t>
         </is>
       </c>
       <c r="G193" t="n">
@@ -38428,13 +38428,13 @@
         </is>
       </c>
       <c r="P193" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Q193" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="R193" t="n">
-        <v>0</v>
+        <v>7.95</v>
       </c>
       <c r="S193" t="n">
         <v>0</v>
@@ -38577,7 +38577,7 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
@@ -38587,12 +38587,12 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>Lokomotiv Moskva</t>
+          <t>Radnički Niš</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Baltika</t>
+          <t>LFK Mladost Lučani</t>
         </is>
       </c>
       <c r="G194" t="n">
@@ -38625,13 +38625,13 @@
         </is>
       </c>
       <c r="P194" t="n">
-        <v>2.25</v>
+        <v>1.71</v>
       </c>
       <c r="Q194" t="n">
-        <v>3.66</v>
+        <v>3.54</v>
       </c>
       <c r="R194" t="n">
-        <v>3.36</v>
+        <v>4.32</v>
       </c>
       <c r="S194" t="n">
         <v>0</v>
@@ -38670,10 +38670,10 @@
         <v>0</v>
       </c>
       <c r="AE194" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AF194" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG194" t="n">
         <v>0</v>
@@ -38774,22 +38774,22 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>Radnički Niš</t>
+          <t>Copiapó</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>LFK Mladost Lučani</t>
+          <t>Unión San Felipe</t>
         </is>
       </c>
       <c r="G195" t="n">
@@ -38822,13 +38822,13 @@
         </is>
       </c>
       <c r="P195" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="Q195" t="n">
-        <v>3.54</v>
+        <v>0</v>
       </c>
       <c r="R195" t="n">
-        <v>4.32</v>
+        <v>0</v>
       </c>
       <c r="S195" t="n">
         <v>0</v>
@@ -38867,10 +38867,10 @@
         <v>0</v>
       </c>
       <c r="AE195" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AF195" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AG195" t="n">
         <v>0</v>
@@ -38971,7 +38971,7 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
@@ -38981,12 +38981,12 @@
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>Spartak Subotica</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Napredak</t>
+          <t>Granada CF</t>
         </is>
       </c>
       <c r="G196" t="n">
@@ -39019,13 +39019,13 @@
         </is>
       </c>
       <c r="P196" t="n">
-        <v>1.55</v>
+        <v>1.91</v>
       </c>
       <c r="Q196" t="n">
-        <v>3.95</v>
+        <v>3.53</v>
       </c>
       <c r="R196" t="n">
-        <v>4.96</v>
+        <v>3.91</v>
       </c>
       <c r="S196" t="n">
         <v>0</v>
@@ -39064,10 +39064,10 @@
         <v>0</v>
       </c>
       <c r="AE196" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AF196" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AG196" t="n">
         <v>0</v>
@@ -39168,22 +39168,22 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>Kansas City</t>
+          <t>Spartak Subotica</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Chicago Red Stars</t>
+          <t>Napredak</t>
         </is>
       </c>
       <c r="G197" t="n">
@@ -39216,13 +39216,13 @@
         </is>
       </c>
       <c r="P197" t="n">
-        <v>1.3</v>
+        <v>1.55</v>
       </c>
       <c r="Q197" t="n">
-        <v>5.1</v>
+        <v>3.95</v>
       </c>
       <c r="R197" t="n">
-        <v>7.95</v>
+        <v>4.96</v>
       </c>
       <c r="S197" t="n">
         <v>0</v>
@@ -39562,22 +39562,22 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>KA</t>
+          <t>Békéscsaba</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>ÍBV</t>
+          <t>Kozármisleny</t>
         </is>
       </c>
       <c r="G199" t="n">
@@ -39610,13 +39610,13 @@
         </is>
       </c>
       <c r="P199" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="Q199" t="n">
-        <v>4.45</v>
+        <v>0</v>
       </c>
       <c r="R199" t="n">
-        <v>5.12</v>
+        <v>0</v>
       </c>
       <c r="S199" t="n">
         <v>0</v>
@@ -39956,7 +39956,7 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
@@ -39966,12 +39966,12 @@
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>Hapoel Katamon</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Bnei Sakhnin</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="G201" t="n">
@@ -40004,13 +40004,13 @@
         </is>
       </c>
       <c r="P201" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Q201" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R201" t="n">
-        <v>0</v>
+        <v>3.13</v>
       </c>
       <c r="S201" t="n">
         <v>0</v>
@@ -40049,10 +40049,10 @@
         <v>0</v>
       </c>
       <c r="AE201" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AF201" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AG201" t="n">
         <v>0</v>
@@ -40153,7 +40153,7 @@
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
@@ -40163,12 +40163,12 @@
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>Ironi Tiberias</t>
+          <t>Csákvári TK</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>Maccabi Netanya</t>
+          <t>Soroksár SC</t>
         </is>
       </c>
       <c r="G202" t="n">
@@ -40350,7 +40350,7 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
@@ -40360,12 +40360,12 @@
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>Csákvári TK</t>
+          <t>Hapoel Katamon</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>Soroksár SC</t>
+          <t>Bnei Sakhnin</t>
         </is>
       </c>
       <c r="G203" t="n">
@@ -40547,7 +40547,7 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
@@ -40557,12 +40557,12 @@
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>Békéscsaba</t>
+          <t>Ironi Tiberias</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>Kozármisleny</t>
+          <t>Maccabi Netanya</t>
         </is>
       </c>
       <c r="G204" t="n">
@@ -40744,7 +40744,7 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
@@ -40754,12 +40754,12 @@
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>Dinamo Batumi</t>
+          <t>KA</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>Samgurali</t>
+          <t>ÍBV</t>
         </is>
       </c>
       <c r="G205" t="n">
@@ -40792,13 +40792,13 @@
         </is>
       </c>
       <c r="P205" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="Q205" t="n">
-        <v>0</v>
+        <v>4.45</v>
       </c>
       <c r="R205" t="n">
-        <v>0</v>
+        <v>5.12</v>
       </c>
       <c r="S205" t="n">
         <v>0</v>
@@ -40941,22 +40941,22 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Dinamo Batumi</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Samgurali</t>
         </is>
       </c>
       <c r="G206" t="n">
@@ -40989,13 +40989,13 @@
         </is>
       </c>
       <c r="P206" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Q206" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="R206" t="n">
-        <v>3.13</v>
+        <v>0</v>
       </c>
       <c r="S206" t="n">
         <v>0</v>
@@ -41034,10 +41034,10 @@
         <v>0</v>
       </c>
       <c r="AE206" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AF206" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AG206" t="n">
         <v>0</v>
@@ -41729,22 +41729,22 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>UTS Rabat</t>
+          <t>New England II</t>
         </is>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>Maghreb Fès</t>
+          <t>New York City II</t>
         </is>
       </c>
       <c r="G210" t="n">
@@ -41926,7 +41926,7 @@
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
@@ -41936,12 +41936,12 @@
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>CODM Meknès</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>RSB Berkane</t>
+          <t>Dhamk</t>
         </is>
       </c>
       <c r="G211" t="n">
@@ -42123,22 +42123,22 @@
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>New England II</t>
+          <t>UTS Rabat</t>
         </is>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>New York City II</t>
+          <t>Maghreb Fès</t>
         </is>
       </c>
       <c r="G212" t="n">
@@ -42320,7 +42320,7 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
@@ -42330,12 +42330,12 @@
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>CODM Meknès</t>
         </is>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>Dhamk</t>
+          <t>RSB Berkane</t>
         </is>
       </c>
       <c r="G213" t="n">
@@ -43108,7 +43108,7 @@
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
@@ -43118,12 +43118,12 @@
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>FC Barcelona</t>
+          <t>Rennes</t>
         </is>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Paris</t>
         </is>
       </c>
       <c r="G217" t="n">
@@ -43156,13 +43156,13 @@
         </is>
       </c>
       <c r="P217" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="Q217" t="n">
-        <v>0</v>
+        <v>4.73</v>
       </c>
       <c r="R217" t="n">
-        <v>0</v>
+        <v>5.79</v>
       </c>
       <c r="S217" t="n">
         <v>0</v>
@@ -43207,10 +43207,10 @@
         <v>0</v>
       </c>
       <c r="AG217" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AH217" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AI217" t="n">
         <v>0</v>
@@ -43512,12 +43512,12 @@
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>Toulouse</t>
+          <t>Le Havre</t>
         </is>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>Olympique Lyonnais</t>
+          <t>Olympique Marseille</t>
         </is>
       </c>
       <c r="G219" t="n">
@@ -43550,13 +43550,13 @@
         </is>
       </c>
       <c r="P219" t="n">
-        <v>3.8</v>
+        <v>4.68</v>
       </c>
       <c r="Q219" t="n">
-        <v>3.78</v>
+        <v>4.32</v>
       </c>
       <c r="R219" t="n">
-        <v>2.05</v>
+        <v>1.76</v>
       </c>
       <c r="S219" t="n">
         <v>0</v>
@@ -43595,10 +43595,10 @@
         <v>0</v>
       </c>
       <c r="AE219" t="n">
-        <v>1.73</v>
+        <v>1.58</v>
       </c>
       <c r="AF219" t="n">
-        <v>1.98</v>
+        <v>2.25</v>
       </c>
       <c r="AG219" t="n">
         <v>0</v>
@@ -43699,22 +43699,22 @@
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>Rennes</t>
+          <t>Remo</t>
         </is>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>Paris</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="G220" t="n">
@@ -43747,13 +43747,13 @@
         </is>
       </c>
       <c r="P220" t="n">
-        <v>1.59</v>
+        <v>5.3</v>
       </c>
       <c r="Q220" t="n">
-        <v>4.73</v>
+        <v>3.73</v>
       </c>
       <c r="R220" t="n">
-        <v>5.79</v>
+        <v>1.71</v>
       </c>
       <c r="S220" t="n">
         <v>0</v>
@@ -43792,16 +43792,16 @@
         <v>0</v>
       </c>
       <c r="AE220" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AF220" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AG220" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AH220" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AI220" t="n">
         <v>0</v>
@@ -43906,12 +43906,12 @@
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Angers SCO</t>
         </is>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>Brest</t>
+          <t>Strasbourg</t>
         </is>
       </c>
       <c r="G221" t="n">
@@ -43944,13 +43944,13 @@
         </is>
       </c>
       <c r="P221" t="n">
-        <v>1.18</v>
+        <v>4.05</v>
       </c>
       <c r="Q221" t="n">
-        <v>9.15</v>
+        <v>3.76</v>
       </c>
       <c r="R221" t="n">
-        <v>17</v>
+        <v>1.99</v>
       </c>
       <c r="S221" t="n">
         <v>0</v>
@@ -43989,16 +43989,16 @@
         <v>0</v>
       </c>
       <c r="AE221" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AF221" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG221" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AH221" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AI221" t="n">
         <v>0</v>
@@ -44093,22 +44093,22 @@
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>Monaco</t>
+          <t>Club Atlético Güemes</t>
         </is>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>Lille</t>
+          <t>Quilmes</t>
         </is>
       </c>
       <c r="G222" t="n">
@@ -44141,13 +44141,13 @@
         </is>
       </c>
       <c r="P222" t="n">
-        <v>2.38</v>
+        <v>2.61</v>
       </c>
       <c r="Q222" t="n">
-        <v>3.9</v>
+        <v>2.74</v>
       </c>
       <c r="R222" t="n">
-        <v>2.96</v>
+        <v>2.76</v>
       </c>
       <c r="S222" t="n">
         <v>0</v>
@@ -44180,16 +44180,16 @@
         <v>0</v>
       </c>
       <c r="AC222" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AD222" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AE222" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AF222" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AG222" t="n">
         <v>0</v>
@@ -44487,22 +44487,22 @@
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>Club Atlético Güemes</t>
+          <t>Toulouse</t>
         </is>
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>Quilmes</t>
+          <t>Olympique Lyonnais</t>
         </is>
       </c>
       <c r="G224" t="n">
@@ -44535,13 +44535,13 @@
         </is>
       </c>
       <c r="P224" t="n">
-        <v>2.61</v>
+        <v>3.8</v>
       </c>
       <c r="Q224" t="n">
-        <v>2.74</v>
+        <v>3.78</v>
       </c>
       <c r="R224" t="n">
-        <v>2.76</v>
+        <v>2.05</v>
       </c>
       <c r="S224" t="n">
         <v>0</v>
@@ -44574,16 +44574,16 @@
         <v>0</v>
       </c>
       <c r="AC224" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AD224" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AE224" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AF224" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AG224" t="n">
         <v>0</v>
@@ -44684,7 +44684,7 @@
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
@@ -44694,12 +44694,12 @@
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>Independiente Petrolero</t>
+          <t>Náutico</t>
         </is>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>Club Always Ready</t>
+          <t>América Mineiro</t>
         </is>
       </c>
       <c r="G225" t="n">
@@ -44732,13 +44732,13 @@
         </is>
       </c>
       <c r="P225" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="Q225" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R225" t="n">
-        <v>0</v>
+        <v>4.39</v>
       </c>
       <c r="S225" t="n">
         <v>0</v>
@@ -44881,7 +44881,7 @@
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
@@ -44891,12 +44891,12 @@
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>Angers SCO</t>
+          <t>FC Barcelona</t>
         </is>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>Strasbourg</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="G226" t="n">
@@ -44929,13 +44929,13 @@
         </is>
       </c>
       <c r="P226" t="n">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="Q226" t="n">
-        <v>3.76</v>
+        <v>0</v>
       </c>
       <c r="R226" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="S226" t="n">
         <v>0</v>
@@ -44974,10 +44974,10 @@
         <v>0</v>
       </c>
       <c r="AE226" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AF226" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AG226" t="n">
         <v>0</v>
@@ -45078,22 +45078,22 @@
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>Le Havre</t>
+          <t>Independiente Petrolero</t>
         </is>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>Olympique Marseille</t>
+          <t>Club Always Ready</t>
         </is>
       </c>
       <c r="G227" t="n">
@@ -45126,13 +45126,13 @@
         </is>
       </c>
       <c r="P227" t="n">
-        <v>4.68</v>
+        <v>0</v>
       </c>
       <c r="Q227" t="n">
-        <v>4.32</v>
+        <v>0</v>
       </c>
       <c r="R227" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="S227" t="n">
         <v>0</v>
@@ -45171,10 +45171,10 @@
         <v>0</v>
       </c>
       <c r="AE227" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AF227" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AG227" t="n">
         <v>0</v>
@@ -45275,22 +45275,22 @@
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>Atlético Mineiro</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>Botafogo</t>
+          <t>Brest</t>
         </is>
       </c>
       <c r="G228" t="n">
@@ -45323,13 +45323,13 @@
         </is>
       </c>
       <c r="P228" t="n">
-        <v>2.15</v>
+        <v>1.18</v>
       </c>
       <c r="Q228" t="n">
-        <v>3.44</v>
+        <v>9.15</v>
       </c>
       <c r="R228" t="n">
-        <v>3.5</v>
+        <v>17</v>
       </c>
       <c r="S228" t="n">
         <v>0</v>
@@ -45368,16 +45368,16 @@
         <v>0</v>
       </c>
       <c r="AE228" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AF228" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AG228" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AH228" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AI228" t="n">
         <v>0</v>
@@ -45482,12 +45482,12 @@
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>Remo</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>Botafogo</t>
         </is>
       </c>
       <c r="G229" t="n">
@@ -45520,13 +45520,13 @@
         </is>
       </c>
       <c r="P229" t="n">
-        <v>5.3</v>
+        <v>2.15</v>
       </c>
       <c r="Q229" t="n">
-        <v>3.73</v>
+        <v>3.44</v>
       </c>
       <c r="R229" t="n">
-        <v>1.71</v>
+        <v>3.5</v>
       </c>
       <c r="S229" t="n">
         <v>0</v>
@@ -45568,7 +45568,7 @@
         <v>1.95</v>
       </c>
       <c r="AF229" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="AG229" t="n">
         <v>0</v>
@@ -45669,22 +45669,22 @@
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>Náutico</t>
+          <t>Monaco</t>
         </is>
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>América Mineiro</t>
+          <t>Lille</t>
         </is>
       </c>
       <c r="G230" t="n">
@@ -45717,13 +45717,13 @@
         </is>
       </c>
       <c r="P230" t="n">
-        <v>1.79</v>
+        <v>2.38</v>
       </c>
       <c r="Q230" t="n">
-        <v>3.5</v>
+        <v>3.9</v>
       </c>
       <c r="R230" t="n">
-        <v>4.39</v>
+        <v>2.96</v>
       </c>
       <c r="S230" t="n">
         <v>0</v>
@@ -45762,10 +45762,10 @@
         <v>0</v>
       </c>
       <c r="AE230" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AF230" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AG230" t="n">
         <v>0</v>
@@ -46073,12 +46073,12 @@
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>Chaco For Ever</t>
+          <t>San Martín San Juan</t>
         </is>
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>Ciudad de Bolívar</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="G232" t="n">
@@ -46111,13 +46111,13 @@
         </is>
       </c>
       <c r="P232" t="n">
-        <v>2.14</v>
+        <v>1.82</v>
       </c>
       <c r="Q232" t="n">
-        <v>2.73</v>
+        <v>2.98</v>
       </c>
       <c r="R232" t="n">
-        <v>3.77</v>
+        <v>4.66</v>
       </c>
       <c r="S232" t="n">
         <v>0</v>
@@ -46150,10 +46150,10 @@
         <v>0</v>
       </c>
       <c r="AC232" t="n">
-        <v>1.72</v>
+        <v>1.6</v>
       </c>
       <c r="AD232" t="n">
-        <v>1.98</v>
+        <v>2.15</v>
       </c>
       <c r="AE232" t="n">
         <v>0</v>
@@ -46270,12 +46270,12 @@
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>San Martín San Juan</t>
+          <t>Godoy Cruz</t>
         </is>
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>Patronato</t>
+          <t>Racing Córdoba</t>
         </is>
       </c>
       <c r="G233" t="n">
@@ -46308,13 +46308,13 @@
         </is>
       </c>
       <c r="P233" t="n">
-        <v>1.82</v>
+        <v>1.49</v>
       </c>
       <c r="Q233" t="n">
-        <v>2.98</v>
+        <v>3.52</v>
       </c>
       <c r="R233" t="n">
-        <v>4.66</v>
+        <v>6.94</v>
       </c>
       <c r="S233" t="n">
         <v>0</v>
@@ -46347,10 +46347,10 @@
         <v>0</v>
       </c>
       <c r="AC233" t="n">
-        <v>1.6</v>
+        <v>1.52</v>
       </c>
       <c r="AD233" t="n">
-        <v>2.15</v>
+        <v>2.35</v>
       </c>
       <c r="AE233" t="n">
         <v>0</v>
@@ -46467,12 +46467,12 @@
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>Godoy Cruz</t>
+          <t>Chaco For Ever</t>
         </is>
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>Racing Córdoba</t>
+          <t>Ciudad de Bolívar</t>
         </is>
       </c>
       <c r="G234" t="n">
@@ -46505,13 +46505,13 @@
         </is>
       </c>
       <c r="P234" t="n">
-        <v>1.49</v>
+        <v>2.14</v>
       </c>
       <c r="Q234" t="n">
-        <v>3.52</v>
+        <v>2.73</v>
       </c>
       <c r="R234" t="n">
-        <v>6.94</v>
+        <v>3.77</v>
       </c>
       <c r="S234" t="n">
         <v>0</v>
@@ -46544,10 +46544,10 @@
         <v>0</v>
       </c>
       <c r="AC234" t="n">
-        <v>1.52</v>
+        <v>1.72</v>
       </c>
       <c r="AD234" t="n">
-        <v>2.35</v>
+        <v>1.98</v>
       </c>
       <c r="AE234" t="n">
         <v>0</v>
@@ -46654,22 +46654,22 @@
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>Central Norte</t>
+          <t>Hassania Agadir</t>
         </is>
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>Deportivo Madryn</t>
+          <t>FAR Rabat</t>
         </is>
       </c>
       <c r="G235" t="n">
@@ -46702,13 +46702,13 @@
         </is>
       </c>
       <c r="P235" t="n">
-        <v>2.46</v>
+        <v>0</v>
       </c>
       <c r="Q235" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="R235" t="n">
-        <v>3.17</v>
+        <v>0</v>
       </c>
       <c r="S235" t="n">
         <v>0</v>
@@ -46741,10 +46741,10 @@
         <v>0</v>
       </c>
       <c r="AC235" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AD235" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AE235" t="n">
         <v>0</v>
@@ -46851,22 +46851,22 @@
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>Hassania Agadir</t>
+          <t>Central Norte</t>
         </is>
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>FAR Rabat</t>
+          <t>Deportivo Madryn</t>
         </is>
       </c>
       <c r="G236" t="n">
@@ -46899,13 +46899,13 @@
         </is>
       </c>
       <c r="P236" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="Q236" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="R236" t="n">
-        <v>0</v>
+        <v>3.17</v>
       </c>
       <c r="S236" t="n">
         <v>0</v>
@@ -46938,10 +46938,10 @@
         <v>0</v>
       </c>
       <c r="AC236" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AD236" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AE236" t="n">
         <v>0</v>
@@ -47048,7 +47048,7 @@
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D237" t="inlineStr">
@@ -47058,12 +47058,12 @@
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>Bay</t>
+          <t>Portland Timbers II</t>
         </is>
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>Utah Royals</t>
+          <t>LA Galaxy II</t>
         </is>
       </c>
       <c r="G237" t="n">
@@ -47442,7 +47442,7 @@
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D239" t="inlineStr">
@@ -47452,12 +47452,12 @@
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t>Portland Timbers II</t>
+          <t>Bay</t>
         </is>
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>LA Galaxy II</t>
+          <t>Utah Royals</t>
         </is>
       </c>
       <c r="G239" t="n">
@@ -47639,7 +47639,7 @@
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
@@ -47649,12 +47649,12 @@
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>CS Emelec</t>
+          <t>New York City</t>
         </is>
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>Libertad</t>
+          <t>Columbus Crew</t>
         </is>
       </c>
       <c r="G240" t="n">
@@ -47687,13 +47687,13 @@
         </is>
       </c>
       <c r="P240" t="n">
-        <v>1.67</v>
+        <v>2.23</v>
       </c>
       <c r="Q240" t="n">
-        <v>3.61</v>
+        <v>3.71</v>
       </c>
       <c r="R240" t="n">
-        <v>5.14</v>
+        <v>3.21</v>
       </c>
       <c r="S240" t="n">
         <v>0</v>
@@ -47732,10 +47732,10 @@
         <v>0</v>
       </c>
       <c r="AE240" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AF240" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AG240" t="n">
         <v>0</v>
@@ -47836,7 +47836,7 @@
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D241" t="inlineStr">
@@ -47846,12 +47846,12 @@
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>New York City</t>
+          <t>CS Emelec</t>
         </is>
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>Columbus Crew</t>
+          <t>Libertad</t>
         </is>
       </c>
       <c r="G241" t="n">
@@ -47884,13 +47884,13 @@
         </is>
       </c>
       <c r="P241" t="n">
-        <v>2.23</v>
+        <v>1.67</v>
       </c>
       <c r="Q241" t="n">
-        <v>3.71</v>
+        <v>3.61</v>
       </c>
       <c r="R241" t="n">
-        <v>3.21</v>
+        <v>5.14</v>
       </c>
       <c r="S241" t="n">
         <v>0</v>
@@ -47929,10 +47929,10 @@
         <v>0</v>
       </c>
       <c r="AE241" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AF241" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AG241" t="n">
         <v>0</v>
@@ -48427,7 +48427,7 @@
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D244" t="inlineStr">
@@ -48437,12 +48437,12 @@
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>Mirassol</t>
         </is>
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>Chapecoense</t>
         </is>
       </c>
       <c r="G244" t="n">
@@ -48475,13 +48475,13 @@
         </is>
       </c>
       <c r="P244" t="n">
-        <v>2.81</v>
+        <v>1.79</v>
       </c>
       <c r="Q244" t="n">
-        <v>3.08</v>
+        <v>3.62</v>
       </c>
       <c r="R244" t="n">
-        <v>2.51</v>
+        <v>4.84</v>
       </c>
       <c r="S244" t="n">
         <v>0</v>
@@ -48520,10 +48520,10 @@
         <v>0</v>
       </c>
       <c r="AE244" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AF244" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG244" t="n">
         <v>0</v>
@@ -48634,12 +48634,12 @@
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>Corinthians</t>
         </is>
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>Bragantino</t>
+          <t>São Paulo</t>
         </is>
       </c>
       <c r="G245" t="n">
@@ -48672,13 +48672,13 @@
         </is>
       </c>
       <c r="P245" t="n">
-        <v>2.13</v>
+        <v>2.26</v>
       </c>
       <c r="Q245" t="n">
-        <v>3.34</v>
+        <v>3.22</v>
       </c>
       <c r="R245" t="n">
-        <v>3.67</v>
+        <v>3.46</v>
       </c>
       <c r="S245" t="n">
         <v>0</v>
@@ -48717,10 +48717,10 @@
         <v>0</v>
       </c>
       <c r="AE245" t="n">
-        <v>1.95</v>
+        <v>2.25</v>
       </c>
       <c r="AF245" t="n">
-        <v>1.73</v>
+        <v>1.57</v>
       </c>
       <c r="AG245" t="n">
         <v>0</v>
@@ -48821,7 +48821,7 @@
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D246" t="inlineStr">
@@ -48831,12 +48831,12 @@
       </c>
       <c r="E246" t="inlineStr">
         <is>
-          <t>Mirassol</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>Chapecoense</t>
+          <t>Fortaleza</t>
         </is>
       </c>
       <c r="G246" t="n">
@@ -48869,13 +48869,13 @@
         </is>
       </c>
       <c r="P246" t="n">
-        <v>1.79</v>
+        <v>2.81</v>
       </c>
       <c r="Q246" t="n">
-        <v>3.62</v>
+        <v>3.08</v>
       </c>
       <c r="R246" t="n">
-        <v>4.84</v>
+        <v>2.51</v>
       </c>
       <c r="S246" t="n">
         <v>0</v>
@@ -48914,10 +48914,10 @@
         <v>0</v>
       </c>
       <c r="AE246" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AF246" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AG246" t="n">
         <v>0</v>
@@ -49028,12 +49028,12 @@
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>Corinthians</t>
+          <t>Santos</t>
         </is>
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>São Paulo</t>
+          <t>Bragantino</t>
         </is>
       </c>
       <c r="G247" t="n">
@@ -49066,13 +49066,13 @@
         </is>
       </c>
       <c r="P247" t="n">
-        <v>2.26</v>
+        <v>2.13</v>
       </c>
       <c r="Q247" t="n">
-        <v>3.22</v>
+        <v>3.34</v>
       </c>
       <c r="R247" t="n">
-        <v>3.46</v>
+        <v>3.67</v>
       </c>
       <c r="S247" t="n">
         <v>0</v>
@@ -49111,10 +49111,10 @@
         <v>0</v>
       </c>
       <c r="AE247" t="n">
-        <v>2.25</v>
+        <v>1.95</v>
       </c>
       <c r="AF247" t="n">
-        <v>1.57</v>
+        <v>1.73</v>
       </c>
       <c r="AG247" t="n">
         <v>0</v>
@@ -49412,7 +49412,7 @@
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D249" t="inlineStr">
@@ -49422,12 +49422,12 @@
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>Grêmio</t>
+          <t>Novorizontino</t>
         </is>
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="G249" t="n">
@@ -49460,13 +49460,13 @@
         </is>
       </c>
       <c r="P249" t="n">
-        <v>3.79</v>
+        <v>0</v>
       </c>
       <c r="Q249" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="R249" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="S249" t="n">
         <v>0</v>
@@ -49505,10 +49505,10 @@
         <v>0</v>
       </c>
       <c r="AE249" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AF249" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AG249" t="n">
         <v>0</v>
@@ -49609,7 +49609,7 @@
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D250" t="inlineStr">
@@ -49619,12 +49619,12 @@
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>Grêmio</t>
         </is>
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="G250" t="n">
@@ -49657,13 +49657,13 @@
         </is>
       </c>
       <c r="P250" t="n">
-        <v>0</v>
+        <v>3.79</v>
       </c>
       <c r="Q250" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="R250" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="S250" t="n">
         <v>0</v>
@@ -49702,10 +49702,10 @@
         <v>0</v>
       </c>
       <c r="AE250" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AF250" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AG250" t="n">
         <v>0</v>
@@ -49806,7 +49806,7 @@
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
@@ -49816,12 +49816,12 @@
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>Seattle Reign</t>
+          <t>Atlanta United II</t>
         </is>
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>Washington Spirit</t>
+          <t>Orlando City II</t>
         </is>
       </c>
       <c r="G251" t="n">
@@ -49854,13 +49854,13 @@
         </is>
       </c>
       <c r="P251" t="n">
-        <v>4.44</v>
+        <v>0</v>
       </c>
       <c r="Q251" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="R251" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="S251" t="n">
         <v>0</v>
@@ -49899,10 +49899,10 @@
         <v>0</v>
       </c>
       <c r="AE251" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="AF251" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AG251" t="n">
         <v>0</v>
@@ -50003,7 +50003,7 @@
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D252" t="inlineStr">
@@ -50013,12 +50013,12 @@
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>Minnesota United</t>
+          <t>Seattle Reign</t>
         </is>
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>Austin</t>
+          <t>Washington Spirit</t>
         </is>
       </c>
       <c r="G252" t="n">
@@ -50051,13 +50051,13 @@
         </is>
       </c>
       <c r="P252" t="n">
-        <v>1.72</v>
+        <v>4.44</v>
       </c>
       <c r="Q252" t="n">
-        <v>3.97</v>
+        <v>3.5</v>
       </c>
       <c r="R252" t="n">
-        <v>5.09</v>
+        <v>1.73</v>
       </c>
       <c r="S252" t="n">
         <v>0</v>
@@ -50096,10 +50096,10 @@
         <v>0</v>
       </c>
       <c r="AE252" t="n">
-        <v>1.7</v>
+        <v>1.99</v>
       </c>
       <c r="AF252" t="n">
-        <v>2</v>
+        <v>1.76</v>
       </c>
       <c r="AG252" t="n">
         <v>0</v>
@@ -50200,7 +50200,7 @@
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
@@ -50210,12 +50210,12 @@
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>Atlanta United II</t>
+          <t>Minnesota United</t>
         </is>
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>Orlando City II</t>
+          <t>Austin</t>
         </is>
       </c>
       <c r="G253" t="n">
@@ -50248,13 +50248,13 @@
         </is>
       </c>
       <c r="P253" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="Q253" t="n">
-        <v>0</v>
+        <v>3.97</v>
       </c>
       <c r="R253" t="n">
-        <v>0</v>
+        <v>5.09</v>
       </c>
       <c r="S253" t="n">
         <v>0</v>
@@ -50293,10 +50293,10 @@
         <v>0</v>
       </c>
       <c r="AE253" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AF253" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG253" t="n">
         <v>0</v>
@@ -50594,7 +50594,7 @@
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D255" t="inlineStr">
@@ -50604,12 +50604,12 @@
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>Vasco da Gama</t>
+          <t>Blooming</t>
         </is>
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>Atlético PR</t>
+          <t>Bolívar</t>
         </is>
       </c>
       <c r="G255" t="n">
@@ -50642,13 +50642,13 @@
         </is>
       </c>
       <c r="P255" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="Q255" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="R255" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="S255" t="n">
         <v>0</v>
@@ -50791,7 +50791,7 @@
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D256" t="inlineStr">
@@ -50801,12 +50801,12 @@
       </c>
       <c r="E256" t="inlineStr">
         <is>
-          <t>Blooming</t>
+          <t>Vasco da Gama</t>
         </is>
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>Bolívar</t>
+          <t>Atlético PR</t>
         </is>
       </c>
       <c r="G256" t="n">
@@ -50839,13 +50839,13 @@
         </is>
       </c>
       <c r="P256" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="Q256" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R256" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="S256" t="n">
         <v>0</v>

--- a/jogos_2026-05-10.xlsx
+++ b/jogos_2026-05-10.xlsx
@@ -753,7 +753,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Australia New South Wales NPL</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -763,12 +763,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Rockdale City Suns</t>
+          <t>Ulsan</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Sydney II</t>
+          <t>Bucheon 1995</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -950,7 +950,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>Australia New South Wales NPL</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Seongnam</t>
+          <t>Rockdale City Suns</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Jeonnam Dragons</t>
+          <t>Sydney II</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -998,13 +998,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>3.61</v>
+        <v>0</v>
       </c>
       <c r="S3" t="n">
         <v>0</v>
@@ -1147,7 +1147,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Australia New South Wales NPL</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Blacktown City</t>
+          <t>Seongnam</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>St. George Saints</t>
+          <t>Jeonnam Dragons</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1195,13 +1195,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>3.61</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
@@ -1344,7 +1344,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>Australia New South Wales NPL</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Ulsan</t>
+          <t>Blacktown City</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Bucheon 1995</t>
+          <t>St. George Saints</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Yanbian Longding</t>
+          <t>Shaanxi Union</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Guangxi Hengchen</t>
+          <t>Shanghai Jiading</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Shaanxi Union</t>
+          <t>Yanbian Longding</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Shanghai Jiading</t>
+          <t>Guangxi Hengchen</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Busan I'Park</t>
+          <t>Anyang</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Cheonan City</t>
+          <t>Jeonbuk Motors</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2574,13 +2574,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>4.67</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
         <v>0</v>
@@ -2619,10 +2619,10 @@
         <v>0</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AG11" t="n">
         <v>0</v>
@@ -2723,7 +2723,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Anyang</t>
+          <t>Ansan Greeners</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Jeonbuk Motors</t>
+          <t>Yongin City</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2771,13 +2771,13 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="S12" t="n">
         <v>0</v>
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Ansan Greeners</t>
+          <t>Busan I'Park</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Yongin City</t>
+          <t>Cheonan City</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2968,13 +2968,13 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>3.65</v>
+        <v>1.63</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.32</v>
+        <v>3.7</v>
       </c>
       <c r="R13" t="n">
-        <v>1.91</v>
+        <v>4.67</v>
       </c>
       <c r="S13" t="n">
         <v>0</v>
@@ -3013,10 +3013,10 @@
         <v>0</v>
       </c>
       <c r="AE13" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AF13" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AG13" t="n">
         <v>0</v>
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Viktoria Žižkov</t>
+          <t>Slavia Praha U21</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Sparta Praha II</t>
+          <t>Táborsko</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Slavia Praha U21</t>
+          <t>Viktoria Žižkov</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Táborsko</t>
+          <t>Sparta Praha II</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Persija</t>
+          <t>Persita</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Persib</t>
+          <t>Persijap</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Persita</t>
+          <t>Persija</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Persijap</t>
+          <t>Persib</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3905,22 +3905,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Orenburg</t>
+          <t>Qingdao Youth Island</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Krylya Sovetov</t>
+          <t>Wuhan Three Towns</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3953,13 +3953,13 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
         <v>0</v>
@@ -4102,22 +4102,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Qingdao Youth Island</t>
+          <t>Orenburg</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Wuhan Three Towns</t>
+          <t>Krylya Sovetov</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4150,13 +4150,13 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="S19" t="n">
         <v>0</v>
@@ -4299,22 +4299,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Polonia Warszawa</t>
+          <t>Gyeongnam</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Górnik Łęczna</t>
+          <t>Gimhae City</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,13 +4347,13 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="S20" t="n">
         <v>0</v>
@@ -4496,22 +4496,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Sokol Saratov</t>
+          <t>Sichuan Jiuniu</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Spartak Kostroma</t>
+          <t>Shandong Luneng</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,13 +4544,13 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>4.98</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>3.66</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
         <v>0</v>
@@ -4693,22 +4693,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Sichuan Jiuniu</t>
+          <t>Levante W</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Shandong Luneng</t>
+          <t>Logroño W</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4890,22 +4890,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Levante W</t>
+          <t>Ulytau</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Logroño W</t>
+          <t>Kairat</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -5284,22 +5284,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Ulytau</t>
+          <t>Hoang Anh Gia Lai</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Kairat</t>
+          <t>Pho Hien</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5481,7 +5481,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Hoang Anh Gia Lai</t>
+          <t>Polonia Warszawa</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Pho Hien</t>
+          <t>Górnik Łęczna</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5678,22 +5678,22 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Gyeongnam</t>
+          <t>Sokol Saratov</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Gimhae City</t>
+          <t>Spartak Kostroma</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5726,13 +5726,13 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>2.15</v>
+        <v>4.98</v>
       </c>
       <c r="Q27" t="n">
-        <v>3.16</v>
+        <v>3.66</v>
       </c>
       <c r="R27" t="n">
-        <v>3.14</v>
+        <v>1.75</v>
       </c>
       <c r="S27" t="n">
         <v>0</v>
@@ -6466,7 +6466,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Ayutthaya United</t>
+          <t>Celtic</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Port FC</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6514,13 +6514,13 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>5.09</v>
+        <v>2.2</v>
       </c>
       <c r="Q31" t="n">
-        <v>4.18</v>
+        <v>3.7</v>
       </c>
       <c r="R31" t="n">
-        <v>1.64</v>
+        <v>3</v>
       </c>
       <c r="S31" t="n">
         <v>0</v>
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Rayong</t>
+          <t>Kanchanaburi</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Bangkok United</t>
+          <t>Ratchaburi</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6711,13 +6711,13 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>3.4</v>
+        <v>3.32</v>
       </c>
       <c r="Q32" t="n">
-        <v>3.63</v>
+        <v>3.95</v>
       </c>
       <c r="R32" t="n">
-        <v>2.09</v>
+        <v>2.03</v>
       </c>
       <c r="S32" t="n">
         <v>0</v>
@@ -6860,22 +6860,22 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Piteå Women</t>
+          <t>Chiangrai United</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Rosengard Women</t>
+          <t>Uthai Thani</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -6908,13 +6908,13 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="Q33" t="n">
-        <v>0</v>
+        <v>3.36</v>
       </c>
       <c r="R33" t="n">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="S33" t="n">
         <v>0</v>
@@ -6953,10 +6953,10 @@
         <v>0</v>
       </c>
       <c r="AE33" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AF33" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AG33" t="n">
         <v>0</v>
@@ -7057,22 +7057,22 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Celtic</t>
+          <t>Shenyang Urban</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Yunnan Yukun</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7105,13 +7105,13 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="R34" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="S34" t="n">
         <v>0</v>
@@ -7254,22 +7254,22 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Shenzhen Juniors</t>
+          <t>Hà Nội II</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Hebei Kungfu</t>
+          <t>Viettel</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7451,22 +7451,22 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Chiangrai United</t>
+          <t>Piteå Women</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Uthai Thani</t>
+          <t>Rosengard Women</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7499,13 +7499,13 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>3.36</v>
+        <v>0</v>
       </c>
       <c r="R36" t="n">
-        <v>2.64</v>
+        <v>0</v>
       </c>
       <c r="S36" t="n">
         <v>0</v>
@@ -7544,10 +7544,10 @@
         <v>0</v>
       </c>
       <c r="AE36" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AF36" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AG36" t="n">
         <v>0</v>
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Kanchanaburi</t>
+          <t>Rayong</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Ratchaburi</t>
+          <t>Bangkok United</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7696,13 +7696,13 @@
         </is>
       </c>
       <c r="P37" t="n">
-        <v>3.32</v>
+        <v>3.4</v>
       </c>
       <c r="Q37" t="n">
-        <v>3.95</v>
+        <v>3.63</v>
       </c>
       <c r="R37" t="n">
-        <v>2.03</v>
+        <v>2.09</v>
       </c>
       <c r="S37" t="n">
         <v>0</v>
@@ -7845,22 +7845,22 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Altay</t>
+          <t>Bangkok Glass</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Ordabasy</t>
+          <t>Prachuap</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -7893,13 +7893,13 @@
         </is>
       </c>
       <c r="P38" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="Q38" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="R38" t="n">
-        <v>0</v>
+        <v>4.35</v>
       </c>
       <c r="S38" t="n">
         <v>0</v>
@@ -8042,22 +8042,22 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Chonburi</t>
+          <t>Shenzhen Juniors</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Nakhon Ratchasima</t>
+          <t>Hebei Kungfu</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8090,13 +8090,13 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>4.18</v>
+        <v>0</v>
       </c>
       <c r="R39" t="n">
-        <v>5.3</v>
+        <v>0</v>
       </c>
       <c r="S39" t="n">
         <v>0</v>
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Bangkok Glass</t>
+          <t>Buriram United</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Prachuap</t>
+          <t>Lamphun Warrior</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8287,13 +8287,13 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>1.78</v>
+        <v>1.24</v>
       </c>
       <c r="Q40" t="n">
-        <v>3.9</v>
+        <v>6.73</v>
       </c>
       <c r="R40" t="n">
-        <v>4.35</v>
+        <v>10.6</v>
       </c>
       <c r="S40" t="n">
         <v>0</v>
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Buriram United</t>
+          <t>Ayutthaya United</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Lamphun Warrior</t>
+          <t>Port FC</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8484,13 +8484,13 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>1.24</v>
+        <v>5.09</v>
       </c>
       <c r="Q41" t="n">
-        <v>6.73</v>
+        <v>4.18</v>
       </c>
       <c r="R41" t="n">
-        <v>10.6</v>
+        <v>1.64</v>
       </c>
       <c r="S41" t="n">
         <v>0</v>
@@ -8633,7 +8633,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Sukhothai</t>
+          <t>Ho Chi Minh City</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Muang Thong United</t>
+          <t>Song Lam Nghe An</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8681,13 +8681,13 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>3.61</v>
+        <v>0</v>
       </c>
       <c r="R42" t="n">
-        <v>2.77</v>
+        <v>0</v>
       </c>
       <c r="S42" t="n">
         <v>0</v>
@@ -8830,22 +8830,22 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Hà Nội II</t>
+          <t>Altay</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Viettel</t>
+          <t>Ordabasy</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -9027,22 +9027,22 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Shenyang Urban</t>
+          <t>Sukhothai</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Yunnan Yukun</t>
+          <t>Muang Thong United</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9075,13 +9075,13 @@
         </is>
       </c>
       <c r="P44" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="Q44" t="n">
-        <v>0</v>
+        <v>3.61</v>
       </c>
       <c r="R44" t="n">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="S44" t="n">
         <v>0</v>
@@ -9224,7 +9224,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Ho Chi Minh City</t>
+          <t>Chonburi</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Song Lam Nghe An</t>
+          <t>Nakhon Ratchasima</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9272,13 +9272,13 @@
         </is>
       </c>
       <c r="P45" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="Q45" t="n">
-        <v>0</v>
+        <v>4.18</v>
       </c>
       <c r="R45" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="S45" t="n">
         <v>0</v>
@@ -9815,22 +9815,22 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Singapore S.League</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Home United</t>
+          <t>Hertha BSC</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Albirex Niigata S</t>
+          <t>Greuther Fürth</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -9863,13 +9863,13 @@
         </is>
       </c>
       <c r="P48" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="Q48" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="R48" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="S48" t="n">
         <v>0</v>
@@ -9914,10 +9914,10 @@
         <v>0</v>
       </c>
       <c r="AG48" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AH48" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AI48" t="n">
         <v>0</v>
@@ -10012,7 +10012,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -10022,12 +10022,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Nõmme Kalju</t>
+          <t>Nantong Zhiyun</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Tallinna FC Flora</t>
+          <t>Wuxi Wugou</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10060,13 +10060,13 @@
         </is>
       </c>
       <c r="P49" t="n">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="Q49" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="R49" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="S49" t="n">
         <v>0</v>
@@ -10406,22 +10406,22 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Kerala Blasters</t>
+          <t>Dongguan United</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Mohammedan</t>
+          <t>Suzhou Dongwu</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10454,13 +10454,13 @@
         </is>
       </c>
       <c r="P51" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="Q51" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="R51" t="n">
-        <v>7.37</v>
+        <v>0</v>
       </c>
       <c r="S51" t="n">
         <v>0</v>
@@ -10613,12 +10613,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Hougang United</t>
+          <t>Home United</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Tampines Rovers</t>
+          <t>Albirex Niigata S</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10800,22 +10800,22 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Hertha BSC</t>
+          <t>Nõmme Kalju</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Greuther Fürth</t>
+          <t>Tallinna FC Flora</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -10848,13 +10848,13 @@
         </is>
       </c>
       <c r="P53" t="n">
-        <v>1.78</v>
+        <v>2.27</v>
       </c>
       <c r="Q53" t="n">
-        <v>4.15</v>
+        <v>3.7</v>
       </c>
       <c r="R53" t="n">
-        <v>3.8</v>
+        <v>2.6</v>
       </c>
       <c r="S53" t="n">
         <v>0</v>
@@ -10899,10 +10899,10 @@
         <v>0</v>
       </c>
       <c r="AG53" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AH53" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AI53" t="n">
         <v>0</v>
@@ -10997,22 +10997,22 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Nantong Zhiyun</t>
+          <t>Kerala Blasters</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Wuxi Wugou</t>
+          <t>Mohammedan</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11045,13 +11045,13 @@
         </is>
       </c>
       <c r="P54" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="Q54" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="R54" t="n">
-        <v>0</v>
+        <v>7.37</v>
       </c>
       <c r="S54" t="n">
         <v>0</v>
@@ -11194,22 +11194,22 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Singapore S.League</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Dongguan United</t>
+          <t>Hougang United</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Suzhou Dongwu</t>
+          <t>Tampines Rovers</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11391,7 +11391,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -11401,12 +11401,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Fortuna Düsseldorf</t>
+          <t>KAA Gent</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Elversberg</t>
+          <t>RSC Anderlecht</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11439,13 +11439,13 @@
         </is>
       </c>
       <c r="P56" t="n">
-        <v>2.88</v>
+        <v>2.32</v>
       </c>
       <c r="Q56" t="n">
-        <v>3.8</v>
+        <v>3.71</v>
       </c>
       <c r="R56" t="n">
-        <v>2.19</v>
+        <v>2.89</v>
       </c>
       <c r="S56" t="n">
         <v>0</v>
@@ -11598,12 +11598,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Preußen Münster</t>
+          <t>Fortuna Düsseldorf</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Darmstadt 98</t>
+          <t>Elversberg</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11636,13 +11636,13 @@
         </is>
       </c>
       <c r="P57" t="n">
-        <v>2.29</v>
+        <v>2.88</v>
       </c>
       <c r="Q57" t="n">
-        <v>3.74</v>
+        <v>3.8</v>
       </c>
       <c r="R57" t="n">
-        <v>2.76</v>
+        <v>2.19</v>
       </c>
       <c r="S57" t="n">
         <v>0</v>
@@ -11785,7 +11785,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -11795,12 +11795,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>KAA Gent</t>
+          <t>Preußen Münster</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>RSC Anderlecht</t>
+          <t>Darmstadt 98</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -11833,13 +11833,13 @@
         </is>
       </c>
       <c r="P58" t="n">
-        <v>2.32</v>
+        <v>2.29</v>
       </c>
       <c r="Q58" t="n">
-        <v>3.71</v>
+        <v>3.74</v>
       </c>
       <c r="R58" t="n">
-        <v>2.89</v>
+        <v>2.76</v>
       </c>
       <c r="S58" t="n">
         <v>0</v>
@@ -12770,22 +12770,22 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>RCD Mallorca</t>
+          <t>Qingdao Jonoon</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>Dalian Zhixing</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -12967,22 +12967,22 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AIK</t>
+          <t>Zenit</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Djurgården</t>
+          <t>FK Sochi</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -13015,13 +13015,13 @@
         </is>
       </c>
       <c r="P64" t="n">
-        <v>2.35</v>
+        <v>1.21</v>
       </c>
       <c r="Q64" t="n">
-        <v>3.35</v>
+        <v>7.41</v>
       </c>
       <c r="R64" t="n">
-        <v>2.87</v>
+        <v>17.5</v>
       </c>
       <c r="S64" t="n">
         <v>0</v>
@@ -13558,22 +13558,22 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Aktobe</t>
+          <t>PSIM Yogyakarta</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Kaisar</t>
+          <t>Malut United</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -13952,22 +13952,22 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Nordsjælland</t>
+          <t>Aktobe</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Midtjylland</t>
+          <t>Kaisar</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -14000,13 +14000,13 @@
         </is>
       </c>
       <c r="P69" t="n">
-        <v>3.36</v>
+        <v>0</v>
       </c>
       <c r="Q69" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="R69" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="S69" t="n">
         <v>0</v>
@@ -14149,7 +14149,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -14159,12 +14159,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Qingdao Jonoon</t>
+          <t>Kalmar</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Dalian Zhixing</t>
+          <t>Halmstad</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -14197,13 +14197,13 @@
         </is>
       </c>
       <c r="P70" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="Q70" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R70" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="S70" t="n">
         <v>0</v>
@@ -14346,7 +14346,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -14356,12 +14356,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Meshakhte</t>
+          <t>AIK</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Dila</t>
+          <t>Djurgården</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -14394,13 +14394,13 @@
         </is>
       </c>
       <c r="P71" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="Q71" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="R71" t="n">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="S71" t="n">
         <v>0</v>
@@ -14543,22 +14543,22 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Kalmar</t>
+          <t>Nordsjælland</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Halmstad</t>
+          <t>Midtjylland</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -14591,13 +14591,13 @@
         </is>
       </c>
       <c r="P72" t="n">
-        <v>1.92</v>
+        <v>3.36</v>
       </c>
       <c r="Q72" t="n">
-        <v>3.4</v>
+        <v>3.65</v>
       </c>
       <c r="R72" t="n">
-        <v>3.9</v>
+        <v>1.99</v>
       </c>
       <c r="S72" t="n">
         <v>0</v>
@@ -14740,7 +14740,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -14750,12 +14750,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Zenit</t>
+          <t>RCD Mallorca</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>FK Sochi</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -14788,13 +14788,13 @@
         </is>
       </c>
       <c r="P73" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="Q73" t="n">
-        <v>7.41</v>
+        <v>0</v>
       </c>
       <c r="R73" t="n">
-        <v>17.5</v>
+        <v>0</v>
       </c>
       <c r="S73" t="n">
         <v>0</v>
@@ -14937,22 +14937,22 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>PSIM Yogyakarta</t>
+          <t>Meshakhte</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Malut United</t>
+          <t>Dila</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -15134,7 +15134,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -15144,12 +15144,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Kuala Lumpur</t>
+          <t>Công An Nhân Dân</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Negeri Sembilan</t>
+          <t>Nam Dinh</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -15331,7 +15331,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -15341,12 +15341,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Công An Nhân Dân</t>
+          <t>Kuala Lumpur</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Nam Dinh</t>
+          <t>Negeri Sembilan</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -15528,22 +15528,22 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Rosenborg</t>
+          <t>Baník Ostrava U21</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Lillestrøm</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -15576,13 +15576,13 @@
         </is>
       </c>
       <c r="P77" t="n">
-        <v>2.79</v>
+        <v>0</v>
       </c>
       <c r="Q77" t="n">
-        <v>3.67</v>
+        <v>0</v>
       </c>
       <c r="R77" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="S77" t="n">
         <v>0</v>
@@ -15725,22 +15725,22 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Tychy 71</t>
+          <t>Rosenborg</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Ruch Chorzów</t>
+          <t>Lillestrøm</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -15773,13 +15773,13 @@
         </is>
       </c>
       <c r="P78" t="n">
-        <v>4</v>
+        <v>2.79</v>
       </c>
       <c r="Q78" t="n">
-        <v>3.6</v>
+        <v>3.67</v>
       </c>
       <c r="R78" t="n">
-        <v>1.83</v>
+        <v>2.41</v>
       </c>
       <c r="S78" t="n">
         <v>0</v>
@@ -15922,7 +15922,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -15932,12 +15932,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Baník Ostrava U21</t>
+          <t>Tychy 71</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Ústí nad Labem</t>
+          <t>Ruch Chorzów</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -15970,13 +15970,13 @@
         </is>
       </c>
       <c r="P79" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Q79" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R79" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="S79" t="n">
         <v>0</v>
@@ -16316,22 +16316,22 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Uppsala W</t>
+          <t>Kelantan United</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Vittsjö</t>
+          <t>Johor Darul Ta'zim</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -16513,7 +16513,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -16523,12 +16523,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Arba Minch Kenema</t>
+          <t>Sigma Olomouc</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Welayta Dicha</t>
+          <t>Bohemians 1905</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -16710,7 +16710,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -16720,12 +16720,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Burnley</t>
+          <t>Arba Minch Kenema</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Aston Villa</t>
+          <t>Welayta Dicha</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -16758,13 +16758,13 @@
         </is>
       </c>
       <c r="P83" t="n">
-        <v>5.38</v>
+        <v>0</v>
       </c>
       <c r="Q83" t="n">
-        <v>4.37</v>
+        <v>0</v>
       </c>
       <c r="R83" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="S83" t="n">
         <v>0</v>
@@ -16907,22 +16907,22 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Nottingham Forest</t>
+          <t>Uppsala W</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Newcastle United</t>
+          <t>Vittsjö</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -16955,13 +16955,13 @@
         </is>
       </c>
       <c r="P84" t="n">
-        <v>2.46</v>
+        <v>0</v>
       </c>
       <c r="Q84" t="n">
-        <v>3.66</v>
+        <v>0</v>
       </c>
       <c r="R84" t="n">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="S84" t="n">
         <v>0</v>
@@ -17000,10 +17000,10 @@
         <v>0</v>
       </c>
       <c r="AE84" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AF84" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AG84" t="n">
         <v>0</v>
@@ -17104,7 +17104,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -17114,12 +17114,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Botoşani</t>
+          <t>Burnley</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Petrolul 52</t>
+          <t>Aston Villa</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -17152,13 +17152,13 @@
         </is>
       </c>
       <c r="P85" t="n">
-        <v>2.21</v>
+        <v>5.38</v>
       </c>
       <c r="Q85" t="n">
-        <v>3.22</v>
+        <v>4.37</v>
       </c>
       <c r="R85" t="n">
-        <v>3.22</v>
+        <v>1.67</v>
       </c>
       <c r="S85" t="n">
         <v>0</v>
@@ -17301,7 +17301,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -17311,12 +17311,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Crystal Palace</t>
+          <t>NK Primorje</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Mura</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -17349,13 +17349,13 @@
         </is>
       </c>
       <c r="P86" t="n">
-        <v>2.69</v>
+        <v>2.59</v>
       </c>
       <c r="Q86" t="n">
-        <v>3.31</v>
+        <v>3.45</v>
       </c>
       <c r="R86" t="n">
-        <v>2.92</v>
+        <v>2.3</v>
       </c>
       <c r="S86" t="n">
         <v>0</v>
@@ -17394,10 +17394,10 @@
         <v>0</v>
       </c>
       <c r="AE86" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AF86" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AG86" t="n">
         <v>0</v>
@@ -17508,12 +17508,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Sigma Olomouc</t>
+          <t>Pardubice</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Bohemians 1905</t>
+          <t>Karviná</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -17695,7 +17695,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -17705,12 +17705,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Cremonese</t>
+          <t>Botoşani</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Pisa</t>
+          <t>Petrolul 52</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -17743,13 +17743,13 @@
         </is>
       </c>
       <c r="P88" t="n">
-        <v>2.1</v>
+        <v>2.21</v>
       </c>
       <c r="Q88" t="n">
-        <v>3.42</v>
+        <v>3.22</v>
       </c>
       <c r="R88" t="n">
-        <v>4.07</v>
+        <v>3.22</v>
       </c>
       <c r="S88" t="n">
         <v>0</v>
@@ -17788,10 +17788,10 @@
         <v>0</v>
       </c>
       <c r="AE88" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AF88" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AG88" t="n">
         <v>0</v>
@@ -17892,7 +17892,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -17902,12 +17902,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Turan</t>
+          <t>Fiorentina</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Karvan FK</t>
+          <t>Genoa</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -17940,13 +17940,13 @@
         </is>
       </c>
       <c r="P89" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="Q89" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="R89" t="n">
-        <v>0</v>
+        <v>4.01</v>
       </c>
       <c r="S89" t="n">
         <v>0</v>
@@ -17985,10 +17985,10 @@
         <v>0</v>
       </c>
       <c r="AE89" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AF89" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AG89" t="n">
         <v>0</v>
@@ -18089,7 +18089,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -18099,12 +18099,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>NK Primorje</t>
+          <t>Nottingham Forest</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Mura</t>
+          <t>Newcastle United</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -18137,13 +18137,13 @@
         </is>
       </c>
       <c r="P90" t="n">
-        <v>2.59</v>
+        <v>2.46</v>
       </c>
       <c r="Q90" t="n">
-        <v>3.45</v>
+        <v>3.66</v>
       </c>
       <c r="R90" t="n">
-        <v>2.3</v>
+        <v>2.99</v>
       </c>
       <c r="S90" t="n">
         <v>0</v>
@@ -18182,10 +18182,10 @@
         <v>0</v>
       </c>
       <c r="AE90" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AF90" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AG90" t="n">
         <v>0</v>
@@ -18286,22 +18286,22 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Astana</t>
+          <t>Turan</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Kyzyl-Zhar</t>
+          <t>Karvan FK</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -18334,13 +18334,13 @@
         </is>
       </c>
       <c r="P91" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Q91" t="n">
-        <v>3.76</v>
+        <v>0</v>
       </c>
       <c r="R91" t="n">
-        <v>4.15</v>
+        <v>0</v>
       </c>
       <c r="S91" t="n">
         <v>0</v>
@@ -18483,7 +18483,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -18493,12 +18493,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Pardubice</t>
+          <t>Cremonese</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Karviná</t>
+          <t>Pisa</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -18531,13 +18531,13 @@
         </is>
       </c>
       <c r="P92" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Q92" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="R92" t="n">
-        <v>0</v>
+        <v>4.07</v>
       </c>
       <c r="S92" t="n">
         <v>0</v>
@@ -18576,10 +18576,10 @@
         <v>0</v>
       </c>
       <c r="AE92" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AF92" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AG92" t="n">
         <v>0</v>
@@ -18680,22 +18680,22 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Fiorentina</t>
+          <t>Astana</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Genoa</t>
+          <t>Kyzyl-Zhar</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -18728,13 +18728,13 @@
         </is>
       </c>
       <c r="P93" t="n">
-        <v>2.09</v>
+        <v>1.8</v>
       </c>
       <c r="Q93" t="n">
-        <v>3.48</v>
+        <v>3.76</v>
       </c>
       <c r="R93" t="n">
-        <v>4.01</v>
+        <v>4.15</v>
       </c>
       <c r="S93" t="n">
         <v>0</v>
@@ -18773,10 +18773,10 @@
         <v>0</v>
       </c>
       <c r="AE93" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AF93" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AG93" t="n">
         <v>0</v>
@@ -18877,7 +18877,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -18887,12 +18887,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Kelantan United</t>
+          <t>Crystal Palace</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Johor Darul Ta'zim</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -18925,13 +18925,13 @@
         </is>
       </c>
       <c r="P94" t="n">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="Q94" t="n">
-        <v>0</v>
+        <v>3.31</v>
       </c>
       <c r="R94" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="S94" t="n">
         <v>0</v>
@@ -18970,10 +18970,10 @@
         <v>0</v>
       </c>
       <c r="AE94" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AF94" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AG94" t="n">
         <v>0</v>
@@ -19468,7 +19468,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -19478,12 +19478,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Volos NFC</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Levadiakos</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -19516,13 +19516,13 @@
         </is>
       </c>
       <c r="P97" t="n">
-        <v>3.04</v>
+        <v>2.17</v>
       </c>
       <c r="Q97" t="n">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="R97" t="n">
-        <v>2.32</v>
+        <v>3.21</v>
       </c>
       <c r="S97" t="n">
         <v>0</v>
@@ -19561,10 +19561,10 @@
         <v>0</v>
       </c>
       <c r="AE97" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AF97" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AG97" t="n">
         <v>0</v>
@@ -19665,7 +19665,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -19675,12 +19675,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>NorthEast United</t>
+          <t>Volos NFC</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Chennaiyin</t>
+          <t>Levadiakos</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -19713,13 +19713,13 @@
         </is>
       </c>
       <c r="P98" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="Q98" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R98" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="S98" t="n">
         <v>0</v>
@@ -19862,22 +19862,22 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>EB - Streymur</t>
+          <t>Aris</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Víkingur</t>
+          <t>OFI</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -20059,22 +20059,22 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Nõmme United</t>
+          <t>Osijek</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Paide</t>
+          <t>Istra 1961</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -20107,13 +20107,13 @@
         </is>
       </c>
       <c r="P100" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="Q100" t="n">
-        <v>3.88</v>
+        <v>0</v>
       </c>
       <c r="R100" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="S100" t="n">
         <v>0</v>
@@ -20256,7 +20256,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -20266,12 +20266,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Royal Antwerp FC</t>
+          <t>Honvéd W</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Sporting Charleroi</t>
+          <t>Vasas</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -20304,13 +20304,13 @@
         </is>
       </c>
       <c r="P101" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="Q101" t="n">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="R101" t="n">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="S101" t="n">
         <v>0</v>
@@ -20349,10 +20349,10 @@
         <v>0</v>
       </c>
       <c r="AE101" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AF101" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AG101" t="n">
         <v>0</v>
@@ -20453,7 +20453,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -20463,12 +20463,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Aris</t>
+          <t>NorthEast United</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>OFI</t>
+          <t>Chennaiyin</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -20650,7 +20650,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -20660,12 +20660,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Royal Antwerp FC</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Sporting Charleroi</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -20698,13 +20698,13 @@
         </is>
       </c>
       <c r="P103" t="n">
-        <v>2.17</v>
+        <v>2.38</v>
       </c>
       <c r="Q103" t="n">
-        <v>3.4</v>
+        <v>3.24</v>
       </c>
       <c r="R103" t="n">
-        <v>3.21</v>
+        <v>3.14</v>
       </c>
       <c r="S103" t="n">
         <v>0</v>
@@ -20743,10 +20743,10 @@
         <v>0</v>
       </c>
       <c r="AE103" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AF103" t="n">
         <v>1.8</v>
-      </c>
-      <c r="AF103" t="n">
-        <v>1.88</v>
       </c>
       <c r="AG103" t="n">
         <v>0</v>
@@ -21044,22 +21044,22 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Silkeborg</t>
+          <t>Nõmme United</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>Paide</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -21092,13 +21092,13 @@
         </is>
       </c>
       <c r="P105" t="n">
-        <v>4.68</v>
+        <v>3.58</v>
       </c>
       <c r="Q105" t="n">
-        <v>4</v>
+        <v>3.88</v>
       </c>
       <c r="R105" t="n">
-        <v>1.63</v>
+        <v>1.78</v>
       </c>
       <c r="S105" t="n">
         <v>0</v>
@@ -21241,7 +21241,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -21251,12 +21251,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Osijek</t>
+          <t>Silkeborg</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Istra 1961</t>
+          <t>København</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -21289,13 +21289,13 @@
         </is>
       </c>
       <c r="P106" t="n">
-        <v>0</v>
+        <v>4.68</v>
       </c>
       <c r="Q106" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R106" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="S106" t="n">
         <v>0</v>
@@ -21438,22 +21438,22 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Honvéd W</t>
+          <t>B36</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Vasas</t>
+          <t>KÍ</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -21645,12 +21645,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>B36</t>
+          <t>EB - Streymur</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>KÍ</t>
+          <t>Víkingur</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -22620,7 +22620,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -22630,12 +22630,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Sion</t>
+          <t>Viktoria Köln</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Thun</t>
+          <t>Alemannia Aachen</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -22668,13 +22668,13 @@
         </is>
       </c>
       <c r="P113" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Q113" t="n">
-        <v>3.64</v>
+        <v>0</v>
       </c>
       <c r="R113" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="S113" t="n">
         <v>0</v>
@@ -23014,7 +23014,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -23024,12 +23024,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Viktoria Köln</t>
+          <t>Sion</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Alemannia Aachen</t>
+          <t>Thun</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -23062,13 +23062,13 @@
         </is>
       </c>
       <c r="P115" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Q115" t="n">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="R115" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="S115" t="n">
         <v>0</v>
@@ -23418,12 +23418,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Feyenoord</t>
+          <t>Fortuna Sittard</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>AZ</t>
+          <t>PEC Zwolle</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -23456,13 +23456,13 @@
         </is>
       </c>
       <c r="P117" t="n">
-        <v>1.78</v>
+        <v>1.96</v>
       </c>
       <c r="Q117" t="n">
-        <v>4.17</v>
+        <v>4.05</v>
       </c>
       <c r="R117" t="n">
-        <v>4.17</v>
+        <v>3.5</v>
       </c>
       <c r="S117" t="n">
         <v>0</v>
@@ -23507,10 +23507,10 @@
         <v>0</v>
       </c>
       <c r="AG117" t="n">
-        <v>1.9</v>
+        <v>2.2</v>
       </c>
       <c r="AH117" t="n">
-        <v>1.77</v>
+        <v>1.58</v>
       </c>
       <c r="AI117" t="n">
         <v>0</v>
@@ -23615,12 +23615,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>NAC Breda</t>
+          <t>Excelsior</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Heerenveen</t>
+          <t>Volendam</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -23653,13 +23653,13 @@
         </is>
       </c>
       <c r="P118" t="n">
-        <v>2.49</v>
+        <v>1.77</v>
       </c>
       <c r="Q118" t="n">
-        <v>3.77</v>
+        <v>4.17</v>
       </c>
       <c r="R118" t="n">
-        <v>2.67</v>
+        <v>4.22</v>
       </c>
       <c r="S118" t="n">
         <v>0</v>
@@ -23698,7 +23698,7 @@
         <v>0</v>
       </c>
       <c r="AE118" t="n">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="AF118" t="n">
         <v>2.3</v>
@@ -23812,12 +23812,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Twente</t>
+          <t>Telstar</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Sparta Rotterdam</t>
+          <t>Heracles</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -23850,13 +23850,13 @@
         </is>
       </c>
       <c r="P119" t="n">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="Q119" t="n">
-        <v>5.14</v>
+        <v>4.94</v>
       </c>
       <c r="R119" t="n">
-        <v>6.53</v>
+        <v>6.07</v>
       </c>
       <c r="S119" t="n">
         <v>0</v>
@@ -23901,10 +23901,10 @@
         <v>0</v>
       </c>
       <c r="AG119" t="n">
-        <v>1.93</v>
+        <v>1.98</v>
       </c>
       <c r="AH119" t="n">
-        <v>1.77</v>
+        <v>1.72</v>
       </c>
       <c r="AI119" t="n">
         <v>0</v>
@@ -24009,12 +24009,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Fortuna Sittard</t>
+          <t>Ajax</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>PEC Zwolle</t>
+          <t>Utrecht</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -24047,13 +24047,13 @@
         </is>
       </c>
       <c r="P120" t="n">
-        <v>1.96</v>
+        <v>1.71</v>
       </c>
       <c r="Q120" t="n">
-        <v>4.05</v>
+        <v>4.37</v>
       </c>
       <c r="R120" t="n">
-        <v>3.5</v>
+        <v>4.42</v>
       </c>
       <c r="S120" t="n">
         <v>0</v>
@@ -24098,10 +24098,10 @@
         <v>0</v>
       </c>
       <c r="AG120" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="AH120" t="n">
-        <v>1.58</v>
+        <v>1.65</v>
       </c>
       <c r="AI120" t="n">
         <v>0</v>
@@ -24206,12 +24206,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Telstar</t>
+          <t>Groningen</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Heracles</t>
+          <t>NEC</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -24244,13 +24244,13 @@
         </is>
       </c>
       <c r="P121" t="n">
-        <v>1.48</v>
+        <v>2.78</v>
       </c>
       <c r="Q121" t="n">
-        <v>4.94</v>
+        <v>3.89</v>
       </c>
       <c r="R121" t="n">
-        <v>6.07</v>
+        <v>2.36</v>
       </c>
       <c r="S121" t="n">
         <v>0</v>
@@ -24295,10 +24295,10 @@
         <v>0</v>
       </c>
       <c r="AG121" t="n">
-        <v>1.98</v>
+        <v>2.05</v>
       </c>
       <c r="AH121" t="n">
-        <v>1.72</v>
+        <v>1.68</v>
       </c>
       <c r="AI121" t="n">
         <v>0</v>
@@ -24403,12 +24403,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Excelsior</t>
+          <t>Twente</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Volendam</t>
+          <t>Sparta Rotterdam</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -24441,61 +24441,61 @@
         </is>
       </c>
       <c r="P122" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="Q122" t="n">
+        <v>5.14</v>
+      </c>
+      <c r="R122" t="n">
+        <v>6.53</v>
+      </c>
+      <c r="S122" t="n">
+        <v>0</v>
+      </c>
+      <c r="T122" t="n">
+        <v>0</v>
+      </c>
+      <c r="U122" t="n">
+        <v>0</v>
+      </c>
+      <c r="V122" t="n">
+        <v>0</v>
+      </c>
+      <c r="W122" t="n">
+        <v>0</v>
+      </c>
+      <c r="X122" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y122" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z122" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA122" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB122" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC122" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD122" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE122" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF122" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG122" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AH122" t="n">
         <v>1.77</v>
-      </c>
-      <c r="Q122" t="n">
-        <v>4.17</v>
-      </c>
-      <c r="R122" t="n">
-        <v>4.22</v>
-      </c>
-      <c r="S122" t="n">
-        <v>0</v>
-      </c>
-      <c r="T122" t="n">
-        <v>0</v>
-      </c>
-      <c r="U122" t="n">
-        <v>0</v>
-      </c>
-      <c r="V122" t="n">
-        <v>0</v>
-      </c>
-      <c r="W122" t="n">
-        <v>0</v>
-      </c>
-      <c r="X122" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y122" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z122" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA122" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB122" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC122" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD122" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE122" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AF122" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AG122" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH122" t="n">
-        <v>0</v>
       </c>
       <c r="AI122" t="n">
         <v>0</v>
@@ -24600,12 +24600,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Ajax</t>
+          <t>Go Ahead Eagles</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Utrecht</t>
+          <t>PSV</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -24638,13 +24638,13 @@
         </is>
       </c>
       <c r="P123" t="n">
-        <v>1.71</v>
+        <v>4.48</v>
       </c>
       <c r="Q123" t="n">
-        <v>4.37</v>
+        <v>4.74</v>
       </c>
       <c r="R123" t="n">
-        <v>4.42</v>
+        <v>1.65</v>
       </c>
       <c r="S123" t="n">
         <v>0</v>
@@ -24689,10 +24689,10 @@
         <v>0</v>
       </c>
       <c r="AG123" t="n">
-        <v>2.1</v>
+        <v>1.68</v>
       </c>
       <c r="AH123" t="n">
-        <v>1.65</v>
+        <v>2.05</v>
       </c>
       <c r="AI123" t="n">
         <v>0</v>
@@ -24797,12 +24797,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Groningen</t>
+          <t>Feyenoord</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>NEC</t>
+          <t>AZ</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -24835,13 +24835,13 @@
         </is>
       </c>
       <c r="P124" t="n">
-        <v>2.78</v>
+        <v>1.78</v>
       </c>
       <c r="Q124" t="n">
-        <v>3.89</v>
+        <v>4.17</v>
       </c>
       <c r="R124" t="n">
-        <v>2.36</v>
+        <v>4.17</v>
       </c>
       <c r="S124" t="n">
         <v>0</v>
@@ -24886,10 +24886,10 @@
         <v>0</v>
       </c>
       <c r="AG124" t="n">
-        <v>2.05</v>
+        <v>1.9</v>
       </c>
       <c r="AH124" t="n">
-        <v>1.68</v>
+        <v>1.77</v>
       </c>
       <c r="AI124" t="n">
         <v>0</v>
@@ -24994,12 +24994,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Go Ahead Eagles</t>
+          <t>NAC Breda</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>PSV</t>
+          <t>Heerenveen</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -25032,13 +25032,13 @@
         </is>
       </c>
       <c r="P125" t="n">
-        <v>4.48</v>
+        <v>2.49</v>
       </c>
       <c r="Q125" t="n">
-        <v>4.74</v>
+        <v>3.77</v>
       </c>
       <c r="R125" t="n">
-        <v>1.65</v>
+        <v>2.67</v>
       </c>
       <c r="S125" t="n">
         <v>0</v>
@@ -25077,16 +25077,16 @@
         <v>0</v>
       </c>
       <c r="AE125" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AF125" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AG125" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AH125" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AI125" t="n">
         <v>0</v>
@@ -25181,22 +25181,22 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Shkendija</t>
+          <t>Saburtalo</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Struga</t>
+          <t>Torpedo Kutaisi</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -25378,22 +25378,22 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>KFUM</t>
+          <t>Croatia Zmijavci</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Viking</t>
+          <t>Jarun</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -25426,13 +25426,13 @@
         </is>
       </c>
       <c r="P127" t="n">
-        <v>3.87</v>
+        <v>0</v>
       </c>
       <c r="Q127" t="n">
-        <v>3.87</v>
+        <v>0</v>
       </c>
       <c r="R127" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="S127" t="n">
         <v>0</v>
@@ -25575,7 +25575,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -25585,12 +25585,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Croatia Zmijavci</t>
+          <t>Paphos</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Jarun</t>
+          <t>Aris</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -25772,7 +25772,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -25782,12 +25782,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Real Madrid W</t>
+          <t>Omonia Nicosia</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Atletico Madrid W</t>
+          <t>AEK Larnaca</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -25969,7 +25969,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -25979,12 +25979,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Zbrojovka Brno</t>
+          <t>Apollon</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Vlašim</t>
+          <t>APOEL</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -26166,7 +26166,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -26176,12 +26176,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Rapid Wien</t>
+          <t>Szentlőrinc SE</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Austria Wien</t>
+          <t>Videoton</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -26214,13 +26214,13 @@
         </is>
       </c>
       <c r="P131" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Q131" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="R131" t="n">
-        <v>2.96</v>
+        <v>0</v>
       </c>
       <c r="S131" t="n">
         <v>0</v>
@@ -26363,22 +26363,22 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Sandefjord</t>
+          <t>Zbrojovka Brno</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Kristiansund</t>
+          <t>Vlašim</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -26411,13 +26411,13 @@
         </is>
       </c>
       <c r="P132" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="Q132" t="n">
-        <v>4.44</v>
+        <v>0</v>
       </c>
       <c r="R132" t="n">
-        <v>5.16</v>
+        <v>0</v>
       </c>
       <c r="S132" t="n">
         <v>0</v>
@@ -26560,7 +26560,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -26570,12 +26570,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Saburtalo</t>
+          <t>Moss</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Torpedo Kutaisi</t>
+          <t>Bryne</t>
         </is>
       </c>
       <c r="G133" t="n">
@@ -26608,13 +26608,13 @@
         </is>
       </c>
       <c r="P133" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Q133" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="R133" t="n">
-        <v>0</v>
+        <v>3.01</v>
       </c>
       <c r="S133" t="n">
         <v>0</v>
@@ -26767,12 +26767,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Pelister</t>
+          <t>Vardar</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Shkupi</t>
+          <t>Sileks</t>
         </is>
       </c>
       <c r="G134" t="n">
@@ -26954,7 +26954,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -26964,12 +26964,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Budafoki MTE</t>
+          <t>Shkendija</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>BVSC</t>
+          <t>Struga</t>
         </is>
       </c>
       <c r="G135" t="n">
@@ -27151,7 +27151,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -27161,12 +27161,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Paphos</t>
+          <t>Real Madrid W</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Aris</t>
+          <t>Atletico Madrid W</t>
         </is>
       </c>
       <c r="G136" t="n">
@@ -27348,22 +27348,22 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Tromsø</t>
+          <t>Makedonija GjP</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Molde</t>
+          <t>Tikveš</t>
         </is>
       </c>
       <c r="G137" t="n">
@@ -27396,13 +27396,13 @@
         </is>
       </c>
       <c r="P137" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="Q137" t="n">
-        <v>3.82</v>
+        <v>0</v>
       </c>
       <c r="R137" t="n">
-        <v>4.13</v>
+        <v>0</v>
       </c>
       <c r="S137" t="n">
         <v>0</v>
@@ -27545,22 +27545,22 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Åsane</t>
+          <t>Pelister</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Strømsgodset</t>
+          <t>Shkupi</t>
         </is>
       </c>
       <c r="G138" t="n">
@@ -27593,13 +27593,13 @@
         </is>
       </c>
       <c r="P138" t="n">
-        <v>5.4</v>
+        <v>0</v>
       </c>
       <c r="Q138" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="R138" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="S138" t="n">
         <v>0</v>
@@ -27752,12 +27752,12 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Akademija Pandev</t>
+          <t>Aresimi</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Rabotnički</t>
+          <t>FK Bashkimi Kumanovo</t>
         </is>
       </c>
       <c r="G139" t="n">
@@ -27939,22 +27939,22 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Aresimi</t>
+          <t>Åsane</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>FK Bashkimi Kumanovo</t>
+          <t>Strømsgodset</t>
         </is>
       </c>
       <c r="G140" t="n">
@@ -27987,13 +27987,13 @@
         </is>
       </c>
       <c r="P140" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="Q140" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="R140" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="S140" t="n">
         <v>0</v>
@@ -28136,7 +28136,7 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -28146,12 +28146,12 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Vardar</t>
+          <t>Hartberg</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Sileks</t>
+          <t>Sturm Graz</t>
         </is>
       </c>
       <c r="G141" t="n">
@@ -28184,13 +28184,13 @@
         </is>
       </c>
       <c r="P141" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="Q141" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R141" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="S141" t="n">
         <v>0</v>
@@ -28229,10 +28229,10 @@
         <v>0</v>
       </c>
       <c r="AE141" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AF141" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG141" t="n">
         <v>0</v>
@@ -28343,12 +28343,12 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Sandnes Ulf</t>
+          <t>Sogndal</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Stabæk</t>
+          <t>Haugesund</t>
         </is>
       </c>
       <c r="G142" t="n">
@@ -28381,13 +28381,13 @@
         </is>
       </c>
       <c r="P142" t="n">
-        <v>4.07</v>
+        <v>3.1</v>
       </c>
       <c r="Q142" t="n">
-        <v>3.9</v>
+        <v>3.7</v>
       </c>
       <c r="R142" t="n">
-        <v>1.78</v>
+        <v>2.12</v>
       </c>
       <c r="S142" t="n">
         <v>0</v>
@@ -28530,22 +28530,22 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Makedonija GjP</t>
+          <t>Sandnes Ulf</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Tikveš</t>
+          <t>Stabæk</t>
         </is>
       </c>
       <c r="G143" t="n">
@@ -28578,13 +28578,13 @@
         </is>
       </c>
       <c r="P143" t="n">
-        <v>0</v>
+        <v>4.07</v>
       </c>
       <c r="Q143" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="R143" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="S143" t="n">
         <v>0</v>
@@ -28727,7 +28727,7 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -28737,12 +28737,12 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Omonia Nicosia</t>
+          <t>LASK Linz</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>AEK Larnaca</t>
+          <t>Salzburg</t>
         </is>
       </c>
       <c r="G144" t="n">
@@ -28775,13 +28775,13 @@
         </is>
       </c>
       <c r="P144" t="n">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="Q144" t="n">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="R144" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="S144" t="n">
         <v>0</v>
@@ -29121,7 +29121,7 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -29131,12 +29131,12 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Hartberg</t>
+          <t>Akademija Pandev</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Sturm Graz</t>
+          <t>Rabotnički</t>
         </is>
       </c>
       <c r="G146" t="n">
@@ -29169,13 +29169,13 @@
         </is>
       </c>
       <c r="P146" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="Q146" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R146" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="S146" t="n">
         <v>0</v>
@@ -29214,10 +29214,10 @@
         <v>0</v>
       </c>
       <c r="AE146" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AF146" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AG146" t="n">
         <v>0</v>
@@ -29318,7 +29318,7 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
@@ -29328,12 +29328,12 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Szentlőrinc SE</t>
+          <t>Mebrat Hayl</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Videoton</t>
+          <t>Fasil Ketema</t>
         </is>
       </c>
       <c r="G147" t="n">
@@ -29525,12 +29525,12 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Moss</t>
+          <t>Strømmen</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Bryne</t>
+          <t>Hødd</t>
         </is>
       </c>
       <c r="G148" t="n">
@@ -29563,13 +29563,13 @@
         </is>
       </c>
       <c r="P148" t="n">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="Q148" t="n">
-        <v>3.7</v>
+        <v>3.4</v>
       </c>
       <c r="R148" t="n">
-        <v>3.01</v>
+        <v>3.2</v>
       </c>
       <c r="S148" t="n">
         <v>0</v>
@@ -29712,7 +29712,7 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
@@ -29722,12 +29722,12 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Pogoń Siedlce</t>
+          <t>Kecskeméti TE</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Stal Rzeszów</t>
+          <t>Mezőkövesd-Zsóry</t>
         </is>
       </c>
       <c r="G149" t="n">
@@ -29760,13 +29760,13 @@
         </is>
       </c>
       <c r="P149" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="Q149" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R149" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="S149" t="n">
         <v>0</v>
@@ -29909,7 +29909,7 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
@@ -29919,12 +29919,12 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Ajka</t>
+          <t>Rapid Wien</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Szeged 2011</t>
+          <t>Austria Wien</t>
         </is>
       </c>
       <c r="G150" t="n">
@@ -29957,13 +29957,13 @@
         </is>
       </c>
       <c r="P150" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Q150" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="R150" t="n">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="S150" t="n">
         <v>0</v>
@@ -30106,7 +30106,7 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
@@ -30116,12 +30116,12 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Sogndal</t>
+          <t>KFUM</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Haugesund</t>
+          <t>Viking</t>
         </is>
       </c>
       <c r="G151" t="n">
@@ -30154,13 +30154,13 @@
         </is>
       </c>
       <c r="P151" t="n">
-        <v>3.1</v>
+        <v>3.87</v>
       </c>
       <c r="Q151" t="n">
-        <v>3.7</v>
+        <v>3.87</v>
       </c>
       <c r="R151" t="n">
-        <v>2.12</v>
+        <v>1.89</v>
       </c>
       <c r="S151" t="n">
         <v>0</v>
@@ -30303,7 +30303,7 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
@@ -30313,12 +30313,12 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Apollon</t>
+          <t>Pogoń Siedlce</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>APOEL</t>
+          <t>Stal Rzeszów</t>
         </is>
       </c>
       <c r="G152" t="n">
@@ -30351,13 +30351,13 @@
         </is>
       </c>
       <c r="P152" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="Q152" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R152" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="S152" t="n">
         <v>0</v>
@@ -30500,7 +30500,7 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
@@ -30510,12 +30510,12 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>LASK Linz</t>
+          <t>Budafoki MTE</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Salzburg</t>
+          <t>BVSC</t>
         </is>
       </c>
       <c r="G153" t="n">
@@ -30548,13 +30548,13 @@
         </is>
       </c>
       <c r="P153" t="n">
-        <v>2.51</v>
+        <v>0</v>
       </c>
       <c r="Q153" t="n">
-        <v>3.78</v>
+        <v>0</v>
       </c>
       <c r="R153" t="n">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="S153" t="n">
         <v>0</v>
@@ -30697,7 +30697,7 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
@@ -30707,12 +30707,12 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Mebrat Hayl</t>
+          <t>Karcag SE</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Fasil Ketema</t>
+          <t>Tiszakécske</t>
         </is>
       </c>
       <c r="G154" t="n">
@@ -30894,22 +30894,22 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Karcag SE</t>
+          <t>Sandefjord</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Tiszakécske</t>
+          <t>Kristiansund</t>
         </is>
       </c>
       <c r="G155" t="n">
@@ -30942,13 +30942,13 @@
         </is>
       </c>
       <c r="P155" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="Q155" t="n">
-        <v>0</v>
+        <v>4.44</v>
       </c>
       <c r="R155" t="n">
-        <v>0</v>
+        <v>5.16</v>
       </c>
       <c r="S155" t="n">
         <v>0</v>
@@ -31091,22 +31091,22 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Kecskeméti TE</t>
+          <t>Tromsø</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Mezőkövesd-Zsóry</t>
+          <t>Molde</t>
         </is>
       </c>
       <c r="G156" t="n">
@@ -31139,13 +31139,13 @@
         </is>
       </c>
       <c r="P156" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="Q156" t="n">
-        <v>0</v>
+        <v>3.82</v>
       </c>
       <c r="R156" t="n">
-        <v>0</v>
+        <v>4.13</v>
       </c>
       <c r="S156" t="n">
         <v>0</v>
@@ -31288,22 +31288,22 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Strømmen</t>
+          <t>Ajka</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Hødd</t>
+          <t>Szeged 2011</t>
         </is>
       </c>
       <c r="G157" t="n">
@@ -31336,13 +31336,13 @@
         </is>
       </c>
       <c r="P157" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Q157" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="R157" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="S157" t="n">
         <v>0</v>
@@ -31495,12 +31495,12 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Bani Yas</t>
+          <t>Dibba Al Fujairah</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Shabab Al Ahli Dubai</t>
+          <t>Ajman</t>
         </is>
       </c>
       <c r="G158" t="n">
@@ -31692,12 +31692,12 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Dibba Al Fujairah</t>
+          <t>Al Bataeh</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Ajman</t>
+          <t>Al Sharjah</t>
         </is>
       </c>
       <c r="G159" t="n">
@@ -32086,12 +32086,12 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Al Bataeh</t>
+          <t>Bani Yas</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Al Sharjah</t>
+          <t>Shabab Al Ahli Dubai</t>
         </is>
       </c>
       <c r="G161" t="n">
@@ -32273,7 +32273,7 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
@@ -32283,12 +32283,12 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>Neftçi</t>
+          <t>West Ham United</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>İnter Bakı</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="G162" t="n">
@@ -32321,13 +32321,13 @@
         </is>
       </c>
       <c r="P162" t="n">
-        <v>0</v>
+        <v>5.17</v>
       </c>
       <c r="Q162" t="n">
-        <v>0</v>
+        <v>4.37</v>
       </c>
       <c r="R162" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="S162" t="n">
         <v>0</v>
@@ -32366,10 +32366,10 @@
         <v>0</v>
       </c>
       <c r="AE162" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AF162" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AG162" t="n">
         <v>0</v>
@@ -32470,7 +32470,7 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
@@ -32480,12 +32480,12 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>Nieciecza</t>
+          <t>Neftçi</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Legia Warszawa</t>
+          <t>İnter Bakı</t>
         </is>
       </c>
       <c r="G163" t="n">
@@ -32518,13 +32518,13 @@
         </is>
       </c>
       <c r="P163" t="n">
-        <v>4.09</v>
+        <v>0</v>
       </c>
       <c r="Q163" t="n">
-        <v>3.78</v>
+        <v>0</v>
       </c>
       <c r="R163" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="S163" t="n">
         <v>0</v>
@@ -32864,7 +32864,7 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
@@ -32874,12 +32874,12 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>West Ham United</t>
+          <t>Nieciecza</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Legia Warszawa</t>
         </is>
       </c>
       <c r="G165" t="n">
@@ -32912,13 +32912,13 @@
         </is>
       </c>
       <c r="P165" t="n">
-        <v>5.17</v>
+        <v>4.09</v>
       </c>
       <c r="Q165" t="n">
-        <v>4.37</v>
+        <v>3.78</v>
       </c>
       <c r="R165" t="n">
-        <v>1.69</v>
+        <v>1.77</v>
       </c>
       <c r="S165" t="n">
         <v>0</v>
@@ -32957,10 +32957,10 @@
         <v>0</v>
       </c>
       <c r="AE165" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AF165" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AG165" t="n">
         <v>0</v>
@@ -33268,12 +33268,12 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>Dečić</t>
+          <t>Mladost DG</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>FK Jezero Plav</t>
+          <t>Petrovac</t>
         </is>
       </c>
       <c r="G167" t="n">
@@ -33455,22 +33455,22 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>Mladost DG</t>
+          <t>Panevėžys</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Petrovac</t>
+          <t>Kauno Žalgiris</t>
         </is>
       </c>
       <c r="G168" t="n">
@@ -33652,7 +33652,7 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
@@ -33662,12 +33662,12 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>Vysočina Jihlava</t>
+          <t>Mornar</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Hanácká</t>
+          <t>Bokelj</t>
         </is>
       </c>
       <c r="G169" t="n">
@@ -33849,7 +33849,7 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
@@ -33859,12 +33859,12 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>Dinamo Bucureşti</t>
+          <t>Parma</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Argeș</t>
+          <t>Roma</t>
         </is>
       </c>
       <c r="G170" t="n">
@@ -33897,13 +33897,13 @@
         </is>
       </c>
       <c r="P170" t="n">
-        <v>1.83</v>
+        <v>5</v>
       </c>
       <c r="Q170" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="R170" t="n">
-        <v>4.3</v>
+        <v>1.75</v>
       </c>
       <c r="S170" t="n">
         <v>0</v>
@@ -34046,7 +34046,7 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
@@ -34056,12 +34056,12 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>Parma</t>
+          <t>Vysočina Jihlava</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Roma</t>
+          <t>Hanácká</t>
         </is>
       </c>
       <c r="G171" t="n">
@@ -34094,13 +34094,13 @@
         </is>
       </c>
       <c r="P171" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="Q171" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="R171" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="S171" t="n">
         <v>0</v>
@@ -34243,22 +34243,22 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>Panevėžys</t>
+          <t>Ittihad Tanger</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Kauno Žalgiris</t>
+          <t>Difaâ El Jadida</t>
         </is>
       </c>
       <c r="G172" t="n">
@@ -34440,7 +34440,7 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
@@ -34450,12 +34450,12 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>Ittihad Tanger</t>
+          <t>Arsenal Tivat</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Difaâ El Jadida</t>
+          <t>Sutjeska</t>
         </is>
       </c>
       <c r="G173" t="n">
@@ -34637,7 +34637,7 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
@@ -34647,12 +34647,12 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>Mornar</t>
+          <t>Dinamo Bucureşti</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Bokelj</t>
+          <t>Argeș</t>
         </is>
       </c>
       <c r="G174" t="n">
@@ -34685,13 +34685,13 @@
         </is>
       </c>
       <c r="P174" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="Q174" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R174" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="S174" t="n">
         <v>0</v>
@@ -34834,7 +34834,7 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
@@ -34844,12 +34844,12 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>Jedinstvo</t>
+          <t>Brøndby</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Budućnost</t>
+          <t>AGF</t>
         </is>
       </c>
       <c r="G175" t="n">
@@ -35031,7 +35031,7 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
@@ -35041,12 +35041,12 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>Brøndby</t>
+          <t>Dečić</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>AGF</t>
+          <t>FK Jezero Plav</t>
         </is>
       </c>
       <c r="G176" t="n">
@@ -35238,12 +35238,12 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>Arsenal Tivat</t>
+          <t>Jedinstvo</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Sutjeska</t>
+          <t>Budućnost</t>
         </is>
       </c>
       <c r="G177" t="n">
@@ -35622,22 +35622,22 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>Slaven Koprivnica</t>
+          <t>07 Vestur</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Gorica</t>
+          <t>B68</t>
         </is>
       </c>
       <c r="G179" t="n">
@@ -35819,22 +35819,22 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>Skála</t>
+          <t>Slaven Koprivnica</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>AB</t>
+          <t>Gorica</t>
         </is>
       </c>
       <c r="G180" t="n">
@@ -36016,22 +36016,22 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>07 Vestur</t>
+          <t>Dobrudzha 1919</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>B68</t>
+          <t>Beroe</t>
         </is>
       </c>
       <c r="G181" t="n">
@@ -36064,13 +36064,13 @@
         </is>
       </c>
       <c r="P181" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="Q181" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R181" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="S181" t="n">
         <v>0</v>
@@ -36213,22 +36213,22 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>Dobrudzha 1919</t>
+          <t>Skála</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Beroe</t>
+          <t>AB</t>
         </is>
       </c>
       <c r="G182" t="n">
@@ -36261,13 +36261,13 @@
         </is>
       </c>
       <c r="P182" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="Q182" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="R182" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="S182" t="n">
         <v>0</v>
@@ -36410,7 +36410,7 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
@@ -36420,12 +36420,12 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>Jablonec</t>
+          <t>IMT Novi Beograd</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Hradec Králové</t>
+          <t>Radnički Kragujevac</t>
         </is>
       </c>
       <c r="G183" t="n">
@@ -36458,13 +36458,13 @@
         </is>
       </c>
       <c r="P183" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Q183" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R183" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="S183" t="n">
         <v>0</v>
@@ -36607,22 +36607,22 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>Lokomotiv Moskva</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Baltika</t>
+          <t>San Luis</t>
         </is>
       </c>
       <c r="G184" t="n">
@@ -36655,13 +36655,13 @@
         </is>
       </c>
       <c r="P184" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Q184" t="n">
-        <v>3.66</v>
+        <v>0</v>
       </c>
       <c r="R184" t="n">
-        <v>3.36</v>
+        <v>0</v>
       </c>
       <c r="S184" t="n">
         <v>0</v>
@@ -36804,7 +36804,7 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
@@ -36814,12 +36814,12 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>Olympiakos Piraeus</t>
+          <t>Radnički Niš</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>PAOK</t>
+          <t>LFK Mladost Lučani</t>
         </is>
       </c>
       <c r="G185" t="n">
@@ -36852,13 +36852,13 @@
         </is>
       </c>
       <c r="P185" t="n">
-        <v>1.82</v>
+        <v>1.71</v>
       </c>
       <c r="Q185" t="n">
-        <v>3.1</v>
+        <v>3.54</v>
       </c>
       <c r="R185" t="n">
-        <v>4.56</v>
+        <v>4.32</v>
       </c>
       <c r="S185" t="n">
         <v>0</v>
@@ -36897,10 +36897,10 @@
         <v>0</v>
       </c>
       <c r="AE185" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AF185" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG185" t="n">
         <v>0</v>
@@ -37001,22 +37001,22 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Spartak Subotica</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>San Luis</t>
+          <t>Napredak</t>
         </is>
       </c>
       <c r="G186" t="n">
@@ -37049,13 +37049,13 @@
         </is>
       </c>
       <c r="P186" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="Q186" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="R186" t="n">
-        <v>0</v>
+        <v>4.96</v>
       </c>
       <c r="S186" t="n">
         <v>0</v>
@@ -37198,22 +37198,22 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>Union Saint-Gilloise</t>
+          <t>Copiapó</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>KV Mechelen</t>
+          <t>Unión San Felipe</t>
         </is>
       </c>
       <c r="G187" t="n">
@@ -37246,13 +37246,13 @@
         </is>
       </c>
       <c r="P187" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="Q187" t="n">
-        <v>5.66</v>
+        <v>0</v>
       </c>
       <c r="R187" t="n">
-        <v>8.98</v>
+        <v>0</v>
       </c>
       <c r="S187" t="n">
         <v>0</v>
@@ -37395,7 +37395,7 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
@@ -37405,12 +37405,12 @@
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>Bačka Topola</t>
+          <t>Union Saint-Gilloise</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Javor Ivanjica</t>
+          <t>KV Mechelen</t>
         </is>
       </c>
       <c r="G188" t="n">
@@ -37443,13 +37443,13 @@
         </is>
       </c>
       <c r="P188" t="n">
-        <v>1.51</v>
+        <v>1.28</v>
       </c>
       <c r="Q188" t="n">
-        <v>3.8</v>
+        <v>5.66</v>
       </c>
       <c r="R188" t="n">
-        <v>5.75</v>
+        <v>8.98</v>
       </c>
       <c r="S188" t="n">
         <v>0</v>
@@ -37488,10 +37488,10 @@
         <v>0</v>
       </c>
       <c r="AE188" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AF188" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AG188" t="n">
         <v>0</v>
@@ -37592,22 +37592,22 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>Real Oviedo</t>
+          <t>Kansas City</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Getafe CF</t>
+          <t>Chicago Red Stars</t>
         </is>
       </c>
       <c r="G189" t="n">
@@ -37640,13 +37640,13 @@
         </is>
       </c>
       <c r="P189" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Q189" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="R189" t="n">
-        <v>0</v>
+        <v>7.95</v>
       </c>
       <c r="S189" t="n">
         <v>0</v>
@@ -37789,7 +37789,7 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
@@ -37799,12 +37799,12 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>Mirandés</t>
+          <t>Jablonec</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>SD Eibar</t>
+          <t>Hradec Králové</t>
         </is>
       </c>
       <c r="G190" t="n">
@@ -37837,13 +37837,13 @@
         </is>
       </c>
       <c r="P190" t="n">
-        <v>3.12</v>
+        <v>0</v>
       </c>
       <c r="Q190" t="n">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="R190" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="S190" t="n">
         <v>0</v>
@@ -37996,12 +37996,12 @@
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>IMT Novi Beograd</t>
+          <t>Bačka Topola</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>Javor Ivanjica</t>
         </is>
       </c>
       <c r="G191" t="n">
@@ -38034,13 +38034,13 @@
         </is>
       </c>
       <c r="P191" t="n">
-        <v>2.15</v>
+        <v>1.51</v>
       </c>
       <c r="Q191" t="n">
-        <v>3.3</v>
+        <v>3.8</v>
       </c>
       <c r="R191" t="n">
-        <v>3.25</v>
+        <v>5.75</v>
       </c>
       <c r="S191" t="n">
         <v>0</v>
@@ -38079,10 +38079,10 @@
         <v>0</v>
       </c>
       <c r="AE191" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AF191" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG191" t="n">
         <v>0</v>
@@ -38183,7 +38183,7 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
@@ -38193,12 +38193,12 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>AEK Athens</t>
+          <t>Real Oviedo</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Panathinaikos</t>
+          <t>Getafe CF</t>
         </is>
       </c>
       <c r="G192" t="n">
@@ -38231,13 +38231,13 @@
         </is>
       </c>
       <c r="P192" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="Q192" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="R192" t="n">
-        <v>6.76</v>
+        <v>0</v>
       </c>
       <c r="S192" t="n">
         <v>0</v>
@@ -38380,22 +38380,22 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>Kansas City</t>
+          <t>Olympiakos Piraeus</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Chicago Red Stars</t>
+          <t>PAOK</t>
         </is>
       </c>
       <c r="G193" t="n">
@@ -38428,13 +38428,13 @@
         </is>
       </c>
       <c r="P193" t="n">
-        <v>1.3</v>
+        <v>1.82</v>
       </c>
       <c r="Q193" t="n">
-        <v>5.1</v>
+        <v>3.1</v>
       </c>
       <c r="R193" t="n">
-        <v>7.95</v>
+        <v>4.56</v>
       </c>
       <c r="S193" t="n">
         <v>0</v>
@@ -38577,7 +38577,7 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
@@ -38587,12 +38587,12 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>Radnički Niš</t>
+          <t>Lokomotiv Moskva</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>LFK Mladost Lučani</t>
+          <t>Baltika</t>
         </is>
       </c>
       <c r="G194" t="n">
@@ -38625,13 +38625,13 @@
         </is>
       </c>
       <c r="P194" t="n">
-        <v>1.71</v>
+        <v>2.25</v>
       </c>
       <c r="Q194" t="n">
-        <v>3.54</v>
+        <v>3.66</v>
       </c>
       <c r="R194" t="n">
-        <v>4.32</v>
+        <v>3.36</v>
       </c>
       <c r="S194" t="n">
         <v>0</v>
@@ -38670,10 +38670,10 @@
         <v>0</v>
       </c>
       <c r="AE194" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AF194" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AG194" t="n">
         <v>0</v>
@@ -38774,22 +38774,22 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>Copiapó</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Unión San Felipe</t>
+          <t>Granada CF</t>
         </is>
       </c>
       <c r="G195" t="n">
@@ -38822,13 +38822,13 @@
         </is>
       </c>
       <c r="P195" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="Q195" t="n">
-        <v>0</v>
+        <v>3.53</v>
       </c>
       <c r="R195" t="n">
-        <v>0</v>
+        <v>3.91</v>
       </c>
       <c r="S195" t="n">
         <v>0</v>
@@ -38867,10 +38867,10 @@
         <v>0</v>
       </c>
       <c r="AE195" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AF195" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AG195" t="n">
         <v>0</v>
@@ -38971,7 +38971,7 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
@@ -38981,12 +38981,12 @@
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>Córdoba</t>
+          <t>AEK Athens</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Granada CF</t>
+          <t>Panathinaikos</t>
         </is>
       </c>
       <c r="G196" t="n">
@@ -39019,13 +39019,13 @@
         </is>
       </c>
       <c r="P196" t="n">
-        <v>1.91</v>
+        <v>1.45</v>
       </c>
       <c r="Q196" t="n">
-        <v>3.53</v>
+        <v>3.8</v>
       </c>
       <c r="R196" t="n">
-        <v>3.91</v>
+        <v>6.76</v>
       </c>
       <c r="S196" t="n">
         <v>0</v>
@@ -39064,10 +39064,10 @@
         <v>0</v>
       </c>
       <c r="AE196" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AF196" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AG196" t="n">
         <v>0</v>
@@ -39168,7 +39168,7 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
@@ -39178,12 +39178,12 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>Spartak Subotica</t>
+          <t>Mirandés</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Napredak</t>
+          <t>SD Eibar</t>
         </is>
       </c>
       <c r="G197" t="n">
@@ -39216,13 +39216,13 @@
         </is>
       </c>
       <c r="P197" t="n">
-        <v>1.55</v>
+        <v>3.12</v>
       </c>
       <c r="Q197" t="n">
-        <v>3.95</v>
+        <v>3.22</v>
       </c>
       <c r="R197" t="n">
-        <v>4.96</v>
+        <v>2.43</v>
       </c>
       <c r="S197" t="n">
         <v>0</v>
@@ -39375,12 +39375,12 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>Hapoel Haifa</t>
+          <t>Ironi Tiberias</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Ashdod</t>
+          <t>Maccabi Netanya</t>
         </is>
       </c>
       <c r="G198" t="n">
@@ -39413,13 +39413,13 @@
         </is>
       </c>
       <c r="P198" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Q198" t="n">
-        <v>3.38</v>
+        <v>0</v>
       </c>
       <c r="R198" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="S198" t="n">
         <v>0</v>
@@ -39562,22 +39562,22 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>Békéscsaba</t>
+          <t>KA</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>Kozármisleny</t>
+          <t>ÍBV</t>
         </is>
       </c>
       <c r="G199" t="n">
@@ -39610,13 +39610,13 @@
         </is>
       </c>
       <c r="P199" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="Q199" t="n">
-        <v>0</v>
+        <v>4.45</v>
       </c>
       <c r="R199" t="n">
-        <v>0</v>
+        <v>5.12</v>
       </c>
       <c r="S199" t="n">
         <v>0</v>
@@ -39759,7 +39759,7 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
@@ -39769,12 +39769,12 @@
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>Tenerife W</t>
+          <t>Hapoel Haifa</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Barcelona W</t>
+          <t>Ashdod</t>
         </is>
       </c>
       <c r="G200" t="n">
@@ -39807,13 +39807,13 @@
         </is>
       </c>
       <c r="P200" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Q200" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="R200" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="S200" t="n">
         <v>0</v>
@@ -39956,7 +39956,7 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
@@ -39966,12 +39966,12 @@
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Hapoel Katamon</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Bnei Sakhnin</t>
         </is>
       </c>
       <c r="G201" t="n">
@@ -40004,13 +40004,13 @@
         </is>
       </c>
       <c r="P201" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Q201" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="R201" t="n">
-        <v>3.13</v>
+        <v>0</v>
       </c>
       <c r="S201" t="n">
         <v>0</v>
@@ -40049,10 +40049,10 @@
         <v>0</v>
       </c>
       <c r="AE201" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AF201" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AG201" t="n">
         <v>0</v>
@@ -40153,7 +40153,7 @@
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
@@ -40163,12 +40163,12 @@
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>Csákvári TK</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>Soroksár SC</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="G202" t="n">
@@ -40201,13 +40201,13 @@
         </is>
       </c>
       <c r="P202" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Q202" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R202" t="n">
-        <v>0</v>
+        <v>3.13</v>
       </c>
       <c r="S202" t="n">
         <v>0</v>
@@ -40246,10 +40246,10 @@
         <v>0</v>
       </c>
       <c r="AE202" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AF202" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AG202" t="n">
         <v>0</v>
@@ -40350,7 +40350,7 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
@@ -40360,12 +40360,12 @@
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>Hapoel Katamon</t>
+          <t>Békéscsaba</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>Bnei Sakhnin</t>
+          <t>Kozármisleny</t>
         </is>
       </c>
       <c r="G203" t="n">
@@ -40547,7 +40547,7 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
@@ -40557,12 +40557,12 @@
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>Ironi Tiberias</t>
+          <t>Tenerife W</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>Maccabi Netanya</t>
+          <t>Barcelona W</t>
         </is>
       </c>
       <c r="G204" t="n">
@@ -40744,7 +40744,7 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
@@ -40754,12 +40754,12 @@
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>KA</t>
+          <t>Dinamo Batumi</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>ÍBV</t>
+          <t>Samgurali</t>
         </is>
       </c>
       <c r="G205" t="n">
@@ -40792,13 +40792,13 @@
         </is>
       </c>
       <c r="P205" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="Q205" t="n">
-        <v>4.45</v>
+        <v>0</v>
       </c>
       <c r="R205" t="n">
-        <v>5.12</v>
+        <v>0</v>
       </c>
       <c r="S205" t="n">
         <v>0</v>
@@ -40941,22 +40941,22 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>Dinamo Batumi</t>
+          <t>Csákvári TK</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>Samgurali</t>
+          <t>Soroksár SC</t>
         </is>
       </c>
       <c r="G206" t="n">
@@ -41335,7 +41335,7 @@
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
@@ -41345,12 +41345,12 @@
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>Mainz 05</t>
+          <t>Hoffenheim II</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>Union Berlin</t>
+          <t>Saarbrucken</t>
         </is>
       </c>
       <c r="G208" t="n">
@@ -41383,13 +41383,13 @@
         </is>
       </c>
       <c r="P208" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="Q208" t="n">
-        <v>3.94</v>
+        <v>0</v>
       </c>
       <c r="R208" t="n">
-        <v>4.41</v>
+        <v>0</v>
       </c>
       <c r="S208" t="n">
         <v>0</v>
@@ -41428,10 +41428,10 @@
         <v>0</v>
       </c>
       <c r="AE208" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AF208" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AG208" t="n">
         <v>0</v>
@@ -41532,7 +41532,7 @@
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
@@ -41542,12 +41542,12 @@
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>Hoffenheim II</t>
+          <t>Mainz 05</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>Saarbrucken</t>
+          <t>Union Berlin</t>
         </is>
       </c>
       <c r="G209" t="n">
@@ -41580,13 +41580,13 @@
         </is>
       </c>
       <c r="P209" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="Q209" t="n">
-        <v>0</v>
+        <v>3.94</v>
       </c>
       <c r="R209" t="n">
-        <v>0</v>
+        <v>4.41</v>
       </c>
       <c r="S209" t="n">
         <v>0</v>
@@ -41625,10 +41625,10 @@
         <v>0</v>
       </c>
       <c r="AE209" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AF209" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AG209" t="n">
         <v>0</v>
@@ -41729,22 +41729,22 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>New England II</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>New York City II</t>
+          <t>Dhamk</t>
         </is>
       </c>
       <c r="G210" t="n">
@@ -41926,7 +41926,7 @@
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
@@ -41936,12 +41936,12 @@
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>CODM Meknès</t>
         </is>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>Dhamk</t>
+          <t>RSB Berkane</t>
         </is>
       </c>
       <c r="G211" t="n">
@@ -42320,22 +42320,22 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>CODM Meknès</t>
+          <t>New England II</t>
         </is>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>RSB Berkane</t>
+          <t>New York City II</t>
         </is>
       </c>
       <c r="G213" t="n">
@@ -42517,22 +42517,22 @@
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>Varzim</t>
+          <t>Chacarita Juniors</t>
         </is>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>CF Os Belenenses</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="G214" t="n">
@@ -42565,13 +42565,13 @@
         </is>
       </c>
       <c r="P214" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="Q214" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="R214" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="S214" t="n">
         <v>0</v>
@@ -42604,10 +42604,10 @@
         <v>0</v>
       </c>
       <c r="AC214" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AD214" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AE214" t="n">
         <v>0</v>
@@ -42714,22 +42714,22 @@
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>Chacarita Juniors</t>
+          <t>Varzim</t>
         </is>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>CF Os Belenenses</t>
         </is>
       </c>
       <c r="G215" t="n">
@@ -42762,13 +42762,13 @@
         </is>
       </c>
       <c r="P215" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="Q215" t="n">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="R215" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="S215" t="n">
         <v>0</v>
@@ -42801,10 +42801,10 @@
         <v>0</v>
       </c>
       <c r="AC215" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AD215" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AE215" t="n">
         <v>0</v>
@@ -43118,12 +43118,12 @@
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>Rennes</t>
+          <t>Auxerre</t>
         </is>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>Paris</t>
+          <t>Nice</t>
         </is>
       </c>
       <c r="G217" t="n">
@@ -43156,13 +43156,13 @@
         </is>
       </c>
       <c r="P217" t="n">
-        <v>1.59</v>
+        <v>2.48</v>
       </c>
       <c r="Q217" t="n">
-        <v>4.73</v>
+        <v>3.5</v>
       </c>
       <c r="R217" t="n">
-        <v>5.79</v>
+        <v>3.07</v>
       </c>
       <c r="S217" t="n">
         <v>0</v>
@@ -43201,16 +43201,16 @@
         <v>0</v>
       </c>
       <c r="AE217" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AF217" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AG217" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AH217" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AI217" t="n">
         <v>0</v>
@@ -43305,7 +43305,7 @@
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
@@ -43315,12 +43315,12 @@
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>Botafogo</t>
         </is>
       </c>
       <c r="G218" t="n">
@@ -43353,13 +43353,13 @@
         </is>
       </c>
       <c r="P218" t="n">
-        <v>2.35</v>
+        <v>2.15</v>
       </c>
       <c r="Q218" t="n">
-        <v>2.9</v>
+        <v>3.44</v>
       </c>
       <c r="R218" t="n">
-        <v>3.04</v>
+        <v>3.5</v>
       </c>
       <c r="S218" t="n">
         <v>0</v>
@@ -43392,16 +43392,16 @@
         <v>0</v>
       </c>
       <c r="AC218" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AD218" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AE218" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AF218" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG218" t="n">
         <v>0</v>
@@ -43699,22 +43699,22 @@
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>Remo</t>
+          <t>Rennes</t>
         </is>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>Paris</t>
         </is>
       </c>
       <c r="G220" t="n">
@@ -43747,13 +43747,13 @@
         </is>
       </c>
       <c r="P220" t="n">
-        <v>5.3</v>
+        <v>1.59</v>
       </c>
       <c r="Q220" t="n">
-        <v>3.73</v>
+        <v>4.73</v>
       </c>
       <c r="R220" t="n">
-        <v>1.71</v>
+        <v>5.79</v>
       </c>
       <c r="S220" t="n">
         <v>0</v>
@@ -43792,16 +43792,16 @@
         <v>0</v>
       </c>
       <c r="AE220" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AF220" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AG220" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AH220" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AI220" t="n">
         <v>0</v>
@@ -44093,22 +44093,22 @@
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>Club Atlético Güemes</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>Quilmes</t>
+          <t>Brest</t>
         </is>
       </c>
       <c r="G222" t="n">
@@ -44141,13 +44141,13 @@
         </is>
       </c>
       <c r="P222" t="n">
-        <v>2.61</v>
+        <v>1.18</v>
       </c>
       <c r="Q222" t="n">
-        <v>2.74</v>
+        <v>9.15</v>
       </c>
       <c r="R222" t="n">
-        <v>2.76</v>
+        <v>17</v>
       </c>
       <c r="S222" t="n">
         <v>0</v>
@@ -44180,10 +44180,10 @@
         <v>0</v>
       </c>
       <c r="AC222" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AD222" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AE222" t="n">
         <v>0</v>
@@ -44192,10 +44192,10 @@
         <v>0</v>
       </c>
       <c r="AG222" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AH222" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AI222" t="n">
         <v>0</v>
@@ -44300,12 +44300,12 @@
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>Metz</t>
+          <t>Monaco</t>
         </is>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>Lorient</t>
+          <t>Lille</t>
         </is>
       </c>
       <c r="G223" t="n">
@@ -44338,13 +44338,13 @@
         </is>
       </c>
       <c r="P223" t="n">
-        <v>3.17</v>
+        <v>2.38</v>
       </c>
       <c r="Q223" t="n">
-        <v>3.68</v>
+        <v>3.9</v>
       </c>
       <c r="R223" t="n">
-        <v>2.34</v>
+        <v>2.96</v>
       </c>
       <c r="S223" t="n">
         <v>0</v>
@@ -44383,10 +44383,10 @@
         <v>0</v>
       </c>
       <c r="AE223" t="n">
-        <v>1.72</v>
+        <v>1.58</v>
       </c>
       <c r="AF223" t="n">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="AG223" t="n">
         <v>0</v>
@@ -44487,7 +44487,7 @@
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
@@ -44497,12 +44497,12 @@
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>Toulouse</t>
+          <t>FC Barcelona</t>
         </is>
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>Olympique Lyonnais</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="G224" t="n">
@@ -44535,13 +44535,13 @@
         </is>
       </c>
       <c r="P224" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="Q224" t="n">
-        <v>3.78</v>
+        <v>0</v>
       </c>
       <c r="R224" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="S224" t="n">
         <v>0</v>
@@ -44580,10 +44580,10 @@
         <v>0</v>
       </c>
       <c r="AE224" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AF224" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AG224" t="n">
         <v>0</v>
@@ -44684,22 +44684,22 @@
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>Náutico</t>
+          <t>Metz</t>
         </is>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>América Mineiro</t>
+          <t>Lorient</t>
         </is>
       </c>
       <c r="G225" t="n">
@@ -44732,13 +44732,13 @@
         </is>
       </c>
       <c r="P225" t="n">
-        <v>1.79</v>
+        <v>3.17</v>
       </c>
       <c r="Q225" t="n">
-        <v>3.5</v>
+        <v>3.68</v>
       </c>
       <c r="R225" t="n">
-        <v>4.39</v>
+        <v>2.34</v>
       </c>
       <c r="S225" t="n">
         <v>0</v>
@@ -44777,10 +44777,10 @@
         <v>0</v>
       </c>
       <c r="AE225" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AF225" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG225" t="n">
         <v>0</v>
@@ -44881,22 +44881,22 @@
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>FC Barcelona</t>
+          <t>Remo</t>
         </is>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="G226" t="n">
@@ -44929,13 +44929,13 @@
         </is>
       </c>
       <c r="P226" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="Q226" t="n">
-        <v>0</v>
+        <v>3.73</v>
       </c>
       <c r="R226" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="S226" t="n">
         <v>0</v>
@@ -44974,10 +44974,10 @@
         <v>0</v>
       </c>
       <c r="AE226" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AF226" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AG226" t="n">
         <v>0</v>
@@ -45078,7 +45078,7 @@
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
@@ -45088,12 +45088,12 @@
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>Independiente Petrolero</t>
+          <t>Náutico</t>
         </is>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>Club Always Ready</t>
+          <t>América Mineiro</t>
         </is>
       </c>
       <c r="G227" t="n">
@@ -45126,13 +45126,13 @@
         </is>
       </c>
       <c r="P227" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="Q227" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R227" t="n">
-        <v>0</v>
+        <v>4.39</v>
       </c>
       <c r="S227" t="n">
         <v>0</v>
@@ -45285,12 +45285,12 @@
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Toulouse</t>
         </is>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>Brest</t>
+          <t>Olympique Lyonnais</t>
         </is>
       </c>
       <c r="G228" t="n">
@@ -45323,13 +45323,13 @@
         </is>
       </c>
       <c r="P228" t="n">
-        <v>1.18</v>
+        <v>3.8</v>
       </c>
       <c r="Q228" t="n">
-        <v>9.15</v>
+        <v>3.78</v>
       </c>
       <c r="R228" t="n">
-        <v>17</v>
+        <v>2.05</v>
       </c>
       <c r="S228" t="n">
         <v>0</v>
@@ -45368,16 +45368,16 @@
         <v>0</v>
       </c>
       <c r="AE228" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AF228" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AG228" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AH228" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AI228" t="n">
         <v>0</v>
@@ -45472,7 +45472,7 @@
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D229" t="inlineStr">
@@ -45482,12 +45482,12 @@
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>Atlético Mineiro</t>
+          <t>Independiente Petrolero</t>
         </is>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>Botafogo</t>
+          <t>Club Always Ready</t>
         </is>
       </c>
       <c r="G229" t="n">
@@ -45520,13 +45520,13 @@
         </is>
       </c>
       <c r="P229" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Q229" t="n">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="R229" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="S229" t="n">
         <v>0</v>
@@ -45565,10 +45565,10 @@
         <v>0</v>
       </c>
       <c r="AE229" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AF229" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AG229" t="n">
         <v>0</v>
@@ -45669,22 +45669,22 @@
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>Monaco</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>Lille</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="G230" t="n">
@@ -45717,13 +45717,13 @@
         </is>
       </c>
       <c r="P230" t="n">
-        <v>2.38</v>
+        <v>2.35</v>
       </c>
       <c r="Q230" t="n">
-        <v>3.9</v>
+        <v>2.9</v>
       </c>
       <c r="R230" t="n">
-        <v>2.96</v>
+        <v>3.04</v>
       </c>
       <c r="S230" t="n">
         <v>0</v>
@@ -45756,16 +45756,16 @@
         <v>0</v>
       </c>
       <c r="AC230" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AD230" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AE230" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AF230" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AG230" t="n">
         <v>0</v>
@@ -45866,22 +45866,22 @@
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>Auxerre</t>
+          <t>Club Atlético Güemes</t>
         </is>
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>Nice</t>
+          <t>Quilmes</t>
         </is>
       </c>
       <c r="G231" t="n">
@@ -45914,13 +45914,13 @@
         </is>
       </c>
       <c r="P231" t="n">
-        <v>2.48</v>
+        <v>2.61</v>
       </c>
       <c r="Q231" t="n">
-        <v>3.5</v>
+        <v>2.74</v>
       </c>
       <c r="R231" t="n">
-        <v>3.07</v>
+        <v>2.76</v>
       </c>
       <c r="S231" t="n">
         <v>0</v>
@@ -45953,16 +45953,16 @@
         <v>0</v>
       </c>
       <c r="AC231" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AD231" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AE231" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AF231" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AG231" t="n">
         <v>0</v>
@@ -46270,12 +46270,12 @@
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>Godoy Cruz</t>
+          <t>Chaco For Ever</t>
         </is>
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>Racing Córdoba</t>
+          <t>Ciudad de Bolívar</t>
         </is>
       </c>
       <c r="G233" t="n">
@@ -46308,13 +46308,13 @@
         </is>
       </c>
       <c r="P233" t="n">
-        <v>1.49</v>
+        <v>2.14</v>
       </c>
       <c r="Q233" t="n">
-        <v>3.52</v>
+        <v>2.73</v>
       </c>
       <c r="R233" t="n">
-        <v>6.94</v>
+        <v>3.77</v>
       </c>
       <c r="S233" t="n">
         <v>0</v>
@@ -46347,10 +46347,10 @@
         <v>0</v>
       </c>
       <c r="AC233" t="n">
-        <v>1.52</v>
+        <v>1.72</v>
       </c>
       <c r="AD233" t="n">
-        <v>2.35</v>
+        <v>1.98</v>
       </c>
       <c r="AE233" t="n">
         <v>0</v>
@@ -46467,12 +46467,12 @@
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>Chaco For Ever</t>
+          <t>Godoy Cruz</t>
         </is>
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>Ciudad de Bolívar</t>
+          <t>Racing Córdoba</t>
         </is>
       </c>
       <c r="G234" t="n">
@@ -46505,13 +46505,13 @@
         </is>
       </c>
       <c r="P234" t="n">
-        <v>2.14</v>
+        <v>1.49</v>
       </c>
       <c r="Q234" t="n">
-        <v>2.73</v>
+        <v>3.52</v>
       </c>
       <c r="R234" t="n">
-        <v>3.77</v>
+        <v>6.94</v>
       </c>
       <c r="S234" t="n">
         <v>0</v>
@@ -46544,10 +46544,10 @@
         <v>0</v>
       </c>
       <c r="AC234" t="n">
-        <v>1.72</v>
+        <v>1.52</v>
       </c>
       <c r="AD234" t="n">
-        <v>1.98</v>
+        <v>2.35</v>
       </c>
       <c r="AE234" t="n">
         <v>0</v>
@@ -46654,22 +46654,22 @@
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>Hassania Agadir</t>
+          <t>Los Angeles II</t>
         </is>
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>FAR Rabat</t>
+          <t>Real Monarchs</t>
         </is>
       </c>
       <c r="G235" t="n">
@@ -46851,7 +46851,7 @@
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D236" t="inlineStr">
@@ -46861,12 +46861,12 @@
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>Central Norte</t>
+          <t>Bay</t>
         </is>
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>Deportivo Madryn</t>
+          <t>Utah Royals</t>
         </is>
       </c>
       <c r="G236" t="n">
@@ -46899,13 +46899,13 @@
         </is>
       </c>
       <c r="P236" t="n">
-        <v>2.46</v>
+        <v>0</v>
       </c>
       <c r="Q236" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="R236" t="n">
-        <v>3.17</v>
+        <v>0</v>
       </c>
       <c r="S236" t="n">
         <v>0</v>
@@ -46938,10 +46938,10 @@
         <v>0</v>
       </c>
       <c r="AC236" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AD236" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AE236" t="n">
         <v>0</v>
@@ -47048,7 +47048,7 @@
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D237" t="inlineStr">
@@ -47058,12 +47058,12 @@
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>Portland Timbers II</t>
+          <t>Central Norte</t>
         </is>
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>LA Galaxy II</t>
+          <t>Deportivo Madryn</t>
         </is>
       </c>
       <c r="G237" t="n">
@@ -47096,13 +47096,13 @@
         </is>
       </c>
       <c r="P237" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="Q237" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="R237" t="n">
-        <v>0</v>
+        <v>3.17</v>
       </c>
       <c r="S237" t="n">
         <v>0</v>
@@ -47135,10 +47135,10 @@
         <v>0</v>
       </c>
       <c r="AC237" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AD237" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AE237" t="n">
         <v>0</v>
@@ -47245,22 +47245,22 @@
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>Los Angeles II</t>
+          <t>Hassania Agadir</t>
         </is>
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>Real Monarchs</t>
+          <t>FAR Rabat</t>
         </is>
       </c>
       <c r="G238" t="n">
@@ -47442,7 +47442,7 @@
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D239" t="inlineStr">
@@ -47452,12 +47452,12 @@
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t>Bay</t>
+          <t>Portland Timbers II</t>
         </is>
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>Utah Royals</t>
+          <t>LA Galaxy II</t>
         </is>
       </c>
       <c r="G239" t="n">
@@ -47639,7 +47639,7 @@
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
@@ -47649,12 +47649,12 @@
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>New York City</t>
+          <t>CS Emelec</t>
         </is>
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>Columbus Crew</t>
+          <t>Libertad</t>
         </is>
       </c>
       <c r="G240" t="n">
@@ -47687,13 +47687,13 @@
         </is>
       </c>
       <c r="P240" t="n">
-        <v>2.23</v>
+        <v>1.67</v>
       </c>
       <c r="Q240" t="n">
-        <v>3.71</v>
+        <v>3.61</v>
       </c>
       <c r="R240" t="n">
-        <v>3.21</v>
+        <v>5.14</v>
       </c>
       <c r="S240" t="n">
         <v>0</v>
@@ -47732,10 +47732,10 @@
         <v>0</v>
       </c>
       <c r="AE240" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AF240" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AG240" t="n">
         <v>0</v>
@@ -47836,7 +47836,7 @@
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D241" t="inlineStr">
@@ -47846,12 +47846,12 @@
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>CS Emelec</t>
+          <t>New York City</t>
         </is>
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>Libertad</t>
+          <t>Columbus Crew</t>
         </is>
       </c>
       <c r="G241" t="n">
@@ -47884,13 +47884,13 @@
         </is>
       </c>
       <c r="P241" t="n">
-        <v>1.67</v>
+        <v>2.23</v>
       </c>
       <c r="Q241" t="n">
-        <v>3.61</v>
+        <v>3.71</v>
       </c>
       <c r="R241" t="n">
-        <v>5.14</v>
+        <v>3.21</v>
       </c>
       <c r="S241" t="n">
         <v>0</v>
@@ -47929,10 +47929,10 @@
         <v>0</v>
       </c>
       <c r="AE241" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AF241" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AG241" t="n">
         <v>0</v>
@@ -50003,7 +50003,7 @@
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D252" t="inlineStr">
@@ -50013,12 +50013,12 @@
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>Seattle Reign</t>
+          <t>Minnesota United</t>
         </is>
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>Washington Spirit</t>
+          <t>Austin</t>
         </is>
       </c>
       <c r="G252" t="n">
@@ -50051,13 +50051,13 @@
         </is>
       </c>
       <c r="P252" t="n">
-        <v>4.44</v>
+        <v>1.72</v>
       </c>
       <c r="Q252" t="n">
-        <v>3.5</v>
+        <v>3.97</v>
       </c>
       <c r="R252" t="n">
-        <v>1.73</v>
+        <v>5.09</v>
       </c>
       <c r="S252" t="n">
         <v>0</v>
@@ -50096,10 +50096,10 @@
         <v>0</v>
       </c>
       <c r="AE252" t="n">
-        <v>1.99</v>
+        <v>1.7</v>
       </c>
       <c r="AF252" t="n">
-        <v>1.76</v>
+        <v>2</v>
       </c>
       <c r="AG252" t="n">
         <v>0</v>
@@ -50200,7 +50200,7 @@
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
@@ -50210,12 +50210,12 @@
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>Minnesota United</t>
+          <t>Seattle Reign</t>
         </is>
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>Austin</t>
+          <t>Washington Spirit</t>
         </is>
       </c>
       <c r="G253" t="n">
@@ -50248,13 +50248,13 @@
         </is>
       </c>
       <c r="P253" t="n">
-        <v>1.72</v>
+        <v>4.44</v>
       </c>
       <c r="Q253" t="n">
-        <v>3.97</v>
+        <v>3.5</v>
       </c>
       <c r="R253" t="n">
-        <v>5.09</v>
+        <v>1.73</v>
       </c>
       <c r="S253" t="n">
         <v>0</v>
@@ -50293,10 +50293,10 @@
         <v>0</v>
       </c>
       <c r="AE253" t="n">
-        <v>1.7</v>
+        <v>1.99</v>
       </c>
       <c r="AF253" t="n">
-        <v>2</v>
+        <v>1.76</v>
       </c>
       <c r="AG253" t="n">
         <v>0</v>
@@ -50594,7 +50594,7 @@
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D255" t="inlineStr">
@@ -50604,12 +50604,12 @@
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>Blooming</t>
+          <t>Vasco da Gama</t>
         </is>
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>Bolívar</t>
+          <t>Atlético PR</t>
         </is>
       </c>
       <c r="G255" t="n">
@@ -50642,13 +50642,13 @@
         </is>
       </c>
       <c r="P255" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="Q255" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R255" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="S255" t="n">
         <v>0</v>
@@ -50791,7 +50791,7 @@
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D256" t="inlineStr">
@@ -50801,12 +50801,12 @@
       </c>
       <c r="E256" t="inlineStr">
         <is>
-          <t>Vasco da Gama</t>
+          <t>Blooming</t>
         </is>
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>Atlético PR</t>
+          <t>Bolívar</t>
         </is>
       </c>
       <c r="G256" t="n">
@@ -50839,13 +50839,13 @@
         </is>
       </c>
       <c r="P256" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="Q256" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="R256" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="S256" t="n">
         <v>0</v>

--- a/jogos_2026-05-10.xlsx
+++ b/jogos_2026-05-10.xlsx
@@ -753,7 +753,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>Australia New South Wales NPL</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -763,12 +763,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Ulsan</t>
+          <t>Blacktown City</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Bucheon 1995</t>
+          <t>St. George Saints</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -1344,7 +1344,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Australia New South Wales NPL</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Blacktown City</t>
+          <t>Ulsan</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>St. George Saints</t>
+          <t>Bucheon 1995</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Shaanxi Union</t>
+          <t>Yanbian Longding</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Shanghai Jiading</t>
+          <t>Guangxi Hengchen</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1935,22 +1935,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Yanbian Longding</t>
+          <t>Ufa</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Guangxi Hengchen</t>
+          <t>Rotor Volgograd</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1983,13 +1983,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>3.67</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>3.11</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="S8" t="n">
         <v>0</v>
@@ -2329,22 +2329,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Ufa</t>
+          <t>Shaanxi Union</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rotor Volgograd</t>
+          <t>Shanghai Jiading</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Slavia Praha U21</t>
+          <t>Viktoria Žižkov</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Táborsko</t>
+          <t>Sparta Praha II</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Viktoria Žižkov</t>
+          <t>Slavia Praha U21</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Sparta Praha II</t>
+          <t>Táborsko</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Persita</t>
+          <t>Persija</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Persijap</t>
+          <t>Persib</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Persija</t>
+          <t>Persita</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Persib</t>
+          <t>Persijap</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3905,22 +3905,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Qingdao Youth Island</t>
+          <t>Orenburg</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Wuhan Three Towns</t>
+          <t>Krylya Sovetov</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3953,13 +3953,13 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="S18" t="n">
         <v>0</v>
@@ -4102,22 +4102,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Orenburg</t>
+          <t>Qingdao Youth Island</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Krylya Sovetov</t>
+          <t>Wuhan Three Towns</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4150,13 +4150,13 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
         <v>0</v>
@@ -4299,22 +4299,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Gyeongnam</t>
+          <t>Sheger Ketema</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Gimhae City</t>
+          <t>Sidama Bunna</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,13 +4347,13 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.16</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
         <v>0</v>
@@ -4496,22 +4496,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Sichuan Jiuniu</t>
+          <t>Hoang Anh Gia Lai</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Shandong Luneng</t>
+          <t>Pho Hien</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4693,22 +4693,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Levante W</t>
+          <t>Ulytau</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Logroño W</t>
+          <t>Kairat</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4890,22 +4890,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Ulytau</t>
+          <t>Amarante</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Kairat</t>
+          <t>União Santarém</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -5087,7 +5087,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Sheger Ketema</t>
+          <t>Levante W</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Sidama Bunna</t>
+          <t>Logroño W</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5284,22 +5284,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Hoang Anh Gia Lai</t>
+          <t>Gyeongnam</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Pho Hien</t>
+          <t>Gimhae City</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5332,13 +5332,13 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="R25" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="S25" t="n">
         <v>0</v>
@@ -5481,7 +5481,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Polonia Warszawa</t>
+          <t>Sokol Saratov</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Górnik Łęczna</t>
+          <t>Spartak Kostroma</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5529,13 +5529,13 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>0</v>
+        <v>4.98</v>
       </c>
       <c r="Q26" t="n">
-        <v>0</v>
+        <v>3.66</v>
       </c>
       <c r="R26" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="S26" t="n">
         <v>0</v>
@@ -5678,7 +5678,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Sokol Saratov</t>
+          <t>Polonia Warszawa</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Spartak Kostroma</t>
+          <t>Górnik Łęczna</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5726,13 +5726,13 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>4.98</v>
+        <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>3.66</v>
+        <v>0</v>
       </c>
       <c r="R27" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="S27" t="n">
         <v>0</v>
@@ -5875,22 +5875,22 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Amarante</t>
+          <t>Sichuan Jiuniu</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>União Santarém</t>
+          <t>Shandong Luneng</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -6466,22 +6466,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Celtic</t>
+          <t>Shenyang Urban</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Yunnan Yukun</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6514,13 +6514,13 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="R31" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="S31" t="n">
         <v>0</v>
@@ -6663,22 +6663,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Kanchanaburi</t>
+          <t>Shenzhen Juniors</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Ratchaburi</t>
+          <t>Hebei Kungfu</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6711,13 +6711,13 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>3.32</v>
+        <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="R32" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="S32" t="n">
         <v>0</v>
@@ -6860,7 +6860,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Chiangrai United</t>
+          <t>Hà Nội II</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Uthai Thani</t>
+          <t>Viettel</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -6908,13 +6908,13 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>3.36</v>
+        <v>0</v>
       </c>
       <c r="R33" t="n">
-        <v>2.64</v>
+        <v>0</v>
       </c>
       <c r="S33" t="n">
         <v>0</v>
@@ -6953,10 +6953,10 @@
         <v>0</v>
       </c>
       <c r="AE33" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AF33" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AG33" t="n">
         <v>0</v>
@@ -7057,22 +7057,22 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Shenyang Urban</t>
+          <t>Rayong</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Yunnan Yukun</t>
+          <t>Bangkok United</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7105,13 +7105,13 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="Q34" t="n">
-        <v>0</v>
+        <v>3.63</v>
       </c>
       <c r="R34" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="S34" t="n">
         <v>0</v>
@@ -7254,7 +7254,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Hà Nội II</t>
+          <t>Sukhothai</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Viettel</t>
+          <t>Muang Thong United</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7302,13 +7302,13 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="Q35" t="n">
-        <v>0</v>
+        <v>3.61</v>
       </c>
       <c r="R35" t="n">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="S35" t="n">
         <v>0</v>
@@ -7451,22 +7451,22 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Piteå Women</t>
+          <t>Ayutthaya United</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Rosengard Women</t>
+          <t>Port FC</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7499,13 +7499,13 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>0</v>
+        <v>5.09</v>
       </c>
       <c r="Q36" t="n">
-        <v>0</v>
+        <v>4.18</v>
       </c>
       <c r="R36" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="S36" t="n">
         <v>0</v>
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Rayong</t>
+          <t>Chiangrai United</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Bangkok United</t>
+          <t>Uthai Thani</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7696,13 +7696,13 @@
         </is>
       </c>
       <c r="P37" t="n">
-        <v>3.4</v>
+        <v>2.7</v>
       </c>
       <c r="Q37" t="n">
-        <v>3.63</v>
+        <v>3.36</v>
       </c>
       <c r="R37" t="n">
-        <v>2.09</v>
+        <v>2.64</v>
       </c>
       <c r="S37" t="n">
         <v>0</v>
@@ -7741,10 +7741,10 @@
         <v>0</v>
       </c>
       <c r="AE37" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AF37" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AG37" t="n">
         <v>0</v>
@@ -7845,7 +7845,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Bangkok Glass</t>
+          <t>Ho Chi Minh City</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Prachuap</t>
+          <t>Song Lam Nghe An</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -7893,13 +7893,13 @@
         </is>
       </c>
       <c r="P38" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="R38" t="n">
-        <v>4.35</v>
+        <v>0</v>
       </c>
       <c r="S38" t="n">
         <v>0</v>
@@ -8042,22 +8042,22 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Shenzhen Juniors</t>
+          <t>Celtic</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Hebei Kungfu</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8090,13 +8090,13 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Q39" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="R39" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="S39" t="n">
         <v>0</v>
@@ -8239,22 +8239,22 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Buriram United</t>
+          <t>Altay</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Lamphun Warrior</t>
+          <t>Ordabasy</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8287,13 +8287,13 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>6.73</v>
+        <v>0</v>
       </c>
       <c r="R40" t="n">
-        <v>10.6</v>
+        <v>0</v>
       </c>
       <c r="S40" t="n">
         <v>0</v>
@@ -8436,22 +8436,22 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Ayutthaya United</t>
+          <t>Piteå Women</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Port FC</t>
+          <t>Rosengard Women</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8484,13 +8484,13 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>5.09</v>
+        <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>4.18</v>
+        <v>0</v>
       </c>
       <c r="R41" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="S41" t="n">
         <v>0</v>
@@ -8633,7 +8633,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Ho Chi Minh City</t>
+          <t>Buriram United</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Song Lam Nghe An</t>
+          <t>Lamphun Warrior</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8681,13 +8681,13 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="Q42" t="n">
-        <v>0</v>
+        <v>6.73</v>
       </c>
       <c r="R42" t="n">
-        <v>0</v>
+        <v>10.6</v>
       </c>
       <c r="S42" t="n">
         <v>0</v>
@@ -8830,22 +8830,22 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Altay</t>
+          <t>Bangkok Glass</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Ordabasy</t>
+          <t>Prachuap</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -8878,13 +8878,13 @@
         </is>
       </c>
       <c r="P43" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="Q43" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="R43" t="n">
-        <v>0</v>
+        <v>4.35</v>
       </c>
       <c r="S43" t="n">
         <v>0</v>
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Sukhothai</t>
+          <t>Kanchanaburi</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Muang Thong United</t>
+          <t>Ratchaburi</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9075,13 +9075,13 @@
         </is>
       </c>
       <c r="P44" t="n">
-        <v>2.44</v>
+        <v>3.32</v>
       </c>
       <c r="Q44" t="n">
-        <v>3.61</v>
+        <v>3.95</v>
       </c>
       <c r="R44" t="n">
-        <v>2.77</v>
+        <v>2.03</v>
       </c>
       <c r="S44" t="n">
         <v>0</v>
@@ -9815,22 +9815,22 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Hertha BSC</t>
+          <t>Nantong Zhiyun</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Greuther Fürth</t>
+          <t>Wuxi Wugou</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -9863,13 +9863,13 @@
         </is>
       </c>
       <c r="P48" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="Q48" t="n">
-        <v>4.15</v>
+        <v>0</v>
       </c>
       <c r="R48" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="S48" t="n">
         <v>0</v>
@@ -9914,10 +9914,10 @@
         <v>0</v>
       </c>
       <c r="AG48" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AH48" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AI48" t="n">
         <v>0</v>
@@ -10022,12 +10022,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Nantong Zhiyun</t>
+          <t>Dongguan United</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Wuxi Wugou</t>
+          <t>Suzhou Dongwu</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10209,22 +10209,22 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Havelse</t>
+          <t>Nõmme Kalju</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Schweinfurt</t>
+          <t>Tallinna FC Flora</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10257,13 +10257,13 @@
         </is>
       </c>
       <c r="P50" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="Q50" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="R50" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="S50" t="n">
         <v>0</v>
@@ -10406,22 +10406,22 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Singapore S.League</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Dongguan United</t>
+          <t>Home United</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Suzhou Dongwu</t>
+          <t>Albirex Niigata S</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10603,22 +10603,22 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Singapore S.League</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Home United</t>
+          <t>Fortuna Düsseldorf</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Albirex Niigata S</t>
+          <t>Elversberg</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10651,13 +10651,13 @@
         </is>
       </c>
       <c r="P52" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="Q52" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="R52" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="S52" t="n">
         <v>0</v>
@@ -10800,22 +10800,22 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Nõmme Kalju</t>
+          <t>Hertha BSC</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Tallinna FC Flora</t>
+          <t>Greuther Fürth</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -10848,13 +10848,13 @@
         </is>
       </c>
       <c r="P53" t="n">
-        <v>2.27</v>
+        <v>1.78</v>
       </c>
       <c r="Q53" t="n">
-        <v>3.7</v>
+        <v>4.15</v>
       </c>
       <c r="R53" t="n">
-        <v>2.6</v>
+        <v>3.8</v>
       </c>
       <c r="S53" t="n">
         <v>0</v>
@@ -10899,10 +10899,10 @@
         <v>0</v>
       </c>
       <c r="AG53" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AH53" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AI53" t="n">
         <v>0</v>
@@ -11194,22 +11194,22 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Singapore S.League</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Hougang United</t>
+          <t>Havelse</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Tampines Rovers</t>
+          <t>Schweinfurt</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11391,7 +11391,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -11401,12 +11401,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>KAA Gent</t>
+          <t>Preußen Münster</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>RSC Anderlecht</t>
+          <t>Darmstadt 98</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11439,13 +11439,13 @@
         </is>
       </c>
       <c r="P56" t="n">
-        <v>2.32</v>
+        <v>2.29</v>
       </c>
       <c r="Q56" t="n">
-        <v>3.71</v>
+        <v>3.74</v>
       </c>
       <c r="R56" t="n">
-        <v>2.89</v>
+        <v>2.76</v>
       </c>
       <c r="S56" t="n">
         <v>0</v>
@@ -11588,22 +11588,22 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Singapore S.League</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Fortuna Düsseldorf</t>
+          <t>Hougang United</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Elversberg</t>
+          <t>Tampines Rovers</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11636,13 +11636,13 @@
         </is>
       </c>
       <c r="P57" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="Q57" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="R57" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="S57" t="n">
         <v>0</v>
@@ -11785,7 +11785,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -11795,12 +11795,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Preußen Münster</t>
+          <t>KAA Gent</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Darmstadt 98</t>
+          <t>RSC Anderlecht</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -11833,13 +11833,13 @@
         </is>
       </c>
       <c r="P58" t="n">
-        <v>2.29</v>
+        <v>2.32</v>
       </c>
       <c r="Q58" t="n">
-        <v>3.74</v>
+        <v>3.71</v>
       </c>
       <c r="R58" t="n">
-        <v>2.76</v>
+        <v>2.89</v>
       </c>
       <c r="S58" t="n">
         <v>0</v>
@@ -12573,7 +12573,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -12583,12 +12583,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Bahardar</t>
+          <t>FC Andorra</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Welwalo Adigrat Uni</t>
+          <t>UD Las Palmas</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12621,13 +12621,13 @@
         </is>
       </c>
       <c r="P62" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="Q62" t="n">
-        <v>0</v>
+        <v>3.43</v>
       </c>
       <c r="R62" t="n">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="S62" t="n">
         <v>0</v>
@@ -12770,7 +12770,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -12780,12 +12780,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Qingdao Jonoon</t>
+          <t>Aktobe</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Dalian Zhixing</t>
+          <t>Kaisar</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -12967,7 +12967,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -12977,12 +12977,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Zenit</t>
+          <t>Vejle</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>FK Sochi</t>
+          <t>Fredericia</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -13015,13 +13015,13 @@
         </is>
       </c>
       <c r="P64" t="n">
-        <v>1.21</v>
+        <v>2.58</v>
       </c>
       <c r="Q64" t="n">
-        <v>7.41</v>
+        <v>3.62</v>
       </c>
       <c r="R64" t="n">
-        <v>17.5</v>
+        <v>2.45</v>
       </c>
       <c r="S64" t="n">
         <v>0</v>
@@ -13164,7 +13164,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -13174,12 +13174,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Lugano</t>
+          <t>Zenit</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>St. Gallen</t>
+          <t>FK Sochi</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -13212,13 +13212,13 @@
         </is>
       </c>
       <c r="P65" t="n">
-        <v>2.36</v>
+        <v>1.21</v>
       </c>
       <c r="Q65" t="n">
-        <v>3.54</v>
+        <v>7.41</v>
       </c>
       <c r="R65" t="n">
-        <v>2.73</v>
+        <v>17.5</v>
       </c>
       <c r="S65" t="n">
         <v>0</v>
@@ -13361,22 +13361,22 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>FC Andorra</t>
+          <t>Meshakhte</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>UD Las Palmas</t>
+          <t>Dila</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -13409,13 +13409,13 @@
         </is>
       </c>
       <c r="P66" t="n">
-        <v>2.46</v>
+        <v>0</v>
       </c>
       <c r="Q66" t="n">
-        <v>3.43</v>
+        <v>0</v>
       </c>
       <c r="R66" t="n">
-        <v>2.91</v>
+        <v>0</v>
       </c>
       <c r="S66" t="n">
         <v>0</v>
@@ -13558,7 +13558,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -13568,12 +13568,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>PSIM Yogyakarta</t>
+          <t>RCD Mallorca</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Malut United</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -13755,22 +13755,22 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Vejle</t>
+          <t>Qingdao Jonoon</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Fredericia</t>
+          <t>Dalian Zhixing</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -13803,13 +13803,13 @@
         </is>
       </c>
       <c r="P68" t="n">
-        <v>2.58</v>
+        <v>0</v>
       </c>
       <c r="Q68" t="n">
-        <v>3.62</v>
+        <v>0</v>
       </c>
       <c r="R68" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="S68" t="n">
         <v>0</v>
@@ -13952,22 +13952,22 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Aktobe</t>
+          <t>Bahardar</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Kaisar</t>
+          <t>Welwalo Adigrat Uni</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -14149,22 +14149,22 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Kalmar</t>
+          <t>Nordsjælland</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Halmstad</t>
+          <t>Midtjylland</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -14197,13 +14197,13 @@
         </is>
       </c>
       <c r="P70" t="n">
-        <v>1.92</v>
+        <v>3.36</v>
       </c>
       <c r="Q70" t="n">
-        <v>3.4</v>
+        <v>3.65</v>
       </c>
       <c r="R70" t="n">
-        <v>3.9</v>
+        <v>1.99</v>
       </c>
       <c r="S70" t="n">
         <v>0</v>
@@ -14346,22 +14346,22 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AIK</t>
+          <t>PSIM Yogyakarta</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Djurgården</t>
+          <t>Malut United</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -14394,13 +14394,13 @@
         </is>
       </c>
       <c r="P71" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="Q71" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="R71" t="n">
-        <v>2.87</v>
+        <v>0</v>
       </c>
       <c r="S71" t="n">
         <v>0</v>
@@ -14543,7 +14543,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -14553,12 +14553,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Nordsjælland</t>
+          <t>Lugano</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Midtjylland</t>
+          <t>St. Gallen</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -14591,13 +14591,13 @@
         </is>
       </c>
       <c r="P72" t="n">
-        <v>3.36</v>
+        <v>2.36</v>
       </c>
       <c r="Q72" t="n">
-        <v>3.65</v>
+        <v>3.54</v>
       </c>
       <c r="R72" t="n">
-        <v>1.99</v>
+        <v>2.73</v>
       </c>
       <c r="S72" t="n">
         <v>0</v>
@@ -14740,22 +14740,22 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>RCD Mallorca</t>
+          <t>Kalmar</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>Halmstad</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -14788,13 +14788,13 @@
         </is>
       </c>
       <c r="P73" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="Q73" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R73" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="S73" t="n">
         <v>0</v>
@@ -14937,7 +14937,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -14947,12 +14947,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Meshakhte</t>
+          <t>AIK</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Dila</t>
+          <t>Djurgården</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -14985,13 +14985,13 @@
         </is>
       </c>
       <c r="P74" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="Q74" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="R74" t="n">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="S74" t="n">
         <v>0</v>
@@ -15528,7 +15528,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -15538,12 +15538,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Baník Ostrava U21</t>
+          <t>Tychy 71</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Ústí nad Labem</t>
+          <t>Ruch Chorzów</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -15576,13 +15576,13 @@
         </is>
       </c>
       <c r="P77" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Q77" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R77" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="S77" t="n">
         <v>0</v>
@@ -15922,7 +15922,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -15932,12 +15932,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Tychy 71</t>
+          <t>Baník Ostrava U21</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Ruch Chorzów</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -15970,13 +15970,13 @@
         </is>
       </c>
       <c r="P79" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="Q79" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R79" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="S79" t="n">
         <v>0</v>
@@ -16316,7 +16316,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -16326,12 +16326,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Kelantan United</t>
+          <t>Arba Minch Kenema</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Johor Darul Ta'zim</t>
+          <t>Welayta Dicha</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -16513,22 +16513,22 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Sigma Olomouc</t>
+          <t>Astana</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Bohemians 1905</t>
+          <t>Kyzyl-Zhar</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -16561,13 +16561,13 @@
         </is>
       </c>
       <c r="P82" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Q82" t="n">
-        <v>0</v>
+        <v>3.76</v>
       </c>
       <c r="R82" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="S82" t="n">
         <v>0</v>
@@ -16710,7 +16710,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -16720,12 +16720,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Arba Minch Kenema</t>
+          <t>Kelantan United</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Welayta Dicha</t>
+          <t>Johor Darul Ta'zim</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -16907,22 +16907,22 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Uppsala W</t>
+          <t>NK Primorje</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Vittsjö</t>
+          <t>Mura</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -16955,13 +16955,13 @@
         </is>
       </c>
       <c r="P84" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="Q84" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="R84" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S84" t="n">
         <v>0</v>
@@ -17301,7 +17301,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -17311,12 +17311,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>NK Primorje</t>
+          <t>Turan</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Mura</t>
+          <t>Karvan FK</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -17349,13 +17349,13 @@
         </is>
       </c>
       <c r="P86" t="n">
-        <v>2.59</v>
+        <v>0</v>
       </c>
       <c r="Q86" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="R86" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="S86" t="n">
         <v>0</v>
@@ -17498,7 +17498,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -17508,12 +17508,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Pardubice</t>
+          <t>Cremonese</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Karviná</t>
+          <t>Pisa</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -17546,13 +17546,13 @@
         </is>
       </c>
       <c r="P87" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Q87" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="R87" t="n">
-        <v>0</v>
+        <v>4.07</v>
       </c>
       <c r="S87" t="n">
         <v>0</v>
@@ -17591,10 +17591,10 @@
         <v>0</v>
       </c>
       <c r="AE87" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AF87" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AG87" t="n">
         <v>0</v>
@@ -17695,22 +17695,22 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Botoşani</t>
+          <t>Uppsala W</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Petrolul 52</t>
+          <t>Vittsjö</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -17743,13 +17743,13 @@
         </is>
       </c>
       <c r="P88" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="Q88" t="n">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="R88" t="n">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="S88" t="n">
         <v>0</v>
@@ -17892,7 +17892,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -17902,12 +17902,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Fiorentina</t>
+          <t>Nottingham Forest</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Genoa</t>
+          <t>Newcastle United</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -17940,13 +17940,13 @@
         </is>
       </c>
       <c r="P89" t="n">
-        <v>2.09</v>
+        <v>2.46</v>
       </c>
       <c r="Q89" t="n">
-        <v>3.48</v>
+        <v>3.66</v>
       </c>
       <c r="R89" t="n">
-        <v>4.01</v>
+        <v>2.99</v>
       </c>
       <c r="S89" t="n">
         <v>0</v>
@@ -17985,10 +17985,10 @@
         <v>0</v>
       </c>
       <c r="AE89" t="n">
-        <v>1.98</v>
+        <v>1.68</v>
       </c>
       <c r="AF89" t="n">
-        <v>1.73</v>
+        <v>2.05</v>
       </c>
       <c r="AG89" t="n">
         <v>0</v>
@@ -18099,12 +18099,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Nottingham Forest</t>
+          <t>Crystal Palace</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Newcastle United</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -18137,13 +18137,13 @@
         </is>
       </c>
       <c r="P90" t="n">
-        <v>2.46</v>
+        <v>2.69</v>
       </c>
       <c r="Q90" t="n">
-        <v>3.66</v>
+        <v>3.31</v>
       </c>
       <c r="R90" t="n">
-        <v>2.99</v>
+        <v>2.92</v>
       </c>
       <c r="S90" t="n">
         <v>0</v>
@@ -18182,10 +18182,10 @@
         <v>0</v>
       </c>
       <c r="AE90" t="n">
-        <v>1.68</v>
+        <v>1.87</v>
       </c>
       <c r="AF90" t="n">
-        <v>2.05</v>
+        <v>1.89</v>
       </c>
       <c r="AG90" t="n">
         <v>0</v>
@@ -18286,7 +18286,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -18296,12 +18296,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Turan</t>
+          <t>Botoşani</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Karvan FK</t>
+          <t>Petrolul 52</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -18334,13 +18334,13 @@
         </is>
       </c>
       <c r="P91" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="Q91" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="R91" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="S91" t="n">
         <v>0</v>
@@ -18483,7 +18483,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -18493,12 +18493,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Cremonese</t>
+          <t>Sigma Olomouc</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Pisa</t>
+          <t>Bohemians 1905</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -18531,13 +18531,13 @@
         </is>
       </c>
       <c r="P92" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Q92" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="R92" t="n">
-        <v>4.07</v>
+        <v>0</v>
       </c>
       <c r="S92" t="n">
         <v>0</v>
@@ -18576,10 +18576,10 @@
         <v>0</v>
       </c>
       <c r="AE92" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AF92" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AG92" t="n">
         <v>0</v>
@@ -18680,22 +18680,22 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Astana</t>
+          <t>Pardubice</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Kyzyl-Zhar</t>
+          <t>Karviná</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -18728,13 +18728,13 @@
         </is>
       </c>
       <c r="P93" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Q93" t="n">
-        <v>3.76</v>
+        <v>0</v>
       </c>
       <c r="R93" t="n">
-        <v>4.15</v>
+        <v>0</v>
       </c>
       <c r="S93" t="n">
         <v>0</v>
@@ -18877,7 +18877,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -18887,12 +18887,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Crystal Palace</t>
+          <t>Fiorentina</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Genoa</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -18925,13 +18925,13 @@
         </is>
       </c>
       <c r="P94" t="n">
-        <v>2.69</v>
+        <v>2.09</v>
       </c>
       <c r="Q94" t="n">
-        <v>3.31</v>
+        <v>3.48</v>
       </c>
       <c r="R94" t="n">
-        <v>2.92</v>
+        <v>4.01</v>
       </c>
       <c r="S94" t="n">
         <v>0</v>
@@ -18970,10 +18970,10 @@
         <v>0</v>
       </c>
       <c r="AE94" t="n">
-        <v>1.87</v>
+        <v>1.98</v>
       </c>
       <c r="AF94" t="n">
-        <v>1.89</v>
+        <v>1.73</v>
       </c>
       <c r="AG94" t="n">
         <v>0</v>
@@ -19468,7 +19468,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -19478,12 +19478,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>NorthEast United</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Chennaiyin</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -19516,13 +19516,13 @@
         </is>
       </c>
       <c r="P97" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="Q97" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="R97" t="n">
-        <v>3.21</v>
+        <v>0</v>
       </c>
       <c r="S97" t="n">
         <v>0</v>
@@ -19561,10 +19561,10 @@
         <v>0</v>
       </c>
       <c r="AE97" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AF97" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AG97" t="n">
         <v>0</v>
@@ -19665,7 +19665,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -19675,12 +19675,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Volos NFC</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Levadiakos</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -19713,13 +19713,13 @@
         </is>
       </c>
       <c r="P98" t="n">
-        <v>3.04</v>
+        <v>2.17</v>
       </c>
       <c r="Q98" t="n">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="R98" t="n">
-        <v>2.32</v>
+        <v>3.21</v>
       </c>
       <c r="S98" t="n">
         <v>0</v>
@@ -19758,10 +19758,10 @@
         <v>0</v>
       </c>
       <c r="AE98" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AF98" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AG98" t="n">
         <v>0</v>
@@ -19862,7 +19862,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -19872,12 +19872,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Aris</t>
+          <t>Royal Antwerp FC</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>OFI</t>
+          <t>Sporting Charleroi</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -19910,13 +19910,13 @@
         </is>
       </c>
       <c r="P99" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="Q99" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="R99" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="S99" t="n">
         <v>0</v>
@@ -19955,10 +19955,10 @@
         <v>0</v>
       </c>
       <c r="AE99" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AF99" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG99" t="n">
         <v>0</v>
@@ -20256,7 +20256,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -20266,12 +20266,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Honvéd W</t>
+          <t>Silkeborg</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Vasas</t>
+          <t>København</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -20304,13 +20304,13 @@
         </is>
       </c>
       <c r="P101" t="n">
-        <v>0</v>
+        <v>4.68</v>
       </c>
       <c r="Q101" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R101" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="S101" t="n">
         <v>0</v>
@@ -20453,22 +20453,22 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>NorthEast United</t>
+          <t>Banga</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Chennaiyin</t>
+          <t>TransINVEST Vilnius</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -20650,7 +20650,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -20660,12 +20660,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Royal Antwerp FC</t>
+          <t>Honvéd W</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Sporting Charleroi</t>
+          <t>Vasas</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -20698,13 +20698,13 @@
         </is>
       </c>
       <c r="P103" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="Q103" t="n">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="R103" t="n">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="S103" t="n">
         <v>0</v>
@@ -20743,10 +20743,10 @@
         <v>0</v>
       </c>
       <c r="AE103" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AF103" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AG103" t="n">
         <v>0</v>
@@ -20847,22 +20847,22 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Banga</t>
+          <t>Volos NFC</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>TransINVEST Vilnius</t>
+          <t>Levadiakos</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -20895,13 +20895,13 @@
         </is>
       </c>
       <c r="P104" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="Q104" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R104" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="S104" t="n">
         <v>0</v>
@@ -21044,7 +21044,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -21054,12 +21054,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Nõmme United</t>
+          <t>EB - Streymur</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Paide</t>
+          <t>Víkingur</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -21092,13 +21092,13 @@
         </is>
       </c>
       <c r="P105" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="Q105" t="n">
-        <v>3.88</v>
+        <v>0</v>
       </c>
       <c r="R105" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="S105" t="n">
         <v>0</v>
@@ -21241,22 +21241,22 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Silkeborg</t>
+          <t>B36</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>KÍ</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -21289,13 +21289,13 @@
         </is>
       </c>
       <c r="P106" t="n">
-        <v>4.68</v>
+        <v>0</v>
       </c>
       <c r="Q106" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R106" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="S106" t="n">
         <v>0</v>
@@ -21438,22 +21438,22 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>B36</t>
+          <t>Aris</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>KÍ</t>
+          <t>OFI</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -21635,7 +21635,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -21645,12 +21645,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>EB - Streymur</t>
+          <t>Nõmme United</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Víkingur</t>
+          <t>Paide</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -21683,13 +21683,13 @@
         </is>
       </c>
       <c r="P108" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="Q108" t="n">
-        <v>0</v>
+        <v>3.88</v>
       </c>
       <c r="R108" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="S108" t="n">
         <v>0</v>
@@ -21832,7 +21832,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -21842,12 +21842,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Akhmat Grozny</t>
+          <t>Athletic Club Bilbao</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Makhachkala</t>
+          <t>Valencia CF</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -21880,13 +21880,13 @@
         </is>
       </c>
       <c r="P109" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="Q109" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="R109" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="S109" t="n">
         <v>0</v>
@@ -22226,7 +22226,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -22236,12 +22236,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Athletic Club Bilbao</t>
+          <t>Akhmat Grozny</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Valencia CF</t>
+          <t>Makhachkala</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -22274,13 +22274,13 @@
         </is>
       </c>
       <c r="P111" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="Q111" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="R111" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="S111" t="n">
         <v>0</v>
@@ -22423,7 +22423,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -22433,12 +22433,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Young Boys</t>
+          <t>Viktoria Köln</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Basel</t>
+          <t>Alemannia Aachen</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -22471,13 +22471,13 @@
         </is>
       </c>
       <c r="P112" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="Q112" t="n">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="R112" t="n">
-        <v>3.57</v>
+        <v>0</v>
       </c>
       <c r="S112" t="n">
         <v>0</v>
@@ -22522,10 +22522,10 @@
         <v>0</v>
       </c>
       <c r="AG112" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AH112" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AI112" t="n">
         <v>0</v>
@@ -22620,22 +22620,22 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Viktoria Köln</t>
+          <t>Häcken</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Alemannia Aachen</t>
+          <t>Malmö FF</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -22668,13 +22668,13 @@
         </is>
       </c>
       <c r="P113" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="Q113" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="R113" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="S113" t="n">
         <v>0</v>
@@ -22817,7 +22817,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -22827,12 +22827,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Neftekhimik</t>
+          <t>Young Boys</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Volga Ulyanovsk</t>
+          <t>Basel</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -22865,13 +22865,13 @@
         </is>
       </c>
       <c r="P114" t="n">
-        <v>2.09</v>
+        <v>1.85</v>
       </c>
       <c r="Q114" t="n">
-        <v>3.17</v>
+        <v>4.05</v>
       </c>
       <c r="R114" t="n">
-        <v>3.6</v>
+        <v>3.57</v>
       </c>
       <c r="S114" t="n">
         <v>0</v>
@@ -22916,10 +22916,10 @@
         <v>0</v>
       </c>
       <c r="AG114" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AH114" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AI114" t="n">
         <v>0</v>
@@ -23211,22 +23211,22 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Häcken</t>
+          <t>Neftekhimik</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Malmö FF</t>
+          <t>Volga Ulyanovsk</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -23259,13 +23259,13 @@
         </is>
       </c>
       <c r="P116" t="n">
-        <v>2.27</v>
+        <v>2.09</v>
       </c>
       <c r="Q116" t="n">
-        <v>3.58</v>
+        <v>3.17</v>
       </c>
       <c r="R116" t="n">
-        <v>2.88</v>
+        <v>3.6</v>
       </c>
       <c r="S116" t="n">
         <v>0</v>
@@ -23418,12 +23418,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Fortuna Sittard</t>
+          <t>Feyenoord</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>PEC Zwolle</t>
+          <t>AZ</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -23456,13 +23456,13 @@
         </is>
       </c>
       <c r="P117" t="n">
-        <v>1.96</v>
+        <v>1.78</v>
       </c>
       <c r="Q117" t="n">
-        <v>4.05</v>
+        <v>4.17</v>
       </c>
       <c r="R117" t="n">
-        <v>3.5</v>
+        <v>4.17</v>
       </c>
       <c r="S117" t="n">
         <v>0</v>
@@ -23507,10 +23507,10 @@
         <v>0</v>
       </c>
       <c r="AG117" t="n">
-        <v>2.2</v>
+        <v>1.9</v>
       </c>
       <c r="AH117" t="n">
-        <v>1.58</v>
+        <v>1.77</v>
       </c>
       <c r="AI117" t="n">
         <v>0</v>
@@ -23615,12 +23615,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Excelsior</t>
+          <t>Telstar</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Volendam</t>
+          <t>Heracles</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -23653,13 +23653,13 @@
         </is>
       </c>
       <c r="P118" t="n">
-        <v>1.77</v>
+        <v>1.48</v>
       </c>
       <c r="Q118" t="n">
-        <v>4.17</v>
+        <v>4.94</v>
       </c>
       <c r="R118" t="n">
-        <v>4.22</v>
+        <v>6.07</v>
       </c>
       <c r="S118" t="n">
         <v>0</v>
@@ -23698,16 +23698,16 @@
         <v>0</v>
       </c>
       <c r="AE118" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AF118" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AG118" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AH118" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AI118" t="n">
         <v>0</v>
@@ -23812,12 +23812,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Telstar</t>
+          <t>Excelsior</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Heracles</t>
+          <t>Volendam</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -23850,13 +23850,13 @@
         </is>
       </c>
       <c r="P119" t="n">
-        <v>1.48</v>
+        <v>1.77</v>
       </c>
       <c r="Q119" t="n">
-        <v>4.94</v>
+        <v>4.17</v>
       </c>
       <c r="R119" t="n">
-        <v>6.07</v>
+        <v>4.22</v>
       </c>
       <c r="S119" t="n">
         <v>0</v>
@@ -23895,16 +23895,16 @@
         <v>0</v>
       </c>
       <c r="AE119" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AF119" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AG119" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AH119" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AI119" t="n">
         <v>0</v>
@@ -24009,12 +24009,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Ajax</t>
+          <t>Fortuna Sittard</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Utrecht</t>
+          <t>PEC Zwolle</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -24047,13 +24047,13 @@
         </is>
       </c>
       <c r="P120" t="n">
-        <v>1.71</v>
+        <v>1.96</v>
       </c>
       <c r="Q120" t="n">
-        <v>4.37</v>
+        <v>4.05</v>
       </c>
       <c r="R120" t="n">
-        <v>4.42</v>
+        <v>3.5</v>
       </c>
       <c r="S120" t="n">
         <v>0</v>
@@ -24098,10 +24098,10 @@
         <v>0</v>
       </c>
       <c r="AG120" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="AH120" t="n">
-        <v>1.65</v>
+        <v>1.58</v>
       </c>
       <c r="AI120" t="n">
         <v>0</v>
@@ -24206,12 +24206,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Groningen</t>
+          <t>Go Ahead Eagles</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>NEC</t>
+          <t>PSV</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -24244,13 +24244,13 @@
         </is>
       </c>
       <c r="P121" t="n">
-        <v>2.78</v>
+        <v>4.48</v>
       </c>
       <c r="Q121" t="n">
-        <v>3.89</v>
+        <v>4.74</v>
       </c>
       <c r="R121" t="n">
-        <v>2.36</v>
+        <v>1.65</v>
       </c>
       <c r="S121" t="n">
         <v>0</v>
@@ -24295,10 +24295,10 @@
         <v>0</v>
       </c>
       <c r="AG121" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AH121" t="n">
         <v>2.05</v>
-      </c>
-      <c r="AH121" t="n">
-        <v>1.68</v>
       </c>
       <c r="AI121" t="n">
         <v>0</v>
@@ -24600,12 +24600,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Go Ahead Eagles</t>
+          <t>Ajax</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>PSV</t>
+          <t>Utrecht</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -24638,61 +24638,61 @@
         </is>
       </c>
       <c r="P123" t="n">
-        <v>4.48</v>
+        <v>1.71</v>
       </c>
       <c r="Q123" t="n">
-        <v>4.74</v>
+        <v>4.37</v>
       </c>
       <c r="R123" t="n">
+        <v>4.42</v>
+      </c>
+      <c r="S123" t="n">
+        <v>0</v>
+      </c>
+      <c r="T123" t="n">
+        <v>0</v>
+      </c>
+      <c r="U123" t="n">
+        <v>0</v>
+      </c>
+      <c r="V123" t="n">
+        <v>0</v>
+      </c>
+      <c r="W123" t="n">
+        <v>0</v>
+      </c>
+      <c r="X123" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y123" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z123" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA123" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB123" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC123" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD123" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE123" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF123" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG123" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AH123" t="n">
         <v>1.65</v>
-      </c>
-      <c r="S123" t="n">
-        <v>0</v>
-      </c>
-      <c r="T123" t="n">
-        <v>0</v>
-      </c>
-      <c r="U123" t="n">
-        <v>0</v>
-      </c>
-      <c r="V123" t="n">
-        <v>0</v>
-      </c>
-      <c r="W123" t="n">
-        <v>0</v>
-      </c>
-      <c r="X123" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y123" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z123" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA123" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB123" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC123" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD123" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE123" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF123" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG123" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AH123" t="n">
-        <v>2.05</v>
       </c>
       <c r="AI123" t="n">
         <v>0</v>
@@ -24797,12 +24797,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Feyenoord</t>
+          <t>NAC Breda</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>AZ</t>
+          <t>Heerenveen</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -24835,13 +24835,13 @@
         </is>
       </c>
       <c r="P124" t="n">
-        <v>1.78</v>
+        <v>2.49</v>
       </c>
       <c r="Q124" t="n">
-        <v>4.17</v>
+        <v>3.77</v>
       </c>
       <c r="R124" t="n">
-        <v>4.17</v>
+        <v>2.67</v>
       </c>
       <c r="S124" t="n">
         <v>0</v>
@@ -24880,16 +24880,16 @@
         <v>0</v>
       </c>
       <c r="AE124" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AF124" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AG124" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AH124" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AI124" t="n">
         <v>0</v>
@@ -24994,12 +24994,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>NAC Breda</t>
+          <t>Groningen</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Heerenveen</t>
+          <t>NEC</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -25032,13 +25032,13 @@
         </is>
       </c>
       <c r="P125" t="n">
-        <v>2.49</v>
+        <v>2.78</v>
       </c>
       <c r="Q125" t="n">
-        <v>3.77</v>
+        <v>3.89</v>
       </c>
       <c r="R125" t="n">
-        <v>2.67</v>
+        <v>2.36</v>
       </c>
       <c r="S125" t="n">
         <v>0</v>
@@ -25077,16 +25077,16 @@
         <v>0</v>
       </c>
       <c r="AE125" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AF125" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AG125" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AH125" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AI125" t="n">
         <v>0</v>
@@ -25181,22 +25181,22 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Saburtalo</t>
+          <t>Rapid Wien</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Torpedo Kutaisi</t>
+          <t>Austria Wien</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -25229,13 +25229,13 @@
         </is>
       </c>
       <c r="P126" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Q126" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="R126" t="n">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="S126" t="n">
         <v>0</v>
@@ -25378,7 +25378,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -25388,12 +25388,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Croatia Zmijavci</t>
+          <t>Akademija Pandev</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Jarun</t>
+          <t>Rabotnički</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -25575,22 +25575,22 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Paphos</t>
+          <t>Sogndal</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Aris</t>
+          <t>Haugesund</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -25623,13 +25623,13 @@
         </is>
       </c>
       <c r="P128" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="Q128" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="R128" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="S128" t="n">
         <v>0</v>
@@ -25772,22 +25772,22 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Omonia Nicosia</t>
+          <t>Moss</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>AEK Larnaca</t>
+          <t>Bryne</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -25820,13 +25820,13 @@
         </is>
       </c>
       <c r="P129" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Q129" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="R129" t="n">
-        <v>0</v>
+        <v>3.01</v>
       </c>
       <c r="S129" t="n">
         <v>0</v>
@@ -25969,7 +25969,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -25979,12 +25979,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Apollon</t>
+          <t>Budafoki MTE</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>APOEL</t>
+          <t>BVSC</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -26166,7 +26166,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -26176,12 +26176,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Szentlőrinc SE</t>
+          <t>Mebrat Hayl</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Videoton</t>
+          <t>Fasil Ketema</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -26363,22 +26363,22 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Zbrojovka Brno</t>
+          <t>Sandnes Ulf</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Vlašim</t>
+          <t>Stabæk</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -26411,13 +26411,13 @@
         </is>
       </c>
       <c r="P132" t="n">
-        <v>0</v>
+        <v>4.07</v>
       </c>
       <c r="Q132" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="R132" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="S132" t="n">
         <v>0</v>
@@ -26560,22 +26560,22 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Moss</t>
+          <t>Pogoń Siedlce</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Bryne</t>
+          <t>Stal Rzeszów</t>
         </is>
       </c>
       <c r="G133" t="n">
@@ -26608,13 +26608,13 @@
         </is>
       </c>
       <c r="P133" t="n">
-        <v>2.15</v>
+        <v>2.55</v>
       </c>
       <c r="Q133" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="R133" t="n">
-        <v>3.01</v>
+        <v>2.43</v>
       </c>
       <c r="S133" t="n">
         <v>0</v>
@@ -26757,22 +26757,22 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Vardar</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Sileks</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="G134" t="n">
@@ -26805,13 +26805,13 @@
         </is>
       </c>
       <c r="P134" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="Q134" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R134" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="S134" t="n">
         <v>0</v>
@@ -26954,7 +26954,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -26964,12 +26964,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Shkendija</t>
+          <t>Szentlőrinc SE</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Struga</t>
+          <t>Videoton</t>
         </is>
       </c>
       <c r="G135" t="n">
@@ -27151,22 +27151,22 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Real Madrid W</t>
+          <t>Strømmen</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Atletico Madrid W</t>
+          <t>Hødd</t>
         </is>
       </c>
       <c r="G136" t="n">
@@ -27199,13 +27199,13 @@
         </is>
       </c>
       <c r="P136" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Q136" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R136" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="S136" t="n">
         <v>0</v>
@@ -27348,7 +27348,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -27358,12 +27358,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Makedonija GjP</t>
+          <t>Zbrojovka Brno</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Tikveš</t>
+          <t>Vlašim</t>
         </is>
       </c>
       <c r="G137" t="n">
@@ -27545,7 +27545,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -27555,12 +27555,12 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Pelister</t>
+          <t>Kecskeméti TE</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Shkupi</t>
+          <t>Mezőkövesd-Zsóry</t>
         </is>
       </c>
       <c r="G138" t="n">
@@ -27752,12 +27752,12 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Aresimi</t>
+          <t>Pelister</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>FK Bashkimi Kumanovo</t>
+          <t>Shkupi</t>
         </is>
       </c>
       <c r="G139" t="n">
@@ -27939,22 +27939,22 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Åsane</t>
+          <t>Paphos</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Strømsgodset</t>
+          <t>Aris</t>
         </is>
       </c>
       <c r="G140" t="n">
@@ -27987,13 +27987,13 @@
         </is>
       </c>
       <c r="P140" t="n">
-        <v>5.4</v>
+        <v>0</v>
       </c>
       <c r="Q140" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="R140" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="S140" t="n">
         <v>0</v>
@@ -28136,7 +28136,7 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -28146,12 +28146,12 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Hartberg</t>
+          <t>Omonia Nicosia</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Sturm Graz</t>
+          <t>AEK Larnaca</t>
         </is>
       </c>
       <c r="G141" t="n">
@@ -28184,13 +28184,13 @@
         </is>
       </c>
       <c r="P141" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="Q141" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R141" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="S141" t="n">
         <v>0</v>
@@ -28229,10 +28229,10 @@
         <v>0</v>
       </c>
       <c r="AE141" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AF141" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AG141" t="n">
         <v>0</v>
@@ -28333,22 +28333,22 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Sogndal</t>
+          <t>Hartberg</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Haugesund</t>
+          <t>Sturm Graz</t>
         </is>
       </c>
       <c r="G142" t="n">
@@ -28381,13 +28381,13 @@
         </is>
       </c>
       <c r="P142" t="n">
-        <v>3.1</v>
+        <v>3.75</v>
       </c>
       <c r="Q142" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="R142" t="n">
-        <v>2.12</v>
+        <v>1.91</v>
       </c>
       <c r="S142" t="n">
         <v>0</v>
@@ -28426,10 +28426,10 @@
         <v>0</v>
       </c>
       <c r="AE142" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AF142" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG142" t="n">
         <v>0</v>
@@ -28530,22 +28530,22 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Sandnes Ulf</t>
+          <t>Croatia Zmijavci</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Stabæk</t>
+          <t>Jarun</t>
         </is>
       </c>
       <c r="G143" t="n">
@@ -28578,13 +28578,13 @@
         </is>
       </c>
       <c r="P143" t="n">
-        <v>4.07</v>
+        <v>0</v>
       </c>
       <c r="Q143" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="R143" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="S143" t="n">
         <v>0</v>
@@ -28727,7 +28727,7 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -28737,12 +28737,12 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>LASK Linz</t>
+          <t>Apollon</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Salzburg</t>
+          <t>APOEL</t>
         </is>
       </c>
       <c r="G144" t="n">
@@ -28775,13 +28775,13 @@
         </is>
       </c>
       <c r="P144" t="n">
-        <v>2.51</v>
+        <v>0</v>
       </c>
       <c r="Q144" t="n">
-        <v>3.78</v>
+        <v>0</v>
       </c>
       <c r="R144" t="n">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="S144" t="n">
         <v>0</v>
@@ -28924,22 +28924,22 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>LASK Linz</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Salzburg</t>
         </is>
       </c>
       <c r="G145" t="n">
@@ -28972,13 +28972,13 @@
         </is>
       </c>
       <c r="P145" t="n">
-        <v>2.65</v>
+        <v>2.51</v>
       </c>
       <c r="Q145" t="n">
-        <v>3.6</v>
+        <v>3.78</v>
       </c>
       <c r="R145" t="n">
-        <v>2.4</v>
+        <v>2.44</v>
       </c>
       <c r="S145" t="n">
         <v>0</v>
@@ -29121,22 +29121,22 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Akademija Pandev</t>
+          <t>KFUM</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Rabotnički</t>
+          <t>Viking</t>
         </is>
       </c>
       <c r="G146" t="n">
@@ -29169,13 +29169,13 @@
         </is>
       </c>
       <c r="P146" t="n">
-        <v>0</v>
+        <v>3.87</v>
       </c>
       <c r="Q146" t="n">
-        <v>0</v>
+        <v>3.87</v>
       </c>
       <c r="R146" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="S146" t="n">
         <v>0</v>
@@ -29318,7 +29318,7 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
@@ -29328,12 +29328,12 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Mebrat Hayl</t>
+          <t>Aresimi</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Fasil Ketema</t>
+          <t>FK Bashkimi Kumanovo</t>
         </is>
       </c>
       <c r="G147" t="n">
@@ -29515,7 +29515,7 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
@@ -29525,12 +29525,12 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Strømmen</t>
+          <t>Saburtalo</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Hødd</t>
+          <t>Torpedo Kutaisi</t>
         </is>
       </c>
       <c r="G148" t="n">
@@ -29563,13 +29563,13 @@
         </is>
       </c>
       <c r="P148" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Q148" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="R148" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="S148" t="n">
         <v>0</v>
@@ -29722,12 +29722,12 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Kecskeméti TE</t>
+          <t>Karcag SE</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Mezőkövesd-Zsóry</t>
+          <t>Tiszakécske</t>
         </is>
       </c>
       <c r="G149" t="n">
@@ -29909,7 +29909,7 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
@@ -29919,12 +29919,12 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Rapid Wien</t>
+          <t>Vardar</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Austria Wien</t>
+          <t>Sileks</t>
         </is>
       </c>
       <c r="G150" t="n">
@@ -29957,13 +29957,13 @@
         </is>
       </c>
       <c r="P150" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Q150" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="R150" t="n">
-        <v>2.96</v>
+        <v>0</v>
       </c>
       <c r="S150" t="n">
         <v>0</v>
@@ -30106,22 +30106,22 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>KFUM</t>
+          <t>Shkendija</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Viking</t>
+          <t>Struga</t>
         </is>
       </c>
       <c r="G151" t="n">
@@ -30154,13 +30154,13 @@
         </is>
       </c>
       <c r="P151" t="n">
-        <v>3.87</v>
+        <v>0</v>
       </c>
       <c r="Q151" t="n">
-        <v>3.87</v>
+        <v>0</v>
       </c>
       <c r="R151" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="S151" t="n">
         <v>0</v>
@@ -30303,22 +30303,22 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Pogoń Siedlce</t>
+          <t>Sandefjord</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Stal Rzeszów</t>
+          <t>Kristiansund</t>
         </is>
       </c>
       <c r="G152" t="n">
@@ -30351,13 +30351,13 @@
         </is>
       </c>
       <c r="P152" t="n">
-        <v>2.55</v>
+        <v>1.59</v>
       </c>
       <c r="Q152" t="n">
-        <v>3.6</v>
+        <v>4.44</v>
       </c>
       <c r="R152" t="n">
-        <v>2.43</v>
+        <v>5.16</v>
       </c>
       <c r="S152" t="n">
         <v>0</v>
@@ -30500,7 +30500,7 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
@@ -30510,12 +30510,12 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Budafoki MTE</t>
+          <t>Real Madrid W</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>BVSC</t>
+          <t>Atletico Madrid W</t>
         </is>
       </c>
       <c r="G153" t="n">
@@ -30697,22 +30697,22 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Karcag SE</t>
+          <t>Åsane</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Tiszakécske</t>
+          <t>Strømsgodset</t>
         </is>
       </c>
       <c r="G154" t="n">
@@ -30745,13 +30745,13 @@
         </is>
       </c>
       <c r="P154" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="Q154" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="R154" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="S154" t="n">
         <v>0</v>
@@ -30894,22 +30894,22 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Sandefjord</t>
+          <t>Makedonija GjP</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Kristiansund</t>
+          <t>Tikveš</t>
         </is>
       </c>
       <c r="G155" t="n">
@@ -30942,13 +30942,13 @@
         </is>
       </c>
       <c r="P155" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="Q155" t="n">
-        <v>4.44</v>
+        <v>0</v>
       </c>
       <c r="R155" t="n">
-        <v>5.16</v>
+        <v>0</v>
       </c>
       <c r="S155" t="n">
         <v>0</v>
@@ -31495,12 +31495,12 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Dibba Al Fujairah</t>
+          <t>Al Bataeh</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Ajman</t>
+          <t>Al Sharjah</t>
         </is>
       </c>
       <c r="G158" t="n">
@@ -31692,12 +31692,12 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Al Bataeh</t>
+          <t>Bani Yas</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Al Sharjah</t>
+          <t>Shabab Al Ahli Dubai</t>
         </is>
       </c>
       <c r="G159" t="n">
@@ -32086,12 +32086,12 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Bani Yas</t>
+          <t>Dibba Al Fujairah</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Shabab Al Ahli Dubai</t>
+          <t>Ajman</t>
         </is>
       </c>
       <c r="G161" t="n">
@@ -32273,7 +32273,7 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
@@ -32283,12 +32283,12 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>West Ham United</t>
+          <t>Köln</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Heidenheim</t>
         </is>
       </c>
       <c r="G162" t="n">
@@ -32321,13 +32321,13 @@
         </is>
       </c>
       <c r="P162" t="n">
-        <v>5.17</v>
+        <v>1.78</v>
       </c>
       <c r="Q162" t="n">
-        <v>4.37</v>
+        <v>4.32</v>
       </c>
       <c r="R162" t="n">
-        <v>1.69</v>
+        <v>4.52</v>
       </c>
       <c r="S162" t="n">
         <v>0</v>
@@ -32366,16 +32366,16 @@
         <v>0</v>
       </c>
       <c r="AE162" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AF162" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AG162" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AH162" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AI162" t="n">
         <v>0</v>
@@ -32864,7 +32864,7 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
@@ -32874,12 +32874,12 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>Nieciecza</t>
+          <t>West Ham United</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Legia Warszawa</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="G165" t="n">
@@ -32912,13 +32912,13 @@
         </is>
       </c>
       <c r="P165" t="n">
-        <v>4.09</v>
+        <v>5.17</v>
       </c>
       <c r="Q165" t="n">
-        <v>3.78</v>
+        <v>4.37</v>
       </c>
       <c r="R165" t="n">
-        <v>1.77</v>
+        <v>1.69</v>
       </c>
       <c r="S165" t="n">
         <v>0</v>
@@ -32957,10 +32957,10 @@
         <v>0</v>
       </c>
       <c r="AE165" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AF165" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AG165" t="n">
         <v>0</v>
@@ -33061,7 +33061,7 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
@@ -33071,12 +33071,12 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>Köln</t>
+          <t>Nieciecza</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Heidenheim</t>
+          <t>Legia Warszawa</t>
         </is>
       </c>
       <c r="G166" t="n">
@@ -33109,13 +33109,13 @@
         </is>
       </c>
       <c r="P166" t="n">
-        <v>1.78</v>
+        <v>4.09</v>
       </c>
       <c r="Q166" t="n">
-        <v>4.32</v>
+        <v>3.78</v>
       </c>
       <c r="R166" t="n">
-        <v>4.52</v>
+        <v>1.77</v>
       </c>
       <c r="S166" t="n">
         <v>0</v>
@@ -33160,10 +33160,10 @@
         <v>0</v>
       </c>
       <c r="AG166" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AH166" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AI166" t="n">
         <v>0</v>
@@ -33258,7 +33258,7 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
@@ -33268,12 +33268,12 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>Mladost DG</t>
+          <t>Dinamo Bucureşti</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Petrovac</t>
+          <t>Argeș</t>
         </is>
       </c>
       <c r="G167" t="n">
@@ -33306,13 +33306,13 @@
         </is>
       </c>
       <c r="P167" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="Q167" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R167" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="S167" t="n">
         <v>0</v>
@@ -33652,7 +33652,7 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
@@ -33662,12 +33662,12 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>Mornar</t>
+          <t>Vysočina Jihlava</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Bokelj</t>
+          <t>Hanácká</t>
         </is>
       </c>
       <c r="G169" t="n">
@@ -33849,7 +33849,7 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
@@ -33859,12 +33859,12 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>Parma</t>
+          <t>Dečić</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Roma</t>
+          <t>FK Jezero Plav</t>
         </is>
       </c>
       <c r="G170" t="n">
@@ -33897,13 +33897,13 @@
         </is>
       </c>
       <c r="P170" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="Q170" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="R170" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="S170" t="n">
         <v>0</v>
@@ -34046,7 +34046,7 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
@@ -34056,12 +34056,12 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>Vysočina Jihlava</t>
+          <t>Parma</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Hanácká</t>
+          <t>Roma</t>
         </is>
       </c>
       <c r="G171" t="n">
@@ -34094,13 +34094,13 @@
         </is>
       </c>
       <c r="P171" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="Q171" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R171" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="S171" t="n">
         <v>0</v>
@@ -34243,7 +34243,7 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
@@ -34253,12 +34253,12 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>Ittihad Tanger</t>
+          <t>Mornar</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Difaâ El Jadida</t>
+          <t>Bokelj</t>
         </is>
       </c>
       <c r="G172" t="n">
@@ -34440,7 +34440,7 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
@@ -34450,12 +34450,12 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>Arsenal Tivat</t>
+          <t>Ittihad Tanger</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Sutjeska</t>
+          <t>Difaâ El Jadida</t>
         </is>
       </c>
       <c r="G173" t="n">
@@ -34637,7 +34637,7 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
@@ -34647,12 +34647,12 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>Dinamo Bucureşti</t>
+          <t>Brøndby</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Argeș</t>
+          <t>AGF</t>
         </is>
       </c>
       <c r="G174" t="n">
@@ -34685,13 +34685,13 @@
         </is>
       </c>
       <c r="P174" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="Q174" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="R174" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="S174" t="n">
         <v>0</v>
@@ -34834,7 +34834,7 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
@@ -34844,12 +34844,12 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>Brøndby</t>
+          <t>Arsenal Tivat</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>AGF</t>
+          <t>Sutjeska</t>
         </is>
       </c>
       <c r="G175" t="n">
@@ -35041,12 +35041,12 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>Dečić</t>
+          <t>Mladost DG</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>FK Jezero Plav</t>
+          <t>Petrovac</t>
         </is>
       </c>
       <c r="G176" t="n">
@@ -35819,22 +35819,22 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>Slaven Koprivnica</t>
+          <t>Skála</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Gorica</t>
+          <t>AB</t>
         </is>
       </c>
       <c r="G180" t="n">
@@ -36213,22 +36213,22 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>Skála</t>
+          <t>Slaven Koprivnica</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>AB</t>
+          <t>Gorica</t>
         </is>
       </c>
       <c r="G182" t="n">
@@ -36410,22 +36410,22 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>IMT Novi Beograd</t>
+          <t>Kansas City</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>Chicago Red Stars</t>
         </is>
       </c>
       <c r="G183" t="n">
@@ -36458,13 +36458,13 @@
         </is>
       </c>
       <c r="P183" t="n">
-